--- a/11_プロジェクト計画書.xlsx
+++ b/11_プロジェクト計画書.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24334"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\azrfilsrv01\部門\情報ITクリエイター事業部\10_情報処理教育\50_卒業制作\00_科目指導資料\10_企画書・プロジェクト計画書\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\k_tanoue\Documents\GitHub\tanouesoftware\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AB2CD162-391E-466D-8F2F-49817A775B74}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{38BB8CC4-7E2B-4C96-810A-9F58E918F916}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="プロジェクト計画" sheetId="1" r:id="rId1"/>
@@ -37,15 +37,12 @@
         <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
-    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
-      <xlwcv:version setVersion="1"/>
-    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="193" uniqueCount="105">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="194" uniqueCount="106">
   <si>
     <t>プロジェクト計画書</t>
     <rPh sb="6" eb="9">
@@ -1010,6 +1007,24 @@
   </si>
   <si>
     <t>　サーバ(サービス)</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>①：なぜ
+地震災害後、建物の被害状況や修理の必要性が分からず、必要な手続きや対応に困る被災者が多い。そこで、被災直後の情報収集や初期対応を支援することを目的とする。
+②：ソリューション
+建物内部の写真と簡単な質問を入力すると、AIが被害状況の目安を分析し、修理費用や罹災証明書の手続き、修理業者など、状況に応じた情報を提示する。
+③：期待する効果
+被災者が被害状況を把握しやすくなり、「何をすればよいか分からない」という不安を減らす。また、復旧に必要な情報を一つのシステムで確認できることで、被災後の初期対応や復旧作業の効率化が期待できる。</t>
+    <rPh sb="5" eb="7">
+      <t>ジシン</t>
+    </rPh>
+    <rPh sb="167" eb="169">
+      <t>キタイ</t>
+    </rPh>
+    <rPh sb="171" eb="173">
+      <t>コウカ</t>
+    </rPh>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -2051,512 +2066,512 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="66" xfId="1" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="2" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="2" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="2" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="51" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="50" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="51" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="50" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="51" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="21" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="21" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="176" fontId="7" fillId="0" borderId="48" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1">
+    <xf numFmtId="176" fontId="7" fillId="0" borderId="49" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="33" xfId="1" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="7" fillId="0" borderId="48" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="7" fillId="0" borderId="49" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="21" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="34" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="35" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="25" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="16" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="46" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="7" fillId="0" borderId="52" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="7" fillId="0" borderId="53" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="7" fillId="0" borderId="54" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="7" fillId="0" borderId="55" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="7" fillId="0" borderId="58" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="7" fillId="0" borderId="59" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="32" xfId="1" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="40" xfId="1" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="22" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="7" fillId="0" borderId="48" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="7" fillId="0" borderId="49" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="23" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="24" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="41" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="42" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="43" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="7" fillId="0" borderId="62" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="7" fillId="0" borderId="63" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="60" xfId="1" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="57" xfId="1" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="23" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="61" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="25" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="16" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="46" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="7" fillId="0" borderId="62" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="7" fillId="0" borderId="63" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="7" fillId="0" borderId="52" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="7" fillId="0" borderId="53" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="23" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="61" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="41" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="42" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="56" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="7" fillId="0" borderId="52" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="7" fillId="0" borderId="53" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="34" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="35" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="7" fillId="0" borderId="54" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="7" fillId="0" borderId="55" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="36" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="26" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="7" fillId="0" borderId="58" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="7" fillId="0" borderId="59" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="7" fillId="0" borderId="54" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="7" fillId="0" borderId="55" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="7" fillId="0" borderId="58" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="7" fillId="0" borderId="59" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="34" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="35" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="25" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="16" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="46" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="7" fillId="0" borderId="62" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="7" fillId="0" borderId="63" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="61" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="56" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="37" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="38" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="21" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="22" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="44" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="45" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="25" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="46" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="47" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="16" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="31" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="33" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="50" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="51" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="50" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="51" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="32" xfId="1" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="40" xfId="1" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="34" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="35" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="25" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="16" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="46" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="34" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="35" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="25" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="16" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="46" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="34" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="35" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="25" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="16" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="46" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="7" fillId="0" borderId="54" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="7" fillId="0" borderId="55" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="7" fillId="0" borderId="54" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="7" fillId="0" borderId="55" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="7" fillId="0" borderId="54" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="7" fillId="0" borderId="55" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="36" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="26" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="7" fillId="0" borderId="58" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="7" fillId="0" borderId="59" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="7" fillId="0" borderId="58" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="7" fillId="0" borderId="59" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="7" fillId="0" borderId="58" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="7" fillId="0" borderId="59" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="37" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="38" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="21" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="22" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="7" fillId="0" borderId="48" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="7" fillId="0" borderId="49" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="21" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="44" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="45" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="25" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="46" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="47" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="16" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="31" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="33" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="21" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="22" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="7" fillId="0" borderId="49" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="7" fillId="0" borderId="48" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="7" fillId="0" borderId="49" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="7" fillId="0" borderId="48" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="7" fillId="0" borderId="62" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="7" fillId="0" borderId="63" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="23" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="61" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="41" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="42" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="56" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="33" xfId="1" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="7" fillId="0" borderId="52" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="7" fillId="0" borderId="53" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="24" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="43" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="7" fillId="0" borderId="62" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="7" fillId="0" borderId="63" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="60" xfId="1" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="57" xfId="1" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="23" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="61" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="9" fontId="7" fillId="0" borderId="62" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="7" fillId="0" borderId="63" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="7" fillId="0" borderId="52" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="7" fillId="0" borderId="53" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="23" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="61" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="41" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="42" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="56" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="7" fillId="0" borderId="52" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="7" fillId="0" borderId="53" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="51" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="21" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -3081,9 +3096,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office テーマ">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -3121,9 +3136,9 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
-        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -3156,26 +3171,9 @@
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -3208,26 +3206,9 @@
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -3401,7 +3382,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:J122"/>
+  <dimension ref="A1:J125"/>
   <sheetFormatPr defaultColWidth="10" defaultRowHeight="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="5" style="3" customWidth="1"/>
@@ -3410,1108 +3391,1108 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" s="2" customFormat="1" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="52" t="s">
+      <c r="A1" s="27" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="52"/>
-      <c r="C1" s="52"/>
-      <c r="D1" s="52"/>
-      <c r="E1" s="52"/>
-      <c r="F1" s="52"/>
-      <c r="G1" s="52"/>
-      <c r="H1" s="52"/>
-      <c r="I1" s="52"/>
-      <c r="J1" s="52"/>
+      <c r="B1" s="27"/>
+      <c r="C1" s="27"/>
+      <c r="D1" s="27"/>
+      <c r="E1" s="27"/>
+      <c r="F1" s="27"/>
+      <c r="G1" s="27"/>
+      <c r="H1" s="27"/>
+      <c r="I1" s="27"/>
+      <c r="J1" s="27"/>
     </row>
     <row r="2" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="27">
+      <c r="A2" s="28">
         <v>1</v>
       </c>
-      <c r="B2" s="34" t="s">
+      <c r="B2" s="32" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="34"/>
-      <c r="D2" s="34"/>
-      <c r="E2" s="172"/>
-      <c r="F2" s="172"/>
-      <c r="G2" s="172"/>
-      <c r="H2" s="172"/>
-      <c r="I2" s="172"/>
-      <c r="J2" s="173"/>
+      <c r="C2" s="32"/>
+      <c r="D2" s="32"/>
+      <c r="E2" s="78"/>
+      <c r="F2" s="78"/>
+      <c r="G2" s="78"/>
+      <c r="H2" s="78"/>
+      <c r="I2" s="78"/>
+      <c r="J2" s="79"/>
     </row>
     <row r="3" spans="1:10" ht="13.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="31"/>
-      <c r="B3" s="35"/>
-      <c r="C3" s="35"/>
-      <c r="D3" s="35"/>
-      <c r="E3" s="174"/>
-      <c r="F3" s="174"/>
-      <c r="G3" s="174"/>
-      <c r="H3" s="174"/>
-      <c r="I3" s="174"/>
-      <c r="J3" s="175"/>
+      <c r="A3" s="29"/>
+      <c r="B3" s="77"/>
+      <c r="C3" s="77"/>
+      <c r="D3" s="77"/>
+      <c r="E3" s="80"/>
+      <c r="F3" s="80"/>
+      <c r="G3" s="80"/>
+      <c r="H3" s="80"/>
+      <c r="I3" s="80"/>
+      <c r="J3" s="81"/>
     </row>
     <row r="4" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="27">
+      <c r="A4" s="28">
         <v>2</v>
       </c>
-      <c r="B4" s="32" t="s">
+      <c r="B4" s="42" t="s">
         <v>2</v>
       </c>
-      <c r="C4" s="32"/>
-      <c r="D4" s="32"/>
-      <c r="E4" s="32"/>
-      <c r="F4" s="32"/>
-      <c r="G4" s="32"/>
-      <c r="H4" s="32"/>
-      <c r="I4" s="32"/>
-      <c r="J4" s="33"/>
+      <c r="C4" s="42"/>
+      <c r="D4" s="42"/>
+      <c r="E4" s="42"/>
+      <c r="F4" s="42"/>
+      <c r="G4" s="42"/>
+      <c r="H4" s="42"/>
+      <c r="I4" s="42"/>
+      <c r="J4" s="43"/>
     </row>
     <row r="5" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="28"/>
-      <c r="B5" s="40" t="s">
+      <c r="A5" s="30"/>
+      <c r="B5" s="45" t="s">
         <v>3</v>
       </c>
-      <c r="C5" s="40"/>
-      <c r="D5" s="40"/>
-      <c r="E5" s="40"/>
-      <c r="F5" s="40"/>
-      <c r="G5" s="40"/>
-      <c r="H5" s="40"/>
-      <c r="I5" s="40"/>
-      <c r="J5" s="41"/>
+      <c r="C5" s="45"/>
+      <c r="D5" s="45"/>
+      <c r="E5" s="45"/>
+      <c r="F5" s="45"/>
+      <c r="G5" s="45"/>
+      <c r="H5" s="45"/>
+      <c r="I5" s="45"/>
+      <c r="J5" s="46"/>
     </row>
     <row r="6" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="28"/>
-      <c r="B6" s="40"/>
-      <c r="C6" s="40"/>
-      <c r="D6" s="40"/>
-      <c r="E6" s="40"/>
-      <c r="F6" s="40"/>
-      <c r="G6" s="40"/>
-      <c r="H6" s="40"/>
-      <c r="I6" s="40"/>
-      <c r="J6" s="41"/>
+      <c r="A6" s="30"/>
+      <c r="B6" s="45"/>
+      <c r="C6" s="45"/>
+      <c r="D6" s="45"/>
+      <c r="E6" s="45"/>
+      <c r="F6" s="45"/>
+      <c r="G6" s="45"/>
+      <c r="H6" s="45"/>
+      <c r="I6" s="45"/>
+      <c r="J6" s="46"/>
     </row>
     <row r="7" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="28"/>
-      <c r="B7" s="42"/>
-      <c r="C7" s="42"/>
-      <c r="D7" s="42"/>
-      <c r="E7" s="42"/>
-      <c r="F7" s="42"/>
-      <c r="G7" s="42"/>
-      <c r="H7" s="42"/>
-      <c r="I7" s="42"/>
-      <c r="J7" s="43"/>
+      <c r="A7" s="30"/>
+      <c r="B7" s="47"/>
+      <c r="C7" s="47"/>
+      <c r="D7" s="47"/>
+      <c r="E7" s="47"/>
+      <c r="F7" s="47"/>
+      <c r="G7" s="47"/>
+      <c r="H7" s="47"/>
+      <c r="I7" s="47"/>
+      <c r="J7" s="48"/>
     </row>
     <row r="8" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="28"/>
-      <c r="B8" s="179"/>
-      <c r="C8" s="180"/>
-      <c r="D8" s="180"/>
-      <c r="E8" s="180"/>
-      <c r="F8" s="180"/>
-      <c r="G8" s="180"/>
-      <c r="H8" s="180"/>
-      <c r="I8" s="180"/>
-      <c r="J8" s="181"/>
+      <c r="A8" s="30"/>
+      <c r="B8" s="76" t="s">
+        <v>105</v>
+      </c>
+      <c r="C8" s="52"/>
+      <c r="D8" s="52"/>
+      <c r="E8" s="52"/>
+      <c r="F8" s="52"/>
+      <c r="G8" s="52"/>
+      <c r="H8" s="52"/>
+      <c r="I8" s="52"/>
+      <c r="J8" s="53"/>
     </row>
     <row r="9" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="28"/>
-      <c r="B9" s="182"/>
-      <c r="C9" s="183"/>
-      <c r="D9" s="183"/>
-      <c r="E9" s="183"/>
-      <c r="F9" s="183"/>
-      <c r="G9" s="183"/>
-      <c r="H9" s="183"/>
-      <c r="I9" s="183"/>
-      <c r="J9" s="184"/>
+      <c r="A9" s="30"/>
+      <c r="B9" s="54"/>
+      <c r="C9" s="55"/>
+      <c r="D9" s="55"/>
+      <c r="E9" s="55"/>
+      <c r="F9" s="55"/>
+      <c r="G9" s="55"/>
+      <c r="H9" s="55"/>
+      <c r="I9" s="55"/>
+      <c r="J9" s="56"/>
     </row>
     <row r="10" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="28"/>
-      <c r="B10" s="182"/>
-      <c r="C10" s="183"/>
-      <c r="D10" s="183"/>
-      <c r="E10" s="183"/>
-      <c r="F10" s="183"/>
-      <c r="G10" s="183"/>
-      <c r="H10" s="183"/>
-      <c r="I10" s="183"/>
-      <c r="J10" s="184"/>
+      <c r="A10" s="30"/>
+      <c r="B10" s="54"/>
+      <c r="C10" s="55"/>
+      <c r="D10" s="55"/>
+      <c r="E10" s="55"/>
+      <c r="F10" s="55"/>
+      <c r="G10" s="55"/>
+      <c r="H10" s="55"/>
+      <c r="I10" s="55"/>
+      <c r="J10" s="56"/>
     </row>
     <row r="11" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="28"/>
-      <c r="B11" s="182"/>
-      <c r="C11" s="183"/>
-      <c r="D11" s="183"/>
-      <c r="E11" s="183"/>
-      <c r="F11" s="183"/>
-      <c r="G11" s="183"/>
-      <c r="H11" s="183"/>
-      <c r="I11" s="183"/>
-      <c r="J11" s="184"/>
+      <c r="A11" s="30"/>
+      <c r="B11" s="54"/>
+      <c r="C11" s="55"/>
+      <c r="D11" s="55"/>
+      <c r="E11" s="55"/>
+      <c r="F11" s="55"/>
+      <c r="G11" s="55"/>
+      <c r="H11" s="55"/>
+      <c r="I11" s="55"/>
+      <c r="J11" s="56"/>
     </row>
     <row r="12" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="28"/>
-      <c r="B12" s="182"/>
-      <c r="C12" s="183"/>
-      <c r="D12" s="183"/>
-      <c r="E12" s="183"/>
-      <c r="F12" s="183"/>
-      <c r="G12" s="183"/>
-      <c r="H12" s="183"/>
-      <c r="I12" s="183"/>
-      <c r="J12" s="184"/>
+      <c r="A12" s="30"/>
+      <c r="B12" s="54"/>
+      <c r="C12" s="55"/>
+      <c r="D12" s="55"/>
+      <c r="E12" s="55"/>
+      <c r="F12" s="55"/>
+      <c r="G12" s="55"/>
+      <c r="H12" s="55"/>
+      <c r="I12" s="55"/>
+      <c r="J12" s="56"/>
     </row>
     <row r="13" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="28"/>
-      <c r="B13" s="182"/>
-      <c r="C13" s="183"/>
-      <c r="D13" s="183"/>
-      <c r="E13" s="183"/>
-      <c r="F13" s="183"/>
-      <c r="G13" s="183"/>
-      <c r="H13" s="183"/>
-      <c r="I13" s="183"/>
-      <c r="J13" s="184"/>
+      <c r="A13" s="30"/>
+      <c r="B13" s="54"/>
+      <c r="C13" s="55"/>
+      <c r="D13" s="55"/>
+      <c r="E13" s="55"/>
+      <c r="F13" s="55"/>
+      <c r="G13" s="55"/>
+      <c r="H13" s="55"/>
+      <c r="I13" s="55"/>
+      <c r="J13" s="56"/>
     </row>
     <row r="14" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A14" s="28"/>
-      <c r="B14" s="182"/>
-      <c r="C14" s="183"/>
-      <c r="D14" s="183"/>
-      <c r="E14" s="183"/>
-      <c r="F14" s="183"/>
-      <c r="G14" s="183"/>
-      <c r="H14" s="183"/>
-      <c r="I14" s="183"/>
-      <c r="J14" s="184"/>
+      <c r="A14" s="30"/>
+      <c r="B14" s="54"/>
+      <c r="C14" s="55"/>
+      <c r="D14" s="55"/>
+      <c r="E14" s="55"/>
+      <c r="F14" s="55"/>
+      <c r="G14" s="55"/>
+      <c r="H14" s="55"/>
+      <c r="I14" s="55"/>
+      <c r="J14" s="56"/>
     </row>
     <row r="15" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A15" s="28"/>
-      <c r="B15" s="182"/>
-      <c r="C15" s="183"/>
-      <c r="D15" s="183"/>
-      <c r="E15" s="183"/>
-      <c r="F15" s="183"/>
-      <c r="G15" s="183"/>
-      <c r="H15" s="183"/>
-      <c r="I15" s="183"/>
-      <c r="J15" s="184"/>
+      <c r="A15" s="30"/>
+      <c r="B15" s="54"/>
+      <c r="C15" s="55"/>
+      <c r="D15" s="55"/>
+      <c r="E15" s="55"/>
+      <c r="F15" s="55"/>
+      <c r="G15" s="55"/>
+      <c r="H15" s="55"/>
+      <c r="I15" s="55"/>
+      <c r="J15" s="56"/>
     </row>
     <row r="16" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A16" s="28"/>
-      <c r="B16" s="182"/>
-      <c r="C16" s="183"/>
-      <c r="D16" s="183"/>
-      <c r="E16" s="183"/>
-      <c r="F16" s="183"/>
-      <c r="G16" s="183"/>
-      <c r="H16" s="183"/>
-      <c r="I16" s="183"/>
-      <c r="J16" s="184"/>
-    </row>
-    <row r="17" spans="1:10" ht="13.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="31"/>
-      <c r="B17" s="182"/>
-      <c r="C17" s="183"/>
-      <c r="D17" s="183"/>
-      <c r="E17" s="183"/>
-      <c r="F17" s="183"/>
-      <c r="G17" s="183"/>
-      <c r="H17" s="183"/>
-      <c r="I17" s="183"/>
-      <c r="J17" s="184"/>
+      <c r="A16" s="30"/>
+      <c r="B16" s="54"/>
+      <c r="C16" s="55"/>
+      <c r="D16" s="55"/>
+      <c r="E16" s="55"/>
+      <c r="F16" s="55"/>
+      <c r="G16" s="55"/>
+      <c r="H16" s="55"/>
+      <c r="I16" s="55"/>
+      <c r="J16" s="56"/>
+    </row>
+    <row r="17" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A17" s="29"/>
+      <c r="B17" s="54"/>
+      <c r="C17" s="55"/>
+      <c r="D17" s="55"/>
+      <c r="E17" s="55"/>
+      <c r="F17" s="55"/>
+      <c r="G17" s="55"/>
+      <c r="H17" s="55"/>
+      <c r="I17" s="55"/>
+      <c r="J17" s="56"/>
     </row>
     <row r="18" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A18" s="27">
+      <c r="A18" s="29"/>
+      <c r="B18" s="54"/>
+      <c r="C18" s="55"/>
+      <c r="D18" s="55"/>
+      <c r="E18" s="55"/>
+      <c r="F18" s="55"/>
+      <c r="G18" s="55"/>
+      <c r="H18" s="55"/>
+      <c r="I18" s="55"/>
+      <c r="J18" s="56"/>
+    </row>
+    <row r="19" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A19" s="29"/>
+      <c r="B19" s="54"/>
+      <c r="C19" s="55"/>
+      <c r="D19" s="55"/>
+      <c r="E19" s="55"/>
+      <c r="F19" s="55"/>
+      <c r="G19" s="55"/>
+      <c r="H19" s="55"/>
+      <c r="I19" s="55"/>
+      <c r="J19" s="56"/>
+    </row>
+    <row r="20" spans="1:10" ht="13.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="29"/>
+      <c r="B20" s="54"/>
+      <c r="C20" s="55"/>
+      <c r="D20" s="55"/>
+      <c r="E20" s="55"/>
+      <c r="F20" s="55"/>
+      <c r="G20" s="55"/>
+      <c r="H20" s="55"/>
+      <c r="I20" s="55"/>
+      <c r="J20" s="56"/>
+    </row>
+    <row r="21" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A21" s="28">
         <v>3</v>
       </c>
-      <c r="B18" s="32" t="s">
+      <c r="B21" s="42" t="s">
         <v>4</v>
       </c>
-      <c r="C18" s="32"/>
-      <c r="D18" s="32"/>
-      <c r="E18" s="32"/>
-      <c r="F18" s="32"/>
-      <c r="G18" s="32"/>
-      <c r="H18" s="32"/>
-      <c r="I18" s="32"/>
-      <c r="J18" s="33"/>
-    </row>
-    <row r="19" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A19" s="28"/>
-      <c r="B19" s="44" t="s">
+      <c r="C21" s="42"/>
+      <c r="D21" s="42"/>
+      <c r="E21" s="42"/>
+      <c r="F21" s="42"/>
+      <c r="G21" s="42"/>
+      <c r="H21" s="42"/>
+      <c r="I21" s="42"/>
+      <c r="J21" s="43"/>
+    </row>
+    <row r="22" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A22" s="30"/>
+      <c r="B22" s="64" t="s">
         <v>5</v>
       </c>
-      <c r="C19" s="45"/>
-      <c r="D19" s="45"/>
-      <c r="E19" s="45"/>
-      <c r="F19" s="45"/>
-      <c r="G19" s="45"/>
-      <c r="H19" s="45"/>
-      <c r="I19" s="45"/>
-      <c r="J19" s="46"/>
-    </row>
-    <row r="20" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A20" s="28"/>
-      <c r="B20" s="44"/>
-      <c r="C20" s="45"/>
-      <c r="D20" s="45"/>
-      <c r="E20" s="45"/>
-      <c r="F20" s="45"/>
-      <c r="G20" s="45"/>
-      <c r="H20" s="45"/>
-      <c r="I20" s="45"/>
-      <c r="J20" s="46"/>
-    </row>
-    <row r="21" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A21" s="28"/>
-      <c r="B21" s="44"/>
-      <c r="C21" s="45"/>
-      <c r="D21" s="45"/>
-      <c r="E21" s="45"/>
-      <c r="F21" s="45"/>
-      <c r="G21" s="45"/>
-      <c r="H21" s="45"/>
-      <c r="I21" s="45"/>
-      <c r="J21" s="46"/>
-    </row>
-    <row r="22" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A22" s="28"/>
-      <c r="B22" s="47"/>
-      <c r="C22" s="48"/>
-      <c r="D22" s="48"/>
-      <c r="E22" s="48"/>
-      <c r="F22" s="48"/>
-      <c r="G22" s="48"/>
-      <c r="H22" s="48"/>
-      <c r="I22" s="48"/>
-      <c r="J22" s="49"/>
+      <c r="C22" s="65"/>
+      <c r="D22" s="65"/>
+      <c r="E22" s="65"/>
+      <c r="F22" s="65"/>
+      <c r="G22" s="65"/>
+      <c r="H22" s="65"/>
+      <c r="I22" s="65"/>
+      <c r="J22" s="66"/>
     </row>
     <row r="23" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A23" s="28"/>
-      <c r="B23" s="185"/>
-      <c r="C23" s="185"/>
-      <c r="D23" s="185"/>
-      <c r="E23" s="185"/>
-      <c r="F23" s="185"/>
-      <c r="G23" s="185"/>
-      <c r="H23" s="185"/>
-      <c r="I23" s="185"/>
-      <c r="J23" s="186"/>
+      <c r="A23" s="30"/>
+      <c r="B23" s="64"/>
+      <c r="C23" s="65"/>
+      <c r="D23" s="65"/>
+      <c r="E23" s="65"/>
+      <c r="F23" s="65"/>
+      <c r="G23" s="65"/>
+      <c r="H23" s="65"/>
+      <c r="I23" s="65"/>
+      <c r="J23" s="66"/>
     </row>
     <row r="24" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A24" s="28"/>
-      <c r="B24" s="185"/>
-      <c r="C24" s="185"/>
-      <c r="D24" s="185"/>
-      <c r="E24" s="185"/>
-      <c r="F24" s="185"/>
-      <c r="G24" s="185"/>
-      <c r="H24" s="185"/>
-      <c r="I24" s="185"/>
-      <c r="J24" s="186"/>
+      <c r="A24" s="30"/>
+      <c r="B24" s="64"/>
+      <c r="C24" s="65"/>
+      <c r="D24" s="65"/>
+      <c r="E24" s="65"/>
+      <c r="F24" s="65"/>
+      <c r="G24" s="65"/>
+      <c r="H24" s="65"/>
+      <c r="I24" s="65"/>
+      <c r="J24" s="66"/>
     </row>
     <row r="25" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A25" s="28"/>
-      <c r="B25" s="185"/>
-      <c r="C25" s="185"/>
-      <c r="D25" s="185"/>
-      <c r="E25" s="185"/>
-      <c r="F25" s="185"/>
-      <c r="G25" s="185"/>
-      <c r="H25" s="185"/>
-      <c r="I25" s="185"/>
-      <c r="J25" s="186"/>
+      <c r="A25" s="30"/>
+      <c r="B25" s="67"/>
+      <c r="C25" s="68"/>
+      <c r="D25" s="68"/>
+      <c r="E25" s="68"/>
+      <c r="F25" s="68"/>
+      <c r="G25" s="68"/>
+      <c r="H25" s="68"/>
+      <c r="I25" s="68"/>
+      <c r="J25" s="69"/>
     </row>
     <row r="26" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A26" s="28"/>
-      <c r="B26" s="185"/>
-      <c r="C26" s="185"/>
-      <c r="D26" s="185"/>
-      <c r="E26" s="185"/>
-      <c r="F26" s="185"/>
-      <c r="G26" s="185"/>
-      <c r="H26" s="185"/>
-      <c r="I26" s="185"/>
-      <c r="J26" s="186"/>
+      <c r="A26" s="30"/>
+      <c r="B26" s="70"/>
+      <c r="C26" s="70"/>
+      <c r="D26" s="70"/>
+      <c r="E26" s="70"/>
+      <c r="F26" s="70"/>
+      <c r="G26" s="70"/>
+      <c r="H26" s="70"/>
+      <c r="I26" s="70"/>
+      <c r="J26" s="71"/>
     </row>
     <row r="27" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A27" s="28"/>
-      <c r="B27" s="185"/>
-      <c r="C27" s="185"/>
-      <c r="D27" s="185"/>
-      <c r="E27" s="185"/>
-      <c r="F27" s="185"/>
-      <c r="G27" s="185"/>
-      <c r="H27" s="185"/>
-      <c r="I27" s="185"/>
-      <c r="J27" s="186"/>
+      <c r="A27" s="30"/>
+      <c r="B27" s="70"/>
+      <c r="C27" s="70"/>
+      <c r="D27" s="70"/>
+      <c r="E27" s="70"/>
+      <c r="F27" s="70"/>
+      <c r="G27" s="70"/>
+      <c r="H27" s="70"/>
+      <c r="I27" s="70"/>
+      <c r="J27" s="71"/>
     </row>
     <row r="28" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A28" s="28"/>
-      <c r="B28" s="185"/>
-      <c r="C28" s="185"/>
-      <c r="D28" s="185"/>
-      <c r="E28" s="185"/>
-      <c r="F28" s="185"/>
-      <c r="G28" s="185"/>
-      <c r="H28" s="185"/>
-      <c r="I28" s="185"/>
-      <c r="J28" s="186"/>
+      <c r="A28" s="30"/>
+      <c r="B28" s="70"/>
+      <c r="C28" s="70"/>
+      <c r="D28" s="70"/>
+      <c r="E28" s="70"/>
+      <c r="F28" s="70"/>
+      <c r="G28" s="70"/>
+      <c r="H28" s="70"/>
+      <c r="I28" s="70"/>
+      <c r="J28" s="71"/>
     </row>
     <row r="29" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A29" s="28"/>
-      <c r="B29" s="185"/>
-      <c r="C29" s="185"/>
-      <c r="D29" s="185"/>
-      <c r="E29" s="185"/>
-      <c r="F29" s="185"/>
-      <c r="G29" s="185"/>
-      <c r="H29" s="185"/>
-      <c r="I29" s="185"/>
-      <c r="J29" s="186"/>
+      <c r="A29" s="30"/>
+      <c r="B29" s="70"/>
+      <c r="C29" s="70"/>
+      <c r="D29" s="70"/>
+      <c r="E29" s="70"/>
+      <c r="F29" s="70"/>
+      <c r="G29" s="70"/>
+      <c r="H29" s="70"/>
+      <c r="I29" s="70"/>
+      <c r="J29" s="71"/>
     </row>
     <row r="30" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A30" s="28"/>
-      <c r="B30" s="185"/>
-      <c r="C30" s="185"/>
-      <c r="D30" s="185"/>
-      <c r="E30" s="185"/>
-      <c r="F30" s="185"/>
-      <c r="G30" s="185"/>
-      <c r="H30" s="185"/>
-      <c r="I30" s="185"/>
-      <c r="J30" s="186"/>
+      <c r="A30" s="30"/>
+      <c r="B30" s="70"/>
+      <c r="C30" s="70"/>
+      <c r="D30" s="70"/>
+      <c r="E30" s="70"/>
+      <c r="F30" s="70"/>
+      <c r="G30" s="70"/>
+      <c r="H30" s="70"/>
+      <c r="I30" s="70"/>
+      <c r="J30" s="71"/>
     </row>
     <row r="31" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A31" s="28"/>
-      <c r="B31" s="185"/>
-      <c r="C31" s="185"/>
-      <c r="D31" s="185"/>
-      <c r="E31" s="185"/>
-      <c r="F31" s="185"/>
-      <c r="G31" s="185"/>
-      <c r="H31" s="185"/>
-      <c r="I31" s="185"/>
-      <c r="J31" s="186"/>
+      <c r="A31" s="30"/>
+      <c r="B31" s="70"/>
+      <c r="C31" s="70"/>
+      <c r="D31" s="70"/>
+      <c r="E31" s="70"/>
+      <c r="F31" s="70"/>
+      <c r="G31" s="70"/>
+      <c r="H31" s="70"/>
+      <c r="I31" s="70"/>
+      <c r="J31" s="71"/>
     </row>
     <row r="32" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A32" s="28"/>
-      <c r="B32" s="185"/>
-      <c r="C32" s="185"/>
-      <c r="D32" s="185"/>
-      <c r="E32" s="185"/>
-      <c r="F32" s="185"/>
-      <c r="G32" s="185"/>
-      <c r="H32" s="185"/>
-      <c r="I32" s="185"/>
-      <c r="J32" s="186"/>
+      <c r="A32" s="30"/>
+      <c r="B32" s="70"/>
+      <c r="C32" s="70"/>
+      <c r="D32" s="70"/>
+      <c r="E32" s="70"/>
+      <c r="F32" s="70"/>
+      <c r="G32" s="70"/>
+      <c r="H32" s="70"/>
+      <c r="I32" s="70"/>
+      <c r="J32" s="71"/>
     </row>
     <row r="33" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A33" s="28"/>
-      <c r="B33" s="185"/>
-      <c r="C33" s="185"/>
-      <c r="D33" s="185"/>
-      <c r="E33" s="185"/>
-      <c r="F33" s="185"/>
-      <c r="G33" s="185"/>
-      <c r="H33" s="185"/>
-      <c r="I33" s="185"/>
-      <c r="J33" s="186"/>
+      <c r="A33" s="30"/>
+      <c r="B33" s="70"/>
+      <c r="C33" s="70"/>
+      <c r="D33" s="70"/>
+      <c r="E33" s="70"/>
+      <c r="F33" s="70"/>
+      <c r="G33" s="70"/>
+      <c r="H33" s="70"/>
+      <c r="I33" s="70"/>
+      <c r="J33" s="71"/>
     </row>
     <row r="34" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A34" s="28"/>
-      <c r="B34" s="185"/>
-      <c r="C34" s="185"/>
-      <c r="D34" s="185"/>
-      <c r="E34" s="185"/>
-      <c r="F34" s="185"/>
-      <c r="G34" s="185"/>
-      <c r="H34" s="185"/>
-      <c r="I34" s="185"/>
-      <c r="J34" s="186"/>
+      <c r="A34" s="30"/>
+      <c r="B34" s="70"/>
+      <c r="C34" s="70"/>
+      <c r="D34" s="70"/>
+      <c r="E34" s="70"/>
+      <c r="F34" s="70"/>
+      <c r="G34" s="70"/>
+      <c r="H34" s="70"/>
+      <c r="I34" s="70"/>
+      <c r="J34" s="71"/>
     </row>
     <row r="35" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A35" s="28"/>
-      <c r="B35" s="185"/>
-      <c r="C35" s="185"/>
-      <c r="D35" s="185"/>
-      <c r="E35" s="185"/>
-      <c r="F35" s="185"/>
-      <c r="G35" s="185"/>
-      <c r="H35" s="185"/>
-      <c r="I35" s="185"/>
-      <c r="J35" s="186"/>
+      <c r="A35" s="30"/>
+      <c r="B35" s="70"/>
+      <c r="C35" s="70"/>
+      <c r="D35" s="70"/>
+      <c r="E35" s="70"/>
+      <c r="F35" s="70"/>
+      <c r="G35" s="70"/>
+      <c r="H35" s="70"/>
+      <c r="I35" s="70"/>
+      <c r="J35" s="71"/>
     </row>
     <row r="36" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A36" s="28"/>
-      <c r="B36" s="185"/>
-      <c r="C36" s="185"/>
-      <c r="D36" s="185"/>
-      <c r="E36" s="185"/>
-      <c r="F36" s="185"/>
-      <c r="G36" s="185"/>
-      <c r="H36" s="185"/>
-      <c r="I36" s="185"/>
-      <c r="J36" s="186"/>
+      <c r="A36" s="30"/>
+      <c r="B36" s="70"/>
+      <c r="C36" s="70"/>
+      <c r="D36" s="70"/>
+      <c r="E36" s="70"/>
+      <c r="F36" s="70"/>
+      <c r="G36" s="70"/>
+      <c r="H36" s="70"/>
+      <c r="I36" s="70"/>
+      <c r="J36" s="71"/>
     </row>
     <row r="37" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A37" s="28"/>
-      <c r="B37" s="185"/>
-      <c r="C37" s="185"/>
-      <c r="D37" s="185"/>
-      <c r="E37" s="185"/>
-      <c r="F37" s="185"/>
-      <c r="G37" s="185"/>
-      <c r="H37" s="185"/>
-      <c r="I37" s="185"/>
-      <c r="J37" s="186"/>
+      <c r="A37" s="30"/>
+      <c r="B37" s="70"/>
+      <c r="C37" s="70"/>
+      <c r="D37" s="70"/>
+      <c r="E37" s="70"/>
+      <c r="F37" s="70"/>
+      <c r="G37" s="70"/>
+      <c r="H37" s="70"/>
+      <c r="I37" s="70"/>
+      <c r="J37" s="71"/>
     </row>
     <row r="38" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A38" s="28"/>
-      <c r="B38" s="185"/>
-      <c r="C38" s="185"/>
-      <c r="D38" s="185"/>
-      <c r="E38" s="185"/>
-      <c r="F38" s="185"/>
-      <c r="G38" s="185"/>
-      <c r="H38" s="185"/>
-      <c r="I38" s="185"/>
-      <c r="J38" s="186"/>
+      <c r="A38" s="30"/>
+      <c r="B38" s="70"/>
+      <c r="C38" s="70"/>
+      <c r="D38" s="70"/>
+      <c r="E38" s="70"/>
+      <c r="F38" s="70"/>
+      <c r="G38" s="70"/>
+      <c r="H38" s="70"/>
+      <c r="I38" s="70"/>
+      <c r="J38" s="71"/>
     </row>
     <row r="39" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A39" s="28"/>
-      <c r="B39" s="185"/>
-      <c r="C39" s="185"/>
-      <c r="D39" s="185"/>
-      <c r="E39" s="185"/>
-      <c r="F39" s="185"/>
-      <c r="G39" s="185"/>
-      <c r="H39" s="185"/>
-      <c r="I39" s="185"/>
-      <c r="J39" s="186"/>
+      <c r="A39" s="30"/>
+      <c r="B39" s="70"/>
+      <c r="C39" s="70"/>
+      <c r="D39" s="70"/>
+      <c r="E39" s="70"/>
+      <c r="F39" s="70"/>
+      <c r="G39" s="70"/>
+      <c r="H39" s="70"/>
+      <c r="I39" s="70"/>
+      <c r="J39" s="71"/>
     </row>
     <row r="40" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A40" s="28"/>
-      <c r="B40" s="185"/>
-      <c r="C40" s="185"/>
-      <c r="D40" s="185"/>
-      <c r="E40" s="185"/>
-      <c r="F40" s="185"/>
-      <c r="G40" s="185"/>
-      <c r="H40" s="185"/>
-      <c r="I40" s="185"/>
-      <c r="J40" s="186"/>
+      <c r="A40" s="30"/>
+      <c r="B40" s="70"/>
+      <c r="C40" s="70"/>
+      <c r="D40" s="70"/>
+      <c r="E40" s="70"/>
+      <c r="F40" s="70"/>
+      <c r="G40" s="70"/>
+      <c r="H40" s="70"/>
+      <c r="I40" s="70"/>
+      <c r="J40" s="71"/>
     </row>
     <row r="41" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A41" s="28"/>
-      <c r="B41" s="185"/>
-      <c r="C41" s="185"/>
-      <c r="D41" s="185"/>
-      <c r="E41" s="185"/>
-      <c r="F41" s="185"/>
-      <c r="G41" s="185"/>
-      <c r="H41" s="185"/>
-      <c r="I41" s="185"/>
-      <c r="J41" s="186"/>
+      <c r="A41" s="30"/>
+      <c r="B41" s="70"/>
+      <c r="C41" s="70"/>
+      <c r="D41" s="70"/>
+      <c r="E41" s="70"/>
+      <c r="F41" s="70"/>
+      <c r="G41" s="70"/>
+      <c r="H41" s="70"/>
+      <c r="I41" s="70"/>
+      <c r="J41" s="71"/>
     </row>
     <row r="42" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A42" s="28"/>
-      <c r="B42" s="185"/>
-      <c r="C42" s="185"/>
-      <c r="D42" s="185"/>
-      <c r="E42" s="185"/>
-      <c r="F42" s="185"/>
-      <c r="G42" s="185"/>
-      <c r="H42" s="185"/>
-      <c r="I42" s="185"/>
-      <c r="J42" s="186"/>
+      <c r="A42" s="30"/>
+      <c r="B42" s="70"/>
+      <c r="C42" s="70"/>
+      <c r="D42" s="70"/>
+      <c r="E42" s="70"/>
+      <c r="F42" s="70"/>
+      <c r="G42" s="70"/>
+      <c r="H42" s="70"/>
+      <c r="I42" s="70"/>
+      <c r="J42" s="71"/>
     </row>
     <row r="43" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A43" s="28"/>
-      <c r="B43" s="185"/>
-      <c r="C43" s="185"/>
-      <c r="D43" s="185"/>
-      <c r="E43" s="185"/>
-      <c r="F43" s="185"/>
-      <c r="G43" s="185"/>
-      <c r="H43" s="185"/>
-      <c r="I43" s="185"/>
-      <c r="J43" s="186"/>
+      <c r="A43" s="30"/>
+      <c r="B43" s="70"/>
+      <c r="C43" s="70"/>
+      <c r="D43" s="70"/>
+      <c r="E43" s="70"/>
+      <c r="F43" s="70"/>
+      <c r="G43" s="70"/>
+      <c r="H43" s="70"/>
+      <c r="I43" s="70"/>
+      <c r="J43" s="71"/>
     </row>
     <row r="44" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A44" s="28"/>
-      <c r="B44" s="185"/>
-      <c r="C44" s="185"/>
-      <c r="D44" s="185"/>
-      <c r="E44" s="185"/>
-      <c r="F44" s="185"/>
-      <c r="G44" s="185"/>
-      <c r="H44" s="185"/>
-      <c r="I44" s="185"/>
-      <c r="J44" s="186"/>
+      <c r="A44" s="30"/>
+      <c r="B44" s="70"/>
+      <c r="C44" s="70"/>
+      <c r="D44" s="70"/>
+      <c r="E44" s="70"/>
+      <c r="F44" s="70"/>
+      <c r="G44" s="70"/>
+      <c r="H44" s="70"/>
+      <c r="I44" s="70"/>
+      <c r="J44" s="71"/>
     </row>
     <row r="45" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A45" s="28"/>
-      <c r="B45" s="185"/>
-      <c r="C45" s="185"/>
-      <c r="D45" s="185"/>
-      <c r="E45" s="185"/>
-      <c r="F45" s="185"/>
-      <c r="G45" s="185"/>
-      <c r="H45" s="185"/>
-      <c r="I45" s="185"/>
-      <c r="J45" s="186"/>
+      <c r="A45" s="30"/>
+      <c r="B45" s="70"/>
+      <c r="C45" s="70"/>
+      <c r="D45" s="70"/>
+      <c r="E45" s="70"/>
+      <c r="F45" s="70"/>
+      <c r="G45" s="70"/>
+      <c r="H45" s="70"/>
+      <c r="I45" s="70"/>
+      <c r="J45" s="71"/>
     </row>
     <row r="46" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A46" s="28"/>
-      <c r="B46" s="185"/>
-      <c r="C46" s="185"/>
-      <c r="D46" s="185"/>
-      <c r="E46" s="185"/>
-      <c r="F46" s="185"/>
-      <c r="G46" s="185"/>
-      <c r="H46" s="185"/>
-      <c r="I46" s="185"/>
-      <c r="J46" s="186"/>
+      <c r="A46" s="30"/>
+      <c r="B46" s="70"/>
+      <c r="C46" s="70"/>
+      <c r="D46" s="70"/>
+      <c r="E46" s="70"/>
+      <c r="F46" s="70"/>
+      <c r="G46" s="70"/>
+      <c r="H46" s="70"/>
+      <c r="I46" s="70"/>
+      <c r="J46" s="71"/>
     </row>
     <row r="47" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A47" s="28"/>
-      <c r="B47" s="185"/>
-      <c r="C47" s="185"/>
-      <c r="D47" s="185"/>
-      <c r="E47" s="185"/>
-      <c r="F47" s="185"/>
-      <c r="G47" s="185"/>
-      <c r="H47" s="185"/>
-      <c r="I47" s="185"/>
-      <c r="J47" s="186"/>
+      <c r="A47" s="30"/>
+      <c r="B47" s="70"/>
+      <c r="C47" s="70"/>
+      <c r="D47" s="70"/>
+      <c r="E47" s="70"/>
+      <c r="F47" s="70"/>
+      <c r="G47" s="70"/>
+      <c r="H47" s="70"/>
+      <c r="I47" s="70"/>
+      <c r="J47" s="71"/>
     </row>
     <row r="48" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A48" s="28"/>
-      <c r="B48" s="185"/>
-      <c r="C48" s="185"/>
-      <c r="D48" s="185"/>
-      <c r="E48" s="185"/>
-      <c r="F48" s="185"/>
-      <c r="G48" s="185"/>
-      <c r="H48" s="185"/>
-      <c r="I48" s="185"/>
-      <c r="J48" s="186"/>
+      <c r="A48" s="30"/>
+      <c r="B48" s="70"/>
+      <c r="C48" s="70"/>
+      <c r="D48" s="70"/>
+      <c r="E48" s="70"/>
+      <c r="F48" s="70"/>
+      <c r="G48" s="70"/>
+      <c r="H48" s="70"/>
+      <c r="I48" s="70"/>
+      <c r="J48" s="71"/>
     </row>
     <row r="49" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A49" s="28"/>
-      <c r="B49" s="185"/>
-      <c r="C49" s="185"/>
-      <c r="D49" s="185"/>
-      <c r="E49" s="185"/>
-      <c r="F49" s="185"/>
-      <c r="G49" s="185"/>
-      <c r="H49" s="185"/>
-      <c r="I49" s="185"/>
-      <c r="J49" s="186"/>
+      <c r="A49" s="30"/>
+      <c r="B49" s="70"/>
+      <c r="C49" s="70"/>
+      <c r="D49" s="70"/>
+      <c r="E49" s="70"/>
+      <c r="F49" s="70"/>
+      <c r="G49" s="70"/>
+      <c r="H49" s="70"/>
+      <c r="I49" s="70"/>
+      <c r="J49" s="71"/>
     </row>
     <row r="50" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A50" s="28"/>
-      <c r="B50" s="185"/>
-      <c r="C50" s="185"/>
-      <c r="D50" s="185"/>
-      <c r="E50" s="185"/>
-      <c r="F50" s="185"/>
-      <c r="G50" s="185"/>
-      <c r="H50" s="185"/>
-      <c r="I50" s="185"/>
-      <c r="J50" s="186"/>
+      <c r="A50" s="30"/>
+      <c r="B50" s="70"/>
+      <c r="C50" s="70"/>
+      <c r="D50" s="70"/>
+      <c r="E50" s="70"/>
+      <c r="F50" s="70"/>
+      <c r="G50" s="70"/>
+      <c r="H50" s="70"/>
+      <c r="I50" s="70"/>
+      <c r="J50" s="71"/>
     </row>
     <row r="51" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A51" s="28"/>
-      <c r="B51" s="185"/>
-      <c r="C51" s="185"/>
-      <c r="D51" s="185"/>
-      <c r="E51" s="185"/>
-      <c r="F51" s="185"/>
-      <c r="G51" s="185"/>
-      <c r="H51" s="185"/>
-      <c r="I51" s="185"/>
-      <c r="J51" s="186"/>
+      <c r="A51" s="30"/>
+      <c r="B51" s="70"/>
+      <c r="C51" s="70"/>
+      <c r="D51" s="70"/>
+      <c r="E51" s="70"/>
+      <c r="F51" s="70"/>
+      <c r="G51" s="70"/>
+      <c r="H51" s="70"/>
+      <c r="I51" s="70"/>
+      <c r="J51" s="71"/>
     </row>
     <row r="52" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A52" s="28"/>
-      <c r="B52" s="185"/>
-      <c r="C52" s="185"/>
-      <c r="D52" s="185"/>
-      <c r="E52" s="185"/>
-      <c r="F52" s="185"/>
-      <c r="G52" s="185"/>
-      <c r="H52" s="185"/>
-      <c r="I52" s="185"/>
-      <c r="J52" s="186"/>
+      <c r="A52" s="30"/>
+      <c r="B52" s="70"/>
+      <c r="C52" s="70"/>
+      <c r="D52" s="70"/>
+      <c r="E52" s="70"/>
+      <c r="F52" s="70"/>
+      <c r="G52" s="70"/>
+      <c r="H52" s="70"/>
+      <c r="I52" s="70"/>
+      <c r="J52" s="71"/>
     </row>
     <row r="53" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A53" s="28"/>
-      <c r="B53" s="185"/>
-      <c r="C53" s="185"/>
-      <c r="D53" s="185"/>
-      <c r="E53" s="185"/>
-      <c r="F53" s="185"/>
-      <c r="G53" s="185"/>
-      <c r="H53" s="185"/>
-      <c r="I53" s="185"/>
-      <c r="J53" s="186"/>
+      <c r="A53" s="30"/>
+      <c r="B53" s="70"/>
+      <c r="C53" s="70"/>
+      <c r="D53" s="70"/>
+      <c r="E53" s="70"/>
+      <c r="F53" s="70"/>
+      <c r="G53" s="70"/>
+      <c r="H53" s="70"/>
+      <c r="I53" s="70"/>
+      <c r="J53" s="71"/>
     </row>
     <row r="54" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A54" s="28"/>
-      <c r="B54" s="185"/>
-      <c r="C54" s="185"/>
-      <c r="D54" s="185"/>
-      <c r="E54" s="185"/>
-      <c r="F54" s="185"/>
-      <c r="G54" s="185"/>
-      <c r="H54" s="185"/>
-      <c r="I54" s="185"/>
-      <c r="J54" s="186"/>
+      <c r="A54" s="30"/>
+      <c r="B54" s="70"/>
+      <c r="C54" s="70"/>
+      <c r="D54" s="70"/>
+      <c r="E54" s="70"/>
+      <c r="F54" s="70"/>
+      <c r="G54" s="70"/>
+      <c r="H54" s="70"/>
+      <c r="I54" s="70"/>
+      <c r="J54" s="71"/>
     </row>
     <row r="55" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A55" s="28"/>
-      <c r="B55" s="185"/>
-      <c r="C55" s="185"/>
-      <c r="D55" s="185"/>
-      <c r="E55" s="185"/>
-      <c r="F55" s="185"/>
-      <c r="G55" s="185"/>
-      <c r="H55" s="185"/>
-      <c r="I55" s="185"/>
-      <c r="J55" s="186"/>
+      <c r="A55" s="30"/>
+      <c r="B55" s="70"/>
+      <c r="C55" s="70"/>
+      <c r="D55" s="70"/>
+      <c r="E55" s="70"/>
+      <c r="F55" s="70"/>
+      <c r="G55" s="70"/>
+      <c r="H55" s="70"/>
+      <c r="I55" s="70"/>
+      <c r="J55" s="71"/>
     </row>
     <row r="56" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A56" s="28"/>
-      <c r="B56" s="185"/>
-      <c r="C56" s="185"/>
-      <c r="D56" s="185"/>
-      <c r="E56" s="185"/>
-      <c r="F56" s="185"/>
-      <c r="G56" s="185"/>
-      <c r="H56" s="185"/>
-      <c r="I56" s="185"/>
-      <c r="J56" s="186"/>
+      <c r="A56" s="30"/>
+      <c r="B56" s="70"/>
+      <c r="C56" s="70"/>
+      <c r="D56" s="70"/>
+      <c r="E56" s="70"/>
+      <c r="F56" s="70"/>
+      <c r="G56" s="70"/>
+      <c r="H56" s="70"/>
+      <c r="I56" s="70"/>
+      <c r="J56" s="71"/>
     </row>
     <row r="57" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A57" s="28"/>
-      <c r="B57" s="185"/>
-      <c r="C57" s="185"/>
-      <c r="D57" s="185"/>
-      <c r="E57" s="185"/>
-      <c r="F57" s="185"/>
-      <c r="G57" s="185"/>
-      <c r="H57" s="185"/>
-      <c r="I57" s="185"/>
-      <c r="J57" s="186"/>
+      <c r="A57" s="30"/>
+      <c r="B57" s="70"/>
+      <c r="C57" s="70"/>
+      <c r="D57" s="70"/>
+      <c r="E57" s="70"/>
+      <c r="F57" s="70"/>
+      <c r="G57" s="70"/>
+      <c r="H57" s="70"/>
+      <c r="I57" s="70"/>
+      <c r="J57" s="71"/>
     </row>
     <row r="58" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A58" s="28"/>
-      <c r="B58" s="185"/>
-      <c r="C58" s="185"/>
-      <c r="D58" s="185"/>
-      <c r="E58" s="185"/>
-      <c r="F58" s="185"/>
-      <c r="G58" s="185"/>
-      <c r="H58" s="185"/>
-      <c r="I58" s="185"/>
-      <c r="J58" s="186"/>
-    </row>
-    <row r="59" spans="1:10" ht="13.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A59" s="29"/>
-      <c r="B59" s="187"/>
-      <c r="C59" s="187"/>
-      <c r="D59" s="187"/>
-      <c r="E59" s="187"/>
-      <c r="F59" s="187"/>
-      <c r="G59" s="187"/>
-      <c r="H59" s="187"/>
-      <c r="I59" s="187"/>
-      <c r="J59" s="188"/>
+      <c r="A58" s="30"/>
+      <c r="B58" s="70"/>
+      <c r="C58" s="70"/>
+      <c r="D58" s="70"/>
+      <c r="E58" s="70"/>
+      <c r="F58" s="70"/>
+      <c r="G58" s="70"/>
+      <c r="H58" s="70"/>
+      <c r="I58" s="70"/>
+      <c r="J58" s="71"/>
+    </row>
+    <row r="59" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A59" s="30"/>
+      <c r="B59" s="70"/>
+      <c r="C59" s="70"/>
+      <c r="D59" s="70"/>
+      <c r="E59" s="70"/>
+      <c r="F59" s="70"/>
+      <c r="G59" s="70"/>
+      <c r="H59" s="70"/>
+      <c r="I59" s="70"/>
+      <c r="J59" s="71"/>
     </row>
     <row r="60" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A60" s="27">
+      <c r="A60" s="30"/>
+      <c r="B60" s="70"/>
+      <c r="C60" s="70"/>
+      <c r="D60" s="70"/>
+      <c r="E60" s="70"/>
+      <c r="F60" s="70"/>
+      <c r="G60" s="70"/>
+      <c r="H60" s="70"/>
+      <c r="I60" s="70"/>
+      <c r="J60" s="71"/>
+    </row>
+    <row r="61" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A61" s="30"/>
+      <c r="B61" s="70"/>
+      <c r="C61" s="70"/>
+      <c r="D61" s="70"/>
+      <c r="E61" s="70"/>
+      <c r="F61" s="70"/>
+      <c r="G61" s="70"/>
+      <c r="H61" s="70"/>
+      <c r="I61" s="70"/>
+      <c r="J61" s="71"/>
+    </row>
+    <row r="62" spans="1:10" ht="13.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A62" s="31"/>
+      <c r="B62" s="72"/>
+      <c r="C62" s="72"/>
+      <c r="D62" s="72"/>
+      <c r="E62" s="72"/>
+      <c r="F62" s="72"/>
+      <c r="G62" s="72"/>
+      <c r="H62" s="72"/>
+      <c r="I62" s="72"/>
+      <c r="J62" s="73"/>
+    </row>
+    <row r="63" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A63" s="28">
         <v>4</v>
       </c>
-      <c r="B60" s="34" t="s">
+      <c r="B63" s="32" t="s">
         <v>6</v>
       </c>
-      <c r="C60" s="34"/>
-      <c r="D60" s="34"/>
-      <c r="E60" s="34"/>
-      <c r="F60" s="34"/>
-      <c r="G60" s="34"/>
-      <c r="H60" s="34"/>
-      <c r="I60" s="34"/>
-      <c r="J60" s="51"/>
-    </row>
-    <row r="61" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A61" s="28"/>
-      <c r="B61" s="30" t="s">
+      <c r="C63" s="32"/>
+      <c r="D63" s="32"/>
+      <c r="E63" s="32"/>
+      <c r="F63" s="32"/>
+      <c r="G63" s="32"/>
+      <c r="H63" s="32"/>
+      <c r="I63" s="32"/>
+      <c r="J63" s="33"/>
+    </row>
+    <row r="64" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A64" s="30"/>
+      <c r="B64" s="74" t="s">
         <v>7</v>
       </c>
-      <c r="C61" s="30"/>
-      <c r="D61" s="78"/>
-      <c r="E61" s="78"/>
-      <c r="F61" s="78"/>
-      <c r="G61" s="78"/>
-      <c r="H61" s="78"/>
-      <c r="I61" s="78"/>
-      <c r="J61" s="176"/>
-    </row>
-    <row r="62" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A62" s="28"/>
-      <c r="B62" s="30" t="s">
+      <c r="C64" s="74"/>
+      <c r="D64" s="34"/>
+      <c r="E64" s="34"/>
+      <c r="F64" s="34"/>
+      <c r="G64" s="34"/>
+      <c r="H64" s="34"/>
+      <c r="I64" s="34"/>
+      <c r="J64" s="35"/>
+    </row>
+    <row r="65" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A65" s="30"/>
+      <c r="B65" s="74" t="s">
         <v>8</v>
       </c>
-      <c r="C62" s="30"/>
-      <c r="D62" s="78"/>
-      <c r="E62" s="78"/>
-      <c r="F62" s="78"/>
-      <c r="G62" s="78"/>
-      <c r="H62" s="78"/>
-      <c r="I62" s="78"/>
-      <c r="J62" s="176"/>
-    </row>
-    <row r="63" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A63" s="28"/>
-      <c r="B63" s="30" t="s">
+      <c r="C65" s="74"/>
+      <c r="D65" s="34"/>
+      <c r="E65" s="34"/>
+      <c r="F65" s="34"/>
+      <c r="G65" s="34"/>
+      <c r="H65" s="34"/>
+      <c r="I65" s="34"/>
+      <c r="J65" s="35"/>
+    </row>
+    <row r="66" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A66" s="30"/>
+      <c r="B66" s="74" t="s">
         <v>9</v>
       </c>
-      <c r="C63" s="30"/>
-      <c r="D63" s="78"/>
-      <c r="E63" s="78"/>
-      <c r="F63" s="78"/>
-      <c r="G63" s="78"/>
-      <c r="H63" s="78"/>
-      <c r="I63" s="78"/>
-      <c r="J63" s="176"/>
-    </row>
-    <row r="64" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A64" s="28"/>
-      <c r="B64" s="30" t="s">
+      <c r="C66" s="74"/>
+      <c r="D66" s="34"/>
+      <c r="E66" s="34"/>
+      <c r="F66" s="34"/>
+      <c r="G66" s="34"/>
+      <c r="H66" s="34"/>
+      <c r="I66" s="34"/>
+      <c r="J66" s="35"/>
+    </row>
+    <row r="67" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A67" s="30"/>
+      <c r="B67" s="74" t="s">
         <v>104</v>
       </c>
-      <c r="C64" s="30"/>
-      <c r="D64" s="78"/>
-      <c r="E64" s="78"/>
-      <c r="F64" s="78"/>
-      <c r="G64" s="78"/>
-      <c r="H64" s="78"/>
-      <c r="I64" s="78"/>
-      <c r="J64" s="176"/>
-    </row>
-    <row r="65" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A65" s="28"/>
-      <c r="B65" s="30" t="s">
+      <c r="C67" s="74"/>
+      <c r="D67" s="34"/>
+      <c r="E67" s="34"/>
+      <c r="F67" s="34"/>
+      <c r="G67" s="34"/>
+      <c r="H67" s="34"/>
+      <c r="I67" s="34"/>
+      <c r="J67" s="35"/>
+    </row>
+    <row r="68" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A68" s="30"/>
+      <c r="B68" s="74" t="s">
         <v>10</v>
       </c>
-      <c r="C65" s="30"/>
-      <c r="D65" s="30"/>
-      <c r="E65" s="30"/>
-      <c r="F65" s="30"/>
-      <c r="G65" s="30"/>
-      <c r="H65" s="30"/>
-      <c r="I65" s="30"/>
-      <c r="J65" s="50"/>
-    </row>
-    <row r="66" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A66" s="28"/>
-      <c r="B66" s="189"/>
-      <c r="C66" s="189"/>
-      <c r="D66" s="189"/>
-      <c r="E66" s="189"/>
-      <c r="F66" s="189"/>
-      <c r="G66" s="189"/>
-      <c r="H66" s="189"/>
-      <c r="I66" s="189"/>
-      <c r="J66" s="190"/>
-    </row>
-    <row r="67" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A67" s="28"/>
-      <c r="B67" s="189"/>
-      <c r="C67" s="189"/>
-      <c r="D67" s="189"/>
-      <c r="E67" s="189"/>
-      <c r="F67" s="189"/>
-      <c r="G67" s="189"/>
-      <c r="H67" s="189"/>
-      <c r="I67" s="189"/>
-      <c r="J67" s="190"/>
-    </row>
-    <row r="68" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A68" s="28"/>
-      <c r="B68" s="189"/>
-      <c r="C68" s="189"/>
-      <c r="D68" s="189"/>
-      <c r="E68" s="189"/>
-      <c r="F68" s="189"/>
-      <c r="G68" s="189"/>
-      <c r="H68" s="189"/>
-      <c r="I68" s="189"/>
-      <c r="J68" s="190"/>
+      <c r="C68" s="74"/>
+      <c r="D68" s="74"/>
+      <c r="E68" s="74"/>
+      <c r="F68" s="74"/>
+      <c r="G68" s="74"/>
+      <c r="H68" s="74"/>
+      <c r="I68" s="74"/>
+      <c r="J68" s="75"/>
     </row>
     <row r="69" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A69" s="28"/>
-      <c r="B69" s="189"/>
-      <c r="C69" s="189"/>
-      <c r="D69" s="189"/>
-      <c r="E69" s="189"/>
-      <c r="F69" s="189"/>
-      <c r="G69" s="189"/>
-      <c r="H69" s="189"/>
-      <c r="I69" s="189"/>
-      <c r="J69" s="190"/>
+      <c r="A69" s="30"/>
+      <c r="B69" s="60"/>
+      <c r="C69" s="60"/>
+      <c r="D69" s="60"/>
+      <c r="E69" s="60"/>
+      <c r="F69" s="60"/>
+      <c r="G69" s="60"/>
+      <c r="H69" s="60"/>
+      <c r="I69" s="60"/>
+      <c r="J69" s="61"/>
     </row>
     <row r="70" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A70" s="28"/>
-      <c r="B70" s="189"/>
-      <c r="C70" s="189"/>
-      <c r="D70" s="189"/>
-      <c r="E70" s="189"/>
-      <c r="F70" s="189"/>
-      <c r="G70" s="189"/>
-      <c r="H70" s="189"/>
-      <c r="I70" s="189"/>
-      <c r="J70" s="190"/>
+      <c r="A70" s="30"/>
+      <c r="B70" s="60"/>
+      <c r="C70" s="60"/>
+      <c r="D70" s="60"/>
+      <c r="E70" s="60"/>
+      <c r="F70" s="60"/>
+      <c r="G70" s="60"/>
+      <c r="H70" s="60"/>
+      <c r="I70" s="60"/>
+      <c r="J70" s="61"/>
     </row>
     <row r="71" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A71" s="28"/>
-      <c r="B71" s="189"/>
-      <c r="C71" s="189"/>
-      <c r="D71" s="189"/>
-      <c r="E71" s="189"/>
-      <c r="F71" s="189"/>
-      <c r="G71" s="189"/>
-      <c r="H71" s="189"/>
-      <c r="I71" s="189"/>
-      <c r="J71" s="190"/>
+      <c r="A71" s="30"/>
+      <c r="B71" s="60"/>
+      <c r="C71" s="60"/>
+      <c r="D71" s="60"/>
+      <c r="E71" s="60"/>
+      <c r="F71" s="60"/>
+      <c r="G71" s="60"/>
+      <c r="H71" s="60"/>
+      <c r="I71" s="60"/>
+      <c r="J71" s="61"/>
     </row>
     <row r="72" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A72" s="28"/>
-      <c r="B72" s="189"/>
-      <c r="C72" s="189"/>
-      <c r="D72" s="189"/>
-      <c r="E72" s="189"/>
-      <c r="F72" s="189"/>
-      <c r="G72" s="189"/>
-      <c r="H72" s="189"/>
-      <c r="I72" s="189"/>
-      <c r="J72" s="190"/>
+      <c r="A72" s="30"/>
+      <c r="B72" s="60"/>
+      <c r="C72" s="60"/>
+      <c r="D72" s="60"/>
+      <c r="E72" s="60"/>
+      <c r="F72" s="60"/>
+      <c r="G72" s="60"/>
+      <c r="H72" s="60"/>
+      <c r="I72" s="60"/>
+      <c r="J72" s="61"/>
     </row>
     <row r="73" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A73" s="28"/>
-      <c r="B73" s="189"/>
-      <c r="C73" s="189"/>
-      <c r="D73" s="189"/>
-      <c r="E73" s="189"/>
-      <c r="F73" s="189"/>
-      <c r="G73" s="189"/>
-      <c r="H73" s="189"/>
-      <c r="I73" s="189"/>
-      <c r="J73" s="190"/>
+      <c r="A73" s="30"/>
+      <c r="B73" s="60"/>
+      <c r="C73" s="60"/>
+      <c r="D73" s="60"/>
+      <c r="E73" s="60"/>
+      <c r="F73" s="60"/>
+      <c r="G73" s="60"/>
+      <c r="H73" s="60"/>
+      <c r="I73" s="60"/>
+      <c r="J73" s="61"/>
     </row>
     <row r="74" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A74" s="28"/>
-      <c r="B74" s="189"/>
-      <c r="C74" s="189"/>
-      <c r="D74" s="189"/>
-      <c r="E74" s="189"/>
-      <c r="F74" s="189"/>
-      <c r="G74" s="189"/>
-      <c r="H74" s="189"/>
-      <c r="I74" s="189"/>
-      <c r="J74" s="190"/>
+      <c r="A74" s="30"/>
+      <c r="B74" s="60"/>
+      <c r="C74" s="60"/>
+      <c r="D74" s="60"/>
+      <c r="E74" s="60"/>
+      <c r="F74" s="60"/>
+      <c r="G74" s="60"/>
+      <c r="H74" s="60"/>
+      <c r="I74" s="60"/>
+      <c r="J74" s="61"/>
     </row>
     <row r="75" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A75" s="28"/>
-      <c r="B75" s="189"/>
-      <c r="C75" s="189"/>
-      <c r="D75" s="189"/>
-      <c r="E75" s="189"/>
-      <c r="F75" s="189"/>
-      <c r="G75" s="189"/>
-      <c r="H75" s="189"/>
-      <c r="I75" s="189"/>
-      <c r="J75" s="190"/>
+      <c r="A75" s="30"/>
+      <c r="B75" s="60"/>
+      <c r="C75" s="60"/>
+      <c r="D75" s="60"/>
+      <c r="E75" s="60"/>
+      <c r="F75" s="60"/>
+      <c r="G75" s="60"/>
+      <c r="H75" s="60"/>
+      <c r="I75" s="60"/>
+      <c r="J75" s="61"/>
     </row>
     <row r="76" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A76" s="28"/>
-      <c r="B76" s="189"/>
-      <c r="C76" s="189"/>
-      <c r="D76" s="189"/>
-      <c r="E76" s="189"/>
-      <c r="F76" s="189"/>
-      <c r="G76" s="189"/>
-      <c r="H76" s="189"/>
-      <c r="I76" s="189"/>
-      <c r="J76" s="190"/>
+      <c r="A76" s="30"/>
+      <c r="B76" s="60"/>
+      <c r="C76" s="60"/>
+      <c r="D76" s="60"/>
+      <c r="E76" s="60"/>
+      <c r="F76" s="60"/>
+      <c r="G76" s="60"/>
+      <c r="H76" s="60"/>
+      <c r="I76" s="60"/>
+      <c r="J76" s="61"/>
     </row>
     <row r="77" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A77" s="28"/>
-      <c r="B77" s="189"/>
-      <c r="C77" s="189"/>
-      <c r="D77" s="189"/>
-      <c r="E77" s="189"/>
-      <c r="F77" s="189"/>
-      <c r="G77" s="189"/>
-      <c r="H77" s="189"/>
-      <c r="I77" s="189"/>
-      <c r="J77" s="190"/>
+      <c r="A77" s="30"/>
+      <c r="B77" s="60"/>
+      <c r="C77" s="60"/>
+      <c r="D77" s="60"/>
+      <c r="E77" s="60"/>
+      <c r="F77" s="60"/>
+      <c r="G77" s="60"/>
+      <c r="H77" s="60"/>
+      <c r="I77" s="60"/>
+      <c r="J77" s="61"/>
     </row>
     <row r="78" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A78" s="28"/>
-      <c r="B78" s="189"/>
-      <c r="C78" s="189"/>
-      <c r="D78" s="189"/>
-      <c r="E78" s="189"/>
-      <c r="F78" s="189"/>
-      <c r="G78" s="189"/>
-      <c r="H78" s="189"/>
-      <c r="I78" s="189"/>
-      <c r="J78" s="190"/>
+      <c r="A78" s="30"/>
+      <c r="B78" s="60"/>
+      <c r="C78" s="60"/>
+      <c r="D78" s="60"/>
+      <c r="E78" s="60"/>
+      <c r="F78" s="60"/>
+      <c r="G78" s="60"/>
+      <c r="H78" s="60"/>
+      <c r="I78" s="60"/>
+      <c r="J78" s="61"/>
     </row>
     <row r="79" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A79" s="28"/>
-      <c r="B79" s="189"/>
-      <c r="C79" s="189"/>
-      <c r="D79" s="189"/>
-      <c r="E79" s="189"/>
-      <c r="F79" s="189"/>
-      <c r="G79" s="189"/>
-      <c r="H79" s="189"/>
-      <c r="I79" s="189"/>
-      <c r="J79" s="190"/>
+      <c r="A79" s="30"/>
+      <c r="B79" s="60"/>
+      <c r="C79" s="60"/>
+      <c r="D79" s="60"/>
+      <c r="E79" s="60"/>
+      <c r="F79" s="60"/>
+      <c r="G79" s="60"/>
+      <c r="H79" s="60"/>
+      <c r="I79" s="60"/>
+      <c r="J79" s="61"/>
     </row>
     <row r="80" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A80" s="28"/>
-      <c r="B80" s="189"/>
-      <c r="C80" s="189"/>
-      <c r="D80" s="189"/>
-      <c r="E80" s="189"/>
-      <c r="F80" s="189"/>
-      <c r="G80" s="189"/>
-      <c r="H80" s="189"/>
-      <c r="I80" s="189"/>
-      <c r="J80" s="190"/>
+      <c r="A80" s="30"/>
+      <c r="B80" s="60"/>
+      <c r="C80" s="60"/>
+      <c r="D80" s="60"/>
+      <c r="E80" s="60"/>
+      <c r="F80" s="60"/>
+      <c r="G80" s="60"/>
+      <c r="H80" s="60"/>
+      <c r="I80" s="60"/>
+      <c r="J80" s="61"/>
     </row>
     <row r="81" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A81" s="28"/>
-      <c r="B81" s="189"/>
-      <c r="C81" s="189"/>
-      <c r="D81" s="189"/>
-      <c r="E81" s="189"/>
-      <c r="F81" s="189"/>
-      <c r="G81" s="189"/>
-      <c r="H81" s="189"/>
-      <c r="I81" s="189"/>
-      <c r="J81" s="190"/>
+      <c r="A81" s="30"/>
+      <c r="B81" s="60"/>
+      <c r="C81" s="60"/>
+      <c r="D81" s="60"/>
+      <c r="E81" s="60"/>
+      <c r="F81" s="60"/>
+      <c r="G81" s="60"/>
+      <c r="H81" s="60"/>
+      <c r="I81" s="60"/>
+      <c r="J81" s="61"/>
     </row>
     <row r="82" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A82" s="28"/>
-      <c r="B82" s="189"/>
-      <c r="C82" s="189"/>
-      <c r="D82" s="189"/>
-      <c r="E82" s="189"/>
-      <c r="F82" s="189"/>
-      <c r="G82" s="189"/>
-      <c r="H82" s="189"/>
-      <c r="I82" s="189"/>
-      <c r="J82" s="190"/>
-    </row>
-    <row r="83" spans="1:10" ht="13.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A83" s="31"/>
-      <c r="B83" s="58"/>
-      <c r="C83" s="58"/>
-      <c r="D83" s="58"/>
-      <c r="E83" s="58"/>
-      <c r="F83" s="58"/>
-      <c r="G83" s="58"/>
-      <c r="H83" s="58"/>
-      <c r="I83" s="58"/>
-      <c r="J83" s="191"/>
+      <c r="A82" s="30"/>
+      <c r="B82" s="60"/>
+      <c r="C82" s="60"/>
+      <c r="D82" s="60"/>
+      <c r="E82" s="60"/>
+      <c r="F82" s="60"/>
+      <c r="G82" s="60"/>
+      <c r="H82" s="60"/>
+      <c r="I82" s="60"/>
+      <c r="J82" s="61"/>
+    </row>
+    <row r="83" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A83" s="30"/>
+      <c r="B83" s="60"/>
+      <c r="C83" s="60"/>
+      <c r="D83" s="60"/>
+      <c r="E83" s="60"/>
+      <c r="F83" s="60"/>
+      <c r="G83" s="60"/>
+      <c r="H83" s="60"/>
+      <c r="I83" s="60"/>
+      <c r="J83" s="61"/>
     </row>
     <row r="84" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A84" s="27">
+      <c r="A84" s="30"/>
+      <c r="B84" s="60"/>
+      <c r="C84" s="60"/>
+      <c r="D84" s="60"/>
+      <c r="E84" s="60"/>
+      <c r="F84" s="60"/>
+      <c r="G84" s="60"/>
+      <c r="H84" s="60"/>
+      <c r="I84" s="60"/>
+      <c r="J84" s="61"/>
+    </row>
+    <row r="85" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A85" s="30"/>
+      <c r="B85" s="60"/>
+      <c r="C85" s="60"/>
+      <c r="D85" s="60"/>
+      <c r="E85" s="60"/>
+      <c r="F85" s="60"/>
+      <c r="G85" s="60"/>
+      <c r="H85" s="60"/>
+      <c r="I85" s="60"/>
+      <c r="J85" s="61"/>
+    </row>
+    <row r="86" spans="1:10" ht="13.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A86" s="29"/>
+      <c r="B86" s="62"/>
+      <c r="C86" s="62"/>
+      <c r="D86" s="62"/>
+      <c r="E86" s="62"/>
+      <c r="F86" s="62"/>
+      <c r="G86" s="62"/>
+      <c r="H86" s="62"/>
+      <c r="I86" s="62"/>
+      <c r="J86" s="63"/>
+    </row>
+    <row r="87" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A87" s="28">
         <v>5</v>
       </c>
-      <c r="B84" s="34" t="s">
+      <c r="B87" s="32" t="s">
         <v>11</v>
       </c>
-      <c r="C84" s="34"/>
-      <c r="D84" s="34"/>
-      <c r="E84" s="34"/>
-      <c r="F84" s="34"/>
-      <c r="G84" s="34"/>
-      <c r="H84" s="34"/>
-      <c r="I84" s="34"/>
-      <c r="J84" s="51"/>
-    </row>
-    <row r="85" spans="1:10" ht="13.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A85" s="28"/>
-      <c r="B85" s="56" t="s">
+      <c r="C87" s="32"/>
+      <c r="D87" s="32"/>
+      <c r="E87" s="32"/>
+      <c r="F87" s="32"/>
+      <c r="G87" s="32"/>
+      <c r="H87" s="32"/>
+      <c r="I87" s="32"/>
+      <c r="J87" s="33"/>
+    </row>
+    <row r="88" spans="1:10" ht="13.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A88" s="30"/>
+      <c r="B88" s="49" t="s">
         <v>12</v>
       </c>
-      <c r="C85" s="56"/>
-      <c r="D85" s="56"/>
-      <c r="E85" s="56"/>
-      <c r="F85" s="56"/>
-      <c r="G85" s="56"/>
-      <c r="H85" s="56"/>
-      <c r="I85" s="56"/>
-      <c r="J85" s="57"/>
-    </row>
-    <row r="86" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A86" s="27">
+      <c r="C88" s="49"/>
+      <c r="D88" s="49"/>
+      <c r="E88" s="49"/>
+      <c r="F88" s="49"/>
+      <c r="G88" s="49"/>
+      <c r="H88" s="49"/>
+      <c r="I88" s="49"/>
+      <c r="J88" s="50"/>
+    </row>
+    <row r="89" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A89" s="28">
         <v>6</v>
       </c>
-      <c r="B86" s="32" t="s">
+      <c r="B89" s="42" t="s">
         <v>13</v>
       </c>
-      <c r="C86" s="32"/>
-      <c r="D86" s="32"/>
-      <c r="E86" s="32"/>
-      <c r="F86" s="32"/>
-      <c r="G86" s="32"/>
-      <c r="H86" s="32"/>
-      <c r="I86" s="32"/>
-      <c r="J86" s="33"/>
-    </row>
-    <row r="87" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A87" s="55"/>
-      <c r="B87" s="40" t="s">
-        <v>14</v>
-      </c>
-      <c r="C87" s="40"/>
-      <c r="D87" s="40"/>
-      <c r="E87" s="40"/>
-      <c r="F87" s="40"/>
-      <c r="G87" s="40"/>
-      <c r="H87" s="40"/>
-      <c r="I87" s="40"/>
-      <c r="J87" s="41"/>
-    </row>
-    <row r="88" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A88" s="55"/>
-      <c r="B88" s="40"/>
-      <c r="C88" s="40"/>
-      <c r="D88" s="40"/>
-      <c r="E88" s="40"/>
-      <c r="F88" s="40"/>
-      <c r="G88" s="40"/>
-      <c r="H88" s="40"/>
-      <c r="I88" s="40"/>
-      <c r="J88" s="41"/>
-    </row>
-    <row r="89" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A89" s="55"/>
-      <c r="B89" s="42"/>
       <c r="C89" s="42"/>
       <c r="D89" s="42"/>
       <c r="E89" s="42"/>
@@ -4522,454 +4503,492 @@
       <c r="J89" s="43"/>
     </row>
     <row r="90" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A90" s="28"/>
-      <c r="B90" s="192"/>
-      <c r="C90" s="180"/>
-      <c r="D90" s="180"/>
-      <c r="E90" s="180"/>
-      <c r="F90" s="180"/>
-      <c r="G90" s="180"/>
-      <c r="H90" s="180"/>
-      <c r="I90" s="180"/>
-      <c r="J90" s="181"/>
+      <c r="A90" s="44"/>
+      <c r="B90" s="45" t="s">
+        <v>14</v>
+      </c>
+      <c r="C90" s="45"/>
+      <c r="D90" s="45"/>
+      <c r="E90" s="45"/>
+      <c r="F90" s="45"/>
+      <c r="G90" s="45"/>
+      <c r="H90" s="45"/>
+      <c r="I90" s="45"/>
+      <c r="J90" s="46"/>
     </row>
     <row r="91" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A91" s="28"/>
-      <c r="B91" s="182"/>
-      <c r="C91" s="183"/>
-      <c r="D91" s="183"/>
-      <c r="E91" s="183"/>
-      <c r="F91" s="183"/>
-      <c r="G91" s="183"/>
-      <c r="H91" s="183"/>
-      <c r="I91" s="183"/>
-      <c r="J91" s="184"/>
+      <c r="A91" s="44"/>
+      <c r="B91" s="45"/>
+      <c r="C91" s="45"/>
+      <c r="D91" s="45"/>
+      <c r="E91" s="45"/>
+      <c r="F91" s="45"/>
+      <c r="G91" s="45"/>
+      <c r="H91" s="45"/>
+      <c r="I91" s="45"/>
+      <c r="J91" s="46"/>
     </row>
     <row r="92" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A92" s="28"/>
-      <c r="B92" s="182"/>
-      <c r="C92" s="183"/>
-      <c r="D92" s="183"/>
-      <c r="E92" s="183"/>
-      <c r="F92" s="183"/>
-      <c r="G92" s="183"/>
-      <c r="H92" s="183"/>
-      <c r="I92" s="183"/>
-      <c r="J92" s="184"/>
+      <c r="A92" s="44"/>
+      <c r="B92" s="47"/>
+      <c r="C92" s="47"/>
+      <c r="D92" s="47"/>
+      <c r="E92" s="47"/>
+      <c r="F92" s="47"/>
+      <c r="G92" s="47"/>
+      <c r="H92" s="47"/>
+      <c r="I92" s="47"/>
+      <c r="J92" s="48"/>
     </row>
     <row r="93" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A93" s="28"/>
-      <c r="B93" s="182"/>
-      <c r="C93" s="183"/>
-      <c r="D93" s="183"/>
-      <c r="E93" s="183"/>
-      <c r="F93" s="183"/>
-      <c r="G93" s="183"/>
-      <c r="H93" s="183"/>
-      <c r="I93" s="183"/>
-      <c r="J93" s="184"/>
+      <c r="A93" s="30"/>
+      <c r="B93" s="51"/>
+      <c r="C93" s="52"/>
+      <c r="D93" s="52"/>
+      <c r="E93" s="52"/>
+      <c r="F93" s="52"/>
+      <c r="G93" s="52"/>
+      <c r="H93" s="52"/>
+      <c r="I93" s="52"/>
+      <c r="J93" s="53"/>
     </row>
     <row r="94" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A94" s="28"/>
-      <c r="B94" s="182"/>
-      <c r="C94" s="183"/>
-      <c r="D94" s="183"/>
-      <c r="E94" s="183"/>
-      <c r="F94" s="183"/>
-      <c r="G94" s="183"/>
-      <c r="H94" s="183"/>
-      <c r="I94" s="183"/>
-      <c r="J94" s="184"/>
+      <c r="A94" s="30"/>
+      <c r="B94" s="54"/>
+      <c r="C94" s="55"/>
+      <c r="D94" s="55"/>
+      <c r="E94" s="55"/>
+      <c r="F94" s="55"/>
+      <c r="G94" s="55"/>
+      <c r="H94" s="55"/>
+      <c r="I94" s="55"/>
+      <c r="J94" s="56"/>
     </row>
     <row r="95" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A95" s="28"/>
-      <c r="B95" s="182"/>
-      <c r="C95" s="183"/>
-      <c r="D95" s="183"/>
-      <c r="E95" s="183"/>
-      <c r="F95" s="183"/>
-      <c r="G95" s="183"/>
-      <c r="H95" s="183"/>
-      <c r="I95" s="183"/>
-      <c r="J95" s="184"/>
+      <c r="A95" s="30"/>
+      <c r="B95" s="54"/>
+      <c r="C95" s="55"/>
+      <c r="D95" s="55"/>
+      <c r="E95" s="55"/>
+      <c r="F95" s="55"/>
+      <c r="G95" s="55"/>
+      <c r="H95" s="55"/>
+      <c r="I95" s="55"/>
+      <c r="J95" s="56"/>
     </row>
     <row r="96" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A96" s="28"/>
-      <c r="B96" s="182"/>
-      <c r="C96" s="183"/>
-      <c r="D96" s="183"/>
-      <c r="E96" s="183"/>
-      <c r="F96" s="183"/>
-      <c r="G96" s="183"/>
-      <c r="H96" s="183"/>
-      <c r="I96" s="183"/>
-      <c r="J96" s="184"/>
+      <c r="A96" s="30"/>
+      <c r="B96" s="54"/>
+      <c r="C96" s="55"/>
+      <c r="D96" s="55"/>
+      <c r="E96" s="55"/>
+      <c r="F96" s="55"/>
+      <c r="G96" s="55"/>
+      <c r="H96" s="55"/>
+      <c r="I96" s="55"/>
+      <c r="J96" s="56"/>
     </row>
     <row r="97" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A97" s="28"/>
-      <c r="B97" s="182"/>
-      <c r="C97" s="183"/>
-      <c r="D97" s="183"/>
-      <c r="E97" s="183"/>
-      <c r="F97" s="183"/>
-      <c r="G97" s="183"/>
-      <c r="H97" s="183"/>
-      <c r="I97" s="183"/>
-      <c r="J97" s="184"/>
+      <c r="A97" s="30"/>
+      <c r="B97" s="54"/>
+      <c r="C97" s="55"/>
+      <c r="D97" s="55"/>
+      <c r="E97" s="55"/>
+      <c r="F97" s="55"/>
+      <c r="G97" s="55"/>
+      <c r="H97" s="55"/>
+      <c r="I97" s="55"/>
+      <c r="J97" s="56"/>
     </row>
     <row r="98" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A98" s="28"/>
-      <c r="B98" s="182"/>
-      <c r="C98" s="183"/>
-      <c r="D98" s="183"/>
-      <c r="E98" s="183"/>
-      <c r="F98" s="183"/>
-      <c r="G98" s="183"/>
-      <c r="H98" s="183"/>
-      <c r="I98" s="183"/>
-      <c r="J98" s="184"/>
+      <c r="A98" s="30"/>
+      <c r="B98" s="54"/>
+      <c r="C98" s="55"/>
+      <c r="D98" s="55"/>
+      <c r="E98" s="55"/>
+      <c r="F98" s="55"/>
+      <c r="G98" s="55"/>
+      <c r="H98" s="55"/>
+      <c r="I98" s="55"/>
+      <c r="J98" s="56"/>
     </row>
     <row r="99" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A99" s="28"/>
-      <c r="B99" s="182"/>
-      <c r="C99" s="183"/>
-      <c r="D99" s="183"/>
-      <c r="E99" s="183"/>
-      <c r="F99" s="183"/>
-      <c r="G99" s="183"/>
-      <c r="H99" s="183"/>
-      <c r="I99" s="183"/>
-      <c r="J99" s="184"/>
+      <c r="A99" s="30"/>
+      <c r="B99" s="54"/>
+      <c r="C99" s="55"/>
+      <c r="D99" s="55"/>
+      <c r="E99" s="55"/>
+      <c r="F99" s="55"/>
+      <c r="G99" s="55"/>
+      <c r="H99" s="55"/>
+      <c r="I99" s="55"/>
+      <c r="J99" s="56"/>
     </row>
     <row r="100" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A100" s="28"/>
-      <c r="B100" s="182"/>
-      <c r="C100" s="183"/>
-      <c r="D100" s="183"/>
-      <c r="E100" s="183"/>
-      <c r="F100" s="183"/>
-      <c r="G100" s="183"/>
-      <c r="H100" s="183"/>
-      <c r="I100" s="183"/>
-      <c r="J100" s="184"/>
+      <c r="A100" s="30"/>
+      <c r="B100" s="54"/>
+      <c r="C100" s="55"/>
+      <c r="D100" s="55"/>
+      <c r="E100" s="55"/>
+      <c r="F100" s="55"/>
+      <c r="G100" s="55"/>
+      <c r="H100" s="55"/>
+      <c r="I100" s="55"/>
+      <c r="J100" s="56"/>
     </row>
     <row r="101" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A101" s="28"/>
-      <c r="B101" s="182"/>
-      <c r="C101" s="183"/>
-      <c r="D101" s="183"/>
-      <c r="E101" s="183"/>
-      <c r="F101" s="183"/>
-      <c r="G101" s="183"/>
-      <c r="H101" s="183"/>
-      <c r="I101" s="183"/>
-      <c r="J101" s="184"/>
+      <c r="A101" s="30"/>
+      <c r="B101" s="54"/>
+      <c r="C101" s="55"/>
+      <c r="D101" s="55"/>
+      <c r="E101" s="55"/>
+      <c r="F101" s="55"/>
+      <c r="G101" s="55"/>
+      <c r="H101" s="55"/>
+      <c r="I101" s="55"/>
+      <c r="J101" s="56"/>
     </row>
     <row r="102" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A102" s="28"/>
-      <c r="B102" s="182"/>
-      <c r="C102" s="183"/>
-      <c r="D102" s="183"/>
-      <c r="E102" s="183"/>
-      <c r="F102" s="183"/>
-      <c r="G102" s="183"/>
-      <c r="H102" s="183"/>
-      <c r="I102" s="183"/>
-      <c r="J102" s="184"/>
+      <c r="A102" s="30"/>
+      <c r="B102" s="54"/>
+      <c r="C102" s="55"/>
+      <c r="D102" s="55"/>
+      <c r="E102" s="55"/>
+      <c r="F102" s="55"/>
+      <c r="G102" s="55"/>
+      <c r="H102" s="55"/>
+      <c r="I102" s="55"/>
+      <c r="J102" s="56"/>
     </row>
     <row r="103" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A103" s="28"/>
-      <c r="B103" s="182"/>
-      <c r="C103" s="183"/>
-      <c r="D103" s="183"/>
-      <c r="E103" s="183"/>
-      <c r="F103" s="183"/>
-      <c r="G103" s="183"/>
-      <c r="H103" s="183"/>
-      <c r="I103" s="183"/>
-      <c r="J103" s="184"/>
-    </row>
-    <row r="104" spans="1:10" ht="13.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A104" s="29"/>
-      <c r="B104" s="193"/>
-      <c r="C104" s="194"/>
-      <c r="D104" s="194"/>
-      <c r="E104" s="194"/>
-      <c r="F104" s="194"/>
-      <c r="G104" s="194"/>
-      <c r="H104" s="194"/>
-      <c r="I104" s="194"/>
-      <c r="J104" s="195"/>
+      <c r="A103" s="30"/>
+      <c r="B103" s="54"/>
+      <c r="C103" s="55"/>
+      <c r="D103" s="55"/>
+      <c r="E103" s="55"/>
+      <c r="F103" s="55"/>
+      <c r="G103" s="55"/>
+      <c r="H103" s="55"/>
+      <c r="I103" s="55"/>
+      <c r="J103" s="56"/>
+    </row>
+    <row r="104" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A104" s="30"/>
+      <c r="B104" s="54"/>
+      <c r="C104" s="55"/>
+      <c r="D104" s="55"/>
+      <c r="E104" s="55"/>
+      <c r="F104" s="55"/>
+      <c r="G104" s="55"/>
+      <c r="H104" s="55"/>
+      <c r="I104" s="55"/>
+      <c r="J104" s="56"/>
     </row>
     <row r="105" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A105" s="27">
+      <c r="A105" s="30"/>
+      <c r="B105" s="54"/>
+      <c r="C105" s="55"/>
+      <c r="D105" s="55"/>
+      <c r="E105" s="55"/>
+      <c r="F105" s="55"/>
+      <c r="G105" s="55"/>
+      <c r="H105" s="55"/>
+      <c r="I105" s="55"/>
+      <c r="J105" s="56"/>
+    </row>
+    <row r="106" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A106" s="30"/>
+      <c r="B106" s="54"/>
+      <c r="C106" s="55"/>
+      <c r="D106" s="55"/>
+      <c r="E106" s="55"/>
+      <c r="F106" s="55"/>
+      <c r="G106" s="55"/>
+      <c r="H106" s="55"/>
+      <c r="I106" s="55"/>
+      <c r="J106" s="56"/>
+    </row>
+    <row r="107" spans="1:10" ht="13.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A107" s="31"/>
+      <c r="B107" s="57"/>
+      <c r="C107" s="58"/>
+      <c r="D107" s="58"/>
+      <c r="E107" s="58"/>
+      <c r="F107" s="58"/>
+      <c r="G107" s="58"/>
+      <c r="H107" s="58"/>
+      <c r="I107" s="58"/>
+      <c r="J107" s="59"/>
+    </row>
+    <row r="108" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A108" s="28">
         <v>7</v>
       </c>
-      <c r="B105" s="34" t="s">
+      <c r="B108" s="32" t="s">
         <v>15</v>
       </c>
-      <c r="C105" s="34"/>
-      <c r="D105" s="34"/>
-      <c r="E105" s="34"/>
-      <c r="F105" s="34"/>
-      <c r="G105" s="34"/>
-      <c r="H105" s="34"/>
-      <c r="I105" s="34"/>
-      <c r="J105" s="51"/>
-    </row>
-    <row r="106" spans="1:10" ht="13.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A106" s="31"/>
-      <c r="B106" s="36" t="s">
+      <c r="C108" s="32"/>
+      <c r="D108" s="32"/>
+      <c r="E108" s="32"/>
+      <c r="F108" s="32"/>
+      <c r="G108" s="32"/>
+      <c r="H108" s="32"/>
+      <c r="I108" s="32"/>
+      <c r="J108" s="33"/>
+    </row>
+    <row r="109" spans="1:10" ht="13.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A109" s="29"/>
+      <c r="B109" s="40" t="s">
         <v>16</v>
       </c>
-      <c r="C106" s="36"/>
-      <c r="D106" s="36"/>
-      <c r="E106" s="36"/>
-      <c r="F106" s="36"/>
-      <c r="G106" s="36"/>
-      <c r="H106" s="36"/>
-      <c r="I106" s="36"/>
-      <c r="J106" s="37"/>
-    </row>
-    <row r="107" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A107" s="27">
+      <c r="C109" s="40"/>
+      <c r="D109" s="40"/>
+      <c r="E109" s="40"/>
+      <c r="F109" s="40"/>
+      <c r="G109" s="40"/>
+      <c r="H109" s="40"/>
+      <c r="I109" s="40"/>
+      <c r="J109" s="41"/>
+    </row>
+    <row r="110" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A110" s="28">
         <v>8</v>
       </c>
-      <c r="B107" s="34" t="s">
+      <c r="B110" s="32" t="s">
         <v>17</v>
       </c>
-      <c r="C107" s="34"/>
-      <c r="D107" s="34"/>
-      <c r="E107" s="34"/>
-      <c r="F107" s="34"/>
-      <c r="G107" s="34"/>
-      <c r="H107" s="34"/>
-      <c r="I107" s="34"/>
-      <c r="J107" s="51"/>
-    </row>
-    <row r="108" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A108" s="28"/>
-      <c r="B108" s="78"/>
-      <c r="C108" s="78"/>
-      <c r="D108" s="78"/>
-      <c r="E108" s="78"/>
-      <c r="F108" s="78"/>
-      <c r="G108" s="78"/>
-      <c r="H108" s="78"/>
-      <c r="I108" s="78"/>
-      <c r="J108" s="176"/>
-    </row>
-    <row r="109" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A109" s="28"/>
-      <c r="B109" s="78"/>
-      <c r="C109" s="78"/>
-      <c r="D109" s="78"/>
-      <c r="E109" s="78"/>
-      <c r="F109" s="78"/>
-      <c r="G109" s="78"/>
-      <c r="H109" s="78"/>
-      <c r="I109" s="78"/>
-      <c r="J109" s="176"/>
-    </row>
-    <row r="110" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A110" s="28"/>
-      <c r="B110" s="78"/>
-      <c r="C110" s="78"/>
-      <c r="D110" s="78"/>
-      <c r="E110" s="78"/>
-      <c r="F110" s="78"/>
-      <c r="G110" s="78"/>
-      <c r="H110" s="78"/>
-      <c r="I110" s="78"/>
-      <c r="J110" s="176"/>
+      <c r="C110" s="32"/>
+      <c r="D110" s="32"/>
+      <c r="E110" s="32"/>
+      <c r="F110" s="32"/>
+      <c r="G110" s="32"/>
+      <c r="H110" s="32"/>
+      <c r="I110" s="32"/>
+      <c r="J110" s="33"/>
     </row>
     <row r="111" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A111" s="28"/>
-      <c r="B111" s="78"/>
-      <c r="C111" s="78"/>
-      <c r="D111" s="78"/>
-      <c r="E111" s="78"/>
-      <c r="F111" s="78"/>
-      <c r="G111" s="78"/>
-      <c r="H111" s="78"/>
-      <c r="I111" s="78"/>
-      <c r="J111" s="176"/>
+      <c r="A111" s="30"/>
+      <c r="B111" s="34"/>
+      <c r="C111" s="34"/>
+      <c r="D111" s="34"/>
+      <c r="E111" s="34"/>
+      <c r="F111" s="34"/>
+      <c r="G111" s="34"/>
+      <c r="H111" s="34"/>
+      <c r="I111" s="34"/>
+      <c r="J111" s="35"/>
     </row>
     <row r="112" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A112" s="28"/>
-      <c r="B112" s="78"/>
-      <c r="C112" s="78"/>
-      <c r="D112" s="78"/>
-      <c r="E112" s="78"/>
-      <c r="F112" s="78"/>
-      <c r="G112" s="78"/>
-      <c r="H112" s="78"/>
-      <c r="I112" s="78"/>
-      <c r="J112" s="176"/>
+      <c r="A112" s="30"/>
+      <c r="B112" s="34"/>
+      <c r="C112" s="34"/>
+      <c r="D112" s="34"/>
+      <c r="E112" s="34"/>
+      <c r="F112" s="34"/>
+      <c r="G112" s="34"/>
+      <c r="H112" s="34"/>
+      <c r="I112" s="34"/>
+      <c r="J112" s="35"/>
     </row>
     <row r="113" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A113" s="28"/>
-      <c r="B113" s="78"/>
-      <c r="C113" s="78"/>
-      <c r="D113" s="78"/>
-      <c r="E113" s="78"/>
-      <c r="F113" s="78"/>
-      <c r="G113" s="78"/>
-      <c r="H113" s="78"/>
-      <c r="I113" s="78"/>
-      <c r="J113" s="176"/>
+      <c r="A113" s="30"/>
+      <c r="B113" s="34"/>
+      <c r="C113" s="34"/>
+      <c r="D113" s="34"/>
+      <c r="E113" s="34"/>
+      <c r="F113" s="34"/>
+      <c r="G113" s="34"/>
+      <c r="H113" s="34"/>
+      <c r="I113" s="34"/>
+      <c r="J113" s="35"/>
     </row>
     <row r="114" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A114" s="28"/>
-      <c r="B114" s="53" t="s">
+      <c r="A114" s="30"/>
+      <c r="B114" s="34"/>
+      <c r="C114" s="34"/>
+      <c r="D114" s="34"/>
+      <c r="E114" s="34"/>
+      <c r="F114" s="34"/>
+      <c r="G114" s="34"/>
+      <c r="H114" s="34"/>
+      <c r="I114" s="34"/>
+      <c r="J114" s="35"/>
+    </row>
+    <row r="115" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A115" s="30"/>
+      <c r="B115" s="34"/>
+      <c r="C115" s="34"/>
+      <c r="D115" s="34"/>
+      <c r="E115" s="34"/>
+      <c r="F115" s="34"/>
+      <c r="G115" s="34"/>
+      <c r="H115" s="34"/>
+      <c r="I115" s="34"/>
+      <c r="J115" s="35"/>
+    </row>
+    <row r="116" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A116" s="30"/>
+      <c r="B116" s="34"/>
+      <c r="C116" s="34"/>
+      <c r="D116" s="34"/>
+      <c r="E116" s="34"/>
+      <c r="F116" s="34"/>
+      <c r="G116" s="34"/>
+      <c r="H116" s="34"/>
+      <c r="I116" s="34"/>
+      <c r="J116" s="35"/>
+    </row>
+    <row r="117" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A117" s="30"/>
+      <c r="B117" s="36" t="s">
         <v>18</v>
       </c>
-      <c r="C114" s="53"/>
-      <c r="D114" s="53"/>
-      <c r="E114" s="53"/>
-      <c r="F114" s="53"/>
-      <c r="G114" s="53"/>
-      <c r="H114" s="53"/>
-      <c r="I114" s="53"/>
-      <c r="J114" s="54"/>
-    </row>
-    <row r="115" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A115" s="28"/>
-      <c r="B115" s="78"/>
-      <c r="C115" s="78"/>
-      <c r="D115" s="78"/>
-      <c r="E115" s="78"/>
-      <c r="F115" s="78"/>
-      <c r="G115" s="78"/>
-      <c r="H115" s="78"/>
-      <c r="I115" s="78"/>
-      <c r="J115" s="176"/>
-    </row>
-    <row r="116" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A116" s="28"/>
-      <c r="B116" s="78"/>
-      <c r="C116" s="78"/>
-      <c r="D116" s="78"/>
-      <c r="E116" s="78"/>
-      <c r="F116" s="78"/>
-      <c r="G116" s="78"/>
-      <c r="H116" s="78"/>
-      <c r="I116" s="78"/>
-      <c r="J116" s="176"/>
-    </row>
-    <row r="117" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A117" s="28"/>
-      <c r="B117" s="78"/>
-      <c r="C117" s="78"/>
-      <c r="D117" s="78"/>
-      <c r="E117" s="78"/>
-      <c r="F117" s="78"/>
-      <c r="G117" s="78"/>
-      <c r="H117" s="78"/>
-      <c r="I117" s="78"/>
-      <c r="J117" s="176"/>
+      <c r="C117" s="36"/>
+      <c r="D117" s="36"/>
+      <c r="E117" s="36"/>
+      <c r="F117" s="36"/>
+      <c r="G117" s="36"/>
+      <c r="H117" s="36"/>
+      <c r="I117" s="36"/>
+      <c r="J117" s="37"/>
     </row>
     <row r="118" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A118" s="28"/>
-      <c r="B118" s="78"/>
-      <c r="C118" s="78"/>
-      <c r="D118" s="78"/>
-      <c r="E118" s="78"/>
-      <c r="F118" s="78"/>
-      <c r="G118" s="78"/>
-      <c r="H118" s="78"/>
-      <c r="I118" s="78"/>
-      <c r="J118" s="176"/>
+      <c r="A118" s="30"/>
+      <c r="B118" s="34"/>
+      <c r="C118" s="34"/>
+      <c r="D118" s="34"/>
+      <c r="E118" s="34"/>
+      <c r="F118" s="34"/>
+      <c r="G118" s="34"/>
+      <c r="H118" s="34"/>
+      <c r="I118" s="34"/>
+      <c r="J118" s="35"/>
     </row>
     <row r="119" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A119" s="28"/>
-      <c r="B119" s="78"/>
-      <c r="C119" s="78"/>
-      <c r="D119" s="78"/>
-      <c r="E119" s="78"/>
-      <c r="F119" s="78"/>
-      <c r="G119" s="78"/>
-      <c r="H119" s="78"/>
-      <c r="I119" s="78"/>
-      <c r="J119" s="176"/>
+      <c r="A119" s="30"/>
+      <c r="B119" s="34"/>
+      <c r="C119" s="34"/>
+      <c r="D119" s="34"/>
+      <c r="E119" s="34"/>
+      <c r="F119" s="34"/>
+      <c r="G119" s="34"/>
+      <c r="H119" s="34"/>
+      <c r="I119" s="34"/>
+      <c r="J119" s="35"/>
     </row>
     <row r="120" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A120" s="28"/>
-      <c r="B120" s="78"/>
-      <c r="C120" s="78"/>
-      <c r="D120" s="78"/>
-      <c r="E120" s="78"/>
-      <c r="F120" s="78"/>
-      <c r="G120" s="78"/>
-      <c r="H120" s="78"/>
-      <c r="I120" s="78"/>
-      <c r="J120" s="176"/>
+      <c r="A120" s="30"/>
+      <c r="B120" s="34"/>
+      <c r="C120" s="34"/>
+      <c r="D120" s="34"/>
+      <c r="E120" s="34"/>
+      <c r="F120" s="34"/>
+      <c r="G120" s="34"/>
+      <c r="H120" s="34"/>
+      <c r="I120" s="34"/>
+      <c r="J120" s="35"/>
     </row>
     <row r="121" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A121" s="28"/>
-      <c r="B121" s="78"/>
-      <c r="C121" s="78"/>
-      <c r="D121" s="78"/>
-      <c r="E121" s="78"/>
-      <c r="F121" s="78"/>
-      <c r="G121" s="78"/>
-      <c r="H121" s="78"/>
-      <c r="I121" s="78"/>
-      <c r="J121" s="176"/>
-    </row>
-    <row r="122" spans="1:10" ht="13.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A122" s="29"/>
-      <c r="B122" s="177"/>
-      <c r="C122" s="177"/>
-      <c r="D122" s="177"/>
-      <c r="E122" s="177"/>
-      <c r="F122" s="177"/>
-      <c r="G122" s="177"/>
-      <c r="H122" s="177"/>
-      <c r="I122" s="177"/>
-      <c r="J122" s="178"/>
+      <c r="A121" s="30"/>
+      <c r="B121" s="34"/>
+      <c r="C121" s="34"/>
+      <c r="D121" s="34"/>
+      <c r="E121" s="34"/>
+      <c r="F121" s="34"/>
+      <c r="G121" s="34"/>
+      <c r="H121" s="34"/>
+      <c r="I121" s="34"/>
+      <c r="J121" s="35"/>
+    </row>
+    <row r="122" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A122" s="30"/>
+      <c r="B122" s="34"/>
+      <c r="C122" s="34"/>
+      <c r="D122" s="34"/>
+      <c r="E122" s="34"/>
+      <c r="F122" s="34"/>
+      <c r="G122" s="34"/>
+      <c r="H122" s="34"/>
+      <c r="I122" s="34"/>
+      <c r="J122" s="35"/>
+    </row>
+    <row r="123" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A123" s="30"/>
+      <c r="B123" s="34"/>
+      <c r="C123" s="34"/>
+      <c r="D123" s="34"/>
+      <c r="E123" s="34"/>
+      <c r="F123" s="34"/>
+      <c r="G123" s="34"/>
+      <c r="H123" s="34"/>
+      <c r="I123" s="34"/>
+      <c r="J123" s="35"/>
+    </row>
+    <row r="124" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A124" s="30"/>
+      <c r="B124" s="34"/>
+      <c r="C124" s="34"/>
+      <c r="D124" s="34"/>
+      <c r="E124" s="34"/>
+      <c r="F124" s="34"/>
+      <c r="G124" s="34"/>
+      <c r="H124" s="34"/>
+      <c r="I124" s="34"/>
+      <c r="J124" s="35"/>
+    </row>
+    <row r="125" spans="1:10" ht="13.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A125" s="31"/>
+      <c r="B125" s="38"/>
+      <c r="C125" s="38"/>
+      <c r="D125" s="38"/>
+      <c r="E125" s="38"/>
+      <c r="F125" s="38"/>
+      <c r="G125" s="38"/>
+      <c r="H125" s="38"/>
+      <c r="I125" s="38"/>
+      <c r="J125" s="39"/>
     </row>
   </sheetData>
   <mergeCells count="39">
-    <mergeCell ref="A1:J1"/>
-    <mergeCell ref="A105:A106"/>
-    <mergeCell ref="A107:A122"/>
-    <mergeCell ref="B107:J107"/>
-    <mergeCell ref="B108:J113"/>
-    <mergeCell ref="B114:J114"/>
-    <mergeCell ref="B115:J122"/>
-    <mergeCell ref="B106:J106"/>
-    <mergeCell ref="B105:J105"/>
-    <mergeCell ref="B86:J86"/>
-    <mergeCell ref="A86:A104"/>
-    <mergeCell ref="B87:J89"/>
-    <mergeCell ref="A84:A85"/>
-    <mergeCell ref="B84:J84"/>
-    <mergeCell ref="B85:J85"/>
-    <mergeCell ref="B90:J104"/>
-    <mergeCell ref="B66:J83"/>
-    <mergeCell ref="A60:A83"/>
-    <mergeCell ref="D61:J61"/>
-    <mergeCell ref="B5:J7"/>
-    <mergeCell ref="B19:J22"/>
-    <mergeCell ref="B23:J59"/>
-    <mergeCell ref="B18:J18"/>
-    <mergeCell ref="B65:J65"/>
-    <mergeCell ref="B8:J17"/>
-    <mergeCell ref="B60:J60"/>
-    <mergeCell ref="D64:J64"/>
+    <mergeCell ref="A21:A62"/>
     <mergeCell ref="B64:C64"/>
-    <mergeCell ref="D63:J63"/>
-    <mergeCell ref="B63:C63"/>
-    <mergeCell ref="D62:J62"/>
-    <mergeCell ref="B62:C62"/>
-    <mergeCell ref="A18:A59"/>
-    <mergeCell ref="B61:C61"/>
     <mergeCell ref="A2:A3"/>
-    <mergeCell ref="A4:A17"/>
+    <mergeCell ref="A4:A20"/>
     <mergeCell ref="B4:J4"/>
     <mergeCell ref="B2:D3"/>
     <mergeCell ref="E2:J3"/>
+    <mergeCell ref="B69:J86"/>
+    <mergeCell ref="A63:A86"/>
+    <mergeCell ref="D64:J64"/>
+    <mergeCell ref="B5:J7"/>
+    <mergeCell ref="B22:J25"/>
+    <mergeCell ref="B26:J62"/>
+    <mergeCell ref="B21:J21"/>
+    <mergeCell ref="B68:J68"/>
+    <mergeCell ref="B8:J20"/>
+    <mergeCell ref="B63:J63"/>
+    <mergeCell ref="D67:J67"/>
+    <mergeCell ref="B67:C67"/>
+    <mergeCell ref="D66:J66"/>
+    <mergeCell ref="B66:C66"/>
+    <mergeCell ref="D65:J65"/>
+    <mergeCell ref="B65:C65"/>
+    <mergeCell ref="A1:J1"/>
+    <mergeCell ref="A108:A109"/>
+    <mergeCell ref="A110:A125"/>
+    <mergeCell ref="B110:J110"/>
+    <mergeCell ref="B111:J116"/>
+    <mergeCell ref="B117:J117"/>
+    <mergeCell ref="B118:J125"/>
+    <mergeCell ref="B109:J109"/>
+    <mergeCell ref="B108:J108"/>
+    <mergeCell ref="B89:J89"/>
+    <mergeCell ref="A89:A107"/>
+    <mergeCell ref="B90:J92"/>
+    <mergeCell ref="A87:A88"/>
+    <mergeCell ref="B87:J87"/>
+    <mergeCell ref="B88:J88"/>
+    <mergeCell ref="B93:J107"/>
   </mergeCells>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.75" right="0.75" top="0.6" bottom="0.61" header="0.4" footer="0.39"/>
@@ -4978,8 +4997,8 @@
     <oddFooter>&amp;C&amp;P / &amp;N ページ</oddFooter>
   </headerFooter>
   <rowBreaks count="2" manualBreakCount="2">
-    <brk id="59" max="16383" man="1"/>
-    <brk id="104" max="16383" man="1"/>
+    <brk id="62" max="16383" man="1"/>
+    <brk id="107" max="16383" man="1"/>
   </rowBreaks>
 </worksheet>
 </file>
@@ -4998,71 +5017,71 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="35" t="s">
+      <c r="A1" s="77" t="s">
         <v>19</v>
       </c>
-      <c r="B1" s="35"/>
-      <c r="C1" s="35"/>
+      <c r="B1" s="77"/>
+      <c r="C1" s="77"/>
     </row>
     <row r="2" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="67" t="s">
+      <c r="A2" s="85" t="s">
         <v>20</v>
       </c>
-      <c r="B2" s="67"/>
-      <c r="C2" s="67"/>
-      <c r="D2" s="67"/>
-      <c r="E2" s="67"/>
-      <c r="F2" s="67"/>
-      <c r="G2" s="67"/>
-      <c r="H2" s="67"/>
+      <c r="B2" s="85"/>
+      <c r="C2" s="85"/>
+      <c r="D2" s="85"/>
+      <c r="E2" s="85"/>
+      <c r="F2" s="85"/>
+      <c r="G2" s="85"/>
+      <c r="H2" s="85"/>
     </row>
     <row r="3" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="67"/>
-      <c r="B3" s="67"/>
-      <c r="C3" s="67"/>
-      <c r="D3" s="67"/>
-      <c r="E3" s="67"/>
-      <c r="F3" s="67"/>
-      <c r="G3" s="67"/>
-      <c r="H3" s="67"/>
+      <c r="A3" s="85"/>
+      <c r="B3" s="85"/>
+      <c r="C3" s="85"/>
+      <c r="D3" s="85"/>
+      <c r="E3" s="85"/>
+      <c r="F3" s="85"/>
+      <c r="G3" s="85"/>
+      <c r="H3" s="85"/>
     </row>
     <row r="4" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="67"/>
-      <c r="B4" s="67"/>
-      <c r="C4" s="67"/>
-      <c r="D4" s="67"/>
-      <c r="E4" s="67"/>
-      <c r="F4" s="67"/>
-      <c r="G4" s="67"/>
-      <c r="H4" s="67"/>
+      <c r="A4" s="85"/>
+      <c r="B4" s="85"/>
+      <c r="C4" s="85"/>
+      <c r="D4" s="85"/>
+      <c r="E4" s="85"/>
+      <c r="F4" s="85"/>
+      <c r="G4" s="85"/>
+      <c r="H4" s="85"/>
     </row>
     <row r="5" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="56"/>
-      <c r="B5" s="56"/>
-      <c r="C5" s="56"/>
+      <c r="A5" s="49"/>
+      <c r="B5" s="49"/>
+      <c r="C5" s="49"/>
     </row>
     <row r="6" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="66" t="s">
+      <c r="A6" s="84" t="s">
         <v>21</v>
       </c>
-      <c r="B6" s="66" t="s">
+      <c r="B6" s="84" t="s">
         <v>22</v>
       </c>
-      <c r="C6" s="66"/>
-      <c r="D6" s="66"/>
-      <c r="E6" s="66" t="s">
+      <c r="C6" s="84"/>
+      <c r="D6" s="84"/>
+      <c r="E6" s="84" t="s">
         <v>23</v>
       </c>
-      <c r="F6" s="68" t="s">
+      <c r="F6" s="86" t="s">
         <v>24</v>
       </c>
-      <c r="G6" s="69"/>
-      <c r="H6" s="72" t="s">
+      <c r="G6" s="87"/>
+      <c r="H6" s="90" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="7" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="66"/>
+      <c r="A7" s="84"/>
       <c r="B7" s="23" t="s">
         <v>26</v>
       </c>
@@ -5072,19 +5091,19 @@
       <c r="D7" s="23" t="s">
         <v>28</v>
       </c>
-      <c r="E7" s="66"/>
-      <c r="F7" s="70"/>
-      <c r="G7" s="71"/>
-      <c r="H7" s="73"/>
+      <c r="E7" s="84"/>
+      <c r="F7" s="88"/>
+      <c r="G7" s="89"/>
+      <c r="H7" s="91"/>
     </row>
     <row r="8" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="4">
         <v>1</v>
       </c>
-      <c r="B8" s="58" t="s">
+      <c r="B8" s="62" t="s">
         <v>29</v>
       </c>
-      <c r="C8" s="61" t="s">
+      <c r="C8" s="94" t="s">
         <v>30</v>
       </c>
       <c r="D8" s="4" t="s">
@@ -5093,10 +5112,10 @@
       <c r="E8" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="F8" s="63" t="s">
+      <c r="F8" s="82" t="s">
         <v>32</v>
       </c>
-      <c r="G8" s="64"/>
+      <c r="G8" s="83"/>
       <c r="H8" s="22" t="s">
         <v>33</v>
       </c>
@@ -5105,18 +5124,18 @@
       <c r="A9" s="4">
         <v>2</v>
       </c>
-      <c r="B9" s="60"/>
-      <c r="C9" s="62"/>
+      <c r="B9" s="92"/>
+      <c r="C9" s="95"/>
       <c r="D9" s="4" t="s">
         <v>34</v>
       </c>
       <c r="E9" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="F9" s="63" t="s">
+      <c r="F9" s="82" t="s">
         <v>32</v>
       </c>
-      <c r="G9" s="64"/>
+      <c r="G9" s="83"/>
       <c r="H9" s="22" t="s">
         <v>35</v>
       </c>
@@ -5125,8 +5144,8 @@
       <c r="A10" s="4">
         <v>3</v>
       </c>
-      <c r="B10" s="60"/>
-      <c r="C10" s="58" t="s">
+      <c r="B10" s="92"/>
+      <c r="C10" s="62" t="s">
         <v>36</v>
       </c>
       <c r="D10" s="4" t="s">
@@ -5135,10 +5154,10 @@
       <c r="E10" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="F10" s="63" t="s">
+      <c r="F10" s="82" t="s">
         <v>32</v>
       </c>
-      <c r="G10" s="64"/>
+      <c r="G10" s="83"/>
       <c r="H10" s="22" t="s">
         <v>35</v>
       </c>
@@ -5147,18 +5166,18 @@
       <c r="A11" s="4">
         <v>4</v>
       </c>
-      <c r="B11" s="59"/>
-      <c r="C11" s="59"/>
+      <c r="B11" s="93"/>
+      <c r="C11" s="93"/>
       <c r="D11" s="4" t="s">
         <v>38</v>
       </c>
       <c r="E11" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="F11" s="63" t="s">
+      <c r="F11" s="82" t="s">
         <v>32</v>
       </c>
-      <c r="G11" s="64"/>
+      <c r="G11" s="83"/>
       <c r="H11" s="22" t="s">
         <v>35</v>
       </c>
@@ -5167,7 +5186,7 @@
       <c r="A12" s="4">
         <v>5</v>
       </c>
-      <c r="B12" s="58" t="s">
+      <c r="B12" s="62" t="s">
         <v>39</v>
       </c>
       <c r="C12" s="4" t="s">
@@ -5177,10 +5196,10 @@
       <c r="E12" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="F12" s="63" t="s">
+      <c r="F12" s="82" t="s">
         <v>32</v>
       </c>
-      <c r="G12" s="64"/>
+      <c r="G12" s="83"/>
       <c r="H12" s="22" t="s">
         <v>33</v>
       </c>
@@ -5189,7 +5208,7 @@
       <c r="A13" s="4">
         <v>6</v>
       </c>
-      <c r="B13" s="59"/>
+      <c r="B13" s="93"/>
       <c r="C13" s="4" t="s">
         <v>41</v>
       </c>
@@ -5197,10 +5216,10 @@
       <c r="E13" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="F13" s="63" t="s">
+      <c r="F13" s="82" t="s">
         <v>32</v>
       </c>
-      <c r="G13" s="65"/>
+      <c r="G13" s="96"/>
       <c r="H13" s="22" t="s">
         <v>33</v>
       </c>
@@ -5209,7 +5228,7 @@
       <c r="A14" s="4">
         <v>7</v>
       </c>
-      <c r="B14" s="58" t="s">
+      <c r="B14" s="62" t="s">
         <v>42</v>
       </c>
       <c r="C14" s="4" t="s">
@@ -5219,10 +5238,10 @@
       <c r="E14" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="F14" s="63" t="s">
+      <c r="F14" s="82" t="s">
         <v>32</v>
       </c>
-      <c r="G14" s="64"/>
+      <c r="G14" s="83"/>
       <c r="H14" s="22" t="s">
         <v>33</v>
       </c>
@@ -5231,7 +5250,7 @@
       <c r="A15" s="4">
         <v>8</v>
       </c>
-      <c r="B15" s="59"/>
+      <c r="B15" s="93"/>
       <c r="C15" s="4" t="s">
         <v>44</v>
       </c>
@@ -5239,10 +5258,10 @@
       <c r="E15" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="F15" s="63" t="s">
+      <c r="F15" s="82" t="s">
         <v>32</v>
       </c>
-      <c r="G15" s="64"/>
+      <c r="G15" s="83"/>
       <c r="H15" s="22" t="s">
         <v>35</v>
       </c>
@@ -5251,7 +5270,7 @@
       <c r="A16" s="4">
         <v>9</v>
       </c>
-      <c r="B16" s="58" t="s">
+      <c r="B16" s="62" t="s">
         <v>45</v>
       </c>
       <c r="C16" s="4" t="s">
@@ -5261,10 +5280,10 @@
       <c r="E16" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="F16" s="63" t="s">
+      <c r="F16" s="82" t="s">
         <v>32</v>
       </c>
-      <c r="G16" s="64"/>
+      <c r="G16" s="83"/>
       <c r="H16" s="22" t="s">
         <v>35</v>
       </c>
@@ -5273,7 +5292,7 @@
       <c r="A17" s="4">
         <v>10</v>
       </c>
-      <c r="B17" s="59"/>
+      <c r="B17" s="93"/>
       <c r="C17" s="4" t="s">
         <v>48</v>
       </c>
@@ -5281,10 +5300,10 @@
       <c r="E17" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="F17" s="63" t="s">
+      <c r="F17" s="82" t="s">
         <v>32</v>
       </c>
-      <c r="G17" s="64"/>
+      <c r="G17" s="83"/>
       <c r="H17" s="22" t="s">
         <v>35</v>
       </c>
@@ -5293,7 +5312,7 @@
       <c r="A18" s="4">
         <v>11</v>
       </c>
-      <c r="B18" s="58" t="s">
+      <c r="B18" s="62" t="s">
         <v>49</v>
       </c>
       <c r="C18" s="4" t="s">
@@ -5303,10 +5322,10 @@
       <c r="E18" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="F18" s="63" t="s">
+      <c r="F18" s="82" t="s">
         <v>32</v>
       </c>
-      <c r="G18" s="64"/>
+      <c r="G18" s="83"/>
       <c r="H18" s="22" t="s">
         <v>33</v>
       </c>
@@ -5315,7 +5334,7 @@
       <c r="A19" s="4">
         <v>12</v>
       </c>
-      <c r="B19" s="59"/>
+      <c r="B19" s="93"/>
       <c r="C19" s="4" t="s">
         <v>49</v>
       </c>
@@ -5323,10 +5342,10 @@
       <c r="E19" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="F19" s="63" t="s">
+      <c r="F19" s="82" t="s">
         <v>32</v>
       </c>
-      <c r="G19" s="64"/>
+      <c r="G19" s="83"/>
       <c r="H19" s="22" t="s">
         <v>33</v>
       </c>
@@ -5335,7 +5354,7 @@
       <c r="A20" s="4">
         <v>13</v>
       </c>
-      <c r="B20" s="58" t="s">
+      <c r="B20" s="62" t="s">
         <v>51</v>
       </c>
       <c r="C20" s="4" t="s">
@@ -5345,10 +5364,10 @@
       <c r="E20" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="F20" s="63" t="s">
+      <c r="F20" s="82" t="s">
         <v>32</v>
       </c>
-      <c r="G20" s="64"/>
+      <c r="G20" s="83"/>
       <c r="H20" s="22" t="s">
         <v>35</v>
       </c>
@@ -5357,7 +5376,7 @@
       <c r="A21" s="4">
         <v>14</v>
       </c>
-      <c r="B21" s="59"/>
+      <c r="B21" s="93"/>
       <c r="C21" s="4" t="s">
         <v>53</v>
       </c>
@@ -5365,10 +5384,10 @@
       <c r="E21" s="4" t="s">
         <v>54</v>
       </c>
-      <c r="F21" s="63" t="s">
+      <c r="F21" s="82" t="s">
         <v>32</v>
       </c>
-      <c r="G21" s="64"/>
+      <c r="G21" s="83"/>
       <c r="H21" s="22" t="s">
         <v>35</v>
       </c>
@@ -5377,7 +5396,7 @@
       <c r="A22" s="4">
         <v>15</v>
       </c>
-      <c r="B22" s="58" t="s">
+      <c r="B22" s="62" t="s">
         <v>55</v>
       </c>
       <c r="C22" s="4" t="s">
@@ -5387,10 +5406,10 @@
       <c r="E22" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="F22" s="63" t="s">
+      <c r="F22" s="82" t="s">
         <v>32</v>
       </c>
-      <c r="G22" s="64"/>
+      <c r="G22" s="83"/>
       <c r="H22" s="22" t="s">
         <v>33</v>
       </c>
@@ -5399,7 +5418,7 @@
       <c r="A23" s="4">
         <v>16</v>
       </c>
-      <c r="B23" s="59"/>
+      <c r="B23" s="93"/>
       <c r="C23" s="4" t="s">
         <v>57</v>
       </c>
@@ -5407,10 +5426,10 @@
       <c r="E23" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="F23" s="63" t="s">
+      <c r="F23" s="82" t="s">
         <v>32</v>
       </c>
-      <c r="G23" s="64"/>
+      <c r="G23" s="83"/>
       <c r="H23" s="22" t="s">
         <v>33</v>
       </c>
@@ -5423,8 +5442,8 @@
       <c r="C24" s="4"/>
       <c r="D24" s="4"/>
       <c r="E24" s="4"/>
-      <c r="F24" s="63"/>
-      <c r="G24" s="64"/>
+      <c r="F24" s="82"/>
+      <c r="G24" s="83"/>
       <c r="H24" s="4"/>
     </row>
     <row r="25" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -5435,8 +5454,8 @@
       <c r="C25" s="4"/>
       <c r="D25" s="4"/>
       <c r="E25" s="4"/>
-      <c r="F25" s="63"/>
-      <c r="G25" s="64"/>
+      <c r="F25" s="82"/>
+      <c r="G25" s="83"/>
       <c r="H25" s="4"/>
     </row>
     <row r="26" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -5447,8 +5466,8 @@
       <c r="C26" s="4"/>
       <c r="D26" s="4"/>
       <c r="E26" s="4"/>
-      <c r="F26" s="63"/>
-      <c r="G26" s="64"/>
+      <c r="F26" s="82"/>
+      <c r="G26" s="83"/>
       <c r="H26" s="4"/>
     </row>
     <row r="27" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -5459,8 +5478,8 @@
       <c r="C27" s="4"/>
       <c r="D27" s="4"/>
       <c r="E27" s="4"/>
-      <c r="F27" s="63"/>
-      <c r="G27" s="64"/>
+      <c r="F27" s="82"/>
+      <c r="G27" s="83"/>
       <c r="H27" s="4"/>
     </row>
     <row r="28" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -5471,8 +5490,8 @@
       <c r="C28" s="4"/>
       <c r="D28" s="4"/>
       <c r="E28" s="4"/>
-      <c r="F28" s="63"/>
-      <c r="G28" s="64"/>
+      <c r="F28" s="82"/>
+      <c r="G28" s="83"/>
       <c r="H28" s="4"/>
     </row>
     <row r="29" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -5483,8 +5502,8 @@
       <c r="C29" s="4"/>
       <c r="D29" s="4"/>
       <c r="E29" s="4"/>
-      <c r="F29" s="63"/>
-      <c r="G29" s="64"/>
+      <c r="F29" s="82"/>
+      <c r="G29" s="83"/>
       <c r="H29" s="4"/>
     </row>
     <row r="30" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -5495,8 +5514,8 @@
       <c r="C30" s="4"/>
       <c r="D30" s="4"/>
       <c r="E30" s="4"/>
-      <c r="F30" s="63"/>
-      <c r="G30" s="64"/>
+      <c r="F30" s="82"/>
+      <c r="G30" s="83"/>
       <c r="H30" s="4"/>
     </row>
     <row r="31" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -5507,8 +5526,8 @@
       <c r="C31" s="4"/>
       <c r="D31" s="4"/>
       <c r="E31" s="4"/>
-      <c r="F31" s="63"/>
-      <c r="G31" s="64"/>
+      <c r="F31" s="82"/>
+      <c r="G31" s="83"/>
       <c r="H31" s="4"/>
     </row>
     <row r="32" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -5519,8 +5538,8 @@
       <c r="C32" s="4"/>
       <c r="D32" s="4"/>
       <c r="E32" s="4"/>
-      <c r="F32" s="63"/>
-      <c r="G32" s="64"/>
+      <c r="F32" s="82"/>
+      <c r="G32" s="83"/>
       <c r="H32" s="4"/>
     </row>
     <row r="33" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -5531,8 +5550,8 @@
       <c r="C33" s="4"/>
       <c r="D33" s="4"/>
       <c r="E33" s="4"/>
-      <c r="F33" s="63"/>
-      <c r="G33" s="64"/>
+      <c r="F33" s="82"/>
+      <c r="G33" s="83"/>
       <c r="H33" s="4"/>
     </row>
     <row r="34" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -5543,8 +5562,8 @@
       <c r="C34" s="4"/>
       <c r="D34" s="4"/>
       <c r="E34" s="4"/>
-      <c r="F34" s="63"/>
-      <c r="G34" s="64"/>
+      <c r="F34" s="82"/>
+      <c r="G34" s="83"/>
       <c r="H34" s="4"/>
     </row>
     <row r="35" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -5555,8 +5574,8 @@
       <c r="C35" s="4"/>
       <c r="D35" s="4"/>
       <c r="E35" s="4"/>
-      <c r="F35" s="63"/>
-      <c r="G35" s="64"/>
+      <c r="F35" s="82"/>
+      <c r="G35" s="83"/>
       <c r="H35" s="4"/>
     </row>
     <row r="36" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -5567,8 +5586,8 @@
       <c r="C36" s="4"/>
       <c r="D36" s="4"/>
       <c r="E36" s="4"/>
-      <c r="F36" s="63"/>
-      <c r="G36" s="64"/>
+      <c r="F36" s="82"/>
+      <c r="G36" s="83"/>
       <c r="H36" s="4"/>
     </row>
     <row r="37" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -5579,40 +5598,18 @@
       <c r="C37" s="4"/>
       <c r="D37" s="4"/>
       <c r="E37" s="4"/>
-      <c r="F37" s="63"/>
-      <c r="G37" s="64"/>
+      <c r="F37" s="82"/>
+      <c r="G37" s="83"/>
       <c r="H37" s="4"/>
     </row>
   </sheetData>
   <mergeCells count="47">
-    <mergeCell ref="F33:G33"/>
-    <mergeCell ref="F34:G34"/>
-    <mergeCell ref="F35:G35"/>
-    <mergeCell ref="F36:G36"/>
-    <mergeCell ref="F37:G37"/>
-    <mergeCell ref="F28:G28"/>
-    <mergeCell ref="F29:G29"/>
-    <mergeCell ref="F30:G30"/>
-    <mergeCell ref="F31:G31"/>
-    <mergeCell ref="F32:G32"/>
-    <mergeCell ref="F23:G23"/>
-    <mergeCell ref="F24:G24"/>
-    <mergeCell ref="F25:G25"/>
-    <mergeCell ref="F26:G26"/>
-    <mergeCell ref="F27:G27"/>
-    <mergeCell ref="F18:G18"/>
-    <mergeCell ref="F19:G19"/>
-    <mergeCell ref="F20:G20"/>
-    <mergeCell ref="F21:G21"/>
-    <mergeCell ref="F22:G22"/>
-    <mergeCell ref="A1:C1"/>
-    <mergeCell ref="A5:C5"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="B6:D6"/>
-    <mergeCell ref="E6:E7"/>
-    <mergeCell ref="A2:H4"/>
-    <mergeCell ref="F6:G7"/>
-    <mergeCell ref="H6:H7"/>
+    <mergeCell ref="B20:B21"/>
+    <mergeCell ref="B22:B23"/>
+    <mergeCell ref="B12:B13"/>
+    <mergeCell ref="B14:B15"/>
+    <mergeCell ref="B16:B17"/>
+    <mergeCell ref="B18:B19"/>
     <mergeCell ref="B8:B11"/>
     <mergeCell ref="C8:C9"/>
     <mergeCell ref="C10:C11"/>
@@ -5626,12 +5623,34 @@
     <mergeCell ref="F11:G11"/>
     <mergeCell ref="F12:G12"/>
     <mergeCell ref="F13:G13"/>
-    <mergeCell ref="B20:B21"/>
-    <mergeCell ref="B22:B23"/>
-    <mergeCell ref="B12:B13"/>
-    <mergeCell ref="B14:B15"/>
-    <mergeCell ref="B16:B17"/>
-    <mergeCell ref="B18:B19"/>
+    <mergeCell ref="A1:C1"/>
+    <mergeCell ref="A5:C5"/>
+    <mergeCell ref="A6:A7"/>
+    <mergeCell ref="B6:D6"/>
+    <mergeCell ref="E6:E7"/>
+    <mergeCell ref="A2:H4"/>
+    <mergeCell ref="F6:G7"/>
+    <mergeCell ref="H6:H7"/>
+    <mergeCell ref="F18:G18"/>
+    <mergeCell ref="F19:G19"/>
+    <mergeCell ref="F20:G20"/>
+    <mergeCell ref="F21:G21"/>
+    <mergeCell ref="F22:G22"/>
+    <mergeCell ref="F23:G23"/>
+    <mergeCell ref="F24:G24"/>
+    <mergeCell ref="F25:G25"/>
+    <mergeCell ref="F26:G26"/>
+    <mergeCell ref="F27:G27"/>
+    <mergeCell ref="F28:G28"/>
+    <mergeCell ref="F29:G29"/>
+    <mergeCell ref="F30:G30"/>
+    <mergeCell ref="F31:G31"/>
+    <mergeCell ref="F32:G32"/>
+    <mergeCell ref="F33:G33"/>
+    <mergeCell ref="F34:G34"/>
+    <mergeCell ref="F35:G35"/>
+    <mergeCell ref="F36:G36"/>
+    <mergeCell ref="F37:G37"/>
   </mergeCells>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.75" right="0.75" top="0.6" bottom="0.61" header="0.4" footer="0.39"/>
@@ -5658,90 +5677,90 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="79" t="s">
+      <c r="A1" s="97" t="s">
         <v>58</v>
       </c>
-      <c r="B1" s="80"/>
-      <c r="C1" s="81"/>
+      <c r="B1" s="98"/>
+      <c r="C1" s="99"/>
       <c r="D1" s="19"/>
     </row>
     <row r="2" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="67" t="s">
+      <c r="A2" s="85" t="s">
         <v>59</v>
       </c>
-      <c r="B2" s="67"/>
-      <c r="C2" s="67"/>
-      <c r="D2" s="67"/>
-      <c r="E2" s="67"/>
-      <c r="F2" s="67"/>
-      <c r="G2" s="67"/>
-      <c r="H2" s="67"/>
-      <c r="I2" s="67"/>
+      <c r="B2" s="85"/>
+      <c r="C2" s="85"/>
+      <c r="D2" s="85"/>
+      <c r="E2" s="85"/>
+      <c r="F2" s="85"/>
+      <c r="G2" s="85"/>
+      <c r="H2" s="85"/>
+      <c r="I2" s="85"/>
     </row>
     <row r="3" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="67"/>
-      <c r="B3" s="67"/>
-      <c r="C3" s="67"/>
-      <c r="D3" s="67"/>
-      <c r="E3" s="67"/>
-      <c r="F3" s="67"/>
-      <c r="G3" s="67"/>
-      <c r="H3" s="67"/>
-      <c r="I3" s="67"/>
+      <c r="A3" s="85"/>
+      <c r="B3" s="85"/>
+      <c r="C3" s="85"/>
+      <c r="D3" s="85"/>
+      <c r="E3" s="85"/>
+      <c r="F3" s="85"/>
+      <c r="G3" s="85"/>
+      <c r="H3" s="85"/>
+      <c r="I3" s="85"/>
     </row>
     <row r="4" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="56"/>
-      <c r="B4" s="56"/>
+      <c r="A4" s="49"/>
+      <c r="B4" s="49"/>
     </row>
     <row r="5" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="66" t="s">
+      <c r="A5" s="84" t="s">
         <v>21</v>
       </c>
-      <c r="B5" s="72" t="s">
+      <c r="B5" s="90" t="s">
         <v>60</v>
       </c>
-      <c r="C5" s="72" t="s">
+      <c r="C5" s="90" t="s">
         <v>61</v>
       </c>
-      <c r="D5" s="68" t="s">
+      <c r="D5" s="86" t="s">
         <v>24</v>
       </c>
-      <c r="E5" s="69"/>
-      <c r="F5" s="69"/>
-      <c r="G5" s="69"/>
-      <c r="H5" s="69"/>
-      <c r="I5" s="66" t="s">
+      <c r="E5" s="87"/>
+      <c r="F5" s="87"/>
+      <c r="G5" s="87"/>
+      <c r="H5" s="87"/>
+      <c r="I5" s="84" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="6" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="66"/>
-      <c r="B6" s="73"/>
-      <c r="C6" s="73"/>
-      <c r="D6" s="70"/>
-      <c r="E6" s="71"/>
-      <c r="F6" s="71"/>
-      <c r="G6" s="71"/>
-      <c r="H6" s="71"/>
-      <c r="I6" s="66"/>
+      <c r="A6" s="84"/>
+      <c r="B6" s="91"/>
+      <c r="C6" s="91"/>
+      <c r="D6" s="88"/>
+      <c r="E6" s="89"/>
+      <c r="F6" s="89"/>
+      <c r="G6" s="89"/>
+      <c r="H6" s="89"/>
+      <c r="I6" s="84"/>
     </row>
     <row r="7" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="4">
         <v>1</v>
       </c>
-      <c r="B7" s="74" t="s">
+      <c r="B7" s="103" t="s">
         <v>62</v>
       </c>
       <c r="C7" s="22" t="s">
         <v>63</v>
       </c>
-      <c r="D7" s="78" t="s">
+      <c r="D7" s="34" t="s">
         <v>32</v>
       </c>
-      <c r="E7" s="78"/>
-      <c r="F7" s="78"/>
-      <c r="G7" s="78"/>
-      <c r="H7" s="78"/>
+      <c r="E7" s="34"/>
+      <c r="F7" s="34"/>
+      <c r="G7" s="34"/>
+      <c r="H7" s="34"/>
       <c r="I7" s="22" t="s">
         <v>64</v>
       </c>
@@ -5750,15 +5769,15 @@
       <c r="A8" s="4">
         <v>2</v>
       </c>
-      <c r="B8" s="75"/>
+      <c r="B8" s="101"/>
       <c r="C8" s="22"/>
-      <c r="D8" s="78" t="s">
+      <c r="D8" s="34" t="s">
         <v>65</v>
       </c>
-      <c r="E8" s="78"/>
-      <c r="F8" s="78"/>
-      <c r="G8" s="78"/>
-      <c r="H8" s="78"/>
+      <c r="E8" s="34"/>
+      <c r="F8" s="34"/>
+      <c r="G8" s="34"/>
+      <c r="H8" s="34"/>
       <c r="I8" s="22" t="s">
         <v>66</v>
       </c>
@@ -5767,45 +5786,45 @@
       <c r="A9" s="4">
         <v>3</v>
       </c>
-      <c r="B9" s="75"/>
+      <c r="B9" s="101"/>
       <c r="C9" s="22"/>
-      <c r="D9" s="78"/>
-      <c r="E9" s="78"/>
-      <c r="F9" s="78"/>
-      <c r="G9" s="78"/>
-      <c r="H9" s="78"/>
+      <c r="D9" s="34"/>
+      <c r="E9" s="34"/>
+      <c r="F9" s="34"/>
+      <c r="G9" s="34"/>
+      <c r="H9" s="34"/>
       <c r="I9" s="4"/>
     </row>
     <row r="10" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="4">
         <v>4</v>
       </c>
-      <c r="B10" s="76"/>
+      <c r="B10" s="102"/>
       <c r="C10" s="22"/>
-      <c r="D10" s="78"/>
-      <c r="E10" s="78"/>
-      <c r="F10" s="78"/>
-      <c r="G10" s="78"/>
-      <c r="H10" s="78"/>
+      <c r="D10" s="34"/>
+      <c r="E10" s="34"/>
+      <c r="F10" s="34"/>
+      <c r="G10" s="34"/>
+      <c r="H10" s="34"/>
       <c r="I10" s="4"/>
     </row>
     <row r="11" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="4">
         <v>5</v>
       </c>
-      <c r="B11" s="77" t="s">
+      <c r="B11" s="100" t="s">
         <v>67</v>
       </c>
       <c r="C11" s="22" t="s">
         <v>68</v>
       </c>
-      <c r="D11" s="78" t="s">
+      <c r="D11" s="34" t="s">
         <v>32</v>
       </c>
-      <c r="E11" s="78"/>
-      <c r="F11" s="78"/>
-      <c r="G11" s="78"/>
-      <c r="H11" s="78"/>
+      <c r="E11" s="34"/>
+      <c r="F11" s="34"/>
+      <c r="G11" s="34"/>
+      <c r="H11" s="34"/>
       <c r="I11" s="22" t="s">
         <v>66</v>
       </c>
@@ -5814,15 +5833,15 @@
       <c r="A12" s="4">
         <v>6</v>
       </c>
-      <c r="B12" s="75"/>
+      <c r="B12" s="101"/>
       <c r="C12" s="4"/>
-      <c r="D12" s="78" t="s">
+      <c r="D12" s="34" t="s">
         <v>69</v>
       </c>
-      <c r="E12" s="78"/>
-      <c r="F12" s="78"/>
-      <c r="G12" s="78"/>
-      <c r="H12" s="78"/>
+      <c r="E12" s="34"/>
+      <c r="F12" s="34"/>
+      <c r="G12" s="34"/>
+      <c r="H12" s="34"/>
       <c r="I12" s="22" t="s">
         <v>64</v>
       </c>
@@ -5831,15 +5850,15 @@
       <c r="A13" s="4">
         <v>7</v>
       </c>
-      <c r="B13" s="75"/>
+      <c r="B13" s="101"/>
       <c r="C13" s="4"/>
-      <c r="D13" s="78" t="s">
+      <c r="D13" s="34" t="s">
         <v>70</v>
       </c>
-      <c r="E13" s="78"/>
-      <c r="F13" s="78"/>
-      <c r="G13" s="78"/>
-      <c r="H13" s="78"/>
+      <c r="E13" s="34"/>
+      <c r="F13" s="34"/>
+      <c r="G13" s="34"/>
+      <c r="H13" s="34"/>
       <c r="I13" s="22" t="s">
         <v>64</v>
       </c>
@@ -5848,229 +5867,229 @@
       <c r="A14" s="4">
         <v>8</v>
       </c>
-      <c r="B14" s="76"/>
+      <c r="B14" s="102"/>
       <c r="C14" s="4"/>
-      <c r="D14" s="78"/>
-      <c r="E14" s="78"/>
-      <c r="F14" s="78"/>
-      <c r="G14" s="78"/>
-      <c r="H14" s="78"/>
+      <c r="D14" s="34"/>
+      <c r="E14" s="34"/>
+      <c r="F14" s="34"/>
+      <c r="G14" s="34"/>
+      <c r="H14" s="34"/>
       <c r="I14" s="4"/>
     </row>
     <row r="15" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="4">
         <v>9</v>
       </c>
-      <c r="B15" s="77" t="s">
+      <c r="B15" s="100" t="s">
         <v>71</v>
       </c>
       <c r="C15" s="4"/>
-      <c r="D15" s="78"/>
-      <c r="E15" s="78"/>
-      <c r="F15" s="78"/>
-      <c r="G15" s="78"/>
-      <c r="H15" s="78"/>
+      <c r="D15" s="34"/>
+      <c r="E15" s="34"/>
+      <c r="F15" s="34"/>
+      <c r="G15" s="34"/>
+      <c r="H15" s="34"/>
       <c r="I15" s="4"/>
     </row>
     <row r="16" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="4">
         <v>10</v>
       </c>
-      <c r="B16" s="75"/>
+      <c r="B16" s="101"/>
       <c r="C16" s="4"/>
-      <c r="D16" s="78"/>
-      <c r="E16" s="78"/>
-      <c r="F16" s="78"/>
-      <c r="G16" s="78"/>
-      <c r="H16" s="78"/>
+      <c r="D16" s="34"/>
+      <c r="E16" s="34"/>
+      <c r="F16" s="34"/>
+      <c r="G16" s="34"/>
+      <c r="H16" s="34"/>
       <c r="I16" s="4"/>
     </row>
     <row r="17" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="4">
         <v>11</v>
       </c>
-      <c r="B17" s="75"/>
+      <c r="B17" s="101"/>
       <c r="C17" s="4"/>
-      <c r="D17" s="78"/>
-      <c r="E17" s="78"/>
-      <c r="F17" s="78"/>
-      <c r="G17" s="78"/>
-      <c r="H17" s="78"/>
+      <c r="D17" s="34"/>
+      <c r="E17" s="34"/>
+      <c r="F17" s="34"/>
+      <c r="G17" s="34"/>
+      <c r="H17" s="34"/>
       <c r="I17" s="4"/>
     </row>
     <row r="18" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="4">
         <v>12</v>
       </c>
-      <c r="B18" s="76"/>
+      <c r="B18" s="102"/>
       <c r="C18" s="4"/>
-      <c r="D18" s="78"/>
-      <c r="E18" s="78"/>
-      <c r="F18" s="78"/>
-      <c r="G18" s="78"/>
-      <c r="H18" s="78"/>
+      <c r="D18" s="34"/>
+      <c r="E18" s="34"/>
+      <c r="F18" s="34"/>
+      <c r="G18" s="34"/>
+      <c r="H18" s="34"/>
       <c r="I18" s="4"/>
     </row>
     <row r="19" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="4">
         <v>13</v>
       </c>
-      <c r="B19" s="77" t="s">
+      <c r="B19" s="100" t="s">
         <v>72</v>
       </c>
       <c r="C19" s="4"/>
-      <c r="D19" s="78"/>
-      <c r="E19" s="78"/>
-      <c r="F19" s="78"/>
-      <c r="G19" s="78"/>
-      <c r="H19" s="78"/>
+      <c r="D19" s="34"/>
+      <c r="E19" s="34"/>
+      <c r="F19" s="34"/>
+      <c r="G19" s="34"/>
+      <c r="H19" s="34"/>
       <c r="I19" s="4"/>
     </row>
     <row r="20" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="4">
         <v>14</v>
       </c>
-      <c r="B20" s="75"/>
+      <c r="B20" s="101"/>
       <c r="C20" s="4"/>
-      <c r="D20" s="78"/>
-      <c r="E20" s="78"/>
-      <c r="F20" s="78"/>
-      <c r="G20" s="78"/>
-      <c r="H20" s="78"/>
+      <c r="D20" s="34"/>
+      <c r="E20" s="34"/>
+      <c r="F20" s="34"/>
+      <c r="G20" s="34"/>
+      <c r="H20" s="34"/>
       <c r="I20" s="4"/>
     </row>
     <row r="21" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="4">
         <v>15</v>
       </c>
-      <c r="B21" s="75"/>
+      <c r="B21" s="101"/>
       <c r="C21" s="4"/>
-      <c r="D21" s="78"/>
-      <c r="E21" s="78"/>
-      <c r="F21" s="78"/>
-      <c r="G21" s="78"/>
-      <c r="H21" s="78"/>
+      <c r="D21" s="34"/>
+      <c r="E21" s="34"/>
+      <c r="F21" s="34"/>
+      <c r="G21" s="34"/>
+      <c r="H21" s="34"/>
       <c r="I21" s="4"/>
     </row>
     <row r="22" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="4">
         <v>16</v>
       </c>
-      <c r="B22" s="76"/>
+      <c r="B22" s="102"/>
       <c r="C22" s="4"/>
-      <c r="D22" s="78"/>
-      <c r="E22" s="78"/>
-      <c r="F22" s="78"/>
-      <c r="G22" s="78"/>
-      <c r="H22" s="78"/>
+      <c r="D22" s="34"/>
+      <c r="E22" s="34"/>
+      <c r="F22" s="34"/>
+      <c r="G22" s="34"/>
+      <c r="H22" s="34"/>
       <c r="I22" s="4"/>
     </row>
     <row r="23" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="4">
         <v>17</v>
       </c>
-      <c r="B23" s="77" t="s">
+      <c r="B23" s="100" t="s">
         <v>73</v>
       </c>
       <c r="C23" s="4"/>
-      <c r="D23" s="78"/>
-      <c r="E23" s="78"/>
-      <c r="F23" s="78"/>
-      <c r="G23" s="78"/>
-      <c r="H23" s="78"/>
+      <c r="D23" s="34"/>
+      <c r="E23" s="34"/>
+      <c r="F23" s="34"/>
+      <c r="G23" s="34"/>
+      <c r="H23" s="34"/>
       <c r="I23" s="4"/>
     </row>
     <row r="24" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" s="4">
         <v>18</v>
       </c>
-      <c r="B24" s="75"/>
+      <c r="B24" s="101"/>
       <c r="C24" s="4"/>
-      <c r="D24" s="78"/>
-      <c r="E24" s="78"/>
-      <c r="F24" s="78"/>
-      <c r="G24" s="78"/>
-      <c r="H24" s="78"/>
+      <c r="D24" s="34"/>
+      <c r="E24" s="34"/>
+      <c r="F24" s="34"/>
+      <c r="G24" s="34"/>
+      <c r="H24" s="34"/>
       <c r="I24" s="4"/>
     </row>
     <row r="25" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A25" s="4">
         <v>19</v>
       </c>
-      <c r="B25" s="75"/>
+      <c r="B25" s="101"/>
       <c r="C25" s="4"/>
-      <c r="D25" s="78"/>
-      <c r="E25" s="78"/>
-      <c r="F25" s="78"/>
-      <c r="G25" s="78"/>
-      <c r="H25" s="78"/>
+      <c r="D25" s="34"/>
+      <c r="E25" s="34"/>
+      <c r="F25" s="34"/>
+      <c r="G25" s="34"/>
+      <c r="H25" s="34"/>
       <c r="I25" s="4"/>
     </row>
     <row r="26" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26" s="4">
         <v>20</v>
       </c>
-      <c r="B26" s="76"/>
+      <c r="B26" s="102"/>
       <c r="C26" s="4"/>
-      <c r="D26" s="78"/>
-      <c r="E26" s="78"/>
-      <c r="F26" s="78"/>
-      <c r="G26" s="78"/>
-      <c r="H26" s="78"/>
+      <c r="D26" s="34"/>
+      <c r="E26" s="34"/>
+      <c r="F26" s="34"/>
+      <c r="G26" s="34"/>
+      <c r="H26" s="34"/>
       <c r="I26" s="4"/>
     </row>
     <row r="27" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A27" s="4">
         <v>21</v>
       </c>
-      <c r="B27" s="77" t="s">
+      <c r="B27" s="100" t="s">
         <v>74</v>
       </c>
       <c r="C27" s="4"/>
-      <c r="D27" s="78"/>
-      <c r="E27" s="78"/>
-      <c r="F27" s="78"/>
-      <c r="G27" s="78"/>
-      <c r="H27" s="78"/>
+      <c r="D27" s="34"/>
+      <c r="E27" s="34"/>
+      <c r="F27" s="34"/>
+      <c r="G27" s="34"/>
+      <c r="H27" s="34"/>
       <c r="I27" s="4"/>
     </row>
     <row r="28" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A28" s="4">
         <v>22</v>
       </c>
-      <c r="B28" s="75"/>
+      <c r="B28" s="101"/>
       <c r="C28" s="4"/>
-      <c r="D28" s="78"/>
-      <c r="E28" s="78"/>
-      <c r="F28" s="78"/>
-      <c r="G28" s="78"/>
-      <c r="H28" s="78"/>
+      <c r="D28" s="34"/>
+      <c r="E28" s="34"/>
+      <c r="F28" s="34"/>
+      <c r="G28" s="34"/>
+      <c r="H28" s="34"/>
       <c r="I28" s="4"/>
     </row>
     <row r="29" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A29" s="4">
         <v>23</v>
       </c>
-      <c r="B29" s="75"/>
+      <c r="B29" s="101"/>
       <c r="C29" s="4"/>
-      <c r="D29" s="78"/>
-      <c r="E29" s="78"/>
-      <c r="F29" s="78"/>
-      <c r="G29" s="78"/>
-      <c r="H29" s="78"/>
+      <c r="D29" s="34"/>
+      <c r="E29" s="34"/>
+      <c r="F29" s="34"/>
+      <c r="G29" s="34"/>
+      <c r="H29" s="34"/>
       <c r="I29" s="4"/>
     </row>
     <row r="30" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A30" s="4">
         <v>24</v>
       </c>
-      <c r="B30" s="76"/>
+      <c r="B30" s="102"/>
       <c r="C30" s="4"/>
-      <c r="D30" s="78"/>
-      <c r="E30" s="78"/>
-      <c r="F30" s="78"/>
-      <c r="G30" s="78"/>
-      <c r="H30" s="78"/>
+      <c r="D30" s="34"/>
+      <c r="E30" s="34"/>
+      <c r="F30" s="34"/>
+      <c r="G30" s="34"/>
+      <c r="H30" s="34"/>
       <c r="I30" s="4"/>
     </row>
     <row r="31" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -6079,11 +6098,11 @@
       </c>
       <c r="B31" s="4"/>
       <c r="C31" s="4"/>
-      <c r="D31" s="78"/>
-      <c r="E31" s="78"/>
-      <c r="F31" s="78"/>
-      <c r="G31" s="78"/>
-      <c r="H31" s="78"/>
+      <c r="D31" s="34"/>
+      <c r="E31" s="34"/>
+      <c r="F31" s="34"/>
+      <c r="G31" s="34"/>
+      <c r="H31" s="34"/>
       <c r="I31" s="4"/>
     </row>
     <row r="32" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -6092,11 +6111,11 @@
       </c>
       <c r="B32" s="4"/>
       <c r="C32" s="4"/>
-      <c r="D32" s="78"/>
-      <c r="E32" s="78"/>
-      <c r="F32" s="78"/>
-      <c r="G32" s="78"/>
-      <c r="H32" s="78"/>
+      <c r="D32" s="34"/>
+      <c r="E32" s="34"/>
+      <c r="F32" s="34"/>
+      <c r="G32" s="34"/>
+      <c r="H32" s="34"/>
       <c r="I32" s="4"/>
     </row>
     <row r="33" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -6105,11 +6124,11 @@
       </c>
       <c r="B33" s="4"/>
       <c r="C33" s="4"/>
-      <c r="D33" s="78"/>
-      <c r="E33" s="78"/>
-      <c r="F33" s="78"/>
-      <c r="G33" s="78"/>
-      <c r="H33" s="78"/>
+      <c r="D33" s="34"/>
+      <c r="E33" s="34"/>
+      <c r="F33" s="34"/>
+      <c r="G33" s="34"/>
+      <c r="H33" s="34"/>
       <c r="I33" s="4"/>
     </row>
     <row r="34" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -6118,11 +6137,11 @@
       </c>
       <c r="B34" s="4"/>
       <c r="C34" s="4"/>
-      <c r="D34" s="78"/>
-      <c r="E34" s="78"/>
-      <c r="F34" s="78"/>
-      <c r="G34" s="78"/>
-      <c r="H34" s="78"/>
+      <c r="D34" s="34"/>
+      <c r="E34" s="34"/>
+      <c r="F34" s="34"/>
+      <c r="G34" s="34"/>
+      <c r="H34" s="34"/>
       <c r="I34" s="4"/>
     </row>
     <row r="35" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -6131,11 +6150,11 @@
       </c>
       <c r="B35" s="4"/>
       <c r="C35" s="4"/>
-      <c r="D35" s="78"/>
-      <c r="E35" s="78"/>
-      <c r="F35" s="78"/>
-      <c r="G35" s="78"/>
-      <c r="H35" s="78"/>
+      <c r="D35" s="34"/>
+      <c r="E35" s="34"/>
+      <c r="F35" s="34"/>
+      <c r="G35" s="34"/>
+      <c r="H35" s="34"/>
       <c r="I35" s="4"/>
     </row>
     <row r="36" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -6144,15 +6163,43 @@
       </c>
       <c r="B36" s="4"/>
       <c r="C36" s="4"/>
-      <c r="D36" s="78"/>
-      <c r="E36" s="78"/>
-      <c r="F36" s="78"/>
-      <c r="G36" s="78"/>
-      <c r="H36" s="78"/>
+      <c r="D36" s="34"/>
+      <c r="E36" s="34"/>
+      <c r="F36" s="34"/>
+      <c r="G36" s="34"/>
+      <c r="H36" s="34"/>
       <c r="I36" s="4"/>
     </row>
   </sheetData>
   <mergeCells count="44">
+    <mergeCell ref="B7:B10"/>
+    <mergeCell ref="B15:B18"/>
+    <mergeCell ref="B19:B22"/>
+    <mergeCell ref="B23:B26"/>
+    <mergeCell ref="B27:B30"/>
+    <mergeCell ref="A2:I3"/>
+    <mergeCell ref="A4:B4"/>
+    <mergeCell ref="A5:A6"/>
+    <mergeCell ref="C5:C6"/>
+    <mergeCell ref="B5:B6"/>
+    <mergeCell ref="D5:H6"/>
+    <mergeCell ref="I5:I6"/>
+    <mergeCell ref="D15:H15"/>
+    <mergeCell ref="D16:H16"/>
+    <mergeCell ref="D17:H17"/>
+    <mergeCell ref="D25:H25"/>
+    <mergeCell ref="D26:H26"/>
+    <mergeCell ref="D20:H20"/>
+    <mergeCell ref="D21:H21"/>
+    <mergeCell ref="D22:H22"/>
+    <mergeCell ref="D23:H23"/>
+    <mergeCell ref="D24:H24"/>
+    <mergeCell ref="D36:H36"/>
+    <mergeCell ref="D27:H27"/>
+    <mergeCell ref="D28:H28"/>
+    <mergeCell ref="D29:H29"/>
+    <mergeCell ref="D30:H30"/>
+    <mergeCell ref="D31:H31"/>
     <mergeCell ref="A1:C1"/>
     <mergeCell ref="D32:H32"/>
     <mergeCell ref="D33:H33"/>
@@ -6169,34 +6216,6 @@
     <mergeCell ref="D12:H12"/>
     <mergeCell ref="D13:H13"/>
     <mergeCell ref="D14:H14"/>
-    <mergeCell ref="D36:H36"/>
-    <mergeCell ref="D27:H27"/>
-    <mergeCell ref="D28:H28"/>
-    <mergeCell ref="D29:H29"/>
-    <mergeCell ref="D30:H30"/>
-    <mergeCell ref="D31:H31"/>
-    <mergeCell ref="D15:H15"/>
-    <mergeCell ref="D16:H16"/>
-    <mergeCell ref="D17:H17"/>
-    <mergeCell ref="D25:H25"/>
-    <mergeCell ref="D26:H26"/>
-    <mergeCell ref="D20:H20"/>
-    <mergeCell ref="D21:H21"/>
-    <mergeCell ref="D22:H22"/>
-    <mergeCell ref="D23:H23"/>
-    <mergeCell ref="D24:H24"/>
-    <mergeCell ref="A2:I3"/>
-    <mergeCell ref="A4:B4"/>
-    <mergeCell ref="A5:A6"/>
-    <mergeCell ref="C5:C6"/>
-    <mergeCell ref="B5:B6"/>
-    <mergeCell ref="D5:H6"/>
-    <mergeCell ref="I5:I6"/>
-    <mergeCell ref="B7:B10"/>
-    <mergeCell ref="B15:B18"/>
-    <mergeCell ref="B19:B22"/>
-    <mergeCell ref="B23:B26"/>
-    <mergeCell ref="B27:B30"/>
   </mergeCells>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.75" right="0.75" top="0.6" bottom="0.61" header="0.4" footer="0.39"/>
@@ -6220,23 +6239,23 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:52" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B1" s="169" t="s">
+      <c r="B1" s="104" t="s">
         <v>75</v>
       </c>
-      <c r="C1" s="170"/>
-      <c r="D1" s="170"/>
-      <c r="E1" s="170"/>
-      <c r="F1" s="170"/>
-      <c r="G1" s="170"/>
-      <c r="H1" s="170"/>
-      <c r="I1" s="170"/>
-      <c r="J1" s="170"/>
-      <c r="K1" s="170"/>
-      <c r="L1" s="170"/>
-      <c r="M1" s="170"/>
-      <c r="N1" s="170"/>
-      <c r="O1" s="170"/>
-      <c r="P1" s="170"/>
+      <c r="C1" s="105"/>
+      <c r="D1" s="105"/>
+      <c r="E1" s="105"/>
+      <c r="F1" s="105"/>
+      <c r="G1" s="105"/>
+      <c r="H1" s="105"/>
+      <c r="I1" s="105"/>
+      <c r="J1" s="105"/>
+      <c r="K1" s="105"/>
+      <c r="L1" s="105"/>
+      <c r="M1" s="105"/>
+      <c r="N1" s="105"/>
+      <c r="O1" s="105"/>
+      <c r="P1" s="105"/>
       <c r="Q1" s="21"/>
       <c r="R1" s="20"/>
       <c r="S1" s="20"/>
@@ -6253,139 +6272,139 @@
       <c r="AD1" s="20"/>
     </row>
     <row r="2" spans="2:52" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B2" s="118" t="s">
+      <c r="B2" s="184" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="118"/>
-      <c r="D2" s="118"/>
-      <c r="E2" s="118"/>
-      <c r="F2" s="118"/>
-      <c r="G2" s="118"/>
-      <c r="H2" s="118"/>
-      <c r="I2" s="118"/>
-      <c r="J2" s="122"/>
-      <c r="K2" s="122"/>
-      <c r="L2" s="122"/>
-      <c r="M2" s="122"/>
-      <c r="N2" s="122"/>
-      <c r="O2" s="122"/>
-      <c r="P2" s="122"/>
-      <c r="Q2" s="122"/>
-      <c r="R2" s="122"/>
-      <c r="S2" s="122"/>
-      <c r="T2" s="122"/>
-      <c r="U2" s="122"/>
-      <c r="V2" s="122"/>
-      <c r="W2" s="122"/>
-      <c r="X2" s="122"/>
-      <c r="Y2" s="122"/>
-      <c r="Z2" s="122"/>
-      <c r="AA2" s="122"/>
-      <c r="AB2" s="122"/>
-      <c r="AC2" s="122"/>
-      <c r="AD2" s="122"/>
+      <c r="C2" s="184"/>
+      <c r="D2" s="184"/>
+      <c r="E2" s="184"/>
+      <c r="F2" s="184"/>
+      <c r="G2" s="184"/>
+      <c r="H2" s="184"/>
+      <c r="I2" s="184"/>
+      <c r="J2" s="113"/>
+      <c r="K2" s="113"/>
+      <c r="L2" s="113"/>
+      <c r="M2" s="113"/>
+      <c r="N2" s="113"/>
+      <c r="O2" s="113"/>
+      <c r="P2" s="113"/>
+      <c r="Q2" s="113"/>
+      <c r="R2" s="113"/>
+      <c r="S2" s="113"/>
+      <c r="T2" s="113"/>
+      <c r="U2" s="113"/>
+      <c r="V2" s="113"/>
+      <c r="W2" s="113"/>
+      <c r="X2" s="113"/>
+      <c r="Y2" s="113"/>
+      <c r="Z2" s="113"/>
+      <c r="AA2" s="113"/>
+      <c r="AB2" s="113"/>
+      <c r="AC2" s="113"/>
+      <c r="AD2" s="113"/>
     </row>
     <row r="3" spans="2:52" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="4" spans="2:52" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B4" s="129" t="s">
+      <c r="B4" s="192" t="s">
         <v>76</v>
       </c>
-      <c r="C4" s="116"/>
-      <c r="D4" s="116"/>
-      <c r="E4" s="116"/>
-      <c r="F4" s="116"/>
-      <c r="G4" s="116"/>
-      <c r="H4" s="116"/>
-      <c r="I4" s="116"/>
-      <c r="J4" s="116" t="s">
+      <c r="C4" s="182"/>
+      <c r="D4" s="182"/>
+      <c r="E4" s="182"/>
+      <c r="F4" s="182"/>
+      <c r="G4" s="182"/>
+      <c r="H4" s="182"/>
+      <c r="I4" s="182"/>
+      <c r="J4" s="182" t="s">
         <v>77</v>
       </c>
-      <c r="K4" s="116"/>
-      <c r="L4" s="116"/>
-      <c r="M4" s="116"/>
-      <c r="N4" s="116"/>
-      <c r="O4" s="116"/>
-      <c r="P4" s="116"/>
-      <c r="Q4" s="123" t="s">
+      <c r="K4" s="182"/>
+      <c r="L4" s="182"/>
+      <c r="M4" s="182"/>
+      <c r="N4" s="182"/>
+      <c r="O4" s="182"/>
+      <c r="P4" s="182"/>
+      <c r="Q4" s="186" t="s">
         <v>78</v>
       </c>
-      <c r="R4" s="127"/>
-      <c r="S4" s="124"/>
-      <c r="T4" s="123" t="s">
+      <c r="R4" s="190"/>
+      <c r="S4" s="187"/>
+      <c r="T4" s="186" t="s">
         <v>79</v>
       </c>
-      <c r="U4" s="127"/>
-      <c r="V4" s="127"/>
-      <c r="W4" s="124"/>
-      <c r="X4" s="123" t="s">
+      <c r="U4" s="190"/>
+      <c r="V4" s="190"/>
+      <c r="W4" s="187"/>
+      <c r="X4" s="186" t="s">
         <v>80</v>
       </c>
-      <c r="Y4" s="124"/>
-      <c r="Z4" s="116" t="s">
+      <c r="Y4" s="187"/>
+      <c r="Z4" s="182" t="s">
         <v>81</v>
       </c>
-      <c r="AA4" s="116"/>
-      <c r="AB4" s="116"/>
-      <c r="AC4" s="116" t="s">
+      <c r="AA4" s="182"/>
+      <c r="AB4" s="182"/>
+      <c r="AC4" s="182" t="s">
         <v>81</v>
       </c>
-      <c r="AD4" s="116"/>
-      <c r="AE4" s="116"/>
-      <c r="AF4" s="116" t="s">
+      <c r="AD4" s="182"/>
+      <c r="AE4" s="182"/>
+      <c r="AF4" s="182" t="s">
         <v>81</v>
       </c>
-      <c r="AG4" s="116"/>
-      <c r="AH4" s="116"/>
-      <c r="AI4" s="116" t="s">
+      <c r="AG4" s="182"/>
+      <c r="AH4" s="182"/>
+      <c r="AI4" s="182" t="s">
         <v>81</v>
       </c>
-      <c r="AJ4" s="116"/>
-      <c r="AK4" s="116"/>
-      <c r="AL4" s="116" t="s">
+      <c r="AJ4" s="182"/>
+      <c r="AK4" s="182"/>
+      <c r="AL4" s="182" t="s">
         <v>81</v>
       </c>
-      <c r="AM4" s="116"/>
-      <c r="AN4" s="116"/>
-      <c r="AO4" s="116" t="s">
+      <c r="AM4" s="182"/>
+      <c r="AN4" s="182"/>
+      <c r="AO4" s="182" t="s">
         <v>82</v>
       </c>
-      <c r="AP4" s="116"/>
-      <c r="AQ4" s="116"/>
-      <c r="AR4" s="116"/>
-      <c r="AS4" s="116"/>
-      <c r="AT4" s="116"/>
-      <c r="AU4" s="116"/>
-      <c r="AV4" s="116"/>
-      <c r="AW4" s="116"/>
-      <c r="AX4" s="116"/>
-      <c r="AY4" s="116"/>
-      <c r="AZ4" s="117"/>
+      <c r="AP4" s="182"/>
+      <c r="AQ4" s="182"/>
+      <c r="AR4" s="182"/>
+      <c r="AS4" s="182"/>
+      <c r="AT4" s="182"/>
+      <c r="AU4" s="182"/>
+      <c r="AV4" s="182"/>
+      <c r="AW4" s="182"/>
+      <c r="AX4" s="182"/>
+      <c r="AY4" s="182"/>
+      <c r="AZ4" s="183"/>
     </row>
     <row r="5" spans="2:52" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B5" s="130"/>
-      <c r="C5" s="118"/>
-      <c r="D5" s="118"/>
-      <c r="E5" s="118"/>
-      <c r="F5" s="118"/>
-      <c r="G5" s="118"/>
-      <c r="H5" s="118"/>
-      <c r="I5" s="118"/>
-      <c r="J5" s="118"/>
-      <c r="K5" s="118"/>
-      <c r="L5" s="118"/>
-      <c r="M5" s="118"/>
-      <c r="N5" s="118"/>
-      <c r="O5" s="118"/>
-      <c r="P5" s="118"/>
-      <c r="Q5" s="125"/>
-      <c r="R5" s="128"/>
-      <c r="S5" s="126"/>
-      <c r="T5" s="125"/>
-      <c r="U5" s="128"/>
-      <c r="V5" s="128"/>
-      <c r="W5" s="126"/>
-      <c r="X5" s="125"/>
-      <c r="Y5" s="126"/>
+      <c r="B5" s="193"/>
+      <c r="C5" s="184"/>
+      <c r="D5" s="184"/>
+      <c r="E5" s="184"/>
+      <c r="F5" s="184"/>
+      <c r="G5" s="184"/>
+      <c r="H5" s="184"/>
+      <c r="I5" s="184"/>
+      <c r="J5" s="184"/>
+      <c r="K5" s="184"/>
+      <c r="L5" s="184"/>
+      <c r="M5" s="184"/>
+      <c r="N5" s="184"/>
+      <c r="O5" s="184"/>
+      <c r="P5" s="184"/>
+      <c r="Q5" s="188"/>
+      <c r="R5" s="191"/>
+      <c r="S5" s="189"/>
+      <c r="T5" s="188"/>
+      <c r="U5" s="191"/>
+      <c r="V5" s="191"/>
+      <c r="W5" s="189"/>
+      <c r="X5" s="188"/>
+      <c r="Y5" s="189"/>
       <c r="Z5" s="6" t="s">
         <v>83</v>
       </c>
@@ -6431,54 +6450,54 @@
       <c r="AN5" s="8" t="s">
         <v>85</v>
       </c>
-      <c r="AO5" s="118"/>
-      <c r="AP5" s="118"/>
-      <c r="AQ5" s="118"/>
-      <c r="AR5" s="118"/>
-      <c r="AS5" s="118"/>
-      <c r="AT5" s="118"/>
-      <c r="AU5" s="118"/>
-      <c r="AV5" s="118"/>
-      <c r="AW5" s="118"/>
-      <c r="AX5" s="118"/>
-      <c r="AY5" s="118"/>
-      <c r="AZ5" s="119"/>
+      <c r="AO5" s="184"/>
+      <c r="AP5" s="184"/>
+      <c r="AQ5" s="184"/>
+      <c r="AR5" s="184"/>
+      <c r="AS5" s="184"/>
+      <c r="AT5" s="184"/>
+      <c r="AU5" s="184"/>
+      <c r="AV5" s="184"/>
+      <c r="AW5" s="184"/>
+      <c r="AX5" s="184"/>
+      <c r="AY5" s="184"/>
+      <c r="AZ5" s="185"/>
     </row>
     <row r="6" spans="2:52" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B6" s="145">
+      <c r="B6" s="110">
         <v>1</v>
       </c>
-      <c r="C6" s="131" t="s">
+      <c r="C6" s="106" t="s">
         <v>86</v>
       </c>
-      <c r="D6" s="131"/>
-      <c r="E6" s="131"/>
-      <c r="F6" s="131"/>
-      <c r="G6" s="131"/>
-      <c r="H6" s="131"/>
-      <c r="I6" s="131"/>
-      <c r="J6" s="131"/>
-      <c r="K6" s="131"/>
-      <c r="L6" s="131"/>
-      <c r="M6" s="131"/>
-      <c r="N6" s="131"/>
-      <c r="O6" s="131"/>
-      <c r="P6" s="131"/>
-      <c r="Q6" s="122"/>
-      <c r="R6" s="122"/>
-      <c r="S6" s="122"/>
-      <c r="T6" s="136" t="s">
+      <c r="D6" s="106"/>
+      <c r="E6" s="106"/>
+      <c r="F6" s="106"/>
+      <c r="G6" s="106"/>
+      <c r="H6" s="106"/>
+      <c r="I6" s="106"/>
+      <c r="J6" s="106"/>
+      <c r="K6" s="106"/>
+      <c r="L6" s="106"/>
+      <c r="M6" s="106"/>
+      <c r="N6" s="106"/>
+      <c r="O6" s="106"/>
+      <c r="P6" s="106"/>
+      <c r="Q6" s="113"/>
+      <c r="R6" s="113"/>
+      <c r="S6" s="113"/>
+      <c r="T6" s="111" t="s">
         <v>87</v>
       </c>
-      <c r="U6" s="136"/>
-      <c r="V6" s="134">
+      <c r="U6" s="111"/>
+      <c r="V6" s="108">
         <v>0</v>
       </c>
-      <c r="W6" s="134"/>
-      <c r="X6" s="120">
+      <c r="W6" s="108"/>
+      <c r="X6" s="129">
         <v>0</v>
       </c>
-      <c r="Y6" s="120"/>
+      <c r="Y6" s="129"/>
       <c r="Z6" s="9"/>
       <c r="AA6" s="10"/>
       <c r="AB6" s="11"/>
@@ -6494,50 +6513,50 @@
       <c r="AL6" s="9"/>
       <c r="AM6" s="10"/>
       <c r="AN6" s="11"/>
-      <c r="AO6" s="131"/>
-      <c r="AP6" s="131"/>
-      <c r="AQ6" s="131"/>
-      <c r="AR6" s="131"/>
-      <c r="AS6" s="131"/>
-      <c r="AT6" s="131"/>
-      <c r="AU6" s="131"/>
-      <c r="AV6" s="131"/>
-      <c r="AW6" s="131"/>
-      <c r="AX6" s="131"/>
-      <c r="AY6" s="131"/>
-      <c r="AZ6" s="132"/>
+      <c r="AO6" s="106"/>
+      <c r="AP6" s="106"/>
+      <c r="AQ6" s="106"/>
+      <c r="AR6" s="106"/>
+      <c r="AS6" s="106"/>
+      <c r="AT6" s="106"/>
+      <c r="AU6" s="106"/>
+      <c r="AV6" s="106"/>
+      <c r="AW6" s="106"/>
+      <c r="AX6" s="106"/>
+      <c r="AY6" s="106"/>
+      <c r="AZ6" s="128"/>
     </row>
     <row r="7" spans="2:52" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B7" s="145"/>
-      <c r="C7" s="131"/>
-      <c r="D7" s="131"/>
-      <c r="E7" s="131"/>
-      <c r="F7" s="131"/>
-      <c r="G7" s="131"/>
-      <c r="H7" s="131"/>
-      <c r="I7" s="131"/>
-      <c r="J7" s="131"/>
-      <c r="K7" s="131"/>
-      <c r="L7" s="131"/>
-      <c r="M7" s="131"/>
-      <c r="N7" s="131"/>
-      <c r="O7" s="131"/>
-      <c r="P7" s="131"/>
-      <c r="Q7" s="122"/>
-      <c r="R7" s="122"/>
-      <c r="S7" s="122"/>
-      <c r="T7" s="133" t="s">
+      <c r="B7" s="110"/>
+      <c r="C7" s="106"/>
+      <c r="D7" s="106"/>
+      <c r="E7" s="106"/>
+      <c r="F7" s="106"/>
+      <c r="G7" s="106"/>
+      <c r="H7" s="106"/>
+      <c r="I7" s="106"/>
+      <c r="J7" s="106"/>
+      <c r="K7" s="106"/>
+      <c r="L7" s="106"/>
+      <c r="M7" s="106"/>
+      <c r="N7" s="106"/>
+      <c r="O7" s="106"/>
+      <c r="P7" s="106"/>
+      <c r="Q7" s="113"/>
+      <c r="R7" s="113"/>
+      <c r="S7" s="113"/>
+      <c r="T7" s="112" t="s">
         <v>25</v>
       </c>
-      <c r="U7" s="133"/>
-      <c r="V7" s="135">
+      <c r="U7" s="112"/>
+      <c r="V7" s="109">
         <v>0</v>
       </c>
-      <c r="W7" s="135"/>
-      <c r="X7" s="121">
+      <c r="W7" s="109"/>
+      <c r="X7" s="130">
         <v>0</v>
       </c>
-      <c r="Y7" s="121"/>
+      <c r="Y7" s="130"/>
       <c r="Z7" s="12"/>
       <c r="AA7" s="13"/>
       <c r="AB7" s="14"/>
@@ -6553,54 +6572,54 @@
       <c r="AL7" s="12"/>
       <c r="AM7" s="13"/>
       <c r="AN7" s="14"/>
-      <c r="AO7" s="131"/>
-      <c r="AP7" s="131"/>
-      <c r="AQ7" s="131"/>
-      <c r="AR7" s="131"/>
-      <c r="AS7" s="131"/>
-      <c r="AT7" s="131"/>
-      <c r="AU7" s="131"/>
-      <c r="AV7" s="131"/>
-      <c r="AW7" s="131"/>
-      <c r="AX7" s="131"/>
-      <c r="AY7" s="131"/>
-      <c r="AZ7" s="132"/>
+      <c r="AO7" s="106"/>
+      <c r="AP7" s="106"/>
+      <c r="AQ7" s="106"/>
+      <c r="AR7" s="106"/>
+      <c r="AS7" s="106"/>
+      <c r="AT7" s="106"/>
+      <c r="AU7" s="106"/>
+      <c r="AV7" s="106"/>
+      <c r="AW7" s="106"/>
+      <c r="AX7" s="106"/>
+      <c r="AY7" s="106"/>
+      <c r="AZ7" s="128"/>
     </row>
     <row r="8" spans="2:52" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B8" s="145">
+      <c r="B8" s="110">
         <v>2</v>
       </c>
-      <c r="C8" s="131" t="s">
+      <c r="C8" s="106" t="s">
         <v>88</v>
       </c>
-      <c r="D8" s="131"/>
-      <c r="E8" s="131"/>
-      <c r="F8" s="131"/>
-      <c r="G8" s="131"/>
-      <c r="H8" s="131"/>
-      <c r="I8" s="131"/>
-      <c r="J8" s="90"/>
-      <c r="K8" s="91"/>
-      <c r="L8" s="91"/>
-      <c r="M8" s="91"/>
-      <c r="N8" s="91"/>
-      <c r="O8" s="91"/>
-      <c r="P8" s="92"/>
-      <c r="Q8" s="122"/>
-      <c r="R8" s="122"/>
-      <c r="S8" s="122"/>
-      <c r="T8" s="136" t="s">
+      <c r="D8" s="106"/>
+      <c r="E8" s="106"/>
+      <c r="F8" s="106"/>
+      <c r="G8" s="106"/>
+      <c r="H8" s="106"/>
+      <c r="I8" s="106"/>
+      <c r="J8" s="114"/>
+      <c r="K8" s="115"/>
+      <c r="L8" s="115"/>
+      <c r="M8" s="115"/>
+      <c r="N8" s="115"/>
+      <c r="O8" s="115"/>
+      <c r="P8" s="116"/>
+      <c r="Q8" s="113"/>
+      <c r="R8" s="113"/>
+      <c r="S8" s="113"/>
+      <c r="T8" s="111" t="s">
         <v>87</v>
       </c>
-      <c r="U8" s="136"/>
-      <c r="V8" s="134">
+      <c r="U8" s="111"/>
+      <c r="V8" s="108">
         <v>0</v>
       </c>
-      <c r="W8" s="134"/>
-      <c r="X8" s="120">
+      <c r="W8" s="108"/>
+      <c r="X8" s="129">
         <v>0</v>
       </c>
-      <c r="Y8" s="120"/>
+      <c r="Y8" s="129"/>
       <c r="Z8" s="9"/>
       <c r="AA8" s="10"/>
       <c r="AB8" s="11"/>
@@ -6616,50 +6635,50 @@
       <c r="AL8" s="9"/>
       <c r="AM8" s="10"/>
       <c r="AN8" s="11"/>
-      <c r="AO8" s="131"/>
-      <c r="AP8" s="131"/>
-      <c r="AQ8" s="131"/>
-      <c r="AR8" s="131"/>
-      <c r="AS8" s="131"/>
-      <c r="AT8" s="131"/>
-      <c r="AU8" s="131"/>
-      <c r="AV8" s="131"/>
-      <c r="AW8" s="131"/>
-      <c r="AX8" s="131"/>
-      <c r="AY8" s="131"/>
-      <c r="AZ8" s="132"/>
+      <c r="AO8" s="106"/>
+      <c r="AP8" s="106"/>
+      <c r="AQ8" s="106"/>
+      <c r="AR8" s="106"/>
+      <c r="AS8" s="106"/>
+      <c r="AT8" s="106"/>
+      <c r="AU8" s="106"/>
+      <c r="AV8" s="106"/>
+      <c r="AW8" s="106"/>
+      <c r="AX8" s="106"/>
+      <c r="AY8" s="106"/>
+      <c r="AZ8" s="128"/>
     </row>
     <row r="9" spans="2:52" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B9" s="145"/>
-      <c r="C9" s="131"/>
-      <c r="D9" s="131"/>
-      <c r="E9" s="131"/>
-      <c r="F9" s="131"/>
-      <c r="G9" s="131"/>
-      <c r="H9" s="131"/>
-      <c r="I9" s="131"/>
-      <c r="J9" s="93"/>
-      <c r="K9" s="94"/>
-      <c r="L9" s="94"/>
-      <c r="M9" s="94"/>
-      <c r="N9" s="94"/>
-      <c r="O9" s="94"/>
-      <c r="P9" s="95"/>
-      <c r="Q9" s="122"/>
-      <c r="R9" s="122"/>
-      <c r="S9" s="122"/>
-      <c r="T9" s="133" t="s">
+      <c r="B9" s="110"/>
+      <c r="C9" s="106"/>
+      <c r="D9" s="106"/>
+      <c r="E9" s="106"/>
+      <c r="F9" s="106"/>
+      <c r="G9" s="106"/>
+      <c r="H9" s="106"/>
+      <c r="I9" s="106"/>
+      <c r="J9" s="117"/>
+      <c r="K9" s="118"/>
+      <c r="L9" s="118"/>
+      <c r="M9" s="118"/>
+      <c r="N9" s="118"/>
+      <c r="O9" s="118"/>
+      <c r="P9" s="119"/>
+      <c r="Q9" s="113"/>
+      <c r="R9" s="113"/>
+      <c r="S9" s="113"/>
+      <c r="T9" s="112" t="s">
         <v>25</v>
       </c>
-      <c r="U9" s="133"/>
-      <c r="V9" s="135">
+      <c r="U9" s="112"/>
+      <c r="V9" s="109">
         <v>0</v>
       </c>
-      <c r="W9" s="135"/>
-      <c r="X9" s="121">
+      <c r="W9" s="109"/>
+      <c r="X9" s="130">
         <v>0</v>
       </c>
-      <c r="Y9" s="121"/>
+      <c r="Y9" s="130"/>
       <c r="Z9" s="12"/>
       <c r="AA9" s="13"/>
       <c r="AB9" s="14"/>
@@ -6675,54 +6694,54 @@
       <c r="AL9" s="12"/>
       <c r="AM9" s="13"/>
       <c r="AN9" s="14"/>
-      <c r="AO9" s="131"/>
-      <c r="AP9" s="131"/>
-      <c r="AQ9" s="131"/>
-      <c r="AR9" s="131"/>
-      <c r="AS9" s="131"/>
-      <c r="AT9" s="131"/>
-      <c r="AU9" s="131"/>
-      <c r="AV9" s="131"/>
-      <c r="AW9" s="131"/>
-      <c r="AX9" s="131"/>
-      <c r="AY9" s="131"/>
-      <c r="AZ9" s="132"/>
+      <c r="AO9" s="106"/>
+      <c r="AP9" s="106"/>
+      <c r="AQ9" s="106"/>
+      <c r="AR9" s="106"/>
+      <c r="AS9" s="106"/>
+      <c r="AT9" s="106"/>
+      <c r="AU9" s="106"/>
+      <c r="AV9" s="106"/>
+      <c r="AW9" s="106"/>
+      <c r="AX9" s="106"/>
+      <c r="AY9" s="106"/>
+      <c r="AZ9" s="128"/>
     </row>
     <row r="10" spans="2:52" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B10" s="145">
+      <c r="B10" s="110">
         <v>3</v>
       </c>
-      <c r="C10" s="131" t="s">
+      <c r="C10" s="106" t="s">
         <v>89</v>
       </c>
-      <c r="D10" s="131"/>
-      <c r="E10" s="131"/>
-      <c r="F10" s="131"/>
-      <c r="G10" s="131"/>
-      <c r="H10" s="131"/>
-      <c r="I10" s="131"/>
-      <c r="J10" s="131"/>
-      <c r="K10" s="131"/>
-      <c r="L10" s="131"/>
-      <c r="M10" s="131"/>
-      <c r="N10" s="131"/>
-      <c r="O10" s="131"/>
-      <c r="P10" s="131"/>
-      <c r="Q10" s="122"/>
-      <c r="R10" s="122"/>
-      <c r="S10" s="122"/>
-      <c r="T10" s="136" t="s">
+      <c r="D10" s="106"/>
+      <c r="E10" s="106"/>
+      <c r="F10" s="106"/>
+      <c r="G10" s="106"/>
+      <c r="H10" s="106"/>
+      <c r="I10" s="106"/>
+      <c r="J10" s="106"/>
+      <c r="K10" s="106"/>
+      <c r="L10" s="106"/>
+      <c r="M10" s="106"/>
+      <c r="N10" s="106"/>
+      <c r="O10" s="106"/>
+      <c r="P10" s="106"/>
+      <c r="Q10" s="113"/>
+      <c r="R10" s="113"/>
+      <c r="S10" s="113"/>
+      <c r="T10" s="111" t="s">
         <v>87</v>
       </c>
-      <c r="U10" s="136"/>
-      <c r="V10" s="134">
+      <c r="U10" s="111"/>
+      <c r="V10" s="108">
         <v>0</v>
       </c>
-      <c r="W10" s="134"/>
-      <c r="X10" s="120">
+      <c r="W10" s="108"/>
+      <c r="X10" s="129">
         <v>0</v>
       </c>
-      <c r="Y10" s="120"/>
+      <c r="Y10" s="129"/>
       <c r="Z10" s="9"/>
       <c r="AA10" s="10"/>
       <c r="AB10" s="11"/>
@@ -6738,50 +6757,50 @@
       <c r="AL10" s="9"/>
       <c r="AM10" s="10"/>
       <c r="AN10" s="11"/>
-      <c r="AO10" s="131"/>
-      <c r="AP10" s="131"/>
-      <c r="AQ10" s="131"/>
-      <c r="AR10" s="131"/>
-      <c r="AS10" s="131"/>
-      <c r="AT10" s="131"/>
-      <c r="AU10" s="131"/>
-      <c r="AV10" s="131"/>
-      <c r="AW10" s="131"/>
-      <c r="AX10" s="131"/>
-      <c r="AY10" s="131"/>
-      <c r="AZ10" s="132"/>
+      <c r="AO10" s="106"/>
+      <c r="AP10" s="106"/>
+      <c r="AQ10" s="106"/>
+      <c r="AR10" s="106"/>
+      <c r="AS10" s="106"/>
+      <c r="AT10" s="106"/>
+      <c r="AU10" s="106"/>
+      <c r="AV10" s="106"/>
+      <c r="AW10" s="106"/>
+      <c r="AX10" s="106"/>
+      <c r="AY10" s="106"/>
+      <c r="AZ10" s="128"/>
     </row>
     <row r="11" spans="2:52" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B11" s="145"/>
-      <c r="C11" s="131"/>
-      <c r="D11" s="131"/>
-      <c r="E11" s="131"/>
-      <c r="F11" s="131"/>
-      <c r="G11" s="131"/>
-      <c r="H11" s="131"/>
-      <c r="I11" s="131"/>
-      <c r="J11" s="131"/>
-      <c r="K11" s="131"/>
-      <c r="L11" s="131"/>
-      <c r="M11" s="131"/>
-      <c r="N11" s="131"/>
-      <c r="O11" s="131"/>
-      <c r="P11" s="131"/>
-      <c r="Q11" s="122"/>
-      <c r="R11" s="122"/>
-      <c r="S11" s="122"/>
-      <c r="T11" s="133" t="s">
+      <c r="B11" s="110"/>
+      <c r="C11" s="106"/>
+      <c r="D11" s="106"/>
+      <c r="E11" s="106"/>
+      <c r="F11" s="106"/>
+      <c r="G11" s="106"/>
+      <c r="H11" s="106"/>
+      <c r="I11" s="106"/>
+      <c r="J11" s="106"/>
+      <c r="K11" s="106"/>
+      <c r="L11" s="106"/>
+      <c r="M11" s="106"/>
+      <c r="N11" s="106"/>
+      <c r="O11" s="106"/>
+      <c r="P11" s="106"/>
+      <c r="Q11" s="113"/>
+      <c r="R11" s="113"/>
+      <c r="S11" s="113"/>
+      <c r="T11" s="112" t="s">
         <v>25</v>
       </c>
-      <c r="U11" s="133"/>
-      <c r="V11" s="135">
+      <c r="U11" s="112"/>
+      <c r="V11" s="109">
         <v>0</v>
       </c>
-      <c r="W11" s="135"/>
-      <c r="X11" s="121">
+      <c r="W11" s="109"/>
+      <c r="X11" s="130">
         <v>0</v>
       </c>
-      <c r="Y11" s="121"/>
+      <c r="Y11" s="130"/>
       <c r="Z11" s="12"/>
       <c r="AA11" s="13"/>
       <c r="AB11" s="14"/>
@@ -6797,54 +6816,54 @@
       <c r="AL11" s="12"/>
       <c r="AM11" s="13"/>
       <c r="AN11" s="14"/>
-      <c r="AO11" s="131"/>
-      <c r="AP11" s="131"/>
-      <c r="AQ11" s="131"/>
-      <c r="AR11" s="131"/>
-      <c r="AS11" s="131"/>
-      <c r="AT11" s="131"/>
-      <c r="AU11" s="131"/>
-      <c r="AV11" s="131"/>
-      <c r="AW11" s="131"/>
-      <c r="AX11" s="131"/>
-      <c r="AY11" s="131"/>
-      <c r="AZ11" s="132"/>
+      <c r="AO11" s="106"/>
+      <c r="AP11" s="106"/>
+      <c r="AQ11" s="106"/>
+      <c r="AR11" s="106"/>
+      <c r="AS11" s="106"/>
+      <c r="AT11" s="106"/>
+      <c r="AU11" s="106"/>
+      <c r="AV11" s="106"/>
+      <c r="AW11" s="106"/>
+      <c r="AX11" s="106"/>
+      <c r="AY11" s="106"/>
+      <c r="AZ11" s="128"/>
     </row>
     <row r="12" spans="2:52" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B12" s="145">
+      <c r="B12" s="110">
         <v>4</v>
       </c>
-      <c r="C12" s="131" t="s">
+      <c r="C12" s="106" t="s">
         <v>90</v>
       </c>
-      <c r="D12" s="131"/>
-      <c r="E12" s="131"/>
-      <c r="F12" s="131"/>
-      <c r="G12" s="131"/>
-      <c r="H12" s="131"/>
-      <c r="I12" s="131"/>
-      <c r="J12" s="131"/>
-      <c r="K12" s="131"/>
-      <c r="L12" s="131"/>
-      <c r="M12" s="131"/>
-      <c r="N12" s="131"/>
-      <c r="O12" s="131"/>
-      <c r="P12" s="131"/>
-      <c r="Q12" s="96"/>
-      <c r="R12" s="97"/>
-      <c r="S12" s="98"/>
-      <c r="T12" s="136" t="s">
+      <c r="D12" s="106"/>
+      <c r="E12" s="106"/>
+      <c r="F12" s="106"/>
+      <c r="G12" s="106"/>
+      <c r="H12" s="106"/>
+      <c r="I12" s="106"/>
+      <c r="J12" s="106"/>
+      <c r="K12" s="106"/>
+      <c r="L12" s="106"/>
+      <c r="M12" s="106"/>
+      <c r="N12" s="106"/>
+      <c r="O12" s="106"/>
+      <c r="P12" s="106"/>
+      <c r="Q12" s="172"/>
+      <c r="R12" s="173"/>
+      <c r="S12" s="174"/>
+      <c r="T12" s="111" t="s">
         <v>87</v>
       </c>
-      <c r="U12" s="136"/>
-      <c r="V12" s="134">
+      <c r="U12" s="111"/>
+      <c r="V12" s="108">
         <v>0</v>
       </c>
-      <c r="W12" s="134"/>
-      <c r="X12" s="120">
+      <c r="W12" s="108"/>
+      <c r="X12" s="129">
         <v>0</v>
       </c>
-      <c r="Y12" s="120"/>
+      <c r="Y12" s="129"/>
       <c r="Z12" s="9"/>
       <c r="AA12" s="10"/>
       <c r="AB12" s="11"/>
@@ -6860,50 +6879,50 @@
       <c r="AL12" s="9"/>
       <c r="AM12" s="10"/>
       <c r="AN12" s="11"/>
-      <c r="AO12" s="131"/>
-      <c r="AP12" s="131"/>
-      <c r="AQ12" s="131"/>
-      <c r="AR12" s="131"/>
-      <c r="AS12" s="131"/>
-      <c r="AT12" s="131"/>
-      <c r="AU12" s="131"/>
-      <c r="AV12" s="131"/>
-      <c r="AW12" s="131"/>
-      <c r="AX12" s="131"/>
-      <c r="AY12" s="131"/>
-      <c r="AZ12" s="132"/>
+      <c r="AO12" s="106"/>
+      <c r="AP12" s="106"/>
+      <c r="AQ12" s="106"/>
+      <c r="AR12" s="106"/>
+      <c r="AS12" s="106"/>
+      <c r="AT12" s="106"/>
+      <c r="AU12" s="106"/>
+      <c r="AV12" s="106"/>
+      <c r="AW12" s="106"/>
+      <c r="AX12" s="106"/>
+      <c r="AY12" s="106"/>
+      <c r="AZ12" s="128"/>
     </row>
     <row r="13" spans="2:52" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B13" s="145"/>
-      <c r="C13" s="131"/>
-      <c r="D13" s="131"/>
-      <c r="E13" s="131"/>
-      <c r="F13" s="131"/>
-      <c r="G13" s="131"/>
-      <c r="H13" s="131"/>
-      <c r="I13" s="131"/>
-      <c r="J13" s="131"/>
-      <c r="K13" s="131"/>
-      <c r="L13" s="131"/>
-      <c r="M13" s="131"/>
-      <c r="N13" s="131"/>
-      <c r="O13" s="131"/>
-      <c r="P13" s="131"/>
-      <c r="Q13" s="99"/>
-      <c r="R13" s="100"/>
-      <c r="S13" s="101"/>
-      <c r="T13" s="133" t="s">
+      <c r="B13" s="110"/>
+      <c r="C13" s="106"/>
+      <c r="D13" s="106"/>
+      <c r="E13" s="106"/>
+      <c r="F13" s="106"/>
+      <c r="G13" s="106"/>
+      <c r="H13" s="106"/>
+      <c r="I13" s="106"/>
+      <c r="J13" s="106"/>
+      <c r="K13" s="106"/>
+      <c r="L13" s="106"/>
+      <c r="M13" s="106"/>
+      <c r="N13" s="106"/>
+      <c r="O13" s="106"/>
+      <c r="P13" s="106"/>
+      <c r="Q13" s="175"/>
+      <c r="R13" s="176"/>
+      <c r="S13" s="177"/>
+      <c r="T13" s="112" t="s">
         <v>25</v>
       </c>
-      <c r="U13" s="133"/>
-      <c r="V13" s="135">
+      <c r="U13" s="112"/>
+      <c r="V13" s="109">
         <v>0</v>
       </c>
-      <c r="W13" s="135"/>
-      <c r="X13" s="121">
+      <c r="W13" s="109"/>
+      <c r="X13" s="130">
         <v>0</v>
       </c>
-      <c r="Y13" s="121"/>
+      <c r="Y13" s="130"/>
       <c r="Z13" s="12"/>
       <c r="AA13" s="13"/>
       <c r="AB13" s="14"/>
@@ -6919,54 +6938,54 @@
       <c r="AL13" s="12"/>
       <c r="AM13" s="13"/>
       <c r="AN13" s="14"/>
-      <c r="AO13" s="131"/>
-      <c r="AP13" s="131"/>
-      <c r="AQ13" s="131"/>
-      <c r="AR13" s="131"/>
-      <c r="AS13" s="131"/>
-      <c r="AT13" s="131"/>
-      <c r="AU13" s="131"/>
-      <c r="AV13" s="131"/>
-      <c r="AW13" s="131"/>
-      <c r="AX13" s="131"/>
-      <c r="AY13" s="131"/>
-      <c r="AZ13" s="132"/>
+      <c r="AO13" s="106"/>
+      <c r="AP13" s="106"/>
+      <c r="AQ13" s="106"/>
+      <c r="AR13" s="106"/>
+      <c r="AS13" s="106"/>
+      <c r="AT13" s="106"/>
+      <c r="AU13" s="106"/>
+      <c r="AV13" s="106"/>
+      <c r="AW13" s="106"/>
+      <c r="AX13" s="106"/>
+      <c r="AY13" s="106"/>
+      <c r="AZ13" s="128"/>
     </row>
     <row r="14" spans="2:52" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B14" s="145">
+      <c r="B14" s="110">
         <v>5</v>
       </c>
-      <c r="C14" s="90" t="s">
+      <c r="C14" s="114" t="s">
         <v>91</v>
       </c>
-      <c r="D14" s="91"/>
-      <c r="E14" s="91"/>
-      <c r="F14" s="91"/>
-      <c r="G14" s="91"/>
-      <c r="H14" s="91"/>
-      <c r="I14" s="92"/>
-      <c r="J14" s="171"/>
-      <c r="K14" s="131"/>
-      <c r="L14" s="131"/>
-      <c r="M14" s="131"/>
-      <c r="N14" s="131"/>
-      <c r="O14" s="131"/>
-      <c r="P14" s="131"/>
-      <c r="Q14" s="96"/>
-      <c r="R14" s="97"/>
-      <c r="S14" s="98"/>
-      <c r="T14" s="136" t="s">
+      <c r="D14" s="115"/>
+      <c r="E14" s="115"/>
+      <c r="F14" s="115"/>
+      <c r="G14" s="115"/>
+      <c r="H14" s="115"/>
+      <c r="I14" s="116"/>
+      <c r="J14" s="107"/>
+      <c r="K14" s="106"/>
+      <c r="L14" s="106"/>
+      <c r="M14" s="106"/>
+      <c r="N14" s="106"/>
+      <c r="O14" s="106"/>
+      <c r="P14" s="106"/>
+      <c r="Q14" s="172"/>
+      <c r="R14" s="173"/>
+      <c r="S14" s="174"/>
+      <c r="T14" s="111" t="s">
         <v>87</v>
       </c>
-      <c r="U14" s="136"/>
-      <c r="V14" s="134">
+      <c r="U14" s="111"/>
+      <c r="V14" s="108">
         <v>0</v>
       </c>
-      <c r="W14" s="134"/>
-      <c r="X14" s="120">
+      <c r="W14" s="108"/>
+      <c r="X14" s="129">
         <v>0</v>
       </c>
-      <c r="Y14" s="120"/>
+      <c r="Y14" s="129"/>
       <c r="Z14" s="9"/>
       <c r="AA14" s="10"/>
       <c r="AB14" s="11"/>
@@ -6982,50 +7001,50 @@
       <c r="AL14" s="9"/>
       <c r="AM14" s="10"/>
       <c r="AN14" s="11"/>
-      <c r="AO14" s="131"/>
-      <c r="AP14" s="131"/>
-      <c r="AQ14" s="131"/>
-      <c r="AR14" s="131"/>
-      <c r="AS14" s="131"/>
-      <c r="AT14" s="131"/>
-      <c r="AU14" s="131"/>
-      <c r="AV14" s="131"/>
-      <c r="AW14" s="131"/>
-      <c r="AX14" s="131"/>
-      <c r="AY14" s="131"/>
-      <c r="AZ14" s="132"/>
+      <c r="AO14" s="106"/>
+      <c r="AP14" s="106"/>
+      <c r="AQ14" s="106"/>
+      <c r="AR14" s="106"/>
+      <c r="AS14" s="106"/>
+      <c r="AT14" s="106"/>
+      <c r="AU14" s="106"/>
+      <c r="AV14" s="106"/>
+      <c r="AW14" s="106"/>
+      <c r="AX14" s="106"/>
+      <c r="AY14" s="106"/>
+      <c r="AZ14" s="128"/>
     </row>
     <row r="15" spans="2:52" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B15" s="145"/>
-      <c r="C15" s="93"/>
-      <c r="D15" s="94"/>
-      <c r="E15" s="94"/>
-      <c r="F15" s="94"/>
-      <c r="G15" s="94"/>
-      <c r="H15" s="94"/>
-      <c r="I15" s="95"/>
-      <c r="J15" s="131"/>
-      <c r="K15" s="131"/>
-      <c r="L15" s="131"/>
-      <c r="M15" s="131"/>
-      <c r="N15" s="131"/>
-      <c r="O15" s="131"/>
-      <c r="P15" s="131"/>
-      <c r="Q15" s="99"/>
-      <c r="R15" s="100"/>
-      <c r="S15" s="101"/>
-      <c r="T15" s="133" t="s">
+      <c r="B15" s="110"/>
+      <c r="C15" s="117"/>
+      <c r="D15" s="118"/>
+      <c r="E15" s="118"/>
+      <c r="F15" s="118"/>
+      <c r="G15" s="118"/>
+      <c r="H15" s="118"/>
+      <c r="I15" s="119"/>
+      <c r="J15" s="106"/>
+      <c r="K15" s="106"/>
+      <c r="L15" s="106"/>
+      <c r="M15" s="106"/>
+      <c r="N15" s="106"/>
+      <c r="O15" s="106"/>
+      <c r="P15" s="106"/>
+      <c r="Q15" s="175"/>
+      <c r="R15" s="176"/>
+      <c r="S15" s="177"/>
+      <c r="T15" s="112" t="s">
         <v>25</v>
       </c>
-      <c r="U15" s="133"/>
-      <c r="V15" s="135">
+      <c r="U15" s="112"/>
+      <c r="V15" s="109">
         <v>0</v>
       </c>
-      <c r="W15" s="135"/>
-      <c r="X15" s="121">
+      <c r="W15" s="109"/>
+      <c r="X15" s="130">
         <v>0</v>
       </c>
-      <c r="Y15" s="121"/>
+      <c r="Y15" s="130"/>
       <c r="Z15" s="12"/>
       <c r="AA15" s="13"/>
       <c r="AB15" s="14"/>
@@ -7041,54 +7060,54 @@
       <c r="AL15" s="12"/>
       <c r="AM15" s="13"/>
       <c r="AN15" s="14"/>
-      <c r="AO15" s="131"/>
-      <c r="AP15" s="131"/>
-      <c r="AQ15" s="131"/>
-      <c r="AR15" s="131"/>
-      <c r="AS15" s="131"/>
-      <c r="AT15" s="131"/>
-      <c r="AU15" s="131"/>
-      <c r="AV15" s="131"/>
-      <c r="AW15" s="131"/>
-      <c r="AX15" s="131"/>
-      <c r="AY15" s="131"/>
-      <c r="AZ15" s="132"/>
+      <c r="AO15" s="106"/>
+      <c r="AP15" s="106"/>
+      <c r="AQ15" s="106"/>
+      <c r="AR15" s="106"/>
+      <c r="AS15" s="106"/>
+      <c r="AT15" s="106"/>
+      <c r="AU15" s="106"/>
+      <c r="AV15" s="106"/>
+      <c r="AW15" s="106"/>
+      <c r="AX15" s="106"/>
+      <c r="AY15" s="106"/>
+      <c r="AZ15" s="128"/>
     </row>
     <row r="16" spans="2:52" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B16" s="145">
+      <c r="B16" s="110">
         <v>6</v>
       </c>
-      <c r="C16" s="90" t="s">
+      <c r="C16" s="114" t="s">
         <v>92</v>
       </c>
-      <c r="D16" s="91"/>
-      <c r="E16" s="91"/>
-      <c r="F16" s="91"/>
-      <c r="G16" s="91"/>
-      <c r="H16" s="91"/>
-      <c r="I16" s="92"/>
-      <c r="J16" s="171"/>
-      <c r="K16" s="131"/>
-      <c r="L16" s="131"/>
-      <c r="M16" s="131"/>
-      <c r="N16" s="131"/>
-      <c r="O16" s="131"/>
-      <c r="P16" s="131"/>
-      <c r="Q16" s="122"/>
-      <c r="R16" s="122"/>
-      <c r="S16" s="122"/>
-      <c r="T16" s="136" t="s">
+      <c r="D16" s="115"/>
+      <c r="E16" s="115"/>
+      <c r="F16" s="115"/>
+      <c r="G16" s="115"/>
+      <c r="H16" s="115"/>
+      <c r="I16" s="116"/>
+      <c r="J16" s="107"/>
+      <c r="K16" s="106"/>
+      <c r="L16" s="106"/>
+      <c r="M16" s="106"/>
+      <c r="N16" s="106"/>
+      <c r="O16" s="106"/>
+      <c r="P16" s="106"/>
+      <c r="Q16" s="113"/>
+      <c r="R16" s="113"/>
+      <c r="S16" s="113"/>
+      <c r="T16" s="111" t="s">
         <v>87</v>
       </c>
-      <c r="U16" s="136"/>
-      <c r="V16" s="134">
+      <c r="U16" s="111"/>
+      <c r="V16" s="108">
         <v>0</v>
       </c>
-      <c r="W16" s="134"/>
-      <c r="X16" s="120">
+      <c r="W16" s="108"/>
+      <c r="X16" s="129">
         <v>0</v>
       </c>
-      <c r="Y16" s="120"/>
+      <c r="Y16" s="129"/>
       <c r="Z16" s="9"/>
       <c r="AA16" s="10"/>
       <c r="AB16" s="11"/>
@@ -7104,50 +7123,50 @@
       <c r="AL16" s="9"/>
       <c r="AM16" s="10"/>
       <c r="AN16" s="11"/>
-      <c r="AO16" s="131"/>
-      <c r="AP16" s="131"/>
-      <c r="AQ16" s="131"/>
-      <c r="AR16" s="131"/>
-      <c r="AS16" s="131"/>
-      <c r="AT16" s="131"/>
-      <c r="AU16" s="131"/>
-      <c r="AV16" s="131"/>
-      <c r="AW16" s="131"/>
-      <c r="AX16" s="131"/>
-      <c r="AY16" s="131"/>
-      <c r="AZ16" s="132"/>
+      <c r="AO16" s="106"/>
+      <c r="AP16" s="106"/>
+      <c r="AQ16" s="106"/>
+      <c r="AR16" s="106"/>
+      <c r="AS16" s="106"/>
+      <c r="AT16" s="106"/>
+      <c r="AU16" s="106"/>
+      <c r="AV16" s="106"/>
+      <c r="AW16" s="106"/>
+      <c r="AX16" s="106"/>
+      <c r="AY16" s="106"/>
+      <c r="AZ16" s="128"/>
     </row>
     <row r="17" spans="2:52" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B17" s="145"/>
-      <c r="C17" s="93"/>
-      <c r="D17" s="94"/>
-      <c r="E17" s="94"/>
-      <c r="F17" s="94"/>
-      <c r="G17" s="94"/>
-      <c r="H17" s="94"/>
-      <c r="I17" s="95"/>
-      <c r="J17" s="131"/>
-      <c r="K17" s="131"/>
-      <c r="L17" s="131"/>
-      <c r="M17" s="131"/>
-      <c r="N17" s="131"/>
-      <c r="O17" s="131"/>
-      <c r="P17" s="131"/>
-      <c r="Q17" s="122"/>
-      <c r="R17" s="122"/>
-      <c r="S17" s="122"/>
-      <c r="T17" s="133" t="s">
+      <c r="B17" s="110"/>
+      <c r="C17" s="117"/>
+      <c r="D17" s="118"/>
+      <c r="E17" s="118"/>
+      <c r="F17" s="118"/>
+      <c r="G17" s="118"/>
+      <c r="H17" s="118"/>
+      <c r="I17" s="119"/>
+      <c r="J17" s="106"/>
+      <c r="K17" s="106"/>
+      <c r="L17" s="106"/>
+      <c r="M17" s="106"/>
+      <c r="N17" s="106"/>
+      <c r="O17" s="106"/>
+      <c r="P17" s="106"/>
+      <c r="Q17" s="113"/>
+      <c r="R17" s="113"/>
+      <c r="S17" s="113"/>
+      <c r="T17" s="112" t="s">
         <v>25</v>
       </c>
-      <c r="U17" s="133"/>
-      <c r="V17" s="135">
+      <c r="U17" s="112"/>
+      <c r="V17" s="109">
         <v>0</v>
       </c>
-      <c r="W17" s="135"/>
-      <c r="X17" s="121">
+      <c r="W17" s="109"/>
+      <c r="X17" s="130">
         <v>0</v>
       </c>
-      <c r="Y17" s="121"/>
+      <c r="Y17" s="130"/>
       <c r="Z17" s="12"/>
       <c r="AA17" s="13"/>
       <c r="AB17" s="14"/>
@@ -7163,54 +7182,54 @@
       <c r="AL17" s="12"/>
       <c r="AM17" s="13"/>
       <c r="AN17" s="14"/>
-      <c r="AO17" s="131"/>
-      <c r="AP17" s="131"/>
-      <c r="AQ17" s="131"/>
-      <c r="AR17" s="131"/>
-      <c r="AS17" s="131"/>
-      <c r="AT17" s="131"/>
-      <c r="AU17" s="131"/>
-      <c r="AV17" s="131"/>
-      <c r="AW17" s="131"/>
-      <c r="AX17" s="131"/>
-      <c r="AY17" s="131"/>
-      <c r="AZ17" s="132"/>
+      <c r="AO17" s="106"/>
+      <c r="AP17" s="106"/>
+      <c r="AQ17" s="106"/>
+      <c r="AR17" s="106"/>
+      <c r="AS17" s="106"/>
+      <c r="AT17" s="106"/>
+      <c r="AU17" s="106"/>
+      <c r="AV17" s="106"/>
+      <c r="AW17" s="106"/>
+      <c r="AX17" s="106"/>
+      <c r="AY17" s="106"/>
+      <c r="AZ17" s="128"/>
     </row>
     <row r="18" spans="2:52" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B18" s="82">
+      <c r="B18" s="126">
         <v>7</v>
       </c>
-      <c r="C18" s="84" t="s">
+      <c r="C18" s="159" t="s">
         <v>93</v>
       </c>
-      <c r="D18" s="85"/>
-      <c r="E18" s="85"/>
-      <c r="F18" s="85"/>
-      <c r="G18" s="85"/>
-      <c r="H18" s="85"/>
-      <c r="I18" s="86"/>
-      <c r="J18" s="90"/>
-      <c r="K18" s="91"/>
-      <c r="L18" s="91"/>
-      <c r="M18" s="91"/>
-      <c r="N18" s="91"/>
-      <c r="O18" s="91"/>
-      <c r="P18" s="92"/>
-      <c r="Q18" s="96"/>
-      <c r="R18" s="97"/>
-      <c r="S18" s="98"/>
-      <c r="T18" s="102" t="s">
+      <c r="D18" s="160"/>
+      <c r="E18" s="160"/>
+      <c r="F18" s="160"/>
+      <c r="G18" s="160"/>
+      <c r="H18" s="160"/>
+      <c r="I18" s="161"/>
+      <c r="J18" s="114"/>
+      <c r="K18" s="115"/>
+      <c r="L18" s="115"/>
+      <c r="M18" s="115"/>
+      <c r="N18" s="115"/>
+      <c r="O18" s="115"/>
+      <c r="P18" s="116"/>
+      <c r="Q18" s="172"/>
+      <c r="R18" s="173"/>
+      <c r="S18" s="174"/>
+      <c r="T18" s="162" t="s">
         <v>87</v>
       </c>
-      <c r="U18" s="103"/>
-      <c r="V18" s="104">
+      <c r="U18" s="163"/>
+      <c r="V18" s="122">
         <v>0</v>
       </c>
-      <c r="W18" s="105"/>
-      <c r="X18" s="106">
+      <c r="W18" s="123"/>
+      <c r="X18" s="168">
         <v>0</v>
       </c>
-      <c r="Y18" s="107"/>
+      <c r="Y18" s="169"/>
       <c r="Z18" s="9"/>
       <c r="AA18" s="10"/>
       <c r="AB18" s="11"/>
@@ -7226,50 +7245,50 @@
       <c r="AL18" s="9"/>
       <c r="AM18" s="10"/>
       <c r="AN18" s="11"/>
-      <c r="AO18" s="90"/>
-      <c r="AP18" s="91"/>
-      <c r="AQ18" s="91"/>
-      <c r="AR18" s="91"/>
-      <c r="AS18" s="91"/>
-      <c r="AT18" s="91"/>
-      <c r="AU18" s="91"/>
-      <c r="AV18" s="91"/>
-      <c r="AW18" s="91"/>
-      <c r="AX18" s="91"/>
-      <c r="AY18" s="91"/>
-      <c r="AZ18" s="108"/>
+      <c r="AO18" s="114"/>
+      <c r="AP18" s="115"/>
+      <c r="AQ18" s="115"/>
+      <c r="AR18" s="115"/>
+      <c r="AS18" s="115"/>
+      <c r="AT18" s="115"/>
+      <c r="AU18" s="115"/>
+      <c r="AV18" s="115"/>
+      <c r="AW18" s="115"/>
+      <c r="AX18" s="115"/>
+      <c r="AY18" s="115"/>
+      <c r="AZ18" s="164"/>
     </row>
     <row r="19" spans="2:52" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B19" s="83"/>
-      <c r="C19" s="87"/>
-      <c r="D19" s="88"/>
-      <c r="E19" s="88"/>
-      <c r="F19" s="88"/>
-      <c r="G19" s="88"/>
-      <c r="H19" s="88"/>
-      <c r="I19" s="89"/>
-      <c r="J19" s="93"/>
-      <c r="K19" s="94"/>
-      <c r="L19" s="94"/>
-      <c r="M19" s="94"/>
-      <c r="N19" s="94"/>
-      <c r="O19" s="94"/>
-      <c r="P19" s="95"/>
-      <c r="Q19" s="99"/>
-      <c r="R19" s="100"/>
-      <c r="S19" s="101"/>
-      <c r="T19" s="110" t="s">
+      <c r="B19" s="127"/>
+      <c r="C19" s="144"/>
+      <c r="D19" s="145"/>
+      <c r="E19" s="145"/>
+      <c r="F19" s="145"/>
+      <c r="G19" s="145"/>
+      <c r="H19" s="145"/>
+      <c r="I19" s="146"/>
+      <c r="J19" s="117"/>
+      <c r="K19" s="118"/>
+      <c r="L19" s="118"/>
+      <c r="M19" s="118"/>
+      <c r="N19" s="118"/>
+      <c r="O19" s="118"/>
+      <c r="P19" s="119"/>
+      <c r="Q19" s="175"/>
+      <c r="R19" s="176"/>
+      <c r="S19" s="177"/>
+      <c r="T19" s="166" t="s">
         <v>25</v>
       </c>
-      <c r="U19" s="111"/>
-      <c r="V19" s="112">
+      <c r="U19" s="167"/>
+      <c r="V19" s="124">
         <v>0</v>
       </c>
-      <c r="W19" s="113"/>
-      <c r="X19" s="114">
+      <c r="W19" s="125"/>
+      <c r="X19" s="170">
         <v>0</v>
       </c>
-      <c r="Y19" s="115"/>
+      <c r="Y19" s="171"/>
       <c r="Z19" s="12"/>
       <c r="AA19" s="13"/>
       <c r="AB19" s="14"/>
@@ -7285,54 +7304,54 @@
       <c r="AL19" s="12"/>
       <c r="AM19" s="13"/>
       <c r="AN19" s="14"/>
-      <c r="AO19" s="93"/>
-      <c r="AP19" s="94"/>
-      <c r="AQ19" s="94"/>
-      <c r="AR19" s="94"/>
-      <c r="AS19" s="94"/>
-      <c r="AT19" s="94"/>
-      <c r="AU19" s="94"/>
-      <c r="AV19" s="94"/>
-      <c r="AW19" s="94"/>
-      <c r="AX19" s="94"/>
-      <c r="AY19" s="94"/>
-      <c r="AZ19" s="109"/>
+      <c r="AO19" s="117"/>
+      <c r="AP19" s="118"/>
+      <c r="AQ19" s="118"/>
+      <c r="AR19" s="118"/>
+      <c r="AS19" s="118"/>
+      <c r="AT19" s="118"/>
+      <c r="AU19" s="118"/>
+      <c r="AV19" s="118"/>
+      <c r="AW19" s="118"/>
+      <c r="AX19" s="118"/>
+      <c r="AY19" s="118"/>
+      <c r="AZ19" s="165"/>
     </row>
     <row r="20" spans="2:52" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B20" s="82">
+      <c r="B20" s="126">
         <v>8</v>
       </c>
-      <c r="C20" s="84" t="s">
+      <c r="C20" s="159" t="s">
         <v>94</v>
       </c>
-      <c r="D20" s="85"/>
-      <c r="E20" s="85"/>
-      <c r="F20" s="85"/>
-      <c r="G20" s="85"/>
-      <c r="H20" s="85"/>
-      <c r="I20" s="86"/>
-      <c r="J20" s="90"/>
-      <c r="K20" s="91"/>
-      <c r="L20" s="91"/>
-      <c r="M20" s="91"/>
-      <c r="N20" s="91"/>
-      <c r="O20" s="91"/>
-      <c r="P20" s="92"/>
-      <c r="Q20" s="96"/>
-      <c r="R20" s="97"/>
-      <c r="S20" s="98"/>
-      <c r="T20" s="102" t="s">
+      <c r="D20" s="160"/>
+      <c r="E20" s="160"/>
+      <c r="F20" s="160"/>
+      <c r="G20" s="160"/>
+      <c r="H20" s="160"/>
+      <c r="I20" s="161"/>
+      <c r="J20" s="114"/>
+      <c r="K20" s="115"/>
+      <c r="L20" s="115"/>
+      <c r="M20" s="115"/>
+      <c r="N20" s="115"/>
+      <c r="O20" s="115"/>
+      <c r="P20" s="116"/>
+      <c r="Q20" s="172"/>
+      <c r="R20" s="173"/>
+      <c r="S20" s="174"/>
+      <c r="T20" s="162" t="s">
         <v>87</v>
       </c>
-      <c r="U20" s="103"/>
-      <c r="V20" s="104">
+      <c r="U20" s="163"/>
+      <c r="V20" s="122">
         <v>0</v>
       </c>
-      <c r="W20" s="105"/>
-      <c r="X20" s="106">
+      <c r="W20" s="123"/>
+      <c r="X20" s="168">
         <v>0</v>
       </c>
-      <c r="Y20" s="107"/>
+      <c r="Y20" s="169"/>
       <c r="Z20" s="9"/>
       <c r="AA20" s="10"/>
       <c r="AB20" s="11"/>
@@ -7348,50 +7367,50 @@
       <c r="AL20" s="9"/>
       <c r="AM20" s="10"/>
       <c r="AN20" s="11"/>
-      <c r="AO20" s="90"/>
-      <c r="AP20" s="91"/>
-      <c r="AQ20" s="91"/>
-      <c r="AR20" s="91"/>
-      <c r="AS20" s="91"/>
-      <c r="AT20" s="91"/>
-      <c r="AU20" s="91"/>
-      <c r="AV20" s="91"/>
-      <c r="AW20" s="91"/>
-      <c r="AX20" s="91"/>
-      <c r="AY20" s="91"/>
-      <c r="AZ20" s="108"/>
+      <c r="AO20" s="114"/>
+      <c r="AP20" s="115"/>
+      <c r="AQ20" s="115"/>
+      <c r="AR20" s="115"/>
+      <c r="AS20" s="115"/>
+      <c r="AT20" s="115"/>
+      <c r="AU20" s="115"/>
+      <c r="AV20" s="115"/>
+      <c r="AW20" s="115"/>
+      <c r="AX20" s="115"/>
+      <c r="AY20" s="115"/>
+      <c r="AZ20" s="164"/>
     </row>
     <row r="21" spans="2:52" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B21" s="83"/>
-      <c r="C21" s="87"/>
-      <c r="D21" s="88"/>
-      <c r="E21" s="88"/>
-      <c r="F21" s="88"/>
-      <c r="G21" s="88"/>
-      <c r="H21" s="88"/>
-      <c r="I21" s="89"/>
-      <c r="J21" s="93"/>
-      <c r="K21" s="94"/>
-      <c r="L21" s="94"/>
-      <c r="M21" s="94"/>
-      <c r="N21" s="94"/>
-      <c r="O21" s="94"/>
-      <c r="P21" s="95"/>
-      <c r="Q21" s="99"/>
-      <c r="R21" s="100"/>
-      <c r="S21" s="101"/>
-      <c r="T21" s="110" t="s">
+      <c r="B21" s="127"/>
+      <c r="C21" s="144"/>
+      <c r="D21" s="145"/>
+      <c r="E21" s="145"/>
+      <c r="F21" s="145"/>
+      <c r="G21" s="145"/>
+      <c r="H21" s="145"/>
+      <c r="I21" s="146"/>
+      <c r="J21" s="117"/>
+      <c r="K21" s="118"/>
+      <c r="L21" s="118"/>
+      <c r="M21" s="118"/>
+      <c r="N21" s="118"/>
+      <c r="O21" s="118"/>
+      <c r="P21" s="119"/>
+      <c r="Q21" s="175"/>
+      <c r="R21" s="176"/>
+      <c r="S21" s="177"/>
+      <c r="T21" s="166" t="s">
         <v>25</v>
       </c>
-      <c r="U21" s="111"/>
-      <c r="V21" s="112">
+      <c r="U21" s="167"/>
+      <c r="V21" s="124">
         <v>0</v>
       </c>
-      <c r="W21" s="113"/>
-      <c r="X21" s="114">
+      <c r="W21" s="125"/>
+      <c r="X21" s="170">
         <v>0</v>
       </c>
-      <c r="Y21" s="115"/>
+      <c r="Y21" s="171"/>
       <c r="Z21" s="12"/>
       <c r="AA21" s="13"/>
       <c r="AB21" s="14"/>
@@ -7407,54 +7426,54 @@
       <c r="AL21" s="12"/>
       <c r="AM21" s="13"/>
       <c r="AN21" s="14"/>
-      <c r="AO21" s="93"/>
-      <c r="AP21" s="94"/>
-      <c r="AQ21" s="94"/>
-      <c r="AR21" s="94"/>
-      <c r="AS21" s="94"/>
-      <c r="AT21" s="94"/>
-      <c r="AU21" s="94"/>
-      <c r="AV21" s="94"/>
-      <c r="AW21" s="94"/>
-      <c r="AX21" s="94"/>
-      <c r="AY21" s="94"/>
-      <c r="AZ21" s="109"/>
+      <c r="AO21" s="117"/>
+      <c r="AP21" s="118"/>
+      <c r="AQ21" s="118"/>
+      <c r="AR21" s="118"/>
+      <c r="AS21" s="118"/>
+      <c r="AT21" s="118"/>
+      <c r="AU21" s="118"/>
+      <c r="AV21" s="118"/>
+      <c r="AW21" s="118"/>
+      <c r="AX21" s="118"/>
+      <c r="AY21" s="118"/>
+      <c r="AZ21" s="165"/>
     </row>
     <row r="22" spans="2:52" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B22" s="152">
+      <c r="B22" s="139">
         <v>9</v>
       </c>
-      <c r="C22" s="154" t="s">
+      <c r="C22" s="141" t="s">
         <v>95</v>
       </c>
-      <c r="D22" s="155"/>
-      <c r="E22" s="155"/>
-      <c r="F22" s="155"/>
-      <c r="G22" s="155"/>
-      <c r="H22" s="155"/>
-      <c r="I22" s="156"/>
-      <c r="J22" s="139"/>
-      <c r="K22" s="140"/>
-      <c r="L22" s="140"/>
-      <c r="M22" s="140"/>
-      <c r="N22" s="140"/>
-      <c r="O22" s="140"/>
-      <c r="P22" s="141"/>
-      <c r="Q22" s="161"/>
-      <c r="R22" s="162"/>
-      <c r="S22" s="163"/>
-      <c r="T22" s="157" t="s">
+      <c r="D22" s="142"/>
+      <c r="E22" s="142"/>
+      <c r="F22" s="142"/>
+      <c r="G22" s="142"/>
+      <c r="H22" s="142"/>
+      <c r="I22" s="143"/>
+      <c r="J22" s="131"/>
+      <c r="K22" s="132"/>
+      <c r="L22" s="132"/>
+      <c r="M22" s="132"/>
+      <c r="N22" s="132"/>
+      <c r="O22" s="132"/>
+      <c r="P22" s="180"/>
+      <c r="Q22" s="151"/>
+      <c r="R22" s="152"/>
+      <c r="S22" s="153"/>
+      <c r="T22" s="147" t="s">
         <v>87</v>
       </c>
-      <c r="U22" s="158"/>
-      <c r="V22" s="137">
+      <c r="U22" s="148"/>
+      <c r="V22" s="178">
         <v>0</v>
       </c>
-      <c r="W22" s="138"/>
-      <c r="X22" s="150">
+      <c r="W22" s="179"/>
+      <c r="X22" s="137">
         <v>0</v>
       </c>
-      <c r="Y22" s="151"/>
+      <c r="Y22" s="138"/>
       <c r="Z22" s="24"/>
       <c r="AA22" s="25"/>
       <c r="AB22" s="26"/>
@@ -7470,50 +7489,50 @@
       <c r="AL22" s="24"/>
       <c r="AM22" s="25"/>
       <c r="AN22" s="26"/>
-      <c r="AO22" s="139"/>
-      <c r="AP22" s="140"/>
-      <c r="AQ22" s="140"/>
-      <c r="AR22" s="140"/>
-      <c r="AS22" s="140"/>
-      <c r="AT22" s="140"/>
-      <c r="AU22" s="140"/>
-      <c r="AV22" s="140"/>
-      <c r="AW22" s="140"/>
-      <c r="AX22" s="140"/>
-      <c r="AY22" s="140"/>
-      <c r="AZ22" s="148"/>
+      <c r="AO22" s="131"/>
+      <c r="AP22" s="132"/>
+      <c r="AQ22" s="132"/>
+      <c r="AR22" s="132"/>
+      <c r="AS22" s="132"/>
+      <c r="AT22" s="132"/>
+      <c r="AU22" s="132"/>
+      <c r="AV22" s="132"/>
+      <c r="AW22" s="132"/>
+      <c r="AX22" s="132"/>
+      <c r="AY22" s="132"/>
+      <c r="AZ22" s="133"/>
     </row>
     <row r="23" spans="2:52" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B23" s="153"/>
-      <c r="C23" s="87"/>
-      <c r="D23" s="88"/>
-      <c r="E23" s="88"/>
-      <c r="F23" s="88"/>
-      <c r="G23" s="88"/>
-      <c r="H23" s="88"/>
-      <c r="I23" s="89"/>
-      <c r="J23" s="142"/>
-      <c r="K23" s="143"/>
-      <c r="L23" s="143"/>
-      <c r="M23" s="143"/>
-      <c r="N23" s="143"/>
-      <c r="O23" s="143"/>
-      <c r="P23" s="144"/>
-      <c r="Q23" s="164"/>
-      <c r="R23" s="165"/>
-      <c r="S23" s="166"/>
-      <c r="T23" s="159" t="s">
+      <c r="B23" s="140"/>
+      <c r="C23" s="144"/>
+      <c r="D23" s="145"/>
+      <c r="E23" s="145"/>
+      <c r="F23" s="145"/>
+      <c r="G23" s="145"/>
+      <c r="H23" s="145"/>
+      <c r="I23" s="146"/>
+      <c r="J23" s="134"/>
+      <c r="K23" s="135"/>
+      <c r="L23" s="135"/>
+      <c r="M23" s="135"/>
+      <c r="N23" s="135"/>
+      <c r="O23" s="135"/>
+      <c r="P23" s="181"/>
+      <c r="Q23" s="154"/>
+      <c r="R23" s="155"/>
+      <c r="S23" s="156"/>
+      <c r="T23" s="149" t="s">
         <v>25</v>
       </c>
-      <c r="U23" s="160"/>
-      <c r="V23" s="146">
+      <c r="U23" s="150"/>
+      <c r="V23" s="120">
         <v>0</v>
       </c>
-      <c r="W23" s="147"/>
-      <c r="X23" s="167">
+      <c r="W23" s="121"/>
+      <c r="X23" s="157">
         <v>0</v>
       </c>
-      <c r="Y23" s="168"/>
+      <c r="Y23" s="158"/>
       <c r="Z23" s="15"/>
       <c r="AA23" s="16"/>
       <c r="AB23" s="17"/>
@@ -7529,18 +7548,18 @@
       <c r="AL23" s="15"/>
       <c r="AM23" s="16"/>
       <c r="AN23" s="17"/>
-      <c r="AO23" s="142"/>
-      <c r="AP23" s="143"/>
-      <c r="AQ23" s="143"/>
-      <c r="AR23" s="143"/>
-      <c r="AS23" s="143"/>
-      <c r="AT23" s="143"/>
-      <c r="AU23" s="143"/>
-      <c r="AV23" s="143"/>
-      <c r="AW23" s="143"/>
-      <c r="AX23" s="143"/>
-      <c r="AY23" s="143"/>
-      <c r="AZ23" s="149"/>
+      <c r="AO23" s="134"/>
+      <c r="AP23" s="135"/>
+      <c r="AQ23" s="135"/>
+      <c r="AR23" s="135"/>
+      <c r="AS23" s="135"/>
+      <c r="AT23" s="135"/>
+      <c r="AU23" s="135"/>
+      <c r="AV23" s="135"/>
+      <c r="AW23" s="135"/>
+      <c r="AX23" s="135"/>
+      <c r="AY23" s="135"/>
+      <c r="AZ23" s="136"/>
     </row>
     <row r="24" spans="2:52" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D24" s="18"/>
@@ -7599,27 +7618,74 @@
     <row r="50" ht="18" customHeight="1" x14ac:dyDescent="0.2"/>
   </sheetData>
   <mergeCells count="113">
-    <mergeCell ref="B1:P1"/>
-    <mergeCell ref="J10:P11"/>
-    <mergeCell ref="J12:P13"/>
-    <mergeCell ref="J14:P15"/>
-    <mergeCell ref="J16:P17"/>
-    <mergeCell ref="V10:W10"/>
-    <mergeCell ref="V11:W11"/>
-    <mergeCell ref="V13:W13"/>
-    <mergeCell ref="V14:W14"/>
-    <mergeCell ref="V15:W15"/>
-    <mergeCell ref="V17:W17"/>
-    <mergeCell ref="B6:B7"/>
-    <mergeCell ref="T6:U6"/>
-    <mergeCell ref="T7:U7"/>
-    <mergeCell ref="B10:B11"/>
-    <mergeCell ref="C10:I11"/>
-    <mergeCell ref="Q8:S9"/>
-    <mergeCell ref="Q10:S11"/>
-    <mergeCell ref="B8:B9"/>
-    <mergeCell ref="C8:I9"/>
-    <mergeCell ref="J8:P9"/>
+    <mergeCell ref="B20:B21"/>
+    <mergeCell ref="C20:I21"/>
+    <mergeCell ref="J20:P21"/>
+    <mergeCell ref="Q20:S21"/>
+    <mergeCell ref="T20:U20"/>
+    <mergeCell ref="V20:W20"/>
+    <mergeCell ref="X20:Y20"/>
+    <mergeCell ref="AO20:AZ21"/>
+    <mergeCell ref="T21:U21"/>
+    <mergeCell ref="V21:W21"/>
+    <mergeCell ref="X21:Y21"/>
+    <mergeCell ref="AO4:AZ5"/>
+    <mergeCell ref="AI4:AK4"/>
+    <mergeCell ref="AL4:AN4"/>
+    <mergeCell ref="AF4:AH4"/>
+    <mergeCell ref="X6:Y6"/>
+    <mergeCell ref="X7:Y7"/>
+    <mergeCell ref="X8:Y8"/>
+    <mergeCell ref="B2:I2"/>
+    <mergeCell ref="J2:AD2"/>
+    <mergeCell ref="X4:Y5"/>
+    <mergeCell ref="T4:W5"/>
+    <mergeCell ref="Z4:AB4"/>
+    <mergeCell ref="AC4:AE4"/>
+    <mergeCell ref="B4:I5"/>
+    <mergeCell ref="J4:P5"/>
+    <mergeCell ref="Q4:S5"/>
+    <mergeCell ref="AO6:AZ7"/>
+    <mergeCell ref="C6:I7"/>
+    <mergeCell ref="Q6:S7"/>
+    <mergeCell ref="J6:P7"/>
+    <mergeCell ref="AO10:AZ11"/>
+    <mergeCell ref="T11:U11"/>
+    <mergeCell ref="X9:Y9"/>
+    <mergeCell ref="X10:Y10"/>
+    <mergeCell ref="X11:Y11"/>
+    <mergeCell ref="V8:W8"/>
+    <mergeCell ref="V9:W9"/>
+    <mergeCell ref="AO8:AZ9"/>
+    <mergeCell ref="V6:W6"/>
+    <mergeCell ref="V7:W7"/>
+    <mergeCell ref="T9:U9"/>
+    <mergeCell ref="T10:U10"/>
+    <mergeCell ref="T8:U8"/>
+    <mergeCell ref="AO18:AZ19"/>
+    <mergeCell ref="T19:U19"/>
+    <mergeCell ref="X18:Y18"/>
+    <mergeCell ref="X19:Y19"/>
+    <mergeCell ref="Q18:S19"/>
+    <mergeCell ref="V22:W22"/>
+    <mergeCell ref="J22:P23"/>
+    <mergeCell ref="B12:B13"/>
+    <mergeCell ref="C12:I13"/>
+    <mergeCell ref="T12:U12"/>
+    <mergeCell ref="AO12:AZ13"/>
+    <mergeCell ref="T13:U13"/>
+    <mergeCell ref="X12:Y12"/>
+    <mergeCell ref="X13:Y13"/>
+    <mergeCell ref="V12:W12"/>
+    <mergeCell ref="B14:B15"/>
+    <mergeCell ref="C14:I15"/>
+    <mergeCell ref="T14:U14"/>
+    <mergeCell ref="AO14:AZ15"/>
+    <mergeCell ref="T15:U15"/>
+    <mergeCell ref="X14:Y14"/>
+    <mergeCell ref="X15:Y15"/>
+    <mergeCell ref="Q12:S13"/>
+    <mergeCell ref="Q14:S15"/>
     <mergeCell ref="V23:W23"/>
     <mergeCell ref="V18:W18"/>
     <mergeCell ref="V19:W19"/>
@@ -7644,74 +7710,27 @@
     <mergeCell ref="X23:Y23"/>
     <mergeCell ref="C18:I19"/>
     <mergeCell ref="T18:U18"/>
-    <mergeCell ref="AO18:AZ19"/>
-    <mergeCell ref="T19:U19"/>
-    <mergeCell ref="X18:Y18"/>
-    <mergeCell ref="X19:Y19"/>
-    <mergeCell ref="Q18:S19"/>
-    <mergeCell ref="V22:W22"/>
-    <mergeCell ref="J22:P23"/>
-    <mergeCell ref="B12:B13"/>
-    <mergeCell ref="C12:I13"/>
-    <mergeCell ref="T12:U12"/>
-    <mergeCell ref="AO12:AZ13"/>
-    <mergeCell ref="T13:U13"/>
-    <mergeCell ref="X12:Y12"/>
-    <mergeCell ref="X13:Y13"/>
-    <mergeCell ref="V12:W12"/>
-    <mergeCell ref="B14:B15"/>
-    <mergeCell ref="C14:I15"/>
-    <mergeCell ref="T14:U14"/>
-    <mergeCell ref="AO14:AZ15"/>
-    <mergeCell ref="T15:U15"/>
-    <mergeCell ref="X14:Y14"/>
-    <mergeCell ref="X15:Y15"/>
-    <mergeCell ref="Q12:S13"/>
-    <mergeCell ref="Q14:S15"/>
-    <mergeCell ref="AO10:AZ11"/>
-    <mergeCell ref="T11:U11"/>
-    <mergeCell ref="X9:Y9"/>
-    <mergeCell ref="X10:Y10"/>
-    <mergeCell ref="X11:Y11"/>
-    <mergeCell ref="V8:W8"/>
-    <mergeCell ref="V9:W9"/>
-    <mergeCell ref="AO8:AZ9"/>
-    <mergeCell ref="V6:W6"/>
-    <mergeCell ref="V7:W7"/>
-    <mergeCell ref="T9:U9"/>
-    <mergeCell ref="T10:U10"/>
-    <mergeCell ref="T8:U8"/>
-    <mergeCell ref="AO4:AZ5"/>
-    <mergeCell ref="AI4:AK4"/>
-    <mergeCell ref="AL4:AN4"/>
-    <mergeCell ref="AF4:AH4"/>
-    <mergeCell ref="X6:Y6"/>
-    <mergeCell ref="X7:Y7"/>
-    <mergeCell ref="X8:Y8"/>
-    <mergeCell ref="B2:I2"/>
-    <mergeCell ref="J2:AD2"/>
-    <mergeCell ref="X4:Y5"/>
-    <mergeCell ref="T4:W5"/>
-    <mergeCell ref="Z4:AB4"/>
-    <mergeCell ref="AC4:AE4"/>
-    <mergeCell ref="B4:I5"/>
-    <mergeCell ref="J4:P5"/>
-    <mergeCell ref="Q4:S5"/>
-    <mergeCell ref="AO6:AZ7"/>
-    <mergeCell ref="C6:I7"/>
-    <mergeCell ref="Q6:S7"/>
-    <mergeCell ref="J6:P7"/>
-    <mergeCell ref="B20:B21"/>
-    <mergeCell ref="C20:I21"/>
-    <mergeCell ref="J20:P21"/>
-    <mergeCell ref="Q20:S21"/>
-    <mergeCell ref="T20:U20"/>
-    <mergeCell ref="V20:W20"/>
-    <mergeCell ref="X20:Y20"/>
-    <mergeCell ref="AO20:AZ21"/>
-    <mergeCell ref="T21:U21"/>
-    <mergeCell ref="V21:W21"/>
-    <mergeCell ref="X21:Y21"/>
+    <mergeCell ref="B1:P1"/>
+    <mergeCell ref="J10:P11"/>
+    <mergeCell ref="J12:P13"/>
+    <mergeCell ref="J14:P15"/>
+    <mergeCell ref="J16:P17"/>
+    <mergeCell ref="V10:W10"/>
+    <mergeCell ref="V11:W11"/>
+    <mergeCell ref="V13:W13"/>
+    <mergeCell ref="V14:W14"/>
+    <mergeCell ref="V15:W15"/>
+    <mergeCell ref="V17:W17"/>
+    <mergeCell ref="B6:B7"/>
+    <mergeCell ref="T6:U6"/>
+    <mergeCell ref="T7:U7"/>
+    <mergeCell ref="B10:B11"/>
+    <mergeCell ref="C10:I11"/>
+    <mergeCell ref="Q8:S9"/>
+    <mergeCell ref="Q10:S11"/>
+    <mergeCell ref="B8:B9"/>
+    <mergeCell ref="C8:I9"/>
+    <mergeCell ref="J8:P9"/>
   </mergeCells>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.51200000000000001" footer="0.51200000000000001"/>
@@ -7735,610 +7754,609 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="27">
+      <c r="A1" s="28">
         <v>1</v>
       </c>
-      <c r="B1" s="34" t="s">
+      <c r="B1" s="32" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="34"/>
-      <c r="D1" s="34"/>
-      <c r="E1" s="172"/>
-      <c r="F1" s="172"/>
-      <c r="G1" s="172"/>
-      <c r="H1" s="172"/>
-      <c r="I1" s="172"/>
-      <c r="J1" s="173"/>
+      <c r="C1" s="32"/>
+      <c r="D1" s="32"/>
+      <c r="E1" s="78"/>
+      <c r="F1" s="78"/>
+      <c r="G1" s="78"/>
+      <c r="H1" s="78"/>
+      <c r="I1" s="78"/>
+      <c r="J1" s="79"/>
     </row>
     <row r="2" spans="1:10" ht="13.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="31"/>
-      <c r="B2" s="35"/>
-      <c r="C2" s="35"/>
-      <c r="D2" s="35"/>
-      <c r="E2" s="174"/>
-      <c r="F2" s="174"/>
-      <c r="G2" s="174"/>
-      <c r="H2" s="174"/>
-      <c r="I2" s="174"/>
-      <c r="J2" s="175"/>
+      <c r="A2" s="29"/>
+      <c r="B2" s="77"/>
+      <c r="C2" s="77"/>
+      <c r="D2" s="77"/>
+      <c r="E2" s="80"/>
+      <c r="F2" s="80"/>
+      <c r="G2" s="80"/>
+      <c r="H2" s="80"/>
+      <c r="I2" s="80"/>
+      <c r="J2" s="81"/>
     </row>
     <row r="3" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="27">
+      <c r="A3" s="28">
         <v>2</v>
       </c>
-      <c r="B3" s="34" t="s">
+      <c r="B3" s="32" t="s">
         <v>96</v>
       </c>
-      <c r="C3" s="34"/>
-      <c r="D3" s="34"/>
-      <c r="E3" s="34"/>
-      <c r="F3" s="34"/>
-      <c r="G3" s="34"/>
-      <c r="H3" s="34"/>
-      <c r="I3" s="34"/>
-      <c r="J3" s="51"/>
+      <c r="C3" s="32"/>
+      <c r="D3" s="32"/>
+      <c r="E3" s="32"/>
+      <c r="F3" s="32"/>
+      <c r="G3" s="32"/>
+      <c r="H3" s="32"/>
+      <c r="I3" s="32"/>
+      <c r="J3" s="33"/>
     </row>
     <row r="4" spans="1:10" ht="13.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="28"/>
-      <c r="B4" s="38" t="s">
+      <c r="A4" s="30"/>
+      <c r="B4" s="194" t="s">
         <v>97</v>
       </c>
-      <c r="C4" s="38"/>
-      <c r="D4" s="38"/>
-      <c r="E4" s="38"/>
-      <c r="F4" s="38"/>
-      <c r="G4" s="38"/>
-      <c r="H4" s="38"/>
-      <c r="I4" s="38"/>
-      <c r="J4" s="39"/>
+      <c r="C4" s="194"/>
+      <c r="D4" s="194"/>
+      <c r="E4" s="194"/>
+      <c r="F4" s="194"/>
+      <c r="G4" s="194"/>
+      <c r="H4" s="194"/>
+      <c r="I4" s="194"/>
+      <c r="J4" s="195"/>
     </row>
     <row r="5" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="27">
+      <c r="A5" s="28">
         <v>3</v>
       </c>
-      <c r="B5" s="34" t="s">
+      <c r="B5" s="32" t="s">
         <v>98</v>
       </c>
-      <c r="C5" s="34"/>
-      <c r="D5" s="34"/>
-      <c r="E5" s="34"/>
-      <c r="F5" s="34"/>
-      <c r="G5" s="34"/>
-      <c r="H5" s="34"/>
-      <c r="I5" s="34"/>
-      <c r="J5" s="51"/>
+      <c r="C5" s="32"/>
+      <c r="D5" s="32"/>
+      <c r="E5" s="32"/>
+      <c r="F5" s="32"/>
+      <c r="G5" s="32"/>
+      <c r="H5" s="32"/>
+      <c r="I5" s="32"/>
+      <c r="J5" s="33"/>
     </row>
     <row r="6" spans="1:10" ht="13.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="31"/>
-      <c r="B6" s="36" t="s">
+      <c r="A6" s="29"/>
+      <c r="B6" s="40" t="s">
         <v>16</v>
       </c>
-      <c r="C6" s="36"/>
-      <c r="D6" s="36"/>
-      <c r="E6" s="36"/>
-      <c r="F6" s="36"/>
-      <c r="G6" s="36"/>
-      <c r="H6" s="36"/>
-      <c r="I6" s="36"/>
-      <c r="J6" s="37"/>
+      <c r="C6" s="40"/>
+      <c r="D6" s="40"/>
+      <c r="E6" s="40"/>
+      <c r="F6" s="40"/>
+      <c r="G6" s="40"/>
+      <c r="H6" s="40"/>
+      <c r="I6" s="40"/>
+      <c r="J6" s="41"/>
     </row>
     <row r="7" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="27">
+      <c r="A7" s="28">
         <v>4</v>
       </c>
-      <c r="B7" s="34" t="s">
+      <c r="B7" s="32" t="s">
         <v>99</v>
       </c>
-      <c r="C7" s="34"/>
-      <c r="D7" s="34"/>
-      <c r="E7" s="34"/>
-      <c r="F7" s="34"/>
-      <c r="G7" s="34"/>
-      <c r="H7" s="34"/>
-      <c r="I7" s="34"/>
-      <c r="J7" s="51"/>
+      <c r="C7" s="32"/>
+      <c r="D7" s="32"/>
+      <c r="E7" s="32"/>
+      <c r="F7" s="32"/>
+      <c r="G7" s="32"/>
+      <c r="H7" s="32"/>
+      <c r="I7" s="32"/>
+      <c r="J7" s="33"/>
     </row>
     <row r="8" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="28"/>
-      <c r="B8" s="53" t="s">
+      <c r="A8" s="30"/>
+      <c r="B8" s="36" t="s">
         <v>100</v>
       </c>
-      <c r="C8" s="53"/>
-      <c r="D8" s="53"/>
-      <c r="E8" s="53"/>
-      <c r="F8" s="53"/>
-      <c r="G8" s="53"/>
-      <c r="H8" s="53"/>
-      <c r="I8" s="53"/>
-      <c r="J8" s="54"/>
+      <c r="C8" s="36"/>
+      <c r="D8" s="36"/>
+      <c r="E8" s="36"/>
+      <c r="F8" s="36"/>
+      <c r="G8" s="36"/>
+      <c r="H8" s="36"/>
+      <c r="I8" s="36"/>
+      <c r="J8" s="37"/>
     </row>
     <row r="9" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="28"/>
-      <c r="B9" s="78"/>
-      <c r="C9" s="78"/>
-      <c r="D9" s="78"/>
-      <c r="E9" s="78"/>
-      <c r="F9" s="78"/>
-      <c r="G9" s="78"/>
-      <c r="H9" s="78"/>
-      <c r="I9" s="78"/>
-      <c r="J9" s="176"/>
+      <c r="A9" s="30"/>
+      <c r="B9" s="34"/>
+      <c r="C9" s="34"/>
+      <c r="D9" s="34"/>
+      <c r="E9" s="34"/>
+      <c r="F9" s="34"/>
+      <c r="G9" s="34"/>
+      <c r="H9" s="34"/>
+      <c r="I9" s="34"/>
+      <c r="J9" s="35"/>
     </row>
     <row r="10" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="28"/>
-      <c r="B10" s="78"/>
-      <c r="C10" s="78"/>
-      <c r="D10" s="78"/>
-      <c r="E10" s="78"/>
-      <c r="F10" s="78"/>
-      <c r="G10" s="78"/>
-      <c r="H10" s="78"/>
-      <c r="I10" s="78"/>
-      <c r="J10" s="176"/>
+      <c r="A10" s="30"/>
+      <c r="B10" s="34"/>
+      <c r="C10" s="34"/>
+      <c r="D10" s="34"/>
+      <c r="E10" s="34"/>
+      <c r="F10" s="34"/>
+      <c r="G10" s="34"/>
+      <c r="H10" s="34"/>
+      <c r="I10" s="34"/>
+      <c r="J10" s="35"/>
     </row>
     <row r="11" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="28"/>
-      <c r="B11" s="78"/>
-      <c r="C11" s="78"/>
-      <c r="D11" s="78"/>
-      <c r="E11" s="78"/>
-      <c r="F11" s="78"/>
-      <c r="G11" s="78"/>
-      <c r="H11" s="78"/>
-      <c r="I11" s="78"/>
-      <c r="J11" s="176"/>
+      <c r="A11" s="30"/>
+      <c r="B11" s="34"/>
+      <c r="C11" s="34"/>
+      <c r="D11" s="34"/>
+      <c r="E11" s="34"/>
+      <c r="F11" s="34"/>
+      <c r="G11" s="34"/>
+      <c r="H11" s="34"/>
+      <c r="I11" s="34"/>
+      <c r="J11" s="35"/>
     </row>
     <row r="12" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="28"/>
-      <c r="B12" s="78"/>
-      <c r="C12" s="78"/>
-      <c r="D12" s="78"/>
-      <c r="E12" s="78"/>
-      <c r="F12" s="78"/>
-      <c r="G12" s="78"/>
-      <c r="H12" s="78"/>
-      <c r="I12" s="78"/>
-      <c r="J12" s="176"/>
+      <c r="A12" s="30"/>
+      <c r="B12" s="34"/>
+      <c r="C12" s="34"/>
+      <c r="D12" s="34"/>
+      <c r="E12" s="34"/>
+      <c r="F12" s="34"/>
+      <c r="G12" s="34"/>
+      <c r="H12" s="34"/>
+      <c r="I12" s="34"/>
+      <c r="J12" s="35"/>
     </row>
     <row r="13" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="28"/>
-      <c r="B13" s="78"/>
-      <c r="C13" s="78"/>
-      <c r="D13" s="78"/>
-      <c r="E13" s="78"/>
-      <c r="F13" s="78"/>
-      <c r="G13" s="78"/>
-      <c r="H13" s="78"/>
-      <c r="I13" s="78"/>
-      <c r="J13" s="176"/>
+      <c r="A13" s="30"/>
+      <c r="B13" s="34"/>
+      <c r="C13" s="34"/>
+      <c r="D13" s="34"/>
+      <c r="E13" s="34"/>
+      <c r="F13" s="34"/>
+      <c r="G13" s="34"/>
+      <c r="H13" s="34"/>
+      <c r="I13" s="34"/>
+      <c r="J13" s="35"/>
     </row>
     <row r="14" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A14" s="28"/>
-      <c r="B14" s="78"/>
-      <c r="C14" s="78"/>
-      <c r="D14" s="78"/>
-      <c r="E14" s="78"/>
-      <c r="F14" s="78"/>
-      <c r="G14" s="78"/>
-      <c r="H14" s="78"/>
-      <c r="I14" s="78"/>
-      <c r="J14" s="176"/>
+      <c r="A14" s="30"/>
+      <c r="B14" s="34"/>
+      <c r="C14" s="34"/>
+      <c r="D14" s="34"/>
+      <c r="E14" s="34"/>
+      <c r="F14" s="34"/>
+      <c r="G14" s="34"/>
+      <c r="H14" s="34"/>
+      <c r="I14" s="34"/>
+      <c r="J14" s="35"/>
     </row>
     <row r="15" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A15" s="28"/>
-      <c r="B15" s="53" t="s">
+      <c r="A15" s="30"/>
+      <c r="B15" s="36" t="s">
         <v>101</v>
       </c>
-      <c r="C15" s="53"/>
-      <c r="D15" s="53"/>
-      <c r="E15" s="53"/>
-      <c r="F15" s="53"/>
-      <c r="G15" s="53"/>
-      <c r="H15" s="53"/>
-      <c r="I15" s="53"/>
-      <c r="J15" s="54"/>
+      <c r="C15" s="36"/>
+      <c r="D15" s="36"/>
+      <c r="E15" s="36"/>
+      <c r="F15" s="36"/>
+      <c r="G15" s="36"/>
+      <c r="H15" s="36"/>
+      <c r="I15" s="36"/>
+      <c r="J15" s="37"/>
     </row>
     <row r="16" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A16" s="28"/>
-      <c r="B16" s="78"/>
-      <c r="C16" s="78"/>
-      <c r="D16" s="78"/>
-      <c r="E16" s="78"/>
-      <c r="F16" s="78"/>
-      <c r="G16" s="78"/>
-      <c r="H16" s="78"/>
-      <c r="I16" s="78"/>
-      <c r="J16" s="176"/>
+      <c r="A16" s="30"/>
+      <c r="B16" s="34"/>
+      <c r="C16" s="34"/>
+      <c r="D16" s="34"/>
+      <c r="E16" s="34"/>
+      <c r="F16" s="34"/>
+      <c r="G16" s="34"/>
+      <c r="H16" s="34"/>
+      <c r="I16" s="34"/>
+      <c r="J16" s="35"/>
     </row>
     <row r="17" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A17" s="28"/>
-      <c r="B17" s="78"/>
-      <c r="C17" s="78"/>
-      <c r="D17" s="78"/>
-      <c r="E17" s="78"/>
-      <c r="F17" s="78"/>
-      <c r="G17" s="78"/>
-      <c r="H17" s="78"/>
-      <c r="I17" s="78"/>
-      <c r="J17" s="176"/>
+      <c r="A17" s="30"/>
+      <c r="B17" s="34"/>
+      <c r="C17" s="34"/>
+      <c r="D17" s="34"/>
+      <c r="E17" s="34"/>
+      <c r="F17" s="34"/>
+      <c r="G17" s="34"/>
+      <c r="H17" s="34"/>
+      <c r="I17" s="34"/>
+      <c r="J17" s="35"/>
     </row>
     <row r="18" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A18" s="28"/>
-      <c r="B18" s="78"/>
-      <c r="C18" s="78"/>
-      <c r="D18" s="78"/>
-      <c r="E18" s="78"/>
-      <c r="F18" s="78"/>
-      <c r="G18" s="78"/>
-      <c r="H18" s="78"/>
-      <c r="I18" s="78"/>
-      <c r="J18" s="176"/>
+      <c r="A18" s="30"/>
+      <c r="B18" s="34"/>
+      <c r="C18" s="34"/>
+      <c r="D18" s="34"/>
+      <c r="E18" s="34"/>
+      <c r="F18" s="34"/>
+      <c r="G18" s="34"/>
+      <c r="H18" s="34"/>
+      <c r="I18" s="34"/>
+      <c r="J18" s="35"/>
     </row>
     <row r="19" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A19" s="28"/>
-      <c r="B19" s="78"/>
-      <c r="C19" s="78"/>
-      <c r="D19" s="78"/>
-      <c r="E19" s="78"/>
-      <c r="F19" s="78"/>
-      <c r="G19" s="78"/>
-      <c r="H19" s="78"/>
-      <c r="I19" s="78"/>
-      <c r="J19" s="176"/>
+      <c r="A19" s="30"/>
+      <c r="B19" s="34"/>
+      <c r="C19" s="34"/>
+      <c r="D19" s="34"/>
+      <c r="E19" s="34"/>
+      <c r="F19" s="34"/>
+      <c r="G19" s="34"/>
+      <c r="H19" s="34"/>
+      <c r="I19" s="34"/>
+      <c r="J19" s="35"/>
     </row>
     <row r="20" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A20" s="28"/>
-      <c r="B20" s="78"/>
-      <c r="C20" s="78"/>
-      <c r="D20" s="78"/>
-      <c r="E20" s="78"/>
-      <c r="F20" s="78"/>
-      <c r="G20" s="78"/>
-      <c r="H20" s="78"/>
-      <c r="I20" s="78"/>
-      <c r="J20" s="176"/>
+      <c r="A20" s="30"/>
+      <c r="B20" s="34"/>
+      <c r="C20" s="34"/>
+      <c r="D20" s="34"/>
+      <c r="E20" s="34"/>
+      <c r="F20" s="34"/>
+      <c r="G20" s="34"/>
+      <c r="H20" s="34"/>
+      <c r="I20" s="34"/>
+      <c r="J20" s="35"/>
     </row>
     <row r="21" spans="1:10" ht="13.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="31"/>
-      <c r="B21" s="174"/>
-      <c r="C21" s="174"/>
-      <c r="D21" s="174"/>
-      <c r="E21" s="174"/>
-      <c r="F21" s="174"/>
-      <c r="G21" s="174"/>
-      <c r="H21" s="174"/>
-      <c r="I21" s="174"/>
-      <c r="J21" s="175"/>
+      <c r="A21" s="29"/>
+      <c r="B21" s="80"/>
+      <c r="C21" s="80"/>
+      <c r="D21" s="80"/>
+      <c r="E21" s="80"/>
+      <c r="F21" s="80"/>
+      <c r="G21" s="80"/>
+      <c r="H21" s="80"/>
+      <c r="I21" s="80"/>
+      <c r="J21" s="81"/>
     </row>
     <row r="22" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A22" s="27">
+      <c r="A22" s="28">
         <v>5</v>
       </c>
-      <c r="B22" s="34" t="s">
+      <c r="B22" s="32" t="s">
         <v>102</v>
       </c>
-      <c r="C22" s="34"/>
-      <c r="D22" s="34"/>
-      <c r="E22" s="34"/>
-      <c r="F22" s="34"/>
-      <c r="G22" s="34"/>
-      <c r="H22" s="34"/>
-      <c r="I22" s="34"/>
-      <c r="J22" s="51"/>
+      <c r="C22" s="32"/>
+      <c r="D22" s="32"/>
+      <c r="E22" s="32"/>
+      <c r="F22" s="32"/>
+      <c r="G22" s="32"/>
+      <c r="H22" s="32"/>
+      <c r="I22" s="32"/>
+      <c r="J22" s="33"/>
     </row>
     <row r="23" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A23" s="28"/>
-      <c r="B23" s="78"/>
-      <c r="C23" s="78"/>
-      <c r="D23" s="78"/>
-      <c r="E23" s="78"/>
-      <c r="F23" s="78"/>
-      <c r="G23" s="78"/>
-      <c r="H23" s="78"/>
-      <c r="I23" s="78"/>
-      <c r="J23" s="176"/>
+      <c r="A23" s="30"/>
+      <c r="B23" s="34"/>
+      <c r="C23" s="34"/>
+      <c r="D23" s="34"/>
+      <c r="E23" s="34"/>
+      <c r="F23" s="34"/>
+      <c r="G23" s="34"/>
+      <c r="H23" s="34"/>
+      <c r="I23" s="34"/>
+      <c r="J23" s="35"/>
     </row>
     <row r="24" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A24" s="28"/>
-      <c r="B24" s="78"/>
-      <c r="C24" s="78"/>
-      <c r="D24" s="78"/>
-      <c r="E24" s="78"/>
-      <c r="F24" s="78"/>
-      <c r="G24" s="78"/>
-      <c r="H24" s="78"/>
-      <c r="I24" s="78"/>
-      <c r="J24" s="176"/>
+      <c r="A24" s="30"/>
+      <c r="B24" s="34"/>
+      <c r="C24" s="34"/>
+      <c r="D24" s="34"/>
+      <c r="E24" s="34"/>
+      <c r="F24" s="34"/>
+      <c r="G24" s="34"/>
+      <c r="H24" s="34"/>
+      <c r="I24" s="34"/>
+      <c r="J24" s="35"/>
     </row>
     <row r="25" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A25" s="28"/>
-      <c r="B25" s="78"/>
-      <c r="C25" s="78"/>
-      <c r="D25" s="78"/>
-      <c r="E25" s="78"/>
-      <c r="F25" s="78"/>
-      <c r="G25" s="78"/>
-      <c r="H25" s="78"/>
-      <c r="I25" s="78"/>
-      <c r="J25" s="176"/>
+      <c r="A25" s="30"/>
+      <c r="B25" s="34"/>
+      <c r="C25" s="34"/>
+      <c r="D25" s="34"/>
+      <c r="E25" s="34"/>
+      <c r="F25" s="34"/>
+      <c r="G25" s="34"/>
+      <c r="H25" s="34"/>
+      <c r="I25" s="34"/>
+      <c r="J25" s="35"/>
     </row>
     <row r="26" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A26" s="28"/>
-      <c r="B26" s="78"/>
-      <c r="C26" s="78"/>
-      <c r="D26" s="78"/>
-      <c r="E26" s="78"/>
-      <c r="F26" s="78"/>
-      <c r="G26" s="78"/>
-      <c r="H26" s="78"/>
-      <c r="I26" s="78"/>
-      <c r="J26" s="176"/>
+      <c r="A26" s="30"/>
+      <c r="B26" s="34"/>
+      <c r="C26" s="34"/>
+      <c r="D26" s="34"/>
+      <c r="E26" s="34"/>
+      <c r="F26" s="34"/>
+      <c r="G26" s="34"/>
+      <c r="H26" s="34"/>
+      <c r="I26" s="34"/>
+      <c r="J26" s="35"/>
     </row>
     <row r="27" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A27" s="28"/>
-      <c r="B27" s="78"/>
-      <c r="C27" s="78"/>
-      <c r="D27" s="78"/>
-      <c r="E27" s="78"/>
-      <c r="F27" s="78"/>
-      <c r="G27" s="78"/>
-      <c r="H27" s="78"/>
-      <c r="I27" s="78"/>
-      <c r="J27" s="176"/>
+      <c r="A27" s="30"/>
+      <c r="B27" s="34"/>
+      <c r="C27" s="34"/>
+      <c r="D27" s="34"/>
+      <c r="E27" s="34"/>
+      <c r="F27" s="34"/>
+      <c r="G27" s="34"/>
+      <c r="H27" s="34"/>
+      <c r="I27" s="34"/>
+      <c r="J27" s="35"/>
     </row>
     <row r="28" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A28" s="28"/>
-      <c r="B28" s="78"/>
-      <c r="C28" s="78"/>
-      <c r="D28" s="78"/>
-      <c r="E28" s="78"/>
-      <c r="F28" s="78"/>
-      <c r="G28" s="78"/>
-      <c r="H28" s="78"/>
-      <c r="I28" s="78"/>
-      <c r="J28" s="176"/>
+      <c r="A28" s="30"/>
+      <c r="B28" s="34"/>
+      <c r="C28" s="34"/>
+      <c r="D28" s="34"/>
+      <c r="E28" s="34"/>
+      <c r="F28" s="34"/>
+      <c r="G28" s="34"/>
+      <c r="H28" s="34"/>
+      <c r="I28" s="34"/>
+      <c r="J28" s="35"/>
     </row>
     <row r="29" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A29" s="28"/>
-      <c r="B29" s="78"/>
-      <c r="C29" s="78"/>
-      <c r="D29" s="78"/>
-      <c r="E29" s="78"/>
-      <c r="F29" s="78"/>
-      <c r="G29" s="78"/>
-      <c r="H29" s="78"/>
-      <c r="I29" s="78"/>
-      <c r="J29" s="176"/>
+      <c r="A29" s="30"/>
+      <c r="B29" s="34"/>
+      <c r="C29" s="34"/>
+      <c r="D29" s="34"/>
+      <c r="E29" s="34"/>
+      <c r="F29" s="34"/>
+      <c r="G29" s="34"/>
+      <c r="H29" s="34"/>
+      <c r="I29" s="34"/>
+      <c r="J29" s="35"/>
     </row>
     <row r="30" spans="1:10" ht="13.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="31"/>
-      <c r="B30" s="174"/>
-      <c r="C30" s="174"/>
-      <c r="D30" s="174"/>
-      <c r="E30" s="174"/>
-      <c r="F30" s="174"/>
-      <c r="G30" s="174"/>
-      <c r="H30" s="174"/>
-      <c r="I30" s="174"/>
-      <c r="J30" s="175"/>
+      <c r="A30" s="29"/>
+      <c r="B30" s="80"/>
+      <c r="C30" s="80"/>
+      <c r="D30" s="80"/>
+      <c r="E30" s="80"/>
+      <c r="F30" s="80"/>
+      <c r="G30" s="80"/>
+      <c r="H30" s="80"/>
+      <c r="I30" s="80"/>
+      <c r="J30" s="81"/>
     </row>
     <row r="31" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A31" s="27">
+      <c r="A31" s="28">
         <v>6</v>
       </c>
-      <c r="B31" s="34" t="s">
+      <c r="B31" s="32" t="s">
         <v>103</v>
       </c>
-      <c r="C31" s="34"/>
-      <c r="D31" s="34"/>
-      <c r="E31" s="34"/>
-      <c r="F31" s="34"/>
-      <c r="G31" s="34"/>
-      <c r="H31" s="34"/>
-      <c r="I31" s="34"/>
-      <c r="J31" s="51"/>
+      <c r="C31" s="32"/>
+      <c r="D31" s="32"/>
+      <c r="E31" s="32"/>
+      <c r="F31" s="32"/>
+      <c r="G31" s="32"/>
+      <c r="H31" s="32"/>
+      <c r="I31" s="32"/>
+      <c r="J31" s="33"/>
     </row>
     <row r="32" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A32" s="28"/>
-      <c r="B32" s="78"/>
-      <c r="C32" s="78"/>
-      <c r="D32" s="78"/>
-      <c r="E32" s="78"/>
-      <c r="F32" s="78"/>
-      <c r="G32" s="78"/>
-      <c r="H32" s="78"/>
-      <c r="I32" s="78"/>
-      <c r="J32" s="176"/>
+      <c r="A32" s="30"/>
+      <c r="B32" s="34"/>
+      <c r="C32" s="34"/>
+      <c r="D32" s="34"/>
+      <c r="E32" s="34"/>
+      <c r="F32" s="34"/>
+      <c r="G32" s="34"/>
+      <c r="H32" s="34"/>
+      <c r="I32" s="34"/>
+      <c r="J32" s="35"/>
     </row>
     <row r="33" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A33" s="28"/>
-      <c r="B33" s="78"/>
-      <c r="C33" s="78"/>
-      <c r="D33" s="78"/>
-      <c r="E33" s="78"/>
-      <c r="F33" s="78"/>
-      <c r="G33" s="78"/>
-      <c r="H33" s="78"/>
-      <c r="I33" s="78"/>
-      <c r="J33" s="176"/>
+      <c r="A33" s="30"/>
+      <c r="B33" s="34"/>
+      <c r="C33" s="34"/>
+      <c r="D33" s="34"/>
+      <c r="E33" s="34"/>
+      <c r="F33" s="34"/>
+      <c r="G33" s="34"/>
+      <c r="H33" s="34"/>
+      <c r="I33" s="34"/>
+      <c r="J33" s="35"/>
     </row>
     <row r="34" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A34" s="28"/>
-      <c r="B34" s="78"/>
-      <c r="C34" s="78"/>
-      <c r="D34" s="78"/>
-      <c r="E34" s="78"/>
-      <c r="F34" s="78"/>
-      <c r="G34" s="78"/>
-      <c r="H34" s="78"/>
-      <c r="I34" s="78"/>
-      <c r="J34" s="176"/>
+      <c r="A34" s="30"/>
+      <c r="B34" s="34"/>
+      <c r="C34" s="34"/>
+      <c r="D34" s="34"/>
+      <c r="E34" s="34"/>
+      <c r="F34" s="34"/>
+      <c r="G34" s="34"/>
+      <c r="H34" s="34"/>
+      <c r="I34" s="34"/>
+      <c r="J34" s="35"/>
     </row>
     <row r="35" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A35" s="28"/>
-      <c r="B35" s="78"/>
-      <c r="C35" s="78"/>
-      <c r="D35" s="78"/>
-      <c r="E35" s="78"/>
-      <c r="F35" s="78"/>
-      <c r="G35" s="78"/>
-      <c r="H35" s="78"/>
-      <c r="I35" s="78"/>
-      <c r="J35" s="176"/>
+      <c r="A35" s="30"/>
+      <c r="B35" s="34"/>
+      <c r="C35" s="34"/>
+      <c r="D35" s="34"/>
+      <c r="E35" s="34"/>
+      <c r="F35" s="34"/>
+      <c r="G35" s="34"/>
+      <c r="H35" s="34"/>
+      <c r="I35" s="34"/>
+      <c r="J35" s="35"/>
     </row>
     <row r="36" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A36" s="28"/>
-      <c r="B36" s="78"/>
-      <c r="C36" s="78"/>
-      <c r="D36" s="78"/>
-      <c r="E36" s="78"/>
-      <c r="F36" s="78"/>
-      <c r="G36" s="78"/>
-      <c r="H36" s="78"/>
-      <c r="I36" s="78"/>
-      <c r="J36" s="176"/>
+      <c r="A36" s="30"/>
+      <c r="B36" s="34"/>
+      <c r="C36" s="34"/>
+      <c r="D36" s="34"/>
+      <c r="E36" s="34"/>
+      <c r="F36" s="34"/>
+      <c r="G36" s="34"/>
+      <c r="H36" s="34"/>
+      <c r="I36" s="34"/>
+      <c r="J36" s="35"/>
     </row>
     <row r="37" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A37" s="28"/>
-      <c r="B37" s="78"/>
-      <c r="C37" s="78"/>
-      <c r="D37" s="78"/>
-      <c r="E37" s="78"/>
-      <c r="F37" s="78"/>
-      <c r="G37" s="78"/>
-      <c r="H37" s="78"/>
-      <c r="I37" s="78"/>
-      <c r="J37" s="176"/>
+      <c r="A37" s="30"/>
+      <c r="B37" s="34"/>
+      <c r="C37" s="34"/>
+      <c r="D37" s="34"/>
+      <c r="E37" s="34"/>
+      <c r="F37" s="34"/>
+      <c r="G37" s="34"/>
+      <c r="H37" s="34"/>
+      <c r="I37" s="34"/>
+      <c r="J37" s="35"/>
     </row>
     <row r="38" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A38" s="28"/>
-      <c r="B38" s="78"/>
-      <c r="C38" s="78"/>
-      <c r="D38" s="78"/>
-      <c r="E38" s="78"/>
-      <c r="F38" s="78"/>
-      <c r="G38" s="78"/>
-      <c r="H38" s="78"/>
-      <c r="I38" s="78"/>
-      <c r="J38" s="176"/>
+      <c r="A38" s="30"/>
+      <c r="B38" s="34"/>
+      <c r="C38" s="34"/>
+      <c r="D38" s="34"/>
+      <c r="E38" s="34"/>
+      <c r="F38" s="34"/>
+      <c r="G38" s="34"/>
+      <c r="H38" s="34"/>
+      <c r="I38" s="34"/>
+      <c r="J38" s="35"/>
     </row>
     <row r="39" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A39" s="28"/>
-      <c r="B39" s="78"/>
-      <c r="C39" s="78"/>
-      <c r="D39" s="78"/>
-      <c r="E39" s="78"/>
-      <c r="F39" s="78"/>
-      <c r="G39" s="78"/>
-      <c r="H39" s="78"/>
-      <c r="I39" s="78"/>
-      <c r="J39" s="176"/>
+      <c r="A39" s="30"/>
+      <c r="B39" s="34"/>
+      <c r="C39" s="34"/>
+      <c r="D39" s="34"/>
+      <c r="E39" s="34"/>
+      <c r="F39" s="34"/>
+      <c r="G39" s="34"/>
+      <c r="H39" s="34"/>
+      <c r="I39" s="34"/>
+      <c r="J39" s="35"/>
     </row>
     <row r="40" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A40" s="28"/>
-      <c r="B40" s="78"/>
-      <c r="C40" s="78"/>
-      <c r="D40" s="78"/>
-      <c r="E40" s="78"/>
-      <c r="F40" s="78"/>
-      <c r="G40" s="78"/>
-      <c r="H40" s="78"/>
-      <c r="I40" s="78"/>
-      <c r="J40" s="176"/>
+      <c r="A40" s="30"/>
+      <c r="B40" s="34"/>
+      <c r="C40" s="34"/>
+      <c r="D40" s="34"/>
+      <c r="E40" s="34"/>
+      <c r="F40" s="34"/>
+      <c r="G40" s="34"/>
+      <c r="H40" s="34"/>
+      <c r="I40" s="34"/>
+      <c r="J40" s="35"/>
     </row>
     <row r="41" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A41" s="28"/>
-      <c r="B41" s="78"/>
-      <c r="C41" s="78"/>
-      <c r="D41" s="78"/>
-      <c r="E41" s="78"/>
-      <c r="F41" s="78"/>
-      <c r="G41" s="78"/>
-      <c r="H41" s="78"/>
-      <c r="I41" s="78"/>
-      <c r="J41" s="176"/>
+      <c r="A41" s="30"/>
+      <c r="B41" s="34"/>
+      <c r="C41" s="34"/>
+      <c r="D41" s="34"/>
+      <c r="E41" s="34"/>
+      <c r="F41" s="34"/>
+      <c r="G41" s="34"/>
+      <c r="H41" s="34"/>
+      <c r="I41" s="34"/>
+      <c r="J41" s="35"/>
     </row>
     <row r="42" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A42" s="28"/>
-      <c r="B42" s="78"/>
-      <c r="C42" s="78"/>
-      <c r="D42" s="78"/>
-      <c r="E42" s="78"/>
-      <c r="F42" s="78"/>
-      <c r="G42" s="78"/>
-      <c r="H42" s="78"/>
-      <c r="I42" s="78"/>
-      <c r="J42" s="176"/>
+      <c r="A42" s="30"/>
+      <c r="B42" s="34"/>
+      <c r="C42" s="34"/>
+      <c r="D42" s="34"/>
+      <c r="E42" s="34"/>
+      <c r="F42" s="34"/>
+      <c r="G42" s="34"/>
+      <c r="H42" s="34"/>
+      <c r="I42" s="34"/>
+      <c r="J42" s="35"/>
     </row>
     <row r="43" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A43" s="28"/>
-      <c r="B43" s="78"/>
-      <c r="C43" s="78"/>
-      <c r="D43" s="78"/>
-      <c r="E43" s="78"/>
-      <c r="F43" s="78"/>
-      <c r="G43" s="78"/>
-      <c r="H43" s="78"/>
-      <c r="I43" s="78"/>
-      <c r="J43" s="176"/>
+      <c r="A43" s="30"/>
+      <c r="B43" s="34"/>
+      <c r="C43" s="34"/>
+      <c r="D43" s="34"/>
+      <c r="E43" s="34"/>
+      <c r="F43" s="34"/>
+      <c r="G43" s="34"/>
+      <c r="H43" s="34"/>
+      <c r="I43" s="34"/>
+      <c r="J43" s="35"/>
     </row>
     <row r="44" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A44" s="28"/>
-      <c r="B44" s="78"/>
-      <c r="C44" s="78"/>
-      <c r="D44" s="78"/>
-      <c r="E44" s="78"/>
-      <c r="F44" s="78"/>
-      <c r="G44" s="78"/>
-      <c r="H44" s="78"/>
-      <c r="I44" s="78"/>
-      <c r="J44" s="176"/>
+      <c r="A44" s="30"/>
+      <c r="B44" s="34"/>
+      <c r="C44" s="34"/>
+      <c r="D44" s="34"/>
+      <c r="E44" s="34"/>
+      <c r="F44" s="34"/>
+      <c r="G44" s="34"/>
+      <c r="H44" s="34"/>
+      <c r="I44" s="34"/>
+      <c r="J44" s="35"/>
     </row>
     <row r="45" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A45" s="28"/>
-      <c r="B45" s="78"/>
-      <c r="C45" s="78"/>
-      <c r="D45" s="78"/>
-      <c r="E45" s="78"/>
-      <c r="F45" s="78"/>
-      <c r="G45" s="78"/>
-      <c r="H45" s="78"/>
-      <c r="I45" s="78"/>
-      <c r="J45" s="176"/>
+      <c r="A45" s="30"/>
+      <c r="B45" s="34"/>
+      <c r="C45" s="34"/>
+      <c r="D45" s="34"/>
+      <c r="E45" s="34"/>
+      <c r="F45" s="34"/>
+      <c r="G45" s="34"/>
+      <c r="H45" s="34"/>
+      <c r="I45" s="34"/>
+      <c r="J45" s="35"/>
     </row>
     <row r="46" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A46" s="28"/>
-      <c r="B46" s="78"/>
-      <c r="C46" s="78"/>
-      <c r="D46" s="78"/>
-      <c r="E46" s="78"/>
-      <c r="F46" s="78"/>
-      <c r="G46" s="78"/>
-      <c r="H46" s="78"/>
-      <c r="I46" s="78"/>
-      <c r="J46" s="176"/>
+      <c r="A46" s="30"/>
+      <c r="B46" s="34"/>
+      <c r="C46" s="34"/>
+      <c r="D46" s="34"/>
+      <c r="E46" s="34"/>
+      <c r="F46" s="34"/>
+      <c r="G46" s="34"/>
+      <c r="H46" s="34"/>
+      <c r="I46" s="34"/>
+      <c r="J46" s="35"/>
     </row>
     <row r="47" spans="1:10" ht="13.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A47" s="29"/>
-      <c r="B47" s="177"/>
-      <c r="C47" s="177"/>
-      <c r="D47" s="177"/>
-      <c r="E47" s="177"/>
-      <c r="F47" s="177"/>
-      <c r="G47" s="177"/>
-      <c r="H47" s="177"/>
-      <c r="I47" s="177"/>
-      <c r="J47" s="178"/>
+      <c r="A47" s="31"/>
+      <c r="B47" s="38"/>
+      <c r="C47" s="38"/>
+      <c r="D47" s="38"/>
+      <c r="E47" s="38"/>
+      <c r="F47" s="38"/>
+      <c r="G47" s="38"/>
+      <c r="H47" s="38"/>
+      <c r="I47" s="38"/>
+      <c r="J47" s="39"/>
     </row>
   </sheetData>
   <mergeCells count="21">
-    <mergeCell ref="B32:J47"/>
-    <mergeCell ref="A31:A47"/>
-    <mergeCell ref="B16:J21"/>
-    <mergeCell ref="A22:A30"/>
-    <mergeCell ref="B23:J30"/>
-    <mergeCell ref="B22:J22"/>
-    <mergeCell ref="B31:J31"/>
+    <mergeCell ref="B3:J3"/>
+    <mergeCell ref="B4:J4"/>
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="B1:D2"/>
+    <mergeCell ref="E1:J2"/>
+    <mergeCell ref="A3:A4"/>
     <mergeCell ref="B15:J15"/>
     <mergeCell ref="B8:J8"/>
     <mergeCell ref="A5:A6"/>
@@ -8347,12 +8365,13 @@
     <mergeCell ref="B7:J7"/>
     <mergeCell ref="B9:J14"/>
     <mergeCell ref="A7:A21"/>
-    <mergeCell ref="B3:J3"/>
-    <mergeCell ref="B4:J4"/>
-    <mergeCell ref="A1:A2"/>
-    <mergeCell ref="B1:D2"/>
-    <mergeCell ref="E1:J2"/>
-    <mergeCell ref="A3:A4"/>
+    <mergeCell ref="B32:J47"/>
+    <mergeCell ref="A31:A47"/>
+    <mergeCell ref="B16:J21"/>
+    <mergeCell ref="A22:A30"/>
+    <mergeCell ref="B23:J30"/>
+    <mergeCell ref="B22:J22"/>
+    <mergeCell ref="B31:J31"/>
   </mergeCells>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.51200000000000001" footer="0.51200000000000001"/>
@@ -8376,15 +8395,6 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="ドキュメント" ma:contentTypeID="0x01010058BEBA3CD4E69545839402B5D4E5400B" ma:contentTypeVersion="13" ma:contentTypeDescription="新しいドキュメントを作成します。" ma:contentTypeScope="" ma:versionID="85fadafb228503a8e253560e9cdffc69">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="88cc3c26-756f-41ab-80ed-43e7289fee5b" xmlns:ns3="55239288-d498-4dd6-9609-491b39ec8fae" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="9785dde68d2e35ac7b66dd15e8e44124" ns2:_="" ns3:_="">
     <xsd:import namespace="88cc3c26-756f-41ab-80ed-43e7289fee5b"/>
@@ -8591,6 +8601,15 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{82E555AC-3D9C-4ECE-9578-D2E452F320B7}">
   <ds:schemaRefs>
@@ -8604,18 +8623,35 @@
     <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
     <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
     <ds:schemaRef ds:uri="96e9746f-acab-410f-8363-815e1ac6f97e"/>
+    <ds:schemaRef ds:uri="88cc3c26-756f-41ab-80ed-43e7289fee5b"/>
+    <ds:schemaRef ds:uri="55239288-d498-4dd6-9609-491b39ec8fae"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{18D765C5-969E-4095-9A45-9E80C6C2EDED}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="88cc3c26-756f-41ab-80ed-43e7289fee5b"/>
+    <ds:schemaRef ds:uri="55239288-d498-4dd6-9609-491b39ec8fae"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0843C284-C2B9-4564-B59A-F2FA129FE5C7}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{18D765C5-969E-4095-9A45-9E80C6C2EDED}"/>
 </file>
--- a/11_プロジェクト計画書.xlsx
+++ b/11_プロジェクト計画書.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\k_tanoue\Documents\GitHub\tanouesoftware\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{38BB8CC4-7E2B-4C96-810A-9F58E918F916}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1A6AD94D-7C90-4AC5-8CD9-CDBCFFA2E0DF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-90" yWindow="0" windowWidth="9780" windowHeight="10170" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="プロジェクト計画" sheetId="1" r:id="rId1"/>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="194" uniqueCount="106">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="195" uniqueCount="107">
   <si>
     <t>プロジェクト計画書</t>
     <rPh sb="6" eb="9">
@@ -1024,6 +1024,31 @@
     </rPh>
     <rPh sb="171" eb="173">
       <t>コウカ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>①：概要
+②：実現可能な機能
+③：システム規模
+④：システムとの関係</t>
+    <rPh sb="2" eb="4">
+      <t>ガイヨウ</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>ジツゲン</t>
+    </rPh>
+    <rPh sb="10" eb="12">
+      <t>カノウ</t>
+    </rPh>
+    <rPh sb="13" eb="15">
+      <t>キノウ</t>
+    </rPh>
+    <rPh sb="23" eb="25">
+      <t>キボ</t>
+    </rPh>
+    <rPh sb="35" eb="37">
+      <t>カンケイ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -2066,33 +2091,132 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="66" xfId="1" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="8" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
@@ -2111,27 +2235,9 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="2" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
@@ -2141,21 +2247,6 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
@@ -2165,71 +2256,17 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="50" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -2237,6 +2274,9 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="51" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2261,20 +2301,17 @@
     <xf numFmtId="0" fontId="10" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="50" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -2285,17 +2322,266 @@
     <xf numFmtId="0" fontId="8" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="32" xfId="1" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="40" xfId="1" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="34" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="35" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="25" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="16" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="46" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="34" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="35" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="25" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="16" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="46" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="34" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="35" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="25" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="16" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="46" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="7" fillId="0" borderId="54" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="7" fillId="0" borderId="55" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="7" fillId="0" borderId="54" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="7" fillId="0" borderId="55" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="7" fillId="0" borderId="54" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="7" fillId="0" borderId="55" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="36" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="26" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="7" fillId="0" borderId="58" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="7" fillId="0" borderId="59" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="7" fillId="0" borderId="58" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="7" fillId="0" borderId="59" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="7" fillId="0" borderId="58" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="7" fillId="0" borderId="59" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="37" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="38" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="21" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="22" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="7" fillId="0" borderId="48" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="7" fillId="0" borderId="49" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="21" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="44" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="50" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="45" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="25" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="46" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="47" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="16" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="31" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="33" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="21" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="22" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="7" fillId="0" borderId="49" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="7" fillId="0" borderId="48" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="7" fillId="0" borderId="49" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="7" fillId="0" borderId="48" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="7" fillId="0" borderId="62" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="7" fillId="0" borderId="63" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="23" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="61" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="41" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="42" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="56" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="33" xfId="1" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="7" fillId="0" borderId="52" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="7" fillId="0" borderId="53" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="24" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="43" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="7" fillId="0" borderId="62" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="7" fillId="0" borderId="63" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="60" xfId="1" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="57" xfId="1" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="23" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="61" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="7" fillId="0" borderId="62" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="7" fillId="0" borderId="63" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="7" fillId="0" borderId="52" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="7" fillId="0" borderId="53" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="23" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="61" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="41" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="42" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="56" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="7" fillId="0" borderId="52" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="7" fillId="0" borderId="53" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -2304,268 +2590,7 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="21" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="21" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="176" fontId="7" fillId="0" borderId="48" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="7" fillId="0" borderId="49" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="33" xfId="1" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="7" fillId="0" borderId="48" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="7" fillId="0" borderId="49" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="21" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="34" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="35" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="25" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="16" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="46" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="7" fillId="0" borderId="52" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="7" fillId="0" borderId="53" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="7" fillId="0" borderId="54" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="7" fillId="0" borderId="55" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="7" fillId="0" borderId="58" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="7" fillId="0" borderId="59" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="32" xfId="1" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="40" xfId="1" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="22" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="7" fillId="0" borderId="48" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="7" fillId="0" borderId="49" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="23" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="24" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="41" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="42" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="43" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="7" fillId="0" borderId="62" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="7" fillId="0" borderId="63" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="60" xfId="1" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="57" xfId="1" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="23" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="61" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="25" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="16" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="46" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="9" fontId="7" fillId="0" borderId="62" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="7" fillId="0" borderId="63" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="7" fillId="0" borderId="52" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="7" fillId="0" borderId="53" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="23" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="61" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="41" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="42" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="56" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="7" fillId="0" borderId="52" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="7" fillId="0" borderId="53" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="34" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="35" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="9" fontId="7" fillId="0" borderId="54" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="7" fillId="0" borderId="55" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="36" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="26" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="7" fillId="0" borderId="58" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="7" fillId="0" borderId="59" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="7" fillId="0" borderId="54" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="7" fillId="0" borderId="55" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="7" fillId="0" borderId="58" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="7" fillId="0" borderId="59" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="34" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="35" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="25" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="16" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="46" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="7" fillId="0" borderId="62" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="7" fillId="0" borderId="63" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="61" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="56" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="37" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="38" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="21" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="22" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="44" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="45" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="25" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="46" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="47" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="16" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="31" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="33" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
@@ -3391,1572 +3416,1583 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" s="2" customFormat="1" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="27" t="s">
+      <c r="A1" s="68" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="27"/>
-      <c r="C1" s="27"/>
-      <c r="D1" s="27"/>
-      <c r="E1" s="27"/>
-      <c r="F1" s="27"/>
-      <c r="G1" s="27"/>
-      <c r="H1" s="27"/>
-      <c r="I1" s="27"/>
-      <c r="J1" s="27"/>
+      <c r="B1" s="68"/>
+      <c r="C1" s="68"/>
+      <c r="D1" s="68"/>
+      <c r="E1" s="68"/>
+      <c r="F1" s="68"/>
+      <c r="G1" s="68"/>
+      <c r="H1" s="68"/>
+      <c r="I1" s="68"/>
+      <c r="J1" s="68"/>
     </row>
     <row r="2" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="28">
+      <c r="A2" s="27">
         <v>1</v>
       </c>
-      <c r="B2" s="32" t="s">
+      <c r="B2" s="34" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="32"/>
-      <c r="D2" s="32"/>
-      <c r="E2" s="78"/>
-      <c r="F2" s="78"/>
-      <c r="G2" s="78"/>
-      <c r="H2" s="78"/>
-      <c r="I2" s="78"/>
-      <c r="J2" s="79"/>
+      <c r="C2" s="34"/>
+      <c r="D2" s="34"/>
+      <c r="E2" s="36"/>
+      <c r="F2" s="36"/>
+      <c r="G2" s="36"/>
+      <c r="H2" s="36"/>
+      <c r="I2" s="36"/>
+      <c r="J2" s="37"/>
     </row>
     <row r="3" spans="1:10" ht="13.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="29"/>
-      <c r="B3" s="77"/>
-      <c r="C3" s="77"/>
-      <c r="D3" s="77"/>
-      <c r="E3" s="80"/>
-      <c r="F3" s="80"/>
-      <c r="G3" s="80"/>
-      <c r="H3" s="80"/>
-      <c r="I3" s="80"/>
-      <c r="J3" s="81"/>
+      <c r="A3" s="31"/>
+      <c r="B3" s="35"/>
+      <c r="C3" s="35"/>
+      <c r="D3" s="35"/>
+      <c r="E3" s="38"/>
+      <c r="F3" s="38"/>
+      <c r="G3" s="38"/>
+      <c r="H3" s="38"/>
+      <c r="I3" s="38"/>
+      <c r="J3" s="39"/>
     </row>
     <row r="4" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="28">
+      <c r="A4" s="27">
         <v>2</v>
       </c>
-      <c r="B4" s="42" t="s">
+      <c r="B4" s="32" t="s">
         <v>2</v>
       </c>
-      <c r="C4" s="42"/>
-      <c r="D4" s="42"/>
-      <c r="E4" s="42"/>
-      <c r="F4" s="42"/>
-      <c r="G4" s="42"/>
-      <c r="H4" s="42"/>
-      <c r="I4" s="42"/>
-      <c r="J4" s="43"/>
+      <c r="C4" s="32"/>
+      <c r="D4" s="32"/>
+      <c r="E4" s="32"/>
+      <c r="F4" s="32"/>
+      <c r="G4" s="32"/>
+      <c r="H4" s="32"/>
+      <c r="I4" s="32"/>
+      <c r="J4" s="33"/>
     </row>
     <row r="5" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="30"/>
-      <c r="B5" s="45" t="s">
+      <c r="A5" s="28"/>
+      <c r="B5" s="46" t="s">
         <v>3</v>
       </c>
-      <c r="C5" s="45"/>
-      <c r="D5" s="45"/>
-      <c r="E5" s="45"/>
-      <c r="F5" s="45"/>
-      <c r="G5" s="45"/>
-      <c r="H5" s="45"/>
-      <c r="I5" s="45"/>
-      <c r="J5" s="46"/>
+      <c r="C5" s="46"/>
+      <c r="D5" s="46"/>
+      <c r="E5" s="46"/>
+      <c r="F5" s="46"/>
+      <c r="G5" s="46"/>
+      <c r="H5" s="46"/>
+      <c r="I5" s="46"/>
+      <c r="J5" s="47"/>
     </row>
     <row r="6" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="30"/>
-      <c r="B6" s="45"/>
-      <c r="C6" s="45"/>
-      <c r="D6" s="45"/>
-      <c r="E6" s="45"/>
-      <c r="F6" s="45"/>
-      <c r="G6" s="45"/>
-      <c r="H6" s="45"/>
-      <c r="I6" s="45"/>
-      <c r="J6" s="46"/>
+      <c r="A6" s="28"/>
+      <c r="B6" s="46"/>
+      <c r="C6" s="46"/>
+      <c r="D6" s="46"/>
+      <c r="E6" s="46"/>
+      <c r="F6" s="46"/>
+      <c r="G6" s="46"/>
+      <c r="H6" s="46"/>
+      <c r="I6" s="46"/>
+      <c r="J6" s="47"/>
     </row>
     <row r="7" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="30"/>
-      <c r="B7" s="47"/>
-      <c r="C7" s="47"/>
-      <c r="D7" s="47"/>
-      <c r="E7" s="47"/>
-      <c r="F7" s="47"/>
-      <c r="G7" s="47"/>
-      <c r="H7" s="47"/>
-      <c r="I7" s="47"/>
-      <c r="J7" s="48"/>
+      <c r="A7" s="28"/>
+      <c r="B7" s="48"/>
+      <c r="C7" s="48"/>
+      <c r="D7" s="48"/>
+      <c r="E7" s="48"/>
+      <c r="F7" s="48"/>
+      <c r="G7" s="48"/>
+      <c r="H7" s="48"/>
+      <c r="I7" s="48"/>
+      <c r="J7" s="49"/>
     </row>
     <row r="8" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="30"/>
-      <c r="B8" s="76" t="s">
+      <c r="A8" s="28"/>
+      <c r="B8" s="61" t="s">
         <v>105</v>
       </c>
-      <c r="C8" s="52"/>
-      <c r="D8" s="52"/>
-      <c r="E8" s="52"/>
-      <c r="F8" s="52"/>
-      <c r="G8" s="52"/>
-      <c r="H8" s="52"/>
-      <c r="I8" s="52"/>
-      <c r="J8" s="53"/>
+      <c r="C8" s="62"/>
+      <c r="D8" s="62"/>
+      <c r="E8" s="62"/>
+      <c r="F8" s="62"/>
+      <c r="G8" s="62"/>
+      <c r="H8" s="62"/>
+      <c r="I8" s="62"/>
+      <c r="J8" s="63"/>
     </row>
     <row r="9" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="30"/>
-      <c r="B9" s="54"/>
-      <c r="C9" s="55"/>
-      <c r="D9" s="55"/>
-      <c r="E9" s="55"/>
-      <c r="F9" s="55"/>
-      <c r="G9" s="55"/>
-      <c r="H9" s="55"/>
-      <c r="I9" s="55"/>
-      <c r="J9" s="56"/>
+      <c r="A9" s="28"/>
+      <c r="B9" s="64"/>
+      <c r="C9" s="65"/>
+      <c r="D9" s="65"/>
+      <c r="E9" s="65"/>
+      <c r="F9" s="65"/>
+      <c r="G9" s="65"/>
+      <c r="H9" s="65"/>
+      <c r="I9" s="65"/>
+      <c r="J9" s="66"/>
     </row>
     <row r="10" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="30"/>
-      <c r="B10" s="54"/>
-      <c r="C10" s="55"/>
-      <c r="D10" s="55"/>
-      <c r="E10" s="55"/>
-      <c r="F10" s="55"/>
-      <c r="G10" s="55"/>
-      <c r="H10" s="55"/>
-      <c r="I10" s="55"/>
-      <c r="J10" s="56"/>
+      <c r="A10" s="28"/>
+      <c r="B10" s="64"/>
+      <c r="C10" s="65"/>
+      <c r="D10" s="65"/>
+      <c r="E10" s="65"/>
+      <c r="F10" s="65"/>
+      <c r="G10" s="65"/>
+      <c r="H10" s="65"/>
+      <c r="I10" s="65"/>
+      <c r="J10" s="66"/>
     </row>
     <row r="11" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="30"/>
-      <c r="B11" s="54"/>
-      <c r="C11" s="55"/>
-      <c r="D11" s="55"/>
-      <c r="E11" s="55"/>
-      <c r="F11" s="55"/>
-      <c r="G11" s="55"/>
-      <c r="H11" s="55"/>
-      <c r="I11" s="55"/>
-      <c r="J11" s="56"/>
+      <c r="A11" s="28"/>
+      <c r="B11" s="64"/>
+      <c r="C11" s="65"/>
+      <c r="D11" s="65"/>
+      <c r="E11" s="65"/>
+      <c r="F11" s="65"/>
+      <c r="G11" s="65"/>
+      <c r="H11" s="65"/>
+      <c r="I11" s="65"/>
+      <c r="J11" s="66"/>
     </row>
     <row r="12" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="30"/>
-      <c r="B12" s="54"/>
-      <c r="C12" s="55"/>
-      <c r="D12" s="55"/>
-      <c r="E12" s="55"/>
-      <c r="F12" s="55"/>
-      <c r="G12" s="55"/>
-      <c r="H12" s="55"/>
-      <c r="I12" s="55"/>
-      <c r="J12" s="56"/>
+      <c r="A12" s="28"/>
+      <c r="B12" s="64"/>
+      <c r="C12" s="65"/>
+      <c r="D12" s="65"/>
+      <c r="E12" s="65"/>
+      <c r="F12" s="65"/>
+      <c r="G12" s="65"/>
+      <c r="H12" s="65"/>
+      <c r="I12" s="65"/>
+      <c r="J12" s="66"/>
     </row>
     <row r="13" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="30"/>
-      <c r="B13" s="54"/>
-      <c r="C13" s="55"/>
-      <c r="D13" s="55"/>
-      <c r="E13" s="55"/>
-      <c r="F13" s="55"/>
-      <c r="G13" s="55"/>
-      <c r="H13" s="55"/>
-      <c r="I13" s="55"/>
-      <c r="J13" s="56"/>
+      <c r="A13" s="28"/>
+      <c r="B13" s="64"/>
+      <c r="C13" s="65"/>
+      <c r="D13" s="65"/>
+      <c r="E13" s="65"/>
+      <c r="F13" s="65"/>
+      <c r="G13" s="65"/>
+      <c r="H13" s="65"/>
+      <c r="I13" s="65"/>
+      <c r="J13" s="66"/>
     </row>
     <row r="14" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A14" s="30"/>
-      <c r="B14" s="54"/>
-      <c r="C14" s="55"/>
-      <c r="D14" s="55"/>
-      <c r="E14" s="55"/>
-      <c r="F14" s="55"/>
-      <c r="G14" s="55"/>
-      <c r="H14" s="55"/>
-      <c r="I14" s="55"/>
-      <c r="J14" s="56"/>
+      <c r="A14" s="28"/>
+      <c r="B14" s="64"/>
+      <c r="C14" s="65"/>
+      <c r="D14" s="65"/>
+      <c r="E14" s="65"/>
+      <c r="F14" s="65"/>
+      <c r="G14" s="65"/>
+      <c r="H14" s="65"/>
+      <c r="I14" s="65"/>
+      <c r="J14" s="66"/>
     </row>
     <row r="15" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A15" s="30"/>
-      <c r="B15" s="54"/>
-      <c r="C15" s="55"/>
-      <c r="D15" s="55"/>
-      <c r="E15" s="55"/>
-      <c r="F15" s="55"/>
-      <c r="G15" s="55"/>
-      <c r="H15" s="55"/>
-      <c r="I15" s="55"/>
-      <c r="J15" s="56"/>
+      <c r="A15" s="28"/>
+      <c r="B15" s="64"/>
+      <c r="C15" s="65"/>
+      <c r="D15" s="65"/>
+      <c r="E15" s="65"/>
+      <c r="F15" s="65"/>
+      <c r="G15" s="65"/>
+      <c r="H15" s="65"/>
+      <c r="I15" s="65"/>
+      <c r="J15" s="66"/>
     </row>
     <row r="16" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A16" s="30"/>
-      <c r="B16" s="54"/>
-      <c r="C16" s="55"/>
-      <c r="D16" s="55"/>
-      <c r="E16" s="55"/>
-      <c r="F16" s="55"/>
-      <c r="G16" s="55"/>
-      <c r="H16" s="55"/>
-      <c r="I16" s="55"/>
-      <c r="J16" s="56"/>
+      <c r="A16" s="28"/>
+      <c r="B16" s="64"/>
+      <c r="C16" s="65"/>
+      <c r="D16" s="65"/>
+      <c r="E16" s="65"/>
+      <c r="F16" s="65"/>
+      <c r="G16" s="65"/>
+      <c r="H16" s="65"/>
+      <c r="I16" s="65"/>
+      <c r="J16" s="66"/>
     </row>
     <row r="17" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A17" s="29"/>
-      <c r="B17" s="54"/>
-      <c r="C17" s="55"/>
-      <c r="D17" s="55"/>
-      <c r="E17" s="55"/>
-      <c r="F17" s="55"/>
-      <c r="G17" s="55"/>
-      <c r="H17" s="55"/>
-      <c r="I17" s="55"/>
-      <c r="J17" s="56"/>
+      <c r="A17" s="31"/>
+      <c r="B17" s="64"/>
+      <c r="C17" s="65"/>
+      <c r="D17" s="65"/>
+      <c r="E17" s="65"/>
+      <c r="F17" s="65"/>
+      <c r="G17" s="65"/>
+      <c r="H17" s="65"/>
+      <c r="I17" s="65"/>
+      <c r="J17" s="66"/>
     </row>
     <row r="18" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A18" s="29"/>
-      <c r="B18" s="54"/>
-      <c r="C18" s="55"/>
-      <c r="D18" s="55"/>
-      <c r="E18" s="55"/>
-      <c r="F18" s="55"/>
-      <c r="G18" s="55"/>
-      <c r="H18" s="55"/>
-      <c r="I18" s="55"/>
-      <c r="J18" s="56"/>
+      <c r="A18" s="31"/>
+      <c r="B18" s="64"/>
+      <c r="C18" s="65"/>
+      <c r="D18" s="65"/>
+      <c r="E18" s="65"/>
+      <c r="F18" s="65"/>
+      <c r="G18" s="65"/>
+      <c r="H18" s="65"/>
+      <c r="I18" s="65"/>
+      <c r="J18" s="66"/>
     </row>
     <row r="19" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A19" s="29"/>
-      <c r="B19" s="54"/>
-      <c r="C19" s="55"/>
-      <c r="D19" s="55"/>
-      <c r="E19" s="55"/>
-      <c r="F19" s="55"/>
-      <c r="G19" s="55"/>
-      <c r="H19" s="55"/>
-      <c r="I19" s="55"/>
-      <c r="J19" s="56"/>
+      <c r="A19" s="31"/>
+      <c r="B19" s="64"/>
+      <c r="C19" s="65"/>
+      <c r="D19" s="65"/>
+      <c r="E19" s="65"/>
+      <c r="F19" s="65"/>
+      <c r="G19" s="65"/>
+      <c r="H19" s="65"/>
+      <c r="I19" s="65"/>
+      <c r="J19" s="66"/>
     </row>
     <row r="20" spans="1:10" ht="13.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="29"/>
-      <c r="B20" s="54"/>
-      <c r="C20" s="55"/>
-      <c r="D20" s="55"/>
-      <c r="E20" s="55"/>
-      <c r="F20" s="55"/>
-      <c r="G20" s="55"/>
-      <c r="H20" s="55"/>
-      <c r="I20" s="55"/>
-      <c r="J20" s="56"/>
+      <c r="A20" s="31"/>
+      <c r="B20" s="64"/>
+      <c r="C20" s="65"/>
+      <c r="D20" s="65"/>
+      <c r="E20" s="65"/>
+      <c r="F20" s="65"/>
+      <c r="G20" s="65"/>
+      <c r="H20" s="65"/>
+      <c r="I20" s="65"/>
+      <c r="J20" s="66"/>
     </row>
     <row r="21" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A21" s="28">
+      <c r="A21" s="27">
         <v>3</v>
       </c>
-      <c r="B21" s="42" t="s">
+      <c r="B21" s="32" t="s">
         <v>4</v>
       </c>
-      <c r="C21" s="42"/>
-      <c r="D21" s="42"/>
-      <c r="E21" s="42"/>
-      <c r="F21" s="42"/>
-      <c r="G21" s="42"/>
-      <c r="H21" s="42"/>
-      <c r="I21" s="42"/>
-      <c r="J21" s="43"/>
+      <c r="C21" s="32"/>
+      <c r="D21" s="32"/>
+      <c r="E21" s="32"/>
+      <c r="F21" s="32"/>
+      <c r="G21" s="32"/>
+      <c r="H21" s="32"/>
+      <c r="I21" s="32"/>
+      <c r="J21" s="33"/>
     </row>
     <row r="22" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A22" s="30"/>
-      <c r="B22" s="64" t="s">
+      <c r="A22" s="28"/>
+      <c r="B22" s="50" t="s">
         <v>5</v>
       </c>
-      <c r="C22" s="65"/>
-      <c r="D22" s="65"/>
-      <c r="E22" s="65"/>
-      <c r="F22" s="65"/>
-      <c r="G22" s="65"/>
-      <c r="H22" s="65"/>
-      <c r="I22" s="65"/>
-      <c r="J22" s="66"/>
+      <c r="C22" s="51"/>
+      <c r="D22" s="51"/>
+      <c r="E22" s="51"/>
+      <c r="F22" s="51"/>
+      <c r="G22" s="51"/>
+      <c r="H22" s="51"/>
+      <c r="I22" s="51"/>
+      <c r="J22" s="52"/>
     </row>
     <row r="23" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A23" s="30"/>
-      <c r="B23" s="64"/>
-      <c r="C23" s="65"/>
-      <c r="D23" s="65"/>
-      <c r="E23" s="65"/>
-      <c r="F23" s="65"/>
-      <c r="G23" s="65"/>
-      <c r="H23" s="65"/>
-      <c r="I23" s="65"/>
-      <c r="J23" s="66"/>
+      <c r="A23" s="28"/>
+      <c r="B23" s="50"/>
+      <c r="C23" s="51"/>
+      <c r="D23" s="51"/>
+      <c r="E23" s="51"/>
+      <c r="F23" s="51"/>
+      <c r="G23" s="51"/>
+      <c r="H23" s="51"/>
+      <c r="I23" s="51"/>
+      <c r="J23" s="52"/>
     </row>
     <row r="24" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A24" s="30"/>
-      <c r="B24" s="64"/>
-      <c r="C24" s="65"/>
-      <c r="D24" s="65"/>
-      <c r="E24" s="65"/>
-      <c r="F24" s="65"/>
-      <c r="G24" s="65"/>
-      <c r="H24" s="65"/>
-      <c r="I24" s="65"/>
-      <c r="J24" s="66"/>
+      <c r="A24" s="28"/>
+      <c r="B24" s="50"/>
+      <c r="C24" s="51"/>
+      <c r="D24" s="51"/>
+      <c r="E24" s="51"/>
+      <c r="F24" s="51"/>
+      <c r="G24" s="51"/>
+      <c r="H24" s="51"/>
+      <c r="I24" s="51"/>
+      <c r="J24" s="52"/>
     </row>
     <row r="25" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A25" s="30"/>
-      <c r="B25" s="67"/>
-      <c r="C25" s="68"/>
-      <c r="D25" s="68"/>
-      <c r="E25" s="68"/>
-      <c r="F25" s="68"/>
-      <c r="G25" s="68"/>
-      <c r="H25" s="68"/>
-      <c r="I25" s="68"/>
-      <c r="J25" s="69"/>
+      <c r="A25" s="28"/>
+      <c r="B25" s="53"/>
+      <c r="C25" s="54"/>
+      <c r="D25" s="54"/>
+      <c r="E25" s="54"/>
+      <c r="F25" s="54"/>
+      <c r="G25" s="54"/>
+      <c r="H25" s="54"/>
+      <c r="I25" s="54"/>
+      <c r="J25" s="55"/>
     </row>
     <row r="26" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A26" s="30"/>
-      <c r="B26" s="70"/>
-      <c r="C26" s="70"/>
-      <c r="D26" s="70"/>
-      <c r="E26" s="70"/>
-      <c r="F26" s="70"/>
-      <c r="G26" s="70"/>
-      <c r="H26" s="70"/>
-      <c r="I26" s="70"/>
-      <c r="J26" s="71"/>
+      <c r="A26" s="28"/>
+      <c r="B26" s="56" t="s">
+        <v>106</v>
+      </c>
+      <c r="C26" s="56"/>
+      <c r="D26" s="56"/>
+      <c r="E26" s="56"/>
+      <c r="F26" s="56"/>
+      <c r="G26" s="56"/>
+      <c r="H26" s="56"/>
+      <c r="I26" s="56"/>
+      <c r="J26" s="57"/>
     </row>
     <row r="27" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A27" s="30"/>
-      <c r="B27" s="70"/>
-      <c r="C27" s="70"/>
-      <c r="D27" s="70"/>
-      <c r="E27" s="70"/>
-      <c r="F27" s="70"/>
-      <c r="G27" s="70"/>
-      <c r="H27" s="70"/>
-      <c r="I27" s="70"/>
-      <c r="J27" s="71"/>
+      <c r="A27" s="28"/>
+      <c r="B27" s="56"/>
+      <c r="C27" s="56"/>
+      <c r="D27" s="56"/>
+      <c r="E27" s="56"/>
+      <c r="F27" s="56"/>
+      <c r="G27" s="56"/>
+      <c r="H27" s="56"/>
+      <c r="I27" s="56"/>
+      <c r="J27" s="57"/>
     </row>
     <row r="28" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A28" s="30"/>
-      <c r="B28" s="70"/>
-      <c r="C28" s="70"/>
-      <c r="D28" s="70"/>
-      <c r="E28" s="70"/>
-      <c r="F28" s="70"/>
-      <c r="G28" s="70"/>
-      <c r="H28" s="70"/>
-      <c r="I28" s="70"/>
-      <c r="J28" s="71"/>
+      <c r="A28" s="28"/>
+      <c r="B28" s="56"/>
+      <c r="C28" s="56"/>
+      <c r="D28" s="56"/>
+      <c r="E28" s="56"/>
+      <c r="F28" s="56"/>
+      <c r="G28" s="56"/>
+      <c r="H28" s="56"/>
+      <c r="I28" s="56"/>
+      <c r="J28" s="57"/>
     </row>
     <row r="29" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A29" s="30"/>
-      <c r="B29" s="70"/>
-      <c r="C29" s="70"/>
-      <c r="D29" s="70"/>
-      <c r="E29" s="70"/>
-      <c r="F29" s="70"/>
-      <c r="G29" s="70"/>
-      <c r="H29" s="70"/>
-      <c r="I29" s="70"/>
-      <c r="J29" s="71"/>
+      <c r="A29" s="28"/>
+      <c r="B29" s="56"/>
+      <c r="C29" s="56"/>
+      <c r="D29" s="56"/>
+      <c r="E29" s="56"/>
+      <c r="F29" s="56"/>
+      <c r="G29" s="56"/>
+      <c r="H29" s="56"/>
+      <c r="I29" s="56"/>
+      <c r="J29" s="57"/>
     </row>
     <row r="30" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A30" s="30"/>
-      <c r="B30" s="70"/>
-      <c r="C30" s="70"/>
-      <c r="D30" s="70"/>
-      <c r="E30" s="70"/>
-      <c r="F30" s="70"/>
-      <c r="G30" s="70"/>
-      <c r="H30" s="70"/>
-      <c r="I30" s="70"/>
-      <c r="J30" s="71"/>
+      <c r="A30" s="28"/>
+      <c r="B30" s="56"/>
+      <c r="C30" s="56"/>
+      <c r="D30" s="56"/>
+      <c r="E30" s="56"/>
+      <c r="F30" s="56"/>
+      <c r="G30" s="56"/>
+      <c r="H30" s="56"/>
+      <c r="I30" s="56"/>
+      <c r="J30" s="57"/>
     </row>
     <row r="31" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A31" s="30"/>
-      <c r="B31" s="70"/>
-      <c r="C31" s="70"/>
-      <c r="D31" s="70"/>
-      <c r="E31" s="70"/>
-      <c r="F31" s="70"/>
-      <c r="G31" s="70"/>
-      <c r="H31" s="70"/>
-      <c r="I31" s="70"/>
-      <c r="J31" s="71"/>
+      <c r="A31" s="28"/>
+      <c r="B31" s="56"/>
+      <c r="C31" s="56"/>
+      <c r="D31" s="56"/>
+      <c r="E31" s="56"/>
+      <c r="F31" s="56"/>
+      <c r="G31" s="56"/>
+      <c r="H31" s="56"/>
+      <c r="I31" s="56"/>
+      <c r="J31" s="57"/>
     </row>
     <row r="32" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A32" s="30"/>
-      <c r="B32" s="70"/>
-      <c r="C32" s="70"/>
-      <c r="D32" s="70"/>
-      <c r="E32" s="70"/>
-      <c r="F32" s="70"/>
-      <c r="G32" s="70"/>
-      <c r="H32" s="70"/>
-      <c r="I32" s="70"/>
-      <c r="J32" s="71"/>
+      <c r="A32" s="28"/>
+      <c r="B32" s="56"/>
+      <c r="C32" s="56"/>
+      <c r="D32" s="56"/>
+      <c r="E32" s="56"/>
+      <c r="F32" s="56"/>
+      <c r="G32" s="56"/>
+      <c r="H32" s="56"/>
+      <c r="I32" s="56"/>
+      <c r="J32" s="57"/>
     </row>
     <row r="33" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A33" s="30"/>
-      <c r="B33" s="70"/>
-      <c r="C33" s="70"/>
-      <c r="D33" s="70"/>
-      <c r="E33" s="70"/>
-      <c r="F33" s="70"/>
-      <c r="G33" s="70"/>
-      <c r="H33" s="70"/>
-      <c r="I33" s="70"/>
-      <c r="J33" s="71"/>
+      <c r="A33" s="28"/>
+      <c r="B33" s="56"/>
+      <c r="C33" s="56"/>
+      <c r="D33" s="56"/>
+      <c r="E33" s="56"/>
+      <c r="F33" s="56"/>
+      <c r="G33" s="56"/>
+      <c r="H33" s="56"/>
+      <c r="I33" s="56"/>
+      <c r="J33" s="57"/>
     </row>
     <row r="34" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A34" s="30"/>
-      <c r="B34" s="70"/>
-      <c r="C34" s="70"/>
-      <c r="D34" s="70"/>
-      <c r="E34" s="70"/>
-      <c r="F34" s="70"/>
-      <c r="G34" s="70"/>
-      <c r="H34" s="70"/>
-      <c r="I34" s="70"/>
-      <c r="J34" s="71"/>
+      <c r="A34" s="28"/>
+      <c r="B34" s="56"/>
+      <c r="C34" s="56"/>
+      <c r="D34" s="56"/>
+      <c r="E34" s="56"/>
+      <c r="F34" s="56"/>
+      <c r="G34" s="56"/>
+      <c r="H34" s="56"/>
+      <c r="I34" s="56"/>
+      <c r="J34" s="57"/>
     </row>
     <row r="35" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A35" s="30"/>
-      <c r="B35" s="70"/>
-      <c r="C35" s="70"/>
-      <c r="D35" s="70"/>
-      <c r="E35" s="70"/>
-      <c r="F35" s="70"/>
-      <c r="G35" s="70"/>
-      <c r="H35" s="70"/>
-      <c r="I35" s="70"/>
-      <c r="J35" s="71"/>
+      <c r="A35" s="28"/>
+      <c r="B35" s="56"/>
+      <c r="C35" s="56"/>
+      <c r="D35" s="56"/>
+      <c r="E35" s="56"/>
+      <c r="F35" s="56"/>
+      <c r="G35" s="56"/>
+      <c r="H35" s="56"/>
+      <c r="I35" s="56"/>
+      <c r="J35" s="57"/>
     </row>
     <row r="36" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A36" s="30"/>
-      <c r="B36" s="70"/>
-      <c r="C36" s="70"/>
-      <c r="D36" s="70"/>
-      <c r="E36" s="70"/>
-      <c r="F36" s="70"/>
-      <c r="G36" s="70"/>
-      <c r="H36" s="70"/>
-      <c r="I36" s="70"/>
-      <c r="J36" s="71"/>
+      <c r="A36" s="28"/>
+      <c r="B36" s="56"/>
+      <c r="C36" s="56"/>
+      <c r="D36" s="56"/>
+      <c r="E36" s="56"/>
+      <c r="F36" s="56"/>
+      <c r="G36" s="56"/>
+      <c r="H36" s="56"/>
+      <c r="I36" s="56"/>
+      <c r="J36" s="57"/>
     </row>
     <row r="37" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A37" s="30"/>
-      <c r="B37" s="70"/>
-      <c r="C37" s="70"/>
-      <c r="D37" s="70"/>
-      <c r="E37" s="70"/>
-      <c r="F37" s="70"/>
-      <c r="G37" s="70"/>
-      <c r="H37" s="70"/>
-      <c r="I37" s="70"/>
-      <c r="J37" s="71"/>
+      <c r="A37" s="28"/>
+      <c r="B37" s="56"/>
+      <c r="C37" s="56"/>
+      <c r="D37" s="56"/>
+      <c r="E37" s="56"/>
+      <c r="F37" s="56"/>
+      <c r="G37" s="56"/>
+      <c r="H37" s="56"/>
+      <c r="I37" s="56"/>
+      <c r="J37" s="57"/>
     </row>
     <row r="38" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A38" s="30"/>
-      <c r="B38" s="70"/>
-      <c r="C38" s="70"/>
-      <c r="D38" s="70"/>
-      <c r="E38" s="70"/>
-      <c r="F38" s="70"/>
-      <c r="G38" s="70"/>
-      <c r="H38" s="70"/>
-      <c r="I38" s="70"/>
-      <c r="J38" s="71"/>
+      <c r="A38" s="28"/>
+      <c r="B38" s="56"/>
+      <c r="C38" s="56"/>
+      <c r="D38" s="56"/>
+      <c r="E38" s="56"/>
+      <c r="F38" s="56"/>
+      <c r="G38" s="56"/>
+      <c r="H38" s="56"/>
+      <c r="I38" s="56"/>
+      <c r="J38" s="57"/>
     </row>
     <row r="39" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A39" s="30"/>
-      <c r="B39" s="70"/>
-      <c r="C39" s="70"/>
-      <c r="D39" s="70"/>
-      <c r="E39" s="70"/>
-      <c r="F39" s="70"/>
-      <c r="G39" s="70"/>
-      <c r="H39" s="70"/>
-      <c r="I39" s="70"/>
-      <c r="J39" s="71"/>
+      <c r="A39" s="28"/>
+      <c r="B39" s="56"/>
+      <c r="C39" s="56"/>
+      <c r="D39" s="56"/>
+      <c r="E39" s="56"/>
+      <c r="F39" s="56"/>
+      <c r="G39" s="56"/>
+      <c r="H39" s="56"/>
+      <c r="I39" s="56"/>
+      <c r="J39" s="57"/>
     </row>
     <row r="40" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A40" s="30"/>
-      <c r="B40" s="70"/>
-      <c r="C40" s="70"/>
-      <c r="D40" s="70"/>
-      <c r="E40" s="70"/>
-      <c r="F40" s="70"/>
-      <c r="G40" s="70"/>
-      <c r="H40" s="70"/>
-      <c r="I40" s="70"/>
-      <c r="J40" s="71"/>
+      <c r="A40" s="28"/>
+      <c r="B40" s="56"/>
+      <c r="C40" s="56"/>
+      <c r="D40" s="56"/>
+      <c r="E40" s="56"/>
+      <c r="F40" s="56"/>
+      <c r="G40" s="56"/>
+      <c r="H40" s="56"/>
+      <c r="I40" s="56"/>
+      <c r="J40" s="57"/>
     </row>
     <row r="41" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A41" s="30"/>
-      <c r="B41" s="70"/>
-      <c r="C41" s="70"/>
-      <c r="D41" s="70"/>
-      <c r="E41" s="70"/>
-      <c r="F41" s="70"/>
-      <c r="G41" s="70"/>
-      <c r="H41" s="70"/>
-      <c r="I41" s="70"/>
-      <c r="J41" s="71"/>
+      <c r="A41" s="28"/>
+      <c r="B41" s="56"/>
+      <c r="C41" s="56"/>
+      <c r="D41" s="56"/>
+      <c r="E41" s="56"/>
+      <c r="F41" s="56"/>
+      <c r="G41" s="56"/>
+      <c r="H41" s="56"/>
+      <c r="I41" s="56"/>
+      <c r="J41" s="57"/>
     </row>
     <row r="42" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A42" s="30"/>
-      <c r="B42" s="70"/>
-      <c r="C42" s="70"/>
-      <c r="D42" s="70"/>
-      <c r="E42" s="70"/>
-      <c r="F42" s="70"/>
-      <c r="G42" s="70"/>
-      <c r="H42" s="70"/>
-      <c r="I42" s="70"/>
-      <c r="J42" s="71"/>
+      <c r="A42" s="28"/>
+      <c r="B42" s="56"/>
+      <c r="C42" s="56"/>
+      <c r="D42" s="56"/>
+      <c r="E42" s="56"/>
+      <c r="F42" s="56"/>
+      <c r="G42" s="56"/>
+      <c r="H42" s="56"/>
+      <c r="I42" s="56"/>
+      <c r="J42" s="57"/>
     </row>
     <row r="43" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A43" s="30"/>
-      <c r="B43" s="70"/>
-      <c r="C43" s="70"/>
-      <c r="D43" s="70"/>
-      <c r="E43" s="70"/>
-      <c r="F43" s="70"/>
-      <c r="G43" s="70"/>
-      <c r="H43" s="70"/>
-      <c r="I43" s="70"/>
-      <c r="J43" s="71"/>
+      <c r="A43" s="28"/>
+      <c r="B43" s="56"/>
+      <c r="C43" s="56"/>
+      <c r="D43" s="56"/>
+      <c r="E43" s="56"/>
+      <c r="F43" s="56"/>
+      <c r="G43" s="56"/>
+      <c r="H43" s="56"/>
+      <c r="I43" s="56"/>
+      <c r="J43" s="57"/>
     </row>
     <row r="44" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A44" s="30"/>
-      <c r="B44" s="70"/>
-      <c r="C44" s="70"/>
-      <c r="D44" s="70"/>
-      <c r="E44" s="70"/>
-      <c r="F44" s="70"/>
-      <c r="G44" s="70"/>
-      <c r="H44" s="70"/>
-      <c r="I44" s="70"/>
-      <c r="J44" s="71"/>
+      <c r="A44" s="28"/>
+      <c r="B44" s="56"/>
+      <c r="C44" s="56"/>
+      <c r="D44" s="56"/>
+      <c r="E44" s="56"/>
+      <c r="F44" s="56"/>
+      <c r="G44" s="56"/>
+      <c r="H44" s="56"/>
+      <c r="I44" s="56"/>
+      <c r="J44" s="57"/>
     </row>
     <row r="45" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A45" s="30"/>
-      <c r="B45" s="70"/>
-      <c r="C45" s="70"/>
-      <c r="D45" s="70"/>
-      <c r="E45" s="70"/>
-      <c r="F45" s="70"/>
-      <c r="G45" s="70"/>
-      <c r="H45" s="70"/>
-      <c r="I45" s="70"/>
-      <c r="J45" s="71"/>
+      <c r="A45" s="28"/>
+      <c r="B45" s="56"/>
+      <c r="C45" s="56"/>
+      <c r="D45" s="56"/>
+      <c r="E45" s="56"/>
+      <c r="F45" s="56"/>
+      <c r="G45" s="56"/>
+      <c r="H45" s="56"/>
+      <c r="I45" s="56"/>
+      <c r="J45" s="57"/>
     </row>
     <row r="46" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A46" s="30"/>
-      <c r="B46" s="70"/>
-      <c r="C46" s="70"/>
-      <c r="D46" s="70"/>
-      <c r="E46" s="70"/>
-      <c r="F46" s="70"/>
-      <c r="G46" s="70"/>
-      <c r="H46" s="70"/>
-      <c r="I46" s="70"/>
-      <c r="J46" s="71"/>
+      <c r="A46" s="28"/>
+      <c r="B46" s="56"/>
+      <c r="C46" s="56"/>
+      <c r="D46" s="56"/>
+      <c r="E46" s="56"/>
+      <c r="F46" s="56"/>
+      <c r="G46" s="56"/>
+      <c r="H46" s="56"/>
+      <c r="I46" s="56"/>
+      <c r="J46" s="57"/>
     </row>
     <row r="47" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A47" s="30"/>
-      <c r="B47" s="70"/>
-      <c r="C47" s="70"/>
-      <c r="D47" s="70"/>
-      <c r="E47" s="70"/>
-      <c r="F47" s="70"/>
-      <c r="G47" s="70"/>
-      <c r="H47" s="70"/>
-      <c r="I47" s="70"/>
-      <c r="J47" s="71"/>
+      <c r="A47" s="28"/>
+      <c r="B47" s="56"/>
+      <c r="C47" s="56"/>
+      <c r="D47" s="56"/>
+      <c r="E47" s="56"/>
+      <c r="F47" s="56"/>
+      <c r="G47" s="56"/>
+      <c r="H47" s="56"/>
+      <c r="I47" s="56"/>
+      <c r="J47" s="57"/>
     </row>
     <row r="48" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A48" s="30"/>
-      <c r="B48" s="70"/>
-      <c r="C48" s="70"/>
-      <c r="D48" s="70"/>
-      <c r="E48" s="70"/>
-      <c r="F48" s="70"/>
-      <c r="G48" s="70"/>
-      <c r="H48" s="70"/>
-      <c r="I48" s="70"/>
-      <c r="J48" s="71"/>
+      <c r="A48" s="28"/>
+      <c r="B48" s="56"/>
+      <c r="C48" s="56"/>
+      <c r="D48" s="56"/>
+      <c r="E48" s="56"/>
+      <c r="F48" s="56"/>
+      <c r="G48" s="56"/>
+      <c r="H48" s="56"/>
+      <c r="I48" s="56"/>
+      <c r="J48" s="57"/>
     </row>
     <row r="49" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A49" s="30"/>
-      <c r="B49" s="70"/>
-      <c r="C49" s="70"/>
-      <c r="D49" s="70"/>
-      <c r="E49" s="70"/>
-      <c r="F49" s="70"/>
-      <c r="G49" s="70"/>
-      <c r="H49" s="70"/>
-      <c r="I49" s="70"/>
-      <c r="J49" s="71"/>
+      <c r="A49" s="28"/>
+      <c r="B49" s="56"/>
+      <c r="C49" s="56"/>
+      <c r="D49" s="56"/>
+      <c r="E49" s="56"/>
+      <c r="F49" s="56"/>
+      <c r="G49" s="56"/>
+      <c r="H49" s="56"/>
+      <c r="I49" s="56"/>
+      <c r="J49" s="57"/>
     </row>
     <row r="50" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A50" s="30"/>
-      <c r="B50" s="70"/>
-      <c r="C50" s="70"/>
-      <c r="D50" s="70"/>
-      <c r="E50" s="70"/>
-      <c r="F50" s="70"/>
-      <c r="G50" s="70"/>
-      <c r="H50" s="70"/>
-      <c r="I50" s="70"/>
-      <c r="J50" s="71"/>
+      <c r="A50" s="28"/>
+      <c r="B50" s="56"/>
+      <c r="C50" s="56"/>
+      <c r="D50" s="56"/>
+      <c r="E50" s="56"/>
+      <c r="F50" s="56"/>
+      <c r="G50" s="56"/>
+      <c r="H50" s="56"/>
+      <c r="I50" s="56"/>
+      <c r="J50" s="57"/>
     </row>
     <row r="51" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A51" s="30"/>
-      <c r="B51" s="70"/>
-      <c r="C51" s="70"/>
-      <c r="D51" s="70"/>
-      <c r="E51" s="70"/>
-      <c r="F51" s="70"/>
-      <c r="G51" s="70"/>
-      <c r="H51" s="70"/>
-      <c r="I51" s="70"/>
-      <c r="J51" s="71"/>
+      <c r="A51" s="28"/>
+      <c r="B51" s="56"/>
+      <c r="C51" s="56"/>
+      <c r="D51" s="56"/>
+      <c r="E51" s="56"/>
+      <c r="F51" s="56"/>
+      <c r="G51" s="56"/>
+      <c r="H51" s="56"/>
+      <c r="I51" s="56"/>
+      <c r="J51" s="57"/>
     </row>
     <row r="52" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A52" s="30"/>
-      <c r="B52" s="70"/>
-      <c r="C52" s="70"/>
-      <c r="D52" s="70"/>
-      <c r="E52" s="70"/>
-      <c r="F52" s="70"/>
-      <c r="G52" s="70"/>
-      <c r="H52" s="70"/>
-      <c r="I52" s="70"/>
-      <c r="J52" s="71"/>
+      <c r="A52" s="28"/>
+      <c r="B52" s="56"/>
+      <c r="C52" s="56"/>
+      <c r="D52" s="56"/>
+      <c r="E52" s="56"/>
+      <c r="F52" s="56"/>
+      <c r="G52" s="56"/>
+      <c r="H52" s="56"/>
+      <c r="I52" s="56"/>
+      <c r="J52" s="57"/>
     </row>
     <row r="53" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A53" s="30"/>
-      <c r="B53" s="70"/>
-      <c r="C53" s="70"/>
-      <c r="D53" s="70"/>
-      <c r="E53" s="70"/>
-      <c r="F53" s="70"/>
-      <c r="G53" s="70"/>
-      <c r="H53" s="70"/>
-      <c r="I53" s="70"/>
-      <c r="J53" s="71"/>
+      <c r="A53" s="28"/>
+      <c r="B53" s="56"/>
+      <c r="C53" s="56"/>
+      <c r="D53" s="56"/>
+      <c r="E53" s="56"/>
+      <c r="F53" s="56"/>
+      <c r="G53" s="56"/>
+      <c r="H53" s="56"/>
+      <c r="I53" s="56"/>
+      <c r="J53" s="57"/>
     </row>
     <row r="54" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A54" s="30"/>
-      <c r="B54" s="70"/>
-      <c r="C54" s="70"/>
-      <c r="D54" s="70"/>
-      <c r="E54" s="70"/>
-      <c r="F54" s="70"/>
-      <c r="G54" s="70"/>
-      <c r="H54" s="70"/>
-      <c r="I54" s="70"/>
-      <c r="J54" s="71"/>
+      <c r="A54" s="28"/>
+      <c r="B54" s="56"/>
+      <c r="C54" s="56"/>
+      <c r="D54" s="56"/>
+      <c r="E54" s="56"/>
+      <c r="F54" s="56"/>
+      <c r="G54" s="56"/>
+      <c r="H54" s="56"/>
+      <c r="I54" s="56"/>
+      <c r="J54" s="57"/>
     </row>
     <row r="55" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A55" s="30"/>
-      <c r="B55" s="70"/>
-      <c r="C55" s="70"/>
-      <c r="D55" s="70"/>
-      <c r="E55" s="70"/>
-      <c r="F55" s="70"/>
-      <c r="G55" s="70"/>
-      <c r="H55" s="70"/>
-      <c r="I55" s="70"/>
-      <c r="J55" s="71"/>
+      <c r="A55" s="28"/>
+      <c r="B55" s="56"/>
+      <c r="C55" s="56"/>
+      <c r="D55" s="56"/>
+      <c r="E55" s="56"/>
+      <c r="F55" s="56"/>
+      <c r="G55" s="56"/>
+      <c r="H55" s="56"/>
+      <c r="I55" s="56"/>
+      <c r="J55" s="57"/>
     </row>
     <row r="56" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A56" s="30"/>
-      <c r="B56" s="70"/>
-      <c r="C56" s="70"/>
-      <c r="D56" s="70"/>
-      <c r="E56" s="70"/>
-      <c r="F56" s="70"/>
-      <c r="G56" s="70"/>
-      <c r="H56" s="70"/>
-      <c r="I56" s="70"/>
-      <c r="J56" s="71"/>
+      <c r="A56" s="28"/>
+      <c r="B56" s="56"/>
+      <c r="C56" s="56"/>
+      <c r="D56" s="56"/>
+      <c r="E56" s="56"/>
+      <c r="F56" s="56"/>
+      <c r="G56" s="56"/>
+      <c r="H56" s="56"/>
+      <c r="I56" s="56"/>
+      <c r="J56" s="57"/>
     </row>
     <row r="57" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A57" s="30"/>
-      <c r="B57" s="70"/>
-      <c r="C57" s="70"/>
-      <c r="D57" s="70"/>
-      <c r="E57" s="70"/>
-      <c r="F57" s="70"/>
-      <c r="G57" s="70"/>
-      <c r="H57" s="70"/>
-      <c r="I57" s="70"/>
-      <c r="J57" s="71"/>
+      <c r="A57" s="28"/>
+      <c r="B57" s="56"/>
+      <c r="C57" s="56"/>
+      <c r="D57" s="56"/>
+      <c r="E57" s="56"/>
+      <c r="F57" s="56"/>
+      <c r="G57" s="56"/>
+      <c r="H57" s="56"/>
+      <c r="I57" s="56"/>
+      <c r="J57" s="57"/>
     </row>
     <row r="58" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A58" s="30"/>
-      <c r="B58" s="70"/>
-      <c r="C58" s="70"/>
-      <c r="D58" s="70"/>
-      <c r="E58" s="70"/>
-      <c r="F58" s="70"/>
-      <c r="G58" s="70"/>
-      <c r="H58" s="70"/>
-      <c r="I58" s="70"/>
-      <c r="J58" s="71"/>
+      <c r="A58" s="28"/>
+      <c r="B58" s="56"/>
+      <c r="C58" s="56"/>
+      <c r="D58" s="56"/>
+      <c r="E58" s="56"/>
+      <c r="F58" s="56"/>
+      <c r="G58" s="56"/>
+      <c r="H58" s="56"/>
+      <c r="I58" s="56"/>
+      <c r="J58" s="57"/>
     </row>
     <row r="59" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A59" s="30"/>
-      <c r="B59" s="70"/>
-      <c r="C59" s="70"/>
-      <c r="D59" s="70"/>
-      <c r="E59" s="70"/>
-      <c r="F59" s="70"/>
-      <c r="G59" s="70"/>
-      <c r="H59" s="70"/>
-      <c r="I59" s="70"/>
-      <c r="J59" s="71"/>
+      <c r="A59" s="28"/>
+      <c r="B59" s="56"/>
+      <c r="C59" s="56"/>
+      <c r="D59" s="56"/>
+      <c r="E59" s="56"/>
+      <c r="F59" s="56"/>
+      <c r="G59" s="56"/>
+      <c r="H59" s="56"/>
+      <c r="I59" s="56"/>
+      <c r="J59" s="57"/>
     </row>
     <row r="60" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A60" s="30"/>
-      <c r="B60" s="70"/>
-      <c r="C60" s="70"/>
-      <c r="D60" s="70"/>
-      <c r="E60" s="70"/>
-      <c r="F60" s="70"/>
-      <c r="G60" s="70"/>
-      <c r="H60" s="70"/>
-      <c r="I60" s="70"/>
-      <c r="J60" s="71"/>
+      <c r="A60" s="28"/>
+      <c r="B60" s="56"/>
+      <c r="C60" s="56"/>
+      <c r="D60" s="56"/>
+      <c r="E60" s="56"/>
+      <c r="F60" s="56"/>
+      <c r="G60" s="56"/>
+      <c r="H60" s="56"/>
+      <c r="I60" s="56"/>
+      <c r="J60" s="57"/>
     </row>
     <row r="61" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A61" s="30"/>
-      <c r="B61" s="70"/>
-      <c r="C61" s="70"/>
-      <c r="D61" s="70"/>
-      <c r="E61" s="70"/>
-      <c r="F61" s="70"/>
-      <c r="G61" s="70"/>
-      <c r="H61" s="70"/>
-      <c r="I61" s="70"/>
-      <c r="J61" s="71"/>
+      <c r="A61" s="28"/>
+      <c r="B61" s="56"/>
+      <c r="C61" s="56"/>
+      <c r="D61" s="56"/>
+      <c r="E61" s="56"/>
+      <c r="F61" s="56"/>
+      <c r="G61" s="56"/>
+      <c r="H61" s="56"/>
+      <c r="I61" s="56"/>
+      <c r="J61" s="57"/>
     </row>
     <row r="62" spans="1:10" ht="13.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A62" s="31"/>
-      <c r="B62" s="72"/>
-      <c r="C62" s="72"/>
-      <c r="D62" s="72"/>
-      <c r="E62" s="72"/>
-      <c r="F62" s="72"/>
-      <c r="G62" s="72"/>
-      <c r="H62" s="72"/>
-      <c r="I62" s="72"/>
-      <c r="J62" s="73"/>
+      <c r="A62" s="29"/>
+      <c r="B62" s="58"/>
+      <c r="C62" s="58"/>
+      <c r="D62" s="58"/>
+      <c r="E62" s="58"/>
+      <c r="F62" s="58"/>
+      <c r="G62" s="58"/>
+      <c r="H62" s="58"/>
+      <c r="I62" s="58"/>
+      <c r="J62" s="59"/>
     </row>
     <row r="63" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A63" s="28">
+      <c r="A63" s="27">
         <v>4</v>
       </c>
-      <c r="B63" s="32" t="s">
+      <c r="B63" s="34" t="s">
         <v>6</v>
       </c>
-      <c r="C63" s="32"/>
-      <c r="D63" s="32"/>
-      <c r="E63" s="32"/>
-      <c r="F63" s="32"/>
-      <c r="G63" s="32"/>
-      <c r="H63" s="32"/>
-      <c r="I63" s="32"/>
-      <c r="J63" s="33"/>
+      <c r="C63" s="34"/>
+      <c r="D63" s="34"/>
+      <c r="E63" s="34"/>
+      <c r="F63" s="34"/>
+      <c r="G63" s="34"/>
+      <c r="H63" s="34"/>
+      <c r="I63" s="34"/>
+      <c r="J63" s="67"/>
     </row>
     <row r="64" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A64" s="30"/>
-      <c r="B64" s="74" t="s">
+      <c r="A64" s="28"/>
+      <c r="B64" s="30" t="s">
         <v>7</v>
       </c>
-      <c r="C64" s="74"/>
-      <c r="D64" s="34"/>
-      <c r="E64" s="34"/>
-      <c r="F64" s="34"/>
-      <c r="G64" s="34"/>
-      <c r="H64" s="34"/>
-      <c r="I64" s="34"/>
-      <c r="J64" s="35"/>
+      <c r="C64" s="30"/>
+      <c r="D64" s="44"/>
+      <c r="E64" s="44"/>
+      <c r="F64" s="44"/>
+      <c r="G64" s="44"/>
+      <c r="H64" s="44"/>
+      <c r="I64" s="44"/>
+      <c r="J64" s="45"/>
     </row>
     <row r="65" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A65" s="30"/>
-      <c r="B65" s="74" t="s">
+      <c r="A65" s="28"/>
+      <c r="B65" s="30" t="s">
         <v>8</v>
       </c>
-      <c r="C65" s="74"/>
-      <c r="D65" s="34"/>
-      <c r="E65" s="34"/>
-      <c r="F65" s="34"/>
-      <c r="G65" s="34"/>
-      <c r="H65" s="34"/>
-      <c r="I65" s="34"/>
-      <c r="J65" s="35"/>
+      <c r="C65" s="30"/>
+      <c r="D65" s="44"/>
+      <c r="E65" s="44"/>
+      <c r="F65" s="44"/>
+      <c r="G65" s="44"/>
+      <c r="H65" s="44"/>
+      <c r="I65" s="44"/>
+      <c r="J65" s="45"/>
     </row>
     <row r="66" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A66" s="30"/>
-      <c r="B66" s="74" t="s">
+      <c r="A66" s="28"/>
+      <c r="B66" s="30" t="s">
         <v>9</v>
       </c>
-      <c r="C66" s="74"/>
-      <c r="D66" s="34"/>
-      <c r="E66" s="34"/>
-      <c r="F66" s="34"/>
-      <c r="G66" s="34"/>
-      <c r="H66" s="34"/>
-      <c r="I66" s="34"/>
-      <c r="J66" s="35"/>
+      <c r="C66" s="30"/>
+      <c r="D66" s="44"/>
+      <c r="E66" s="44"/>
+      <c r="F66" s="44"/>
+      <c r="G66" s="44"/>
+      <c r="H66" s="44"/>
+      <c r="I66" s="44"/>
+      <c r="J66" s="45"/>
     </row>
     <row r="67" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A67" s="30"/>
-      <c r="B67" s="74" t="s">
+      <c r="A67" s="28"/>
+      <c r="B67" s="30" t="s">
         <v>104</v>
       </c>
-      <c r="C67" s="74"/>
-      <c r="D67" s="34"/>
-      <c r="E67" s="34"/>
-      <c r="F67" s="34"/>
-      <c r="G67" s="34"/>
-      <c r="H67" s="34"/>
-      <c r="I67" s="34"/>
-      <c r="J67" s="35"/>
+      <c r="C67" s="30"/>
+      <c r="D67" s="44"/>
+      <c r="E67" s="44"/>
+      <c r="F67" s="44"/>
+      <c r="G67" s="44"/>
+      <c r="H67" s="44"/>
+      <c r="I67" s="44"/>
+      <c r="J67" s="45"/>
     </row>
     <row r="68" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A68" s="30"/>
-      <c r="B68" s="74" t="s">
+      <c r="A68" s="28"/>
+      <c r="B68" s="30" t="s">
         <v>10</v>
       </c>
-      <c r="C68" s="74"/>
-      <c r="D68" s="74"/>
-      <c r="E68" s="74"/>
-      <c r="F68" s="74"/>
-      <c r="G68" s="74"/>
-      <c r="H68" s="74"/>
-      <c r="I68" s="74"/>
-      <c r="J68" s="75"/>
+      <c r="C68" s="30"/>
+      <c r="D68" s="30"/>
+      <c r="E68" s="30"/>
+      <c r="F68" s="30"/>
+      <c r="G68" s="30"/>
+      <c r="H68" s="30"/>
+      <c r="I68" s="30"/>
+      <c r="J68" s="60"/>
     </row>
     <row r="69" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A69" s="30"/>
-      <c r="B69" s="60"/>
-      <c r="C69" s="60"/>
-      <c r="D69" s="60"/>
-      <c r="E69" s="60"/>
-      <c r="F69" s="60"/>
-      <c r="G69" s="60"/>
-      <c r="H69" s="60"/>
-      <c r="I69" s="60"/>
-      <c r="J69" s="61"/>
+      <c r="A69" s="28"/>
+      <c r="B69" s="40"/>
+      <c r="C69" s="40"/>
+      <c r="D69" s="40"/>
+      <c r="E69" s="40"/>
+      <c r="F69" s="40"/>
+      <c r="G69" s="40"/>
+      <c r="H69" s="40"/>
+      <c r="I69" s="40"/>
+      <c r="J69" s="41"/>
     </row>
     <row r="70" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A70" s="30"/>
-      <c r="B70" s="60"/>
-      <c r="C70" s="60"/>
-      <c r="D70" s="60"/>
-      <c r="E70" s="60"/>
-      <c r="F70" s="60"/>
-      <c r="G70" s="60"/>
-      <c r="H70" s="60"/>
-      <c r="I70" s="60"/>
-      <c r="J70" s="61"/>
+      <c r="A70" s="28"/>
+      <c r="B70" s="40"/>
+      <c r="C70" s="40"/>
+      <c r="D70" s="40"/>
+      <c r="E70" s="40"/>
+      <c r="F70" s="40"/>
+      <c r="G70" s="40"/>
+      <c r="H70" s="40"/>
+      <c r="I70" s="40"/>
+      <c r="J70" s="41"/>
     </row>
     <row r="71" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A71" s="30"/>
-      <c r="B71" s="60"/>
-      <c r="C71" s="60"/>
-      <c r="D71" s="60"/>
-      <c r="E71" s="60"/>
-      <c r="F71" s="60"/>
-      <c r="G71" s="60"/>
-      <c r="H71" s="60"/>
-      <c r="I71" s="60"/>
-      <c r="J71" s="61"/>
+      <c r="A71" s="28"/>
+      <c r="B71" s="40"/>
+      <c r="C71" s="40"/>
+      <c r="D71" s="40"/>
+      <c r="E71" s="40"/>
+      <c r="F71" s="40"/>
+      <c r="G71" s="40"/>
+      <c r="H71" s="40"/>
+      <c r="I71" s="40"/>
+      <c r="J71" s="41"/>
     </row>
     <row r="72" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A72" s="30"/>
-      <c r="B72" s="60"/>
-      <c r="C72" s="60"/>
-      <c r="D72" s="60"/>
-      <c r="E72" s="60"/>
-      <c r="F72" s="60"/>
-      <c r="G72" s="60"/>
-      <c r="H72" s="60"/>
-      <c r="I72" s="60"/>
-      <c r="J72" s="61"/>
+      <c r="A72" s="28"/>
+      <c r="B72" s="40"/>
+      <c r="C72" s="40"/>
+      <c r="D72" s="40"/>
+      <c r="E72" s="40"/>
+      <c r="F72" s="40"/>
+      <c r="G72" s="40"/>
+      <c r="H72" s="40"/>
+      <c r="I72" s="40"/>
+      <c r="J72" s="41"/>
     </row>
     <row r="73" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A73" s="30"/>
-      <c r="B73" s="60"/>
-      <c r="C73" s="60"/>
-      <c r="D73" s="60"/>
-      <c r="E73" s="60"/>
-      <c r="F73" s="60"/>
-      <c r="G73" s="60"/>
-      <c r="H73" s="60"/>
-      <c r="I73" s="60"/>
-      <c r="J73" s="61"/>
+      <c r="A73" s="28"/>
+      <c r="B73" s="40"/>
+      <c r="C73" s="40"/>
+      <c r="D73" s="40"/>
+      <c r="E73" s="40"/>
+      <c r="F73" s="40"/>
+      <c r="G73" s="40"/>
+      <c r="H73" s="40"/>
+      <c r="I73" s="40"/>
+      <c r="J73" s="41"/>
     </row>
     <row r="74" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A74" s="30"/>
-      <c r="B74" s="60"/>
-      <c r="C74" s="60"/>
-      <c r="D74" s="60"/>
-      <c r="E74" s="60"/>
-      <c r="F74" s="60"/>
-      <c r="G74" s="60"/>
-      <c r="H74" s="60"/>
-      <c r="I74" s="60"/>
-      <c r="J74" s="61"/>
+      <c r="A74" s="28"/>
+      <c r="B74" s="40"/>
+      <c r="C74" s="40"/>
+      <c r="D74" s="40"/>
+      <c r="E74" s="40"/>
+      <c r="F74" s="40"/>
+      <c r="G74" s="40"/>
+      <c r="H74" s="40"/>
+      <c r="I74" s="40"/>
+      <c r="J74" s="41"/>
     </row>
     <row r="75" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A75" s="30"/>
-      <c r="B75" s="60"/>
-      <c r="C75" s="60"/>
-      <c r="D75" s="60"/>
-      <c r="E75" s="60"/>
-      <c r="F75" s="60"/>
-      <c r="G75" s="60"/>
-      <c r="H75" s="60"/>
-      <c r="I75" s="60"/>
-      <c r="J75" s="61"/>
+      <c r="A75" s="28"/>
+      <c r="B75" s="40"/>
+      <c r="C75" s="40"/>
+      <c r="D75" s="40"/>
+      <c r="E75" s="40"/>
+      <c r="F75" s="40"/>
+      <c r="G75" s="40"/>
+      <c r="H75" s="40"/>
+      <c r="I75" s="40"/>
+      <c r="J75" s="41"/>
     </row>
     <row r="76" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A76" s="30"/>
-      <c r="B76" s="60"/>
-      <c r="C76" s="60"/>
-      <c r="D76" s="60"/>
-      <c r="E76" s="60"/>
-      <c r="F76" s="60"/>
-      <c r="G76" s="60"/>
-      <c r="H76" s="60"/>
-      <c r="I76" s="60"/>
-      <c r="J76" s="61"/>
+      <c r="A76" s="28"/>
+      <c r="B76" s="40"/>
+      <c r="C76" s="40"/>
+      <c r="D76" s="40"/>
+      <c r="E76" s="40"/>
+      <c r="F76" s="40"/>
+      <c r="G76" s="40"/>
+      <c r="H76" s="40"/>
+      <c r="I76" s="40"/>
+      <c r="J76" s="41"/>
     </row>
     <row r="77" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A77" s="30"/>
-      <c r="B77" s="60"/>
-      <c r="C77" s="60"/>
-      <c r="D77" s="60"/>
-      <c r="E77" s="60"/>
-      <c r="F77" s="60"/>
-      <c r="G77" s="60"/>
-      <c r="H77" s="60"/>
-      <c r="I77" s="60"/>
-      <c r="J77" s="61"/>
+      <c r="A77" s="28"/>
+      <c r="B77" s="40"/>
+      <c r="C77" s="40"/>
+      <c r="D77" s="40"/>
+      <c r="E77" s="40"/>
+      <c r="F77" s="40"/>
+      <c r="G77" s="40"/>
+      <c r="H77" s="40"/>
+      <c r="I77" s="40"/>
+      <c r="J77" s="41"/>
     </row>
     <row r="78" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A78" s="30"/>
-      <c r="B78" s="60"/>
-      <c r="C78" s="60"/>
-      <c r="D78" s="60"/>
-      <c r="E78" s="60"/>
-      <c r="F78" s="60"/>
-      <c r="G78" s="60"/>
-      <c r="H78" s="60"/>
-      <c r="I78" s="60"/>
-      <c r="J78" s="61"/>
+      <c r="A78" s="28"/>
+      <c r="B78" s="40"/>
+      <c r="C78" s="40"/>
+      <c r="D78" s="40"/>
+      <c r="E78" s="40"/>
+      <c r="F78" s="40"/>
+      <c r="G78" s="40"/>
+      <c r="H78" s="40"/>
+      <c r="I78" s="40"/>
+      <c r="J78" s="41"/>
     </row>
     <row r="79" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A79" s="30"/>
-      <c r="B79" s="60"/>
-      <c r="C79" s="60"/>
-      <c r="D79" s="60"/>
-      <c r="E79" s="60"/>
-      <c r="F79" s="60"/>
-      <c r="G79" s="60"/>
-      <c r="H79" s="60"/>
-      <c r="I79" s="60"/>
-      <c r="J79" s="61"/>
+      <c r="A79" s="28"/>
+      <c r="B79" s="40"/>
+      <c r="C79" s="40"/>
+      <c r="D79" s="40"/>
+      <c r="E79" s="40"/>
+      <c r="F79" s="40"/>
+      <c r="G79" s="40"/>
+      <c r="H79" s="40"/>
+      <c r="I79" s="40"/>
+      <c r="J79" s="41"/>
     </row>
     <row r="80" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A80" s="30"/>
-      <c r="B80" s="60"/>
-      <c r="C80" s="60"/>
-      <c r="D80" s="60"/>
-      <c r="E80" s="60"/>
-      <c r="F80" s="60"/>
-      <c r="G80" s="60"/>
-      <c r="H80" s="60"/>
-      <c r="I80" s="60"/>
-      <c r="J80" s="61"/>
+      <c r="A80" s="28"/>
+      <c r="B80" s="40"/>
+      <c r="C80" s="40"/>
+      <c r="D80" s="40"/>
+      <c r="E80" s="40"/>
+      <c r="F80" s="40"/>
+      <c r="G80" s="40"/>
+      <c r="H80" s="40"/>
+      <c r="I80" s="40"/>
+      <c r="J80" s="41"/>
     </row>
     <row r="81" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A81" s="30"/>
-      <c r="B81" s="60"/>
-      <c r="C81" s="60"/>
-      <c r="D81" s="60"/>
-      <c r="E81" s="60"/>
-      <c r="F81" s="60"/>
-      <c r="G81" s="60"/>
-      <c r="H81" s="60"/>
-      <c r="I81" s="60"/>
-      <c r="J81" s="61"/>
+      <c r="A81" s="28"/>
+      <c r="B81" s="40"/>
+      <c r="C81" s="40"/>
+      <c r="D81" s="40"/>
+      <c r="E81" s="40"/>
+      <c r="F81" s="40"/>
+      <c r="G81" s="40"/>
+      <c r="H81" s="40"/>
+      <c r="I81" s="40"/>
+      <c r="J81" s="41"/>
     </row>
     <row r="82" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A82" s="30"/>
-      <c r="B82" s="60"/>
-      <c r="C82" s="60"/>
-      <c r="D82" s="60"/>
-      <c r="E82" s="60"/>
-      <c r="F82" s="60"/>
-      <c r="G82" s="60"/>
-      <c r="H82" s="60"/>
-      <c r="I82" s="60"/>
-      <c r="J82" s="61"/>
+      <c r="A82" s="28"/>
+      <c r="B82" s="40"/>
+      <c r="C82" s="40"/>
+      <c r="D82" s="40"/>
+      <c r="E82" s="40"/>
+      <c r="F82" s="40"/>
+      <c r="G82" s="40"/>
+      <c r="H82" s="40"/>
+      <c r="I82" s="40"/>
+      <c r="J82" s="41"/>
     </row>
     <row r="83" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A83" s="30"/>
-      <c r="B83" s="60"/>
-      <c r="C83" s="60"/>
-      <c r="D83" s="60"/>
-      <c r="E83" s="60"/>
-      <c r="F83" s="60"/>
-      <c r="G83" s="60"/>
-      <c r="H83" s="60"/>
-      <c r="I83" s="60"/>
-      <c r="J83" s="61"/>
+      <c r="A83" s="28"/>
+      <c r="B83" s="40"/>
+      <c r="C83" s="40"/>
+      <c r="D83" s="40"/>
+      <c r="E83" s="40"/>
+      <c r="F83" s="40"/>
+      <c r="G83" s="40"/>
+      <c r="H83" s="40"/>
+      <c r="I83" s="40"/>
+      <c r="J83" s="41"/>
     </row>
     <row r="84" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A84" s="30"/>
-      <c r="B84" s="60"/>
-      <c r="C84" s="60"/>
-      <c r="D84" s="60"/>
-      <c r="E84" s="60"/>
-      <c r="F84" s="60"/>
-      <c r="G84" s="60"/>
-      <c r="H84" s="60"/>
-      <c r="I84" s="60"/>
-      <c r="J84" s="61"/>
+      <c r="A84" s="28"/>
+      <c r="B84" s="40"/>
+      <c r="C84" s="40"/>
+      <c r="D84" s="40"/>
+      <c r="E84" s="40"/>
+      <c r="F84" s="40"/>
+      <c r="G84" s="40"/>
+      <c r="H84" s="40"/>
+      <c r="I84" s="40"/>
+      <c r="J84" s="41"/>
     </row>
     <row r="85" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A85" s="30"/>
-      <c r="B85" s="60"/>
-      <c r="C85" s="60"/>
-      <c r="D85" s="60"/>
-      <c r="E85" s="60"/>
-      <c r="F85" s="60"/>
-      <c r="G85" s="60"/>
-      <c r="H85" s="60"/>
-      <c r="I85" s="60"/>
-      <c r="J85" s="61"/>
+      <c r="A85" s="28"/>
+      <c r="B85" s="40"/>
+      <c r="C85" s="40"/>
+      <c r="D85" s="40"/>
+      <c r="E85" s="40"/>
+      <c r="F85" s="40"/>
+      <c r="G85" s="40"/>
+      <c r="H85" s="40"/>
+      <c r="I85" s="40"/>
+      <c r="J85" s="41"/>
     </row>
     <row r="86" spans="1:10" ht="13.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A86" s="29"/>
-      <c r="B86" s="62"/>
-      <c r="C86" s="62"/>
-      <c r="D86" s="62"/>
-      <c r="E86" s="62"/>
-      <c r="F86" s="62"/>
-      <c r="G86" s="62"/>
-      <c r="H86" s="62"/>
-      <c r="I86" s="62"/>
-      <c r="J86" s="63"/>
+      <c r="A86" s="31"/>
+      <c r="B86" s="42"/>
+      <c r="C86" s="42"/>
+      <c r="D86" s="42"/>
+      <c r="E86" s="42"/>
+      <c r="F86" s="42"/>
+      <c r="G86" s="42"/>
+      <c r="H86" s="42"/>
+      <c r="I86" s="42"/>
+      <c r="J86" s="43"/>
     </row>
     <row r="87" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A87" s="28">
+      <c r="A87" s="27">
         <v>5</v>
       </c>
-      <c r="B87" s="32" t="s">
+      <c r="B87" s="34" t="s">
         <v>11</v>
       </c>
-      <c r="C87" s="32"/>
-      <c r="D87" s="32"/>
-      <c r="E87" s="32"/>
-      <c r="F87" s="32"/>
-      <c r="G87" s="32"/>
-      <c r="H87" s="32"/>
-      <c r="I87" s="32"/>
-      <c r="J87" s="33"/>
+      <c r="C87" s="34"/>
+      <c r="D87" s="34"/>
+      <c r="E87" s="34"/>
+      <c r="F87" s="34"/>
+      <c r="G87" s="34"/>
+      <c r="H87" s="34"/>
+      <c r="I87" s="34"/>
+      <c r="J87" s="67"/>
     </row>
     <row r="88" spans="1:10" ht="13.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A88" s="30"/>
-      <c r="B88" s="49" t="s">
+      <c r="A88" s="28"/>
+      <c r="B88" s="76" t="s">
         <v>12</v>
       </c>
-      <c r="C88" s="49"/>
-      <c r="D88" s="49"/>
-      <c r="E88" s="49"/>
-      <c r="F88" s="49"/>
-      <c r="G88" s="49"/>
-      <c r="H88" s="49"/>
-      <c r="I88" s="49"/>
-      <c r="J88" s="50"/>
+      <c r="C88" s="76"/>
+      <c r="D88" s="76"/>
+      <c r="E88" s="76"/>
+      <c r="F88" s="76"/>
+      <c r="G88" s="76"/>
+      <c r="H88" s="76"/>
+      <c r="I88" s="76"/>
+      <c r="J88" s="77"/>
     </row>
     <row r="89" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A89" s="28">
+      <c r="A89" s="27">
         <v>6</v>
       </c>
-      <c r="B89" s="42" t="s">
+      <c r="B89" s="32" t="s">
         <v>13</v>
       </c>
-      <c r="C89" s="42"/>
-      <c r="D89" s="42"/>
-      <c r="E89" s="42"/>
-      <c r="F89" s="42"/>
-      <c r="G89" s="42"/>
-      <c r="H89" s="42"/>
-      <c r="I89" s="42"/>
-      <c r="J89" s="43"/>
+      <c r="C89" s="32"/>
+      <c r="D89" s="32"/>
+      <c r="E89" s="32"/>
+      <c r="F89" s="32"/>
+      <c r="G89" s="32"/>
+      <c r="H89" s="32"/>
+      <c r="I89" s="32"/>
+      <c r="J89" s="33"/>
     </row>
     <row r="90" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A90" s="44"/>
-      <c r="B90" s="45" t="s">
+      <c r="A90" s="75"/>
+      <c r="B90" s="46" t="s">
         <v>14</v>
       </c>
-      <c r="C90" s="45"/>
-      <c r="D90" s="45"/>
-      <c r="E90" s="45"/>
-      <c r="F90" s="45"/>
-      <c r="G90" s="45"/>
-      <c r="H90" s="45"/>
-      <c r="I90" s="45"/>
-      <c r="J90" s="46"/>
+      <c r="C90" s="46"/>
+      <c r="D90" s="46"/>
+      <c r="E90" s="46"/>
+      <c r="F90" s="46"/>
+      <c r="G90" s="46"/>
+      <c r="H90" s="46"/>
+      <c r="I90" s="46"/>
+      <c r="J90" s="47"/>
     </row>
     <row r="91" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A91" s="44"/>
-      <c r="B91" s="45"/>
-      <c r="C91" s="45"/>
-      <c r="D91" s="45"/>
-      <c r="E91" s="45"/>
-      <c r="F91" s="45"/>
-      <c r="G91" s="45"/>
-      <c r="H91" s="45"/>
-      <c r="I91" s="45"/>
-      <c r="J91" s="46"/>
+      <c r="A91" s="75"/>
+      <c r="B91" s="46"/>
+      <c r="C91" s="46"/>
+      <c r="D91" s="46"/>
+      <c r="E91" s="46"/>
+      <c r="F91" s="46"/>
+      <c r="G91" s="46"/>
+      <c r="H91" s="46"/>
+      <c r="I91" s="46"/>
+      <c r="J91" s="47"/>
     </row>
     <row r="92" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A92" s="44"/>
-      <c r="B92" s="47"/>
-      <c r="C92" s="47"/>
-      <c r="D92" s="47"/>
-      <c r="E92" s="47"/>
-      <c r="F92" s="47"/>
-      <c r="G92" s="47"/>
-      <c r="H92" s="47"/>
-      <c r="I92" s="47"/>
-      <c r="J92" s="48"/>
+      <c r="A92" s="75"/>
+      <c r="B92" s="48"/>
+      <c r="C92" s="48"/>
+      <c r="D92" s="48"/>
+      <c r="E92" s="48"/>
+      <c r="F92" s="48"/>
+      <c r="G92" s="48"/>
+      <c r="H92" s="48"/>
+      <c r="I92" s="48"/>
+      <c r="J92" s="49"/>
     </row>
     <row r="93" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A93" s="30"/>
-      <c r="B93" s="51"/>
-      <c r="C93" s="52"/>
-      <c r="D93" s="52"/>
-      <c r="E93" s="52"/>
-      <c r="F93" s="52"/>
-      <c r="G93" s="52"/>
-      <c r="H93" s="52"/>
-      <c r="I93" s="52"/>
-      <c r="J93" s="53"/>
+      <c r="A93" s="28"/>
+      <c r="B93" s="78"/>
+      <c r="C93" s="62"/>
+      <c r="D93" s="62"/>
+      <c r="E93" s="62"/>
+      <c r="F93" s="62"/>
+      <c r="G93" s="62"/>
+      <c r="H93" s="62"/>
+      <c r="I93" s="62"/>
+      <c r="J93" s="63"/>
     </row>
     <row r="94" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A94" s="30"/>
-      <c r="B94" s="54"/>
-      <c r="C94" s="55"/>
-      <c r="D94" s="55"/>
-      <c r="E94" s="55"/>
-      <c r="F94" s="55"/>
-      <c r="G94" s="55"/>
-      <c r="H94" s="55"/>
-      <c r="I94" s="55"/>
-      <c r="J94" s="56"/>
+      <c r="A94" s="28"/>
+      <c r="B94" s="64"/>
+      <c r="C94" s="65"/>
+      <c r="D94" s="65"/>
+      <c r="E94" s="65"/>
+      <c r="F94" s="65"/>
+      <c r="G94" s="65"/>
+      <c r="H94" s="65"/>
+      <c r="I94" s="65"/>
+      <c r="J94" s="66"/>
     </row>
     <row r="95" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A95" s="30"/>
-      <c r="B95" s="54"/>
-      <c r="C95" s="55"/>
-      <c r="D95" s="55"/>
-      <c r="E95" s="55"/>
-      <c r="F95" s="55"/>
-      <c r="G95" s="55"/>
-      <c r="H95" s="55"/>
-      <c r="I95" s="55"/>
-      <c r="J95" s="56"/>
+      <c r="A95" s="28"/>
+      <c r="B95" s="64"/>
+      <c r="C95" s="65"/>
+      <c r="D95" s="65"/>
+      <c r="E95" s="65"/>
+      <c r="F95" s="65"/>
+      <c r="G95" s="65"/>
+      <c r="H95" s="65"/>
+      <c r="I95" s="65"/>
+      <c r="J95" s="66"/>
     </row>
     <row r="96" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A96" s="30"/>
-      <c r="B96" s="54"/>
-      <c r="C96" s="55"/>
-      <c r="D96" s="55"/>
-      <c r="E96" s="55"/>
-      <c r="F96" s="55"/>
-      <c r="G96" s="55"/>
-      <c r="H96" s="55"/>
-      <c r="I96" s="55"/>
-      <c r="J96" s="56"/>
+      <c r="A96" s="28"/>
+      <c r="B96" s="64"/>
+      <c r="C96" s="65"/>
+      <c r="D96" s="65"/>
+      <c r="E96" s="65"/>
+      <c r="F96" s="65"/>
+      <c r="G96" s="65"/>
+      <c r="H96" s="65"/>
+      <c r="I96" s="65"/>
+      <c r="J96" s="66"/>
     </row>
     <row r="97" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A97" s="30"/>
-      <c r="B97" s="54"/>
-      <c r="C97" s="55"/>
-      <c r="D97" s="55"/>
-      <c r="E97" s="55"/>
-      <c r="F97" s="55"/>
-      <c r="G97" s="55"/>
-      <c r="H97" s="55"/>
-      <c r="I97" s="55"/>
-      <c r="J97" s="56"/>
+      <c r="A97" s="28"/>
+      <c r="B97" s="64"/>
+      <c r="C97" s="65"/>
+      <c r="D97" s="65"/>
+      <c r="E97" s="65"/>
+      <c r="F97" s="65"/>
+      <c r="G97" s="65"/>
+      <c r="H97" s="65"/>
+      <c r="I97" s="65"/>
+      <c r="J97" s="66"/>
     </row>
     <row r="98" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A98" s="30"/>
-      <c r="B98" s="54"/>
-      <c r="C98" s="55"/>
-      <c r="D98" s="55"/>
-      <c r="E98" s="55"/>
-      <c r="F98" s="55"/>
-      <c r="G98" s="55"/>
-      <c r="H98" s="55"/>
-      <c r="I98" s="55"/>
-      <c r="J98" s="56"/>
+      <c r="A98" s="28"/>
+      <c r="B98" s="64"/>
+      <c r="C98" s="65"/>
+      <c r="D98" s="65"/>
+      <c r="E98" s="65"/>
+      <c r="F98" s="65"/>
+      <c r="G98" s="65"/>
+      <c r="H98" s="65"/>
+      <c r="I98" s="65"/>
+      <c r="J98" s="66"/>
     </row>
     <row r="99" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A99" s="30"/>
-      <c r="B99" s="54"/>
-      <c r="C99" s="55"/>
-      <c r="D99" s="55"/>
-      <c r="E99" s="55"/>
-      <c r="F99" s="55"/>
-      <c r="G99" s="55"/>
-      <c r="H99" s="55"/>
-      <c r="I99" s="55"/>
-      <c r="J99" s="56"/>
+      <c r="A99" s="28"/>
+      <c r="B99" s="64"/>
+      <c r="C99" s="65"/>
+      <c r="D99" s="65"/>
+      <c r="E99" s="65"/>
+      <c r="F99" s="65"/>
+      <c r="G99" s="65"/>
+      <c r="H99" s="65"/>
+      <c r="I99" s="65"/>
+      <c r="J99" s="66"/>
     </row>
     <row r="100" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A100" s="30"/>
-      <c r="B100" s="54"/>
-      <c r="C100" s="55"/>
-      <c r="D100" s="55"/>
-      <c r="E100" s="55"/>
-      <c r="F100" s="55"/>
-      <c r="G100" s="55"/>
-      <c r="H100" s="55"/>
-      <c r="I100" s="55"/>
-      <c r="J100" s="56"/>
+      <c r="A100" s="28"/>
+      <c r="B100" s="64"/>
+      <c r="C100" s="65"/>
+      <c r="D100" s="65"/>
+      <c r="E100" s="65"/>
+      <c r="F100" s="65"/>
+      <c r="G100" s="65"/>
+      <c r="H100" s="65"/>
+      <c r="I100" s="65"/>
+      <c r="J100" s="66"/>
     </row>
     <row r="101" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A101" s="30"/>
-      <c r="B101" s="54"/>
-      <c r="C101" s="55"/>
-      <c r="D101" s="55"/>
-      <c r="E101" s="55"/>
-      <c r="F101" s="55"/>
-      <c r="G101" s="55"/>
-      <c r="H101" s="55"/>
-      <c r="I101" s="55"/>
-      <c r="J101" s="56"/>
+      <c r="A101" s="28"/>
+      <c r="B101" s="64"/>
+      <c r="C101" s="65"/>
+      <c r="D101" s="65"/>
+      <c r="E101" s="65"/>
+      <c r="F101" s="65"/>
+      <c r="G101" s="65"/>
+      <c r="H101" s="65"/>
+      <c r="I101" s="65"/>
+      <c r="J101" s="66"/>
     </row>
     <row r="102" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A102" s="30"/>
-      <c r="B102" s="54"/>
-      <c r="C102" s="55"/>
-      <c r="D102" s="55"/>
-      <c r="E102" s="55"/>
-      <c r="F102" s="55"/>
-      <c r="G102" s="55"/>
-      <c r="H102" s="55"/>
-      <c r="I102" s="55"/>
-      <c r="J102" s="56"/>
+      <c r="A102" s="28"/>
+      <c r="B102" s="64"/>
+      <c r="C102" s="65"/>
+      <c r="D102" s="65"/>
+      <c r="E102" s="65"/>
+      <c r="F102" s="65"/>
+      <c r="G102" s="65"/>
+      <c r="H102" s="65"/>
+      <c r="I102" s="65"/>
+      <c r="J102" s="66"/>
     </row>
     <row r="103" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A103" s="30"/>
-      <c r="B103" s="54"/>
-      <c r="C103" s="55"/>
-      <c r="D103" s="55"/>
-      <c r="E103" s="55"/>
-      <c r="F103" s="55"/>
-      <c r="G103" s="55"/>
-      <c r="H103" s="55"/>
-      <c r="I103" s="55"/>
-      <c r="J103" s="56"/>
+      <c r="A103" s="28"/>
+      <c r="B103" s="64"/>
+      <c r="C103" s="65"/>
+      <c r="D103" s="65"/>
+      <c r="E103" s="65"/>
+      <c r="F103" s="65"/>
+      <c r="G103" s="65"/>
+      <c r="H103" s="65"/>
+      <c r="I103" s="65"/>
+      <c r="J103" s="66"/>
     </row>
     <row r="104" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A104" s="30"/>
-      <c r="B104" s="54"/>
-      <c r="C104" s="55"/>
-      <c r="D104" s="55"/>
-      <c r="E104" s="55"/>
-      <c r="F104" s="55"/>
-      <c r="G104" s="55"/>
-      <c r="H104" s="55"/>
-      <c r="I104" s="55"/>
-      <c r="J104" s="56"/>
+      <c r="A104" s="28"/>
+      <c r="B104" s="64"/>
+      <c r="C104" s="65"/>
+      <c r="D104" s="65"/>
+      <c r="E104" s="65"/>
+      <c r="F104" s="65"/>
+      <c r="G104" s="65"/>
+      <c r="H104" s="65"/>
+      <c r="I104" s="65"/>
+      <c r="J104" s="66"/>
     </row>
     <row r="105" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A105" s="30"/>
-      <c r="B105" s="54"/>
-      <c r="C105" s="55"/>
-      <c r="D105" s="55"/>
-      <c r="E105" s="55"/>
-      <c r="F105" s="55"/>
-      <c r="G105" s="55"/>
-      <c r="H105" s="55"/>
-      <c r="I105" s="55"/>
-      <c r="J105" s="56"/>
+      <c r="A105" s="28"/>
+      <c r="B105" s="64"/>
+      <c r="C105" s="65"/>
+      <c r="D105" s="65"/>
+      <c r="E105" s="65"/>
+      <c r="F105" s="65"/>
+      <c r="G105" s="65"/>
+      <c r="H105" s="65"/>
+      <c r="I105" s="65"/>
+      <c r="J105" s="66"/>
     </row>
     <row r="106" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A106" s="30"/>
-      <c r="B106" s="54"/>
-      <c r="C106" s="55"/>
-      <c r="D106" s="55"/>
-      <c r="E106" s="55"/>
-      <c r="F106" s="55"/>
-      <c r="G106" s="55"/>
-      <c r="H106" s="55"/>
-      <c r="I106" s="55"/>
-      <c r="J106" s="56"/>
+      <c r="A106" s="28"/>
+      <c r="B106" s="64"/>
+      <c r="C106" s="65"/>
+      <c r="D106" s="65"/>
+      <c r="E106" s="65"/>
+      <c r="F106" s="65"/>
+      <c r="G106" s="65"/>
+      <c r="H106" s="65"/>
+      <c r="I106" s="65"/>
+      <c r="J106" s="66"/>
     </row>
     <row r="107" spans="1:10" ht="13.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A107" s="31"/>
-      <c r="B107" s="57"/>
-      <c r="C107" s="58"/>
-      <c r="D107" s="58"/>
-      <c r="E107" s="58"/>
-      <c r="F107" s="58"/>
-      <c r="G107" s="58"/>
-      <c r="H107" s="58"/>
-      <c r="I107" s="58"/>
-      <c r="J107" s="59"/>
+      <c r="A107" s="29"/>
+      <c r="B107" s="79"/>
+      <c r="C107" s="80"/>
+      <c r="D107" s="80"/>
+      <c r="E107" s="80"/>
+      <c r="F107" s="80"/>
+      <c r="G107" s="80"/>
+      <c r="H107" s="80"/>
+      <c r="I107" s="80"/>
+      <c r="J107" s="81"/>
     </row>
     <row r="108" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A108" s="28">
+      <c r="A108" s="27">
         <v>7</v>
       </c>
-      <c r="B108" s="32" t="s">
+      <c r="B108" s="34" t="s">
         <v>15</v>
       </c>
-      <c r="C108" s="32"/>
-      <c r="D108" s="32"/>
-      <c r="E108" s="32"/>
-      <c r="F108" s="32"/>
-      <c r="G108" s="32"/>
-      <c r="H108" s="32"/>
-      <c r="I108" s="32"/>
-      <c r="J108" s="33"/>
+      <c r="C108" s="34"/>
+      <c r="D108" s="34"/>
+      <c r="E108" s="34"/>
+      <c r="F108" s="34"/>
+      <c r="G108" s="34"/>
+      <c r="H108" s="34"/>
+      <c r="I108" s="34"/>
+      <c r="J108" s="67"/>
     </row>
     <row r="109" spans="1:10" ht="13.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A109" s="29"/>
-      <c r="B109" s="40" t="s">
+      <c r="A109" s="31"/>
+      <c r="B109" s="73" t="s">
         <v>16</v>
       </c>
-      <c r="C109" s="40"/>
-      <c r="D109" s="40"/>
-      <c r="E109" s="40"/>
-      <c r="F109" s="40"/>
-      <c r="G109" s="40"/>
-      <c r="H109" s="40"/>
-      <c r="I109" s="40"/>
-      <c r="J109" s="41"/>
+      <c r="C109" s="73"/>
+      <c r="D109" s="73"/>
+      <c r="E109" s="73"/>
+      <c r="F109" s="73"/>
+      <c r="G109" s="73"/>
+      <c r="H109" s="73"/>
+      <c r="I109" s="73"/>
+      <c r="J109" s="74"/>
     </row>
     <row r="110" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A110" s="28">
+      <c r="A110" s="27">
         <v>8</v>
       </c>
-      <c r="B110" s="32" t="s">
+      <c r="B110" s="34" t="s">
         <v>17</v>
       </c>
-      <c r="C110" s="32"/>
-      <c r="D110" s="32"/>
-      <c r="E110" s="32"/>
-      <c r="F110" s="32"/>
-      <c r="G110" s="32"/>
-      <c r="H110" s="32"/>
-      <c r="I110" s="32"/>
-      <c r="J110" s="33"/>
+      <c r="C110" s="34"/>
+      <c r="D110" s="34"/>
+      <c r="E110" s="34"/>
+      <c r="F110" s="34"/>
+      <c r="G110" s="34"/>
+      <c r="H110" s="34"/>
+      <c r="I110" s="34"/>
+      <c r="J110" s="67"/>
     </row>
     <row r="111" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A111" s="30"/>
-      <c r="B111" s="34"/>
-      <c r="C111" s="34"/>
-      <c r="D111" s="34"/>
-      <c r="E111" s="34"/>
-      <c r="F111" s="34"/>
-      <c r="G111" s="34"/>
-      <c r="H111" s="34"/>
-      <c r="I111" s="34"/>
-      <c r="J111" s="35"/>
+      <c r="A111" s="28"/>
+      <c r="B111" s="44"/>
+      <c r="C111" s="44"/>
+      <c r="D111" s="44"/>
+      <c r="E111" s="44"/>
+      <c r="F111" s="44"/>
+      <c r="G111" s="44"/>
+      <c r="H111" s="44"/>
+      <c r="I111" s="44"/>
+      <c r="J111" s="45"/>
     </row>
     <row r="112" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A112" s="30"/>
-      <c r="B112" s="34"/>
-      <c r="C112" s="34"/>
-      <c r="D112" s="34"/>
-      <c r="E112" s="34"/>
-      <c r="F112" s="34"/>
-      <c r="G112" s="34"/>
-      <c r="H112" s="34"/>
-      <c r="I112" s="34"/>
-      <c r="J112" s="35"/>
+      <c r="A112" s="28"/>
+      <c r="B112" s="44"/>
+      <c r="C112" s="44"/>
+      <c r="D112" s="44"/>
+      <c r="E112" s="44"/>
+      <c r="F112" s="44"/>
+      <c r="G112" s="44"/>
+      <c r="H112" s="44"/>
+      <c r="I112" s="44"/>
+      <c r="J112" s="45"/>
     </row>
     <row r="113" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A113" s="30"/>
-      <c r="B113" s="34"/>
-      <c r="C113" s="34"/>
-      <c r="D113" s="34"/>
-      <c r="E113" s="34"/>
-      <c r="F113" s="34"/>
-      <c r="G113" s="34"/>
-      <c r="H113" s="34"/>
-      <c r="I113" s="34"/>
-      <c r="J113" s="35"/>
+      <c r="A113" s="28"/>
+      <c r="B113" s="44"/>
+      <c r="C113" s="44"/>
+      <c r="D113" s="44"/>
+      <c r="E113" s="44"/>
+      <c r="F113" s="44"/>
+      <c r="G113" s="44"/>
+      <c r="H113" s="44"/>
+      <c r="I113" s="44"/>
+      <c r="J113" s="45"/>
     </row>
     <row r="114" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A114" s="30"/>
-      <c r="B114" s="34"/>
-      <c r="C114" s="34"/>
-      <c r="D114" s="34"/>
-      <c r="E114" s="34"/>
-      <c r="F114" s="34"/>
-      <c r="G114" s="34"/>
-      <c r="H114" s="34"/>
-      <c r="I114" s="34"/>
-      <c r="J114" s="35"/>
+      <c r="A114" s="28"/>
+      <c r="B114" s="44"/>
+      <c r="C114" s="44"/>
+      <c r="D114" s="44"/>
+      <c r="E114" s="44"/>
+      <c r="F114" s="44"/>
+      <c r="G114" s="44"/>
+      <c r="H114" s="44"/>
+      <c r="I114" s="44"/>
+      <c r="J114" s="45"/>
     </row>
     <row r="115" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A115" s="30"/>
-      <c r="B115" s="34"/>
-      <c r="C115" s="34"/>
-      <c r="D115" s="34"/>
-      <c r="E115" s="34"/>
-      <c r="F115" s="34"/>
-      <c r="G115" s="34"/>
-      <c r="H115" s="34"/>
-      <c r="I115" s="34"/>
-      <c r="J115" s="35"/>
+      <c r="A115" s="28"/>
+      <c r="B115" s="44"/>
+      <c r="C115" s="44"/>
+      <c r="D115" s="44"/>
+      <c r="E115" s="44"/>
+      <c r="F115" s="44"/>
+      <c r="G115" s="44"/>
+      <c r="H115" s="44"/>
+      <c r="I115" s="44"/>
+      <c r="J115" s="45"/>
     </row>
     <row r="116" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A116" s="30"/>
-      <c r="B116" s="34"/>
-      <c r="C116" s="34"/>
-      <c r="D116" s="34"/>
-      <c r="E116" s="34"/>
-      <c r="F116" s="34"/>
-      <c r="G116" s="34"/>
-      <c r="H116" s="34"/>
-      <c r="I116" s="34"/>
-      <c r="J116" s="35"/>
+      <c r="A116" s="28"/>
+      <c r="B116" s="44"/>
+      <c r="C116" s="44"/>
+      <c r="D116" s="44"/>
+      <c r="E116" s="44"/>
+      <c r="F116" s="44"/>
+      <c r="G116" s="44"/>
+      <c r="H116" s="44"/>
+      <c r="I116" s="44"/>
+      <c r="J116" s="45"/>
     </row>
     <row r="117" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A117" s="30"/>
-      <c r="B117" s="36" t="s">
+      <c r="A117" s="28"/>
+      <c r="B117" s="69" t="s">
         <v>18</v>
       </c>
-      <c r="C117" s="36"/>
-      <c r="D117" s="36"/>
-      <c r="E117" s="36"/>
-      <c r="F117" s="36"/>
-      <c r="G117" s="36"/>
-      <c r="H117" s="36"/>
-      <c r="I117" s="36"/>
-      <c r="J117" s="37"/>
+      <c r="C117" s="69"/>
+      <c r="D117" s="69"/>
+      <c r="E117" s="69"/>
+      <c r="F117" s="69"/>
+      <c r="G117" s="69"/>
+      <c r="H117" s="69"/>
+      <c r="I117" s="69"/>
+      <c r="J117" s="70"/>
     </row>
     <row r="118" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A118" s="30"/>
-      <c r="B118" s="34"/>
-      <c r="C118" s="34"/>
-      <c r="D118" s="34"/>
-      <c r="E118" s="34"/>
-      <c r="F118" s="34"/>
-      <c r="G118" s="34"/>
-      <c r="H118" s="34"/>
-      <c r="I118" s="34"/>
-      <c r="J118" s="35"/>
+      <c r="A118" s="28"/>
+      <c r="B118" s="44"/>
+      <c r="C118" s="44"/>
+      <c r="D118" s="44"/>
+      <c r="E118" s="44"/>
+      <c r="F118" s="44"/>
+      <c r="G118" s="44"/>
+      <c r="H118" s="44"/>
+      <c r="I118" s="44"/>
+      <c r="J118" s="45"/>
     </row>
     <row r="119" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A119" s="30"/>
-      <c r="B119" s="34"/>
-      <c r="C119" s="34"/>
-      <c r="D119" s="34"/>
-      <c r="E119" s="34"/>
-      <c r="F119" s="34"/>
-      <c r="G119" s="34"/>
-      <c r="H119" s="34"/>
-      <c r="I119" s="34"/>
-      <c r="J119" s="35"/>
+      <c r="A119" s="28"/>
+      <c r="B119" s="44"/>
+      <c r="C119" s="44"/>
+      <c r="D119" s="44"/>
+      <c r="E119" s="44"/>
+      <c r="F119" s="44"/>
+      <c r="G119" s="44"/>
+      <c r="H119" s="44"/>
+      <c r="I119" s="44"/>
+      <c r="J119" s="45"/>
     </row>
     <row r="120" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A120" s="30"/>
-      <c r="B120" s="34"/>
-      <c r="C120" s="34"/>
-      <c r="D120" s="34"/>
-      <c r="E120" s="34"/>
-      <c r="F120" s="34"/>
-      <c r="G120" s="34"/>
-      <c r="H120" s="34"/>
-      <c r="I120" s="34"/>
-      <c r="J120" s="35"/>
+      <c r="A120" s="28"/>
+      <c r="B120" s="44"/>
+      <c r="C120" s="44"/>
+      <c r="D120" s="44"/>
+      <c r="E120" s="44"/>
+      <c r="F120" s="44"/>
+      <c r="G120" s="44"/>
+      <c r="H120" s="44"/>
+      <c r="I120" s="44"/>
+      <c r="J120" s="45"/>
     </row>
     <row r="121" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A121" s="30"/>
-      <c r="B121" s="34"/>
-      <c r="C121" s="34"/>
-      <c r="D121" s="34"/>
-      <c r="E121" s="34"/>
-      <c r="F121" s="34"/>
-      <c r="G121" s="34"/>
-      <c r="H121" s="34"/>
-      <c r="I121" s="34"/>
-      <c r="J121" s="35"/>
+      <c r="A121" s="28"/>
+      <c r="B121" s="44"/>
+      <c r="C121" s="44"/>
+      <c r="D121" s="44"/>
+      <c r="E121" s="44"/>
+      <c r="F121" s="44"/>
+      <c r="G121" s="44"/>
+      <c r="H121" s="44"/>
+      <c r="I121" s="44"/>
+      <c r="J121" s="45"/>
     </row>
     <row r="122" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A122" s="30"/>
-      <c r="B122" s="34"/>
-      <c r="C122" s="34"/>
-      <c r="D122" s="34"/>
-      <c r="E122" s="34"/>
-      <c r="F122" s="34"/>
-      <c r="G122" s="34"/>
-      <c r="H122" s="34"/>
-      <c r="I122" s="34"/>
-      <c r="J122" s="35"/>
+      <c r="A122" s="28"/>
+      <c r="B122" s="44"/>
+      <c r="C122" s="44"/>
+      <c r="D122" s="44"/>
+      <c r="E122" s="44"/>
+      <c r="F122" s="44"/>
+      <c r="G122" s="44"/>
+      <c r="H122" s="44"/>
+      <c r="I122" s="44"/>
+      <c r="J122" s="45"/>
     </row>
     <row r="123" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A123" s="30"/>
-      <c r="B123" s="34"/>
-      <c r="C123" s="34"/>
-      <c r="D123" s="34"/>
-      <c r="E123" s="34"/>
-      <c r="F123" s="34"/>
-      <c r="G123" s="34"/>
-      <c r="H123" s="34"/>
-      <c r="I123" s="34"/>
-      <c r="J123" s="35"/>
+      <c r="A123" s="28"/>
+      <c r="B123" s="44"/>
+      <c r="C123" s="44"/>
+      <c r="D123" s="44"/>
+      <c r="E123" s="44"/>
+      <c r="F123" s="44"/>
+      <c r="G123" s="44"/>
+      <c r="H123" s="44"/>
+      <c r="I123" s="44"/>
+      <c r="J123" s="45"/>
     </row>
     <row r="124" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A124" s="30"/>
-      <c r="B124" s="34"/>
-      <c r="C124" s="34"/>
-      <c r="D124" s="34"/>
-      <c r="E124" s="34"/>
-      <c r="F124" s="34"/>
-      <c r="G124" s="34"/>
-      <c r="H124" s="34"/>
-      <c r="I124" s="34"/>
-      <c r="J124" s="35"/>
+      <c r="A124" s="28"/>
+      <c r="B124" s="44"/>
+      <c r="C124" s="44"/>
+      <c r="D124" s="44"/>
+      <c r="E124" s="44"/>
+      <c r="F124" s="44"/>
+      <c r="G124" s="44"/>
+      <c r="H124" s="44"/>
+      <c r="I124" s="44"/>
+      <c r="J124" s="45"/>
     </row>
     <row r="125" spans="1:10" ht="13.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A125" s="31"/>
-      <c r="B125" s="38"/>
-      <c r="C125" s="38"/>
-      <c r="D125" s="38"/>
-      <c r="E125" s="38"/>
-      <c r="F125" s="38"/>
-      <c r="G125" s="38"/>
-      <c r="H125" s="38"/>
-      <c r="I125" s="38"/>
-      <c r="J125" s="39"/>
+      <c r="A125" s="29"/>
+      <c r="B125" s="71"/>
+      <c r="C125" s="71"/>
+      <c r="D125" s="71"/>
+      <c r="E125" s="71"/>
+      <c r="F125" s="71"/>
+      <c r="G125" s="71"/>
+      <c r="H125" s="71"/>
+      <c r="I125" s="71"/>
+      <c r="J125" s="72"/>
     </row>
   </sheetData>
   <mergeCells count="39">
-    <mergeCell ref="A21:A62"/>
-    <mergeCell ref="B64:C64"/>
-    <mergeCell ref="A2:A3"/>
-    <mergeCell ref="A4:A20"/>
-    <mergeCell ref="B4:J4"/>
-    <mergeCell ref="B2:D3"/>
-    <mergeCell ref="E2:J3"/>
+    <mergeCell ref="A1:J1"/>
+    <mergeCell ref="A108:A109"/>
+    <mergeCell ref="A110:A125"/>
+    <mergeCell ref="B110:J110"/>
+    <mergeCell ref="B111:J116"/>
+    <mergeCell ref="B117:J117"/>
+    <mergeCell ref="B118:J125"/>
+    <mergeCell ref="B109:J109"/>
+    <mergeCell ref="B108:J108"/>
+    <mergeCell ref="B89:J89"/>
+    <mergeCell ref="A89:A107"/>
+    <mergeCell ref="B90:J92"/>
+    <mergeCell ref="A87:A88"/>
+    <mergeCell ref="B87:J87"/>
+    <mergeCell ref="B88:J88"/>
+    <mergeCell ref="B93:J107"/>
     <mergeCell ref="B69:J86"/>
     <mergeCell ref="A63:A86"/>
     <mergeCell ref="D64:J64"/>
@@ -4973,22 +5009,13 @@
     <mergeCell ref="B66:C66"/>
     <mergeCell ref="D65:J65"/>
     <mergeCell ref="B65:C65"/>
-    <mergeCell ref="A1:J1"/>
-    <mergeCell ref="A108:A109"/>
-    <mergeCell ref="A110:A125"/>
-    <mergeCell ref="B110:J110"/>
-    <mergeCell ref="B111:J116"/>
-    <mergeCell ref="B117:J117"/>
-    <mergeCell ref="B118:J125"/>
-    <mergeCell ref="B109:J109"/>
-    <mergeCell ref="B108:J108"/>
-    <mergeCell ref="B89:J89"/>
-    <mergeCell ref="A89:A107"/>
-    <mergeCell ref="B90:J92"/>
-    <mergeCell ref="A87:A88"/>
-    <mergeCell ref="B87:J87"/>
-    <mergeCell ref="B88:J88"/>
-    <mergeCell ref="B93:J107"/>
+    <mergeCell ref="A21:A62"/>
+    <mergeCell ref="B64:C64"/>
+    <mergeCell ref="A2:A3"/>
+    <mergeCell ref="A4:A20"/>
+    <mergeCell ref="B4:J4"/>
+    <mergeCell ref="B2:D3"/>
+    <mergeCell ref="E2:J3"/>
   </mergeCells>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.75" right="0.75" top="0.6" bottom="0.61" header="0.4" footer="0.39"/>
@@ -5017,71 +5044,71 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="77" t="s">
+      <c r="A1" s="35" t="s">
         <v>19</v>
       </c>
-      <c r="B1" s="77"/>
-      <c r="C1" s="77"/>
+      <c r="B1" s="35"/>
+      <c r="C1" s="35"/>
     </row>
     <row r="2" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="85" t="s">
+      <c r="A2" s="90" t="s">
         <v>20</v>
       </c>
-      <c r="B2" s="85"/>
-      <c r="C2" s="85"/>
-      <c r="D2" s="85"/>
-      <c r="E2" s="85"/>
-      <c r="F2" s="85"/>
-      <c r="G2" s="85"/>
-      <c r="H2" s="85"/>
+      <c r="B2" s="90"/>
+      <c r="C2" s="90"/>
+      <c r="D2" s="90"/>
+      <c r="E2" s="90"/>
+      <c r="F2" s="90"/>
+      <c r="G2" s="90"/>
+      <c r="H2" s="90"/>
     </row>
     <row r="3" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="85"/>
-      <c r="B3" s="85"/>
-      <c r="C3" s="85"/>
-      <c r="D3" s="85"/>
-      <c r="E3" s="85"/>
-      <c r="F3" s="85"/>
-      <c r="G3" s="85"/>
-      <c r="H3" s="85"/>
+      <c r="A3" s="90"/>
+      <c r="B3" s="90"/>
+      <c r="C3" s="90"/>
+      <c r="D3" s="90"/>
+      <c r="E3" s="90"/>
+      <c r="F3" s="90"/>
+      <c r="G3" s="90"/>
+      <c r="H3" s="90"/>
     </row>
     <row r="4" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="85"/>
-      <c r="B4" s="85"/>
-      <c r="C4" s="85"/>
-      <c r="D4" s="85"/>
-      <c r="E4" s="85"/>
-      <c r="F4" s="85"/>
-      <c r="G4" s="85"/>
-      <c r="H4" s="85"/>
+      <c r="A4" s="90"/>
+      <c r="B4" s="90"/>
+      <c r="C4" s="90"/>
+      <c r="D4" s="90"/>
+      <c r="E4" s="90"/>
+      <c r="F4" s="90"/>
+      <c r="G4" s="90"/>
+      <c r="H4" s="90"/>
     </row>
     <row r="5" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="49"/>
-      <c r="B5" s="49"/>
-      <c r="C5" s="49"/>
+      <c r="A5" s="76"/>
+      <c r="B5" s="76"/>
+      <c r="C5" s="76"/>
     </row>
     <row r="6" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="84" t="s">
+      <c r="A6" s="89" t="s">
         <v>21</v>
       </c>
-      <c r="B6" s="84" t="s">
+      <c r="B6" s="89" t="s">
         <v>22</v>
       </c>
-      <c r="C6" s="84"/>
-      <c r="D6" s="84"/>
-      <c r="E6" s="84" t="s">
+      <c r="C6" s="89"/>
+      <c r="D6" s="89"/>
+      <c r="E6" s="89" t="s">
         <v>23</v>
       </c>
-      <c r="F6" s="86" t="s">
+      <c r="F6" s="91" t="s">
         <v>24</v>
       </c>
-      <c r="G6" s="87"/>
-      <c r="H6" s="90" t="s">
+      <c r="G6" s="92"/>
+      <c r="H6" s="95" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="7" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="84"/>
+      <c r="A7" s="89"/>
       <c r="B7" s="23" t="s">
         <v>26</v>
       </c>
@@ -5091,19 +5118,19 @@
       <c r="D7" s="23" t="s">
         <v>28</v>
       </c>
-      <c r="E7" s="84"/>
-      <c r="F7" s="88"/>
-      <c r="G7" s="89"/>
-      <c r="H7" s="91"/>
+      <c r="E7" s="89"/>
+      <c r="F7" s="93"/>
+      <c r="G7" s="94"/>
+      <c r="H7" s="96"/>
     </row>
     <row r="8" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="4">
         <v>1</v>
       </c>
-      <c r="B8" s="62" t="s">
+      <c r="B8" s="42" t="s">
         <v>29</v>
       </c>
-      <c r="C8" s="94" t="s">
+      <c r="C8" s="84" t="s">
         <v>30</v>
       </c>
       <c r="D8" s="4" t="s">
@@ -5112,10 +5139,10 @@
       <c r="E8" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="F8" s="82" t="s">
+      <c r="F8" s="86" t="s">
         <v>32</v>
       </c>
-      <c r="G8" s="83"/>
+      <c r="G8" s="87"/>
       <c r="H8" s="22" t="s">
         <v>33</v>
       </c>
@@ -5124,18 +5151,18 @@
       <c r="A9" s="4">
         <v>2</v>
       </c>
-      <c r="B9" s="92"/>
-      <c r="C9" s="95"/>
+      <c r="B9" s="83"/>
+      <c r="C9" s="85"/>
       <c r="D9" s="4" t="s">
         <v>34</v>
       </c>
       <c r="E9" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="F9" s="82" t="s">
+      <c r="F9" s="86" t="s">
         <v>32</v>
       </c>
-      <c r="G9" s="83"/>
+      <c r="G9" s="87"/>
       <c r="H9" s="22" t="s">
         <v>35</v>
       </c>
@@ -5144,8 +5171,8 @@
       <c r="A10" s="4">
         <v>3</v>
       </c>
-      <c r="B10" s="92"/>
-      <c r="C10" s="62" t="s">
+      <c r="B10" s="83"/>
+      <c r="C10" s="42" t="s">
         <v>36</v>
       </c>
       <c r="D10" s="4" t="s">
@@ -5154,10 +5181,10 @@
       <c r="E10" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="F10" s="82" t="s">
+      <c r="F10" s="86" t="s">
         <v>32</v>
       </c>
-      <c r="G10" s="83"/>
+      <c r="G10" s="87"/>
       <c r="H10" s="22" t="s">
         <v>35</v>
       </c>
@@ -5166,18 +5193,18 @@
       <c r="A11" s="4">
         <v>4</v>
       </c>
-      <c r="B11" s="93"/>
-      <c r="C11" s="93"/>
+      <c r="B11" s="82"/>
+      <c r="C11" s="82"/>
       <c r="D11" s="4" t="s">
         <v>38</v>
       </c>
       <c r="E11" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="F11" s="82" t="s">
+      <c r="F11" s="86" t="s">
         <v>32</v>
       </c>
-      <c r="G11" s="83"/>
+      <c r="G11" s="87"/>
       <c r="H11" s="22" t="s">
         <v>35</v>
       </c>
@@ -5186,7 +5213,7 @@
       <c r="A12" s="4">
         <v>5</v>
       </c>
-      <c r="B12" s="62" t="s">
+      <c r="B12" s="42" t="s">
         <v>39</v>
       </c>
       <c r="C12" s="4" t="s">
@@ -5196,10 +5223,10 @@
       <c r="E12" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="F12" s="82" t="s">
+      <c r="F12" s="86" t="s">
         <v>32</v>
       </c>
-      <c r="G12" s="83"/>
+      <c r="G12" s="87"/>
       <c r="H12" s="22" t="s">
         <v>33</v>
       </c>
@@ -5208,7 +5235,7 @@
       <c r="A13" s="4">
         <v>6</v>
       </c>
-      <c r="B13" s="93"/>
+      <c r="B13" s="82"/>
       <c r="C13" s="4" t="s">
         <v>41</v>
       </c>
@@ -5216,10 +5243,10 @@
       <c r="E13" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="F13" s="82" t="s">
+      <c r="F13" s="86" t="s">
         <v>32</v>
       </c>
-      <c r="G13" s="96"/>
+      <c r="G13" s="88"/>
       <c r="H13" s="22" t="s">
         <v>33</v>
       </c>
@@ -5228,7 +5255,7 @@
       <c r="A14" s="4">
         <v>7</v>
       </c>
-      <c r="B14" s="62" t="s">
+      <c r="B14" s="42" t="s">
         <v>42</v>
       </c>
       <c r="C14" s="4" t="s">
@@ -5238,10 +5265,10 @@
       <c r="E14" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="F14" s="82" t="s">
+      <c r="F14" s="86" t="s">
         <v>32</v>
       </c>
-      <c r="G14" s="83"/>
+      <c r="G14" s="87"/>
       <c r="H14" s="22" t="s">
         <v>33</v>
       </c>
@@ -5250,7 +5277,7 @@
       <c r="A15" s="4">
         <v>8</v>
       </c>
-      <c r="B15" s="93"/>
+      <c r="B15" s="82"/>
       <c r="C15" s="4" t="s">
         <v>44</v>
       </c>
@@ -5258,10 +5285,10 @@
       <c r="E15" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="F15" s="82" t="s">
+      <c r="F15" s="86" t="s">
         <v>32</v>
       </c>
-      <c r="G15" s="83"/>
+      <c r="G15" s="87"/>
       <c r="H15" s="22" t="s">
         <v>35</v>
       </c>
@@ -5270,7 +5297,7 @@
       <c r="A16" s="4">
         <v>9</v>
       </c>
-      <c r="B16" s="62" t="s">
+      <c r="B16" s="42" t="s">
         <v>45</v>
       </c>
       <c r="C16" s="4" t="s">
@@ -5280,10 +5307,10 @@
       <c r="E16" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="F16" s="82" t="s">
+      <c r="F16" s="86" t="s">
         <v>32</v>
       </c>
-      <c r="G16" s="83"/>
+      <c r="G16" s="87"/>
       <c r="H16" s="22" t="s">
         <v>35</v>
       </c>
@@ -5292,7 +5319,7 @@
       <c r="A17" s="4">
         <v>10</v>
       </c>
-      <c r="B17" s="93"/>
+      <c r="B17" s="82"/>
       <c r="C17" s="4" t="s">
         <v>48</v>
       </c>
@@ -5300,10 +5327,10 @@
       <c r="E17" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="F17" s="82" t="s">
+      <c r="F17" s="86" t="s">
         <v>32</v>
       </c>
-      <c r="G17" s="83"/>
+      <c r="G17" s="87"/>
       <c r="H17" s="22" t="s">
         <v>35</v>
       </c>
@@ -5312,7 +5339,7 @@
       <c r="A18" s="4">
         <v>11</v>
       </c>
-      <c r="B18" s="62" t="s">
+      <c r="B18" s="42" t="s">
         <v>49</v>
       </c>
       <c r="C18" s="4" t="s">
@@ -5322,10 +5349,10 @@
       <c r="E18" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="F18" s="82" t="s">
+      <c r="F18" s="86" t="s">
         <v>32</v>
       </c>
-      <c r="G18" s="83"/>
+      <c r="G18" s="87"/>
       <c r="H18" s="22" t="s">
         <v>33</v>
       </c>
@@ -5334,7 +5361,7 @@
       <c r="A19" s="4">
         <v>12</v>
       </c>
-      <c r="B19" s="93"/>
+      <c r="B19" s="82"/>
       <c r="C19" s="4" t="s">
         <v>49</v>
       </c>
@@ -5342,10 +5369,10 @@
       <c r="E19" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="F19" s="82" t="s">
+      <c r="F19" s="86" t="s">
         <v>32</v>
       </c>
-      <c r="G19" s="83"/>
+      <c r="G19" s="87"/>
       <c r="H19" s="22" t="s">
         <v>33</v>
       </c>
@@ -5354,7 +5381,7 @@
       <c r="A20" s="4">
         <v>13</v>
       </c>
-      <c r="B20" s="62" t="s">
+      <c r="B20" s="42" t="s">
         <v>51</v>
       </c>
       <c r="C20" s="4" t="s">
@@ -5364,10 +5391,10 @@
       <c r="E20" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="F20" s="82" t="s">
+      <c r="F20" s="86" t="s">
         <v>32</v>
       </c>
-      <c r="G20" s="83"/>
+      <c r="G20" s="87"/>
       <c r="H20" s="22" t="s">
         <v>35</v>
       </c>
@@ -5376,7 +5403,7 @@
       <c r="A21" s="4">
         <v>14</v>
       </c>
-      <c r="B21" s="93"/>
+      <c r="B21" s="82"/>
       <c r="C21" s="4" t="s">
         <v>53</v>
       </c>
@@ -5384,10 +5411,10 @@
       <c r="E21" s="4" t="s">
         <v>54</v>
       </c>
-      <c r="F21" s="82" t="s">
+      <c r="F21" s="86" t="s">
         <v>32</v>
       </c>
-      <c r="G21" s="83"/>
+      <c r="G21" s="87"/>
       <c r="H21" s="22" t="s">
         <v>35</v>
       </c>
@@ -5396,7 +5423,7 @@
       <c r="A22" s="4">
         <v>15</v>
       </c>
-      <c r="B22" s="62" t="s">
+      <c r="B22" s="42" t="s">
         <v>55</v>
       </c>
       <c r="C22" s="4" t="s">
@@ -5406,10 +5433,10 @@
       <c r="E22" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="F22" s="82" t="s">
+      <c r="F22" s="86" t="s">
         <v>32</v>
       </c>
-      <c r="G22" s="83"/>
+      <c r="G22" s="87"/>
       <c r="H22" s="22" t="s">
         <v>33</v>
       </c>
@@ -5418,7 +5445,7 @@
       <c r="A23" s="4">
         <v>16</v>
       </c>
-      <c r="B23" s="93"/>
+      <c r="B23" s="82"/>
       <c r="C23" s="4" t="s">
         <v>57</v>
       </c>
@@ -5426,10 +5453,10 @@
       <c r="E23" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="F23" s="82" t="s">
+      <c r="F23" s="86" t="s">
         <v>32</v>
       </c>
-      <c r="G23" s="83"/>
+      <c r="G23" s="87"/>
       <c r="H23" s="22" t="s">
         <v>33</v>
       </c>
@@ -5442,8 +5469,8 @@
       <c r="C24" s="4"/>
       <c r="D24" s="4"/>
       <c r="E24" s="4"/>
-      <c r="F24" s="82"/>
-      <c r="G24" s="83"/>
+      <c r="F24" s="86"/>
+      <c r="G24" s="87"/>
       <c r="H24" s="4"/>
     </row>
     <row r="25" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -5454,8 +5481,8 @@
       <c r="C25" s="4"/>
       <c r="D25" s="4"/>
       <c r="E25" s="4"/>
-      <c r="F25" s="82"/>
-      <c r="G25" s="83"/>
+      <c r="F25" s="86"/>
+      <c r="G25" s="87"/>
       <c r="H25" s="4"/>
     </row>
     <row r="26" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -5466,8 +5493,8 @@
       <c r="C26" s="4"/>
       <c r="D26" s="4"/>
       <c r="E26" s="4"/>
-      <c r="F26" s="82"/>
-      <c r="G26" s="83"/>
+      <c r="F26" s="86"/>
+      <c r="G26" s="87"/>
       <c r="H26" s="4"/>
     </row>
     <row r="27" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -5478,8 +5505,8 @@
       <c r="C27" s="4"/>
       <c r="D27" s="4"/>
       <c r="E27" s="4"/>
-      <c r="F27" s="82"/>
-      <c r="G27" s="83"/>
+      <c r="F27" s="86"/>
+      <c r="G27" s="87"/>
       <c r="H27" s="4"/>
     </row>
     <row r="28" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -5490,8 +5517,8 @@
       <c r="C28" s="4"/>
       <c r="D28" s="4"/>
       <c r="E28" s="4"/>
-      <c r="F28" s="82"/>
-      <c r="G28" s="83"/>
+      <c r="F28" s="86"/>
+      <c r="G28" s="87"/>
       <c r="H28" s="4"/>
     </row>
     <row r="29" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -5502,8 +5529,8 @@
       <c r="C29" s="4"/>
       <c r="D29" s="4"/>
       <c r="E29" s="4"/>
-      <c r="F29" s="82"/>
-      <c r="G29" s="83"/>
+      <c r="F29" s="86"/>
+      <c r="G29" s="87"/>
       <c r="H29" s="4"/>
     </row>
     <row r="30" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -5514,8 +5541,8 @@
       <c r="C30" s="4"/>
       <c r="D30" s="4"/>
       <c r="E30" s="4"/>
-      <c r="F30" s="82"/>
-      <c r="G30" s="83"/>
+      <c r="F30" s="86"/>
+      <c r="G30" s="87"/>
       <c r="H30" s="4"/>
     </row>
     <row r="31" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -5526,8 +5553,8 @@
       <c r="C31" s="4"/>
       <c r="D31" s="4"/>
       <c r="E31" s="4"/>
-      <c r="F31" s="82"/>
-      <c r="G31" s="83"/>
+      <c r="F31" s="86"/>
+      <c r="G31" s="87"/>
       <c r="H31" s="4"/>
     </row>
     <row r="32" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -5538,8 +5565,8 @@
       <c r="C32" s="4"/>
       <c r="D32" s="4"/>
       <c r="E32" s="4"/>
-      <c r="F32" s="82"/>
-      <c r="G32" s="83"/>
+      <c r="F32" s="86"/>
+      <c r="G32" s="87"/>
       <c r="H32" s="4"/>
     </row>
     <row r="33" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -5550,8 +5577,8 @@
       <c r="C33" s="4"/>
       <c r="D33" s="4"/>
       <c r="E33" s="4"/>
-      <c r="F33" s="82"/>
-      <c r="G33" s="83"/>
+      <c r="F33" s="86"/>
+      <c r="G33" s="87"/>
       <c r="H33" s="4"/>
     </row>
     <row r="34" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -5562,8 +5589,8 @@
       <c r="C34" s="4"/>
       <c r="D34" s="4"/>
       <c r="E34" s="4"/>
-      <c r="F34" s="82"/>
-      <c r="G34" s="83"/>
+      <c r="F34" s="86"/>
+      <c r="G34" s="87"/>
       <c r="H34" s="4"/>
     </row>
     <row r="35" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -5574,8 +5601,8 @@
       <c r="C35" s="4"/>
       <c r="D35" s="4"/>
       <c r="E35" s="4"/>
-      <c r="F35" s="82"/>
-      <c r="G35" s="83"/>
+      <c r="F35" s="86"/>
+      <c r="G35" s="87"/>
       <c r="H35" s="4"/>
     </row>
     <row r="36" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -5586,8 +5613,8 @@
       <c r="C36" s="4"/>
       <c r="D36" s="4"/>
       <c r="E36" s="4"/>
-      <c r="F36" s="82"/>
-      <c r="G36" s="83"/>
+      <c r="F36" s="86"/>
+      <c r="G36" s="87"/>
       <c r="H36" s="4"/>
     </row>
     <row r="37" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -5598,18 +5625,40 @@
       <c r="C37" s="4"/>
       <c r="D37" s="4"/>
       <c r="E37" s="4"/>
-      <c r="F37" s="82"/>
-      <c r="G37" s="83"/>
+      <c r="F37" s="86"/>
+      <c r="G37" s="87"/>
       <c r="H37" s="4"/>
     </row>
   </sheetData>
   <mergeCells count="47">
-    <mergeCell ref="B20:B21"/>
-    <mergeCell ref="B22:B23"/>
-    <mergeCell ref="B12:B13"/>
-    <mergeCell ref="B14:B15"/>
-    <mergeCell ref="B16:B17"/>
-    <mergeCell ref="B18:B19"/>
+    <mergeCell ref="F33:G33"/>
+    <mergeCell ref="F34:G34"/>
+    <mergeCell ref="F35:G35"/>
+    <mergeCell ref="F36:G36"/>
+    <mergeCell ref="F37:G37"/>
+    <mergeCell ref="F28:G28"/>
+    <mergeCell ref="F29:G29"/>
+    <mergeCell ref="F30:G30"/>
+    <mergeCell ref="F31:G31"/>
+    <mergeCell ref="F32:G32"/>
+    <mergeCell ref="F23:G23"/>
+    <mergeCell ref="F24:G24"/>
+    <mergeCell ref="F25:G25"/>
+    <mergeCell ref="F26:G26"/>
+    <mergeCell ref="F27:G27"/>
+    <mergeCell ref="F18:G18"/>
+    <mergeCell ref="F19:G19"/>
+    <mergeCell ref="F20:G20"/>
+    <mergeCell ref="F21:G21"/>
+    <mergeCell ref="F22:G22"/>
+    <mergeCell ref="A1:C1"/>
+    <mergeCell ref="A5:C5"/>
+    <mergeCell ref="A6:A7"/>
+    <mergeCell ref="B6:D6"/>
+    <mergeCell ref="E6:E7"/>
+    <mergeCell ref="A2:H4"/>
+    <mergeCell ref="F6:G7"/>
+    <mergeCell ref="H6:H7"/>
     <mergeCell ref="B8:B11"/>
     <mergeCell ref="C8:C9"/>
     <mergeCell ref="C10:C11"/>
@@ -5623,34 +5672,12 @@
     <mergeCell ref="F11:G11"/>
     <mergeCell ref="F12:G12"/>
     <mergeCell ref="F13:G13"/>
-    <mergeCell ref="A1:C1"/>
-    <mergeCell ref="A5:C5"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="B6:D6"/>
-    <mergeCell ref="E6:E7"/>
-    <mergeCell ref="A2:H4"/>
-    <mergeCell ref="F6:G7"/>
-    <mergeCell ref="H6:H7"/>
-    <mergeCell ref="F18:G18"/>
-    <mergeCell ref="F19:G19"/>
-    <mergeCell ref="F20:G20"/>
-    <mergeCell ref="F21:G21"/>
-    <mergeCell ref="F22:G22"/>
-    <mergeCell ref="F23:G23"/>
-    <mergeCell ref="F24:G24"/>
-    <mergeCell ref="F25:G25"/>
-    <mergeCell ref="F26:G26"/>
-    <mergeCell ref="F27:G27"/>
-    <mergeCell ref="F28:G28"/>
-    <mergeCell ref="F29:G29"/>
-    <mergeCell ref="F30:G30"/>
-    <mergeCell ref="F31:G31"/>
-    <mergeCell ref="F32:G32"/>
-    <mergeCell ref="F33:G33"/>
-    <mergeCell ref="F34:G34"/>
-    <mergeCell ref="F35:G35"/>
-    <mergeCell ref="F36:G36"/>
-    <mergeCell ref="F37:G37"/>
+    <mergeCell ref="B20:B21"/>
+    <mergeCell ref="B22:B23"/>
+    <mergeCell ref="B12:B13"/>
+    <mergeCell ref="B14:B15"/>
+    <mergeCell ref="B16:B17"/>
+    <mergeCell ref="B18:B19"/>
   </mergeCells>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.75" right="0.75" top="0.6" bottom="0.61" header="0.4" footer="0.39"/>
@@ -5677,90 +5704,90 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="97" t="s">
+      <c r="A1" s="101" t="s">
         <v>58</v>
       </c>
-      <c r="B1" s="98"/>
-      <c r="C1" s="99"/>
+      <c r="B1" s="102"/>
+      <c r="C1" s="103"/>
       <c r="D1" s="19"/>
     </row>
     <row r="2" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="85" t="s">
+      <c r="A2" s="90" t="s">
         <v>59</v>
       </c>
-      <c r="B2" s="85"/>
-      <c r="C2" s="85"/>
-      <c r="D2" s="85"/>
-      <c r="E2" s="85"/>
-      <c r="F2" s="85"/>
-      <c r="G2" s="85"/>
-      <c r="H2" s="85"/>
-      <c r="I2" s="85"/>
+      <c r="B2" s="90"/>
+      <c r="C2" s="90"/>
+      <c r="D2" s="90"/>
+      <c r="E2" s="90"/>
+      <c r="F2" s="90"/>
+      <c r="G2" s="90"/>
+      <c r="H2" s="90"/>
+      <c r="I2" s="90"/>
     </row>
     <row r="3" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="85"/>
-      <c r="B3" s="85"/>
-      <c r="C3" s="85"/>
-      <c r="D3" s="85"/>
-      <c r="E3" s="85"/>
-      <c r="F3" s="85"/>
-      <c r="G3" s="85"/>
-      <c r="H3" s="85"/>
-      <c r="I3" s="85"/>
+      <c r="A3" s="90"/>
+      <c r="B3" s="90"/>
+      <c r="C3" s="90"/>
+      <c r="D3" s="90"/>
+      <c r="E3" s="90"/>
+      <c r="F3" s="90"/>
+      <c r="G3" s="90"/>
+      <c r="H3" s="90"/>
+      <c r="I3" s="90"/>
     </row>
     <row r="4" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="49"/>
-      <c r="B4" s="49"/>
+      <c r="A4" s="76"/>
+      <c r="B4" s="76"/>
     </row>
     <row r="5" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="84" t="s">
+      <c r="A5" s="89" t="s">
         <v>21</v>
       </c>
-      <c r="B5" s="90" t="s">
+      <c r="B5" s="95" t="s">
         <v>60</v>
       </c>
-      <c r="C5" s="90" t="s">
+      <c r="C5" s="95" t="s">
         <v>61</v>
       </c>
-      <c r="D5" s="86" t="s">
+      <c r="D5" s="91" t="s">
         <v>24</v>
       </c>
-      <c r="E5" s="87"/>
-      <c r="F5" s="87"/>
-      <c r="G5" s="87"/>
-      <c r="H5" s="87"/>
-      <c r="I5" s="84" t="s">
+      <c r="E5" s="92"/>
+      <c r="F5" s="92"/>
+      <c r="G5" s="92"/>
+      <c r="H5" s="92"/>
+      <c r="I5" s="89" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="6" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="84"/>
-      <c r="B6" s="91"/>
-      <c r="C6" s="91"/>
-      <c r="D6" s="88"/>
-      <c r="E6" s="89"/>
-      <c r="F6" s="89"/>
-      <c r="G6" s="89"/>
-      <c r="H6" s="89"/>
-      <c r="I6" s="84"/>
+      <c r="A6" s="89"/>
+      <c r="B6" s="96"/>
+      <c r="C6" s="96"/>
+      <c r="D6" s="93"/>
+      <c r="E6" s="94"/>
+      <c r="F6" s="94"/>
+      <c r="G6" s="94"/>
+      <c r="H6" s="94"/>
+      <c r="I6" s="89"/>
     </row>
     <row r="7" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="4">
         <v>1</v>
       </c>
-      <c r="B7" s="103" t="s">
+      <c r="B7" s="97" t="s">
         <v>62</v>
       </c>
       <c r="C7" s="22" t="s">
         <v>63</v>
       </c>
-      <c r="D7" s="34" t="s">
+      <c r="D7" s="44" t="s">
         <v>32</v>
       </c>
-      <c r="E7" s="34"/>
-      <c r="F7" s="34"/>
-      <c r="G7" s="34"/>
-      <c r="H7" s="34"/>
+      <c r="E7" s="44"/>
+      <c r="F7" s="44"/>
+      <c r="G7" s="44"/>
+      <c r="H7" s="44"/>
       <c r="I7" s="22" t="s">
         <v>64</v>
       </c>
@@ -5769,15 +5796,15 @@
       <c r="A8" s="4">
         <v>2</v>
       </c>
-      <c r="B8" s="101"/>
+      <c r="B8" s="98"/>
       <c r="C8" s="22"/>
-      <c r="D8" s="34" t="s">
+      <c r="D8" s="44" t="s">
         <v>65</v>
       </c>
-      <c r="E8" s="34"/>
-      <c r="F8" s="34"/>
-      <c r="G8" s="34"/>
-      <c r="H8" s="34"/>
+      <c r="E8" s="44"/>
+      <c r="F8" s="44"/>
+      <c r="G8" s="44"/>
+      <c r="H8" s="44"/>
       <c r="I8" s="22" t="s">
         <v>66</v>
       </c>
@@ -5786,26 +5813,26 @@
       <c r="A9" s="4">
         <v>3</v>
       </c>
-      <c r="B9" s="101"/>
+      <c r="B9" s="98"/>
       <c r="C9" s="22"/>
-      <c r="D9" s="34"/>
-      <c r="E9" s="34"/>
-      <c r="F9" s="34"/>
-      <c r="G9" s="34"/>
-      <c r="H9" s="34"/>
+      <c r="D9" s="44"/>
+      <c r="E9" s="44"/>
+      <c r="F9" s="44"/>
+      <c r="G9" s="44"/>
+      <c r="H9" s="44"/>
       <c r="I9" s="4"/>
     </row>
     <row r="10" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="4">
         <v>4</v>
       </c>
-      <c r="B10" s="102"/>
+      <c r="B10" s="99"/>
       <c r="C10" s="22"/>
-      <c r="D10" s="34"/>
-      <c r="E10" s="34"/>
-      <c r="F10" s="34"/>
-      <c r="G10" s="34"/>
-      <c r="H10" s="34"/>
+      <c r="D10" s="44"/>
+      <c r="E10" s="44"/>
+      <c r="F10" s="44"/>
+      <c r="G10" s="44"/>
+      <c r="H10" s="44"/>
       <c r="I10" s="4"/>
     </row>
     <row r="11" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -5818,13 +5845,13 @@
       <c r="C11" s="22" t="s">
         <v>68</v>
       </c>
-      <c r="D11" s="34" t="s">
+      <c r="D11" s="44" t="s">
         <v>32</v>
       </c>
-      <c r="E11" s="34"/>
-      <c r="F11" s="34"/>
-      <c r="G11" s="34"/>
-      <c r="H11" s="34"/>
+      <c r="E11" s="44"/>
+      <c r="F11" s="44"/>
+      <c r="G11" s="44"/>
+      <c r="H11" s="44"/>
       <c r="I11" s="22" t="s">
         <v>66</v>
       </c>
@@ -5833,15 +5860,15 @@
       <c r="A12" s="4">
         <v>6</v>
       </c>
-      <c r="B12" s="101"/>
+      <c r="B12" s="98"/>
       <c r="C12" s="4"/>
-      <c r="D12" s="34" t="s">
+      <c r="D12" s="44" t="s">
         <v>69</v>
       </c>
-      <c r="E12" s="34"/>
-      <c r="F12" s="34"/>
-      <c r="G12" s="34"/>
-      <c r="H12" s="34"/>
+      <c r="E12" s="44"/>
+      <c r="F12" s="44"/>
+      <c r="G12" s="44"/>
+      <c r="H12" s="44"/>
       <c r="I12" s="22" t="s">
         <v>64</v>
       </c>
@@ -5850,15 +5877,15 @@
       <c r="A13" s="4">
         <v>7</v>
       </c>
-      <c r="B13" s="101"/>
+      <c r="B13" s="98"/>
       <c r="C13" s="4"/>
-      <c r="D13" s="34" t="s">
+      <c r="D13" s="44" t="s">
         <v>70</v>
       </c>
-      <c r="E13" s="34"/>
-      <c r="F13" s="34"/>
-      <c r="G13" s="34"/>
-      <c r="H13" s="34"/>
+      <c r="E13" s="44"/>
+      <c r="F13" s="44"/>
+      <c r="G13" s="44"/>
+      <c r="H13" s="44"/>
       <c r="I13" s="22" t="s">
         <v>64</v>
       </c>
@@ -5867,13 +5894,13 @@
       <c r="A14" s="4">
         <v>8</v>
       </c>
-      <c r="B14" s="102"/>
+      <c r="B14" s="99"/>
       <c r="C14" s="4"/>
-      <c r="D14" s="34"/>
-      <c r="E14" s="34"/>
-      <c r="F14" s="34"/>
-      <c r="G14" s="34"/>
-      <c r="H14" s="34"/>
+      <c r="D14" s="44"/>
+      <c r="E14" s="44"/>
+      <c r="F14" s="44"/>
+      <c r="G14" s="44"/>
+      <c r="H14" s="44"/>
       <c r="I14" s="4"/>
     </row>
     <row r="15" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -5884,50 +5911,50 @@
         <v>71</v>
       </c>
       <c r="C15" s="4"/>
-      <c r="D15" s="34"/>
-      <c r="E15" s="34"/>
-      <c r="F15" s="34"/>
-      <c r="G15" s="34"/>
-      <c r="H15" s="34"/>
+      <c r="D15" s="44"/>
+      <c r="E15" s="44"/>
+      <c r="F15" s="44"/>
+      <c r="G15" s="44"/>
+      <c r="H15" s="44"/>
       <c r="I15" s="4"/>
     </row>
     <row r="16" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="4">
         <v>10</v>
       </c>
-      <c r="B16" s="101"/>
+      <c r="B16" s="98"/>
       <c r="C16" s="4"/>
-      <c r="D16" s="34"/>
-      <c r="E16" s="34"/>
-      <c r="F16" s="34"/>
-      <c r="G16" s="34"/>
-      <c r="H16" s="34"/>
+      <c r="D16" s="44"/>
+      <c r="E16" s="44"/>
+      <c r="F16" s="44"/>
+      <c r="G16" s="44"/>
+      <c r="H16" s="44"/>
       <c r="I16" s="4"/>
     </row>
     <row r="17" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="4">
         <v>11</v>
       </c>
-      <c r="B17" s="101"/>
+      <c r="B17" s="98"/>
       <c r="C17" s="4"/>
-      <c r="D17" s="34"/>
-      <c r="E17" s="34"/>
-      <c r="F17" s="34"/>
-      <c r="G17" s="34"/>
-      <c r="H17" s="34"/>
+      <c r="D17" s="44"/>
+      <c r="E17" s="44"/>
+      <c r="F17" s="44"/>
+      <c r="G17" s="44"/>
+      <c r="H17" s="44"/>
       <c r="I17" s="4"/>
     </row>
     <row r="18" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="4">
         <v>12</v>
       </c>
-      <c r="B18" s="102"/>
+      <c r="B18" s="99"/>
       <c r="C18" s="4"/>
-      <c r="D18" s="34"/>
-      <c r="E18" s="34"/>
-      <c r="F18" s="34"/>
-      <c r="G18" s="34"/>
-      <c r="H18" s="34"/>
+      <c r="D18" s="44"/>
+      <c r="E18" s="44"/>
+      <c r="F18" s="44"/>
+      <c r="G18" s="44"/>
+      <c r="H18" s="44"/>
       <c r="I18" s="4"/>
     </row>
     <row r="19" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -5938,50 +5965,50 @@
         <v>72</v>
       </c>
       <c r="C19" s="4"/>
-      <c r="D19" s="34"/>
-      <c r="E19" s="34"/>
-      <c r="F19" s="34"/>
-      <c r="G19" s="34"/>
-      <c r="H19" s="34"/>
+      <c r="D19" s="44"/>
+      <c r="E19" s="44"/>
+      <c r="F19" s="44"/>
+      <c r="G19" s="44"/>
+      <c r="H19" s="44"/>
       <c r="I19" s="4"/>
     </row>
     <row r="20" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="4">
         <v>14</v>
       </c>
-      <c r="B20" s="101"/>
+      <c r="B20" s="98"/>
       <c r="C20" s="4"/>
-      <c r="D20" s="34"/>
-      <c r="E20" s="34"/>
-      <c r="F20" s="34"/>
-      <c r="G20" s="34"/>
-      <c r="H20" s="34"/>
+      <c r="D20" s="44"/>
+      <c r="E20" s="44"/>
+      <c r="F20" s="44"/>
+      <c r="G20" s="44"/>
+      <c r="H20" s="44"/>
       <c r="I20" s="4"/>
     </row>
     <row r="21" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="4">
         <v>15</v>
       </c>
-      <c r="B21" s="101"/>
+      <c r="B21" s="98"/>
       <c r="C21" s="4"/>
-      <c r="D21" s="34"/>
-      <c r="E21" s="34"/>
-      <c r="F21" s="34"/>
-      <c r="G21" s="34"/>
-      <c r="H21" s="34"/>
+      <c r="D21" s="44"/>
+      <c r="E21" s="44"/>
+      <c r="F21" s="44"/>
+      <c r="G21" s="44"/>
+      <c r="H21" s="44"/>
       <c r="I21" s="4"/>
     </row>
     <row r="22" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="4">
         <v>16</v>
       </c>
-      <c r="B22" s="102"/>
+      <c r="B22" s="99"/>
       <c r="C22" s="4"/>
-      <c r="D22" s="34"/>
-      <c r="E22" s="34"/>
-      <c r="F22" s="34"/>
-      <c r="G22" s="34"/>
-      <c r="H22" s="34"/>
+      <c r="D22" s="44"/>
+      <c r="E22" s="44"/>
+      <c r="F22" s="44"/>
+      <c r="G22" s="44"/>
+      <c r="H22" s="44"/>
       <c r="I22" s="4"/>
     </row>
     <row r="23" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -5992,50 +6019,50 @@
         <v>73</v>
       </c>
       <c r="C23" s="4"/>
-      <c r="D23" s="34"/>
-      <c r="E23" s="34"/>
-      <c r="F23" s="34"/>
-      <c r="G23" s="34"/>
-      <c r="H23" s="34"/>
+      <c r="D23" s="44"/>
+      <c r="E23" s="44"/>
+      <c r="F23" s="44"/>
+      <c r="G23" s="44"/>
+      <c r="H23" s="44"/>
       <c r="I23" s="4"/>
     </row>
     <row r="24" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" s="4">
         <v>18</v>
       </c>
-      <c r="B24" s="101"/>
+      <c r="B24" s="98"/>
       <c r="C24" s="4"/>
-      <c r="D24" s="34"/>
-      <c r="E24" s="34"/>
-      <c r="F24" s="34"/>
-      <c r="G24" s="34"/>
-      <c r="H24" s="34"/>
+      <c r="D24" s="44"/>
+      <c r="E24" s="44"/>
+      <c r="F24" s="44"/>
+      <c r="G24" s="44"/>
+      <c r="H24" s="44"/>
       <c r="I24" s="4"/>
     </row>
     <row r="25" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A25" s="4">
         <v>19</v>
       </c>
-      <c r="B25" s="101"/>
+      <c r="B25" s="98"/>
       <c r="C25" s="4"/>
-      <c r="D25" s="34"/>
-      <c r="E25" s="34"/>
-      <c r="F25" s="34"/>
-      <c r="G25" s="34"/>
-      <c r="H25" s="34"/>
+      <c r="D25" s="44"/>
+      <c r="E25" s="44"/>
+      <c r="F25" s="44"/>
+      <c r="G25" s="44"/>
+      <c r="H25" s="44"/>
       <c r="I25" s="4"/>
     </row>
     <row r="26" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26" s="4">
         <v>20</v>
       </c>
-      <c r="B26" s="102"/>
+      <c r="B26" s="99"/>
       <c r="C26" s="4"/>
-      <c r="D26" s="34"/>
-      <c r="E26" s="34"/>
-      <c r="F26" s="34"/>
-      <c r="G26" s="34"/>
-      <c r="H26" s="34"/>
+      <c r="D26" s="44"/>
+      <c r="E26" s="44"/>
+      <c r="F26" s="44"/>
+      <c r="G26" s="44"/>
+      <c r="H26" s="44"/>
       <c r="I26" s="4"/>
     </row>
     <row r="27" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -6046,50 +6073,50 @@
         <v>74</v>
       </c>
       <c r="C27" s="4"/>
-      <c r="D27" s="34"/>
-      <c r="E27" s="34"/>
-      <c r="F27" s="34"/>
-      <c r="G27" s="34"/>
-      <c r="H27" s="34"/>
+      <c r="D27" s="44"/>
+      <c r="E27" s="44"/>
+      <c r="F27" s="44"/>
+      <c r="G27" s="44"/>
+      <c r="H27" s="44"/>
       <c r="I27" s="4"/>
     </row>
     <row r="28" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A28" s="4">
         <v>22</v>
       </c>
-      <c r="B28" s="101"/>
+      <c r="B28" s="98"/>
       <c r="C28" s="4"/>
-      <c r="D28" s="34"/>
-      <c r="E28" s="34"/>
-      <c r="F28" s="34"/>
-      <c r="G28" s="34"/>
-      <c r="H28" s="34"/>
+      <c r="D28" s="44"/>
+      <c r="E28" s="44"/>
+      <c r="F28" s="44"/>
+      <c r="G28" s="44"/>
+      <c r="H28" s="44"/>
       <c r="I28" s="4"/>
     </row>
     <row r="29" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A29" s="4">
         <v>23</v>
       </c>
-      <c r="B29" s="101"/>
+      <c r="B29" s="98"/>
       <c r="C29" s="4"/>
-      <c r="D29" s="34"/>
-      <c r="E29" s="34"/>
-      <c r="F29" s="34"/>
-      <c r="G29" s="34"/>
-      <c r="H29" s="34"/>
+      <c r="D29" s="44"/>
+      <c r="E29" s="44"/>
+      <c r="F29" s="44"/>
+      <c r="G29" s="44"/>
+      <c r="H29" s="44"/>
       <c r="I29" s="4"/>
     </row>
     <row r="30" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A30" s="4">
         <v>24</v>
       </c>
-      <c r="B30" s="102"/>
+      <c r="B30" s="99"/>
       <c r="C30" s="4"/>
-      <c r="D30" s="34"/>
-      <c r="E30" s="34"/>
-      <c r="F30" s="34"/>
-      <c r="G30" s="34"/>
-      <c r="H30" s="34"/>
+      <c r="D30" s="44"/>
+      <c r="E30" s="44"/>
+      <c r="F30" s="44"/>
+      <c r="G30" s="44"/>
+      <c r="H30" s="44"/>
       <c r="I30" s="4"/>
     </row>
     <row r="31" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -6098,11 +6125,11 @@
       </c>
       <c r="B31" s="4"/>
       <c r="C31" s="4"/>
-      <c r="D31" s="34"/>
-      <c r="E31" s="34"/>
-      <c r="F31" s="34"/>
-      <c r="G31" s="34"/>
-      <c r="H31" s="34"/>
+      <c r="D31" s="44"/>
+      <c r="E31" s="44"/>
+      <c r="F31" s="44"/>
+      <c r="G31" s="44"/>
+      <c r="H31" s="44"/>
       <c r="I31" s="4"/>
     </row>
     <row r="32" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -6111,11 +6138,11 @@
       </c>
       <c r="B32" s="4"/>
       <c r="C32" s="4"/>
-      <c r="D32" s="34"/>
-      <c r="E32" s="34"/>
-      <c r="F32" s="34"/>
-      <c r="G32" s="34"/>
-      <c r="H32" s="34"/>
+      <c r="D32" s="44"/>
+      <c r="E32" s="44"/>
+      <c r="F32" s="44"/>
+      <c r="G32" s="44"/>
+      <c r="H32" s="44"/>
       <c r="I32" s="4"/>
     </row>
     <row r="33" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -6124,11 +6151,11 @@
       </c>
       <c r="B33" s="4"/>
       <c r="C33" s="4"/>
-      <c r="D33" s="34"/>
-      <c r="E33" s="34"/>
-      <c r="F33" s="34"/>
-      <c r="G33" s="34"/>
-      <c r="H33" s="34"/>
+      <c r="D33" s="44"/>
+      <c r="E33" s="44"/>
+      <c r="F33" s="44"/>
+      <c r="G33" s="44"/>
+      <c r="H33" s="44"/>
       <c r="I33" s="4"/>
     </row>
     <row r="34" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -6137,11 +6164,11 @@
       </c>
       <c r="B34" s="4"/>
       <c r="C34" s="4"/>
-      <c r="D34" s="34"/>
-      <c r="E34" s="34"/>
-      <c r="F34" s="34"/>
-      <c r="G34" s="34"/>
-      <c r="H34" s="34"/>
+      <c r="D34" s="44"/>
+      <c r="E34" s="44"/>
+      <c r="F34" s="44"/>
+      <c r="G34" s="44"/>
+      <c r="H34" s="44"/>
       <c r="I34" s="4"/>
     </row>
     <row r="35" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -6150,11 +6177,11 @@
       </c>
       <c r="B35" s="4"/>
       <c r="C35" s="4"/>
-      <c r="D35" s="34"/>
-      <c r="E35" s="34"/>
-      <c r="F35" s="34"/>
-      <c r="G35" s="34"/>
-      <c r="H35" s="34"/>
+      <c r="D35" s="44"/>
+      <c r="E35" s="44"/>
+      <c r="F35" s="44"/>
+      <c r="G35" s="44"/>
+      <c r="H35" s="44"/>
       <c r="I35" s="4"/>
     </row>
     <row r="36" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -6163,43 +6190,15 @@
       </c>
       <c r="B36" s="4"/>
       <c r="C36" s="4"/>
-      <c r="D36" s="34"/>
-      <c r="E36" s="34"/>
-      <c r="F36" s="34"/>
-      <c r="G36" s="34"/>
-      <c r="H36" s="34"/>
+      <c r="D36" s="44"/>
+      <c r="E36" s="44"/>
+      <c r="F36" s="44"/>
+      <c r="G36" s="44"/>
+      <c r="H36" s="44"/>
       <c r="I36" s="4"/>
     </row>
   </sheetData>
   <mergeCells count="44">
-    <mergeCell ref="B7:B10"/>
-    <mergeCell ref="B15:B18"/>
-    <mergeCell ref="B19:B22"/>
-    <mergeCell ref="B23:B26"/>
-    <mergeCell ref="B27:B30"/>
-    <mergeCell ref="A2:I3"/>
-    <mergeCell ref="A4:B4"/>
-    <mergeCell ref="A5:A6"/>
-    <mergeCell ref="C5:C6"/>
-    <mergeCell ref="B5:B6"/>
-    <mergeCell ref="D5:H6"/>
-    <mergeCell ref="I5:I6"/>
-    <mergeCell ref="D15:H15"/>
-    <mergeCell ref="D16:H16"/>
-    <mergeCell ref="D17:H17"/>
-    <mergeCell ref="D25:H25"/>
-    <mergeCell ref="D26:H26"/>
-    <mergeCell ref="D20:H20"/>
-    <mergeCell ref="D21:H21"/>
-    <mergeCell ref="D22:H22"/>
-    <mergeCell ref="D23:H23"/>
-    <mergeCell ref="D24:H24"/>
-    <mergeCell ref="D36:H36"/>
-    <mergeCell ref="D27:H27"/>
-    <mergeCell ref="D28:H28"/>
-    <mergeCell ref="D29:H29"/>
-    <mergeCell ref="D30:H30"/>
-    <mergeCell ref="D31:H31"/>
     <mergeCell ref="A1:C1"/>
     <mergeCell ref="D32:H32"/>
     <mergeCell ref="D33:H33"/>
@@ -6216,6 +6215,34 @@
     <mergeCell ref="D12:H12"/>
     <mergeCell ref="D13:H13"/>
     <mergeCell ref="D14:H14"/>
+    <mergeCell ref="D36:H36"/>
+    <mergeCell ref="D27:H27"/>
+    <mergeCell ref="D28:H28"/>
+    <mergeCell ref="D29:H29"/>
+    <mergeCell ref="D30:H30"/>
+    <mergeCell ref="D31:H31"/>
+    <mergeCell ref="D15:H15"/>
+    <mergeCell ref="D16:H16"/>
+    <mergeCell ref="D17:H17"/>
+    <mergeCell ref="D25:H25"/>
+    <mergeCell ref="D26:H26"/>
+    <mergeCell ref="D20:H20"/>
+    <mergeCell ref="D21:H21"/>
+    <mergeCell ref="D22:H22"/>
+    <mergeCell ref="D23:H23"/>
+    <mergeCell ref="D24:H24"/>
+    <mergeCell ref="A2:I3"/>
+    <mergeCell ref="A4:B4"/>
+    <mergeCell ref="A5:A6"/>
+    <mergeCell ref="C5:C6"/>
+    <mergeCell ref="B5:B6"/>
+    <mergeCell ref="D5:H6"/>
+    <mergeCell ref="I5:I6"/>
+    <mergeCell ref="B7:B10"/>
+    <mergeCell ref="B15:B18"/>
+    <mergeCell ref="B19:B22"/>
+    <mergeCell ref="B23:B26"/>
+    <mergeCell ref="B27:B30"/>
   </mergeCells>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.75" right="0.75" top="0.6" bottom="0.61" header="0.4" footer="0.39"/>
@@ -6239,23 +6266,23 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:52" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B1" s="104" t="s">
+      <c r="B1" s="191" t="s">
         <v>75</v>
       </c>
-      <c r="C1" s="105"/>
-      <c r="D1" s="105"/>
-      <c r="E1" s="105"/>
-      <c r="F1" s="105"/>
-      <c r="G1" s="105"/>
-      <c r="H1" s="105"/>
-      <c r="I1" s="105"/>
-      <c r="J1" s="105"/>
-      <c r="K1" s="105"/>
-      <c r="L1" s="105"/>
-      <c r="M1" s="105"/>
-      <c r="N1" s="105"/>
-      <c r="O1" s="105"/>
-      <c r="P1" s="105"/>
+      <c r="C1" s="192"/>
+      <c r="D1" s="192"/>
+      <c r="E1" s="192"/>
+      <c r="F1" s="192"/>
+      <c r="G1" s="192"/>
+      <c r="H1" s="192"/>
+      <c r="I1" s="192"/>
+      <c r="J1" s="192"/>
+      <c r="K1" s="192"/>
+      <c r="L1" s="192"/>
+      <c r="M1" s="192"/>
+      <c r="N1" s="192"/>
+      <c r="O1" s="192"/>
+      <c r="P1" s="192"/>
       <c r="Q1" s="21"/>
       <c r="R1" s="20"/>
       <c r="S1" s="20"/>
@@ -6272,139 +6299,139 @@
       <c r="AD1" s="20"/>
     </row>
     <row r="2" spans="2:52" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B2" s="184" t="s">
+      <c r="B2" s="140" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="184"/>
-      <c r="D2" s="184"/>
-      <c r="E2" s="184"/>
-      <c r="F2" s="184"/>
-      <c r="G2" s="184"/>
-      <c r="H2" s="184"/>
-      <c r="I2" s="184"/>
-      <c r="J2" s="113"/>
-      <c r="K2" s="113"/>
-      <c r="L2" s="113"/>
-      <c r="M2" s="113"/>
-      <c r="N2" s="113"/>
-      <c r="O2" s="113"/>
-      <c r="P2" s="113"/>
-      <c r="Q2" s="113"/>
-      <c r="R2" s="113"/>
-      <c r="S2" s="113"/>
-      <c r="T2" s="113"/>
-      <c r="U2" s="113"/>
-      <c r="V2" s="113"/>
-      <c r="W2" s="113"/>
-      <c r="X2" s="113"/>
-      <c r="Y2" s="113"/>
-      <c r="Z2" s="113"/>
-      <c r="AA2" s="113"/>
-      <c r="AB2" s="113"/>
-      <c r="AC2" s="113"/>
-      <c r="AD2" s="113"/>
+      <c r="C2" s="140"/>
+      <c r="D2" s="140"/>
+      <c r="E2" s="140"/>
+      <c r="F2" s="140"/>
+      <c r="G2" s="140"/>
+      <c r="H2" s="140"/>
+      <c r="I2" s="140"/>
+      <c r="J2" s="144"/>
+      <c r="K2" s="144"/>
+      <c r="L2" s="144"/>
+      <c r="M2" s="144"/>
+      <c r="N2" s="144"/>
+      <c r="O2" s="144"/>
+      <c r="P2" s="144"/>
+      <c r="Q2" s="144"/>
+      <c r="R2" s="144"/>
+      <c r="S2" s="144"/>
+      <c r="T2" s="144"/>
+      <c r="U2" s="144"/>
+      <c r="V2" s="144"/>
+      <c r="W2" s="144"/>
+      <c r="X2" s="144"/>
+      <c r="Y2" s="144"/>
+      <c r="Z2" s="144"/>
+      <c r="AA2" s="144"/>
+      <c r="AB2" s="144"/>
+      <c r="AC2" s="144"/>
+      <c r="AD2" s="144"/>
     </row>
     <row r="3" spans="2:52" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="4" spans="2:52" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B4" s="192" t="s">
+      <c r="B4" s="151" t="s">
         <v>76</v>
       </c>
-      <c r="C4" s="182"/>
-      <c r="D4" s="182"/>
-      <c r="E4" s="182"/>
-      <c r="F4" s="182"/>
-      <c r="G4" s="182"/>
-      <c r="H4" s="182"/>
-      <c r="I4" s="182"/>
-      <c r="J4" s="182" t="s">
+      <c r="C4" s="138"/>
+      <c r="D4" s="138"/>
+      <c r="E4" s="138"/>
+      <c r="F4" s="138"/>
+      <c r="G4" s="138"/>
+      <c r="H4" s="138"/>
+      <c r="I4" s="138"/>
+      <c r="J4" s="138" t="s">
         <v>77</v>
       </c>
-      <c r="K4" s="182"/>
-      <c r="L4" s="182"/>
-      <c r="M4" s="182"/>
-      <c r="N4" s="182"/>
-      <c r="O4" s="182"/>
-      <c r="P4" s="182"/>
-      <c r="Q4" s="186" t="s">
+      <c r="K4" s="138"/>
+      <c r="L4" s="138"/>
+      <c r="M4" s="138"/>
+      <c r="N4" s="138"/>
+      <c r="O4" s="138"/>
+      <c r="P4" s="138"/>
+      <c r="Q4" s="145" t="s">
         <v>78</v>
       </c>
-      <c r="R4" s="190"/>
-      <c r="S4" s="187"/>
-      <c r="T4" s="186" t="s">
+      <c r="R4" s="149"/>
+      <c r="S4" s="146"/>
+      <c r="T4" s="145" t="s">
         <v>79</v>
       </c>
-      <c r="U4" s="190"/>
-      <c r="V4" s="190"/>
-      <c r="W4" s="187"/>
-      <c r="X4" s="186" t="s">
+      <c r="U4" s="149"/>
+      <c r="V4" s="149"/>
+      <c r="W4" s="146"/>
+      <c r="X4" s="145" t="s">
         <v>80</v>
       </c>
-      <c r="Y4" s="187"/>
-      <c r="Z4" s="182" t="s">
+      <c r="Y4" s="146"/>
+      <c r="Z4" s="138" t="s">
         <v>81</v>
       </c>
-      <c r="AA4" s="182"/>
-      <c r="AB4" s="182"/>
-      <c r="AC4" s="182" t="s">
+      <c r="AA4" s="138"/>
+      <c r="AB4" s="138"/>
+      <c r="AC4" s="138" t="s">
         <v>81</v>
       </c>
-      <c r="AD4" s="182"/>
-      <c r="AE4" s="182"/>
-      <c r="AF4" s="182" t="s">
+      <c r="AD4" s="138"/>
+      <c r="AE4" s="138"/>
+      <c r="AF4" s="138" t="s">
         <v>81</v>
       </c>
-      <c r="AG4" s="182"/>
-      <c r="AH4" s="182"/>
-      <c r="AI4" s="182" t="s">
+      <c r="AG4" s="138"/>
+      <c r="AH4" s="138"/>
+      <c r="AI4" s="138" t="s">
         <v>81</v>
       </c>
-      <c r="AJ4" s="182"/>
-      <c r="AK4" s="182"/>
-      <c r="AL4" s="182" t="s">
+      <c r="AJ4" s="138"/>
+      <c r="AK4" s="138"/>
+      <c r="AL4" s="138" t="s">
         <v>81</v>
       </c>
-      <c r="AM4" s="182"/>
-      <c r="AN4" s="182"/>
-      <c r="AO4" s="182" t="s">
+      <c r="AM4" s="138"/>
+      <c r="AN4" s="138"/>
+      <c r="AO4" s="138" t="s">
         <v>82</v>
       </c>
-      <c r="AP4" s="182"/>
-      <c r="AQ4" s="182"/>
-      <c r="AR4" s="182"/>
-      <c r="AS4" s="182"/>
-      <c r="AT4" s="182"/>
-      <c r="AU4" s="182"/>
-      <c r="AV4" s="182"/>
-      <c r="AW4" s="182"/>
-      <c r="AX4" s="182"/>
-      <c r="AY4" s="182"/>
-      <c r="AZ4" s="183"/>
+      <c r="AP4" s="138"/>
+      <c r="AQ4" s="138"/>
+      <c r="AR4" s="138"/>
+      <c r="AS4" s="138"/>
+      <c r="AT4" s="138"/>
+      <c r="AU4" s="138"/>
+      <c r="AV4" s="138"/>
+      <c r="AW4" s="138"/>
+      <c r="AX4" s="138"/>
+      <c r="AY4" s="138"/>
+      <c r="AZ4" s="139"/>
     </row>
     <row r="5" spans="2:52" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B5" s="193"/>
-      <c r="C5" s="184"/>
-      <c r="D5" s="184"/>
-      <c r="E5" s="184"/>
-      <c r="F5" s="184"/>
-      <c r="G5" s="184"/>
-      <c r="H5" s="184"/>
-      <c r="I5" s="184"/>
-      <c r="J5" s="184"/>
-      <c r="K5" s="184"/>
-      <c r="L5" s="184"/>
-      <c r="M5" s="184"/>
-      <c r="N5" s="184"/>
-      <c r="O5" s="184"/>
-      <c r="P5" s="184"/>
-      <c r="Q5" s="188"/>
-      <c r="R5" s="191"/>
-      <c r="S5" s="189"/>
-      <c r="T5" s="188"/>
-      <c r="U5" s="191"/>
-      <c r="V5" s="191"/>
-      <c r="W5" s="189"/>
-      <c r="X5" s="188"/>
-      <c r="Y5" s="189"/>
+      <c r="B5" s="152"/>
+      <c r="C5" s="140"/>
+      <c r="D5" s="140"/>
+      <c r="E5" s="140"/>
+      <c r="F5" s="140"/>
+      <c r="G5" s="140"/>
+      <c r="H5" s="140"/>
+      <c r="I5" s="140"/>
+      <c r="J5" s="140"/>
+      <c r="K5" s="140"/>
+      <c r="L5" s="140"/>
+      <c r="M5" s="140"/>
+      <c r="N5" s="140"/>
+      <c r="O5" s="140"/>
+      <c r="P5" s="140"/>
+      <c r="Q5" s="147"/>
+      <c r="R5" s="150"/>
+      <c r="S5" s="148"/>
+      <c r="T5" s="147"/>
+      <c r="U5" s="150"/>
+      <c r="V5" s="150"/>
+      <c r="W5" s="148"/>
+      <c r="X5" s="147"/>
+      <c r="Y5" s="148"/>
       <c r="Z5" s="6" t="s">
         <v>83</v>
       </c>
@@ -6450,54 +6477,54 @@
       <c r="AN5" s="8" t="s">
         <v>85</v>
       </c>
-      <c r="AO5" s="184"/>
-      <c r="AP5" s="184"/>
-      <c r="AQ5" s="184"/>
-      <c r="AR5" s="184"/>
-      <c r="AS5" s="184"/>
-      <c r="AT5" s="184"/>
-      <c r="AU5" s="184"/>
-      <c r="AV5" s="184"/>
-      <c r="AW5" s="184"/>
-      <c r="AX5" s="184"/>
-      <c r="AY5" s="184"/>
-      <c r="AZ5" s="185"/>
+      <c r="AO5" s="140"/>
+      <c r="AP5" s="140"/>
+      <c r="AQ5" s="140"/>
+      <c r="AR5" s="140"/>
+      <c r="AS5" s="140"/>
+      <c r="AT5" s="140"/>
+      <c r="AU5" s="140"/>
+      <c r="AV5" s="140"/>
+      <c r="AW5" s="140"/>
+      <c r="AX5" s="140"/>
+      <c r="AY5" s="140"/>
+      <c r="AZ5" s="141"/>
     </row>
     <row r="6" spans="2:52" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B6" s="110">
+      <c r="B6" s="167">
         <v>1</v>
       </c>
-      <c r="C6" s="106" t="s">
+      <c r="C6" s="153" t="s">
         <v>86</v>
       </c>
-      <c r="D6" s="106"/>
-      <c r="E6" s="106"/>
-      <c r="F6" s="106"/>
-      <c r="G6" s="106"/>
-      <c r="H6" s="106"/>
-      <c r="I6" s="106"/>
-      <c r="J6" s="106"/>
-      <c r="K6" s="106"/>
-      <c r="L6" s="106"/>
-      <c r="M6" s="106"/>
-      <c r="N6" s="106"/>
-      <c r="O6" s="106"/>
-      <c r="P6" s="106"/>
-      <c r="Q6" s="113"/>
-      <c r="R6" s="113"/>
-      <c r="S6" s="113"/>
-      <c r="T6" s="111" t="s">
+      <c r="D6" s="153"/>
+      <c r="E6" s="153"/>
+      <c r="F6" s="153"/>
+      <c r="G6" s="153"/>
+      <c r="H6" s="153"/>
+      <c r="I6" s="153"/>
+      <c r="J6" s="153"/>
+      <c r="K6" s="153"/>
+      <c r="L6" s="153"/>
+      <c r="M6" s="153"/>
+      <c r="N6" s="153"/>
+      <c r="O6" s="153"/>
+      <c r="P6" s="153"/>
+      <c r="Q6" s="144"/>
+      <c r="R6" s="144"/>
+      <c r="S6" s="144"/>
+      <c r="T6" s="158" t="s">
         <v>87</v>
       </c>
-      <c r="U6" s="111"/>
-      <c r="V6" s="108">
+      <c r="U6" s="158"/>
+      <c r="V6" s="156">
         <v>0</v>
       </c>
-      <c r="W6" s="108"/>
-      <c r="X6" s="129">
+      <c r="W6" s="156"/>
+      <c r="X6" s="142">
         <v>0</v>
       </c>
-      <c r="Y6" s="129"/>
+      <c r="Y6" s="142"/>
       <c r="Z6" s="9"/>
       <c r="AA6" s="10"/>
       <c r="AB6" s="11"/>
@@ -6513,50 +6540,50 @@
       <c r="AL6" s="9"/>
       <c r="AM6" s="10"/>
       <c r="AN6" s="11"/>
-      <c r="AO6" s="106"/>
-      <c r="AP6" s="106"/>
-      <c r="AQ6" s="106"/>
-      <c r="AR6" s="106"/>
-      <c r="AS6" s="106"/>
-      <c r="AT6" s="106"/>
-      <c r="AU6" s="106"/>
-      <c r="AV6" s="106"/>
-      <c r="AW6" s="106"/>
-      <c r="AX6" s="106"/>
-      <c r="AY6" s="106"/>
-      <c r="AZ6" s="128"/>
+      <c r="AO6" s="153"/>
+      <c r="AP6" s="153"/>
+      <c r="AQ6" s="153"/>
+      <c r="AR6" s="153"/>
+      <c r="AS6" s="153"/>
+      <c r="AT6" s="153"/>
+      <c r="AU6" s="153"/>
+      <c r="AV6" s="153"/>
+      <c r="AW6" s="153"/>
+      <c r="AX6" s="153"/>
+      <c r="AY6" s="153"/>
+      <c r="AZ6" s="154"/>
     </row>
     <row r="7" spans="2:52" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B7" s="110"/>
-      <c r="C7" s="106"/>
-      <c r="D7" s="106"/>
-      <c r="E7" s="106"/>
-      <c r="F7" s="106"/>
-      <c r="G7" s="106"/>
-      <c r="H7" s="106"/>
-      <c r="I7" s="106"/>
-      <c r="J7" s="106"/>
-      <c r="K7" s="106"/>
-      <c r="L7" s="106"/>
-      <c r="M7" s="106"/>
-      <c r="N7" s="106"/>
-      <c r="O7" s="106"/>
-      <c r="P7" s="106"/>
-      <c r="Q7" s="113"/>
-      <c r="R7" s="113"/>
-      <c r="S7" s="113"/>
-      <c r="T7" s="112" t="s">
+      <c r="B7" s="167"/>
+      <c r="C7" s="153"/>
+      <c r="D7" s="153"/>
+      <c r="E7" s="153"/>
+      <c r="F7" s="153"/>
+      <c r="G7" s="153"/>
+      <c r="H7" s="153"/>
+      <c r="I7" s="153"/>
+      <c r="J7" s="153"/>
+      <c r="K7" s="153"/>
+      <c r="L7" s="153"/>
+      <c r="M7" s="153"/>
+      <c r="N7" s="153"/>
+      <c r="O7" s="153"/>
+      <c r="P7" s="153"/>
+      <c r="Q7" s="144"/>
+      <c r="R7" s="144"/>
+      <c r="S7" s="144"/>
+      <c r="T7" s="155" t="s">
         <v>25</v>
       </c>
-      <c r="U7" s="112"/>
-      <c r="V7" s="109">
+      <c r="U7" s="155"/>
+      <c r="V7" s="157">
         <v>0</v>
       </c>
-      <c r="W7" s="109"/>
-      <c r="X7" s="130">
+      <c r="W7" s="157"/>
+      <c r="X7" s="143">
         <v>0</v>
       </c>
-      <c r="Y7" s="130"/>
+      <c r="Y7" s="143"/>
       <c r="Z7" s="12"/>
       <c r="AA7" s="13"/>
       <c r="AB7" s="14"/>
@@ -6572,54 +6599,54 @@
       <c r="AL7" s="12"/>
       <c r="AM7" s="13"/>
       <c r="AN7" s="14"/>
-      <c r="AO7" s="106"/>
-      <c r="AP7" s="106"/>
-      <c r="AQ7" s="106"/>
-      <c r="AR7" s="106"/>
-      <c r="AS7" s="106"/>
-      <c r="AT7" s="106"/>
-      <c r="AU7" s="106"/>
-      <c r="AV7" s="106"/>
-      <c r="AW7" s="106"/>
-      <c r="AX7" s="106"/>
-      <c r="AY7" s="106"/>
-      <c r="AZ7" s="128"/>
+      <c r="AO7" s="153"/>
+      <c r="AP7" s="153"/>
+      <c r="AQ7" s="153"/>
+      <c r="AR7" s="153"/>
+      <c r="AS7" s="153"/>
+      <c r="AT7" s="153"/>
+      <c r="AU7" s="153"/>
+      <c r="AV7" s="153"/>
+      <c r="AW7" s="153"/>
+      <c r="AX7" s="153"/>
+      <c r="AY7" s="153"/>
+      <c r="AZ7" s="154"/>
     </row>
     <row r="8" spans="2:52" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B8" s="110">
+      <c r="B8" s="167">
         <v>2</v>
       </c>
-      <c r="C8" s="106" t="s">
+      <c r="C8" s="153" t="s">
         <v>88</v>
       </c>
-      <c r="D8" s="106"/>
-      <c r="E8" s="106"/>
-      <c r="F8" s="106"/>
-      <c r="G8" s="106"/>
-      <c r="H8" s="106"/>
-      <c r="I8" s="106"/>
-      <c r="J8" s="114"/>
-      <c r="K8" s="115"/>
-      <c r="L8" s="115"/>
-      <c r="M8" s="115"/>
-      <c r="N8" s="115"/>
-      <c r="O8" s="115"/>
-      <c r="P8" s="116"/>
-      <c r="Q8" s="113"/>
-      <c r="R8" s="113"/>
-      <c r="S8" s="113"/>
-      <c r="T8" s="111" t="s">
+      <c r="D8" s="153"/>
+      <c r="E8" s="153"/>
+      <c r="F8" s="153"/>
+      <c r="G8" s="153"/>
+      <c r="H8" s="153"/>
+      <c r="I8" s="153"/>
+      <c r="J8" s="112"/>
+      <c r="K8" s="113"/>
+      <c r="L8" s="113"/>
+      <c r="M8" s="113"/>
+      <c r="N8" s="113"/>
+      <c r="O8" s="113"/>
+      <c r="P8" s="114"/>
+      <c r="Q8" s="144"/>
+      <c r="R8" s="144"/>
+      <c r="S8" s="144"/>
+      <c r="T8" s="158" t="s">
         <v>87</v>
       </c>
-      <c r="U8" s="111"/>
-      <c r="V8" s="108">
+      <c r="U8" s="158"/>
+      <c r="V8" s="156">
         <v>0</v>
       </c>
-      <c r="W8" s="108"/>
-      <c r="X8" s="129">
+      <c r="W8" s="156"/>
+      <c r="X8" s="142">
         <v>0</v>
       </c>
-      <c r="Y8" s="129"/>
+      <c r="Y8" s="142"/>
       <c r="Z8" s="9"/>
       <c r="AA8" s="10"/>
       <c r="AB8" s="11"/>
@@ -6635,50 +6662,50 @@
       <c r="AL8" s="9"/>
       <c r="AM8" s="10"/>
       <c r="AN8" s="11"/>
-      <c r="AO8" s="106"/>
-      <c r="AP8" s="106"/>
-      <c r="AQ8" s="106"/>
-      <c r="AR8" s="106"/>
-      <c r="AS8" s="106"/>
-      <c r="AT8" s="106"/>
-      <c r="AU8" s="106"/>
-      <c r="AV8" s="106"/>
-      <c r="AW8" s="106"/>
-      <c r="AX8" s="106"/>
-      <c r="AY8" s="106"/>
-      <c r="AZ8" s="128"/>
+      <c r="AO8" s="153"/>
+      <c r="AP8" s="153"/>
+      <c r="AQ8" s="153"/>
+      <c r="AR8" s="153"/>
+      <c r="AS8" s="153"/>
+      <c r="AT8" s="153"/>
+      <c r="AU8" s="153"/>
+      <c r="AV8" s="153"/>
+      <c r="AW8" s="153"/>
+      <c r="AX8" s="153"/>
+      <c r="AY8" s="153"/>
+      <c r="AZ8" s="154"/>
     </row>
     <row r="9" spans="2:52" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B9" s="110"/>
-      <c r="C9" s="106"/>
-      <c r="D9" s="106"/>
-      <c r="E9" s="106"/>
-      <c r="F9" s="106"/>
-      <c r="G9" s="106"/>
-      <c r="H9" s="106"/>
-      <c r="I9" s="106"/>
-      <c r="J9" s="117"/>
-      <c r="K9" s="118"/>
-      <c r="L9" s="118"/>
-      <c r="M9" s="118"/>
-      <c r="N9" s="118"/>
-      <c r="O9" s="118"/>
-      <c r="P9" s="119"/>
-      <c r="Q9" s="113"/>
-      <c r="R9" s="113"/>
-      <c r="S9" s="113"/>
-      <c r="T9" s="112" t="s">
+      <c r="B9" s="167"/>
+      <c r="C9" s="153"/>
+      <c r="D9" s="153"/>
+      <c r="E9" s="153"/>
+      <c r="F9" s="153"/>
+      <c r="G9" s="153"/>
+      <c r="H9" s="153"/>
+      <c r="I9" s="153"/>
+      <c r="J9" s="115"/>
+      <c r="K9" s="116"/>
+      <c r="L9" s="116"/>
+      <c r="M9" s="116"/>
+      <c r="N9" s="116"/>
+      <c r="O9" s="116"/>
+      <c r="P9" s="117"/>
+      <c r="Q9" s="144"/>
+      <c r="R9" s="144"/>
+      <c r="S9" s="144"/>
+      <c r="T9" s="155" t="s">
         <v>25</v>
       </c>
-      <c r="U9" s="112"/>
-      <c r="V9" s="109">
+      <c r="U9" s="155"/>
+      <c r="V9" s="157">
         <v>0</v>
       </c>
-      <c r="W9" s="109"/>
-      <c r="X9" s="130">
+      <c r="W9" s="157"/>
+      <c r="X9" s="143">
         <v>0</v>
       </c>
-      <c r="Y9" s="130"/>
+      <c r="Y9" s="143"/>
       <c r="Z9" s="12"/>
       <c r="AA9" s="13"/>
       <c r="AB9" s="14"/>
@@ -6694,54 +6721,54 @@
       <c r="AL9" s="12"/>
       <c r="AM9" s="13"/>
       <c r="AN9" s="14"/>
-      <c r="AO9" s="106"/>
-      <c r="AP9" s="106"/>
-      <c r="AQ9" s="106"/>
-      <c r="AR9" s="106"/>
-      <c r="AS9" s="106"/>
-      <c r="AT9" s="106"/>
-      <c r="AU9" s="106"/>
-      <c r="AV9" s="106"/>
-      <c r="AW9" s="106"/>
-      <c r="AX9" s="106"/>
-      <c r="AY9" s="106"/>
-      <c r="AZ9" s="128"/>
+      <c r="AO9" s="153"/>
+      <c r="AP9" s="153"/>
+      <c r="AQ9" s="153"/>
+      <c r="AR9" s="153"/>
+      <c r="AS9" s="153"/>
+      <c r="AT9" s="153"/>
+      <c r="AU9" s="153"/>
+      <c r="AV9" s="153"/>
+      <c r="AW9" s="153"/>
+      <c r="AX9" s="153"/>
+      <c r="AY9" s="153"/>
+      <c r="AZ9" s="154"/>
     </row>
     <row r="10" spans="2:52" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B10" s="110">
+      <c r="B10" s="167">
         <v>3</v>
       </c>
-      <c r="C10" s="106" t="s">
+      <c r="C10" s="153" t="s">
         <v>89</v>
       </c>
-      <c r="D10" s="106"/>
-      <c r="E10" s="106"/>
-      <c r="F10" s="106"/>
-      <c r="G10" s="106"/>
-      <c r="H10" s="106"/>
-      <c r="I10" s="106"/>
-      <c r="J10" s="106"/>
-      <c r="K10" s="106"/>
-      <c r="L10" s="106"/>
-      <c r="M10" s="106"/>
-      <c r="N10" s="106"/>
-      <c r="O10" s="106"/>
-      <c r="P10" s="106"/>
-      <c r="Q10" s="113"/>
-      <c r="R10" s="113"/>
-      <c r="S10" s="113"/>
-      <c r="T10" s="111" t="s">
+      <c r="D10" s="153"/>
+      <c r="E10" s="153"/>
+      <c r="F10" s="153"/>
+      <c r="G10" s="153"/>
+      <c r="H10" s="153"/>
+      <c r="I10" s="153"/>
+      <c r="J10" s="153"/>
+      <c r="K10" s="153"/>
+      <c r="L10" s="153"/>
+      <c r="M10" s="153"/>
+      <c r="N10" s="153"/>
+      <c r="O10" s="153"/>
+      <c r="P10" s="153"/>
+      <c r="Q10" s="144"/>
+      <c r="R10" s="144"/>
+      <c r="S10" s="144"/>
+      <c r="T10" s="158" t="s">
         <v>87</v>
       </c>
-      <c r="U10" s="111"/>
-      <c r="V10" s="108">
+      <c r="U10" s="158"/>
+      <c r="V10" s="156">
         <v>0</v>
       </c>
-      <c r="W10" s="108"/>
-      <c r="X10" s="129">
+      <c r="W10" s="156"/>
+      <c r="X10" s="142">
         <v>0</v>
       </c>
-      <c r="Y10" s="129"/>
+      <c r="Y10" s="142"/>
       <c r="Z10" s="9"/>
       <c r="AA10" s="10"/>
       <c r="AB10" s="11"/>
@@ -6757,50 +6784,50 @@
       <c r="AL10" s="9"/>
       <c r="AM10" s="10"/>
       <c r="AN10" s="11"/>
-      <c r="AO10" s="106"/>
-      <c r="AP10" s="106"/>
-      <c r="AQ10" s="106"/>
-      <c r="AR10" s="106"/>
-      <c r="AS10" s="106"/>
-      <c r="AT10" s="106"/>
-      <c r="AU10" s="106"/>
-      <c r="AV10" s="106"/>
-      <c r="AW10" s="106"/>
-      <c r="AX10" s="106"/>
-      <c r="AY10" s="106"/>
-      <c r="AZ10" s="128"/>
+      <c r="AO10" s="153"/>
+      <c r="AP10" s="153"/>
+      <c r="AQ10" s="153"/>
+      <c r="AR10" s="153"/>
+      <c r="AS10" s="153"/>
+      <c r="AT10" s="153"/>
+      <c r="AU10" s="153"/>
+      <c r="AV10" s="153"/>
+      <c r="AW10" s="153"/>
+      <c r="AX10" s="153"/>
+      <c r="AY10" s="153"/>
+      <c r="AZ10" s="154"/>
     </row>
     <row r="11" spans="2:52" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B11" s="110"/>
-      <c r="C11" s="106"/>
-      <c r="D11" s="106"/>
-      <c r="E11" s="106"/>
-      <c r="F11" s="106"/>
-      <c r="G11" s="106"/>
-      <c r="H11" s="106"/>
-      <c r="I11" s="106"/>
-      <c r="J11" s="106"/>
-      <c r="K11" s="106"/>
-      <c r="L11" s="106"/>
-      <c r="M11" s="106"/>
-      <c r="N11" s="106"/>
-      <c r="O11" s="106"/>
-      <c r="P11" s="106"/>
-      <c r="Q11" s="113"/>
-      <c r="R11" s="113"/>
-      <c r="S11" s="113"/>
-      <c r="T11" s="112" t="s">
+      <c r="B11" s="167"/>
+      <c r="C11" s="153"/>
+      <c r="D11" s="153"/>
+      <c r="E11" s="153"/>
+      <c r="F11" s="153"/>
+      <c r="G11" s="153"/>
+      <c r="H11" s="153"/>
+      <c r="I11" s="153"/>
+      <c r="J11" s="153"/>
+      <c r="K11" s="153"/>
+      <c r="L11" s="153"/>
+      <c r="M11" s="153"/>
+      <c r="N11" s="153"/>
+      <c r="O11" s="153"/>
+      <c r="P11" s="153"/>
+      <c r="Q11" s="144"/>
+      <c r="R11" s="144"/>
+      <c r="S11" s="144"/>
+      <c r="T11" s="155" t="s">
         <v>25</v>
       </c>
-      <c r="U11" s="112"/>
-      <c r="V11" s="109">
+      <c r="U11" s="155"/>
+      <c r="V11" s="157">
         <v>0</v>
       </c>
-      <c r="W11" s="109"/>
-      <c r="X11" s="130">
+      <c r="W11" s="157"/>
+      <c r="X11" s="143">
         <v>0</v>
       </c>
-      <c r="Y11" s="130"/>
+      <c r="Y11" s="143"/>
       <c r="Z11" s="12"/>
       <c r="AA11" s="13"/>
       <c r="AB11" s="14"/>
@@ -6816,54 +6843,54 @@
       <c r="AL11" s="12"/>
       <c r="AM11" s="13"/>
       <c r="AN11" s="14"/>
-      <c r="AO11" s="106"/>
-      <c r="AP11" s="106"/>
-      <c r="AQ11" s="106"/>
-      <c r="AR11" s="106"/>
-      <c r="AS11" s="106"/>
-      <c r="AT11" s="106"/>
-      <c r="AU11" s="106"/>
-      <c r="AV11" s="106"/>
-      <c r="AW11" s="106"/>
-      <c r="AX11" s="106"/>
-      <c r="AY11" s="106"/>
-      <c r="AZ11" s="128"/>
+      <c r="AO11" s="153"/>
+      <c r="AP11" s="153"/>
+      <c r="AQ11" s="153"/>
+      <c r="AR11" s="153"/>
+      <c r="AS11" s="153"/>
+      <c r="AT11" s="153"/>
+      <c r="AU11" s="153"/>
+      <c r="AV11" s="153"/>
+      <c r="AW11" s="153"/>
+      <c r="AX11" s="153"/>
+      <c r="AY11" s="153"/>
+      <c r="AZ11" s="154"/>
     </row>
     <row r="12" spans="2:52" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B12" s="110">
+      <c r="B12" s="167">
         <v>4</v>
       </c>
-      <c r="C12" s="106" t="s">
+      <c r="C12" s="153" t="s">
         <v>90</v>
       </c>
-      <c r="D12" s="106"/>
-      <c r="E12" s="106"/>
-      <c r="F12" s="106"/>
-      <c r="G12" s="106"/>
-      <c r="H12" s="106"/>
-      <c r="I12" s="106"/>
-      <c r="J12" s="106"/>
-      <c r="K12" s="106"/>
-      <c r="L12" s="106"/>
-      <c r="M12" s="106"/>
-      <c r="N12" s="106"/>
-      <c r="O12" s="106"/>
-      <c r="P12" s="106"/>
-      <c r="Q12" s="172"/>
-      <c r="R12" s="173"/>
-      <c r="S12" s="174"/>
-      <c r="T12" s="111" t="s">
+      <c r="D12" s="153"/>
+      <c r="E12" s="153"/>
+      <c r="F12" s="153"/>
+      <c r="G12" s="153"/>
+      <c r="H12" s="153"/>
+      <c r="I12" s="153"/>
+      <c r="J12" s="153"/>
+      <c r="K12" s="153"/>
+      <c r="L12" s="153"/>
+      <c r="M12" s="153"/>
+      <c r="N12" s="153"/>
+      <c r="O12" s="153"/>
+      <c r="P12" s="153"/>
+      <c r="Q12" s="118"/>
+      <c r="R12" s="119"/>
+      <c r="S12" s="120"/>
+      <c r="T12" s="158" t="s">
         <v>87</v>
       </c>
-      <c r="U12" s="111"/>
-      <c r="V12" s="108">
+      <c r="U12" s="158"/>
+      <c r="V12" s="156">
         <v>0</v>
       </c>
-      <c r="W12" s="108"/>
-      <c r="X12" s="129">
+      <c r="W12" s="156"/>
+      <c r="X12" s="142">
         <v>0</v>
       </c>
-      <c r="Y12" s="129"/>
+      <c r="Y12" s="142"/>
       <c r="Z12" s="9"/>
       <c r="AA12" s="10"/>
       <c r="AB12" s="11"/>
@@ -6879,50 +6906,50 @@
       <c r="AL12" s="9"/>
       <c r="AM12" s="10"/>
       <c r="AN12" s="11"/>
-      <c r="AO12" s="106"/>
-      <c r="AP12" s="106"/>
-      <c r="AQ12" s="106"/>
-      <c r="AR12" s="106"/>
-      <c r="AS12" s="106"/>
-      <c r="AT12" s="106"/>
-      <c r="AU12" s="106"/>
-      <c r="AV12" s="106"/>
-      <c r="AW12" s="106"/>
-      <c r="AX12" s="106"/>
-      <c r="AY12" s="106"/>
-      <c r="AZ12" s="128"/>
+      <c r="AO12" s="153"/>
+      <c r="AP12" s="153"/>
+      <c r="AQ12" s="153"/>
+      <c r="AR12" s="153"/>
+      <c r="AS12" s="153"/>
+      <c r="AT12" s="153"/>
+      <c r="AU12" s="153"/>
+      <c r="AV12" s="153"/>
+      <c r="AW12" s="153"/>
+      <c r="AX12" s="153"/>
+      <c r="AY12" s="153"/>
+      <c r="AZ12" s="154"/>
     </row>
     <row r="13" spans="2:52" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B13" s="110"/>
-      <c r="C13" s="106"/>
-      <c r="D13" s="106"/>
-      <c r="E13" s="106"/>
-      <c r="F13" s="106"/>
-      <c r="G13" s="106"/>
-      <c r="H13" s="106"/>
-      <c r="I13" s="106"/>
-      <c r="J13" s="106"/>
-      <c r="K13" s="106"/>
-      <c r="L13" s="106"/>
-      <c r="M13" s="106"/>
-      <c r="N13" s="106"/>
-      <c r="O13" s="106"/>
-      <c r="P13" s="106"/>
-      <c r="Q13" s="175"/>
-      <c r="R13" s="176"/>
-      <c r="S13" s="177"/>
-      <c r="T13" s="112" t="s">
+      <c r="B13" s="167"/>
+      <c r="C13" s="153"/>
+      <c r="D13" s="153"/>
+      <c r="E13" s="153"/>
+      <c r="F13" s="153"/>
+      <c r="G13" s="153"/>
+      <c r="H13" s="153"/>
+      <c r="I13" s="153"/>
+      <c r="J13" s="153"/>
+      <c r="K13" s="153"/>
+      <c r="L13" s="153"/>
+      <c r="M13" s="153"/>
+      <c r="N13" s="153"/>
+      <c r="O13" s="153"/>
+      <c r="P13" s="153"/>
+      <c r="Q13" s="121"/>
+      <c r="R13" s="122"/>
+      <c r="S13" s="123"/>
+      <c r="T13" s="155" t="s">
         <v>25</v>
       </c>
-      <c r="U13" s="112"/>
-      <c r="V13" s="109">
+      <c r="U13" s="155"/>
+      <c r="V13" s="157">
         <v>0</v>
       </c>
-      <c r="W13" s="109"/>
-      <c r="X13" s="130">
+      <c r="W13" s="157"/>
+      <c r="X13" s="143">
         <v>0</v>
       </c>
-      <c r="Y13" s="130"/>
+      <c r="Y13" s="143"/>
       <c r="Z13" s="12"/>
       <c r="AA13" s="13"/>
       <c r="AB13" s="14"/>
@@ -6938,54 +6965,54 @@
       <c r="AL13" s="12"/>
       <c r="AM13" s="13"/>
       <c r="AN13" s="14"/>
-      <c r="AO13" s="106"/>
-      <c r="AP13" s="106"/>
-      <c r="AQ13" s="106"/>
-      <c r="AR13" s="106"/>
-      <c r="AS13" s="106"/>
-      <c r="AT13" s="106"/>
-      <c r="AU13" s="106"/>
-      <c r="AV13" s="106"/>
-      <c r="AW13" s="106"/>
-      <c r="AX13" s="106"/>
-      <c r="AY13" s="106"/>
-      <c r="AZ13" s="128"/>
+      <c r="AO13" s="153"/>
+      <c r="AP13" s="153"/>
+      <c r="AQ13" s="153"/>
+      <c r="AR13" s="153"/>
+      <c r="AS13" s="153"/>
+      <c r="AT13" s="153"/>
+      <c r="AU13" s="153"/>
+      <c r="AV13" s="153"/>
+      <c r="AW13" s="153"/>
+      <c r="AX13" s="153"/>
+      <c r="AY13" s="153"/>
+      <c r="AZ13" s="154"/>
     </row>
     <row r="14" spans="2:52" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B14" s="110">
+      <c r="B14" s="167">
         <v>5</v>
       </c>
-      <c r="C14" s="114" t="s">
+      <c r="C14" s="112" t="s">
         <v>91</v>
       </c>
-      <c r="D14" s="115"/>
-      <c r="E14" s="115"/>
-      <c r="F14" s="115"/>
-      <c r="G14" s="115"/>
-      <c r="H14" s="115"/>
-      <c r="I14" s="116"/>
-      <c r="J14" s="107"/>
-      <c r="K14" s="106"/>
-      <c r="L14" s="106"/>
-      <c r="M14" s="106"/>
-      <c r="N14" s="106"/>
-      <c r="O14" s="106"/>
-      <c r="P14" s="106"/>
-      <c r="Q14" s="172"/>
-      <c r="R14" s="173"/>
-      <c r="S14" s="174"/>
-      <c r="T14" s="111" t="s">
+      <c r="D14" s="113"/>
+      <c r="E14" s="113"/>
+      <c r="F14" s="113"/>
+      <c r="G14" s="113"/>
+      <c r="H14" s="113"/>
+      <c r="I14" s="114"/>
+      <c r="J14" s="193"/>
+      <c r="K14" s="153"/>
+      <c r="L14" s="153"/>
+      <c r="M14" s="153"/>
+      <c r="N14" s="153"/>
+      <c r="O14" s="153"/>
+      <c r="P14" s="153"/>
+      <c r="Q14" s="118"/>
+      <c r="R14" s="119"/>
+      <c r="S14" s="120"/>
+      <c r="T14" s="158" t="s">
         <v>87</v>
       </c>
-      <c r="U14" s="111"/>
-      <c r="V14" s="108">
+      <c r="U14" s="158"/>
+      <c r="V14" s="156">
         <v>0</v>
       </c>
-      <c r="W14" s="108"/>
-      <c r="X14" s="129">
+      <c r="W14" s="156"/>
+      <c r="X14" s="142">
         <v>0</v>
       </c>
-      <c r="Y14" s="129"/>
+      <c r="Y14" s="142"/>
       <c r="Z14" s="9"/>
       <c r="AA14" s="10"/>
       <c r="AB14" s="11"/>
@@ -7001,50 +7028,50 @@
       <c r="AL14" s="9"/>
       <c r="AM14" s="10"/>
       <c r="AN14" s="11"/>
-      <c r="AO14" s="106"/>
-      <c r="AP14" s="106"/>
-      <c r="AQ14" s="106"/>
-      <c r="AR14" s="106"/>
-      <c r="AS14" s="106"/>
-      <c r="AT14" s="106"/>
-      <c r="AU14" s="106"/>
-      <c r="AV14" s="106"/>
-      <c r="AW14" s="106"/>
-      <c r="AX14" s="106"/>
-      <c r="AY14" s="106"/>
-      <c r="AZ14" s="128"/>
+      <c r="AO14" s="153"/>
+      <c r="AP14" s="153"/>
+      <c r="AQ14" s="153"/>
+      <c r="AR14" s="153"/>
+      <c r="AS14" s="153"/>
+      <c r="AT14" s="153"/>
+      <c r="AU14" s="153"/>
+      <c r="AV14" s="153"/>
+      <c r="AW14" s="153"/>
+      <c r="AX14" s="153"/>
+      <c r="AY14" s="153"/>
+      <c r="AZ14" s="154"/>
     </row>
     <row r="15" spans="2:52" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B15" s="110"/>
-      <c r="C15" s="117"/>
-      <c r="D15" s="118"/>
-      <c r="E15" s="118"/>
-      <c r="F15" s="118"/>
-      <c r="G15" s="118"/>
-      <c r="H15" s="118"/>
-      <c r="I15" s="119"/>
-      <c r="J15" s="106"/>
-      <c r="K15" s="106"/>
-      <c r="L15" s="106"/>
-      <c r="M15" s="106"/>
-      <c r="N15" s="106"/>
-      <c r="O15" s="106"/>
-      <c r="P15" s="106"/>
-      <c r="Q15" s="175"/>
-      <c r="R15" s="176"/>
-      <c r="S15" s="177"/>
-      <c r="T15" s="112" t="s">
+      <c r="B15" s="167"/>
+      <c r="C15" s="115"/>
+      <c r="D15" s="116"/>
+      <c r="E15" s="116"/>
+      <c r="F15" s="116"/>
+      <c r="G15" s="116"/>
+      <c r="H15" s="116"/>
+      <c r="I15" s="117"/>
+      <c r="J15" s="153"/>
+      <c r="K15" s="153"/>
+      <c r="L15" s="153"/>
+      <c r="M15" s="153"/>
+      <c r="N15" s="153"/>
+      <c r="O15" s="153"/>
+      <c r="P15" s="153"/>
+      <c r="Q15" s="121"/>
+      <c r="R15" s="122"/>
+      <c r="S15" s="123"/>
+      <c r="T15" s="155" t="s">
         <v>25</v>
       </c>
-      <c r="U15" s="112"/>
-      <c r="V15" s="109">
+      <c r="U15" s="155"/>
+      <c r="V15" s="157">
         <v>0</v>
       </c>
-      <c r="W15" s="109"/>
-      <c r="X15" s="130">
+      <c r="W15" s="157"/>
+      <c r="X15" s="143">
         <v>0</v>
       </c>
-      <c r="Y15" s="130"/>
+      <c r="Y15" s="143"/>
       <c r="Z15" s="12"/>
       <c r="AA15" s="13"/>
       <c r="AB15" s="14"/>
@@ -7060,54 +7087,54 @@
       <c r="AL15" s="12"/>
       <c r="AM15" s="13"/>
       <c r="AN15" s="14"/>
-      <c r="AO15" s="106"/>
-      <c r="AP15" s="106"/>
-      <c r="AQ15" s="106"/>
-      <c r="AR15" s="106"/>
-      <c r="AS15" s="106"/>
-      <c r="AT15" s="106"/>
-      <c r="AU15" s="106"/>
-      <c r="AV15" s="106"/>
-      <c r="AW15" s="106"/>
-      <c r="AX15" s="106"/>
-      <c r="AY15" s="106"/>
-      <c r="AZ15" s="128"/>
+      <c r="AO15" s="153"/>
+      <c r="AP15" s="153"/>
+      <c r="AQ15" s="153"/>
+      <c r="AR15" s="153"/>
+      <c r="AS15" s="153"/>
+      <c r="AT15" s="153"/>
+      <c r="AU15" s="153"/>
+      <c r="AV15" s="153"/>
+      <c r="AW15" s="153"/>
+      <c r="AX15" s="153"/>
+      <c r="AY15" s="153"/>
+      <c r="AZ15" s="154"/>
     </row>
     <row r="16" spans="2:52" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B16" s="110">
+      <c r="B16" s="167">
         <v>6</v>
       </c>
-      <c r="C16" s="114" t="s">
+      <c r="C16" s="112" t="s">
         <v>92</v>
       </c>
-      <c r="D16" s="115"/>
-      <c r="E16" s="115"/>
-      <c r="F16" s="115"/>
-      <c r="G16" s="115"/>
-      <c r="H16" s="115"/>
-      <c r="I16" s="116"/>
-      <c r="J16" s="107"/>
-      <c r="K16" s="106"/>
-      <c r="L16" s="106"/>
-      <c r="M16" s="106"/>
-      <c r="N16" s="106"/>
-      <c r="O16" s="106"/>
-      <c r="P16" s="106"/>
-      <c r="Q16" s="113"/>
-      <c r="R16" s="113"/>
-      <c r="S16" s="113"/>
-      <c r="T16" s="111" t="s">
+      <c r="D16" s="113"/>
+      <c r="E16" s="113"/>
+      <c r="F16" s="113"/>
+      <c r="G16" s="113"/>
+      <c r="H16" s="113"/>
+      <c r="I16" s="114"/>
+      <c r="J16" s="193"/>
+      <c r="K16" s="153"/>
+      <c r="L16" s="153"/>
+      <c r="M16" s="153"/>
+      <c r="N16" s="153"/>
+      <c r="O16" s="153"/>
+      <c r="P16" s="153"/>
+      <c r="Q16" s="144"/>
+      <c r="R16" s="144"/>
+      <c r="S16" s="144"/>
+      <c r="T16" s="158" t="s">
         <v>87</v>
       </c>
-      <c r="U16" s="111"/>
-      <c r="V16" s="108">
+      <c r="U16" s="158"/>
+      <c r="V16" s="156">
         <v>0</v>
       </c>
-      <c r="W16" s="108"/>
-      <c r="X16" s="129">
+      <c r="W16" s="156"/>
+      <c r="X16" s="142">
         <v>0</v>
       </c>
-      <c r="Y16" s="129"/>
+      <c r="Y16" s="142"/>
       <c r="Z16" s="9"/>
       <c r="AA16" s="10"/>
       <c r="AB16" s="11"/>
@@ -7123,50 +7150,50 @@
       <c r="AL16" s="9"/>
       <c r="AM16" s="10"/>
       <c r="AN16" s="11"/>
-      <c r="AO16" s="106"/>
-      <c r="AP16" s="106"/>
-      <c r="AQ16" s="106"/>
-      <c r="AR16" s="106"/>
-      <c r="AS16" s="106"/>
-      <c r="AT16" s="106"/>
-      <c r="AU16" s="106"/>
-      <c r="AV16" s="106"/>
-      <c r="AW16" s="106"/>
-      <c r="AX16" s="106"/>
-      <c r="AY16" s="106"/>
-      <c r="AZ16" s="128"/>
+      <c r="AO16" s="153"/>
+      <c r="AP16" s="153"/>
+      <c r="AQ16" s="153"/>
+      <c r="AR16" s="153"/>
+      <c r="AS16" s="153"/>
+      <c r="AT16" s="153"/>
+      <c r="AU16" s="153"/>
+      <c r="AV16" s="153"/>
+      <c r="AW16" s="153"/>
+      <c r="AX16" s="153"/>
+      <c r="AY16" s="153"/>
+      <c r="AZ16" s="154"/>
     </row>
     <row r="17" spans="2:52" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B17" s="110"/>
-      <c r="C17" s="117"/>
-      <c r="D17" s="118"/>
-      <c r="E17" s="118"/>
-      <c r="F17" s="118"/>
-      <c r="G17" s="118"/>
-      <c r="H17" s="118"/>
-      <c r="I17" s="119"/>
-      <c r="J17" s="106"/>
-      <c r="K17" s="106"/>
-      <c r="L17" s="106"/>
-      <c r="M17" s="106"/>
-      <c r="N17" s="106"/>
-      <c r="O17" s="106"/>
-      <c r="P17" s="106"/>
-      <c r="Q17" s="113"/>
-      <c r="R17" s="113"/>
-      <c r="S17" s="113"/>
-      <c r="T17" s="112" t="s">
+      <c r="B17" s="167"/>
+      <c r="C17" s="115"/>
+      <c r="D17" s="116"/>
+      <c r="E17" s="116"/>
+      <c r="F17" s="116"/>
+      <c r="G17" s="116"/>
+      <c r="H17" s="116"/>
+      <c r="I17" s="117"/>
+      <c r="J17" s="153"/>
+      <c r="K17" s="153"/>
+      <c r="L17" s="153"/>
+      <c r="M17" s="153"/>
+      <c r="N17" s="153"/>
+      <c r="O17" s="153"/>
+      <c r="P17" s="153"/>
+      <c r="Q17" s="144"/>
+      <c r="R17" s="144"/>
+      <c r="S17" s="144"/>
+      <c r="T17" s="155" t="s">
         <v>25</v>
       </c>
-      <c r="U17" s="112"/>
-      <c r="V17" s="109">
+      <c r="U17" s="155"/>
+      <c r="V17" s="157">
         <v>0</v>
       </c>
-      <c r="W17" s="109"/>
-      <c r="X17" s="130">
+      <c r="W17" s="157"/>
+      <c r="X17" s="143">
         <v>0</v>
       </c>
-      <c r="Y17" s="130"/>
+      <c r="Y17" s="143"/>
       <c r="Z17" s="12"/>
       <c r="AA17" s="13"/>
       <c r="AB17" s="14"/>
@@ -7182,54 +7209,54 @@
       <c r="AL17" s="12"/>
       <c r="AM17" s="13"/>
       <c r="AN17" s="14"/>
-      <c r="AO17" s="106"/>
-      <c r="AP17" s="106"/>
-      <c r="AQ17" s="106"/>
-      <c r="AR17" s="106"/>
-      <c r="AS17" s="106"/>
-      <c r="AT17" s="106"/>
-      <c r="AU17" s="106"/>
-      <c r="AV17" s="106"/>
-      <c r="AW17" s="106"/>
-      <c r="AX17" s="106"/>
-      <c r="AY17" s="106"/>
-      <c r="AZ17" s="128"/>
+      <c r="AO17" s="153"/>
+      <c r="AP17" s="153"/>
+      <c r="AQ17" s="153"/>
+      <c r="AR17" s="153"/>
+      <c r="AS17" s="153"/>
+      <c r="AT17" s="153"/>
+      <c r="AU17" s="153"/>
+      <c r="AV17" s="153"/>
+      <c r="AW17" s="153"/>
+      <c r="AX17" s="153"/>
+      <c r="AY17" s="153"/>
+      <c r="AZ17" s="154"/>
     </row>
     <row r="18" spans="2:52" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B18" s="126">
+      <c r="B18" s="104">
         <v>7</v>
       </c>
-      <c r="C18" s="159" t="s">
+      <c r="C18" s="106" t="s">
         <v>93</v>
       </c>
-      <c r="D18" s="160"/>
-      <c r="E18" s="160"/>
-      <c r="F18" s="160"/>
-      <c r="G18" s="160"/>
-      <c r="H18" s="160"/>
-      <c r="I18" s="161"/>
-      <c r="J18" s="114"/>
-      <c r="K18" s="115"/>
-      <c r="L18" s="115"/>
-      <c r="M18" s="115"/>
-      <c r="N18" s="115"/>
-      <c r="O18" s="115"/>
-      <c r="P18" s="116"/>
-      <c r="Q18" s="172"/>
-      <c r="R18" s="173"/>
-      <c r="S18" s="174"/>
-      <c r="T18" s="162" t="s">
+      <c r="D18" s="107"/>
+      <c r="E18" s="107"/>
+      <c r="F18" s="107"/>
+      <c r="G18" s="107"/>
+      <c r="H18" s="107"/>
+      <c r="I18" s="108"/>
+      <c r="J18" s="112"/>
+      <c r="K18" s="113"/>
+      <c r="L18" s="113"/>
+      <c r="M18" s="113"/>
+      <c r="N18" s="113"/>
+      <c r="O18" s="113"/>
+      <c r="P18" s="114"/>
+      <c r="Q18" s="118"/>
+      <c r="R18" s="119"/>
+      <c r="S18" s="120"/>
+      <c r="T18" s="124" t="s">
         <v>87</v>
       </c>
-      <c r="U18" s="163"/>
-      <c r="V18" s="122">
+      <c r="U18" s="125"/>
+      <c r="V18" s="126">
         <v>0</v>
       </c>
-      <c r="W18" s="123"/>
-      <c r="X18" s="168">
+      <c r="W18" s="127"/>
+      <c r="X18" s="128">
         <v>0</v>
       </c>
-      <c r="Y18" s="169"/>
+      <c r="Y18" s="129"/>
       <c r="Z18" s="9"/>
       <c r="AA18" s="10"/>
       <c r="AB18" s="11"/>
@@ -7245,50 +7272,50 @@
       <c r="AL18" s="9"/>
       <c r="AM18" s="10"/>
       <c r="AN18" s="11"/>
-      <c r="AO18" s="114"/>
-      <c r="AP18" s="115"/>
-      <c r="AQ18" s="115"/>
-      <c r="AR18" s="115"/>
-      <c r="AS18" s="115"/>
-      <c r="AT18" s="115"/>
-      <c r="AU18" s="115"/>
-      <c r="AV18" s="115"/>
-      <c r="AW18" s="115"/>
-      <c r="AX18" s="115"/>
-      <c r="AY18" s="115"/>
-      <c r="AZ18" s="164"/>
+      <c r="AO18" s="112"/>
+      <c r="AP18" s="113"/>
+      <c r="AQ18" s="113"/>
+      <c r="AR18" s="113"/>
+      <c r="AS18" s="113"/>
+      <c r="AT18" s="113"/>
+      <c r="AU18" s="113"/>
+      <c r="AV18" s="113"/>
+      <c r="AW18" s="113"/>
+      <c r="AX18" s="113"/>
+      <c r="AY18" s="113"/>
+      <c r="AZ18" s="130"/>
     </row>
     <row r="19" spans="2:52" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B19" s="127"/>
-      <c r="C19" s="144"/>
-      <c r="D19" s="145"/>
-      <c r="E19" s="145"/>
-      <c r="F19" s="145"/>
-      <c r="G19" s="145"/>
-      <c r="H19" s="145"/>
-      <c r="I19" s="146"/>
-      <c r="J19" s="117"/>
-      <c r="K19" s="118"/>
-      <c r="L19" s="118"/>
-      <c r="M19" s="118"/>
-      <c r="N19" s="118"/>
-      <c r="O19" s="118"/>
-      <c r="P19" s="119"/>
-      <c r="Q19" s="175"/>
-      <c r="R19" s="176"/>
-      <c r="S19" s="177"/>
-      <c r="T19" s="166" t="s">
+      <c r="B19" s="105"/>
+      <c r="C19" s="109"/>
+      <c r="D19" s="110"/>
+      <c r="E19" s="110"/>
+      <c r="F19" s="110"/>
+      <c r="G19" s="110"/>
+      <c r="H19" s="110"/>
+      <c r="I19" s="111"/>
+      <c r="J19" s="115"/>
+      <c r="K19" s="116"/>
+      <c r="L19" s="116"/>
+      <c r="M19" s="116"/>
+      <c r="N19" s="116"/>
+      <c r="O19" s="116"/>
+      <c r="P19" s="117"/>
+      <c r="Q19" s="121"/>
+      <c r="R19" s="122"/>
+      <c r="S19" s="123"/>
+      <c r="T19" s="132" t="s">
         <v>25</v>
       </c>
-      <c r="U19" s="167"/>
-      <c r="V19" s="124">
+      <c r="U19" s="133"/>
+      <c r="V19" s="134">
         <v>0</v>
       </c>
-      <c r="W19" s="125"/>
-      <c r="X19" s="170">
+      <c r="W19" s="135"/>
+      <c r="X19" s="136">
         <v>0</v>
       </c>
-      <c r="Y19" s="171"/>
+      <c r="Y19" s="137"/>
       <c r="Z19" s="12"/>
       <c r="AA19" s="13"/>
       <c r="AB19" s="14"/>
@@ -7304,54 +7331,54 @@
       <c r="AL19" s="12"/>
       <c r="AM19" s="13"/>
       <c r="AN19" s="14"/>
-      <c r="AO19" s="117"/>
-      <c r="AP19" s="118"/>
-      <c r="AQ19" s="118"/>
-      <c r="AR19" s="118"/>
-      <c r="AS19" s="118"/>
-      <c r="AT19" s="118"/>
-      <c r="AU19" s="118"/>
-      <c r="AV19" s="118"/>
-      <c r="AW19" s="118"/>
-      <c r="AX19" s="118"/>
-      <c r="AY19" s="118"/>
-      <c r="AZ19" s="165"/>
+      <c r="AO19" s="115"/>
+      <c r="AP19" s="116"/>
+      <c r="AQ19" s="116"/>
+      <c r="AR19" s="116"/>
+      <c r="AS19" s="116"/>
+      <c r="AT19" s="116"/>
+      <c r="AU19" s="116"/>
+      <c r="AV19" s="116"/>
+      <c r="AW19" s="116"/>
+      <c r="AX19" s="116"/>
+      <c r="AY19" s="116"/>
+      <c r="AZ19" s="131"/>
     </row>
     <row r="20" spans="2:52" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B20" s="126">
+      <c r="B20" s="104">
         <v>8</v>
       </c>
-      <c r="C20" s="159" t="s">
+      <c r="C20" s="106" t="s">
         <v>94</v>
       </c>
-      <c r="D20" s="160"/>
-      <c r="E20" s="160"/>
-      <c r="F20" s="160"/>
-      <c r="G20" s="160"/>
-      <c r="H20" s="160"/>
-      <c r="I20" s="161"/>
-      <c r="J20" s="114"/>
-      <c r="K20" s="115"/>
-      <c r="L20" s="115"/>
-      <c r="M20" s="115"/>
-      <c r="N20" s="115"/>
-      <c r="O20" s="115"/>
-      <c r="P20" s="116"/>
-      <c r="Q20" s="172"/>
-      <c r="R20" s="173"/>
-      <c r="S20" s="174"/>
-      <c r="T20" s="162" t="s">
+      <c r="D20" s="107"/>
+      <c r="E20" s="107"/>
+      <c r="F20" s="107"/>
+      <c r="G20" s="107"/>
+      <c r="H20" s="107"/>
+      <c r="I20" s="108"/>
+      <c r="J20" s="112"/>
+      <c r="K20" s="113"/>
+      <c r="L20" s="113"/>
+      <c r="M20" s="113"/>
+      <c r="N20" s="113"/>
+      <c r="O20" s="113"/>
+      <c r="P20" s="114"/>
+      <c r="Q20" s="118"/>
+      <c r="R20" s="119"/>
+      <c r="S20" s="120"/>
+      <c r="T20" s="124" t="s">
         <v>87</v>
       </c>
-      <c r="U20" s="163"/>
-      <c r="V20" s="122">
+      <c r="U20" s="125"/>
+      <c r="V20" s="126">
         <v>0</v>
       </c>
-      <c r="W20" s="123"/>
-      <c r="X20" s="168">
+      <c r="W20" s="127"/>
+      <c r="X20" s="128">
         <v>0</v>
       </c>
-      <c r="Y20" s="169"/>
+      <c r="Y20" s="129"/>
       <c r="Z20" s="9"/>
       <c r="AA20" s="10"/>
       <c r="AB20" s="11"/>
@@ -7367,50 +7394,50 @@
       <c r="AL20" s="9"/>
       <c r="AM20" s="10"/>
       <c r="AN20" s="11"/>
-      <c r="AO20" s="114"/>
-      <c r="AP20" s="115"/>
-      <c r="AQ20" s="115"/>
-      <c r="AR20" s="115"/>
-      <c r="AS20" s="115"/>
-      <c r="AT20" s="115"/>
-      <c r="AU20" s="115"/>
-      <c r="AV20" s="115"/>
-      <c r="AW20" s="115"/>
-      <c r="AX20" s="115"/>
-      <c r="AY20" s="115"/>
-      <c r="AZ20" s="164"/>
+      <c r="AO20" s="112"/>
+      <c r="AP20" s="113"/>
+      <c r="AQ20" s="113"/>
+      <c r="AR20" s="113"/>
+      <c r="AS20" s="113"/>
+      <c r="AT20" s="113"/>
+      <c r="AU20" s="113"/>
+      <c r="AV20" s="113"/>
+      <c r="AW20" s="113"/>
+      <c r="AX20" s="113"/>
+      <c r="AY20" s="113"/>
+      <c r="AZ20" s="130"/>
     </row>
     <row r="21" spans="2:52" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B21" s="127"/>
-      <c r="C21" s="144"/>
-      <c r="D21" s="145"/>
-      <c r="E21" s="145"/>
-      <c r="F21" s="145"/>
-      <c r="G21" s="145"/>
-      <c r="H21" s="145"/>
-      <c r="I21" s="146"/>
-      <c r="J21" s="117"/>
-      <c r="K21" s="118"/>
-      <c r="L21" s="118"/>
-      <c r="M21" s="118"/>
-      <c r="N21" s="118"/>
-      <c r="O21" s="118"/>
-      <c r="P21" s="119"/>
-      <c r="Q21" s="175"/>
-      <c r="R21" s="176"/>
-      <c r="S21" s="177"/>
-      <c r="T21" s="166" t="s">
+      <c r="B21" s="105"/>
+      <c r="C21" s="109"/>
+      <c r="D21" s="110"/>
+      <c r="E21" s="110"/>
+      <c r="F21" s="110"/>
+      <c r="G21" s="110"/>
+      <c r="H21" s="110"/>
+      <c r="I21" s="111"/>
+      <c r="J21" s="115"/>
+      <c r="K21" s="116"/>
+      <c r="L21" s="116"/>
+      <c r="M21" s="116"/>
+      <c r="N21" s="116"/>
+      <c r="O21" s="116"/>
+      <c r="P21" s="117"/>
+      <c r="Q21" s="121"/>
+      <c r="R21" s="122"/>
+      <c r="S21" s="123"/>
+      <c r="T21" s="132" t="s">
         <v>25</v>
       </c>
-      <c r="U21" s="167"/>
-      <c r="V21" s="124">
+      <c r="U21" s="133"/>
+      <c r="V21" s="134">
         <v>0</v>
       </c>
-      <c r="W21" s="125"/>
-      <c r="X21" s="170">
+      <c r="W21" s="135"/>
+      <c r="X21" s="136">
         <v>0</v>
       </c>
-      <c r="Y21" s="171"/>
+      <c r="Y21" s="137"/>
       <c r="Z21" s="12"/>
       <c r="AA21" s="13"/>
       <c r="AB21" s="14"/>
@@ -7426,54 +7453,54 @@
       <c r="AL21" s="12"/>
       <c r="AM21" s="13"/>
       <c r="AN21" s="14"/>
-      <c r="AO21" s="117"/>
-      <c r="AP21" s="118"/>
-      <c r="AQ21" s="118"/>
-      <c r="AR21" s="118"/>
-      <c r="AS21" s="118"/>
-      <c r="AT21" s="118"/>
-      <c r="AU21" s="118"/>
-      <c r="AV21" s="118"/>
-      <c r="AW21" s="118"/>
-      <c r="AX21" s="118"/>
-      <c r="AY21" s="118"/>
-      <c r="AZ21" s="165"/>
+      <c r="AO21" s="115"/>
+      <c r="AP21" s="116"/>
+      <c r="AQ21" s="116"/>
+      <c r="AR21" s="116"/>
+      <c r="AS21" s="116"/>
+      <c r="AT21" s="116"/>
+      <c r="AU21" s="116"/>
+      <c r="AV21" s="116"/>
+      <c r="AW21" s="116"/>
+      <c r="AX21" s="116"/>
+      <c r="AY21" s="116"/>
+      <c r="AZ21" s="131"/>
     </row>
     <row r="22" spans="2:52" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B22" s="139">
+      <c r="B22" s="174">
         <v>9</v>
       </c>
-      <c r="C22" s="141" t="s">
+      <c r="C22" s="176" t="s">
         <v>95</v>
       </c>
-      <c r="D22" s="142"/>
-      <c r="E22" s="142"/>
-      <c r="F22" s="142"/>
-      <c r="G22" s="142"/>
-      <c r="H22" s="142"/>
-      <c r="I22" s="143"/>
-      <c r="J22" s="131"/>
-      <c r="K22" s="132"/>
-      <c r="L22" s="132"/>
-      <c r="M22" s="132"/>
-      <c r="N22" s="132"/>
-      <c r="O22" s="132"/>
-      <c r="P22" s="180"/>
-      <c r="Q22" s="151"/>
-      <c r="R22" s="152"/>
-      <c r="S22" s="153"/>
-      <c r="T22" s="147" t="s">
+      <c r="D22" s="177"/>
+      <c r="E22" s="177"/>
+      <c r="F22" s="177"/>
+      <c r="G22" s="177"/>
+      <c r="H22" s="177"/>
+      <c r="I22" s="178"/>
+      <c r="J22" s="161"/>
+      <c r="K22" s="162"/>
+      <c r="L22" s="162"/>
+      <c r="M22" s="162"/>
+      <c r="N22" s="162"/>
+      <c r="O22" s="162"/>
+      <c r="P22" s="163"/>
+      <c r="Q22" s="183"/>
+      <c r="R22" s="184"/>
+      <c r="S22" s="185"/>
+      <c r="T22" s="179" t="s">
         <v>87</v>
       </c>
-      <c r="U22" s="148"/>
-      <c r="V22" s="178">
+      <c r="U22" s="180"/>
+      <c r="V22" s="159">
         <v>0</v>
       </c>
-      <c r="W22" s="179"/>
-      <c r="X22" s="137">
+      <c r="W22" s="160"/>
+      <c r="X22" s="172">
         <v>0</v>
       </c>
-      <c r="Y22" s="138"/>
+      <c r="Y22" s="173"/>
       <c r="Z22" s="24"/>
       <c r="AA22" s="25"/>
       <c r="AB22" s="26"/>
@@ -7489,50 +7516,50 @@
       <c r="AL22" s="24"/>
       <c r="AM22" s="25"/>
       <c r="AN22" s="26"/>
-      <c r="AO22" s="131"/>
-      <c r="AP22" s="132"/>
-      <c r="AQ22" s="132"/>
-      <c r="AR22" s="132"/>
-      <c r="AS22" s="132"/>
-      <c r="AT22" s="132"/>
-      <c r="AU22" s="132"/>
-      <c r="AV22" s="132"/>
-      <c r="AW22" s="132"/>
-      <c r="AX22" s="132"/>
-      <c r="AY22" s="132"/>
-      <c r="AZ22" s="133"/>
+      <c r="AO22" s="161"/>
+      <c r="AP22" s="162"/>
+      <c r="AQ22" s="162"/>
+      <c r="AR22" s="162"/>
+      <c r="AS22" s="162"/>
+      <c r="AT22" s="162"/>
+      <c r="AU22" s="162"/>
+      <c r="AV22" s="162"/>
+      <c r="AW22" s="162"/>
+      <c r="AX22" s="162"/>
+      <c r="AY22" s="162"/>
+      <c r="AZ22" s="170"/>
     </row>
     <row r="23" spans="2:52" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B23" s="140"/>
-      <c r="C23" s="144"/>
-      <c r="D23" s="145"/>
-      <c r="E23" s="145"/>
-      <c r="F23" s="145"/>
-      <c r="G23" s="145"/>
-      <c r="H23" s="145"/>
-      <c r="I23" s="146"/>
-      <c r="J23" s="134"/>
-      <c r="K23" s="135"/>
-      <c r="L23" s="135"/>
-      <c r="M23" s="135"/>
-      <c r="N23" s="135"/>
-      <c r="O23" s="135"/>
-      <c r="P23" s="181"/>
-      <c r="Q23" s="154"/>
-      <c r="R23" s="155"/>
-      <c r="S23" s="156"/>
-      <c r="T23" s="149" t="s">
+      <c r="B23" s="175"/>
+      <c r="C23" s="109"/>
+      <c r="D23" s="110"/>
+      <c r="E23" s="110"/>
+      <c r="F23" s="110"/>
+      <c r="G23" s="110"/>
+      <c r="H23" s="110"/>
+      <c r="I23" s="111"/>
+      <c r="J23" s="164"/>
+      <c r="K23" s="165"/>
+      <c r="L23" s="165"/>
+      <c r="M23" s="165"/>
+      <c r="N23" s="165"/>
+      <c r="O23" s="165"/>
+      <c r="P23" s="166"/>
+      <c r="Q23" s="186"/>
+      <c r="R23" s="187"/>
+      <c r="S23" s="188"/>
+      <c r="T23" s="181" t="s">
         <v>25</v>
       </c>
-      <c r="U23" s="150"/>
-      <c r="V23" s="120">
+      <c r="U23" s="182"/>
+      <c r="V23" s="168">
         <v>0</v>
       </c>
-      <c r="W23" s="121"/>
-      <c r="X23" s="157">
+      <c r="W23" s="169"/>
+      <c r="X23" s="189">
         <v>0</v>
       </c>
-      <c r="Y23" s="158"/>
+      <c r="Y23" s="190"/>
       <c r="Z23" s="15"/>
       <c r="AA23" s="16"/>
       <c r="AB23" s="17"/>
@@ -7548,18 +7575,18 @@
       <c r="AL23" s="15"/>
       <c r="AM23" s="16"/>
       <c r="AN23" s="17"/>
-      <c r="AO23" s="134"/>
-      <c r="AP23" s="135"/>
-      <c r="AQ23" s="135"/>
-      <c r="AR23" s="135"/>
-      <c r="AS23" s="135"/>
-      <c r="AT23" s="135"/>
-      <c r="AU23" s="135"/>
-      <c r="AV23" s="135"/>
-      <c r="AW23" s="135"/>
-      <c r="AX23" s="135"/>
-      <c r="AY23" s="135"/>
-      <c r="AZ23" s="136"/>
+      <c r="AO23" s="164"/>
+      <c r="AP23" s="165"/>
+      <c r="AQ23" s="165"/>
+      <c r="AR23" s="165"/>
+      <c r="AS23" s="165"/>
+      <c r="AT23" s="165"/>
+      <c r="AU23" s="165"/>
+      <c r="AV23" s="165"/>
+      <c r="AW23" s="165"/>
+      <c r="AX23" s="165"/>
+      <c r="AY23" s="165"/>
+      <c r="AZ23" s="171"/>
     </row>
     <row r="24" spans="2:52" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D24" s="18"/>
@@ -7618,50 +7645,51 @@
     <row r="50" ht="18" customHeight="1" x14ac:dyDescent="0.2"/>
   </sheetData>
   <mergeCells count="113">
-    <mergeCell ref="B20:B21"/>
-    <mergeCell ref="C20:I21"/>
-    <mergeCell ref="J20:P21"/>
-    <mergeCell ref="Q20:S21"/>
-    <mergeCell ref="T20:U20"/>
-    <mergeCell ref="V20:W20"/>
-    <mergeCell ref="X20:Y20"/>
-    <mergeCell ref="AO20:AZ21"/>
-    <mergeCell ref="T21:U21"/>
-    <mergeCell ref="V21:W21"/>
-    <mergeCell ref="X21:Y21"/>
-    <mergeCell ref="AO4:AZ5"/>
-    <mergeCell ref="AI4:AK4"/>
-    <mergeCell ref="AL4:AN4"/>
-    <mergeCell ref="AF4:AH4"/>
-    <mergeCell ref="X6:Y6"/>
-    <mergeCell ref="X7:Y7"/>
-    <mergeCell ref="X8:Y8"/>
-    <mergeCell ref="B2:I2"/>
-    <mergeCell ref="J2:AD2"/>
-    <mergeCell ref="X4:Y5"/>
-    <mergeCell ref="T4:W5"/>
-    <mergeCell ref="Z4:AB4"/>
-    <mergeCell ref="AC4:AE4"/>
-    <mergeCell ref="B4:I5"/>
-    <mergeCell ref="J4:P5"/>
-    <mergeCell ref="Q4:S5"/>
-    <mergeCell ref="AO6:AZ7"/>
-    <mergeCell ref="C6:I7"/>
-    <mergeCell ref="Q6:S7"/>
-    <mergeCell ref="J6:P7"/>
-    <mergeCell ref="AO10:AZ11"/>
-    <mergeCell ref="T11:U11"/>
-    <mergeCell ref="X9:Y9"/>
-    <mergeCell ref="X10:Y10"/>
-    <mergeCell ref="X11:Y11"/>
-    <mergeCell ref="V8:W8"/>
-    <mergeCell ref="V9:W9"/>
-    <mergeCell ref="AO8:AZ9"/>
-    <mergeCell ref="V6:W6"/>
-    <mergeCell ref="V7:W7"/>
-    <mergeCell ref="T9:U9"/>
-    <mergeCell ref="T10:U10"/>
-    <mergeCell ref="T8:U8"/>
+    <mergeCell ref="B1:P1"/>
+    <mergeCell ref="J10:P11"/>
+    <mergeCell ref="J12:P13"/>
+    <mergeCell ref="J14:P15"/>
+    <mergeCell ref="J16:P17"/>
+    <mergeCell ref="V10:W10"/>
+    <mergeCell ref="V11:W11"/>
+    <mergeCell ref="V13:W13"/>
+    <mergeCell ref="V14:W14"/>
+    <mergeCell ref="V15:W15"/>
+    <mergeCell ref="V17:W17"/>
+    <mergeCell ref="B6:B7"/>
+    <mergeCell ref="T6:U6"/>
+    <mergeCell ref="T7:U7"/>
+    <mergeCell ref="B10:B11"/>
+    <mergeCell ref="C10:I11"/>
+    <mergeCell ref="Q8:S9"/>
+    <mergeCell ref="Q10:S11"/>
+    <mergeCell ref="B8:B9"/>
+    <mergeCell ref="C8:I9"/>
+    <mergeCell ref="J8:P9"/>
+    <mergeCell ref="V23:W23"/>
+    <mergeCell ref="V18:W18"/>
+    <mergeCell ref="V19:W19"/>
+    <mergeCell ref="B18:B19"/>
+    <mergeCell ref="AO16:AZ17"/>
+    <mergeCell ref="T17:U17"/>
+    <mergeCell ref="X16:Y16"/>
+    <mergeCell ref="X17:Y17"/>
+    <mergeCell ref="V16:W16"/>
+    <mergeCell ref="AO22:AZ23"/>
+    <mergeCell ref="X22:Y22"/>
+    <mergeCell ref="B16:B17"/>
+    <mergeCell ref="C16:I17"/>
+    <mergeCell ref="T16:U16"/>
+    <mergeCell ref="B22:B23"/>
+    <mergeCell ref="C22:I23"/>
+    <mergeCell ref="J18:P19"/>
+    <mergeCell ref="T22:U22"/>
+    <mergeCell ref="T23:U23"/>
+    <mergeCell ref="Q16:S17"/>
+    <mergeCell ref="Q22:S23"/>
+    <mergeCell ref="X23:Y23"/>
+    <mergeCell ref="C18:I19"/>
+    <mergeCell ref="T18:U18"/>
     <mergeCell ref="AO18:AZ19"/>
     <mergeCell ref="T19:U19"/>
     <mergeCell ref="X18:Y18"/>
@@ -7686,51 +7714,50 @@
     <mergeCell ref="X15:Y15"/>
     <mergeCell ref="Q12:S13"/>
     <mergeCell ref="Q14:S15"/>
-    <mergeCell ref="V23:W23"/>
-    <mergeCell ref="V18:W18"/>
-    <mergeCell ref="V19:W19"/>
-    <mergeCell ref="B18:B19"/>
-    <mergeCell ref="AO16:AZ17"/>
-    <mergeCell ref="T17:U17"/>
-    <mergeCell ref="X16:Y16"/>
-    <mergeCell ref="X17:Y17"/>
-    <mergeCell ref="V16:W16"/>
-    <mergeCell ref="AO22:AZ23"/>
-    <mergeCell ref="X22:Y22"/>
-    <mergeCell ref="B16:B17"/>
-    <mergeCell ref="C16:I17"/>
-    <mergeCell ref="T16:U16"/>
-    <mergeCell ref="B22:B23"/>
-    <mergeCell ref="C22:I23"/>
-    <mergeCell ref="J18:P19"/>
-    <mergeCell ref="T22:U22"/>
-    <mergeCell ref="T23:U23"/>
-    <mergeCell ref="Q16:S17"/>
-    <mergeCell ref="Q22:S23"/>
-    <mergeCell ref="X23:Y23"/>
-    <mergeCell ref="C18:I19"/>
-    <mergeCell ref="T18:U18"/>
-    <mergeCell ref="B1:P1"/>
-    <mergeCell ref="J10:P11"/>
-    <mergeCell ref="J12:P13"/>
-    <mergeCell ref="J14:P15"/>
-    <mergeCell ref="J16:P17"/>
-    <mergeCell ref="V10:W10"/>
-    <mergeCell ref="V11:W11"/>
-    <mergeCell ref="V13:W13"/>
-    <mergeCell ref="V14:W14"/>
-    <mergeCell ref="V15:W15"/>
-    <mergeCell ref="V17:W17"/>
-    <mergeCell ref="B6:B7"/>
-    <mergeCell ref="T6:U6"/>
-    <mergeCell ref="T7:U7"/>
-    <mergeCell ref="B10:B11"/>
-    <mergeCell ref="C10:I11"/>
-    <mergeCell ref="Q8:S9"/>
-    <mergeCell ref="Q10:S11"/>
-    <mergeCell ref="B8:B9"/>
-    <mergeCell ref="C8:I9"/>
-    <mergeCell ref="J8:P9"/>
+    <mergeCell ref="AO10:AZ11"/>
+    <mergeCell ref="T11:U11"/>
+    <mergeCell ref="X9:Y9"/>
+    <mergeCell ref="X10:Y10"/>
+    <mergeCell ref="X11:Y11"/>
+    <mergeCell ref="V8:W8"/>
+    <mergeCell ref="V9:W9"/>
+    <mergeCell ref="AO8:AZ9"/>
+    <mergeCell ref="V6:W6"/>
+    <mergeCell ref="V7:W7"/>
+    <mergeCell ref="T9:U9"/>
+    <mergeCell ref="T10:U10"/>
+    <mergeCell ref="T8:U8"/>
+    <mergeCell ref="AO4:AZ5"/>
+    <mergeCell ref="AI4:AK4"/>
+    <mergeCell ref="AL4:AN4"/>
+    <mergeCell ref="AF4:AH4"/>
+    <mergeCell ref="X6:Y6"/>
+    <mergeCell ref="X7:Y7"/>
+    <mergeCell ref="X8:Y8"/>
+    <mergeCell ref="B2:I2"/>
+    <mergeCell ref="J2:AD2"/>
+    <mergeCell ref="X4:Y5"/>
+    <mergeCell ref="T4:W5"/>
+    <mergeCell ref="Z4:AB4"/>
+    <mergeCell ref="AC4:AE4"/>
+    <mergeCell ref="B4:I5"/>
+    <mergeCell ref="J4:P5"/>
+    <mergeCell ref="Q4:S5"/>
+    <mergeCell ref="AO6:AZ7"/>
+    <mergeCell ref="C6:I7"/>
+    <mergeCell ref="Q6:S7"/>
+    <mergeCell ref="J6:P7"/>
+    <mergeCell ref="B20:B21"/>
+    <mergeCell ref="C20:I21"/>
+    <mergeCell ref="J20:P21"/>
+    <mergeCell ref="Q20:S21"/>
+    <mergeCell ref="T20:U20"/>
+    <mergeCell ref="V20:W20"/>
+    <mergeCell ref="X20:Y20"/>
+    <mergeCell ref="AO20:AZ21"/>
+    <mergeCell ref="T21:U21"/>
+    <mergeCell ref="V21:W21"/>
+    <mergeCell ref="X21:Y21"/>
   </mergeCells>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.51200000000000001" footer="0.51200000000000001"/>
@@ -7754,51 +7781,51 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="28">
+      <c r="A1" s="27">
         <v>1</v>
       </c>
-      <c r="B1" s="32" t="s">
+      <c r="B1" s="34" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="32"/>
-      <c r="D1" s="32"/>
-      <c r="E1" s="78"/>
-      <c r="F1" s="78"/>
-      <c r="G1" s="78"/>
-      <c r="H1" s="78"/>
-      <c r="I1" s="78"/>
-      <c r="J1" s="79"/>
+      <c r="C1" s="34"/>
+      <c r="D1" s="34"/>
+      <c r="E1" s="36"/>
+      <c r="F1" s="36"/>
+      <c r="G1" s="36"/>
+      <c r="H1" s="36"/>
+      <c r="I1" s="36"/>
+      <c r="J1" s="37"/>
     </row>
     <row r="2" spans="1:10" ht="13.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="29"/>
-      <c r="B2" s="77"/>
-      <c r="C2" s="77"/>
-      <c r="D2" s="77"/>
-      <c r="E2" s="80"/>
-      <c r="F2" s="80"/>
-      <c r="G2" s="80"/>
-      <c r="H2" s="80"/>
-      <c r="I2" s="80"/>
-      <c r="J2" s="81"/>
+      <c r="A2" s="31"/>
+      <c r="B2" s="35"/>
+      <c r="C2" s="35"/>
+      <c r="D2" s="35"/>
+      <c r="E2" s="38"/>
+      <c r="F2" s="38"/>
+      <c r="G2" s="38"/>
+      <c r="H2" s="38"/>
+      <c r="I2" s="38"/>
+      <c r="J2" s="39"/>
     </row>
     <row r="3" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="28">
+      <c r="A3" s="27">
         <v>2</v>
       </c>
-      <c r="B3" s="32" t="s">
+      <c r="B3" s="34" t="s">
         <v>96</v>
       </c>
-      <c r="C3" s="32"/>
-      <c r="D3" s="32"/>
-      <c r="E3" s="32"/>
-      <c r="F3" s="32"/>
-      <c r="G3" s="32"/>
-      <c r="H3" s="32"/>
-      <c r="I3" s="32"/>
-      <c r="J3" s="33"/>
+      <c r="C3" s="34"/>
+      <c r="D3" s="34"/>
+      <c r="E3" s="34"/>
+      <c r="F3" s="34"/>
+      <c r="G3" s="34"/>
+      <c r="H3" s="34"/>
+      <c r="I3" s="34"/>
+      <c r="J3" s="67"/>
     </row>
     <row r="4" spans="1:10" ht="13.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="30"/>
+      <c r="A4" s="28"/>
       <c r="B4" s="194" t="s">
         <v>97</v>
       </c>
@@ -7812,551 +7839,552 @@
       <c r="J4" s="195"/>
     </row>
     <row r="5" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="28">
+      <c r="A5" s="27">
         <v>3</v>
       </c>
-      <c r="B5" s="32" t="s">
+      <c r="B5" s="34" t="s">
         <v>98</v>
       </c>
-      <c r="C5" s="32"/>
-      <c r="D5" s="32"/>
-      <c r="E5" s="32"/>
-      <c r="F5" s="32"/>
-      <c r="G5" s="32"/>
-      <c r="H5" s="32"/>
-      <c r="I5" s="32"/>
-      <c r="J5" s="33"/>
+      <c r="C5" s="34"/>
+      <c r="D5" s="34"/>
+      <c r="E5" s="34"/>
+      <c r="F5" s="34"/>
+      <c r="G5" s="34"/>
+      <c r="H5" s="34"/>
+      <c r="I5" s="34"/>
+      <c r="J5" s="67"/>
     </row>
     <row r="6" spans="1:10" ht="13.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="29"/>
-      <c r="B6" s="40" t="s">
+      <c r="A6" s="31"/>
+      <c r="B6" s="73" t="s">
         <v>16</v>
       </c>
-      <c r="C6" s="40"/>
-      <c r="D6" s="40"/>
-      <c r="E6" s="40"/>
-      <c r="F6" s="40"/>
-      <c r="G6" s="40"/>
-      <c r="H6" s="40"/>
-      <c r="I6" s="40"/>
-      <c r="J6" s="41"/>
+      <c r="C6" s="73"/>
+      <c r="D6" s="73"/>
+      <c r="E6" s="73"/>
+      <c r="F6" s="73"/>
+      <c r="G6" s="73"/>
+      <c r="H6" s="73"/>
+      <c r="I6" s="73"/>
+      <c r="J6" s="74"/>
     </row>
     <row r="7" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="28">
+      <c r="A7" s="27">
         <v>4</v>
       </c>
-      <c r="B7" s="32" t="s">
+      <c r="B7" s="34" t="s">
         <v>99</v>
       </c>
-      <c r="C7" s="32"/>
-      <c r="D7" s="32"/>
-      <c r="E7" s="32"/>
-      <c r="F7" s="32"/>
-      <c r="G7" s="32"/>
-      <c r="H7" s="32"/>
-      <c r="I7" s="32"/>
-      <c r="J7" s="33"/>
+      <c r="C7" s="34"/>
+      <c r="D7" s="34"/>
+      <c r="E7" s="34"/>
+      <c r="F7" s="34"/>
+      <c r="G7" s="34"/>
+      <c r="H7" s="34"/>
+      <c r="I7" s="34"/>
+      <c r="J7" s="67"/>
     </row>
     <row r="8" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="30"/>
-      <c r="B8" s="36" t="s">
+      <c r="A8" s="28"/>
+      <c r="B8" s="69" t="s">
         <v>100</v>
       </c>
-      <c r="C8" s="36"/>
-      <c r="D8" s="36"/>
-      <c r="E8" s="36"/>
-      <c r="F8" s="36"/>
-      <c r="G8" s="36"/>
-      <c r="H8" s="36"/>
-      <c r="I8" s="36"/>
-      <c r="J8" s="37"/>
+      <c r="C8" s="69"/>
+      <c r="D8" s="69"/>
+      <c r="E8" s="69"/>
+      <c r="F8" s="69"/>
+      <c r="G8" s="69"/>
+      <c r="H8" s="69"/>
+      <c r="I8" s="69"/>
+      <c r="J8" s="70"/>
     </row>
     <row r="9" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="30"/>
-      <c r="B9" s="34"/>
-      <c r="C9" s="34"/>
-      <c r="D9" s="34"/>
-      <c r="E9" s="34"/>
-      <c r="F9" s="34"/>
-      <c r="G9" s="34"/>
-      <c r="H9" s="34"/>
-      <c r="I9" s="34"/>
-      <c r="J9" s="35"/>
+      <c r="A9" s="28"/>
+      <c r="B9" s="44"/>
+      <c r="C9" s="44"/>
+      <c r="D9" s="44"/>
+      <c r="E9" s="44"/>
+      <c r="F9" s="44"/>
+      <c r="G9" s="44"/>
+      <c r="H9" s="44"/>
+      <c r="I9" s="44"/>
+      <c r="J9" s="45"/>
     </row>
     <row r="10" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="30"/>
-      <c r="B10" s="34"/>
-      <c r="C10" s="34"/>
-      <c r="D10" s="34"/>
-      <c r="E10" s="34"/>
-      <c r="F10" s="34"/>
-      <c r="G10" s="34"/>
-      <c r="H10" s="34"/>
-      <c r="I10" s="34"/>
-      <c r="J10" s="35"/>
+      <c r="A10" s="28"/>
+      <c r="B10" s="44"/>
+      <c r="C10" s="44"/>
+      <c r="D10" s="44"/>
+      <c r="E10" s="44"/>
+      <c r="F10" s="44"/>
+      <c r="G10" s="44"/>
+      <c r="H10" s="44"/>
+      <c r="I10" s="44"/>
+      <c r="J10" s="45"/>
     </row>
     <row r="11" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="30"/>
-      <c r="B11" s="34"/>
-      <c r="C11" s="34"/>
-      <c r="D11" s="34"/>
-      <c r="E11" s="34"/>
-      <c r="F11" s="34"/>
-      <c r="G11" s="34"/>
-      <c r="H11" s="34"/>
-      <c r="I11" s="34"/>
-      <c r="J11" s="35"/>
+      <c r="A11" s="28"/>
+      <c r="B11" s="44"/>
+      <c r="C11" s="44"/>
+      <c r="D11" s="44"/>
+      <c r="E11" s="44"/>
+      <c r="F11" s="44"/>
+      <c r="G11" s="44"/>
+      <c r="H11" s="44"/>
+      <c r="I11" s="44"/>
+      <c r="J11" s="45"/>
     </row>
     <row r="12" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="30"/>
-      <c r="B12" s="34"/>
-      <c r="C12" s="34"/>
-      <c r="D12" s="34"/>
-      <c r="E12" s="34"/>
-      <c r="F12" s="34"/>
-      <c r="G12" s="34"/>
-      <c r="H12" s="34"/>
-      <c r="I12" s="34"/>
-      <c r="J12" s="35"/>
+      <c r="A12" s="28"/>
+      <c r="B12" s="44"/>
+      <c r="C12" s="44"/>
+      <c r="D12" s="44"/>
+      <c r="E12" s="44"/>
+      <c r="F12" s="44"/>
+      <c r="G12" s="44"/>
+      <c r="H12" s="44"/>
+      <c r="I12" s="44"/>
+      <c r="J12" s="45"/>
     </row>
     <row r="13" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="30"/>
-      <c r="B13" s="34"/>
-      <c r="C13" s="34"/>
-      <c r="D13" s="34"/>
-      <c r="E13" s="34"/>
-      <c r="F13" s="34"/>
-      <c r="G13" s="34"/>
-      <c r="H13" s="34"/>
-      <c r="I13" s="34"/>
-      <c r="J13" s="35"/>
+      <c r="A13" s="28"/>
+      <c r="B13" s="44"/>
+      <c r="C13" s="44"/>
+      <c r="D13" s="44"/>
+      <c r="E13" s="44"/>
+      <c r="F13" s="44"/>
+      <c r="G13" s="44"/>
+      <c r="H13" s="44"/>
+      <c r="I13" s="44"/>
+      <c r="J13" s="45"/>
     </row>
     <row r="14" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A14" s="30"/>
-      <c r="B14" s="34"/>
-      <c r="C14" s="34"/>
-      <c r="D14" s="34"/>
-      <c r="E14" s="34"/>
-      <c r="F14" s="34"/>
-      <c r="G14" s="34"/>
-      <c r="H14" s="34"/>
-      <c r="I14" s="34"/>
-      <c r="J14" s="35"/>
+      <c r="A14" s="28"/>
+      <c r="B14" s="44"/>
+      <c r="C14" s="44"/>
+      <c r="D14" s="44"/>
+      <c r="E14" s="44"/>
+      <c r="F14" s="44"/>
+      <c r="G14" s="44"/>
+      <c r="H14" s="44"/>
+      <c r="I14" s="44"/>
+      <c r="J14" s="45"/>
     </row>
     <row r="15" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A15" s="30"/>
-      <c r="B15" s="36" t="s">
+      <c r="A15" s="28"/>
+      <c r="B15" s="69" t="s">
         <v>101</v>
       </c>
-      <c r="C15" s="36"/>
-      <c r="D15" s="36"/>
-      <c r="E15" s="36"/>
-      <c r="F15" s="36"/>
-      <c r="G15" s="36"/>
-      <c r="H15" s="36"/>
-      <c r="I15" s="36"/>
-      <c r="J15" s="37"/>
+      <c r="C15" s="69"/>
+      <c r="D15" s="69"/>
+      <c r="E15" s="69"/>
+      <c r="F15" s="69"/>
+      <c r="G15" s="69"/>
+      <c r="H15" s="69"/>
+      <c r="I15" s="69"/>
+      <c r="J15" s="70"/>
     </row>
     <row r="16" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A16" s="30"/>
-      <c r="B16" s="34"/>
-      <c r="C16" s="34"/>
-      <c r="D16" s="34"/>
-      <c r="E16" s="34"/>
-      <c r="F16" s="34"/>
-      <c r="G16" s="34"/>
-      <c r="H16" s="34"/>
-      <c r="I16" s="34"/>
-      <c r="J16" s="35"/>
+      <c r="A16" s="28"/>
+      <c r="B16" s="44"/>
+      <c r="C16" s="44"/>
+      <c r="D16" s="44"/>
+      <c r="E16" s="44"/>
+      <c r="F16" s="44"/>
+      <c r="G16" s="44"/>
+      <c r="H16" s="44"/>
+      <c r="I16" s="44"/>
+      <c r="J16" s="45"/>
     </row>
     <row r="17" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A17" s="30"/>
-      <c r="B17" s="34"/>
-      <c r="C17" s="34"/>
-      <c r="D17" s="34"/>
-      <c r="E17" s="34"/>
-      <c r="F17" s="34"/>
-      <c r="G17" s="34"/>
-      <c r="H17" s="34"/>
-      <c r="I17" s="34"/>
-      <c r="J17" s="35"/>
+      <c r="A17" s="28"/>
+      <c r="B17" s="44"/>
+      <c r="C17" s="44"/>
+      <c r="D17" s="44"/>
+      <c r="E17" s="44"/>
+      <c r="F17" s="44"/>
+      <c r="G17" s="44"/>
+      <c r="H17" s="44"/>
+      <c r="I17" s="44"/>
+      <c r="J17" s="45"/>
     </row>
     <row r="18" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A18" s="30"/>
-      <c r="B18" s="34"/>
-      <c r="C18" s="34"/>
-      <c r="D18" s="34"/>
-      <c r="E18" s="34"/>
-      <c r="F18" s="34"/>
-      <c r="G18" s="34"/>
-      <c r="H18" s="34"/>
-      <c r="I18" s="34"/>
-      <c r="J18" s="35"/>
+      <c r="A18" s="28"/>
+      <c r="B18" s="44"/>
+      <c r="C18" s="44"/>
+      <c r="D18" s="44"/>
+      <c r="E18" s="44"/>
+      <c r="F18" s="44"/>
+      <c r="G18" s="44"/>
+      <c r="H18" s="44"/>
+      <c r="I18" s="44"/>
+      <c r="J18" s="45"/>
     </row>
     <row r="19" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A19" s="30"/>
-      <c r="B19" s="34"/>
-      <c r="C19" s="34"/>
-      <c r="D19" s="34"/>
-      <c r="E19" s="34"/>
-      <c r="F19" s="34"/>
-      <c r="G19" s="34"/>
-      <c r="H19" s="34"/>
-      <c r="I19" s="34"/>
-      <c r="J19" s="35"/>
+      <c r="A19" s="28"/>
+      <c r="B19" s="44"/>
+      <c r="C19" s="44"/>
+      <c r="D19" s="44"/>
+      <c r="E19" s="44"/>
+      <c r="F19" s="44"/>
+      <c r="G19" s="44"/>
+      <c r="H19" s="44"/>
+      <c r="I19" s="44"/>
+      <c r="J19" s="45"/>
     </row>
     <row r="20" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A20" s="30"/>
-      <c r="B20" s="34"/>
-      <c r="C20" s="34"/>
-      <c r="D20" s="34"/>
-      <c r="E20" s="34"/>
-      <c r="F20" s="34"/>
-      <c r="G20" s="34"/>
-      <c r="H20" s="34"/>
-      <c r="I20" s="34"/>
-      <c r="J20" s="35"/>
+      <c r="A20" s="28"/>
+      <c r="B20" s="44"/>
+      <c r="C20" s="44"/>
+      <c r="D20" s="44"/>
+      <c r="E20" s="44"/>
+      <c r="F20" s="44"/>
+      <c r="G20" s="44"/>
+      <c r="H20" s="44"/>
+      <c r="I20" s="44"/>
+      <c r="J20" s="45"/>
     </row>
     <row r="21" spans="1:10" ht="13.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="29"/>
-      <c r="B21" s="80"/>
-      <c r="C21" s="80"/>
-      <c r="D21" s="80"/>
-      <c r="E21" s="80"/>
-      <c r="F21" s="80"/>
-      <c r="G21" s="80"/>
-      <c r="H21" s="80"/>
-      <c r="I21" s="80"/>
-      <c r="J21" s="81"/>
+      <c r="A21" s="31"/>
+      <c r="B21" s="38"/>
+      <c r="C21" s="38"/>
+      <c r="D21" s="38"/>
+      <c r="E21" s="38"/>
+      <c r="F21" s="38"/>
+      <c r="G21" s="38"/>
+      <c r="H21" s="38"/>
+      <c r="I21" s="38"/>
+      <c r="J21" s="39"/>
     </row>
     <row r="22" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A22" s="28">
+      <c r="A22" s="27">
         <v>5</v>
       </c>
-      <c r="B22" s="32" t="s">
+      <c r="B22" s="34" t="s">
         <v>102</v>
       </c>
-      <c r="C22" s="32"/>
-      <c r="D22" s="32"/>
-      <c r="E22" s="32"/>
-      <c r="F22" s="32"/>
-      <c r="G22" s="32"/>
-      <c r="H22" s="32"/>
-      <c r="I22" s="32"/>
-      <c r="J22" s="33"/>
+      <c r="C22" s="34"/>
+      <c r="D22" s="34"/>
+      <c r="E22" s="34"/>
+      <c r="F22" s="34"/>
+      <c r="G22" s="34"/>
+      <c r="H22" s="34"/>
+      <c r="I22" s="34"/>
+      <c r="J22" s="67"/>
     </row>
     <row r="23" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A23" s="30"/>
-      <c r="B23" s="34"/>
-      <c r="C23" s="34"/>
-      <c r="D23" s="34"/>
-      <c r="E23" s="34"/>
-      <c r="F23" s="34"/>
-      <c r="G23" s="34"/>
-      <c r="H23" s="34"/>
-      <c r="I23" s="34"/>
-      <c r="J23" s="35"/>
+      <c r="A23" s="28"/>
+      <c r="B23" s="44"/>
+      <c r="C23" s="44"/>
+      <c r="D23" s="44"/>
+      <c r="E23" s="44"/>
+      <c r="F23" s="44"/>
+      <c r="G23" s="44"/>
+      <c r="H23" s="44"/>
+      <c r="I23" s="44"/>
+      <c r="J23" s="45"/>
     </row>
     <row r="24" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A24" s="30"/>
-      <c r="B24" s="34"/>
-      <c r="C24" s="34"/>
-      <c r="D24" s="34"/>
-      <c r="E24" s="34"/>
-      <c r="F24" s="34"/>
-      <c r="G24" s="34"/>
-      <c r="H24" s="34"/>
-      <c r="I24" s="34"/>
-      <c r="J24" s="35"/>
+      <c r="A24" s="28"/>
+      <c r="B24" s="44"/>
+      <c r="C24" s="44"/>
+      <c r="D24" s="44"/>
+      <c r="E24" s="44"/>
+      <c r="F24" s="44"/>
+      <c r="G24" s="44"/>
+      <c r="H24" s="44"/>
+      <c r="I24" s="44"/>
+      <c r="J24" s="45"/>
     </row>
     <row r="25" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A25" s="30"/>
-      <c r="B25" s="34"/>
-      <c r="C25" s="34"/>
-      <c r="D25" s="34"/>
-      <c r="E25" s="34"/>
-      <c r="F25" s="34"/>
-      <c r="G25" s="34"/>
-      <c r="H25" s="34"/>
-      <c r="I25" s="34"/>
-      <c r="J25" s="35"/>
+      <c r="A25" s="28"/>
+      <c r="B25" s="44"/>
+      <c r="C25" s="44"/>
+      <c r="D25" s="44"/>
+      <c r="E25" s="44"/>
+      <c r="F25" s="44"/>
+      <c r="G25" s="44"/>
+      <c r="H25" s="44"/>
+      <c r="I25" s="44"/>
+      <c r="J25" s="45"/>
     </row>
     <row r="26" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A26" s="30"/>
-      <c r="B26" s="34"/>
-      <c r="C26" s="34"/>
-      <c r="D26" s="34"/>
-      <c r="E26" s="34"/>
-      <c r="F26" s="34"/>
-      <c r="G26" s="34"/>
-      <c r="H26" s="34"/>
-      <c r="I26" s="34"/>
-      <c r="J26" s="35"/>
+      <c r="A26" s="28"/>
+      <c r="B26" s="44"/>
+      <c r="C26" s="44"/>
+      <c r="D26" s="44"/>
+      <c r="E26" s="44"/>
+      <c r="F26" s="44"/>
+      <c r="G26" s="44"/>
+      <c r="H26" s="44"/>
+      <c r="I26" s="44"/>
+      <c r="J26" s="45"/>
     </row>
     <row r="27" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A27" s="30"/>
-      <c r="B27" s="34"/>
-      <c r="C27" s="34"/>
-      <c r="D27" s="34"/>
-      <c r="E27" s="34"/>
-      <c r="F27" s="34"/>
-      <c r="G27" s="34"/>
-      <c r="H27" s="34"/>
-      <c r="I27" s="34"/>
-      <c r="J27" s="35"/>
+      <c r="A27" s="28"/>
+      <c r="B27" s="44"/>
+      <c r="C27" s="44"/>
+      <c r="D27" s="44"/>
+      <c r="E27" s="44"/>
+      <c r="F27" s="44"/>
+      <c r="G27" s="44"/>
+      <c r="H27" s="44"/>
+      <c r="I27" s="44"/>
+      <c r="J27" s="45"/>
     </row>
     <row r="28" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A28" s="30"/>
-      <c r="B28" s="34"/>
-      <c r="C28" s="34"/>
-      <c r="D28" s="34"/>
-      <c r="E28" s="34"/>
-      <c r="F28" s="34"/>
-      <c r="G28" s="34"/>
-      <c r="H28" s="34"/>
-      <c r="I28" s="34"/>
-      <c r="J28" s="35"/>
+      <c r="A28" s="28"/>
+      <c r="B28" s="44"/>
+      <c r="C28" s="44"/>
+      <c r="D28" s="44"/>
+      <c r="E28" s="44"/>
+      <c r="F28" s="44"/>
+      <c r="G28" s="44"/>
+      <c r="H28" s="44"/>
+      <c r="I28" s="44"/>
+      <c r="J28" s="45"/>
     </row>
     <row r="29" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A29" s="30"/>
-      <c r="B29" s="34"/>
-      <c r="C29" s="34"/>
-      <c r="D29" s="34"/>
-      <c r="E29" s="34"/>
-      <c r="F29" s="34"/>
-      <c r="G29" s="34"/>
-      <c r="H29" s="34"/>
-      <c r="I29" s="34"/>
-      <c r="J29" s="35"/>
+      <c r="A29" s="28"/>
+      <c r="B29" s="44"/>
+      <c r="C29" s="44"/>
+      <c r="D29" s="44"/>
+      <c r="E29" s="44"/>
+      <c r="F29" s="44"/>
+      <c r="G29" s="44"/>
+      <c r="H29" s="44"/>
+      <c r="I29" s="44"/>
+      <c r="J29" s="45"/>
     </row>
     <row r="30" spans="1:10" ht="13.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="29"/>
-      <c r="B30" s="80"/>
-      <c r="C30" s="80"/>
-      <c r="D30" s="80"/>
-      <c r="E30" s="80"/>
-      <c r="F30" s="80"/>
-      <c r="G30" s="80"/>
-      <c r="H30" s="80"/>
-      <c r="I30" s="80"/>
-      <c r="J30" s="81"/>
+      <c r="A30" s="31"/>
+      <c r="B30" s="38"/>
+      <c r="C30" s="38"/>
+      <c r="D30" s="38"/>
+      <c r="E30" s="38"/>
+      <c r="F30" s="38"/>
+      <c r="G30" s="38"/>
+      <c r="H30" s="38"/>
+      <c r="I30" s="38"/>
+      <c r="J30" s="39"/>
     </row>
     <row r="31" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A31" s="28">
+      <c r="A31" s="27">
         <v>6</v>
       </c>
-      <c r="B31" s="32" t="s">
+      <c r="B31" s="34" t="s">
         <v>103</v>
       </c>
-      <c r="C31" s="32"/>
-      <c r="D31" s="32"/>
-      <c r="E31" s="32"/>
-      <c r="F31" s="32"/>
-      <c r="G31" s="32"/>
-      <c r="H31" s="32"/>
-      <c r="I31" s="32"/>
-      <c r="J31" s="33"/>
+      <c r="C31" s="34"/>
+      <c r="D31" s="34"/>
+      <c r="E31" s="34"/>
+      <c r="F31" s="34"/>
+      <c r="G31" s="34"/>
+      <c r="H31" s="34"/>
+      <c r="I31" s="34"/>
+      <c r="J31" s="67"/>
     </row>
     <row r="32" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A32" s="30"/>
-      <c r="B32" s="34"/>
-      <c r="C32" s="34"/>
-      <c r="D32" s="34"/>
-      <c r="E32" s="34"/>
-      <c r="F32" s="34"/>
-      <c r="G32" s="34"/>
-      <c r="H32" s="34"/>
-      <c r="I32" s="34"/>
-      <c r="J32" s="35"/>
+      <c r="A32" s="28"/>
+      <c r="B32" s="44"/>
+      <c r="C32" s="44"/>
+      <c r="D32" s="44"/>
+      <c r="E32" s="44"/>
+      <c r="F32" s="44"/>
+      <c r="G32" s="44"/>
+      <c r="H32" s="44"/>
+      <c r="I32" s="44"/>
+      <c r="J32" s="45"/>
     </row>
     <row r="33" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A33" s="30"/>
-      <c r="B33" s="34"/>
-      <c r="C33" s="34"/>
-      <c r="D33" s="34"/>
-      <c r="E33" s="34"/>
-      <c r="F33" s="34"/>
-      <c r="G33" s="34"/>
-      <c r="H33" s="34"/>
-      <c r="I33" s="34"/>
-      <c r="J33" s="35"/>
+      <c r="A33" s="28"/>
+      <c r="B33" s="44"/>
+      <c r="C33" s="44"/>
+      <c r="D33" s="44"/>
+      <c r="E33" s="44"/>
+      <c r="F33" s="44"/>
+      <c r="G33" s="44"/>
+      <c r="H33" s="44"/>
+      <c r="I33" s="44"/>
+      <c r="J33" s="45"/>
     </row>
     <row r="34" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A34" s="30"/>
-      <c r="B34" s="34"/>
-      <c r="C34" s="34"/>
-      <c r="D34" s="34"/>
-      <c r="E34" s="34"/>
-      <c r="F34" s="34"/>
-      <c r="G34" s="34"/>
-      <c r="H34" s="34"/>
-      <c r="I34" s="34"/>
-      <c r="J34" s="35"/>
+      <c r="A34" s="28"/>
+      <c r="B34" s="44"/>
+      <c r="C34" s="44"/>
+      <c r="D34" s="44"/>
+      <c r="E34" s="44"/>
+      <c r="F34" s="44"/>
+      <c r="G34" s="44"/>
+      <c r="H34" s="44"/>
+      <c r="I34" s="44"/>
+      <c r="J34" s="45"/>
     </row>
     <row r="35" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A35" s="30"/>
-      <c r="B35" s="34"/>
-      <c r="C35" s="34"/>
-      <c r="D35" s="34"/>
-      <c r="E35" s="34"/>
-      <c r="F35" s="34"/>
-      <c r="G35" s="34"/>
-      <c r="H35" s="34"/>
-      <c r="I35" s="34"/>
-      <c r="J35" s="35"/>
+      <c r="A35" s="28"/>
+      <c r="B35" s="44"/>
+      <c r="C35" s="44"/>
+      <c r="D35" s="44"/>
+      <c r="E35" s="44"/>
+      <c r="F35" s="44"/>
+      <c r="G35" s="44"/>
+      <c r="H35" s="44"/>
+      <c r="I35" s="44"/>
+      <c r="J35" s="45"/>
     </row>
     <row r="36" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A36" s="30"/>
-      <c r="B36" s="34"/>
-      <c r="C36" s="34"/>
-      <c r="D36" s="34"/>
-      <c r="E36" s="34"/>
-      <c r="F36" s="34"/>
-      <c r="G36" s="34"/>
-      <c r="H36" s="34"/>
-      <c r="I36" s="34"/>
-      <c r="J36" s="35"/>
+      <c r="A36" s="28"/>
+      <c r="B36" s="44"/>
+      <c r="C36" s="44"/>
+      <c r="D36" s="44"/>
+      <c r="E36" s="44"/>
+      <c r="F36" s="44"/>
+      <c r="G36" s="44"/>
+      <c r="H36" s="44"/>
+      <c r="I36" s="44"/>
+      <c r="J36" s="45"/>
     </row>
     <row r="37" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A37" s="30"/>
-      <c r="B37" s="34"/>
-      <c r="C37" s="34"/>
-      <c r="D37" s="34"/>
-      <c r="E37" s="34"/>
-      <c r="F37" s="34"/>
-      <c r="G37" s="34"/>
-      <c r="H37" s="34"/>
-      <c r="I37" s="34"/>
-      <c r="J37" s="35"/>
+      <c r="A37" s="28"/>
+      <c r="B37" s="44"/>
+      <c r="C37" s="44"/>
+      <c r="D37" s="44"/>
+      <c r="E37" s="44"/>
+      <c r="F37" s="44"/>
+      <c r="G37" s="44"/>
+      <c r="H37" s="44"/>
+      <c r="I37" s="44"/>
+      <c r="J37" s="45"/>
     </row>
     <row r="38" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A38" s="30"/>
-      <c r="B38" s="34"/>
-      <c r="C38" s="34"/>
-      <c r="D38" s="34"/>
-      <c r="E38" s="34"/>
-      <c r="F38" s="34"/>
-      <c r="G38" s="34"/>
-      <c r="H38" s="34"/>
-      <c r="I38" s="34"/>
-      <c r="J38" s="35"/>
+      <c r="A38" s="28"/>
+      <c r="B38" s="44"/>
+      <c r="C38" s="44"/>
+      <c r="D38" s="44"/>
+      <c r="E38" s="44"/>
+      <c r="F38" s="44"/>
+      <c r="G38" s="44"/>
+      <c r="H38" s="44"/>
+      <c r="I38" s="44"/>
+      <c r="J38" s="45"/>
     </row>
     <row r="39" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A39" s="30"/>
-      <c r="B39" s="34"/>
-      <c r="C39" s="34"/>
-      <c r="D39" s="34"/>
-      <c r="E39" s="34"/>
-      <c r="F39" s="34"/>
-      <c r="G39" s="34"/>
-      <c r="H39" s="34"/>
-      <c r="I39" s="34"/>
-      <c r="J39" s="35"/>
+      <c r="A39" s="28"/>
+      <c r="B39" s="44"/>
+      <c r="C39" s="44"/>
+      <c r="D39" s="44"/>
+      <c r="E39" s="44"/>
+      <c r="F39" s="44"/>
+      <c r="G39" s="44"/>
+      <c r="H39" s="44"/>
+      <c r="I39" s="44"/>
+      <c r="J39" s="45"/>
     </row>
     <row r="40" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A40" s="30"/>
-      <c r="B40" s="34"/>
-      <c r="C40" s="34"/>
-      <c r="D40" s="34"/>
-      <c r="E40" s="34"/>
-      <c r="F40" s="34"/>
-      <c r="G40" s="34"/>
-      <c r="H40" s="34"/>
-      <c r="I40" s="34"/>
-      <c r="J40" s="35"/>
+      <c r="A40" s="28"/>
+      <c r="B40" s="44"/>
+      <c r="C40" s="44"/>
+      <c r="D40" s="44"/>
+      <c r="E40" s="44"/>
+      <c r="F40" s="44"/>
+      <c r="G40" s="44"/>
+      <c r="H40" s="44"/>
+      <c r="I40" s="44"/>
+      <c r="J40" s="45"/>
     </row>
     <row r="41" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A41" s="30"/>
-      <c r="B41" s="34"/>
-      <c r="C41" s="34"/>
-      <c r="D41" s="34"/>
-      <c r="E41" s="34"/>
-      <c r="F41" s="34"/>
-      <c r="G41" s="34"/>
-      <c r="H41" s="34"/>
-      <c r="I41" s="34"/>
-      <c r="J41" s="35"/>
+      <c r="A41" s="28"/>
+      <c r="B41" s="44"/>
+      <c r="C41" s="44"/>
+      <c r="D41" s="44"/>
+      <c r="E41" s="44"/>
+      <c r="F41" s="44"/>
+      <c r="G41" s="44"/>
+      <c r="H41" s="44"/>
+      <c r="I41" s="44"/>
+      <c r="J41" s="45"/>
     </row>
     <row r="42" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A42" s="30"/>
-      <c r="B42" s="34"/>
-      <c r="C42" s="34"/>
-      <c r="D42" s="34"/>
-      <c r="E42" s="34"/>
-      <c r="F42" s="34"/>
-      <c r="G42" s="34"/>
-      <c r="H42" s="34"/>
-      <c r="I42" s="34"/>
-      <c r="J42" s="35"/>
+      <c r="A42" s="28"/>
+      <c r="B42" s="44"/>
+      <c r="C42" s="44"/>
+      <c r="D42" s="44"/>
+      <c r="E42" s="44"/>
+      <c r="F42" s="44"/>
+      <c r="G42" s="44"/>
+      <c r="H42" s="44"/>
+      <c r="I42" s="44"/>
+      <c r="J42" s="45"/>
     </row>
     <row r="43" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A43" s="30"/>
-      <c r="B43" s="34"/>
-      <c r="C43" s="34"/>
-      <c r="D43" s="34"/>
-      <c r="E43" s="34"/>
-      <c r="F43" s="34"/>
-      <c r="G43" s="34"/>
-      <c r="H43" s="34"/>
-      <c r="I43" s="34"/>
-      <c r="J43" s="35"/>
+      <c r="A43" s="28"/>
+      <c r="B43" s="44"/>
+      <c r="C43" s="44"/>
+      <c r="D43" s="44"/>
+      <c r="E43" s="44"/>
+      <c r="F43" s="44"/>
+      <c r="G43" s="44"/>
+      <c r="H43" s="44"/>
+      <c r="I43" s="44"/>
+      <c r="J43" s="45"/>
     </row>
     <row r="44" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A44" s="30"/>
-      <c r="B44" s="34"/>
-      <c r="C44" s="34"/>
-      <c r="D44" s="34"/>
-      <c r="E44" s="34"/>
-      <c r="F44" s="34"/>
-      <c r="G44" s="34"/>
-      <c r="H44" s="34"/>
-      <c r="I44" s="34"/>
-      <c r="J44" s="35"/>
+      <c r="A44" s="28"/>
+      <c r="B44" s="44"/>
+      <c r="C44" s="44"/>
+      <c r="D44" s="44"/>
+      <c r="E44" s="44"/>
+      <c r="F44" s="44"/>
+      <c r="G44" s="44"/>
+      <c r="H44" s="44"/>
+      <c r="I44" s="44"/>
+      <c r="J44" s="45"/>
     </row>
     <row r="45" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A45" s="30"/>
-      <c r="B45" s="34"/>
-      <c r="C45" s="34"/>
-      <c r="D45" s="34"/>
-      <c r="E45" s="34"/>
-      <c r="F45" s="34"/>
-      <c r="G45" s="34"/>
-      <c r="H45" s="34"/>
-      <c r="I45" s="34"/>
-      <c r="J45" s="35"/>
+      <c r="A45" s="28"/>
+      <c r="B45" s="44"/>
+      <c r="C45" s="44"/>
+      <c r="D45" s="44"/>
+      <c r="E45" s="44"/>
+      <c r="F45" s="44"/>
+      <c r="G45" s="44"/>
+      <c r="H45" s="44"/>
+      <c r="I45" s="44"/>
+      <c r="J45" s="45"/>
     </row>
     <row r="46" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A46" s="30"/>
-      <c r="B46" s="34"/>
-      <c r="C46" s="34"/>
-      <c r="D46" s="34"/>
-      <c r="E46" s="34"/>
-      <c r="F46" s="34"/>
-      <c r="G46" s="34"/>
-      <c r="H46" s="34"/>
-      <c r="I46" s="34"/>
-      <c r="J46" s="35"/>
+      <c r="A46" s="28"/>
+      <c r="B46" s="44"/>
+      <c r="C46" s="44"/>
+      <c r="D46" s="44"/>
+      <c r="E46" s="44"/>
+      <c r="F46" s="44"/>
+      <c r="G46" s="44"/>
+      <c r="H46" s="44"/>
+      <c r="I46" s="44"/>
+      <c r="J46" s="45"/>
     </row>
     <row r="47" spans="1:10" ht="13.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A47" s="31"/>
-      <c r="B47" s="38"/>
-      <c r="C47" s="38"/>
-      <c r="D47" s="38"/>
-      <c r="E47" s="38"/>
-      <c r="F47" s="38"/>
-      <c r="G47" s="38"/>
-      <c r="H47" s="38"/>
-      <c r="I47" s="38"/>
-      <c r="J47" s="39"/>
+      <c r="A47" s="29"/>
+      <c r="B47" s="71"/>
+      <c r="C47" s="71"/>
+      <c r="D47" s="71"/>
+      <c r="E47" s="71"/>
+      <c r="F47" s="71"/>
+      <c r="G47" s="71"/>
+      <c r="H47" s="71"/>
+      <c r="I47" s="71"/>
+      <c r="J47" s="72"/>
     </row>
   </sheetData>
   <mergeCells count="21">
-    <mergeCell ref="B3:J3"/>
-    <mergeCell ref="B4:J4"/>
-    <mergeCell ref="A1:A2"/>
-    <mergeCell ref="B1:D2"/>
-    <mergeCell ref="E1:J2"/>
-    <mergeCell ref="A3:A4"/>
+    <mergeCell ref="B32:J47"/>
+    <mergeCell ref="A31:A47"/>
+    <mergeCell ref="B16:J21"/>
+    <mergeCell ref="A22:A30"/>
+    <mergeCell ref="B23:J30"/>
+    <mergeCell ref="B22:J22"/>
+    <mergeCell ref="B31:J31"/>
     <mergeCell ref="B15:J15"/>
     <mergeCell ref="B8:J8"/>
     <mergeCell ref="A5:A6"/>
@@ -8365,13 +8393,12 @@
     <mergeCell ref="B7:J7"/>
     <mergeCell ref="B9:J14"/>
     <mergeCell ref="A7:A21"/>
-    <mergeCell ref="B32:J47"/>
-    <mergeCell ref="A31:A47"/>
-    <mergeCell ref="B16:J21"/>
-    <mergeCell ref="A22:A30"/>
-    <mergeCell ref="B23:J30"/>
-    <mergeCell ref="B22:J22"/>
-    <mergeCell ref="B31:J31"/>
+    <mergeCell ref="B3:J3"/>
+    <mergeCell ref="B4:J4"/>
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="B1:D2"/>
+    <mergeCell ref="E1:J2"/>
+    <mergeCell ref="A3:A4"/>
   </mergeCells>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.51200000000000001" footer="0.51200000000000001"/>
@@ -8395,6 +8422,15 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="ドキュメント" ma:contentTypeID="0x01010058BEBA3CD4E69545839402B5D4E5400B" ma:contentTypeVersion="13" ma:contentTypeDescription="新しいドキュメントを作成します。" ma:contentTypeScope="" ma:versionID="85fadafb228503a8e253560e9cdffc69">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="88cc3c26-756f-41ab-80ed-43e7289fee5b" xmlns:ns3="55239288-d498-4dd6-9609-491b39ec8fae" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="9785dde68d2e35ac7b66dd15e8e44124" ns2:_="" ns3:_="">
     <xsd:import namespace="88cc3c26-756f-41ab-80ed-43e7289fee5b"/>
@@ -8601,15 +8637,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{82E555AC-3D9C-4ECE-9578-D2E452F320B7}">
   <ds:schemaRefs>
@@ -8630,6 +8657,14 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0843C284-C2B9-4564-B59A-F2FA129FE5C7}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{18D765C5-969E-4095-9A45-9E80C6C2EDED}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -8646,12 +8681,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0843C284-C2B9-4564-B59A-F2FA129FE5C7}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/11_プロジェクト計画書.xlsx
+++ b/11_プロジェクト計画書.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\k_tanoue\Documents\GitHub\tanouesoftware\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1A6AD94D-7C90-4AC5-8CD9-CDBCFFA2E0DF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CCD04FFD-36B4-45F5-B17D-B55E9F471CA6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-90" yWindow="0" windowWidth="9780" windowHeight="10170" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="プロジェクト計画" sheetId="1" r:id="rId1"/>
@@ -1029,25 +1029,40 @@
   </si>
   <si>
     <t>①：概要
+本システムは、地震によって被害を受けた建物について、利用者が建物内部の写真と簡単な質問を登録することで、AIが被害状況を分析し、今後必要となる対応を案内するWebシステムである。分析結果に応じて、修理費用の目安や罹災証明書の申請方法、修理業者などの情報をまとめて確認できる。また、登録した写真や分析結果を履歴として保存し、後から被害状況や復旧状況を確認できるようにする。
 ②：実現可能な機能
+・被害状況写真の撮影・登録
+・AIによる被害状況分析
+・修理費用の目安提示
+・修理業者の情報提示
+・罹災証明書の申請案内
+・被災後の対応案内
+・被害状況分析履歴
 ③：システム規模
-④：システムとの関係</t>
+・個人(事業者・建物管理者を含む)での利用を想定している
+・災害発生直後にはアクセスが集中すると想定される
+④：システムとの関係
+提案先：建物調査を実施している企業、修理業者
+利用者：災害によって建物や室内に被害を受けた個人・事業者・建物管理者</t>
     <rPh sb="2" eb="4">
       <t>ガイヨウ</t>
     </rPh>
-    <rPh sb="8" eb="10">
+    <rPh sb="194" eb="196">
       <t>ジツゲン</t>
     </rPh>
-    <rPh sb="10" eb="12">
+    <rPh sb="196" eb="198">
       <t>カノウ</t>
     </rPh>
-    <rPh sb="13" eb="15">
+    <rPh sb="199" eb="201">
       <t>キノウ</t>
     </rPh>
-    <rPh sb="23" eb="25">
+    <rPh sb="290" eb="292">
       <t>キボ</t>
     </rPh>
-    <rPh sb="35" eb="37">
+    <rPh sb="307" eb="308">
+      <t>フク</t>
+    </rPh>
+    <rPh sb="356" eb="358">
       <t>カンケイ</t>
     </rPh>
     <phoneticPr fontId="1"/>
@@ -2091,29 +2106,155 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="66" xfId="1" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="2" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="2" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="2" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
@@ -2130,197 +2271,137 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="51" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="50" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="50" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="51" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="51" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="50" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="50" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="51" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="21" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="51" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="21" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="176" fontId="7" fillId="0" borderId="48" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="7" fillId="0" borderId="49" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="33" xfId="1" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="7" fillId="0" borderId="48" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="7" fillId="0" borderId="49" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="21" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="34" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="35" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="25" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="16" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="46" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="7" fillId="0" borderId="52" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="7" fillId="0" borderId="53" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="7" fillId="0" borderId="54" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="7" fillId="0" borderId="55" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="7" fillId="0" borderId="58" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="7" fillId="0" borderId="59" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="32" xfId="1" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
@@ -2328,6 +2409,99 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="40" xfId="1" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="22" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="7" fillId="0" borderId="48" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="7" fillId="0" borderId="49" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="23" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="24" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="41" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="42" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="43" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="7" fillId="0" borderId="62" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="7" fillId="0" borderId="63" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="60" xfId="1" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="57" xfId="1" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="23" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="61" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="25" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="16" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="46" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="7" fillId="0" borderId="62" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="7" fillId="0" borderId="63" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="7" fillId="0" borderId="52" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="7" fillId="0" borderId="53" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="23" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="61" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="41" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="42" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="56" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="7" fillId="0" borderId="52" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="7" fillId="0" borderId="53" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="34" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -2337,32 +2511,35 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="25" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="16" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="46" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="34" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="9" fontId="7" fillId="0" borderId="54" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="7" fillId="0" borderId="55" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="36" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="35" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="26" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="25" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="16" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="46" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="9" fontId="7" fillId="0" borderId="58" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="7" fillId="0" borderId="59" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="7" fillId="0" borderId="54" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="7" fillId="0" borderId="55" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="7" fillId="0" borderId="58" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="7" fillId="0" borderId="59" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="34" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -2382,47 +2559,17 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="46" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="7" fillId="0" borderId="54" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="7" fillId="0" borderId="55" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="7" fillId="0" borderId="54" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1">
+    <xf numFmtId="176" fontId="7" fillId="0" borderId="62" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="7" fillId="0" borderId="55" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1">
+    <xf numFmtId="176" fontId="7" fillId="0" borderId="63" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="7" fillId="0" borderId="54" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="7" fillId="0" borderId="55" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="36" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="61" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="26" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="56" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="7" fillId="0" borderId="58" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="7" fillId="0" borderId="59" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="7" fillId="0" borderId="58" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="7" fillId="0" borderId="59" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="7" fillId="0" borderId="58" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="7" fillId="0" borderId="59" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="2" borderId="37" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -2436,15 +2583,6 @@
     <xf numFmtId="0" fontId="8" fillId="2" borderId="22" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="7" fillId="0" borderId="48" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="7" fillId="0" borderId="49" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="21" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="8" fillId="2" borderId="44" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -2468,129 +2606,6 @@
     </xf>
     <xf numFmtId="0" fontId="8" fillId="2" borderId="33" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="21" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="22" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="7" fillId="0" borderId="49" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="7" fillId="0" borderId="48" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="7" fillId="0" borderId="49" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="7" fillId="0" borderId="48" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="7" fillId="0" borderId="62" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="7" fillId="0" borderId="63" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="23" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="61" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="41" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="42" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="56" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="33" xfId="1" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="7" fillId="0" borderId="52" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="7" fillId="0" borderId="53" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="24" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="43" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="7" fillId="0" borderId="62" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="7" fillId="0" borderId="63" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="60" xfId="1" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="57" xfId="1" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="23" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="61" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="9" fontId="7" fillId="0" borderId="62" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="7" fillId="0" borderId="63" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="7" fillId="0" borderId="52" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="7" fillId="0" borderId="53" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="23" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="61" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="41" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="42" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="56" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="7" fillId="0" borderId="52" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="7" fillId="0" borderId="53" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="51" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="21" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
@@ -3416,1567 +3431,1590 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" s="2" customFormat="1" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="68" t="s">
+      <c r="A1" s="27" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="68"/>
-      <c r="C1" s="68"/>
-      <c r="D1" s="68"/>
-      <c r="E1" s="68"/>
-      <c r="F1" s="68"/>
-      <c r="G1" s="68"/>
-      <c r="H1" s="68"/>
-      <c r="I1" s="68"/>
-      <c r="J1" s="68"/>
+      <c r="B1" s="27"/>
+      <c r="C1" s="27"/>
+      <c r="D1" s="27"/>
+      <c r="E1" s="27"/>
+      <c r="F1" s="27"/>
+      <c r="G1" s="27"/>
+      <c r="H1" s="27"/>
+      <c r="I1" s="27"/>
+      <c r="J1" s="27"/>
     </row>
     <row r="2" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="27">
+      <c r="A2" s="28">
         <v>1</v>
       </c>
-      <c r="B2" s="34" t="s">
+      <c r="B2" s="32" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="34"/>
-      <c r="D2" s="34"/>
-      <c r="E2" s="36"/>
-      <c r="F2" s="36"/>
-      <c r="G2" s="36"/>
-      <c r="H2" s="36"/>
-      <c r="I2" s="36"/>
-      <c r="J2" s="37"/>
+      <c r="C2" s="32"/>
+      <c r="D2" s="32"/>
+      <c r="E2" s="78"/>
+      <c r="F2" s="78"/>
+      <c r="G2" s="78"/>
+      <c r="H2" s="78"/>
+      <c r="I2" s="78"/>
+      <c r="J2" s="79"/>
     </row>
     <row r="3" spans="1:10" ht="13.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="31"/>
-      <c r="B3" s="35"/>
-      <c r="C3" s="35"/>
-      <c r="D3" s="35"/>
-      <c r="E3" s="38"/>
-      <c r="F3" s="38"/>
-      <c r="G3" s="38"/>
-      <c r="H3" s="38"/>
-      <c r="I3" s="38"/>
-      <c r="J3" s="39"/>
+      <c r="A3" s="29"/>
+      <c r="B3" s="77"/>
+      <c r="C3" s="77"/>
+      <c r="D3" s="77"/>
+      <c r="E3" s="80"/>
+      <c r="F3" s="80"/>
+      <c r="G3" s="80"/>
+      <c r="H3" s="80"/>
+      <c r="I3" s="80"/>
+      <c r="J3" s="81"/>
     </row>
     <row r="4" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="27">
+      <c r="A4" s="28">
         <v>2</v>
       </c>
-      <c r="B4" s="32" t="s">
+      <c r="B4" s="42" t="s">
         <v>2</v>
       </c>
-      <c r="C4" s="32"/>
-      <c r="D4" s="32"/>
-      <c r="E4" s="32"/>
-      <c r="F4" s="32"/>
-      <c r="G4" s="32"/>
-      <c r="H4" s="32"/>
-      <c r="I4" s="32"/>
-      <c r="J4" s="33"/>
+      <c r="C4" s="42"/>
+      <c r="D4" s="42"/>
+      <c r="E4" s="42"/>
+      <c r="F4" s="42"/>
+      <c r="G4" s="42"/>
+      <c r="H4" s="42"/>
+      <c r="I4" s="42"/>
+      <c r="J4" s="43"/>
     </row>
     <row r="5" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="28"/>
-      <c r="B5" s="46" t="s">
+      <c r="A5" s="30"/>
+      <c r="B5" s="45" t="s">
         <v>3</v>
       </c>
-      <c r="C5" s="46"/>
-      <c r="D5" s="46"/>
-      <c r="E5" s="46"/>
-      <c r="F5" s="46"/>
-      <c r="G5" s="46"/>
-      <c r="H5" s="46"/>
-      <c r="I5" s="46"/>
-      <c r="J5" s="47"/>
+      <c r="C5" s="45"/>
+      <c r="D5" s="45"/>
+      <c r="E5" s="45"/>
+      <c r="F5" s="45"/>
+      <c r="G5" s="45"/>
+      <c r="H5" s="45"/>
+      <c r="I5" s="45"/>
+      <c r="J5" s="46"/>
     </row>
     <row r="6" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="28"/>
-      <c r="B6" s="46"/>
-      <c r="C6" s="46"/>
-      <c r="D6" s="46"/>
-      <c r="E6" s="46"/>
-      <c r="F6" s="46"/>
-      <c r="G6" s="46"/>
-      <c r="H6" s="46"/>
-      <c r="I6" s="46"/>
-      <c r="J6" s="47"/>
+      <c r="A6" s="30"/>
+      <c r="B6" s="45"/>
+      <c r="C6" s="45"/>
+      <c r="D6" s="45"/>
+      <c r="E6" s="45"/>
+      <c r="F6" s="45"/>
+      <c r="G6" s="45"/>
+      <c r="H6" s="45"/>
+      <c r="I6" s="45"/>
+      <c r="J6" s="46"/>
     </row>
     <row r="7" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="28"/>
-      <c r="B7" s="48"/>
-      <c r="C7" s="48"/>
-      <c r="D7" s="48"/>
-      <c r="E7" s="48"/>
-      <c r="F7" s="48"/>
-      <c r="G7" s="48"/>
-      <c r="H7" s="48"/>
-      <c r="I7" s="48"/>
-      <c r="J7" s="49"/>
+      <c r="A7" s="30"/>
+      <c r="B7" s="47"/>
+      <c r="C7" s="47"/>
+      <c r="D7" s="47"/>
+      <c r="E7" s="47"/>
+      <c r="F7" s="47"/>
+      <c r="G7" s="47"/>
+      <c r="H7" s="47"/>
+      <c r="I7" s="47"/>
+      <c r="J7" s="48"/>
     </row>
     <row r="8" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="28"/>
-      <c r="B8" s="61" t="s">
+      <c r="A8" s="30"/>
+      <c r="B8" s="76" t="s">
         <v>105</v>
       </c>
-      <c r="C8" s="62"/>
-      <c r="D8" s="62"/>
-      <c r="E8" s="62"/>
-      <c r="F8" s="62"/>
-      <c r="G8" s="62"/>
-      <c r="H8" s="62"/>
-      <c r="I8" s="62"/>
-      <c r="J8" s="63"/>
+      <c r="C8" s="52"/>
+      <c r="D8" s="52"/>
+      <c r="E8" s="52"/>
+      <c r="F8" s="52"/>
+      <c r="G8" s="52"/>
+      <c r="H8" s="52"/>
+      <c r="I8" s="52"/>
+      <c r="J8" s="53"/>
     </row>
     <row r="9" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="28"/>
-      <c r="B9" s="64"/>
-      <c r="C9" s="65"/>
-      <c r="D9" s="65"/>
-      <c r="E9" s="65"/>
-      <c r="F9" s="65"/>
-      <c r="G9" s="65"/>
-      <c r="H9" s="65"/>
-      <c r="I9" s="65"/>
-      <c r="J9" s="66"/>
+      <c r="A9" s="30"/>
+      <c r="B9" s="54"/>
+      <c r="C9" s="55"/>
+      <c r="D9" s="55"/>
+      <c r="E9" s="55"/>
+      <c r="F9" s="55"/>
+      <c r="G9" s="55"/>
+      <c r="H9" s="55"/>
+      <c r="I9" s="55"/>
+      <c r="J9" s="56"/>
     </row>
     <row r="10" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="28"/>
-      <c r="B10" s="64"/>
-      <c r="C10" s="65"/>
-      <c r="D10" s="65"/>
-      <c r="E10" s="65"/>
-      <c r="F10" s="65"/>
-      <c r="G10" s="65"/>
-      <c r="H10" s="65"/>
-      <c r="I10" s="65"/>
-      <c r="J10" s="66"/>
+      <c r="A10" s="30"/>
+      <c r="B10" s="54"/>
+      <c r="C10" s="55"/>
+      <c r="D10" s="55"/>
+      <c r="E10" s="55"/>
+      <c r="F10" s="55"/>
+      <c r="G10" s="55"/>
+      <c r="H10" s="55"/>
+      <c r="I10" s="55"/>
+      <c r="J10" s="56"/>
     </row>
     <row r="11" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="28"/>
-      <c r="B11" s="64"/>
-      <c r="C11" s="65"/>
-      <c r="D11" s="65"/>
-      <c r="E11" s="65"/>
-      <c r="F11" s="65"/>
-      <c r="G11" s="65"/>
-      <c r="H11" s="65"/>
-      <c r="I11" s="65"/>
-      <c r="J11" s="66"/>
+      <c r="A11" s="30"/>
+      <c r="B11" s="54"/>
+      <c r="C11" s="55"/>
+      <c r="D11" s="55"/>
+      <c r="E11" s="55"/>
+      <c r="F11" s="55"/>
+      <c r="G11" s="55"/>
+      <c r="H11" s="55"/>
+      <c r="I11" s="55"/>
+      <c r="J11" s="56"/>
     </row>
     <row r="12" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="28"/>
-      <c r="B12" s="64"/>
-      <c r="C12" s="65"/>
-      <c r="D12" s="65"/>
-      <c r="E12" s="65"/>
-      <c r="F12" s="65"/>
-      <c r="G12" s="65"/>
-      <c r="H12" s="65"/>
-      <c r="I12" s="65"/>
-      <c r="J12" s="66"/>
+      <c r="A12" s="30"/>
+      <c r="B12" s="54"/>
+      <c r="C12" s="55"/>
+      <c r="D12" s="55"/>
+      <c r="E12" s="55"/>
+      <c r="F12" s="55"/>
+      <c r="G12" s="55"/>
+      <c r="H12" s="55"/>
+      <c r="I12" s="55"/>
+      <c r="J12" s="56"/>
     </row>
     <row r="13" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="28"/>
-      <c r="B13" s="64"/>
-      <c r="C13" s="65"/>
-      <c r="D13" s="65"/>
-      <c r="E13" s="65"/>
-      <c r="F13" s="65"/>
-      <c r="G13" s="65"/>
-      <c r="H13" s="65"/>
-      <c r="I13" s="65"/>
-      <c r="J13" s="66"/>
+      <c r="A13" s="30"/>
+      <c r="B13" s="54"/>
+      <c r="C13" s="55"/>
+      <c r="D13" s="55"/>
+      <c r="E13" s="55"/>
+      <c r="F13" s="55"/>
+      <c r="G13" s="55"/>
+      <c r="H13" s="55"/>
+      <c r="I13" s="55"/>
+      <c r="J13" s="56"/>
     </row>
     <row r="14" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A14" s="28"/>
-      <c r="B14" s="64"/>
-      <c r="C14" s="65"/>
-      <c r="D14" s="65"/>
-      <c r="E14" s="65"/>
-      <c r="F14" s="65"/>
-      <c r="G14" s="65"/>
-      <c r="H14" s="65"/>
-      <c r="I14" s="65"/>
-      <c r="J14" s="66"/>
+      <c r="A14" s="30"/>
+      <c r="B14" s="54"/>
+      <c r="C14" s="55"/>
+      <c r="D14" s="55"/>
+      <c r="E14" s="55"/>
+      <c r="F14" s="55"/>
+      <c r="G14" s="55"/>
+      <c r="H14" s="55"/>
+      <c r="I14" s="55"/>
+      <c r="J14" s="56"/>
     </row>
     <row r="15" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A15" s="28"/>
-      <c r="B15" s="64"/>
-      <c r="C15" s="65"/>
-      <c r="D15" s="65"/>
-      <c r="E15" s="65"/>
-      <c r="F15" s="65"/>
-      <c r="G15" s="65"/>
-      <c r="H15" s="65"/>
-      <c r="I15" s="65"/>
-      <c r="J15" s="66"/>
+      <c r="A15" s="30"/>
+      <c r="B15" s="54"/>
+      <c r="C15" s="55"/>
+      <c r="D15" s="55"/>
+      <c r="E15" s="55"/>
+      <c r="F15" s="55"/>
+      <c r="G15" s="55"/>
+      <c r="H15" s="55"/>
+      <c r="I15" s="55"/>
+      <c r="J15" s="56"/>
     </row>
     <row r="16" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A16" s="28"/>
-      <c r="B16" s="64"/>
-      <c r="C16" s="65"/>
-      <c r="D16" s="65"/>
-      <c r="E16" s="65"/>
-      <c r="F16" s="65"/>
-      <c r="G16" s="65"/>
-      <c r="H16" s="65"/>
-      <c r="I16" s="65"/>
-      <c r="J16" s="66"/>
+      <c r="A16" s="30"/>
+      <c r="B16" s="54"/>
+      <c r="C16" s="55"/>
+      <c r="D16" s="55"/>
+      <c r="E16" s="55"/>
+      <c r="F16" s="55"/>
+      <c r="G16" s="55"/>
+      <c r="H16" s="55"/>
+      <c r="I16" s="55"/>
+      <c r="J16" s="56"/>
     </row>
     <row r="17" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A17" s="31"/>
-      <c r="B17" s="64"/>
-      <c r="C17" s="65"/>
-      <c r="D17" s="65"/>
-      <c r="E17" s="65"/>
-      <c r="F17" s="65"/>
-      <c r="G17" s="65"/>
-      <c r="H17" s="65"/>
-      <c r="I17" s="65"/>
-      <c r="J17" s="66"/>
+      <c r="A17" s="29"/>
+      <c r="B17" s="54"/>
+      <c r="C17" s="55"/>
+      <c r="D17" s="55"/>
+      <c r="E17" s="55"/>
+      <c r="F17" s="55"/>
+      <c r="G17" s="55"/>
+      <c r="H17" s="55"/>
+      <c r="I17" s="55"/>
+      <c r="J17" s="56"/>
     </row>
     <row r="18" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A18" s="31"/>
-      <c r="B18" s="64"/>
-      <c r="C18" s="65"/>
-      <c r="D18" s="65"/>
-      <c r="E18" s="65"/>
-      <c r="F18" s="65"/>
-      <c r="G18" s="65"/>
-      <c r="H18" s="65"/>
-      <c r="I18" s="65"/>
-      <c r="J18" s="66"/>
+      <c r="A18" s="29"/>
+      <c r="B18" s="54"/>
+      <c r="C18" s="55"/>
+      <c r="D18" s="55"/>
+      <c r="E18" s="55"/>
+      <c r="F18" s="55"/>
+      <c r="G18" s="55"/>
+      <c r="H18" s="55"/>
+      <c r="I18" s="55"/>
+      <c r="J18" s="56"/>
     </row>
     <row r="19" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A19" s="31"/>
-      <c r="B19" s="64"/>
-      <c r="C19" s="65"/>
-      <c r="D19" s="65"/>
-      <c r="E19" s="65"/>
-      <c r="F19" s="65"/>
-      <c r="G19" s="65"/>
-      <c r="H19" s="65"/>
-      <c r="I19" s="65"/>
-      <c r="J19" s="66"/>
+      <c r="A19" s="29"/>
+      <c r="B19" s="54"/>
+      <c r="C19" s="55"/>
+      <c r="D19" s="55"/>
+      <c r="E19" s="55"/>
+      <c r="F19" s="55"/>
+      <c r="G19" s="55"/>
+      <c r="H19" s="55"/>
+      <c r="I19" s="55"/>
+      <c r="J19" s="56"/>
     </row>
     <row r="20" spans="1:10" ht="13.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="31"/>
-      <c r="B20" s="64"/>
-      <c r="C20" s="65"/>
-      <c r="D20" s="65"/>
-      <c r="E20" s="65"/>
-      <c r="F20" s="65"/>
-      <c r="G20" s="65"/>
-      <c r="H20" s="65"/>
-      <c r="I20" s="65"/>
-      <c r="J20" s="66"/>
+      <c r="A20" s="29"/>
+      <c r="B20" s="54"/>
+      <c r="C20" s="55"/>
+      <c r="D20" s="55"/>
+      <c r="E20" s="55"/>
+      <c r="F20" s="55"/>
+      <c r="G20" s="55"/>
+      <c r="H20" s="55"/>
+      <c r="I20" s="55"/>
+      <c r="J20" s="56"/>
     </row>
     <row r="21" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A21" s="27">
+      <c r="A21" s="28">
         <v>3</v>
       </c>
-      <c r="B21" s="32" t="s">
+      <c r="B21" s="42" t="s">
         <v>4</v>
       </c>
-      <c r="C21" s="32"/>
-      <c r="D21" s="32"/>
-      <c r="E21" s="32"/>
-      <c r="F21" s="32"/>
-      <c r="G21" s="32"/>
-      <c r="H21" s="32"/>
-      <c r="I21" s="32"/>
-      <c r="J21" s="33"/>
+      <c r="C21" s="42"/>
+      <c r="D21" s="42"/>
+      <c r="E21" s="42"/>
+      <c r="F21" s="42"/>
+      <c r="G21" s="42"/>
+      <c r="H21" s="42"/>
+      <c r="I21" s="42"/>
+      <c r="J21" s="43"/>
     </row>
     <row r="22" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A22" s="28"/>
-      <c r="B22" s="50" t="s">
+      <c r="A22" s="30"/>
+      <c r="B22" s="64" t="s">
         <v>5</v>
       </c>
-      <c r="C22" s="51"/>
-      <c r="D22" s="51"/>
-      <c r="E22" s="51"/>
-      <c r="F22" s="51"/>
-      <c r="G22" s="51"/>
-      <c r="H22" s="51"/>
-      <c r="I22" s="51"/>
-      <c r="J22" s="52"/>
+      <c r="C22" s="65"/>
+      <c r="D22" s="65"/>
+      <c r="E22" s="65"/>
+      <c r="F22" s="65"/>
+      <c r="G22" s="65"/>
+      <c r="H22" s="65"/>
+      <c r="I22" s="65"/>
+      <c r="J22" s="66"/>
     </row>
     <row r="23" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A23" s="28"/>
-      <c r="B23" s="50"/>
-      <c r="C23" s="51"/>
-      <c r="D23" s="51"/>
-      <c r="E23" s="51"/>
-      <c r="F23" s="51"/>
-      <c r="G23" s="51"/>
-      <c r="H23" s="51"/>
-      <c r="I23" s="51"/>
-      <c r="J23" s="52"/>
+      <c r="A23" s="30"/>
+      <c r="B23" s="64"/>
+      <c r="C23" s="65"/>
+      <c r="D23" s="65"/>
+      <c r="E23" s="65"/>
+      <c r="F23" s="65"/>
+      <c r="G23" s="65"/>
+      <c r="H23" s="65"/>
+      <c r="I23" s="65"/>
+      <c r="J23" s="66"/>
     </row>
     <row r="24" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A24" s="28"/>
-      <c r="B24" s="50"/>
-      <c r="C24" s="51"/>
-      <c r="D24" s="51"/>
-      <c r="E24" s="51"/>
-      <c r="F24" s="51"/>
-      <c r="G24" s="51"/>
-      <c r="H24" s="51"/>
-      <c r="I24" s="51"/>
-      <c r="J24" s="52"/>
+      <c r="A24" s="30"/>
+      <c r="B24" s="64"/>
+      <c r="C24" s="65"/>
+      <c r="D24" s="65"/>
+      <c r="E24" s="65"/>
+      <c r="F24" s="65"/>
+      <c r="G24" s="65"/>
+      <c r="H24" s="65"/>
+      <c r="I24" s="65"/>
+      <c r="J24" s="66"/>
     </row>
     <row r="25" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A25" s="28"/>
-      <c r="B25" s="53"/>
-      <c r="C25" s="54"/>
-      <c r="D25" s="54"/>
-      <c r="E25" s="54"/>
-      <c r="F25" s="54"/>
-      <c r="G25" s="54"/>
-      <c r="H25" s="54"/>
-      <c r="I25" s="54"/>
-      <c r="J25" s="55"/>
+      <c r="A25" s="30"/>
+      <c r="B25" s="67"/>
+      <c r="C25" s="68"/>
+      <c r="D25" s="68"/>
+      <c r="E25" s="68"/>
+      <c r="F25" s="68"/>
+      <c r="G25" s="68"/>
+      <c r="H25" s="68"/>
+      <c r="I25" s="68"/>
+      <c r="J25" s="69"/>
     </row>
     <row r="26" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A26" s="28"/>
-      <c r="B26" s="56" t="s">
+      <c r="A26" s="30"/>
+      <c r="B26" s="70" t="s">
         <v>106</v>
       </c>
-      <c r="C26" s="56"/>
-      <c r="D26" s="56"/>
-      <c r="E26" s="56"/>
-      <c r="F26" s="56"/>
-      <c r="G26" s="56"/>
-      <c r="H26" s="56"/>
-      <c r="I26" s="56"/>
-      <c r="J26" s="57"/>
+      <c r="C26" s="70"/>
+      <c r="D26" s="70"/>
+      <c r="E26" s="70"/>
+      <c r="F26" s="70"/>
+      <c r="G26" s="70"/>
+      <c r="H26" s="70"/>
+      <c r="I26" s="70"/>
+      <c r="J26" s="71"/>
     </row>
     <row r="27" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A27" s="28"/>
-      <c r="B27" s="56"/>
-      <c r="C27" s="56"/>
-      <c r="D27" s="56"/>
-      <c r="E27" s="56"/>
-      <c r="F27" s="56"/>
-      <c r="G27" s="56"/>
-      <c r="H27" s="56"/>
-      <c r="I27" s="56"/>
-      <c r="J27" s="57"/>
+      <c r="A27" s="30"/>
+      <c r="B27" s="70"/>
+      <c r="C27" s="70"/>
+      <c r="D27" s="70"/>
+      <c r="E27" s="70"/>
+      <c r="F27" s="70"/>
+      <c r="G27" s="70"/>
+      <c r="H27" s="70"/>
+      <c r="I27" s="70"/>
+      <c r="J27" s="71"/>
     </row>
     <row r="28" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A28" s="28"/>
-      <c r="B28" s="56"/>
-      <c r="C28" s="56"/>
-      <c r="D28" s="56"/>
-      <c r="E28" s="56"/>
-      <c r="F28" s="56"/>
-      <c r="G28" s="56"/>
-      <c r="H28" s="56"/>
-      <c r="I28" s="56"/>
-      <c r="J28" s="57"/>
+      <c r="A28" s="30"/>
+      <c r="B28" s="70"/>
+      <c r="C28" s="70"/>
+      <c r="D28" s="70"/>
+      <c r="E28" s="70"/>
+      <c r="F28" s="70"/>
+      <c r="G28" s="70"/>
+      <c r="H28" s="70"/>
+      <c r="I28" s="70"/>
+      <c r="J28" s="71"/>
     </row>
     <row r="29" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A29" s="28"/>
-      <c r="B29" s="56"/>
-      <c r="C29" s="56"/>
-      <c r="D29" s="56"/>
-      <c r="E29" s="56"/>
-      <c r="F29" s="56"/>
-      <c r="G29" s="56"/>
-      <c r="H29" s="56"/>
-      <c r="I29" s="56"/>
-      <c r="J29" s="57"/>
+      <c r="A29" s="30"/>
+      <c r="B29" s="70"/>
+      <c r="C29" s="70"/>
+      <c r="D29" s="70"/>
+      <c r="E29" s="70"/>
+      <c r="F29" s="70"/>
+      <c r="G29" s="70"/>
+      <c r="H29" s="70"/>
+      <c r="I29" s="70"/>
+      <c r="J29" s="71"/>
     </row>
     <row r="30" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A30" s="28"/>
-      <c r="B30" s="56"/>
-      <c r="C30" s="56"/>
-      <c r="D30" s="56"/>
-      <c r="E30" s="56"/>
-      <c r="F30" s="56"/>
-      <c r="G30" s="56"/>
-      <c r="H30" s="56"/>
-      <c r="I30" s="56"/>
-      <c r="J30" s="57"/>
+      <c r="A30" s="30"/>
+      <c r="B30" s="70"/>
+      <c r="C30" s="70"/>
+      <c r="D30" s="70"/>
+      <c r="E30" s="70"/>
+      <c r="F30" s="70"/>
+      <c r="G30" s="70"/>
+      <c r="H30" s="70"/>
+      <c r="I30" s="70"/>
+      <c r="J30" s="71"/>
     </row>
     <row r="31" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A31" s="28"/>
-      <c r="B31" s="56"/>
-      <c r="C31" s="56"/>
-      <c r="D31" s="56"/>
-      <c r="E31" s="56"/>
-      <c r="F31" s="56"/>
-      <c r="G31" s="56"/>
-      <c r="H31" s="56"/>
-      <c r="I31" s="56"/>
-      <c r="J31" s="57"/>
+      <c r="A31" s="30"/>
+      <c r="B31" s="70"/>
+      <c r="C31" s="70"/>
+      <c r="D31" s="70"/>
+      <c r="E31" s="70"/>
+      <c r="F31" s="70"/>
+      <c r="G31" s="70"/>
+      <c r="H31" s="70"/>
+      <c r="I31" s="70"/>
+      <c r="J31" s="71"/>
     </row>
     <row r="32" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A32" s="28"/>
-      <c r="B32" s="56"/>
-      <c r="C32" s="56"/>
-      <c r="D32" s="56"/>
-      <c r="E32" s="56"/>
-      <c r="F32" s="56"/>
-      <c r="G32" s="56"/>
-      <c r="H32" s="56"/>
-      <c r="I32" s="56"/>
-      <c r="J32" s="57"/>
+      <c r="A32" s="30"/>
+      <c r="B32" s="70"/>
+      <c r="C32" s="70"/>
+      <c r="D32" s="70"/>
+      <c r="E32" s="70"/>
+      <c r="F32" s="70"/>
+      <c r="G32" s="70"/>
+      <c r="H32" s="70"/>
+      <c r="I32" s="70"/>
+      <c r="J32" s="71"/>
     </row>
     <row r="33" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A33" s="28"/>
-      <c r="B33" s="56"/>
-      <c r="C33" s="56"/>
-      <c r="D33" s="56"/>
-      <c r="E33" s="56"/>
-      <c r="F33" s="56"/>
-      <c r="G33" s="56"/>
-      <c r="H33" s="56"/>
-      <c r="I33" s="56"/>
-      <c r="J33" s="57"/>
+      <c r="A33" s="30"/>
+      <c r="B33" s="70"/>
+      <c r="C33" s="70"/>
+      <c r="D33" s="70"/>
+      <c r="E33" s="70"/>
+      <c r="F33" s="70"/>
+      <c r="G33" s="70"/>
+      <c r="H33" s="70"/>
+      <c r="I33" s="70"/>
+      <c r="J33" s="71"/>
     </row>
     <row r="34" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A34" s="28"/>
-      <c r="B34" s="56"/>
-      <c r="C34" s="56"/>
-      <c r="D34" s="56"/>
-      <c r="E34" s="56"/>
-      <c r="F34" s="56"/>
-      <c r="G34" s="56"/>
-      <c r="H34" s="56"/>
-      <c r="I34" s="56"/>
-      <c r="J34" s="57"/>
+      <c r="A34" s="30"/>
+      <c r="B34" s="70"/>
+      <c r="C34" s="70"/>
+      <c r="D34" s="70"/>
+      <c r="E34" s="70"/>
+      <c r="F34" s="70"/>
+      <c r="G34" s="70"/>
+      <c r="H34" s="70"/>
+      <c r="I34" s="70"/>
+      <c r="J34" s="71"/>
     </row>
     <row r="35" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A35" s="28"/>
-      <c r="B35" s="56"/>
-      <c r="C35" s="56"/>
-      <c r="D35" s="56"/>
-      <c r="E35" s="56"/>
-      <c r="F35" s="56"/>
-      <c r="G35" s="56"/>
-      <c r="H35" s="56"/>
-      <c r="I35" s="56"/>
-      <c r="J35" s="57"/>
+      <c r="A35" s="30"/>
+      <c r="B35" s="70"/>
+      <c r="C35" s="70"/>
+      <c r="D35" s="70"/>
+      <c r="E35" s="70"/>
+      <c r="F35" s="70"/>
+      <c r="G35" s="70"/>
+      <c r="H35" s="70"/>
+      <c r="I35" s="70"/>
+      <c r="J35" s="71"/>
     </row>
     <row r="36" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A36" s="28"/>
-      <c r="B36" s="56"/>
-      <c r="C36" s="56"/>
-      <c r="D36" s="56"/>
-      <c r="E36" s="56"/>
-      <c r="F36" s="56"/>
-      <c r="G36" s="56"/>
-      <c r="H36" s="56"/>
-      <c r="I36" s="56"/>
-      <c r="J36" s="57"/>
+      <c r="A36" s="30"/>
+      <c r="B36" s="70"/>
+      <c r="C36" s="70"/>
+      <c r="D36" s="70"/>
+      <c r="E36" s="70"/>
+      <c r="F36" s="70"/>
+      <c r="G36" s="70"/>
+      <c r="H36" s="70"/>
+      <c r="I36" s="70"/>
+      <c r="J36" s="71"/>
     </row>
     <row r="37" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A37" s="28"/>
-      <c r="B37" s="56"/>
-      <c r="C37" s="56"/>
-      <c r="D37" s="56"/>
-      <c r="E37" s="56"/>
-      <c r="F37" s="56"/>
-      <c r="G37" s="56"/>
-      <c r="H37" s="56"/>
-      <c r="I37" s="56"/>
-      <c r="J37" s="57"/>
+      <c r="A37" s="30"/>
+      <c r="B37" s="70"/>
+      <c r="C37" s="70"/>
+      <c r="D37" s="70"/>
+      <c r="E37" s="70"/>
+      <c r="F37" s="70"/>
+      <c r="G37" s="70"/>
+      <c r="H37" s="70"/>
+      <c r="I37" s="70"/>
+      <c r="J37" s="71"/>
     </row>
     <row r="38" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A38" s="28"/>
-      <c r="B38" s="56"/>
-      <c r="C38" s="56"/>
-      <c r="D38" s="56"/>
-      <c r="E38" s="56"/>
-      <c r="F38" s="56"/>
-      <c r="G38" s="56"/>
-      <c r="H38" s="56"/>
-      <c r="I38" s="56"/>
-      <c r="J38" s="57"/>
+      <c r="A38" s="30"/>
+      <c r="B38" s="70"/>
+      <c r="C38" s="70"/>
+      <c r="D38" s="70"/>
+      <c r="E38" s="70"/>
+      <c r="F38" s="70"/>
+      <c r="G38" s="70"/>
+      <c r="H38" s="70"/>
+      <c r="I38" s="70"/>
+      <c r="J38" s="71"/>
     </row>
     <row r="39" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A39" s="28"/>
-      <c r="B39" s="56"/>
-      <c r="C39" s="56"/>
-      <c r="D39" s="56"/>
-      <c r="E39" s="56"/>
-      <c r="F39" s="56"/>
-      <c r="G39" s="56"/>
-      <c r="H39" s="56"/>
-      <c r="I39" s="56"/>
-      <c r="J39" s="57"/>
+      <c r="A39" s="30"/>
+      <c r="B39" s="70"/>
+      <c r="C39" s="70"/>
+      <c r="D39" s="70"/>
+      <c r="E39" s="70"/>
+      <c r="F39" s="70"/>
+      <c r="G39" s="70"/>
+      <c r="H39" s="70"/>
+      <c r="I39" s="70"/>
+      <c r="J39" s="71"/>
     </row>
     <row r="40" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A40" s="28"/>
-      <c r="B40" s="56"/>
-      <c r="C40" s="56"/>
-      <c r="D40" s="56"/>
-      <c r="E40" s="56"/>
-      <c r="F40" s="56"/>
-      <c r="G40" s="56"/>
-      <c r="H40" s="56"/>
-      <c r="I40" s="56"/>
-      <c r="J40" s="57"/>
+      <c r="A40" s="30"/>
+      <c r="B40" s="70"/>
+      <c r="C40" s="70"/>
+      <c r="D40" s="70"/>
+      <c r="E40" s="70"/>
+      <c r="F40" s="70"/>
+      <c r="G40" s="70"/>
+      <c r="H40" s="70"/>
+      <c r="I40" s="70"/>
+      <c r="J40" s="71"/>
     </row>
     <row r="41" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A41" s="28"/>
-      <c r="B41" s="56"/>
-      <c r="C41" s="56"/>
-      <c r="D41" s="56"/>
-      <c r="E41" s="56"/>
-      <c r="F41" s="56"/>
-      <c r="G41" s="56"/>
-      <c r="H41" s="56"/>
-      <c r="I41" s="56"/>
-      <c r="J41" s="57"/>
+      <c r="A41" s="30"/>
+      <c r="B41" s="70"/>
+      <c r="C41" s="70"/>
+      <c r="D41" s="70"/>
+      <c r="E41" s="70"/>
+      <c r="F41" s="70"/>
+      <c r="G41" s="70"/>
+      <c r="H41" s="70"/>
+      <c r="I41" s="70"/>
+      <c r="J41" s="71"/>
     </row>
     <row r="42" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A42" s="28"/>
-      <c r="B42" s="56"/>
-      <c r="C42" s="56"/>
-      <c r="D42" s="56"/>
-      <c r="E42" s="56"/>
-      <c r="F42" s="56"/>
-      <c r="G42" s="56"/>
-      <c r="H42" s="56"/>
-      <c r="I42" s="56"/>
-      <c r="J42" s="57"/>
+      <c r="A42" s="30"/>
+      <c r="B42" s="70"/>
+      <c r="C42" s="70"/>
+      <c r="D42" s="70"/>
+      <c r="E42" s="70"/>
+      <c r="F42" s="70"/>
+      <c r="G42" s="70"/>
+      <c r="H42" s="70"/>
+      <c r="I42" s="70"/>
+      <c r="J42" s="71"/>
     </row>
     <row r="43" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A43" s="28"/>
-      <c r="B43" s="56"/>
-      <c r="C43" s="56"/>
-      <c r="D43" s="56"/>
-      <c r="E43" s="56"/>
-      <c r="F43" s="56"/>
-      <c r="G43" s="56"/>
-      <c r="H43" s="56"/>
-      <c r="I43" s="56"/>
-      <c r="J43" s="57"/>
+      <c r="A43" s="30"/>
+      <c r="B43" s="70"/>
+      <c r="C43" s="70"/>
+      <c r="D43" s="70"/>
+      <c r="E43" s="70"/>
+      <c r="F43" s="70"/>
+      <c r="G43" s="70"/>
+      <c r="H43" s="70"/>
+      <c r="I43" s="70"/>
+      <c r="J43" s="71"/>
     </row>
     <row r="44" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A44" s="28"/>
-      <c r="B44" s="56"/>
-      <c r="C44" s="56"/>
-      <c r="D44" s="56"/>
-      <c r="E44" s="56"/>
-      <c r="F44" s="56"/>
-      <c r="G44" s="56"/>
-      <c r="H44" s="56"/>
-      <c r="I44" s="56"/>
-      <c r="J44" s="57"/>
+      <c r="A44" s="30"/>
+      <c r="B44" s="70"/>
+      <c r="C44" s="70"/>
+      <c r="D44" s="70"/>
+      <c r="E44" s="70"/>
+      <c r="F44" s="70"/>
+      <c r="G44" s="70"/>
+      <c r="H44" s="70"/>
+      <c r="I44" s="70"/>
+      <c r="J44" s="71"/>
     </row>
     <row r="45" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A45" s="28"/>
-      <c r="B45" s="56"/>
-      <c r="C45" s="56"/>
-      <c r="D45" s="56"/>
-      <c r="E45" s="56"/>
-      <c r="F45" s="56"/>
-      <c r="G45" s="56"/>
-      <c r="H45" s="56"/>
-      <c r="I45" s="56"/>
-      <c r="J45" s="57"/>
+      <c r="A45" s="30"/>
+      <c r="B45" s="70"/>
+      <c r="C45" s="70"/>
+      <c r="D45" s="70"/>
+      <c r="E45" s="70"/>
+      <c r="F45" s="70"/>
+      <c r="G45" s="70"/>
+      <c r="H45" s="70"/>
+      <c r="I45" s="70"/>
+      <c r="J45" s="71"/>
     </row>
     <row r="46" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A46" s="28"/>
-      <c r="B46" s="56"/>
-      <c r="C46" s="56"/>
-      <c r="D46" s="56"/>
-      <c r="E46" s="56"/>
-      <c r="F46" s="56"/>
-      <c r="G46" s="56"/>
-      <c r="H46" s="56"/>
-      <c r="I46" s="56"/>
-      <c r="J46" s="57"/>
+      <c r="A46" s="30"/>
+      <c r="B46" s="70"/>
+      <c r="C46" s="70"/>
+      <c r="D46" s="70"/>
+      <c r="E46" s="70"/>
+      <c r="F46" s="70"/>
+      <c r="G46" s="70"/>
+      <c r="H46" s="70"/>
+      <c r="I46" s="70"/>
+      <c r="J46" s="71"/>
     </row>
     <row r="47" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A47" s="28"/>
-      <c r="B47" s="56"/>
-      <c r="C47" s="56"/>
-      <c r="D47" s="56"/>
-      <c r="E47" s="56"/>
-      <c r="F47" s="56"/>
-      <c r="G47" s="56"/>
-      <c r="H47" s="56"/>
-      <c r="I47" s="56"/>
-      <c r="J47" s="57"/>
+      <c r="A47" s="30"/>
+      <c r="B47" s="70"/>
+      <c r="C47" s="70"/>
+      <c r="D47" s="70"/>
+      <c r="E47" s="70"/>
+      <c r="F47" s="70"/>
+      <c r="G47" s="70"/>
+      <c r="H47" s="70"/>
+      <c r="I47" s="70"/>
+      <c r="J47" s="71"/>
     </row>
     <row r="48" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A48" s="28"/>
-      <c r="B48" s="56"/>
-      <c r="C48" s="56"/>
-      <c r="D48" s="56"/>
-      <c r="E48" s="56"/>
-      <c r="F48" s="56"/>
-      <c r="G48" s="56"/>
-      <c r="H48" s="56"/>
-      <c r="I48" s="56"/>
-      <c r="J48" s="57"/>
+      <c r="A48" s="30"/>
+      <c r="B48" s="70"/>
+      <c r="C48" s="70"/>
+      <c r="D48" s="70"/>
+      <c r="E48" s="70"/>
+      <c r="F48" s="70"/>
+      <c r="G48" s="70"/>
+      <c r="H48" s="70"/>
+      <c r="I48" s="70"/>
+      <c r="J48" s="71"/>
     </row>
     <row r="49" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A49" s="28"/>
-      <c r="B49" s="56"/>
-      <c r="C49" s="56"/>
-      <c r="D49" s="56"/>
-      <c r="E49" s="56"/>
-      <c r="F49" s="56"/>
-      <c r="G49" s="56"/>
-      <c r="H49" s="56"/>
-      <c r="I49" s="56"/>
-      <c r="J49" s="57"/>
+      <c r="A49" s="30"/>
+      <c r="B49" s="70"/>
+      <c r="C49" s="70"/>
+      <c r="D49" s="70"/>
+      <c r="E49" s="70"/>
+      <c r="F49" s="70"/>
+      <c r="G49" s="70"/>
+      <c r="H49" s="70"/>
+      <c r="I49" s="70"/>
+      <c r="J49" s="71"/>
     </row>
     <row r="50" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A50" s="28"/>
-      <c r="B50" s="56"/>
-      <c r="C50" s="56"/>
-      <c r="D50" s="56"/>
-      <c r="E50" s="56"/>
-      <c r="F50" s="56"/>
-      <c r="G50" s="56"/>
-      <c r="H50" s="56"/>
-      <c r="I50" s="56"/>
-      <c r="J50" s="57"/>
+      <c r="A50" s="30"/>
+      <c r="B50" s="70"/>
+      <c r="C50" s="70"/>
+      <c r="D50" s="70"/>
+      <c r="E50" s="70"/>
+      <c r="F50" s="70"/>
+      <c r="G50" s="70"/>
+      <c r="H50" s="70"/>
+      <c r="I50" s="70"/>
+      <c r="J50" s="71"/>
     </row>
     <row r="51" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A51" s="28"/>
-      <c r="B51" s="56"/>
-      <c r="C51" s="56"/>
-      <c r="D51" s="56"/>
-      <c r="E51" s="56"/>
-      <c r="F51" s="56"/>
-      <c r="G51" s="56"/>
-      <c r="H51" s="56"/>
-      <c r="I51" s="56"/>
-      <c r="J51" s="57"/>
+      <c r="A51" s="30"/>
+      <c r="B51" s="70"/>
+      <c r="C51" s="70"/>
+      <c r="D51" s="70"/>
+      <c r="E51" s="70"/>
+      <c r="F51" s="70"/>
+      <c r="G51" s="70"/>
+      <c r="H51" s="70"/>
+      <c r="I51" s="70"/>
+      <c r="J51" s="71"/>
     </row>
     <row r="52" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A52" s="28"/>
-      <c r="B52" s="56"/>
-      <c r="C52" s="56"/>
-      <c r="D52" s="56"/>
-      <c r="E52" s="56"/>
-      <c r="F52" s="56"/>
-      <c r="G52" s="56"/>
-      <c r="H52" s="56"/>
-      <c r="I52" s="56"/>
-      <c r="J52" s="57"/>
+      <c r="A52" s="30"/>
+      <c r="B52" s="70"/>
+      <c r="C52" s="70"/>
+      <c r="D52" s="70"/>
+      <c r="E52" s="70"/>
+      <c r="F52" s="70"/>
+      <c r="G52" s="70"/>
+      <c r="H52" s="70"/>
+      <c r="I52" s="70"/>
+      <c r="J52" s="71"/>
     </row>
     <row r="53" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A53" s="28"/>
-      <c r="B53" s="56"/>
-      <c r="C53" s="56"/>
-      <c r="D53" s="56"/>
-      <c r="E53" s="56"/>
-      <c r="F53" s="56"/>
-      <c r="G53" s="56"/>
-      <c r="H53" s="56"/>
-      <c r="I53" s="56"/>
-      <c r="J53" s="57"/>
+      <c r="A53" s="30"/>
+      <c r="B53" s="70"/>
+      <c r="C53" s="70"/>
+      <c r="D53" s="70"/>
+      <c r="E53" s="70"/>
+      <c r="F53" s="70"/>
+      <c r="G53" s="70"/>
+      <c r="H53" s="70"/>
+      <c r="I53" s="70"/>
+      <c r="J53" s="71"/>
     </row>
     <row r="54" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A54" s="28"/>
-      <c r="B54" s="56"/>
-      <c r="C54" s="56"/>
-      <c r="D54" s="56"/>
-      <c r="E54" s="56"/>
-      <c r="F54" s="56"/>
-      <c r="G54" s="56"/>
-      <c r="H54" s="56"/>
-      <c r="I54" s="56"/>
-      <c r="J54" s="57"/>
+      <c r="A54" s="30"/>
+      <c r="B54" s="70"/>
+      <c r="C54" s="70"/>
+      <c r="D54" s="70"/>
+      <c r="E54" s="70"/>
+      <c r="F54" s="70"/>
+      <c r="G54" s="70"/>
+      <c r="H54" s="70"/>
+      <c r="I54" s="70"/>
+      <c r="J54" s="71"/>
     </row>
     <row r="55" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A55" s="28"/>
-      <c r="B55" s="56"/>
-      <c r="C55" s="56"/>
-      <c r="D55" s="56"/>
-      <c r="E55" s="56"/>
-      <c r="F55" s="56"/>
-      <c r="G55" s="56"/>
-      <c r="H55" s="56"/>
-      <c r="I55" s="56"/>
-      <c r="J55" s="57"/>
+      <c r="A55" s="30"/>
+      <c r="B55" s="70"/>
+      <c r="C55" s="70"/>
+      <c r="D55" s="70"/>
+      <c r="E55" s="70"/>
+      <c r="F55" s="70"/>
+      <c r="G55" s="70"/>
+      <c r="H55" s="70"/>
+      <c r="I55" s="70"/>
+      <c r="J55" s="71"/>
     </row>
     <row r="56" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A56" s="28"/>
-      <c r="B56" s="56"/>
-      <c r="C56" s="56"/>
-      <c r="D56" s="56"/>
-      <c r="E56" s="56"/>
-      <c r="F56" s="56"/>
-      <c r="G56" s="56"/>
-      <c r="H56" s="56"/>
-      <c r="I56" s="56"/>
-      <c r="J56" s="57"/>
+      <c r="A56" s="30"/>
+      <c r="B56" s="70"/>
+      <c r="C56" s="70"/>
+      <c r="D56" s="70"/>
+      <c r="E56" s="70"/>
+      <c r="F56" s="70"/>
+      <c r="G56" s="70"/>
+      <c r="H56" s="70"/>
+      <c r="I56" s="70"/>
+      <c r="J56" s="71"/>
     </row>
     <row r="57" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A57" s="28"/>
-      <c r="B57" s="56"/>
-      <c r="C57" s="56"/>
-      <c r="D57" s="56"/>
-      <c r="E57" s="56"/>
-      <c r="F57" s="56"/>
-      <c r="G57" s="56"/>
-      <c r="H57" s="56"/>
-      <c r="I57" s="56"/>
-      <c r="J57" s="57"/>
+      <c r="A57" s="30"/>
+      <c r="B57" s="70"/>
+      <c r="C57" s="70"/>
+      <c r="D57" s="70"/>
+      <c r="E57" s="70"/>
+      <c r="F57" s="70"/>
+      <c r="G57" s="70"/>
+      <c r="H57" s="70"/>
+      <c r="I57" s="70"/>
+      <c r="J57" s="71"/>
     </row>
     <row r="58" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A58" s="28"/>
-      <c r="B58" s="56"/>
-      <c r="C58" s="56"/>
-      <c r="D58" s="56"/>
-      <c r="E58" s="56"/>
-      <c r="F58" s="56"/>
-      <c r="G58" s="56"/>
-      <c r="H58" s="56"/>
-      <c r="I58" s="56"/>
-      <c r="J58" s="57"/>
+      <c r="A58" s="30"/>
+      <c r="B58" s="70"/>
+      <c r="C58" s="70"/>
+      <c r="D58" s="70"/>
+      <c r="E58" s="70"/>
+      <c r="F58" s="70"/>
+      <c r="G58" s="70"/>
+      <c r="H58" s="70"/>
+      <c r="I58" s="70"/>
+      <c r="J58" s="71"/>
     </row>
     <row r="59" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A59" s="28"/>
-      <c r="B59" s="56"/>
-      <c r="C59" s="56"/>
-      <c r="D59" s="56"/>
-      <c r="E59" s="56"/>
-      <c r="F59" s="56"/>
-      <c r="G59" s="56"/>
-      <c r="H59" s="56"/>
-      <c r="I59" s="56"/>
-      <c r="J59" s="57"/>
+      <c r="A59" s="30"/>
+      <c r="B59" s="70"/>
+      <c r="C59" s="70"/>
+      <c r="D59" s="70"/>
+      <c r="E59" s="70"/>
+      <c r="F59" s="70"/>
+      <c r="G59" s="70"/>
+      <c r="H59" s="70"/>
+      <c r="I59" s="70"/>
+      <c r="J59" s="71"/>
     </row>
     <row r="60" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A60" s="28"/>
-      <c r="B60" s="56"/>
-      <c r="C60" s="56"/>
-      <c r="D60" s="56"/>
-      <c r="E60" s="56"/>
-      <c r="F60" s="56"/>
-      <c r="G60" s="56"/>
-      <c r="H60" s="56"/>
-      <c r="I60" s="56"/>
-      <c r="J60" s="57"/>
+      <c r="A60" s="30"/>
+      <c r="B60" s="70"/>
+      <c r="C60" s="70"/>
+      <c r="D60" s="70"/>
+      <c r="E60" s="70"/>
+      <c r="F60" s="70"/>
+      <c r="G60" s="70"/>
+      <c r="H60" s="70"/>
+      <c r="I60" s="70"/>
+      <c r="J60" s="71"/>
     </row>
     <row r="61" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A61" s="28"/>
-      <c r="B61" s="56"/>
-      <c r="C61" s="56"/>
-      <c r="D61" s="56"/>
-      <c r="E61" s="56"/>
-      <c r="F61" s="56"/>
-      <c r="G61" s="56"/>
-      <c r="H61" s="56"/>
-      <c r="I61" s="56"/>
-      <c r="J61" s="57"/>
+      <c r="A61" s="30"/>
+      <c r="B61" s="70"/>
+      <c r="C61" s="70"/>
+      <c r="D61" s="70"/>
+      <c r="E61" s="70"/>
+      <c r="F61" s="70"/>
+      <c r="G61" s="70"/>
+      <c r="H61" s="70"/>
+      <c r="I61" s="70"/>
+      <c r="J61" s="71"/>
     </row>
     <row r="62" spans="1:10" ht="13.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A62" s="29"/>
-      <c r="B62" s="58"/>
-      <c r="C62" s="58"/>
-      <c r="D62" s="58"/>
-      <c r="E62" s="58"/>
-      <c r="F62" s="58"/>
-      <c r="G62" s="58"/>
-      <c r="H62" s="58"/>
-      <c r="I62" s="58"/>
-      <c r="J62" s="59"/>
+      <c r="A62" s="31"/>
+      <c r="B62" s="72"/>
+      <c r="C62" s="72"/>
+      <c r="D62" s="72"/>
+      <c r="E62" s="72"/>
+      <c r="F62" s="72"/>
+      <c r="G62" s="72"/>
+      <c r="H62" s="72"/>
+      <c r="I62" s="72"/>
+      <c r="J62" s="73"/>
     </row>
     <row r="63" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A63" s="27">
+      <c r="A63" s="28">
         <v>4</v>
       </c>
-      <c r="B63" s="34" t="s">
+      <c r="B63" s="32" t="s">
         <v>6</v>
       </c>
-      <c r="C63" s="34"/>
-      <c r="D63" s="34"/>
-      <c r="E63" s="34"/>
-      <c r="F63" s="34"/>
-      <c r="G63" s="34"/>
-      <c r="H63" s="34"/>
-      <c r="I63" s="34"/>
-      <c r="J63" s="67"/>
+      <c r="C63" s="32"/>
+      <c r="D63" s="32"/>
+      <c r="E63" s="32"/>
+      <c r="F63" s="32"/>
+      <c r="G63" s="32"/>
+      <c r="H63" s="32"/>
+      <c r="I63" s="32"/>
+      <c r="J63" s="33"/>
     </row>
     <row r="64" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A64" s="28"/>
-      <c r="B64" s="30" t="s">
+      <c r="A64" s="30"/>
+      <c r="B64" s="74" t="s">
         <v>7</v>
       </c>
-      <c r="C64" s="30"/>
-      <c r="D64" s="44"/>
-      <c r="E64" s="44"/>
-      <c r="F64" s="44"/>
-      <c r="G64" s="44"/>
-      <c r="H64" s="44"/>
-      <c r="I64" s="44"/>
-      <c r="J64" s="45"/>
+      <c r="C64" s="74"/>
+      <c r="D64" s="34"/>
+      <c r="E64" s="34"/>
+      <c r="F64" s="34"/>
+      <c r="G64" s="34"/>
+      <c r="H64" s="34"/>
+      <c r="I64" s="34"/>
+      <c r="J64" s="35"/>
     </row>
     <row r="65" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A65" s="28"/>
-      <c r="B65" s="30" t="s">
+      <c r="A65" s="30"/>
+      <c r="B65" s="74" t="s">
         <v>8</v>
       </c>
-      <c r="C65" s="30"/>
-      <c r="D65" s="44"/>
-      <c r="E65" s="44"/>
-      <c r="F65" s="44"/>
-      <c r="G65" s="44"/>
-      <c r="H65" s="44"/>
-      <c r="I65" s="44"/>
-      <c r="J65" s="45"/>
+      <c r="C65" s="74"/>
+      <c r="D65" s="34"/>
+      <c r="E65" s="34"/>
+      <c r="F65" s="34"/>
+      <c r="G65" s="34"/>
+      <c r="H65" s="34"/>
+      <c r="I65" s="34"/>
+      <c r="J65" s="35"/>
     </row>
     <row r="66" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A66" s="28"/>
-      <c r="B66" s="30" t="s">
+      <c r="A66" s="30"/>
+      <c r="B66" s="74" t="s">
         <v>9</v>
       </c>
-      <c r="C66" s="30"/>
-      <c r="D66" s="44"/>
-      <c r="E66" s="44"/>
-      <c r="F66" s="44"/>
-      <c r="G66" s="44"/>
-      <c r="H66" s="44"/>
-      <c r="I66" s="44"/>
-      <c r="J66" s="45"/>
+      <c r="C66" s="74"/>
+      <c r="D66" s="34"/>
+      <c r="E66" s="34"/>
+      <c r="F66" s="34"/>
+      <c r="G66" s="34"/>
+      <c r="H66" s="34"/>
+      <c r="I66" s="34"/>
+      <c r="J66" s="35"/>
     </row>
     <row r="67" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A67" s="28"/>
-      <c r="B67" s="30" t="s">
+      <c r="A67" s="30"/>
+      <c r="B67" s="74" t="s">
         <v>104</v>
       </c>
-      <c r="C67" s="30"/>
-      <c r="D67" s="44"/>
-      <c r="E67" s="44"/>
-      <c r="F67" s="44"/>
-      <c r="G67" s="44"/>
-      <c r="H67" s="44"/>
-      <c r="I67" s="44"/>
-      <c r="J67" s="45"/>
+      <c r="C67" s="74"/>
+      <c r="D67" s="34"/>
+      <c r="E67" s="34"/>
+      <c r="F67" s="34"/>
+      <c r="G67" s="34"/>
+      <c r="H67" s="34"/>
+      <c r="I67" s="34"/>
+      <c r="J67" s="35"/>
     </row>
     <row r="68" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A68" s="28"/>
-      <c r="B68" s="30" t="s">
+      <c r="A68" s="30"/>
+      <c r="B68" s="74" t="s">
         <v>10</v>
       </c>
-      <c r="C68" s="30"/>
-      <c r="D68" s="30"/>
-      <c r="E68" s="30"/>
-      <c r="F68" s="30"/>
-      <c r="G68" s="30"/>
-      <c r="H68" s="30"/>
-      <c r="I68" s="30"/>
-      <c r="J68" s="60"/>
+      <c r="C68" s="74"/>
+      <c r="D68" s="74"/>
+      <c r="E68" s="74"/>
+      <c r="F68" s="74"/>
+      <c r="G68" s="74"/>
+      <c r="H68" s="74"/>
+      <c r="I68" s="74"/>
+      <c r="J68" s="75"/>
     </row>
     <row r="69" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A69" s="28"/>
-      <c r="B69" s="40"/>
-      <c r="C69" s="40"/>
-      <c r="D69" s="40"/>
-      <c r="E69" s="40"/>
-      <c r="F69" s="40"/>
-      <c r="G69" s="40"/>
-      <c r="H69" s="40"/>
-      <c r="I69" s="40"/>
-      <c r="J69" s="41"/>
+      <c r="A69" s="30"/>
+      <c r="B69" s="60"/>
+      <c r="C69" s="60"/>
+      <c r="D69" s="60"/>
+      <c r="E69" s="60"/>
+      <c r="F69" s="60"/>
+      <c r="G69" s="60"/>
+      <c r="H69" s="60"/>
+      <c r="I69" s="60"/>
+      <c r="J69" s="61"/>
     </row>
     <row r="70" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A70" s="28"/>
-      <c r="B70" s="40"/>
-      <c r="C70" s="40"/>
-      <c r="D70" s="40"/>
-      <c r="E70" s="40"/>
-      <c r="F70" s="40"/>
-      <c r="G70" s="40"/>
-      <c r="H70" s="40"/>
-      <c r="I70" s="40"/>
-      <c r="J70" s="41"/>
+      <c r="A70" s="30"/>
+      <c r="B70" s="60"/>
+      <c r="C70" s="60"/>
+      <c r="D70" s="60"/>
+      <c r="E70" s="60"/>
+      <c r="F70" s="60"/>
+      <c r="G70" s="60"/>
+      <c r="H70" s="60"/>
+      <c r="I70" s="60"/>
+      <c r="J70" s="61"/>
     </row>
     <row r="71" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A71" s="28"/>
-      <c r="B71" s="40"/>
-      <c r="C71" s="40"/>
-      <c r="D71" s="40"/>
-      <c r="E71" s="40"/>
-      <c r="F71" s="40"/>
-      <c r="G71" s="40"/>
-      <c r="H71" s="40"/>
-      <c r="I71" s="40"/>
-      <c r="J71" s="41"/>
+      <c r="A71" s="30"/>
+      <c r="B71" s="60"/>
+      <c r="C71" s="60"/>
+      <c r="D71" s="60"/>
+      <c r="E71" s="60"/>
+      <c r="F71" s="60"/>
+      <c r="G71" s="60"/>
+      <c r="H71" s="60"/>
+      <c r="I71" s="60"/>
+      <c r="J71" s="61"/>
     </row>
     <row r="72" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A72" s="28"/>
-      <c r="B72" s="40"/>
-      <c r="C72" s="40"/>
-      <c r="D72" s="40"/>
-      <c r="E72" s="40"/>
-      <c r="F72" s="40"/>
-      <c r="G72" s="40"/>
-      <c r="H72" s="40"/>
-      <c r="I72" s="40"/>
-      <c r="J72" s="41"/>
+      <c r="A72" s="30"/>
+      <c r="B72" s="60"/>
+      <c r="C72" s="60"/>
+      <c r="D72" s="60"/>
+      <c r="E72" s="60"/>
+      <c r="F72" s="60"/>
+      <c r="G72" s="60"/>
+      <c r="H72" s="60"/>
+      <c r="I72" s="60"/>
+      <c r="J72" s="61"/>
     </row>
     <row r="73" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A73" s="28"/>
-      <c r="B73" s="40"/>
-      <c r="C73" s="40"/>
-      <c r="D73" s="40"/>
-      <c r="E73" s="40"/>
-      <c r="F73" s="40"/>
-      <c r="G73" s="40"/>
-      <c r="H73" s="40"/>
-      <c r="I73" s="40"/>
-      <c r="J73" s="41"/>
+      <c r="A73" s="30"/>
+      <c r="B73" s="60"/>
+      <c r="C73" s="60"/>
+      <c r="D73" s="60"/>
+      <c r="E73" s="60"/>
+      <c r="F73" s="60"/>
+      <c r="G73" s="60"/>
+      <c r="H73" s="60"/>
+      <c r="I73" s="60"/>
+      <c r="J73" s="61"/>
     </row>
     <row r="74" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A74" s="28"/>
-      <c r="B74" s="40"/>
-      <c r="C74" s="40"/>
-      <c r="D74" s="40"/>
-      <c r="E74" s="40"/>
-      <c r="F74" s="40"/>
-      <c r="G74" s="40"/>
-      <c r="H74" s="40"/>
-      <c r="I74" s="40"/>
-      <c r="J74" s="41"/>
+      <c r="A74" s="30"/>
+      <c r="B74" s="60"/>
+      <c r="C74" s="60"/>
+      <c r="D74" s="60"/>
+      <c r="E74" s="60"/>
+      <c r="F74" s="60"/>
+      <c r="G74" s="60"/>
+      <c r="H74" s="60"/>
+      <c r="I74" s="60"/>
+      <c r="J74" s="61"/>
     </row>
     <row r="75" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A75" s="28"/>
-      <c r="B75" s="40"/>
-      <c r="C75" s="40"/>
-      <c r="D75" s="40"/>
-      <c r="E75" s="40"/>
-      <c r="F75" s="40"/>
-      <c r="G75" s="40"/>
-      <c r="H75" s="40"/>
-      <c r="I75" s="40"/>
-      <c r="J75" s="41"/>
+      <c r="A75" s="30"/>
+      <c r="B75" s="60"/>
+      <c r="C75" s="60"/>
+      <c r="D75" s="60"/>
+      <c r="E75" s="60"/>
+      <c r="F75" s="60"/>
+      <c r="G75" s="60"/>
+      <c r="H75" s="60"/>
+      <c r="I75" s="60"/>
+      <c r="J75" s="61"/>
     </row>
     <row r="76" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A76" s="28"/>
-      <c r="B76" s="40"/>
-      <c r="C76" s="40"/>
-      <c r="D76" s="40"/>
-      <c r="E76" s="40"/>
-      <c r="F76" s="40"/>
-      <c r="G76" s="40"/>
-      <c r="H76" s="40"/>
-      <c r="I76" s="40"/>
-      <c r="J76" s="41"/>
+      <c r="A76" s="30"/>
+      <c r="B76" s="60"/>
+      <c r="C76" s="60"/>
+      <c r="D76" s="60"/>
+      <c r="E76" s="60"/>
+      <c r="F76" s="60"/>
+      <c r="G76" s="60"/>
+      <c r="H76" s="60"/>
+      <c r="I76" s="60"/>
+      <c r="J76" s="61"/>
     </row>
     <row r="77" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A77" s="28"/>
-      <c r="B77" s="40"/>
-      <c r="C77" s="40"/>
-      <c r="D77" s="40"/>
-      <c r="E77" s="40"/>
-      <c r="F77" s="40"/>
-      <c r="G77" s="40"/>
-      <c r="H77" s="40"/>
-      <c r="I77" s="40"/>
-      <c r="J77" s="41"/>
+      <c r="A77" s="30"/>
+      <c r="B77" s="60"/>
+      <c r="C77" s="60"/>
+      <c r="D77" s="60"/>
+      <c r="E77" s="60"/>
+      <c r="F77" s="60"/>
+      <c r="G77" s="60"/>
+      <c r="H77" s="60"/>
+      <c r="I77" s="60"/>
+      <c r="J77" s="61"/>
     </row>
     <row r="78" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A78" s="28"/>
-      <c r="B78" s="40"/>
-      <c r="C78" s="40"/>
-      <c r="D78" s="40"/>
-      <c r="E78" s="40"/>
-      <c r="F78" s="40"/>
-      <c r="G78" s="40"/>
-      <c r="H78" s="40"/>
-      <c r="I78" s="40"/>
-      <c r="J78" s="41"/>
+      <c r="A78" s="30"/>
+      <c r="B78" s="60"/>
+      <c r="C78" s="60"/>
+      <c r="D78" s="60"/>
+      <c r="E78" s="60"/>
+      <c r="F78" s="60"/>
+      <c r="G78" s="60"/>
+      <c r="H78" s="60"/>
+      <c r="I78" s="60"/>
+      <c r="J78" s="61"/>
     </row>
     <row r="79" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A79" s="28"/>
-      <c r="B79" s="40"/>
-      <c r="C79" s="40"/>
-      <c r="D79" s="40"/>
-      <c r="E79" s="40"/>
-      <c r="F79" s="40"/>
-      <c r="G79" s="40"/>
-      <c r="H79" s="40"/>
-      <c r="I79" s="40"/>
-      <c r="J79" s="41"/>
+      <c r="A79" s="30"/>
+      <c r="B79" s="60"/>
+      <c r="C79" s="60"/>
+      <c r="D79" s="60"/>
+      <c r="E79" s="60"/>
+      <c r="F79" s="60"/>
+      <c r="G79" s="60"/>
+      <c r="H79" s="60"/>
+      <c r="I79" s="60"/>
+      <c r="J79" s="61"/>
     </row>
     <row r="80" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A80" s="28"/>
-      <c r="B80" s="40"/>
-      <c r="C80" s="40"/>
-      <c r="D80" s="40"/>
-      <c r="E80" s="40"/>
-      <c r="F80" s="40"/>
-      <c r="G80" s="40"/>
-      <c r="H80" s="40"/>
-      <c r="I80" s="40"/>
-      <c r="J80" s="41"/>
+      <c r="A80" s="30"/>
+      <c r="B80" s="60"/>
+      <c r="C80" s="60"/>
+      <c r="D80" s="60"/>
+      <c r="E80" s="60"/>
+      <c r="F80" s="60"/>
+      <c r="G80" s="60"/>
+      <c r="H80" s="60"/>
+      <c r="I80" s="60"/>
+      <c r="J80" s="61"/>
     </row>
     <row r="81" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A81" s="28"/>
-      <c r="B81" s="40"/>
-      <c r="C81" s="40"/>
-      <c r="D81" s="40"/>
-      <c r="E81" s="40"/>
-      <c r="F81" s="40"/>
-      <c r="G81" s="40"/>
-      <c r="H81" s="40"/>
-      <c r="I81" s="40"/>
-      <c r="J81" s="41"/>
+      <c r="A81" s="30"/>
+      <c r="B81" s="60"/>
+      <c r="C81" s="60"/>
+      <c r="D81" s="60"/>
+      <c r="E81" s="60"/>
+      <c r="F81" s="60"/>
+      <c r="G81" s="60"/>
+      <c r="H81" s="60"/>
+      <c r="I81" s="60"/>
+      <c r="J81" s="61"/>
     </row>
     <row r="82" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A82" s="28"/>
-      <c r="B82" s="40"/>
-      <c r="C82" s="40"/>
-      <c r="D82" s="40"/>
-      <c r="E82" s="40"/>
-      <c r="F82" s="40"/>
-      <c r="G82" s="40"/>
-      <c r="H82" s="40"/>
-      <c r="I82" s="40"/>
-      <c r="J82" s="41"/>
+      <c r="A82" s="30"/>
+      <c r="B82" s="60"/>
+      <c r="C82" s="60"/>
+      <c r="D82" s="60"/>
+      <c r="E82" s="60"/>
+      <c r="F82" s="60"/>
+      <c r="G82" s="60"/>
+      <c r="H82" s="60"/>
+      <c r="I82" s="60"/>
+      <c r="J82" s="61"/>
     </row>
     <row r="83" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A83" s="28"/>
-      <c r="B83" s="40"/>
-      <c r="C83" s="40"/>
-      <c r="D83" s="40"/>
-      <c r="E83" s="40"/>
-      <c r="F83" s="40"/>
-      <c r="G83" s="40"/>
-      <c r="H83" s="40"/>
-      <c r="I83" s="40"/>
-      <c r="J83" s="41"/>
+      <c r="A83" s="30"/>
+      <c r="B83" s="60"/>
+      <c r="C83" s="60"/>
+      <c r="D83" s="60"/>
+      <c r="E83" s="60"/>
+      <c r="F83" s="60"/>
+      <c r="G83" s="60"/>
+      <c r="H83" s="60"/>
+      <c r="I83" s="60"/>
+      <c r="J83" s="61"/>
     </row>
     <row r="84" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A84" s="28"/>
-      <c r="B84" s="40"/>
-      <c r="C84" s="40"/>
-      <c r="D84" s="40"/>
-      <c r="E84" s="40"/>
-      <c r="F84" s="40"/>
-      <c r="G84" s="40"/>
-      <c r="H84" s="40"/>
-      <c r="I84" s="40"/>
-      <c r="J84" s="41"/>
+      <c r="A84" s="30"/>
+      <c r="B84" s="60"/>
+      <c r="C84" s="60"/>
+      <c r="D84" s="60"/>
+      <c r="E84" s="60"/>
+      <c r="F84" s="60"/>
+      <c r="G84" s="60"/>
+      <c r="H84" s="60"/>
+      <c r="I84" s="60"/>
+      <c r="J84" s="61"/>
     </row>
     <row r="85" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A85" s="28"/>
-      <c r="B85" s="40"/>
-      <c r="C85" s="40"/>
-      <c r="D85" s="40"/>
-      <c r="E85" s="40"/>
-      <c r="F85" s="40"/>
-      <c r="G85" s="40"/>
-      <c r="H85" s="40"/>
-      <c r="I85" s="40"/>
-      <c r="J85" s="41"/>
+      <c r="A85" s="30"/>
+      <c r="B85" s="60"/>
+      <c r="C85" s="60"/>
+      <c r="D85" s="60"/>
+      <c r="E85" s="60"/>
+      <c r="F85" s="60"/>
+      <c r="G85" s="60"/>
+      <c r="H85" s="60"/>
+      <c r="I85" s="60"/>
+      <c r="J85" s="61"/>
     </row>
     <row r="86" spans="1:10" ht="13.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A86" s="31"/>
-      <c r="B86" s="42"/>
-      <c r="C86" s="42"/>
-      <c r="D86" s="42"/>
-      <c r="E86" s="42"/>
-      <c r="F86" s="42"/>
-      <c r="G86" s="42"/>
-      <c r="H86" s="42"/>
-      <c r="I86" s="42"/>
-      <c r="J86" s="43"/>
+      <c r="A86" s="29"/>
+      <c r="B86" s="62"/>
+      <c r="C86" s="62"/>
+      <c r="D86" s="62"/>
+      <c r="E86" s="62"/>
+      <c r="F86" s="62"/>
+      <c r="G86" s="62"/>
+      <c r="H86" s="62"/>
+      <c r="I86" s="62"/>
+      <c r="J86" s="63"/>
     </row>
     <row r="87" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A87" s="27">
+      <c r="A87" s="28">
         <v>5</v>
       </c>
-      <c r="B87" s="34" t="s">
+      <c r="B87" s="32" t="s">
         <v>11</v>
       </c>
-      <c r="C87" s="34"/>
-      <c r="D87" s="34"/>
-      <c r="E87" s="34"/>
-      <c r="F87" s="34"/>
-      <c r="G87" s="34"/>
-      <c r="H87" s="34"/>
-      <c r="I87" s="34"/>
-      <c r="J87" s="67"/>
+      <c r="C87" s="32"/>
+      <c r="D87" s="32"/>
+      <c r="E87" s="32"/>
+      <c r="F87" s="32"/>
+      <c r="G87" s="32"/>
+      <c r="H87" s="32"/>
+      <c r="I87" s="32"/>
+      <c r="J87" s="33"/>
     </row>
     <row r="88" spans="1:10" ht="13.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A88" s="28"/>
-      <c r="B88" s="76" t="s">
+      <c r="A88" s="30"/>
+      <c r="B88" s="49" t="s">
         <v>12</v>
       </c>
-      <c r="C88" s="76"/>
-      <c r="D88" s="76"/>
-      <c r="E88" s="76"/>
-      <c r="F88" s="76"/>
-      <c r="G88" s="76"/>
-      <c r="H88" s="76"/>
-      <c r="I88" s="76"/>
-      <c r="J88" s="77"/>
+      <c r="C88" s="49"/>
+      <c r="D88" s="49"/>
+      <c r="E88" s="49"/>
+      <c r="F88" s="49"/>
+      <c r="G88" s="49"/>
+      <c r="H88" s="49"/>
+      <c r="I88" s="49"/>
+      <c r="J88" s="50"/>
     </row>
     <row r="89" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A89" s="27">
+      <c r="A89" s="28">
         <v>6</v>
       </c>
-      <c r="B89" s="32" t="s">
+      <c r="B89" s="42" t="s">
         <v>13</v>
       </c>
-      <c r="C89" s="32"/>
-      <c r="D89" s="32"/>
-      <c r="E89" s="32"/>
-      <c r="F89" s="32"/>
-      <c r="G89" s="32"/>
-      <c r="H89" s="32"/>
-      <c r="I89" s="32"/>
-      <c r="J89" s="33"/>
+      <c r="C89" s="42"/>
+      <c r="D89" s="42"/>
+      <c r="E89" s="42"/>
+      <c r="F89" s="42"/>
+      <c r="G89" s="42"/>
+      <c r="H89" s="42"/>
+      <c r="I89" s="42"/>
+      <c r="J89" s="43"/>
     </row>
     <row r="90" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A90" s="75"/>
-      <c r="B90" s="46" t="s">
+      <c r="A90" s="44"/>
+      <c r="B90" s="45" t="s">
         <v>14</v>
       </c>
-      <c r="C90" s="46"/>
-      <c r="D90" s="46"/>
-      <c r="E90" s="46"/>
-      <c r="F90" s="46"/>
-      <c r="G90" s="46"/>
-      <c r="H90" s="46"/>
-      <c r="I90" s="46"/>
-      <c r="J90" s="47"/>
+      <c r="C90" s="45"/>
+      <c r="D90" s="45"/>
+      <c r="E90" s="45"/>
+      <c r="F90" s="45"/>
+      <c r="G90" s="45"/>
+      <c r="H90" s="45"/>
+      <c r="I90" s="45"/>
+      <c r="J90" s="46"/>
     </row>
     <row r="91" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A91" s="75"/>
-      <c r="B91" s="46"/>
-      <c r="C91" s="46"/>
-      <c r="D91" s="46"/>
-      <c r="E91" s="46"/>
-      <c r="F91" s="46"/>
-      <c r="G91" s="46"/>
-      <c r="H91" s="46"/>
-      <c r="I91" s="46"/>
-      <c r="J91" s="47"/>
+      <c r="A91" s="44"/>
+      <c r="B91" s="45"/>
+      <c r="C91" s="45"/>
+      <c r="D91" s="45"/>
+      <c r="E91" s="45"/>
+      <c r="F91" s="45"/>
+      <c r="G91" s="45"/>
+      <c r="H91" s="45"/>
+      <c r="I91" s="45"/>
+      <c r="J91" s="46"/>
     </row>
     <row r="92" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A92" s="75"/>
-      <c r="B92" s="48"/>
-      <c r="C92" s="48"/>
-      <c r="D92" s="48"/>
-      <c r="E92" s="48"/>
-      <c r="F92" s="48"/>
-      <c r="G92" s="48"/>
-      <c r="H92" s="48"/>
-      <c r="I92" s="48"/>
-      <c r="J92" s="49"/>
+      <c r="A92" s="44"/>
+      <c r="B92" s="47"/>
+      <c r="C92" s="47"/>
+      <c r="D92" s="47"/>
+      <c r="E92" s="47"/>
+      <c r="F92" s="47"/>
+      <c r="G92" s="47"/>
+      <c r="H92" s="47"/>
+      <c r="I92" s="47"/>
+      <c r="J92" s="48"/>
     </row>
     <row r="93" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A93" s="28"/>
-      <c r="B93" s="78"/>
-      <c r="C93" s="62"/>
-      <c r="D93" s="62"/>
-      <c r="E93" s="62"/>
-      <c r="F93" s="62"/>
-      <c r="G93" s="62"/>
-      <c r="H93" s="62"/>
-      <c r="I93" s="62"/>
-      <c r="J93" s="63"/>
+      <c r="A93" s="30"/>
+      <c r="B93" s="51"/>
+      <c r="C93" s="52"/>
+      <c r="D93" s="52"/>
+      <c r="E93" s="52"/>
+      <c r="F93" s="52"/>
+      <c r="G93" s="52"/>
+      <c r="H93" s="52"/>
+      <c r="I93" s="52"/>
+      <c r="J93" s="53"/>
     </row>
     <row r="94" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A94" s="28"/>
-      <c r="B94" s="64"/>
-      <c r="C94" s="65"/>
-      <c r="D94" s="65"/>
-      <c r="E94" s="65"/>
-      <c r="F94" s="65"/>
-      <c r="G94" s="65"/>
-      <c r="H94" s="65"/>
-      <c r="I94" s="65"/>
-      <c r="J94" s="66"/>
+      <c r="A94" s="30"/>
+      <c r="B94" s="54"/>
+      <c r="C94" s="55"/>
+      <c r="D94" s="55"/>
+      <c r="E94" s="55"/>
+      <c r="F94" s="55"/>
+      <c r="G94" s="55"/>
+      <c r="H94" s="55"/>
+      <c r="I94" s="55"/>
+      <c r="J94" s="56"/>
     </row>
     <row r="95" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A95" s="28"/>
-      <c r="B95" s="64"/>
-      <c r="C95" s="65"/>
-      <c r="D95" s="65"/>
-      <c r="E95" s="65"/>
-      <c r="F95" s="65"/>
-      <c r="G95" s="65"/>
-      <c r="H95" s="65"/>
-      <c r="I95" s="65"/>
-      <c r="J95" s="66"/>
+      <c r="A95" s="30"/>
+      <c r="B95" s="54"/>
+      <c r="C95" s="55"/>
+      <c r="D95" s="55"/>
+      <c r="E95" s="55"/>
+      <c r="F95" s="55"/>
+      <c r="G95" s="55"/>
+      <c r="H95" s="55"/>
+      <c r="I95" s="55"/>
+      <c r="J95" s="56"/>
     </row>
     <row r="96" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A96" s="28"/>
-      <c r="B96" s="64"/>
-      <c r="C96" s="65"/>
-      <c r="D96" s="65"/>
-      <c r="E96" s="65"/>
-      <c r="F96" s="65"/>
-      <c r="G96" s="65"/>
-      <c r="H96" s="65"/>
-      <c r="I96" s="65"/>
-      <c r="J96" s="66"/>
+      <c r="A96" s="30"/>
+      <c r="B96" s="54"/>
+      <c r="C96" s="55"/>
+      <c r="D96" s="55"/>
+      <c r="E96" s="55"/>
+      <c r="F96" s="55"/>
+      <c r="G96" s="55"/>
+      <c r="H96" s="55"/>
+      <c r="I96" s="55"/>
+      <c r="J96" s="56"/>
     </row>
     <row r="97" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A97" s="28"/>
-      <c r="B97" s="64"/>
-      <c r="C97" s="65"/>
-      <c r="D97" s="65"/>
-      <c r="E97" s="65"/>
-      <c r="F97" s="65"/>
-      <c r="G97" s="65"/>
-      <c r="H97" s="65"/>
-      <c r="I97" s="65"/>
-      <c r="J97" s="66"/>
+      <c r="A97" s="30"/>
+      <c r="B97" s="54"/>
+      <c r="C97" s="55"/>
+      <c r="D97" s="55"/>
+      <c r="E97" s="55"/>
+      <c r="F97" s="55"/>
+      <c r="G97" s="55"/>
+      <c r="H97" s="55"/>
+      <c r="I97" s="55"/>
+      <c r="J97" s="56"/>
     </row>
     <row r="98" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A98" s="28"/>
-      <c r="B98" s="64"/>
-      <c r="C98" s="65"/>
-      <c r="D98" s="65"/>
-      <c r="E98" s="65"/>
-      <c r="F98" s="65"/>
-      <c r="G98" s="65"/>
-      <c r="H98" s="65"/>
-      <c r="I98" s="65"/>
-      <c r="J98" s="66"/>
+      <c r="A98" s="30"/>
+      <c r="B98" s="54"/>
+      <c r="C98" s="55"/>
+      <c r="D98" s="55"/>
+      <c r="E98" s="55"/>
+      <c r="F98" s="55"/>
+      <c r="G98" s="55"/>
+      <c r="H98" s="55"/>
+      <c r="I98" s="55"/>
+      <c r="J98" s="56"/>
     </row>
     <row r="99" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A99" s="28"/>
-      <c r="B99" s="64"/>
-      <c r="C99" s="65"/>
-      <c r="D99" s="65"/>
-      <c r="E99" s="65"/>
-      <c r="F99" s="65"/>
-      <c r="G99" s="65"/>
-      <c r="H99" s="65"/>
-      <c r="I99" s="65"/>
-      <c r="J99" s="66"/>
+      <c r="A99" s="30"/>
+      <c r="B99" s="54"/>
+      <c r="C99" s="55"/>
+      <c r="D99" s="55"/>
+      <c r="E99" s="55"/>
+      <c r="F99" s="55"/>
+      <c r="G99" s="55"/>
+      <c r="H99" s="55"/>
+      <c r="I99" s="55"/>
+      <c r="J99" s="56"/>
     </row>
     <row r="100" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A100" s="28"/>
-      <c r="B100" s="64"/>
-      <c r="C100" s="65"/>
-      <c r="D100" s="65"/>
-      <c r="E100" s="65"/>
-      <c r="F100" s="65"/>
-      <c r="G100" s="65"/>
-      <c r="H100" s="65"/>
-      <c r="I100" s="65"/>
-      <c r="J100" s="66"/>
+      <c r="A100" s="30"/>
+      <c r="B100" s="54"/>
+      <c r="C100" s="55"/>
+      <c r="D100" s="55"/>
+      <c r="E100" s="55"/>
+      <c r="F100" s="55"/>
+      <c r="G100" s="55"/>
+      <c r="H100" s="55"/>
+      <c r="I100" s="55"/>
+      <c r="J100" s="56"/>
     </row>
     <row r="101" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A101" s="28"/>
-      <c r="B101" s="64"/>
-      <c r="C101" s="65"/>
-      <c r="D101" s="65"/>
-      <c r="E101" s="65"/>
-      <c r="F101" s="65"/>
-      <c r="G101" s="65"/>
-      <c r="H101" s="65"/>
-      <c r="I101" s="65"/>
-      <c r="J101" s="66"/>
+      <c r="A101" s="30"/>
+      <c r="B101" s="54"/>
+      <c r="C101" s="55"/>
+      <c r="D101" s="55"/>
+      <c r="E101" s="55"/>
+      <c r="F101" s="55"/>
+      <c r="G101" s="55"/>
+      <c r="H101" s="55"/>
+      <c r="I101" s="55"/>
+      <c r="J101" s="56"/>
     </row>
     <row r="102" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A102" s="28"/>
-      <c r="B102" s="64"/>
-      <c r="C102" s="65"/>
-      <c r="D102" s="65"/>
-      <c r="E102" s="65"/>
-      <c r="F102" s="65"/>
-      <c r="G102" s="65"/>
-      <c r="H102" s="65"/>
-      <c r="I102" s="65"/>
-      <c r="J102" s="66"/>
+      <c r="A102" s="30"/>
+      <c r="B102" s="54"/>
+      <c r="C102" s="55"/>
+      <c r="D102" s="55"/>
+      <c r="E102" s="55"/>
+      <c r="F102" s="55"/>
+      <c r="G102" s="55"/>
+      <c r="H102" s="55"/>
+      <c r="I102" s="55"/>
+      <c r="J102" s="56"/>
     </row>
     <row r="103" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A103" s="28"/>
-      <c r="B103" s="64"/>
-      <c r="C103" s="65"/>
-      <c r="D103" s="65"/>
-      <c r="E103" s="65"/>
-      <c r="F103" s="65"/>
-      <c r="G103" s="65"/>
-      <c r="H103" s="65"/>
-      <c r="I103" s="65"/>
-      <c r="J103" s="66"/>
+      <c r="A103" s="30"/>
+      <c r="B103" s="54"/>
+      <c r="C103" s="55"/>
+      <c r="D103" s="55"/>
+      <c r="E103" s="55"/>
+      <c r="F103" s="55"/>
+      <c r="G103" s="55"/>
+      <c r="H103" s="55"/>
+      <c r="I103" s="55"/>
+      <c r="J103" s="56"/>
     </row>
     <row r="104" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A104" s="28"/>
-      <c r="B104" s="64"/>
-      <c r="C104" s="65"/>
-      <c r="D104" s="65"/>
-      <c r="E104" s="65"/>
-      <c r="F104" s="65"/>
-      <c r="G104" s="65"/>
-      <c r="H104" s="65"/>
-      <c r="I104" s="65"/>
-      <c r="J104" s="66"/>
+      <c r="A104" s="30"/>
+      <c r="B104" s="54"/>
+      <c r="C104" s="55"/>
+      <c r="D104" s="55"/>
+      <c r="E104" s="55"/>
+      <c r="F104" s="55"/>
+      <c r="G104" s="55"/>
+      <c r="H104" s="55"/>
+      <c r="I104" s="55"/>
+      <c r="J104" s="56"/>
     </row>
     <row r="105" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A105" s="28"/>
-      <c r="B105" s="64"/>
-      <c r="C105" s="65"/>
-      <c r="D105" s="65"/>
-      <c r="E105" s="65"/>
-      <c r="F105" s="65"/>
-      <c r="G105" s="65"/>
-      <c r="H105" s="65"/>
-      <c r="I105" s="65"/>
-      <c r="J105" s="66"/>
+      <c r="A105" s="30"/>
+      <c r="B105" s="54"/>
+      <c r="C105" s="55"/>
+      <c r="D105" s="55"/>
+      <c r="E105" s="55"/>
+      <c r="F105" s="55"/>
+      <c r="G105" s="55"/>
+      <c r="H105" s="55"/>
+      <c r="I105" s="55"/>
+      <c r="J105" s="56"/>
     </row>
     <row r="106" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A106" s="28"/>
-      <c r="B106" s="64"/>
-      <c r="C106" s="65"/>
-      <c r="D106" s="65"/>
-      <c r="E106" s="65"/>
-      <c r="F106" s="65"/>
-      <c r="G106" s="65"/>
-      <c r="H106" s="65"/>
-      <c r="I106" s="65"/>
-      <c r="J106" s="66"/>
+      <c r="A106" s="30"/>
+      <c r="B106" s="54"/>
+      <c r="C106" s="55"/>
+      <c r="D106" s="55"/>
+      <c r="E106" s="55"/>
+      <c r="F106" s="55"/>
+      <c r="G106" s="55"/>
+      <c r="H106" s="55"/>
+      <c r="I106" s="55"/>
+      <c r="J106" s="56"/>
     </row>
     <row r="107" spans="1:10" ht="13.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A107" s="29"/>
-      <c r="B107" s="79"/>
-      <c r="C107" s="80"/>
-      <c r="D107" s="80"/>
-      <c r="E107" s="80"/>
-      <c r="F107" s="80"/>
-      <c r="G107" s="80"/>
-      <c r="H107" s="80"/>
-      <c r="I107" s="80"/>
-      <c r="J107" s="81"/>
+      <c r="A107" s="31"/>
+      <c r="B107" s="57"/>
+      <c r="C107" s="58"/>
+      <c r="D107" s="58"/>
+      <c r="E107" s="58"/>
+      <c r="F107" s="58"/>
+      <c r="G107" s="58"/>
+      <c r="H107" s="58"/>
+      <c r="I107" s="58"/>
+      <c r="J107" s="59"/>
     </row>
     <row r="108" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A108" s="27">
+      <c r="A108" s="28">
         <v>7</v>
       </c>
-      <c r="B108" s="34" t="s">
+      <c r="B108" s="32" t="s">
         <v>15</v>
       </c>
-      <c r="C108" s="34"/>
-      <c r="D108" s="34"/>
-      <c r="E108" s="34"/>
-      <c r="F108" s="34"/>
-      <c r="G108" s="34"/>
-      <c r="H108" s="34"/>
-      <c r="I108" s="34"/>
-      <c r="J108" s="67"/>
+      <c r="C108" s="32"/>
+      <c r="D108" s="32"/>
+      <c r="E108" s="32"/>
+      <c r="F108" s="32"/>
+      <c r="G108" s="32"/>
+      <c r="H108" s="32"/>
+      <c r="I108" s="32"/>
+      <c r="J108" s="33"/>
     </row>
     <row r="109" spans="1:10" ht="13.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A109" s="31"/>
-      <c r="B109" s="73" t="s">
+      <c r="A109" s="29"/>
+      <c r="B109" s="40" t="s">
         <v>16</v>
       </c>
-      <c r="C109" s="73"/>
-      <c r="D109" s="73"/>
-      <c r="E109" s="73"/>
-      <c r="F109" s="73"/>
-      <c r="G109" s="73"/>
-      <c r="H109" s="73"/>
-      <c r="I109" s="73"/>
-      <c r="J109" s="74"/>
+      <c r="C109" s="40"/>
+      <c r="D109" s="40"/>
+      <c r="E109" s="40"/>
+      <c r="F109" s="40"/>
+      <c r="G109" s="40"/>
+      <c r="H109" s="40"/>
+      <c r="I109" s="40"/>
+      <c r="J109" s="41"/>
     </row>
     <row r="110" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A110" s="27">
+      <c r="A110" s="28">
         <v>8</v>
       </c>
-      <c r="B110" s="34" t="s">
+      <c r="B110" s="32" t="s">
         <v>17</v>
       </c>
-      <c r="C110" s="34"/>
-      <c r="D110" s="34"/>
-      <c r="E110" s="34"/>
-      <c r="F110" s="34"/>
-      <c r="G110" s="34"/>
-      <c r="H110" s="34"/>
-      <c r="I110" s="34"/>
-      <c r="J110" s="67"/>
+      <c r="C110" s="32"/>
+      <c r="D110" s="32"/>
+      <c r="E110" s="32"/>
+      <c r="F110" s="32"/>
+      <c r="G110" s="32"/>
+      <c r="H110" s="32"/>
+      <c r="I110" s="32"/>
+      <c r="J110" s="33"/>
     </row>
     <row r="111" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A111" s="28"/>
-      <c r="B111" s="44"/>
-      <c r="C111" s="44"/>
-      <c r="D111" s="44"/>
-      <c r="E111" s="44"/>
-      <c r="F111" s="44"/>
-      <c r="G111" s="44"/>
-      <c r="H111" s="44"/>
-      <c r="I111" s="44"/>
-      <c r="J111" s="45"/>
+      <c r="A111" s="30"/>
+      <c r="B111" s="34"/>
+      <c r="C111" s="34"/>
+      <c r="D111" s="34"/>
+      <c r="E111" s="34"/>
+      <c r="F111" s="34"/>
+      <c r="G111" s="34"/>
+      <c r="H111" s="34"/>
+      <c r="I111" s="34"/>
+      <c r="J111" s="35"/>
     </row>
     <row r="112" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A112" s="28"/>
-      <c r="B112" s="44"/>
-      <c r="C112" s="44"/>
-      <c r="D112" s="44"/>
-      <c r="E112" s="44"/>
-      <c r="F112" s="44"/>
-      <c r="G112" s="44"/>
-      <c r="H112" s="44"/>
-      <c r="I112" s="44"/>
-      <c r="J112" s="45"/>
+      <c r="A112" s="30"/>
+      <c r="B112" s="34"/>
+      <c r="C112" s="34"/>
+      <c r="D112" s="34"/>
+      <c r="E112" s="34"/>
+      <c r="F112" s="34"/>
+      <c r="G112" s="34"/>
+      <c r="H112" s="34"/>
+      <c r="I112" s="34"/>
+      <c r="J112" s="35"/>
     </row>
     <row r="113" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A113" s="28"/>
-      <c r="B113" s="44"/>
-      <c r="C113" s="44"/>
-      <c r="D113" s="44"/>
-      <c r="E113" s="44"/>
-      <c r="F113" s="44"/>
-      <c r="G113" s="44"/>
-      <c r="H113" s="44"/>
-      <c r="I113" s="44"/>
-      <c r="J113" s="45"/>
+      <c r="A113" s="30"/>
+      <c r="B113" s="34"/>
+      <c r="C113" s="34"/>
+      <c r="D113" s="34"/>
+      <c r="E113" s="34"/>
+      <c r="F113" s="34"/>
+      <c r="G113" s="34"/>
+      <c r="H113" s="34"/>
+      <c r="I113" s="34"/>
+      <c r="J113" s="35"/>
     </row>
     <row r="114" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A114" s="28"/>
-      <c r="B114" s="44"/>
-      <c r="C114" s="44"/>
-      <c r="D114" s="44"/>
-      <c r="E114" s="44"/>
-      <c r="F114" s="44"/>
-      <c r="G114" s="44"/>
-      <c r="H114" s="44"/>
-      <c r="I114" s="44"/>
-      <c r="J114" s="45"/>
+      <c r="A114" s="30"/>
+      <c r="B114" s="34"/>
+      <c r="C114" s="34"/>
+      <c r="D114" s="34"/>
+      <c r="E114" s="34"/>
+      <c r="F114" s="34"/>
+      <c r="G114" s="34"/>
+      <c r="H114" s="34"/>
+      <c r="I114" s="34"/>
+      <c r="J114" s="35"/>
     </row>
     <row r="115" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A115" s="28"/>
-      <c r="B115" s="44"/>
-      <c r="C115" s="44"/>
-      <c r="D115" s="44"/>
-      <c r="E115" s="44"/>
-      <c r="F115" s="44"/>
-      <c r="G115" s="44"/>
-      <c r="H115" s="44"/>
-      <c r="I115" s="44"/>
-      <c r="J115" s="45"/>
+      <c r="A115" s="30"/>
+      <c r="B115" s="34"/>
+      <c r="C115" s="34"/>
+      <c r="D115" s="34"/>
+      <c r="E115" s="34"/>
+      <c r="F115" s="34"/>
+      <c r="G115" s="34"/>
+      <c r="H115" s="34"/>
+      <c r="I115" s="34"/>
+      <c r="J115" s="35"/>
     </row>
     <row r="116" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A116" s="28"/>
-      <c r="B116" s="44"/>
-      <c r="C116" s="44"/>
-      <c r="D116" s="44"/>
-      <c r="E116" s="44"/>
-      <c r="F116" s="44"/>
-      <c r="G116" s="44"/>
-      <c r="H116" s="44"/>
-      <c r="I116" s="44"/>
-      <c r="J116" s="45"/>
+      <c r="A116" s="30"/>
+      <c r="B116" s="34"/>
+      <c r="C116" s="34"/>
+      <c r="D116" s="34"/>
+      <c r="E116" s="34"/>
+      <c r="F116" s="34"/>
+      <c r="G116" s="34"/>
+      <c r="H116" s="34"/>
+      <c r="I116" s="34"/>
+      <c r="J116" s="35"/>
     </row>
     <row r="117" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A117" s="28"/>
-      <c r="B117" s="69" t="s">
+      <c r="A117" s="30"/>
+      <c r="B117" s="36" t="s">
         <v>18</v>
       </c>
-      <c r="C117" s="69"/>
-      <c r="D117" s="69"/>
-      <c r="E117" s="69"/>
-      <c r="F117" s="69"/>
-      <c r="G117" s="69"/>
-      <c r="H117" s="69"/>
-      <c r="I117" s="69"/>
-      <c r="J117" s="70"/>
+      <c r="C117" s="36"/>
+      <c r="D117" s="36"/>
+      <c r="E117" s="36"/>
+      <c r="F117" s="36"/>
+      <c r="G117" s="36"/>
+      <c r="H117" s="36"/>
+      <c r="I117" s="36"/>
+      <c r="J117" s="37"/>
     </row>
     <row r="118" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A118" s="28"/>
-      <c r="B118" s="44"/>
-      <c r="C118" s="44"/>
-      <c r="D118" s="44"/>
-      <c r="E118" s="44"/>
-      <c r="F118" s="44"/>
-      <c r="G118" s="44"/>
-      <c r="H118" s="44"/>
-      <c r="I118" s="44"/>
-      <c r="J118" s="45"/>
+      <c r="A118" s="30"/>
+      <c r="B118" s="34"/>
+      <c r="C118" s="34"/>
+      <c r="D118" s="34"/>
+      <c r="E118" s="34"/>
+      <c r="F118" s="34"/>
+      <c r="G118" s="34"/>
+      <c r="H118" s="34"/>
+      <c r="I118" s="34"/>
+      <c r="J118" s="35"/>
     </row>
     <row r="119" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A119" s="28"/>
-      <c r="B119" s="44"/>
-      <c r="C119" s="44"/>
-      <c r="D119" s="44"/>
-      <c r="E119" s="44"/>
-      <c r="F119" s="44"/>
-      <c r="G119" s="44"/>
-      <c r="H119" s="44"/>
-      <c r="I119" s="44"/>
-      <c r="J119" s="45"/>
+      <c r="A119" s="30"/>
+      <c r="B119" s="34"/>
+      <c r="C119" s="34"/>
+      <c r="D119" s="34"/>
+      <c r="E119" s="34"/>
+      <c r="F119" s="34"/>
+      <c r="G119" s="34"/>
+      <c r="H119" s="34"/>
+      <c r="I119" s="34"/>
+      <c r="J119" s="35"/>
     </row>
     <row r="120" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A120" s="28"/>
-      <c r="B120" s="44"/>
-      <c r="C120" s="44"/>
-      <c r="D120" s="44"/>
-      <c r="E120" s="44"/>
-      <c r="F120" s="44"/>
-      <c r="G120" s="44"/>
-      <c r="H120" s="44"/>
-      <c r="I120" s="44"/>
-      <c r="J120" s="45"/>
+      <c r="A120" s="30"/>
+      <c r="B120" s="34"/>
+      <c r="C120" s="34"/>
+      <c r="D120" s="34"/>
+      <c r="E120" s="34"/>
+      <c r="F120" s="34"/>
+      <c r="G120" s="34"/>
+      <c r="H120" s="34"/>
+      <c r="I120" s="34"/>
+      <c r="J120" s="35"/>
     </row>
     <row r="121" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A121" s="28"/>
-      <c r="B121" s="44"/>
-      <c r="C121" s="44"/>
-      <c r="D121" s="44"/>
-      <c r="E121" s="44"/>
-      <c r="F121" s="44"/>
-      <c r="G121" s="44"/>
-      <c r="H121" s="44"/>
-      <c r="I121" s="44"/>
-      <c r="J121" s="45"/>
+      <c r="A121" s="30"/>
+      <c r="B121" s="34"/>
+      <c r="C121" s="34"/>
+      <c r="D121" s="34"/>
+      <c r="E121" s="34"/>
+      <c r="F121" s="34"/>
+      <c r="G121" s="34"/>
+      <c r="H121" s="34"/>
+      <c r="I121" s="34"/>
+      <c r="J121" s="35"/>
     </row>
     <row r="122" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A122" s="28"/>
-      <c r="B122" s="44"/>
-      <c r="C122" s="44"/>
-      <c r="D122" s="44"/>
-      <c r="E122" s="44"/>
-      <c r="F122" s="44"/>
-      <c r="G122" s="44"/>
-      <c r="H122" s="44"/>
-      <c r="I122" s="44"/>
-      <c r="J122" s="45"/>
+      <c r="A122" s="30"/>
+      <c r="B122" s="34"/>
+      <c r="C122" s="34"/>
+      <c r="D122" s="34"/>
+      <c r="E122" s="34"/>
+      <c r="F122" s="34"/>
+      <c r="G122" s="34"/>
+      <c r="H122" s="34"/>
+      <c r="I122" s="34"/>
+      <c r="J122" s="35"/>
     </row>
     <row r="123" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A123" s="28"/>
-      <c r="B123" s="44"/>
-      <c r="C123" s="44"/>
-      <c r="D123" s="44"/>
-      <c r="E123" s="44"/>
-      <c r="F123" s="44"/>
-      <c r="G123" s="44"/>
-      <c r="H123" s="44"/>
-      <c r="I123" s="44"/>
-      <c r="J123" s="45"/>
+      <c r="A123" s="30"/>
+      <c r="B123" s="34"/>
+      <c r="C123" s="34"/>
+      <c r="D123" s="34"/>
+      <c r="E123" s="34"/>
+      <c r="F123" s="34"/>
+      <c r="G123" s="34"/>
+      <c r="H123" s="34"/>
+      <c r="I123" s="34"/>
+      <c r="J123" s="35"/>
     </row>
     <row r="124" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A124" s="28"/>
-      <c r="B124" s="44"/>
-      <c r="C124" s="44"/>
-      <c r="D124" s="44"/>
-      <c r="E124" s="44"/>
-      <c r="F124" s="44"/>
-      <c r="G124" s="44"/>
-      <c r="H124" s="44"/>
-      <c r="I124" s="44"/>
-      <c r="J124" s="45"/>
+      <c r="A124" s="30"/>
+      <c r="B124" s="34"/>
+      <c r="C124" s="34"/>
+      <c r="D124" s="34"/>
+      <c r="E124" s="34"/>
+      <c r="F124" s="34"/>
+      <c r="G124" s="34"/>
+      <c r="H124" s="34"/>
+      <c r="I124" s="34"/>
+      <c r="J124" s="35"/>
     </row>
     <row r="125" spans="1:10" ht="13.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A125" s="29"/>
-      <c r="B125" s="71"/>
-      <c r="C125" s="71"/>
-      <c r="D125" s="71"/>
-      <c r="E125" s="71"/>
-      <c r="F125" s="71"/>
-      <c r="G125" s="71"/>
-      <c r="H125" s="71"/>
-      <c r="I125" s="71"/>
-      <c r="J125" s="72"/>
+      <c r="A125" s="31"/>
+      <c r="B125" s="38"/>
+      <c r="C125" s="38"/>
+      <c r="D125" s="38"/>
+      <c r="E125" s="38"/>
+      <c r="F125" s="38"/>
+      <c r="G125" s="38"/>
+      <c r="H125" s="38"/>
+      <c r="I125" s="38"/>
+      <c r="J125" s="39"/>
     </row>
   </sheetData>
   <mergeCells count="39">
+    <mergeCell ref="A21:A62"/>
+    <mergeCell ref="B64:C64"/>
+    <mergeCell ref="A2:A3"/>
+    <mergeCell ref="A4:A20"/>
+    <mergeCell ref="B4:J4"/>
+    <mergeCell ref="B2:D3"/>
+    <mergeCell ref="E2:J3"/>
+    <mergeCell ref="B69:J86"/>
+    <mergeCell ref="A63:A86"/>
+    <mergeCell ref="D64:J64"/>
+    <mergeCell ref="B5:J7"/>
+    <mergeCell ref="B22:J25"/>
+    <mergeCell ref="B26:J62"/>
+    <mergeCell ref="B21:J21"/>
+    <mergeCell ref="B68:J68"/>
+    <mergeCell ref="B8:J20"/>
+    <mergeCell ref="B63:J63"/>
+    <mergeCell ref="D67:J67"/>
+    <mergeCell ref="B67:C67"/>
+    <mergeCell ref="D66:J66"/>
+    <mergeCell ref="B66:C66"/>
+    <mergeCell ref="D65:J65"/>
+    <mergeCell ref="B65:C65"/>
     <mergeCell ref="A1:J1"/>
     <mergeCell ref="A108:A109"/>
     <mergeCell ref="A110:A125"/>
@@ -4993,29 +5031,6 @@
     <mergeCell ref="B87:J87"/>
     <mergeCell ref="B88:J88"/>
     <mergeCell ref="B93:J107"/>
-    <mergeCell ref="B69:J86"/>
-    <mergeCell ref="A63:A86"/>
-    <mergeCell ref="D64:J64"/>
-    <mergeCell ref="B5:J7"/>
-    <mergeCell ref="B22:J25"/>
-    <mergeCell ref="B26:J62"/>
-    <mergeCell ref="B21:J21"/>
-    <mergeCell ref="B68:J68"/>
-    <mergeCell ref="B8:J20"/>
-    <mergeCell ref="B63:J63"/>
-    <mergeCell ref="D67:J67"/>
-    <mergeCell ref="B67:C67"/>
-    <mergeCell ref="D66:J66"/>
-    <mergeCell ref="B66:C66"/>
-    <mergeCell ref="D65:J65"/>
-    <mergeCell ref="B65:C65"/>
-    <mergeCell ref="A21:A62"/>
-    <mergeCell ref="B64:C64"/>
-    <mergeCell ref="A2:A3"/>
-    <mergeCell ref="A4:A20"/>
-    <mergeCell ref="B4:J4"/>
-    <mergeCell ref="B2:D3"/>
-    <mergeCell ref="E2:J3"/>
   </mergeCells>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.75" right="0.75" top="0.6" bottom="0.61" header="0.4" footer="0.39"/>
@@ -5044,71 +5059,71 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="35" t="s">
+      <c r="A1" s="77" t="s">
         <v>19</v>
       </c>
-      <c r="B1" s="35"/>
-      <c r="C1" s="35"/>
+      <c r="B1" s="77"/>
+      <c r="C1" s="77"/>
     </row>
     <row r="2" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="90" t="s">
+      <c r="A2" s="85" t="s">
         <v>20</v>
       </c>
-      <c r="B2" s="90"/>
-      <c r="C2" s="90"/>
-      <c r="D2" s="90"/>
-      <c r="E2" s="90"/>
-      <c r="F2" s="90"/>
-      <c r="G2" s="90"/>
-      <c r="H2" s="90"/>
+      <c r="B2" s="85"/>
+      <c r="C2" s="85"/>
+      <c r="D2" s="85"/>
+      <c r="E2" s="85"/>
+      <c r="F2" s="85"/>
+      <c r="G2" s="85"/>
+      <c r="H2" s="85"/>
     </row>
     <row r="3" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="90"/>
-      <c r="B3" s="90"/>
-      <c r="C3" s="90"/>
-      <c r="D3" s="90"/>
-      <c r="E3" s="90"/>
-      <c r="F3" s="90"/>
-      <c r="G3" s="90"/>
-      <c r="H3" s="90"/>
+      <c r="A3" s="85"/>
+      <c r="B3" s="85"/>
+      <c r="C3" s="85"/>
+      <c r="D3" s="85"/>
+      <c r="E3" s="85"/>
+      <c r="F3" s="85"/>
+      <c r="G3" s="85"/>
+      <c r="H3" s="85"/>
     </row>
     <row r="4" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="90"/>
-      <c r="B4" s="90"/>
-      <c r="C4" s="90"/>
-      <c r="D4" s="90"/>
-      <c r="E4" s="90"/>
-      <c r="F4" s="90"/>
-      <c r="G4" s="90"/>
-      <c r="H4" s="90"/>
+      <c r="A4" s="85"/>
+      <c r="B4" s="85"/>
+      <c r="C4" s="85"/>
+      <c r="D4" s="85"/>
+      <c r="E4" s="85"/>
+      <c r="F4" s="85"/>
+      <c r="G4" s="85"/>
+      <c r="H4" s="85"/>
     </row>
     <row r="5" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="76"/>
-      <c r="B5" s="76"/>
-      <c r="C5" s="76"/>
+      <c r="A5" s="49"/>
+      <c r="B5" s="49"/>
+      <c r="C5" s="49"/>
     </row>
     <row r="6" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="89" t="s">
+      <c r="A6" s="84" t="s">
         <v>21</v>
       </c>
-      <c r="B6" s="89" t="s">
+      <c r="B6" s="84" t="s">
         <v>22</v>
       </c>
-      <c r="C6" s="89"/>
-      <c r="D6" s="89"/>
-      <c r="E6" s="89" t="s">
+      <c r="C6" s="84"/>
+      <c r="D6" s="84"/>
+      <c r="E6" s="84" t="s">
         <v>23</v>
       </c>
-      <c r="F6" s="91" t="s">
+      <c r="F6" s="86" t="s">
         <v>24</v>
       </c>
-      <c r="G6" s="92"/>
-      <c r="H6" s="95" t="s">
+      <c r="G6" s="87"/>
+      <c r="H6" s="90" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="7" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="89"/>
+      <c r="A7" s="84"/>
       <c r="B7" s="23" t="s">
         <v>26</v>
       </c>
@@ -5118,19 +5133,19 @@
       <c r="D7" s="23" t="s">
         <v>28</v>
       </c>
-      <c r="E7" s="89"/>
-      <c r="F7" s="93"/>
-      <c r="G7" s="94"/>
-      <c r="H7" s="96"/>
+      <c r="E7" s="84"/>
+      <c r="F7" s="88"/>
+      <c r="G7" s="89"/>
+      <c r="H7" s="91"/>
     </row>
     <row r="8" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="4">
         <v>1</v>
       </c>
-      <c r="B8" s="42" t="s">
+      <c r="B8" s="62" t="s">
         <v>29</v>
       </c>
-      <c r="C8" s="84" t="s">
+      <c r="C8" s="94" t="s">
         <v>30</v>
       </c>
       <c r="D8" s="4" t="s">
@@ -5139,10 +5154,10 @@
       <c r="E8" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="F8" s="86" t="s">
+      <c r="F8" s="82" t="s">
         <v>32</v>
       </c>
-      <c r="G8" s="87"/>
+      <c r="G8" s="83"/>
       <c r="H8" s="22" t="s">
         <v>33</v>
       </c>
@@ -5151,18 +5166,18 @@
       <c r="A9" s="4">
         <v>2</v>
       </c>
-      <c r="B9" s="83"/>
-      <c r="C9" s="85"/>
+      <c r="B9" s="92"/>
+      <c r="C9" s="95"/>
       <c r="D9" s="4" t="s">
         <v>34</v>
       </c>
       <c r="E9" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="F9" s="86" t="s">
+      <c r="F9" s="82" t="s">
         <v>32</v>
       </c>
-      <c r="G9" s="87"/>
+      <c r="G9" s="83"/>
       <c r="H9" s="22" t="s">
         <v>35</v>
       </c>
@@ -5171,8 +5186,8 @@
       <c r="A10" s="4">
         <v>3</v>
       </c>
-      <c r="B10" s="83"/>
-      <c r="C10" s="42" t="s">
+      <c r="B10" s="92"/>
+      <c r="C10" s="62" t="s">
         <v>36</v>
       </c>
       <c r="D10" s="4" t="s">
@@ -5181,10 +5196,10 @@
       <c r="E10" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="F10" s="86" t="s">
+      <c r="F10" s="82" t="s">
         <v>32</v>
       </c>
-      <c r="G10" s="87"/>
+      <c r="G10" s="83"/>
       <c r="H10" s="22" t="s">
         <v>35</v>
       </c>
@@ -5193,18 +5208,18 @@
       <c r="A11" s="4">
         <v>4</v>
       </c>
-      <c r="B11" s="82"/>
-      <c r="C11" s="82"/>
+      <c r="B11" s="93"/>
+      <c r="C11" s="93"/>
       <c r="D11" s="4" t="s">
         <v>38</v>
       </c>
       <c r="E11" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="F11" s="86" t="s">
+      <c r="F11" s="82" t="s">
         <v>32</v>
       </c>
-      <c r="G11" s="87"/>
+      <c r="G11" s="83"/>
       <c r="H11" s="22" t="s">
         <v>35</v>
       </c>
@@ -5213,7 +5228,7 @@
       <c r="A12" s="4">
         <v>5</v>
       </c>
-      <c r="B12" s="42" t="s">
+      <c r="B12" s="62" t="s">
         <v>39</v>
       </c>
       <c r="C12" s="4" t="s">
@@ -5223,10 +5238,10 @@
       <c r="E12" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="F12" s="86" t="s">
+      <c r="F12" s="82" t="s">
         <v>32</v>
       </c>
-      <c r="G12" s="87"/>
+      <c r="G12" s="83"/>
       <c r="H12" s="22" t="s">
         <v>33</v>
       </c>
@@ -5235,7 +5250,7 @@
       <c r="A13" s="4">
         <v>6</v>
       </c>
-      <c r="B13" s="82"/>
+      <c r="B13" s="93"/>
       <c r="C13" s="4" t="s">
         <v>41</v>
       </c>
@@ -5243,10 +5258,10 @@
       <c r="E13" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="F13" s="86" t="s">
+      <c r="F13" s="82" t="s">
         <v>32</v>
       </c>
-      <c r="G13" s="88"/>
+      <c r="G13" s="96"/>
       <c r="H13" s="22" t="s">
         <v>33</v>
       </c>
@@ -5255,7 +5270,7 @@
       <c r="A14" s="4">
         <v>7</v>
       </c>
-      <c r="B14" s="42" t="s">
+      <c r="B14" s="62" t="s">
         <v>42</v>
       </c>
       <c r="C14" s="4" t="s">
@@ -5265,10 +5280,10 @@
       <c r="E14" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="F14" s="86" t="s">
+      <c r="F14" s="82" t="s">
         <v>32</v>
       </c>
-      <c r="G14" s="87"/>
+      <c r="G14" s="83"/>
       <c r="H14" s="22" t="s">
         <v>33</v>
       </c>
@@ -5277,7 +5292,7 @@
       <c r="A15" s="4">
         <v>8</v>
       </c>
-      <c r="B15" s="82"/>
+      <c r="B15" s="93"/>
       <c r="C15" s="4" t="s">
         <v>44</v>
       </c>
@@ -5285,10 +5300,10 @@
       <c r="E15" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="F15" s="86" t="s">
+      <c r="F15" s="82" t="s">
         <v>32</v>
       </c>
-      <c r="G15" s="87"/>
+      <c r="G15" s="83"/>
       <c r="H15" s="22" t="s">
         <v>35</v>
       </c>
@@ -5297,7 +5312,7 @@
       <c r="A16" s="4">
         <v>9</v>
       </c>
-      <c r="B16" s="42" t="s">
+      <c r="B16" s="62" t="s">
         <v>45</v>
       </c>
       <c r="C16" s="4" t="s">
@@ -5307,10 +5322,10 @@
       <c r="E16" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="F16" s="86" t="s">
+      <c r="F16" s="82" t="s">
         <v>32</v>
       </c>
-      <c r="G16" s="87"/>
+      <c r="G16" s="83"/>
       <c r="H16" s="22" t="s">
         <v>35</v>
       </c>
@@ -5319,7 +5334,7 @@
       <c r="A17" s="4">
         <v>10</v>
       </c>
-      <c r="B17" s="82"/>
+      <c r="B17" s="93"/>
       <c r="C17" s="4" t="s">
         <v>48</v>
       </c>
@@ -5327,10 +5342,10 @@
       <c r="E17" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="F17" s="86" t="s">
+      <c r="F17" s="82" t="s">
         <v>32</v>
       </c>
-      <c r="G17" s="87"/>
+      <c r="G17" s="83"/>
       <c r="H17" s="22" t="s">
         <v>35</v>
       </c>
@@ -5339,7 +5354,7 @@
       <c r="A18" s="4">
         <v>11</v>
       </c>
-      <c r="B18" s="42" t="s">
+      <c r="B18" s="62" t="s">
         <v>49</v>
       </c>
       <c r="C18" s="4" t="s">
@@ -5349,10 +5364,10 @@
       <c r="E18" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="F18" s="86" t="s">
+      <c r="F18" s="82" t="s">
         <v>32</v>
       </c>
-      <c r="G18" s="87"/>
+      <c r="G18" s="83"/>
       <c r="H18" s="22" t="s">
         <v>33</v>
       </c>
@@ -5361,7 +5376,7 @@
       <c r="A19" s="4">
         <v>12</v>
       </c>
-      <c r="B19" s="82"/>
+      <c r="B19" s="93"/>
       <c r="C19" s="4" t="s">
         <v>49</v>
       </c>
@@ -5369,10 +5384,10 @@
       <c r="E19" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="F19" s="86" t="s">
+      <c r="F19" s="82" t="s">
         <v>32</v>
       </c>
-      <c r="G19" s="87"/>
+      <c r="G19" s="83"/>
       <c r="H19" s="22" t="s">
         <v>33</v>
       </c>
@@ -5381,7 +5396,7 @@
       <c r="A20" s="4">
         <v>13</v>
       </c>
-      <c r="B20" s="42" t="s">
+      <c r="B20" s="62" t="s">
         <v>51</v>
       </c>
       <c r="C20" s="4" t="s">
@@ -5391,10 +5406,10 @@
       <c r="E20" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="F20" s="86" t="s">
+      <c r="F20" s="82" t="s">
         <v>32</v>
       </c>
-      <c r="G20" s="87"/>
+      <c r="G20" s="83"/>
       <c r="H20" s="22" t="s">
         <v>35</v>
       </c>
@@ -5403,7 +5418,7 @@
       <c r="A21" s="4">
         <v>14</v>
       </c>
-      <c r="B21" s="82"/>
+      <c r="B21" s="93"/>
       <c r="C21" s="4" t="s">
         <v>53</v>
       </c>
@@ -5411,10 +5426,10 @@
       <c r="E21" s="4" t="s">
         <v>54</v>
       </c>
-      <c r="F21" s="86" t="s">
+      <c r="F21" s="82" t="s">
         <v>32</v>
       </c>
-      <c r="G21" s="87"/>
+      <c r="G21" s="83"/>
       <c r="H21" s="22" t="s">
         <v>35</v>
       </c>
@@ -5423,7 +5438,7 @@
       <c r="A22" s="4">
         <v>15</v>
       </c>
-      <c r="B22" s="42" t="s">
+      <c r="B22" s="62" t="s">
         <v>55</v>
       </c>
       <c r="C22" s="4" t="s">
@@ -5433,10 +5448,10 @@
       <c r="E22" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="F22" s="86" t="s">
+      <c r="F22" s="82" t="s">
         <v>32</v>
       </c>
-      <c r="G22" s="87"/>
+      <c r="G22" s="83"/>
       <c r="H22" s="22" t="s">
         <v>33</v>
       </c>
@@ -5445,7 +5460,7 @@
       <c r="A23" s="4">
         <v>16</v>
       </c>
-      <c r="B23" s="82"/>
+      <c r="B23" s="93"/>
       <c r="C23" s="4" t="s">
         <v>57</v>
       </c>
@@ -5453,10 +5468,10 @@
       <c r="E23" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="F23" s="86" t="s">
+      <c r="F23" s="82" t="s">
         <v>32</v>
       </c>
-      <c r="G23" s="87"/>
+      <c r="G23" s="83"/>
       <c r="H23" s="22" t="s">
         <v>33</v>
       </c>
@@ -5469,8 +5484,8 @@
       <c r="C24" s="4"/>
       <c r="D24" s="4"/>
       <c r="E24" s="4"/>
-      <c r="F24" s="86"/>
-      <c r="G24" s="87"/>
+      <c r="F24" s="82"/>
+      <c r="G24" s="83"/>
       <c r="H24" s="4"/>
     </row>
     <row r="25" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -5481,8 +5496,8 @@
       <c r="C25" s="4"/>
       <c r="D25" s="4"/>
       <c r="E25" s="4"/>
-      <c r="F25" s="86"/>
-      <c r="G25" s="87"/>
+      <c r="F25" s="82"/>
+      <c r="G25" s="83"/>
       <c r="H25" s="4"/>
     </row>
     <row r="26" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -5493,8 +5508,8 @@
       <c r="C26" s="4"/>
       <c r="D26" s="4"/>
       <c r="E26" s="4"/>
-      <c r="F26" s="86"/>
-      <c r="G26" s="87"/>
+      <c r="F26" s="82"/>
+      <c r="G26" s="83"/>
       <c r="H26" s="4"/>
     </row>
     <row r="27" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -5505,8 +5520,8 @@
       <c r="C27" s="4"/>
       <c r="D27" s="4"/>
       <c r="E27" s="4"/>
-      <c r="F27" s="86"/>
-      <c r="G27" s="87"/>
+      <c r="F27" s="82"/>
+      <c r="G27" s="83"/>
       <c r="H27" s="4"/>
     </row>
     <row r="28" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -5517,8 +5532,8 @@
       <c r="C28" s="4"/>
       <c r="D28" s="4"/>
       <c r="E28" s="4"/>
-      <c r="F28" s="86"/>
-      <c r="G28" s="87"/>
+      <c r="F28" s="82"/>
+      <c r="G28" s="83"/>
       <c r="H28" s="4"/>
     </row>
     <row r="29" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -5529,8 +5544,8 @@
       <c r="C29" s="4"/>
       <c r="D29" s="4"/>
       <c r="E29" s="4"/>
-      <c r="F29" s="86"/>
-      <c r="G29" s="87"/>
+      <c r="F29" s="82"/>
+      <c r="G29" s="83"/>
       <c r="H29" s="4"/>
     </row>
     <row r="30" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -5541,8 +5556,8 @@
       <c r="C30" s="4"/>
       <c r="D30" s="4"/>
       <c r="E30" s="4"/>
-      <c r="F30" s="86"/>
-      <c r="G30" s="87"/>
+      <c r="F30" s="82"/>
+      <c r="G30" s="83"/>
       <c r="H30" s="4"/>
     </row>
     <row r="31" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -5553,8 +5568,8 @@
       <c r="C31" s="4"/>
       <c r="D31" s="4"/>
       <c r="E31" s="4"/>
-      <c r="F31" s="86"/>
-      <c r="G31" s="87"/>
+      <c r="F31" s="82"/>
+      <c r="G31" s="83"/>
       <c r="H31" s="4"/>
     </row>
     <row r="32" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -5565,8 +5580,8 @@
       <c r="C32" s="4"/>
       <c r="D32" s="4"/>
       <c r="E32" s="4"/>
-      <c r="F32" s="86"/>
-      <c r="G32" s="87"/>
+      <c r="F32" s="82"/>
+      <c r="G32" s="83"/>
       <c r="H32" s="4"/>
     </row>
     <row r="33" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -5577,8 +5592,8 @@
       <c r="C33" s="4"/>
       <c r="D33" s="4"/>
       <c r="E33" s="4"/>
-      <c r="F33" s="86"/>
-      <c r="G33" s="87"/>
+      <c r="F33" s="82"/>
+      <c r="G33" s="83"/>
       <c r="H33" s="4"/>
     </row>
     <row r="34" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -5589,8 +5604,8 @@
       <c r="C34" s="4"/>
       <c r="D34" s="4"/>
       <c r="E34" s="4"/>
-      <c r="F34" s="86"/>
-      <c r="G34" s="87"/>
+      <c r="F34" s="82"/>
+      <c r="G34" s="83"/>
       <c r="H34" s="4"/>
     </row>
     <row r="35" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -5601,8 +5616,8 @@
       <c r="C35" s="4"/>
       <c r="D35" s="4"/>
       <c r="E35" s="4"/>
-      <c r="F35" s="86"/>
-      <c r="G35" s="87"/>
+      <c r="F35" s="82"/>
+      <c r="G35" s="83"/>
       <c r="H35" s="4"/>
     </row>
     <row r="36" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -5613,8 +5628,8 @@
       <c r="C36" s="4"/>
       <c r="D36" s="4"/>
       <c r="E36" s="4"/>
-      <c r="F36" s="86"/>
-      <c r="G36" s="87"/>
+      <c r="F36" s="82"/>
+      <c r="G36" s="83"/>
       <c r="H36" s="4"/>
     </row>
     <row r="37" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -5625,40 +5640,18 @@
       <c r="C37" s="4"/>
       <c r="D37" s="4"/>
       <c r="E37" s="4"/>
-      <c r="F37" s="86"/>
-      <c r="G37" s="87"/>
+      <c r="F37" s="82"/>
+      <c r="G37" s="83"/>
       <c r="H37" s="4"/>
     </row>
   </sheetData>
   <mergeCells count="47">
-    <mergeCell ref="F33:G33"/>
-    <mergeCell ref="F34:G34"/>
-    <mergeCell ref="F35:G35"/>
-    <mergeCell ref="F36:G36"/>
-    <mergeCell ref="F37:G37"/>
-    <mergeCell ref="F28:G28"/>
-    <mergeCell ref="F29:G29"/>
-    <mergeCell ref="F30:G30"/>
-    <mergeCell ref="F31:G31"/>
-    <mergeCell ref="F32:G32"/>
-    <mergeCell ref="F23:G23"/>
-    <mergeCell ref="F24:G24"/>
-    <mergeCell ref="F25:G25"/>
-    <mergeCell ref="F26:G26"/>
-    <mergeCell ref="F27:G27"/>
-    <mergeCell ref="F18:G18"/>
-    <mergeCell ref="F19:G19"/>
-    <mergeCell ref="F20:G20"/>
-    <mergeCell ref="F21:G21"/>
-    <mergeCell ref="F22:G22"/>
-    <mergeCell ref="A1:C1"/>
-    <mergeCell ref="A5:C5"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="B6:D6"/>
-    <mergeCell ref="E6:E7"/>
-    <mergeCell ref="A2:H4"/>
-    <mergeCell ref="F6:G7"/>
-    <mergeCell ref="H6:H7"/>
+    <mergeCell ref="B20:B21"/>
+    <mergeCell ref="B22:B23"/>
+    <mergeCell ref="B12:B13"/>
+    <mergeCell ref="B14:B15"/>
+    <mergeCell ref="B16:B17"/>
+    <mergeCell ref="B18:B19"/>
     <mergeCell ref="B8:B11"/>
     <mergeCell ref="C8:C9"/>
     <mergeCell ref="C10:C11"/>
@@ -5672,12 +5665,34 @@
     <mergeCell ref="F11:G11"/>
     <mergeCell ref="F12:G12"/>
     <mergeCell ref="F13:G13"/>
-    <mergeCell ref="B20:B21"/>
-    <mergeCell ref="B22:B23"/>
-    <mergeCell ref="B12:B13"/>
-    <mergeCell ref="B14:B15"/>
-    <mergeCell ref="B16:B17"/>
-    <mergeCell ref="B18:B19"/>
+    <mergeCell ref="A1:C1"/>
+    <mergeCell ref="A5:C5"/>
+    <mergeCell ref="A6:A7"/>
+    <mergeCell ref="B6:D6"/>
+    <mergeCell ref="E6:E7"/>
+    <mergeCell ref="A2:H4"/>
+    <mergeCell ref="F6:G7"/>
+    <mergeCell ref="H6:H7"/>
+    <mergeCell ref="F18:G18"/>
+    <mergeCell ref="F19:G19"/>
+    <mergeCell ref="F20:G20"/>
+    <mergeCell ref="F21:G21"/>
+    <mergeCell ref="F22:G22"/>
+    <mergeCell ref="F23:G23"/>
+    <mergeCell ref="F24:G24"/>
+    <mergeCell ref="F25:G25"/>
+    <mergeCell ref="F26:G26"/>
+    <mergeCell ref="F27:G27"/>
+    <mergeCell ref="F28:G28"/>
+    <mergeCell ref="F29:G29"/>
+    <mergeCell ref="F30:G30"/>
+    <mergeCell ref="F31:G31"/>
+    <mergeCell ref="F32:G32"/>
+    <mergeCell ref="F33:G33"/>
+    <mergeCell ref="F34:G34"/>
+    <mergeCell ref="F35:G35"/>
+    <mergeCell ref="F36:G36"/>
+    <mergeCell ref="F37:G37"/>
   </mergeCells>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.75" right="0.75" top="0.6" bottom="0.61" header="0.4" footer="0.39"/>
@@ -5704,90 +5719,90 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="101" t="s">
+      <c r="A1" s="97" t="s">
         <v>58</v>
       </c>
-      <c r="B1" s="102"/>
-      <c r="C1" s="103"/>
+      <c r="B1" s="98"/>
+      <c r="C1" s="99"/>
       <c r="D1" s="19"/>
     </row>
     <row r="2" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="90" t="s">
+      <c r="A2" s="85" t="s">
         <v>59</v>
       </c>
-      <c r="B2" s="90"/>
-      <c r="C2" s="90"/>
-      <c r="D2" s="90"/>
-      <c r="E2" s="90"/>
-      <c r="F2" s="90"/>
-      <c r="G2" s="90"/>
-      <c r="H2" s="90"/>
-      <c r="I2" s="90"/>
+      <c r="B2" s="85"/>
+      <c r="C2" s="85"/>
+      <c r="D2" s="85"/>
+      <c r="E2" s="85"/>
+      <c r="F2" s="85"/>
+      <c r="G2" s="85"/>
+      <c r="H2" s="85"/>
+      <c r="I2" s="85"/>
     </row>
     <row r="3" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="90"/>
-      <c r="B3" s="90"/>
-      <c r="C3" s="90"/>
-      <c r="D3" s="90"/>
-      <c r="E3" s="90"/>
-      <c r="F3" s="90"/>
-      <c r="G3" s="90"/>
-      <c r="H3" s="90"/>
-      <c r="I3" s="90"/>
+      <c r="A3" s="85"/>
+      <c r="B3" s="85"/>
+      <c r="C3" s="85"/>
+      <c r="D3" s="85"/>
+      <c r="E3" s="85"/>
+      <c r="F3" s="85"/>
+      <c r="G3" s="85"/>
+      <c r="H3" s="85"/>
+      <c r="I3" s="85"/>
     </row>
     <row r="4" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="76"/>
-      <c r="B4" s="76"/>
+      <c r="A4" s="49"/>
+      <c r="B4" s="49"/>
     </row>
     <row r="5" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="89" t="s">
+      <c r="A5" s="84" t="s">
         <v>21</v>
       </c>
-      <c r="B5" s="95" t="s">
+      <c r="B5" s="90" t="s">
         <v>60</v>
       </c>
-      <c r="C5" s="95" t="s">
+      <c r="C5" s="90" t="s">
         <v>61</v>
       </c>
-      <c r="D5" s="91" t="s">
+      <c r="D5" s="86" t="s">
         <v>24</v>
       </c>
-      <c r="E5" s="92"/>
-      <c r="F5" s="92"/>
-      <c r="G5" s="92"/>
-      <c r="H5" s="92"/>
-      <c r="I5" s="89" t="s">
+      <c r="E5" s="87"/>
+      <c r="F5" s="87"/>
+      <c r="G5" s="87"/>
+      <c r="H5" s="87"/>
+      <c r="I5" s="84" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="6" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="89"/>
-      <c r="B6" s="96"/>
-      <c r="C6" s="96"/>
-      <c r="D6" s="93"/>
-      <c r="E6" s="94"/>
-      <c r="F6" s="94"/>
-      <c r="G6" s="94"/>
-      <c r="H6" s="94"/>
-      <c r="I6" s="89"/>
+      <c r="A6" s="84"/>
+      <c r="B6" s="91"/>
+      <c r="C6" s="91"/>
+      <c r="D6" s="88"/>
+      <c r="E6" s="89"/>
+      <c r="F6" s="89"/>
+      <c r="G6" s="89"/>
+      <c r="H6" s="89"/>
+      <c r="I6" s="84"/>
     </row>
     <row r="7" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="4">
         <v>1</v>
       </c>
-      <c r="B7" s="97" t="s">
+      <c r="B7" s="103" t="s">
         <v>62</v>
       </c>
       <c r="C7" s="22" t="s">
         <v>63</v>
       </c>
-      <c r="D7" s="44" t="s">
+      <c r="D7" s="34" t="s">
         <v>32</v>
       </c>
-      <c r="E7" s="44"/>
-      <c r="F7" s="44"/>
-      <c r="G7" s="44"/>
-      <c r="H7" s="44"/>
+      <c r="E7" s="34"/>
+      <c r="F7" s="34"/>
+      <c r="G7" s="34"/>
+      <c r="H7" s="34"/>
       <c r="I7" s="22" t="s">
         <v>64</v>
       </c>
@@ -5796,15 +5811,15 @@
       <c r="A8" s="4">
         <v>2</v>
       </c>
-      <c r="B8" s="98"/>
+      <c r="B8" s="101"/>
       <c r="C8" s="22"/>
-      <c r="D8" s="44" t="s">
+      <c r="D8" s="34" t="s">
         <v>65</v>
       </c>
-      <c r="E8" s="44"/>
-      <c r="F8" s="44"/>
-      <c r="G8" s="44"/>
-      <c r="H8" s="44"/>
+      <c r="E8" s="34"/>
+      <c r="F8" s="34"/>
+      <c r="G8" s="34"/>
+      <c r="H8" s="34"/>
       <c r="I8" s="22" t="s">
         <v>66</v>
       </c>
@@ -5813,26 +5828,26 @@
       <c r="A9" s="4">
         <v>3</v>
       </c>
-      <c r="B9" s="98"/>
+      <c r="B9" s="101"/>
       <c r="C9" s="22"/>
-      <c r="D9" s="44"/>
-      <c r="E9" s="44"/>
-      <c r="F9" s="44"/>
-      <c r="G9" s="44"/>
-      <c r="H9" s="44"/>
+      <c r="D9" s="34"/>
+      <c r="E9" s="34"/>
+      <c r="F9" s="34"/>
+      <c r="G9" s="34"/>
+      <c r="H9" s="34"/>
       <c r="I9" s="4"/>
     </row>
     <row r="10" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="4">
         <v>4</v>
       </c>
-      <c r="B10" s="99"/>
+      <c r="B10" s="102"/>
       <c r="C10" s="22"/>
-      <c r="D10" s="44"/>
-      <c r="E10" s="44"/>
-      <c r="F10" s="44"/>
-      <c r="G10" s="44"/>
-      <c r="H10" s="44"/>
+      <c r="D10" s="34"/>
+      <c r="E10" s="34"/>
+      <c r="F10" s="34"/>
+      <c r="G10" s="34"/>
+      <c r="H10" s="34"/>
       <c r="I10" s="4"/>
     </row>
     <row r="11" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -5845,13 +5860,13 @@
       <c r="C11" s="22" t="s">
         <v>68</v>
       </c>
-      <c r="D11" s="44" t="s">
+      <c r="D11" s="34" t="s">
         <v>32</v>
       </c>
-      <c r="E11" s="44"/>
-      <c r="F11" s="44"/>
-      <c r="G11" s="44"/>
-      <c r="H11" s="44"/>
+      <c r="E11" s="34"/>
+      <c r="F11" s="34"/>
+      <c r="G11" s="34"/>
+      <c r="H11" s="34"/>
       <c r="I11" s="22" t="s">
         <v>66</v>
       </c>
@@ -5860,15 +5875,15 @@
       <c r="A12" s="4">
         <v>6</v>
       </c>
-      <c r="B12" s="98"/>
+      <c r="B12" s="101"/>
       <c r="C12" s="4"/>
-      <c r="D12" s="44" t="s">
+      <c r="D12" s="34" t="s">
         <v>69</v>
       </c>
-      <c r="E12" s="44"/>
-      <c r="F12" s="44"/>
-      <c r="G12" s="44"/>
-      <c r="H12" s="44"/>
+      <c r="E12" s="34"/>
+      <c r="F12" s="34"/>
+      <c r="G12" s="34"/>
+      <c r="H12" s="34"/>
       <c r="I12" s="22" t="s">
         <v>64</v>
       </c>
@@ -5877,15 +5892,15 @@
       <c r="A13" s="4">
         <v>7</v>
       </c>
-      <c r="B13" s="98"/>
+      <c r="B13" s="101"/>
       <c r="C13" s="4"/>
-      <c r="D13" s="44" t="s">
+      <c r="D13" s="34" t="s">
         <v>70</v>
       </c>
-      <c r="E13" s="44"/>
-      <c r="F13" s="44"/>
-      <c r="G13" s="44"/>
-      <c r="H13" s="44"/>
+      <c r="E13" s="34"/>
+      <c r="F13" s="34"/>
+      <c r="G13" s="34"/>
+      <c r="H13" s="34"/>
       <c r="I13" s="22" t="s">
         <v>64</v>
       </c>
@@ -5894,13 +5909,13 @@
       <c r="A14" s="4">
         <v>8</v>
       </c>
-      <c r="B14" s="99"/>
+      <c r="B14" s="102"/>
       <c r="C14" s="4"/>
-      <c r="D14" s="44"/>
-      <c r="E14" s="44"/>
-      <c r="F14" s="44"/>
-      <c r="G14" s="44"/>
-      <c r="H14" s="44"/>
+      <c r="D14" s="34"/>
+      <c r="E14" s="34"/>
+      <c r="F14" s="34"/>
+      <c r="G14" s="34"/>
+      <c r="H14" s="34"/>
       <c r="I14" s="4"/>
     </row>
     <row r="15" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -5911,50 +5926,50 @@
         <v>71</v>
       </c>
       <c r="C15" s="4"/>
-      <c r="D15" s="44"/>
-      <c r="E15" s="44"/>
-      <c r="F15" s="44"/>
-      <c r="G15" s="44"/>
-      <c r="H15" s="44"/>
+      <c r="D15" s="34"/>
+      <c r="E15" s="34"/>
+      <c r="F15" s="34"/>
+      <c r="G15" s="34"/>
+      <c r="H15" s="34"/>
       <c r="I15" s="4"/>
     </row>
     <row r="16" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="4">
         <v>10</v>
       </c>
-      <c r="B16" s="98"/>
+      <c r="B16" s="101"/>
       <c r="C16" s="4"/>
-      <c r="D16" s="44"/>
-      <c r="E16" s="44"/>
-      <c r="F16" s="44"/>
-      <c r="G16" s="44"/>
-      <c r="H16" s="44"/>
+      <c r="D16" s="34"/>
+      <c r="E16" s="34"/>
+      <c r="F16" s="34"/>
+      <c r="G16" s="34"/>
+      <c r="H16" s="34"/>
       <c r="I16" s="4"/>
     </row>
     <row r="17" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="4">
         <v>11</v>
       </c>
-      <c r="B17" s="98"/>
+      <c r="B17" s="101"/>
       <c r="C17" s="4"/>
-      <c r="D17" s="44"/>
-      <c r="E17" s="44"/>
-      <c r="F17" s="44"/>
-      <c r="G17" s="44"/>
-      <c r="H17" s="44"/>
+      <c r="D17" s="34"/>
+      <c r="E17" s="34"/>
+      <c r="F17" s="34"/>
+      <c r="G17" s="34"/>
+      <c r="H17" s="34"/>
       <c r="I17" s="4"/>
     </row>
     <row r="18" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="4">
         <v>12</v>
       </c>
-      <c r="B18" s="99"/>
+      <c r="B18" s="102"/>
       <c r="C18" s="4"/>
-      <c r="D18" s="44"/>
-      <c r="E18" s="44"/>
-      <c r="F18" s="44"/>
-      <c r="G18" s="44"/>
-      <c r="H18" s="44"/>
+      <c r="D18" s="34"/>
+      <c r="E18" s="34"/>
+      <c r="F18" s="34"/>
+      <c r="G18" s="34"/>
+      <c r="H18" s="34"/>
       <c r="I18" s="4"/>
     </row>
     <row r="19" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -5965,50 +5980,50 @@
         <v>72</v>
       </c>
       <c r="C19" s="4"/>
-      <c r="D19" s="44"/>
-      <c r="E19" s="44"/>
-      <c r="F19" s="44"/>
-      <c r="G19" s="44"/>
-      <c r="H19" s="44"/>
+      <c r="D19" s="34"/>
+      <c r="E19" s="34"/>
+      <c r="F19" s="34"/>
+      <c r="G19" s="34"/>
+      <c r="H19" s="34"/>
       <c r="I19" s="4"/>
     </row>
     <row r="20" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="4">
         <v>14</v>
       </c>
-      <c r="B20" s="98"/>
+      <c r="B20" s="101"/>
       <c r="C20" s="4"/>
-      <c r="D20" s="44"/>
-      <c r="E20" s="44"/>
-      <c r="F20" s="44"/>
-      <c r="G20" s="44"/>
-      <c r="H20" s="44"/>
+      <c r="D20" s="34"/>
+      <c r="E20" s="34"/>
+      <c r="F20" s="34"/>
+      <c r="G20" s="34"/>
+      <c r="H20" s="34"/>
       <c r="I20" s="4"/>
     </row>
     <row r="21" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="4">
         <v>15</v>
       </c>
-      <c r="B21" s="98"/>
+      <c r="B21" s="101"/>
       <c r="C21" s="4"/>
-      <c r="D21" s="44"/>
-      <c r="E21" s="44"/>
-      <c r="F21" s="44"/>
-      <c r="G21" s="44"/>
-      <c r="H21" s="44"/>
+      <c r="D21" s="34"/>
+      <c r="E21" s="34"/>
+      <c r="F21" s="34"/>
+      <c r="G21" s="34"/>
+      <c r="H21" s="34"/>
       <c r="I21" s="4"/>
     </row>
     <row r="22" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="4">
         <v>16</v>
       </c>
-      <c r="B22" s="99"/>
+      <c r="B22" s="102"/>
       <c r="C22" s="4"/>
-      <c r="D22" s="44"/>
-      <c r="E22" s="44"/>
-      <c r="F22" s="44"/>
-      <c r="G22" s="44"/>
-      <c r="H22" s="44"/>
+      <c r="D22" s="34"/>
+      <c r="E22" s="34"/>
+      <c r="F22" s="34"/>
+      <c r="G22" s="34"/>
+      <c r="H22" s="34"/>
       <c r="I22" s="4"/>
     </row>
     <row r="23" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -6019,50 +6034,50 @@
         <v>73</v>
       </c>
       <c r="C23" s="4"/>
-      <c r="D23" s="44"/>
-      <c r="E23" s="44"/>
-      <c r="F23" s="44"/>
-      <c r="G23" s="44"/>
-      <c r="H23" s="44"/>
+      <c r="D23" s="34"/>
+      <c r="E23" s="34"/>
+      <c r="F23" s="34"/>
+      <c r="G23" s="34"/>
+      <c r="H23" s="34"/>
       <c r="I23" s="4"/>
     </row>
     <row r="24" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" s="4">
         <v>18</v>
       </c>
-      <c r="B24" s="98"/>
+      <c r="B24" s="101"/>
       <c r="C24" s="4"/>
-      <c r="D24" s="44"/>
-      <c r="E24" s="44"/>
-      <c r="F24" s="44"/>
-      <c r="G24" s="44"/>
-      <c r="H24" s="44"/>
+      <c r="D24" s="34"/>
+      <c r="E24" s="34"/>
+      <c r="F24" s="34"/>
+      <c r="G24" s="34"/>
+      <c r="H24" s="34"/>
       <c r="I24" s="4"/>
     </row>
     <row r="25" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A25" s="4">
         <v>19</v>
       </c>
-      <c r="B25" s="98"/>
+      <c r="B25" s="101"/>
       <c r="C25" s="4"/>
-      <c r="D25" s="44"/>
-      <c r="E25" s="44"/>
-      <c r="F25" s="44"/>
-      <c r="G25" s="44"/>
-      <c r="H25" s="44"/>
+      <c r="D25" s="34"/>
+      <c r="E25" s="34"/>
+      <c r="F25" s="34"/>
+      <c r="G25" s="34"/>
+      <c r="H25" s="34"/>
       <c r="I25" s="4"/>
     </row>
     <row r="26" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26" s="4">
         <v>20</v>
       </c>
-      <c r="B26" s="99"/>
+      <c r="B26" s="102"/>
       <c r="C26" s="4"/>
-      <c r="D26" s="44"/>
-      <c r="E26" s="44"/>
-      <c r="F26" s="44"/>
-      <c r="G26" s="44"/>
-      <c r="H26" s="44"/>
+      <c r="D26" s="34"/>
+      <c r="E26" s="34"/>
+      <c r="F26" s="34"/>
+      <c r="G26" s="34"/>
+      <c r="H26" s="34"/>
       <c r="I26" s="4"/>
     </row>
     <row r="27" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -6073,50 +6088,50 @@
         <v>74</v>
       </c>
       <c r="C27" s="4"/>
-      <c r="D27" s="44"/>
-      <c r="E27" s="44"/>
-      <c r="F27" s="44"/>
-      <c r="G27" s="44"/>
-      <c r="H27" s="44"/>
+      <c r="D27" s="34"/>
+      <c r="E27" s="34"/>
+      <c r="F27" s="34"/>
+      <c r="G27" s="34"/>
+      <c r="H27" s="34"/>
       <c r="I27" s="4"/>
     </row>
     <row r="28" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A28" s="4">
         <v>22</v>
       </c>
-      <c r="B28" s="98"/>
+      <c r="B28" s="101"/>
       <c r="C28" s="4"/>
-      <c r="D28" s="44"/>
-      <c r="E28" s="44"/>
-      <c r="F28" s="44"/>
-      <c r="G28" s="44"/>
-      <c r="H28" s="44"/>
+      <c r="D28" s="34"/>
+      <c r="E28" s="34"/>
+      <c r="F28" s="34"/>
+      <c r="G28" s="34"/>
+      <c r="H28" s="34"/>
       <c r="I28" s="4"/>
     </row>
     <row r="29" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A29" s="4">
         <v>23</v>
       </c>
-      <c r="B29" s="98"/>
+      <c r="B29" s="101"/>
       <c r="C29" s="4"/>
-      <c r="D29" s="44"/>
-      <c r="E29" s="44"/>
-      <c r="F29" s="44"/>
-      <c r="G29" s="44"/>
-      <c r="H29" s="44"/>
+      <c r="D29" s="34"/>
+      <c r="E29" s="34"/>
+      <c r="F29" s="34"/>
+      <c r="G29" s="34"/>
+      <c r="H29" s="34"/>
       <c r="I29" s="4"/>
     </row>
     <row r="30" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A30" s="4">
         <v>24</v>
       </c>
-      <c r="B30" s="99"/>
+      <c r="B30" s="102"/>
       <c r="C30" s="4"/>
-      <c r="D30" s="44"/>
-      <c r="E30" s="44"/>
-      <c r="F30" s="44"/>
-      <c r="G30" s="44"/>
-      <c r="H30" s="44"/>
+      <c r="D30" s="34"/>
+      <c r="E30" s="34"/>
+      <c r="F30" s="34"/>
+      <c r="G30" s="34"/>
+      <c r="H30" s="34"/>
       <c r="I30" s="4"/>
     </row>
     <row r="31" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -6125,11 +6140,11 @@
       </c>
       <c r="B31" s="4"/>
       <c r="C31" s="4"/>
-      <c r="D31" s="44"/>
-      <c r="E31" s="44"/>
-      <c r="F31" s="44"/>
-      <c r="G31" s="44"/>
-      <c r="H31" s="44"/>
+      <c r="D31" s="34"/>
+      <c r="E31" s="34"/>
+      <c r="F31" s="34"/>
+      <c r="G31" s="34"/>
+      <c r="H31" s="34"/>
       <c r="I31" s="4"/>
     </row>
     <row r="32" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -6138,11 +6153,11 @@
       </c>
       <c r="B32" s="4"/>
       <c r="C32" s="4"/>
-      <c r="D32" s="44"/>
-      <c r="E32" s="44"/>
-      <c r="F32" s="44"/>
-      <c r="G32" s="44"/>
-      <c r="H32" s="44"/>
+      <c r="D32" s="34"/>
+      <c r="E32" s="34"/>
+      <c r="F32" s="34"/>
+      <c r="G32" s="34"/>
+      <c r="H32" s="34"/>
       <c r="I32" s="4"/>
     </row>
     <row r="33" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -6151,11 +6166,11 @@
       </c>
       <c r="B33" s="4"/>
       <c r="C33" s="4"/>
-      <c r="D33" s="44"/>
-      <c r="E33" s="44"/>
-      <c r="F33" s="44"/>
-      <c r="G33" s="44"/>
-      <c r="H33" s="44"/>
+      <c r="D33" s="34"/>
+      <c r="E33" s="34"/>
+      <c r="F33" s="34"/>
+      <c r="G33" s="34"/>
+      <c r="H33" s="34"/>
       <c r="I33" s="4"/>
     </row>
     <row r="34" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -6164,11 +6179,11 @@
       </c>
       <c r="B34" s="4"/>
       <c r="C34" s="4"/>
-      <c r="D34" s="44"/>
-      <c r="E34" s="44"/>
-      <c r="F34" s="44"/>
-      <c r="G34" s="44"/>
-      <c r="H34" s="44"/>
+      <c r="D34" s="34"/>
+      <c r="E34" s="34"/>
+      <c r="F34" s="34"/>
+      <c r="G34" s="34"/>
+      <c r="H34" s="34"/>
       <c r="I34" s="4"/>
     </row>
     <row r="35" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -6177,11 +6192,11 @@
       </c>
       <c r="B35" s="4"/>
       <c r="C35" s="4"/>
-      <c r="D35" s="44"/>
-      <c r="E35" s="44"/>
-      <c r="F35" s="44"/>
-      <c r="G35" s="44"/>
-      <c r="H35" s="44"/>
+      <c r="D35" s="34"/>
+      <c r="E35" s="34"/>
+      <c r="F35" s="34"/>
+      <c r="G35" s="34"/>
+      <c r="H35" s="34"/>
       <c r="I35" s="4"/>
     </row>
     <row r="36" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -6190,15 +6205,43 @@
       </c>
       <c r="B36" s="4"/>
       <c r="C36" s="4"/>
-      <c r="D36" s="44"/>
-      <c r="E36" s="44"/>
-      <c r="F36" s="44"/>
-      <c r="G36" s="44"/>
-      <c r="H36" s="44"/>
+      <c r="D36" s="34"/>
+      <c r="E36" s="34"/>
+      <c r="F36" s="34"/>
+      <c r="G36" s="34"/>
+      <c r="H36" s="34"/>
       <c r="I36" s="4"/>
     </row>
   </sheetData>
   <mergeCells count="44">
+    <mergeCell ref="B7:B10"/>
+    <mergeCell ref="B15:B18"/>
+    <mergeCell ref="B19:B22"/>
+    <mergeCell ref="B23:B26"/>
+    <mergeCell ref="B27:B30"/>
+    <mergeCell ref="A2:I3"/>
+    <mergeCell ref="A4:B4"/>
+    <mergeCell ref="A5:A6"/>
+    <mergeCell ref="C5:C6"/>
+    <mergeCell ref="B5:B6"/>
+    <mergeCell ref="D5:H6"/>
+    <mergeCell ref="I5:I6"/>
+    <mergeCell ref="D15:H15"/>
+    <mergeCell ref="D16:H16"/>
+    <mergeCell ref="D17:H17"/>
+    <mergeCell ref="D25:H25"/>
+    <mergeCell ref="D26:H26"/>
+    <mergeCell ref="D20:H20"/>
+    <mergeCell ref="D21:H21"/>
+    <mergeCell ref="D22:H22"/>
+    <mergeCell ref="D23:H23"/>
+    <mergeCell ref="D24:H24"/>
+    <mergeCell ref="D36:H36"/>
+    <mergeCell ref="D27:H27"/>
+    <mergeCell ref="D28:H28"/>
+    <mergeCell ref="D29:H29"/>
+    <mergeCell ref="D30:H30"/>
+    <mergeCell ref="D31:H31"/>
     <mergeCell ref="A1:C1"/>
     <mergeCell ref="D32:H32"/>
     <mergeCell ref="D33:H33"/>
@@ -6215,34 +6258,6 @@
     <mergeCell ref="D12:H12"/>
     <mergeCell ref="D13:H13"/>
     <mergeCell ref="D14:H14"/>
-    <mergeCell ref="D36:H36"/>
-    <mergeCell ref="D27:H27"/>
-    <mergeCell ref="D28:H28"/>
-    <mergeCell ref="D29:H29"/>
-    <mergeCell ref="D30:H30"/>
-    <mergeCell ref="D31:H31"/>
-    <mergeCell ref="D15:H15"/>
-    <mergeCell ref="D16:H16"/>
-    <mergeCell ref="D17:H17"/>
-    <mergeCell ref="D25:H25"/>
-    <mergeCell ref="D26:H26"/>
-    <mergeCell ref="D20:H20"/>
-    <mergeCell ref="D21:H21"/>
-    <mergeCell ref="D22:H22"/>
-    <mergeCell ref="D23:H23"/>
-    <mergeCell ref="D24:H24"/>
-    <mergeCell ref="A2:I3"/>
-    <mergeCell ref="A4:B4"/>
-    <mergeCell ref="A5:A6"/>
-    <mergeCell ref="C5:C6"/>
-    <mergeCell ref="B5:B6"/>
-    <mergeCell ref="D5:H6"/>
-    <mergeCell ref="I5:I6"/>
-    <mergeCell ref="B7:B10"/>
-    <mergeCell ref="B15:B18"/>
-    <mergeCell ref="B19:B22"/>
-    <mergeCell ref="B23:B26"/>
-    <mergeCell ref="B27:B30"/>
   </mergeCells>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.75" right="0.75" top="0.6" bottom="0.61" header="0.4" footer="0.39"/>
@@ -6266,23 +6281,23 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:52" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B1" s="191" t="s">
+      <c r="B1" s="104" t="s">
         <v>75</v>
       </c>
-      <c r="C1" s="192"/>
-      <c r="D1" s="192"/>
-      <c r="E1" s="192"/>
-      <c r="F1" s="192"/>
-      <c r="G1" s="192"/>
-      <c r="H1" s="192"/>
-      <c r="I1" s="192"/>
-      <c r="J1" s="192"/>
-      <c r="K1" s="192"/>
-      <c r="L1" s="192"/>
-      <c r="M1" s="192"/>
-      <c r="N1" s="192"/>
-      <c r="O1" s="192"/>
-      <c r="P1" s="192"/>
+      <c r="C1" s="105"/>
+      <c r="D1" s="105"/>
+      <c r="E1" s="105"/>
+      <c r="F1" s="105"/>
+      <c r="G1" s="105"/>
+      <c r="H1" s="105"/>
+      <c r="I1" s="105"/>
+      <c r="J1" s="105"/>
+      <c r="K1" s="105"/>
+      <c r="L1" s="105"/>
+      <c r="M1" s="105"/>
+      <c r="N1" s="105"/>
+      <c r="O1" s="105"/>
+      <c r="P1" s="105"/>
       <c r="Q1" s="21"/>
       <c r="R1" s="20"/>
       <c r="S1" s="20"/>
@@ -6299,139 +6314,139 @@
       <c r="AD1" s="20"/>
     </row>
     <row r="2" spans="2:52" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B2" s="140" t="s">
+      <c r="B2" s="184" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="140"/>
-      <c r="D2" s="140"/>
-      <c r="E2" s="140"/>
-      <c r="F2" s="140"/>
-      <c r="G2" s="140"/>
-      <c r="H2" s="140"/>
-      <c r="I2" s="140"/>
-      <c r="J2" s="144"/>
-      <c r="K2" s="144"/>
-      <c r="L2" s="144"/>
-      <c r="M2" s="144"/>
-      <c r="N2" s="144"/>
-      <c r="O2" s="144"/>
-      <c r="P2" s="144"/>
-      <c r="Q2" s="144"/>
-      <c r="R2" s="144"/>
-      <c r="S2" s="144"/>
-      <c r="T2" s="144"/>
-      <c r="U2" s="144"/>
-      <c r="V2" s="144"/>
-      <c r="W2" s="144"/>
-      <c r="X2" s="144"/>
-      <c r="Y2" s="144"/>
-      <c r="Z2" s="144"/>
-      <c r="AA2" s="144"/>
-      <c r="AB2" s="144"/>
-      <c r="AC2" s="144"/>
-      <c r="AD2" s="144"/>
+      <c r="C2" s="184"/>
+      <c r="D2" s="184"/>
+      <c r="E2" s="184"/>
+      <c r="F2" s="184"/>
+      <c r="G2" s="184"/>
+      <c r="H2" s="184"/>
+      <c r="I2" s="184"/>
+      <c r="J2" s="113"/>
+      <c r="K2" s="113"/>
+      <c r="L2" s="113"/>
+      <c r="M2" s="113"/>
+      <c r="N2" s="113"/>
+      <c r="O2" s="113"/>
+      <c r="P2" s="113"/>
+      <c r="Q2" s="113"/>
+      <c r="R2" s="113"/>
+      <c r="S2" s="113"/>
+      <c r="T2" s="113"/>
+      <c r="U2" s="113"/>
+      <c r="V2" s="113"/>
+      <c r="W2" s="113"/>
+      <c r="X2" s="113"/>
+      <c r="Y2" s="113"/>
+      <c r="Z2" s="113"/>
+      <c r="AA2" s="113"/>
+      <c r="AB2" s="113"/>
+      <c r="AC2" s="113"/>
+      <c r="AD2" s="113"/>
     </row>
     <row r="3" spans="2:52" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="4" spans="2:52" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B4" s="151" t="s">
+      <c r="B4" s="192" t="s">
         <v>76</v>
       </c>
-      <c r="C4" s="138"/>
-      <c r="D4" s="138"/>
-      <c r="E4" s="138"/>
-      <c r="F4" s="138"/>
-      <c r="G4" s="138"/>
-      <c r="H4" s="138"/>
-      <c r="I4" s="138"/>
-      <c r="J4" s="138" t="s">
+      <c r="C4" s="182"/>
+      <c r="D4" s="182"/>
+      <c r="E4" s="182"/>
+      <c r="F4" s="182"/>
+      <c r="G4" s="182"/>
+      <c r="H4" s="182"/>
+      <c r="I4" s="182"/>
+      <c r="J4" s="182" t="s">
         <v>77</v>
       </c>
-      <c r="K4" s="138"/>
-      <c r="L4" s="138"/>
-      <c r="M4" s="138"/>
-      <c r="N4" s="138"/>
-      <c r="O4" s="138"/>
-      <c r="P4" s="138"/>
-      <c r="Q4" s="145" t="s">
+      <c r="K4" s="182"/>
+      <c r="L4" s="182"/>
+      <c r="M4" s="182"/>
+      <c r="N4" s="182"/>
+      <c r="O4" s="182"/>
+      <c r="P4" s="182"/>
+      <c r="Q4" s="186" t="s">
         <v>78</v>
       </c>
-      <c r="R4" s="149"/>
-      <c r="S4" s="146"/>
-      <c r="T4" s="145" t="s">
+      <c r="R4" s="190"/>
+      <c r="S4" s="187"/>
+      <c r="T4" s="186" t="s">
         <v>79</v>
       </c>
-      <c r="U4" s="149"/>
-      <c r="V4" s="149"/>
-      <c r="W4" s="146"/>
-      <c r="X4" s="145" t="s">
+      <c r="U4" s="190"/>
+      <c r="V4" s="190"/>
+      <c r="W4" s="187"/>
+      <c r="X4" s="186" t="s">
         <v>80</v>
       </c>
-      <c r="Y4" s="146"/>
-      <c r="Z4" s="138" t="s">
+      <c r="Y4" s="187"/>
+      <c r="Z4" s="182" t="s">
         <v>81</v>
       </c>
-      <c r="AA4" s="138"/>
-      <c r="AB4" s="138"/>
-      <c r="AC4" s="138" t="s">
+      <c r="AA4" s="182"/>
+      <c r="AB4" s="182"/>
+      <c r="AC4" s="182" t="s">
         <v>81</v>
       </c>
-      <c r="AD4" s="138"/>
-      <c r="AE4" s="138"/>
-      <c r="AF4" s="138" t="s">
+      <c r="AD4" s="182"/>
+      <c r="AE4" s="182"/>
+      <c r="AF4" s="182" t="s">
         <v>81</v>
       </c>
-      <c r="AG4" s="138"/>
-      <c r="AH4" s="138"/>
-      <c r="AI4" s="138" t="s">
+      <c r="AG4" s="182"/>
+      <c r="AH4" s="182"/>
+      <c r="AI4" s="182" t="s">
         <v>81</v>
       </c>
-      <c r="AJ4" s="138"/>
-      <c r="AK4" s="138"/>
-      <c r="AL4" s="138" t="s">
+      <c r="AJ4" s="182"/>
+      <c r="AK4" s="182"/>
+      <c r="AL4" s="182" t="s">
         <v>81</v>
       </c>
-      <c r="AM4" s="138"/>
-      <c r="AN4" s="138"/>
-      <c r="AO4" s="138" t="s">
+      <c r="AM4" s="182"/>
+      <c r="AN4" s="182"/>
+      <c r="AO4" s="182" t="s">
         <v>82</v>
       </c>
-      <c r="AP4" s="138"/>
-      <c r="AQ4" s="138"/>
-      <c r="AR4" s="138"/>
-      <c r="AS4" s="138"/>
-      <c r="AT4" s="138"/>
-      <c r="AU4" s="138"/>
-      <c r="AV4" s="138"/>
-      <c r="AW4" s="138"/>
-      <c r="AX4" s="138"/>
-      <c r="AY4" s="138"/>
-      <c r="AZ4" s="139"/>
+      <c r="AP4" s="182"/>
+      <c r="AQ4" s="182"/>
+      <c r="AR4" s="182"/>
+      <c r="AS4" s="182"/>
+      <c r="AT4" s="182"/>
+      <c r="AU4" s="182"/>
+      <c r="AV4" s="182"/>
+      <c r="AW4" s="182"/>
+      <c r="AX4" s="182"/>
+      <c r="AY4" s="182"/>
+      <c r="AZ4" s="183"/>
     </row>
     <row r="5" spans="2:52" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B5" s="152"/>
-      <c r="C5" s="140"/>
-      <c r="D5" s="140"/>
-      <c r="E5" s="140"/>
-      <c r="F5" s="140"/>
-      <c r="G5" s="140"/>
-      <c r="H5" s="140"/>
-      <c r="I5" s="140"/>
-      <c r="J5" s="140"/>
-      <c r="K5" s="140"/>
-      <c r="L5" s="140"/>
-      <c r="M5" s="140"/>
-      <c r="N5" s="140"/>
-      <c r="O5" s="140"/>
-      <c r="P5" s="140"/>
-      <c r="Q5" s="147"/>
-      <c r="R5" s="150"/>
-      <c r="S5" s="148"/>
-      <c r="T5" s="147"/>
-      <c r="U5" s="150"/>
-      <c r="V5" s="150"/>
-      <c r="W5" s="148"/>
-      <c r="X5" s="147"/>
-      <c r="Y5" s="148"/>
+      <c r="B5" s="193"/>
+      <c r="C5" s="184"/>
+      <c r="D5" s="184"/>
+      <c r="E5" s="184"/>
+      <c r="F5" s="184"/>
+      <c r="G5" s="184"/>
+      <c r="H5" s="184"/>
+      <c r="I5" s="184"/>
+      <c r="J5" s="184"/>
+      <c r="K5" s="184"/>
+      <c r="L5" s="184"/>
+      <c r="M5" s="184"/>
+      <c r="N5" s="184"/>
+      <c r="O5" s="184"/>
+      <c r="P5" s="184"/>
+      <c r="Q5" s="188"/>
+      <c r="R5" s="191"/>
+      <c r="S5" s="189"/>
+      <c r="T5" s="188"/>
+      <c r="U5" s="191"/>
+      <c r="V5" s="191"/>
+      <c r="W5" s="189"/>
+      <c r="X5" s="188"/>
+      <c r="Y5" s="189"/>
       <c r="Z5" s="6" t="s">
         <v>83</v>
       </c>
@@ -6477,54 +6492,54 @@
       <c r="AN5" s="8" t="s">
         <v>85</v>
       </c>
-      <c r="AO5" s="140"/>
-      <c r="AP5" s="140"/>
-      <c r="AQ5" s="140"/>
-      <c r="AR5" s="140"/>
-      <c r="AS5" s="140"/>
-      <c r="AT5" s="140"/>
-      <c r="AU5" s="140"/>
-      <c r="AV5" s="140"/>
-      <c r="AW5" s="140"/>
-      <c r="AX5" s="140"/>
-      <c r="AY5" s="140"/>
-      <c r="AZ5" s="141"/>
+      <c r="AO5" s="184"/>
+      <c r="AP5" s="184"/>
+      <c r="AQ5" s="184"/>
+      <c r="AR5" s="184"/>
+      <c r="AS5" s="184"/>
+      <c r="AT5" s="184"/>
+      <c r="AU5" s="184"/>
+      <c r="AV5" s="184"/>
+      <c r="AW5" s="184"/>
+      <c r="AX5" s="184"/>
+      <c r="AY5" s="184"/>
+      <c r="AZ5" s="185"/>
     </row>
     <row r="6" spans="2:52" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B6" s="167">
+      <c r="B6" s="110">
         <v>1</v>
       </c>
-      <c r="C6" s="153" t="s">
+      <c r="C6" s="106" t="s">
         <v>86</v>
       </c>
-      <c r="D6" s="153"/>
-      <c r="E6" s="153"/>
-      <c r="F6" s="153"/>
-      <c r="G6" s="153"/>
-      <c r="H6" s="153"/>
-      <c r="I6" s="153"/>
-      <c r="J6" s="153"/>
-      <c r="K6" s="153"/>
-      <c r="L6" s="153"/>
-      <c r="M6" s="153"/>
-      <c r="N6" s="153"/>
-      <c r="O6" s="153"/>
-      <c r="P6" s="153"/>
-      <c r="Q6" s="144"/>
-      <c r="R6" s="144"/>
-      <c r="S6" s="144"/>
-      <c r="T6" s="158" t="s">
+      <c r="D6" s="106"/>
+      <c r="E6" s="106"/>
+      <c r="F6" s="106"/>
+      <c r="G6" s="106"/>
+      <c r="H6" s="106"/>
+      <c r="I6" s="106"/>
+      <c r="J6" s="106"/>
+      <c r="K6" s="106"/>
+      <c r="L6" s="106"/>
+      <c r="M6" s="106"/>
+      <c r="N6" s="106"/>
+      <c r="O6" s="106"/>
+      <c r="P6" s="106"/>
+      <c r="Q6" s="113"/>
+      <c r="R6" s="113"/>
+      <c r="S6" s="113"/>
+      <c r="T6" s="111" t="s">
         <v>87</v>
       </c>
-      <c r="U6" s="158"/>
-      <c r="V6" s="156">
+      <c r="U6" s="111"/>
+      <c r="V6" s="108">
         <v>0</v>
       </c>
-      <c r="W6" s="156"/>
-      <c r="X6" s="142">
+      <c r="W6" s="108"/>
+      <c r="X6" s="129">
         <v>0</v>
       </c>
-      <c r="Y6" s="142"/>
+      <c r="Y6" s="129"/>
       <c r="Z6" s="9"/>
       <c r="AA6" s="10"/>
       <c r="AB6" s="11"/>
@@ -6540,50 +6555,50 @@
       <c r="AL6" s="9"/>
       <c r="AM6" s="10"/>
       <c r="AN6" s="11"/>
-      <c r="AO6" s="153"/>
-      <c r="AP6" s="153"/>
-      <c r="AQ6" s="153"/>
-      <c r="AR6" s="153"/>
-      <c r="AS6" s="153"/>
-      <c r="AT6" s="153"/>
-      <c r="AU6" s="153"/>
-      <c r="AV6" s="153"/>
-      <c r="AW6" s="153"/>
-      <c r="AX6" s="153"/>
-      <c r="AY6" s="153"/>
-      <c r="AZ6" s="154"/>
+      <c r="AO6" s="106"/>
+      <c r="AP6" s="106"/>
+      <c r="AQ6" s="106"/>
+      <c r="AR6" s="106"/>
+      <c r="AS6" s="106"/>
+      <c r="AT6" s="106"/>
+      <c r="AU6" s="106"/>
+      <c r="AV6" s="106"/>
+      <c r="AW6" s="106"/>
+      <c r="AX6" s="106"/>
+      <c r="AY6" s="106"/>
+      <c r="AZ6" s="128"/>
     </row>
     <row r="7" spans="2:52" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B7" s="167"/>
-      <c r="C7" s="153"/>
-      <c r="D7" s="153"/>
-      <c r="E7" s="153"/>
-      <c r="F7" s="153"/>
-      <c r="G7" s="153"/>
-      <c r="H7" s="153"/>
-      <c r="I7" s="153"/>
-      <c r="J7" s="153"/>
-      <c r="K7" s="153"/>
-      <c r="L7" s="153"/>
-      <c r="M7" s="153"/>
-      <c r="N7" s="153"/>
-      <c r="O7" s="153"/>
-      <c r="P7" s="153"/>
-      <c r="Q7" s="144"/>
-      <c r="R7" s="144"/>
-      <c r="S7" s="144"/>
-      <c r="T7" s="155" t="s">
+      <c r="B7" s="110"/>
+      <c r="C7" s="106"/>
+      <c r="D7" s="106"/>
+      <c r="E7" s="106"/>
+      <c r="F7" s="106"/>
+      <c r="G7" s="106"/>
+      <c r="H7" s="106"/>
+      <c r="I7" s="106"/>
+      <c r="J7" s="106"/>
+      <c r="K7" s="106"/>
+      <c r="L7" s="106"/>
+      <c r="M7" s="106"/>
+      <c r="N7" s="106"/>
+      <c r="O7" s="106"/>
+      <c r="P7" s="106"/>
+      <c r="Q7" s="113"/>
+      <c r="R7" s="113"/>
+      <c r="S7" s="113"/>
+      <c r="T7" s="112" t="s">
         <v>25</v>
       </c>
-      <c r="U7" s="155"/>
-      <c r="V7" s="157">
+      <c r="U7" s="112"/>
+      <c r="V7" s="109">
         <v>0</v>
       </c>
-      <c r="W7" s="157"/>
-      <c r="X7" s="143">
+      <c r="W7" s="109"/>
+      <c r="X7" s="130">
         <v>0</v>
       </c>
-      <c r="Y7" s="143"/>
+      <c r="Y7" s="130"/>
       <c r="Z7" s="12"/>
       <c r="AA7" s="13"/>
       <c r="AB7" s="14"/>
@@ -6599,54 +6614,54 @@
       <c r="AL7" s="12"/>
       <c r="AM7" s="13"/>
       <c r="AN7" s="14"/>
-      <c r="AO7" s="153"/>
-      <c r="AP7" s="153"/>
-      <c r="AQ7" s="153"/>
-      <c r="AR7" s="153"/>
-      <c r="AS7" s="153"/>
-      <c r="AT7" s="153"/>
-      <c r="AU7" s="153"/>
-      <c r="AV7" s="153"/>
-      <c r="AW7" s="153"/>
-      <c r="AX7" s="153"/>
-      <c r="AY7" s="153"/>
-      <c r="AZ7" s="154"/>
+      <c r="AO7" s="106"/>
+      <c r="AP7" s="106"/>
+      <c r="AQ7" s="106"/>
+      <c r="AR7" s="106"/>
+      <c r="AS7" s="106"/>
+      <c r="AT7" s="106"/>
+      <c r="AU7" s="106"/>
+      <c r="AV7" s="106"/>
+      <c r="AW7" s="106"/>
+      <c r="AX7" s="106"/>
+      <c r="AY7" s="106"/>
+      <c r="AZ7" s="128"/>
     </row>
     <row r="8" spans="2:52" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B8" s="167">
+      <c r="B8" s="110">
         <v>2</v>
       </c>
-      <c r="C8" s="153" t="s">
+      <c r="C8" s="106" t="s">
         <v>88</v>
       </c>
-      <c r="D8" s="153"/>
-      <c r="E8" s="153"/>
-      <c r="F8" s="153"/>
-      <c r="G8" s="153"/>
-      <c r="H8" s="153"/>
-      <c r="I8" s="153"/>
-      <c r="J8" s="112"/>
-      <c r="K8" s="113"/>
-      <c r="L8" s="113"/>
-      <c r="M8" s="113"/>
-      <c r="N8" s="113"/>
-      <c r="O8" s="113"/>
-      <c r="P8" s="114"/>
-      <c r="Q8" s="144"/>
-      <c r="R8" s="144"/>
-      <c r="S8" s="144"/>
-      <c r="T8" s="158" t="s">
+      <c r="D8" s="106"/>
+      <c r="E8" s="106"/>
+      <c r="F8" s="106"/>
+      <c r="G8" s="106"/>
+      <c r="H8" s="106"/>
+      <c r="I8" s="106"/>
+      <c r="J8" s="114"/>
+      <c r="K8" s="115"/>
+      <c r="L8" s="115"/>
+      <c r="M8" s="115"/>
+      <c r="N8" s="115"/>
+      <c r="O8" s="115"/>
+      <c r="P8" s="116"/>
+      <c r="Q8" s="113"/>
+      <c r="R8" s="113"/>
+      <c r="S8" s="113"/>
+      <c r="T8" s="111" t="s">
         <v>87</v>
       </c>
-      <c r="U8" s="158"/>
-      <c r="V8" s="156">
+      <c r="U8" s="111"/>
+      <c r="V8" s="108">
         <v>0</v>
       </c>
-      <c r="W8" s="156"/>
-      <c r="X8" s="142">
+      <c r="W8" s="108"/>
+      <c r="X8" s="129">
         <v>0</v>
       </c>
-      <c r="Y8" s="142"/>
+      <c r="Y8" s="129"/>
       <c r="Z8" s="9"/>
       <c r="AA8" s="10"/>
       <c r="AB8" s="11"/>
@@ -6662,50 +6677,50 @@
       <c r="AL8" s="9"/>
       <c r="AM8" s="10"/>
       <c r="AN8" s="11"/>
-      <c r="AO8" s="153"/>
-      <c r="AP8" s="153"/>
-      <c r="AQ8" s="153"/>
-      <c r="AR8" s="153"/>
-      <c r="AS8" s="153"/>
-      <c r="AT8" s="153"/>
-      <c r="AU8" s="153"/>
-      <c r="AV8" s="153"/>
-      <c r="AW8" s="153"/>
-      <c r="AX8" s="153"/>
-      <c r="AY8" s="153"/>
-      <c r="AZ8" s="154"/>
+      <c r="AO8" s="106"/>
+      <c r="AP8" s="106"/>
+      <c r="AQ8" s="106"/>
+      <c r="AR8" s="106"/>
+      <c r="AS8" s="106"/>
+      <c r="AT8" s="106"/>
+      <c r="AU8" s="106"/>
+      <c r="AV8" s="106"/>
+      <c r="AW8" s="106"/>
+      <c r="AX8" s="106"/>
+      <c r="AY8" s="106"/>
+      <c r="AZ8" s="128"/>
     </row>
     <row r="9" spans="2:52" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B9" s="167"/>
-      <c r="C9" s="153"/>
-      <c r="D9" s="153"/>
-      <c r="E9" s="153"/>
-      <c r="F9" s="153"/>
-      <c r="G9" s="153"/>
-      <c r="H9" s="153"/>
-      <c r="I9" s="153"/>
-      <c r="J9" s="115"/>
-      <c r="K9" s="116"/>
-      <c r="L9" s="116"/>
-      <c r="M9" s="116"/>
-      <c r="N9" s="116"/>
-      <c r="O9" s="116"/>
-      <c r="P9" s="117"/>
-      <c r="Q9" s="144"/>
-      <c r="R9" s="144"/>
-      <c r="S9" s="144"/>
-      <c r="T9" s="155" t="s">
+      <c r="B9" s="110"/>
+      <c r="C9" s="106"/>
+      <c r="D9" s="106"/>
+      <c r="E9" s="106"/>
+      <c r="F9" s="106"/>
+      <c r="G9" s="106"/>
+      <c r="H9" s="106"/>
+      <c r="I9" s="106"/>
+      <c r="J9" s="117"/>
+      <c r="K9" s="118"/>
+      <c r="L9" s="118"/>
+      <c r="M9" s="118"/>
+      <c r="N9" s="118"/>
+      <c r="O9" s="118"/>
+      <c r="P9" s="119"/>
+      <c r="Q9" s="113"/>
+      <c r="R9" s="113"/>
+      <c r="S9" s="113"/>
+      <c r="T9" s="112" t="s">
         <v>25</v>
       </c>
-      <c r="U9" s="155"/>
-      <c r="V9" s="157">
+      <c r="U9" s="112"/>
+      <c r="V9" s="109">
         <v>0</v>
       </c>
-      <c r="W9" s="157"/>
-      <c r="X9" s="143">
+      <c r="W9" s="109"/>
+      <c r="X9" s="130">
         <v>0</v>
       </c>
-      <c r="Y9" s="143"/>
+      <c r="Y9" s="130"/>
       <c r="Z9" s="12"/>
       <c r="AA9" s="13"/>
       <c r="AB9" s="14"/>
@@ -6721,54 +6736,54 @@
       <c r="AL9" s="12"/>
       <c r="AM9" s="13"/>
       <c r="AN9" s="14"/>
-      <c r="AO9" s="153"/>
-      <c r="AP9" s="153"/>
-      <c r="AQ9" s="153"/>
-      <c r="AR9" s="153"/>
-      <c r="AS9" s="153"/>
-      <c r="AT9" s="153"/>
-      <c r="AU9" s="153"/>
-      <c r="AV9" s="153"/>
-      <c r="AW9" s="153"/>
-      <c r="AX9" s="153"/>
-      <c r="AY9" s="153"/>
-      <c r="AZ9" s="154"/>
+      <c r="AO9" s="106"/>
+      <c r="AP9" s="106"/>
+      <c r="AQ9" s="106"/>
+      <c r="AR9" s="106"/>
+      <c r="AS9" s="106"/>
+      <c r="AT9" s="106"/>
+      <c r="AU9" s="106"/>
+      <c r="AV9" s="106"/>
+      <c r="AW9" s="106"/>
+      <c r="AX9" s="106"/>
+      <c r="AY9" s="106"/>
+      <c r="AZ9" s="128"/>
     </row>
     <row r="10" spans="2:52" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B10" s="167">
+      <c r="B10" s="110">
         <v>3</v>
       </c>
-      <c r="C10" s="153" t="s">
+      <c r="C10" s="106" t="s">
         <v>89</v>
       </c>
-      <c r="D10" s="153"/>
-      <c r="E10" s="153"/>
-      <c r="F10" s="153"/>
-      <c r="G10" s="153"/>
-      <c r="H10" s="153"/>
-      <c r="I10" s="153"/>
-      <c r="J10" s="153"/>
-      <c r="K10" s="153"/>
-      <c r="L10" s="153"/>
-      <c r="M10" s="153"/>
-      <c r="N10" s="153"/>
-      <c r="O10" s="153"/>
-      <c r="P10" s="153"/>
-      <c r="Q10" s="144"/>
-      <c r="R10" s="144"/>
-      <c r="S10" s="144"/>
-      <c r="T10" s="158" t="s">
+      <c r="D10" s="106"/>
+      <c r="E10" s="106"/>
+      <c r="F10" s="106"/>
+      <c r="G10" s="106"/>
+      <c r="H10" s="106"/>
+      <c r="I10" s="106"/>
+      <c r="J10" s="106"/>
+      <c r="K10" s="106"/>
+      <c r="L10" s="106"/>
+      <c r="M10" s="106"/>
+      <c r="N10" s="106"/>
+      <c r="O10" s="106"/>
+      <c r="P10" s="106"/>
+      <c r="Q10" s="113"/>
+      <c r="R10" s="113"/>
+      <c r="S10" s="113"/>
+      <c r="T10" s="111" t="s">
         <v>87</v>
       </c>
-      <c r="U10" s="158"/>
-      <c r="V10" s="156">
+      <c r="U10" s="111"/>
+      <c r="V10" s="108">
         <v>0</v>
       </c>
-      <c r="W10" s="156"/>
-      <c r="X10" s="142">
+      <c r="W10" s="108"/>
+      <c r="X10" s="129">
         <v>0</v>
       </c>
-      <c r="Y10" s="142"/>
+      <c r="Y10" s="129"/>
       <c r="Z10" s="9"/>
       <c r="AA10" s="10"/>
       <c r="AB10" s="11"/>
@@ -6784,50 +6799,50 @@
       <c r="AL10" s="9"/>
       <c r="AM10" s="10"/>
       <c r="AN10" s="11"/>
-      <c r="AO10" s="153"/>
-      <c r="AP10" s="153"/>
-      <c r="AQ10" s="153"/>
-      <c r="AR10" s="153"/>
-      <c r="AS10" s="153"/>
-      <c r="AT10" s="153"/>
-      <c r="AU10" s="153"/>
-      <c r="AV10" s="153"/>
-      <c r="AW10" s="153"/>
-      <c r="AX10" s="153"/>
-      <c r="AY10" s="153"/>
-      <c r="AZ10" s="154"/>
+      <c r="AO10" s="106"/>
+      <c r="AP10" s="106"/>
+      <c r="AQ10" s="106"/>
+      <c r="AR10" s="106"/>
+      <c r="AS10" s="106"/>
+      <c r="AT10" s="106"/>
+      <c r="AU10" s="106"/>
+      <c r="AV10" s="106"/>
+      <c r="AW10" s="106"/>
+      <c r="AX10" s="106"/>
+      <c r="AY10" s="106"/>
+      <c r="AZ10" s="128"/>
     </row>
     <row r="11" spans="2:52" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B11" s="167"/>
-      <c r="C11" s="153"/>
-      <c r="D11" s="153"/>
-      <c r="E11" s="153"/>
-      <c r="F11" s="153"/>
-      <c r="G11" s="153"/>
-      <c r="H11" s="153"/>
-      <c r="I11" s="153"/>
-      <c r="J11" s="153"/>
-      <c r="K11" s="153"/>
-      <c r="L11" s="153"/>
-      <c r="M11" s="153"/>
-      <c r="N11" s="153"/>
-      <c r="O11" s="153"/>
-      <c r="P11" s="153"/>
-      <c r="Q11" s="144"/>
-      <c r="R11" s="144"/>
-      <c r="S11" s="144"/>
-      <c r="T11" s="155" t="s">
+      <c r="B11" s="110"/>
+      <c r="C11" s="106"/>
+      <c r="D11" s="106"/>
+      <c r="E11" s="106"/>
+      <c r="F11" s="106"/>
+      <c r="G11" s="106"/>
+      <c r="H11" s="106"/>
+      <c r="I11" s="106"/>
+      <c r="J11" s="106"/>
+      <c r="K11" s="106"/>
+      <c r="L11" s="106"/>
+      <c r="M11" s="106"/>
+      <c r="N11" s="106"/>
+      <c r="O11" s="106"/>
+      <c r="P11" s="106"/>
+      <c r="Q11" s="113"/>
+      <c r="R11" s="113"/>
+      <c r="S11" s="113"/>
+      <c r="T11" s="112" t="s">
         <v>25</v>
       </c>
-      <c r="U11" s="155"/>
-      <c r="V11" s="157">
+      <c r="U11" s="112"/>
+      <c r="V11" s="109">
         <v>0</v>
       </c>
-      <c r="W11" s="157"/>
-      <c r="X11" s="143">
+      <c r="W11" s="109"/>
+      <c r="X11" s="130">
         <v>0</v>
       </c>
-      <c r="Y11" s="143"/>
+      <c r="Y11" s="130"/>
       <c r="Z11" s="12"/>
       <c r="AA11" s="13"/>
       <c r="AB11" s="14"/>
@@ -6843,54 +6858,54 @@
       <c r="AL11" s="12"/>
       <c r="AM11" s="13"/>
       <c r="AN11" s="14"/>
-      <c r="AO11" s="153"/>
-      <c r="AP11" s="153"/>
-      <c r="AQ11" s="153"/>
-      <c r="AR11" s="153"/>
-      <c r="AS11" s="153"/>
-      <c r="AT11" s="153"/>
-      <c r="AU11" s="153"/>
-      <c r="AV11" s="153"/>
-      <c r="AW11" s="153"/>
-      <c r="AX11" s="153"/>
-      <c r="AY11" s="153"/>
-      <c r="AZ11" s="154"/>
+      <c r="AO11" s="106"/>
+      <c r="AP11" s="106"/>
+      <c r="AQ11" s="106"/>
+      <c r="AR11" s="106"/>
+      <c r="AS11" s="106"/>
+      <c r="AT11" s="106"/>
+      <c r="AU11" s="106"/>
+      <c r="AV11" s="106"/>
+      <c r="AW11" s="106"/>
+      <c r="AX11" s="106"/>
+      <c r="AY11" s="106"/>
+      <c r="AZ11" s="128"/>
     </row>
     <row r="12" spans="2:52" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B12" s="167">
+      <c r="B12" s="110">
         <v>4</v>
       </c>
-      <c r="C12" s="153" t="s">
+      <c r="C12" s="106" t="s">
         <v>90</v>
       </c>
-      <c r="D12" s="153"/>
-      <c r="E12" s="153"/>
-      <c r="F12" s="153"/>
-      <c r="G12" s="153"/>
-      <c r="H12" s="153"/>
-      <c r="I12" s="153"/>
-      <c r="J12" s="153"/>
-      <c r="K12" s="153"/>
-      <c r="L12" s="153"/>
-      <c r="M12" s="153"/>
-      <c r="N12" s="153"/>
-      <c r="O12" s="153"/>
-      <c r="P12" s="153"/>
-      <c r="Q12" s="118"/>
-      <c r="R12" s="119"/>
-      <c r="S12" s="120"/>
-      <c r="T12" s="158" t="s">
+      <c r="D12" s="106"/>
+      <c r="E12" s="106"/>
+      <c r="F12" s="106"/>
+      <c r="G12" s="106"/>
+      <c r="H12" s="106"/>
+      <c r="I12" s="106"/>
+      <c r="J12" s="106"/>
+      <c r="K12" s="106"/>
+      <c r="L12" s="106"/>
+      <c r="M12" s="106"/>
+      <c r="N12" s="106"/>
+      <c r="O12" s="106"/>
+      <c r="P12" s="106"/>
+      <c r="Q12" s="172"/>
+      <c r="R12" s="173"/>
+      <c r="S12" s="174"/>
+      <c r="T12" s="111" t="s">
         <v>87</v>
       </c>
-      <c r="U12" s="158"/>
-      <c r="V12" s="156">
+      <c r="U12" s="111"/>
+      <c r="V12" s="108">
         <v>0</v>
       </c>
-      <c r="W12" s="156"/>
-      <c r="X12" s="142">
+      <c r="W12" s="108"/>
+      <c r="X12" s="129">
         <v>0</v>
       </c>
-      <c r="Y12" s="142"/>
+      <c r="Y12" s="129"/>
       <c r="Z12" s="9"/>
       <c r="AA12" s="10"/>
       <c r="AB12" s="11"/>
@@ -6906,50 +6921,50 @@
       <c r="AL12" s="9"/>
       <c r="AM12" s="10"/>
       <c r="AN12" s="11"/>
-      <c r="AO12" s="153"/>
-      <c r="AP12" s="153"/>
-      <c r="AQ12" s="153"/>
-      <c r="AR12" s="153"/>
-      <c r="AS12" s="153"/>
-      <c r="AT12" s="153"/>
-      <c r="AU12" s="153"/>
-      <c r="AV12" s="153"/>
-      <c r="AW12" s="153"/>
-      <c r="AX12" s="153"/>
-      <c r="AY12" s="153"/>
-      <c r="AZ12" s="154"/>
+      <c r="AO12" s="106"/>
+      <c r="AP12" s="106"/>
+      <c r="AQ12" s="106"/>
+      <c r="AR12" s="106"/>
+      <c r="AS12" s="106"/>
+      <c r="AT12" s="106"/>
+      <c r="AU12" s="106"/>
+      <c r="AV12" s="106"/>
+      <c r="AW12" s="106"/>
+      <c r="AX12" s="106"/>
+      <c r="AY12" s="106"/>
+      <c r="AZ12" s="128"/>
     </row>
     <row r="13" spans="2:52" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B13" s="167"/>
-      <c r="C13" s="153"/>
-      <c r="D13" s="153"/>
-      <c r="E13" s="153"/>
-      <c r="F13" s="153"/>
-      <c r="G13" s="153"/>
-      <c r="H13" s="153"/>
-      <c r="I13" s="153"/>
-      <c r="J13" s="153"/>
-      <c r="K13" s="153"/>
-      <c r="L13" s="153"/>
-      <c r="M13" s="153"/>
-      <c r="N13" s="153"/>
-      <c r="O13" s="153"/>
-      <c r="P13" s="153"/>
-      <c r="Q13" s="121"/>
-      <c r="R13" s="122"/>
-      <c r="S13" s="123"/>
-      <c r="T13" s="155" t="s">
+      <c r="B13" s="110"/>
+      <c r="C13" s="106"/>
+      <c r="D13" s="106"/>
+      <c r="E13" s="106"/>
+      <c r="F13" s="106"/>
+      <c r="G13" s="106"/>
+      <c r="H13" s="106"/>
+      <c r="I13" s="106"/>
+      <c r="J13" s="106"/>
+      <c r="K13" s="106"/>
+      <c r="L13" s="106"/>
+      <c r="M13" s="106"/>
+      <c r="N13" s="106"/>
+      <c r="O13" s="106"/>
+      <c r="P13" s="106"/>
+      <c r="Q13" s="175"/>
+      <c r="R13" s="176"/>
+      <c r="S13" s="177"/>
+      <c r="T13" s="112" t="s">
         <v>25</v>
       </c>
-      <c r="U13" s="155"/>
-      <c r="V13" s="157">
+      <c r="U13" s="112"/>
+      <c r="V13" s="109">
         <v>0</v>
       </c>
-      <c r="W13" s="157"/>
-      <c r="X13" s="143">
+      <c r="W13" s="109"/>
+      <c r="X13" s="130">
         <v>0</v>
       </c>
-      <c r="Y13" s="143"/>
+      <c r="Y13" s="130"/>
       <c r="Z13" s="12"/>
       <c r="AA13" s="13"/>
       <c r="AB13" s="14"/>
@@ -6965,54 +6980,54 @@
       <c r="AL13" s="12"/>
       <c r="AM13" s="13"/>
       <c r="AN13" s="14"/>
-      <c r="AO13" s="153"/>
-      <c r="AP13" s="153"/>
-      <c r="AQ13" s="153"/>
-      <c r="AR13" s="153"/>
-      <c r="AS13" s="153"/>
-      <c r="AT13" s="153"/>
-      <c r="AU13" s="153"/>
-      <c r="AV13" s="153"/>
-      <c r="AW13" s="153"/>
-      <c r="AX13" s="153"/>
-      <c r="AY13" s="153"/>
-      <c r="AZ13" s="154"/>
+      <c r="AO13" s="106"/>
+      <c r="AP13" s="106"/>
+      <c r="AQ13" s="106"/>
+      <c r="AR13" s="106"/>
+      <c r="AS13" s="106"/>
+      <c r="AT13" s="106"/>
+      <c r="AU13" s="106"/>
+      <c r="AV13" s="106"/>
+      <c r="AW13" s="106"/>
+      <c r="AX13" s="106"/>
+      <c r="AY13" s="106"/>
+      <c r="AZ13" s="128"/>
     </row>
     <row r="14" spans="2:52" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B14" s="167">
+      <c r="B14" s="110">
         <v>5</v>
       </c>
-      <c r="C14" s="112" t="s">
+      <c r="C14" s="114" t="s">
         <v>91</v>
       </c>
-      <c r="D14" s="113"/>
-      <c r="E14" s="113"/>
-      <c r="F14" s="113"/>
-      <c r="G14" s="113"/>
-      <c r="H14" s="113"/>
-      <c r="I14" s="114"/>
-      <c r="J14" s="193"/>
-      <c r="K14" s="153"/>
-      <c r="L14" s="153"/>
-      <c r="M14" s="153"/>
-      <c r="N14" s="153"/>
-      <c r="O14" s="153"/>
-      <c r="P14" s="153"/>
-      <c r="Q14" s="118"/>
-      <c r="R14" s="119"/>
-      <c r="S14" s="120"/>
-      <c r="T14" s="158" t="s">
+      <c r="D14" s="115"/>
+      <c r="E14" s="115"/>
+      <c r="F14" s="115"/>
+      <c r="G14" s="115"/>
+      <c r="H14" s="115"/>
+      <c r="I14" s="116"/>
+      <c r="J14" s="107"/>
+      <c r="K14" s="106"/>
+      <c r="L14" s="106"/>
+      <c r="M14" s="106"/>
+      <c r="N14" s="106"/>
+      <c r="O14" s="106"/>
+      <c r="P14" s="106"/>
+      <c r="Q14" s="172"/>
+      <c r="R14" s="173"/>
+      <c r="S14" s="174"/>
+      <c r="T14" s="111" t="s">
         <v>87</v>
       </c>
-      <c r="U14" s="158"/>
-      <c r="V14" s="156">
+      <c r="U14" s="111"/>
+      <c r="V14" s="108">
         <v>0</v>
       </c>
-      <c r="W14" s="156"/>
-      <c r="X14" s="142">
+      <c r="W14" s="108"/>
+      <c r="X14" s="129">
         <v>0</v>
       </c>
-      <c r="Y14" s="142"/>
+      <c r="Y14" s="129"/>
       <c r="Z14" s="9"/>
       <c r="AA14" s="10"/>
       <c r="AB14" s="11"/>
@@ -7028,50 +7043,50 @@
       <c r="AL14" s="9"/>
       <c r="AM14" s="10"/>
       <c r="AN14" s="11"/>
-      <c r="AO14" s="153"/>
-      <c r="AP14" s="153"/>
-      <c r="AQ14" s="153"/>
-      <c r="AR14" s="153"/>
-      <c r="AS14" s="153"/>
-      <c r="AT14" s="153"/>
-      <c r="AU14" s="153"/>
-      <c r="AV14" s="153"/>
-      <c r="AW14" s="153"/>
-      <c r="AX14" s="153"/>
-      <c r="AY14" s="153"/>
-      <c r="AZ14" s="154"/>
+      <c r="AO14" s="106"/>
+      <c r="AP14" s="106"/>
+      <c r="AQ14" s="106"/>
+      <c r="AR14" s="106"/>
+      <c r="AS14" s="106"/>
+      <c r="AT14" s="106"/>
+      <c r="AU14" s="106"/>
+      <c r="AV14" s="106"/>
+      <c r="AW14" s="106"/>
+      <c r="AX14" s="106"/>
+      <c r="AY14" s="106"/>
+      <c r="AZ14" s="128"/>
     </row>
     <row r="15" spans="2:52" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B15" s="167"/>
-      <c r="C15" s="115"/>
-      <c r="D15" s="116"/>
-      <c r="E15" s="116"/>
-      <c r="F15" s="116"/>
-      <c r="G15" s="116"/>
-      <c r="H15" s="116"/>
-      <c r="I15" s="117"/>
-      <c r="J15" s="153"/>
-      <c r="K15" s="153"/>
-      <c r="L15" s="153"/>
-      <c r="M15" s="153"/>
-      <c r="N15" s="153"/>
-      <c r="O15" s="153"/>
-      <c r="P15" s="153"/>
-      <c r="Q15" s="121"/>
-      <c r="R15" s="122"/>
-      <c r="S15" s="123"/>
-      <c r="T15" s="155" t="s">
+      <c r="B15" s="110"/>
+      <c r="C15" s="117"/>
+      <c r="D15" s="118"/>
+      <c r="E15" s="118"/>
+      <c r="F15" s="118"/>
+      <c r="G15" s="118"/>
+      <c r="H15" s="118"/>
+      <c r="I15" s="119"/>
+      <c r="J15" s="106"/>
+      <c r="K15" s="106"/>
+      <c r="L15" s="106"/>
+      <c r="M15" s="106"/>
+      <c r="N15" s="106"/>
+      <c r="O15" s="106"/>
+      <c r="P15" s="106"/>
+      <c r="Q15" s="175"/>
+      <c r="R15" s="176"/>
+      <c r="S15" s="177"/>
+      <c r="T15" s="112" t="s">
         <v>25</v>
       </c>
-      <c r="U15" s="155"/>
-      <c r="V15" s="157">
+      <c r="U15" s="112"/>
+      <c r="V15" s="109">
         <v>0</v>
       </c>
-      <c r="W15" s="157"/>
-      <c r="X15" s="143">
+      <c r="W15" s="109"/>
+      <c r="X15" s="130">
         <v>0</v>
       </c>
-      <c r="Y15" s="143"/>
+      <c r="Y15" s="130"/>
       <c r="Z15" s="12"/>
       <c r="AA15" s="13"/>
       <c r="AB15" s="14"/>
@@ -7087,54 +7102,54 @@
       <c r="AL15" s="12"/>
       <c r="AM15" s="13"/>
       <c r="AN15" s="14"/>
-      <c r="AO15" s="153"/>
-      <c r="AP15" s="153"/>
-      <c r="AQ15" s="153"/>
-      <c r="AR15" s="153"/>
-      <c r="AS15" s="153"/>
-      <c r="AT15" s="153"/>
-      <c r="AU15" s="153"/>
-      <c r="AV15" s="153"/>
-      <c r="AW15" s="153"/>
-      <c r="AX15" s="153"/>
-      <c r="AY15" s="153"/>
-      <c r="AZ15" s="154"/>
+      <c r="AO15" s="106"/>
+      <c r="AP15" s="106"/>
+      <c r="AQ15" s="106"/>
+      <c r="AR15" s="106"/>
+      <c r="AS15" s="106"/>
+      <c r="AT15" s="106"/>
+      <c r="AU15" s="106"/>
+      <c r="AV15" s="106"/>
+      <c r="AW15" s="106"/>
+      <c r="AX15" s="106"/>
+      <c r="AY15" s="106"/>
+      <c r="AZ15" s="128"/>
     </row>
     <row r="16" spans="2:52" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B16" s="167">
+      <c r="B16" s="110">
         <v>6</v>
       </c>
-      <c r="C16" s="112" t="s">
+      <c r="C16" s="114" t="s">
         <v>92</v>
       </c>
-      <c r="D16" s="113"/>
-      <c r="E16" s="113"/>
-      <c r="F16" s="113"/>
-      <c r="G16" s="113"/>
-      <c r="H16" s="113"/>
-      <c r="I16" s="114"/>
-      <c r="J16" s="193"/>
-      <c r="K16" s="153"/>
-      <c r="L16" s="153"/>
-      <c r="M16" s="153"/>
-      <c r="N16" s="153"/>
-      <c r="O16" s="153"/>
-      <c r="P16" s="153"/>
-      <c r="Q16" s="144"/>
-      <c r="R16" s="144"/>
-      <c r="S16" s="144"/>
-      <c r="T16" s="158" t="s">
+      <c r="D16" s="115"/>
+      <c r="E16" s="115"/>
+      <c r="F16" s="115"/>
+      <c r="G16" s="115"/>
+      <c r="H16" s="115"/>
+      <c r="I16" s="116"/>
+      <c r="J16" s="107"/>
+      <c r="K16" s="106"/>
+      <c r="L16" s="106"/>
+      <c r="M16" s="106"/>
+      <c r="N16" s="106"/>
+      <c r="O16" s="106"/>
+      <c r="P16" s="106"/>
+      <c r="Q16" s="113"/>
+      <c r="R16" s="113"/>
+      <c r="S16" s="113"/>
+      <c r="T16" s="111" t="s">
         <v>87</v>
       </c>
-      <c r="U16" s="158"/>
-      <c r="V16" s="156">
+      <c r="U16" s="111"/>
+      <c r="V16" s="108">
         <v>0</v>
       </c>
-      <c r="W16" s="156"/>
-      <c r="X16" s="142">
+      <c r="W16" s="108"/>
+      <c r="X16" s="129">
         <v>0</v>
       </c>
-      <c r="Y16" s="142"/>
+      <c r="Y16" s="129"/>
       <c r="Z16" s="9"/>
       <c r="AA16" s="10"/>
       <c r="AB16" s="11"/>
@@ -7150,50 +7165,50 @@
       <c r="AL16" s="9"/>
       <c r="AM16" s="10"/>
       <c r="AN16" s="11"/>
-      <c r="AO16" s="153"/>
-      <c r="AP16" s="153"/>
-      <c r="AQ16" s="153"/>
-      <c r="AR16" s="153"/>
-      <c r="AS16" s="153"/>
-      <c r="AT16" s="153"/>
-      <c r="AU16" s="153"/>
-      <c r="AV16" s="153"/>
-      <c r="AW16" s="153"/>
-      <c r="AX16" s="153"/>
-      <c r="AY16" s="153"/>
-      <c r="AZ16" s="154"/>
+      <c r="AO16" s="106"/>
+      <c r="AP16" s="106"/>
+      <c r="AQ16" s="106"/>
+      <c r="AR16" s="106"/>
+      <c r="AS16" s="106"/>
+      <c r="AT16" s="106"/>
+      <c r="AU16" s="106"/>
+      <c r="AV16" s="106"/>
+      <c r="AW16" s="106"/>
+      <c r="AX16" s="106"/>
+      <c r="AY16" s="106"/>
+      <c r="AZ16" s="128"/>
     </row>
     <row r="17" spans="2:52" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B17" s="167"/>
-      <c r="C17" s="115"/>
-      <c r="D17" s="116"/>
-      <c r="E17" s="116"/>
-      <c r="F17" s="116"/>
-      <c r="G17" s="116"/>
-      <c r="H17" s="116"/>
-      <c r="I17" s="117"/>
-      <c r="J17" s="153"/>
-      <c r="K17" s="153"/>
-      <c r="L17" s="153"/>
-      <c r="M17" s="153"/>
-      <c r="N17" s="153"/>
-      <c r="O17" s="153"/>
-      <c r="P17" s="153"/>
-      <c r="Q17" s="144"/>
-      <c r="R17" s="144"/>
-      <c r="S17" s="144"/>
-      <c r="T17" s="155" t="s">
+      <c r="B17" s="110"/>
+      <c r="C17" s="117"/>
+      <c r="D17" s="118"/>
+      <c r="E17" s="118"/>
+      <c r="F17" s="118"/>
+      <c r="G17" s="118"/>
+      <c r="H17" s="118"/>
+      <c r="I17" s="119"/>
+      <c r="J17" s="106"/>
+      <c r="K17" s="106"/>
+      <c r="L17" s="106"/>
+      <c r="M17" s="106"/>
+      <c r="N17" s="106"/>
+      <c r="O17" s="106"/>
+      <c r="P17" s="106"/>
+      <c r="Q17" s="113"/>
+      <c r="R17" s="113"/>
+      <c r="S17" s="113"/>
+      <c r="T17" s="112" t="s">
         <v>25</v>
       </c>
-      <c r="U17" s="155"/>
-      <c r="V17" s="157">
+      <c r="U17" s="112"/>
+      <c r="V17" s="109">
         <v>0</v>
       </c>
-      <c r="W17" s="157"/>
-      <c r="X17" s="143">
+      <c r="W17" s="109"/>
+      <c r="X17" s="130">
         <v>0</v>
       </c>
-      <c r="Y17" s="143"/>
+      <c r="Y17" s="130"/>
       <c r="Z17" s="12"/>
       <c r="AA17" s="13"/>
       <c r="AB17" s="14"/>
@@ -7209,54 +7224,54 @@
       <c r="AL17" s="12"/>
       <c r="AM17" s="13"/>
       <c r="AN17" s="14"/>
-      <c r="AO17" s="153"/>
-      <c r="AP17" s="153"/>
-      <c r="AQ17" s="153"/>
-      <c r="AR17" s="153"/>
-      <c r="AS17" s="153"/>
-      <c r="AT17" s="153"/>
-      <c r="AU17" s="153"/>
-      <c r="AV17" s="153"/>
-      <c r="AW17" s="153"/>
-      <c r="AX17" s="153"/>
-      <c r="AY17" s="153"/>
-      <c r="AZ17" s="154"/>
+      <c r="AO17" s="106"/>
+      <c r="AP17" s="106"/>
+      <c r="AQ17" s="106"/>
+      <c r="AR17" s="106"/>
+      <c r="AS17" s="106"/>
+      <c r="AT17" s="106"/>
+      <c r="AU17" s="106"/>
+      <c r="AV17" s="106"/>
+      <c r="AW17" s="106"/>
+      <c r="AX17" s="106"/>
+      <c r="AY17" s="106"/>
+      <c r="AZ17" s="128"/>
     </row>
     <row r="18" spans="2:52" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B18" s="104">
+      <c r="B18" s="126">
         <v>7</v>
       </c>
-      <c r="C18" s="106" t="s">
+      <c r="C18" s="159" t="s">
         <v>93</v>
       </c>
-      <c r="D18" s="107"/>
-      <c r="E18" s="107"/>
-      <c r="F18" s="107"/>
-      <c r="G18" s="107"/>
-      <c r="H18" s="107"/>
-      <c r="I18" s="108"/>
-      <c r="J18" s="112"/>
-      <c r="K18" s="113"/>
-      <c r="L18" s="113"/>
-      <c r="M18" s="113"/>
-      <c r="N18" s="113"/>
-      <c r="O18" s="113"/>
-      <c r="P18" s="114"/>
-      <c r="Q18" s="118"/>
-      <c r="R18" s="119"/>
-      <c r="S18" s="120"/>
-      <c r="T18" s="124" t="s">
+      <c r="D18" s="160"/>
+      <c r="E18" s="160"/>
+      <c r="F18" s="160"/>
+      <c r="G18" s="160"/>
+      <c r="H18" s="160"/>
+      <c r="I18" s="161"/>
+      <c r="J18" s="114"/>
+      <c r="K18" s="115"/>
+      <c r="L18" s="115"/>
+      <c r="M18" s="115"/>
+      <c r="N18" s="115"/>
+      <c r="O18" s="115"/>
+      <c r="P18" s="116"/>
+      <c r="Q18" s="172"/>
+      <c r="R18" s="173"/>
+      <c r="S18" s="174"/>
+      <c r="T18" s="162" t="s">
         <v>87</v>
       </c>
-      <c r="U18" s="125"/>
-      <c r="V18" s="126">
+      <c r="U18" s="163"/>
+      <c r="V18" s="122">
         <v>0</v>
       </c>
-      <c r="W18" s="127"/>
-      <c r="X18" s="128">
+      <c r="W18" s="123"/>
+      <c r="X18" s="168">
         <v>0</v>
       </c>
-      <c r="Y18" s="129"/>
+      <c r="Y18" s="169"/>
       <c r="Z18" s="9"/>
       <c r="AA18" s="10"/>
       <c r="AB18" s="11"/>
@@ -7272,50 +7287,50 @@
       <c r="AL18" s="9"/>
       <c r="AM18" s="10"/>
       <c r="AN18" s="11"/>
-      <c r="AO18" s="112"/>
-      <c r="AP18" s="113"/>
-      <c r="AQ18" s="113"/>
-      <c r="AR18" s="113"/>
-      <c r="AS18" s="113"/>
-      <c r="AT18" s="113"/>
-      <c r="AU18" s="113"/>
-      <c r="AV18" s="113"/>
-      <c r="AW18" s="113"/>
-      <c r="AX18" s="113"/>
-      <c r="AY18" s="113"/>
-      <c r="AZ18" s="130"/>
+      <c r="AO18" s="114"/>
+      <c r="AP18" s="115"/>
+      <c r="AQ18" s="115"/>
+      <c r="AR18" s="115"/>
+      <c r="AS18" s="115"/>
+      <c r="AT18" s="115"/>
+      <c r="AU18" s="115"/>
+      <c r="AV18" s="115"/>
+      <c r="AW18" s="115"/>
+      <c r="AX18" s="115"/>
+      <c r="AY18" s="115"/>
+      <c r="AZ18" s="164"/>
     </row>
     <row r="19" spans="2:52" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B19" s="105"/>
-      <c r="C19" s="109"/>
-      <c r="D19" s="110"/>
-      <c r="E19" s="110"/>
-      <c r="F19" s="110"/>
-      <c r="G19" s="110"/>
-      <c r="H19" s="110"/>
-      <c r="I19" s="111"/>
-      <c r="J19" s="115"/>
-      <c r="K19" s="116"/>
-      <c r="L19" s="116"/>
-      <c r="M19" s="116"/>
-      <c r="N19" s="116"/>
-      <c r="O19" s="116"/>
-      <c r="P19" s="117"/>
-      <c r="Q19" s="121"/>
-      <c r="R19" s="122"/>
-      <c r="S19" s="123"/>
-      <c r="T19" s="132" t="s">
+      <c r="B19" s="127"/>
+      <c r="C19" s="144"/>
+      <c r="D19" s="145"/>
+      <c r="E19" s="145"/>
+      <c r="F19" s="145"/>
+      <c r="G19" s="145"/>
+      <c r="H19" s="145"/>
+      <c r="I19" s="146"/>
+      <c r="J19" s="117"/>
+      <c r="K19" s="118"/>
+      <c r="L19" s="118"/>
+      <c r="M19" s="118"/>
+      <c r="N19" s="118"/>
+      <c r="O19" s="118"/>
+      <c r="P19" s="119"/>
+      <c r="Q19" s="175"/>
+      <c r="R19" s="176"/>
+      <c r="S19" s="177"/>
+      <c r="T19" s="166" t="s">
         <v>25</v>
       </c>
-      <c r="U19" s="133"/>
-      <c r="V19" s="134">
+      <c r="U19" s="167"/>
+      <c r="V19" s="124">
         <v>0</v>
       </c>
-      <c r="W19" s="135"/>
-      <c r="X19" s="136">
+      <c r="W19" s="125"/>
+      <c r="X19" s="170">
         <v>0</v>
       </c>
-      <c r="Y19" s="137"/>
+      <c r="Y19" s="171"/>
       <c r="Z19" s="12"/>
       <c r="AA19" s="13"/>
       <c r="AB19" s="14"/>
@@ -7331,54 +7346,54 @@
       <c r="AL19" s="12"/>
       <c r="AM19" s="13"/>
       <c r="AN19" s="14"/>
-      <c r="AO19" s="115"/>
-      <c r="AP19" s="116"/>
-      <c r="AQ19" s="116"/>
-      <c r="AR19" s="116"/>
-      <c r="AS19" s="116"/>
-      <c r="AT19" s="116"/>
-      <c r="AU19" s="116"/>
-      <c r="AV19" s="116"/>
-      <c r="AW19" s="116"/>
-      <c r="AX19" s="116"/>
-      <c r="AY19" s="116"/>
-      <c r="AZ19" s="131"/>
+      <c r="AO19" s="117"/>
+      <c r="AP19" s="118"/>
+      <c r="AQ19" s="118"/>
+      <c r="AR19" s="118"/>
+      <c r="AS19" s="118"/>
+      <c r="AT19" s="118"/>
+      <c r="AU19" s="118"/>
+      <c r="AV19" s="118"/>
+      <c r="AW19" s="118"/>
+      <c r="AX19" s="118"/>
+      <c r="AY19" s="118"/>
+      <c r="AZ19" s="165"/>
     </row>
     <row r="20" spans="2:52" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B20" s="104">
+      <c r="B20" s="126">
         <v>8</v>
       </c>
-      <c r="C20" s="106" t="s">
+      <c r="C20" s="159" t="s">
         <v>94</v>
       </c>
-      <c r="D20" s="107"/>
-      <c r="E20" s="107"/>
-      <c r="F20" s="107"/>
-      <c r="G20" s="107"/>
-      <c r="H20" s="107"/>
-      <c r="I20" s="108"/>
-      <c r="J20" s="112"/>
-      <c r="K20" s="113"/>
-      <c r="L20" s="113"/>
-      <c r="M20" s="113"/>
-      <c r="N20" s="113"/>
-      <c r="O20" s="113"/>
-      <c r="P20" s="114"/>
-      <c r="Q20" s="118"/>
-      <c r="R20" s="119"/>
-      <c r="S20" s="120"/>
-      <c r="T20" s="124" t="s">
+      <c r="D20" s="160"/>
+      <c r="E20" s="160"/>
+      <c r="F20" s="160"/>
+      <c r="G20" s="160"/>
+      <c r="H20" s="160"/>
+      <c r="I20" s="161"/>
+      <c r="J20" s="114"/>
+      <c r="K20" s="115"/>
+      <c r="L20" s="115"/>
+      <c r="M20" s="115"/>
+      <c r="N20" s="115"/>
+      <c r="O20" s="115"/>
+      <c r="P20" s="116"/>
+      <c r="Q20" s="172"/>
+      <c r="R20" s="173"/>
+      <c r="S20" s="174"/>
+      <c r="T20" s="162" t="s">
         <v>87</v>
       </c>
-      <c r="U20" s="125"/>
-      <c r="V20" s="126">
+      <c r="U20" s="163"/>
+      <c r="V20" s="122">
         <v>0</v>
       </c>
-      <c r="W20" s="127"/>
-      <c r="X20" s="128">
+      <c r="W20" s="123"/>
+      <c r="X20" s="168">
         <v>0</v>
       </c>
-      <c r="Y20" s="129"/>
+      <c r="Y20" s="169"/>
       <c r="Z20" s="9"/>
       <c r="AA20" s="10"/>
       <c r="AB20" s="11"/>
@@ -7394,50 +7409,50 @@
       <c r="AL20" s="9"/>
       <c r="AM20" s="10"/>
       <c r="AN20" s="11"/>
-      <c r="AO20" s="112"/>
-      <c r="AP20" s="113"/>
-      <c r="AQ20" s="113"/>
-      <c r="AR20" s="113"/>
-      <c r="AS20" s="113"/>
-      <c r="AT20" s="113"/>
-      <c r="AU20" s="113"/>
-      <c r="AV20" s="113"/>
-      <c r="AW20" s="113"/>
-      <c r="AX20" s="113"/>
-      <c r="AY20" s="113"/>
-      <c r="AZ20" s="130"/>
+      <c r="AO20" s="114"/>
+      <c r="AP20" s="115"/>
+      <c r="AQ20" s="115"/>
+      <c r="AR20" s="115"/>
+      <c r="AS20" s="115"/>
+      <c r="AT20" s="115"/>
+      <c r="AU20" s="115"/>
+      <c r="AV20" s="115"/>
+      <c r="AW20" s="115"/>
+      <c r="AX20" s="115"/>
+      <c r="AY20" s="115"/>
+      <c r="AZ20" s="164"/>
     </row>
     <row r="21" spans="2:52" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B21" s="105"/>
-      <c r="C21" s="109"/>
-      <c r="D21" s="110"/>
-      <c r="E21" s="110"/>
-      <c r="F21" s="110"/>
-      <c r="G21" s="110"/>
-      <c r="H21" s="110"/>
-      <c r="I21" s="111"/>
-      <c r="J21" s="115"/>
-      <c r="K21" s="116"/>
-      <c r="L21" s="116"/>
-      <c r="M21" s="116"/>
-      <c r="N21" s="116"/>
-      <c r="O21" s="116"/>
-      <c r="P21" s="117"/>
-      <c r="Q21" s="121"/>
-      <c r="R21" s="122"/>
-      <c r="S21" s="123"/>
-      <c r="T21" s="132" t="s">
+      <c r="B21" s="127"/>
+      <c r="C21" s="144"/>
+      <c r="D21" s="145"/>
+      <c r="E21" s="145"/>
+      <c r="F21" s="145"/>
+      <c r="G21" s="145"/>
+      <c r="H21" s="145"/>
+      <c r="I21" s="146"/>
+      <c r="J21" s="117"/>
+      <c r="K21" s="118"/>
+      <c r="L21" s="118"/>
+      <c r="M21" s="118"/>
+      <c r="N21" s="118"/>
+      <c r="O21" s="118"/>
+      <c r="P21" s="119"/>
+      <c r="Q21" s="175"/>
+      <c r="R21" s="176"/>
+      <c r="S21" s="177"/>
+      <c r="T21" s="166" t="s">
         <v>25</v>
       </c>
-      <c r="U21" s="133"/>
-      <c r="V21" s="134">
+      <c r="U21" s="167"/>
+      <c r="V21" s="124">
         <v>0</v>
       </c>
-      <c r="W21" s="135"/>
-      <c r="X21" s="136">
+      <c r="W21" s="125"/>
+      <c r="X21" s="170">
         <v>0</v>
       </c>
-      <c r="Y21" s="137"/>
+      <c r="Y21" s="171"/>
       <c r="Z21" s="12"/>
       <c r="AA21" s="13"/>
       <c r="AB21" s="14"/>
@@ -7453,54 +7468,54 @@
       <c r="AL21" s="12"/>
       <c r="AM21" s="13"/>
       <c r="AN21" s="14"/>
-      <c r="AO21" s="115"/>
-      <c r="AP21" s="116"/>
-      <c r="AQ21" s="116"/>
-      <c r="AR21" s="116"/>
-      <c r="AS21" s="116"/>
-      <c r="AT21" s="116"/>
-      <c r="AU21" s="116"/>
-      <c r="AV21" s="116"/>
-      <c r="AW21" s="116"/>
-      <c r="AX21" s="116"/>
-      <c r="AY21" s="116"/>
-      <c r="AZ21" s="131"/>
+      <c r="AO21" s="117"/>
+      <c r="AP21" s="118"/>
+      <c r="AQ21" s="118"/>
+      <c r="AR21" s="118"/>
+      <c r="AS21" s="118"/>
+      <c r="AT21" s="118"/>
+      <c r="AU21" s="118"/>
+      <c r="AV21" s="118"/>
+      <c r="AW21" s="118"/>
+      <c r="AX21" s="118"/>
+      <c r="AY21" s="118"/>
+      <c r="AZ21" s="165"/>
     </row>
     <row r="22" spans="2:52" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B22" s="174">
+      <c r="B22" s="139">
         <v>9</v>
       </c>
-      <c r="C22" s="176" t="s">
+      <c r="C22" s="141" t="s">
         <v>95</v>
       </c>
-      <c r="D22" s="177"/>
-      <c r="E22" s="177"/>
-      <c r="F22" s="177"/>
-      <c r="G22" s="177"/>
-      <c r="H22" s="177"/>
-      <c r="I22" s="178"/>
-      <c r="J22" s="161"/>
-      <c r="K22" s="162"/>
-      <c r="L22" s="162"/>
-      <c r="M22" s="162"/>
-      <c r="N22" s="162"/>
-      <c r="O22" s="162"/>
-      <c r="P22" s="163"/>
-      <c r="Q22" s="183"/>
-      <c r="R22" s="184"/>
-      <c r="S22" s="185"/>
-      <c r="T22" s="179" t="s">
+      <c r="D22" s="142"/>
+      <c r="E22" s="142"/>
+      <c r="F22" s="142"/>
+      <c r="G22" s="142"/>
+      <c r="H22" s="142"/>
+      <c r="I22" s="143"/>
+      <c r="J22" s="131"/>
+      <c r="K22" s="132"/>
+      <c r="L22" s="132"/>
+      <c r="M22" s="132"/>
+      <c r="N22" s="132"/>
+      <c r="O22" s="132"/>
+      <c r="P22" s="180"/>
+      <c r="Q22" s="151"/>
+      <c r="R22" s="152"/>
+      <c r="S22" s="153"/>
+      <c r="T22" s="147" t="s">
         <v>87</v>
       </c>
-      <c r="U22" s="180"/>
-      <c r="V22" s="159">
+      <c r="U22" s="148"/>
+      <c r="V22" s="178">
         <v>0</v>
       </c>
-      <c r="W22" s="160"/>
-      <c r="X22" s="172">
+      <c r="W22" s="179"/>
+      <c r="X22" s="137">
         <v>0</v>
       </c>
-      <c r="Y22" s="173"/>
+      <c r="Y22" s="138"/>
       <c r="Z22" s="24"/>
       <c r="AA22" s="25"/>
       <c r="AB22" s="26"/>
@@ -7516,50 +7531,50 @@
       <c r="AL22" s="24"/>
       <c r="AM22" s="25"/>
       <c r="AN22" s="26"/>
-      <c r="AO22" s="161"/>
-      <c r="AP22" s="162"/>
-      <c r="AQ22" s="162"/>
-      <c r="AR22" s="162"/>
-      <c r="AS22" s="162"/>
-      <c r="AT22" s="162"/>
-      <c r="AU22" s="162"/>
-      <c r="AV22" s="162"/>
-      <c r="AW22" s="162"/>
-      <c r="AX22" s="162"/>
-      <c r="AY22" s="162"/>
-      <c r="AZ22" s="170"/>
+      <c r="AO22" s="131"/>
+      <c r="AP22" s="132"/>
+      <c r="AQ22" s="132"/>
+      <c r="AR22" s="132"/>
+      <c r="AS22" s="132"/>
+      <c r="AT22" s="132"/>
+      <c r="AU22" s="132"/>
+      <c r="AV22" s="132"/>
+      <c r="AW22" s="132"/>
+      <c r="AX22" s="132"/>
+      <c r="AY22" s="132"/>
+      <c r="AZ22" s="133"/>
     </row>
     <row r="23" spans="2:52" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B23" s="175"/>
-      <c r="C23" s="109"/>
-      <c r="D23" s="110"/>
-      <c r="E23" s="110"/>
-      <c r="F23" s="110"/>
-      <c r="G23" s="110"/>
-      <c r="H23" s="110"/>
-      <c r="I23" s="111"/>
-      <c r="J23" s="164"/>
-      <c r="K23" s="165"/>
-      <c r="L23" s="165"/>
-      <c r="M23" s="165"/>
-      <c r="N23" s="165"/>
-      <c r="O23" s="165"/>
-      <c r="P23" s="166"/>
-      <c r="Q23" s="186"/>
-      <c r="R23" s="187"/>
-      <c r="S23" s="188"/>
-      <c r="T23" s="181" t="s">
+      <c r="B23" s="140"/>
+      <c r="C23" s="144"/>
+      <c r="D23" s="145"/>
+      <c r="E23" s="145"/>
+      <c r="F23" s="145"/>
+      <c r="G23" s="145"/>
+      <c r="H23" s="145"/>
+      <c r="I23" s="146"/>
+      <c r="J23" s="134"/>
+      <c r="K23" s="135"/>
+      <c r="L23" s="135"/>
+      <c r="M23" s="135"/>
+      <c r="N23" s="135"/>
+      <c r="O23" s="135"/>
+      <c r="P23" s="181"/>
+      <c r="Q23" s="154"/>
+      <c r="R23" s="155"/>
+      <c r="S23" s="156"/>
+      <c r="T23" s="149" t="s">
         <v>25</v>
       </c>
-      <c r="U23" s="182"/>
-      <c r="V23" s="168">
+      <c r="U23" s="150"/>
+      <c r="V23" s="120">
         <v>0</v>
       </c>
-      <c r="W23" s="169"/>
-      <c r="X23" s="189">
+      <c r="W23" s="121"/>
+      <c r="X23" s="157">
         <v>0</v>
       </c>
-      <c r="Y23" s="190"/>
+      <c r="Y23" s="158"/>
       <c r="Z23" s="15"/>
       <c r="AA23" s="16"/>
       <c r="AB23" s="17"/>
@@ -7575,18 +7590,18 @@
       <c r="AL23" s="15"/>
       <c r="AM23" s="16"/>
       <c r="AN23" s="17"/>
-      <c r="AO23" s="164"/>
-      <c r="AP23" s="165"/>
-      <c r="AQ23" s="165"/>
-      <c r="AR23" s="165"/>
-      <c r="AS23" s="165"/>
-      <c r="AT23" s="165"/>
-      <c r="AU23" s="165"/>
-      <c r="AV23" s="165"/>
-      <c r="AW23" s="165"/>
-      <c r="AX23" s="165"/>
-      <c r="AY23" s="165"/>
-      <c r="AZ23" s="171"/>
+      <c r="AO23" s="134"/>
+      <c r="AP23" s="135"/>
+      <c r="AQ23" s="135"/>
+      <c r="AR23" s="135"/>
+      <c r="AS23" s="135"/>
+      <c r="AT23" s="135"/>
+      <c r="AU23" s="135"/>
+      <c r="AV23" s="135"/>
+      <c r="AW23" s="135"/>
+      <c r="AX23" s="135"/>
+      <c r="AY23" s="135"/>
+      <c r="AZ23" s="136"/>
     </row>
     <row r="24" spans="2:52" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D24" s="18"/>
@@ -7645,27 +7660,74 @@
     <row r="50" ht="18" customHeight="1" x14ac:dyDescent="0.2"/>
   </sheetData>
   <mergeCells count="113">
-    <mergeCell ref="B1:P1"/>
-    <mergeCell ref="J10:P11"/>
-    <mergeCell ref="J12:P13"/>
-    <mergeCell ref="J14:P15"/>
-    <mergeCell ref="J16:P17"/>
-    <mergeCell ref="V10:W10"/>
-    <mergeCell ref="V11:W11"/>
-    <mergeCell ref="V13:W13"/>
-    <mergeCell ref="V14:W14"/>
-    <mergeCell ref="V15:W15"/>
-    <mergeCell ref="V17:W17"/>
-    <mergeCell ref="B6:B7"/>
-    <mergeCell ref="T6:U6"/>
-    <mergeCell ref="T7:U7"/>
-    <mergeCell ref="B10:B11"/>
-    <mergeCell ref="C10:I11"/>
-    <mergeCell ref="Q8:S9"/>
-    <mergeCell ref="Q10:S11"/>
-    <mergeCell ref="B8:B9"/>
-    <mergeCell ref="C8:I9"/>
-    <mergeCell ref="J8:P9"/>
+    <mergeCell ref="B20:B21"/>
+    <mergeCell ref="C20:I21"/>
+    <mergeCell ref="J20:P21"/>
+    <mergeCell ref="Q20:S21"/>
+    <mergeCell ref="T20:U20"/>
+    <mergeCell ref="V20:W20"/>
+    <mergeCell ref="X20:Y20"/>
+    <mergeCell ref="AO20:AZ21"/>
+    <mergeCell ref="T21:U21"/>
+    <mergeCell ref="V21:W21"/>
+    <mergeCell ref="X21:Y21"/>
+    <mergeCell ref="AO4:AZ5"/>
+    <mergeCell ref="AI4:AK4"/>
+    <mergeCell ref="AL4:AN4"/>
+    <mergeCell ref="AF4:AH4"/>
+    <mergeCell ref="X6:Y6"/>
+    <mergeCell ref="X7:Y7"/>
+    <mergeCell ref="X8:Y8"/>
+    <mergeCell ref="B2:I2"/>
+    <mergeCell ref="J2:AD2"/>
+    <mergeCell ref="X4:Y5"/>
+    <mergeCell ref="T4:W5"/>
+    <mergeCell ref="Z4:AB4"/>
+    <mergeCell ref="AC4:AE4"/>
+    <mergeCell ref="B4:I5"/>
+    <mergeCell ref="J4:P5"/>
+    <mergeCell ref="Q4:S5"/>
+    <mergeCell ref="AO6:AZ7"/>
+    <mergeCell ref="C6:I7"/>
+    <mergeCell ref="Q6:S7"/>
+    <mergeCell ref="J6:P7"/>
+    <mergeCell ref="AO10:AZ11"/>
+    <mergeCell ref="T11:U11"/>
+    <mergeCell ref="X9:Y9"/>
+    <mergeCell ref="X10:Y10"/>
+    <mergeCell ref="X11:Y11"/>
+    <mergeCell ref="V8:W8"/>
+    <mergeCell ref="V9:W9"/>
+    <mergeCell ref="AO8:AZ9"/>
+    <mergeCell ref="V6:W6"/>
+    <mergeCell ref="V7:W7"/>
+    <mergeCell ref="T9:U9"/>
+    <mergeCell ref="T10:U10"/>
+    <mergeCell ref="T8:U8"/>
+    <mergeCell ref="AO18:AZ19"/>
+    <mergeCell ref="T19:U19"/>
+    <mergeCell ref="X18:Y18"/>
+    <mergeCell ref="X19:Y19"/>
+    <mergeCell ref="Q18:S19"/>
+    <mergeCell ref="V22:W22"/>
+    <mergeCell ref="J22:P23"/>
+    <mergeCell ref="B12:B13"/>
+    <mergeCell ref="C12:I13"/>
+    <mergeCell ref="T12:U12"/>
+    <mergeCell ref="AO12:AZ13"/>
+    <mergeCell ref="T13:U13"/>
+    <mergeCell ref="X12:Y12"/>
+    <mergeCell ref="X13:Y13"/>
+    <mergeCell ref="V12:W12"/>
+    <mergeCell ref="B14:B15"/>
+    <mergeCell ref="C14:I15"/>
+    <mergeCell ref="T14:U14"/>
+    <mergeCell ref="AO14:AZ15"/>
+    <mergeCell ref="T15:U15"/>
+    <mergeCell ref="X14:Y14"/>
+    <mergeCell ref="X15:Y15"/>
+    <mergeCell ref="Q12:S13"/>
+    <mergeCell ref="Q14:S15"/>
     <mergeCell ref="V23:W23"/>
     <mergeCell ref="V18:W18"/>
     <mergeCell ref="V19:W19"/>
@@ -7690,74 +7752,27 @@
     <mergeCell ref="X23:Y23"/>
     <mergeCell ref="C18:I19"/>
     <mergeCell ref="T18:U18"/>
-    <mergeCell ref="AO18:AZ19"/>
-    <mergeCell ref="T19:U19"/>
-    <mergeCell ref="X18:Y18"/>
-    <mergeCell ref="X19:Y19"/>
-    <mergeCell ref="Q18:S19"/>
-    <mergeCell ref="V22:W22"/>
-    <mergeCell ref="J22:P23"/>
-    <mergeCell ref="B12:B13"/>
-    <mergeCell ref="C12:I13"/>
-    <mergeCell ref="T12:U12"/>
-    <mergeCell ref="AO12:AZ13"/>
-    <mergeCell ref="T13:U13"/>
-    <mergeCell ref="X12:Y12"/>
-    <mergeCell ref="X13:Y13"/>
-    <mergeCell ref="V12:W12"/>
-    <mergeCell ref="B14:B15"/>
-    <mergeCell ref="C14:I15"/>
-    <mergeCell ref="T14:U14"/>
-    <mergeCell ref="AO14:AZ15"/>
-    <mergeCell ref="T15:U15"/>
-    <mergeCell ref="X14:Y14"/>
-    <mergeCell ref="X15:Y15"/>
-    <mergeCell ref="Q12:S13"/>
-    <mergeCell ref="Q14:S15"/>
-    <mergeCell ref="AO10:AZ11"/>
-    <mergeCell ref="T11:U11"/>
-    <mergeCell ref="X9:Y9"/>
-    <mergeCell ref="X10:Y10"/>
-    <mergeCell ref="X11:Y11"/>
-    <mergeCell ref="V8:W8"/>
-    <mergeCell ref="V9:W9"/>
-    <mergeCell ref="AO8:AZ9"/>
-    <mergeCell ref="V6:W6"/>
-    <mergeCell ref="V7:W7"/>
-    <mergeCell ref="T9:U9"/>
-    <mergeCell ref="T10:U10"/>
-    <mergeCell ref="T8:U8"/>
-    <mergeCell ref="AO4:AZ5"/>
-    <mergeCell ref="AI4:AK4"/>
-    <mergeCell ref="AL4:AN4"/>
-    <mergeCell ref="AF4:AH4"/>
-    <mergeCell ref="X6:Y6"/>
-    <mergeCell ref="X7:Y7"/>
-    <mergeCell ref="X8:Y8"/>
-    <mergeCell ref="B2:I2"/>
-    <mergeCell ref="J2:AD2"/>
-    <mergeCell ref="X4:Y5"/>
-    <mergeCell ref="T4:W5"/>
-    <mergeCell ref="Z4:AB4"/>
-    <mergeCell ref="AC4:AE4"/>
-    <mergeCell ref="B4:I5"/>
-    <mergeCell ref="J4:P5"/>
-    <mergeCell ref="Q4:S5"/>
-    <mergeCell ref="AO6:AZ7"/>
-    <mergeCell ref="C6:I7"/>
-    <mergeCell ref="Q6:S7"/>
-    <mergeCell ref="J6:P7"/>
-    <mergeCell ref="B20:B21"/>
-    <mergeCell ref="C20:I21"/>
-    <mergeCell ref="J20:P21"/>
-    <mergeCell ref="Q20:S21"/>
-    <mergeCell ref="T20:U20"/>
-    <mergeCell ref="V20:W20"/>
-    <mergeCell ref="X20:Y20"/>
-    <mergeCell ref="AO20:AZ21"/>
-    <mergeCell ref="T21:U21"/>
-    <mergeCell ref="V21:W21"/>
-    <mergeCell ref="X21:Y21"/>
+    <mergeCell ref="B1:P1"/>
+    <mergeCell ref="J10:P11"/>
+    <mergeCell ref="J12:P13"/>
+    <mergeCell ref="J14:P15"/>
+    <mergeCell ref="J16:P17"/>
+    <mergeCell ref="V10:W10"/>
+    <mergeCell ref="V11:W11"/>
+    <mergeCell ref="V13:W13"/>
+    <mergeCell ref="V14:W14"/>
+    <mergeCell ref="V15:W15"/>
+    <mergeCell ref="V17:W17"/>
+    <mergeCell ref="B6:B7"/>
+    <mergeCell ref="T6:U6"/>
+    <mergeCell ref="T7:U7"/>
+    <mergeCell ref="B10:B11"/>
+    <mergeCell ref="C10:I11"/>
+    <mergeCell ref="Q8:S9"/>
+    <mergeCell ref="Q10:S11"/>
+    <mergeCell ref="B8:B9"/>
+    <mergeCell ref="C8:I9"/>
+    <mergeCell ref="J8:P9"/>
   </mergeCells>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.51200000000000001" footer="0.51200000000000001"/>
@@ -7781,51 +7796,51 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="27">
+      <c r="A1" s="28">
         <v>1</v>
       </c>
-      <c r="B1" s="34" t="s">
+      <c r="B1" s="32" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="34"/>
-      <c r="D1" s="34"/>
-      <c r="E1" s="36"/>
-      <c r="F1" s="36"/>
-      <c r="G1" s="36"/>
-      <c r="H1" s="36"/>
-      <c r="I1" s="36"/>
-      <c r="J1" s="37"/>
+      <c r="C1" s="32"/>
+      <c r="D1" s="32"/>
+      <c r="E1" s="78"/>
+      <c r="F1" s="78"/>
+      <c r="G1" s="78"/>
+      <c r="H1" s="78"/>
+      <c r="I1" s="78"/>
+      <c r="J1" s="79"/>
     </row>
     <row r="2" spans="1:10" ht="13.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="31"/>
-      <c r="B2" s="35"/>
-      <c r="C2" s="35"/>
-      <c r="D2" s="35"/>
-      <c r="E2" s="38"/>
-      <c r="F2" s="38"/>
-      <c r="G2" s="38"/>
-      <c r="H2" s="38"/>
-      <c r="I2" s="38"/>
-      <c r="J2" s="39"/>
+      <c r="A2" s="29"/>
+      <c r="B2" s="77"/>
+      <c r="C2" s="77"/>
+      <c r="D2" s="77"/>
+      <c r="E2" s="80"/>
+      <c r="F2" s="80"/>
+      <c r="G2" s="80"/>
+      <c r="H2" s="80"/>
+      <c r="I2" s="80"/>
+      <c r="J2" s="81"/>
     </row>
     <row r="3" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="27">
+      <c r="A3" s="28">
         <v>2</v>
       </c>
-      <c r="B3" s="34" t="s">
+      <c r="B3" s="32" t="s">
         <v>96</v>
       </c>
-      <c r="C3" s="34"/>
-      <c r="D3" s="34"/>
-      <c r="E3" s="34"/>
-      <c r="F3" s="34"/>
-      <c r="G3" s="34"/>
-      <c r="H3" s="34"/>
-      <c r="I3" s="34"/>
-      <c r="J3" s="67"/>
+      <c r="C3" s="32"/>
+      <c r="D3" s="32"/>
+      <c r="E3" s="32"/>
+      <c r="F3" s="32"/>
+      <c r="G3" s="32"/>
+      <c r="H3" s="32"/>
+      <c r="I3" s="32"/>
+      <c r="J3" s="33"/>
     </row>
     <row r="4" spans="1:10" ht="13.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="28"/>
+      <c r="A4" s="30"/>
       <c r="B4" s="194" t="s">
         <v>97</v>
       </c>
@@ -7839,552 +7854,551 @@
       <c r="J4" s="195"/>
     </row>
     <row r="5" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="27">
+      <c r="A5" s="28">
         <v>3</v>
       </c>
-      <c r="B5" s="34" t="s">
+      <c r="B5" s="32" t="s">
         <v>98</v>
       </c>
-      <c r="C5" s="34"/>
-      <c r="D5" s="34"/>
-      <c r="E5" s="34"/>
-      <c r="F5" s="34"/>
-      <c r="G5" s="34"/>
-      <c r="H5" s="34"/>
-      <c r="I5" s="34"/>
-      <c r="J5" s="67"/>
+      <c r="C5" s="32"/>
+      <c r="D5" s="32"/>
+      <c r="E5" s="32"/>
+      <c r="F5" s="32"/>
+      <c r="G5" s="32"/>
+      <c r="H5" s="32"/>
+      <c r="I5" s="32"/>
+      <c r="J5" s="33"/>
     </row>
     <row r="6" spans="1:10" ht="13.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="31"/>
-      <c r="B6" s="73" t="s">
+      <c r="A6" s="29"/>
+      <c r="B6" s="40" t="s">
         <v>16</v>
       </c>
-      <c r="C6" s="73"/>
-      <c r="D6" s="73"/>
-      <c r="E6" s="73"/>
-      <c r="F6" s="73"/>
-      <c r="G6" s="73"/>
-      <c r="H6" s="73"/>
-      <c r="I6" s="73"/>
-      <c r="J6" s="74"/>
+      <c r="C6" s="40"/>
+      <c r="D6" s="40"/>
+      <c r="E6" s="40"/>
+      <c r="F6" s="40"/>
+      <c r="G6" s="40"/>
+      <c r="H6" s="40"/>
+      <c r="I6" s="40"/>
+      <c r="J6" s="41"/>
     </row>
     <row r="7" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="27">
+      <c r="A7" s="28">
         <v>4</v>
       </c>
-      <c r="B7" s="34" t="s">
+      <c r="B7" s="32" t="s">
         <v>99</v>
       </c>
-      <c r="C7" s="34"/>
-      <c r="D7" s="34"/>
-      <c r="E7" s="34"/>
-      <c r="F7" s="34"/>
-      <c r="G7" s="34"/>
-      <c r="H7" s="34"/>
-      <c r="I7" s="34"/>
-      <c r="J7" s="67"/>
+      <c r="C7" s="32"/>
+      <c r="D7" s="32"/>
+      <c r="E7" s="32"/>
+      <c r="F7" s="32"/>
+      <c r="G7" s="32"/>
+      <c r="H7" s="32"/>
+      <c r="I7" s="32"/>
+      <c r="J7" s="33"/>
     </row>
     <row r="8" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="28"/>
-      <c r="B8" s="69" t="s">
+      <c r="A8" s="30"/>
+      <c r="B8" s="36" t="s">
         <v>100</v>
       </c>
-      <c r="C8" s="69"/>
-      <c r="D8" s="69"/>
-      <c r="E8" s="69"/>
-      <c r="F8" s="69"/>
-      <c r="G8" s="69"/>
-      <c r="H8" s="69"/>
-      <c r="I8" s="69"/>
-      <c r="J8" s="70"/>
+      <c r="C8" s="36"/>
+      <c r="D8" s="36"/>
+      <c r="E8" s="36"/>
+      <c r="F8" s="36"/>
+      <c r="G8" s="36"/>
+      <c r="H8" s="36"/>
+      <c r="I8" s="36"/>
+      <c r="J8" s="37"/>
     </row>
     <row r="9" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="28"/>
-      <c r="B9" s="44"/>
-      <c r="C9" s="44"/>
-      <c r="D9" s="44"/>
-      <c r="E9" s="44"/>
-      <c r="F9" s="44"/>
-      <c r="G9" s="44"/>
-      <c r="H9" s="44"/>
-      <c r="I9" s="44"/>
-      <c r="J9" s="45"/>
+      <c r="A9" s="30"/>
+      <c r="B9" s="34"/>
+      <c r="C9" s="34"/>
+      <c r="D9" s="34"/>
+      <c r="E9" s="34"/>
+      <c r="F9" s="34"/>
+      <c r="G9" s="34"/>
+      <c r="H9" s="34"/>
+      <c r="I9" s="34"/>
+      <c r="J9" s="35"/>
     </row>
     <row r="10" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="28"/>
-      <c r="B10" s="44"/>
-      <c r="C10" s="44"/>
-      <c r="D10" s="44"/>
-      <c r="E10" s="44"/>
-      <c r="F10" s="44"/>
-      <c r="G10" s="44"/>
-      <c r="H10" s="44"/>
-      <c r="I10" s="44"/>
-      <c r="J10" s="45"/>
+      <c r="A10" s="30"/>
+      <c r="B10" s="34"/>
+      <c r="C10" s="34"/>
+      <c r="D10" s="34"/>
+      <c r="E10" s="34"/>
+      <c r="F10" s="34"/>
+      <c r="G10" s="34"/>
+      <c r="H10" s="34"/>
+      <c r="I10" s="34"/>
+      <c r="J10" s="35"/>
     </row>
     <row r="11" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="28"/>
-      <c r="B11" s="44"/>
-      <c r="C11" s="44"/>
-      <c r="D11" s="44"/>
-      <c r="E11" s="44"/>
-      <c r="F11" s="44"/>
-      <c r="G11" s="44"/>
-      <c r="H11" s="44"/>
-      <c r="I11" s="44"/>
-      <c r="J11" s="45"/>
+      <c r="A11" s="30"/>
+      <c r="B11" s="34"/>
+      <c r="C11" s="34"/>
+      <c r="D11" s="34"/>
+      <c r="E11" s="34"/>
+      <c r="F11" s="34"/>
+      <c r="G11" s="34"/>
+      <c r="H11" s="34"/>
+      <c r="I11" s="34"/>
+      <c r="J11" s="35"/>
     </row>
     <row r="12" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="28"/>
-      <c r="B12" s="44"/>
-      <c r="C12" s="44"/>
-      <c r="D12" s="44"/>
-      <c r="E12" s="44"/>
-      <c r="F12" s="44"/>
-      <c r="G12" s="44"/>
-      <c r="H12" s="44"/>
-      <c r="I12" s="44"/>
-      <c r="J12" s="45"/>
+      <c r="A12" s="30"/>
+      <c r="B12" s="34"/>
+      <c r="C12" s="34"/>
+      <c r="D12" s="34"/>
+      <c r="E12" s="34"/>
+      <c r="F12" s="34"/>
+      <c r="G12" s="34"/>
+      <c r="H12" s="34"/>
+      <c r="I12" s="34"/>
+      <c r="J12" s="35"/>
     </row>
     <row r="13" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="28"/>
-      <c r="B13" s="44"/>
-      <c r="C13" s="44"/>
-      <c r="D13" s="44"/>
-      <c r="E13" s="44"/>
-      <c r="F13" s="44"/>
-      <c r="G13" s="44"/>
-      <c r="H13" s="44"/>
-      <c r="I13" s="44"/>
-      <c r="J13" s="45"/>
+      <c r="A13" s="30"/>
+      <c r="B13" s="34"/>
+      <c r="C13" s="34"/>
+      <c r="D13" s="34"/>
+      <c r="E13" s="34"/>
+      <c r="F13" s="34"/>
+      <c r="G13" s="34"/>
+      <c r="H13" s="34"/>
+      <c r="I13" s="34"/>
+      <c r="J13" s="35"/>
     </row>
     <row r="14" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A14" s="28"/>
-      <c r="B14" s="44"/>
-      <c r="C14" s="44"/>
-      <c r="D14" s="44"/>
-      <c r="E14" s="44"/>
-      <c r="F14" s="44"/>
-      <c r="G14" s="44"/>
-      <c r="H14" s="44"/>
-      <c r="I14" s="44"/>
-      <c r="J14" s="45"/>
+      <c r="A14" s="30"/>
+      <c r="B14" s="34"/>
+      <c r="C14" s="34"/>
+      <c r="D14" s="34"/>
+      <c r="E14" s="34"/>
+      <c r="F14" s="34"/>
+      <c r="G14" s="34"/>
+      <c r="H14" s="34"/>
+      <c r="I14" s="34"/>
+      <c r="J14" s="35"/>
     </row>
     <row r="15" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A15" s="28"/>
-      <c r="B15" s="69" t="s">
+      <c r="A15" s="30"/>
+      <c r="B15" s="36" t="s">
         <v>101</v>
       </c>
-      <c r="C15" s="69"/>
-      <c r="D15" s="69"/>
-      <c r="E15" s="69"/>
-      <c r="F15" s="69"/>
-      <c r="G15" s="69"/>
-      <c r="H15" s="69"/>
-      <c r="I15" s="69"/>
-      <c r="J15" s="70"/>
+      <c r="C15" s="36"/>
+      <c r="D15" s="36"/>
+      <c r="E15" s="36"/>
+      <c r="F15" s="36"/>
+      <c r="G15" s="36"/>
+      <c r="H15" s="36"/>
+      <c r="I15" s="36"/>
+      <c r="J15" s="37"/>
     </row>
     <row r="16" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A16" s="28"/>
-      <c r="B16" s="44"/>
-      <c r="C16" s="44"/>
-      <c r="D16" s="44"/>
-      <c r="E16" s="44"/>
-      <c r="F16" s="44"/>
-      <c r="G16" s="44"/>
-      <c r="H16" s="44"/>
-      <c r="I16" s="44"/>
-      <c r="J16" s="45"/>
+      <c r="A16" s="30"/>
+      <c r="B16" s="34"/>
+      <c r="C16" s="34"/>
+      <c r="D16" s="34"/>
+      <c r="E16" s="34"/>
+      <c r="F16" s="34"/>
+      <c r="G16" s="34"/>
+      <c r="H16" s="34"/>
+      <c r="I16" s="34"/>
+      <c r="J16" s="35"/>
     </row>
     <row r="17" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A17" s="28"/>
-      <c r="B17" s="44"/>
-      <c r="C17" s="44"/>
-      <c r="D17" s="44"/>
-      <c r="E17" s="44"/>
-      <c r="F17" s="44"/>
-      <c r="G17" s="44"/>
-      <c r="H17" s="44"/>
-      <c r="I17" s="44"/>
-      <c r="J17" s="45"/>
+      <c r="A17" s="30"/>
+      <c r="B17" s="34"/>
+      <c r="C17" s="34"/>
+      <c r="D17" s="34"/>
+      <c r="E17" s="34"/>
+      <c r="F17" s="34"/>
+      <c r="G17" s="34"/>
+      <c r="H17" s="34"/>
+      <c r="I17" s="34"/>
+      <c r="J17" s="35"/>
     </row>
     <row r="18" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A18" s="28"/>
-      <c r="B18" s="44"/>
-      <c r="C18" s="44"/>
-      <c r="D18" s="44"/>
-      <c r="E18" s="44"/>
-      <c r="F18" s="44"/>
-      <c r="G18" s="44"/>
-      <c r="H18" s="44"/>
-      <c r="I18" s="44"/>
-      <c r="J18" s="45"/>
+      <c r="A18" s="30"/>
+      <c r="B18" s="34"/>
+      <c r="C18" s="34"/>
+      <c r="D18" s="34"/>
+      <c r="E18" s="34"/>
+      <c r="F18" s="34"/>
+      <c r="G18" s="34"/>
+      <c r="H18" s="34"/>
+      <c r="I18" s="34"/>
+      <c r="J18" s="35"/>
     </row>
     <row r="19" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A19" s="28"/>
-      <c r="B19" s="44"/>
-      <c r="C19" s="44"/>
-      <c r="D19" s="44"/>
-      <c r="E19" s="44"/>
-      <c r="F19" s="44"/>
-      <c r="G19" s="44"/>
-      <c r="H19" s="44"/>
-      <c r="I19" s="44"/>
-      <c r="J19" s="45"/>
+      <c r="A19" s="30"/>
+      <c r="B19" s="34"/>
+      <c r="C19" s="34"/>
+      <c r="D19" s="34"/>
+      <c r="E19" s="34"/>
+      <c r="F19" s="34"/>
+      <c r="G19" s="34"/>
+      <c r="H19" s="34"/>
+      <c r="I19" s="34"/>
+      <c r="J19" s="35"/>
     </row>
     <row r="20" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A20" s="28"/>
-      <c r="B20" s="44"/>
-      <c r="C20" s="44"/>
-      <c r="D20" s="44"/>
-      <c r="E20" s="44"/>
-      <c r="F20" s="44"/>
-      <c r="G20" s="44"/>
-      <c r="H20" s="44"/>
-      <c r="I20" s="44"/>
-      <c r="J20" s="45"/>
+      <c r="A20" s="30"/>
+      <c r="B20" s="34"/>
+      <c r="C20" s="34"/>
+      <c r="D20" s="34"/>
+      <c r="E20" s="34"/>
+      <c r="F20" s="34"/>
+      <c r="G20" s="34"/>
+      <c r="H20" s="34"/>
+      <c r="I20" s="34"/>
+      <c r="J20" s="35"/>
     </row>
     <row r="21" spans="1:10" ht="13.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="31"/>
-      <c r="B21" s="38"/>
-      <c r="C21" s="38"/>
-      <c r="D21" s="38"/>
-      <c r="E21" s="38"/>
-      <c r="F21" s="38"/>
-      <c r="G21" s="38"/>
-      <c r="H21" s="38"/>
-      <c r="I21" s="38"/>
-      <c r="J21" s="39"/>
+      <c r="A21" s="29"/>
+      <c r="B21" s="80"/>
+      <c r="C21" s="80"/>
+      <c r="D21" s="80"/>
+      <c r="E21" s="80"/>
+      <c r="F21" s="80"/>
+      <c r="G21" s="80"/>
+      <c r="H21" s="80"/>
+      <c r="I21" s="80"/>
+      <c r="J21" s="81"/>
     </row>
     <row r="22" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A22" s="27">
+      <c r="A22" s="28">
         <v>5</v>
       </c>
-      <c r="B22" s="34" t="s">
+      <c r="B22" s="32" t="s">
         <v>102</v>
       </c>
-      <c r="C22" s="34"/>
-      <c r="D22" s="34"/>
-      <c r="E22" s="34"/>
-      <c r="F22" s="34"/>
-      <c r="G22" s="34"/>
-      <c r="H22" s="34"/>
-      <c r="I22" s="34"/>
-      <c r="J22" s="67"/>
+      <c r="C22" s="32"/>
+      <c r="D22" s="32"/>
+      <c r="E22" s="32"/>
+      <c r="F22" s="32"/>
+      <c r="G22" s="32"/>
+      <c r="H22" s="32"/>
+      <c r="I22" s="32"/>
+      <c r="J22" s="33"/>
     </row>
     <row r="23" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A23" s="28"/>
-      <c r="B23" s="44"/>
-      <c r="C23" s="44"/>
-      <c r="D23" s="44"/>
-      <c r="E23" s="44"/>
-      <c r="F23" s="44"/>
-      <c r="G23" s="44"/>
-      <c r="H23" s="44"/>
-      <c r="I23" s="44"/>
-      <c r="J23" s="45"/>
+      <c r="A23" s="30"/>
+      <c r="B23" s="34"/>
+      <c r="C23" s="34"/>
+      <c r="D23" s="34"/>
+      <c r="E23" s="34"/>
+      <c r="F23" s="34"/>
+      <c r="G23" s="34"/>
+      <c r="H23" s="34"/>
+      <c r="I23" s="34"/>
+      <c r="J23" s="35"/>
     </row>
     <row r="24" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A24" s="28"/>
-      <c r="B24" s="44"/>
-      <c r="C24" s="44"/>
-      <c r="D24" s="44"/>
-      <c r="E24" s="44"/>
-      <c r="F24" s="44"/>
-      <c r="G24" s="44"/>
-      <c r="H24" s="44"/>
-      <c r="I24" s="44"/>
-      <c r="J24" s="45"/>
+      <c r="A24" s="30"/>
+      <c r="B24" s="34"/>
+      <c r="C24" s="34"/>
+      <c r="D24" s="34"/>
+      <c r="E24" s="34"/>
+      <c r="F24" s="34"/>
+      <c r="G24" s="34"/>
+      <c r="H24" s="34"/>
+      <c r="I24" s="34"/>
+      <c r="J24" s="35"/>
     </row>
     <row r="25" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A25" s="28"/>
-      <c r="B25" s="44"/>
-      <c r="C25" s="44"/>
-      <c r="D25" s="44"/>
-      <c r="E25" s="44"/>
-      <c r="F25" s="44"/>
-      <c r="G25" s="44"/>
-      <c r="H25" s="44"/>
-      <c r="I25" s="44"/>
-      <c r="J25" s="45"/>
+      <c r="A25" s="30"/>
+      <c r="B25" s="34"/>
+      <c r="C25" s="34"/>
+      <c r="D25" s="34"/>
+      <c r="E25" s="34"/>
+      <c r="F25" s="34"/>
+      <c r="G25" s="34"/>
+      <c r="H25" s="34"/>
+      <c r="I25" s="34"/>
+      <c r="J25" s="35"/>
     </row>
     <row r="26" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A26" s="28"/>
-      <c r="B26" s="44"/>
-      <c r="C26" s="44"/>
-      <c r="D26" s="44"/>
-      <c r="E26" s="44"/>
-      <c r="F26" s="44"/>
-      <c r="G26" s="44"/>
-      <c r="H26" s="44"/>
-      <c r="I26" s="44"/>
-      <c r="J26" s="45"/>
+      <c r="A26" s="30"/>
+      <c r="B26" s="34"/>
+      <c r="C26" s="34"/>
+      <c r="D26" s="34"/>
+      <c r="E26" s="34"/>
+      <c r="F26" s="34"/>
+      <c r="G26" s="34"/>
+      <c r="H26" s="34"/>
+      <c r="I26" s="34"/>
+      <c r="J26" s="35"/>
     </row>
     <row r="27" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A27" s="28"/>
-      <c r="B27" s="44"/>
-      <c r="C27" s="44"/>
-      <c r="D27" s="44"/>
-      <c r="E27" s="44"/>
-      <c r="F27" s="44"/>
-      <c r="G27" s="44"/>
-      <c r="H27" s="44"/>
-      <c r="I27" s="44"/>
-      <c r="J27" s="45"/>
+      <c r="A27" s="30"/>
+      <c r="B27" s="34"/>
+      <c r="C27" s="34"/>
+      <c r="D27" s="34"/>
+      <c r="E27" s="34"/>
+      <c r="F27" s="34"/>
+      <c r="G27" s="34"/>
+      <c r="H27" s="34"/>
+      <c r="I27" s="34"/>
+      <c r="J27" s="35"/>
     </row>
     <row r="28" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A28" s="28"/>
-      <c r="B28" s="44"/>
-      <c r="C28" s="44"/>
-      <c r="D28" s="44"/>
-      <c r="E28" s="44"/>
-      <c r="F28" s="44"/>
-      <c r="G28" s="44"/>
-      <c r="H28" s="44"/>
-      <c r="I28" s="44"/>
-      <c r="J28" s="45"/>
+      <c r="A28" s="30"/>
+      <c r="B28" s="34"/>
+      <c r="C28" s="34"/>
+      <c r="D28" s="34"/>
+      <c r="E28" s="34"/>
+      <c r="F28" s="34"/>
+      <c r="G28" s="34"/>
+      <c r="H28" s="34"/>
+      <c r="I28" s="34"/>
+      <c r="J28" s="35"/>
     </row>
     <row r="29" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A29" s="28"/>
-      <c r="B29" s="44"/>
-      <c r="C29" s="44"/>
-      <c r="D29" s="44"/>
-      <c r="E29" s="44"/>
-      <c r="F29" s="44"/>
-      <c r="G29" s="44"/>
-      <c r="H29" s="44"/>
-      <c r="I29" s="44"/>
-      <c r="J29" s="45"/>
+      <c r="A29" s="30"/>
+      <c r="B29" s="34"/>
+      <c r="C29" s="34"/>
+      <c r="D29" s="34"/>
+      <c r="E29" s="34"/>
+      <c r="F29" s="34"/>
+      <c r="G29" s="34"/>
+      <c r="H29" s="34"/>
+      <c r="I29" s="34"/>
+      <c r="J29" s="35"/>
     </row>
     <row r="30" spans="1:10" ht="13.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="31"/>
-      <c r="B30" s="38"/>
-      <c r="C30" s="38"/>
-      <c r="D30" s="38"/>
-      <c r="E30" s="38"/>
-      <c r="F30" s="38"/>
-      <c r="G30" s="38"/>
-      <c r="H30" s="38"/>
-      <c r="I30" s="38"/>
-      <c r="J30" s="39"/>
+      <c r="A30" s="29"/>
+      <c r="B30" s="80"/>
+      <c r="C30" s="80"/>
+      <c r="D30" s="80"/>
+      <c r="E30" s="80"/>
+      <c r="F30" s="80"/>
+      <c r="G30" s="80"/>
+      <c r="H30" s="80"/>
+      <c r="I30" s="80"/>
+      <c r="J30" s="81"/>
     </row>
     <row r="31" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A31" s="27">
+      <c r="A31" s="28">
         <v>6</v>
       </c>
-      <c r="B31" s="34" t="s">
+      <c r="B31" s="32" t="s">
         <v>103</v>
       </c>
-      <c r="C31" s="34"/>
-      <c r="D31" s="34"/>
-      <c r="E31" s="34"/>
-      <c r="F31" s="34"/>
-      <c r="G31" s="34"/>
-      <c r="H31" s="34"/>
-      <c r="I31" s="34"/>
-      <c r="J31" s="67"/>
+      <c r="C31" s="32"/>
+      <c r="D31" s="32"/>
+      <c r="E31" s="32"/>
+      <c r="F31" s="32"/>
+      <c r="G31" s="32"/>
+      <c r="H31" s="32"/>
+      <c r="I31" s="32"/>
+      <c r="J31" s="33"/>
     </row>
     <row r="32" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A32" s="28"/>
-      <c r="B32" s="44"/>
-      <c r="C32" s="44"/>
-      <c r="D32" s="44"/>
-      <c r="E32" s="44"/>
-      <c r="F32" s="44"/>
-      <c r="G32" s="44"/>
-      <c r="H32" s="44"/>
-      <c r="I32" s="44"/>
-      <c r="J32" s="45"/>
+      <c r="A32" s="30"/>
+      <c r="B32" s="34"/>
+      <c r="C32" s="34"/>
+      <c r="D32" s="34"/>
+      <c r="E32" s="34"/>
+      <c r="F32" s="34"/>
+      <c r="G32" s="34"/>
+      <c r="H32" s="34"/>
+      <c r="I32" s="34"/>
+      <c r="J32" s="35"/>
     </row>
     <row r="33" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A33" s="28"/>
-      <c r="B33" s="44"/>
-      <c r="C33" s="44"/>
-      <c r="D33" s="44"/>
-      <c r="E33" s="44"/>
-      <c r="F33" s="44"/>
-      <c r="G33" s="44"/>
-      <c r="H33" s="44"/>
-      <c r="I33" s="44"/>
-      <c r="J33" s="45"/>
+      <c r="A33" s="30"/>
+      <c r="B33" s="34"/>
+      <c r="C33" s="34"/>
+      <c r="D33" s="34"/>
+      <c r="E33" s="34"/>
+      <c r="F33" s="34"/>
+      <c r="G33" s="34"/>
+      <c r="H33" s="34"/>
+      <c r="I33" s="34"/>
+      <c r="J33" s="35"/>
     </row>
     <row r="34" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A34" s="28"/>
-      <c r="B34" s="44"/>
-      <c r="C34" s="44"/>
-      <c r="D34" s="44"/>
-      <c r="E34" s="44"/>
-      <c r="F34" s="44"/>
-      <c r="G34" s="44"/>
-      <c r="H34" s="44"/>
-      <c r="I34" s="44"/>
-      <c r="J34" s="45"/>
+      <c r="A34" s="30"/>
+      <c r="B34" s="34"/>
+      <c r="C34" s="34"/>
+      <c r="D34" s="34"/>
+      <c r="E34" s="34"/>
+      <c r="F34" s="34"/>
+      <c r="G34" s="34"/>
+      <c r="H34" s="34"/>
+      <c r="I34" s="34"/>
+      <c r="J34" s="35"/>
     </row>
     <row r="35" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A35" s="28"/>
-      <c r="B35" s="44"/>
-      <c r="C35" s="44"/>
-      <c r="D35" s="44"/>
-      <c r="E35" s="44"/>
-      <c r="F35" s="44"/>
-      <c r="G35" s="44"/>
-      <c r="H35" s="44"/>
-      <c r="I35" s="44"/>
-      <c r="J35" s="45"/>
+      <c r="A35" s="30"/>
+      <c r="B35" s="34"/>
+      <c r="C35" s="34"/>
+      <c r="D35" s="34"/>
+      <c r="E35" s="34"/>
+      <c r="F35" s="34"/>
+      <c r="G35" s="34"/>
+      <c r="H35" s="34"/>
+      <c r="I35" s="34"/>
+      <c r="J35" s="35"/>
     </row>
     <row r="36" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A36" s="28"/>
-      <c r="B36" s="44"/>
-      <c r="C36" s="44"/>
-      <c r="D36" s="44"/>
-      <c r="E36" s="44"/>
-      <c r="F36" s="44"/>
-      <c r="G36" s="44"/>
-      <c r="H36" s="44"/>
-      <c r="I36" s="44"/>
-      <c r="J36" s="45"/>
+      <c r="A36" s="30"/>
+      <c r="B36" s="34"/>
+      <c r="C36" s="34"/>
+      <c r="D36" s="34"/>
+      <c r="E36" s="34"/>
+      <c r="F36" s="34"/>
+      <c r="G36" s="34"/>
+      <c r="H36" s="34"/>
+      <c r="I36" s="34"/>
+      <c r="J36" s="35"/>
     </row>
     <row r="37" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A37" s="28"/>
-      <c r="B37" s="44"/>
-      <c r="C37" s="44"/>
-      <c r="D37" s="44"/>
-      <c r="E37" s="44"/>
-      <c r="F37" s="44"/>
-      <c r="G37" s="44"/>
-      <c r="H37" s="44"/>
-      <c r="I37" s="44"/>
-      <c r="J37" s="45"/>
+      <c r="A37" s="30"/>
+      <c r="B37" s="34"/>
+      <c r="C37" s="34"/>
+      <c r="D37" s="34"/>
+      <c r="E37" s="34"/>
+      <c r="F37" s="34"/>
+      <c r="G37" s="34"/>
+      <c r="H37" s="34"/>
+      <c r="I37" s="34"/>
+      <c r="J37" s="35"/>
     </row>
     <row r="38" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A38" s="28"/>
-      <c r="B38" s="44"/>
-      <c r="C38" s="44"/>
-      <c r="D38" s="44"/>
-      <c r="E38" s="44"/>
-      <c r="F38" s="44"/>
-      <c r="G38" s="44"/>
-      <c r="H38" s="44"/>
-      <c r="I38" s="44"/>
-      <c r="J38" s="45"/>
+      <c r="A38" s="30"/>
+      <c r="B38" s="34"/>
+      <c r="C38" s="34"/>
+      <c r="D38" s="34"/>
+      <c r="E38" s="34"/>
+      <c r="F38" s="34"/>
+      <c r="G38" s="34"/>
+      <c r="H38" s="34"/>
+      <c r="I38" s="34"/>
+      <c r="J38" s="35"/>
     </row>
     <row r="39" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A39" s="28"/>
-      <c r="B39" s="44"/>
-      <c r="C39" s="44"/>
-      <c r="D39" s="44"/>
-      <c r="E39" s="44"/>
-      <c r="F39" s="44"/>
-      <c r="G39" s="44"/>
-      <c r="H39" s="44"/>
-      <c r="I39" s="44"/>
-      <c r="J39" s="45"/>
+      <c r="A39" s="30"/>
+      <c r="B39" s="34"/>
+      <c r="C39" s="34"/>
+      <c r="D39" s="34"/>
+      <c r="E39" s="34"/>
+      <c r="F39" s="34"/>
+      <c r="G39" s="34"/>
+      <c r="H39" s="34"/>
+      <c r="I39" s="34"/>
+      <c r="J39" s="35"/>
     </row>
     <row r="40" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A40" s="28"/>
-      <c r="B40" s="44"/>
-      <c r="C40" s="44"/>
-      <c r="D40" s="44"/>
-      <c r="E40" s="44"/>
-      <c r="F40" s="44"/>
-      <c r="G40" s="44"/>
-      <c r="H40" s="44"/>
-      <c r="I40" s="44"/>
-      <c r="J40" s="45"/>
+      <c r="A40" s="30"/>
+      <c r="B40" s="34"/>
+      <c r="C40" s="34"/>
+      <c r="D40" s="34"/>
+      <c r="E40" s="34"/>
+      <c r="F40" s="34"/>
+      <c r="G40" s="34"/>
+      <c r="H40" s="34"/>
+      <c r="I40" s="34"/>
+      <c r="J40" s="35"/>
     </row>
     <row r="41" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A41" s="28"/>
-      <c r="B41" s="44"/>
-      <c r="C41" s="44"/>
-      <c r="D41" s="44"/>
-      <c r="E41" s="44"/>
-      <c r="F41" s="44"/>
-      <c r="G41" s="44"/>
-      <c r="H41" s="44"/>
-      <c r="I41" s="44"/>
-      <c r="J41" s="45"/>
+      <c r="A41" s="30"/>
+      <c r="B41" s="34"/>
+      <c r="C41" s="34"/>
+      <c r="D41" s="34"/>
+      <c r="E41" s="34"/>
+      <c r="F41" s="34"/>
+      <c r="G41" s="34"/>
+      <c r="H41" s="34"/>
+      <c r="I41" s="34"/>
+      <c r="J41" s="35"/>
     </row>
     <row r="42" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A42" s="28"/>
-      <c r="B42" s="44"/>
-      <c r="C42" s="44"/>
-      <c r="D42" s="44"/>
-      <c r="E42" s="44"/>
-      <c r="F42" s="44"/>
-      <c r="G42" s="44"/>
-      <c r="H42" s="44"/>
-      <c r="I42" s="44"/>
-      <c r="J42" s="45"/>
+      <c r="A42" s="30"/>
+      <c r="B42" s="34"/>
+      <c r="C42" s="34"/>
+      <c r="D42" s="34"/>
+      <c r="E42" s="34"/>
+      <c r="F42" s="34"/>
+      <c r="G42" s="34"/>
+      <c r="H42" s="34"/>
+      <c r="I42" s="34"/>
+      <c r="J42" s="35"/>
     </row>
     <row r="43" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A43" s="28"/>
-      <c r="B43" s="44"/>
-      <c r="C43" s="44"/>
-      <c r="D43" s="44"/>
-      <c r="E43" s="44"/>
-      <c r="F43" s="44"/>
-      <c r="G43" s="44"/>
-      <c r="H43" s="44"/>
-      <c r="I43" s="44"/>
-      <c r="J43" s="45"/>
+      <c r="A43" s="30"/>
+      <c r="B43" s="34"/>
+      <c r="C43" s="34"/>
+      <c r="D43" s="34"/>
+      <c r="E43" s="34"/>
+      <c r="F43" s="34"/>
+      <c r="G43" s="34"/>
+      <c r="H43" s="34"/>
+      <c r="I43" s="34"/>
+      <c r="J43" s="35"/>
     </row>
     <row r="44" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A44" s="28"/>
-      <c r="B44" s="44"/>
-      <c r="C44" s="44"/>
-      <c r="D44" s="44"/>
-      <c r="E44" s="44"/>
-      <c r="F44" s="44"/>
-      <c r="G44" s="44"/>
-      <c r="H44" s="44"/>
-      <c r="I44" s="44"/>
-      <c r="J44" s="45"/>
+      <c r="A44" s="30"/>
+      <c r="B44" s="34"/>
+      <c r="C44" s="34"/>
+      <c r="D44" s="34"/>
+      <c r="E44" s="34"/>
+      <c r="F44" s="34"/>
+      <c r="G44" s="34"/>
+      <c r="H44" s="34"/>
+      <c r="I44" s="34"/>
+      <c r="J44" s="35"/>
     </row>
     <row r="45" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A45" s="28"/>
-      <c r="B45" s="44"/>
-      <c r="C45" s="44"/>
-      <c r="D45" s="44"/>
-      <c r="E45" s="44"/>
-      <c r="F45" s="44"/>
-      <c r="G45" s="44"/>
-      <c r="H45" s="44"/>
-      <c r="I45" s="44"/>
-      <c r="J45" s="45"/>
+      <c r="A45" s="30"/>
+      <c r="B45" s="34"/>
+      <c r="C45" s="34"/>
+      <c r="D45" s="34"/>
+      <c r="E45" s="34"/>
+      <c r="F45" s="34"/>
+      <c r="G45" s="34"/>
+      <c r="H45" s="34"/>
+      <c r="I45" s="34"/>
+      <c r="J45" s="35"/>
     </row>
     <row r="46" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A46" s="28"/>
-      <c r="B46" s="44"/>
-      <c r="C46" s="44"/>
-      <c r="D46" s="44"/>
-      <c r="E46" s="44"/>
-      <c r="F46" s="44"/>
-      <c r="G46" s="44"/>
-      <c r="H46" s="44"/>
-      <c r="I46" s="44"/>
-      <c r="J46" s="45"/>
+      <c r="A46" s="30"/>
+      <c r="B46" s="34"/>
+      <c r="C46" s="34"/>
+      <c r="D46" s="34"/>
+      <c r="E46" s="34"/>
+      <c r="F46" s="34"/>
+      <c r="G46" s="34"/>
+      <c r="H46" s="34"/>
+      <c r="I46" s="34"/>
+      <c r="J46" s="35"/>
     </row>
     <row r="47" spans="1:10" ht="13.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A47" s="29"/>
-      <c r="B47" s="71"/>
-      <c r="C47" s="71"/>
-      <c r="D47" s="71"/>
-      <c r="E47" s="71"/>
-      <c r="F47" s="71"/>
-      <c r="G47" s="71"/>
-      <c r="H47" s="71"/>
-      <c r="I47" s="71"/>
-      <c r="J47" s="72"/>
+      <c r="A47" s="31"/>
+      <c r="B47" s="38"/>
+      <c r="C47" s="38"/>
+      <c r="D47" s="38"/>
+      <c r="E47" s="38"/>
+      <c r="F47" s="38"/>
+      <c r="G47" s="38"/>
+      <c r="H47" s="38"/>
+      <c r="I47" s="38"/>
+      <c r="J47" s="39"/>
     </row>
   </sheetData>
   <mergeCells count="21">
-    <mergeCell ref="B32:J47"/>
-    <mergeCell ref="A31:A47"/>
-    <mergeCell ref="B16:J21"/>
-    <mergeCell ref="A22:A30"/>
-    <mergeCell ref="B23:J30"/>
-    <mergeCell ref="B22:J22"/>
-    <mergeCell ref="B31:J31"/>
+    <mergeCell ref="B3:J3"/>
+    <mergeCell ref="B4:J4"/>
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="B1:D2"/>
+    <mergeCell ref="E1:J2"/>
+    <mergeCell ref="A3:A4"/>
     <mergeCell ref="B15:J15"/>
     <mergeCell ref="B8:J8"/>
     <mergeCell ref="A5:A6"/>
@@ -8393,12 +8407,13 @@
     <mergeCell ref="B7:J7"/>
     <mergeCell ref="B9:J14"/>
     <mergeCell ref="A7:A21"/>
-    <mergeCell ref="B3:J3"/>
-    <mergeCell ref="B4:J4"/>
-    <mergeCell ref="A1:A2"/>
-    <mergeCell ref="B1:D2"/>
-    <mergeCell ref="E1:J2"/>
-    <mergeCell ref="A3:A4"/>
+    <mergeCell ref="B32:J47"/>
+    <mergeCell ref="A31:A47"/>
+    <mergeCell ref="B16:J21"/>
+    <mergeCell ref="A22:A30"/>
+    <mergeCell ref="B23:J30"/>
+    <mergeCell ref="B22:J22"/>
+    <mergeCell ref="B31:J31"/>
   </mergeCells>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.51200000000000001" footer="0.51200000000000001"/>
@@ -8422,15 +8437,6 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="ドキュメント" ma:contentTypeID="0x01010058BEBA3CD4E69545839402B5D4E5400B" ma:contentTypeVersion="13" ma:contentTypeDescription="新しいドキュメントを作成します。" ma:contentTypeScope="" ma:versionID="85fadafb228503a8e253560e9cdffc69">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="88cc3c26-756f-41ab-80ed-43e7289fee5b" xmlns:ns3="55239288-d498-4dd6-9609-491b39ec8fae" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="9785dde68d2e35ac7b66dd15e8e44124" ns2:_="" ns3:_="">
     <xsd:import namespace="88cc3c26-756f-41ab-80ed-43e7289fee5b"/>
@@ -8637,6 +8643,15 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{82E555AC-3D9C-4ECE-9578-D2E452F320B7}">
   <ds:schemaRefs>
@@ -8657,14 +8672,6 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0843C284-C2B9-4564-B59A-F2FA129FE5C7}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{18D765C5-969E-4095-9A45-9E80C6C2EDED}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -8681,4 +8688,12 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0843C284-C2B9-4564-B59A-F2FA129FE5C7}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/11_プロジェクト計画書.xlsx
+++ b/11_プロジェクト計画書.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\k_tanoue\Documents\GitHub\tanouesoftware\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CCD04FFD-36B4-45F5-B17D-B55E9F471CA6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9711C1D7-0033-42E5-B830-3D30125165A1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="195" uniqueCount="107">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="199" uniqueCount="111">
   <si>
     <t>プロジェクト計画書</t>
     <rPh sb="6" eb="9">
@@ -1065,6 +1065,22 @@
     <rPh sb="356" eb="358">
       <t>カンケイ</t>
     </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Python, HTML, CSS, JavaScript</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>VisualStudioCode, Git/GitHub</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>AWS, Flask, Gemini API, LINE Login</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Amazon Linux 2023</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -2106,33 +2122,132 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="66" xfId="1" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="8" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
@@ -2151,27 +2266,9 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="2" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
@@ -2181,21 +2278,6 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
@@ -2205,71 +2287,17 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="50" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -2277,6 +2305,9 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="51" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2301,20 +2332,17 @@
     <xf numFmtId="0" fontId="10" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="50" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -2325,17 +2353,266 @@
     <xf numFmtId="0" fontId="8" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="32" xfId="1" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="40" xfId="1" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="34" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="35" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="25" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="16" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="46" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="34" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="35" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="25" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="16" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="46" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="34" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="35" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="25" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="16" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="46" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="7" fillId="0" borderId="54" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="7" fillId="0" borderId="55" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="7" fillId="0" borderId="54" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="7" fillId="0" borderId="55" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="7" fillId="0" borderId="54" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="7" fillId="0" borderId="55" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="36" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="26" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="7" fillId="0" borderId="58" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="7" fillId="0" borderId="59" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="7" fillId="0" borderId="58" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="7" fillId="0" borderId="59" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="7" fillId="0" borderId="58" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="7" fillId="0" borderId="59" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="37" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="38" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="21" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="22" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="7" fillId="0" borderId="48" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="7" fillId="0" borderId="49" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="21" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="44" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="50" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="45" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="25" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="46" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="47" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="16" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="31" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="33" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="21" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="22" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="7" fillId="0" borderId="49" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="7" fillId="0" borderId="48" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="7" fillId="0" borderId="49" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="7" fillId="0" borderId="48" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="7" fillId="0" borderId="62" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="7" fillId="0" borderId="63" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="23" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="61" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="41" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="42" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="56" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="33" xfId="1" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="7" fillId="0" borderId="52" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="7" fillId="0" borderId="53" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="24" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="43" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="7" fillId="0" borderId="62" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="7" fillId="0" borderId="63" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="60" xfId="1" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="57" xfId="1" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="23" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="61" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="7" fillId="0" borderId="62" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="7" fillId="0" borderId="63" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="7" fillId="0" borderId="52" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="7" fillId="0" borderId="53" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="23" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="61" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="41" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="42" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="56" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="7" fillId="0" borderId="52" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="7" fillId="0" borderId="53" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -2344,268 +2621,7 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="21" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="21" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="176" fontId="7" fillId="0" borderId="48" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="7" fillId="0" borderId="49" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="33" xfId="1" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="7" fillId="0" borderId="48" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="7" fillId="0" borderId="49" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="21" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="34" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="35" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="25" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="16" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="46" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="7" fillId="0" borderId="52" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="7" fillId="0" borderId="53" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="7" fillId="0" borderId="54" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="7" fillId="0" borderId="55" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="7" fillId="0" borderId="58" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="7" fillId="0" borderId="59" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="32" xfId="1" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="40" xfId="1" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="22" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="7" fillId="0" borderId="48" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="7" fillId="0" borderId="49" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="23" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="24" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="41" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="42" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="43" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="7" fillId="0" borderId="62" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="7" fillId="0" borderId="63" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="60" xfId="1" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="57" xfId="1" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="23" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="61" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="25" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="16" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="46" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="9" fontId="7" fillId="0" borderId="62" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="7" fillId="0" borderId="63" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="7" fillId="0" borderId="52" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="7" fillId="0" borderId="53" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="23" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="61" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="41" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="42" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="56" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="7" fillId="0" borderId="52" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="7" fillId="0" borderId="53" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="34" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="35" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="9" fontId="7" fillId="0" borderId="54" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="7" fillId="0" borderId="55" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="36" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="26" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="7" fillId="0" borderId="58" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="7" fillId="0" borderId="59" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="7" fillId="0" borderId="54" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="7" fillId="0" borderId="55" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="7" fillId="0" borderId="58" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="7" fillId="0" borderId="59" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="34" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="35" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="25" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="16" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="46" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="7" fillId="0" borderId="62" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="7" fillId="0" borderId="63" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="61" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="56" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="37" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="38" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="21" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="22" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="44" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="45" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="25" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="46" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="47" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="16" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="31" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="33" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
@@ -3431,1574 +3447,1591 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" s="2" customFormat="1" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="27" t="s">
+      <c r="A1" s="68" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="27"/>
-      <c r="C1" s="27"/>
-      <c r="D1" s="27"/>
-      <c r="E1" s="27"/>
-      <c r="F1" s="27"/>
-      <c r="G1" s="27"/>
-      <c r="H1" s="27"/>
-      <c r="I1" s="27"/>
-      <c r="J1" s="27"/>
+      <c r="B1" s="68"/>
+      <c r="C1" s="68"/>
+      <c r="D1" s="68"/>
+      <c r="E1" s="68"/>
+      <c r="F1" s="68"/>
+      <c r="G1" s="68"/>
+      <c r="H1" s="68"/>
+      <c r="I1" s="68"/>
+      <c r="J1" s="68"/>
     </row>
     <row r="2" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="28">
+      <c r="A2" s="27">
         <v>1</v>
       </c>
-      <c r="B2" s="32" t="s">
+      <c r="B2" s="34" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="32"/>
-      <c r="D2" s="32"/>
-      <c r="E2" s="78"/>
-      <c r="F2" s="78"/>
-      <c r="G2" s="78"/>
-      <c r="H2" s="78"/>
-      <c r="I2" s="78"/>
-      <c r="J2" s="79"/>
+      <c r="C2" s="34"/>
+      <c r="D2" s="34"/>
+      <c r="E2" s="36"/>
+      <c r="F2" s="36"/>
+      <c r="G2" s="36"/>
+      <c r="H2" s="36"/>
+      <c r="I2" s="36"/>
+      <c r="J2" s="37"/>
     </row>
     <row r="3" spans="1:10" ht="13.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="29"/>
-      <c r="B3" s="77"/>
-      <c r="C3" s="77"/>
-      <c r="D3" s="77"/>
-      <c r="E3" s="80"/>
-      <c r="F3" s="80"/>
-      <c r="G3" s="80"/>
-      <c r="H3" s="80"/>
-      <c r="I3" s="80"/>
-      <c r="J3" s="81"/>
+      <c r="A3" s="31"/>
+      <c r="B3" s="35"/>
+      <c r="C3" s="35"/>
+      <c r="D3" s="35"/>
+      <c r="E3" s="38"/>
+      <c r="F3" s="38"/>
+      <c r="G3" s="38"/>
+      <c r="H3" s="38"/>
+      <c r="I3" s="38"/>
+      <c r="J3" s="39"/>
     </row>
     <row r="4" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="28">
+      <c r="A4" s="27">
         <v>2</v>
       </c>
-      <c r="B4" s="42" t="s">
+      <c r="B4" s="32" t="s">
         <v>2</v>
       </c>
-      <c r="C4" s="42"/>
-      <c r="D4" s="42"/>
-      <c r="E4" s="42"/>
-      <c r="F4" s="42"/>
-      <c r="G4" s="42"/>
-      <c r="H4" s="42"/>
-      <c r="I4" s="42"/>
-      <c r="J4" s="43"/>
+      <c r="C4" s="32"/>
+      <c r="D4" s="32"/>
+      <c r="E4" s="32"/>
+      <c r="F4" s="32"/>
+      <c r="G4" s="32"/>
+      <c r="H4" s="32"/>
+      <c r="I4" s="32"/>
+      <c r="J4" s="33"/>
     </row>
     <row r="5" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="30"/>
-      <c r="B5" s="45" t="s">
+      <c r="A5" s="28"/>
+      <c r="B5" s="46" t="s">
         <v>3</v>
       </c>
-      <c r="C5" s="45"/>
-      <c r="D5" s="45"/>
-      <c r="E5" s="45"/>
-      <c r="F5" s="45"/>
-      <c r="G5" s="45"/>
-      <c r="H5" s="45"/>
-      <c r="I5" s="45"/>
-      <c r="J5" s="46"/>
+      <c r="C5" s="46"/>
+      <c r="D5" s="46"/>
+      <c r="E5" s="46"/>
+      <c r="F5" s="46"/>
+      <c r="G5" s="46"/>
+      <c r="H5" s="46"/>
+      <c r="I5" s="46"/>
+      <c r="J5" s="47"/>
     </row>
     <row r="6" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="30"/>
-      <c r="B6" s="45"/>
-      <c r="C6" s="45"/>
-      <c r="D6" s="45"/>
-      <c r="E6" s="45"/>
-      <c r="F6" s="45"/>
-      <c r="G6" s="45"/>
-      <c r="H6" s="45"/>
-      <c r="I6" s="45"/>
-      <c r="J6" s="46"/>
+      <c r="A6" s="28"/>
+      <c r="B6" s="46"/>
+      <c r="C6" s="46"/>
+      <c r="D6" s="46"/>
+      <c r="E6" s="46"/>
+      <c r="F6" s="46"/>
+      <c r="G6" s="46"/>
+      <c r="H6" s="46"/>
+      <c r="I6" s="46"/>
+      <c r="J6" s="47"/>
     </row>
     <row r="7" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="30"/>
-      <c r="B7" s="47"/>
-      <c r="C7" s="47"/>
-      <c r="D7" s="47"/>
-      <c r="E7" s="47"/>
-      <c r="F7" s="47"/>
-      <c r="G7" s="47"/>
-      <c r="H7" s="47"/>
-      <c r="I7" s="47"/>
-      <c r="J7" s="48"/>
+      <c r="A7" s="28"/>
+      <c r="B7" s="48"/>
+      <c r="C7" s="48"/>
+      <c r="D7" s="48"/>
+      <c r="E7" s="48"/>
+      <c r="F7" s="48"/>
+      <c r="G7" s="48"/>
+      <c r="H7" s="48"/>
+      <c r="I7" s="48"/>
+      <c r="J7" s="49"/>
     </row>
     <row r="8" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="30"/>
-      <c r="B8" s="76" t="s">
+      <c r="A8" s="28"/>
+      <c r="B8" s="61" t="s">
         <v>105</v>
       </c>
-      <c r="C8" s="52"/>
-      <c r="D8" s="52"/>
-      <c r="E8" s="52"/>
-      <c r="F8" s="52"/>
-      <c r="G8" s="52"/>
-      <c r="H8" s="52"/>
-      <c r="I8" s="52"/>
-      <c r="J8" s="53"/>
+      <c r="C8" s="62"/>
+      <c r="D8" s="62"/>
+      <c r="E8" s="62"/>
+      <c r="F8" s="62"/>
+      <c r="G8" s="62"/>
+      <c r="H8" s="62"/>
+      <c r="I8" s="62"/>
+      <c r="J8" s="63"/>
     </row>
     <row r="9" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="30"/>
-      <c r="B9" s="54"/>
-      <c r="C9" s="55"/>
-      <c r="D9" s="55"/>
-      <c r="E9" s="55"/>
-      <c r="F9" s="55"/>
-      <c r="G9" s="55"/>
-      <c r="H9" s="55"/>
-      <c r="I9" s="55"/>
-      <c r="J9" s="56"/>
+      <c r="A9" s="28"/>
+      <c r="B9" s="64"/>
+      <c r="C9" s="65"/>
+      <c r="D9" s="65"/>
+      <c r="E9" s="65"/>
+      <c r="F9" s="65"/>
+      <c r="G9" s="65"/>
+      <c r="H9" s="65"/>
+      <c r="I9" s="65"/>
+      <c r="J9" s="66"/>
     </row>
     <row r="10" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="30"/>
-      <c r="B10" s="54"/>
-      <c r="C10" s="55"/>
-      <c r="D10" s="55"/>
-      <c r="E10" s="55"/>
-      <c r="F10" s="55"/>
-      <c r="G10" s="55"/>
-      <c r="H10" s="55"/>
-      <c r="I10" s="55"/>
-      <c r="J10" s="56"/>
+      <c r="A10" s="28"/>
+      <c r="B10" s="64"/>
+      <c r="C10" s="65"/>
+      <c r="D10" s="65"/>
+      <c r="E10" s="65"/>
+      <c r="F10" s="65"/>
+      <c r="G10" s="65"/>
+      <c r="H10" s="65"/>
+      <c r="I10" s="65"/>
+      <c r="J10" s="66"/>
     </row>
     <row r="11" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="30"/>
-      <c r="B11" s="54"/>
-      <c r="C11" s="55"/>
-      <c r="D11" s="55"/>
-      <c r="E11" s="55"/>
-      <c r="F11" s="55"/>
-      <c r="G11" s="55"/>
-      <c r="H11" s="55"/>
-      <c r="I11" s="55"/>
-      <c r="J11" s="56"/>
+      <c r="A11" s="28"/>
+      <c r="B11" s="64"/>
+      <c r="C11" s="65"/>
+      <c r="D11" s="65"/>
+      <c r="E11" s="65"/>
+      <c r="F11" s="65"/>
+      <c r="G11" s="65"/>
+      <c r="H11" s="65"/>
+      <c r="I11" s="65"/>
+      <c r="J11" s="66"/>
     </row>
     <row r="12" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="30"/>
-      <c r="B12" s="54"/>
-      <c r="C12" s="55"/>
-      <c r="D12" s="55"/>
-      <c r="E12" s="55"/>
-      <c r="F12" s="55"/>
-      <c r="G12" s="55"/>
-      <c r="H12" s="55"/>
-      <c r="I12" s="55"/>
-      <c r="J12" s="56"/>
+      <c r="A12" s="28"/>
+      <c r="B12" s="64"/>
+      <c r="C12" s="65"/>
+      <c r="D12" s="65"/>
+      <c r="E12" s="65"/>
+      <c r="F12" s="65"/>
+      <c r="G12" s="65"/>
+      <c r="H12" s="65"/>
+      <c r="I12" s="65"/>
+      <c r="J12" s="66"/>
     </row>
     <row r="13" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="30"/>
-      <c r="B13" s="54"/>
-      <c r="C13" s="55"/>
-      <c r="D13" s="55"/>
-      <c r="E13" s="55"/>
-      <c r="F13" s="55"/>
-      <c r="G13" s="55"/>
-      <c r="H13" s="55"/>
-      <c r="I13" s="55"/>
-      <c r="J13" s="56"/>
+      <c r="A13" s="28"/>
+      <c r="B13" s="64"/>
+      <c r="C13" s="65"/>
+      <c r="D13" s="65"/>
+      <c r="E13" s="65"/>
+      <c r="F13" s="65"/>
+      <c r="G13" s="65"/>
+      <c r="H13" s="65"/>
+      <c r="I13" s="65"/>
+      <c r="J13" s="66"/>
     </row>
     <row r="14" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A14" s="30"/>
-      <c r="B14" s="54"/>
-      <c r="C14" s="55"/>
-      <c r="D14" s="55"/>
-      <c r="E14" s="55"/>
-      <c r="F14" s="55"/>
-      <c r="G14" s="55"/>
-      <c r="H14" s="55"/>
-      <c r="I14" s="55"/>
-      <c r="J14" s="56"/>
+      <c r="A14" s="28"/>
+      <c r="B14" s="64"/>
+      <c r="C14" s="65"/>
+      <c r="D14" s="65"/>
+      <c r="E14" s="65"/>
+      <c r="F14" s="65"/>
+      <c r="G14" s="65"/>
+      <c r="H14" s="65"/>
+      <c r="I14" s="65"/>
+      <c r="J14" s="66"/>
     </row>
     <row r="15" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A15" s="30"/>
-      <c r="B15" s="54"/>
-      <c r="C15" s="55"/>
-      <c r="D15" s="55"/>
-      <c r="E15" s="55"/>
-      <c r="F15" s="55"/>
-      <c r="G15" s="55"/>
-      <c r="H15" s="55"/>
-      <c r="I15" s="55"/>
-      <c r="J15" s="56"/>
+      <c r="A15" s="28"/>
+      <c r="B15" s="64"/>
+      <c r="C15" s="65"/>
+      <c r="D15" s="65"/>
+      <c r="E15" s="65"/>
+      <c r="F15" s="65"/>
+      <c r="G15" s="65"/>
+      <c r="H15" s="65"/>
+      <c r="I15" s="65"/>
+      <c r="J15" s="66"/>
     </row>
     <row r="16" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A16" s="30"/>
-      <c r="B16" s="54"/>
-      <c r="C16" s="55"/>
-      <c r="D16" s="55"/>
-      <c r="E16" s="55"/>
-      <c r="F16" s="55"/>
-      <c r="G16" s="55"/>
-      <c r="H16" s="55"/>
-      <c r="I16" s="55"/>
-      <c r="J16" s="56"/>
+      <c r="A16" s="28"/>
+      <c r="B16" s="64"/>
+      <c r="C16" s="65"/>
+      <c r="D16" s="65"/>
+      <c r="E16" s="65"/>
+      <c r="F16" s="65"/>
+      <c r="G16" s="65"/>
+      <c r="H16" s="65"/>
+      <c r="I16" s="65"/>
+      <c r="J16" s="66"/>
     </row>
     <row r="17" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A17" s="29"/>
-      <c r="B17" s="54"/>
-      <c r="C17" s="55"/>
-      <c r="D17" s="55"/>
-      <c r="E17" s="55"/>
-      <c r="F17" s="55"/>
-      <c r="G17" s="55"/>
-      <c r="H17" s="55"/>
-      <c r="I17" s="55"/>
-      <c r="J17" s="56"/>
+      <c r="A17" s="31"/>
+      <c r="B17" s="64"/>
+      <c r="C17" s="65"/>
+      <c r="D17" s="65"/>
+      <c r="E17" s="65"/>
+      <c r="F17" s="65"/>
+      <c r="G17" s="65"/>
+      <c r="H17" s="65"/>
+      <c r="I17" s="65"/>
+      <c r="J17" s="66"/>
     </row>
     <row r="18" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A18" s="29"/>
-      <c r="B18" s="54"/>
-      <c r="C18" s="55"/>
-      <c r="D18" s="55"/>
-      <c r="E18" s="55"/>
-      <c r="F18" s="55"/>
-      <c r="G18" s="55"/>
-      <c r="H18" s="55"/>
-      <c r="I18" s="55"/>
-      <c r="J18" s="56"/>
+      <c r="A18" s="31"/>
+      <c r="B18" s="64"/>
+      <c r="C18" s="65"/>
+      <c r="D18" s="65"/>
+      <c r="E18" s="65"/>
+      <c r="F18" s="65"/>
+      <c r="G18" s="65"/>
+      <c r="H18" s="65"/>
+      <c r="I18" s="65"/>
+      <c r="J18" s="66"/>
     </row>
     <row r="19" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A19" s="29"/>
-      <c r="B19" s="54"/>
-      <c r="C19" s="55"/>
-      <c r="D19" s="55"/>
-      <c r="E19" s="55"/>
-      <c r="F19" s="55"/>
-      <c r="G19" s="55"/>
-      <c r="H19" s="55"/>
-      <c r="I19" s="55"/>
-      <c r="J19" s="56"/>
+      <c r="A19" s="31"/>
+      <c r="B19" s="64"/>
+      <c r="C19" s="65"/>
+      <c r="D19" s="65"/>
+      <c r="E19" s="65"/>
+      <c r="F19" s="65"/>
+      <c r="G19" s="65"/>
+      <c r="H19" s="65"/>
+      <c r="I19" s="65"/>
+      <c r="J19" s="66"/>
     </row>
     <row r="20" spans="1:10" ht="13.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="29"/>
-      <c r="B20" s="54"/>
-      <c r="C20" s="55"/>
-      <c r="D20" s="55"/>
-      <c r="E20" s="55"/>
-      <c r="F20" s="55"/>
-      <c r="G20" s="55"/>
-      <c r="H20" s="55"/>
-      <c r="I20" s="55"/>
-      <c r="J20" s="56"/>
+      <c r="A20" s="31"/>
+      <c r="B20" s="64"/>
+      <c r="C20" s="65"/>
+      <c r="D20" s="65"/>
+      <c r="E20" s="65"/>
+      <c r="F20" s="65"/>
+      <c r="G20" s="65"/>
+      <c r="H20" s="65"/>
+      <c r="I20" s="65"/>
+      <c r="J20" s="66"/>
     </row>
     <row r="21" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A21" s="28">
+      <c r="A21" s="27">
         <v>3</v>
       </c>
-      <c r="B21" s="42" t="s">
+      <c r="B21" s="32" t="s">
         <v>4</v>
       </c>
-      <c r="C21" s="42"/>
-      <c r="D21" s="42"/>
-      <c r="E21" s="42"/>
-      <c r="F21" s="42"/>
-      <c r="G21" s="42"/>
-      <c r="H21" s="42"/>
-      <c r="I21" s="42"/>
-      <c r="J21" s="43"/>
+      <c r="C21" s="32"/>
+      <c r="D21" s="32"/>
+      <c r="E21" s="32"/>
+      <c r="F21" s="32"/>
+      <c r="G21" s="32"/>
+      <c r="H21" s="32"/>
+      <c r="I21" s="32"/>
+      <c r="J21" s="33"/>
     </row>
     <row r="22" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A22" s="30"/>
-      <c r="B22" s="64" t="s">
+      <c r="A22" s="28"/>
+      <c r="B22" s="50" t="s">
         <v>5</v>
       </c>
-      <c r="C22" s="65"/>
-      <c r="D22" s="65"/>
-      <c r="E22" s="65"/>
-      <c r="F22" s="65"/>
-      <c r="G22" s="65"/>
-      <c r="H22" s="65"/>
-      <c r="I22" s="65"/>
-      <c r="J22" s="66"/>
+      <c r="C22" s="51"/>
+      <c r="D22" s="51"/>
+      <c r="E22" s="51"/>
+      <c r="F22" s="51"/>
+      <c r="G22" s="51"/>
+      <c r="H22" s="51"/>
+      <c r="I22" s="51"/>
+      <c r="J22" s="52"/>
     </row>
     <row r="23" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A23" s="30"/>
-      <c r="B23" s="64"/>
-      <c r="C23" s="65"/>
-      <c r="D23" s="65"/>
-      <c r="E23" s="65"/>
-      <c r="F23" s="65"/>
-      <c r="G23" s="65"/>
-      <c r="H23" s="65"/>
-      <c r="I23" s="65"/>
-      <c r="J23" s="66"/>
+      <c r="A23" s="28"/>
+      <c r="B23" s="50"/>
+      <c r="C23" s="51"/>
+      <c r="D23" s="51"/>
+      <c r="E23" s="51"/>
+      <c r="F23" s="51"/>
+      <c r="G23" s="51"/>
+      <c r="H23" s="51"/>
+      <c r="I23" s="51"/>
+      <c r="J23" s="52"/>
     </row>
     <row r="24" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A24" s="30"/>
-      <c r="B24" s="64"/>
-      <c r="C24" s="65"/>
-      <c r="D24" s="65"/>
-      <c r="E24" s="65"/>
-      <c r="F24" s="65"/>
-      <c r="G24" s="65"/>
-      <c r="H24" s="65"/>
-      <c r="I24" s="65"/>
-      <c r="J24" s="66"/>
+      <c r="A24" s="28"/>
+      <c r="B24" s="50"/>
+      <c r="C24" s="51"/>
+      <c r="D24" s="51"/>
+      <c r="E24" s="51"/>
+      <c r="F24" s="51"/>
+      <c r="G24" s="51"/>
+      <c r="H24" s="51"/>
+      <c r="I24" s="51"/>
+      <c r="J24" s="52"/>
     </row>
     <row r="25" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A25" s="30"/>
-      <c r="B25" s="67"/>
-      <c r="C25" s="68"/>
-      <c r="D25" s="68"/>
-      <c r="E25" s="68"/>
-      <c r="F25" s="68"/>
-      <c r="G25" s="68"/>
-      <c r="H25" s="68"/>
-      <c r="I25" s="68"/>
-      <c r="J25" s="69"/>
+      <c r="A25" s="28"/>
+      <c r="B25" s="53"/>
+      <c r="C25" s="54"/>
+      <c r="D25" s="54"/>
+      <c r="E25" s="54"/>
+      <c r="F25" s="54"/>
+      <c r="G25" s="54"/>
+      <c r="H25" s="54"/>
+      <c r="I25" s="54"/>
+      <c r="J25" s="55"/>
     </row>
     <row r="26" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A26" s="30"/>
-      <c r="B26" s="70" t="s">
+      <c r="A26" s="28"/>
+      <c r="B26" s="56" t="s">
         <v>106</v>
       </c>
-      <c r="C26" s="70"/>
-      <c r="D26" s="70"/>
-      <c r="E26" s="70"/>
-      <c r="F26" s="70"/>
-      <c r="G26" s="70"/>
-      <c r="H26" s="70"/>
-      <c r="I26" s="70"/>
-      <c r="J26" s="71"/>
+      <c r="C26" s="56"/>
+      <c r="D26" s="56"/>
+      <c r="E26" s="56"/>
+      <c r="F26" s="56"/>
+      <c r="G26" s="56"/>
+      <c r="H26" s="56"/>
+      <c r="I26" s="56"/>
+      <c r="J26" s="57"/>
     </row>
     <row r="27" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A27" s="30"/>
-      <c r="B27" s="70"/>
-      <c r="C27" s="70"/>
-      <c r="D27" s="70"/>
-      <c r="E27" s="70"/>
-      <c r="F27" s="70"/>
-      <c r="G27" s="70"/>
-      <c r="H27" s="70"/>
-      <c r="I27" s="70"/>
-      <c r="J27" s="71"/>
+      <c r="A27" s="28"/>
+      <c r="B27" s="56"/>
+      <c r="C27" s="56"/>
+      <c r="D27" s="56"/>
+      <c r="E27" s="56"/>
+      <c r="F27" s="56"/>
+      <c r="G27" s="56"/>
+      <c r="H27" s="56"/>
+      <c r="I27" s="56"/>
+      <c r="J27" s="57"/>
     </row>
     <row r="28" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A28" s="30"/>
-      <c r="B28" s="70"/>
-      <c r="C28" s="70"/>
-      <c r="D28" s="70"/>
-      <c r="E28" s="70"/>
-      <c r="F28" s="70"/>
-      <c r="G28" s="70"/>
-      <c r="H28" s="70"/>
-      <c r="I28" s="70"/>
-      <c r="J28" s="71"/>
+      <c r="A28" s="28"/>
+      <c r="B28" s="56"/>
+      <c r="C28" s="56"/>
+      <c r="D28" s="56"/>
+      <c r="E28" s="56"/>
+      <c r="F28" s="56"/>
+      <c r="G28" s="56"/>
+      <c r="H28" s="56"/>
+      <c r="I28" s="56"/>
+      <c r="J28" s="57"/>
     </row>
     <row r="29" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A29" s="30"/>
-      <c r="B29" s="70"/>
-      <c r="C29" s="70"/>
-      <c r="D29" s="70"/>
-      <c r="E29" s="70"/>
-      <c r="F29" s="70"/>
-      <c r="G29" s="70"/>
-      <c r="H29" s="70"/>
-      <c r="I29" s="70"/>
-      <c r="J29" s="71"/>
+      <c r="A29" s="28"/>
+      <c r="B29" s="56"/>
+      <c r="C29" s="56"/>
+      <c r="D29" s="56"/>
+      <c r="E29" s="56"/>
+      <c r="F29" s="56"/>
+      <c r="G29" s="56"/>
+      <c r="H29" s="56"/>
+      <c r="I29" s="56"/>
+      <c r="J29" s="57"/>
     </row>
     <row r="30" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A30" s="30"/>
-      <c r="B30" s="70"/>
-      <c r="C30" s="70"/>
-      <c r="D30" s="70"/>
-      <c r="E30" s="70"/>
-      <c r="F30" s="70"/>
-      <c r="G30" s="70"/>
-      <c r="H30" s="70"/>
-      <c r="I30" s="70"/>
-      <c r="J30" s="71"/>
+      <c r="A30" s="28"/>
+      <c r="B30" s="56"/>
+      <c r="C30" s="56"/>
+      <c r="D30" s="56"/>
+      <c r="E30" s="56"/>
+      <c r="F30" s="56"/>
+      <c r="G30" s="56"/>
+      <c r="H30" s="56"/>
+      <c r="I30" s="56"/>
+      <c r="J30" s="57"/>
     </row>
     <row r="31" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A31" s="30"/>
-      <c r="B31" s="70"/>
-      <c r="C31" s="70"/>
-      <c r="D31" s="70"/>
-      <c r="E31" s="70"/>
-      <c r="F31" s="70"/>
-      <c r="G31" s="70"/>
-      <c r="H31" s="70"/>
-      <c r="I31" s="70"/>
-      <c r="J31" s="71"/>
+      <c r="A31" s="28"/>
+      <c r="B31" s="56"/>
+      <c r="C31" s="56"/>
+      <c r="D31" s="56"/>
+      <c r="E31" s="56"/>
+      <c r="F31" s="56"/>
+      <c r="G31" s="56"/>
+      <c r="H31" s="56"/>
+      <c r="I31" s="56"/>
+      <c r="J31" s="57"/>
     </row>
     <row r="32" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A32" s="30"/>
-      <c r="B32" s="70"/>
-      <c r="C32" s="70"/>
-      <c r="D32" s="70"/>
-      <c r="E32" s="70"/>
-      <c r="F32" s="70"/>
-      <c r="G32" s="70"/>
-      <c r="H32" s="70"/>
-      <c r="I32" s="70"/>
-      <c r="J32" s="71"/>
+      <c r="A32" s="28"/>
+      <c r="B32" s="56"/>
+      <c r="C32" s="56"/>
+      <c r="D32" s="56"/>
+      <c r="E32" s="56"/>
+      <c r="F32" s="56"/>
+      <c r="G32" s="56"/>
+      <c r="H32" s="56"/>
+      <c r="I32" s="56"/>
+      <c r="J32" s="57"/>
     </row>
     <row r="33" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A33" s="30"/>
-      <c r="B33" s="70"/>
-      <c r="C33" s="70"/>
-      <c r="D33" s="70"/>
-      <c r="E33" s="70"/>
-      <c r="F33" s="70"/>
-      <c r="G33" s="70"/>
-      <c r="H33" s="70"/>
-      <c r="I33" s="70"/>
-      <c r="J33" s="71"/>
+      <c r="A33" s="28"/>
+      <c r="B33" s="56"/>
+      <c r="C33" s="56"/>
+      <c r="D33" s="56"/>
+      <c r="E33" s="56"/>
+      <c r="F33" s="56"/>
+      <c r="G33" s="56"/>
+      <c r="H33" s="56"/>
+      <c r="I33" s="56"/>
+      <c r="J33" s="57"/>
     </row>
     <row r="34" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A34" s="30"/>
-      <c r="B34" s="70"/>
-      <c r="C34" s="70"/>
-      <c r="D34" s="70"/>
-      <c r="E34" s="70"/>
-      <c r="F34" s="70"/>
-      <c r="G34" s="70"/>
-      <c r="H34" s="70"/>
-      <c r="I34" s="70"/>
-      <c r="J34" s="71"/>
+      <c r="A34" s="28"/>
+      <c r="B34" s="56"/>
+      <c r="C34" s="56"/>
+      <c r="D34" s="56"/>
+      <c r="E34" s="56"/>
+      <c r="F34" s="56"/>
+      <c r="G34" s="56"/>
+      <c r="H34" s="56"/>
+      <c r="I34" s="56"/>
+      <c r="J34" s="57"/>
     </row>
     <row r="35" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A35" s="30"/>
-      <c r="B35" s="70"/>
-      <c r="C35" s="70"/>
-      <c r="D35" s="70"/>
-      <c r="E35" s="70"/>
-      <c r="F35" s="70"/>
-      <c r="G35" s="70"/>
-      <c r="H35" s="70"/>
-      <c r="I35" s="70"/>
-      <c r="J35" s="71"/>
+      <c r="A35" s="28"/>
+      <c r="B35" s="56"/>
+      <c r="C35" s="56"/>
+      <c r="D35" s="56"/>
+      <c r="E35" s="56"/>
+      <c r="F35" s="56"/>
+      <c r="G35" s="56"/>
+      <c r="H35" s="56"/>
+      <c r="I35" s="56"/>
+      <c r="J35" s="57"/>
     </row>
     <row r="36" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A36" s="30"/>
-      <c r="B36" s="70"/>
-      <c r="C36" s="70"/>
-      <c r="D36" s="70"/>
-      <c r="E36" s="70"/>
-      <c r="F36" s="70"/>
-      <c r="G36" s="70"/>
-      <c r="H36" s="70"/>
-      <c r="I36" s="70"/>
-      <c r="J36" s="71"/>
+      <c r="A36" s="28"/>
+      <c r="B36" s="56"/>
+      <c r="C36" s="56"/>
+      <c r="D36" s="56"/>
+      <c r="E36" s="56"/>
+      <c r="F36" s="56"/>
+      <c r="G36" s="56"/>
+      <c r="H36" s="56"/>
+      <c r="I36" s="56"/>
+      <c r="J36" s="57"/>
     </row>
     <row r="37" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A37" s="30"/>
-      <c r="B37" s="70"/>
-      <c r="C37" s="70"/>
-      <c r="D37" s="70"/>
-      <c r="E37" s="70"/>
-      <c r="F37" s="70"/>
-      <c r="G37" s="70"/>
-      <c r="H37" s="70"/>
-      <c r="I37" s="70"/>
-      <c r="J37" s="71"/>
+      <c r="A37" s="28"/>
+      <c r="B37" s="56"/>
+      <c r="C37" s="56"/>
+      <c r="D37" s="56"/>
+      <c r="E37" s="56"/>
+      <c r="F37" s="56"/>
+      <c r="G37" s="56"/>
+      <c r="H37" s="56"/>
+      <c r="I37" s="56"/>
+      <c r="J37" s="57"/>
     </row>
     <row r="38" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A38" s="30"/>
-      <c r="B38" s="70"/>
-      <c r="C38" s="70"/>
-      <c r="D38" s="70"/>
-      <c r="E38" s="70"/>
-      <c r="F38" s="70"/>
-      <c r="G38" s="70"/>
-      <c r="H38" s="70"/>
-      <c r="I38" s="70"/>
-      <c r="J38" s="71"/>
+      <c r="A38" s="28"/>
+      <c r="B38" s="56"/>
+      <c r="C38" s="56"/>
+      <c r="D38" s="56"/>
+      <c r="E38" s="56"/>
+      <c r="F38" s="56"/>
+      <c r="G38" s="56"/>
+      <c r="H38" s="56"/>
+      <c r="I38" s="56"/>
+      <c r="J38" s="57"/>
     </row>
     <row r="39" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A39" s="30"/>
-      <c r="B39" s="70"/>
-      <c r="C39" s="70"/>
-      <c r="D39" s="70"/>
-      <c r="E39" s="70"/>
-      <c r="F39" s="70"/>
-      <c r="G39" s="70"/>
-      <c r="H39" s="70"/>
-      <c r="I39" s="70"/>
-      <c r="J39" s="71"/>
+      <c r="A39" s="28"/>
+      <c r="B39" s="56"/>
+      <c r="C39" s="56"/>
+      <c r="D39" s="56"/>
+      <c r="E39" s="56"/>
+      <c r="F39" s="56"/>
+      <c r="G39" s="56"/>
+      <c r="H39" s="56"/>
+      <c r="I39" s="56"/>
+      <c r="J39" s="57"/>
     </row>
     <row r="40" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A40" s="30"/>
-      <c r="B40" s="70"/>
-      <c r="C40" s="70"/>
-      <c r="D40" s="70"/>
-      <c r="E40" s="70"/>
-      <c r="F40" s="70"/>
-      <c r="G40" s="70"/>
-      <c r="H40" s="70"/>
-      <c r="I40" s="70"/>
-      <c r="J40" s="71"/>
+      <c r="A40" s="28"/>
+      <c r="B40" s="56"/>
+      <c r="C40" s="56"/>
+      <c r="D40" s="56"/>
+      <c r="E40" s="56"/>
+      <c r="F40" s="56"/>
+      <c r="G40" s="56"/>
+      <c r="H40" s="56"/>
+      <c r="I40" s="56"/>
+      <c r="J40" s="57"/>
     </row>
     <row r="41" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A41" s="30"/>
-      <c r="B41" s="70"/>
-      <c r="C41" s="70"/>
-      <c r="D41" s="70"/>
-      <c r="E41" s="70"/>
-      <c r="F41" s="70"/>
-      <c r="G41" s="70"/>
-      <c r="H41" s="70"/>
-      <c r="I41" s="70"/>
-      <c r="J41" s="71"/>
+      <c r="A41" s="28"/>
+      <c r="B41" s="56"/>
+      <c r="C41" s="56"/>
+      <c r="D41" s="56"/>
+      <c r="E41" s="56"/>
+      <c r="F41" s="56"/>
+      <c r="G41" s="56"/>
+      <c r="H41" s="56"/>
+      <c r="I41" s="56"/>
+      <c r="J41" s="57"/>
     </row>
     <row r="42" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A42" s="30"/>
-      <c r="B42" s="70"/>
-      <c r="C42" s="70"/>
-      <c r="D42" s="70"/>
-      <c r="E42" s="70"/>
-      <c r="F42" s="70"/>
-      <c r="G42" s="70"/>
-      <c r="H42" s="70"/>
-      <c r="I42" s="70"/>
-      <c r="J42" s="71"/>
+      <c r="A42" s="28"/>
+      <c r="B42" s="56"/>
+      <c r="C42" s="56"/>
+      <c r="D42" s="56"/>
+      <c r="E42" s="56"/>
+      <c r="F42" s="56"/>
+      <c r="G42" s="56"/>
+      <c r="H42" s="56"/>
+      <c r="I42" s="56"/>
+      <c r="J42" s="57"/>
     </row>
     <row r="43" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A43" s="30"/>
-      <c r="B43" s="70"/>
-      <c r="C43" s="70"/>
-      <c r="D43" s="70"/>
-      <c r="E43" s="70"/>
-      <c r="F43" s="70"/>
-      <c r="G43" s="70"/>
-      <c r="H43" s="70"/>
-      <c r="I43" s="70"/>
-      <c r="J43" s="71"/>
+      <c r="A43" s="28"/>
+      <c r="B43" s="56"/>
+      <c r="C43" s="56"/>
+      <c r="D43" s="56"/>
+      <c r="E43" s="56"/>
+      <c r="F43" s="56"/>
+      <c r="G43" s="56"/>
+      <c r="H43" s="56"/>
+      <c r="I43" s="56"/>
+      <c r="J43" s="57"/>
     </row>
     <row r="44" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A44" s="30"/>
-      <c r="B44" s="70"/>
-      <c r="C44" s="70"/>
-      <c r="D44" s="70"/>
-      <c r="E44" s="70"/>
-      <c r="F44" s="70"/>
-      <c r="G44" s="70"/>
-      <c r="H44" s="70"/>
-      <c r="I44" s="70"/>
-      <c r="J44" s="71"/>
+      <c r="A44" s="28"/>
+      <c r="B44" s="56"/>
+      <c r="C44" s="56"/>
+      <c r="D44" s="56"/>
+      <c r="E44" s="56"/>
+      <c r="F44" s="56"/>
+      <c r="G44" s="56"/>
+      <c r="H44" s="56"/>
+      <c r="I44" s="56"/>
+      <c r="J44" s="57"/>
     </row>
     <row r="45" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A45" s="30"/>
-      <c r="B45" s="70"/>
-      <c r="C45" s="70"/>
-      <c r="D45" s="70"/>
-      <c r="E45" s="70"/>
-      <c r="F45" s="70"/>
-      <c r="G45" s="70"/>
-      <c r="H45" s="70"/>
-      <c r="I45" s="70"/>
-      <c r="J45" s="71"/>
+      <c r="A45" s="28"/>
+      <c r="B45" s="56"/>
+      <c r="C45" s="56"/>
+      <c r="D45" s="56"/>
+      <c r="E45" s="56"/>
+      <c r="F45" s="56"/>
+      <c r="G45" s="56"/>
+      <c r="H45" s="56"/>
+      <c r="I45" s="56"/>
+      <c r="J45" s="57"/>
     </row>
     <row r="46" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A46" s="30"/>
-      <c r="B46" s="70"/>
-      <c r="C46" s="70"/>
-      <c r="D46" s="70"/>
-      <c r="E46" s="70"/>
-      <c r="F46" s="70"/>
-      <c r="G46" s="70"/>
-      <c r="H46" s="70"/>
-      <c r="I46" s="70"/>
-      <c r="J46" s="71"/>
+      <c r="A46" s="28"/>
+      <c r="B46" s="56"/>
+      <c r="C46" s="56"/>
+      <c r="D46" s="56"/>
+      <c r="E46" s="56"/>
+      <c r="F46" s="56"/>
+      <c r="G46" s="56"/>
+      <c r="H46" s="56"/>
+      <c r="I46" s="56"/>
+      <c r="J46" s="57"/>
     </row>
     <row r="47" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A47" s="30"/>
-      <c r="B47" s="70"/>
-      <c r="C47" s="70"/>
-      <c r="D47" s="70"/>
-      <c r="E47" s="70"/>
-      <c r="F47" s="70"/>
-      <c r="G47" s="70"/>
-      <c r="H47" s="70"/>
-      <c r="I47" s="70"/>
-      <c r="J47" s="71"/>
+      <c r="A47" s="28"/>
+      <c r="B47" s="56"/>
+      <c r="C47" s="56"/>
+      <c r="D47" s="56"/>
+      <c r="E47" s="56"/>
+      <c r="F47" s="56"/>
+      <c r="G47" s="56"/>
+      <c r="H47" s="56"/>
+      <c r="I47" s="56"/>
+      <c r="J47" s="57"/>
     </row>
     <row r="48" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A48" s="30"/>
-      <c r="B48" s="70"/>
-      <c r="C48" s="70"/>
-      <c r="D48" s="70"/>
-      <c r="E48" s="70"/>
-      <c r="F48" s="70"/>
-      <c r="G48" s="70"/>
-      <c r="H48" s="70"/>
-      <c r="I48" s="70"/>
-      <c r="J48" s="71"/>
+      <c r="A48" s="28"/>
+      <c r="B48" s="56"/>
+      <c r="C48" s="56"/>
+      <c r="D48" s="56"/>
+      <c r="E48" s="56"/>
+      <c r="F48" s="56"/>
+      <c r="G48" s="56"/>
+      <c r="H48" s="56"/>
+      <c r="I48" s="56"/>
+      <c r="J48" s="57"/>
     </row>
     <row r="49" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A49" s="30"/>
-      <c r="B49" s="70"/>
-      <c r="C49" s="70"/>
-      <c r="D49" s="70"/>
-      <c r="E49" s="70"/>
-      <c r="F49" s="70"/>
-      <c r="G49" s="70"/>
-      <c r="H49" s="70"/>
-      <c r="I49" s="70"/>
-      <c r="J49" s="71"/>
+      <c r="A49" s="28"/>
+      <c r="B49" s="56"/>
+      <c r="C49" s="56"/>
+      <c r="D49" s="56"/>
+      <c r="E49" s="56"/>
+      <c r="F49" s="56"/>
+      <c r="G49" s="56"/>
+      <c r="H49" s="56"/>
+      <c r="I49" s="56"/>
+      <c r="J49" s="57"/>
     </row>
     <row r="50" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A50" s="30"/>
-      <c r="B50" s="70"/>
-      <c r="C50" s="70"/>
-      <c r="D50" s="70"/>
-      <c r="E50" s="70"/>
-      <c r="F50" s="70"/>
-      <c r="G50" s="70"/>
-      <c r="H50" s="70"/>
-      <c r="I50" s="70"/>
-      <c r="J50" s="71"/>
+      <c r="A50" s="28"/>
+      <c r="B50" s="56"/>
+      <c r="C50" s="56"/>
+      <c r="D50" s="56"/>
+      <c r="E50" s="56"/>
+      <c r="F50" s="56"/>
+      <c r="G50" s="56"/>
+      <c r="H50" s="56"/>
+      <c r="I50" s="56"/>
+      <c r="J50" s="57"/>
     </row>
     <row r="51" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A51" s="30"/>
-      <c r="B51" s="70"/>
-      <c r="C51" s="70"/>
-      <c r="D51" s="70"/>
-      <c r="E51" s="70"/>
-      <c r="F51" s="70"/>
-      <c r="G51" s="70"/>
-      <c r="H51" s="70"/>
-      <c r="I51" s="70"/>
-      <c r="J51" s="71"/>
+      <c r="A51" s="28"/>
+      <c r="B51" s="56"/>
+      <c r="C51" s="56"/>
+      <c r="D51" s="56"/>
+      <c r="E51" s="56"/>
+      <c r="F51" s="56"/>
+      <c r="G51" s="56"/>
+      <c r="H51" s="56"/>
+      <c r="I51" s="56"/>
+      <c r="J51" s="57"/>
     </row>
     <row r="52" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A52" s="30"/>
-      <c r="B52" s="70"/>
-      <c r="C52" s="70"/>
-      <c r="D52" s="70"/>
-      <c r="E52" s="70"/>
-      <c r="F52" s="70"/>
-      <c r="G52" s="70"/>
-      <c r="H52" s="70"/>
-      <c r="I52" s="70"/>
-      <c r="J52" s="71"/>
+      <c r="A52" s="28"/>
+      <c r="B52" s="56"/>
+      <c r="C52" s="56"/>
+      <c r="D52" s="56"/>
+      <c r="E52" s="56"/>
+      <c r="F52" s="56"/>
+      <c r="G52" s="56"/>
+      <c r="H52" s="56"/>
+      <c r="I52" s="56"/>
+      <c r="J52" s="57"/>
     </row>
     <row r="53" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A53" s="30"/>
-      <c r="B53" s="70"/>
-      <c r="C53" s="70"/>
-      <c r="D53" s="70"/>
-      <c r="E53" s="70"/>
-      <c r="F53" s="70"/>
-      <c r="G53" s="70"/>
-      <c r="H53" s="70"/>
-      <c r="I53" s="70"/>
-      <c r="J53" s="71"/>
+      <c r="A53" s="28"/>
+      <c r="B53" s="56"/>
+      <c r="C53" s="56"/>
+      <c r="D53" s="56"/>
+      <c r="E53" s="56"/>
+      <c r="F53" s="56"/>
+      <c r="G53" s="56"/>
+      <c r="H53" s="56"/>
+      <c r="I53" s="56"/>
+      <c r="J53" s="57"/>
     </row>
     <row r="54" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A54" s="30"/>
-      <c r="B54" s="70"/>
-      <c r="C54" s="70"/>
-      <c r="D54" s="70"/>
-      <c r="E54" s="70"/>
-      <c r="F54" s="70"/>
-      <c r="G54" s="70"/>
-      <c r="H54" s="70"/>
-      <c r="I54" s="70"/>
-      <c r="J54" s="71"/>
+      <c r="A54" s="28"/>
+      <c r="B54" s="56"/>
+      <c r="C54" s="56"/>
+      <c r="D54" s="56"/>
+      <c r="E54" s="56"/>
+      <c r="F54" s="56"/>
+      <c r="G54" s="56"/>
+      <c r="H54" s="56"/>
+      <c r="I54" s="56"/>
+      <c r="J54" s="57"/>
     </row>
     <row r="55" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A55" s="30"/>
-      <c r="B55" s="70"/>
-      <c r="C55" s="70"/>
-      <c r="D55" s="70"/>
-      <c r="E55" s="70"/>
-      <c r="F55" s="70"/>
-      <c r="G55" s="70"/>
-      <c r="H55" s="70"/>
-      <c r="I55" s="70"/>
-      <c r="J55" s="71"/>
+      <c r="A55" s="28"/>
+      <c r="B55" s="56"/>
+      <c r="C55" s="56"/>
+      <c r="D55" s="56"/>
+      <c r="E55" s="56"/>
+      <c r="F55" s="56"/>
+      <c r="G55" s="56"/>
+      <c r="H55" s="56"/>
+      <c r="I55" s="56"/>
+      <c r="J55" s="57"/>
     </row>
     <row r="56" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A56" s="30"/>
-      <c r="B56" s="70"/>
-      <c r="C56" s="70"/>
-      <c r="D56" s="70"/>
-      <c r="E56" s="70"/>
-      <c r="F56" s="70"/>
-      <c r="G56" s="70"/>
-      <c r="H56" s="70"/>
-      <c r="I56" s="70"/>
-      <c r="J56" s="71"/>
+      <c r="A56" s="28"/>
+      <c r="B56" s="56"/>
+      <c r="C56" s="56"/>
+      <c r="D56" s="56"/>
+      <c r="E56" s="56"/>
+      <c r="F56" s="56"/>
+      <c r="G56" s="56"/>
+      <c r="H56" s="56"/>
+      <c r="I56" s="56"/>
+      <c r="J56" s="57"/>
     </row>
     <row r="57" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A57" s="30"/>
-      <c r="B57" s="70"/>
-      <c r="C57" s="70"/>
-      <c r="D57" s="70"/>
-      <c r="E57" s="70"/>
-      <c r="F57" s="70"/>
-      <c r="G57" s="70"/>
-      <c r="H57" s="70"/>
-      <c r="I57" s="70"/>
-      <c r="J57" s="71"/>
+      <c r="A57" s="28"/>
+      <c r="B57" s="56"/>
+      <c r="C57" s="56"/>
+      <c r="D57" s="56"/>
+      <c r="E57" s="56"/>
+      <c r="F57" s="56"/>
+      <c r="G57" s="56"/>
+      <c r="H57" s="56"/>
+      <c r="I57" s="56"/>
+      <c r="J57" s="57"/>
     </row>
     <row r="58" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A58" s="30"/>
-      <c r="B58" s="70"/>
-      <c r="C58" s="70"/>
-      <c r="D58" s="70"/>
-      <c r="E58" s="70"/>
-      <c r="F58" s="70"/>
-      <c r="G58" s="70"/>
-      <c r="H58" s="70"/>
-      <c r="I58" s="70"/>
-      <c r="J58" s="71"/>
+      <c r="A58" s="28"/>
+      <c r="B58" s="56"/>
+      <c r="C58" s="56"/>
+      <c r="D58" s="56"/>
+      <c r="E58" s="56"/>
+      <c r="F58" s="56"/>
+      <c r="G58" s="56"/>
+      <c r="H58" s="56"/>
+      <c r="I58" s="56"/>
+      <c r="J58" s="57"/>
     </row>
     <row r="59" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A59" s="30"/>
-      <c r="B59" s="70"/>
-      <c r="C59" s="70"/>
-      <c r="D59" s="70"/>
-      <c r="E59" s="70"/>
-      <c r="F59" s="70"/>
-      <c r="G59" s="70"/>
-      <c r="H59" s="70"/>
-      <c r="I59" s="70"/>
-      <c r="J59" s="71"/>
+      <c r="A59" s="28"/>
+      <c r="B59" s="56"/>
+      <c r="C59" s="56"/>
+      <c r="D59" s="56"/>
+      <c r="E59" s="56"/>
+      <c r="F59" s="56"/>
+      <c r="G59" s="56"/>
+      <c r="H59" s="56"/>
+      <c r="I59" s="56"/>
+      <c r="J59" s="57"/>
     </row>
     <row r="60" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A60" s="30"/>
-      <c r="B60" s="70"/>
-      <c r="C60" s="70"/>
-      <c r="D60" s="70"/>
-      <c r="E60" s="70"/>
-      <c r="F60" s="70"/>
-      <c r="G60" s="70"/>
-      <c r="H60" s="70"/>
-      <c r="I60" s="70"/>
-      <c r="J60" s="71"/>
+      <c r="A60" s="28"/>
+      <c r="B60" s="56"/>
+      <c r="C60" s="56"/>
+      <c r="D60" s="56"/>
+      <c r="E60" s="56"/>
+      <c r="F60" s="56"/>
+      <c r="G60" s="56"/>
+      <c r="H60" s="56"/>
+      <c r="I60" s="56"/>
+      <c r="J60" s="57"/>
     </row>
     <row r="61" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A61" s="30"/>
-      <c r="B61" s="70"/>
-      <c r="C61" s="70"/>
-      <c r="D61" s="70"/>
-      <c r="E61" s="70"/>
-      <c r="F61" s="70"/>
-      <c r="G61" s="70"/>
-      <c r="H61" s="70"/>
-      <c r="I61" s="70"/>
-      <c r="J61" s="71"/>
+      <c r="A61" s="28"/>
+      <c r="B61" s="56"/>
+      <c r="C61" s="56"/>
+      <c r="D61" s="56"/>
+      <c r="E61" s="56"/>
+      <c r="F61" s="56"/>
+      <c r="G61" s="56"/>
+      <c r="H61" s="56"/>
+      <c r="I61" s="56"/>
+      <c r="J61" s="57"/>
     </row>
     <row r="62" spans="1:10" ht="13.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A62" s="31"/>
-      <c r="B62" s="72"/>
-      <c r="C62" s="72"/>
-      <c r="D62" s="72"/>
-      <c r="E62" s="72"/>
-      <c r="F62" s="72"/>
-      <c r="G62" s="72"/>
-      <c r="H62" s="72"/>
-      <c r="I62" s="72"/>
-      <c r="J62" s="73"/>
+      <c r="A62" s="29"/>
+      <c r="B62" s="58"/>
+      <c r="C62" s="58"/>
+      <c r="D62" s="58"/>
+      <c r="E62" s="58"/>
+      <c r="F62" s="58"/>
+      <c r="G62" s="58"/>
+      <c r="H62" s="58"/>
+      <c r="I62" s="58"/>
+      <c r="J62" s="59"/>
     </row>
     <row r="63" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A63" s="28">
+      <c r="A63" s="27">
         <v>4</v>
       </c>
-      <c r="B63" s="32" t="s">
+      <c r="B63" s="34" t="s">
         <v>6</v>
       </c>
-      <c r="C63" s="32"/>
-      <c r="D63" s="32"/>
-      <c r="E63" s="32"/>
-      <c r="F63" s="32"/>
-      <c r="G63" s="32"/>
-      <c r="H63" s="32"/>
-      <c r="I63" s="32"/>
-      <c r="J63" s="33"/>
+      <c r="C63" s="34"/>
+      <c r="D63" s="34"/>
+      <c r="E63" s="34"/>
+      <c r="F63" s="34"/>
+      <c r="G63" s="34"/>
+      <c r="H63" s="34"/>
+      <c r="I63" s="34"/>
+      <c r="J63" s="67"/>
     </row>
     <row r="64" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A64" s="30"/>
-      <c r="B64" s="74" t="s">
+      <c r="A64" s="28"/>
+      <c r="B64" s="30" t="s">
         <v>7</v>
       </c>
-      <c r="C64" s="74"/>
-      <c r="D64" s="34"/>
-      <c r="E64" s="34"/>
-      <c r="F64" s="34"/>
-      <c r="G64" s="34"/>
-      <c r="H64" s="34"/>
-      <c r="I64" s="34"/>
-      <c r="J64" s="35"/>
+      <c r="C64" s="30"/>
+      <c r="D64" s="44" t="s">
+        <v>110</v>
+      </c>
+      <c r="E64" s="44"/>
+      <c r="F64" s="44"/>
+      <c r="G64" s="44"/>
+      <c r="H64" s="44"/>
+      <c r="I64" s="44"/>
+      <c r="J64" s="45"/>
     </row>
     <row r="65" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A65" s="30"/>
-      <c r="B65" s="74" t="s">
+      <c r="A65" s="28"/>
+      <c r="B65" s="30" t="s">
         <v>8</v>
       </c>
-      <c r="C65" s="74"/>
-      <c r="D65" s="34"/>
-      <c r="E65" s="34"/>
-      <c r="F65" s="34"/>
-      <c r="G65" s="34"/>
-      <c r="H65" s="34"/>
-      <c r="I65" s="34"/>
-      <c r="J65" s="35"/>
+      <c r="C65" s="30"/>
+      <c r="D65" s="44" t="s">
+        <v>108</v>
+      </c>
+      <c r="E65" s="44"/>
+      <c r="F65" s="44"/>
+      <c r="G65" s="44"/>
+      <c r="H65" s="44"/>
+      <c r="I65" s="44"/>
+      <c r="J65" s="45"/>
     </row>
     <row r="66" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A66" s="30"/>
-      <c r="B66" s="74" t="s">
+      <c r="A66" s="28"/>
+      <c r="B66" s="30" t="s">
         <v>9</v>
       </c>
-      <c r="C66" s="74"/>
-      <c r="D66" s="34"/>
-      <c r="E66" s="34"/>
-      <c r="F66" s="34"/>
-      <c r="G66" s="34"/>
-      <c r="H66" s="34"/>
-      <c r="I66" s="34"/>
-      <c r="J66" s="35"/>
+      <c r="C66" s="30"/>
+      <c r="D66" s="44" t="s">
+        <v>107</v>
+      </c>
+      <c r="E66" s="44"/>
+      <c r="F66" s="44"/>
+      <c r="G66" s="44"/>
+      <c r="H66" s="44"/>
+      <c r="I66" s="44"/>
+      <c r="J66" s="45"/>
     </row>
     <row r="67" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A67" s="30"/>
-      <c r="B67" s="74" t="s">
+      <c r="A67" s="28"/>
+      <c r="B67" s="30" t="s">
         <v>104</v>
       </c>
-      <c r="C67" s="74"/>
-      <c r="D67" s="34"/>
-      <c r="E67" s="34"/>
-      <c r="F67" s="34"/>
-      <c r="G67" s="34"/>
-      <c r="H67" s="34"/>
-      <c r="I67" s="34"/>
-      <c r="J67" s="35"/>
+      <c r="C67" s="30"/>
+      <c r="D67" s="44" t="s">
+        <v>109</v>
+      </c>
+      <c r="E67" s="44"/>
+      <c r="F67" s="44"/>
+      <c r="G67" s="44"/>
+      <c r="H67" s="44"/>
+      <c r="I67" s="44"/>
+      <c r="J67" s="45"/>
     </row>
     <row r="68" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A68" s="30"/>
-      <c r="B68" s="74" t="s">
+      <c r="A68" s="28"/>
+      <c r="B68" s="30" t="s">
         <v>10</v>
       </c>
-      <c r="C68" s="74"/>
-      <c r="D68" s="74"/>
-      <c r="E68" s="74"/>
-      <c r="F68" s="74"/>
-      <c r="G68" s="74"/>
-      <c r="H68" s="74"/>
-      <c r="I68" s="74"/>
-      <c r="J68" s="75"/>
+      <c r="C68" s="30"/>
+      <c r="D68" s="30"/>
+      <c r="E68" s="30"/>
+      <c r="F68" s="30"/>
+      <c r="G68" s="30"/>
+      <c r="H68" s="30"/>
+      <c r="I68" s="30"/>
+      <c r="J68" s="60"/>
     </row>
     <row r="69" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A69" s="30"/>
-      <c r="B69" s="60"/>
-      <c r="C69" s="60"/>
-      <c r="D69" s="60"/>
-      <c r="E69" s="60"/>
-      <c r="F69" s="60"/>
-      <c r="G69" s="60"/>
-      <c r="H69" s="60"/>
-      <c r="I69" s="60"/>
-      <c r="J69" s="61"/>
+      <c r="A69" s="28"/>
+      <c r="B69" s="40"/>
+      <c r="C69" s="40"/>
+      <c r="D69" s="40"/>
+      <c r="E69" s="40"/>
+      <c r="F69" s="40"/>
+      <c r="G69" s="40"/>
+      <c r="H69" s="40"/>
+      <c r="I69" s="40"/>
+      <c r="J69" s="41"/>
     </row>
     <row r="70" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A70" s="30"/>
-      <c r="B70" s="60"/>
-      <c r="C70" s="60"/>
-      <c r="D70" s="60"/>
-      <c r="E70" s="60"/>
-      <c r="F70" s="60"/>
-      <c r="G70" s="60"/>
-      <c r="H70" s="60"/>
-      <c r="I70" s="60"/>
-      <c r="J70" s="61"/>
+      <c r="A70" s="28"/>
+      <c r="B70" s="40"/>
+      <c r="C70" s="40"/>
+      <c r="D70" s="40"/>
+      <c r="E70" s="40"/>
+      <c r="F70" s="40"/>
+      <c r="G70" s="40"/>
+      <c r="H70" s="40"/>
+      <c r="I70" s="40"/>
+      <c r="J70" s="41"/>
     </row>
     <row r="71" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A71" s="30"/>
-      <c r="B71" s="60"/>
-      <c r="C71" s="60"/>
-      <c r="D71" s="60"/>
-      <c r="E71" s="60"/>
-      <c r="F71" s="60"/>
-      <c r="G71" s="60"/>
-      <c r="H71" s="60"/>
-      <c r="I71" s="60"/>
-      <c r="J71" s="61"/>
+      <c r="A71" s="28"/>
+      <c r="B71" s="40"/>
+      <c r="C71" s="40"/>
+      <c r="D71" s="40"/>
+      <c r="E71" s="40"/>
+      <c r="F71" s="40"/>
+      <c r="G71" s="40"/>
+      <c r="H71" s="40"/>
+      <c r="I71" s="40"/>
+      <c r="J71" s="41"/>
     </row>
     <row r="72" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A72" s="30"/>
-      <c r="B72" s="60"/>
-      <c r="C72" s="60"/>
-      <c r="D72" s="60"/>
-      <c r="E72" s="60"/>
-      <c r="F72" s="60"/>
-      <c r="G72" s="60"/>
-      <c r="H72" s="60"/>
-      <c r="I72" s="60"/>
-      <c r="J72" s="61"/>
+      <c r="A72" s="28"/>
+      <c r="B72" s="40"/>
+      <c r="C72" s="40"/>
+      <c r="D72" s="40"/>
+      <c r="E72" s="40"/>
+      <c r="F72" s="40"/>
+      <c r="G72" s="40"/>
+      <c r="H72" s="40"/>
+      <c r="I72" s="40"/>
+      <c r="J72" s="41"/>
     </row>
     <row r="73" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A73" s="30"/>
-      <c r="B73" s="60"/>
-      <c r="C73" s="60"/>
-      <c r="D73" s="60"/>
-      <c r="E73" s="60"/>
-      <c r="F73" s="60"/>
-      <c r="G73" s="60"/>
-      <c r="H73" s="60"/>
-      <c r="I73" s="60"/>
-      <c r="J73" s="61"/>
+      <c r="A73" s="28"/>
+      <c r="B73" s="40"/>
+      <c r="C73" s="40"/>
+      <c r="D73" s="40"/>
+      <c r="E73" s="40"/>
+      <c r="F73" s="40"/>
+      <c r="G73" s="40"/>
+      <c r="H73" s="40"/>
+      <c r="I73" s="40"/>
+      <c r="J73" s="41"/>
     </row>
     <row r="74" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A74" s="30"/>
-      <c r="B74" s="60"/>
-      <c r="C74" s="60"/>
-      <c r="D74" s="60"/>
-      <c r="E74" s="60"/>
-      <c r="F74" s="60"/>
-      <c r="G74" s="60"/>
-      <c r="H74" s="60"/>
-      <c r="I74" s="60"/>
-      <c r="J74" s="61"/>
+      <c r="A74" s="28"/>
+      <c r="B74" s="40"/>
+      <c r="C74" s="40"/>
+      <c r="D74" s="40"/>
+      <c r="E74" s="40"/>
+      <c r="F74" s="40"/>
+      <c r="G74" s="40"/>
+      <c r="H74" s="40"/>
+      <c r="I74" s="40"/>
+      <c r="J74" s="41"/>
     </row>
     <row r="75" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A75" s="30"/>
-      <c r="B75" s="60"/>
-      <c r="C75" s="60"/>
-      <c r="D75" s="60"/>
-      <c r="E75" s="60"/>
-      <c r="F75" s="60"/>
-      <c r="G75" s="60"/>
-      <c r="H75" s="60"/>
-      <c r="I75" s="60"/>
-      <c r="J75" s="61"/>
+      <c r="A75" s="28"/>
+      <c r="B75" s="40"/>
+      <c r="C75" s="40"/>
+      <c r="D75" s="40"/>
+      <c r="E75" s="40"/>
+      <c r="F75" s="40"/>
+      <c r="G75" s="40"/>
+      <c r="H75" s="40"/>
+      <c r="I75" s="40"/>
+      <c r="J75" s="41"/>
     </row>
     <row r="76" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A76" s="30"/>
-      <c r="B76" s="60"/>
-      <c r="C76" s="60"/>
-      <c r="D76" s="60"/>
-      <c r="E76" s="60"/>
-      <c r="F76" s="60"/>
-      <c r="G76" s="60"/>
-      <c r="H76" s="60"/>
-      <c r="I76" s="60"/>
-      <c r="J76" s="61"/>
+      <c r="A76" s="28"/>
+      <c r="B76" s="40"/>
+      <c r="C76" s="40"/>
+      <c r="D76" s="40"/>
+      <c r="E76" s="40"/>
+      <c r="F76" s="40"/>
+      <c r="G76" s="40"/>
+      <c r="H76" s="40"/>
+      <c r="I76" s="40"/>
+      <c r="J76" s="41"/>
     </row>
     <row r="77" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A77" s="30"/>
-      <c r="B77" s="60"/>
-      <c r="C77" s="60"/>
-      <c r="D77" s="60"/>
-      <c r="E77" s="60"/>
-      <c r="F77" s="60"/>
-      <c r="G77" s="60"/>
-      <c r="H77" s="60"/>
-      <c r="I77" s="60"/>
-      <c r="J77" s="61"/>
+      <c r="A77" s="28"/>
+      <c r="B77" s="40"/>
+      <c r="C77" s="40"/>
+      <c r="D77" s="40"/>
+      <c r="E77" s="40"/>
+      <c r="F77" s="40"/>
+      <c r="G77" s="40"/>
+      <c r="H77" s="40"/>
+      <c r="I77" s="40"/>
+      <c r="J77" s="41"/>
     </row>
     <row r="78" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A78" s="30"/>
-      <c r="B78" s="60"/>
-      <c r="C78" s="60"/>
-      <c r="D78" s="60"/>
-      <c r="E78" s="60"/>
-      <c r="F78" s="60"/>
-      <c r="G78" s="60"/>
-      <c r="H78" s="60"/>
-      <c r="I78" s="60"/>
-      <c r="J78" s="61"/>
+      <c r="A78" s="28"/>
+      <c r="B78" s="40"/>
+      <c r="C78" s="40"/>
+      <c r="D78" s="40"/>
+      <c r="E78" s="40"/>
+      <c r="F78" s="40"/>
+      <c r="G78" s="40"/>
+      <c r="H78" s="40"/>
+      <c r="I78" s="40"/>
+      <c r="J78" s="41"/>
     </row>
     <row r="79" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A79" s="30"/>
-      <c r="B79" s="60"/>
-      <c r="C79" s="60"/>
-      <c r="D79" s="60"/>
-      <c r="E79" s="60"/>
-      <c r="F79" s="60"/>
-      <c r="G79" s="60"/>
-      <c r="H79" s="60"/>
-      <c r="I79" s="60"/>
-      <c r="J79" s="61"/>
+      <c r="A79" s="28"/>
+      <c r="B79" s="40"/>
+      <c r="C79" s="40"/>
+      <c r="D79" s="40"/>
+      <c r="E79" s="40"/>
+      <c r="F79" s="40"/>
+      <c r="G79" s="40"/>
+      <c r="H79" s="40"/>
+      <c r="I79" s="40"/>
+      <c r="J79" s="41"/>
     </row>
     <row r="80" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A80" s="30"/>
-      <c r="B80" s="60"/>
-      <c r="C80" s="60"/>
-      <c r="D80" s="60"/>
-      <c r="E80" s="60"/>
-      <c r="F80" s="60"/>
-      <c r="G80" s="60"/>
-      <c r="H80" s="60"/>
-      <c r="I80" s="60"/>
-      <c r="J80" s="61"/>
+      <c r="A80" s="28"/>
+      <c r="B80" s="40"/>
+      <c r="C80" s="40"/>
+      <c r="D80" s="40"/>
+      <c r="E80" s="40"/>
+      <c r="F80" s="40"/>
+      <c r="G80" s="40"/>
+      <c r="H80" s="40"/>
+      <c r="I80" s="40"/>
+      <c r="J80" s="41"/>
     </row>
     <row r="81" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A81" s="30"/>
-      <c r="B81" s="60"/>
-      <c r="C81" s="60"/>
-      <c r="D81" s="60"/>
-      <c r="E81" s="60"/>
-      <c r="F81" s="60"/>
-      <c r="G81" s="60"/>
-      <c r="H81" s="60"/>
-      <c r="I81" s="60"/>
-      <c r="J81" s="61"/>
+      <c r="A81" s="28"/>
+      <c r="B81" s="40"/>
+      <c r="C81" s="40"/>
+      <c r="D81" s="40"/>
+      <c r="E81" s="40"/>
+      <c r="F81" s="40"/>
+      <c r="G81" s="40"/>
+      <c r="H81" s="40"/>
+      <c r="I81" s="40"/>
+      <c r="J81" s="41"/>
     </row>
     <row r="82" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A82" s="30"/>
-      <c r="B82" s="60"/>
-      <c r="C82" s="60"/>
-      <c r="D82" s="60"/>
-      <c r="E82" s="60"/>
-      <c r="F82" s="60"/>
-      <c r="G82" s="60"/>
-      <c r="H82" s="60"/>
-      <c r="I82" s="60"/>
-      <c r="J82" s="61"/>
+      <c r="A82" s="28"/>
+      <c r="B82" s="40"/>
+      <c r="C82" s="40"/>
+      <c r="D82" s="40"/>
+      <c r="E82" s="40"/>
+      <c r="F82" s="40"/>
+      <c r="G82" s="40"/>
+      <c r="H82" s="40"/>
+      <c r="I82" s="40"/>
+      <c r="J82" s="41"/>
     </row>
     <row r="83" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A83" s="30"/>
-      <c r="B83" s="60"/>
-      <c r="C83" s="60"/>
-      <c r="D83" s="60"/>
-      <c r="E83" s="60"/>
-      <c r="F83" s="60"/>
-      <c r="G83" s="60"/>
-      <c r="H83" s="60"/>
-      <c r="I83" s="60"/>
-      <c r="J83" s="61"/>
+      <c r="A83" s="28"/>
+      <c r="B83" s="40"/>
+      <c r="C83" s="40"/>
+      <c r="D83" s="40"/>
+      <c r="E83" s="40"/>
+      <c r="F83" s="40"/>
+      <c r="G83" s="40"/>
+      <c r="H83" s="40"/>
+      <c r="I83" s="40"/>
+      <c r="J83" s="41"/>
     </row>
     <row r="84" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A84" s="30"/>
-      <c r="B84" s="60"/>
-      <c r="C84" s="60"/>
-      <c r="D84" s="60"/>
-      <c r="E84" s="60"/>
-      <c r="F84" s="60"/>
-      <c r="G84" s="60"/>
-      <c r="H84" s="60"/>
-      <c r="I84" s="60"/>
-      <c r="J84" s="61"/>
+      <c r="A84" s="28"/>
+      <c r="B84" s="40"/>
+      <c r="C84" s="40"/>
+      <c r="D84" s="40"/>
+      <c r="E84" s="40"/>
+      <c r="F84" s="40"/>
+      <c r="G84" s="40"/>
+      <c r="H84" s="40"/>
+      <c r="I84" s="40"/>
+      <c r="J84" s="41"/>
     </row>
     <row r="85" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A85" s="30"/>
-      <c r="B85" s="60"/>
-      <c r="C85" s="60"/>
-      <c r="D85" s="60"/>
-      <c r="E85" s="60"/>
-      <c r="F85" s="60"/>
-      <c r="G85" s="60"/>
-      <c r="H85" s="60"/>
-      <c r="I85" s="60"/>
-      <c r="J85" s="61"/>
+      <c r="A85" s="28"/>
+      <c r="B85" s="40"/>
+      <c r="C85" s="40"/>
+      <c r="D85" s="40"/>
+      <c r="E85" s="40"/>
+      <c r="F85" s="40"/>
+      <c r="G85" s="40"/>
+      <c r="H85" s="40"/>
+      <c r="I85" s="40"/>
+      <c r="J85" s="41"/>
     </row>
     <row r="86" spans="1:10" ht="13.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A86" s="29"/>
-      <c r="B86" s="62"/>
-      <c r="C86" s="62"/>
-      <c r="D86" s="62"/>
-      <c r="E86" s="62"/>
-      <c r="F86" s="62"/>
-      <c r="G86" s="62"/>
-      <c r="H86" s="62"/>
-      <c r="I86" s="62"/>
-      <c r="J86" s="63"/>
+      <c r="A86" s="31"/>
+      <c r="B86" s="42"/>
+      <c r="C86" s="42"/>
+      <c r="D86" s="42"/>
+      <c r="E86" s="42"/>
+      <c r="F86" s="42"/>
+      <c r="G86" s="42"/>
+      <c r="H86" s="42"/>
+      <c r="I86" s="42"/>
+      <c r="J86" s="43"/>
     </row>
     <row r="87" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A87" s="28">
+      <c r="A87" s="27">
         <v>5</v>
       </c>
-      <c r="B87" s="32" t="s">
+      <c r="B87" s="34" t="s">
         <v>11</v>
       </c>
-      <c r="C87" s="32"/>
-      <c r="D87" s="32"/>
-      <c r="E87" s="32"/>
-      <c r="F87" s="32"/>
-      <c r="G87" s="32"/>
-      <c r="H87" s="32"/>
-      <c r="I87" s="32"/>
-      <c r="J87" s="33"/>
+      <c r="C87" s="34"/>
+      <c r="D87" s="34"/>
+      <c r="E87" s="34"/>
+      <c r="F87" s="34"/>
+      <c r="G87" s="34"/>
+      <c r="H87" s="34"/>
+      <c r="I87" s="34"/>
+      <c r="J87" s="67"/>
     </row>
     <row r="88" spans="1:10" ht="13.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A88" s="30"/>
-      <c r="B88" s="49" t="s">
+      <c r="A88" s="28"/>
+      <c r="B88" s="76" t="s">
         <v>12</v>
       </c>
-      <c r="C88" s="49"/>
-      <c r="D88" s="49"/>
-      <c r="E88" s="49"/>
-      <c r="F88" s="49"/>
-      <c r="G88" s="49"/>
-      <c r="H88" s="49"/>
-      <c r="I88" s="49"/>
-      <c r="J88" s="50"/>
+      <c r="C88" s="76"/>
+      <c r="D88" s="76"/>
+      <c r="E88" s="76"/>
+      <c r="F88" s="76"/>
+      <c r="G88" s="76"/>
+      <c r="H88" s="76"/>
+      <c r="I88" s="76"/>
+      <c r="J88" s="77"/>
     </row>
     <row r="89" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A89" s="28">
+      <c r="A89" s="27">
         <v>6</v>
       </c>
-      <c r="B89" s="42" t="s">
+      <c r="B89" s="32" t="s">
         <v>13</v>
       </c>
-      <c r="C89" s="42"/>
-      <c r="D89" s="42"/>
-      <c r="E89" s="42"/>
-      <c r="F89" s="42"/>
-      <c r="G89" s="42"/>
-      <c r="H89" s="42"/>
-      <c r="I89" s="42"/>
-      <c r="J89" s="43"/>
+      <c r="C89" s="32"/>
+      <c r="D89" s="32"/>
+      <c r="E89" s="32"/>
+      <c r="F89" s="32"/>
+      <c r="G89" s="32"/>
+      <c r="H89" s="32"/>
+      <c r="I89" s="32"/>
+      <c r="J89" s="33"/>
     </row>
     <row r="90" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A90" s="44"/>
-      <c r="B90" s="45" t="s">
+      <c r="A90" s="75"/>
+      <c r="B90" s="46" t="s">
         <v>14</v>
       </c>
-      <c r="C90" s="45"/>
-      <c r="D90" s="45"/>
-      <c r="E90" s="45"/>
-      <c r="F90" s="45"/>
-      <c r="G90" s="45"/>
-      <c r="H90" s="45"/>
-      <c r="I90" s="45"/>
-      <c r="J90" s="46"/>
+      <c r="C90" s="46"/>
+      <c r="D90" s="46"/>
+      <c r="E90" s="46"/>
+      <c r="F90" s="46"/>
+      <c r="G90" s="46"/>
+      <c r="H90" s="46"/>
+      <c r="I90" s="46"/>
+      <c r="J90" s="47"/>
     </row>
     <row r="91" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A91" s="44"/>
-      <c r="B91" s="45"/>
-      <c r="C91" s="45"/>
-      <c r="D91" s="45"/>
-      <c r="E91" s="45"/>
-      <c r="F91" s="45"/>
-      <c r="G91" s="45"/>
-      <c r="H91" s="45"/>
-      <c r="I91" s="45"/>
-      <c r="J91" s="46"/>
+      <c r="A91" s="75"/>
+      <c r="B91" s="46"/>
+      <c r="C91" s="46"/>
+      <c r="D91" s="46"/>
+      <c r="E91" s="46"/>
+      <c r="F91" s="46"/>
+      <c r="G91" s="46"/>
+      <c r="H91" s="46"/>
+      <c r="I91" s="46"/>
+      <c r="J91" s="47"/>
     </row>
     <row r="92" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A92" s="44"/>
-      <c r="B92" s="47"/>
-      <c r="C92" s="47"/>
-      <c r="D92" s="47"/>
-      <c r="E92" s="47"/>
-      <c r="F92" s="47"/>
-      <c r="G92" s="47"/>
-      <c r="H92" s="47"/>
-      <c r="I92" s="47"/>
-      <c r="J92" s="48"/>
+      <c r="A92" s="75"/>
+      <c r="B92" s="48"/>
+      <c r="C92" s="48"/>
+      <c r="D92" s="48"/>
+      <c r="E92" s="48"/>
+      <c r="F92" s="48"/>
+      <c r="G92" s="48"/>
+      <c r="H92" s="48"/>
+      <c r="I92" s="48"/>
+      <c r="J92" s="49"/>
     </row>
     <row r="93" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A93" s="30"/>
-      <c r="B93" s="51"/>
-      <c r="C93" s="52"/>
-      <c r="D93" s="52"/>
-      <c r="E93" s="52"/>
-      <c r="F93" s="52"/>
-      <c r="G93" s="52"/>
-      <c r="H93" s="52"/>
-      <c r="I93" s="52"/>
-      <c r="J93" s="53"/>
+      <c r="A93" s="28"/>
+      <c r="B93" s="78"/>
+      <c r="C93" s="62"/>
+      <c r="D93" s="62"/>
+      <c r="E93" s="62"/>
+      <c r="F93" s="62"/>
+      <c r="G93" s="62"/>
+      <c r="H93" s="62"/>
+      <c r="I93" s="62"/>
+      <c r="J93" s="63"/>
     </row>
     <row r="94" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A94" s="30"/>
-      <c r="B94" s="54"/>
-      <c r="C94" s="55"/>
-      <c r="D94" s="55"/>
-      <c r="E94" s="55"/>
-      <c r="F94" s="55"/>
-      <c r="G94" s="55"/>
-      <c r="H94" s="55"/>
-      <c r="I94" s="55"/>
-      <c r="J94" s="56"/>
+      <c r="A94" s="28"/>
+      <c r="B94" s="64"/>
+      <c r="C94" s="65"/>
+      <c r="D94" s="65"/>
+      <c r="E94" s="65"/>
+      <c r="F94" s="65"/>
+      <c r="G94" s="65"/>
+      <c r="H94" s="65"/>
+      <c r="I94" s="65"/>
+      <c r="J94" s="66"/>
     </row>
     <row r="95" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A95" s="30"/>
-      <c r="B95" s="54"/>
-      <c r="C95" s="55"/>
-      <c r="D95" s="55"/>
-      <c r="E95" s="55"/>
-      <c r="F95" s="55"/>
-      <c r="G95" s="55"/>
-      <c r="H95" s="55"/>
-      <c r="I95" s="55"/>
-      <c r="J95" s="56"/>
+      <c r="A95" s="28"/>
+      <c r="B95" s="64"/>
+      <c r="C95" s="65"/>
+      <c r="D95" s="65"/>
+      <c r="E95" s="65"/>
+      <c r="F95" s="65"/>
+      <c r="G95" s="65"/>
+      <c r="H95" s="65"/>
+      <c r="I95" s="65"/>
+      <c r="J95" s="66"/>
     </row>
     <row r="96" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A96" s="30"/>
-      <c r="B96" s="54"/>
-      <c r="C96" s="55"/>
-      <c r="D96" s="55"/>
-      <c r="E96" s="55"/>
-      <c r="F96" s="55"/>
-      <c r="G96" s="55"/>
-      <c r="H96" s="55"/>
-      <c r="I96" s="55"/>
-      <c r="J96" s="56"/>
+      <c r="A96" s="28"/>
+      <c r="B96" s="64"/>
+      <c r="C96" s="65"/>
+      <c r="D96" s="65"/>
+      <c r="E96" s="65"/>
+      <c r="F96" s="65"/>
+      <c r="G96" s="65"/>
+      <c r="H96" s="65"/>
+      <c r="I96" s="65"/>
+      <c r="J96" s="66"/>
     </row>
     <row r="97" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A97" s="30"/>
-      <c r="B97" s="54"/>
-      <c r="C97" s="55"/>
-      <c r="D97" s="55"/>
-      <c r="E97" s="55"/>
-      <c r="F97" s="55"/>
-      <c r="G97" s="55"/>
-      <c r="H97" s="55"/>
-      <c r="I97" s="55"/>
-      <c r="J97" s="56"/>
+      <c r="A97" s="28"/>
+      <c r="B97" s="64"/>
+      <c r="C97" s="65"/>
+      <c r="D97" s="65"/>
+      <c r="E97" s="65"/>
+      <c r="F97" s="65"/>
+      <c r="G97" s="65"/>
+      <c r="H97" s="65"/>
+      <c r="I97" s="65"/>
+      <c r="J97" s="66"/>
     </row>
     <row r="98" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A98" s="30"/>
-      <c r="B98" s="54"/>
-      <c r="C98" s="55"/>
-      <c r="D98" s="55"/>
-      <c r="E98" s="55"/>
-      <c r="F98" s="55"/>
-      <c r="G98" s="55"/>
-      <c r="H98" s="55"/>
-      <c r="I98" s="55"/>
-      <c r="J98" s="56"/>
+      <c r="A98" s="28"/>
+      <c r="B98" s="64"/>
+      <c r="C98" s="65"/>
+      <c r="D98" s="65"/>
+      <c r="E98" s="65"/>
+      <c r="F98" s="65"/>
+      <c r="G98" s="65"/>
+      <c r="H98" s="65"/>
+      <c r="I98" s="65"/>
+      <c r="J98" s="66"/>
     </row>
     <row r="99" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A99" s="30"/>
-      <c r="B99" s="54"/>
-      <c r="C99" s="55"/>
-      <c r="D99" s="55"/>
-      <c r="E99" s="55"/>
-      <c r="F99" s="55"/>
-      <c r="G99" s="55"/>
-      <c r="H99" s="55"/>
-      <c r="I99" s="55"/>
-      <c r="J99" s="56"/>
+      <c r="A99" s="28"/>
+      <c r="B99" s="64"/>
+      <c r="C99" s="65"/>
+      <c r="D99" s="65"/>
+      <c r="E99" s="65"/>
+      <c r="F99" s="65"/>
+      <c r="G99" s="65"/>
+      <c r="H99" s="65"/>
+      <c r="I99" s="65"/>
+      <c r="J99" s="66"/>
     </row>
     <row r="100" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A100" s="30"/>
-      <c r="B100" s="54"/>
-      <c r="C100" s="55"/>
-      <c r="D100" s="55"/>
-      <c r="E100" s="55"/>
-      <c r="F100" s="55"/>
-      <c r="G100" s="55"/>
-      <c r="H100" s="55"/>
-      <c r="I100" s="55"/>
-      <c r="J100" s="56"/>
+      <c r="A100" s="28"/>
+      <c r="B100" s="64"/>
+      <c r="C100" s="65"/>
+      <c r="D100" s="65"/>
+      <c r="E100" s="65"/>
+      <c r="F100" s="65"/>
+      <c r="G100" s="65"/>
+      <c r="H100" s="65"/>
+      <c r="I100" s="65"/>
+      <c r="J100" s="66"/>
     </row>
     <row r="101" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A101" s="30"/>
-      <c r="B101" s="54"/>
-      <c r="C101" s="55"/>
-      <c r="D101" s="55"/>
-      <c r="E101" s="55"/>
-      <c r="F101" s="55"/>
-      <c r="G101" s="55"/>
-      <c r="H101" s="55"/>
-      <c r="I101" s="55"/>
-      <c r="J101" s="56"/>
+      <c r="A101" s="28"/>
+      <c r="B101" s="64"/>
+      <c r="C101" s="65"/>
+      <c r="D101" s="65"/>
+      <c r="E101" s="65"/>
+      <c r="F101" s="65"/>
+      <c r="G101" s="65"/>
+      <c r="H101" s="65"/>
+      <c r="I101" s="65"/>
+      <c r="J101" s="66"/>
     </row>
     <row r="102" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A102" s="30"/>
-      <c r="B102" s="54"/>
-      <c r="C102" s="55"/>
-      <c r="D102" s="55"/>
-      <c r="E102" s="55"/>
-      <c r="F102" s="55"/>
-      <c r="G102" s="55"/>
-      <c r="H102" s="55"/>
-      <c r="I102" s="55"/>
-      <c r="J102" s="56"/>
+      <c r="A102" s="28"/>
+      <c r="B102" s="64"/>
+      <c r="C102" s="65"/>
+      <c r="D102" s="65"/>
+      <c r="E102" s="65"/>
+      <c r="F102" s="65"/>
+      <c r="G102" s="65"/>
+      <c r="H102" s="65"/>
+      <c r="I102" s="65"/>
+      <c r="J102" s="66"/>
     </row>
     <row r="103" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A103" s="30"/>
-      <c r="B103" s="54"/>
-      <c r="C103" s="55"/>
-      <c r="D103" s="55"/>
-      <c r="E103" s="55"/>
-      <c r="F103" s="55"/>
-      <c r="G103" s="55"/>
-      <c r="H103" s="55"/>
-      <c r="I103" s="55"/>
-      <c r="J103" s="56"/>
+      <c r="A103" s="28"/>
+      <c r="B103" s="64"/>
+      <c r="C103" s="65"/>
+      <c r="D103" s="65"/>
+      <c r="E103" s="65"/>
+      <c r="F103" s="65"/>
+      <c r="G103" s="65"/>
+      <c r="H103" s="65"/>
+      <c r="I103" s="65"/>
+      <c r="J103" s="66"/>
     </row>
     <row r="104" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A104" s="30"/>
-      <c r="B104" s="54"/>
-      <c r="C104" s="55"/>
-      <c r="D104" s="55"/>
-      <c r="E104" s="55"/>
-      <c r="F104" s="55"/>
-      <c r="G104" s="55"/>
-      <c r="H104" s="55"/>
-      <c r="I104" s="55"/>
-      <c r="J104" s="56"/>
+      <c r="A104" s="28"/>
+      <c r="B104" s="64"/>
+      <c r="C104" s="65"/>
+      <c r="D104" s="65"/>
+      <c r="E104" s="65"/>
+      <c r="F104" s="65"/>
+      <c r="G104" s="65"/>
+      <c r="H104" s="65"/>
+      <c r="I104" s="65"/>
+      <c r="J104" s="66"/>
     </row>
     <row r="105" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A105" s="30"/>
-      <c r="B105" s="54"/>
-      <c r="C105" s="55"/>
-      <c r="D105" s="55"/>
-      <c r="E105" s="55"/>
-      <c r="F105" s="55"/>
-      <c r="G105" s="55"/>
-      <c r="H105" s="55"/>
-      <c r="I105" s="55"/>
-      <c r="J105" s="56"/>
+      <c r="A105" s="28"/>
+      <c r="B105" s="64"/>
+      <c r="C105" s="65"/>
+      <c r="D105" s="65"/>
+      <c r="E105" s="65"/>
+      <c r="F105" s="65"/>
+      <c r="G105" s="65"/>
+      <c r="H105" s="65"/>
+      <c r="I105" s="65"/>
+      <c r="J105" s="66"/>
     </row>
     <row r="106" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A106" s="30"/>
-      <c r="B106" s="54"/>
-      <c r="C106" s="55"/>
-      <c r="D106" s="55"/>
-      <c r="E106" s="55"/>
-      <c r="F106" s="55"/>
-      <c r="G106" s="55"/>
-      <c r="H106" s="55"/>
-      <c r="I106" s="55"/>
-      <c r="J106" s="56"/>
+      <c r="A106" s="28"/>
+      <c r="B106" s="64"/>
+      <c r="C106" s="65"/>
+      <c r="D106" s="65"/>
+      <c r="E106" s="65"/>
+      <c r="F106" s="65"/>
+      <c r="G106" s="65"/>
+      <c r="H106" s="65"/>
+      <c r="I106" s="65"/>
+      <c r="J106" s="66"/>
     </row>
     <row r="107" spans="1:10" ht="13.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A107" s="31"/>
-      <c r="B107" s="57"/>
-      <c r="C107" s="58"/>
-      <c r="D107" s="58"/>
-      <c r="E107" s="58"/>
-      <c r="F107" s="58"/>
-      <c r="G107" s="58"/>
-      <c r="H107" s="58"/>
-      <c r="I107" s="58"/>
-      <c r="J107" s="59"/>
+      <c r="A107" s="29"/>
+      <c r="B107" s="79"/>
+      <c r="C107" s="80"/>
+      <c r="D107" s="80"/>
+      <c r="E107" s="80"/>
+      <c r="F107" s="80"/>
+      <c r="G107" s="80"/>
+      <c r="H107" s="80"/>
+      <c r="I107" s="80"/>
+      <c r="J107" s="81"/>
     </row>
     <row r="108" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A108" s="28">
+      <c r="A108" s="27">
         <v>7</v>
       </c>
-      <c r="B108" s="32" t="s">
+      <c r="B108" s="34" t="s">
         <v>15</v>
       </c>
-      <c r="C108" s="32"/>
-      <c r="D108" s="32"/>
-      <c r="E108" s="32"/>
-      <c r="F108" s="32"/>
-      <c r="G108" s="32"/>
-      <c r="H108" s="32"/>
-      <c r="I108" s="32"/>
-      <c r="J108" s="33"/>
+      <c r="C108" s="34"/>
+      <c r="D108" s="34"/>
+      <c r="E108" s="34"/>
+      <c r="F108" s="34"/>
+      <c r="G108" s="34"/>
+      <c r="H108" s="34"/>
+      <c r="I108" s="34"/>
+      <c r="J108" s="67"/>
     </row>
     <row r="109" spans="1:10" ht="13.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A109" s="29"/>
-      <c r="B109" s="40" t="s">
+      <c r="A109" s="31"/>
+      <c r="B109" s="73" t="s">
         <v>16</v>
       </c>
-      <c r="C109" s="40"/>
-      <c r="D109" s="40"/>
-      <c r="E109" s="40"/>
-      <c r="F109" s="40"/>
-      <c r="G109" s="40"/>
-      <c r="H109" s="40"/>
-      <c r="I109" s="40"/>
-      <c r="J109" s="41"/>
+      <c r="C109" s="73"/>
+      <c r="D109" s="73"/>
+      <c r="E109" s="73"/>
+      <c r="F109" s="73"/>
+      <c r="G109" s="73"/>
+      <c r="H109" s="73"/>
+      <c r="I109" s="73"/>
+      <c r="J109" s="74"/>
     </row>
     <row r="110" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A110" s="28">
+      <c r="A110" s="27">
         <v>8</v>
       </c>
-      <c r="B110" s="32" t="s">
+      <c r="B110" s="34" t="s">
         <v>17</v>
       </c>
-      <c r="C110" s="32"/>
-      <c r="D110" s="32"/>
-      <c r="E110" s="32"/>
-      <c r="F110" s="32"/>
-      <c r="G110" s="32"/>
-      <c r="H110" s="32"/>
-      <c r="I110" s="32"/>
-      <c r="J110" s="33"/>
+      <c r="C110" s="34"/>
+      <c r="D110" s="34"/>
+      <c r="E110" s="34"/>
+      <c r="F110" s="34"/>
+      <c r="G110" s="34"/>
+      <c r="H110" s="34"/>
+      <c r="I110" s="34"/>
+      <c r="J110" s="67"/>
     </row>
     <row r="111" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A111" s="30"/>
-      <c r="B111" s="34"/>
-      <c r="C111" s="34"/>
-      <c r="D111" s="34"/>
-      <c r="E111" s="34"/>
-      <c r="F111" s="34"/>
-      <c r="G111" s="34"/>
-      <c r="H111" s="34"/>
-      <c r="I111" s="34"/>
-      <c r="J111" s="35"/>
+      <c r="A111" s="28"/>
+      <c r="B111" s="44"/>
+      <c r="C111" s="44"/>
+      <c r="D111" s="44"/>
+      <c r="E111" s="44"/>
+      <c r="F111" s="44"/>
+      <c r="G111" s="44"/>
+      <c r="H111" s="44"/>
+      <c r="I111" s="44"/>
+      <c r="J111" s="45"/>
     </row>
     <row r="112" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A112" s="30"/>
-      <c r="B112" s="34"/>
-      <c r="C112" s="34"/>
-      <c r="D112" s="34"/>
-      <c r="E112" s="34"/>
-      <c r="F112" s="34"/>
-      <c r="G112" s="34"/>
-      <c r="H112" s="34"/>
-      <c r="I112" s="34"/>
-      <c r="J112" s="35"/>
+      <c r="A112" s="28"/>
+      <c r="B112" s="44"/>
+      <c r="C112" s="44"/>
+      <c r="D112" s="44"/>
+      <c r="E112" s="44"/>
+      <c r="F112" s="44"/>
+      <c r="G112" s="44"/>
+      <c r="H112" s="44"/>
+      <c r="I112" s="44"/>
+      <c r="J112" s="45"/>
     </row>
     <row r="113" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A113" s="30"/>
-      <c r="B113" s="34"/>
-      <c r="C113" s="34"/>
-      <c r="D113" s="34"/>
-      <c r="E113" s="34"/>
-      <c r="F113" s="34"/>
-      <c r="G113" s="34"/>
-      <c r="H113" s="34"/>
-      <c r="I113" s="34"/>
-      <c r="J113" s="35"/>
+      <c r="A113" s="28"/>
+      <c r="B113" s="44"/>
+      <c r="C113" s="44"/>
+      <c r="D113" s="44"/>
+      <c r="E113" s="44"/>
+      <c r="F113" s="44"/>
+      <c r="G113" s="44"/>
+      <c r="H113" s="44"/>
+      <c r="I113" s="44"/>
+      <c r="J113" s="45"/>
     </row>
     <row r="114" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A114" s="30"/>
-      <c r="B114" s="34"/>
-      <c r="C114" s="34"/>
-      <c r="D114" s="34"/>
-      <c r="E114" s="34"/>
-      <c r="F114" s="34"/>
-      <c r="G114" s="34"/>
-      <c r="H114" s="34"/>
-      <c r="I114" s="34"/>
-      <c r="J114" s="35"/>
+      <c r="A114" s="28"/>
+      <c r="B114" s="44"/>
+      <c r="C114" s="44"/>
+      <c r="D114" s="44"/>
+      <c r="E114" s="44"/>
+      <c r="F114" s="44"/>
+      <c r="G114" s="44"/>
+      <c r="H114" s="44"/>
+      <c r="I114" s="44"/>
+      <c r="J114" s="45"/>
     </row>
     <row r="115" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A115" s="30"/>
-      <c r="B115" s="34"/>
-      <c r="C115" s="34"/>
-      <c r="D115" s="34"/>
-      <c r="E115" s="34"/>
-      <c r="F115" s="34"/>
-      <c r="G115" s="34"/>
-      <c r="H115" s="34"/>
-      <c r="I115" s="34"/>
-      <c r="J115" s="35"/>
+      <c r="A115" s="28"/>
+      <c r="B115" s="44"/>
+      <c r="C115" s="44"/>
+      <c r="D115" s="44"/>
+      <c r="E115" s="44"/>
+      <c r="F115" s="44"/>
+      <c r="G115" s="44"/>
+      <c r="H115" s="44"/>
+      <c r="I115" s="44"/>
+      <c r="J115" s="45"/>
     </row>
     <row r="116" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A116" s="30"/>
-      <c r="B116" s="34"/>
-      <c r="C116" s="34"/>
-      <c r="D116" s="34"/>
-      <c r="E116" s="34"/>
-      <c r="F116" s="34"/>
-      <c r="G116" s="34"/>
-      <c r="H116" s="34"/>
-      <c r="I116" s="34"/>
-      <c r="J116" s="35"/>
+      <c r="A116" s="28"/>
+      <c r="B116" s="44"/>
+      <c r="C116" s="44"/>
+      <c r="D116" s="44"/>
+      <c r="E116" s="44"/>
+      <c r="F116" s="44"/>
+      <c r="G116" s="44"/>
+      <c r="H116" s="44"/>
+      <c r="I116" s="44"/>
+      <c r="J116" s="45"/>
     </row>
     <row r="117" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A117" s="30"/>
-      <c r="B117" s="36" t="s">
+      <c r="A117" s="28"/>
+      <c r="B117" s="69" t="s">
         <v>18</v>
       </c>
-      <c r="C117" s="36"/>
-      <c r="D117" s="36"/>
-      <c r="E117" s="36"/>
-      <c r="F117" s="36"/>
-      <c r="G117" s="36"/>
-      <c r="H117" s="36"/>
-      <c r="I117" s="36"/>
-      <c r="J117" s="37"/>
+      <c r="C117" s="69"/>
+      <c r="D117" s="69"/>
+      <c r="E117" s="69"/>
+      <c r="F117" s="69"/>
+      <c r="G117" s="69"/>
+      <c r="H117" s="69"/>
+      <c r="I117" s="69"/>
+      <c r="J117" s="70"/>
     </row>
     <row r="118" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A118" s="30"/>
-      <c r="B118" s="34"/>
-      <c r="C118" s="34"/>
-      <c r="D118" s="34"/>
-      <c r="E118" s="34"/>
-      <c r="F118" s="34"/>
-      <c r="G118" s="34"/>
-      <c r="H118" s="34"/>
-      <c r="I118" s="34"/>
-      <c r="J118" s="35"/>
+      <c r="A118" s="28"/>
+      <c r="B118" s="44"/>
+      <c r="C118" s="44"/>
+      <c r="D118" s="44"/>
+      <c r="E118" s="44"/>
+      <c r="F118" s="44"/>
+      <c r="G118" s="44"/>
+      <c r="H118" s="44"/>
+      <c r="I118" s="44"/>
+      <c r="J118" s="45"/>
     </row>
     <row r="119" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A119" s="30"/>
-      <c r="B119" s="34"/>
-      <c r="C119" s="34"/>
-      <c r="D119" s="34"/>
-      <c r="E119" s="34"/>
-      <c r="F119" s="34"/>
-      <c r="G119" s="34"/>
-      <c r="H119" s="34"/>
-      <c r="I119" s="34"/>
-      <c r="J119" s="35"/>
+      <c r="A119" s="28"/>
+      <c r="B119" s="44"/>
+      <c r="C119" s="44"/>
+      <c r="D119" s="44"/>
+      <c r="E119" s="44"/>
+      <c r="F119" s="44"/>
+      <c r="G119" s="44"/>
+      <c r="H119" s="44"/>
+      <c r="I119" s="44"/>
+      <c r="J119" s="45"/>
     </row>
     <row r="120" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A120" s="30"/>
-      <c r="B120" s="34"/>
-      <c r="C120" s="34"/>
-      <c r="D120" s="34"/>
-      <c r="E120" s="34"/>
-      <c r="F120" s="34"/>
-      <c r="G120" s="34"/>
-      <c r="H120" s="34"/>
-      <c r="I120" s="34"/>
-      <c r="J120" s="35"/>
+      <c r="A120" s="28"/>
+      <c r="B120" s="44"/>
+      <c r="C120" s="44"/>
+      <c r="D120" s="44"/>
+      <c r="E120" s="44"/>
+      <c r="F120" s="44"/>
+      <c r="G120" s="44"/>
+      <c r="H120" s="44"/>
+      <c r="I120" s="44"/>
+      <c r="J120" s="45"/>
     </row>
     <row r="121" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A121" s="30"/>
-      <c r="B121" s="34"/>
-      <c r="C121" s="34"/>
-      <c r="D121" s="34"/>
-      <c r="E121" s="34"/>
-      <c r="F121" s="34"/>
-      <c r="G121" s="34"/>
-      <c r="H121" s="34"/>
-      <c r="I121" s="34"/>
-      <c r="J121" s="35"/>
+      <c r="A121" s="28"/>
+      <c r="B121" s="44"/>
+      <c r="C121" s="44"/>
+      <c r="D121" s="44"/>
+      <c r="E121" s="44"/>
+      <c r="F121" s="44"/>
+      <c r="G121" s="44"/>
+      <c r="H121" s="44"/>
+      <c r="I121" s="44"/>
+      <c r="J121" s="45"/>
     </row>
     <row r="122" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A122" s="30"/>
-      <c r="B122" s="34"/>
-      <c r="C122" s="34"/>
-      <c r="D122" s="34"/>
-      <c r="E122" s="34"/>
-      <c r="F122" s="34"/>
-      <c r="G122" s="34"/>
-      <c r="H122" s="34"/>
-      <c r="I122" s="34"/>
-      <c r="J122" s="35"/>
+      <c r="A122" s="28"/>
+      <c r="B122" s="44"/>
+      <c r="C122" s="44"/>
+      <c r="D122" s="44"/>
+      <c r="E122" s="44"/>
+      <c r="F122" s="44"/>
+      <c r="G122" s="44"/>
+      <c r="H122" s="44"/>
+      <c r="I122" s="44"/>
+      <c r="J122" s="45"/>
     </row>
     <row r="123" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A123" s="30"/>
-      <c r="B123" s="34"/>
-      <c r="C123" s="34"/>
-      <c r="D123" s="34"/>
-      <c r="E123" s="34"/>
-      <c r="F123" s="34"/>
-      <c r="G123" s="34"/>
-      <c r="H123" s="34"/>
-      <c r="I123" s="34"/>
-      <c r="J123" s="35"/>
+      <c r="A123" s="28"/>
+      <c r="B123" s="44"/>
+      <c r="C123" s="44"/>
+      <c r="D123" s="44"/>
+      <c r="E123" s="44"/>
+      <c r="F123" s="44"/>
+      <c r="G123" s="44"/>
+      <c r="H123" s="44"/>
+      <c r="I123" s="44"/>
+      <c r="J123" s="45"/>
     </row>
     <row r="124" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A124" s="30"/>
-      <c r="B124" s="34"/>
-      <c r="C124" s="34"/>
-      <c r="D124" s="34"/>
-      <c r="E124" s="34"/>
-      <c r="F124" s="34"/>
-      <c r="G124" s="34"/>
-      <c r="H124" s="34"/>
-      <c r="I124" s="34"/>
-      <c r="J124" s="35"/>
+      <c r="A124" s="28"/>
+      <c r="B124" s="44"/>
+      <c r="C124" s="44"/>
+      <c r="D124" s="44"/>
+      <c r="E124" s="44"/>
+      <c r="F124" s="44"/>
+      <c r="G124" s="44"/>
+      <c r="H124" s="44"/>
+      <c r="I124" s="44"/>
+      <c r="J124" s="45"/>
     </row>
     <row r="125" spans="1:10" ht="13.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A125" s="31"/>
-      <c r="B125" s="38"/>
-      <c r="C125" s="38"/>
-      <c r="D125" s="38"/>
-      <c r="E125" s="38"/>
-      <c r="F125" s="38"/>
-      <c r="G125" s="38"/>
-      <c r="H125" s="38"/>
-      <c r="I125" s="38"/>
-      <c r="J125" s="39"/>
+      <c r="A125" s="29"/>
+      <c r="B125" s="71"/>
+      <c r="C125" s="71"/>
+      <c r="D125" s="71"/>
+      <c r="E125" s="71"/>
+      <c r="F125" s="71"/>
+      <c r="G125" s="71"/>
+      <c r="H125" s="71"/>
+      <c r="I125" s="71"/>
+      <c r="J125" s="72"/>
     </row>
   </sheetData>
   <mergeCells count="39">
-    <mergeCell ref="A21:A62"/>
-    <mergeCell ref="B64:C64"/>
-    <mergeCell ref="A2:A3"/>
-    <mergeCell ref="A4:A20"/>
-    <mergeCell ref="B4:J4"/>
-    <mergeCell ref="B2:D3"/>
-    <mergeCell ref="E2:J3"/>
+    <mergeCell ref="A1:J1"/>
+    <mergeCell ref="A108:A109"/>
+    <mergeCell ref="A110:A125"/>
+    <mergeCell ref="B110:J110"/>
+    <mergeCell ref="B111:J116"/>
+    <mergeCell ref="B117:J117"/>
+    <mergeCell ref="B118:J125"/>
+    <mergeCell ref="B109:J109"/>
+    <mergeCell ref="B108:J108"/>
+    <mergeCell ref="B89:J89"/>
+    <mergeCell ref="A89:A107"/>
+    <mergeCell ref="B90:J92"/>
+    <mergeCell ref="A87:A88"/>
+    <mergeCell ref="B87:J87"/>
+    <mergeCell ref="B88:J88"/>
+    <mergeCell ref="B93:J107"/>
     <mergeCell ref="B69:J86"/>
     <mergeCell ref="A63:A86"/>
     <mergeCell ref="D64:J64"/>
@@ -5015,22 +5048,13 @@
     <mergeCell ref="B66:C66"/>
     <mergeCell ref="D65:J65"/>
     <mergeCell ref="B65:C65"/>
-    <mergeCell ref="A1:J1"/>
-    <mergeCell ref="A108:A109"/>
-    <mergeCell ref="A110:A125"/>
-    <mergeCell ref="B110:J110"/>
-    <mergeCell ref="B111:J116"/>
-    <mergeCell ref="B117:J117"/>
-    <mergeCell ref="B118:J125"/>
-    <mergeCell ref="B109:J109"/>
-    <mergeCell ref="B108:J108"/>
-    <mergeCell ref="B89:J89"/>
-    <mergeCell ref="A89:A107"/>
-    <mergeCell ref="B90:J92"/>
-    <mergeCell ref="A87:A88"/>
-    <mergeCell ref="B87:J87"/>
-    <mergeCell ref="B88:J88"/>
-    <mergeCell ref="B93:J107"/>
+    <mergeCell ref="A21:A62"/>
+    <mergeCell ref="B64:C64"/>
+    <mergeCell ref="A2:A3"/>
+    <mergeCell ref="A4:A20"/>
+    <mergeCell ref="B4:J4"/>
+    <mergeCell ref="B2:D3"/>
+    <mergeCell ref="E2:J3"/>
   </mergeCells>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.75" right="0.75" top="0.6" bottom="0.61" header="0.4" footer="0.39"/>
@@ -5059,71 +5083,71 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="77" t="s">
+      <c r="A1" s="35" t="s">
         <v>19</v>
       </c>
-      <c r="B1" s="77"/>
-      <c r="C1" s="77"/>
+      <c r="B1" s="35"/>
+      <c r="C1" s="35"/>
     </row>
     <row r="2" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="85" t="s">
+      <c r="A2" s="90" t="s">
         <v>20</v>
       </c>
-      <c r="B2" s="85"/>
-      <c r="C2" s="85"/>
-      <c r="D2" s="85"/>
-      <c r="E2" s="85"/>
-      <c r="F2" s="85"/>
-      <c r="G2" s="85"/>
-      <c r="H2" s="85"/>
+      <c r="B2" s="90"/>
+      <c r="C2" s="90"/>
+      <c r="D2" s="90"/>
+      <c r="E2" s="90"/>
+      <c r="F2" s="90"/>
+      <c r="G2" s="90"/>
+      <c r="H2" s="90"/>
     </row>
     <row r="3" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="85"/>
-      <c r="B3" s="85"/>
-      <c r="C3" s="85"/>
-      <c r="D3" s="85"/>
-      <c r="E3" s="85"/>
-      <c r="F3" s="85"/>
-      <c r="G3" s="85"/>
-      <c r="H3" s="85"/>
+      <c r="A3" s="90"/>
+      <c r="B3" s="90"/>
+      <c r="C3" s="90"/>
+      <c r="D3" s="90"/>
+      <c r="E3" s="90"/>
+      <c r="F3" s="90"/>
+      <c r="G3" s="90"/>
+      <c r="H3" s="90"/>
     </row>
     <row r="4" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="85"/>
-      <c r="B4" s="85"/>
-      <c r="C4" s="85"/>
-      <c r="D4" s="85"/>
-      <c r="E4" s="85"/>
-      <c r="F4" s="85"/>
-      <c r="G4" s="85"/>
-      <c r="H4" s="85"/>
+      <c r="A4" s="90"/>
+      <c r="B4" s="90"/>
+      <c r="C4" s="90"/>
+      <c r="D4" s="90"/>
+      <c r="E4" s="90"/>
+      <c r="F4" s="90"/>
+      <c r="G4" s="90"/>
+      <c r="H4" s="90"/>
     </row>
     <row r="5" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="49"/>
-      <c r="B5" s="49"/>
-      <c r="C5" s="49"/>
+      <c r="A5" s="76"/>
+      <c r="B5" s="76"/>
+      <c r="C5" s="76"/>
     </row>
     <row r="6" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="84" t="s">
+      <c r="A6" s="89" t="s">
         <v>21</v>
       </c>
-      <c r="B6" s="84" t="s">
+      <c r="B6" s="89" t="s">
         <v>22</v>
       </c>
-      <c r="C6" s="84"/>
-      <c r="D6" s="84"/>
-      <c r="E6" s="84" t="s">
+      <c r="C6" s="89"/>
+      <c r="D6" s="89"/>
+      <c r="E6" s="89" t="s">
         <v>23</v>
       </c>
-      <c r="F6" s="86" t="s">
+      <c r="F6" s="91" t="s">
         <v>24</v>
       </c>
-      <c r="G6" s="87"/>
-      <c r="H6" s="90" t="s">
+      <c r="G6" s="92"/>
+      <c r="H6" s="95" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="7" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="84"/>
+      <c r="A7" s="89"/>
       <c r="B7" s="23" t="s">
         <v>26</v>
       </c>
@@ -5133,19 +5157,19 @@
       <c r="D7" s="23" t="s">
         <v>28</v>
       </c>
-      <c r="E7" s="84"/>
-      <c r="F7" s="88"/>
-      <c r="G7" s="89"/>
-      <c r="H7" s="91"/>
+      <c r="E7" s="89"/>
+      <c r="F7" s="93"/>
+      <c r="G7" s="94"/>
+      <c r="H7" s="96"/>
     </row>
     <row r="8" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="4">
         <v>1</v>
       </c>
-      <c r="B8" s="62" t="s">
+      <c r="B8" s="42" t="s">
         <v>29</v>
       </c>
-      <c r="C8" s="94" t="s">
+      <c r="C8" s="84" t="s">
         <v>30</v>
       </c>
       <c r="D8" s="4" t="s">
@@ -5154,10 +5178,10 @@
       <c r="E8" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="F8" s="82" t="s">
+      <c r="F8" s="86" t="s">
         <v>32</v>
       </c>
-      <c r="G8" s="83"/>
+      <c r="G8" s="87"/>
       <c r="H8" s="22" t="s">
         <v>33</v>
       </c>
@@ -5166,18 +5190,18 @@
       <c r="A9" s="4">
         <v>2</v>
       </c>
-      <c r="B9" s="92"/>
-      <c r="C9" s="95"/>
+      <c r="B9" s="83"/>
+      <c r="C9" s="85"/>
       <c r="D9" s="4" t="s">
         <v>34</v>
       </c>
       <c r="E9" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="F9" s="82" t="s">
+      <c r="F9" s="86" t="s">
         <v>32</v>
       </c>
-      <c r="G9" s="83"/>
+      <c r="G9" s="87"/>
       <c r="H9" s="22" t="s">
         <v>35</v>
       </c>
@@ -5186,8 +5210,8 @@
       <c r="A10" s="4">
         <v>3</v>
       </c>
-      <c r="B10" s="92"/>
-      <c r="C10" s="62" t="s">
+      <c r="B10" s="83"/>
+      <c r="C10" s="42" t="s">
         <v>36</v>
       </c>
       <c r="D10" s="4" t="s">
@@ -5196,10 +5220,10 @@
       <c r="E10" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="F10" s="82" t="s">
+      <c r="F10" s="86" t="s">
         <v>32</v>
       </c>
-      <c r="G10" s="83"/>
+      <c r="G10" s="87"/>
       <c r="H10" s="22" t="s">
         <v>35</v>
       </c>
@@ -5208,18 +5232,18 @@
       <c r="A11" s="4">
         <v>4</v>
       </c>
-      <c r="B11" s="93"/>
-      <c r="C11" s="93"/>
+      <c r="B11" s="82"/>
+      <c r="C11" s="82"/>
       <c r="D11" s="4" t="s">
         <v>38</v>
       </c>
       <c r="E11" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="F11" s="82" t="s">
+      <c r="F11" s="86" t="s">
         <v>32</v>
       </c>
-      <c r="G11" s="83"/>
+      <c r="G11" s="87"/>
       <c r="H11" s="22" t="s">
         <v>35</v>
       </c>
@@ -5228,7 +5252,7 @@
       <c r="A12" s="4">
         <v>5</v>
       </c>
-      <c r="B12" s="62" t="s">
+      <c r="B12" s="42" t="s">
         <v>39</v>
       </c>
       <c r="C12" s="4" t="s">
@@ -5238,10 +5262,10 @@
       <c r="E12" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="F12" s="82" t="s">
+      <c r="F12" s="86" t="s">
         <v>32</v>
       </c>
-      <c r="G12" s="83"/>
+      <c r="G12" s="87"/>
       <c r="H12" s="22" t="s">
         <v>33</v>
       </c>
@@ -5250,7 +5274,7 @@
       <c r="A13" s="4">
         <v>6</v>
       </c>
-      <c r="B13" s="93"/>
+      <c r="B13" s="82"/>
       <c r="C13" s="4" t="s">
         <v>41</v>
       </c>
@@ -5258,10 +5282,10 @@
       <c r="E13" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="F13" s="82" t="s">
+      <c r="F13" s="86" t="s">
         <v>32</v>
       </c>
-      <c r="G13" s="96"/>
+      <c r="G13" s="88"/>
       <c r="H13" s="22" t="s">
         <v>33</v>
       </c>
@@ -5270,7 +5294,7 @@
       <c r="A14" s="4">
         <v>7</v>
       </c>
-      <c r="B14" s="62" t="s">
+      <c r="B14" s="42" t="s">
         <v>42</v>
       </c>
       <c r="C14" s="4" t="s">
@@ -5280,10 +5304,10 @@
       <c r="E14" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="F14" s="82" t="s">
+      <c r="F14" s="86" t="s">
         <v>32</v>
       </c>
-      <c r="G14" s="83"/>
+      <c r="G14" s="87"/>
       <c r="H14" s="22" t="s">
         <v>33</v>
       </c>
@@ -5292,7 +5316,7 @@
       <c r="A15" s="4">
         <v>8</v>
       </c>
-      <c r="B15" s="93"/>
+      <c r="B15" s="82"/>
       <c r="C15" s="4" t="s">
         <v>44</v>
       </c>
@@ -5300,10 +5324,10 @@
       <c r="E15" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="F15" s="82" t="s">
+      <c r="F15" s="86" t="s">
         <v>32</v>
       </c>
-      <c r="G15" s="83"/>
+      <c r="G15" s="87"/>
       <c r="H15" s="22" t="s">
         <v>35</v>
       </c>
@@ -5312,7 +5336,7 @@
       <c r="A16" s="4">
         <v>9</v>
       </c>
-      <c r="B16" s="62" t="s">
+      <c r="B16" s="42" t="s">
         <v>45</v>
       </c>
       <c r="C16" s="4" t="s">
@@ -5322,10 +5346,10 @@
       <c r="E16" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="F16" s="82" t="s">
+      <c r="F16" s="86" t="s">
         <v>32</v>
       </c>
-      <c r="G16" s="83"/>
+      <c r="G16" s="87"/>
       <c r="H16" s="22" t="s">
         <v>35</v>
       </c>
@@ -5334,7 +5358,7 @@
       <c r="A17" s="4">
         <v>10</v>
       </c>
-      <c r="B17" s="93"/>
+      <c r="B17" s="82"/>
       <c r="C17" s="4" t="s">
         <v>48</v>
       </c>
@@ -5342,10 +5366,10 @@
       <c r="E17" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="F17" s="82" t="s">
+      <c r="F17" s="86" t="s">
         <v>32</v>
       </c>
-      <c r="G17" s="83"/>
+      <c r="G17" s="87"/>
       <c r="H17" s="22" t="s">
         <v>35</v>
       </c>
@@ -5354,7 +5378,7 @@
       <c r="A18" s="4">
         <v>11</v>
       </c>
-      <c r="B18" s="62" t="s">
+      <c r="B18" s="42" t="s">
         <v>49</v>
       </c>
       <c r="C18" s="4" t="s">
@@ -5364,10 +5388,10 @@
       <c r="E18" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="F18" s="82" t="s">
+      <c r="F18" s="86" t="s">
         <v>32</v>
       </c>
-      <c r="G18" s="83"/>
+      <c r="G18" s="87"/>
       <c r="H18" s="22" t="s">
         <v>33</v>
       </c>
@@ -5376,7 +5400,7 @@
       <c r="A19" s="4">
         <v>12</v>
       </c>
-      <c r="B19" s="93"/>
+      <c r="B19" s="82"/>
       <c r="C19" s="4" t="s">
         <v>49</v>
       </c>
@@ -5384,10 +5408,10 @@
       <c r="E19" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="F19" s="82" t="s">
+      <c r="F19" s="86" t="s">
         <v>32</v>
       </c>
-      <c r="G19" s="83"/>
+      <c r="G19" s="87"/>
       <c r="H19" s="22" t="s">
         <v>33</v>
       </c>
@@ -5396,7 +5420,7 @@
       <c r="A20" s="4">
         <v>13</v>
       </c>
-      <c r="B20" s="62" t="s">
+      <c r="B20" s="42" t="s">
         <v>51</v>
       </c>
       <c r="C20" s="4" t="s">
@@ -5406,10 +5430,10 @@
       <c r="E20" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="F20" s="82" t="s">
+      <c r="F20" s="86" t="s">
         <v>32</v>
       </c>
-      <c r="G20" s="83"/>
+      <c r="G20" s="87"/>
       <c r="H20" s="22" t="s">
         <v>35</v>
       </c>
@@ -5418,7 +5442,7 @@
       <c r="A21" s="4">
         <v>14</v>
       </c>
-      <c r="B21" s="93"/>
+      <c r="B21" s="82"/>
       <c r="C21" s="4" t="s">
         <v>53</v>
       </c>
@@ -5426,10 +5450,10 @@
       <c r="E21" s="4" t="s">
         <v>54</v>
       </c>
-      <c r="F21" s="82" t="s">
+      <c r="F21" s="86" t="s">
         <v>32</v>
       </c>
-      <c r="G21" s="83"/>
+      <c r="G21" s="87"/>
       <c r="H21" s="22" t="s">
         <v>35</v>
       </c>
@@ -5438,7 +5462,7 @@
       <c r="A22" s="4">
         <v>15</v>
       </c>
-      <c r="B22" s="62" t="s">
+      <c r="B22" s="42" t="s">
         <v>55</v>
       </c>
       <c r="C22" s="4" t="s">
@@ -5448,10 +5472,10 @@
       <c r="E22" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="F22" s="82" t="s">
+      <c r="F22" s="86" t="s">
         <v>32</v>
       </c>
-      <c r="G22" s="83"/>
+      <c r="G22" s="87"/>
       <c r="H22" s="22" t="s">
         <v>33</v>
       </c>
@@ -5460,7 +5484,7 @@
       <c r="A23" s="4">
         <v>16</v>
       </c>
-      <c r="B23" s="93"/>
+      <c r="B23" s="82"/>
       <c r="C23" s="4" t="s">
         <v>57</v>
       </c>
@@ -5468,10 +5492,10 @@
       <c r="E23" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="F23" s="82" t="s">
+      <c r="F23" s="86" t="s">
         <v>32</v>
       </c>
-      <c r="G23" s="83"/>
+      <c r="G23" s="87"/>
       <c r="H23" s="22" t="s">
         <v>33</v>
       </c>
@@ -5484,8 +5508,8 @@
       <c r="C24" s="4"/>
       <c r="D24" s="4"/>
       <c r="E24" s="4"/>
-      <c r="F24" s="82"/>
-      <c r="G24" s="83"/>
+      <c r="F24" s="86"/>
+      <c r="G24" s="87"/>
       <c r="H24" s="4"/>
     </row>
     <row r="25" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -5496,8 +5520,8 @@
       <c r="C25" s="4"/>
       <c r="D25" s="4"/>
       <c r="E25" s="4"/>
-      <c r="F25" s="82"/>
-      <c r="G25" s="83"/>
+      <c r="F25" s="86"/>
+      <c r="G25" s="87"/>
       <c r="H25" s="4"/>
     </row>
     <row r="26" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -5508,8 +5532,8 @@
       <c r="C26" s="4"/>
       <c r="D26" s="4"/>
       <c r="E26" s="4"/>
-      <c r="F26" s="82"/>
-      <c r="G26" s="83"/>
+      <c r="F26" s="86"/>
+      <c r="G26" s="87"/>
       <c r="H26" s="4"/>
     </row>
     <row r="27" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -5520,8 +5544,8 @@
       <c r="C27" s="4"/>
       <c r="D27" s="4"/>
       <c r="E27" s="4"/>
-      <c r="F27" s="82"/>
-      <c r="G27" s="83"/>
+      <c r="F27" s="86"/>
+      <c r="G27" s="87"/>
       <c r="H27" s="4"/>
     </row>
     <row r="28" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -5532,8 +5556,8 @@
       <c r="C28" s="4"/>
       <c r="D28" s="4"/>
       <c r="E28" s="4"/>
-      <c r="F28" s="82"/>
-      <c r="G28" s="83"/>
+      <c r="F28" s="86"/>
+      <c r="G28" s="87"/>
       <c r="H28" s="4"/>
     </row>
     <row r="29" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -5544,8 +5568,8 @@
       <c r="C29" s="4"/>
       <c r="D29" s="4"/>
       <c r="E29" s="4"/>
-      <c r="F29" s="82"/>
-      <c r="G29" s="83"/>
+      <c r="F29" s="86"/>
+      <c r="G29" s="87"/>
       <c r="H29" s="4"/>
     </row>
     <row r="30" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -5556,8 +5580,8 @@
       <c r="C30" s="4"/>
       <c r="D30" s="4"/>
       <c r="E30" s="4"/>
-      <c r="F30" s="82"/>
-      <c r="G30" s="83"/>
+      <c r="F30" s="86"/>
+      <c r="G30" s="87"/>
       <c r="H30" s="4"/>
     </row>
     <row r="31" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -5568,8 +5592,8 @@
       <c r="C31" s="4"/>
       <c r="D31" s="4"/>
       <c r="E31" s="4"/>
-      <c r="F31" s="82"/>
-      <c r="G31" s="83"/>
+      <c r="F31" s="86"/>
+      <c r="G31" s="87"/>
       <c r="H31" s="4"/>
     </row>
     <row r="32" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -5580,8 +5604,8 @@
       <c r="C32" s="4"/>
       <c r="D32" s="4"/>
       <c r="E32" s="4"/>
-      <c r="F32" s="82"/>
-      <c r="G32" s="83"/>
+      <c r="F32" s="86"/>
+      <c r="G32" s="87"/>
       <c r="H32" s="4"/>
     </row>
     <row r="33" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -5592,8 +5616,8 @@
       <c r="C33" s="4"/>
       <c r="D33" s="4"/>
       <c r="E33" s="4"/>
-      <c r="F33" s="82"/>
-      <c r="G33" s="83"/>
+      <c r="F33" s="86"/>
+      <c r="G33" s="87"/>
       <c r="H33" s="4"/>
     </row>
     <row r="34" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -5604,8 +5628,8 @@
       <c r="C34" s="4"/>
       <c r="D34" s="4"/>
       <c r="E34" s="4"/>
-      <c r="F34" s="82"/>
-      <c r="G34" s="83"/>
+      <c r="F34" s="86"/>
+      <c r="G34" s="87"/>
       <c r="H34" s="4"/>
     </row>
     <row r="35" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -5616,8 +5640,8 @@
       <c r="C35" s="4"/>
       <c r="D35" s="4"/>
       <c r="E35" s="4"/>
-      <c r="F35" s="82"/>
-      <c r="G35" s="83"/>
+      <c r="F35" s="86"/>
+      <c r="G35" s="87"/>
       <c r="H35" s="4"/>
     </row>
     <row r="36" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -5628,8 +5652,8 @@
       <c r="C36" s="4"/>
       <c r="D36" s="4"/>
       <c r="E36" s="4"/>
-      <c r="F36" s="82"/>
-      <c r="G36" s="83"/>
+      <c r="F36" s="86"/>
+      <c r="G36" s="87"/>
       <c r="H36" s="4"/>
     </row>
     <row r="37" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -5640,18 +5664,40 @@
       <c r="C37" s="4"/>
       <c r="D37" s="4"/>
       <c r="E37" s="4"/>
-      <c r="F37" s="82"/>
-      <c r="G37" s="83"/>
+      <c r="F37" s="86"/>
+      <c r="G37" s="87"/>
       <c r="H37" s="4"/>
     </row>
   </sheetData>
   <mergeCells count="47">
-    <mergeCell ref="B20:B21"/>
-    <mergeCell ref="B22:B23"/>
-    <mergeCell ref="B12:B13"/>
-    <mergeCell ref="B14:B15"/>
-    <mergeCell ref="B16:B17"/>
-    <mergeCell ref="B18:B19"/>
+    <mergeCell ref="F33:G33"/>
+    <mergeCell ref="F34:G34"/>
+    <mergeCell ref="F35:G35"/>
+    <mergeCell ref="F36:G36"/>
+    <mergeCell ref="F37:G37"/>
+    <mergeCell ref="F28:G28"/>
+    <mergeCell ref="F29:G29"/>
+    <mergeCell ref="F30:G30"/>
+    <mergeCell ref="F31:G31"/>
+    <mergeCell ref="F32:G32"/>
+    <mergeCell ref="F23:G23"/>
+    <mergeCell ref="F24:G24"/>
+    <mergeCell ref="F25:G25"/>
+    <mergeCell ref="F26:G26"/>
+    <mergeCell ref="F27:G27"/>
+    <mergeCell ref="F18:G18"/>
+    <mergeCell ref="F19:G19"/>
+    <mergeCell ref="F20:G20"/>
+    <mergeCell ref="F21:G21"/>
+    <mergeCell ref="F22:G22"/>
+    <mergeCell ref="A1:C1"/>
+    <mergeCell ref="A5:C5"/>
+    <mergeCell ref="A6:A7"/>
+    <mergeCell ref="B6:D6"/>
+    <mergeCell ref="E6:E7"/>
+    <mergeCell ref="A2:H4"/>
+    <mergeCell ref="F6:G7"/>
+    <mergeCell ref="H6:H7"/>
     <mergeCell ref="B8:B11"/>
     <mergeCell ref="C8:C9"/>
     <mergeCell ref="C10:C11"/>
@@ -5665,34 +5711,12 @@
     <mergeCell ref="F11:G11"/>
     <mergeCell ref="F12:G12"/>
     <mergeCell ref="F13:G13"/>
-    <mergeCell ref="A1:C1"/>
-    <mergeCell ref="A5:C5"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="B6:D6"/>
-    <mergeCell ref="E6:E7"/>
-    <mergeCell ref="A2:H4"/>
-    <mergeCell ref="F6:G7"/>
-    <mergeCell ref="H6:H7"/>
-    <mergeCell ref="F18:G18"/>
-    <mergeCell ref="F19:G19"/>
-    <mergeCell ref="F20:G20"/>
-    <mergeCell ref="F21:G21"/>
-    <mergeCell ref="F22:G22"/>
-    <mergeCell ref="F23:G23"/>
-    <mergeCell ref="F24:G24"/>
-    <mergeCell ref="F25:G25"/>
-    <mergeCell ref="F26:G26"/>
-    <mergeCell ref="F27:G27"/>
-    <mergeCell ref="F28:G28"/>
-    <mergeCell ref="F29:G29"/>
-    <mergeCell ref="F30:G30"/>
-    <mergeCell ref="F31:G31"/>
-    <mergeCell ref="F32:G32"/>
-    <mergeCell ref="F33:G33"/>
-    <mergeCell ref="F34:G34"/>
-    <mergeCell ref="F35:G35"/>
-    <mergeCell ref="F36:G36"/>
-    <mergeCell ref="F37:G37"/>
+    <mergeCell ref="B20:B21"/>
+    <mergeCell ref="B22:B23"/>
+    <mergeCell ref="B12:B13"/>
+    <mergeCell ref="B14:B15"/>
+    <mergeCell ref="B16:B17"/>
+    <mergeCell ref="B18:B19"/>
   </mergeCells>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.75" right="0.75" top="0.6" bottom="0.61" header="0.4" footer="0.39"/>
@@ -5719,90 +5743,90 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="97" t="s">
+      <c r="A1" s="101" t="s">
         <v>58</v>
       </c>
-      <c r="B1" s="98"/>
-      <c r="C1" s="99"/>
+      <c r="B1" s="102"/>
+      <c r="C1" s="103"/>
       <c r="D1" s="19"/>
     </row>
     <row r="2" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="85" t="s">
+      <c r="A2" s="90" t="s">
         <v>59</v>
       </c>
-      <c r="B2" s="85"/>
-      <c r="C2" s="85"/>
-      <c r="D2" s="85"/>
-      <c r="E2" s="85"/>
-      <c r="F2" s="85"/>
-      <c r="G2" s="85"/>
-      <c r="H2" s="85"/>
-      <c r="I2" s="85"/>
+      <c r="B2" s="90"/>
+      <c r="C2" s="90"/>
+      <c r="D2" s="90"/>
+      <c r="E2" s="90"/>
+      <c r="F2" s="90"/>
+      <c r="G2" s="90"/>
+      <c r="H2" s="90"/>
+      <c r="I2" s="90"/>
     </row>
     <row r="3" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="85"/>
-      <c r="B3" s="85"/>
-      <c r="C3" s="85"/>
-      <c r="D3" s="85"/>
-      <c r="E3" s="85"/>
-      <c r="F3" s="85"/>
-      <c r="G3" s="85"/>
-      <c r="H3" s="85"/>
-      <c r="I3" s="85"/>
+      <c r="A3" s="90"/>
+      <c r="B3" s="90"/>
+      <c r="C3" s="90"/>
+      <c r="D3" s="90"/>
+      <c r="E3" s="90"/>
+      <c r="F3" s="90"/>
+      <c r="G3" s="90"/>
+      <c r="H3" s="90"/>
+      <c r="I3" s="90"/>
     </row>
     <row r="4" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="49"/>
-      <c r="B4" s="49"/>
+      <c r="A4" s="76"/>
+      <c r="B4" s="76"/>
     </row>
     <row r="5" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="84" t="s">
+      <c r="A5" s="89" t="s">
         <v>21</v>
       </c>
-      <c r="B5" s="90" t="s">
+      <c r="B5" s="95" t="s">
         <v>60</v>
       </c>
-      <c r="C5" s="90" t="s">
+      <c r="C5" s="95" t="s">
         <v>61</v>
       </c>
-      <c r="D5" s="86" t="s">
+      <c r="D5" s="91" t="s">
         <v>24</v>
       </c>
-      <c r="E5" s="87"/>
-      <c r="F5" s="87"/>
-      <c r="G5" s="87"/>
-      <c r="H5" s="87"/>
-      <c r="I5" s="84" t="s">
+      <c r="E5" s="92"/>
+      <c r="F5" s="92"/>
+      <c r="G5" s="92"/>
+      <c r="H5" s="92"/>
+      <c r="I5" s="89" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="6" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="84"/>
-      <c r="B6" s="91"/>
-      <c r="C6" s="91"/>
-      <c r="D6" s="88"/>
-      <c r="E6" s="89"/>
-      <c r="F6" s="89"/>
-      <c r="G6" s="89"/>
-      <c r="H6" s="89"/>
-      <c r="I6" s="84"/>
+      <c r="A6" s="89"/>
+      <c r="B6" s="96"/>
+      <c r="C6" s="96"/>
+      <c r="D6" s="93"/>
+      <c r="E6" s="94"/>
+      <c r="F6" s="94"/>
+      <c r="G6" s="94"/>
+      <c r="H6" s="94"/>
+      <c r="I6" s="89"/>
     </row>
     <row r="7" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="4">
         <v>1</v>
       </c>
-      <c r="B7" s="103" t="s">
+      <c r="B7" s="97" t="s">
         <v>62</v>
       </c>
       <c r="C7" s="22" t="s">
         <v>63</v>
       </c>
-      <c r="D7" s="34" t="s">
+      <c r="D7" s="44" t="s">
         <v>32</v>
       </c>
-      <c r="E7" s="34"/>
-      <c r="F7" s="34"/>
-      <c r="G7" s="34"/>
-      <c r="H7" s="34"/>
+      <c r="E7" s="44"/>
+      <c r="F7" s="44"/>
+      <c r="G7" s="44"/>
+      <c r="H7" s="44"/>
       <c r="I7" s="22" t="s">
         <v>64</v>
       </c>
@@ -5811,15 +5835,15 @@
       <c r="A8" s="4">
         <v>2</v>
       </c>
-      <c r="B8" s="101"/>
+      <c r="B8" s="98"/>
       <c r="C8" s="22"/>
-      <c r="D8" s="34" t="s">
+      <c r="D8" s="44" t="s">
         <v>65</v>
       </c>
-      <c r="E8" s="34"/>
-      <c r="F8" s="34"/>
-      <c r="G8" s="34"/>
-      <c r="H8" s="34"/>
+      <c r="E8" s="44"/>
+      <c r="F8" s="44"/>
+      <c r="G8" s="44"/>
+      <c r="H8" s="44"/>
       <c r="I8" s="22" t="s">
         <v>66</v>
       </c>
@@ -5828,26 +5852,26 @@
       <c r="A9" s="4">
         <v>3</v>
       </c>
-      <c r="B9" s="101"/>
+      <c r="B9" s="98"/>
       <c r="C9" s="22"/>
-      <c r="D9" s="34"/>
-      <c r="E9" s="34"/>
-      <c r="F9" s="34"/>
-      <c r="G9" s="34"/>
-      <c r="H9" s="34"/>
+      <c r="D9" s="44"/>
+      <c r="E9" s="44"/>
+      <c r="F9" s="44"/>
+      <c r="G9" s="44"/>
+      <c r="H9" s="44"/>
       <c r="I9" s="4"/>
     </row>
     <row r="10" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="4">
         <v>4</v>
       </c>
-      <c r="B10" s="102"/>
+      <c r="B10" s="99"/>
       <c r="C10" s="22"/>
-      <c r="D10" s="34"/>
-      <c r="E10" s="34"/>
-      <c r="F10" s="34"/>
-      <c r="G10" s="34"/>
-      <c r="H10" s="34"/>
+      <c r="D10" s="44"/>
+      <c r="E10" s="44"/>
+      <c r="F10" s="44"/>
+      <c r="G10" s="44"/>
+      <c r="H10" s="44"/>
       <c r="I10" s="4"/>
     </row>
     <row r="11" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -5860,13 +5884,13 @@
       <c r="C11" s="22" t="s">
         <v>68</v>
       </c>
-      <c r="D11" s="34" t="s">
+      <c r="D11" s="44" t="s">
         <v>32</v>
       </c>
-      <c r="E11" s="34"/>
-      <c r="F11" s="34"/>
-      <c r="G11" s="34"/>
-      <c r="H11" s="34"/>
+      <c r="E11" s="44"/>
+      <c r="F11" s="44"/>
+      <c r="G11" s="44"/>
+      <c r="H11" s="44"/>
       <c r="I11" s="22" t="s">
         <v>66</v>
       </c>
@@ -5875,15 +5899,15 @@
       <c r="A12" s="4">
         <v>6</v>
       </c>
-      <c r="B12" s="101"/>
+      <c r="B12" s="98"/>
       <c r="C12" s="4"/>
-      <c r="D12" s="34" t="s">
+      <c r="D12" s="44" t="s">
         <v>69</v>
       </c>
-      <c r="E12" s="34"/>
-      <c r="F12" s="34"/>
-      <c r="G12" s="34"/>
-      <c r="H12" s="34"/>
+      <c r="E12" s="44"/>
+      <c r="F12" s="44"/>
+      <c r="G12" s="44"/>
+      <c r="H12" s="44"/>
       <c r="I12" s="22" t="s">
         <v>64</v>
       </c>
@@ -5892,15 +5916,15 @@
       <c r="A13" s="4">
         <v>7</v>
       </c>
-      <c r="B13" s="101"/>
+      <c r="B13" s="98"/>
       <c r="C13" s="4"/>
-      <c r="D13" s="34" t="s">
+      <c r="D13" s="44" t="s">
         <v>70</v>
       </c>
-      <c r="E13" s="34"/>
-      <c r="F13" s="34"/>
-      <c r="G13" s="34"/>
-      <c r="H13" s="34"/>
+      <c r="E13" s="44"/>
+      <c r="F13" s="44"/>
+      <c r="G13" s="44"/>
+      <c r="H13" s="44"/>
       <c r="I13" s="22" t="s">
         <v>64</v>
       </c>
@@ -5909,13 +5933,13 @@
       <c r="A14" s="4">
         <v>8</v>
       </c>
-      <c r="B14" s="102"/>
+      <c r="B14" s="99"/>
       <c r="C14" s="4"/>
-      <c r="D14" s="34"/>
-      <c r="E14" s="34"/>
-      <c r="F14" s="34"/>
-      <c r="G14" s="34"/>
-      <c r="H14" s="34"/>
+      <c r="D14" s="44"/>
+      <c r="E14" s="44"/>
+      <c r="F14" s="44"/>
+      <c r="G14" s="44"/>
+      <c r="H14" s="44"/>
       <c r="I14" s="4"/>
     </row>
     <row r="15" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -5926,50 +5950,50 @@
         <v>71</v>
       </c>
       <c r="C15" s="4"/>
-      <c r="D15" s="34"/>
-      <c r="E15" s="34"/>
-      <c r="F15" s="34"/>
-      <c r="G15" s="34"/>
-      <c r="H15" s="34"/>
+      <c r="D15" s="44"/>
+      <c r="E15" s="44"/>
+      <c r="F15" s="44"/>
+      <c r="G15" s="44"/>
+      <c r="H15" s="44"/>
       <c r="I15" s="4"/>
     </row>
     <row r="16" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="4">
         <v>10</v>
       </c>
-      <c r="B16" s="101"/>
+      <c r="B16" s="98"/>
       <c r="C16" s="4"/>
-      <c r="D16" s="34"/>
-      <c r="E16" s="34"/>
-      <c r="F16" s="34"/>
-      <c r="G16" s="34"/>
-      <c r="H16" s="34"/>
+      <c r="D16" s="44"/>
+      <c r="E16" s="44"/>
+      <c r="F16" s="44"/>
+      <c r="G16" s="44"/>
+      <c r="H16" s="44"/>
       <c r="I16" s="4"/>
     </row>
     <row r="17" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="4">
         <v>11</v>
       </c>
-      <c r="B17" s="101"/>
+      <c r="B17" s="98"/>
       <c r="C17" s="4"/>
-      <c r="D17" s="34"/>
-      <c r="E17" s="34"/>
-      <c r="F17" s="34"/>
-      <c r="G17" s="34"/>
-      <c r="H17" s="34"/>
+      <c r="D17" s="44"/>
+      <c r="E17" s="44"/>
+      <c r="F17" s="44"/>
+      <c r="G17" s="44"/>
+      <c r="H17" s="44"/>
       <c r="I17" s="4"/>
     </row>
     <row r="18" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="4">
         <v>12</v>
       </c>
-      <c r="B18" s="102"/>
+      <c r="B18" s="99"/>
       <c r="C18" s="4"/>
-      <c r="D18" s="34"/>
-      <c r="E18" s="34"/>
-      <c r="F18" s="34"/>
-      <c r="G18" s="34"/>
-      <c r="H18" s="34"/>
+      <c r="D18" s="44"/>
+      <c r="E18" s="44"/>
+      <c r="F18" s="44"/>
+      <c r="G18" s="44"/>
+      <c r="H18" s="44"/>
       <c r="I18" s="4"/>
     </row>
     <row r="19" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -5980,50 +6004,50 @@
         <v>72</v>
       </c>
       <c r="C19" s="4"/>
-      <c r="D19" s="34"/>
-      <c r="E19" s="34"/>
-      <c r="F19" s="34"/>
-      <c r="G19" s="34"/>
-      <c r="H19" s="34"/>
+      <c r="D19" s="44"/>
+      <c r="E19" s="44"/>
+      <c r="F19" s="44"/>
+      <c r="G19" s="44"/>
+      <c r="H19" s="44"/>
       <c r="I19" s="4"/>
     </row>
     <row r="20" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="4">
         <v>14</v>
       </c>
-      <c r="B20" s="101"/>
+      <c r="B20" s="98"/>
       <c r="C20" s="4"/>
-      <c r="D20" s="34"/>
-      <c r="E20" s="34"/>
-      <c r="F20" s="34"/>
-      <c r="G20" s="34"/>
-      <c r="H20" s="34"/>
+      <c r="D20" s="44"/>
+      <c r="E20" s="44"/>
+      <c r="F20" s="44"/>
+      <c r="G20" s="44"/>
+      <c r="H20" s="44"/>
       <c r="I20" s="4"/>
     </row>
     <row r="21" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="4">
         <v>15</v>
       </c>
-      <c r="B21" s="101"/>
+      <c r="B21" s="98"/>
       <c r="C21" s="4"/>
-      <c r="D21" s="34"/>
-      <c r="E21" s="34"/>
-      <c r="F21" s="34"/>
-      <c r="G21" s="34"/>
-      <c r="H21" s="34"/>
+      <c r="D21" s="44"/>
+      <c r="E21" s="44"/>
+      <c r="F21" s="44"/>
+      <c r="G21" s="44"/>
+      <c r="H21" s="44"/>
       <c r="I21" s="4"/>
     </row>
     <row r="22" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="4">
         <v>16</v>
       </c>
-      <c r="B22" s="102"/>
+      <c r="B22" s="99"/>
       <c r="C22" s="4"/>
-      <c r="D22" s="34"/>
-      <c r="E22" s="34"/>
-      <c r="F22" s="34"/>
-      <c r="G22" s="34"/>
-      <c r="H22" s="34"/>
+      <c r="D22" s="44"/>
+      <c r="E22" s="44"/>
+      <c r="F22" s="44"/>
+      <c r="G22" s="44"/>
+      <c r="H22" s="44"/>
       <c r="I22" s="4"/>
     </row>
     <row r="23" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -6034,50 +6058,50 @@
         <v>73</v>
       </c>
       <c r="C23" s="4"/>
-      <c r="D23" s="34"/>
-      <c r="E23" s="34"/>
-      <c r="F23" s="34"/>
-      <c r="G23" s="34"/>
-      <c r="H23" s="34"/>
+      <c r="D23" s="44"/>
+      <c r="E23" s="44"/>
+      <c r="F23" s="44"/>
+      <c r="G23" s="44"/>
+      <c r="H23" s="44"/>
       <c r="I23" s="4"/>
     </row>
     <row r="24" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" s="4">
         <v>18</v>
       </c>
-      <c r="B24" s="101"/>
+      <c r="B24" s="98"/>
       <c r="C24" s="4"/>
-      <c r="D24" s="34"/>
-      <c r="E24" s="34"/>
-      <c r="F24" s="34"/>
-      <c r="G24" s="34"/>
-      <c r="H24" s="34"/>
+      <c r="D24" s="44"/>
+      <c r="E24" s="44"/>
+      <c r="F24" s="44"/>
+      <c r="G24" s="44"/>
+      <c r="H24" s="44"/>
       <c r="I24" s="4"/>
     </row>
     <row r="25" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A25" s="4">
         <v>19</v>
       </c>
-      <c r="B25" s="101"/>
+      <c r="B25" s="98"/>
       <c r="C25" s="4"/>
-      <c r="D25" s="34"/>
-      <c r="E25" s="34"/>
-      <c r="F25" s="34"/>
-      <c r="G25" s="34"/>
-      <c r="H25" s="34"/>
+      <c r="D25" s="44"/>
+      <c r="E25" s="44"/>
+      <c r="F25" s="44"/>
+      <c r="G25" s="44"/>
+      <c r="H25" s="44"/>
       <c r="I25" s="4"/>
     </row>
     <row r="26" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26" s="4">
         <v>20</v>
       </c>
-      <c r="B26" s="102"/>
+      <c r="B26" s="99"/>
       <c r="C26" s="4"/>
-      <c r="D26" s="34"/>
-      <c r="E26" s="34"/>
-      <c r="F26" s="34"/>
-      <c r="G26" s="34"/>
-      <c r="H26" s="34"/>
+      <c r="D26" s="44"/>
+      <c r="E26" s="44"/>
+      <c r="F26" s="44"/>
+      <c r="G26" s="44"/>
+      <c r="H26" s="44"/>
       <c r="I26" s="4"/>
     </row>
     <row r="27" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -6088,50 +6112,50 @@
         <v>74</v>
       </c>
       <c r="C27" s="4"/>
-      <c r="D27" s="34"/>
-      <c r="E27" s="34"/>
-      <c r="F27" s="34"/>
-      <c r="G27" s="34"/>
-      <c r="H27" s="34"/>
+      <c r="D27" s="44"/>
+      <c r="E27" s="44"/>
+      <c r="F27" s="44"/>
+      <c r="G27" s="44"/>
+      <c r="H27" s="44"/>
       <c r="I27" s="4"/>
     </row>
     <row r="28" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A28" s="4">
         <v>22</v>
       </c>
-      <c r="B28" s="101"/>
+      <c r="B28" s="98"/>
       <c r="C28" s="4"/>
-      <c r="D28" s="34"/>
-      <c r="E28" s="34"/>
-      <c r="F28" s="34"/>
-      <c r="G28" s="34"/>
-      <c r="H28" s="34"/>
+      <c r="D28" s="44"/>
+      <c r="E28" s="44"/>
+      <c r="F28" s="44"/>
+      <c r="G28" s="44"/>
+      <c r="H28" s="44"/>
       <c r="I28" s="4"/>
     </row>
     <row r="29" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A29" s="4">
         <v>23</v>
       </c>
-      <c r="B29" s="101"/>
+      <c r="B29" s="98"/>
       <c r="C29" s="4"/>
-      <c r="D29" s="34"/>
-      <c r="E29" s="34"/>
-      <c r="F29" s="34"/>
-      <c r="G29" s="34"/>
-      <c r="H29" s="34"/>
+      <c r="D29" s="44"/>
+      <c r="E29" s="44"/>
+      <c r="F29" s="44"/>
+      <c r="G29" s="44"/>
+      <c r="H29" s="44"/>
       <c r="I29" s="4"/>
     </row>
     <row r="30" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A30" s="4">
         <v>24</v>
       </c>
-      <c r="B30" s="102"/>
+      <c r="B30" s="99"/>
       <c r="C30" s="4"/>
-      <c r="D30" s="34"/>
-      <c r="E30" s="34"/>
-      <c r="F30" s="34"/>
-      <c r="G30" s="34"/>
-      <c r="H30" s="34"/>
+      <c r="D30" s="44"/>
+      <c r="E30" s="44"/>
+      <c r="F30" s="44"/>
+      <c r="G30" s="44"/>
+      <c r="H30" s="44"/>
       <c r="I30" s="4"/>
     </row>
     <row r="31" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -6140,11 +6164,11 @@
       </c>
       <c r="B31" s="4"/>
       <c r="C31" s="4"/>
-      <c r="D31" s="34"/>
-      <c r="E31" s="34"/>
-      <c r="F31" s="34"/>
-      <c r="G31" s="34"/>
-      <c r="H31" s="34"/>
+      <c r="D31" s="44"/>
+      <c r="E31" s="44"/>
+      <c r="F31" s="44"/>
+      <c r="G31" s="44"/>
+      <c r="H31" s="44"/>
       <c r="I31" s="4"/>
     </row>
     <row r="32" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -6153,11 +6177,11 @@
       </c>
       <c r="B32" s="4"/>
       <c r="C32" s="4"/>
-      <c r="D32" s="34"/>
-      <c r="E32" s="34"/>
-      <c r="F32" s="34"/>
-      <c r="G32" s="34"/>
-      <c r="H32" s="34"/>
+      <c r="D32" s="44"/>
+      <c r="E32" s="44"/>
+      <c r="F32" s="44"/>
+      <c r="G32" s="44"/>
+      <c r="H32" s="44"/>
       <c r="I32" s="4"/>
     </row>
     <row r="33" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -6166,11 +6190,11 @@
       </c>
       <c r="B33" s="4"/>
       <c r="C33" s="4"/>
-      <c r="D33" s="34"/>
-      <c r="E33" s="34"/>
-      <c r="F33" s="34"/>
-      <c r="G33" s="34"/>
-      <c r="H33" s="34"/>
+      <c r="D33" s="44"/>
+      <c r="E33" s="44"/>
+      <c r="F33" s="44"/>
+      <c r="G33" s="44"/>
+      <c r="H33" s="44"/>
       <c r="I33" s="4"/>
     </row>
     <row r="34" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -6179,11 +6203,11 @@
       </c>
       <c r="B34" s="4"/>
       <c r="C34" s="4"/>
-      <c r="D34" s="34"/>
-      <c r="E34" s="34"/>
-      <c r="F34" s="34"/>
-      <c r="G34" s="34"/>
-      <c r="H34" s="34"/>
+      <c r="D34" s="44"/>
+      <c r="E34" s="44"/>
+      <c r="F34" s="44"/>
+      <c r="G34" s="44"/>
+      <c r="H34" s="44"/>
       <c r="I34" s="4"/>
     </row>
     <row r="35" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -6192,11 +6216,11 @@
       </c>
       <c r="B35" s="4"/>
       <c r="C35" s="4"/>
-      <c r="D35" s="34"/>
-      <c r="E35" s="34"/>
-      <c r="F35" s="34"/>
-      <c r="G35" s="34"/>
-      <c r="H35" s="34"/>
+      <c r="D35" s="44"/>
+      <c r="E35" s="44"/>
+      <c r="F35" s="44"/>
+      <c r="G35" s="44"/>
+      <c r="H35" s="44"/>
       <c r="I35" s="4"/>
     </row>
     <row r="36" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -6205,43 +6229,15 @@
       </c>
       <c r="B36" s="4"/>
       <c r="C36" s="4"/>
-      <c r="D36" s="34"/>
-      <c r="E36" s="34"/>
-      <c r="F36" s="34"/>
-      <c r="G36" s="34"/>
-      <c r="H36" s="34"/>
+      <c r="D36" s="44"/>
+      <c r="E36" s="44"/>
+      <c r="F36" s="44"/>
+      <c r="G36" s="44"/>
+      <c r="H36" s="44"/>
       <c r="I36" s="4"/>
     </row>
   </sheetData>
   <mergeCells count="44">
-    <mergeCell ref="B7:B10"/>
-    <mergeCell ref="B15:B18"/>
-    <mergeCell ref="B19:B22"/>
-    <mergeCell ref="B23:B26"/>
-    <mergeCell ref="B27:B30"/>
-    <mergeCell ref="A2:I3"/>
-    <mergeCell ref="A4:B4"/>
-    <mergeCell ref="A5:A6"/>
-    <mergeCell ref="C5:C6"/>
-    <mergeCell ref="B5:B6"/>
-    <mergeCell ref="D5:H6"/>
-    <mergeCell ref="I5:I6"/>
-    <mergeCell ref="D15:H15"/>
-    <mergeCell ref="D16:H16"/>
-    <mergeCell ref="D17:H17"/>
-    <mergeCell ref="D25:H25"/>
-    <mergeCell ref="D26:H26"/>
-    <mergeCell ref="D20:H20"/>
-    <mergeCell ref="D21:H21"/>
-    <mergeCell ref="D22:H22"/>
-    <mergeCell ref="D23:H23"/>
-    <mergeCell ref="D24:H24"/>
-    <mergeCell ref="D36:H36"/>
-    <mergeCell ref="D27:H27"/>
-    <mergeCell ref="D28:H28"/>
-    <mergeCell ref="D29:H29"/>
-    <mergeCell ref="D30:H30"/>
-    <mergeCell ref="D31:H31"/>
     <mergeCell ref="A1:C1"/>
     <mergeCell ref="D32:H32"/>
     <mergeCell ref="D33:H33"/>
@@ -6258,6 +6254,34 @@
     <mergeCell ref="D12:H12"/>
     <mergeCell ref="D13:H13"/>
     <mergeCell ref="D14:H14"/>
+    <mergeCell ref="D36:H36"/>
+    <mergeCell ref="D27:H27"/>
+    <mergeCell ref="D28:H28"/>
+    <mergeCell ref="D29:H29"/>
+    <mergeCell ref="D30:H30"/>
+    <mergeCell ref="D31:H31"/>
+    <mergeCell ref="D15:H15"/>
+    <mergeCell ref="D16:H16"/>
+    <mergeCell ref="D17:H17"/>
+    <mergeCell ref="D25:H25"/>
+    <mergeCell ref="D26:H26"/>
+    <mergeCell ref="D20:H20"/>
+    <mergeCell ref="D21:H21"/>
+    <mergeCell ref="D22:H22"/>
+    <mergeCell ref="D23:H23"/>
+    <mergeCell ref="D24:H24"/>
+    <mergeCell ref="A2:I3"/>
+    <mergeCell ref="A4:B4"/>
+    <mergeCell ref="A5:A6"/>
+    <mergeCell ref="C5:C6"/>
+    <mergeCell ref="B5:B6"/>
+    <mergeCell ref="D5:H6"/>
+    <mergeCell ref="I5:I6"/>
+    <mergeCell ref="B7:B10"/>
+    <mergeCell ref="B15:B18"/>
+    <mergeCell ref="B19:B22"/>
+    <mergeCell ref="B23:B26"/>
+    <mergeCell ref="B27:B30"/>
   </mergeCells>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.75" right="0.75" top="0.6" bottom="0.61" header="0.4" footer="0.39"/>
@@ -6281,23 +6305,23 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:52" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B1" s="104" t="s">
+      <c r="B1" s="191" t="s">
         <v>75</v>
       </c>
-      <c r="C1" s="105"/>
-      <c r="D1" s="105"/>
-      <c r="E1" s="105"/>
-      <c r="F1" s="105"/>
-      <c r="G1" s="105"/>
-      <c r="H1" s="105"/>
-      <c r="I1" s="105"/>
-      <c r="J1" s="105"/>
-      <c r="K1" s="105"/>
-      <c r="L1" s="105"/>
-      <c r="M1" s="105"/>
-      <c r="N1" s="105"/>
-      <c r="O1" s="105"/>
-      <c r="P1" s="105"/>
+      <c r="C1" s="192"/>
+      <c r="D1" s="192"/>
+      <c r="E1" s="192"/>
+      <c r="F1" s="192"/>
+      <c r="G1" s="192"/>
+      <c r="H1" s="192"/>
+      <c r="I1" s="192"/>
+      <c r="J1" s="192"/>
+      <c r="K1" s="192"/>
+      <c r="L1" s="192"/>
+      <c r="M1" s="192"/>
+      <c r="N1" s="192"/>
+      <c r="O1" s="192"/>
+      <c r="P1" s="192"/>
       <c r="Q1" s="21"/>
       <c r="R1" s="20"/>
       <c r="S1" s="20"/>
@@ -6314,139 +6338,139 @@
       <c r="AD1" s="20"/>
     </row>
     <row r="2" spans="2:52" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B2" s="184" t="s">
+      <c r="B2" s="140" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="184"/>
-      <c r="D2" s="184"/>
-      <c r="E2" s="184"/>
-      <c r="F2" s="184"/>
-      <c r="G2" s="184"/>
-      <c r="H2" s="184"/>
-      <c r="I2" s="184"/>
-      <c r="J2" s="113"/>
-      <c r="K2" s="113"/>
-      <c r="L2" s="113"/>
-      <c r="M2" s="113"/>
-      <c r="N2" s="113"/>
-      <c r="O2" s="113"/>
-      <c r="P2" s="113"/>
-      <c r="Q2" s="113"/>
-      <c r="R2" s="113"/>
-      <c r="S2" s="113"/>
-      <c r="T2" s="113"/>
-      <c r="U2" s="113"/>
-      <c r="V2" s="113"/>
-      <c r="W2" s="113"/>
-      <c r="X2" s="113"/>
-      <c r="Y2" s="113"/>
-      <c r="Z2" s="113"/>
-      <c r="AA2" s="113"/>
-      <c r="AB2" s="113"/>
-      <c r="AC2" s="113"/>
-      <c r="AD2" s="113"/>
+      <c r="C2" s="140"/>
+      <c r="D2" s="140"/>
+      <c r="E2" s="140"/>
+      <c r="F2" s="140"/>
+      <c r="G2" s="140"/>
+      <c r="H2" s="140"/>
+      <c r="I2" s="140"/>
+      <c r="J2" s="144"/>
+      <c r="K2" s="144"/>
+      <c r="L2" s="144"/>
+      <c r="M2" s="144"/>
+      <c r="N2" s="144"/>
+      <c r="O2" s="144"/>
+      <c r="P2" s="144"/>
+      <c r="Q2" s="144"/>
+      <c r="R2" s="144"/>
+      <c r="S2" s="144"/>
+      <c r="T2" s="144"/>
+      <c r="U2" s="144"/>
+      <c r="V2" s="144"/>
+      <c r="W2" s="144"/>
+      <c r="X2" s="144"/>
+      <c r="Y2" s="144"/>
+      <c r="Z2" s="144"/>
+      <c r="AA2" s="144"/>
+      <c r="AB2" s="144"/>
+      <c r="AC2" s="144"/>
+      <c r="AD2" s="144"/>
     </row>
     <row r="3" spans="2:52" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="4" spans="2:52" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B4" s="192" t="s">
+      <c r="B4" s="151" t="s">
         <v>76</v>
       </c>
-      <c r="C4" s="182"/>
-      <c r="D4" s="182"/>
-      <c r="E4" s="182"/>
-      <c r="F4" s="182"/>
-      <c r="G4" s="182"/>
-      <c r="H4" s="182"/>
-      <c r="I4" s="182"/>
-      <c r="J4" s="182" t="s">
+      <c r="C4" s="138"/>
+      <c r="D4" s="138"/>
+      <c r="E4" s="138"/>
+      <c r="F4" s="138"/>
+      <c r="G4" s="138"/>
+      <c r="H4" s="138"/>
+      <c r="I4" s="138"/>
+      <c r="J4" s="138" t="s">
         <v>77</v>
       </c>
-      <c r="K4" s="182"/>
-      <c r="L4" s="182"/>
-      <c r="M4" s="182"/>
-      <c r="N4" s="182"/>
-      <c r="O4" s="182"/>
-      <c r="P4" s="182"/>
-      <c r="Q4" s="186" t="s">
+      <c r="K4" s="138"/>
+      <c r="L4" s="138"/>
+      <c r="M4" s="138"/>
+      <c r="N4" s="138"/>
+      <c r="O4" s="138"/>
+      <c r="P4" s="138"/>
+      <c r="Q4" s="145" t="s">
         <v>78</v>
       </c>
-      <c r="R4" s="190"/>
-      <c r="S4" s="187"/>
-      <c r="T4" s="186" t="s">
+      <c r="R4" s="149"/>
+      <c r="S4" s="146"/>
+      <c r="T4" s="145" t="s">
         <v>79</v>
       </c>
-      <c r="U4" s="190"/>
-      <c r="V4" s="190"/>
-      <c r="W4" s="187"/>
-      <c r="X4" s="186" t="s">
+      <c r="U4" s="149"/>
+      <c r="V4" s="149"/>
+      <c r="W4" s="146"/>
+      <c r="X4" s="145" t="s">
         <v>80</v>
       </c>
-      <c r="Y4" s="187"/>
-      <c r="Z4" s="182" t="s">
+      <c r="Y4" s="146"/>
+      <c r="Z4" s="138" t="s">
         <v>81</v>
       </c>
-      <c r="AA4" s="182"/>
-      <c r="AB4" s="182"/>
-      <c r="AC4" s="182" t="s">
+      <c r="AA4" s="138"/>
+      <c r="AB4" s="138"/>
+      <c r="AC4" s="138" t="s">
         <v>81</v>
       </c>
-      <c r="AD4" s="182"/>
-      <c r="AE4" s="182"/>
-      <c r="AF4" s="182" t="s">
+      <c r="AD4" s="138"/>
+      <c r="AE4" s="138"/>
+      <c r="AF4" s="138" t="s">
         <v>81</v>
       </c>
-      <c r="AG4" s="182"/>
-      <c r="AH4" s="182"/>
-      <c r="AI4" s="182" t="s">
+      <c r="AG4" s="138"/>
+      <c r="AH4" s="138"/>
+      <c r="AI4" s="138" t="s">
         <v>81</v>
       </c>
-      <c r="AJ4" s="182"/>
-      <c r="AK4" s="182"/>
-      <c r="AL4" s="182" t="s">
+      <c r="AJ4" s="138"/>
+      <c r="AK4" s="138"/>
+      <c r="AL4" s="138" t="s">
         <v>81</v>
       </c>
-      <c r="AM4" s="182"/>
-      <c r="AN4" s="182"/>
-      <c r="AO4" s="182" t="s">
+      <c r="AM4" s="138"/>
+      <c r="AN4" s="138"/>
+      <c r="AO4" s="138" t="s">
         <v>82</v>
       </c>
-      <c r="AP4" s="182"/>
-      <c r="AQ4" s="182"/>
-      <c r="AR4" s="182"/>
-      <c r="AS4" s="182"/>
-      <c r="AT4" s="182"/>
-      <c r="AU4" s="182"/>
-      <c r="AV4" s="182"/>
-      <c r="AW4" s="182"/>
-      <c r="AX4" s="182"/>
-      <c r="AY4" s="182"/>
-      <c r="AZ4" s="183"/>
+      <c r="AP4" s="138"/>
+      <c r="AQ4" s="138"/>
+      <c r="AR4" s="138"/>
+      <c r="AS4" s="138"/>
+      <c r="AT4" s="138"/>
+      <c r="AU4" s="138"/>
+      <c r="AV4" s="138"/>
+      <c r="AW4" s="138"/>
+      <c r="AX4" s="138"/>
+      <c r="AY4" s="138"/>
+      <c r="AZ4" s="139"/>
     </row>
     <row r="5" spans="2:52" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B5" s="193"/>
-      <c r="C5" s="184"/>
-      <c r="D5" s="184"/>
-      <c r="E5" s="184"/>
-      <c r="F5" s="184"/>
-      <c r="G5" s="184"/>
-      <c r="H5" s="184"/>
-      <c r="I5" s="184"/>
-      <c r="J5" s="184"/>
-      <c r="K5" s="184"/>
-      <c r="L5" s="184"/>
-      <c r="M5" s="184"/>
-      <c r="N5" s="184"/>
-      <c r="O5" s="184"/>
-      <c r="P5" s="184"/>
-      <c r="Q5" s="188"/>
-      <c r="R5" s="191"/>
-      <c r="S5" s="189"/>
-      <c r="T5" s="188"/>
-      <c r="U5" s="191"/>
-      <c r="V5" s="191"/>
-      <c r="W5" s="189"/>
-      <c r="X5" s="188"/>
-      <c r="Y5" s="189"/>
+      <c r="B5" s="152"/>
+      <c r="C5" s="140"/>
+      <c r="D5" s="140"/>
+      <c r="E5" s="140"/>
+      <c r="F5" s="140"/>
+      <c r="G5" s="140"/>
+      <c r="H5" s="140"/>
+      <c r="I5" s="140"/>
+      <c r="J5" s="140"/>
+      <c r="K5" s="140"/>
+      <c r="L5" s="140"/>
+      <c r="M5" s="140"/>
+      <c r="N5" s="140"/>
+      <c r="O5" s="140"/>
+      <c r="P5" s="140"/>
+      <c r="Q5" s="147"/>
+      <c r="R5" s="150"/>
+      <c r="S5" s="148"/>
+      <c r="T5" s="147"/>
+      <c r="U5" s="150"/>
+      <c r="V5" s="150"/>
+      <c r="W5" s="148"/>
+      <c r="X5" s="147"/>
+      <c r="Y5" s="148"/>
       <c r="Z5" s="6" t="s">
         <v>83</v>
       </c>
@@ -6492,54 +6516,54 @@
       <c r="AN5" s="8" t="s">
         <v>85</v>
       </c>
-      <c r="AO5" s="184"/>
-      <c r="AP5" s="184"/>
-      <c r="AQ5" s="184"/>
-      <c r="AR5" s="184"/>
-      <c r="AS5" s="184"/>
-      <c r="AT5" s="184"/>
-      <c r="AU5" s="184"/>
-      <c r="AV5" s="184"/>
-      <c r="AW5" s="184"/>
-      <c r="AX5" s="184"/>
-      <c r="AY5" s="184"/>
-      <c r="AZ5" s="185"/>
+      <c r="AO5" s="140"/>
+      <c r="AP5" s="140"/>
+      <c r="AQ5" s="140"/>
+      <c r="AR5" s="140"/>
+      <c r="AS5" s="140"/>
+      <c r="AT5" s="140"/>
+      <c r="AU5" s="140"/>
+      <c r="AV5" s="140"/>
+      <c r="AW5" s="140"/>
+      <c r="AX5" s="140"/>
+      <c r="AY5" s="140"/>
+      <c r="AZ5" s="141"/>
     </row>
     <row r="6" spans="2:52" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B6" s="110">
+      <c r="B6" s="167">
         <v>1</v>
       </c>
-      <c r="C6" s="106" t="s">
+      <c r="C6" s="153" t="s">
         <v>86</v>
       </c>
-      <c r="D6" s="106"/>
-      <c r="E6" s="106"/>
-      <c r="F6" s="106"/>
-      <c r="G6" s="106"/>
-      <c r="H6" s="106"/>
-      <c r="I6" s="106"/>
-      <c r="J6" s="106"/>
-      <c r="K6" s="106"/>
-      <c r="L6" s="106"/>
-      <c r="M6" s="106"/>
-      <c r="N6" s="106"/>
-      <c r="O6" s="106"/>
-      <c r="P6" s="106"/>
-      <c r="Q6" s="113"/>
-      <c r="R6" s="113"/>
-      <c r="S6" s="113"/>
-      <c r="T6" s="111" t="s">
+      <c r="D6" s="153"/>
+      <c r="E6" s="153"/>
+      <c r="F6" s="153"/>
+      <c r="G6" s="153"/>
+      <c r="H6" s="153"/>
+      <c r="I6" s="153"/>
+      <c r="J6" s="153"/>
+      <c r="K6" s="153"/>
+      <c r="L6" s="153"/>
+      <c r="M6" s="153"/>
+      <c r="N6" s="153"/>
+      <c r="O6" s="153"/>
+      <c r="P6" s="153"/>
+      <c r="Q6" s="144"/>
+      <c r="R6" s="144"/>
+      <c r="S6" s="144"/>
+      <c r="T6" s="158" t="s">
         <v>87</v>
       </c>
-      <c r="U6" s="111"/>
-      <c r="V6" s="108">
+      <c r="U6" s="158"/>
+      <c r="V6" s="156">
         <v>0</v>
       </c>
-      <c r="W6" s="108"/>
-      <c r="X6" s="129">
+      <c r="W6" s="156"/>
+      <c r="X6" s="142">
         <v>0</v>
       </c>
-      <c r="Y6" s="129"/>
+      <c r="Y6" s="142"/>
       <c r="Z6" s="9"/>
       <c r="AA6" s="10"/>
       <c r="AB6" s="11"/>
@@ -6555,50 +6579,50 @@
       <c r="AL6" s="9"/>
       <c r="AM6" s="10"/>
       <c r="AN6" s="11"/>
-      <c r="AO6" s="106"/>
-      <c r="AP6" s="106"/>
-      <c r="AQ6" s="106"/>
-      <c r="AR6" s="106"/>
-      <c r="AS6" s="106"/>
-      <c r="AT6" s="106"/>
-      <c r="AU6" s="106"/>
-      <c r="AV6" s="106"/>
-      <c r="AW6" s="106"/>
-      <c r="AX6" s="106"/>
-      <c r="AY6" s="106"/>
-      <c r="AZ6" s="128"/>
+      <c r="AO6" s="153"/>
+      <c r="AP6" s="153"/>
+      <c r="AQ6" s="153"/>
+      <c r="AR6" s="153"/>
+      <c r="AS6" s="153"/>
+      <c r="AT6" s="153"/>
+      <c r="AU6" s="153"/>
+      <c r="AV6" s="153"/>
+      <c r="AW6" s="153"/>
+      <c r="AX6" s="153"/>
+      <c r="AY6" s="153"/>
+      <c r="AZ6" s="154"/>
     </row>
     <row r="7" spans="2:52" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B7" s="110"/>
-      <c r="C7" s="106"/>
-      <c r="D7" s="106"/>
-      <c r="E7" s="106"/>
-      <c r="F7" s="106"/>
-      <c r="G7" s="106"/>
-      <c r="H7" s="106"/>
-      <c r="I7" s="106"/>
-      <c r="J7" s="106"/>
-      <c r="K7" s="106"/>
-      <c r="L7" s="106"/>
-      <c r="M7" s="106"/>
-      <c r="N7" s="106"/>
-      <c r="O7" s="106"/>
-      <c r="P7" s="106"/>
-      <c r="Q7" s="113"/>
-      <c r="R7" s="113"/>
-      <c r="S7" s="113"/>
-      <c r="T7" s="112" t="s">
+      <c r="B7" s="167"/>
+      <c r="C7" s="153"/>
+      <c r="D7" s="153"/>
+      <c r="E7" s="153"/>
+      <c r="F7" s="153"/>
+      <c r="G7" s="153"/>
+      <c r="H7" s="153"/>
+      <c r="I7" s="153"/>
+      <c r="J7" s="153"/>
+      <c r="K7" s="153"/>
+      <c r="L7" s="153"/>
+      <c r="M7" s="153"/>
+      <c r="N7" s="153"/>
+      <c r="O7" s="153"/>
+      <c r="P7" s="153"/>
+      <c r="Q7" s="144"/>
+      <c r="R7" s="144"/>
+      <c r="S7" s="144"/>
+      <c r="T7" s="155" t="s">
         <v>25</v>
       </c>
-      <c r="U7" s="112"/>
-      <c r="V7" s="109">
+      <c r="U7" s="155"/>
+      <c r="V7" s="157">
         <v>0</v>
       </c>
-      <c r="W7" s="109"/>
-      <c r="X7" s="130">
+      <c r="W7" s="157"/>
+      <c r="X7" s="143">
         <v>0</v>
       </c>
-      <c r="Y7" s="130"/>
+      <c r="Y7" s="143"/>
       <c r="Z7" s="12"/>
       <c r="AA7" s="13"/>
       <c r="AB7" s="14"/>
@@ -6614,54 +6638,54 @@
       <c r="AL7" s="12"/>
       <c r="AM7" s="13"/>
       <c r="AN7" s="14"/>
-      <c r="AO7" s="106"/>
-      <c r="AP7" s="106"/>
-      <c r="AQ7" s="106"/>
-      <c r="AR7" s="106"/>
-      <c r="AS7" s="106"/>
-      <c r="AT7" s="106"/>
-      <c r="AU7" s="106"/>
-      <c r="AV7" s="106"/>
-      <c r="AW7" s="106"/>
-      <c r="AX7" s="106"/>
-      <c r="AY7" s="106"/>
-      <c r="AZ7" s="128"/>
+      <c r="AO7" s="153"/>
+      <c r="AP7" s="153"/>
+      <c r="AQ7" s="153"/>
+      <c r="AR7" s="153"/>
+      <c r="AS7" s="153"/>
+      <c r="AT7" s="153"/>
+      <c r="AU7" s="153"/>
+      <c r="AV7" s="153"/>
+      <c r="AW7" s="153"/>
+      <c r="AX7" s="153"/>
+      <c r="AY7" s="153"/>
+      <c r="AZ7" s="154"/>
     </row>
     <row r="8" spans="2:52" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B8" s="110">
+      <c r="B8" s="167">
         <v>2</v>
       </c>
-      <c r="C8" s="106" t="s">
+      <c r="C8" s="153" t="s">
         <v>88</v>
       </c>
-      <c r="D8" s="106"/>
-      <c r="E8" s="106"/>
-      <c r="F8" s="106"/>
-      <c r="G8" s="106"/>
-      <c r="H8" s="106"/>
-      <c r="I8" s="106"/>
-      <c r="J8" s="114"/>
-      <c r="K8" s="115"/>
-      <c r="L8" s="115"/>
-      <c r="M8" s="115"/>
-      <c r="N8" s="115"/>
-      <c r="O8" s="115"/>
-      <c r="P8" s="116"/>
-      <c r="Q8" s="113"/>
-      <c r="R8" s="113"/>
-      <c r="S8" s="113"/>
-      <c r="T8" s="111" t="s">
+      <c r="D8" s="153"/>
+      <c r="E8" s="153"/>
+      <c r="F8" s="153"/>
+      <c r="G8" s="153"/>
+      <c r="H8" s="153"/>
+      <c r="I8" s="153"/>
+      <c r="J8" s="112"/>
+      <c r="K8" s="113"/>
+      <c r="L8" s="113"/>
+      <c r="M8" s="113"/>
+      <c r="N8" s="113"/>
+      <c r="O8" s="113"/>
+      <c r="P8" s="114"/>
+      <c r="Q8" s="144"/>
+      <c r="R8" s="144"/>
+      <c r="S8" s="144"/>
+      <c r="T8" s="158" t="s">
         <v>87</v>
       </c>
-      <c r="U8" s="111"/>
-      <c r="V8" s="108">
+      <c r="U8" s="158"/>
+      <c r="V8" s="156">
         <v>0</v>
       </c>
-      <c r="W8" s="108"/>
-      <c r="X8" s="129">
+      <c r="W8" s="156"/>
+      <c r="X8" s="142">
         <v>0</v>
       </c>
-      <c r="Y8" s="129"/>
+      <c r="Y8" s="142"/>
       <c r="Z8" s="9"/>
       <c r="AA8" s="10"/>
       <c r="AB8" s="11"/>
@@ -6677,50 +6701,50 @@
       <c r="AL8" s="9"/>
       <c r="AM8" s="10"/>
       <c r="AN8" s="11"/>
-      <c r="AO8" s="106"/>
-      <c r="AP8" s="106"/>
-      <c r="AQ8" s="106"/>
-      <c r="AR8" s="106"/>
-      <c r="AS8" s="106"/>
-      <c r="AT8" s="106"/>
-      <c r="AU8" s="106"/>
-      <c r="AV8" s="106"/>
-      <c r="AW8" s="106"/>
-      <c r="AX8" s="106"/>
-      <c r="AY8" s="106"/>
-      <c r="AZ8" s="128"/>
+      <c r="AO8" s="153"/>
+      <c r="AP8" s="153"/>
+      <c r="AQ8" s="153"/>
+      <c r="AR8" s="153"/>
+      <c r="AS8" s="153"/>
+      <c r="AT8" s="153"/>
+      <c r="AU8" s="153"/>
+      <c r="AV8" s="153"/>
+      <c r="AW8" s="153"/>
+      <c r="AX8" s="153"/>
+      <c r="AY8" s="153"/>
+      <c r="AZ8" s="154"/>
     </row>
     <row r="9" spans="2:52" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B9" s="110"/>
-      <c r="C9" s="106"/>
-      <c r="D9" s="106"/>
-      <c r="E9" s="106"/>
-      <c r="F9" s="106"/>
-      <c r="G9" s="106"/>
-      <c r="H9" s="106"/>
-      <c r="I9" s="106"/>
-      <c r="J9" s="117"/>
-      <c r="K9" s="118"/>
-      <c r="L9" s="118"/>
-      <c r="M9" s="118"/>
-      <c r="N9" s="118"/>
-      <c r="O9" s="118"/>
-      <c r="P9" s="119"/>
-      <c r="Q9" s="113"/>
-      <c r="R9" s="113"/>
-      <c r="S9" s="113"/>
-      <c r="T9" s="112" t="s">
+      <c r="B9" s="167"/>
+      <c r="C9" s="153"/>
+      <c r="D9" s="153"/>
+      <c r="E9" s="153"/>
+      <c r="F9" s="153"/>
+      <c r="G9" s="153"/>
+      <c r="H9" s="153"/>
+      <c r="I9" s="153"/>
+      <c r="J9" s="115"/>
+      <c r="K9" s="116"/>
+      <c r="L9" s="116"/>
+      <c r="M9" s="116"/>
+      <c r="N9" s="116"/>
+      <c r="O9" s="116"/>
+      <c r="P9" s="117"/>
+      <c r="Q9" s="144"/>
+      <c r="R9" s="144"/>
+      <c r="S9" s="144"/>
+      <c r="T9" s="155" t="s">
         <v>25</v>
       </c>
-      <c r="U9" s="112"/>
-      <c r="V9" s="109">
+      <c r="U9" s="155"/>
+      <c r="V9" s="157">
         <v>0</v>
       </c>
-      <c r="W9" s="109"/>
-      <c r="X9" s="130">
+      <c r="W9" s="157"/>
+      <c r="X9" s="143">
         <v>0</v>
       </c>
-      <c r="Y9" s="130"/>
+      <c r="Y9" s="143"/>
       <c r="Z9" s="12"/>
       <c r="AA9" s="13"/>
       <c r="AB9" s="14"/>
@@ -6736,54 +6760,54 @@
       <c r="AL9" s="12"/>
       <c r="AM9" s="13"/>
       <c r="AN9" s="14"/>
-      <c r="AO9" s="106"/>
-      <c r="AP9" s="106"/>
-      <c r="AQ9" s="106"/>
-      <c r="AR9" s="106"/>
-      <c r="AS9" s="106"/>
-      <c r="AT9" s="106"/>
-      <c r="AU9" s="106"/>
-      <c r="AV9" s="106"/>
-      <c r="AW9" s="106"/>
-      <c r="AX9" s="106"/>
-      <c r="AY9" s="106"/>
-      <c r="AZ9" s="128"/>
+      <c r="AO9" s="153"/>
+      <c r="AP9" s="153"/>
+      <c r="AQ9" s="153"/>
+      <c r="AR9" s="153"/>
+      <c r="AS9" s="153"/>
+      <c r="AT9" s="153"/>
+      <c r="AU9" s="153"/>
+      <c r="AV9" s="153"/>
+      <c r="AW9" s="153"/>
+      <c r="AX9" s="153"/>
+      <c r="AY9" s="153"/>
+      <c r="AZ9" s="154"/>
     </row>
     <row r="10" spans="2:52" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B10" s="110">
+      <c r="B10" s="167">
         <v>3</v>
       </c>
-      <c r="C10" s="106" t="s">
+      <c r="C10" s="153" t="s">
         <v>89</v>
       </c>
-      <c r="D10" s="106"/>
-      <c r="E10" s="106"/>
-      <c r="F10" s="106"/>
-      <c r="G10" s="106"/>
-      <c r="H10" s="106"/>
-      <c r="I10" s="106"/>
-      <c r="J10" s="106"/>
-      <c r="K10" s="106"/>
-      <c r="L10" s="106"/>
-      <c r="M10" s="106"/>
-      <c r="N10" s="106"/>
-      <c r="O10" s="106"/>
-      <c r="P10" s="106"/>
-      <c r="Q10" s="113"/>
-      <c r="R10" s="113"/>
-      <c r="S10" s="113"/>
-      <c r="T10" s="111" t="s">
+      <c r="D10" s="153"/>
+      <c r="E10" s="153"/>
+      <c r="F10" s="153"/>
+      <c r="G10" s="153"/>
+      <c r="H10" s="153"/>
+      <c r="I10" s="153"/>
+      <c r="J10" s="153"/>
+      <c r="K10" s="153"/>
+      <c r="L10" s="153"/>
+      <c r="M10" s="153"/>
+      <c r="N10" s="153"/>
+      <c r="O10" s="153"/>
+      <c r="P10" s="153"/>
+      <c r="Q10" s="144"/>
+      <c r="R10" s="144"/>
+      <c r="S10" s="144"/>
+      <c r="T10" s="158" t="s">
         <v>87</v>
       </c>
-      <c r="U10" s="111"/>
-      <c r="V10" s="108">
+      <c r="U10" s="158"/>
+      <c r="V10" s="156">
         <v>0</v>
       </c>
-      <c r="W10" s="108"/>
-      <c r="X10" s="129">
+      <c r="W10" s="156"/>
+      <c r="X10" s="142">
         <v>0</v>
       </c>
-      <c r="Y10" s="129"/>
+      <c r="Y10" s="142"/>
       <c r="Z10" s="9"/>
       <c r="AA10" s="10"/>
       <c r="AB10" s="11"/>
@@ -6799,50 +6823,50 @@
       <c r="AL10" s="9"/>
       <c r="AM10" s="10"/>
       <c r="AN10" s="11"/>
-      <c r="AO10" s="106"/>
-      <c r="AP10" s="106"/>
-      <c r="AQ10" s="106"/>
-      <c r="AR10" s="106"/>
-      <c r="AS10" s="106"/>
-      <c r="AT10" s="106"/>
-      <c r="AU10" s="106"/>
-      <c r="AV10" s="106"/>
-      <c r="AW10" s="106"/>
-      <c r="AX10" s="106"/>
-      <c r="AY10" s="106"/>
-      <c r="AZ10" s="128"/>
+      <c r="AO10" s="153"/>
+      <c r="AP10" s="153"/>
+      <c r="AQ10" s="153"/>
+      <c r="AR10" s="153"/>
+      <c r="AS10" s="153"/>
+      <c r="AT10" s="153"/>
+      <c r="AU10" s="153"/>
+      <c r="AV10" s="153"/>
+      <c r="AW10" s="153"/>
+      <c r="AX10" s="153"/>
+      <c r="AY10" s="153"/>
+      <c r="AZ10" s="154"/>
     </row>
     <row r="11" spans="2:52" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B11" s="110"/>
-      <c r="C11" s="106"/>
-      <c r="D11" s="106"/>
-      <c r="E11" s="106"/>
-      <c r="F11" s="106"/>
-      <c r="G11" s="106"/>
-      <c r="H11" s="106"/>
-      <c r="I11" s="106"/>
-      <c r="J11" s="106"/>
-      <c r="K11" s="106"/>
-      <c r="L11" s="106"/>
-      <c r="M11" s="106"/>
-      <c r="N11" s="106"/>
-      <c r="O11" s="106"/>
-      <c r="P11" s="106"/>
-      <c r="Q11" s="113"/>
-      <c r="R11" s="113"/>
-      <c r="S11" s="113"/>
-      <c r="T11" s="112" t="s">
+      <c r="B11" s="167"/>
+      <c r="C11" s="153"/>
+      <c r="D11" s="153"/>
+      <c r="E11" s="153"/>
+      <c r="F11" s="153"/>
+      <c r="G11" s="153"/>
+      <c r="H11" s="153"/>
+      <c r="I11" s="153"/>
+      <c r="J11" s="153"/>
+      <c r="K11" s="153"/>
+      <c r="L11" s="153"/>
+      <c r="M11" s="153"/>
+      <c r="N11" s="153"/>
+      <c r="O11" s="153"/>
+      <c r="P11" s="153"/>
+      <c r="Q11" s="144"/>
+      <c r="R11" s="144"/>
+      <c r="S11" s="144"/>
+      <c r="T11" s="155" t="s">
         <v>25</v>
       </c>
-      <c r="U11" s="112"/>
-      <c r="V11" s="109">
+      <c r="U11" s="155"/>
+      <c r="V11" s="157">
         <v>0</v>
       </c>
-      <c r="W11" s="109"/>
-      <c r="X11" s="130">
+      <c r="W11" s="157"/>
+      <c r="X11" s="143">
         <v>0</v>
       </c>
-      <c r="Y11" s="130"/>
+      <c r="Y11" s="143"/>
       <c r="Z11" s="12"/>
       <c r="AA11" s="13"/>
       <c r="AB11" s="14"/>
@@ -6858,54 +6882,54 @@
       <c r="AL11" s="12"/>
       <c r="AM11" s="13"/>
       <c r="AN11" s="14"/>
-      <c r="AO11" s="106"/>
-      <c r="AP11" s="106"/>
-      <c r="AQ11" s="106"/>
-      <c r="AR11" s="106"/>
-      <c r="AS11" s="106"/>
-      <c r="AT11" s="106"/>
-      <c r="AU11" s="106"/>
-      <c r="AV11" s="106"/>
-      <c r="AW11" s="106"/>
-      <c r="AX11" s="106"/>
-      <c r="AY11" s="106"/>
-      <c r="AZ11" s="128"/>
+      <c r="AO11" s="153"/>
+      <c r="AP11" s="153"/>
+      <c r="AQ11" s="153"/>
+      <c r="AR11" s="153"/>
+      <c r="AS11" s="153"/>
+      <c r="AT11" s="153"/>
+      <c r="AU11" s="153"/>
+      <c r="AV11" s="153"/>
+      <c r="AW11" s="153"/>
+      <c r="AX11" s="153"/>
+      <c r="AY11" s="153"/>
+      <c r="AZ11" s="154"/>
     </row>
     <row r="12" spans="2:52" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B12" s="110">
+      <c r="B12" s="167">
         <v>4</v>
       </c>
-      <c r="C12" s="106" t="s">
+      <c r="C12" s="153" t="s">
         <v>90</v>
       </c>
-      <c r="D12" s="106"/>
-      <c r="E12" s="106"/>
-      <c r="F12" s="106"/>
-      <c r="G12" s="106"/>
-      <c r="H12" s="106"/>
-      <c r="I12" s="106"/>
-      <c r="J12" s="106"/>
-      <c r="K12" s="106"/>
-      <c r="L12" s="106"/>
-      <c r="M12" s="106"/>
-      <c r="N12" s="106"/>
-      <c r="O12" s="106"/>
-      <c r="P12" s="106"/>
-      <c r="Q12" s="172"/>
-      <c r="R12" s="173"/>
-      <c r="S12" s="174"/>
-      <c r="T12" s="111" t="s">
+      <c r="D12" s="153"/>
+      <c r="E12" s="153"/>
+      <c r="F12" s="153"/>
+      <c r="G12" s="153"/>
+      <c r="H12" s="153"/>
+      <c r="I12" s="153"/>
+      <c r="J12" s="153"/>
+      <c r="K12" s="153"/>
+      <c r="L12" s="153"/>
+      <c r="M12" s="153"/>
+      <c r="N12" s="153"/>
+      <c r="O12" s="153"/>
+      <c r="P12" s="153"/>
+      <c r="Q12" s="118"/>
+      <c r="R12" s="119"/>
+      <c r="S12" s="120"/>
+      <c r="T12" s="158" t="s">
         <v>87</v>
       </c>
-      <c r="U12" s="111"/>
-      <c r="V12" s="108">
+      <c r="U12" s="158"/>
+      <c r="V12" s="156">
         <v>0</v>
       </c>
-      <c r="W12" s="108"/>
-      <c r="X12" s="129">
+      <c r="W12" s="156"/>
+      <c r="X12" s="142">
         <v>0</v>
       </c>
-      <c r="Y12" s="129"/>
+      <c r="Y12" s="142"/>
       <c r="Z12" s="9"/>
       <c r="AA12" s="10"/>
       <c r="AB12" s="11"/>
@@ -6921,50 +6945,50 @@
       <c r="AL12" s="9"/>
       <c r="AM12" s="10"/>
       <c r="AN12" s="11"/>
-      <c r="AO12" s="106"/>
-      <c r="AP12" s="106"/>
-      <c r="AQ12" s="106"/>
-      <c r="AR12" s="106"/>
-      <c r="AS12" s="106"/>
-      <c r="AT12" s="106"/>
-      <c r="AU12" s="106"/>
-      <c r="AV12" s="106"/>
-      <c r="AW12" s="106"/>
-      <c r="AX12" s="106"/>
-      <c r="AY12" s="106"/>
-      <c r="AZ12" s="128"/>
+      <c r="AO12" s="153"/>
+      <c r="AP12" s="153"/>
+      <c r="AQ12" s="153"/>
+      <c r="AR12" s="153"/>
+      <c r="AS12" s="153"/>
+      <c r="AT12" s="153"/>
+      <c r="AU12" s="153"/>
+      <c r="AV12" s="153"/>
+      <c r="AW12" s="153"/>
+      <c r="AX12" s="153"/>
+      <c r="AY12" s="153"/>
+      <c r="AZ12" s="154"/>
     </row>
     <row r="13" spans="2:52" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B13" s="110"/>
-      <c r="C13" s="106"/>
-      <c r="D13" s="106"/>
-      <c r="E13" s="106"/>
-      <c r="F13" s="106"/>
-      <c r="G13" s="106"/>
-      <c r="H13" s="106"/>
-      <c r="I13" s="106"/>
-      <c r="J13" s="106"/>
-      <c r="K13" s="106"/>
-      <c r="L13" s="106"/>
-      <c r="M13" s="106"/>
-      <c r="N13" s="106"/>
-      <c r="O13" s="106"/>
-      <c r="P13" s="106"/>
-      <c r="Q13" s="175"/>
-      <c r="R13" s="176"/>
-      <c r="S13" s="177"/>
-      <c r="T13" s="112" t="s">
+      <c r="B13" s="167"/>
+      <c r="C13" s="153"/>
+      <c r="D13" s="153"/>
+      <c r="E13" s="153"/>
+      <c r="F13" s="153"/>
+      <c r="G13" s="153"/>
+      <c r="H13" s="153"/>
+      <c r="I13" s="153"/>
+      <c r="J13" s="153"/>
+      <c r="K13" s="153"/>
+      <c r="L13" s="153"/>
+      <c r="M13" s="153"/>
+      <c r="N13" s="153"/>
+      <c r="O13" s="153"/>
+      <c r="P13" s="153"/>
+      <c r="Q13" s="121"/>
+      <c r="R13" s="122"/>
+      <c r="S13" s="123"/>
+      <c r="T13" s="155" t="s">
         <v>25</v>
       </c>
-      <c r="U13" s="112"/>
-      <c r="V13" s="109">
+      <c r="U13" s="155"/>
+      <c r="V13" s="157">
         <v>0</v>
       </c>
-      <c r="W13" s="109"/>
-      <c r="X13" s="130">
+      <c r="W13" s="157"/>
+      <c r="X13" s="143">
         <v>0</v>
       </c>
-      <c r="Y13" s="130"/>
+      <c r="Y13" s="143"/>
       <c r="Z13" s="12"/>
       <c r="AA13" s="13"/>
       <c r="AB13" s="14"/>
@@ -6980,54 +7004,54 @@
       <c r="AL13" s="12"/>
       <c r="AM13" s="13"/>
       <c r="AN13" s="14"/>
-      <c r="AO13" s="106"/>
-      <c r="AP13" s="106"/>
-      <c r="AQ13" s="106"/>
-      <c r="AR13" s="106"/>
-      <c r="AS13" s="106"/>
-      <c r="AT13" s="106"/>
-      <c r="AU13" s="106"/>
-      <c r="AV13" s="106"/>
-      <c r="AW13" s="106"/>
-      <c r="AX13" s="106"/>
-      <c r="AY13" s="106"/>
-      <c r="AZ13" s="128"/>
+      <c r="AO13" s="153"/>
+      <c r="AP13" s="153"/>
+      <c r="AQ13" s="153"/>
+      <c r="AR13" s="153"/>
+      <c r="AS13" s="153"/>
+      <c r="AT13" s="153"/>
+      <c r="AU13" s="153"/>
+      <c r="AV13" s="153"/>
+      <c r="AW13" s="153"/>
+      <c r="AX13" s="153"/>
+      <c r="AY13" s="153"/>
+      <c r="AZ13" s="154"/>
     </row>
     <row r="14" spans="2:52" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B14" s="110">
+      <c r="B14" s="167">
         <v>5</v>
       </c>
-      <c r="C14" s="114" t="s">
+      <c r="C14" s="112" t="s">
         <v>91</v>
       </c>
-      <c r="D14" s="115"/>
-      <c r="E14" s="115"/>
-      <c r="F14" s="115"/>
-      <c r="G14" s="115"/>
-      <c r="H14" s="115"/>
-      <c r="I14" s="116"/>
-      <c r="J14" s="107"/>
-      <c r="K14" s="106"/>
-      <c r="L14" s="106"/>
-      <c r="M14" s="106"/>
-      <c r="N14" s="106"/>
-      <c r="O14" s="106"/>
-      <c r="P14" s="106"/>
-      <c r="Q14" s="172"/>
-      <c r="R14" s="173"/>
-      <c r="S14" s="174"/>
-      <c r="T14" s="111" t="s">
+      <c r="D14" s="113"/>
+      <c r="E14" s="113"/>
+      <c r="F14" s="113"/>
+      <c r="G14" s="113"/>
+      <c r="H14" s="113"/>
+      <c r="I14" s="114"/>
+      <c r="J14" s="193"/>
+      <c r="K14" s="153"/>
+      <c r="L14" s="153"/>
+      <c r="M14" s="153"/>
+      <c r="N14" s="153"/>
+      <c r="O14" s="153"/>
+      <c r="P14" s="153"/>
+      <c r="Q14" s="118"/>
+      <c r="R14" s="119"/>
+      <c r="S14" s="120"/>
+      <c r="T14" s="158" t="s">
         <v>87</v>
       </c>
-      <c r="U14" s="111"/>
-      <c r="V14" s="108">
+      <c r="U14" s="158"/>
+      <c r="V14" s="156">
         <v>0</v>
       </c>
-      <c r="W14" s="108"/>
-      <c r="X14" s="129">
+      <c r="W14" s="156"/>
+      <c r="X14" s="142">
         <v>0</v>
       </c>
-      <c r="Y14" s="129"/>
+      <c r="Y14" s="142"/>
       <c r="Z14" s="9"/>
       <c r="AA14" s="10"/>
       <c r="AB14" s="11"/>
@@ -7043,50 +7067,50 @@
       <c r="AL14" s="9"/>
       <c r="AM14" s="10"/>
       <c r="AN14" s="11"/>
-      <c r="AO14" s="106"/>
-      <c r="AP14" s="106"/>
-      <c r="AQ14" s="106"/>
-      <c r="AR14" s="106"/>
-      <c r="AS14" s="106"/>
-      <c r="AT14" s="106"/>
-      <c r="AU14" s="106"/>
-      <c r="AV14" s="106"/>
-      <c r="AW14" s="106"/>
-      <c r="AX14" s="106"/>
-      <c r="AY14" s="106"/>
-      <c r="AZ14" s="128"/>
+      <c r="AO14" s="153"/>
+      <c r="AP14" s="153"/>
+      <c r="AQ14" s="153"/>
+      <c r="AR14" s="153"/>
+      <c r="AS14" s="153"/>
+      <c r="AT14" s="153"/>
+      <c r="AU14" s="153"/>
+      <c r="AV14" s="153"/>
+      <c r="AW14" s="153"/>
+      <c r="AX14" s="153"/>
+      <c r="AY14" s="153"/>
+      <c r="AZ14" s="154"/>
     </row>
     <row r="15" spans="2:52" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B15" s="110"/>
-      <c r="C15" s="117"/>
-      <c r="D15" s="118"/>
-      <c r="E15" s="118"/>
-      <c r="F15" s="118"/>
-      <c r="G15" s="118"/>
-      <c r="H15" s="118"/>
-      <c r="I15" s="119"/>
-      <c r="J15" s="106"/>
-      <c r="K15" s="106"/>
-      <c r="L15" s="106"/>
-      <c r="M15" s="106"/>
-      <c r="N15" s="106"/>
-      <c r="O15" s="106"/>
-      <c r="P15" s="106"/>
-      <c r="Q15" s="175"/>
-      <c r="R15" s="176"/>
-      <c r="S15" s="177"/>
-      <c r="T15" s="112" t="s">
+      <c r="B15" s="167"/>
+      <c r="C15" s="115"/>
+      <c r="D15" s="116"/>
+      <c r="E15" s="116"/>
+      <c r="F15" s="116"/>
+      <c r="G15" s="116"/>
+      <c r="H15" s="116"/>
+      <c r="I15" s="117"/>
+      <c r="J15" s="153"/>
+      <c r="K15" s="153"/>
+      <c r="L15" s="153"/>
+      <c r="M15" s="153"/>
+      <c r="N15" s="153"/>
+      <c r="O15" s="153"/>
+      <c r="P15" s="153"/>
+      <c r="Q15" s="121"/>
+      <c r="R15" s="122"/>
+      <c r="S15" s="123"/>
+      <c r="T15" s="155" t="s">
         <v>25</v>
       </c>
-      <c r="U15" s="112"/>
-      <c r="V15" s="109">
+      <c r="U15" s="155"/>
+      <c r="V15" s="157">
         <v>0</v>
       </c>
-      <c r="W15" s="109"/>
-      <c r="X15" s="130">
+      <c r="W15" s="157"/>
+      <c r="X15" s="143">
         <v>0</v>
       </c>
-      <c r="Y15" s="130"/>
+      <c r="Y15" s="143"/>
       <c r="Z15" s="12"/>
       <c r="AA15" s="13"/>
       <c r="AB15" s="14"/>
@@ -7102,54 +7126,54 @@
       <c r="AL15" s="12"/>
       <c r="AM15" s="13"/>
       <c r="AN15" s="14"/>
-      <c r="AO15" s="106"/>
-      <c r="AP15" s="106"/>
-      <c r="AQ15" s="106"/>
-      <c r="AR15" s="106"/>
-      <c r="AS15" s="106"/>
-      <c r="AT15" s="106"/>
-      <c r="AU15" s="106"/>
-      <c r="AV15" s="106"/>
-      <c r="AW15" s="106"/>
-      <c r="AX15" s="106"/>
-      <c r="AY15" s="106"/>
-      <c r="AZ15" s="128"/>
+      <c r="AO15" s="153"/>
+      <c r="AP15" s="153"/>
+      <c r="AQ15" s="153"/>
+      <c r="AR15" s="153"/>
+      <c r="AS15" s="153"/>
+      <c r="AT15" s="153"/>
+      <c r="AU15" s="153"/>
+      <c r="AV15" s="153"/>
+      <c r="AW15" s="153"/>
+      <c r="AX15" s="153"/>
+      <c r="AY15" s="153"/>
+      <c r="AZ15" s="154"/>
     </row>
     <row r="16" spans="2:52" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B16" s="110">
+      <c r="B16" s="167">
         <v>6</v>
       </c>
-      <c r="C16" s="114" t="s">
+      <c r="C16" s="112" t="s">
         <v>92</v>
       </c>
-      <c r="D16" s="115"/>
-      <c r="E16" s="115"/>
-      <c r="F16" s="115"/>
-      <c r="G16" s="115"/>
-      <c r="H16" s="115"/>
-      <c r="I16" s="116"/>
-      <c r="J16" s="107"/>
-      <c r="K16" s="106"/>
-      <c r="L16" s="106"/>
-      <c r="M16" s="106"/>
-      <c r="N16" s="106"/>
-      <c r="O16" s="106"/>
-      <c r="P16" s="106"/>
-      <c r="Q16" s="113"/>
-      <c r="R16" s="113"/>
-      <c r="S16" s="113"/>
-      <c r="T16" s="111" t="s">
+      <c r="D16" s="113"/>
+      <c r="E16" s="113"/>
+      <c r="F16" s="113"/>
+      <c r="G16" s="113"/>
+      <c r="H16" s="113"/>
+      <c r="I16" s="114"/>
+      <c r="J16" s="193"/>
+      <c r="K16" s="153"/>
+      <c r="L16" s="153"/>
+      <c r="M16" s="153"/>
+      <c r="N16" s="153"/>
+      <c r="O16" s="153"/>
+      <c r="P16" s="153"/>
+      <c r="Q16" s="144"/>
+      <c r="R16" s="144"/>
+      <c r="S16" s="144"/>
+      <c r="T16" s="158" t="s">
         <v>87</v>
       </c>
-      <c r="U16" s="111"/>
-      <c r="V16" s="108">
+      <c r="U16" s="158"/>
+      <c r="V16" s="156">
         <v>0</v>
       </c>
-      <c r="W16" s="108"/>
-      <c r="X16" s="129">
+      <c r="W16" s="156"/>
+      <c r="X16" s="142">
         <v>0</v>
       </c>
-      <c r="Y16" s="129"/>
+      <c r="Y16" s="142"/>
       <c r="Z16" s="9"/>
       <c r="AA16" s="10"/>
       <c r="AB16" s="11"/>
@@ -7165,50 +7189,50 @@
       <c r="AL16" s="9"/>
       <c r="AM16" s="10"/>
       <c r="AN16" s="11"/>
-      <c r="AO16" s="106"/>
-      <c r="AP16" s="106"/>
-      <c r="AQ16" s="106"/>
-      <c r="AR16" s="106"/>
-      <c r="AS16" s="106"/>
-      <c r="AT16" s="106"/>
-      <c r="AU16" s="106"/>
-      <c r="AV16" s="106"/>
-      <c r="AW16" s="106"/>
-      <c r="AX16" s="106"/>
-      <c r="AY16" s="106"/>
-      <c r="AZ16" s="128"/>
+      <c r="AO16" s="153"/>
+      <c r="AP16" s="153"/>
+      <c r="AQ16" s="153"/>
+      <c r="AR16" s="153"/>
+      <c r="AS16" s="153"/>
+      <c r="AT16" s="153"/>
+      <c r="AU16" s="153"/>
+      <c r="AV16" s="153"/>
+      <c r="AW16" s="153"/>
+      <c r="AX16" s="153"/>
+      <c r="AY16" s="153"/>
+      <c r="AZ16" s="154"/>
     </row>
     <row r="17" spans="2:52" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B17" s="110"/>
-      <c r="C17" s="117"/>
-      <c r="D17" s="118"/>
-      <c r="E17" s="118"/>
-      <c r="F17" s="118"/>
-      <c r="G17" s="118"/>
-      <c r="H17" s="118"/>
-      <c r="I17" s="119"/>
-      <c r="J17" s="106"/>
-      <c r="K17" s="106"/>
-      <c r="L17" s="106"/>
-      <c r="M17" s="106"/>
-      <c r="N17" s="106"/>
-      <c r="O17" s="106"/>
-      <c r="P17" s="106"/>
-      <c r="Q17" s="113"/>
-      <c r="R17" s="113"/>
-      <c r="S17" s="113"/>
-      <c r="T17" s="112" t="s">
+      <c r="B17" s="167"/>
+      <c r="C17" s="115"/>
+      <c r="D17" s="116"/>
+      <c r="E17" s="116"/>
+      <c r="F17" s="116"/>
+      <c r="G17" s="116"/>
+      <c r="H17" s="116"/>
+      <c r="I17" s="117"/>
+      <c r="J17" s="153"/>
+      <c r="K17" s="153"/>
+      <c r="L17" s="153"/>
+      <c r="M17" s="153"/>
+      <c r="N17" s="153"/>
+      <c r="O17" s="153"/>
+      <c r="P17" s="153"/>
+      <c r="Q17" s="144"/>
+      <c r="R17" s="144"/>
+      <c r="S17" s="144"/>
+      <c r="T17" s="155" t="s">
         <v>25</v>
       </c>
-      <c r="U17" s="112"/>
-      <c r="V17" s="109">
+      <c r="U17" s="155"/>
+      <c r="V17" s="157">
         <v>0</v>
       </c>
-      <c r="W17" s="109"/>
-      <c r="X17" s="130">
+      <c r="W17" s="157"/>
+      <c r="X17" s="143">
         <v>0</v>
       </c>
-      <c r="Y17" s="130"/>
+      <c r="Y17" s="143"/>
       <c r="Z17" s="12"/>
       <c r="AA17" s="13"/>
       <c r="AB17" s="14"/>
@@ -7224,54 +7248,54 @@
       <c r="AL17" s="12"/>
       <c r="AM17" s="13"/>
       <c r="AN17" s="14"/>
-      <c r="AO17" s="106"/>
-      <c r="AP17" s="106"/>
-      <c r="AQ17" s="106"/>
-      <c r="AR17" s="106"/>
-      <c r="AS17" s="106"/>
-      <c r="AT17" s="106"/>
-      <c r="AU17" s="106"/>
-      <c r="AV17" s="106"/>
-      <c r="AW17" s="106"/>
-      <c r="AX17" s="106"/>
-      <c r="AY17" s="106"/>
-      <c r="AZ17" s="128"/>
+      <c r="AO17" s="153"/>
+      <c r="AP17" s="153"/>
+      <c r="AQ17" s="153"/>
+      <c r="AR17" s="153"/>
+      <c r="AS17" s="153"/>
+      <c r="AT17" s="153"/>
+      <c r="AU17" s="153"/>
+      <c r="AV17" s="153"/>
+      <c r="AW17" s="153"/>
+      <c r="AX17" s="153"/>
+      <c r="AY17" s="153"/>
+      <c r="AZ17" s="154"/>
     </row>
     <row r="18" spans="2:52" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B18" s="126">
+      <c r="B18" s="104">
         <v>7</v>
       </c>
-      <c r="C18" s="159" t="s">
+      <c r="C18" s="106" t="s">
         <v>93</v>
       </c>
-      <c r="D18" s="160"/>
-      <c r="E18" s="160"/>
-      <c r="F18" s="160"/>
-      <c r="G18" s="160"/>
-      <c r="H18" s="160"/>
-      <c r="I18" s="161"/>
-      <c r="J18" s="114"/>
-      <c r="K18" s="115"/>
-      <c r="L18" s="115"/>
-      <c r="M18" s="115"/>
-      <c r="N18" s="115"/>
-      <c r="O18" s="115"/>
-      <c r="P18" s="116"/>
-      <c r="Q18" s="172"/>
-      <c r="R18" s="173"/>
-      <c r="S18" s="174"/>
-      <c r="T18" s="162" t="s">
+      <c r="D18" s="107"/>
+      <c r="E18" s="107"/>
+      <c r="F18" s="107"/>
+      <c r="G18" s="107"/>
+      <c r="H18" s="107"/>
+      <c r="I18" s="108"/>
+      <c r="J18" s="112"/>
+      <c r="K18" s="113"/>
+      <c r="L18" s="113"/>
+      <c r="M18" s="113"/>
+      <c r="N18" s="113"/>
+      <c r="O18" s="113"/>
+      <c r="P18" s="114"/>
+      <c r="Q18" s="118"/>
+      <c r="R18" s="119"/>
+      <c r="S18" s="120"/>
+      <c r="T18" s="124" t="s">
         <v>87</v>
       </c>
-      <c r="U18" s="163"/>
-      <c r="V18" s="122">
+      <c r="U18" s="125"/>
+      <c r="V18" s="126">
         <v>0</v>
       </c>
-      <c r="W18" s="123"/>
-      <c r="X18" s="168">
+      <c r="W18" s="127"/>
+      <c r="X18" s="128">
         <v>0</v>
       </c>
-      <c r="Y18" s="169"/>
+      <c r="Y18" s="129"/>
       <c r="Z18" s="9"/>
       <c r="AA18" s="10"/>
       <c r="AB18" s="11"/>
@@ -7287,50 +7311,50 @@
       <c r="AL18" s="9"/>
       <c r="AM18" s="10"/>
       <c r="AN18" s="11"/>
-      <c r="AO18" s="114"/>
-      <c r="AP18" s="115"/>
-      <c r="AQ18" s="115"/>
-      <c r="AR18" s="115"/>
-      <c r="AS18" s="115"/>
-      <c r="AT18" s="115"/>
-      <c r="AU18" s="115"/>
-      <c r="AV18" s="115"/>
-      <c r="AW18" s="115"/>
-      <c r="AX18" s="115"/>
-      <c r="AY18" s="115"/>
-      <c r="AZ18" s="164"/>
+      <c r="AO18" s="112"/>
+      <c r="AP18" s="113"/>
+      <c r="AQ18" s="113"/>
+      <c r="AR18" s="113"/>
+      <c r="AS18" s="113"/>
+      <c r="AT18" s="113"/>
+      <c r="AU18" s="113"/>
+      <c r="AV18" s="113"/>
+      <c r="AW18" s="113"/>
+      <c r="AX18" s="113"/>
+      <c r="AY18" s="113"/>
+      <c r="AZ18" s="130"/>
     </row>
     <row r="19" spans="2:52" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B19" s="127"/>
-      <c r="C19" s="144"/>
-      <c r="D19" s="145"/>
-      <c r="E19" s="145"/>
-      <c r="F19" s="145"/>
-      <c r="G19" s="145"/>
-      <c r="H19" s="145"/>
-      <c r="I19" s="146"/>
-      <c r="J19" s="117"/>
-      <c r="K19" s="118"/>
-      <c r="L19" s="118"/>
-      <c r="M19" s="118"/>
-      <c r="N19" s="118"/>
-      <c r="O19" s="118"/>
-      <c r="P19" s="119"/>
-      <c r="Q19" s="175"/>
-      <c r="R19" s="176"/>
-      <c r="S19" s="177"/>
-      <c r="T19" s="166" t="s">
+      <c r="B19" s="105"/>
+      <c r="C19" s="109"/>
+      <c r="D19" s="110"/>
+      <c r="E19" s="110"/>
+      <c r="F19" s="110"/>
+      <c r="G19" s="110"/>
+      <c r="H19" s="110"/>
+      <c r="I19" s="111"/>
+      <c r="J19" s="115"/>
+      <c r="K19" s="116"/>
+      <c r="L19" s="116"/>
+      <c r="M19" s="116"/>
+      <c r="N19" s="116"/>
+      <c r="O19" s="116"/>
+      <c r="P19" s="117"/>
+      <c r="Q19" s="121"/>
+      <c r="R19" s="122"/>
+      <c r="S19" s="123"/>
+      <c r="T19" s="132" t="s">
         <v>25</v>
       </c>
-      <c r="U19" s="167"/>
-      <c r="V19" s="124">
+      <c r="U19" s="133"/>
+      <c r="V19" s="134">
         <v>0</v>
       </c>
-      <c r="W19" s="125"/>
-      <c r="X19" s="170">
+      <c r="W19" s="135"/>
+      <c r="X19" s="136">
         <v>0</v>
       </c>
-      <c r="Y19" s="171"/>
+      <c r="Y19" s="137"/>
       <c r="Z19" s="12"/>
       <c r="AA19" s="13"/>
       <c r="AB19" s="14"/>
@@ -7346,54 +7370,54 @@
       <c r="AL19" s="12"/>
       <c r="AM19" s="13"/>
       <c r="AN19" s="14"/>
-      <c r="AO19" s="117"/>
-      <c r="AP19" s="118"/>
-      <c r="AQ19" s="118"/>
-      <c r="AR19" s="118"/>
-      <c r="AS19" s="118"/>
-      <c r="AT19" s="118"/>
-      <c r="AU19" s="118"/>
-      <c r="AV19" s="118"/>
-      <c r="AW19" s="118"/>
-      <c r="AX19" s="118"/>
-      <c r="AY19" s="118"/>
-      <c r="AZ19" s="165"/>
+      <c r="AO19" s="115"/>
+      <c r="AP19" s="116"/>
+      <c r="AQ19" s="116"/>
+      <c r="AR19" s="116"/>
+      <c r="AS19" s="116"/>
+      <c r="AT19" s="116"/>
+      <c r="AU19" s="116"/>
+      <c r="AV19" s="116"/>
+      <c r="AW19" s="116"/>
+      <c r="AX19" s="116"/>
+      <c r="AY19" s="116"/>
+      <c r="AZ19" s="131"/>
     </row>
     <row r="20" spans="2:52" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B20" s="126">
+      <c r="B20" s="104">
         <v>8</v>
       </c>
-      <c r="C20" s="159" t="s">
+      <c r="C20" s="106" t="s">
         <v>94</v>
       </c>
-      <c r="D20" s="160"/>
-      <c r="E20" s="160"/>
-      <c r="F20" s="160"/>
-      <c r="G20" s="160"/>
-      <c r="H20" s="160"/>
-      <c r="I20" s="161"/>
-      <c r="J20" s="114"/>
-      <c r="K20" s="115"/>
-      <c r="L20" s="115"/>
-      <c r="M20" s="115"/>
-      <c r="N20" s="115"/>
-      <c r="O20" s="115"/>
-      <c r="P20" s="116"/>
-      <c r="Q20" s="172"/>
-      <c r="R20" s="173"/>
-      <c r="S20" s="174"/>
-      <c r="T20" s="162" t="s">
+      <c r="D20" s="107"/>
+      <c r="E20" s="107"/>
+      <c r="F20" s="107"/>
+      <c r="G20" s="107"/>
+      <c r="H20" s="107"/>
+      <c r="I20" s="108"/>
+      <c r="J20" s="112"/>
+      <c r="K20" s="113"/>
+      <c r="L20" s="113"/>
+      <c r="M20" s="113"/>
+      <c r="N20" s="113"/>
+      <c r="O20" s="113"/>
+      <c r="P20" s="114"/>
+      <c r="Q20" s="118"/>
+      <c r="R20" s="119"/>
+      <c r="S20" s="120"/>
+      <c r="T20" s="124" t="s">
         <v>87</v>
       </c>
-      <c r="U20" s="163"/>
-      <c r="V20" s="122">
+      <c r="U20" s="125"/>
+      <c r="V20" s="126">
         <v>0</v>
       </c>
-      <c r="W20" s="123"/>
-      <c r="X20" s="168">
+      <c r="W20" s="127"/>
+      <c r="X20" s="128">
         <v>0</v>
       </c>
-      <c r="Y20" s="169"/>
+      <c r="Y20" s="129"/>
       <c r="Z20" s="9"/>
       <c r="AA20" s="10"/>
       <c r="AB20" s="11"/>
@@ -7409,50 +7433,50 @@
       <c r="AL20" s="9"/>
       <c r="AM20" s="10"/>
       <c r="AN20" s="11"/>
-      <c r="AO20" s="114"/>
-      <c r="AP20" s="115"/>
-      <c r="AQ20" s="115"/>
-      <c r="AR20" s="115"/>
-      <c r="AS20" s="115"/>
-      <c r="AT20" s="115"/>
-      <c r="AU20" s="115"/>
-      <c r="AV20" s="115"/>
-      <c r="AW20" s="115"/>
-      <c r="AX20" s="115"/>
-      <c r="AY20" s="115"/>
-      <c r="AZ20" s="164"/>
+      <c r="AO20" s="112"/>
+      <c r="AP20" s="113"/>
+      <c r="AQ20" s="113"/>
+      <c r="AR20" s="113"/>
+      <c r="AS20" s="113"/>
+      <c r="AT20" s="113"/>
+      <c r="AU20" s="113"/>
+      <c r="AV20" s="113"/>
+      <c r="AW20" s="113"/>
+      <c r="AX20" s="113"/>
+      <c r="AY20" s="113"/>
+      <c r="AZ20" s="130"/>
     </row>
     <row r="21" spans="2:52" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B21" s="127"/>
-      <c r="C21" s="144"/>
-      <c r="D21" s="145"/>
-      <c r="E21" s="145"/>
-      <c r="F21" s="145"/>
-      <c r="G21" s="145"/>
-      <c r="H21" s="145"/>
-      <c r="I21" s="146"/>
-      <c r="J21" s="117"/>
-      <c r="K21" s="118"/>
-      <c r="L21" s="118"/>
-      <c r="M21" s="118"/>
-      <c r="N21" s="118"/>
-      <c r="O21" s="118"/>
-      <c r="P21" s="119"/>
-      <c r="Q21" s="175"/>
-      <c r="R21" s="176"/>
-      <c r="S21" s="177"/>
-      <c r="T21" s="166" t="s">
+      <c r="B21" s="105"/>
+      <c r="C21" s="109"/>
+      <c r="D21" s="110"/>
+      <c r="E21" s="110"/>
+      <c r="F21" s="110"/>
+      <c r="G21" s="110"/>
+      <c r="H21" s="110"/>
+      <c r="I21" s="111"/>
+      <c r="J21" s="115"/>
+      <c r="K21" s="116"/>
+      <c r="L21" s="116"/>
+      <c r="M21" s="116"/>
+      <c r="N21" s="116"/>
+      <c r="O21" s="116"/>
+      <c r="P21" s="117"/>
+      <c r="Q21" s="121"/>
+      <c r="R21" s="122"/>
+      <c r="S21" s="123"/>
+      <c r="T21" s="132" t="s">
         <v>25</v>
       </c>
-      <c r="U21" s="167"/>
-      <c r="V21" s="124">
+      <c r="U21" s="133"/>
+      <c r="V21" s="134">
         <v>0</v>
       </c>
-      <c r="W21" s="125"/>
-      <c r="X21" s="170">
+      <c r="W21" s="135"/>
+      <c r="X21" s="136">
         <v>0</v>
       </c>
-      <c r="Y21" s="171"/>
+      <c r="Y21" s="137"/>
       <c r="Z21" s="12"/>
       <c r="AA21" s="13"/>
       <c r="AB21" s="14"/>
@@ -7468,54 +7492,54 @@
       <c r="AL21" s="12"/>
       <c r="AM21" s="13"/>
       <c r="AN21" s="14"/>
-      <c r="AO21" s="117"/>
-      <c r="AP21" s="118"/>
-      <c r="AQ21" s="118"/>
-      <c r="AR21" s="118"/>
-      <c r="AS21" s="118"/>
-      <c r="AT21" s="118"/>
-      <c r="AU21" s="118"/>
-      <c r="AV21" s="118"/>
-      <c r="AW21" s="118"/>
-      <c r="AX21" s="118"/>
-      <c r="AY21" s="118"/>
-      <c r="AZ21" s="165"/>
+      <c r="AO21" s="115"/>
+      <c r="AP21" s="116"/>
+      <c r="AQ21" s="116"/>
+      <c r="AR21" s="116"/>
+      <c r="AS21" s="116"/>
+      <c r="AT21" s="116"/>
+      <c r="AU21" s="116"/>
+      <c r="AV21" s="116"/>
+      <c r="AW21" s="116"/>
+      <c r="AX21" s="116"/>
+      <c r="AY21" s="116"/>
+      <c r="AZ21" s="131"/>
     </row>
     <row r="22" spans="2:52" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B22" s="139">
+      <c r="B22" s="174">
         <v>9</v>
       </c>
-      <c r="C22" s="141" t="s">
+      <c r="C22" s="176" t="s">
         <v>95</v>
       </c>
-      <c r="D22" s="142"/>
-      <c r="E22" s="142"/>
-      <c r="F22" s="142"/>
-      <c r="G22" s="142"/>
-      <c r="H22" s="142"/>
-      <c r="I22" s="143"/>
-      <c r="J22" s="131"/>
-      <c r="K22" s="132"/>
-      <c r="L22" s="132"/>
-      <c r="M22" s="132"/>
-      <c r="N22" s="132"/>
-      <c r="O22" s="132"/>
-      <c r="P22" s="180"/>
-      <c r="Q22" s="151"/>
-      <c r="R22" s="152"/>
-      <c r="S22" s="153"/>
-      <c r="T22" s="147" t="s">
+      <c r="D22" s="177"/>
+      <c r="E22" s="177"/>
+      <c r="F22" s="177"/>
+      <c r="G22" s="177"/>
+      <c r="H22" s="177"/>
+      <c r="I22" s="178"/>
+      <c r="J22" s="161"/>
+      <c r="K22" s="162"/>
+      <c r="L22" s="162"/>
+      <c r="M22" s="162"/>
+      <c r="N22" s="162"/>
+      <c r="O22" s="162"/>
+      <c r="P22" s="163"/>
+      <c r="Q22" s="183"/>
+      <c r="R22" s="184"/>
+      <c r="S22" s="185"/>
+      <c r="T22" s="179" t="s">
         <v>87</v>
       </c>
-      <c r="U22" s="148"/>
-      <c r="V22" s="178">
+      <c r="U22" s="180"/>
+      <c r="V22" s="159">
         <v>0</v>
       </c>
-      <c r="W22" s="179"/>
-      <c r="X22" s="137">
+      <c r="W22" s="160"/>
+      <c r="X22" s="172">
         <v>0</v>
       </c>
-      <c r="Y22" s="138"/>
+      <c r="Y22" s="173"/>
       <c r="Z22" s="24"/>
       <c r="AA22" s="25"/>
       <c r="AB22" s="26"/>
@@ -7531,50 +7555,50 @@
       <c r="AL22" s="24"/>
       <c r="AM22" s="25"/>
       <c r="AN22" s="26"/>
-      <c r="AO22" s="131"/>
-      <c r="AP22" s="132"/>
-      <c r="AQ22" s="132"/>
-      <c r="AR22" s="132"/>
-      <c r="AS22" s="132"/>
-      <c r="AT22" s="132"/>
-      <c r="AU22" s="132"/>
-      <c r="AV22" s="132"/>
-      <c r="AW22" s="132"/>
-      <c r="AX22" s="132"/>
-      <c r="AY22" s="132"/>
-      <c r="AZ22" s="133"/>
+      <c r="AO22" s="161"/>
+      <c r="AP22" s="162"/>
+      <c r="AQ22" s="162"/>
+      <c r="AR22" s="162"/>
+      <c r="AS22" s="162"/>
+      <c r="AT22" s="162"/>
+      <c r="AU22" s="162"/>
+      <c r="AV22" s="162"/>
+      <c r="AW22" s="162"/>
+      <c r="AX22" s="162"/>
+      <c r="AY22" s="162"/>
+      <c r="AZ22" s="170"/>
     </row>
     <row r="23" spans="2:52" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B23" s="140"/>
-      <c r="C23" s="144"/>
-      <c r="D23" s="145"/>
-      <c r="E23" s="145"/>
-      <c r="F23" s="145"/>
-      <c r="G23" s="145"/>
-      <c r="H23" s="145"/>
-      <c r="I23" s="146"/>
-      <c r="J23" s="134"/>
-      <c r="K23" s="135"/>
-      <c r="L23" s="135"/>
-      <c r="M23" s="135"/>
-      <c r="N23" s="135"/>
-      <c r="O23" s="135"/>
-      <c r="P23" s="181"/>
-      <c r="Q23" s="154"/>
-      <c r="R23" s="155"/>
-      <c r="S23" s="156"/>
-      <c r="T23" s="149" t="s">
+      <c r="B23" s="175"/>
+      <c r="C23" s="109"/>
+      <c r="D23" s="110"/>
+      <c r="E23" s="110"/>
+      <c r="F23" s="110"/>
+      <c r="G23" s="110"/>
+      <c r="H23" s="110"/>
+      <c r="I23" s="111"/>
+      <c r="J23" s="164"/>
+      <c r="K23" s="165"/>
+      <c r="L23" s="165"/>
+      <c r="M23" s="165"/>
+      <c r="N23" s="165"/>
+      <c r="O23" s="165"/>
+      <c r="P23" s="166"/>
+      <c r="Q23" s="186"/>
+      <c r="R23" s="187"/>
+      <c r="S23" s="188"/>
+      <c r="T23" s="181" t="s">
         <v>25</v>
       </c>
-      <c r="U23" s="150"/>
-      <c r="V23" s="120">
+      <c r="U23" s="182"/>
+      <c r="V23" s="168">
         <v>0</v>
       </c>
-      <c r="W23" s="121"/>
-      <c r="X23" s="157">
+      <c r="W23" s="169"/>
+      <c r="X23" s="189">
         <v>0</v>
       </c>
-      <c r="Y23" s="158"/>
+      <c r="Y23" s="190"/>
       <c r="Z23" s="15"/>
       <c r="AA23" s="16"/>
       <c r="AB23" s="17"/>
@@ -7590,18 +7614,18 @@
       <c r="AL23" s="15"/>
       <c r="AM23" s="16"/>
       <c r="AN23" s="17"/>
-      <c r="AO23" s="134"/>
-      <c r="AP23" s="135"/>
-      <c r="AQ23" s="135"/>
-      <c r="AR23" s="135"/>
-      <c r="AS23" s="135"/>
-      <c r="AT23" s="135"/>
-      <c r="AU23" s="135"/>
-      <c r="AV23" s="135"/>
-      <c r="AW23" s="135"/>
-      <c r="AX23" s="135"/>
-      <c r="AY23" s="135"/>
-      <c r="AZ23" s="136"/>
+      <c r="AO23" s="164"/>
+      <c r="AP23" s="165"/>
+      <c r="AQ23" s="165"/>
+      <c r="AR23" s="165"/>
+      <c r="AS23" s="165"/>
+      <c r="AT23" s="165"/>
+      <c r="AU23" s="165"/>
+      <c r="AV23" s="165"/>
+      <c r="AW23" s="165"/>
+      <c r="AX23" s="165"/>
+      <c r="AY23" s="165"/>
+      <c r="AZ23" s="171"/>
     </row>
     <row r="24" spans="2:52" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D24" s="18"/>
@@ -7660,50 +7684,51 @@
     <row r="50" ht="18" customHeight="1" x14ac:dyDescent="0.2"/>
   </sheetData>
   <mergeCells count="113">
-    <mergeCell ref="B20:B21"/>
-    <mergeCell ref="C20:I21"/>
-    <mergeCell ref="J20:P21"/>
-    <mergeCell ref="Q20:S21"/>
-    <mergeCell ref="T20:U20"/>
-    <mergeCell ref="V20:W20"/>
-    <mergeCell ref="X20:Y20"/>
-    <mergeCell ref="AO20:AZ21"/>
-    <mergeCell ref="T21:U21"/>
-    <mergeCell ref="V21:W21"/>
-    <mergeCell ref="X21:Y21"/>
-    <mergeCell ref="AO4:AZ5"/>
-    <mergeCell ref="AI4:AK4"/>
-    <mergeCell ref="AL4:AN4"/>
-    <mergeCell ref="AF4:AH4"/>
-    <mergeCell ref="X6:Y6"/>
-    <mergeCell ref="X7:Y7"/>
-    <mergeCell ref="X8:Y8"/>
-    <mergeCell ref="B2:I2"/>
-    <mergeCell ref="J2:AD2"/>
-    <mergeCell ref="X4:Y5"/>
-    <mergeCell ref="T4:W5"/>
-    <mergeCell ref="Z4:AB4"/>
-    <mergeCell ref="AC4:AE4"/>
-    <mergeCell ref="B4:I5"/>
-    <mergeCell ref="J4:P5"/>
-    <mergeCell ref="Q4:S5"/>
-    <mergeCell ref="AO6:AZ7"/>
-    <mergeCell ref="C6:I7"/>
-    <mergeCell ref="Q6:S7"/>
-    <mergeCell ref="J6:P7"/>
-    <mergeCell ref="AO10:AZ11"/>
-    <mergeCell ref="T11:U11"/>
-    <mergeCell ref="X9:Y9"/>
-    <mergeCell ref="X10:Y10"/>
-    <mergeCell ref="X11:Y11"/>
-    <mergeCell ref="V8:W8"/>
-    <mergeCell ref="V9:W9"/>
-    <mergeCell ref="AO8:AZ9"/>
-    <mergeCell ref="V6:W6"/>
-    <mergeCell ref="V7:W7"/>
-    <mergeCell ref="T9:U9"/>
-    <mergeCell ref="T10:U10"/>
-    <mergeCell ref="T8:U8"/>
+    <mergeCell ref="B1:P1"/>
+    <mergeCell ref="J10:P11"/>
+    <mergeCell ref="J12:P13"/>
+    <mergeCell ref="J14:P15"/>
+    <mergeCell ref="J16:P17"/>
+    <mergeCell ref="V10:W10"/>
+    <mergeCell ref="V11:W11"/>
+    <mergeCell ref="V13:W13"/>
+    <mergeCell ref="V14:W14"/>
+    <mergeCell ref="V15:W15"/>
+    <mergeCell ref="V17:W17"/>
+    <mergeCell ref="B6:B7"/>
+    <mergeCell ref="T6:U6"/>
+    <mergeCell ref="T7:U7"/>
+    <mergeCell ref="B10:B11"/>
+    <mergeCell ref="C10:I11"/>
+    <mergeCell ref="Q8:S9"/>
+    <mergeCell ref="Q10:S11"/>
+    <mergeCell ref="B8:B9"/>
+    <mergeCell ref="C8:I9"/>
+    <mergeCell ref="J8:P9"/>
+    <mergeCell ref="V23:W23"/>
+    <mergeCell ref="V18:W18"/>
+    <mergeCell ref="V19:W19"/>
+    <mergeCell ref="B18:B19"/>
+    <mergeCell ref="AO16:AZ17"/>
+    <mergeCell ref="T17:U17"/>
+    <mergeCell ref="X16:Y16"/>
+    <mergeCell ref="X17:Y17"/>
+    <mergeCell ref="V16:W16"/>
+    <mergeCell ref="AO22:AZ23"/>
+    <mergeCell ref="X22:Y22"/>
+    <mergeCell ref="B16:B17"/>
+    <mergeCell ref="C16:I17"/>
+    <mergeCell ref="T16:U16"/>
+    <mergeCell ref="B22:B23"/>
+    <mergeCell ref="C22:I23"/>
+    <mergeCell ref="J18:P19"/>
+    <mergeCell ref="T22:U22"/>
+    <mergeCell ref="T23:U23"/>
+    <mergeCell ref="Q16:S17"/>
+    <mergeCell ref="Q22:S23"/>
+    <mergeCell ref="X23:Y23"/>
+    <mergeCell ref="C18:I19"/>
+    <mergeCell ref="T18:U18"/>
     <mergeCell ref="AO18:AZ19"/>
     <mergeCell ref="T19:U19"/>
     <mergeCell ref="X18:Y18"/>
@@ -7728,51 +7753,50 @@
     <mergeCell ref="X15:Y15"/>
     <mergeCell ref="Q12:S13"/>
     <mergeCell ref="Q14:S15"/>
-    <mergeCell ref="V23:W23"/>
-    <mergeCell ref="V18:W18"/>
-    <mergeCell ref="V19:W19"/>
-    <mergeCell ref="B18:B19"/>
-    <mergeCell ref="AO16:AZ17"/>
-    <mergeCell ref="T17:U17"/>
-    <mergeCell ref="X16:Y16"/>
-    <mergeCell ref="X17:Y17"/>
-    <mergeCell ref="V16:W16"/>
-    <mergeCell ref="AO22:AZ23"/>
-    <mergeCell ref="X22:Y22"/>
-    <mergeCell ref="B16:B17"/>
-    <mergeCell ref="C16:I17"/>
-    <mergeCell ref="T16:U16"/>
-    <mergeCell ref="B22:B23"/>
-    <mergeCell ref="C22:I23"/>
-    <mergeCell ref="J18:P19"/>
-    <mergeCell ref="T22:U22"/>
-    <mergeCell ref="T23:U23"/>
-    <mergeCell ref="Q16:S17"/>
-    <mergeCell ref="Q22:S23"/>
-    <mergeCell ref="X23:Y23"/>
-    <mergeCell ref="C18:I19"/>
-    <mergeCell ref="T18:U18"/>
-    <mergeCell ref="B1:P1"/>
-    <mergeCell ref="J10:P11"/>
-    <mergeCell ref="J12:P13"/>
-    <mergeCell ref="J14:P15"/>
-    <mergeCell ref="J16:P17"/>
-    <mergeCell ref="V10:W10"/>
-    <mergeCell ref="V11:W11"/>
-    <mergeCell ref="V13:W13"/>
-    <mergeCell ref="V14:W14"/>
-    <mergeCell ref="V15:W15"/>
-    <mergeCell ref="V17:W17"/>
-    <mergeCell ref="B6:B7"/>
-    <mergeCell ref="T6:U6"/>
-    <mergeCell ref="T7:U7"/>
-    <mergeCell ref="B10:B11"/>
-    <mergeCell ref="C10:I11"/>
-    <mergeCell ref="Q8:S9"/>
-    <mergeCell ref="Q10:S11"/>
-    <mergeCell ref="B8:B9"/>
-    <mergeCell ref="C8:I9"/>
-    <mergeCell ref="J8:P9"/>
+    <mergeCell ref="AO10:AZ11"/>
+    <mergeCell ref="T11:U11"/>
+    <mergeCell ref="X9:Y9"/>
+    <mergeCell ref="X10:Y10"/>
+    <mergeCell ref="X11:Y11"/>
+    <mergeCell ref="V8:W8"/>
+    <mergeCell ref="V9:W9"/>
+    <mergeCell ref="AO8:AZ9"/>
+    <mergeCell ref="V6:W6"/>
+    <mergeCell ref="V7:W7"/>
+    <mergeCell ref="T9:U9"/>
+    <mergeCell ref="T10:U10"/>
+    <mergeCell ref="T8:U8"/>
+    <mergeCell ref="AO4:AZ5"/>
+    <mergeCell ref="AI4:AK4"/>
+    <mergeCell ref="AL4:AN4"/>
+    <mergeCell ref="AF4:AH4"/>
+    <mergeCell ref="X6:Y6"/>
+    <mergeCell ref="X7:Y7"/>
+    <mergeCell ref="X8:Y8"/>
+    <mergeCell ref="B2:I2"/>
+    <mergeCell ref="J2:AD2"/>
+    <mergeCell ref="X4:Y5"/>
+    <mergeCell ref="T4:W5"/>
+    <mergeCell ref="Z4:AB4"/>
+    <mergeCell ref="AC4:AE4"/>
+    <mergeCell ref="B4:I5"/>
+    <mergeCell ref="J4:P5"/>
+    <mergeCell ref="Q4:S5"/>
+    <mergeCell ref="AO6:AZ7"/>
+    <mergeCell ref="C6:I7"/>
+    <mergeCell ref="Q6:S7"/>
+    <mergeCell ref="J6:P7"/>
+    <mergeCell ref="B20:B21"/>
+    <mergeCell ref="C20:I21"/>
+    <mergeCell ref="J20:P21"/>
+    <mergeCell ref="Q20:S21"/>
+    <mergeCell ref="T20:U20"/>
+    <mergeCell ref="V20:W20"/>
+    <mergeCell ref="X20:Y20"/>
+    <mergeCell ref="AO20:AZ21"/>
+    <mergeCell ref="T21:U21"/>
+    <mergeCell ref="V21:W21"/>
+    <mergeCell ref="X21:Y21"/>
   </mergeCells>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.51200000000000001" footer="0.51200000000000001"/>
@@ -7796,51 +7820,51 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="28">
+      <c r="A1" s="27">
         <v>1</v>
       </c>
-      <c r="B1" s="32" t="s">
+      <c r="B1" s="34" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="32"/>
-      <c r="D1" s="32"/>
-      <c r="E1" s="78"/>
-      <c r="F1" s="78"/>
-      <c r="G1" s="78"/>
-      <c r="H1" s="78"/>
-      <c r="I1" s="78"/>
-      <c r="J1" s="79"/>
+      <c r="C1" s="34"/>
+      <c r="D1" s="34"/>
+      <c r="E1" s="36"/>
+      <c r="F1" s="36"/>
+      <c r="G1" s="36"/>
+      <c r="H1" s="36"/>
+      <c r="I1" s="36"/>
+      <c r="J1" s="37"/>
     </row>
     <row r="2" spans="1:10" ht="13.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="29"/>
-      <c r="B2" s="77"/>
-      <c r="C2" s="77"/>
-      <c r="D2" s="77"/>
-      <c r="E2" s="80"/>
-      <c r="F2" s="80"/>
-      <c r="G2" s="80"/>
-      <c r="H2" s="80"/>
-      <c r="I2" s="80"/>
-      <c r="J2" s="81"/>
+      <c r="A2" s="31"/>
+      <c r="B2" s="35"/>
+      <c r="C2" s="35"/>
+      <c r="D2" s="35"/>
+      <c r="E2" s="38"/>
+      <c r="F2" s="38"/>
+      <c r="G2" s="38"/>
+      <c r="H2" s="38"/>
+      <c r="I2" s="38"/>
+      <c r="J2" s="39"/>
     </row>
     <row r="3" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="28">
+      <c r="A3" s="27">
         <v>2</v>
       </c>
-      <c r="B3" s="32" t="s">
+      <c r="B3" s="34" t="s">
         <v>96</v>
       </c>
-      <c r="C3" s="32"/>
-      <c r="D3" s="32"/>
-      <c r="E3" s="32"/>
-      <c r="F3" s="32"/>
-      <c r="G3" s="32"/>
-      <c r="H3" s="32"/>
-      <c r="I3" s="32"/>
-      <c r="J3" s="33"/>
+      <c r="C3" s="34"/>
+      <c r="D3" s="34"/>
+      <c r="E3" s="34"/>
+      <c r="F3" s="34"/>
+      <c r="G3" s="34"/>
+      <c r="H3" s="34"/>
+      <c r="I3" s="34"/>
+      <c r="J3" s="67"/>
     </row>
     <row r="4" spans="1:10" ht="13.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="30"/>
+      <c r="A4" s="28"/>
       <c r="B4" s="194" t="s">
         <v>97</v>
       </c>
@@ -7854,551 +7878,552 @@
       <c r="J4" s="195"/>
     </row>
     <row r="5" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="28">
+      <c r="A5" s="27">
         <v>3</v>
       </c>
-      <c r="B5" s="32" t="s">
+      <c r="B5" s="34" t="s">
         <v>98</v>
       </c>
-      <c r="C5" s="32"/>
-      <c r="D5" s="32"/>
-      <c r="E5" s="32"/>
-      <c r="F5" s="32"/>
-      <c r="G5" s="32"/>
-      <c r="H5" s="32"/>
-      <c r="I5" s="32"/>
-      <c r="J5" s="33"/>
+      <c r="C5" s="34"/>
+      <c r="D5" s="34"/>
+      <c r="E5" s="34"/>
+      <c r="F5" s="34"/>
+      <c r="G5" s="34"/>
+      <c r="H5" s="34"/>
+      <c r="I5" s="34"/>
+      <c r="J5" s="67"/>
     </row>
     <row r="6" spans="1:10" ht="13.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="29"/>
-      <c r="B6" s="40" t="s">
+      <c r="A6" s="31"/>
+      <c r="B6" s="73" t="s">
         <v>16</v>
       </c>
-      <c r="C6" s="40"/>
-      <c r="D6" s="40"/>
-      <c r="E6" s="40"/>
-      <c r="F6" s="40"/>
-      <c r="G6" s="40"/>
-      <c r="H6" s="40"/>
-      <c r="I6" s="40"/>
-      <c r="J6" s="41"/>
+      <c r="C6" s="73"/>
+      <c r="D6" s="73"/>
+      <c r="E6" s="73"/>
+      <c r="F6" s="73"/>
+      <c r="G6" s="73"/>
+      <c r="H6" s="73"/>
+      <c r="I6" s="73"/>
+      <c r="J6" s="74"/>
     </row>
     <row r="7" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="28">
+      <c r="A7" s="27">
         <v>4</v>
       </c>
-      <c r="B7" s="32" t="s">
+      <c r="B7" s="34" t="s">
         <v>99</v>
       </c>
-      <c r="C7" s="32"/>
-      <c r="D7" s="32"/>
-      <c r="E7" s="32"/>
-      <c r="F7" s="32"/>
-      <c r="G7" s="32"/>
-      <c r="H7" s="32"/>
-      <c r="I7" s="32"/>
-      <c r="J7" s="33"/>
+      <c r="C7" s="34"/>
+      <c r="D7" s="34"/>
+      <c r="E7" s="34"/>
+      <c r="F7" s="34"/>
+      <c r="G7" s="34"/>
+      <c r="H7" s="34"/>
+      <c r="I7" s="34"/>
+      <c r="J7" s="67"/>
     </row>
     <row r="8" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="30"/>
-      <c r="B8" s="36" t="s">
+      <c r="A8" s="28"/>
+      <c r="B8" s="69" t="s">
         <v>100</v>
       </c>
-      <c r="C8" s="36"/>
-      <c r="D8" s="36"/>
-      <c r="E8" s="36"/>
-      <c r="F8" s="36"/>
-      <c r="G8" s="36"/>
-      <c r="H8" s="36"/>
-      <c r="I8" s="36"/>
-      <c r="J8" s="37"/>
+      <c r="C8" s="69"/>
+      <c r="D8" s="69"/>
+      <c r="E8" s="69"/>
+      <c r="F8" s="69"/>
+      <c r="G8" s="69"/>
+      <c r="H8" s="69"/>
+      <c r="I8" s="69"/>
+      <c r="J8" s="70"/>
     </row>
     <row r="9" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="30"/>
-      <c r="B9" s="34"/>
-      <c r="C9" s="34"/>
-      <c r="D9" s="34"/>
-      <c r="E9" s="34"/>
-      <c r="F9" s="34"/>
-      <c r="G9" s="34"/>
-      <c r="H9" s="34"/>
-      <c r="I9" s="34"/>
-      <c r="J9" s="35"/>
+      <c r="A9" s="28"/>
+      <c r="B9" s="44"/>
+      <c r="C9" s="44"/>
+      <c r="D9" s="44"/>
+      <c r="E9" s="44"/>
+      <c r="F9" s="44"/>
+      <c r="G9" s="44"/>
+      <c r="H9" s="44"/>
+      <c r="I9" s="44"/>
+      <c r="J9" s="45"/>
     </row>
     <row r="10" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="30"/>
-      <c r="B10" s="34"/>
-      <c r="C10" s="34"/>
-      <c r="D10" s="34"/>
-      <c r="E10" s="34"/>
-      <c r="F10" s="34"/>
-      <c r="G10" s="34"/>
-      <c r="H10" s="34"/>
-      <c r="I10" s="34"/>
-      <c r="J10" s="35"/>
+      <c r="A10" s="28"/>
+      <c r="B10" s="44"/>
+      <c r="C10" s="44"/>
+      <c r="D10" s="44"/>
+      <c r="E10" s="44"/>
+      <c r="F10" s="44"/>
+      <c r="G10" s="44"/>
+      <c r="H10" s="44"/>
+      <c r="I10" s="44"/>
+      <c r="J10" s="45"/>
     </row>
     <row r="11" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="30"/>
-      <c r="B11" s="34"/>
-      <c r="C11" s="34"/>
-      <c r="D11" s="34"/>
-      <c r="E11" s="34"/>
-      <c r="F11" s="34"/>
-      <c r="G11" s="34"/>
-      <c r="H11" s="34"/>
-      <c r="I11" s="34"/>
-      <c r="J11" s="35"/>
+      <c r="A11" s="28"/>
+      <c r="B11" s="44"/>
+      <c r="C11" s="44"/>
+      <c r="D11" s="44"/>
+      <c r="E11" s="44"/>
+      <c r="F11" s="44"/>
+      <c r="G11" s="44"/>
+      <c r="H11" s="44"/>
+      <c r="I11" s="44"/>
+      <c r="J11" s="45"/>
     </row>
     <row r="12" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="30"/>
-      <c r="B12" s="34"/>
-      <c r="C12" s="34"/>
-      <c r="D12" s="34"/>
-      <c r="E12" s="34"/>
-      <c r="F12" s="34"/>
-      <c r="G12" s="34"/>
-      <c r="H12" s="34"/>
-      <c r="I12" s="34"/>
-      <c r="J12" s="35"/>
+      <c r="A12" s="28"/>
+      <c r="B12" s="44"/>
+      <c r="C12" s="44"/>
+      <c r="D12" s="44"/>
+      <c r="E12" s="44"/>
+      <c r="F12" s="44"/>
+      <c r="G12" s="44"/>
+      <c r="H12" s="44"/>
+      <c r="I12" s="44"/>
+      <c r="J12" s="45"/>
     </row>
     <row r="13" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="30"/>
-      <c r="B13" s="34"/>
-      <c r="C13" s="34"/>
-      <c r="D13" s="34"/>
-      <c r="E13" s="34"/>
-      <c r="F13" s="34"/>
-      <c r="G13" s="34"/>
-      <c r="H13" s="34"/>
-      <c r="I13" s="34"/>
-      <c r="J13" s="35"/>
+      <c r="A13" s="28"/>
+      <c r="B13" s="44"/>
+      <c r="C13" s="44"/>
+      <c r="D13" s="44"/>
+      <c r="E13" s="44"/>
+      <c r="F13" s="44"/>
+      <c r="G13" s="44"/>
+      <c r="H13" s="44"/>
+      <c r="I13" s="44"/>
+      <c r="J13" s="45"/>
     </row>
     <row r="14" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A14" s="30"/>
-      <c r="B14" s="34"/>
-      <c r="C14" s="34"/>
-      <c r="D14" s="34"/>
-      <c r="E14" s="34"/>
-      <c r="F14" s="34"/>
-      <c r="G14" s="34"/>
-      <c r="H14" s="34"/>
-      <c r="I14" s="34"/>
-      <c r="J14" s="35"/>
+      <c r="A14" s="28"/>
+      <c r="B14" s="44"/>
+      <c r="C14" s="44"/>
+      <c r="D14" s="44"/>
+      <c r="E14" s="44"/>
+      <c r="F14" s="44"/>
+      <c r="G14" s="44"/>
+      <c r="H14" s="44"/>
+      <c r="I14" s="44"/>
+      <c r="J14" s="45"/>
     </row>
     <row r="15" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A15" s="30"/>
-      <c r="B15" s="36" t="s">
+      <c r="A15" s="28"/>
+      <c r="B15" s="69" t="s">
         <v>101</v>
       </c>
-      <c r="C15" s="36"/>
-      <c r="D15" s="36"/>
-      <c r="E15" s="36"/>
-      <c r="F15" s="36"/>
-      <c r="G15" s="36"/>
-      <c r="H15" s="36"/>
-      <c r="I15" s="36"/>
-      <c r="J15" s="37"/>
+      <c r="C15" s="69"/>
+      <c r="D15" s="69"/>
+      <c r="E15" s="69"/>
+      <c r="F15" s="69"/>
+      <c r="G15" s="69"/>
+      <c r="H15" s="69"/>
+      <c r="I15" s="69"/>
+      <c r="J15" s="70"/>
     </row>
     <row r="16" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A16" s="30"/>
-      <c r="B16" s="34"/>
-      <c r="C16" s="34"/>
-      <c r="D16" s="34"/>
-      <c r="E16" s="34"/>
-      <c r="F16" s="34"/>
-      <c r="G16" s="34"/>
-      <c r="H16" s="34"/>
-      <c r="I16" s="34"/>
-      <c r="J16" s="35"/>
+      <c r="A16" s="28"/>
+      <c r="B16" s="44"/>
+      <c r="C16" s="44"/>
+      <c r="D16" s="44"/>
+      <c r="E16" s="44"/>
+      <c r="F16" s="44"/>
+      <c r="G16" s="44"/>
+      <c r="H16" s="44"/>
+      <c r="I16" s="44"/>
+      <c r="J16" s="45"/>
     </row>
     <row r="17" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A17" s="30"/>
-      <c r="B17" s="34"/>
-      <c r="C17" s="34"/>
-      <c r="D17" s="34"/>
-      <c r="E17" s="34"/>
-      <c r="F17" s="34"/>
-      <c r="G17" s="34"/>
-      <c r="H17" s="34"/>
-      <c r="I17" s="34"/>
-      <c r="J17" s="35"/>
+      <c r="A17" s="28"/>
+      <c r="B17" s="44"/>
+      <c r="C17" s="44"/>
+      <c r="D17" s="44"/>
+      <c r="E17" s="44"/>
+      <c r="F17" s="44"/>
+      <c r="G17" s="44"/>
+      <c r="H17" s="44"/>
+      <c r="I17" s="44"/>
+      <c r="J17" s="45"/>
     </row>
     <row r="18" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A18" s="30"/>
-      <c r="B18" s="34"/>
-      <c r="C18" s="34"/>
-      <c r="D18" s="34"/>
-      <c r="E18" s="34"/>
-      <c r="F18" s="34"/>
-      <c r="G18" s="34"/>
-      <c r="H18" s="34"/>
-      <c r="I18" s="34"/>
-      <c r="J18" s="35"/>
+      <c r="A18" s="28"/>
+      <c r="B18" s="44"/>
+      <c r="C18" s="44"/>
+      <c r="D18" s="44"/>
+      <c r="E18" s="44"/>
+      <c r="F18" s="44"/>
+      <c r="G18" s="44"/>
+      <c r="H18" s="44"/>
+      <c r="I18" s="44"/>
+      <c r="J18" s="45"/>
     </row>
     <row r="19" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A19" s="30"/>
-      <c r="B19" s="34"/>
-      <c r="C19" s="34"/>
-      <c r="D19" s="34"/>
-      <c r="E19" s="34"/>
-      <c r="F19" s="34"/>
-      <c r="G19" s="34"/>
-      <c r="H19" s="34"/>
-      <c r="I19" s="34"/>
-      <c r="J19" s="35"/>
+      <c r="A19" s="28"/>
+      <c r="B19" s="44"/>
+      <c r="C19" s="44"/>
+      <c r="D19" s="44"/>
+      <c r="E19" s="44"/>
+      <c r="F19" s="44"/>
+      <c r="G19" s="44"/>
+      <c r="H19" s="44"/>
+      <c r="I19" s="44"/>
+      <c r="J19" s="45"/>
     </row>
     <row r="20" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A20" s="30"/>
-      <c r="B20" s="34"/>
-      <c r="C20" s="34"/>
-      <c r="D20" s="34"/>
-      <c r="E20" s="34"/>
-      <c r="F20" s="34"/>
-      <c r="G20" s="34"/>
-      <c r="H20" s="34"/>
-      <c r="I20" s="34"/>
-      <c r="J20" s="35"/>
+      <c r="A20" s="28"/>
+      <c r="B20" s="44"/>
+      <c r="C20" s="44"/>
+      <c r="D20" s="44"/>
+      <c r="E20" s="44"/>
+      <c r="F20" s="44"/>
+      <c r="G20" s="44"/>
+      <c r="H20" s="44"/>
+      <c r="I20" s="44"/>
+      <c r="J20" s="45"/>
     </row>
     <row r="21" spans="1:10" ht="13.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="29"/>
-      <c r="B21" s="80"/>
-      <c r="C21" s="80"/>
-      <c r="D21" s="80"/>
-      <c r="E21" s="80"/>
-      <c r="F21" s="80"/>
-      <c r="G21" s="80"/>
-      <c r="H21" s="80"/>
-      <c r="I21" s="80"/>
-      <c r="J21" s="81"/>
+      <c r="A21" s="31"/>
+      <c r="B21" s="38"/>
+      <c r="C21" s="38"/>
+      <c r="D21" s="38"/>
+      <c r="E21" s="38"/>
+      <c r="F21" s="38"/>
+      <c r="G21" s="38"/>
+      <c r="H21" s="38"/>
+      <c r="I21" s="38"/>
+      <c r="J21" s="39"/>
     </row>
     <row r="22" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A22" s="28">
+      <c r="A22" s="27">
         <v>5</v>
       </c>
-      <c r="B22" s="32" t="s">
+      <c r="B22" s="34" t="s">
         <v>102</v>
       </c>
-      <c r="C22" s="32"/>
-      <c r="D22" s="32"/>
-      <c r="E22" s="32"/>
-      <c r="F22" s="32"/>
-      <c r="G22" s="32"/>
-      <c r="H22" s="32"/>
-      <c r="I22" s="32"/>
-      <c r="J22" s="33"/>
+      <c r="C22" s="34"/>
+      <c r="D22" s="34"/>
+      <c r="E22" s="34"/>
+      <c r="F22" s="34"/>
+      <c r="G22" s="34"/>
+      <c r="H22" s="34"/>
+      <c r="I22" s="34"/>
+      <c r="J22" s="67"/>
     </row>
     <row r="23" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A23" s="30"/>
-      <c r="B23" s="34"/>
-      <c r="C23" s="34"/>
-      <c r="D23" s="34"/>
-      <c r="E23" s="34"/>
-      <c r="F23" s="34"/>
-      <c r="G23" s="34"/>
-      <c r="H23" s="34"/>
-      <c r="I23" s="34"/>
-      <c r="J23" s="35"/>
+      <c r="A23" s="28"/>
+      <c r="B23" s="44"/>
+      <c r="C23" s="44"/>
+      <c r="D23" s="44"/>
+      <c r="E23" s="44"/>
+      <c r="F23" s="44"/>
+      <c r="G23" s="44"/>
+      <c r="H23" s="44"/>
+      <c r="I23" s="44"/>
+      <c r="J23" s="45"/>
     </row>
     <row r="24" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A24" s="30"/>
-      <c r="B24" s="34"/>
-      <c r="C24" s="34"/>
-      <c r="D24" s="34"/>
-      <c r="E24" s="34"/>
-      <c r="F24" s="34"/>
-      <c r="G24" s="34"/>
-      <c r="H24" s="34"/>
-      <c r="I24" s="34"/>
-      <c r="J24" s="35"/>
+      <c r="A24" s="28"/>
+      <c r="B24" s="44"/>
+      <c r="C24" s="44"/>
+      <c r="D24" s="44"/>
+      <c r="E24" s="44"/>
+      <c r="F24" s="44"/>
+      <c r="G24" s="44"/>
+      <c r="H24" s="44"/>
+      <c r="I24" s="44"/>
+      <c r="J24" s="45"/>
     </row>
     <row r="25" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A25" s="30"/>
-      <c r="B25" s="34"/>
-      <c r="C25" s="34"/>
-      <c r="D25" s="34"/>
-      <c r="E25" s="34"/>
-      <c r="F25" s="34"/>
-      <c r="G25" s="34"/>
-      <c r="H25" s="34"/>
-      <c r="I25" s="34"/>
-      <c r="J25" s="35"/>
+      <c r="A25" s="28"/>
+      <c r="B25" s="44"/>
+      <c r="C25" s="44"/>
+      <c r="D25" s="44"/>
+      <c r="E25" s="44"/>
+      <c r="F25" s="44"/>
+      <c r="G25" s="44"/>
+      <c r="H25" s="44"/>
+      <c r="I25" s="44"/>
+      <c r="J25" s="45"/>
     </row>
     <row r="26" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A26" s="30"/>
-      <c r="B26" s="34"/>
-      <c r="C26" s="34"/>
-      <c r="D26" s="34"/>
-      <c r="E26" s="34"/>
-      <c r="F26" s="34"/>
-      <c r="G26" s="34"/>
-      <c r="H26" s="34"/>
-      <c r="I26" s="34"/>
-      <c r="J26" s="35"/>
+      <c r="A26" s="28"/>
+      <c r="B26" s="44"/>
+      <c r="C26" s="44"/>
+      <c r="D26" s="44"/>
+      <c r="E26" s="44"/>
+      <c r="F26" s="44"/>
+      <c r="G26" s="44"/>
+      <c r="H26" s="44"/>
+      <c r="I26" s="44"/>
+      <c r="J26" s="45"/>
     </row>
     <row r="27" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A27" s="30"/>
-      <c r="B27" s="34"/>
-      <c r="C27" s="34"/>
-      <c r="D27" s="34"/>
-      <c r="E27" s="34"/>
-      <c r="F27" s="34"/>
-      <c r="G27" s="34"/>
-      <c r="H27" s="34"/>
-      <c r="I27" s="34"/>
-      <c r="J27" s="35"/>
+      <c r="A27" s="28"/>
+      <c r="B27" s="44"/>
+      <c r="C27" s="44"/>
+      <c r="D27" s="44"/>
+      <c r="E27" s="44"/>
+      <c r="F27" s="44"/>
+      <c r="G27" s="44"/>
+      <c r="H27" s="44"/>
+      <c r="I27" s="44"/>
+      <c r="J27" s="45"/>
     </row>
     <row r="28" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A28" s="30"/>
-      <c r="B28" s="34"/>
-      <c r="C28" s="34"/>
-      <c r="D28" s="34"/>
-      <c r="E28" s="34"/>
-      <c r="F28" s="34"/>
-      <c r="G28" s="34"/>
-      <c r="H28" s="34"/>
-      <c r="I28" s="34"/>
-      <c r="J28" s="35"/>
+      <c r="A28" s="28"/>
+      <c r="B28" s="44"/>
+      <c r="C28" s="44"/>
+      <c r="D28" s="44"/>
+      <c r="E28" s="44"/>
+      <c r="F28" s="44"/>
+      <c r="G28" s="44"/>
+      <c r="H28" s="44"/>
+      <c r="I28" s="44"/>
+      <c r="J28" s="45"/>
     </row>
     <row r="29" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A29" s="30"/>
-      <c r="B29" s="34"/>
-      <c r="C29" s="34"/>
-      <c r="D29" s="34"/>
-      <c r="E29" s="34"/>
-      <c r="F29" s="34"/>
-      <c r="G29" s="34"/>
-      <c r="H29" s="34"/>
-      <c r="I29" s="34"/>
-      <c r="J29" s="35"/>
+      <c r="A29" s="28"/>
+      <c r="B29" s="44"/>
+      <c r="C29" s="44"/>
+      <c r="D29" s="44"/>
+      <c r="E29" s="44"/>
+      <c r="F29" s="44"/>
+      <c r="G29" s="44"/>
+      <c r="H29" s="44"/>
+      <c r="I29" s="44"/>
+      <c r="J29" s="45"/>
     </row>
     <row r="30" spans="1:10" ht="13.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="29"/>
-      <c r="B30" s="80"/>
-      <c r="C30" s="80"/>
-      <c r="D30" s="80"/>
-      <c r="E30" s="80"/>
-      <c r="F30" s="80"/>
-      <c r="G30" s="80"/>
-      <c r="H30" s="80"/>
-      <c r="I30" s="80"/>
-      <c r="J30" s="81"/>
+      <c r="A30" s="31"/>
+      <c r="B30" s="38"/>
+      <c r="C30" s="38"/>
+      <c r="D30" s="38"/>
+      <c r="E30" s="38"/>
+      <c r="F30" s="38"/>
+      <c r="G30" s="38"/>
+      <c r="H30" s="38"/>
+      <c r="I30" s="38"/>
+      <c r="J30" s="39"/>
     </row>
     <row r="31" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A31" s="28">
+      <c r="A31" s="27">
         <v>6</v>
       </c>
-      <c r="B31" s="32" t="s">
+      <c r="B31" s="34" t="s">
         <v>103</v>
       </c>
-      <c r="C31" s="32"/>
-      <c r="D31" s="32"/>
-      <c r="E31" s="32"/>
-      <c r="F31" s="32"/>
-      <c r="G31" s="32"/>
-      <c r="H31" s="32"/>
-      <c r="I31" s="32"/>
-      <c r="J31" s="33"/>
+      <c r="C31" s="34"/>
+      <c r="D31" s="34"/>
+      <c r="E31" s="34"/>
+      <c r="F31" s="34"/>
+      <c r="G31" s="34"/>
+      <c r="H31" s="34"/>
+      <c r="I31" s="34"/>
+      <c r="J31" s="67"/>
     </row>
     <row r="32" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A32" s="30"/>
-      <c r="B32" s="34"/>
-      <c r="C32" s="34"/>
-      <c r="D32" s="34"/>
-      <c r="E32" s="34"/>
-      <c r="F32" s="34"/>
-      <c r="G32" s="34"/>
-      <c r="H32" s="34"/>
-      <c r="I32" s="34"/>
-      <c r="J32" s="35"/>
+      <c r="A32" s="28"/>
+      <c r="B32" s="44"/>
+      <c r="C32" s="44"/>
+      <c r="D32" s="44"/>
+      <c r="E32" s="44"/>
+      <c r="F32" s="44"/>
+      <c r="G32" s="44"/>
+      <c r="H32" s="44"/>
+      <c r="I32" s="44"/>
+      <c r="J32" s="45"/>
     </row>
     <row r="33" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A33" s="30"/>
-      <c r="B33" s="34"/>
-      <c r="C33" s="34"/>
-      <c r="D33" s="34"/>
-      <c r="E33" s="34"/>
-      <c r="F33" s="34"/>
-      <c r="G33" s="34"/>
-      <c r="H33" s="34"/>
-      <c r="I33" s="34"/>
-      <c r="J33" s="35"/>
+      <c r="A33" s="28"/>
+      <c r="B33" s="44"/>
+      <c r="C33" s="44"/>
+      <c r="D33" s="44"/>
+      <c r="E33" s="44"/>
+      <c r="F33" s="44"/>
+      <c r="G33" s="44"/>
+      <c r="H33" s="44"/>
+      <c r="I33" s="44"/>
+      <c r="J33" s="45"/>
     </row>
     <row r="34" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A34" s="30"/>
-      <c r="B34" s="34"/>
-      <c r="C34" s="34"/>
-      <c r="D34" s="34"/>
-      <c r="E34" s="34"/>
-      <c r="F34" s="34"/>
-      <c r="G34" s="34"/>
-      <c r="H34" s="34"/>
-      <c r="I34" s="34"/>
-      <c r="J34" s="35"/>
+      <c r="A34" s="28"/>
+      <c r="B34" s="44"/>
+      <c r="C34" s="44"/>
+      <c r="D34" s="44"/>
+      <c r="E34" s="44"/>
+      <c r="F34" s="44"/>
+      <c r="G34" s="44"/>
+      <c r="H34" s="44"/>
+      <c r="I34" s="44"/>
+      <c r="J34" s="45"/>
     </row>
     <row r="35" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A35" s="30"/>
-      <c r="B35" s="34"/>
-      <c r="C35" s="34"/>
-      <c r="D35" s="34"/>
-      <c r="E35" s="34"/>
-      <c r="F35" s="34"/>
-      <c r="G35" s="34"/>
-      <c r="H35" s="34"/>
-      <c r="I35" s="34"/>
-      <c r="J35" s="35"/>
+      <c r="A35" s="28"/>
+      <c r="B35" s="44"/>
+      <c r="C35" s="44"/>
+      <c r="D35" s="44"/>
+      <c r="E35" s="44"/>
+      <c r="F35" s="44"/>
+      <c r="G35" s="44"/>
+      <c r="H35" s="44"/>
+      <c r="I35" s="44"/>
+      <c r="J35" s="45"/>
     </row>
     <row r="36" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A36" s="30"/>
-      <c r="B36" s="34"/>
-      <c r="C36" s="34"/>
-      <c r="D36" s="34"/>
-      <c r="E36" s="34"/>
-      <c r="F36" s="34"/>
-      <c r="G36" s="34"/>
-      <c r="H36" s="34"/>
-      <c r="I36" s="34"/>
-      <c r="J36" s="35"/>
+      <c r="A36" s="28"/>
+      <c r="B36" s="44"/>
+      <c r="C36" s="44"/>
+      <c r="D36" s="44"/>
+      <c r="E36" s="44"/>
+      <c r="F36" s="44"/>
+      <c r="G36" s="44"/>
+      <c r="H36" s="44"/>
+      <c r="I36" s="44"/>
+      <c r="J36" s="45"/>
     </row>
     <row r="37" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A37" s="30"/>
-      <c r="B37" s="34"/>
-      <c r="C37" s="34"/>
-      <c r="D37" s="34"/>
-      <c r="E37" s="34"/>
-      <c r="F37" s="34"/>
-      <c r="G37" s="34"/>
-      <c r="H37" s="34"/>
-      <c r="I37" s="34"/>
-      <c r="J37" s="35"/>
+      <c r="A37" s="28"/>
+      <c r="B37" s="44"/>
+      <c r="C37" s="44"/>
+      <c r="D37" s="44"/>
+      <c r="E37" s="44"/>
+      <c r="F37" s="44"/>
+      <c r="G37" s="44"/>
+      <c r="H37" s="44"/>
+      <c r="I37" s="44"/>
+      <c r="J37" s="45"/>
     </row>
     <row r="38" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A38" s="30"/>
-      <c r="B38" s="34"/>
-      <c r="C38" s="34"/>
-      <c r="D38" s="34"/>
-      <c r="E38" s="34"/>
-      <c r="F38" s="34"/>
-      <c r="G38" s="34"/>
-      <c r="H38" s="34"/>
-      <c r="I38" s="34"/>
-      <c r="J38" s="35"/>
+      <c r="A38" s="28"/>
+      <c r="B38" s="44"/>
+      <c r="C38" s="44"/>
+      <c r="D38" s="44"/>
+      <c r="E38" s="44"/>
+      <c r="F38" s="44"/>
+      <c r="G38" s="44"/>
+      <c r="H38" s="44"/>
+      <c r="I38" s="44"/>
+      <c r="J38" s="45"/>
     </row>
     <row r="39" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A39" s="30"/>
-      <c r="B39" s="34"/>
-      <c r="C39" s="34"/>
-      <c r="D39" s="34"/>
-      <c r="E39" s="34"/>
-      <c r="F39" s="34"/>
-      <c r="G39" s="34"/>
-      <c r="H39" s="34"/>
-      <c r="I39" s="34"/>
-      <c r="J39" s="35"/>
+      <c r="A39" s="28"/>
+      <c r="B39" s="44"/>
+      <c r="C39" s="44"/>
+      <c r="D39" s="44"/>
+      <c r="E39" s="44"/>
+      <c r="F39" s="44"/>
+      <c r="G39" s="44"/>
+      <c r="H39" s="44"/>
+      <c r="I39" s="44"/>
+      <c r="J39" s="45"/>
     </row>
     <row r="40" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A40" s="30"/>
-      <c r="B40" s="34"/>
-      <c r="C40" s="34"/>
-      <c r="D40" s="34"/>
-      <c r="E40" s="34"/>
-      <c r="F40" s="34"/>
-      <c r="G40" s="34"/>
-      <c r="H40" s="34"/>
-      <c r="I40" s="34"/>
-      <c r="J40" s="35"/>
+      <c r="A40" s="28"/>
+      <c r="B40" s="44"/>
+      <c r="C40" s="44"/>
+      <c r="D40" s="44"/>
+      <c r="E40" s="44"/>
+      <c r="F40" s="44"/>
+      <c r="G40" s="44"/>
+      <c r="H40" s="44"/>
+      <c r="I40" s="44"/>
+      <c r="J40" s="45"/>
     </row>
     <row r="41" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A41" s="30"/>
-      <c r="B41" s="34"/>
-      <c r="C41" s="34"/>
-      <c r="D41" s="34"/>
-      <c r="E41" s="34"/>
-      <c r="F41" s="34"/>
-      <c r="G41" s="34"/>
-      <c r="H41" s="34"/>
-      <c r="I41" s="34"/>
-      <c r="J41" s="35"/>
+      <c r="A41" s="28"/>
+      <c r="B41" s="44"/>
+      <c r="C41" s="44"/>
+      <c r="D41" s="44"/>
+      <c r="E41" s="44"/>
+      <c r="F41" s="44"/>
+      <c r="G41" s="44"/>
+      <c r="H41" s="44"/>
+      <c r="I41" s="44"/>
+      <c r="J41" s="45"/>
     </row>
     <row r="42" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A42" s="30"/>
-      <c r="B42" s="34"/>
-      <c r="C42" s="34"/>
-      <c r="D42" s="34"/>
-      <c r="E42" s="34"/>
-      <c r="F42" s="34"/>
-      <c r="G42" s="34"/>
-      <c r="H42" s="34"/>
-      <c r="I42" s="34"/>
-      <c r="J42" s="35"/>
+      <c r="A42" s="28"/>
+      <c r="B42" s="44"/>
+      <c r="C42" s="44"/>
+      <c r="D42" s="44"/>
+      <c r="E42" s="44"/>
+      <c r="F42" s="44"/>
+      <c r="G42" s="44"/>
+      <c r="H42" s="44"/>
+      <c r="I42" s="44"/>
+      <c r="J42" s="45"/>
     </row>
     <row r="43" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A43" s="30"/>
-      <c r="B43" s="34"/>
-      <c r="C43" s="34"/>
-      <c r="D43" s="34"/>
-      <c r="E43" s="34"/>
-      <c r="F43" s="34"/>
-      <c r="G43" s="34"/>
-      <c r="H43" s="34"/>
-      <c r="I43" s="34"/>
-      <c r="J43" s="35"/>
+      <c r="A43" s="28"/>
+      <c r="B43" s="44"/>
+      <c r="C43" s="44"/>
+      <c r="D43" s="44"/>
+      <c r="E43" s="44"/>
+      <c r="F43" s="44"/>
+      <c r="G43" s="44"/>
+      <c r="H43" s="44"/>
+      <c r="I43" s="44"/>
+      <c r="J43" s="45"/>
     </row>
     <row r="44" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A44" s="30"/>
-      <c r="B44" s="34"/>
-      <c r="C44" s="34"/>
-      <c r="D44" s="34"/>
-      <c r="E44" s="34"/>
-      <c r="F44" s="34"/>
-      <c r="G44" s="34"/>
-      <c r="H44" s="34"/>
-      <c r="I44" s="34"/>
-      <c r="J44" s="35"/>
+      <c r="A44" s="28"/>
+      <c r="B44" s="44"/>
+      <c r="C44" s="44"/>
+      <c r="D44" s="44"/>
+      <c r="E44" s="44"/>
+      <c r="F44" s="44"/>
+      <c r="G44" s="44"/>
+      <c r="H44" s="44"/>
+      <c r="I44" s="44"/>
+      <c r="J44" s="45"/>
     </row>
     <row r="45" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A45" s="30"/>
-      <c r="B45" s="34"/>
-      <c r="C45" s="34"/>
-      <c r="D45" s="34"/>
-      <c r="E45" s="34"/>
-      <c r="F45" s="34"/>
-      <c r="G45" s="34"/>
-      <c r="H45" s="34"/>
-      <c r="I45" s="34"/>
-      <c r="J45" s="35"/>
+      <c r="A45" s="28"/>
+      <c r="B45" s="44"/>
+      <c r="C45" s="44"/>
+      <c r="D45" s="44"/>
+      <c r="E45" s="44"/>
+      <c r="F45" s="44"/>
+      <c r="G45" s="44"/>
+      <c r="H45" s="44"/>
+      <c r="I45" s="44"/>
+      <c r="J45" s="45"/>
     </row>
     <row r="46" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A46" s="30"/>
-      <c r="B46" s="34"/>
-      <c r="C46" s="34"/>
-      <c r="D46" s="34"/>
-      <c r="E46" s="34"/>
-      <c r="F46" s="34"/>
-      <c r="G46" s="34"/>
-      <c r="H46" s="34"/>
-      <c r="I46" s="34"/>
-      <c r="J46" s="35"/>
+      <c r="A46" s="28"/>
+      <c r="B46" s="44"/>
+      <c r="C46" s="44"/>
+      <c r="D46" s="44"/>
+      <c r="E46" s="44"/>
+      <c r="F46" s="44"/>
+      <c r="G46" s="44"/>
+      <c r="H46" s="44"/>
+      <c r="I46" s="44"/>
+      <c r="J46" s="45"/>
     </row>
     <row r="47" spans="1:10" ht="13.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A47" s="31"/>
-      <c r="B47" s="38"/>
-      <c r="C47" s="38"/>
-      <c r="D47" s="38"/>
-      <c r="E47" s="38"/>
-      <c r="F47" s="38"/>
-      <c r="G47" s="38"/>
-      <c r="H47" s="38"/>
-      <c r="I47" s="38"/>
-      <c r="J47" s="39"/>
+      <c r="A47" s="29"/>
+      <c r="B47" s="71"/>
+      <c r="C47" s="71"/>
+      <c r="D47" s="71"/>
+      <c r="E47" s="71"/>
+      <c r="F47" s="71"/>
+      <c r="G47" s="71"/>
+      <c r="H47" s="71"/>
+      <c r="I47" s="71"/>
+      <c r="J47" s="72"/>
     </row>
   </sheetData>
   <mergeCells count="21">
-    <mergeCell ref="B3:J3"/>
-    <mergeCell ref="B4:J4"/>
-    <mergeCell ref="A1:A2"/>
-    <mergeCell ref="B1:D2"/>
-    <mergeCell ref="E1:J2"/>
-    <mergeCell ref="A3:A4"/>
+    <mergeCell ref="B32:J47"/>
+    <mergeCell ref="A31:A47"/>
+    <mergeCell ref="B16:J21"/>
+    <mergeCell ref="A22:A30"/>
+    <mergeCell ref="B23:J30"/>
+    <mergeCell ref="B22:J22"/>
+    <mergeCell ref="B31:J31"/>
     <mergeCell ref="B15:J15"/>
     <mergeCell ref="B8:J8"/>
     <mergeCell ref="A5:A6"/>
@@ -8407,13 +8432,12 @@
     <mergeCell ref="B7:J7"/>
     <mergeCell ref="B9:J14"/>
     <mergeCell ref="A7:A21"/>
-    <mergeCell ref="B32:J47"/>
-    <mergeCell ref="A31:A47"/>
-    <mergeCell ref="B16:J21"/>
-    <mergeCell ref="A22:A30"/>
-    <mergeCell ref="B23:J30"/>
-    <mergeCell ref="B22:J22"/>
-    <mergeCell ref="B31:J31"/>
+    <mergeCell ref="B3:J3"/>
+    <mergeCell ref="B4:J4"/>
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="B1:D2"/>
+    <mergeCell ref="E1:J2"/>
+    <mergeCell ref="A3:A4"/>
   </mergeCells>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.51200000000000001" footer="0.51200000000000001"/>
@@ -8437,6 +8461,15 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="ドキュメント" ma:contentTypeID="0x01010058BEBA3CD4E69545839402B5D4E5400B" ma:contentTypeVersion="13" ma:contentTypeDescription="新しいドキュメントを作成します。" ma:contentTypeScope="" ma:versionID="85fadafb228503a8e253560e9cdffc69">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="88cc3c26-756f-41ab-80ed-43e7289fee5b" xmlns:ns3="55239288-d498-4dd6-9609-491b39ec8fae" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="9785dde68d2e35ac7b66dd15e8e44124" ns2:_="" ns3:_="">
     <xsd:import namespace="88cc3c26-756f-41ab-80ed-43e7289fee5b"/>
@@ -8643,15 +8676,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{82E555AC-3D9C-4ECE-9578-D2E452F320B7}">
   <ds:schemaRefs>
@@ -8672,6 +8696,14 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0843C284-C2B9-4564-B59A-F2FA129FE5C7}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{18D765C5-969E-4095-9A45-9E80C6C2EDED}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -8688,12 +8720,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0843C284-C2B9-4564-B59A-F2FA129FE5C7}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/11_プロジェクト計画書.xlsx
+++ b/11_プロジェクト計画書.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\k_tanoue\Documents\GitHub\tanouesoftware\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9711C1D7-0033-42E5-B830-3D30125165A1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4F6E0CD4-E445-47D9-9AC1-E2E31E94AD35}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="プロジェクト計画" sheetId="1" r:id="rId1"/>
@@ -21,7 +21,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="1">'別紙１） 機能要件'!$A$1:$H$39</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="2">'別紙１）非機能要件'!$A$1:$I$38</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="2">'別紙１）非機能要件'!$A$1:$I$39</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="3">'別紙２）開発スケジュール予定＆実績'!$A$1:$AZ$23</definedName>
   </definedNames>
   <calcPr calcId="191028"/>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="199" uniqueCount="111">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="194" uniqueCount="145">
   <si>
     <t>プロジェクト計画書</t>
     <rPh sb="6" eb="9">
@@ -297,341 +297,6 @@
     <phoneticPr fontId="4"/>
   </si>
   <si>
-    <t>新規取引</t>
-    <rPh sb="0" eb="2">
-      <t>シンキ</t>
-    </rPh>
-    <rPh sb="2" eb="4">
-      <t>トリヒキ</t>
-    </rPh>
-    <phoneticPr fontId="4"/>
-  </si>
-  <si>
-    <t>新規取引申請</t>
-    <rPh sb="0" eb="2">
-      <t>シンキ</t>
-    </rPh>
-    <rPh sb="2" eb="4">
-      <t>トリヒキ</t>
-    </rPh>
-    <rPh sb="4" eb="6">
-      <t>シンセイ</t>
-    </rPh>
-    <phoneticPr fontId="4"/>
-  </si>
-  <si>
-    <t>入力系</t>
-    <rPh sb="0" eb="2">
-      <t>ニュウリョク</t>
-    </rPh>
-    <rPh sb="2" eb="3">
-      <t>ケイ</t>
-    </rPh>
-    <phoneticPr fontId="4"/>
-  </si>
-  <si>
-    <t>ｘｘｘができる</t>
-    <phoneticPr fontId="4"/>
-  </si>
-  <si>
-    <t>実装済み</t>
-    <rPh sb="0" eb="2">
-      <t>ジッソウ</t>
-    </rPh>
-    <rPh sb="2" eb="3">
-      <t>ス</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>新規取引申請承認</t>
-    <rPh sb="0" eb="2">
-      <t>シンキ</t>
-    </rPh>
-    <rPh sb="2" eb="4">
-      <t>トリヒキ</t>
-    </rPh>
-    <rPh sb="4" eb="6">
-      <t>シンセイ</t>
-    </rPh>
-    <rPh sb="6" eb="8">
-      <t>ショウニン</t>
-    </rPh>
-    <phoneticPr fontId="4"/>
-  </si>
-  <si>
-    <t>未実施</t>
-    <rPh sb="0" eb="3">
-      <t>ミジッシ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>信用調査結果登録</t>
-    <rPh sb="0" eb="2">
-      <t>シンヨウ</t>
-    </rPh>
-    <rPh sb="2" eb="4">
-      <t>チョウサ</t>
-    </rPh>
-    <rPh sb="4" eb="6">
-      <t>ケッカ</t>
-    </rPh>
-    <rPh sb="6" eb="8">
-      <t>トウロク</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>与信限度額登録</t>
-    <rPh sb="0" eb="2">
-      <t>ヨシン</t>
-    </rPh>
-    <rPh sb="2" eb="4">
-      <t>ゲンド</t>
-    </rPh>
-    <rPh sb="4" eb="5">
-      <t>ガク</t>
-    </rPh>
-    <rPh sb="5" eb="7">
-      <t>トウロク</t>
-    </rPh>
-    <phoneticPr fontId="4"/>
-  </si>
-  <si>
-    <t>販売条件登録</t>
-    <rPh sb="0" eb="2">
-      <t>ハンバイ</t>
-    </rPh>
-    <rPh sb="2" eb="4">
-      <t>ジョウケン</t>
-    </rPh>
-    <rPh sb="4" eb="6">
-      <t>トウロク</t>
-    </rPh>
-    <phoneticPr fontId="4"/>
-  </si>
-  <si>
-    <t>受注管理</t>
-    <rPh sb="0" eb="2">
-      <t>ジュチュウ</t>
-    </rPh>
-    <rPh sb="2" eb="4">
-      <t>カンリ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>受注案件登録</t>
-    <rPh sb="0" eb="2">
-      <t>ジュチュウ</t>
-    </rPh>
-    <rPh sb="2" eb="4">
-      <t>アンケン</t>
-    </rPh>
-    <rPh sb="4" eb="6">
-      <t>トウロク</t>
-    </rPh>
-    <phoneticPr fontId="4"/>
-  </si>
-  <si>
-    <t>受注内容登録</t>
-    <rPh sb="0" eb="2">
-      <t>ジュチュウ</t>
-    </rPh>
-    <rPh sb="2" eb="4">
-      <t>ナイヨウ</t>
-    </rPh>
-    <rPh sb="4" eb="6">
-      <t>トウロク</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>出荷管理</t>
-    <rPh sb="0" eb="2">
-      <t>シュッカ</t>
-    </rPh>
-    <rPh sb="2" eb="4">
-      <t>カンリ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>出荷予定登録</t>
-    <rPh sb="0" eb="2">
-      <t>シュッカ</t>
-    </rPh>
-    <rPh sb="2" eb="4">
-      <t>ヨテイ</t>
-    </rPh>
-    <rPh sb="4" eb="6">
-      <t>トウロク</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>出荷依頼</t>
-    <rPh sb="0" eb="2">
-      <t>シュッカ</t>
-    </rPh>
-    <rPh sb="2" eb="4">
-      <t>イライ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>在庫引当</t>
-    <rPh sb="0" eb="2">
-      <t>ザイコ</t>
-    </rPh>
-    <rPh sb="2" eb="3">
-      <t>ヒ</t>
-    </rPh>
-    <rPh sb="3" eb="4">
-      <t>ア</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>在庫確認</t>
-    <rPh sb="0" eb="2">
-      <t>ザイコ</t>
-    </rPh>
-    <rPh sb="2" eb="4">
-      <t>カクニン</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>参照系</t>
-    <rPh sb="0" eb="2">
-      <t>サンショウ</t>
-    </rPh>
-    <rPh sb="2" eb="3">
-      <t>ケイ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>在庫引当</t>
-    <rPh sb="0" eb="2">
-      <t>ザイコ</t>
-    </rPh>
-    <rPh sb="2" eb="4">
-      <t>ヒキアテ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>製品有高帳更新</t>
-    <rPh sb="0" eb="2">
-      <t>セイヒン</t>
-    </rPh>
-    <rPh sb="2" eb="4">
-      <t>アリダカ</t>
-    </rPh>
-    <rPh sb="4" eb="5">
-      <t>チョウ</t>
-    </rPh>
-    <rPh sb="5" eb="7">
-      <t>コウシン</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>製品有高帳参照</t>
-    <rPh sb="0" eb="2">
-      <t>セイヒン</t>
-    </rPh>
-    <rPh sb="2" eb="4">
-      <t>アリダカ</t>
-    </rPh>
-    <rPh sb="4" eb="5">
-      <t>チョウ</t>
-    </rPh>
-    <rPh sb="5" eb="7">
-      <t>サンショウ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>債権管理</t>
-    <rPh sb="0" eb="2">
-      <t>サイケン</t>
-    </rPh>
-    <rPh sb="2" eb="4">
-      <t>カンリ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>債権計上データ取込</t>
-    <rPh sb="0" eb="2">
-      <t>サイケン</t>
-    </rPh>
-    <rPh sb="2" eb="4">
-      <t>ケイジョウ</t>
-    </rPh>
-    <rPh sb="7" eb="9">
-      <t>トリコミ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>請求書発行</t>
-    <rPh sb="0" eb="3">
-      <t>セイキュウショ</t>
-    </rPh>
-    <rPh sb="3" eb="5">
-      <t>ハッコウ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>帳票系</t>
-    <rPh sb="0" eb="2">
-      <t>チョウヒョウ</t>
-    </rPh>
-    <rPh sb="2" eb="3">
-      <t>ケイ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>入金管理</t>
-    <rPh sb="0" eb="2">
-      <t>ニュウキン</t>
-    </rPh>
-    <rPh sb="2" eb="4">
-      <t>カンリ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>入金入力</t>
-    <rPh sb="0" eb="2">
-      <t>ニュウキン</t>
-    </rPh>
-    <rPh sb="2" eb="4">
-      <t>ニュウリョク</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>入金予定変更</t>
-    <rPh sb="0" eb="2">
-      <t>ニュウキン</t>
-    </rPh>
-    <rPh sb="2" eb="4">
-      <t>ヨテイ</t>
-    </rPh>
-    <rPh sb="4" eb="6">
-      <t>ヘンコウ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>別紙1.システムの非機能要件</t>
     <rPh sb="0" eb="2">
       <t>ベッシ</t>
@@ -661,38 +326,6 @@
       <t>カヨウセイ</t>
     </rPh>
     <phoneticPr fontId="4"/>
-  </si>
-  <si>
-    <t>稼働率</t>
-    <rPh sb="0" eb="2">
-      <t>カドウ</t>
-    </rPh>
-    <rPh sb="2" eb="3">
-      <t>リツ</t>
-    </rPh>
-    <phoneticPr fontId="4"/>
-  </si>
-  <si>
-    <t>達成</t>
-  </si>
-  <si>
-    <t>〇％以上の稼働率を保証する</t>
-    <rPh sb="2" eb="4">
-      <t>イジョウ</t>
-    </rPh>
-    <rPh sb="5" eb="7">
-      <t>カドウ</t>
-    </rPh>
-    <rPh sb="7" eb="8">
-      <t>リツ</t>
-    </rPh>
-    <rPh sb="9" eb="11">
-      <t>ホショウ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>未達成</t>
   </si>
   <si>
     <t>性能
@@ -704,51 +337,6 @@
       <t>カクチョウセイ</t>
     </rPh>
     <phoneticPr fontId="4"/>
-  </si>
-  <si>
-    <t>レスポンスタイム</t>
-    <phoneticPr fontId="4"/>
-  </si>
-  <si>
-    <t>〇〇処理（機能）において、〇秒以内に実行できる</t>
-    <rPh sb="2" eb="4">
-      <t>ショリ</t>
-    </rPh>
-    <rPh sb="5" eb="7">
-      <t>キノウ</t>
-    </rPh>
-    <rPh sb="14" eb="15">
-      <t>ビョウ</t>
-    </rPh>
-    <rPh sb="15" eb="17">
-      <t>イナイ</t>
-    </rPh>
-    <rPh sb="18" eb="20">
-      <t>ジッコウ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>ピーク時において、××処理（機能）を〇秒以内に実行できる</t>
-    <rPh sb="3" eb="4">
-      <t>ジ</t>
-    </rPh>
-    <rPh sb="11" eb="13">
-      <t>ショリ</t>
-    </rPh>
-    <rPh sb="14" eb="16">
-      <t>キノウ</t>
-    </rPh>
-    <rPh sb="19" eb="20">
-      <t>ビョウ</t>
-    </rPh>
-    <rPh sb="20" eb="22">
-      <t>イナイ</t>
-    </rPh>
-    <rPh sb="23" eb="25">
-      <t>ジッコウ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
   </si>
   <si>
     <t>運用
@@ -1081,6 +669,955 @@
   </si>
   <si>
     <t>Amazon Linux 2023</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>被害状況管理</t>
+    <rPh sb="0" eb="2">
+      <t>ヒガイ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>ジョウキョウ</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>カンリ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>被害情報登録</t>
+    <rPh sb="0" eb="2">
+      <t>ヒガイ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>ジョウホウ</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>トウロク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>建物情報登録</t>
+    <rPh sb="0" eb="2">
+      <t>タテモノ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>ジョウホウ</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>トウロク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>被害写真登録</t>
+    <rPh sb="0" eb="2">
+      <t>ヒガイ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>シャシン</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>トウロク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>質問回答登録</t>
+    <rPh sb="0" eb="2">
+      <t>シツモン</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>カイトウ</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>トウロク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>被害情報更新</t>
+    <rPh sb="0" eb="2">
+      <t>ヒガイ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>ジョウホウ</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>コウシン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>被害情報編集</t>
+    <rPh sb="0" eb="2">
+      <t>ヒガイ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>ジョウホウ</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>ヘンシュウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>被害情報削除</t>
+    <rPh sb="0" eb="2">
+      <t>ヒガイ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>ジョウホウ</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>サクジョ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>被害状況分析</t>
+    <rPh sb="0" eb="2">
+      <t>ヒガイ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>ジョウキョウ</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>ブンセキ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>AI分析</t>
+    <rPh sb="2" eb="4">
+      <t>ブンセキ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>被害状況分析実行</t>
+    <rPh sb="0" eb="2">
+      <t>ヒガイ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>ジョウキョウ</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>ブンセキ</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>ジッコウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>分析結果確認</t>
+    <rPh sb="0" eb="2">
+      <t>ブンセキ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>ケッカ</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>カクニン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>分析結果表示</t>
+    <rPh sb="0" eb="2">
+      <t>ブンセキ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>ケッカ</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>ヒョウジ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>被害分析履歴</t>
+    <rPh sb="0" eb="2">
+      <t>ヒガイ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>ブンセキ</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>リレキ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>履歴一覧表示</t>
+    <rPh sb="0" eb="2">
+      <t>リレキ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>イチラン</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>ヒョウジ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>履歴詳細表示</t>
+    <rPh sb="0" eb="2">
+      <t>リレキ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>ショウサイ</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>ヒョウジ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>復旧支援</t>
+    <rPh sb="0" eb="2">
+      <t>フッキュウ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>シエン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>修理費用情報</t>
+    <rPh sb="0" eb="2">
+      <t>シュウリ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>ヒヨウ</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>ジョウホウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>修理費用目安表示</t>
+    <rPh sb="0" eb="2">
+      <t>シュウリ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>ヒヨウ</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>メヤス</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>ヒョウジ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>修理業者情報</t>
+    <rPh sb="0" eb="2">
+      <t>シュウリ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>ギョウシャ</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>ジョウホウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>修理業者表示</t>
+    <rPh sb="0" eb="2">
+      <t>シュウリ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>ギョウシャ</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>ヒョウジ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>各種申請情報</t>
+    <rPh sb="0" eb="2">
+      <t>カクシュ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>シンセイ</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>ジョウホウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>罹災証明書申請案内</t>
+    <rPh sb="0" eb="2">
+      <t>リサイ</t>
+    </rPh>
+    <rPh sb="2" eb="5">
+      <t>ショウメイショ</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>シンセイ</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>アンナイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ユーザ認証</t>
+    <rPh sb="3" eb="5">
+      <t>ニンショウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>認証</t>
+    <rPh sb="0" eb="2">
+      <t>ニンショウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>LINEログイン</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ログアウト</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>入力系</t>
+    <rPh sb="0" eb="2">
+      <t>ニュウリョク</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>ケイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>AI・分析系</t>
+    <rPh sb="3" eb="5">
+      <t>ブンセキ</t>
+    </rPh>
+    <rPh sb="5" eb="6">
+      <t>ケイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>参照系</t>
+    <rPh sb="0" eb="2">
+      <t>サンショウ</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>ケイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>認証系</t>
+    <rPh sb="0" eb="2">
+      <t>ニンショウ</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>ケイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>建物の情報(築年数等)を登録できる</t>
+    <rPh sb="0" eb="2">
+      <t>タテモノ</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>ジョウホウ</t>
+    </rPh>
+    <rPh sb="6" eb="7">
+      <t>チク</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>ネンスウ</t>
+    </rPh>
+    <rPh sb="9" eb="10">
+      <t>トウ</t>
+    </rPh>
+    <rPh sb="12" eb="14">
+      <t>トウロク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>被害写真を登録できる</t>
+    <rPh sb="0" eb="2">
+      <t>ヒガイ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>シャシン</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>トウロク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>被害状況質問への回答を登録できる</t>
+    <rPh sb="0" eb="2">
+      <t>ヒガイ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>ジョウキョウ</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>シツモン</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>カイトウ</t>
+    </rPh>
+    <rPh sb="11" eb="13">
+      <t>トウロク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>登録した被害情報を編集できる</t>
+    <rPh sb="0" eb="2">
+      <t>トウロク</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>ヒガイ</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>ジョウホウ</t>
+    </rPh>
+    <rPh sb="9" eb="11">
+      <t>ヘンシュウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>登録した被害情報を削除できる</t>
+    <rPh sb="0" eb="2">
+      <t>トウロク</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>ヒガイ</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>ジョウホウ</t>
+    </rPh>
+    <rPh sb="9" eb="11">
+      <t>サクジョ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>分析結果を表示できる</t>
+    <rPh sb="0" eb="2">
+      <t>ブンセキ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>ケッカ</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>ヒョウジ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>分析結果履歴の一覧を表示できる</t>
+    <rPh sb="0" eb="2">
+      <t>ブンセキ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>ケッカ</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>リレキ</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>イチラン</t>
+    </rPh>
+    <rPh sb="10" eb="12">
+      <t>ヒョウジ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>分析結果履歴の詳細を表示できる</t>
+    <rPh sb="0" eb="2">
+      <t>ブンセキ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>ケッカ</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>リレキ</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>ショウサイ</t>
+    </rPh>
+    <rPh sb="10" eb="12">
+      <t>ヒョウジ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>被害状況の目安をAIで分析できる</t>
+    <rPh sb="0" eb="2">
+      <t>ヒガイ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>ジョウキョウ</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>メヤス</t>
+    </rPh>
+    <rPh sb="11" eb="13">
+      <t>ブンセキ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>修理費用の目安を表示できる</t>
+    <rPh sb="0" eb="2">
+      <t>シュウリ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>ヒヨウ</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>メヤス</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>ヒョウジ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>罹災証明書申請の案内ができる</t>
+    <rPh sb="0" eb="2">
+      <t>リサイ</t>
+    </rPh>
+    <rPh sb="2" eb="5">
+      <t>ショウメイショ</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>シンセイ</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>アンナイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ログアウトができる</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>LINEアカウントでログインができる</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>建物周辺の修理業者を表示できる</t>
+    <rPh sb="0" eb="2">
+      <t>タテモノ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>シュウヘン</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>シュウリ</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>ギョウシャ</t>
+    </rPh>
+    <rPh sb="10" eb="12">
+      <t>ヒョウジ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>稼働率</t>
+    <rPh sb="0" eb="2">
+      <t>カドウ</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>リツ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>月間稼働率99.0%以上を目標とする</t>
+    <rPh sb="0" eb="2">
+      <t>ゲッカン</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>カドウ</t>
+    </rPh>
+    <rPh sb="4" eb="5">
+      <t>リツ</t>
+    </rPh>
+    <rPh sb="10" eb="12">
+      <t>イジョウ</t>
+    </rPh>
+    <rPh sb="13" eb="15">
+      <t>モクヒョウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>レスポンスタイム</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>通常の画面操作に対して3秒以内に応答する</t>
+    <rPh sb="0" eb="2">
+      <t>ツウジョウ</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>ガメン</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>ソウサ</t>
+    </rPh>
+    <rPh sb="8" eb="9">
+      <t>タイ</t>
+    </rPh>
+    <rPh sb="12" eb="13">
+      <t>ビョウ</t>
+    </rPh>
+    <rPh sb="13" eb="15">
+      <t>イナイ</t>
+    </rPh>
+    <rPh sb="16" eb="18">
+      <t>オウトウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>AI(Gemini API)による分析が30秒以内で完了することを目標とする</t>
+    <rPh sb="17" eb="19">
+      <t>ブンセキ</t>
+    </rPh>
+    <rPh sb="22" eb="23">
+      <t>ビョウ</t>
+    </rPh>
+    <rPh sb="23" eb="25">
+      <t>イナイ</t>
+    </rPh>
+    <rPh sb="26" eb="28">
+      <t>カンリョウ</t>
+    </rPh>
+    <rPh sb="33" eb="35">
+      <t>モクヒョウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>拡張性</t>
+    <rPh sb="0" eb="3">
+      <t>カクチョウセイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>災害発生後の利用者急増を想定し、利用者数の増加に応じてAWSのサーバーリソースを拡張できる構成とする</t>
+    <rPh sb="0" eb="2">
+      <t>サイガイ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>ハッセイ</t>
+    </rPh>
+    <rPh sb="4" eb="5">
+      <t>ゴ</t>
+    </rPh>
+    <rPh sb="6" eb="9">
+      <t>リヨウシャ</t>
+    </rPh>
+    <rPh sb="9" eb="11">
+      <t>キュウゾウ</t>
+    </rPh>
+    <rPh sb="12" eb="14">
+      <t>ソウテイ</t>
+    </rPh>
+    <rPh sb="16" eb="18">
+      <t>リヨウ</t>
+    </rPh>
+    <rPh sb="18" eb="19">
+      <t>シャ</t>
+    </rPh>
+    <rPh sb="19" eb="20">
+      <t>スウ</t>
+    </rPh>
+    <rPh sb="21" eb="23">
+      <t>ゾウカ</t>
+    </rPh>
+    <rPh sb="24" eb="25">
+      <t>オウ</t>
+    </rPh>
+    <rPh sb="40" eb="42">
+      <t>カクチョウ</t>
+    </rPh>
+    <rPh sb="45" eb="47">
+      <t>コウセイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>運用保守性</t>
+    <rPh sb="0" eb="2">
+      <t>ウンヨウ</t>
+    </rPh>
+    <rPh sb="2" eb="5">
+      <t>ホシュセイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>データベースを1日1回バックアップする</t>
+    <rPh sb="8" eb="9">
+      <t>ニチ</t>
+    </rPh>
+    <rPh sb="10" eb="11">
+      <t>カイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>環境移行</t>
+    <rPh sb="0" eb="2">
+      <t>カンキョウ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>イコウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ローカル開発環境からAWS EC2の本番環境へ移行して動作できる構成とする</t>
+    <rPh sb="4" eb="6">
+      <t>カイハツ</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>カンキョウ</t>
+    </rPh>
+    <rPh sb="18" eb="20">
+      <t>ホンバン</t>
+    </rPh>
+    <rPh sb="20" eb="22">
+      <t>カンキョウ</t>
+    </rPh>
+    <rPh sb="23" eb="25">
+      <t>イコウ</t>
+    </rPh>
+    <rPh sb="27" eb="29">
+      <t>ドウサ</t>
+    </rPh>
+    <rPh sb="32" eb="34">
+      <t>コウセイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>通信暗号化</t>
+    <rPh sb="0" eb="2">
+      <t>ツウシン</t>
+    </rPh>
+    <rPh sb="2" eb="5">
+      <t>アンゴウカ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>HTTPS通信を使用してデータを暗号化する</t>
+    <rPh sb="5" eb="7">
+      <t>ツウシン</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>シヨウ</t>
+    </rPh>
+    <rPh sb="16" eb="19">
+      <t>アンゴウカ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>認証</t>
+    <rPh sb="0" eb="2">
+      <t>ニンショウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>LINE Loginを利用し、本人確認を行った利用者のみシステムを利用できるようにする</t>
+    <rPh sb="11" eb="13">
+      <t>リヨウ</t>
+    </rPh>
+    <rPh sb="15" eb="17">
+      <t>ホンニン</t>
+    </rPh>
+    <rPh sb="17" eb="19">
+      <t>カクニン</t>
+    </rPh>
+    <rPh sb="20" eb="21">
+      <t>オコナ</t>
+    </rPh>
+    <rPh sb="23" eb="26">
+      <t>リヨウシャ</t>
+    </rPh>
+    <rPh sb="33" eb="35">
+      <t>リヨウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>認可</t>
+    <rPh sb="0" eb="2">
+      <t>ニンカ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>利用者自身の被害情報・写真・分析結果のみ参照・編集できるようにする</t>
+    <rPh sb="0" eb="3">
+      <t>リヨウシャ</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>ジシン</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>ヒガイ</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>ジョウホウ</t>
+    </rPh>
+    <rPh sb="11" eb="13">
+      <t>シャシン</t>
+    </rPh>
+    <rPh sb="14" eb="16">
+      <t>ブンセキ</t>
+    </rPh>
+    <rPh sb="16" eb="18">
+      <t>ケッカ</t>
+    </rPh>
+    <rPh sb="20" eb="22">
+      <t>サンショウ</t>
+    </rPh>
+    <rPh sb="23" eb="25">
+      <t>ヘンシュウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>アップロード制御</t>
+    <rPh sb="6" eb="8">
+      <t>セイギョ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>アップロードできる画像のファイル形式・容量などを制限し、不正なファイルの登録を防止する</t>
+    <rPh sb="9" eb="11">
+      <t>ガゾウ</t>
+    </rPh>
+    <rPh sb="16" eb="18">
+      <t>ケイシキ</t>
+    </rPh>
+    <rPh sb="19" eb="21">
+      <t>ヨウリョウ</t>
+    </rPh>
+    <rPh sb="24" eb="26">
+      <t>セイゲン</t>
+    </rPh>
+    <rPh sb="28" eb="30">
+      <t>フセイ</t>
+    </rPh>
+    <rPh sb="36" eb="38">
+      <t>トウロク</t>
+    </rPh>
+    <rPh sb="39" eb="41">
+      <t>ボウシ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>APIキー管理</t>
+    <rPh sb="5" eb="7">
+      <t>カンリ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>対応ブラウザ</t>
+    <rPh sb="0" eb="2">
+      <t>タイオウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Gemini APIの認証情報を利用者側に公開せず、サーバー側で安全に管理する</t>
+    <rPh sb="11" eb="13">
+      <t>ニンショウ</t>
+    </rPh>
+    <rPh sb="13" eb="15">
+      <t>ジョウホウ</t>
+    </rPh>
+    <rPh sb="16" eb="19">
+      <t>リヨウシャ</t>
+    </rPh>
+    <rPh sb="19" eb="20">
+      <t>ガワ</t>
+    </rPh>
+    <rPh sb="21" eb="23">
+      <t>コウカイ</t>
+    </rPh>
+    <rPh sb="30" eb="31">
+      <t>ガワ</t>
+    </rPh>
+    <rPh sb="32" eb="34">
+      <t>アンゼン</t>
+    </rPh>
+    <rPh sb="35" eb="37">
+      <t>カンリ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Android:Chrome、iOS:Safari、Windows:Edge・Chromeの最新版に対応する</t>
+    <rPh sb="46" eb="49">
+      <t>サイシンバン</t>
+    </rPh>
+    <rPh sb="50" eb="52">
+      <t>タイオウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>対応デバイス</t>
+    <rPh sb="0" eb="2">
+      <t>タイオウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Android・iOSを搭載したスマートフォン及びWindows PCに対応する</t>
+    <rPh sb="12" eb="14">
+      <t>トウサイ</t>
+    </rPh>
+    <rPh sb="23" eb="24">
+      <t>オヨ</t>
+    </rPh>
+    <rPh sb="36" eb="38">
+      <t>タイオウ</t>
+    </rPh>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -2040,7 +2577,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="196">
+  <cellXfs count="203">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -2122,6 +2659,69 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="66" xfId="1" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="50" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="51" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="51" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="2" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
@@ -2173,9 +2773,6 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -2269,9 +2866,6 @@
     <xf numFmtId="0" fontId="7" fillId="2" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
@@ -2287,71 +2881,23 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="50" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="50" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="50" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="51" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="50" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="51" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="32" xfId="1" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
@@ -2628,6 +3174,18 @@
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="50" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -3447,1393 +4005,1393 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" s="2" customFormat="1" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="68" t="s">
+      <c r="A1" s="88" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="68"/>
-      <c r="C1" s="68"/>
-      <c r="D1" s="68"/>
-      <c r="E1" s="68"/>
-      <c r="F1" s="68"/>
-      <c r="G1" s="68"/>
-      <c r="H1" s="68"/>
-      <c r="I1" s="68"/>
-      <c r="J1" s="68"/>
+      <c r="B1" s="88"/>
+      <c r="C1" s="88"/>
+      <c r="D1" s="88"/>
+      <c r="E1" s="88"/>
+      <c r="F1" s="88"/>
+      <c r="G1" s="88"/>
+      <c r="H1" s="88"/>
+      <c r="I1" s="88"/>
+      <c r="J1" s="88"/>
     </row>
     <row r="2" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="27">
+      <c r="A2" s="48">
         <v>1</v>
       </c>
-      <c r="B2" s="34" t="s">
+      <c r="B2" s="55" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="34"/>
-      <c r="D2" s="34"/>
-      <c r="E2" s="36"/>
-      <c r="F2" s="36"/>
-      <c r="G2" s="36"/>
-      <c r="H2" s="36"/>
-      <c r="I2" s="36"/>
-      <c r="J2" s="37"/>
+      <c r="C2" s="55"/>
+      <c r="D2" s="55"/>
+      <c r="E2" s="57"/>
+      <c r="F2" s="57"/>
+      <c r="G2" s="57"/>
+      <c r="H2" s="57"/>
+      <c r="I2" s="57"/>
+      <c r="J2" s="58"/>
     </row>
     <row r="3" spans="1:10" ht="13.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="31"/>
-      <c r="B3" s="35"/>
-      <c r="C3" s="35"/>
-      <c r="D3" s="35"/>
-      <c r="E3" s="38"/>
-      <c r="F3" s="38"/>
-      <c r="G3" s="38"/>
-      <c r="H3" s="38"/>
-      <c r="I3" s="38"/>
-      <c r="J3" s="39"/>
+      <c r="A3" s="52"/>
+      <c r="B3" s="56"/>
+      <c r="C3" s="56"/>
+      <c r="D3" s="56"/>
+      <c r="E3" s="59"/>
+      <c r="F3" s="59"/>
+      <c r="G3" s="59"/>
+      <c r="H3" s="59"/>
+      <c r="I3" s="59"/>
+      <c r="J3" s="60"/>
     </row>
     <row r="4" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="27">
+      <c r="A4" s="48">
         <v>2</v>
       </c>
-      <c r="B4" s="32" t="s">
+      <c r="B4" s="53" t="s">
         <v>2</v>
       </c>
-      <c r="C4" s="32"/>
-      <c r="D4" s="32"/>
-      <c r="E4" s="32"/>
-      <c r="F4" s="32"/>
-      <c r="G4" s="32"/>
-      <c r="H4" s="32"/>
-      <c r="I4" s="32"/>
-      <c r="J4" s="33"/>
+      <c r="C4" s="53"/>
+      <c r="D4" s="53"/>
+      <c r="E4" s="53"/>
+      <c r="F4" s="53"/>
+      <c r="G4" s="53"/>
+      <c r="H4" s="53"/>
+      <c r="I4" s="53"/>
+      <c r="J4" s="54"/>
     </row>
     <row r="5" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="28"/>
-      <c r="B5" s="46" t="s">
+      <c r="A5" s="49"/>
+      <c r="B5" s="66" t="s">
         <v>3</v>
       </c>
-      <c r="C5" s="46"/>
-      <c r="D5" s="46"/>
-      <c r="E5" s="46"/>
-      <c r="F5" s="46"/>
-      <c r="G5" s="46"/>
-      <c r="H5" s="46"/>
-      <c r="I5" s="46"/>
-      <c r="J5" s="47"/>
+      <c r="C5" s="66"/>
+      <c r="D5" s="66"/>
+      <c r="E5" s="66"/>
+      <c r="F5" s="66"/>
+      <c r="G5" s="66"/>
+      <c r="H5" s="66"/>
+      <c r="I5" s="66"/>
+      <c r="J5" s="67"/>
     </row>
     <row r="6" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="28"/>
-      <c r="B6" s="46"/>
-      <c r="C6" s="46"/>
-      <c r="D6" s="46"/>
-      <c r="E6" s="46"/>
-      <c r="F6" s="46"/>
-      <c r="G6" s="46"/>
-      <c r="H6" s="46"/>
-      <c r="I6" s="46"/>
-      <c r="J6" s="47"/>
+      <c r="A6" s="49"/>
+      <c r="B6" s="66"/>
+      <c r="C6" s="66"/>
+      <c r="D6" s="66"/>
+      <c r="E6" s="66"/>
+      <c r="F6" s="66"/>
+      <c r="G6" s="66"/>
+      <c r="H6" s="66"/>
+      <c r="I6" s="66"/>
+      <c r="J6" s="67"/>
     </row>
     <row r="7" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="28"/>
-      <c r="B7" s="48"/>
-      <c r="C7" s="48"/>
-      <c r="D7" s="48"/>
-      <c r="E7" s="48"/>
-      <c r="F7" s="48"/>
-      <c r="G7" s="48"/>
-      <c r="H7" s="48"/>
-      <c r="I7" s="48"/>
-      <c r="J7" s="49"/>
+      <c r="A7" s="49"/>
+      <c r="B7" s="68"/>
+      <c r="C7" s="68"/>
+      <c r="D7" s="68"/>
+      <c r="E7" s="68"/>
+      <c r="F7" s="68"/>
+      <c r="G7" s="68"/>
+      <c r="H7" s="68"/>
+      <c r="I7" s="68"/>
+      <c r="J7" s="69"/>
     </row>
     <row r="8" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="28"/>
-      <c r="B8" s="61" t="s">
-        <v>105</v>
-      </c>
-      <c r="C8" s="62"/>
-      <c r="D8" s="62"/>
-      <c r="E8" s="62"/>
-      <c r="F8" s="62"/>
-      <c r="G8" s="62"/>
-      <c r="H8" s="62"/>
-      <c r="I8" s="62"/>
-      <c r="J8" s="63"/>
+      <c r="A8" s="49"/>
+      <c r="B8" s="81" t="s">
+        <v>69</v>
+      </c>
+      <c r="C8" s="82"/>
+      <c r="D8" s="82"/>
+      <c r="E8" s="82"/>
+      <c r="F8" s="82"/>
+      <c r="G8" s="82"/>
+      <c r="H8" s="82"/>
+      <c r="I8" s="82"/>
+      <c r="J8" s="83"/>
     </row>
     <row r="9" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="28"/>
-      <c r="B9" s="64"/>
-      <c r="C9" s="65"/>
-      <c r="D9" s="65"/>
-      <c r="E9" s="65"/>
-      <c r="F9" s="65"/>
-      <c r="G9" s="65"/>
-      <c r="H9" s="65"/>
-      <c r="I9" s="65"/>
-      <c r="J9" s="66"/>
+      <c r="A9" s="49"/>
+      <c r="B9" s="84"/>
+      <c r="C9" s="85"/>
+      <c r="D9" s="85"/>
+      <c r="E9" s="85"/>
+      <c r="F9" s="85"/>
+      <c r="G9" s="85"/>
+      <c r="H9" s="85"/>
+      <c r="I9" s="85"/>
+      <c r="J9" s="86"/>
     </row>
     <row r="10" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="28"/>
-      <c r="B10" s="64"/>
-      <c r="C10" s="65"/>
-      <c r="D10" s="65"/>
-      <c r="E10" s="65"/>
-      <c r="F10" s="65"/>
-      <c r="G10" s="65"/>
-      <c r="H10" s="65"/>
-      <c r="I10" s="65"/>
-      <c r="J10" s="66"/>
+      <c r="A10" s="49"/>
+      <c r="B10" s="84"/>
+      <c r="C10" s="85"/>
+      <c r="D10" s="85"/>
+      <c r="E10" s="85"/>
+      <c r="F10" s="85"/>
+      <c r="G10" s="85"/>
+      <c r="H10" s="85"/>
+      <c r="I10" s="85"/>
+      <c r="J10" s="86"/>
     </row>
     <row r="11" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="28"/>
-      <c r="B11" s="64"/>
-      <c r="C11" s="65"/>
-      <c r="D11" s="65"/>
-      <c r="E11" s="65"/>
-      <c r="F11" s="65"/>
-      <c r="G11" s="65"/>
-      <c r="H11" s="65"/>
-      <c r="I11" s="65"/>
-      <c r="J11" s="66"/>
+      <c r="A11" s="49"/>
+      <c r="B11" s="84"/>
+      <c r="C11" s="85"/>
+      <c r="D11" s="85"/>
+      <c r="E11" s="85"/>
+      <c r="F11" s="85"/>
+      <c r="G11" s="85"/>
+      <c r="H11" s="85"/>
+      <c r="I11" s="85"/>
+      <c r="J11" s="86"/>
     </row>
     <row r="12" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="28"/>
-      <c r="B12" s="64"/>
-      <c r="C12" s="65"/>
-      <c r="D12" s="65"/>
-      <c r="E12" s="65"/>
-      <c r="F12" s="65"/>
-      <c r="G12" s="65"/>
-      <c r="H12" s="65"/>
-      <c r="I12" s="65"/>
-      <c r="J12" s="66"/>
+      <c r="A12" s="49"/>
+      <c r="B12" s="84"/>
+      <c r="C12" s="85"/>
+      <c r="D12" s="85"/>
+      <c r="E12" s="85"/>
+      <c r="F12" s="85"/>
+      <c r="G12" s="85"/>
+      <c r="H12" s="85"/>
+      <c r="I12" s="85"/>
+      <c r="J12" s="86"/>
     </row>
     <row r="13" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="28"/>
-      <c r="B13" s="64"/>
-      <c r="C13" s="65"/>
-      <c r="D13" s="65"/>
-      <c r="E13" s="65"/>
-      <c r="F13" s="65"/>
-      <c r="G13" s="65"/>
-      <c r="H13" s="65"/>
-      <c r="I13" s="65"/>
-      <c r="J13" s="66"/>
+      <c r="A13" s="49"/>
+      <c r="B13" s="84"/>
+      <c r="C13" s="85"/>
+      <c r="D13" s="85"/>
+      <c r="E13" s="85"/>
+      <c r="F13" s="85"/>
+      <c r="G13" s="85"/>
+      <c r="H13" s="85"/>
+      <c r="I13" s="85"/>
+      <c r="J13" s="86"/>
     </row>
     <row r="14" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A14" s="28"/>
-      <c r="B14" s="64"/>
-      <c r="C14" s="65"/>
-      <c r="D14" s="65"/>
-      <c r="E14" s="65"/>
-      <c r="F14" s="65"/>
-      <c r="G14" s="65"/>
-      <c r="H14" s="65"/>
-      <c r="I14" s="65"/>
-      <c r="J14" s="66"/>
+      <c r="A14" s="49"/>
+      <c r="B14" s="84"/>
+      <c r="C14" s="85"/>
+      <c r="D14" s="85"/>
+      <c r="E14" s="85"/>
+      <c r="F14" s="85"/>
+      <c r="G14" s="85"/>
+      <c r="H14" s="85"/>
+      <c r="I14" s="85"/>
+      <c r="J14" s="86"/>
     </row>
     <row r="15" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A15" s="28"/>
-      <c r="B15" s="64"/>
-      <c r="C15" s="65"/>
-      <c r="D15" s="65"/>
-      <c r="E15" s="65"/>
-      <c r="F15" s="65"/>
-      <c r="G15" s="65"/>
-      <c r="H15" s="65"/>
-      <c r="I15" s="65"/>
-      <c r="J15" s="66"/>
+      <c r="A15" s="49"/>
+      <c r="B15" s="84"/>
+      <c r="C15" s="85"/>
+      <c r="D15" s="85"/>
+      <c r="E15" s="85"/>
+      <c r="F15" s="85"/>
+      <c r="G15" s="85"/>
+      <c r="H15" s="85"/>
+      <c r="I15" s="85"/>
+      <c r="J15" s="86"/>
     </row>
     <row r="16" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A16" s="28"/>
-      <c r="B16" s="64"/>
-      <c r="C16" s="65"/>
-      <c r="D16" s="65"/>
-      <c r="E16" s="65"/>
-      <c r="F16" s="65"/>
-      <c r="G16" s="65"/>
-      <c r="H16" s="65"/>
-      <c r="I16" s="65"/>
-      <c r="J16" s="66"/>
+      <c r="A16" s="49"/>
+      <c r="B16" s="84"/>
+      <c r="C16" s="85"/>
+      <c r="D16" s="85"/>
+      <c r="E16" s="85"/>
+      <c r="F16" s="85"/>
+      <c r="G16" s="85"/>
+      <c r="H16" s="85"/>
+      <c r="I16" s="85"/>
+      <c r="J16" s="86"/>
     </row>
     <row r="17" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A17" s="31"/>
-      <c r="B17" s="64"/>
-      <c r="C17" s="65"/>
-      <c r="D17" s="65"/>
-      <c r="E17" s="65"/>
-      <c r="F17" s="65"/>
-      <c r="G17" s="65"/>
-      <c r="H17" s="65"/>
-      <c r="I17" s="65"/>
-      <c r="J17" s="66"/>
+      <c r="A17" s="52"/>
+      <c r="B17" s="84"/>
+      <c r="C17" s="85"/>
+      <c r="D17" s="85"/>
+      <c r="E17" s="85"/>
+      <c r="F17" s="85"/>
+      <c r="G17" s="85"/>
+      <c r="H17" s="85"/>
+      <c r="I17" s="85"/>
+      <c r="J17" s="86"/>
     </row>
     <row r="18" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A18" s="31"/>
-      <c r="B18" s="64"/>
-      <c r="C18" s="65"/>
-      <c r="D18" s="65"/>
-      <c r="E18" s="65"/>
-      <c r="F18" s="65"/>
-      <c r="G18" s="65"/>
-      <c r="H18" s="65"/>
-      <c r="I18" s="65"/>
-      <c r="J18" s="66"/>
+      <c r="A18" s="52"/>
+      <c r="B18" s="84"/>
+      <c r="C18" s="85"/>
+      <c r="D18" s="85"/>
+      <c r="E18" s="85"/>
+      <c r="F18" s="85"/>
+      <c r="G18" s="85"/>
+      <c r="H18" s="85"/>
+      <c r="I18" s="85"/>
+      <c r="J18" s="86"/>
     </row>
     <row r="19" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A19" s="31"/>
-      <c r="B19" s="64"/>
-      <c r="C19" s="65"/>
-      <c r="D19" s="65"/>
-      <c r="E19" s="65"/>
-      <c r="F19" s="65"/>
-      <c r="G19" s="65"/>
-      <c r="H19" s="65"/>
-      <c r="I19" s="65"/>
-      <c r="J19" s="66"/>
+      <c r="A19" s="52"/>
+      <c r="B19" s="84"/>
+      <c r="C19" s="85"/>
+      <c r="D19" s="85"/>
+      <c r="E19" s="85"/>
+      <c r="F19" s="85"/>
+      <c r="G19" s="85"/>
+      <c r="H19" s="85"/>
+      <c r="I19" s="85"/>
+      <c r="J19" s="86"/>
     </row>
     <row r="20" spans="1:10" ht="13.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="31"/>
-      <c r="B20" s="64"/>
-      <c r="C20" s="65"/>
-      <c r="D20" s="65"/>
-      <c r="E20" s="65"/>
-      <c r="F20" s="65"/>
-      <c r="G20" s="65"/>
-      <c r="H20" s="65"/>
-      <c r="I20" s="65"/>
-      <c r="J20" s="66"/>
+      <c r="A20" s="52"/>
+      <c r="B20" s="84"/>
+      <c r="C20" s="85"/>
+      <c r="D20" s="85"/>
+      <c r="E20" s="85"/>
+      <c r="F20" s="85"/>
+      <c r="G20" s="85"/>
+      <c r="H20" s="85"/>
+      <c r="I20" s="85"/>
+      <c r="J20" s="86"/>
     </row>
     <row r="21" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A21" s="27">
+      <c r="A21" s="48">
         <v>3</v>
       </c>
-      <c r="B21" s="32" t="s">
+      <c r="B21" s="53" t="s">
         <v>4</v>
       </c>
-      <c r="C21" s="32"/>
-      <c r="D21" s="32"/>
-      <c r="E21" s="32"/>
-      <c r="F21" s="32"/>
-      <c r="G21" s="32"/>
-      <c r="H21" s="32"/>
-      <c r="I21" s="32"/>
-      <c r="J21" s="33"/>
+      <c r="C21" s="53"/>
+      <c r="D21" s="53"/>
+      <c r="E21" s="53"/>
+      <c r="F21" s="53"/>
+      <c r="G21" s="53"/>
+      <c r="H21" s="53"/>
+      <c r="I21" s="53"/>
+      <c r="J21" s="54"/>
     </row>
     <row r="22" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A22" s="28"/>
-      <c r="B22" s="50" t="s">
+      <c r="A22" s="49"/>
+      <c r="B22" s="70" t="s">
         <v>5</v>
       </c>
-      <c r="C22" s="51"/>
-      <c r="D22" s="51"/>
-      <c r="E22" s="51"/>
-      <c r="F22" s="51"/>
-      <c r="G22" s="51"/>
-      <c r="H22" s="51"/>
-      <c r="I22" s="51"/>
-      <c r="J22" s="52"/>
+      <c r="C22" s="71"/>
+      <c r="D22" s="71"/>
+      <c r="E22" s="71"/>
+      <c r="F22" s="71"/>
+      <c r="G22" s="71"/>
+      <c r="H22" s="71"/>
+      <c r="I22" s="71"/>
+      <c r="J22" s="72"/>
     </row>
     <row r="23" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A23" s="28"/>
-      <c r="B23" s="50"/>
-      <c r="C23" s="51"/>
-      <c r="D23" s="51"/>
-      <c r="E23" s="51"/>
-      <c r="F23" s="51"/>
-      <c r="G23" s="51"/>
-      <c r="H23" s="51"/>
-      <c r="I23" s="51"/>
-      <c r="J23" s="52"/>
+      <c r="A23" s="49"/>
+      <c r="B23" s="70"/>
+      <c r="C23" s="71"/>
+      <c r="D23" s="71"/>
+      <c r="E23" s="71"/>
+      <c r="F23" s="71"/>
+      <c r="G23" s="71"/>
+      <c r="H23" s="71"/>
+      <c r="I23" s="71"/>
+      <c r="J23" s="72"/>
     </row>
     <row r="24" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A24" s="28"/>
-      <c r="B24" s="50"/>
-      <c r="C24" s="51"/>
-      <c r="D24" s="51"/>
-      <c r="E24" s="51"/>
-      <c r="F24" s="51"/>
-      <c r="G24" s="51"/>
-      <c r="H24" s="51"/>
-      <c r="I24" s="51"/>
-      <c r="J24" s="52"/>
+      <c r="A24" s="49"/>
+      <c r="B24" s="70"/>
+      <c r="C24" s="71"/>
+      <c r="D24" s="71"/>
+      <c r="E24" s="71"/>
+      <c r="F24" s="71"/>
+      <c r="G24" s="71"/>
+      <c r="H24" s="71"/>
+      <c r="I24" s="71"/>
+      <c r="J24" s="72"/>
     </row>
     <row r="25" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A25" s="28"/>
-      <c r="B25" s="53"/>
-      <c r="C25" s="54"/>
-      <c r="D25" s="54"/>
-      <c r="E25" s="54"/>
-      <c r="F25" s="54"/>
-      <c r="G25" s="54"/>
-      <c r="H25" s="54"/>
-      <c r="I25" s="54"/>
-      <c r="J25" s="55"/>
+      <c r="A25" s="49"/>
+      <c r="B25" s="73"/>
+      <c r="C25" s="74"/>
+      <c r="D25" s="74"/>
+      <c r="E25" s="74"/>
+      <c r="F25" s="74"/>
+      <c r="G25" s="74"/>
+      <c r="H25" s="74"/>
+      <c r="I25" s="74"/>
+      <c r="J25" s="75"/>
     </row>
     <row r="26" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A26" s="28"/>
-      <c r="B26" s="56" t="s">
-        <v>106</v>
-      </c>
-      <c r="C26" s="56"/>
-      <c r="D26" s="56"/>
-      <c r="E26" s="56"/>
-      <c r="F26" s="56"/>
-      <c r="G26" s="56"/>
-      <c r="H26" s="56"/>
-      <c r="I26" s="56"/>
-      <c r="J26" s="57"/>
+      <c r="A26" s="49"/>
+      <c r="B26" s="76" t="s">
+        <v>70</v>
+      </c>
+      <c r="C26" s="76"/>
+      <c r="D26" s="76"/>
+      <c r="E26" s="76"/>
+      <c r="F26" s="76"/>
+      <c r="G26" s="76"/>
+      <c r="H26" s="76"/>
+      <c r="I26" s="76"/>
+      <c r="J26" s="77"/>
     </row>
     <row r="27" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A27" s="28"/>
-      <c r="B27" s="56"/>
-      <c r="C27" s="56"/>
-      <c r="D27" s="56"/>
-      <c r="E27" s="56"/>
-      <c r="F27" s="56"/>
-      <c r="G27" s="56"/>
-      <c r="H27" s="56"/>
-      <c r="I27" s="56"/>
-      <c r="J27" s="57"/>
+      <c r="A27" s="49"/>
+      <c r="B27" s="76"/>
+      <c r="C27" s="76"/>
+      <c r="D27" s="76"/>
+      <c r="E27" s="76"/>
+      <c r="F27" s="76"/>
+      <c r="G27" s="76"/>
+      <c r="H27" s="76"/>
+      <c r="I27" s="76"/>
+      <c r="J27" s="77"/>
     </row>
     <row r="28" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A28" s="28"/>
-      <c r="B28" s="56"/>
-      <c r="C28" s="56"/>
-      <c r="D28" s="56"/>
-      <c r="E28" s="56"/>
-      <c r="F28" s="56"/>
-      <c r="G28" s="56"/>
-      <c r="H28" s="56"/>
-      <c r="I28" s="56"/>
-      <c r="J28" s="57"/>
+      <c r="A28" s="49"/>
+      <c r="B28" s="76"/>
+      <c r="C28" s="76"/>
+      <c r="D28" s="76"/>
+      <c r="E28" s="76"/>
+      <c r="F28" s="76"/>
+      <c r="G28" s="76"/>
+      <c r="H28" s="76"/>
+      <c r="I28" s="76"/>
+      <c r="J28" s="77"/>
     </row>
     <row r="29" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A29" s="28"/>
-      <c r="B29" s="56"/>
-      <c r="C29" s="56"/>
-      <c r="D29" s="56"/>
-      <c r="E29" s="56"/>
-      <c r="F29" s="56"/>
-      <c r="G29" s="56"/>
-      <c r="H29" s="56"/>
-      <c r="I29" s="56"/>
-      <c r="J29" s="57"/>
+      <c r="A29" s="49"/>
+      <c r="B29" s="76"/>
+      <c r="C29" s="76"/>
+      <c r="D29" s="76"/>
+      <c r="E29" s="76"/>
+      <c r="F29" s="76"/>
+      <c r="G29" s="76"/>
+      <c r="H29" s="76"/>
+      <c r="I29" s="76"/>
+      <c r="J29" s="77"/>
     </row>
     <row r="30" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A30" s="28"/>
-      <c r="B30" s="56"/>
-      <c r="C30" s="56"/>
-      <c r="D30" s="56"/>
-      <c r="E30" s="56"/>
-      <c r="F30" s="56"/>
-      <c r="G30" s="56"/>
-      <c r="H30" s="56"/>
-      <c r="I30" s="56"/>
-      <c r="J30" s="57"/>
+      <c r="A30" s="49"/>
+      <c r="B30" s="76"/>
+      <c r="C30" s="76"/>
+      <c r="D30" s="76"/>
+      <c r="E30" s="76"/>
+      <c r="F30" s="76"/>
+      <c r="G30" s="76"/>
+      <c r="H30" s="76"/>
+      <c r="I30" s="76"/>
+      <c r="J30" s="77"/>
     </row>
     <row r="31" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A31" s="28"/>
-      <c r="B31" s="56"/>
-      <c r="C31" s="56"/>
-      <c r="D31" s="56"/>
-      <c r="E31" s="56"/>
-      <c r="F31" s="56"/>
-      <c r="G31" s="56"/>
-      <c r="H31" s="56"/>
-      <c r="I31" s="56"/>
-      <c r="J31" s="57"/>
+      <c r="A31" s="49"/>
+      <c r="B31" s="76"/>
+      <c r="C31" s="76"/>
+      <c r="D31" s="76"/>
+      <c r="E31" s="76"/>
+      <c r="F31" s="76"/>
+      <c r="G31" s="76"/>
+      <c r="H31" s="76"/>
+      <c r="I31" s="76"/>
+      <c r="J31" s="77"/>
     </row>
     <row r="32" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A32" s="28"/>
-      <c r="B32" s="56"/>
-      <c r="C32" s="56"/>
-      <c r="D32" s="56"/>
-      <c r="E32" s="56"/>
-      <c r="F32" s="56"/>
-      <c r="G32" s="56"/>
-      <c r="H32" s="56"/>
-      <c r="I32" s="56"/>
-      <c r="J32" s="57"/>
+      <c r="A32" s="49"/>
+      <c r="B32" s="76"/>
+      <c r="C32" s="76"/>
+      <c r="D32" s="76"/>
+      <c r="E32" s="76"/>
+      <c r="F32" s="76"/>
+      <c r="G32" s="76"/>
+      <c r="H32" s="76"/>
+      <c r="I32" s="76"/>
+      <c r="J32" s="77"/>
     </row>
     <row r="33" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A33" s="28"/>
-      <c r="B33" s="56"/>
-      <c r="C33" s="56"/>
-      <c r="D33" s="56"/>
-      <c r="E33" s="56"/>
-      <c r="F33" s="56"/>
-      <c r="G33" s="56"/>
-      <c r="H33" s="56"/>
-      <c r="I33" s="56"/>
-      <c r="J33" s="57"/>
+      <c r="A33" s="49"/>
+      <c r="B33" s="76"/>
+      <c r="C33" s="76"/>
+      <c r="D33" s="76"/>
+      <c r="E33" s="76"/>
+      <c r="F33" s="76"/>
+      <c r="G33" s="76"/>
+      <c r="H33" s="76"/>
+      <c r="I33" s="76"/>
+      <c r="J33" s="77"/>
     </row>
     <row r="34" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A34" s="28"/>
-      <c r="B34" s="56"/>
-      <c r="C34" s="56"/>
-      <c r="D34" s="56"/>
-      <c r="E34" s="56"/>
-      <c r="F34" s="56"/>
-      <c r="G34" s="56"/>
-      <c r="H34" s="56"/>
-      <c r="I34" s="56"/>
-      <c r="J34" s="57"/>
+      <c r="A34" s="49"/>
+      <c r="B34" s="76"/>
+      <c r="C34" s="76"/>
+      <c r="D34" s="76"/>
+      <c r="E34" s="76"/>
+      <c r="F34" s="76"/>
+      <c r="G34" s="76"/>
+      <c r="H34" s="76"/>
+      <c r="I34" s="76"/>
+      <c r="J34" s="77"/>
     </row>
     <row r="35" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A35" s="28"/>
-      <c r="B35" s="56"/>
-      <c r="C35" s="56"/>
-      <c r="D35" s="56"/>
-      <c r="E35" s="56"/>
-      <c r="F35" s="56"/>
-      <c r="G35" s="56"/>
-      <c r="H35" s="56"/>
-      <c r="I35" s="56"/>
-      <c r="J35" s="57"/>
+      <c r="A35" s="49"/>
+      <c r="B35" s="76"/>
+      <c r="C35" s="76"/>
+      <c r="D35" s="76"/>
+      <c r="E35" s="76"/>
+      <c r="F35" s="76"/>
+      <c r="G35" s="76"/>
+      <c r="H35" s="76"/>
+      <c r="I35" s="76"/>
+      <c r="J35" s="77"/>
     </row>
     <row r="36" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A36" s="28"/>
-      <c r="B36" s="56"/>
-      <c r="C36" s="56"/>
-      <c r="D36" s="56"/>
-      <c r="E36" s="56"/>
-      <c r="F36" s="56"/>
-      <c r="G36" s="56"/>
-      <c r="H36" s="56"/>
-      <c r="I36" s="56"/>
-      <c r="J36" s="57"/>
+      <c r="A36" s="49"/>
+      <c r="B36" s="76"/>
+      <c r="C36" s="76"/>
+      <c r="D36" s="76"/>
+      <c r="E36" s="76"/>
+      <c r="F36" s="76"/>
+      <c r="G36" s="76"/>
+      <c r="H36" s="76"/>
+      <c r="I36" s="76"/>
+      <c r="J36" s="77"/>
     </row>
     <row r="37" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A37" s="28"/>
-      <c r="B37" s="56"/>
-      <c r="C37" s="56"/>
-      <c r="D37" s="56"/>
-      <c r="E37" s="56"/>
-      <c r="F37" s="56"/>
-      <c r="G37" s="56"/>
-      <c r="H37" s="56"/>
-      <c r="I37" s="56"/>
-      <c r="J37" s="57"/>
+      <c r="A37" s="49"/>
+      <c r="B37" s="76"/>
+      <c r="C37" s="76"/>
+      <c r="D37" s="76"/>
+      <c r="E37" s="76"/>
+      <c r="F37" s="76"/>
+      <c r="G37" s="76"/>
+      <c r="H37" s="76"/>
+      <c r="I37" s="76"/>
+      <c r="J37" s="77"/>
     </row>
     <row r="38" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A38" s="28"/>
-      <c r="B38" s="56"/>
-      <c r="C38" s="56"/>
-      <c r="D38" s="56"/>
-      <c r="E38" s="56"/>
-      <c r="F38" s="56"/>
-      <c r="G38" s="56"/>
-      <c r="H38" s="56"/>
-      <c r="I38" s="56"/>
-      <c r="J38" s="57"/>
+      <c r="A38" s="49"/>
+      <c r="B38" s="76"/>
+      <c r="C38" s="76"/>
+      <c r="D38" s="76"/>
+      <c r="E38" s="76"/>
+      <c r="F38" s="76"/>
+      <c r="G38" s="76"/>
+      <c r="H38" s="76"/>
+      <c r="I38" s="76"/>
+      <c r="J38" s="77"/>
     </row>
     <row r="39" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A39" s="28"/>
-      <c r="B39" s="56"/>
-      <c r="C39" s="56"/>
-      <c r="D39" s="56"/>
-      <c r="E39" s="56"/>
-      <c r="F39" s="56"/>
-      <c r="G39" s="56"/>
-      <c r="H39" s="56"/>
-      <c r="I39" s="56"/>
-      <c r="J39" s="57"/>
+      <c r="A39" s="49"/>
+      <c r="B39" s="76"/>
+      <c r="C39" s="76"/>
+      <c r="D39" s="76"/>
+      <c r="E39" s="76"/>
+      <c r="F39" s="76"/>
+      <c r="G39" s="76"/>
+      <c r="H39" s="76"/>
+      <c r="I39" s="76"/>
+      <c r="J39" s="77"/>
     </row>
     <row r="40" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A40" s="28"/>
-      <c r="B40" s="56"/>
-      <c r="C40" s="56"/>
-      <c r="D40" s="56"/>
-      <c r="E40" s="56"/>
-      <c r="F40" s="56"/>
-      <c r="G40" s="56"/>
-      <c r="H40" s="56"/>
-      <c r="I40" s="56"/>
-      <c r="J40" s="57"/>
+      <c r="A40" s="49"/>
+      <c r="B40" s="76"/>
+      <c r="C40" s="76"/>
+      <c r="D40" s="76"/>
+      <c r="E40" s="76"/>
+      <c r="F40" s="76"/>
+      <c r="G40" s="76"/>
+      <c r="H40" s="76"/>
+      <c r="I40" s="76"/>
+      <c r="J40" s="77"/>
     </row>
     <row r="41" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A41" s="28"/>
-      <c r="B41" s="56"/>
-      <c r="C41" s="56"/>
-      <c r="D41" s="56"/>
-      <c r="E41" s="56"/>
-      <c r="F41" s="56"/>
-      <c r="G41" s="56"/>
-      <c r="H41" s="56"/>
-      <c r="I41" s="56"/>
-      <c r="J41" s="57"/>
+      <c r="A41" s="49"/>
+      <c r="B41" s="76"/>
+      <c r="C41" s="76"/>
+      <c r="D41" s="76"/>
+      <c r="E41" s="76"/>
+      <c r="F41" s="76"/>
+      <c r="G41" s="76"/>
+      <c r="H41" s="76"/>
+      <c r="I41" s="76"/>
+      <c r="J41" s="77"/>
     </row>
     <row r="42" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A42" s="28"/>
-      <c r="B42" s="56"/>
-      <c r="C42" s="56"/>
-      <c r="D42" s="56"/>
-      <c r="E42" s="56"/>
-      <c r="F42" s="56"/>
-      <c r="G42" s="56"/>
-      <c r="H42" s="56"/>
-      <c r="I42" s="56"/>
-      <c r="J42" s="57"/>
+      <c r="A42" s="49"/>
+      <c r="B42" s="76"/>
+      <c r="C42" s="76"/>
+      <c r="D42" s="76"/>
+      <c r="E42" s="76"/>
+      <c r="F42" s="76"/>
+      <c r="G42" s="76"/>
+      <c r="H42" s="76"/>
+      <c r="I42" s="76"/>
+      <c r="J42" s="77"/>
     </row>
     <row r="43" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A43" s="28"/>
-      <c r="B43" s="56"/>
-      <c r="C43" s="56"/>
-      <c r="D43" s="56"/>
-      <c r="E43" s="56"/>
-      <c r="F43" s="56"/>
-      <c r="G43" s="56"/>
-      <c r="H43" s="56"/>
-      <c r="I43" s="56"/>
-      <c r="J43" s="57"/>
+      <c r="A43" s="49"/>
+      <c r="B43" s="76"/>
+      <c r="C43" s="76"/>
+      <c r="D43" s="76"/>
+      <c r="E43" s="76"/>
+      <c r="F43" s="76"/>
+      <c r="G43" s="76"/>
+      <c r="H43" s="76"/>
+      <c r="I43" s="76"/>
+      <c r="J43" s="77"/>
     </row>
     <row r="44" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A44" s="28"/>
-      <c r="B44" s="56"/>
-      <c r="C44" s="56"/>
-      <c r="D44" s="56"/>
-      <c r="E44" s="56"/>
-      <c r="F44" s="56"/>
-      <c r="G44" s="56"/>
-      <c r="H44" s="56"/>
-      <c r="I44" s="56"/>
-      <c r="J44" s="57"/>
+      <c r="A44" s="49"/>
+      <c r="B44" s="76"/>
+      <c r="C44" s="76"/>
+      <c r="D44" s="76"/>
+      <c r="E44" s="76"/>
+      <c r="F44" s="76"/>
+      <c r="G44" s="76"/>
+      <c r="H44" s="76"/>
+      <c r="I44" s="76"/>
+      <c r="J44" s="77"/>
     </row>
     <row r="45" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A45" s="28"/>
-      <c r="B45" s="56"/>
-      <c r="C45" s="56"/>
-      <c r="D45" s="56"/>
-      <c r="E45" s="56"/>
-      <c r="F45" s="56"/>
-      <c r="G45" s="56"/>
-      <c r="H45" s="56"/>
-      <c r="I45" s="56"/>
-      <c r="J45" s="57"/>
+      <c r="A45" s="49"/>
+      <c r="B45" s="76"/>
+      <c r="C45" s="76"/>
+      <c r="D45" s="76"/>
+      <c r="E45" s="76"/>
+      <c r="F45" s="76"/>
+      <c r="G45" s="76"/>
+      <c r="H45" s="76"/>
+      <c r="I45" s="76"/>
+      <c r="J45" s="77"/>
     </row>
     <row r="46" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A46" s="28"/>
-      <c r="B46" s="56"/>
-      <c r="C46" s="56"/>
-      <c r="D46" s="56"/>
-      <c r="E46" s="56"/>
-      <c r="F46" s="56"/>
-      <c r="G46" s="56"/>
-      <c r="H46" s="56"/>
-      <c r="I46" s="56"/>
-      <c r="J46" s="57"/>
+      <c r="A46" s="49"/>
+      <c r="B46" s="76"/>
+      <c r="C46" s="76"/>
+      <c r="D46" s="76"/>
+      <c r="E46" s="76"/>
+      <c r="F46" s="76"/>
+      <c r="G46" s="76"/>
+      <c r="H46" s="76"/>
+      <c r="I46" s="76"/>
+      <c r="J46" s="77"/>
     </row>
     <row r="47" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A47" s="28"/>
-      <c r="B47" s="56"/>
-      <c r="C47" s="56"/>
-      <c r="D47" s="56"/>
-      <c r="E47" s="56"/>
-      <c r="F47" s="56"/>
-      <c r="G47" s="56"/>
-      <c r="H47" s="56"/>
-      <c r="I47" s="56"/>
-      <c r="J47" s="57"/>
+      <c r="A47" s="49"/>
+      <c r="B47" s="76"/>
+      <c r="C47" s="76"/>
+      <c r="D47" s="76"/>
+      <c r="E47" s="76"/>
+      <c r="F47" s="76"/>
+      <c r="G47" s="76"/>
+      <c r="H47" s="76"/>
+      <c r="I47" s="76"/>
+      <c r="J47" s="77"/>
     </row>
     <row r="48" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A48" s="28"/>
-      <c r="B48" s="56"/>
-      <c r="C48" s="56"/>
-      <c r="D48" s="56"/>
-      <c r="E48" s="56"/>
-      <c r="F48" s="56"/>
-      <c r="G48" s="56"/>
-      <c r="H48" s="56"/>
-      <c r="I48" s="56"/>
-      <c r="J48" s="57"/>
+      <c r="A48" s="49"/>
+      <c r="B48" s="76"/>
+      <c r="C48" s="76"/>
+      <c r="D48" s="76"/>
+      <c r="E48" s="76"/>
+      <c r="F48" s="76"/>
+      <c r="G48" s="76"/>
+      <c r="H48" s="76"/>
+      <c r="I48" s="76"/>
+      <c r="J48" s="77"/>
     </row>
     <row r="49" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A49" s="28"/>
-      <c r="B49" s="56"/>
-      <c r="C49" s="56"/>
-      <c r="D49" s="56"/>
-      <c r="E49" s="56"/>
-      <c r="F49" s="56"/>
-      <c r="G49" s="56"/>
-      <c r="H49" s="56"/>
-      <c r="I49" s="56"/>
-      <c r="J49" s="57"/>
+      <c r="A49" s="49"/>
+      <c r="B49" s="76"/>
+      <c r="C49" s="76"/>
+      <c r="D49" s="76"/>
+      <c r="E49" s="76"/>
+      <c r="F49" s="76"/>
+      <c r="G49" s="76"/>
+      <c r="H49" s="76"/>
+      <c r="I49" s="76"/>
+      <c r="J49" s="77"/>
     </row>
     <row r="50" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A50" s="28"/>
-      <c r="B50" s="56"/>
-      <c r="C50" s="56"/>
-      <c r="D50" s="56"/>
-      <c r="E50" s="56"/>
-      <c r="F50" s="56"/>
-      <c r="G50" s="56"/>
-      <c r="H50" s="56"/>
-      <c r="I50" s="56"/>
-      <c r="J50" s="57"/>
+      <c r="A50" s="49"/>
+      <c r="B50" s="76"/>
+      <c r="C50" s="76"/>
+      <c r="D50" s="76"/>
+      <c r="E50" s="76"/>
+      <c r="F50" s="76"/>
+      <c r="G50" s="76"/>
+      <c r="H50" s="76"/>
+      <c r="I50" s="76"/>
+      <c r="J50" s="77"/>
     </row>
     <row r="51" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A51" s="28"/>
-      <c r="B51" s="56"/>
-      <c r="C51" s="56"/>
-      <c r="D51" s="56"/>
-      <c r="E51" s="56"/>
-      <c r="F51" s="56"/>
-      <c r="G51" s="56"/>
-      <c r="H51" s="56"/>
-      <c r="I51" s="56"/>
-      <c r="J51" s="57"/>
+      <c r="A51" s="49"/>
+      <c r="B51" s="76"/>
+      <c r="C51" s="76"/>
+      <c r="D51" s="76"/>
+      <c r="E51" s="76"/>
+      <c r="F51" s="76"/>
+      <c r="G51" s="76"/>
+      <c r="H51" s="76"/>
+      <c r="I51" s="76"/>
+      <c r="J51" s="77"/>
     </row>
     <row r="52" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A52" s="28"/>
-      <c r="B52" s="56"/>
-      <c r="C52" s="56"/>
-      <c r="D52" s="56"/>
-      <c r="E52" s="56"/>
-      <c r="F52" s="56"/>
-      <c r="G52" s="56"/>
-      <c r="H52" s="56"/>
-      <c r="I52" s="56"/>
-      <c r="J52" s="57"/>
+      <c r="A52" s="49"/>
+      <c r="B52" s="76"/>
+      <c r="C52" s="76"/>
+      <c r="D52" s="76"/>
+      <c r="E52" s="76"/>
+      <c r="F52" s="76"/>
+      <c r="G52" s="76"/>
+      <c r="H52" s="76"/>
+      <c r="I52" s="76"/>
+      <c r="J52" s="77"/>
     </row>
     <row r="53" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A53" s="28"/>
-      <c r="B53" s="56"/>
-      <c r="C53" s="56"/>
-      <c r="D53" s="56"/>
-      <c r="E53" s="56"/>
-      <c r="F53" s="56"/>
-      <c r="G53" s="56"/>
-      <c r="H53" s="56"/>
-      <c r="I53" s="56"/>
-      <c r="J53" s="57"/>
+      <c r="A53" s="49"/>
+      <c r="B53" s="76"/>
+      <c r="C53" s="76"/>
+      <c r="D53" s="76"/>
+      <c r="E53" s="76"/>
+      <c r="F53" s="76"/>
+      <c r="G53" s="76"/>
+      <c r="H53" s="76"/>
+      <c r="I53" s="76"/>
+      <c r="J53" s="77"/>
     </row>
     <row r="54" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A54" s="28"/>
-      <c r="B54" s="56"/>
-      <c r="C54" s="56"/>
-      <c r="D54" s="56"/>
-      <c r="E54" s="56"/>
-      <c r="F54" s="56"/>
-      <c r="G54" s="56"/>
-      <c r="H54" s="56"/>
-      <c r="I54" s="56"/>
-      <c r="J54" s="57"/>
+      <c r="A54" s="49"/>
+      <c r="B54" s="76"/>
+      <c r="C54" s="76"/>
+      <c r="D54" s="76"/>
+      <c r="E54" s="76"/>
+      <c r="F54" s="76"/>
+      <c r="G54" s="76"/>
+      <c r="H54" s="76"/>
+      <c r="I54" s="76"/>
+      <c r="J54" s="77"/>
     </row>
     <row r="55" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A55" s="28"/>
-      <c r="B55" s="56"/>
-      <c r="C55" s="56"/>
-      <c r="D55" s="56"/>
-      <c r="E55" s="56"/>
-      <c r="F55" s="56"/>
-      <c r="G55" s="56"/>
-      <c r="H55" s="56"/>
-      <c r="I55" s="56"/>
-      <c r="J55" s="57"/>
+      <c r="A55" s="49"/>
+      <c r="B55" s="76"/>
+      <c r="C55" s="76"/>
+      <c r="D55" s="76"/>
+      <c r="E55" s="76"/>
+      <c r="F55" s="76"/>
+      <c r="G55" s="76"/>
+      <c r="H55" s="76"/>
+      <c r="I55" s="76"/>
+      <c r="J55" s="77"/>
     </row>
     <row r="56" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A56" s="28"/>
-      <c r="B56" s="56"/>
-      <c r="C56" s="56"/>
-      <c r="D56" s="56"/>
-      <c r="E56" s="56"/>
-      <c r="F56" s="56"/>
-      <c r="G56" s="56"/>
-      <c r="H56" s="56"/>
-      <c r="I56" s="56"/>
-      <c r="J56" s="57"/>
+      <c r="A56" s="49"/>
+      <c r="B56" s="76"/>
+      <c r="C56" s="76"/>
+      <c r="D56" s="76"/>
+      <c r="E56" s="76"/>
+      <c r="F56" s="76"/>
+      <c r="G56" s="76"/>
+      <c r="H56" s="76"/>
+      <c r="I56" s="76"/>
+      <c r="J56" s="77"/>
     </row>
     <row r="57" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A57" s="28"/>
-      <c r="B57" s="56"/>
-      <c r="C57" s="56"/>
-      <c r="D57" s="56"/>
-      <c r="E57" s="56"/>
-      <c r="F57" s="56"/>
-      <c r="G57" s="56"/>
-      <c r="H57" s="56"/>
-      <c r="I57" s="56"/>
-      <c r="J57" s="57"/>
+      <c r="A57" s="49"/>
+      <c r="B57" s="76"/>
+      <c r="C57" s="76"/>
+      <c r="D57" s="76"/>
+      <c r="E57" s="76"/>
+      <c r="F57" s="76"/>
+      <c r="G57" s="76"/>
+      <c r="H57" s="76"/>
+      <c r="I57" s="76"/>
+      <c r="J57" s="77"/>
     </row>
     <row r="58" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A58" s="28"/>
-      <c r="B58" s="56"/>
-      <c r="C58" s="56"/>
-      <c r="D58" s="56"/>
-      <c r="E58" s="56"/>
-      <c r="F58" s="56"/>
-      <c r="G58" s="56"/>
-      <c r="H58" s="56"/>
-      <c r="I58" s="56"/>
-      <c r="J58" s="57"/>
+      <c r="A58" s="49"/>
+      <c r="B58" s="76"/>
+      <c r="C58" s="76"/>
+      <c r="D58" s="76"/>
+      <c r="E58" s="76"/>
+      <c r="F58" s="76"/>
+      <c r="G58" s="76"/>
+      <c r="H58" s="76"/>
+      <c r="I58" s="76"/>
+      <c r="J58" s="77"/>
     </row>
     <row r="59" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A59" s="28"/>
-      <c r="B59" s="56"/>
-      <c r="C59" s="56"/>
-      <c r="D59" s="56"/>
-      <c r="E59" s="56"/>
-      <c r="F59" s="56"/>
-      <c r="G59" s="56"/>
-      <c r="H59" s="56"/>
-      <c r="I59" s="56"/>
-      <c r="J59" s="57"/>
+      <c r="A59" s="49"/>
+      <c r="B59" s="76"/>
+      <c r="C59" s="76"/>
+      <c r="D59" s="76"/>
+      <c r="E59" s="76"/>
+      <c r="F59" s="76"/>
+      <c r="G59" s="76"/>
+      <c r="H59" s="76"/>
+      <c r="I59" s="76"/>
+      <c r="J59" s="77"/>
     </row>
     <row r="60" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A60" s="28"/>
-      <c r="B60" s="56"/>
-      <c r="C60" s="56"/>
-      <c r="D60" s="56"/>
-      <c r="E60" s="56"/>
-      <c r="F60" s="56"/>
-      <c r="G60" s="56"/>
-      <c r="H60" s="56"/>
-      <c r="I60" s="56"/>
-      <c r="J60" s="57"/>
+      <c r="A60" s="49"/>
+      <c r="B60" s="76"/>
+      <c r="C60" s="76"/>
+      <c r="D60" s="76"/>
+      <c r="E60" s="76"/>
+      <c r="F60" s="76"/>
+      <c r="G60" s="76"/>
+      <c r="H60" s="76"/>
+      <c r="I60" s="76"/>
+      <c r="J60" s="77"/>
     </row>
     <row r="61" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A61" s="28"/>
-      <c r="B61" s="56"/>
-      <c r="C61" s="56"/>
-      <c r="D61" s="56"/>
-      <c r="E61" s="56"/>
-      <c r="F61" s="56"/>
-      <c r="G61" s="56"/>
-      <c r="H61" s="56"/>
-      <c r="I61" s="56"/>
-      <c r="J61" s="57"/>
+      <c r="A61" s="49"/>
+      <c r="B61" s="76"/>
+      <c r="C61" s="76"/>
+      <c r="D61" s="76"/>
+      <c r="E61" s="76"/>
+      <c r="F61" s="76"/>
+      <c r="G61" s="76"/>
+      <c r="H61" s="76"/>
+      <c r="I61" s="76"/>
+      <c r="J61" s="77"/>
     </row>
     <row r="62" spans="1:10" ht="13.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A62" s="29"/>
-      <c r="B62" s="58"/>
-      <c r="C62" s="58"/>
-      <c r="D62" s="58"/>
-      <c r="E62" s="58"/>
-      <c r="F62" s="58"/>
-      <c r="G62" s="58"/>
-      <c r="H62" s="58"/>
-      <c r="I62" s="58"/>
-      <c r="J62" s="59"/>
+      <c r="A62" s="50"/>
+      <c r="B62" s="78"/>
+      <c r="C62" s="78"/>
+      <c r="D62" s="78"/>
+      <c r="E62" s="78"/>
+      <c r="F62" s="78"/>
+      <c r="G62" s="78"/>
+      <c r="H62" s="78"/>
+      <c r="I62" s="78"/>
+      <c r="J62" s="79"/>
     </row>
     <row r="63" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A63" s="27">
+      <c r="A63" s="48">
         <v>4</v>
       </c>
-      <c r="B63" s="34" t="s">
+      <c r="B63" s="55" t="s">
         <v>6</v>
       </c>
-      <c r="C63" s="34"/>
-      <c r="D63" s="34"/>
-      <c r="E63" s="34"/>
-      <c r="F63" s="34"/>
-      <c r="G63" s="34"/>
-      <c r="H63" s="34"/>
-      <c r="I63" s="34"/>
-      <c r="J63" s="67"/>
+      <c r="C63" s="55"/>
+      <c r="D63" s="55"/>
+      <c r="E63" s="55"/>
+      <c r="F63" s="55"/>
+      <c r="G63" s="55"/>
+      <c r="H63" s="55"/>
+      <c r="I63" s="55"/>
+      <c r="J63" s="87"/>
     </row>
     <row r="64" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A64" s="28"/>
-      <c r="B64" s="30" t="s">
+      <c r="A64" s="49"/>
+      <c r="B64" s="51" t="s">
         <v>7</v>
       </c>
-      <c r="C64" s="30"/>
+      <c r="C64" s="51"/>
       <c r="D64" s="44" t="s">
-        <v>110</v>
+        <v>74</v>
       </c>
       <c r="E64" s="44"/>
       <c r="F64" s="44"/>
       <c r="G64" s="44"/>
       <c r="H64" s="44"/>
       <c r="I64" s="44"/>
-      <c r="J64" s="45"/>
+      <c r="J64" s="65"/>
     </row>
     <row r="65" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A65" s="28"/>
-      <c r="B65" s="30" t="s">
+      <c r="A65" s="49"/>
+      <c r="B65" s="51" t="s">
         <v>8</v>
       </c>
-      <c r="C65" s="30"/>
+      <c r="C65" s="51"/>
       <c r="D65" s="44" t="s">
-        <v>108</v>
+        <v>72</v>
       </c>
       <c r="E65" s="44"/>
       <c r="F65" s="44"/>
       <c r="G65" s="44"/>
       <c r="H65" s="44"/>
       <c r="I65" s="44"/>
-      <c r="J65" s="45"/>
+      <c r="J65" s="65"/>
     </row>
     <row r="66" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A66" s="28"/>
-      <c r="B66" s="30" t="s">
+      <c r="A66" s="49"/>
+      <c r="B66" s="51" t="s">
         <v>9</v>
       </c>
-      <c r="C66" s="30"/>
+      <c r="C66" s="51"/>
       <c r="D66" s="44" t="s">
-        <v>107</v>
+        <v>71</v>
       </c>
       <c r="E66" s="44"/>
       <c r="F66" s="44"/>
       <c r="G66" s="44"/>
       <c r="H66" s="44"/>
       <c r="I66" s="44"/>
-      <c r="J66" s="45"/>
+      <c r="J66" s="65"/>
     </row>
     <row r="67" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A67" s="28"/>
-      <c r="B67" s="30" t="s">
-        <v>104</v>
-      </c>
-      <c r="C67" s="30"/>
+      <c r="A67" s="49"/>
+      <c r="B67" s="51" t="s">
+        <v>68</v>
+      </c>
+      <c r="C67" s="51"/>
       <c r="D67" s="44" t="s">
-        <v>109</v>
+        <v>73</v>
       </c>
       <c r="E67" s="44"/>
       <c r="F67" s="44"/>
       <c r="G67" s="44"/>
       <c r="H67" s="44"/>
       <c r="I67" s="44"/>
-      <c r="J67" s="45"/>
+      <c r="J67" s="65"/>
     </row>
     <row r="68" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A68" s="28"/>
-      <c r="B68" s="30" t="s">
+      <c r="A68" s="49"/>
+      <c r="B68" s="51" t="s">
         <v>10</v>
       </c>
-      <c r="C68" s="30"/>
-      <c r="D68" s="30"/>
-      <c r="E68" s="30"/>
-      <c r="F68" s="30"/>
-      <c r="G68" s="30"/>
-      <c r="H68" s="30"/>
-      <c r="I68" s="30"/>
-      <c r="J68" s="60"/>
+      <c r="C68" s="51"/>
+      <c r="D68" s="51"/>
+      <c r="E68" s="51"/>
+      <c r="F68" s="51"/>
+      <c r="G68" s="51"/>
+      <c r="H68" s="51"/>
+      <c r="I68" s="51"/>
+      <c r="J68" s="80"/>
     </row>
     <row r="69" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A69" s="28"/>
-      <c r="B69" s="40"/>
-      <c r="C69" s="40"/>
-      <c r="D69" s="40"/>
-      <c r="E69" s="40"/>
-      <c r="F69" s="40"/>
-      <c r="G69" s="40"/>
-      <c r="H69" s="40"/>
-      <c r="I69" s="40"/>
-      <c r="J69" s="41"/>
+      <c r="A69" s="49"/>
+      <c r="B69" s="61"/>
+      <c r="C69" s="61"/>
+      <c r="D69" s="61"/>
+      <c r="E69" s="61"/>
+      <c r="F69" s="61"/>
+      <c r="G69" s="61"/>
+      <c r="H69" s="61"/>
+      <c r="I69" s="61"/>
+      <c r="J69" s="62"/>
     </row>
     <row r="70" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A70" s="28"/>
-      <c r="B70" s="40"/>
-      <c r="C70" s="40"/>
-      <c r="D70" s="40"/>
-      <c r="E70" s="40"/>
-      <c r="F70" s="40"/>
-      <c r="G70" s="40"/>
-      <c r="H70" s="40"/>
-      <c r="I70" s="40"/>
-      <c r="J70" s="41"/>
+      <c r="A70" s="49"/>
+      <c r="B70" s="61"/>
+      <c r="C70" s="61"/>
+      <c r="D70" s="61"/>
+      <c r="E70" s="61"/>
+      <c r="F70" s="61"/>
+      <c r="G70" s="61"/>
+      <c r="H70" s="61"/>
+      <c r="I70" s="61"/>
+      <c r="J70" s="62"/>
     </row>
     <row r="71" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A71" s="28"/>
-      <c r="B71" s="40"/>
-      <c r="C71" s="40"/>
-      <c r="D71" s="40"/>
-      <c r="E71" s="40"/>
-      <c r="F71" s="40"/>
-      <c r="G71" s="40"/>
-      <c r="H71" s="40"/>
-      <c r="I71" s="40"/>
-      <c r="J71" s="41"/>
+      <c r="A71" s="49"/>
+      <c r="B71" s="61"/>
+      <c r="C71" s="61"/>
+      <c r="D71" s="61"/>
+      <c r="E71" s="61"/>
+      <c r="F71" s="61"/>
+      <c r="G71" s="61"/>
+      <c r="H71" s="61"/>
+      <c r="I71" s="61"/>
+      <c r="J71" s="62"/>
     </row>
     <row r="72" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A72" s="28"/>
-      <c r="B72" s="40"/>
-      <c r="C72" s="40"/>
-      <c r="D72" s="40"/>
-      <c r="E72" s="40"/>
-      <c r="F72" s="40"/>
-      <c r="G72" s="40"/>
-      <c r="H72" s="40"/>
-      <c r="I72" s="40"/>
-      <c r="J72" s="41"/>
+      <c r="A72" s="49"/>
+      <c r="B72" s="61"/>
+      <c r="C72" s="61"/>
+      <c r="D72" s="61"/>
+      <c r="E72" s="61"/>
+      <c r="F72" s="61"/>
+      <c r="G72" s="61"/>
+      <c r="H72" s="61"/>
+      <c r="I72" s="61"/>
+      <c r="J72" s="62"/>
     </row>
     <row r="73" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A73" s="28"/>
-      <c r="B73" s="40"/>
-      <c r="C73" s="40"/>
-      <c r="D73" s="40"/>
-      <c r="E73" s="40"/>
-      <c r="F73" s="40"/>
-      <c r="G73" s="40"/>
-      <c r="H73" s="40"/>
-      <c r="I73" s="40"/>
-      <c r="J73" s="41"/>
+      <c r="A73" s="49"/>
+      <c r="B73" s="61"/>
+      <c r="C73" s="61"/>
+      <c r="D73" s="61"/>
+      <c r="E73" s="61"/>
+      <c r="F73" s="61"/>
+      <c r="G73" s="61"/>
+      <c r="H73" s="61"/>
+      <c r="I73" s="61"/>
+      <c r="J73" s="62"/>
     </row>
     <row r="74" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A74" s="28"/>
-      <c r="B74" s="40"/>
-      <c r="C74" s="40"/>
-      <c r="D74" s="40"/>
-      <c r="E74" s="40"/>
-      <c r="F74" s="40"/>
-      <c r="G74" s="40"/>
-      <c r="H74" s="40"/>
-      <c r="I74" s="40"/>
-      <c r="J74" s="41"/>
+      <c r="A74" s="49"/>
+      <c r="B74" s="61"/>
+      <c r="C74" s="61"/>
+      <c r="D74" s="61"/>
+      <c r="E74" s="61"/>
+      <c r="F74" s="61"/>
+      <c r="G74" s="61"/>
+      <c r="H74" s="61"/>
+      <c r="I74" s="61"/>
+      <c r="J74" s="62"/>
     </row>
     <row r="75" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A75" s="28"/>
-      <c r="B75" s="40"/>
-      <c r="C75" s="40"/>
-      <c r="D75" s="40"/>
-      <c r="E75" s="40"/>
-      <c r="F75" s="40"/>
-      <c r="G75" s="40"/>
-      <c r="H75" s="40"/>
-      <c r="I75" s="40"/>
-      <c r="J75" s="41"/>
+      <c r="A75" s="49"/>
+      <c r="B75" s="61"/>
+      <c r="C75" s="61"/>
+      <c r="D75" s="61"/>
+      <c r="E75" s="61"/>
+      <c r="F75" s="61"/>
+      <c r="G75" s="61"/>
+      <c r="H75" s="61"/>
+      <c r="I75" s="61"/>
+      <c r="J75" s="62"/>
     </row>
     <row r="76" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A76" s="28"/>
-      <c r="B76" s="40"/>
-      <c r="C76" s="40"/>
-      <c r="D76" s="40"/>
-      <c r="E76" s="40"/>
-      <c r="F76" s="40"/>
-      <c r="G76" s="40"/>
-      <c r="H76" s="40"/>
-      <c r="I76" s="40"/>
-      <c r="J76" s="41"/>
+      <c r="A76" s="49"/>
+      <c r="B76" s="61"/>
+      <c r="C76" s="61"/>
+      <c r="D76" s="61"/>
+      <c r="E76" s="61"/>
+      <c r="F76" s="61"/>
+      <c r="G76" s="61"/>
+      <c r="H76" s="61"/>
+      <c r="I76" s="61"/>
+      <c r="J76" s="62"/>
     </row>
     <row r="77" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A77" s="28"/>
-      <c r="B77" s="40"/>
-      <c r="C77" s="40"/>
-      <c r="D77" s="40"/>
-      <c r="E77" s="40"/>
-      <c r="F77" s="40"/>
-      <c r="G77" s="40"/>
-      <c r="H77" s="40"/>
-      <c r="I77" s="40"/>
-      <c r="J77" s="41"/>
+      <c r="A77" s="49"/>
+      <c r="B77" s="61"/>
+      <c r="C77" s="61"/>
+      <c r="D77" s="61"/>
+      <c r="E77" s="61"/>
+      <c r="F77" s="61"/>
+      <c r="G77" s="61"/>
+      <c r="H77" s="61"/>
+      <c r="I77" s="61"/>
+      <c r="J77" s="62"/>
     </row>
     <row r="78" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A78" s="28"/>
-      <c r="B78" s="40"/>
-      <c r="C78" s="40"/>
-      <c r="D78" s="40"/>
-      <c r="E78" s="40"/>
-      <c r="F78" s="40"/>
-      <c r="G78" s="40"/>
-      <c r="H78" s="40"/>
-      <c r="I78" s="40"/>
-      <c r="J78" s="41"/>
+      <c r="A78" s="49"/>
+      <c r="B78" s="61"/>
+      <c r="C78" s="61"/>
+      <c r="D78" s="61"/>
+      <c r="E78" s="61"/>
+      <c r="F78" s="61"/>
+      <c r="G78" s="61"/>
+      <c r="H78" s="61"/>
+      <c r="I78" s="61"/>
+      <c r="J78" s="62"/>
     </row>
     <row r="79" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A79" s="28"/>
-      <c r="B79" s="40"/>
-      <c r="C79" s="40"/>
-      <c r="D79" s="40"/>
-      <c r="E79" s="40"/>
-      <c r="F79" s="40"/>
-      <c r="G79" s="40"/>
-      <c r="H79" s="40"/>
-      <c r="I79" s="40"/>
-      <c r="J79" s="41"/>
+      <c r="A79" s="49"/>
+      <c r="B79" s="61"/>
+      <c r="C79" s="61"/>
+      <c r="D79" s="61"/>
+      <c r="E79" s="61"/>
+      <c r="F79" s="61"/>
+      <c r="G79" s="61"/>
+      <c r="H79" s="61"/>
+      <c r="I79" s="61"/>
+      <c r="J79" s="62"/>
     </row>
     <row r="80" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A80" s="28"/>
-      <c r="B80" s="40"/>
-      <c r="C80" s="40"/>
-      <c r="D80" s="40"/>
-      <c r="E80" s="40"/>
-      <c r="F80" s="40"/>
-      <c r="G80" s="40"/>
-      <c r="H80" s="40"/>
-      <c r="I80" s="40"/>
-      <c r="J80" s="41"/>
+      <c r="A80" s="49"/>
+      <c r="B80" s="61"/>
+      <c r="C80" s="61"/>
+      <c r="D80" s="61"/>
+      <c r="E80" s="61"/>
+      <c r="F80" s="61"/>
+      <c r="G80" s="61"/>
+      <c r="H80" s="61"/>
+      <c r="I80" s="61"/>
+      <c r="J80" s="62"/>
     </row>
     <row r="81" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A81" s="28"/>
-      <c r="B81" s="40"/>
-      <c r="C81" s="40"/>
-      <c r="D81" s="40"/>
-      <c r="E81" s="40"/>
-      <c r="F81" s="40"/>
-      <c r="G81" s="40"/>
-      <c r="H81" s="40"/>
-      <c r="I81" s="40"/>
-      <c r="J81" s="41"/>
+      <c r="A81" s="49"/>
+      <c r="B81" s="61"/>
+      <c r="C81" s="61"/>
+      <c r="D81" s="61"/>
+      <c r="E81" s="61"/>
+      <c r="F81" s="61"/>
+      <c r="G81" s="61"/>
+      <c r="H81" s="61"/>
+      <c r="I81" s="61"/>
+      <c r="J81" s="62"/>
     </row>
     <row r="82" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A82" s="28"/>
-      <c r="B82" s="40"/>
-      <c r="C82" s="40"/>
-      <c r="D82" s="40"/>
-      <c r="E82" s="40"/>
-      <c r="F82" s="40"/>
-      <c r="G82" s="40"/>
-      <c r="H82" s="40"/>
-      <c r="I82" s="40"/>
-      <c r="J82" s="41"/>
+      <c r="A82" s="49"/>
+      <c r="B82" s="61"/>
+      <c r="C82" s="61"/>
+      <c r="D82" s="61"/>
+      <c r="E82" s="61"/>
+      <c r="F82" s="61"/>
+      <c r="G82" s="61"/>
+      <c r="H82" s="61"/>
+      <c r="I82" s="61"/>
+      <c r="J82" s="62"/>
     </row>
     <row r="83" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A83" s="28"/>
-      <c r="B83" s="40"/>
-      <c r="C83" s="40"/>
-      <c r="D83" s="40"/>
-      <c r="E83" s="40"/>
-      <c r="F83" s="40"/>
-      <c r="G83" s="40"/>
-      <c r="H83" s="40"/>
-      <c r="I83" s="40"/>
-      <c r="J83" s="41"/>
+      <c r="A83" s="49"/>
+      <c r="B83" s="61"/>
+      <c r="C83" s="61"/>
+      <c r="D83" s="61"/>
+      <c r="E83" s="61"/>
+      <c r="F83" s="61"/>
+      <c r="G83" s="61"/>
+      <c r="H83" s="61"/>
+      <c r="I83" s="61"/>
+      <c r="J83" s="62"/>
     </row>
     <row r="84" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A84" s="28"/>
-      <c r="B84" s="40"/>
-      <c r="C84" s="40"/>
-      <c r="D84" s="40"/>
-      <c r="E84" s="40"/>
-      <c r="F84" s="40"/>
-      <c r="G84" s="40"/>
-      <c r="H84" s="40"/>
-      <c r="I84" s="40"/>
-      <c r="J84" s="41"/>
+      <c r="A84" s="49"/>
+      <c r="B84" s="61"/>
+      <c r="C84" s="61"/>
+      <c r="D84" s="61"/>
+      <c r="E84" s="61"/>
+      <c r="F84" s="61"/>
+      <c r="G84" s="61"/>
+      <c r="H84" s="61"/>
+      <c r="I84" s="61"/>
+      <c r="J84" s="62"/>
     </row>
     <row r="85" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A85" s="28"/>
-      <c r="B85" s="40"/>
-      <c r="C85" s="40"/>
-      <c r="D85" s="40"/>
-      <c r="E85" s="40"/>
-      <c r="F85" s="40"/>
-      <c r="G85" s="40"/>
-      <c r="H85" s="40"/>
-      <c r="I85" s="40"/>
-      <c r="J85" s="41"/>
+      <c r="A85" s="49"/>
+      <c r="B85" s="61"/>
+      <c r="C85" s="61"/>
+      <c r="D85" s="61"/>
+      <c r="E85" s="61"/>
+      <c r="F85" s="61"/>
+      <c r="G85" s="61"/>
+      <c r="H85" s="61"/>
+      <c r="I85" s="61"/>
+      <c r="J85" s="62"/>
     </row>
     <row r="86" spans="1:10" ht="13.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A86" s="31"/>
-      <c r="B86" s="42"/>
-      <c r="C86" s="42"/>
-      <c r="D86" s="42"/>
-      <c r="E86" s="42"/>
-      <c r="F86" s="42"/>
-      <c r="G86" s="42"/>
-      <c r="H86" s="42"/>
-      <c r="I86" s="42"/>
-      <c r="J86" s="43"/>
+      <c r="A86" s="52"/>
+      <c r="B86" s="63"/>
+      <c r="C86" s="63"/>
+      <c r="D86" s="63"/>
+      <c r="E86" s="63"/>
+      <c r="F86" s="63"/>
+      <c r="G86" s="63"/>
+      <c r="H86" s="63"/>
+      <c r="I86" s="63"/>
+      <c r="J86" s="64"/>
     </row>
     <row r="87" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A87" s="27">
+      <c r="A87" s="48">
         <v>5</v>
       </c>
-      <c r="B87" s="34" t="s">
+      <c r="B87" s="55" t="s">
         <v>11</v>
       </c>
-      <c r="C87" s="34"/>
-      <c r="D87" s="34"/>
-      <c r="E87" s="34"/>
-      <c r="F87" s="34"/>
-      <c r="G87" s="34"/>
-      <c r="H87" s="34"/>
-      <c r="I87" s="34"/>
-      <c r="J87" s="67"/>
+      <c r="C87" s="55"/>
+      <c r="D87" s="55"/>
+      <c r="E87" s="55"/>
+      <c r="F87" s="55"/>
+      <c r="G87" s="55"/>
+      <c r="H87" s="55"/>
+      <c r="I87" s="55"/>
+      <c r="J87" s="87"/>
     </row>
     <row r="88" spans="1:10" ht="13.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A88" s="28"/>
-      <c r="B88" s="76" t="s">
+      <c r="A88" s="49"/>
+      <c r="B88" s="33" t="s">
         <v>12</v>
       </c>
-      <c r="C88" s="76"/>
-      <c r="D88" s="76"/>
-      <c r="E88" s="76"/>
-      <c r="F88" s="76"/>
-      <c r="G88" s="76"/>
-      <c r="H88" s="76"/>
-      <c r="I88" s="76"/>
-      <c r="J88" s="77"/>
+      <c r="C88" s="33"/>
+      <c r="D88" s="33"/>
+      <c r="E88" s="33"/>
+      <c r="F88" s="33"/>
+      <c r="G88" s="33"/>
+      <c r="H88" s="33"/>
+      <c r="I88" s="33"/>
+      <c r="J88" s="96"/>
     </row>
     <row r="89" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A89" s="27">
+      <c r="A89" s="48">
         <v>6</v>
       </c>
-      <c r="B89" s="32" t="s">
+      <c r="B89" s="53" t="s">
         <v>13</v>
       </c>
-      <c r="C89" s="32"/>
-      <c r="D89" s="32"/>
-      <c r="E89" s="32"/>
-      <c r="F89" s="32"/>
-      <c r="G89" s="32"/>
-      <c r="H89" s="32"/>
-      <c r="I89" s="32"/>
-      <c r="J89" s="33"/>
+      <c r="C89" s="53"/>
+      <c r="D89" s="53"/>
+      <c r="E89" s="53"/>
+      <c r="F89" s="53"/>
+      <c r="G89" s="53"/>
+      <c r="H89" s="53"/>
+      <c r="I89" s="53"/>
+      <c r="J89" s="54"/>
     </row>
     <row r="90" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A90" s="75"/>
-      <c r="B90" s="46" t="s">
+      <c r="A90" s="95"/>
+      <c r="B90" s="66" t="s">
         <v>14</v>
       </c>
-      <c r="C90" s="46"/>
-      <c r="D90" s="46"/>
-      <c r="E90" s="46"/>
-      <c r="F90" s="46"/>
-      <c r="G90" s="46"/>
-      <c r="H90" s="46"/>
-      <c r="I90" s="46"/>
-      <c r="J90" s="47"/>
+      <c r="C90" s="66"/>
+      <c r="D90" s="66"/>
+      <c r="E90" s="66"/>
+      <c r="F90" s="66"/>
+      <c r="G90" s="66"/>
+      <c r="H90" s="66"/>
+      <c r="I90" s="66"/>
+      <c r="J90" s="67"/>
     </row>
     <row r="91" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A91" s="75"/>
-      <c r="B91" s="46"/>
-      <c r="C91" s="46"/>
-      <c r="D91" s="46"/>
-      <c r="E91" s="46"/>
-      <c r="F91" s="46"/>
-      <c r="G91" s="46"/>
-      <c r="H91" s="46"/>
-      <c r="I91" s="46"/>
-      <c r="J91" s="47"/>
+      <c r="A91" s="95"/>
+      <c r="B91" s="66"/>
+      <c r="C91" s="66"/>
+      <c r="D91" s="66"/>
+      <c r="E91" s="66"/>
+      <c r="F91" s="66"/>
+      <c r="G91" s="66"/>
+      <c r="H91" s="66"/>
+      <c r="I91" s="66"/>
+      <c r="J91" s="67"/>
     </row>
     <row r="92" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A92" s="75"/>
-      <c r="B92" s="48"/>
-      <c r="C92" s="48"/>
-      <c r="D92" s="48"/>
-      <c r="E92" s="48"/>
-      <c r="F92" s="48"/>
-      <c r="G92" s="48"/>
-      <c r="H92" s="48"/>
-      <c r="I92" s="48"/>
-      <c r="J92" s="49"/>
+      <c r="A92" s="95"/>
+      <c r="B92" s="68"/>
+      <c r="C92" s="68"/>
+      <c r="D92" s="68"/>
+      <c r="E92" s="68"/>
+      <c r="F92" s="68"/>
+      <c r="G92" s="68"/>
+      <c r="H92" s="68"/>
+      <c r="I92" s="68"/>
+      <c r="J92" s="69"/>
     </row>
     <row r="93" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A93" s="28"/>
-      <c r="B93" s="78"/>
-      <c r="C93" s="62"/>
-      <c r="D93" s="62"/>
-      <c r="E93" s="62"/>
-      <c r="F93" s="62"/>
-      <c r="G93" s="62"/>
-      <c r="H93" s="62"/>
-      <c r="I93" s="62"/>
-      <c r="J93" s="63"/>
+      <c r="A93" s="49"/>
+      <c r="B93" s="97"/>
+      <c r="C93" s="82"/>
+      <c r="D93" s="82"/>
+      <c r="E93" s="82"/>
+      <c r="F93" s="82"/>
+      <c r="G93" s="82"/>
+      <c r="H93" s="82"/>
+      <c r="I93" s="82"/>
+      <c r="J93" s="83"/>
     </row>
     <row r="94" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A94" s="28"/>
-      <c r="B94" s="64"/>
-      <c r="C94" s="65"/>
-      <c r="D94" s="65"/>
-      <c r="E94" s="65"/>
-      <c r="F94" s="65"/>
-      <c r="G94" s="65"/>
-      <c r="H94" s="65"/>
-      <c r="I94" s="65"/>
-      <c r="J94" s="66"/>
+      <c r="A94" s="49"/>
+      <c r="B94" s="84"/>
+      <c r="C94" s="85"/>
+      <c r="D94" s="85"/>
+      <c r="E94" s="85"/>
+      <c r="F94" s="85"/>
+      <c r="G94" s="85"/>
+      <c r="H94" s="85"/>
+      <c r="I94" s="85"/>
+      <c r="J94" s="86"/>
     </row>
     <row r="95" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A95" s="28"/>
-      <c r="B95" s="64"/>
-      <c r="C95" s="65"/>
-      <c r="D95" s="65"/>
-      <c r="E95" s="65"/>
-      <c r="F95" s="65"/>
-      <c r="G95" s="65"/>
-      <c r="H95" s="65"/>
-      <c r="I95" s="65"/>
-      <c r="J95" s="66"/>
+      <c r="A95" s="49"/>
+      <c r="B95" s="84"/>
+      <c r="C95" s="85"/>
+      <c r="D95" s="85"/>
+      <c r="E95" s="85"/>
+      <c r="F95" s="85"/>
+      <c r="G95" s="85"/>
+      <c r="H95" s="85"/>
+      <c r="I95" s="85"/>
+      <c r="J95" s="86"/>
     </row>
     <row r="96" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A96" s="28"/>
-      <c r="B96" s="64"/>
-      <c r="C96" s="65"/>
-      <c r="D96" s="65"/>
-      <c r="E96" s="65"/>
-      <c r="F96" s="65"/>
-      <c r="G96" s="65"/>
-      <c r="H96" s="65"/>
-      <c r="I96" s="65"/>
-      <c r="J96" s="66"/>
+      <c r="A96" s="49"/>
+      <c r="B96" s="84"/>
+      <c r="C96" s="85"/>
+      <c r="D96" s="85"/>
+      <c r="E96" s="85"/>
+      <c r="F96" s="85"/>
+      <c r="G96" s="85"/>
+      <c r="H96" s="85"/>
+      <c r="I96" s="85"/>
+      <c r="J96" s="86"/>
     </row>
     <row r="97" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A97" s="28"/>
-      <c r="B97" s="64"/>
-      <c r="C97" s="65"/>
-      <c r="D97" s="65"/>
-      <c r="E97" s="65"/>
-      <c r="F97" s="65"/>
-      <c r="G97" s="65"/>
-      <c r="H97" s="65"/>
-      <c r="I97" s="65"/>
-      <c r="J97" s="66"/>
+      <c r="A97" s="49"/>
+      <c r="B97" s="84"/>
+      <c r="C97" s="85"/>
+      <c r="D97" s="85"/>
+      <c r="E97" s="85"/>
+      <c r="F97" s="85"/>
+      <c r="G97" s="85"/>
+      <c r="H97" s="85"/>
+      <c r="I97" s="85"/>
+      <c r="J97" s="86"/>
     </row>
     <row r="98" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A98" s="28"/>
-      <c r="B98" s="64"/>
-      <c r="C98" s="65"/>
-      <c r="D98" s="65"/>
-      <c r="E98" s="65"/>
-      <c r="F98" s="65"/>
-      <c r="G98" s="65"/>
-      <c r="H98" s="65"/>
-      <c r="I98" s="65"/>
-      <c r="J98" s="66"/>
+      <c r="A98" s="49"/>
+      <c r="B98" s="84"/>
+      <c r="C98" s="85"/>
+      <c r="D98" s="85"/>
+      <c r="E98" s="85"/>
+      <c r="F98" s="85"/>
+      <c r="G98" s="85"/>
+      <c r="H98" s="85"/>
+      <c r="I98" s="85"/>
+      <c r="J98" s="86"/>
     </row>
     <row r="99" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A99" s="28"/>
-      <c r="B99" s="64"/>
-      <c r="C99" s="65"/>
-      <c r="D99" s="65"/>
-      <c r="E99" s="65"/>
-      <c r="F99" s="65"/>
-      <c r="G99" s="65"/>
-      <c r="H99" s="65"/>
-      <c r="I99" s="65"/>
-      <c r="J99" s="66"/>
+      <c r="A99" s="49"/>
+      <c r="B99" s="84"/>
+      <c r="C99" s="85"/>
+      <c r="D99" s="85"/>
+      <c r="E99" s="85"/>
+      <c r="F99" s="85"/>
+      <c r="G99" s="85"/>
+      <c r="H99" s="85"/>
+      <c r="I99" s="85"/>
+      <c r="J99" s="86"/>
     </row>
     <row r="100" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A100" s="28"/>
-      <c r="B100" s="64"/>
-      <c r="C100" s="65"/>
-      <c r="D100" s="65"/>
-      <c r="E100" s="65"/>
-      <c r="F100" s="65"/>
-      <c r="G100" s="65"/>
-      <c r="H100" s="65"/>
-      <c r="I100" s="65"/>
-      <c r="J100" s="66"/>
+      <c r="A100" s="49"/>
+      <c r="B100" s="84"/>
+      <c r="C100" s="85"/>
+      <c r="D100" s="85"/>
+      <c r="E100" s="85"/>
+      <c r="F100" s="85"/>
+      <c r="G100" s="85"/>
+      <c r="H100" s="85"/>
+      <c r="I100" s="85"/>
+      <c r="J100" s="86"/>
     </row>
     <row r="101" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A101" s="28"/>
-      <c r="B101" s="64"/>
-      <c r="C101" s="65"/>
-      <c r="D101" s="65"/>
-      <c r="E101" s="65"/>
-      <c r="F101" s="65"/>
-      <c r="G101" s="65"/>
-      <c r="H101" s="65"/>
-      <c r="I101" s="65"/>
-      <c r="J101" s="66"/>
+      <c r="A101" s="49"/>
+      <c r="B101" s="84"/>
+      <c r="C101" s="85"/>
+      <c r="D101" s="85"/>
+      <c r="E101" s="85"/>
+      <c r="F101" s="85"/>
+      <c r="G101" s="85"/>
+      <c r="H101" s="85"/>
+      <c r="I101" s="85"/>
+      <c r="J101" s="86"/>
     </row>
     <row r="102" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A102" s="28"/>
-      <c r="B102" s="64"/>
-      <c r="C102" s="65"/>
-      <c r="D102" s="65"/>
-      <c r="E102" s="65"/>
-      <c r="F102" s="65"/>
-      <c r="G102" s="65"/>
-      <c r="H102" s="65"/>
-      <c r="I102" s="65"/>
-      <c r="J102" s="66"/>
+      <c r="A102" s="49"/>
+      <c r="B102" s="84"/>
+      <c r="C102" s="85"/>
+      <c r="D102" s="85"/>
+      <c r="E102" s="85"/>
+      <c r="F102" s="85"/>
+      <c r="G102" s="85"/>
+      <c r="H102" s="85"/>
+      <c r="I102" s="85"/>
+      <c r="J102" s="86"/>
     </row>
     <row r="103" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A103" s="28"/>
-      <c r="B103" s="64"/>
-      <c r="C103" s="65"/>
-      <c r="D103" s="65"/>
-      <c r="E103" s="65"/>
-      <c r="F103" s="65"/>
-      <c r="G103" s="65"/>
-      <c r="H103" s="65"/>
-      <c r="I103" s="65"/>
-      <c r="J103" s="66"/>
+      <c r="A103" s="49"/>
+      <c r="B103" s="84"/>
+      <c r="C103" s="85"/>
+      <c r="D103" s="85"/>
+      <c r="E103" s="85"/>
+      <c r="F103" s="85"/>
+      <c r="G103" s="85"/>
+      <c r="H103" s="85"/>
+      <c r="I103" s="85"/>
+      <c r="J103" s="86"/>
     </row>
     <row r="104" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A104" s="28"/>
-      <c r="B104" s="64"/>
-      <c r="C104" s="65"/>
-      <c r="D104" s="65"/>
-      <c r="E104" s="65"/>
-      <c r="F104" s="65"/>
-      <c r="G104" s="65"/>
-      <c r="H104" s="65"/>
-      <c r="I104" s="65"/>
-      <c r="J104" s="66"/>
+      <c r="A104" s="49"/>
+      <c r="B104" s="84"/>
+      <c r="C104" s="85"/>
+      <c r="D104" s="85"/>
+      <c r="E104" s="85"/>
+      <c r="F104" s="85"/>
+      <c r="G104" s="85"/>
+      <c r="H104" s="85"/>
+      <c r="I104" s="85"/>
+      <c r="J104" s="86"/>
     </row>
     <row r="105" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A105" s="28"/>
-      <c r="B105" s="64"/>
-      <c r="C105" s="65"/>
-      <c r="D105" s="65"/>
-      <c r="E105" s="65"/>
-      <c r="F105" s="65"/>
-      <c r="G105" s="65"/>
-      <c r="H105" s="65"/>
-      <c r="I105" s="65"/>
-      <c r="J105" s="66"/>
+      <c r="A105" s="49"/>
+      <c r="B105" s="84"/>
+      <c r="C105" s="85"/>
+      <c r="D105" s="85"/>
+      <c r="E105" s="85"/>
+      <c r="F105" s="85"/>
+      <c r="G105" s="85"/>
+      <c r="H105" s="85"/>
+      <c r="I105" s="85"/>
+      <c r="J105" s="86"/>
     </row>
     <row r="106" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A106" s="28"/>
-      <c r="B106" s="64"/>
-      <c r="C106" s="65"/>
-      <c r="D106" s="65"/>
-      <c r="E106" s="65"/>
-      <c r="F106" s="65"/>
-      <c r="G106" s="65"/>
-      <c r="H106" s="65"/>
-      <c r="I106" s="65"/>
-      <c r="J106" s="66"/>
+      <c r="A106" s="49"/>
+      <c r="B106" s="84"/>
+      <c r="C106" s="85"/>
+      <c r="D106" s="85"/>
+      <c r="E106" s="85"/>
+      <c r="F106" s="85"/>
+      <c r="G106" s="85"/>
+      <c r="H106" s="85"/>
+      <c r="I106" s="85"/>
+      <c r="J106" s="86"/>
     </row>
     <row r="107" spans="1:10" ht="13.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A107" s="29"/>
-      <c r="B107" s="79"/>
-      <c r="C107" s="80"/>
-      <c r="D107" s="80"/>
-      <c r="E107" s="80"/>
-      <c r="F107" s="80"/>
-      <c r="G107" s="80"/>
-      <c r="H107" s="80"/>
-      <c r="I107" s="80"/>
-      <c r="J107" s="81"/>
+      <c r="A107" s="50"/>
+      <c r="B107" s="98"/>
+      <c r="C107" s="99"/>
+      <c r="D107" s="99"/>
+      <c r="E107" s="99"/>
+      <c r="F107" s="99"/>
+      <c r="G107" s="99"/>
+      <c r="H107" s="99"/>
+      <c r="I107" s="99"/>
+      <c r="J107" s="100"/>
     </row>
     <row r="108" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A108" s="27">
+      <c r="A108" s="48">
         <v>7</v>
       </c>
-      <c r="B108" s="34" t="s">
+      <c r="B108" s="55" t="s">
         <v>15</v>
       </c>
-      <c r="C108" s="34"/>
-      <c r="D108" s="34"/>
-      <c r="E108" s="34"/>
-      <c r="F108" s="34"/>
-      <c r="G108" s="34"/>
-      <c r="H108" s="34"/>
-      <c r="I108" s="34"/>
-      <c r="J108" s="67"/>
+      <c r="C108" s="55"/>
+      <c r="D108" s="55"/>
+      <c r="E108" s="55"/>
+      <c r="F108" s="55"/>
+      <c r="G108" s="55"/>
+      <c r="H108" s="55"/>
+      <c r="I108" s="55"/>
+      <c r="J108" s="87"/>
     </row>
     <row r="109" spans="1:10" ht="13.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A109" s="31"/>
-      <c r="B109" s="73" t="s">
+      <c r="A109" s="52"/>
+      <c r="B109" s="93" t="s">
         <v>16</v>
       </c>
-      <c r="C109" s="73"/>
-      <c r="D109" s="73"/>
-      <c r="E109" s="73"/>
-      <c r="F109" s="73"/>
-      <c r="G109" s="73"/>
-      <c r="H109" s="73"/>
-      <c r="I109" s="73"/>
-      <c r="J109" s="74"/>
+      <c r="C109" s="93"/>
+      <c r="D109" s="93"/>
+      <c r="E109" s="93"/>
+      <c r="F109" s="93"/>
+      <c r="G109" s="93"/>
+      <c r="H109" s="93"/>
+      <c r="I109" s="93"/>
+      <c r="J109" s="94"/>
     </row>
     <row r="110" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A110" s="27">
+      <c r="A110" s="48">
         <v>8</v>
       </c>
-      <c r="B110" s="34" t="s">
+      <c r="B110" s="55" t="s">
         <v>17</v>
       </c>
-      <c r="C110" s="34"/>
-      <c r="D110" s="34"/>
-      <c r="E110" s="34"/>
-      <c r="F110" s="34"/>
-      <c r="G110" s="34"/>
-      <c r="H110" s="34"/>
-      <c r="I110" s="34"/>
-      <c r="J110" s="67"/>
+      <c r="C110" s="55"/>
+      <c r="D110" s="55"/>
+      <c r="E110" s="55"/>
+      <c r="F110" s="55"/>
+      <c r="G110" s="55"/>
+      <c r="H110" s="55"/>
+      <c r="I110" s="55"/>
+      <c r="J110" s="87"/>
     </row>
     <row r="111" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A111" s="28"/>
+      <c r="A111" s="49"/>
       <c r="B111" s="44"/>
       <c r="C111" s="44"/>
       <c r="D111" s="44"/>
@@ -4842,10 +5400,10 @@
       <c r="G111" s="44"/>
       <c r="H111" s="44"/>
       <c r="I111" s="44"/>
-      <c r="J111" s="45"/>
+      <c r="J111" s="65"/>
     </row>
     <row r="112" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A112" s="28"/>
+      <c r="A112" s="49"/>
       <c r="B112" s="44"/>
       <c r="C112" s="44"/>
       <c r="D112" s="44"/>
@@ -4854,10 +5412,10 @@
       <c r="G112" s="44"/>
       <c r="H112" s="44"/>
       <c r="I112" s="44"/>
-      <c r="J112" s="45"/>
+      <c r="J112" s="65"/>
     </row>
     <row r="113" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A113" s="28"/>
+      <c r="A113" s="49"/>
       <c r="B113" s="44"/>
       <c r="C113" s="44"/>
       <c r="D113" s="44"/>
@@ -4866,10 +5424,10 @@
       <c r="G113" s="44"/>
       <c r="H113" s="44"/>
       <c r="I113" s="44"/>
-      <c r="J113" s="45"/>
+      <c r="J113" s="65"/>
     </row>
     <row r="114" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A114" s="28"/>
+      <c r="A114" s="49"/>
       <c r="B114" s="44"/>
       <c r="C114" s="44"/>
       <c r="D114" s="44"/>
@@ -4878,10 +5436,10 @@
       <c r="G114" s="44"/>
       <c r="H114" s="44"/>
       <c r="I114" s="44"/>
-      <c r="J114" s="45"/>
+      <c r="J114" s="65"/>
     </row>
     <row r="115" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A115" s="28"/>
+      <c r="A115" s="49"/>
       <c r="B115" s="44"/>
       <c r="C115" s="44"/>
       <c r="D115" s="44"/>
@@ -4890,10 +5448,10 @@
       <c r="G115" s="44"/>
       <c r="H115" s="44"/>
       <c r="I115" s="44"/>
-      <c r="J115" s="45"/>
+      <c r="J115" s="65"/>
     </row>
     <row r="116" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A116" s="28"/>
+      <c r="A116" s="49"/>
       <c r="B116" s="44"/>
       <c r="C116" s="44"/>
       <c r="D116" s="44"/>
@@ -4902,24 +5460,24 @@
       <c r="G116" s="44"/>
       <c r="H116" s="44"/>
       <c r="I116" s="44"/>
-      <c r="J116" s="45"/>
+      <c r="J116" s="65"/>
     </row>
     <row r="117" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A117" s="28"/>
-      <c r="B117" s="69" t="s">
+      <c r="A117" s="49"/>
+      <c r="B117" s="89" t="s">
         <v>18</v>
       </c>
-      <c r="C117" s="69"/>
-      <c r="D117" s="69"/>
-      <c r="E117" s="69"/>
-      <c r="F117" s="69"/>
-      <c r="G117" s="69"/>
-      <c r="H117" s="69"/>
-      <c r="I117" s="69"/>
-      <c r="J117" s="70"/>
+      <c r="C117" s="89"/>
+      <c r="D117" s="89"/>
+      <c r="E117" s="89"/>
+      <c r="F117" s="89"/>
+      <c r="G117" s="89"/>
+      <c r="H117" s="89"/>
+      <c r="I117" s="89"/>
+      <c r="J117" s="90"/>
     </row>
     <row r="118" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A118" s="28"/>
+      <c r="A118" s="49"/>
       <c r="B118" s="44"/>
       <c r="C118" s="44"/>
       <c r="D118" s="44"/>
@@ -4928,10 +5486,10 @@
       <c r="G118" s="44"/>
       <c r="H118" s="44"/>
       <c r="I118" s="44"/>
-      <c r="J118" s="45"/>
+      <c r="J118" s="65"/>
     </row>
     <row r="119" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A119" s="28"/>
+      <c r="A119" s="49"/>
       <c r="B119" s="44"/>
       <c r="C119" s="44"/>
       <c r="D119" s="44"/>
@@ -4940,10 +5498,10 @@
       <c r="G119" s="44"/>
       <c r="H119" s="44"/>
       <c r="I119" s="44"/>
-      <c r="J119" s="45"/>
+      <c r="J119" s="65"/>
     </row>
     <row r="120" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A120" s="28"/>
+      <c r="A120" s="49"/>
       <c r="B120" s="44"/>
       <c r="C120" s="44"/>
       <c r="D120" s="44"/>
@@ -4952,10 +5510,10 @@
       <c r="G120" s="44"/>
       <c r="H120" s="44"/>
       <c r="I120" s="44"/>
-      <c r="J120" s="45"/>
+      <c r="J120" s="65"/>
     </row>
     <row r="121" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A121" s="28"/>
+      <c r="A121" s="49"/>
       <c r="B121" s="44"/>
       <c r="C121" s="44"/>
       <c r="D121" s="44"/>
@@ -4964,10 +5522,10 @@
       <c r="G121" s="44"/>
       <c r="H121" s="44"/>
       <c r="I121" s="44"/>
-      <c r="J121" s="45"/>
+      <c r="J121" s="65"/>
     </row>
     <row r="122" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A122" s="28"/>
+      <c r="A122" s="49"/>
       <c r="B122" s="44"/>
       <c r="C122" s="44"/>
       <c r="D122" s="44"/>
@@ -4976,10 +5534,10 @@
       <c r="G122" s="44"/>
       <c r="H122" s="44"/>
       <c r="I122" s="44"/>
-      <c r="J122" s="45"/>
+      <c r="J122" s="65"/>
     </row>
     <row r="123" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A123" s="28"/>
+      <c r="A123" s="49"/>
       <c r="B123" s="44"/>
       <c r="C123" s="44"/>
       <c r="D123" s="44"/>
@@ -4988,10 +5546,10 @@
       <c r="G123" s="44"/>
       <c r="H123" s="44"/>
       <c r="I123" s="44"/>
-      <c r="J123" s="45"/>
+      <c r="J123" s="65"/>
     </row>
     <row r="124" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A124" s="28"/>
+      <c r="A124" s="49"/>
       <c r="B124" s="44"/>
       <c r="C124" s="44"/>
       <c r="D124" s="44"/>
@@ -5000,19 +5558,19 @@
       <c r="G124" s="44"/>
       <c r="H124" s="44"/>
       <c r="I124" s="44"/>
-      <c r="J124" s="45"/>
+      <c r="J124" s="65"/>
     </row>
     <row r="125" spans="1:10" ht="13.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A125" s="29"/>
-      <c r="B125" s="71"/>
-      <c r="C125" s="71"/>
-      <c r="D125" s="71"/>
-      <c r="E125" s="71"/>
-      <c r="F125" s="71"/>
-      <c r="G125" s="71"/>
-      <c r="H125" s="71"/>
-      <c r="I125" s="71"/>
-      <c r="J125" s="72"/>
+      <c r="A125" s="50"/>
+      <c r="B125" s="91"/>
+      <c r="C125" s="91"/>
+      <c r="D125" s="91"/>
+      <c r="E125" s="91"/>
+      <c r="F125" s="91"/>
+      <c r="G125" s="91"/>
+      <c r="H125" s="91"/>
+      <c r="I125" s="91"/>
+      <c r="J125" s="92"/>
     </row>
   </sheetData>
   <mergeCells count="39">
@@ -5083,71 +5641,71 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="35" t="s">
+      <c r="A1" s="56" t="s">
         <v>19</v>
       </c>
-      <c r="B1" s="35"/>
-      <c r="C1" s="35"/>
+      <c r="B1" s="56"/>
+      <c r="C1" s="56"/>
     </row>
     <row r="2" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="90" t="s">
+      <c r="A2" s="32" t="s">
         <v>20</v>
       </c>
-      <c r="B2" s="90"/>
-      <c r="C2" s="90"/>
-      <c r="D2" s="90"/>
-      <c r="E2" s="90"/>
-      <c r="F2" s="90"/>
-      <c r="G2" s="90"/>
-      <c r="H2" s="90"/>
+      <c r="B2" s="32"/>
+      <c r="C2" s="32"/>
+      <c r="D2" s="32"/>
+      <c r="E2" s="32"/>
+      <c r="F2" s="32"/>
+      <c r="G2" s="32"/>
+      <c r="H2" s="32"/>
     </row>
     <row r="3" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="90"/>
-      <c r="B3" s="90"/>
-      <c r="C3" s="90"/>
-      <c r="D3" s="90"/>
-      <c r="E3" s="90"/>
-      <c r="F3" s="90"/>
-      <c r="G3" s="90"/>
-      <c r="H3" s="90"/>
+      <c r="A3" s="32"/>
+      <c r="B3" s="32"/>
+      <c r="C3" s="32"/>
+      <c r="D3" s="32"/>
+      <c r="E3" s="32"/>
+      <c r="F3" s="32"/>
+      <c r="G3" s="32"/>
+      <c r="H3" s="32"/>
     </row>
     <row r="4" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="90"/>
-      <c r="B4" s="90"/>
-      <c r="C4" s="90"/>
-      <c r="D4" s="90"/>
-      <c r="E4" s="90"/>
-      <c r="F4" s="90"/>
-      <c r="G4" s="90"/>
-      <c r="H4" s="90"/>
+      <c r="A4" s="32"/>
+      <c r="B4" s="32"/>
+      <c r="C4" s="32"/>
+      <c r="D4" s="32"/>
+      <c r="E4" s="32"/>
+      <c r="F4" s="32"/>
+      <c r="G4" s="32"/>
+      <c r="H4" s="32"/>
     </row>
     <row r="5" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="76"/>
-      <c r="B5" s="76"/>
-      <c r="C5" s="76"/>
+      <c r="A5" s="33"/>
+      <c r="B5" s="33"/>
+      <c r="C5" s="33"/>
     </row>
     <row r="6" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="89" t="s">
+      <c r="A6" s="34" t="s">
         <v>21</v>
       </c>
-      <c r="B6" s="89" t="s">
+      <c r="B6" s="34" t="s">
         <v>22</v>
       </c>
-      <c r="C6" s="89"/>
-      <c r="D6" s="89"/>
-      <c r="E6" s="89" t="s">
+      <c r="C6" s="34"/>
+      <c r="D6" s="34"/>
+      <c r="E6" s="34" t="s">
         <v>23</v>
       </c>
-      <c r="F6" s="91" t="s">
+      <c r="F6" s="37" t="s">
         <v>24</v>
       </c>
-      <c r="G6" s="92"/>
-      <c r="H6" s="95" t="s">
+      <c r="G6" s="38"/>
+      <c r="H6" s="35" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="7" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="89"/>
+      <c r="A7" s="34"/>
       <c r="B7" s="23" t="s">
         <v>26</v>
       </c>
@@ -5157,519 +5715,491 @@
       <c r="D7" s="23" t="s">
         <v>28</v>
       </c>
-      <c r="E7" s="89"/>
-      <c r="F7" s="93"/>
-      <c r="G7" s="94"/>
-      <c r="H7" s="96"/>
+      <c r="E7" s="34"/>
+      <c r="F7" s="39"/>
+      <c r="G7" s="40"/>
+      <c r="H7" s="36"/>
     </row>
     <row r="8" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="4">
         <v>1</v>
       </c>
-      <c r="B8" s="42" t="s">
-        <v>29</v>
-      </c>
-      <c r="C8" s="84" t="s">
-        <v>30</v>
-      </c>
-      <c r="D8" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="E8" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="F8" s="86" t="s">
-        <v>32</v>
-      </c>
-      <c r="G8" s="87"/>
-      <c r="H8" s="22" t="s">
-        <v>33</v>
-      </c>
+      <c r="B8" s="63" t="s">
+        <v>75</v>
+      </c>
+      <c r="C8" s="63" t="s">
+        <v>76</v>
+      </c>
+      <c r="D8" s="27" t="s">
+        <v>77</v>
+      </c>
+      <c r="E8" s="27" t="s">
+        <v>102</v>
+      </c>
+      <c r="F8" s="101" t="s">
+        <v>106</v>
+      </c>
+      <c r="G8" s="102"/>
+      <c r="H8" s="27"/>
     </row>
     <row r="9" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="4">
         <v>2</v>
       </c>
-      <c r="B9" s="83"/>
-      <c r="C9" s="85"/>
-      <c r="D9" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="E9" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="F9" s="86" t="s">
-        <v>32</v>
-      </c>
-      <c r="G9" s="87"/>
-      <c r="H9" s="22" t="s">
-        <v>35</v>
-      </c>
+      <c r="B9" s="104"/>
+      <c r="C9" s="104"/>
+      <c r="D9" s="27" t="s">
+        <v>78</v>
+      </c>
+      <c r="E9" s="27" t="s">
+        <v>102</v>
+      </c>
+      <c r="F9" s="101" t="s">
+        <v>107</v>
+      </c>
+      <c r="G9" s="102"/>
+      <c r="H9" s="27"/>
     </row>
     <row r="10" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="4">
         <v>3</v>
       </c>
-      <c r="B10" s="83"/>
-      <c r="C10" s="42" t="s">
-        <v>36</v>
-      </c>
-      <c r="D10" s="4" t="s">
-        <v>37</v>
-      </c>
-      <c r="E10" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="F10" s="86" t="s">
-        <v>32</v>
-      </c>
-      <c r="G10" s="87"/>
-      <c r="H10" s="22" t="s">
-        <v>35</v>
-      </c>
+      <c r="B10" s="104"/>
+      <c r="C10" s="105"/>
+      <c r="D10" s="27" t="s">
+        <v>79</v>
+      </c>
+      <c r="E10" s="27" t="s">
+        <v>102</v>
+      </c>
+      <c r="F10" s="101" t="s">
+        <v>108</v>
+      </c>
+      <c r="G10" s="102"/>
+      <c r="H10" s="27"/>
     </row>
     <row r="11" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="4">
         <v>4</v>
       </c>
-      <c r="B11" s="82"/>
-      <c r="C11" s="82"/>
-      <c r="D11" s="4" t="s">
-        <v>38</v>
-      </c>
-      <c r="E11" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="F11" s="86" t="s">
-        <v>32</v>
-      </c>
-      <c r="G11" s="87"/>
-      <c r="H11" s="22" t="s">
-        <v>35</v>
-      </c>
+      <c r="B11" s="104"/>
+      <c r="C11" s="63" t="s">
+        <v>80</v>
+      </c>
+      <c r="D11" s="27" t="s">
+        <v>81</v>
+      </c>
+      <c r="E11" s="27" t="s">
+        <v>102</v>
+      </c>
+      <c r="F11" s="101" t="s">
+        <v>109</v>
+      </c>
+      <c r="G11" s="102"/>
+      <c r="H11" s="27"/>
     </row>
     <row r="12" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="4">
         <v>5</v>
       </c>
-      <c r="B12" s="42" t="s">
-        <v>39</v>
-      </c>
-      <c r="C12" s="4" t="s">
-        <v>40</v>
-      </c>
-      <c r="D12" s="4"/>
-      <c r="E12" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="F12" s="86" t="s">
-        <v>32</v>
-      </c>
-      <c r="G12" s="87"/>
-      <c r="H12" s="22" t="s">
-        <v>33</v>
-      </c>
+      <c r="B12" s="105"/>
+      <c r="C12" s="105"/>
+      <c r="D12" s="27" t="s">
+        <v>82</v>
+      </c>
+      <c r="E12" s="27" t="s">
+        <v>102</v>
+      </c>
+      <c r="F12" s="101" t="s">
+        <v>110</v>
+      </c>
+      <c r="G12" s="102"/>
+      <c r="H12" s="27"/>
     </row>
     <row r="13" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="4">
         <v>6</v>
       </c>
-      <c r="B13" s="82"/>
-      <c r="C13" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="D13" s="4"/>
-      <c r="E13" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="F13" s="86" t="s">
-        <v>32</v>
-      </c>
-      <c r="G13" s="88"/>
-      <c r="H13" s="22" t="s">
-        <v>33</v>
-      </c>
+      <c r="B13" s="63" t="s">
+        <v>83</v>
+      </c>
+      <c r="C13" s="27" t="s">
+        <v>84</v>
+      </c>
+      <c r="D13" s="27" t="s">
+        <v>85</v>
+      </c>
+      <c r="E13" s="27" t="s">
+        <v>103</v>
+      </c>
+      <c r="F13" s="101" t="s">
+        <v>114</v>
+      </c>
+      <c r="G13" s="102"/>
+      <c r="H13" s="27"/>
     </row>
     <row r="14" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="4">
         <v>7</v>
       </c>
-      <c r="B14" s="42" t="s">
-        <v>42</v>
-      </c>
-      <c r="C14" s="4" t="s">
-        <v>43</v>
-      </c>
-      <c r="D14" s="4"/>
-      <c r="E14" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="F14" s="86" t="s">
-        <v>32</v>
-      </c>
-      <c r="G14" s="87"/>
-      <c r="H14" s="22" t="s">
-        <v>33</v>
-      </c>
+      <c r="B14" s="106"/>
+      <c r="C14" s="27" t="s">
+        <v>86</v>
+      </c>
+      <c r="D14" s="27" t="s">
+        <v>87</v>
+      </c>
+      <c r="E14" s="27" t="s">
+        <v>104</v>
+      </c>
+      <c r="F14" s="101" t="s">
+        <v>111</v>
+      </c>
+      <c r="G14" s="102"/>
+      <c r="H14" s="27"/>
     </row>
     <row r="15" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="4">
         <v>8</v>
       </c>
-      <c r="B15" s="82"/>
-      <c r="C15" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="D15" s="4"/>
-      <c r="E15" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="F15" s="86" t="s">
-        <v>32</v>
-      </c>
-      <c r="G15" s="87"/>
-      <c r="H15" s="22" t="s">
-        <v>35</v>
-      </c>
+      <c r="B15" s="106"/>
+      <c r="C15" s="63" t="s">
+        <v>88</v>
+      </c>
+      <c r="D15" s="27" t="s">
+        <v>89</v>
+      </c>
+      <c r="E15" s="27" t="s">
+        <v>104</v>
+      </c>
+      <c r="F15" s="101" t="s">
+        <v>112</v>
+      </c>
+      <c r="G15" s="102"/>
+      <c r="H15" s="27"/>
     </row>
     <row r="16" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="4">
         <v>9</v>
       </c>
-      <c r="B16" s="42" t="s">
-        <v>45</v>
-      </c>
-      <c r="C16" s="4" t="s">
-        <v>46</v>
-      </c>
-      <c r="D16" s="4"/>
-      <c r="E16" s="4" t="s">
-        <v>47</v>
-      </c>
-      <c r="F16" s="86" t="s">
-        <v>32</v>
-      </c>
-      <c r="G16" s="87"/>
-      <c r="H16" s="22" t="s">
-        <v>35</v>
-      </c>
+      <c r="B16" s="103"/>
+      <c r="C16" s="103"/>
+      <c r="D16" s="27" t="s">
+        <v>90</v>
+      </c>
+      <c r="E16" s="27" t="s">
+        <v>104</v>
+      </c>
+      <c r="F16" s="101" t="s">
+        <v>113</v>
+      </c>
+      <c r="G16" s="102"/>
+      <c r="H16" s="27"/>
     </row>
     <row r="17" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="4">
         <v>10</v>
       </c>
-      <c r="B17" s="82"/>
-      <c r="C17" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="D17" s="4"/>
-      <c r="E17" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="F17" s="86" t="s">
-        <v>32</v>
-      </c>
-      <c r="G17" s="87"/>
-      <c r="H17" s="22" t="s">
-        <v>35</v>
-      </c>
+      <c r="B17" s="63" t="s">
+        <v>91</v>
+      </c>
+      <c r="C17" s="27" t="s">
+        <v>92</v>
+      </c>
+      <c r="D17" s="27" t="s">
+        <v>93</v>
+      </c>
+      <c r="E17" s="27" t="s">
+        <v>104</v>
+      </c>
+      <c r="F17" s="101" t="s">
+        <v>115</v>
+      </c>
+      <c r="G17" s="102"/>
+      <c r="H17" s="27"/>
     </row>
     <row r="18" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="4">
         <v>11</v>
       </c>
-      <c r="B18" s="42" t="s">
-        <v>49</v>
-      </c>
-      <c r="C18" s="4" t="s">
-        <v>50</v>
-      </c>
-      <c r="D18" s="4"/>
-      <c r="E18" s="4" t="s">
-        <v>47</v>
-      </c>
-      <c r="F18" s="86" t="s">
-        <v>32</v>
-      </c>
-      <c r="G18" s="87"/>
-      <c r="H18" s="22" t="s">
-        <v>33</v>
-      </c>
+      <c r="B18" s="106"/>
+      <c r="C18" s="27" t="s">
+        <v>94</v>
+      </c>
+      <c r="D18" s="27" t="s">
+        <v>95</v>
+      </c>
+      <c r="E18" s="27" t="s">
+        <v>104</v>
+      </c>
+      <c r="F18" s="101" t="s">
+        <v>119</v>
+      </c>
+      <c r="G18" s="102"/>
+      <c r="H18" s="27"/>
     </row>
     <row r="19" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="4">
         <v>12</v>
       </c>
-      <c r="B19" s="82"/>
-      <c r="C19" s="4" t="s">
-        <v>49</v>
-      </c>
-      <c r="D19" s="4"/>
-      <c r="E19" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="F19" s="86" t="s">
-        <v>32</v>
-      </c>
-      <c r="G19" s="87"/>
-      <c r="H19" s="22" t="s">
-        <v>33</v>
-      </c>
+      <c r="B19" s="103"/>
+      <c r="C19" s="27" t="s">
+        <v>96</v>
+      </c>
+      <c r="D19" s="27" t="s">
+        <v>97</v>
+      </c>
+      <c r="E19" s="27" t="s">
+        <v>104</v>
+      </c>
+      <c r="F19" s="101" t="s">
+        <v>116</v>
+      </c>
+      <c r="G19" s="102"/>
+      <c r="H19" s="27"/>
     </row>
     <row r="20" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="4">
         <v>13</v>
       </c>
-      <c r="B20" s="42" t="s">
-        <v>51</v>
-      </c>
-      <c r="C20" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="D20" s="4"/>
-      <c r="E20" s="4" t="s">
-        <v>47</v>
-      </c>
-      <c r="F20" s="86" t="s">
-        <v>32</v>
-      </c>
-      <c r="G20" s="87"/>
-      <c r="H20" s="22" t="s">
-        <v>35</v>
-      </c>
+      <c r="B20" s="63" t="s">
+        <v>98</v>
+      </c>
+      <c r="C20" s="63" t="s">
+        <v>99</v>
+      </c>
+      <c r="D20" s="27" t="s">
+        <v>100</v>
+      </c>
+      <c r="E20" s="27" t="s">
+        <v>105</v>
+      </c>
+      <c r="F20" s="101" t="s">
+        <v>118</v>
+      </c>
+      <c r="G20" s="102"/>
+      <c r="H20" s="27"/>
     </row>
     <row r="21" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="4">
         <v>14</v>
       </c>
-      <c r="B21" s="82"/>
-      <c r="C21" s="4" t="s">
-        <v>53</v>
-      </c>
-      <c r="D21" s="4"/>
-      <c r="E21" s="4" t="s">
-        <v>54</v>
-      </c>
-      <c r="F21" s="86" t="s">
-        <v>32</v>
-      </c>
-      <c r="G21" s="87"/>
-      <c r="H21" s="22" t="s">
-        <v>35</v>
-      </c>
+      <c r="B21" s="103"/>
+      <c r="C21" s="103"/>
+      <c r="D21" s="27" t="s">
+        <v>101</v>
+      </c>
+      <c r="E21" s="27" t="s">
+        <v>105</v>
+      </c>
+      <c r="F21" s="101" t="s">
+        <v>117</v>
+      </c>
+      <c r="G21" s="102"/>
+      <c r="H21" s="27"/>
     </row>
     <row r="22" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="4">
         <v>15</v>
       </c>
-      <c r="B22" s="42" t="s">
-        <v>55</v>
-      </c>
-      <c r="C22" s="4" t="s">
-        <v>56</v>
-      </c>
-      <c r="D22" s="4"/>
-      <c r="E22" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="F22" s="86" t="s">
-        <v>32</v>
-      </c>
-      <c r="G22" s="87"/>
-      <c r="H22" s="22" t="s">
-        <v>33</v>
-      </c>
+      <c r="B22" s="27"/>
+      <c r="C22" s="27"/>
+      <c r="D22" s="27"/>
+      <c r="E22" s="27"/>
+      <c r="F22" s="101"/>
+      <c r="G22" s="102"/>
+      <c r="H22" s="27"/>
     </row>
     <row r="23" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="4">
         <v>16</v>
       </c>
-      <c r="B23" s="82"/>
-      <c r="C23" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="D23" s="4"/>
-      <c r="E23" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="F23" s="86" t="s">
-        <v>32</v>
-      </c>
-      <c r="G23" s="87"/>
-      <c r="H23" s="22" t="s">
-        <v>33</v>
-      </c>
+      <c r="B23" s="27"/>
+      <c r="C23" s="27"/>
+      <c r="D23" s="27"/>
+      <c r="E23" s="27"/>
+      <c r="F23" s="101"/>
+      <c r="G23" s="102"/>
+      <c r="H23" s="27"/>
     </row>
     <row r="24" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" s="4">
         <v>17</v>
       </c>
-      <c r="B24" s="4"/>
-      <c r="C24" s="4"/>
-      <c r="D24" s="4"/>
-      <c r="E24" s="4"/>
-      <c r="F24" s="86"/>
-      <c r="G24" s="87"/>
-      <c r="H24" s="4"/>
+      <c r="B24" s="27"/>
+      <c r="C24" s="27"/>
+      <c r="D24" s="27"/>
+      <c r="E24" s="27"/>
+      <c r="F24" s="101"/>
+      <c r="G24" s="102"/>
+      <c r="H24" s="27"/>
     </row>
     <row r="25" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A25" s="4">
         <v>18</v>
       </c>
-      <c r="B25" s="4"/>
-      <c r="C25" s="4"/>
-      <c r="D25" s="4"/>
-      <c r="E25" s="4"/>
-      <c r="F25" s="86"/>
-      <c r="G25" s="87"/>
-      <c r="H25" s="4"/>
+      <c r="B25" s="27"/>
+      <c r="C25" s="27"/>
+      <c r="D25" s="27"/>
+      <c r="E25" s="27"/>
+      <c r="F25" s="101"/>
+      <c r="G25" s="102"/>
+      <c r="H25" s="27"/>
     </row>
     <row r="26" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26" s="4">
         <v>19</v>
       </c>
-      <c r="B26" s="4"/>
-      <c r="C26" s="4"/>
-      <c r="D26" s="4"/>
-      <c r="E26" s="4"/>
-      <c r="F26" s="86"/>
-      <c r="G26" s="87"/>
-      <c r="H26" s="4"/>
+      <c r="B26" s="27"/>
+      <c r="C26" s="27"/>
+      <c r="D26" s="27"/>
+      <c r="E26" s="27"/>
+      <c r="F26" s="101"/>
+      <c r="G26" s="102"/>
+      <c r="H26" s="27"/>
     </row>
     <row r="27" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A27" s="4">
         <v>20</v>
       </c>
-      <c r="B27" s="4"/>
-      <c r="C27" s="4"/>
-      <c r="D27" s="4"/>
-      <c r="E27" s="4"/>
-      <c r="F27" s="86"/>
-      <c r="G27" s="87"/>
-      <c r="H27" s="4"/>
+      <c r="B27" s="27"/>
+      <c r="C27" s="27"/>
+      <c r="D27" s="27"/>
+      <c r="E27" s="27"/>
+      <c r="F27" s="101"/>
+      <c r="G27" s="102"/>
+      <c r="H27" s="27"/>
     </row>
     <row r="28" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A28" s="4">
         <v>21</v>
       </c>
-      <c r="B28" s="4"/>
-      <c r="C28" s="4"/>
-      <c r="D28" s="4"/>
-      <c r="E28" s="4"/>
-      <c r="F28" s="86"/>
-      <c r="G28" s="87"/>
-      <c r="H28" s="4"/>
+      <c r="B28" s="27"/>
+      <c r="C28" s="27"/>
+      <c r="D28" s="27"/>
+      <c r="E28" s="27"/>
+      <c r="F28" s="101"/>
+      <c r="G28" s="102"/>
+      <c r="H28" s="27"/>
     </row>
     <row r="29" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A29" s="4">
         <v>22</v>
       </c>
-      <c r="B29" s="4"/>
-      <c r="C29" s="4"/>
-      <c r="D29" s="4"/>
-      <c r="E29" s="4"/>
-      <c r="F29" s="86"/>
-      <c r="G29" s="87"/>
-      <c r="H29" s="4"/>
+      <c r="B29" s="27"/>
+      <c r="C29" s="27"/>
+      <c r="D29" s="27"/>
+      <c r="E29" s="27"/>
+      <c r="F29" s="101"/>
+      <c r="G29" s="102"/>
+      <c r="H29" s="27"/>
     </row>
     <row r="30" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A30" s="4">
         <v>23</v>
       </c>
-      <c r="B30" s="4"/>
-      <c r="C30" s="4"/>
-      <c r="D30" s="4"/>
-      <c r="E30" s="4"/>
-      <c r="F30" s="86"/>
-      <c r="G30" s="87"/>
-      <c r="H30" s="4"/>
+      <c r="B30" s="27"/>
+      <c r="C30" s="27"/>
+      <c r="D30" s="27"/>
+      <c r="E30" s="27"/>
+      <c r="F30" s="101"/>
+      <c r="G30" s="102"/>
+      <c r="H30" s="27"/>
     </row>
     <row r="31" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A31" s="4">
         <v>24</v>
       </c>
-      <c r="B31" s="4"/>
-      <c r="C31" s="4"/>
-      <c r="D31" s="4"/>
-      <c r="E31" s="4"/>
-      <c r="F31" s="86"/>
-      <c r="G31" s="87"/>
-      <c r="H31" s="4"/>
+      <c r="B31" s="27"/>
+      <c r="C31" s="27"/>
+      <c r="D31" s="27"/>
+      <c r="E31" s="27"/>
+      <c r="F31" s="101"/>
+      <c r="G31" s="102"/>
+      <c r="H31" s="27"/>
     </row>
     <row r="32" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A32" s="4">
         <v>25</v>
       </c>
-      <c r="B32" s="4"/>
-      <c r="C32" s="4"/>
-      <c r="D32" s="4"/>
-      <c r="E32" s="4"/>
-      <c r="F32" s="86"/>
-      <c r="G32" s="87"/>
-      <c r="H32" s="4"/>
+      <c r="B32" s="27"/>
+      <c r="C32" s="27"/>
+      <c r="D32" s="27"/>
+      <c r="E32" s="27"/>
+      <c r="F32" s="101"/>
+      <c r="G32" s="102"/>
+      <c r="H32" s="27"/>
     </row>
     <row r="33" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A33" s="4">
         <v>26</v>
       </c>
-      <c r="B33" s="4"/>
-      <c r="C33" s="4"/>
-      <c r="D33" s="4"/>
-      <c r="E33" s="4"/>
-      <c r="F33" s="86"/>
-      <c r="G33" s="87"/>
-      <c r="H33" s="4"/>
+      <c r="B33" s="27"/>
+      <c r="C33" s="27"/>
+      <c r="D33" s="27"/>
+      <c r="E33" s="27"/>
+      <c r="F33" s="101"/>
+      <c r="G33" s="102"/>
+      <c r="H33" s="27"/>
     </row>
     <row r="34" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A34" s="4">
         <v>27</v>
       </c>
-      <c r="B34" s="4"/>
-      <c r="C34" s="4"/>
-      <c r="D34" s="4"/>
-      <c r="E34" s="4"/>
-      <c r="F34" s="86"/>
-      <c r="G34" s="87"/>
-      <c r="H34" s="4"/>
+      <c r="B34" s="27"/>
+      <c r="C34" s="27"/>
+      <c r="D34" s="27"/>
+      <c r="E34" s="27"/>
+      <c r="F34" s="101"/>
+      <c r="G34" s="102"/>
+      <c r="H34" s="27"/>
     </row>
     <row r="35" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A35" s="4">
         <v>28</v>
       </c>
-      <c r="B35" s="4"/>
-      <c r="C35" s="4"/>
-      <c r="D35" s="4"/>
-      <c r="E35" s="4"/>
-      <c r="F35" s="86"/>
-      <c r="G35" s="87"/>
-      <c r="H35" s="4"/>
+      <c r="B35" s="27"/>
+      <c r="C35" s="27"/>
+      <c r="D35" s="27"/>
+      <c r="E35" s="27"/>
+      <c r="F35" s="101"/>
+      <c r="G35" s="102"/>
+      <c r="H35" s="27"/>
     </row>
     <row r="36" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A36" s="4">
         <v>29</v>
       </c>
-      <c r="B36" s="4"/>
-      <c r="C36" s="4"/>
-      <c r="D36" s="4"/>
-      <c r="E36" s="4"/>
-      <c r="F36" s="86"/>
-      <c r="G36" s="87"/>
-      <c r="H36" s="4"/>
+      <c r="B36" s="27"/>
+      <c r="C36" s="27"/>
+      <c r="D36" s="27"/>
+      <c r="E36" s="27"/>
+      <c r="F36" s="101"/>
+      <c r="G36" s="102"/>
+      <c r="H36" s="27"/>
     </row>
     <row r="37" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A37" s="4">
         <v>30</v>
       </c>
-      <c r="B37" s="4"/>
-      <c r="C37" s="4"/>
-      <c r="D37" s="4"/>
-      <c r="E37" s="4"/>
-      <c r="F37" s="86"/>
-      <c r="G37" s="87"/>
-      <c r="H37" s="4"/>
+      <c r="B37" s="27"/>
+      <c r="C37" s="27"/>
+      <c r="D37" s="27"/>
+      <c r="E37" s="27"/>
+      <c r="F37" s="101"/>
+      <c r="G37" s="102"/>
+      <c r="H37" s="27"/>
     </row>
   </sheetData>
-  <mergeCells count="47">
+  <mergeCells count="46">
+    <mergeCell ref="B20:B21"/>
+    <mergeCell ref="C20:C21"/>
+    <mergeCell ref="B8:B12"/>
+    <mergeCell ref="C8:C10"/>
+    <mergeCell ref="C11:C12"/>
+    <mergeCell ref="B13:B16"/>
+    <mergeCell ref="B17:B19"/>
+    <mergeCell ref="C15:C16"/>
     <mergeCell ref="F33:G33"/>
     <mergeCell ref="F34:G34"/>
     <mergeCell ref="F35:G35"/>
@@ -5690,6 +6220,16 @@
     <mergeCell ref="F20:G20"/>
     <mergeCell ref="F21:G21"/>
     <mergeCell ref="F22:G22"/>
+    <mergeCell ref="F13:G13"/>
+    <mergeCell ref="F14:G14"/>
+    <mergeCell ref="F15:G15"/>
+    <mergeCell ref="F16:G16"/>
+    <mergeCell ref="F17:G17"/>
+    <mergeCell ref="F8:G8"/>
+    <mergeCell ref="F9:G9"/>
+    <mergeCell ref="F10:G10"/>
+    <mergeCell ref="F11:G11"/>
+    <mergeCell ref="F12:G12"/>
     <mergeCell ref="A1:C1"/>
     <mergeCell ref="A5:C5"/>
     <mergeCell ref="A6:A7"/>
@@ -5698,25 +6238,6 @@
     <mergeCell ref="A2:H4"/>
     <mergeCell ref="F6:G7"/>
     <mergeCell ref="H6:H7"/>
-    <mergeCell ref="B8:B11"/>
-    <mergeCell ref="C8:C9"/>
-    <mergeCell ref="C10:C11"/>
-    <mergeCell ref="F16:G16"/>
-    <mergeCell ref="F17:G17"/>
-    <mergeCell ref="F14:G14"/>
-    <mergeCell ref="F15:G15"/>
-    <mergeCell ref="F8:G8"/>
-    <mergeCell ref="F9:G9"/>
-    <mergeCell ref="F10:G10"/>
-    <mergeCell ref="F11:G11"/>
-    <mergeCell ref="F12:G12"/>
-    <mergeCell ref="F13:G13"/>
-    <mergeCell ref="B20:B21"/>
-    <mergeCell ref="B22:B23"/>
-    <mergeCell ref="B12:B13"/>
-    <mergeCell ref="B14:B15"/>
-    <mergeCell ref="B16:B17"/>
-    <mergeCell ref="B18:B19"/>
   </mergeCells>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.75" right="0.75" top="0.6" bottom="0.61" header="0.4" footer="0.39"/>
@@ -5731,7 +6252,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:I36"/>
+  <dimension ref="A1:I37"/>
   <sheetFormatPr defaultColWidth="10" defaultRowHeight="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="10" style="3" customWidth="1"/>
@@ -5743,506 +6264,547 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="101" t="s">
-        <v>58</v>
-      </c>
-      <c r="B1" s="102"/>
-      <c r="C1" s="103"/>
+      <c r="A1" s="41" t="s">
+        <v>29</v>
+      </c>
+      <c r="B1" s="42"/>
+      <c r="C1" s="43"/>
       <c r="D1" s="19"/>
     </row>
     <row r="2" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="90" t="s">
-        <v>59</v>
-      </c>
-      <c r="B2" s="90"/>
-      <c r="C2" s="90"/>
-      <c r="D2" s="90"/>
-      <c r="E2" s="90"/>
-      <c r="F2" s="90"/>
-      <c r="G2" s="90"/>
-      <c r="H2" s="90"/>
-      <c r="I2" s="90"/>
+      <c r="A2" s="32" t="s">
+        <v>30</v>
+      </c>
+      <c r="B2" s="32"/>
+      <c r="C2" s="32"/>
+      <c r="D2" s="32"/>
+      <c r="E2" s="32"/>
+      <c r="F2" s="32"/>
+      <c r="G2" s="32"/>
+      <c r="H2" s="32"/>
+      <c r="I2" s="32"/>
     </row>
     <row r="3" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="90"/>
-      <c r="B3" s="90"/>
-      <c r="C3" s="90"/>
-      <c r="D3" s="90"/>
-      <c r="E3" s="90"/>
-      <c r="F3" s="90"/>
-      <c r="G3" s="90"/>
-      <c r="H3" s="90"/>
-      <c r="I3" s="90"/>
+      <c r="A3" s="32"/>
+      <c r="B3" s="32"/>
+      <c r="C3" s="32"/>
+      <c r="D3" s="32"/>
+      <c r="E3" s="32"/>
+      <c r="F3" s="32"/>
+      <c r="G3" s="32"/>
+      <c r="H3" s="32"/>
+      <c r="I3" s="32"/>
     </row>
     <row r="4" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="76"/>
-      <c r="B4" s="76"/>
+      <c r="A4" s="33"/>
+      <c r="B4" s="33"/>
     </row>
     <row r="5" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="89" t="s">
+      <c r="A5" s="34" t="s">
         <v>21</v>
       </c>
-      <c r="B5" s="95" t="s">
-        <v>60</v>
-      </c>
-      <c r="C5" s="95" t="s">
-        <v>61</v>
-      </c>
-      <c r="D5" s="91" t="s">
+      <c r="B5" s="35" t="s">
+        <v>31</v>
+      </c>
+      <c r="C5" s="35" t="s">
+        <v>32</v>
+      </c>
+      <c r="D5" s="37" t="s">
         <v>24</v>
       </c>
-      <c r="E5" s="92"/>
-      <c r="F5" s="92"/>
-      <c r="G5" s="92"/>
-      <c r="H5" s="92"/>
-      <c r="I5" s="89" t="s">
+      <c r="E5" s="38"/>
+      <c r="F5" s="38"/>
+      <c r="G5" s="38"/>
+      <c r="H5" s="38"/>
+      <c r="I5" s="34" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="6" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="89"/>
-      <c r="B6" s="96"/>
-      <c r="C6" s="96"/>
-      <c r="D6" s="93"/>
-      <c r="E6" s="94"/>
-      <c r="F6" s="94"/>
-      <c r="G6" s="94"/>
-      <c r="H6" s="94"/>
-      <c r="I6" s="89"/>
-    </row>
-    <row r="7" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A6" s="34"/>
+      <c r="B6" s="36"/>
+      <c r="C6" s="36"/>
+      <c r="D6" s="39"/>
+      <c r="E6" s="40"/>
+      <c r="F6" s="40"/>
+      <c r="G6" s="40"/>
+      <c r="H6" s="40"/>
+      <c r="I6" s="34"/>
+    </row>
+    <row r="7" spans="1:9" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A7" s="4">
         <v>1</v>
       </c>
-      <c r="B7" s="97" t="s">
-        <v>62</v>
+      <c r="B7" s="28" t="s">
+        <v>33</v>
       </c>
       <c r="C7" s="22" t="s">
-        <v>63</v>
+        <v>120</v>
       </c>
       <c r="D7" s="44" t="s">
-        <v>32</v>
+        <v>121</v>
       </c>
       <c r="E7" s="44"/>
       <c r="F7" s="44"/>
       <c r="G7" s="44"/>
       <c r="H7" s="44"/>
-      <c r="I7" s="22" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="8" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I7" s="22"/>
+    </row>
+    <row r="8" spans="1:9" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A8" s="4">
         <v>2</v>
       </c>
-      <c r="B8" s="98"/>
+      <c r="B8" s="29"/>
       <c r="C8" s="22"/>
-      <c r="D8" s="44" t="s">
-        <v>65</v>
-      </c>
+      <c r="D8" s="44"/>
       <c r="E8" s="44"/>
       <c r="F8" s="44"/>
       <c r="G8" s="44"/>
       <c r="H8" s="44"/>
-      <c r="I8" s="22" t="s">
-        <v>66</v>
-      </c>
+      <c r="I8" s="22"/>
     </row>
     <row r="9" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="4">
         <v>3</v>
       </c>
-      <c r="B9" s="98"/>
+      <c r="B9" s="29"/>
       <c r="C9" s="22"/>
       <c r="D9" s="44"/>
       <c r="E9" s="44"/>
       <c r="F9" s="44"/>
       <c r="G9" s="44"/>
       <c r="H9" s="44"/>
-      <c r="I9" s="4"/>
+      <c r="I9" s="22"/>
     </row>
     <row r="10" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="4">
         <v>4</v>
       </c>
-      <c r="B10" s="99"/>
+      <c r="B10" s="30"/>
       <c r="C10" s="22"/>
       <c r="D10" s="44"/>
       <c r="E10" s="44"/>
       <c r="F10" s="44"/>
       <c r="G10" s="44"/>
       <c r="H10" s="44"/>
-      <c r="I10" s="4"/>
+      <c r="I10" s="22"/>
     </row>
     <row r="11" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="4">
         <v>5</v>
       </c>
-      <c r="B11" s="100" t="s">
-        <v>67</v>
-      </c>
-      <c r="C11" s="22" t="s">
-        <v>68</v>
+      <c r="B11" s="31" t="s">
+        <v>34</v>
+      </c>
+      <c r="C11" s="28" t="s">
+        <v>122</v>
       </c>
       <c r="D11" s="44" t="s">
-        <v>32</v>
+        <v>123</v>
       </c>
       <c r="E11" s="44"/>
       <c r="F11" s="44"/>
       <c r="G11" s="44"/>
       <c r="H11" s="44"/>
-      <c r="I11" s="22" t="s">
-        <v>66</v>
-      </c>
+      <c r="I11" s="22"/>
     </row>
     <row r="12" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="4">
         <v>6</v>
       </c>
-      <c r="B12" s="98"/>
-      <c r="C12" s="4"/>
+      <c r="B12" s="29"/>
+      <c r="C12" s="30"/>
       <c r="D12" s="44" t="s">
-        <v>69</v>
+        <v>124</v>
       </c>
       <c r="E12" s="44"/>
       <c r="F12" s="44"/>
       <c r="G12" s="44"/>
       <c r="H12" s="44"/>
-      <c r="I12" s="22" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="13" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I12" s="22"/>
+    </row>
+    <row r="13" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="4">
         <v>7</v>
       </c>
-      <c r="B13" s="98"/>
-      <c r="C13" s="4"/>
-      <c r="D13" s="44" t="s">
-        <v>70</v>
-      </c>
-      <c r="E13" s="44"/>
-      <c r="F13" s="44"/>
-      <c r="G13" s="44"/>
-      <c r="H13" s="44"/>
-      <c r="I13" s="22" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="14" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B13" s="29"/>
+      <c r="C13" s="22" t="s">
+        <v>125</v>
+      </c>
+      <c r="D13" s="199" t="s">
+        <v>126</v>
+      </c>
+      <c r="E13" s="199"/>
+      <c r="F13" s="199"/>
+      <c r="G13" s="199"/>
+      <c r="H13" s="199"/>
+      <c r="I13" s="22"/>
+    </row>
+    <row r="14" spans="1:9" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A14" s="4">
         <v>8</v>
       </c>
-      <c r="B14" s="99"/>
-      <c r="C14" s="4"/>
+      <c r="B14" s="30"/>
+      <c r="C14" s="22"/>
       <c r="D14" s="44"/>
       <c r="E14" s="44"/>
       <c r="F14" s="44"/>
       <c r="G14" s="44"/>
       <c r="H14" s="44"/>
-      <c r="I14" s="4"/>
+      <c r="I14" s="22"/>
     </row>
     <row r="15" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="4">
         <v>9</v>
       </c>
-      <c r="B15" s="100" t="s">
-        <v>71</v>
-      </c>
-      <c r="C15" s="4"/>
-      <c r="D15" s="44"/>
+      <c r="B15" s="31" t="s">
+        <v>35</v>
+      </c>
+      <c r="C15" s="22" t="s">
+        <v>127</v>
+      </c>
+      <c r="D15" s="44" t="s">
+        <v>128</v>
+      </c>
       <c r="E15" s="44"/>
       <c r="F15" s="44"/>
       <c r="G15" s="44"/>
       <c r="H15" s="44"/>
-      <c r="I15" s="4"/>
+      <c r="I15" s="22"/>
     </row>
     <row r="16" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="4">
         <v>10</v>
       </c>
-      <c r="B16" s="98"/>
-      <c r="C16" s="4"/>
+      <c r="B16" s="29"/>
+      <c r="C16" s="22"/>
       <c r="D16" s="44"/>
       <c r="E16" s="44"/>
       <c r="F16" s="44"/>
       <c r="G16" s="44"/>
       <c r="H16" s="44"/>
-      <c r="I16" s="4"/>
+      <c r="I16" s="22"/>
     </row>
     <row r="17" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="4">
         <v>11</v>
       </c>
-      <c r="B17" s="98"/>
-      <c r="C17" s="4"/>
+      <c r="B17" s="29"/>
+      <c r="C17" s="22"/>
       <c r="D17" s="44"/>
       <c r="E17" s="44"/>
       <c r="F17" s="44"/>
       <c r="G17" s="44"/>
       <c r="H17" s="44"/>
-      <c r="I17" s="4"/>
+      <c r="I17" s="22"/>
     </row>
     <row r="18" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="4">
         <v>12</v>
       </c>
-      <c r="B18" s="99"/>
-      <c r="C18" s="4"/>
+      <c r="B18" s="30"/>
+      <c r="C18" s="22"/>
       <c r="D18" s="44"/>
       <c r="E18" s="44"/>
       <c r="F18" s="44"/>
       <c r="G18" s="44"/>
       <c r="H18" s="44"/>
-      <c r="I18" s="4"/>
+      <c r="I18" s="22"/>
     </row>
     <row r="19" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="4">
         <v>13</v>
       </c>
-      <c r="B19" s="100" t="s">
-        <v>72</v>
-      </c>
-      <c r="C19" s="4"/>
-      <c r="D19" s="44"/>
+      <c r="B19" s="31" t="s">
+        <v>36</v>
+      </c>
+      <c r="C19" s="22" t="s">
+        <v>129</v>
+      </c>
+      <c r="D19" s="44" t="s">
+        <v>130</v>
+      </c>
       <c r="E19" s="44"/>
       <c r="F19" s="44"/>
       <c r="G19" s="44"/>
       <c r="H19" s="44"/>
-      <c r="I19" s="4"/>
+      <c r="I19" s="22"/>
     </row>
     <row r="20" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="4">
         <v>14</v>
       </c>
-      <c r="B20" s="98"/>
-      <c r="C20" s="4"/>
+      <c r="B20" s="29"/>
+      <c r="C20" s="22"/>
       <c r="D20" s="44"/>
       <c r="E20" s="44"/>
       <c r="F20" s="44"/>
       <c r="G20" s="44"/>
       <c r="H20" s="44"/>
-      <c r="I20" s="4"/>
+      <c r="I20" s="22"/>
     </row>
     <row r="21" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="4">
         <v>15</v>
       </c>
-      <c r="B21" s="98"/>
-      <c r="C21" s="4"/>
+      <c r="B21" s="29"/>
+      <c r="C21" s="22"/>
       <c r="D21" s="44"/>
       <c r="E21" s="44"/>
       <c r="F21" s="44"/>
       <c r="G21" s="44"/>
       <c r="H21" s="44"/>
-      <c r="I21" s="4"/>
+      <c r="I21" s="22"/>
     </row>
     <row r="22" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="4">
         <v>16</v>
       </c>
-      <c r="B22" s="99"/>
-      <c r="C22" s="4"/>
+      <c r="B22" s="30"/>
+      <c r="C22" s="22"/>
       <c r="D22" s="44"/>
       <c r="E22" s="44"/>
       <c r="F22" s="44"/>
       <c r="G22" s="44"/>
       <c r="H22" s="44"/>
-      <c r="I22" s="4"/>
+      <c r="I22" s="22"/>
     </row>
     <row r="23" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="4">
         <v>17</v>
       </c>
-      <c r="B23" s="100" t="s">
-        <v>73</v>
-      </c>
-      <c r="C23" s="4"/>
-      <c r="D23" s="44"/>
+      <c r="B23" s="31" t="s">
+        <v>37</v>
+      </c>
+      <c r="C23" s="22" t="s">
+        <v>131</v>
+      </c>
+      <c r="D23" s="44" t="s">
+        <v>132</v>
+      </c>
       <c r="E23" s="44"/>
       <c r="F23" s="44"/>
       <c r="G23" s="44"/>
       <c r="H23" s="44"/>
-      <c r="I23" s="4"/>
+      <c r="I23" s="22"/>
     </row>
     <row r="24" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" s="4">
         <v>18</v>
       </c>
-      <c r="B24" s="98"/>
-      <c r="C24" s="4"/>
-      <c r="D24" s="44"/>
+      <c r="B24" s="201"/>
+      <c r="C24" s="200" t="s">
+        <v>133</v>
+      </c>
+      <c r="D24" s="44" t="s">
+        <v>134</v>
+      </c>
       <c r="E24" s="44"/>
       <c r="F24" s="44"/>
       <c r="G24" s="44"/>
       <c r="H24" s="44"/>
-      <c r="I24" s="4"/>
+      <c r="I24" s="22"/>
     </row>
     <row r="25" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A25" s="4">
         <v>19</v>
       </c>
-      <c r="B25" s="98"/>
-      <c r="C25" s="4"/>
-      <c r="D25" s="44"/>
+      <c r="B25" s="201"/>
+      <c r="C25" s="22" t="s">
+        <v>135</v>
+      </c>
+      <c r="D25" s="44" t="s">
+        <v>136</v>
+      </c>
       <c r="E25" s="44"/>
       <c r="F25" s="44"/>
       <c r="G25" s="44"/>
       <c r="H25" s="44"/>
-      <c r="I25" s="4"/>
-    </row>
-    <row r="26" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I25" s="22"/>
+    </row>
+    <row r="26" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26" s="4">
         <v>20</v>
       </c>
-      <c r="B26" s="99"/>
-      <c r="C26" s="4"/>
-      <c r="D26" s="44"/>
-      <c r="E26" s="44"/>
-      <c r="F26" s="44"/>
-      <c r="G26" s="44"/>
-      <c r="H26" s="44"/>
-      <c r="I26" s="4"/>
+      <c r="B26" s="201"/>
+      <c r="C26" s="22" t="s">
+        <v>137</v>
+      </c>
+      <c r="D26" s="199" t="s">
+        <v>138</v>
+      </c>
+      <c r="E26" s="199"/>
+      <c r="F26" s="199"/>
+      <c r="G26" s="199"/>
+      <c r="H26" s="199"/>
+      <c r="I26" s="22"/>
     </row>
     <row r="27" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A27" s="4">
         <v>21</v>
       </c>
-      <c r="B27" s="100" t="s">
-        <v>74</v>
-      </c>
-      <c r="C27" s="4"/>
-      <c r="D27" s="44"/>
-      <c r="E27" s="44"/>
-      <c r="F27" s="44"/>
-      <c r="G27" s="44"/>
-      <c r="H27" s="44"/>
-      <c r="I27" s="4"/>
+      <c r="B27" s="202"/>
+      <c r="C27" s="22" t="s">
+        <v>139</v>
+      </c>
+      <c r="D27" s="45" t="s">
+        <v>141</v>
+      </c>
+      <c r="E27" s="46"/>
+      <c r="F27" s="46"/>
+      <c r="G27" s="46"/>
+      <c r="H27" s="47"/>
+      <c r="I27" s="22"/>
     </row>
     <row r="28" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A28" s="4">
         <v>22</v>
       </c>
-      <c r="B28" s="98"/>
-      <c r="C28" s="4"/>
-      <c r="D28" s="44"/>
+      <c r="B28" s="31" t="s">
+        <v>38</v>
+      </c>
+      <c r="C28" s="22" t="s">
+        <v>140</v>
+      </c>
+      <c r="D28" s="44" t="s">
+        <v>142</v>
+      </c>
       <c r="E28" s="44"/>
       <c r="F28" s="44"/>
       <c r="G28" s="44"/>
       <c r="H28" s="44"/>
-      <c r="I28" s="4"/>
+      <c r="I28" s="22"/>
     </row>
     <row r="29" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A29" s="4">
         <v>23</v>
       </c>
-      <c r="B29" s="98"/>
-      <c r="C29" s="4"/>
-      <c r="D29" s="44"/>
+      <c r="B29" s="29"/>
+      <c r="C29" s="22" t="s">
+        <v>143</v>
+      </c>
+      <c r="D29" s="44" t="s">
+        <v>144</v>
+      </c>
       <c r="E29" s="44"/>
       <c r="F29" s="44"/>
       <c r="G29" s="44"/>
       <c r="H29" s="44"/>
-      <c r="I29" s="4"/>
+      <c r="I29" s="22"/>
     </row>
     <row r="30" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A30" s="4">
         <v>24</v>
       </c>
-      <c r="B30" s="99"/>
-      <c r="C30" s="4"/>
+      <c r="B30" s="29"/>
+      <c r="C30" s="22"/>
       <c r="D30" s="44"/>
       <c r="E30" s="44"/>
       <c r="F30" s="44"/>
       <c r="G30" s="44"/>
       <c r="H30" s="44"/>
-      <c r="I30" s="4"/>
+      <c r="I30" s="22"/>
     </row>
     <row r="31" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A31" s="4">
         <v>25</v>
       </c>
-      <c r="B31" s="4"/>
-      <c r="C31" s="4"/>
+      <c r="B31" s="30"/>
+      <c r="C31" s="22"/>
       <c r="D31" s="44"/>
       <c r="E31" s="44"/>
       <c r="F31" s="44"/>
       <c r="G31" s="44"/>
       <c r="H31" s="44"/>
-      <c r="I31" s="4"/>
+      <c r="I31" s="22"/>
     </row>
     <row r="32" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A32" s="4">
         <v>26</v>
       </c>
       <c r="B32" s="4"/>
-      <c r="C32" s="4"/>
+      <c r="C32" s="22"/>
       <c r="D32" s="44"/>
       <c r="E32" s="44"/>
       <c r="F32" s="44"/>
       <c r="G32" s="44"/>
       <c r="H32" s="44"/>
-      <c r="I32" s="4"/>
+      <c r="I32" s="22"/>
     </row>
     <row r="33" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A33" s="4">
         <v>27</v>
       </c>
       <c r="B33" s="4"/>
-      <c r="C33" s="4"/>
+      <c r="C33" s="22"/>
       <c r="D33" s="44"/>
       <c r="E33" s="44"/>
       <c r="F33" s="44"/>
       <c r="G33" s="44"/>
       <c r="H33" s="44"/>
-      <c r="I33" s="4"/>
+      <c r="I33" s="22"/>
     </row>
     <row r="34" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A34" s="4">
         <v>28</v>
       </c>
       <c r="B34" s="4"/>
-      <c r="C34" s="4"/>
+      <c r="C34" s="22"/>
       <c r="D34" s="44"/>
       <c r="E34" s="44"/>
       <c r="F34" s="44"/>
       <c r="G34" s="44"/>
       <c r="H34" s="44"/>
-      <c r="I34" s="4"/>
+      <c r="I34" s="22"/>
     </row>
     <row r="35" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A35" s="4">
         <v>29</v>
       </c>
       <c r="B35" s="4"/>
-      <c r="C35" s="4"/>
+      <c r="C35" s="22"/>
       <c r="D35" s="44"/>
       <c r="E35" s="44"/>
       <c r="F35" s="44"/>
       <c r="G35" s="44"/>
       <c r="H35" s="44"/>
-      <c r="I35" s="4"/>
+      <c r="I35" s="22"/>
     </row>
     <row r="36" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A36" s="4">
         <v>30</v>
       </c>
       <c r="B36" s="4"/>
-      <c r="C36" s="4"/>
+      <c r="C36" s="22"/>
       <c r="D36" s="44"/>
       <c r="E36" s="44"/>
       <c r="F36" s="44"/>
       <c r="G36" s="44"/>
       <c r="H36" s="44"/>
-      <c r="I36" s="4"/>
+      <c r="I36" s="22"/>
+    </row>
+    <row r="37" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A37" s="4">
+        <v>30</v>
+      </c>
+      <c r="B37" s="4"/>
+      <c r="C37" s="22"/>
+      <c r="D37" s="44"/>
+      <c r="E37" s="44"/>
+      <c r="F37" s="44"/>
+      <c r="G37" s="44"/>
+      <c r="H37" s="44"/>
+      <c r="I37" s="22"/>
     </row>
   </sheetData>
-  <mergeCells count="44">
+  <mergeCells count="46">
+    <mergeCell ref="D27:H27"/>
+    <mergeCell ref="C11:C12"/>
     <mergeCell ref="A1:C1"/>
-    <mergeCell ref="D32:H32"/>
     <mergeCell ref="D33:H33"/>
     <mergeCell ref="D34:H34"/>
     <mergeCell ref="D35:H35"/>
+    <mergeCell ref="D36:H36"/>
     <mergeCell ref="B11:B14"/>
     <mergeCell ref="D7:H7"/>
     <mergeCell ref="D18:H18"/>
@@ -6254,12 +6816,12 @@
     <mergeCell ref="D12:H12"/>
     <mergeCell ref="D13:H13"/>
     <mergeCell ref="D14:H14"/>
-    <mergeCell ref="D36:H36"/>
-    <mergeCell ref="D27:H27"/>
+    <mergeCell ref="D37:H37"/>
     <mergeCell ref="D28:H28"/>
     <mergeCell ref="D29:H29"/>
     <mergeCell ref="D30:H30"/>
     <mergeCell ref="D31:H31"/>
+    <mergeCell ref="D32:H32"/>
     <mergeCell ref="D15:H15"/>
     <mergeCell ref="D16:H16"/>
     <mergeCell ref="D17:H17"/>
@@ -6280,8 +6842,8 @@
     <mergeCell ref="B7:B10"/>
     <mergeCell ref="B15:B18"/>
     <mergeCell ref="B19:B22"/>
-    <mergeCell ref="B23:B26"/>
-    <mergeCell ref="B27:B30"/>
+    <mergeCell ref="B28:B31"/>
+    <mergeCell ref="B23:B27"/>
   </mergeCells>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.75" right="0.75" top="0.6" bottom="0.61" header="0.4" footer="0.39"/>
@@ -6305,23 +6867,23 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:52" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B1" s="191" t="s">
-        <v>75</v>
-      </c>
-      <c r="C1" s="192"/>
-      <c r="D1" s="192"/>
-      <c r="E1" s="192"/>
-      <c r="F1" s="192"/>
-      <c r="G1" s="192"/>
-      <c r="H1" s="192"/>
-      <c r="I1" s="192"/>
-      <c r="J1" s="192"/>
-      <c r="K1" s="192"/>
-      <c r="L1" s="192"/>
-      <c r="M1" s="192"/>
-      <c r="N1" s="192"/>
-      <c r="O1" s="192"/>
-      <c r="P1" s="192"/>
+      <c r="B1" s="194" t="s">
+        <v>39</v>
+      </c>
+      <c r="C1" s="195"/>
+      <c r="D1" s="195"/>
+      <c r="E1" s="195"/>
+      <c r="F1" s="195"/>
+      <c r="G1" s="195"/>
+      <c r="H1" s="195"/>
+      <c r="I1" s="195"/>
+      <c r="J1" s="195"/>
+      <c r="K1" s="195"/>
+      <c r="L1" s="195"/>
+      <c r="M1" s="195"/>
+      <c r="N1" s="195"/>
+      <c r="O1" s="195"/>
+      <c r="P1" s="195"/>
       <c r="Q1" s="21"/>
       <c r="R1" s="20"/>
       <c r="S1" s="20"/>
@@ -6338,232 +6900,232 @@
       <c r="AD1" s="20"/>
     </row>
     <row r="2" spans="2:52" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B2" s="140" t="s">
+      <c r="B2" s="143" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="140"/>
-      <c r="D2" s="140"/>
-      <c r="E2" s="140"/>
-      <c r="F2" s="140"/>
-      <c r="G2" s="140"/>
-      <c r="H2" s="140"/>
-      <c r="I2" s="140"/>
-      <c r="J2" s="144"/>
-      <c r="K2" s="144"/>
-      <c r="L2" s="144"/>
-      <c r="M2" s="144"/>
-      <c r="N2" s="144"/>
-      <c r="O2" s="144"/>
-      <c r="P2" s="144"/>
-      <c r="Q2" s="144"/>
-      <c r="R2" s="144"/>
-      <c r="S2" s="144"/>
-      <c r="T2" s="144"/>
-      <c r="U2" s="144"/>
-      <c r="V2" s="144"/>
-      <c r="W2" s="144"/>
-      <c r="X2" s="144"/>
-      <c r="Y2" s="144"/>
-      <c r="Z2" s="144"/>
-      <c r="AA2" s="144"/>
-      <c r="AB2" s="144"/>
-      <c r="AC2" s="144"/>
-      <c r="AD2" s="144"/>
+      <c r="C2" s="143"/>
+      <c r="D2" s="143"/>
+      <c r="E2" s="143"/>
+      <c r="F2" s="143"/>
+      <c r="G2" s="143"/>
+      <c r="H2" s="143"/>
+      <c r="I2" s="143"/>
+      <c r="J2" s="147"/>
+      <c r="K2" s="147"/>
+      <c r="L2" s="147"/>
+      <c r="M2" s="147"/>
+      <c r="N2" s="147"/>
+      <c r="O2" s="147"/>
+      <c r="P2" s="147"/>
+      <c r="Q2" s="147"/>
+      <c r="R2" s="147"/>
+      <c r="S2" s="147"/>
+      <c r="T2" s="147"/>
+      <c r="U2" s="147"/>
+      <c r="V2" s="147"/>
+      <c r="W2" s="147"/>
+      <c r="X2" s="147"/>
+      <c r="Y2" s="147"/>
+      <c r="Z2" s="147"/>
+      <c r="AA2" s="147"/>
+      <c r="AB2" s="147"/>
+      <c r="AC2" s="147"/>
+      <c r="AD2" s="147"/>
     </row>
     <row r="3" spans="2:52" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="4" spans="2:52" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B4" s="151" t="s">
-        <v>76</v>
-      </c>
-      <c r="C4" s="138"/>
-      <c r="D4" s="138"/>
-      <c r="E4" s="138"/>
-      <c r="F4" s="138"/>
-      <c r="G4" s="138"/>
-      <c r="H4" s="138"/>
-      <c r="I4" s="138"/>
-      <c r="J4" s="138" t="s">
-        <v>77</v>
-      </c>
-      <c r="K4" s="138"/>
-      <c r="L4" s="138"/>
-      <c r="M4" s="138"/>
-      <c r="N4" s="138"/>
-      <c r="O4" s="138"/>
-      <c r="P4" s="138"/>
-      <c r="Q4" s="145" t="s">
-        <v>78</v>
-      </c>
-      <c r="R4" s="149"/>
-      <c r="S4" s="146"/>
-      <c r="T4" s="145" t="s">
-        <v>79</v>
-      </c>
-      <c r="U4" s="149"/>
-      <c r="V4" s="149"/>
-      <c r="W4" s="146"/>
-      <c r="X4" s="145" t="s">
-        <v>80</v>
-      </c>
-      <c r="Y4" s="146"/>
-      <c r="Z4" s="138" t="s">
-        <v>81</v>
-      </c>
-      <c r="AA4" s="138"/>
-      <c r="AB4" s="138"/>
-      <c r="AC4" s="138" t="s">
-        <v>81</v>
-      </c>
-      <c r="AD4" s="138"/>
-      <c r="AE4" s="138"/>
-      <c r="AF4" s="138" t="s">
-        <v>81</v>
-      </c>
-      <c r="AG4" s="138"/>
-      <c r="AH4" s="138"/>
-      <c r="AI4" s="138" t="s">
-        <v>81</v>
-      </c>
-      <c r="AJ4" s="138"/>
-      <c r="AK4" s="138"/>
-      <c r="AL4" s="138" t="s">
-        <v>81</v>
-      </c>
-      <c r="AM4" s="138"/>
-      <c r="AN4" s="138"/>
-      <c r="AO4" s="138" t="s">
-        <v>82</v>
-      </c>
-      <c r="AP4" s="138"/>
-      <c r="AQ4" s="138"/>
-      <c r="AR4" s="138"/>
-      <c r="AS4" s="138"/>
-      <c r="AT4" s="138"/>
-      <c r="AU4" s="138"/>
-      <c r="AV4" s="138"/>
-      <c r="AW4" s="138"/>
-      <c r="AX4" s="138"/>
-      <c r="AY4" s="138"/>
-      <c r="AZ4" s="139"/>
+      <c r="B4" s="154" t="s">
+        <v>40</v>
+      </c>
+      <c r="C4" s="141"/>
+      <c r="D4" s="141"/>
+      <c r="E4" s="141"/>
+      <c r="F4" s="141"/>
+      <c r="G4" s="141"/>
+      <c r="H4" s="141"/>
+      <c r="I4" s="141"/>
+      <c r="J4" s="141" t="s">
+        <v>41</v>
+      </c>
+      <c r="K4" s="141"/>
+      <c r="L4" s="141"/>
+      <c r="M4" s="141"/>
+      <c r="N4" s="141"/>
+      <c r="O4" s="141"/>
+      <c r="P4" s="141"/>
+      <c r="Q4" s="148" t="s">
+        <v>42</v>
+      </c>
+      <c r="R4" s="152"/>
+      <c r="S4" s="149"/>
+      <c r="T4" s="148" t="s">
+        <v>43</v>
+      </c>
+      <c r="U4" s="152"/>
+      <c r="V4" s="152"/>
+      <c r="W4" s="149"/>
+      <c r="X4" s="148" t="s">
+        <v>44</v>
+      </c>
+      <c r="Y4" s="149"/>
+      <c r="Z4" s="141" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA4" s="141"/>
+      <c r="AB4" s="141"/>
+      <c r="AC4" s="141" t="s">
+        <v>45</v>
+      </c>
+      <c r="AD4" s="141"/>
+      <c r="AE4" s="141"/>
+      <c r="AF4" s="141" t="s">
+        <v>45</v>
+      </c>
+      <c r="AG4" s="141"/>
+      <c r="AH4" s="141"/>
+      <c r="AI4" s="141" t="s">
+        <v>45</v>
+      </c>
+      <c r="AJ4" s="141"/>
+      <c r="AK4" s="141"/>
+      <c r="AL4" s="141" t="s">
+        <v>45</v>
+      </c>
+      <c r="AM4" s="141"/>
+      <c r="AN4" s="141"/>
+      <c r="AO4" s="141" t="s">
+        <v>46</v>
+      </c>
+      <c r="AP4" s="141"/>
+      <c r="AQ4" s="141"/>
+      <c r="AR4" s="141"/>
+      <c r="AS4" s="141"/>
+      <c r="AT4" s="141"/>
+      <c r="AU4" s="141"/>
+      <c r="AV4" s="141"/>
+      <c r="AW4" s="141"/>
+      <c r="AX4" s="141"/>
+      <c r="AY4" s="141"/>
+      <c r="AZ4" s="142"/>
     </row>
     <row r="5" spans="2:52" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B5" s="152"/>
-      <c r="C5" s="140"/>
-      <c r="D5" s="140"/>
-      <c r="E5" s="140"/>
-      <c r="F5" s="140"/>
-      <c r="G5" s="140"/>
-      <c r="H5" s="140"/>
-      <c r="I5" s="140"/>
-      <c r="J5" s="140"/>
-      <c r="K5" s="140"/>
-      <c r="L5" s="140"/>
-      <c r="M5" s="140"/>
-      <c r="N5" s="140"/>
-      <c r="O5" s="140"/>
-      <c r="P5" s="140"/>
-      <c r="Q5" s="147"/>
-      <c r="R5" s="150"/>
-      <c r="S5" s="148"/>
-      <c r="T5" s="147"/>
-      <c r="U5" s="150"/>
-      <c r="V5" s="150"/>
-      <c r="W5" s="148"/>
-      <c r="X5" s="147"/>
-      <c r="Y5" s="148"/>
+      <c r="B5" s="155"/>
+      <c r="C5" s="143"/>
+      <c r="D5" s="143"/>
+      <c r="E5" s="143"/>
+      <c r="F5" s="143"/>
+      <c r="G5" s="143"/>
+      <c r="H5" s="143"/>
+      <c r="I5" s="143"/>
+      <c r="J5" s="143"/>
+      <c r="K5" s="143"/>
+      <c r="L5" s="143"/>
+      <c r="M5" s="143"/>
+      <c r="N5" s="143"/>
+      <c r="O5" s="143"/>
+      <c r="P5" s="143"/>
+      <c r="Q5" s="150"/>
+      <c r="R5" s="153"/>
+      <c r="S5" s="151"/>
+      <c r="T5" s="150"/>
+      <c r="U5" s="153"/>
+      <c r="V5" s="153"/>
+      <c r="W5" s="151"/>
+      <c r="X5" s="150"/>
+      <c r="Y5" s="151"/>
       <c r="Z5" s="6" t="s">
-        <v>83</v>
+        <v>47</v>
       </c>
       <c r="AA5" s="7" t="s">
-        <v>84</v>
+        <v>48</v>
       </c>
       <c r="AB5" s="8" t="s">
-        <v>85</v>
+        <v>49</v>
       </c>
       <c r="AC5" s="6" t="s">
-        <v>83</v>
+        <v>47</v>
       </c>
       <c r="AD5" s="7" t="s">
-        <v>84</v>
+        <v>48</v>
       </c>
       <c r="AE5" s="8" t="s">
-        <v>85</v>
+        <v>49</v>
       </c>
       <c r="AF5" s="6" t="s">
-        <v>83</v>
+        <v>47</v>
       </c>
       <c r="AG5" s="7" t="s">
-        <v>84</v>
+        <v>48</v>
       </c>
       <c r="AH5" s="8" t="s">
-        <v>85</v>
+        <v>49</v>
       </c>
       <c r="AI5" s="6" t="s">
-        <v>83</v>
+        <v>47</v>
       </c>
       <c r="AJ5" s="7" t="s">
-        <v>84</v>
+        <v>48</v>
       </c>
       <c r="AK5" s="8" t="s">
-        <v>85</v>
+        <v>49</v>
       </c>
       <c r="AL5" s="6" t="s">
-        <v>83</v>
+        <v>47</v>
       </c>
       <c r="AM5" s="7" t="s">
-        <v>84</v>
+        <v>48</v>
       </c>
       <c r="AN5" s="8" t="s">
-        <v>85</v>
-      </c>
-      <c r="AO5" s="140"/>
-      <c r="AP5" s="140"/>
-      <c r="AQ5" s="140"/>
-      <c r="AR5" s="140"/>
-      <c r="AS5" s="140"/>
-      <c r="AT5" s="140"/>
-      <c r="AU5" s="140"/>
-      <c r="AV5" s="140"/>
-      <c r="AW5" s="140"/>
-      <c r="AX5" s="140"/>
-      <c r="AY5" s="140"/>
-      <c r="AZ5" s="141"/>
+        <v>49</v>
+      </c>
+      <c r="AO5" s="143"/>
+      <c r="AP5" s="143"/>
+      <c r="AQ5" s="143"/>
+      <c r="AR5" s="143"/>
+      <c r="AS5" s="143"/>
+      <c r="AT5" s="143"/>
+      <c r="AU5" s="143"/>
+      <c r="AV5" s="143"/>
+      <c r="AW5" s="143"/>
+      <c r="AX5" s="143"/>
+      <c r="AY5" s="143"/>
+      <c r="AZ5" s="144"/>
     </row>
     <row r="6" spans="2:52" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B6" s="167">
+      <c r="B6" s="170">
         <v>1</v>
       </c>
-      <c r="C6" s="153" t="s">
-        <v>86</v>
-      </c>
-      <c r="D6" s="153"/>
-      <c r="E6" s="153"/>
-      <c r="F6" s="153"/>
-      <c r="G6" s="153"/>
-      <c r="H6" s="153"/>
-      <c r="I6" s="153"/>
-      <c r="J6" s="153"/>
-      <c r="K6" s="153"/>
-      <c r="L6" s="153"/>
-      <c r="M6" s="153"/>
-      <c r="N6" s="153"/>
-      <c r="O6" s="153"/>
-      <c r="P6" s="153"/>
-      <c r="Q6" s="144"/>
-      <c r="R6" s="144"/>
-      <c r="S6" s="144"/>
-      <c r="T6" s="158" t="s">
-        <v>87</v>
-      </c>
-      <c r="U6" s="158"/>
-      <c r="V6" s="156">
+      <c r="C6" s="156" t="s">
+        <v>50</v>
+      </c>
+      <c r="D6" s="156"/>
+      <c r="E6" s="156"/>
+      <c r="F6" s="156"/>
+      <c r="G6" s="156"/>
+      <c r="H6" s="156"/>
+      <c r="I6" s="156"/>
+      <c r="J6" s="156"/>
+      <c r="K6" s="156"/>
+      <c r="L6" s="156"/>
+      <c r="M6" s="156"/>
+      <c r="N6" s="156"/>
+      <c r="O6" s="156"/>
+      <c r="P6" s="156"/>
+      <c r="Q6" s="147"/>
+      <c r="R6" s="147"/>
+      <c r="S6" s="147"/>
+      <c r="T6" s="161" t="s">
+        <v>51</v>
+      </c>
+      <c r="U6" s="161"/>
+      <c r="V6" s="159">
         <v>0</v>
       </c>
-      <c r="W6" s="156"/>
-      <c r="X6" s="142">
+      <c r="W6" s="159"/>
+      <c r="X6" s="145">
         <v>0</v>
       </c>
-      <c r="Y6" s="142"/>
+      <c r="Y6" s="145"/>
       <c r="Z6" s="9"/>
       <c r="AA6" s="10"/>
       <c r="AB6" s="11"/>
@@ -6579,50 +7141,50 @@
       <c r="AL6" s="9"/>
       <c r="AM6" s="10"/>
       <c r="AN6" s="11"/>
-      <c r="AO6" s="153"/>
-      <c r="AP6" s="153"/>
-      <c r="AQ6" s="153"/>
-      <c r="AR6" s="153"/>
-      <c r="AS6" s="153"/>
-      <c r="AT6" s="153"/>
-      <c r="AU6" s="153"/>
-      <c r="AV6" s="153"/>
-      <c r="AW6" s="153"/>
-      <c r="AX6" s="153"/>
-      <c r="AY6" s="153"/>
-      <c r="AZ6" s="154"/>
+      <c r="AO6" s="156"/>
+      <c r="AP6" s="156"/>
+      <c r="AQ6" s="156"/>
+      <c r="AR6" s="156"/>
+      <c r="AS6" s="156"/>
+      <c r="AT6" s="156"/>
+      <c r="AU6" s="156"/>
+      <c r="AV6" s="156"/>
+      <c r="AW6" s="156"/>
+      <c r="AX6" s="156"/>
+      <c r="AY6" s="156"/>
+      <c r="AZ6" s="157"/>
     </row>
     <row r="7" spans="2:52" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B7" s="167"/>
-      <c r="C7" s="153"/>
-      <c r="D7" s="153"/>
-      <c r="E7" s="153"/>
-      <c r="F7" s="153"/>
-      <c r="G7" s="153"/>
-      <c r="H7" s="153"/>
-      <c r="I7" s="153"/>
-      <c r="J7" s="153"/>
-      <c r="K7" s="153"/>
-      <c r="L7" s="153"/>
-      <c r="M7" s="153"/>
-      <c r="N7" s="153"/>
-      <c r="O7" s="153"/>
-      <c r="P7" s="153"/>
-      <c r="Q7" s="144"/>
-      <c r="R7" s="144"/>
-      <c r="S7" s="144"/>
-      <c r="T7" s="155" t="s">
+      <c r="B7" s="170"/>
+      <c r="C7" s="156"/>
+      <c r="D7" s="156"/>
+      <c r="E7" s="156"/>
+      <c r="F7" s="156"/>
+      <c r="G7" s="156"/>
+      <c r="H7" s="156"/>
+      <c r="I7" s="156"/>
+      <c r="J7" s="156"/>
+      <c r="K7" s="156"/>
+      <c r="L7" s="156"/>
+      <c r="M7" s="156"/>
+      <c r="N7" s="156"/>
+      <c r="O7" s="156"/>
+      <c r="P7" s="156"/>
+      <c r="Q7" s="147"/>
+      <c r="R7" s="147"/>
+      <c r="S7" s="147"/>
+      <c r="T7" s="158" t="s">
         <v>25</v>
       </c>
-      <c r="U7" s="155"/>
-      <c r="V7" s="157">
+      <c r="U7" s="158"/>
+      <c r="V7" s="160">
         <v>0</v>
       </c>
-      <c r="W7" s="157"/>
-      <c r="X7" s="143">
+      <c r="W7" s="160"/>
+      <c r="X7" s="146">
         <v>0</v>
       </c>
-      <c r="Y7" s="143"/>
+      <c r="Y7" s="146"/>
       <c r="Z7" s="12"/>
       <c r="AA7" s="13"/>
       <c r="AB7" s="14"/>
@@ -6638,54 +7200,54 @@
       <c r="AL7" s="12"/>
       <c r="AM7" s="13"/>
       <c r="AN7" s="14"/>
-      <c r="AO7" s="153"/>
-      <c r="AP7" s="153"/>
-      <c r="AQ7" s="153"/>
-      <c r="AR7" s="153"/>
-      <c r="AS7" s="153"/>
-      <c r="AT7" s="153"/>
-      <c r="AU7" s="153"/>
-      <c r="AV7" s="153"/>
-      <c r="AW7" s="153"/>
-      <c r="AX7" s="153"/>
-      <c r="AY7" s="153"/>
-      <c r="AZ7" s="154"/>
+      <c r="AO7" s="156"/>
+      <c r="AP7" s="156"/>
+      <c r="AQ7" s="156"/>
+      <c r="AR7" s="156"/>
+      <c r="AS7" s="156"/>
+      <c r="AT7" s="156"/>
+      <c r="AU7" s="156"/>
+      <c r="AV7" s="156"/>
+      <c r="AW7" s="156"/>
+      <c r="AX7" s="156"/>
+      <c r="AY7" s="156"/>
+      <c r="AZ7" s="157"/>
     </row>
     <row r="8" spans="2:52" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B8" s="167">
+      <c r="B8" s="170">
         <v>2</v>
       </c>
-      <c r="C8" s="153" t="s">
-        <v>88</v>
-      </c>
-      <c r="D8" s="153"/>
-      <c r="E8" s="153"/>
-      <c r="F8" s="153"/>
-      <c r="G8" s="153"/>
-      <c r="H8" s="153"/>
-      <c r="I8" s="153"/>
-      <c r="J8" s="112"/>
-      <c r="K8" s="113"/>
-      <c r="L8" s="113"/>
-      <c r="M8" s="113"/>
-      <c r="N8" s="113"/>
-      <c r="O8" s="113"/>
-      <c r="P8" s="114"/>
-      <c r="Q8" s="144"/>
-      <c r="R8" s="144"/>
-      <c r="S8" s="144"/>
-      <c r="T8" s="158" t="s">
-        <v>87</v>
-      </c>
-      <c r="U8" s="158"/>
-      <c r="V8" s="156">
+      <c r="C8" s="156" t="s">
+        <v>52</v>
+      </c>
+      <c r="D8" s="156"/>
+      <c r="E8" s="156"/>
+      <c r="F8" s="156"/>
+      <c r="G8" s="156"/>
+      <c r="H8" s="156"/>
+      <c r="I8" s="156"/>
+      <c r="J8" s="115"/>
+      <c r="K8" s="116"/>
+      <c r="L8" s="116"/>
+      <c r="M8" s="116"/>
+      <c r="N8" s="116"/>
+      <c r="O8" s="116"/>
+      <c r="P8" s="117"/>
+      <c r="Q8" s="147"/>
+      <c r="R8" s="147"/>
+      <c r="S8" s="147"/>
+      <c r="T8" s="161" t="s">
+        <v>51</v>
+      </c>
+      <c r="U8" s="161"/>
+      <c r="V8" s="159">
         <v>0</v>
       </c>
-      <c r="W8" s="156"/>
-      <c r="X8" s="142">
+      <c r="W8" s="159"/>
+      <c r="X8" s="145">
         <v>0</v>
       </c>
-      <c r="Y8" s="142"/>
+      <c r="Y8" s="145"/>
       <c r="Z8" s="9"/>
       <c r="AA8" s="10"/>
       <c r="AB8" s="11"/>
@@ -6701,50 +7263,50 @@
       <c r="AL8" s="9"/>
       <c r="AM8" s="10"/>
       <c r="AN8" s="11"/>
-      <c r="AO8" s="153"/>
-      <c r="AP8" s="153"/>
-      <c r="AQ8" s="153"/>
-      <c r="AR8" s="153"/>
-      <c r="AS8" s="153"/>
-      <c r="AT8" s="153"/>
-      <c r="AU8" s="153"/>
-      <c r="AV8" s="153"/>
-      <c r="AW8" s="153"/>
-      <c r="AX8" s="153"/>
-      <c r="AY8" s="153"/>
-      <c r="AZ8" s="154"/>
+      <c r="AO8" s="156"/>
+      <c r="AP8" s="156"/>
+      <c r="AQ8" s="156"/>
+      <c r="AR8" s="156"/>
+      <c r="AS8" s="156"/>
+      <c r="AT8" s="156"/>
+      <c r="AU8" s="156"/>
+      <c r="AV8" s="156"/>
+      <c r="AW8" s="156"/>
+      <c r="AX8" s="156"/>
+      <c r="AY8" s="156"/>
+      <c r="AZ8" s="157"/>
     </row>
     <row r="9" spans="2:52" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B9" s="167"/>
-      <c r="C9" s="153"/>
-      <c r="D9" s="153"/>
-      <c r="E9" s="153"/>
-      <c r="F9" s="153"/>
-      <c r="G9" s="153"/>
-      <c r="H9" s="153"/>
-      <c r="I9" s="153"/>
-      <c r="J9" s="115"/>
-      <c r="K9" s="116"/>
-      <c r="L9" s="116"/>
-      <c r="M9" s="116"/>
-      <c r="N9" s="116"/>
-      <c r="O9" s="116"/>
-      <c r="P9" s="117"/>
-      <c r="Q9" s="144"/>
-      <c r="R9" s="144"/>
-      <c r="S9" s="144"/>
-      <c r="T9" s="155" t="s">
+      <c r="B9" s="170"/>
+      <c r="C9" s="156"/>
+      <c r="D9" s="156"/>
+      <c r="E9" s="156"/>
+      <c r="F9" s="156"/>
+      <c r="G9" s="156"/>
+      <c r="H9" s="156"/>
+      <c r="I9" s="156"/>
+      <c r="J9" s="118"/>
+      <c r="K9" s="119"/>
+      <c r="L9" s="119"/>
+      <c r="M9" s="119"/>
+      <c r="N9" s="119"/>
+      <c r="O9" s="119"/>
+      <c r="P9" s="120"/>
+      <c r="Q9" s="147"/>
+      <c r="R9" s="147"/>
+      <c r="S9" s="147"/>
+      <c r="T9" s="158" t="s">
         <v>25</v>
       </c>
-      <c r="U9" s="155"/>
-      <c r="V9" s="157">
+      <c r="U9" s="158"/>
+      <c r="V9" s="160">
         <v>0</v>
       </c>
-      <c r="W9" s="157"/>
-      <c r="X9" s="143">
+      <c r="W9" s="160"/>
+      <c r="X9" s="146">
         <v>0</v>
       </c>
-      <c r="Y9" s="143"/>
+      <c r="Y9" s="146"/>
       <c r="Z9" s="12"/>
       <c r="AA9" s="13"/>
       <c r="AB9" s="14"/>
@@ -6760,54 +7322,54 @@
       <c r="AL9" s="12"/>
       <c r="AM9" s="13"/>
       <c r="AN9" s="14"/>
-      <c r="AO9" s="153"/>
-      <c r="AP9" s="153"/>
-      <c r="AQ9" s="153"/>
-      <c r="AR9" s="153"/>
-      <c r="AS9" s="153"/>
-      <c r="AT9" s="153"/>
-      <c r="AU9" s="153"/>
-      <c r="AV9" s="153"/>
-      <c r="AW9" s="153"/>
-      <c r="AX9" s="153"/>
-      <c r="AY9" s="153"/>
-      <c r="AZ9" s="154"/>
+      <c r="AO9" s="156"/>
+      <c r="AP9" s="156"/>
+      <c r="AQ9" s="156"/>
+      <c r="AR9" s="156"/>
+      <c r="AS9" s="156"/>
+      <c r="AT9" s="156"/>
+      <c r="AU9" s="156"/>
+      <c r="AV9" s="156"/>
+      <c r="AW9" s="156"/>
+      <c r="AX9" s="156"/>
+      <c r="AY9" s="156"/>
+      <c r="AZ9" s="157"/>
     </row>
     <row r="10" spans="2:52" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B10" s="167">
+      <c r="B10" s="170">
         <v>3</v>
       </c>
-      <c r="C10" s="153" t="s">
-        <v>89</v>
-      </c>
-      <c r="D10" s="153"/>
-      <c r="E10" s="153"/>
-      <c r="F10" s="153"/>
-      <c r="G10" s="153"/>
-      <c r="H10" s="153"/>
-      <c r="I10" s="153"/>
-      <c r="J10" s="153"/>
-      <c r="K10" s="153"/>
-      <c r="L10" s="153"/>
-      <c r="M10" s="153"/>
-      <c r="N10" s="153"/>
-      <c r="O10" s="153"/>
-      <c r="P10" s="153"/>
-      <c r="Q10" s="144"/>
-      <c r="R10" s="144"/>
-      <c r="S10" s="144"/>
-      <c r="T10" s="158" t="s">
-        <v>87</v>
-      </c>
-      <c r="U10" s="158"/>
-      <c r="V10" s="156">
+      <c r="C10" s="156" t="s">
+        <v>53</v>
+      </c>
+      <c r="D10" s="156"/>
+      <c r="E10" s="156"/>
+      <c r="F10" s="156"/>
+      <c r="G10" s="156"/>
+      <c r="H10" s="156"/>
+      <c r="I10" s="156"/>
+      <c r="J10" s="156"/>
+      <c r="K10" s="156"/>
+      <c r="L10" s="156"/>
+      <c r="M10" s="156"/>
+      <c r="N10" s="156"/>
+      <c r="O10" s="156"/>
+      <c r="P10" s="156"/>
+      <c r="Q10" s="147"/>
+      <c r="R10" s="147"/>
+      <c r="S10" s="147"/>
+      <c r="T10" s="161" t="s">
+        <v>51</v>
+      </c>
+      <c r="U10" s="161"/>
+      <c r="V10" s="159">
         <v>0</v>
       </c>
-      <c r="W10" s="156"/>
-      <c r="X10" s="142">
+      <c r="W10" s="159"/>
+      <c r="X10" s="145">
         <v>0</v>
       </c>
-      <c r="Y10" s="142"/>
+      <c r="Y10" s="145"/>
       <c r="Z10" s="9"/>
       <c r="AA10" s="10"/>
       <c r="AB10" s="11"/>
@@ -6823,50 +7385,50 @@
       <c r="AL10" s="9"/>
       <c r="AM10" s="10"/>
       <c r="AN10" s="11"/>
-      <c r="AO10" s="153"/>
-      <c r="AP10" s="153"/>
-      <c r="AQ10" s="153"/>
-      <c r="AR10" s="153"/>
-      <c r="AS10" s="153"/>
-      <c r="AT10" s="153"/>
-      <c r="AU10" s="153"/>
-      <c r="AV10" s="153"/>
-      <c r="AW10" s="153"/>
-      <c r="AX10" s="153"/>
-      <c r="AY10" s="153"/>
-      <c r="AZ10" s="154"/>
+      <c r="AO10" s="156"/>
+      <c r="AP10" s="156"/>
+      <c r="AQ10" s="156"/>
+      <c r="AR10" s="156"/>
+      <c r="AS10" s="156"/>
+      <c r="AT10" s="156"/>
+      <c r="AU10" s="156"/>
+      <c r="AV10" s="156"/>
+      <c r="AW10" s="156"/>
+      <c r="AX10" s="156"/>
+      <c r="AY10" s="156"/>
+      <c r="AZ10" s="157"/>
     </row>
     <row r="11" spans="2:52" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B11" s="167"/>
-      <c r="C11" s="153"/>
-      <c r="D11" s="153"/>
-      <c r="E11" s="153"/>
-      <c r="F11" s="153"/>
-      <c r="G11" s="153"/>
-      <c r="H11" s="153"/>
-      <c r="I11" s="153"/>
-      <c r="J11" s="153"/>
-      <c r="K11" s="153"/>
-      <c r="L11" s="153"/>
-      <c r="M11" s="153"/>
-      <c r="N11" s="153"/>
-      <c r="O11" s="153"/>
-      <c r="P11" s="153"/>
-      <c r="Q11" s="144"/>
-      <c r="R11" s="144"/>
-      <c r="S11" s="144"/>
-      <c r="T11" s="155" t="s">
+      <c r="B11" s="170"/>
+      <c r="C11" s="156"/>
+      <c r="D11" s="156"/>
+      <c r="E11" s="156"/>
+      <c r="F11" s="156"/>
+      <c r="G11" s="156"/>
+      <c r="H11" s="156"/>
+      <c r="I11" s="156"/>
+      <c r="J11" s="156"/>
+      <c r="K11" s="156"/>
+      <c r="L11" s="156"/>
+      <c r="M11" s="156"/>
+      <c r="N11" s="156"/>
+      <c r="O11" s="156"/>
+      <c r="P11" s="156"/>
+      <c r="Q11" s="147"/>
+      <c r="R11" s="147"/>
+      <c r="S11" s="147"/>
+      <c r="T11" s="158" t="s">
         <v>25</v>
       </c>
-      <c r="U11" s="155"/>
-      <c r="V11" s="157">
+      <c r="U11" s="158"/>
+      <c r="V11" s="160">
         <v>0</v>
       </c>
-      <c r="W11" s="157"/>
-      <c r="X11" s="143">
+      <c r="W11" s="160"/>
+      <c r="X11" s="146">
         <v>0</v>
       </c>
-      <c r="Y11" s="143"/>
+      <c r="Y11" s="146"/>
       <c r="Z11" s="12"/>
       <c r="AA11" s="13"/>
       <c r="AB11" s="14"/>
@@ -6882,54 +7444,54 @@
       <c r="AL11" s="12"/>
       <c r="AM11" s="13"/>
       <c r="AN11" s="14"/>
-      <c r="AO11" s="153"/>
-      <c r="AP11" s="153"/>
-      <c r="AQ11" s="153"/>
-      <c r="AR11" s="153"/>
-      <c r="AS11" s="153"/>
-      <c r="AT11" s="153"/>
-      <c r="AU11" s="153"/>
-      <c r="AV11" s="153"/>
-      <c r="AW11" s="153"/>
-      <c r="AX11" s="153"/>
-      <c r="AY11" s="153"/>
-      <c r="AZ11" s="154"/>
+      <c r="AO11" s="156"/>
+      <c r="AP11" s="156"/>
+      <c r="AQ11" s="156"/>
+      <c r="AR11" s="156"/>
+      <c r="AS11" s="156"/>
+      <c r="AT11" s="156"/>
+      <c r="AU11" s="156"/>
+      <c r="AV11" s="156"/>
+      <c r="AW11" s="156"/>
+      <c r="AX11" s="156"/>
+      <c r="AY11" s="156"/>
+      <c r="AZ11" s="157"/>
     </row>
     <row r="12" spans="2:52" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B12" s="167">
+      <c r="B12" s="170">
         <v>4</v>
       </c>
-      <c r="C12" s="153" t="s">
-        <v>90</v>
-      </c>
-      <c r="D12" s="153"/>
-      <c r="E12" s="153"/>
-      <c r="F12" s="153"/>
-      <c r="G12" s="153"/>
-      <c r="H12" s="153"/>
-      <c r="I12" s="153"/>
-      <c r="J12" s="153"/>
-      <c r="K12" s="153"/>
-      <c r="L12" s="153"/>
-      <c r="M12" s="153"/>
-      <c r="N12" s="153"/>
-      <c r="O12" s="153"/>
-      <c r="P12" s="153"/>
-      <c r="Q12" s="118"/>
-      <c r="R12" s="119"/>
-      <c r="S12" s="120"/>
-      <c r="T12" s="158" t="s">
-        <v>87</v>
-      </c>
-      <c r="U12" s="158"/>
-      <c r="V12" s="156">
+      <c r="C12" s="156" t="s">
+        <v>54</v>
+      </c>
+      <c r="D12" s="156"/>
+      <c r="E12" s="156"/>
+      <c r="F12" s="156"/>
+      <c r="G12" s="156"/>
+      <c r="H12" s="156"/>
+      <c r="I12" s="156"/>
+      <c r="J12" s="156"/>
+      <c r="K12" s="156"/>
+      <c r="L12" s="156"/>
+      <c r="M12" s="156"/>
+      <c r="N12" s="156"/>
+      <c r="O12" s="156"/>
+      <c r="P12" s="156"/>
+      <c r="Q12" s="121"/>
+      <c r="R12" s="122"/>
+      <c r="S12" s="123"/>
+      <c r="T12" s="161" t="s">
+        <v>51</v>
+      </c>
+      <c r="U12" s="161"/>
+      <c r="V12" s="159">
         <v>0</v>
       </c>
-      <c r="W12" s="156"/>
-      <c r="X12" s="142">
+      <c r="W12" s="159"/>
+      <c r="X12" s="145">
         <v>0</v>
       </c>
-      <c r="Y12" s="142"/>
+      <c r="Y12" s="145"/>
       <c r="Z12" s="9"/>
       <c r="AA12" s="10"/>
       <c r="AB12" s="11"/>
@@ -6945,50 +7507,50 @@
       <c r="AL12" s="9"/>
       <c r="AM12" s="10"/>
       <c r="AN12" s="11"/>
-      <c r="AO12" s="153"/>
-      <c r="AP12" s="153"/>
-      <c r="AQ12" s="153"/>
-      <c r="AR12" s="153"/>
-      <c r="AS12" s="153"/>
-      <c r="AT12" s="153"/>
-      <c r="AU12" s="153"/>
-      <c r="AV12" s="153"/>
-      <c r="AW12" s="153"/>
-      <c r="AX12" s="153"/>
-      <c r="AY12" s="153"/>
-      <c r="AZ12" s="154"/>
+      <c r="AO12" s="156"/>
+      <c r="AP12" s="156"/>
+      <c r="AQ12" s="156"/>
+      <c r="AR12" s="156"/>
+      <c r="AS12" s="156"/>
+      <c r="AT12" s="156"/>
+      <c r="AU12" s="156"/>
+      <c r="AV12" s="156"/>
+      <c r="AW12" s="156"/>
+      <c r="AX12" s="156"/>
+      <c r="AY12" s="156"/>
+      <c r="AZ12" s="157"/>
     </row>
     <row r="13" spans="2:52" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B13" s="167"/>
-      <c r="C13" s="153"/>
-      <c r="D13" s="153"/>
-      <c r="E13" s="153"/>
-      <c r="F13" s="153"/>
-      <c r="G13" s="153"/>
-      <c r="H13" s="153"/>
-      <c r="I13" s="153"/>
-      <c r="J13" s="153"/>
-      <c r="K13" s="153"/>
-      <c r="L13" s="153"/>
-      <c r="M13" s="153"/>
-      <c r="N13" s="153"/>
-      <c r="O13" s="153"/>
-      <c r="P13" s="153"/>
-      <c r="Q13" s="121"/>
-      <c r="R13" s="122"/>
-      <c r="S13" s="123"/>
-      <c r="T13" s="155" t="s">
+      <c r="B13" s="170"/>
+      <c r="C13" s="156"/>
+      <c r="D13" s="156"/>
+      <c r="E13" s="156"/>
+      <c r="F13" s="156"/>
+      <c r="G13" s="156"/>
+      <c r="H13" s="156"/>
+      <c r="I13" s="156"/>
+      <c r="J13" s="156"/>
+      <c r="K13" s="156"/>
+      <c r="L13" s="156"/>
+      <c r="M13" s="156"/>
+      <c r="N13" s="156"/>
+      <c r="O13" s="156"/>
+      <c r="P13" s="156"/>
+      <c r="Q13" s="124"/>
+      <c r="R13" s="125"/>
+      <c r="S13" s="126"/>
+      <c r="T13" s="158" t="s">
         <v>25</v>
       </c>
-      <c r="U13" s="155"/>
-      <c r="V13" s="157">
+      <c r="U13" s="158"/>
+      <c r="V13" s="160">
         <v>0</v>
       </c>
-      <c r="W13" s="157"/>
-      <c r="X13" s="143">
+      <c r="W13" s="160"/>
+      <c r="X13" s="146">
         <v>0</v>
       </c>
-      <c r="Y13" s="143"/>
+      <c r="Y13" s="146"/>
       <c r="Z13" s="12"/>
       <c r="AA13" s="13"/>
       <c r="AB13" s="14"/>
@@ -7004,54 +7566,54 @@
       <c r="AL13" s="12"/>
       <c r="AM13" s="13"/>
       <c r="AN13" s="14"/>
-      <c r="AO13" s="153"/>
-      <c r="AP13" s="153"/>
-      <c r="AQ13" s="153"/>
-      <c r="AR13" s="153"/>
-      <c r="AS13" s="153"/>
-      <c r="AT13" s="153"/>
-      <c r="AU13" s="153"/>
-      <c r="AV13" s="153"/>
-      <c r="AW13" s="153"/>
-      <c r="AX13" s="153"/>
-      <c r="AY13" s="153"/>
-      <c r="AZ13" s="154"/>
+      <c r="AO13" s="156"/>
+      <c r="AP13" s="156"/>
+      <c r="AQ13" s="156"/>
+      <c r="AR13" s="156"/>
+      <c r="AS13" s="156"/>
+      <c r="AT13" s="156"/>
+      <c r="AU13" s="156"/>
+      <c r="AV13" s="156"/>
+      <c r="AW13" s="156"/>
+      <c r="AX13" s="156"/>
+      <c r="AY13" s="156"/>
+      <c r="AZ13" s="157"/>
     </row>
     <row r="14" spans="2:52" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B14" s="167">
+      <c r="B14" s="170">
         <v>5</v>
       </c>
-      <c r="C14" s="112" t="s">
-        <v>91</v>
-      </c>
-      <c r="D14" s="113"/>
-      <c r="E14" s="113"/>
-      <c r="F14" s="113"/>
-      <c r="G14" s="113"/>
-      <c r="H14" s="113"/>
-      <c r="I14" s="114"/>
-      <c r="J14" s="193"/>
-      <c r="K14" s="153"/>
-      <c r="L14" s="153"/>
-      <c r="M14" s="153"/>
-      <c r="N14" s="153"/>
-      <c r="O14" s="153"/>
-      <c r="P14" s="153"/>
-      <c r="Q14" s="118"/>
-      <c r="R14" s="119"/>
-      <c r="S14" s="120"/>
-      <c r="T14" s="158" t="s">
-        <v>87</v>
-      </c>
-      <c r="U14" s="158"/>
-      <c r="V14" s="156">
+      <c r="C14" s="115" t="s">
+        <v>55</v>
+      </c>
+      <c r="D14" s="116"/>
+      <c r="E14" s="116"/>
+      <c r="F14" s="116"/>
+      <c r="G14" s="116"/>
+      <c r="H14" s="116"/>
+      <c r="I14" s="117"/>
+      <c r="J14" s="196"/>
+      <c r="K14" s="156"/>
+      <c r="L14" s="156"/>
+      <c r="M14" s="156"/>
+      <c r="N14" s="156"/>
+      <c r="O14" s="156"/>
+      <c r="P14" s="156"/>
+      <c r="Q14" s="121"/>
+      <c r="R14" s="122"/>
+      <c r="S14" s="123"/>
+      <c r="T14" s="161" t="s">
+        <v>51</v>
+      </c>
+      <c r="U14" s="161"/>
+      <c r="V14" s="159">
         <v>0</v>
       </c>
-      <c r="W14" s="156"/>
-      <c r="X14" s="142">
+      <c r="W14" s="159"/>
+      <c r="X14" s="145">
         <v>0</v>
       </c>
-      <c r="Y14" s="142"/>
+      <c r="Y14" s="145"/>
       <c r="Z14" s="9"/>
       <c r="AA14" s="10"/>
       <c r="AB14" s="11"/>
@@ -7067,50 +7629,50 @@
       <c r="AL14" s="9"/>
       <c r="AM14" s="10"/>
       <c r="AN14" s="11"/>
-      <c r="AO14" s="153"/>
-      <c r="AP14" s="153"/>
-      <c r="AQ14" s="153"/>
-      <c r="AR14" s="153"/>
-      <c r="AS14" s="153"/>
-      <c r="AT14" s="153"/>
-      <c r="AU14" s="153"/>
-      <c r="AV14" s="153"/>
-      <c r="AW14" s="153"/>
-      <c r="AX14" s="153"/>
-      <c r="AY14" s="153"/>
-      <c r="AZ14" s="154"/>
+      <c r="AO14" s="156"/>
+      <c r="AP14" s="156"/>
+      <c r="AQ14" s="156"/>
+      <c r="AR14" s="156"/>
+      <c r="AS14" s="156"/>
+      <c r="AT14" s="156"/>
+      <c r="AU14" s="156"/>
+      <c r="AV14" s="156"/>
+      <c r="AW14" s="156"/>
+      <c r="AX14" s="156"/>
+      <c r="AY14" s="156"/>
+      <c r="AZ14" s="157"/>
     </row>
     <row r="15" spans="2:52" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B15" s="167"/>
-      <c r="C15" s="115"/>
-      <c r="D15" s="116"/>
-      <c r="E15" s="116"/>
-      <c r="F15" s="116"/>
-      <c r="G15" s="116"/>
-      <c r="H15" s="116"/>
-      <c r="I15" s="117"/>
-      <c r="J15" s="153"/>
-      <c r="K15" s="153"/>
-      <c r="L15" s="153"/>
-      <c r="M15" s="153"/>
-      <c r="N15" s="153"/>
-      <c r="O15" s="153"/>
-      <c r="P15" s="153"/>
-      <c r="Q15" s="121"/>
-      <c r="R15" s="122"/>
-      <c r="S15" s="123"/>
-      <c r="T15" s="155" t="s">
+      <c r="B15" s="170"/>
+      <c r="C15" s="118"/>
+      <c r="D15" s="119"/>
+      <c r="E15" s="119"/>
+      <c r="F15" s="119"/>
+      <c r="G15" s="119"/>
+      <c r="H15" s="119"/>
+      <c r="I15" s="120"/>
+      <c r="J15" s="156"/>
+      <c r="K15" s="156"/>
+      <c r="L15" s="156"/>
+      <c r="M15" s="156"/>
+      <c r="N15" s="156"/>
+      <c r="O15" s="156"/>
+      <c r="P15" s="156"/>
+      <c r="Q15" s="124"/>
+      <c r="R15" s="125"/>
+      <c r="S15" s="126"/>
+      <c r="T15" s="158" t="s">
         <v>25</v>
       </c>
-      <c r="U15" s="155"/>
-      <c r="V15" s="157">
+      <c r="U15" s="158"/>
+      <c r="V15" s="160">
         <v>0</v>
       </c>
-      <c r="W15" s="157"/>
-      <c r="X15" s="143">
+      <c r="W15" s="160"/>
+      <c r="X15" s="146">
         <v>0</v>
       </c>
-      <c r="Y15" s="143"/>
+      <c r="Y15" s="146"/>
       <c r="Z15" s="12"/>
       <c r="AA15" s="13"/>
       <c r="AB15" s="14"/>
@@ -7126,54 +7688,54 @@
       <c r="AL15" s="12"/>
       <c r="AM15" s="13"/>
       <c r="AN15" s="14"/>
-      <c r="AO15" s="153"/>
-      <c r="AP15" s="153"/>
-      <c r="AQ15" s="153"/>
-      <c r="AR15" s="153"/>
-      <c r="AS15" s="153"/>
-      <c r="AT15" s="153"/>
-      <c r="AU15" s="153"/>
-      <c r="AV15" s="153"/>
-      <c r="AW15" s="153"/>
-      <c r="AX15" s="153"/>
-      <c r="AY15" s="153"/>
-      <c r="AZ15" s="154"/>
+      <c r="AO15" s="156"/>
+      <c r="AP15" s="156"/>
+      <c r="AQ15" s="156"/>
+      <c r="AR15" s="156"/>
+      <c r="AS15" s="156"/>
+      <c r="AT15" s="156"/>
+      <c r="AU15" s="156"/>
+      <c r="AV15" s="156"/>
+      <c r="AW15" s="156"/>
+      <c r="AX15" s="156"/>
+      <c r="AY15" s="156"/>
+      <c r="AZ15" s="157"/>
     </row>
     <row r="16" spans="2:52" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B16" s="167">
+      <c r="B16" s="170">
         <v>6</v>
       </c>
-      <c r="C16" s="112" t="s">
-        <v>92</v>
-      </c>
-      <c r="D16" s="113"/>
-      <c r="E16" s="113"/>
-      <c r="F16" s="113"/>
-      <c r="G16" s="113"/>
-      <c r="H16" s="113"/>
-      <c r="I16" s="114"/>
-      <c r="J16" s="193"/>
-      <c r="K16" s="153"/>
-      <c r="L16" s="153"/>
-      <c r="M16" s="153"/>
-      <c r="N16" s="153"/>
-      <c r="O16" s="153"/>
-      <c r="P16" s="153"/>
-      <c r="Q16" s="144"/>
-      <c r="R16" s="144"/>
-      <c r="S16" s="144"/>
-      <c r="T16" s="158" t="s">
-        <v>87</v>
-      </c>
-      <c r="U16" s="158"/>
-      <c r="V16" s="156">
+      <c r="C16" s="115" t="s">
+        <v>56</v>
+      </c>
+      <c r="D16" s="116"/>
+      <c r="E16" s="116"/>
+      <c r="F16" s="116"/>
+      <c r="G16" s="116"/>
+      <c r="H16" s="116"/>
+      <c r="I16" s="117"/>
+      <c r="J16" s="196"/>
+      <c r="K16" s="156"/>
+      <c r="L16" s="156"/>
+      <c r="M16" s="156"/>
+      <c r="N16" s="156"/>
+      <c r="O16" s="156"/>
+      <c r="P16" s="156"/>
+      <c r="Q16" s="147"/>
+      <c r="R16" s="147"/>
+      <c r="S16" s="147"/>
+      <c r="T16" s="161" t="s">
+        <v>51</v>
+      </c>
+      <c r="U16" s="161"/>
+      <c r="V16" s="159">
         <v>0</v>
       </c>
-      <c r="W16" s="156"/>
-      <c r="X16" s="142">
+      <c r="W16" s="159"/>
+      <c r="X16" s="145">
         <v>0</v>
       </c>
-      <c r="Y16" s="142"/>
+      <c r="Y16" s="145"/>
       <c r="Z16" s="9"/>
       <c r="AA16" s="10"/>
       <c r="AB16" s="11"/>
@@ -7189,50 +7751,50 @@
       <c r="AL16" s="9"/>
       <c r="AM16" s="10"/>
       <c r="AN16" s="11"/>
-      <c r="AO16" s="153"/>
-      <c r="AP16" s="153"/>
-      <c r="AQ16" s="153"/>
-      <c r="AR16" s="153"/>
-      <c r="AS16" s="153"/>
-      <c r="AT16" s="153"/>
-      <c r="AU16" s="153"/>
-      <c r="AV16" s="153"/>
-      <c r="AW16" s="153"/>
-      <c r="AX16" s="153"/>
-      <c r="AY16" s="153"/>
-      <c r="AZ16" s="154"/>
+      <c r="AO16" s="156"/>
+      <c r="AP16" s="156"/>
+      <c r="AQ16" s="156"/>
+      <c r="AR16" s="156"/>
+      <c r="AS16" s="156"/>
+      <c r="AT16" s="156"/>
+      <c r="AU16" s="156"/>
+      <c r="AV16" s="156"/>
+      <c r="AW16" s="156"/>
+      <c r="AX16" s="156"/>
+      <c r="AY16" s="156"/>
+      <c r="AZ16" s="157"/>
     </row>
     <row r="17" spans="2:52" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B17" s="167"/>
-      <c r="C17" s="115"/>
-      <c r="D17" s="116"/>
-      <c r="E17" s="116"/>
-      <c r="F17" s="116"/>
-      <c r="G17" s="116"/>
-      <c r="H17" s="116"/>
-      <c r="I17" s="117"/>
-      <c r="J17" s="153"/>
-      <c r="K17" s="153"/>
-      <c r="L17" s="153"/>
-      <c r="M17" s="153"/>
-      <c r="N17" s="153"/>
-      <c r="O17" s="153"/>
-      <c r="P17" s="153"/>
-      <c r="Q17" s="144"/>
-      <c r="R17" s="144"/>
-      <c r="S17" s="144"/>
-      <c r="T17" s="155" t="s">
+      <c r="B17" s="170"/>
+      <c r="C17" s="118"/>
+      <c r="D17" s="119"/>
+      <c r="E17" s="119"/>
+      <c r="F17" s="119"/>
+      <c r="G17" s="119"/>
+      <c r="H17" s="119"/>
+      <c r="I17" s="120"/>
+      <c r="J17" s="156"/>
+      <c r="K17" s="156"/>
+      <c r="L17" s="156"/>
+      <c r="M17" s="156"/>
+      <c r="N17" s="156"/>
+      <c r="O17" s="156"/>
+      <c r="P17" s="156"/>
+      <c r="Q17" s="147"/>
+      <c r="R17" s="147"/>
+      <c r="S17" s="147"/>
+      <c r="T17" s="158" t="s">
         <v>25</v>
       </c>
-      <c r="U17" s="155"/>
-      <c r="V17" s="157">
+      <c r="U17" s="158"/>
+      <c r="V17" s="160">
         <v>0</v>
       </c>
-      <c r="W17" s="157"/>
-      <c r="X17" s="143">
+      <c r="W17" s="160"/>
+      <c r="X17" s="146">
         <v>0</v>
       </c>
-      <c r="Y17" s="143"/>
+      <c r="Y17" s="146"/>
       <c r="Z17" s="12"/>
       <c r="AA17" s="13"/>
       <c r="AB17" s="14"/>
@@ -7248,54 +7810,54 @@
       <c r="AL17" s="12"/>
       <c r="AM17" s="13"/>
       <c r="AN17" s="14"/>
-      <c r="AO17" s="153"/>
-      <c r="AP17" s="153"/>
-      <c r="AQ17" s="153"/>
-      <c r="AR17" s="153"/>
-      <c r="AS17" s="153"/>
-      <c r="AT17" s="153"/>
-      <c r="AU17" s="153"/>
-      <c r="AV17" s="153"/>
-      <c r="AW17" s="153"/>
-      <c r="AX17" s="153"/>
-      <c r="AY17" s="153"/>
-      <c r="AZ17" s="154"/>
+      <c r="AO17" s="156"/>
+      <c r="AP17" s="156"/>
+      <c r="AQ17" s="156"/>
+      <c r="AR17" s="156"/>
+      <c r="AS17" s="156"/>
+      <c r="AT17" s="156"/>
+      <c r="AU17" s="156"/>
+      <c r="AV17" s="156"/>
+      <c r="AW17" s="156"/>
+      <c r="AX17" s="156"/>
+      <c r="AY17" s="156"/>
+      <c r="AZ17" s="157"/>
     </row>
     <row r="18" spans="2:52" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B18" s="104">
+      <c r="B18" s="107">
         <v>7</v>
       </c>
-      <c r="C18" s="106" t="s">
-        <v>93</v>
-      </c>
-      <c r="D18" s="107"/>
-      <c r="E18" s="107"/>
-      <c r="F18" s="107"/>
-      <c r="G18" s="107"/>
-      <c r="H18" s="107"/>
-      <c r="I18" s="108"/>
-      <c r="J18" s="112"/>
-      <c r="K18" s="113"/>
-      <c r="L18" s="113"/>
-      <c r="M18" s="113"/>
-      <c r="N18" s="113"/>
-      <c r="O18" s="113"/>
-      <c r="P18" s="114"/>
-      <c r="Q18" s="118"/>
-      <c r="R18" s="119"/>
-      <c r="S18" s="120"/>
-      <c r="T18" s="124" t="s">
-        <v>87</v>
-      </c>
-      <c r="U18" s="125"/>
-      <c r="V18" s="126">
+      <c r="C18" s="109" t="s">
+        <v>57</v>
+      </c>
+      <c r="D18" s="110"/>
+      <c r="E18" s="110"/>
+      <c r="F18" s="110"/>
+      <c r="G18" s="110"/>
+      <c r="H18" s="110"/>
+      <c r="I18" s="111"/>
+      <c r="J18" s="115"/>
+      <c r="K18" s="116"/>
+      <c r="L18" s="116"/>
+      <c r="M18" s="116"/>
+      <c r="N18" s="116"/>
+      <c r="O18" s="116"/>
+      <c r="P18" s="117"/>
+      <c r="Q18" s="121"/>
+      <c r="R18" s="122"/>
+      <c r="S18" s="123"/>
+      <c r="T18" s="127" t="s">
+        <v>51</v>
+      </c>
+      <c r="U18" s="128"/>
+      <c r="V18" s="129">
         <v>0</v>
       </c>
-      <c r="W18" s="127"/>
-      <c r="X18" s="128">
+      <c r="W18" s="130"/>
+      <c r="X18" s="131">
         <v>0</v>
       </c>
-      <c r="Y18" s="129"/>
+      <c r="Y18" s="132"/>
       <c r="Z18" s="9"/>
       <c r="AA18" s="10"/>
       <c r="AB18" s="11"/>
@@ -7311,50 +7873,50 @@
       <c r="AL18" s="9"/>
       <c r="AM18" s="10"/>
       <c r="AN18" s="11"/>
-      <c r="AO18" s="112"/>
-      <c r="AP18" s="113"/>
-      <c r="AQ18" s="113"/>
-      <c r="AR18" s="113"/>
-      <c r="AS18" s="113"/>
-      <c r="AT18" s="113"/>
-      <c r="AU18" s="113"/>
-      <c r="AV18" s="113"/>
-      <c r="AW18" s="113"/>
-      <c r="AX18" s="113"/>
-      <c r="AY18" s="113"/>
-      <c r="AZ18" s="130"/>
+      <c r="AO18" s="115"/>
+      <c r="AP18" s="116"/>
+      <c r="AQ18" s="116"/>
+      <c r="AR18" s="116"/>
+      <c r="AS18" s="116"/>
+      <c r="AT18" s="116"/>
+      <c r="AU18" s="116"/>
+      <c r="AV18" s="116"/>
+      <c r="AW18" s="116"/>
+      <c r="AX18" s="116"/>
+      <c r="AY18" s="116"/>
+      <c r="AZ18" s="133"/>
     </row>
     <row r="19" spans="2:52" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B19" s="105"/>
-      <c r="C19" s="109"/>
-      <c r="D19" s="110"/>
-      <c r="E19" s="110"/>
-      <c r="F19" s="110"/>
-      <c r="G19" s="110"/>
-      <c r="H19" s="110"/>
-      <c r="I19" s="111"/>
-      <c r="J19" s="115"/>
-      <c r="K19" s="116"/>
-      <c r="L19" s="116"/>
-      <c r="M19" s="116"/>
-      <c r="N19" s="116"/>
-      <c r="O19" s="116"/>
-      <c r="P19" s="117"/>
-      <c r="Q19" s="121"/>
-      <c r="R19" s="122"/>
-      <c r="S19" s="123"/>
-      <c r="T19" s="132" t="s">
+      <c r="B19" s="108"/>
+      <c r="C19" s="112"/>
+      <c r="D19" s="113"/>
+      <c r="E19" s="113"/>
+      <c r="F19" s="113"/>
+      <c r="G19" s="113"/>
+      <c r="H19" s="113"/>
+      <c r="I19" s="114"/>
+      <c r="J19" s="118"/>
+      <c r="K19" s="119"/>
+      <c r="L19" s="119"/>
+      <c r="M19" s="119"/>
+      <c r="N19" s="119"/>
+      <c r="O19" s="119"/>
+      <c r="P19" s="120"/>
+      <c r="Q19" s="124"/>
+      <c r="R19" s="125"/>
+      <c r="S19" s="126"/>
+      <c r="T19" s="135" t="s">
         <v>25</v>
       </c>
-      <c r="U19" s="133"/>
-      <c r="V19" s="134">
+      <c r="U19" s="136"/>
+      <c r="V19" s="137">
         <v>0</v>
       </c>
-      <c r="W19" s="135"/>
-      <c r="X19" s="136">
+      <c r="W19" s="138"/>
+      <c r="X19" s="139">
         <v>0</v>
       </c>
-      <c r="Y19" s="137"/>
+      <c r="Y19" s="140"/>
       <c r="Z19" s="12"/>
       <c r="AA19" s="13"/>
       <c r="AB19" s="14"/>
@@ -7370,54 +7932,54 @@
       <c r="AL19" s="12"/>
       <c r="AM19" s="13"/>
       <c r="AN19" s="14"/>
-      <c r="AO19" s="115"/>
-      <c r="AP19" s="116"/>
-      <c r="AQ19" s="116"/>
-      <c r="AR19" s="116"/>
-      <c r="AS19" s="116"/>
-      <c r="AT19" s="116"/>
-      <c r="AU19" s="116"/>
-      <c r="AV19" s="116"/>
-      <c r="AW19" s="116"/>
-      <c r="AX19" s="116"/>
-      <c r="AY19" s="116"/>
-      <c r="AZ19" s="131"/>
+      <c r="AO19" s="118"/>
+      <c r="AP19" s="119"/>
+      <c r="AQ19" s="119"/>
+      <c r="AR19" s="119"/>
+      <c r="AS19" s="119"/>
+      <c r="AT19" s="119"/>
+      <c r="AU19" s="119"/>
+      <c r="AV19" s="119"/>
+      <c r="AW19" s="119"/>
+      <c r="AX19" s="119"/>
+      <c r="AY19" s="119"/>
+      <c r="AZ19" s="134"/>
     </row>
     <row r="20" spans="2:52" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B20" s="104">
+      <c r="B20" s="107">
         <v>8</v>
       </c>
-      <c r="C20" s="106" t="s">
-        <v>94</v>
-      </c>
-      <c r="D20" s="107"/>
-      <c r="E20" s="107"/>
-      <c r="F20" s="107"/>
-      <c r="G20" s="107"/>
-      <c r="H20" s="107"/>
-      <c r="I20" s="108"/>
-      <c r="J20" s="112"/>
-      <c r="K20" s="113"/>
-      <c r="L20" s="113"/>
-      <c r="M20" s="113"/>
-      <c r="N20" s="113"/>
-      <c r="O20" s="113"/>
-      <c r="P20" s="114"/>
-      <c r="Q20" s="118"/>
-      <c r="R20" s="119"/>
-      <c r="S20" s="120"/>
-      <c r="T20" s="124" t="s">
-        <v>87</v>
-      </c>
-      <c r="U20" s="125"/>
-      <c r="V20" s="126">
+      <c r="C20" s="109" t="s">
+        <v>58</v>
+      </c>
+      <c r="D20" s="110"/>
+      <c r="E20" s="110"/>
+      <c r="F20" s="110"/>
+      <c r="G20" s="110"/>
+      <c r="H20" s="110"/>
+      <c r="I20" s="111"/>
+      <c r="J20" s="115"/>
+      <c r="K20" s="116"/>
+      <c r="L20" s="116"/>
+      <c r="M20" s="116"/>
+      <c r="N20" s="116"/>
+      <c r="O20" s="116"/>
+      <c r="P20" s="117"/>
+      <c r="Q20" s="121"/>
+      <c r="R20" s="122"/>
+      <c r="S20" s="123"/>
+      <c r="T20" s="127" t="s">
+        <v>51</v>
+      </c>
+      <c r="U20" s="128"/>
+      <c r="V20" s="129">
         <v>0</v>
       </c>
-      <c r="W20" s="127"/>
-      <c r="X20" s="128">
+      <c r="W20" s="130"/>
+      <c r="X20" s="131">
         <v>0</v>
       </c>
-      <c r="Y20" s="129"/>
+      <c r="Y20" s="132"/>
       <c r="Z20" s="9"/>
       <c r="AA20" s="10"/>
       <c r="AB20" s="11"/>
@@ -7433,50 +7995,50 @@
       <c r="AL20" s="9"/>
       <c r="AM20" s="10"/>
       <c r="AN20" s="11"/>
-      <c r="AO20" s="112"/>
-      <c r="AP20" s="113"/>
-      <c r="AQ20" s="113"/>
-      <c r="AR20" s="113"/>
-      <c r="AS20" s="113"/>
-      <c r="AT20" s="113"/>
-      <c r="AU20" s="113"/>
-      <c r="AV20" s="113"/>
-      <c r="AW20" s="113"/>
-      <c r="AX20" s="113"/>
-      <c r="AY20" s="113"/>
-      <c r="AZ20" s="130"/>
+      <c r="AO20" s="115"/>
+      <c r="AP20" s="116"/>
+      <c r="AQ20" s="116"/>
+      <c r="AR20" s="116"/>
+      <c r="AS20" s="116"/>
+      <c r="AT20" s="116"/>
+      <c r="AU20" s="116"/>
+      <c r="AV20" s="116"/>
+      <c r="AW20" s="116"/>
+      <c r="AX20" s="116"/>
+      <c r="AY20" s="116"/>
+      <c r="AZ20" s="133"/>
     </row>
     <row r="21" spans="2:52" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B21" s="105"/>
-      <c r="C21" s="109"/>
-      <c r="D21" s="110"/>
-      <c r="E21" s="110"/>
-      <c r="F21" s="110"/>
-      <c r="G21" s="110"/>
-      <c r="H21" s="110"/>
-      <c r="I21" s="111"/>
-      <c r="J21" s="115"/>
-      <c r="K21" s="116"/>
-      <c r="L21" s="116"/>
-      <c r="M21" s="116"/>
-      <c r="N21" s="116"/>
-      <c r="O21" s="116"/>
-      <c r="P21" s="117"/>
-      <c r="Q21" s="121"/>
-      <c r="R21" s="122"/>
-      <c r="S21" s="123"/>
-      <c r="T21" s="132" t="s">
+      <c r="B21" s="108"/>
+      <c r="C21" s="112"/>
+      <c r="D21" s="113"/>
+      <c r="E21" s="113"/>
+      <c r="F21" s="113"/>
+      <c r="G21" s="113"/>
+      <c r="H21" s="113"/>
+      <c r="I21" s="114"/>
+      <c r="J21" s="118"/>
+      <c r="K21" s="119"/>
+      <c r="L21" s="119"/>
+      <c r="M21" s="119"/>
+      <c r="N21" s="119"/>
+      <c r="O21" s="119"/>
+      <c r="P21" s="120"/>
+      <c r="Q21" s="124"/>
+      <c r="R21" s="125"/>
+      <c r="S21" s="126"/>
+      <c r="T21" s="135" t="s">
         <v>25</v>
       </c>
-      <c r="U21" s="133"/>
-      <c r="V21" s="134">
+      <c r="U21" s="136"/>
+      <c r="V21" s="137">
         <v>0</v>
       </c>
-      <c r="W21" s="135"/>
-      <c r="X21" s="136">
+      <c r="W21" s="138"/>
+      <c r="X21" s="139">
         <v>0</v>
       </c>
-      <c r="Y21" s="137"/>
+      <c r="Y21" s="140"/>
       <c r="Z21" s="12"/>
       <c r="AA21" s="13"/>
       <c r="AB21" s="14"/>
@@ -7492,54 +8054,54 @@
       <c r="AL21" s="12"/>
       <c r="AM21" s="13"/>
       <c r="AN21" s="14"/>
-      <c r="AO21" s="115"/>
-      <c r="AP21" s="116"/>
-      <c r="AQ21" s="116"/>
-      <c r="AR21" s="116"/>
-      <c r="AS21" s="116"/>
-      <c r="AT21" s="116"/>
-      <c r="AU21" s="116"/>
-      <c r="AV21" s="116"/>
-      <c r="AW21" s="116"/>
-      <c r="AX21" s="116"/>
-      <c r="AY21" s="116"/>
-      <c r="AZ21" s="131"/>
+      <c r="AO21" s="118"/>
+      <c r="AP21" s="119"/>
+      <c r="AQ21" s="119"/>
+      <c r="AR21" s="119"/>
+      <c r="AS21" s="119"/>
+      <c r="AT21" s="119"/>
+      <c r="AU21" s="119"/>
+      <c r="AV21" s="119"/>
+      <c r="AW21" s="119"/>
+      <c r="AX21" s="119"/>
+      <c r="AY21" s="119"/>
+      <c r="AZ21" s="134"/>
     </row>
     <row r="22" spans="2:52" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B22" s="174">
+      <c r="B22" s="177">
         <v>9</v>
       </c>
-      <c r="C22" s="176" t="s">
-        <v>95</v>
-      </c>
-      <c r="D22" s="177"/>
-      <c r="E22" s="177"/>
-      <c r="F22" s="177"/>
-      <c r="G22" s="177"/>
-      <c r="H22" s="177"/>
-      <c r="I22" s="178"/>
-      <c r="J22" s="161"/>
-      <c r="K22" s="162"/>
-      <c r="L22" s="162"/>
-      <c r="M22" s="162"/>
-      <c r="N22" s="162"/>
-      <c r="O22" s="162"/>
-      <c r="P22" s="163"/>
-      <c r="Q22" s="183"/>
-      <c r="R22" s="184"/>
-      <c r="S22" s="185"/>
-      <c r="T22" s="179" t="s">
-        <v>87</v>
-      </c>
-      <c r="U22" s="180"/>
-      <c r="V22" s="159">
+      <c r="C22" s="179" t="s">
+        <v>59</v>
+      </c>
+      <c r="D22" s="180"/>
+      <c r="E22" s="180"/>
+      <c r="F22" s="180"/>
+      <c r="G22" s="180"/>
+      <c r="H22" s="180"/>
+      <c r="I22" s="181"/>
+      <c r="J22" s="164"/>
+      <c r="K22" s="165"/>
+      <c r="L22" s="165"/>
+      <c r="M22" s="165"/>
+      <c r="N22" s="165"/>
+      <c r="O22" s="165"/>
+      <c r="P22" s="166"/>
+      <c r="Q22" s="186"/>
+      <c r="R22" s="187"/>
+      <c r="S22" s="188"/>
+      <c r="T22" s="182" t="s">
+        <v>51</v>
+      </c>
+      <c r="U22" s="183"/>
+      <c r="V22" s="162">
         <v>0</v>
       </c>
-      <c r="W22" s="160"/>
-      <c r="X22" s="172">
+      <c r="W22" s="163"/>
+      <c r="X22" s="175">
         <v>0</v>
       </c>
-      <c r="Y22" s="173"/>
+      <c r="Y22" s="176"/>
       <c r="Z22" s="24"/>
       <c r="AA22" s="25"/>
       <c r="AB22" s="26"/>
@@ -7555,50 +8117,50 @@
       <c r="AL22" s="24"/>
       <c r="AM22" s="25"/>
       <c r="AN22" s="26"/>
-      <c r="AO22" s="161"/>
-      <c r="AP22" s="162"/>
-      <c r="AQ22" s="162"/>
-      <c r="AR22" s="162"/>
-      <c r="AS22" s="162"/>
-      <c r="AT22" s="162"/>
-      <c r="AU22" s="162"/>
-      <c r="AV22" s="162"/>
-      <c r="AW22" s="162"/>
-      <c r="AX22" s="162"/>
-      <c r="AY22" s="162"/>
-      <c r="AZ22" s="170"/>
+      <c r="AO22" s="164"/>
+      <c r="AP22" s="165"/>
+      <c r="AQ22" s="165"/>
+      <c r="AR22" s="165"/>
+      <c r="AS22" s="165"/>
+      <c r="AT22" s="165"/>
+      <c r="AU22" s="165"/>
+      <c r="AV22" s="165"/>
+      <c r="AW22" s="165"/>
+      <c r="AX22" s="165"/>
+      <c r="AY22" s="165"/>
+      <c r="AZ22" s="173"/>
     </row>
     <row r="23" spans="2:52" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B23" s="175"/>
-      <c r="C23" s="109"/>
-      <c r="D23" s="110"/>
-      <c r="E23" s="110"/>
-      <c r="F23" s="110"/>
-      <c r="G23" s="110"/>
-      <c r="H23" s="110"/>
-      <c r="I23" s="111"/>
-      <c r="J23" s="164"/>
-      <c r="K23" s="165"/>
-      <c r="L23" s="165"/>
-      <c r="M23" s="165"/>
-      <c r="N23" s="165"/>
-      <c r="O23" s="165"/>
-      <c r="P23" s="166"/>
-      <c r="Q23" s="186"/>
-      <c r="R23" s="187"/>
-      <c r="S23" s="188"/>
-      <c r="T23" s="181" t="s">
+      <c r="B23" s="178"/>
+      <c r="C23" s="112"/>
+      <c r="D23" s="113"/>
+      <c r="E23" s="113"/>
+      <c r="F23" s="113"/>
+      <c r="G23" s="113"/>
+      <c r="H23" s="113"/>
+      <c r="I23" s="114"/>
+      <c r="J23" s="167"/>
+      <c r="K23" s="168"/>
+      <c r="L23" s="168"/>
+      <c r="M23" s="168"/>
+      <c r="N23" s="168"/>
+      <c r="O23" s="168"/>
+      <c r="P23" s="169"/>
+      <c r="Q23" s="189"/>
+      <c r="R23" s="190"/>
+      <c r="S23" s="191"/>
+      <c r="T23" s="184" t="s">
         <v>25</v>
       </c>
-      <c r="U23" s="182"/>
-      <c r="V23" s="168">
+      <c r="U23" s="185"/>
+      <c r="V23" s="171">
         <v>0</v>
       </c>
-      <c r="W23" s="169"/>
-      <c r="X23" s="189">
+      <c r="W23" s="172"/>
+      <c r="X23" s="192">
         <v>0</v>
       </c>
-      <c r="Y23" s="190"/>
+      <c r="Y23" s="193"/>
       <c r="Z23" s="15"/>
       <c r="AA23" s="16"/>
       <c r="AB23" s="17"/>
@@ -7614,18 +8176,18 @@
       <c r="AL23" s="15"/>
       <c r="AM23" s="16"/>
       <c r="AN23" s="17"/>
-      <c r="AO23" s="164"/>
-      <c r="AP23" s="165"/>
-      <c r="AQ23" s="165"/>
-      <c r="AR23" s="165"/>
-      <c r="AS23" s="165"/>
-      <c r="AT23" s="165"/>
-      <c r="AU23" s="165"/>
-      <c r="AV23" s="165"/>
-      <c r="AW23" s="165"/>
-      <c r="AX23" s="165"/>
-      <c r="AY23" s="165"/>
-      <c r="AZ23" s="171"/>
+      <c r="AO23" s="167"/>
+      <c r="AP23" s="168"/>
+      <c r="AQ23" s="168"/>
+      <c r="AR23" s="168"/>
+      <c r="AS23" s="168"/>
+      <c r="AT23" s="168"/>
+      <c r="AU23" s="168"/>
+      <c r="AV23" s="168"/>
+      <c r="AW23" s="168"/>
+      <c r="AX23" s="168"/>
+      <c r="AY23" s="168"/>
+      <c r="AZ23" s="174"/>
     </row>
     <row r="24" spans="2:52" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D24" s="18"/>
@@ -7820,125 +8382,125 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="27">
+      <c r="A1" s="48">
         <v>1</v>
       </c>
-      <c r="B1" s="34" t="s">
+      <c r="B1" s="55" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="34"/>
-      <c r="D1" s="34"/>
-      <c r="E1" s="36"/>
-      <c r="F1" s="36"/>
-      <c r="G1" s="36"/>
-      <c r="H1" s="36"/>
-      <c r="I1" s="36"/>
-      <c r="J1" s="37"/>
+      <c r="C1" s="55"/>
+      <c r="D1" s="55"/>
+      <c r="E1" s="57"/>
+      <c r="F1" s="57"/>
+      <c r="G1" s="57"/>
+      <c r="H1" s="57"/>
+      <c r="I1" s="57"/>
+      <c r="J1" s="58"/>
     </row>
     <row r="2" spans="1:10" ht="13.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="31"/>
-      <c r="B2" s="35"/>
-      <c r="C2" s="35"/>
-      <c r="D2" s="35"/>
-      <c r="E2" s="38"/>
-      <c r="F2" s="38"/>
-      <c r="G2" s="38"/>
-      <c r="H2" s="38"/>
-      <c r="I2" s="38"/>
-      <c r="J2" s="39"/>
+      <c r="A2" s="52"/>
+      <c r="B2" s="56"/>
+      <c r="C2" s="56"/>
+      <c r="D2" s="56"/>
+      <c r="E2" s="59"/>
+      <c r="F2" s="59"/>
+      <c r="G2" s="59"/>
+      <c r="H2" s="59"/>
+      <c r="I2" s="59"/>
+      <c r="J2" s="60"/>
     </row>
     <row r="3" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="27">
+      <c r="A3" s="48">
         <v>2</v>
       </c>
-      <c r="B3" s="34" t="s">
-        <v>96</v>
-      </c>
-      <c r="C3" s="34"/>
-      <c r="D3" s="34"/>
-      <c r="E3" s="34"/>
-      <c r="F3" s="34"/>
-      <c r="G3" s="34"/>
-      <c r="H3" s="34"/>
-      <c r="I3" s="34"/>
-      <c r="J3" s="67"/>
+      <c r="B3" s="55" t="s">
+        <v>60</v>
+      </c>
+      <c r="C3" s="55"/>
+      <c r="D3" s="55"/>
+      <c r="E3" s="55"/>
+      <c r="F3" s="55"/>
+      <c r="G3" s="55"/>
+      <c r="H3" s="55"/>
+      <c r="I3" s="55"/>
+      <c r="J3" s="87"/>
     </row>
     <row r="4" spans="1:10" ht="13.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="28"/>
-      <c r="B4" s="194" t="s">
-        <v>97</v>
-      </c>
-      <c r="C4" s="194"/>
-      <c r="D4" s="194"/>
-      <c r="E4" s="194"/>
-      <c r="F4" s="194"/>
-      <c r="G4" s="194"/>
-      <c r="H4" s="194"/>
-      <c r="I4" s="194"/>
-      <c r="J4" s="195"/>
+      <c r="A4" s="49"/>
+      <c r="B4" s="197" t="s">
+        <v>61</v>
+      </c>
+      <c r="C4" s="197"/>
+      <c r="D4" s="197"/>
+      <c r="E4" s="197"/>
+      <c r="F4" s="197"/>
+      <c r="G4" s="197"/>
+      <c r="H4" s="197"/>
+      <c r="I4" s="197"/>
+      <c r="J4" s="198"/>
     </row>
     <row r="5" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="27">
+      <c r="A5" s="48">
         <v>3</v>
       </c>
-      <c r="B5" s="34" t="s">
-        <v>98</v>
-      </c>
-      <c r="C5" s="34"/>
-      <c r="D5" s="34"/>
-      <c r="E5" s="34"/>
-      <c r="F5" s="34"/>
-      <c r="G5" s="34"/>
-      <c r="H5" s="34"/>
-      <c r="I5" s="34"/>
-      <c r="J5" s="67"/>
+      <c r="B5" s="55" t="s">
+        <v>62</v>
+      </c>
+      <c r="C5" s="55"/>
+      <c r="D5" s="55"/>
+      <c r="E5" s="55"/>
+      <c r="F5" s="55"/>
+      <c r="G5" s="55"/>
+      <c r="H5" s="55"/>
+      <c r="I5" s="55"/>
+      <c r="J5" s="87"/>
     </row>
     <row r="6" spans="1:10" ht="13.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="31"/>
-      <c r="B6" s="73" t="s">
+      <c r="A6" s="52"/>
+      <c r="B6" s="93" t="s">
         <v>16</v>
       </c>
-      <c r="C6" s="73"/>
-      <c r="D6" s="73"/>
-      <c r="E6" s="73"/>
-      <c r="F6" s="73"/>
-      <c r="G6" s="73"/>
-      <c r="H6" s="73"/>
-      <c r="I6" s="73"/>
-      <c r="J6" s="74"/>
+      <c r="C6" s="93"/>
+      <c r="D6" s="93"/>
+      <c r="E6" s="93"/>
+      <c r="F6" s="93"/>
+      <c r="G6" s="93"/>
+      <c r="H6" s="93"/>
+      <c r="I6" s="93"/>
+      <c r="J6" s="94"/>
     </row>
     <row r="7" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="27">
+      <c r="A7" s="48">
         <v>4</v>
       </c>
-      <c r="B7" s="34" t="s">
-        <v>99</v>
-      </c>
-      <c r="C7" s="34"/>
-      <c r="D7" s="34"/>
-      <c r="E7" s="34"/>
-      <c r="F7" s="34"/>
-      <c r="G7" s="34"/>
-      <c r="H7" s="34"/>
-      <c r="I7" s="34"/>
-      <c r="J7" s="67"/>
+      <c r="B7" s="55" t="s">
+        <v>63</v>
+      </c>
+      <c r="C7" s="55"/>
+      <c r="D7" s="55"/>
+      <c r="E7" s="55"/>
+      <c r="F7" s="55"/>
+      <c r="G7" s="55"/>
+      <c r="H7" s="55"/>
+      <c r="I7" s="55"/>
+      <c r="J7" s="87"/>
     </row>
     <row r="8" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="28"/>
-      <c r="B8" s="69" t="s">
-        <v>100</v>
-      </c>
-      <c r="C8" s="69"/>
-      <c r="D8" s="69"/>
-      <c r="E8" s="69"/>
-      <c r="F8" s="69"/>
-      <c r="G8" s="69"/>
-      <c r="H8" s="69"/>
-      <c r="I8" s="69"/>
-      <c r="J8" s="70"/>
+      <c r="A8" s="49"/>
+      <c r="B8" s="89" t="s">
+        <v>64</v>
+      </c>
+      <c r="C8" s="89"/>
+      <c r="D8" s="89"/>
+      <c r="E8" s="89"/>
+      <c r="F8" s="89"/>
+      <c r="G8" s="89"/>
+      <c r="H8" s="89"/>
+      <c r="I8" s="89"/>
+      <c r="J8" s="90"/>
     </row>
     <row r="9" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="28"/>
+      <c r="A9" s="49"/>
       <c r="B9" s="44"/>
       <c r="C9" s="44"/>
       <c r="D9" s="44"/>
@@ -7947,10 +8509,10 @@
       <c r="G9" s="44"/>
       <c r="H9" s="44"/>
       <c r="I9" s="44"/>
-      <c r="J9" s="45"/>
+      <c r="J9" s="65"/>
     </row>
     <row r="10" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="28"/>
+      <c r="A10" s="49"/>
       <c r="B10" s="44"/>
       <c r="C10" s="44"/>
       <c r="D10" s="44"/>
@@ -7959,10 +8521,10 @@
       <c r="G10" s="44"/>
       <c r="H10" s="44"/>
       <c r="I10" s="44"/>
-      <c r="J10" s="45"/>
+      <c r="J10" s="65"/>
     </row>
     <row r="11" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="28"/>
+      <c r="A11" s="49"/>
       <c r="B11" s="44"/>
       <c r="C11" s="44"/>
       <c r="D11" s="44"/>
@@ -7971,10 +8533,10 @@
       <c r="G11" s="44"/>
       <c r="H11" s="44"/>
       <c r="I11" s="44"/>
-      <c r="J11" s="45"/>
+      <c r="J11" s="65"/>
     </row>
     <row r="12" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="28"/>
+      <c r="A12" s="49"/>
       <c r="B12" s="44"/>
       <c r="C12" s="44"/>
       <c r="D12" s="44"/>
@@ -7983,10 +8545,10 @@
       <c r="G12" s="44"/>
       <c r="H12" s="44"/>
       <c r="I12" s="44"/>
-      <c r="J12" s="45"/>
+      <c r="J12" s="65"/>
     </row>
     <row r="13" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="28"/>
+      <c r="A13" s="49"/>
       <c r="B13" s="44"/>
       <c r="C13" s="44"/>
       <c r="D13" s="44"/>
@@ -7995,10 +8557,10 @@
       <c r="G13" s="44"/>
       <c r="H13" s="44"/>
       <c r="I13" s="44"/>
-      <c r="J13" s="45"/>
+      <c r="J13" s="65"/>
     </row>
     <row r="14" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A14" s="28"/>
+      <c r="A14" s="49"/>
       <c r="B14" s="44"/>
       <c r="C14" s="44"/>
       <c r="D14" s="44"/>
@@ -8007,24 +8569,24 @@
       <c r="G14" s="44"/>
       <c r="H14" s="44"/>
       <c r="I14" s="44"/>
-      <c r="J14" s="45"/>
+      <c r="J14" s="65"/>
     </row>
     <row r="15" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A15" s="28"/>
-      <c r="B15" s="69" t="s">
-        <v>101</v>
-      </c>
-      <c r="C15" s="69"/>
-      <c r="D15" s="69"/>
-      <c r="E15" s="69"/>
-      <c r="F15" s="69"/>
-      <c r="G15" s="69"/>
-      <c r="H15" s="69"/>
-      <c r="I15" s="69"/>
-      <c r="J15" s="70"/>
+      <c r="A15" s="49"/>
+      <c r="B15" s="89" t="s">
+        <v>65</v>
+      </c>
+      <c r="C15" s="89"/>
+      <c r="D15" s="89"/>
+      <c r="E15" s="89"/>
+      <c r="F15" s="89"/>
+      <c r="G15" s="89"/>
+      <c r="H15" s="89"/>
+      <c r="I15" s="89"/>
+      <c r="J15" s="90"/>
     </row>
     <row r="16" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A16" s="28"/>
+      <c r="A16" s="49"/>
       <c r="B16" s="44"/>
       <c r="C16" s="44"/>
       <c r="D16" s="44"/>
@@ -8033,10 +8595,10 @@
       <c r="G16" s="44"/>
       <c r="H16" s="44"/>
       <c r="I16" s="44"/>
-      <c r="J16" s="45"/>
+      <c r="J16" s="65"/>
     </row>
     <row r="17" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A17" s="28"/>
+      <c r="A17" s="49"/>
       <c r="B17" s="44"/>
       <c r="C17" s="44"/>
       <c r="D17" s="44"/>
@@ -8045,10 +8607,10 @@
       <c r="G17" s="44"/>
       <c r="H17" s="44"/>
       <c r="I17" s="44"/>
-      <c r="J17" s="45"/>
+      <c r="J17" s="65"/>
     </row>
     <row r="18" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A18" s="28"/>
+      <c r="A18" s="49"/>
       <c r="B18" s="44"/>
       <c r="C18" s="44"/>
       <c r="D18" s="44"/>
@@ -8057,10 +8619,10 @@
       <c r="G18" s="44"/>
       <c r="H18" s="44"/>
       <c r="I18" s="44"/>
-      <c r="J18" s="45"/>
+      <c r="J18" s="65"/>
     </row>
     <row r="19" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A19" s="28"/>
+      <c r="A19" s="49"/>
       <c r="B19" s="44"/>
       <c r="C19" s="44"/>
       <c r="D19" s="44"/>
@@ -8069,10 +8631,10 @@
       <c r="G19" s="44"/>
       <c r="H19" s="44"/>
       <c r="I19" s="44"/>
-      <c r="J19" s="45"/>
+      <c r="J19" s="65"/>
     </row>
     <row r="20" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A20" s="28"/>
+      <c r="A20" s="49"/>
       <c r="B20" s="44"/>
       <c r="C20" s="44"/>
       <c r="D20" s="44"/>
@@ -8081,38 +8643,38 @@
       <c r="G20" s="44"/>
       <c r="H20" s="44"/>
       <c r="I20" s="44"/>
-      <c r="J20" s="45"/>
+      <c r="J20" s="65"/>
     </row>
     <row r="21" spans="1:10" ht="13.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="31"/>
-      <c r="B21" s="38"/>
-      <c r="C21" s="38"/>
-      <c r="D21" s="38"/>
-      <c r="E21" s="38"/>
-      <c r="F21" s="38"/>
-      <c r="G21" s="38"/>
-      <c r="H21" s="38"/>
-      <c r="I21" s="38"/>
-      <c r="J21" s="39"/>
+      <c r="A21" s="52"/>
+      <c r="B21" s="59"/>
+      <c r="C21" s="59"/>
+      <c r="D21" s="59"/>
+      <c r="E21" s="59"/>
+      <c r="F21" s="59"/>
+      <c r="G21" s="59"/>
+      <c r="H21" s="59"/>
+      <c r="I21" s="59"/>
+      <c r="J21" s="60"/>
     </row>
     <row r="22" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A22" s="27">
+      <c r="A22" s="48">
         <v>5</v>
       </c>
-      <c r="B22" s="34" t="s">
-        <v>102</v>
-      </c>
-      <c r="C22" s="34"/>
-      <c r="D22" s="34"/>
-      <c r="E22" s="34"/>
-      <c r="F22" s="34"/>
-      <c r="G22" s="34"/>
-      <c r="H22" s="34"/>
-      <c r="I22" s="34"/>
-      <c r="J22" s="67"/>
+      <c r="B22" s="55" t="s">
+        <v>66</v>
+      </c>
+      <c r="C22" s="55"/>
+      <c r="D22" s="55"/>
+      <c r="E22" s="55"/>
+      <c r="F22" s="55"/>
+      <c r="G22" s="55"/>
+      <c r="H22" s="55"/>
+      <c r="I22" s="55"/>
+      <c r="J22" s="87"/>
     </row>
     <row r="23" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A23" s="28"/>
+      <c r="A23" s="49"/>
       <c r="B23" s="44"/>
       <c r="C23" s="44"/>
       <c r="D23" s="44"/>
@@ -8121,10 +8683,10 @@
       <c r="G23" s="44"/>
       <c r="H23" s="44"/>
       <c r="I23" s="44"/>
-      <c r="J23" s="45"/>
+      <c r="J23" s="65"/>
     </row>
     <row r="24" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A24" s="28"/>
+      <c r="A24" s="49"/>
       <c r="B24" s="44"/>
       <c r="C24" s="44"/>
       <c r="D24" s="44"/>
@@ -8133,10 +8695,10 @@
       <c r="G24" s="44"/>
       <c r="H24" s="44"/>
       <c r="I24" s="44"/>
-      <c r="J24" s="45"/>
+      <c r="J24" s="65"/>
     </row>
     <row r="25" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A25" s="28"/>
+      <c r="A25" s="49"/>
       <c r="B25" s="44"/>
       <c r="C25" s="44"/>
       <c r="D25" s="44"/>
@@ -8145,10 +8707,10 @@
       <c r="G25" s="44"/>
       <c r="H25" s="44"/>
       <c r="I25" s="44"/>
-      <c r="J25" s="45"/>
+      <c r="J25" s="65"/>
     </row>
     <row r="26" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A26" s="28"/>
+      <c r="A26" s="49"/>
       <c r="B26" s="44"/>
       <c r="C26" s="44"/>
       <c r="D26" s="44"/>
@@ -8157,10 +8719,10 @@
       <c r="G26" s="44"/>
       <c r="H26" s="44"/>
       <c r="I26" s="44"/>
-      <c r="J26" s="45"/>
+      <c r="J26" s="65"/>
     </row>
     <row r="27" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A27" s="28"/>
+      <c r="A27" s="49"/>
       <c r="B27" s="44"/>
       <c r="C27" s="44"/>
       <c r="D27" s="44"/>
@@ -8169,10 +8731,10 @@
       <c r="G27" s="44"/>
       <c r="H27" s="44"/>
       <c r="I27" s="44"/>
-      <c r="J27" s="45"/>
+      <c r="J27" s="65"/>
     </row>
     <row r="28" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A28" s="28"/>
+      <c r="A28" s="49"/>
       <c r="B28" s="44"/>
       <c r="C28" s="44"/>
       <c r="D28" s="44"/>
@@ -8181,10 +8743,10 @@
       <c r="G28" s="44"/>
       <c r="H28" s="44"/>
       <c r="I28" s="44"/>
-      <c r="J28" s="45"/>
+      <c r="J28" s="65"/>
     </row>
     <row r="29" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A29" s="28"/>
+      <c r="A29" s="49"/>
       <c r="B29" s="44"/>
       <c r="C29" s="44"/>
       <c r="D29" s="44"/>
@@ -8193,38 +8755,38 @@
       <c r="G29" s="44"/>
       <c r="H29" s="44"/>
       <c r="I29" s="44"/>
-      <c r="J29" s="45"/>
+      <c r="J29" s="65"/>
     </row>
     <row r="30" spans="1:10" ht="13.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="31"/>
-      <c r="B30" s="38"/>
-      <c r="C30" s="38"/>
-      <c r="D30" s="38"/>
-      <c r="E30" s="38"/>
-      <c r="F30" s="38"/>
-      <c r="G30" s="38"/>
-      <c r="H30" s="38"/>
-      <c r="I30" s="38"/>
-      <c r="J30" s="39"/>
+      <c r="A30" s="52"/>
+      <c r="B30" s="59"/>
+      <c r="C30" s="59"/>
+      <c r="D30" s="59"/>
+      <c r="E30" s="59"/>
+      <c r="F30" s="59"/>
+      <c r="G30" s="59"/>
+      <c r="H30" s="59"/>
+      <c r="I30" s="59"/>
+      <c r="J30" s="60"/>
     </row>
     <row r="31" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A31" s="27">
+      <c r="A31" s="48">
         <v>6</v>
       </c>
-      <c r="B31" s="34" t="s">
-        <v>103</v>
-      </c>
-      <c r="C31" s="34"/>
-      <c r="D31" s="34"/>
-      <c r="E31" s="34"/>
-      <c r="F31" s="34"/>
-      <c r="G31" s="34"/>
-      <c r="H31" s="34"/>
-      <c r="I31" s="34"/>
-      <c r="J31" s="67"/>
+      <c r="B31" s="55" t="s">
+        <v>67</v>
+      </c>
+      <c r="C31" s="55"/>
+      <c r="D31" s="55"/>
+      <c r="E31" s="55"/>
+      <c r="F31" s="55"/>
+      <c r="G31" s="55"/>
+      <c r="H31" s="55"/>
+      <c r="I31" s="55"/>
+      <c r="J31" s="87"/>
     </row>
     <row r="32" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A32" s="28"/>
+      <c r="A32" s="49"/>
       <c r="B32" s="44"/>
       <c r="C32" s="44"/>
       <c r="D32" s="44"/>
@@ -8233,10 +8795,10 @@
       <c r="G32" s="44"/>
       <c r="H32" s="44"/>
       <c r="I32" s="44"/>
-      <c r="J32" s="45"/>
+      <c r="J32" s="65"/>
     </row>
     <row r="33" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A33" s="28"/>
+      <c r="A33" s="49"/>
       <c r="B33" s="44"/>
       <c r="C33" s="44"/>
       <c r="D33" s="44"/>
@@ -8245,10 +8807,10 @@
       <c r="G33" s="44"/>
       <c r="H33" s="44"/>
       <c r="I33" s="44"/>
-      <c r="J33" s="45"/>
+      <c r="J33" s="65"/>
     </row>
     <row r="34" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A34" s="28"/>
+      <c r="A34" s="49"/>
       <c r="B34" s="44"/>
       <c r="C34" s="44"/>
       <c r="D34" s="44"/>
@@ -8257,10 +8819,10 @@
       <c r="G34" s="44"/>
       <c r="H34" s="44"/>
       <c r="I34" s="44"/>
-      <c r="J34" s="45"/>
+      <c r="J34" s="65"/>
     </row>
     <row r="35" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A35" s="28"/>
+      <c r="A35" s="49"/>
       <c r="B35" s="44"/>
       <c r="C35" s="44"/>
       <c r="D35" s="44"/>
@@ -8269,10 +8831,10 @@
       <c r="G35" s="44"/>
       <c r="H35" s="44"/>
       <c r="I35" s="44"/>
-      <c r="J35" s="45"/>
+      <c r="J35" s="65"/>
     </row>
     <row r="36" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A36" s="28"/>
+      <c r="A36" s="49"/>
       <c r="B36" s="44"/>
       <c r="C36" s="44"/>
       <c r="D36" s="44"/>
@@ -8281,10 +8843,10 @@
       <c r="G36" s="44"/>
       <c r="H36" s="44"/>
       <c r="I36" s="44"/>
-      <c r="J36" s="45"/>
+      <c r="J36" s="65"/>
     </row>
     <row r="37" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A37" s="28"/>
+      <c r="A37" s="49"/>
       <c r="B37" s="44"/>
       <c r="C37" s="44"/>
       <c r="D37" s="44"/>
@@ -8293,10 +8855,10 @@
       <c r="G37" s="44"/>
       <c r="H37" s="44"/>
       <c r="I37" s="44"/>
-      <c r="J37" s="45"/>
+      <c r="J37" s="65"/>
     </row>
     <row r="38" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A38" s="28"/>
+      <c r="A38" s="49"/>
       <c r="B38" s="44"/>
       <c r="C38" s="44"/>
       <c r="D38" s="44"/>
@@ -8305,10 +8867,10 @@
       <c r="G38" s="44"/>
       <c r="H38" s="44"/>
       <c r="I38" s="44"/>
-      <c r="J38" s="45"/>
+      <c r="J38" s="65"/>
     </row>
     <row r="39" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A39" s="28"/>
+      <c r="A39" s="49"/>
       <c r="B39" s="44"/>
       <c r="C39" s="44"/>
       <c r="D39" s="44"/>
@@ -8317,10 +8879,10 @@
       <c r="G39" s="44"/>
       <c r="H39" s="44"/>
       <c r="I39" s="44"/>
-      <c r="J39" s="45"/>
+      <c r="J39" s="65"/>
     </row>
     <row r="40" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A40" s="28"/>
+      <c r="A40" s="49"/>
       <c r="B40" s="44"/>
       <c r="C40" s="44"/>
       <c r="D40" s="44"/>
@@ -8329,10 +8891,10 @@
       <c r="G40" s="44"/>
       <c r="H40" s="44"/>
       <c r="I40" s="44"/>
-      <c r="J40" s="45"/>
+      <c r="J40" s="65"/>
     </row>
     <row r="41" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A41" s="28"/>
+      <c r="A41" s="49"/>
       <c r="B41" s="44"/>
       <c r="C41" s="44"/>
       <c r="D41" s="44"/>
@@ -8341,10 +8903,10 @@
       <c r="G41" s="44"/>
       <c r="H41" s="44"/>
       <c r="I41" s="44"/>
-      <c r="J41" s="45"/>
+      <c r="J41" s="65"/>
     </row>
     <row r="42" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A42" s="28"/>
+      <c r="A42" s="49"/>
       <c r="B42" s="44"/>
       <c r="C42" s="44"/>
       <c r="D42" s="44"/>
@@ -8353,10 +8915,10 @@
       <c r="G42" s="44"/>
       <c r="H42" s="44"/>
       <c r="I42" s="44"/>
-      <c r="J42" s="45"/>
+      <c r="J42" s="65"/>
     </row>
     <row r="43" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A43" s="28"/>
+      <c r="A43" s="49"/>
       <c r="B43" s="44"/>
       <c r="C43" s="44"/>
       <c r="D43" s="44"/>
@@ -8365,10 +8927,10 @@
       <c r="G43" s="44"/>
       <c r="H43" s="44"/>
       <c r="I43" s="44"/>
-      <c r="J43" s="45"/>
+      <c r="J43" s="65"/>
     </row>
     <row r="44" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A44" s="28"/>
+      <c r="A44" s="49"/>
       <c r="B44" s="44"/>
       <c r="C44" s="44"/>
       <c r="D44" s="44"/>
@@ -8377,10 +8939,10 @@
       <c r="G44" s="44"/>
       <c r="H44" s="44"/>
       <c r="I44" s="44"/>
-      <c r="J44" s="45"/>
+      <c r="J44" s="65"/>
     </row>
     <row r="45" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A45" s="28"/>
+      <c r="A45" s="49"/>
       <c r="B45" s="44"/>
       <c r="C45" s="44"/>
       <c r="D45" s="44"/>
@@ -8389,10 +8951,10 @@
       <c r="G45" s="44"/>
       <c r="H45" s="44"/>
       <c r="I45" s="44"/>
-      <c r="J45" s="45"/>
+      <c r="J45" s="65"/>
     </row>
     <row r="46" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A46" s="28"/>
+      <c r="A46" s="49"/>
       <c r="B46" s="44"/>
       <c r="C46" s="44"/>
       <c r="D46" s="44"/>
@@ -8401,19 +8963,19 @@
       <c r="G46" s="44"/>
       <c r="H46" s="44"/>
       <c r="I46" s="44"/>
-      <c r="J46" s="45"/>
+      <c r="J46" s="65"/>
     </row>
     <row r="47" spans="1:10" ht="13.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A47" s="29"/>
-      <c r="B47" s="71"/>
-      <c r="C47" s="71"/>
-      <c r="D47" s="71"/>
-      <c r="E47" s="71"/>
-      <c r="F47" s="71"/>
-      <c r="G47" s="71"/>
-      <c r="H47" s="71"/>
-      <c r="I47" s="71"/>
-      <c r="J47" s="72"/>
+      <c r="A47" s="50"/>
+      <c r="B47" s="91"/>
+      <c r="C47" s="91"/>
+      <c r="D47" s="91"/>
+      <c r="E47" s="91"/>
+      <c r="F47" s="91"/>
+      <c r="G47" s="91"/>
+      <c r="H47" s="91"/>
+      <c r="I47" s="91"/>
+      <c r="J47" s="92"/>
     </row>
   </sheetData>
   <mergeCells count="21">
@@ -8450,17 +9012,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="88cc3c26-756f-41ab-80ed-43e7289fee5b">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="55239288-d498-4dd6-9609-491b39ec8fae" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
   <Display>DocumentLibraryForm</Display>
@@ -8469,7 +9020,7 @@
 </FormTemplates>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="ドキュメント" ma:contentTypeID="0x01010058BEBA3CD4E69545839402B5D4E5400B" ma:contentTypeVersion="13" ma:contentTypeDescription="新しいドキュメントを作成します。" ma:contentTypeScope="" ma:versionID="85fadafb228503a8e253560e9cdffc69">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="88cc3c26-756f-41ab-80ed-43e7289fee5b" xmlns:ns3="55239288-d498-4dd6-9609-491b39ec8fae" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="9785dde68d2e35ac7b66dd15e8e44124" ns2:_="" ns3:_="">
     <xsd:import namespace="88cc3c26-756f-41ab-80ed-43e7289fee5b"/>
@@ -8676,7 +9227,45 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="88cc3c26-756f-41ab-80ed-43e7289fee5b">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="55239288-d498-4dd6-9609-491b39ec8fae" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0843C284-C2B9-4564-B59A-F2FA129FE5C7}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{18D765C5-969E-4095-9A45-9E80C6C2EDED}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="88cc3c26-756f-41ab-80ed-43e7289fee5b"/>
+    <ds:schemaRef ds:uri="55239288-d498-4dd6-9609-491b39ec8fae"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{82E555AC-3D9C-4ECE-9578-D2E452F320B7}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
@@ -8693,31 +9282,4 @@
     <ds:schemaRef ds:uri="55239288-d498-4dd6-9609-491b39ec8fae"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0843C284-C2B9-4564-B59A-F2FA129FE5C7}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{18D765C5-969E-4095-9A45-9E80C6C2EDED}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="88cc3c26-756f-41ab-80ed-43e7289fee5b"/>
-    <ds:schemaRef ds:uri="55239288-d498-4dd6-9609-491b39ec8fae"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/11_プロジェクト計画書.xlsx
+++ b/11_プロジェクト計画書.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\k_tanoue\Documents\GitHub\tanouesoftware\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4F6E0CD4-E445-47D9-9AC1-E2E31E94AD35}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7465072D-82E1-4B77-9BE4-DC66C4710E56}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" firstSheet="2" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="プロジェクト計画" sheetId="1" r:id="rId1"/>
@@ -1591,16 +1591,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>Android:Chrome、iOS:Safari、Windows:Edge・Chromeの最新版に対応する</t>
-    <rPh sb="46" eb="49">
-      <t>サイシンバン</t>
-    </rPh>
-    <rPh sb="50" eb="52">
-      <t>タイオウ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>対応デバイス</t>
     <rPh sb="0" eb="2">
       <t>タイオウ</t>
@@ -1616,6 +1606,16 @@
       <t>オヨ</t>
     </rPh>
     <rPh sb="36" eb="38">
+      <t>タイオウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Android: Chrome、iOS: Safari、Windows: Edge・Chromeの最新版に対応する</t>
+    <rPh sb="49" eb="52">
+      <t>サイシンバン</t>
+    </rPh>
+    <rPh sb="53" eb="55">
       <t>タイオウ</t>
     </rPh>
     <phoneticPr fontId="1"/>
@@ -2662,242 +2662,320 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="50" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="50" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="51" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="51" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="50" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="50" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1">
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="51" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="21" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="21" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="176" fontId="7" fillId="0" borderId="48" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="7" fillId="0" borderId="49" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="33" xfId="1" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="7" fillId="0" borderId="48" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="9" fontId="7" fillId="0" borderId="49" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="21" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="34" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="51" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="35" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="25" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="51" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="16" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="46" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="7" fillId="0" borderId="52" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+    <xf numFmtId="176" fontId="7" fillId="0" borderId="53" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+    <xf numFmtId="176" fontId="7" fillId="0" borderId="54" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+    <xf numFmtId="176" fontId="7" fillId="0" borderId="55" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+    <xf numFmtId="176" fontId="7" fillId="0" borderId="58" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+    <xf numFmtId="176" fontId="7" fillId="0" borderId="59" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="50" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="50" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="32" xfId="1" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
@@ -2905,6 +2983,99 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="40" xfId="1" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="22" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="7" fillId="0" borderId="48" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="7" fillId="0" borderId="49" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="23" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="24" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="41" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="42" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="43" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="7" fillId="0" borderId="62" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="7" fillId="0" borderId="63" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="60" xfId="1" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="57" xfId="1" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="23" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="61" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="25" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="16" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="46" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="7" fillId="0" borderId="62" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="7" fillId="0" borderId="63" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="7" fillId="0" borderId="52" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="7" fillId="0" borderId="53" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="23" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="61" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="41" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="42" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="56" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="7" fillId="0" borderId="52" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="7" fillId="0" borderId="53" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="34" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -2914,32 +3085,35 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="25" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="16" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="46" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="34" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="9" fontId="7" fillId="0" borderId="54" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="7" fillId="0" borderId="55" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="36" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="35" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="26" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="25" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="16" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="46" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="9" fontId="7" fillId="0" borderId="58" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="7" fillId="0" borderId="59" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="7" fillId="0" borderId="54" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="7" fillId="0" borderId="55" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="7" fillId="0" borderId="58" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="7" fillId="0" borderId="59" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="34" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -2959,47 +3133,17 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="46" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="7" fillId="0" borderId="54" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="7" fillId="0" borderId="55" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="7" fillId="0" borderId="54" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1">
+    <xf numFmtId="176" fontId="7" fillId="0" borderId="62" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="7" fillId="0" borderId="55" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1">
+    <xf numFmtId="176" fontId="7" fillId="0" borderId="63" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="7" fillId="0" borderId="54" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="7" fillId="0" borderId="55" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="36" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="61" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="26" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="56" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="7" fillId="0" borderId="58" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="7" fillId="0" borderId="59" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="7" fillId="0" borderId="58" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="7" fillId="0" borderId="59" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="7" fillId="0" borderId="58" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="7" fillId="0" borderId="59" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="2" borderId="37" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -3013,15 +3157,6 @@
     <xf numFmtId="0" fontId="8" fillId="2" borderId="22" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="7" fillId="0" borderId="48" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="7" fillId="0" borderId="49" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="21" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="8" fillId="2" borderId="44" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -3046,146 +3181,11 @@
     <xf numFmtId="0" fontId="8" fillId="2" borderId="33" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="21" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="22" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="7" fillId="0" borderId="49" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="7" fillId="0" borderId="48" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="7" fillId="0" borderId="49" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="7" fillId="0" borderId="48" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="7" fillId="0" borderId="62" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="7" fillId="0" borderId="63" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="23" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="61" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="41" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="42" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="56" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="33" xfId="1" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="7" fillId="0" borderId="52" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="7" fillId="0" borderId="53" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="24" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="43" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="7" fillId="0" borderId="62" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="7" fillId="0" borderId="63" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="60" xfId="1" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="57" xfId="1" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="23" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="61" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="9" fontId="7" fillId="0" borderId="62" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="7" fillId="0" borderId="63" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="7" fillId="0" borderId="52" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="7" fillId="0" borderId="53" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="23" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="61" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="41" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="42" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="56" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="7" fillId="0" borderId="52" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="7" fillId="0" borderId="53" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="51" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="21" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="50" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -4005,1575 +4005,1598 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" s="2" customFormat="1" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="88" t="s">
+      <c r="A1" s="46" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="88"/>
-      <c r="C1" s="88"/>
-      <c r="D1" s="88"/>
-      <c r="E1" s="88"/>
-      <c r="F1" s="88"/>
-      <c r="G1" s="88"/>
-      <c r="H1" s="88"/>
-      <c r="I1" s="88"/>
-      <c r="J1" s="88"/>
+      <c r="B1" s="46"/>
+      <c r="C1" s="46"/>
+      <c r="D1" s="46"/>
+      <c r="E1" s="46"/>
+      <c r="F1" s="46"/>
+      <c r="G1" s="46"/>
+      <c r="H1" s="46"/>
+      <c r="I1" s="46"/>
+      <c r="J1" s="46"/>
     </row>
     <row r="2" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="48">
+      <c r="A2" s="47">
         <v>1</v>
       </c>
-      <c r="B2" s="55" t="s">
+      <c r="B2" s="51" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="55"/>
-      <c r="D2" s="55"/>
-      <c r="E2" s="57"/>
-      <c r="F2" s="57"/>
-      <c r="G2" s="57"/>
-      <c r="H2" s="57"/>
-      <c r="I2" s="57"/>
-      <c r="J2" s="58"/>
+      <c r="C2" s="51"/>
+      <c r="D2" s="51"/>
+      <c r="E2" s="94"/>
+      <c r="F2" s="94"/>
+      <c r="G2" s="94"/>
+      <c r="H2" s="94"/>
+      <c r="I2" s="94"/>
+      <c r="J2" s="95"/>
     </row>
     <row r="3" spans="1:10" ht="13.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="52"/>
-      <c r="B3" s="56"/>
-      <c r="C3" s="56"/>
-      <c r="D3" s="56"/>
-      <c r="E3" s="59"/>
-      <c r="F3" s="59"/>
-      <c r="G3" s="59"/>
-      <c r="H3" s="59"/>
-      <c r="I3" s="59"/>
-      <c r="J3" s="60"/>
+      <c r="A3" s="48"/>
+      <c r="B3" s="36"/>
+      <c r="C3" s="36"/>
+      <c r="D3" s="36"/>
+      <c r="E3" s="96"/>
+      <c r="F3" s="96"/>
+      <c r="G3" s="96"/>
+      <c r="H3" s="96"/>
+      <c r="I3" s="96"/>
+      <c r="J3" s="97"/>
     </row>
     <row r="4" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="48">
+      <c r="A4" s="47">
         <v>2</v>
       </c>
-      <c r="B4" s="53" t="s">
+      <c r="B4" s="61" t="s">
         <v>2</v>
       </c>
-      <c r="C4" s="53"/>
-      <c r="D4" s="53"/>
-      <c r="E4" s="53"/>
-      <c r="F4" s="53"/>
-      <c r="G4" s="53"/>
-      <c r="H4" s="53"/>
-      <c r="I4" s="53"/>
-      <c r="J4" s="54"/>
+      <c r="C4" s="61"/>
+      <c r="D4" s="61"/>
+      <c r="E4" s="61"/>
+      <c r="F4" s="61"/>
+      <c r="G4" s="61"/>
+      <c r="H4" s="61"/>
+      <c r="I4" s="61"/>
+      <c r="J4" s="62"/>
     </row>
     <row r="5" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="49"/>
-      <c r="B5" s="66" t="s">
+      <c r="B5" s="64" t="s">
         <v>3</v>
       </c>
-      <c r="C5" s="66"/>
-      <c r="D5" s="66"/>
-      <c r="E5" s="66"/>
-      <c r="F5" s="66"/>
-      <c r="G5" s="66"/>
-      <c r="H5" s="66"/>
-      <c r="I5" s="66"/>
-      <c r="J5" s="67"/>
+      <c r="C5" s="64"/>
+      <c r="D5" s="64"/>
+      <c r="E5" s="64"/>
+      <c r="F5" s="64"/>
+      <c r="G5" s="64"/>
+      <c r="H5" s="64"/>
+      <c r="I5" s="64"/>
+      <c r="J5" s="65"/>
     </row>
     <row r="6" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="49"/>
-      <c r="B6" s="66"/>
-      <c r="C6" s="66"/>
-      <c r="D6" s="66"/>
-      <c r="E6" s="66"/>
-      <c r="F6" s="66"/>
-      <c r="G6" s="66"/>
-      <c r="H6" s="66"/>
-      <c r="I6" s="66"/>
-      <c r="J6" s="67"/>
+      <c r="B6" s="64"/>
+      <c r="C6" s="64"/>
+      <c r="D6" s="64"/>
+      <c r="E6" s="64"/>
+      <c r="F6" s="64"/>
+      <c r="G6" s="64"/>
+      <c r="H6" s="64"/>
+      <c r="I6" s="64"/>
+      <c r="J6" s="65"/>
     </row>
     <row r="7" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="49"/>
-      <c r="B7" s="68"/>
-      <c r="C7" s="68"/>
-      <c r="D7" s="68"/>
-      <c r="E7" s="68"/>
-      <c r="F7" s="68"/>
-      <c r="G7" s="68"/>
-      <c r="H7" s="68"/>
-      <c r="I7" s="68"/>
-      <c r="J7" s="69"/>
+      <c r="B7" s="66"/>
+      <c r="C7" s="66"/>
+      <c r="D7" s="66"/>
+      <c r="E7" s="66"/>
+      <c r="F7" s="66"/>
+      <c r="G7" s="66"/>
+      <c r="H7" s="66"/>
+      <c r="I7" s="66"/>
+      <c r="J7" s="67"/>
     </row>
     <row r="8" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="49"/>
-      <c r="B8" s="81" t="s">
+      <c r="B8" s="93" t="s">
         <v>69</v>
       </c>
-      <c r="C8" s="82"/>
-      <c r="D8" s="82"/>
-      <c r="E8" s="82"/>
-      <c r="F8" s="82"/>
-      <c r="G8" s="82"/>
-      <c r="H8" s="82"/>
-      <c r="I8" s="82"/>
-      <c r="J8" s="83"/>
+      <c r="C8" s="70"/>
+      <c r="D8" s="70"/>
+      <c r="E8" s="70"/>
+      <c r="F8" s="70"/>
+      <c r="G8" s="70"/>
+      <c r="H8" s="70"/>
+      <c r="I8" s="70"/>
+      <c r="J8" s="71"/>
     </row>
     <row r="9" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="49"/>
-      <c r="B9" s="84"/>
-      <c r="C9" s="85"/>
-      <c r="D9" s="85"/>
-      <c r="E9" s="85"/>
-      <c r="F9" s="85"/>
-      <c r="G9" s="85"/>
-      <c r="H9" s="85"/>
-      <c r="I9" s="85"/>
-      <c r="J9" s="86"/>
+      <c r="B9" s="72"/>
+      <c r="C9" s="73"/>
+      <c r="D9" s="73"/>
+      <c r="E9" s="73"/>
+      <c r="F9" s="73"/>
+      <c r="G9" s="73"/>
+      <c r="H9" s="73"/>
+      <c r="I9" s="73"/>
+      <c r="J9" s="74"/>
     </row>
     <row r="10" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="49"/>
-      <c r="B10" s="84"/>
-      <c r="C10" s="85"/>
-      <c r="D10" s="85"/>
-      <c r="E10" s="85"/>
-      <c r="F10" s="85"/>
-      <c r="G10" s="85"/>
-      <c r="H10" s="85"/>
-      <c r="I10" s="85"/>
-      <c r="J10" s="86"/>
+      <c r="B10" s="72"/>
+      <c r="C10" s="73"/>
+      <c r="D10" s="73"/>
+      <c r="E10" s="73"/>
+      <c r="F10" s="73"/>
+      <c r="G10" s="73"/>
+      <c r="H10" s="73"/>
+      <c r="I10" s="73"/>
+      <c r="J10" s="74"/>
     </row>
     <row r="11" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="49"/>
-      <c r="B11" s="84"/>
-      <c r="C11" s="85"/>
-      <c r="D11" s="85"/>
-      <c r="E11" s="85"/>
-      <c r="F11" s="85"/>
-      <c r="G11" s="85"/>
-      <c r="H11" s="85"/>
-      <c r="I11" s="85"/>
-      <c r="J11" s="86"/>
+      <c r="B11" s="72"/>
+      <c r="C11" s="73"/>
+      <c r="D11" s="73"/>
+      <c r="E11" s="73"/>
+      <c r="F11" s="73"/>
+      <c r="G11" s="73"/>
+      <c r="H11" s="73"/>
+      <c r="I11" s="73"/>
+      <c r="J11" s="74"/>
     </row>
     <row r="12" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="49"/>
-      <c r="B12" s="84"/>
-      <c r="C12" s="85"/>
-      <c r="D12" s="85"/>
-      <c r="E12" s="85"/>
-      <c r="F12" s="85"/>
-      <c r="G12" s="85"/>
-      <c r="H12" s="85"/>
-      <c r="I12" s="85"/>
-      <c r="J12" s="86"/>
+      <c r="B12" s="72"/>
+      <c r="C12" s="73"/>
+      <c r="D12" s="73"/>
+      <c r="E12" s="73"/>
+      <c r="F12" s="73"/>
+      <c r="G12" s="73"/>
+      <c r="H12" s="73"/>
+      <c r="I12" s="73"/>
+      <c r="J12" s="74"/>
     </row>
     <row r="13" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="49"/>
-      <c r="B13" s="84"/>
-      <c r="C13" s="85"/>
-      <c r="D13" s="85"/>
-      <c r="E13" s="85"/>
-      <c r="F13" s="85"/>
-      <c r="G13" s="85"/>
-      <c r="H13" s="85"/>
-      <c r="I13" s="85"/>
-      <c r="J13" s="86"/>
+      <c r="B13" s="72"/>
+      <c r="C13" s="73"/>
+      <c r="D13" s="73"/>
+      <c r="E13" s="73"/>
+      <c r="F13" s="73"/>
+      <c r="G13" s="73"/>
+      <c r="H13" s="73"/>
+      <c r="I13" s="73"/>
+      <c r="J13" s="74"/>
     </row>
     <row r="14" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="49"/>
-      <c r="B14" s="84"/>
-      <c r="C14" s="85"/>
-      <c r="D14" s="85"/>
-      <c r="E14" s="85"/>
-      <c r="F14" s="85"/>
-      <c r="G14" s="85"/>
-      <c r="H14" s="85"/>
-      <c r="I14" s="85"/>
-      <c r="J14" s="86"/>
+      <c r="B14" s="72"/>
+      <c r="C14" s="73"/>
+      <c r="D14" s="73"/>
+      <c r="E14" s="73"/>
+      <c r="F14" s="73"/>
+      <c r="G14" s="73"/>
+      <c r="H14" s="73"/>
+      <c r="I14" s="73"/>
+      <c r="J14" s="74"/>
     </row>
     <row r="15" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="49"/>
-      <c r="B15" s="84"/>
-      <c r="C15" s="85"/>
-      <c r="D15" s="85"/>
-      <c r="E15" s="85"/>
-      <c r="F15" s="85"/>
-      <c r="G15" s="85"/>
-      <c r="H15" s="85"/>
-      <c r="I15" s="85"/>
-      <c r="J15" s="86"/>
+      <c r="B15" s="72"/>
+      <c r="C15" s="73"/>
+      <c r="D15" s="73"/>
+      <c r="E15" s="73"/>
+      <c r="F15" s="73"/>
+      <c r="G15" s="73"/>
+      <c r="H15" s="73"/>
+      <c r="I15" s="73"/>
+      <c r="J15" s="74"/>
     </row>
     <row r="16" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="49"/>
-      <c r="B16" s="84"/>
-      <c r="C16" s="85"/>
-      <c r="D16" s="85"/>
-      <c r="E16" s="85"/>
-      <c r="F16" s="85"/>
-      <c r="G16" s="85"/>
-      <c r="H16" s="85"/>
-      <c r="I16" s="85"/>
-      <c r="J16" s="86"/>
+      <c r="B16" s="72"/>
+      <c r="C16" s="73"/>
+      <c r="D16" s="73"/>
+      <c r="E16" s="73"/>
+      <c r="F16" s="73"/>
+      <c r="G16" s="73"/>
+      <c r="H16" s="73"/>
+      <c r="I16" s="73"/>
+      <c r="J16" s="74"/>
     </row>
     <row r="17" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A17" s="52"/>
-      <c r="B17" s="84"/>
-      <c r="C17" s="85"/>
-      <c r="D17" s="85"/>
-      <c r="E17" s="85"/>
-      <c r="F17" s="85"/>
-      <c r="G17" s="85"/>
-      <c r="H17" s="85"/>
-      <c r="I17" s="85"/>
-      <c r="J17" s="86"/>
+      <c r="A17" s="48"/>
+      <c r="B17" s="72"/>
+      <c r="C17" s="73"/>
+      <c r="D17" s="73"/>
+      <c r="E17" s="73"/>
+      <c r="F17" s="73"/>
+      <c r="G17" s="73"/>
+      <c r="H17" s="73"/>
+      <c r="I17" s="73"/>
+      <c r="J17" s="74"/>
     </row>
     <row r="18" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A18" s="52"/>
-      <c r="B18" s="84"/>
-      <c r="C18" s="85"/>
-      <c r="D18" s="85"/>
-      <c r="E18" s="85"/>
-      <c r="F18" s="85"/>
-      <c r="G18" s="85"/>
-      <c r="H18" s="85"/>
-      <c r="I18" s="85"/>
-      <c r="J18" s="86"/>
+      <c r="A18" s="48"/>
+      <c r="B18" s="72"/>
+      <c r="C18" s="73"/>
+      <c r="D18" s="73"/>
+      <c r="E18" s="73"/>
+      <c r="F18" s="73"/>
+      <c r="G18" s="73"/>
+      <c r="H18" s="73"/>
+      <c r="I18" s="73"/>
+      <c r="J18" s="74"/>
     </row>
     <row r="19" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A19" s="52"/>
-      <c r="B19" s="84"/>
-      <c r="C19" s="85"/>
-      <c r="D19" s="85"/>
-      <c r="E19" s="85"/>
-      <c r="F19" s="85"/>
-      <c r="G19" s="85"/>
-      <c r="H19" s="85"/>
-      <c r="I19" s="85"/>
-      <c r="J19" s="86"/>
+      <c r="A19" s="48"/>
+      <c r="B19" s="72"/>
+      <c r="C19" s="73"/>
+      <c r="D19" s="73"/>
+      <c r="E19" s="73"/>
+      <c r="F19" s="73"/>
+      <c r="G19" s="73"/>
+      <c r="H19" s="73"/>
+      <c r="I19" s="73"/>
+      <c r="J19" s="74"/>
     </row>
     <row r="20" spans="1:10" ht="13.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="52"/>
-      <c r="B20" s="84"/>
-      <c r="C20" s="85"/>
-      <c r="D20" s="85"/>
-      <c r="E20" s="85"/>
-      <c r="F20" s="85"/>
-      <c r="G20" s="85"/>
-      <c r="H20" s="85"/>
-      <c r="I20" s="85"/>
-      <c r="J20" s="86"/>
+      <c r="A20" s="48"/>
+      <c r="B20" s="72"/>
+      <c r="C20" s="73"/>
+      <c r="D20" s="73"/>
+      <c r="E20" s="73"/>
+      <c r="F20" s="73"/>
+      <c r="G20" s="73"/>
+      <c r="H20" s="73"/>
+      <c r="I20" s="73"/>
+      <c r="J20" s="74"/>
     </row>
     <row r="21" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A21" s="48">
+      <c r="A21" s="47">
         <v>3</v>
       </c>
-      <c r="B21" s="53" t="s">
+      <c r="B21" s="61" t="s">
         <v>4</v>
       </c>
-      <c r="C21" s="53"/>
-      <c r="D21" s="53"/>
-      <c r="E21" s="53"/>
-      <c r="F21" s="53"/>
-      <c r="G21" s="53"/>
-      <c r="H21" s="53"/>
-      <c r="I21" s="53"/>
-      <c r="J21" s="54"/>
+      <c r="C21" s="61"/>
+      <c r="D21" s="61"/>
+      <c r="E21" s="61"/>
+      <c r="F21" s="61"/>
+      <c r="G21" s="61"/>
+      <c r="H21" s="61"/>
+      <c r="I21" s="61"/>
+      <c r="J21" s="62"/>
     </row>
     <row r="22" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="49"/>
-      <c r="B22" s="70" t="s">
+      <c r="B22" s="81" t="s">
         <v>5</v>
       </c>
-      <c r="C22" s="71"/>
-      <c r="D22" s="71"/>
-      <c r="E22" s="71"/>
-      <c r="F22" s="71"/>
-      <c r="G22" s="71"/>
-      <c r="H22" s="71"/>
-      <c r="I22" s="71"/>
-      <c r="J22" s="72"/>
+      <c r="C22" s="82"/>
+      <c r="D22" s="82"/>
+      <c r="E22" s="82"/>
+      <c r="F22" s="82"/>
+      <c r="G22" s="82"/>
+      <c r="H22" s="82"/>
+      <c r="I22" s="82"/>
+      <c r="J22" s="83"/>
     </row>
     <row r="23" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="49"/>
-      <c r="B23" s="70"/>
-      <c r="C23" s="71"/>
-      <c r="D23" s="71"/>
-      <c r="E23" s="71"/>
-      <c r="F23" s="71"/>
-      <c r="G23" s="71"/>
-      <c r="H23" s="71"/>
-      <c r="I23" s="71"/>
-      <c r="J23" s="72"/>
+      <c r="B23" s="81"/>
+      <c r="C23" s="82"/>
+      <c r="D23" s="82"/>
+      <c r="E23" s="82"/>
+      <c r="F23" s="82"/>
+      <c r="G23" s="82"/>
+      <c r="H23" s="82"/>
+      <c r="I23" s="82"/>
+      <c r="J23" s="83"/>
     </row>
     <row r="24" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" s="49"/>
-      <c r="B24" s="70"/>
-      <c r="C24" s="71"/>
-      <c r="D24" s="71"/>
-      <c r="E24" s="71"/>
-      <c r="F24" s="71"/>
-      <c r="G24" s="71"/>
-      <c r="H24" s="71"/>
-      <c r="I24" s="71"/>
-      <c r="J24" s="72"/>
+      <c r="B24" s="81"/>
+      <c r="C24" s="82"/>
+      <c r="D24" s="82"/>
+      <c r="E24" s="82"/>
+      <c r="F24" s="82"/>
+      <c r="G24" s="82"/>
+      <c r="H24" s="82"/>
+      <c r="I24" s="82"/>
+      <c r="J24" s="83"/>
     </row>
     <row r="25" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A25" s="49"/>
-      <c r="B25" s="73"/>
-      <c r="C25" s="74"/>
-      <c r="D25" s="74"/>
-      <c r="E25" s="74"/>
-      <c r="F25" s="74"/>
-      <c r="G25" s="74"/>
-      <c r="H25" s="74"/>
-      <c r="I25" s="74"/>
-      <c r="J25" s="75"/>
+      <c r="B25" s="84"/>
+      <c r="C25" s="85"/>
+      <c r="D25" s="85"/>
+      <c r="E25" s="85"/>
+      <c r="F25" s="85"/>
+      <c r="G25" s="85"/>
+      <c r="H25" s="85"/>
+      <c r="I25" s="85"/>
+      <c r="J25" s="86"/>
     </row>
     <row r="26" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26" s="49"/>
-      <c r="B26" s="76" t="s">
+      <c r="B26" s="87" t="s">
         <v>70</v>
       </c>
-      <c r="C26" s="76"/>
-      <c r="D26" s="76"/>
-      <c r="E26" s="76"/>
-      <c r="F26" s="76"/>
-      <c r="G26" s="76"/>
-      <c r="H26" s="76"/>
-      <c r="I26" s="76"/>
-      <c r="J26" s="77"/>
+      <c r="C26" s="87"/>
+      <c r="D26" s="87"/>
+      <c r="E26" s="87"/>
+      <c r="F26" s="87"/>
+      <c r="G26" s="87"/>
+      <c r="H26" s="87"/>
+      <c r="I26" s="87"/>
+      <c r="J26" s="88"/>
     </row>
     <row r="27" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A27" s="49"/>
-      <c r="B27" s="76"/>
-      <c r="C27" s="76"/>
-      <c r="D27" s="76"/>
-      <c r="E27" s="76"/>
-      <c r="F27" s="76"/>
-      <c r="G27" s="76"/>
-      <c r="H27" s="76"/>
-      <c r="I27" s="76"/>
-      <c r="J27" s="77"/>
+      <c r="B27" s="87"/>
+      <c r="C27" s="87"/>
+      <c r="D27" s="87"/>
+      <c r="E27" s="87"/>
+      <c r="F27" s="87"/>
+      <c r="G27" s="87"/>
+      <c r="H27" s="87"/>
+      <c r="I27" s="87"/>
+      <c r="J27" s="88"/>
     </row>
     <row r="28" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A28" s="49"/>
-      <c r="B28" s="76"/>
-      <c r="C28" s="76"/>
-      <c r="D28" s="76"/>
-      <c r="E28" s="76"/>
-      <c r="F28" s="76"/>
-      <c r="G28" s="76"/>
-      <c r="H28" s="76"/>
-      <c r="I28" s="76"/>
-      <c r="J28" s="77"/>
+      <c r="B28" s="87"/>
+      <c r="C28" s="87"/>
+      <c r="D28" s="87"/>
+      <c r="E28" s="87"/>
+      <c r="F28" s="87"/>
+      <c r="G28" s="87"/>
+      <c r="H28" s="87"/>
+      <c r="I28" s="87"/>
+      <c r="J28" s="88"/>
     </row>
     <row r="29" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A29" s="49"/>
-      <c r="B29" s="76"/>
-      <c r="C29" s="76"/>
-      <c r="D29" s="76"/>
-      <c r="E29" s="76"/>
-      <c r="F29" s="76"/>
-      <c r="G29" s="76"/>
-      <c r="H29" s="76"/>
-      <c r="I29" s="76"/>
-      <c r="J29" s="77"/>
+      <c r="B29" s="87"/>
+      <c r="C29" s="87"/>
+      <c r="D29" s="87"/>
+      <c r="E29" s="87"/>
+      <c r="F29" s="87"/>
+      <c r="G29" s="87"/>
+      <c r="H29" s="87"/>
+      <c r="I29" s="87"/>
+      <c r="J29" s="88"/>
     </row>
     <row r="30" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A30" s="49"/>
-      <c r="B30" s="76"/>
-      <c r="C30" s="76"/>
-      <c r="D30" s="76"/>
-      <c r="E30" s="76"/>
-      <c r="F30" s="76"/>
-      <c r="G30" s="76"/>
-      <c r="H30" s="76"/>
-      <c r="I30" s="76"/>
-      <c r="J30" s="77"/>
+      <c r="B30" s="87"/>
+      <c r="C30" s="87"/>
+      <c r="D30" s="87"/>
+      <c r="E30" s="87"/>
+      <c r="F30" s="87"/>
+      <c r="G30" s="87"/>
+      <c r="H30" s="87"/>
+      <c r="I30" s="87"/>
+      <c r="J30" s="88"/>
     </row>
     <row r="31" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A31" s="49"/>
-      <c r="B31" s="76"/>
-      <c r="C31" s="76"/>
-      <c r="D31" s="76"/>
-      <c r="E31" s="76"/>
-      <c r="F31" s="76"/>
-      <c r="G31" s="76"/>
-      <c r="H31" s="76"/>
-      <c r="I31" s="76"/>
-      <c r="J31" s="77"/>
+      <c r="B31" s="87"/>
+      <c r="C31" s="87"/>
+      <c r="D31" s="87"/>
+      <c r="E31" s="87"/>
+      <c r="F31" s="87"/>
+      <c r="G31" s="87"/>
+      <c r="H31" s="87"/>
+      <c r="I31" s="87"/>
+      <c r="J31" s="88"/>
     </row>
     <row r="32" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A32" s="49"/>
-      <c r="B32" s="76"/>
-      <c r="C32" s="76"/>
-      <c r="D32" s="76"/>
-      <c r="E32" s="76"/>
-      <c r="F32" s="76"/>
-      <c r="G32" s="76"/>
-      <c r="H32" s="76"/>
-      <c r="I32" s="76"/>
-      <c r="J32" s="77"/>
+      <c r="B32" s="87"/>
+      <c r="C32" s="87"/>
+      <c r="D32" s="87"/>
+      <c r="E32" s="87"/>
+      <c r="F32" s="87"/>
+      <c r="G32" s="87"/>
+      <c r="H32" s="87"/>
+      <c r="I32" s="87"/>
+      <c r="J32" s="88"/>
     </row>
     <row r="33" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A33" s="49"/>
-      <c r="B33" s="76"/>
-      <c r="C33" s="76"/>
-      <c r="D33" s="76"/>
-      <c r="E33" s="76"/>
-      <c r="F33" s="76"/>
-      <c r="G33" s="76"/>
-      <c r="H33" s="76"/>
-      <c r="I33" s="76"/>
-      <c r="J33" s="77"/>
+      <c r="B33" s="87"/>
+      <c r="C33" s="87"/>
+      <c r="D33" s="87"/>
+      <c r="E33" s="87"/>
+      <c r="F33" s="87"/>
+      <c r="G33" s="87"/>
+      <c r="H33" s="87"/>
+      <c r="I33" s="87"/>
+      <c r="J33" s="88"/>
     </row>
     <row r="34" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A34" s="49"/>
-      <c r="B34" s="76"/>
-      <c r="C34" s="76"/>
-      <c r="D34" s="76"/>
-      <c r="E34" s="76"/>
-      <c r="F34" s="76"/>
-      <c r="G34" s="76"/>
-      <c r="H34" s="76"/>
-      <c r="I34" s="76"/>
-      <c r="J34" s="77"/>
+      <c r="B34" s="87"/>
+      <c r="C34" s="87"/>
+      <c r="D34" s="87"/>
+      <c r="E34" s="87"/>
+      <c r="F34" s="87"/>
+      <c r="G34" s="87"/>
+      <c r="H34" s="87"/>
+      <c r="I34" s="87"/>
+      <c r="J34" s="88"/>
     </row>
     <row r="35" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A35" s="49"/>
-      <c r="B35" s="76"/>
-      <c r="C35" s="76"/>
-      <c r="D35" s="76"/>
-      <c r="E35" s="76"/>
-      <c r="F35" s="76"/>
-      <c r="G35" s="76"/>
-      <c r="H35" s="76"/>
-      <c r="I35" s="76"/>
-      <c r="J35" s="77"/>
+      <c r="B35" s="87"/>
+      <c r="C35" s="87"/>
+      <c r="D35" s="87"/>
+      <c r="E35" s="87"/>
+      <c r="F35" s="87"/>
+      <c r="G35" s="87"/>
+      <c r="H35" s="87"/>
+      <c r="I35" s="87"/>
+      <c r="J35" s="88"/>
     </row>
     <row r="36" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A36" s="49"/>
-      <c r="B36" s="76"/>
-      <c r="C36" s="76"/>
-      <c r="D36" s="76"/>
-      <c r="E36" s="76"/>
-      <c r="F36" s="76"/>
-      <c r="G36" s="76"/>
-      <c r="H36" s="76"/>
-      <c r="I36" s="76"/>
-      <c r="J36" s="77"/>
+      <c r="B36" s="87"/>
+      <c r="C36" s="87"/>
+      <c r="D36" s="87"/>
+      <c r="E36" s="87"/>
+      <c r="F36" s="87"/>
+      <c r="G36" s="87"/>
+      <c r="H36" s="87"/>
+      <c r="I36" s="87"/>
+      <c r="J36" s="88"/>
     </row>
     <row r="37" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A37" s="49"/>
-      <c r="B37" s="76"/>
-      <c r="C37" s="76"/>
-      <c r="D37" s="76"/>
-      <c r="E37" s="76"/>
-      <c r="F37" s="76"/>
-      <c r="G37" s="76"/>
-      <c r="H37" s="76"/>
-      <c r="I37" s="76"/>
-      <c r="J37" s="77"/>
+      <c r="B37" s="87"/>
+      <c r="C37" s="87"/>
+      <c r="D37" s="87"/>
+      <c r="E37" s="87"/>
+      <c r="F37" s="87"/>
+      <c r="G37" s="87"/>
+      <c r="H37" s="87"/>
+      <c r="I37" s="87"/>
+      <c r="J37" s="88"/>
     </row>
     <row r="38" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A38" s="49"/>
-      <c r="B38" s="76"/>
-      <c r="C38" s="76"/>
-      <c r="D38" s="76"/>
-      <c r="E38" s="76"/>
-      <c r="F38" s="76"/>
-      <c r="G38" s="76"/>
-      <c r="H38" s="76"/>
-      <c r="I38" s="76"/>
-      <c r="J38" s="77"/>
+      <c r="B38" s="87"/>
+      <c r="C38" s="87"/>
+      <c r="D38" s="87"/>
+      <c r="E38" s="87"/>
+      <c r="F38" s="87"/>
+      <c r="G38" s="87"/>
+      <c r="H38" s="87"/>
+      <c r="I38" s="87"/>
+      <c r="J38" s="88"/>
     </row>
     <row r="39" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A39" s="49"/>
-      <c r="B39" s="76"/>
-      <c r="C39" s="76"/>
-      <c r="D39" s="76"/>
-      <c r="E39" s="76"/>
-      <c r="F39" s="76"/>
-      <c r="G39" s="76"/>
-      <c r="H39" s="76"/>
-      <c r="I39" s="76"/>
-      <c r="J39" s="77"/>
+      <c r="B39" s="87"/>
+      <c r="C39" s="87"/>
+      <c r="D39" s="87"/>
+      <c r="E39" s="87"/>
+      <c r="F39" s="87"/>
+      <c r="G39" s="87"/>
+      <c r="H39" s="87"/>
+      <c r="I39" s="87"/>
+      <c r="J39" s="88"/>
     </row>
     <row r="40" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A40" s="49"/>
-      <c r="B40" s="76"/>
-      <c r="C40" s="76"/>
-      <c r="D40" s="76"/>
-      <c r="E40" s="76"/>
-      <c r="F40" s="76"/>
-      <c r="G40" s="76"/>
-      <c r="H40" s="76"/>
-      <c r="I40" s="76"/>
-      <c r="J40" s="77"/>
+      <c r="B40" s="87"/>
+      <c r="C40" s="87"/>
+      <c r="D40" s="87"/>
+      <c r="E40" s="87"/>
+      <c r="F40" s="87"/>
+      <c r="G40" s="87"/>
+      <c r="H40" s="87"/>
+      <c r="I40" s="87"/>
+      <c r="J40" s="88"/>
     </row>
     <row r="41" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A41" s="49"/>
-      <c r="B41" s="76"/>
-      <c r="C41" s="76"/>
-      <c r="D41" s="76"/>
-      <c r="E41" s="76"/>
-      <c r="F41" s="76"/>
-      <c r="G41" s="76"/>
-      <c r="H41" s="76"/>
-      <c r="I41" s="76"/>
-      <c r="J41" s="77"/>
+      <c r="B41" s="87"/>
+      <c r="C41" s="87"/>
+      <c r="D41" s="87"/>
+      <c r="E41" s="87"/>
+      <c r="F41" s="87"/>
+      <c r="G41" s="87"/>
+      <c r="H41" s="87"/>
+      <c r="I41" s="87"/>
+      <c r="J41" s="88"/>
     </row>
     <row r="42" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A42" s="49"/>
-      <c r="B42" s="76"/>
-      <c r="C42" s="76"/>
-      <c r="D42" s="76"/>
-      <c r="E42" s="76"/>
-      <c r="F42" s="76"/>
-      <c r="G42" s="76"/>
-      <c r="H42" s="76"/>
-      <c r="I42" s="76"/>
-      <c r="J42" s="77"/>
+      <c r="B42" s="87"/>
+      <c r="C42" s="87"/>
+      <c r="D42" s="87"/>
+      <c r="E42" s="87"/>
+      <c r="F42" s="87"/>
+      <c r="G42" s="87"/>
+      <c r="H42" s="87"/>
+      <c r="I42" s="87"/>
+      <c r="J42" s="88"/>
     </row>
     <row r="43" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A43" s="49"/>
-      <c r="B43" s="76"/>
-      <c r="C43" s="76"/>
-      <c r="D43" s="76"/>
-      <c r="E43" s="76"/>
-      <c r="F43" s="76"/>
-      <c r="G43" s="76"/>
-      <c r="H43" s="76"/>
-      <c r="I43" s="76"/>
-      <c r="J43" s="77"/>
+      <c r="B43" s="87"/>
+      <c r="C43" s="87"/>
+      <c r="D43" s="87"/>
+      <c r="E43" s="87"/>
+      <c r="F43" s="87"/>
+      <c r="G43" s="87"/>
+      <c r="H43" s="87"/>
+      <c r="I43" s="87"/>
+      <c r="J43" s="88"/>
     </row>
     <row r="44" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A44" s="49"/>
-      <c r="B44" s="76"/>
-      <c r="C44" s="76"/>
-      <c r="D44" s="76"/>
-      <c r="E44" s="76"/>
-      <c r="F44" s="76"/>
-      <c r="G44" s="76"/>
-      <c r="H44" s="76"/>
-      <c r="I44" s="76"/>
-      <c r="J44" s="77"/>
+      <c r="B44" s="87"/>
+      <c r="C44" s="87"/>
+      <c r="D44" s="87"/>
+      <c r="E44" s="87"/>
+      <c r="F44" s="87"/>
+      <c r="G44" s="87"/>
+      <c r="H44" s="87"/>
+      <c r="I44" s="87"/>
+      <c r="J44" s="88"/>
     </row>
     <row r="45" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A45" s="49"/>
-      <c r="B45" s="76"/>
-      <c r="C45" s="76"/>
-      <c r="D45" s="76"/>
-      <c r="E45" s="76"/>
-      <c r="F45" s="76"/>
-      <c r="G45" s="76"/>
-      <c r="H45" s="76"/>
-      <c r="I45" s="76"/>
-      <c r="J45" s="77"/>
+      <c r="B45" s="87"/>
+      <c r="C45" s="87"/>
+      <c r="D45" s="87"/>
+      <c r="E45" s="87"/>
+      <c r="F45" s="87"/>
+      <c r="G45" s="87"/>
+      <c r="H45" s="87"/>
+      <c r="I45" s="87"/>
+      <c r="J45" s="88"/>
     </row>
     <row r="46" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A46" s="49"/>
-      <c r="B46" s="76"/>
-      <c r="C46" s="76"/>
-      <c r="D46" s="76"/>
-      <c r="E46" s="76"/>
-      <c r="F46" s="76"/>
-      <c r="G46" s="76"/>
-      <c r="H46" s="76"/>
-      <c r="I46" s="76"/>
-      <c r="J46" s="77"/>
+      <c r="B46" s="87"/>
+      <c r="C46" s="87"/>
+      <c r="D46" s="87"/>
+      <c r="E46" s="87"/>
+      <c r="F46" s="87"/>
+      <c r="G46" s="87"/>
+      <c r="H46" s="87"/>
+      <c r="I46" s="87"/>
+      <c r="J46" s="88"/>
     </row>
     <row r="47" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A47" s="49"/>
-      <c r="B47" s="76"/>
-      <c r="C47" s="76"/>
-      <c r="D47" s="76"/>
-      <c r="E47" s="76"/>
-      <c r="F47" s="76"/>
-      <c r="G47" s="76"/>
-      <c r="H47" s="76"/>
-      <c r="I47" s="76"/>
-      <c r="J47" s="77"/>
+      <c r="B47" s="87"/>
+      <c r="C47" s="87"/>
+      <c r="D47" s="87"/>
+      <c r="E47" s="87"/>
+      <c r="F47" s="87"/>
+      <c r="G47" s="87"/>
+      <c r="H47" s="87"/>
+      <c r="I47" s="87"/>
+      <c r="J47" s="88"/>
     </row>
     <row r="48" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A48" s="49"/>
-      <c r="B48" s="76"/>
-      <c r="C48" s="76"/>
-      <c r="D48" s="76"/>
-      <c r="E48" s="76"/>
-      <c r="F48" s="76"/>
-      <c r="G48" s="76"/>
-      <c r="H48" s="76"/>
-      <c r="I48" s="76"/>
-      <c r="J48" s="77"/>
+      <c r="B48" s="87"/>
+      <c r="C48" s="87"/>
+      <c r="D48" s="87"/>
+      <c r="E48" s="87"/>
+      <c r="F48" s="87"/>
+      <c r="G48" s="87"/>
+      <c r="H48" s="87"/>
+      <c r="I48" s="87"/>
+      <c r="J48" s="88"/>
     </row>
     <row r="49" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A49" s="49"/>
-      <c r="B49" s="76"/>
-      <c r="C49" s="76"/>
-      <c r="D49" s="76"/>
-      <c r="E49" s="76"/>
-      <c r="F49" s="76"/>
-      <c r="G49" s="76"/>
-      <c r="H49" s="76"/>
-      <c r="I49" s="76"/>
-      <c r="J49" s="77"/>
+      <c r="B49" s="87"/>
+      <c r="C49" s="87"/>
+      <c r="D49" s="87"/>
+      <c r="E49" s="87"/>
+      <c r="F49" s="87"/>
+      <c r="G49" s="87"/>
+      <c r="H49" s="87"/>
+      <c r="I49" s="87"/>
+      <c r="J49" s="88"/>
     </row>
     <row r="50" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A50" s="49"/>
-      <c r="B50" s="76"/>
-      <c r="C50" s="76"/>
-      <c r="D50" s="76"/>
-      <c r="E50" s="76"/>
-      <c r="F50" s="76"/>
-      <c r="G50" s="76"/>
-      <c r="H50" s="76"/>
-      <c r="I50" s="76"/>
-      <c r="J50" s="77"/>
+      <c r="B50" s="87"/>
+      <c r="C50" s="87"/>
+      <c r="D50" s="87"/>
+      <c r="E50" s="87"/>
+      <c r="F50" s="87"/>
+      <c r="G50" s="87"/>
+      <c r="H50" s="87"/>
+      <c r="I50" s="87"/>
+      <c r="J50" s="88"/>
     </row>
     <row r="51" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A51" s="49"/>
-      <c r="B51" s="76"/>
-      <c r="C51" s="76"/>
-      <c r="D51" s="76"/>
-      <c r="E51" s="76"/>
-      <c r="F51" s="76"/>
-      <c r="G51" s="76"/>
-      <c r="H51" s="76"/>
-      <c r="I51" s="76"/>
-      <c r="J51" s="77"/>
+      <c r="B51" s="87"/>
+      <c r="C51" s="87"/>
+      <c r="D51" s="87"/>
+      <c r="E51" s="87"/>
+      <c r="F51" s="87"/>
+      <c r="G51" s="87"/>
+      <c r="H51" s="87"/>
+      <c r="I51" s="87"/>
+      <c r="J51" s="88"/>
     </row>
     <row r="52" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A52" s="49"/>
-      <c r="B52" s="76"/>
-      <c r="C52" s="76"/>
-      <c r="D52" s="76"/>
-      <c r="E52" s="76"/>
-      <c r="F52" s="76"/>
-      <c r="G52" s="76"/>
-      <c r="H52" s="76"/>
-      <c r="I52" s="76"/>
-      <c r="J52" s="77"/>
+      <c r="B52" s="87"/>
+      <c r="C52" s="87"/>
+      <c r="D52" s="87"/>
+      <c r="E52" s="87"/>
+      <c r="F52" s="87"/>
+      <c r="G52" s="87"/>
+      <c r="H52" s="87"/>
+      <c r="I52" s="87"/>
+      <c r="J52" s="88"/>
     </row>
     <row r="53" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A53" s="49"/>
-      <c r="B53" s="76"/>
-      <c r="C53" s="76"/>
-      <c r="D53" s="76"/>
-      <c r="E53" s="76"/>
-      <c r="F53" s="76"/>
-      <c r="G53" s="76"/>
-      <c r="H53" s="76"/>
-      <c r="I53" s="76"/>
-      <c r="J53" s="77"/>
+      <c r="B53" s="87"/>
+      <c r="C53" s="87"/>
+      <c r="D53" s="87"/>
+      <c r="E53" s="87"/>
+      <c r="F53" s="87"/>
+      <c r="G53" s="87"/>
+      <c r="H53" s="87"/>
+      <c r="I53" s="87"/>
+      <c r="J53" s="88"/>
     </row>
     <row r="54" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A54" s="49"/>
-      <c r="B54" s="76"/>
-      <c r="C54" s="76"/>
-      <c r="D54" s="76"/>
-      <c r="E54" s="76"/>
-      <c r="F54" s="76"/>
-      <c r="G54" s="76"/>
-      <c r="H54" s="76"/>
-      <c r="I54" s="76"/>
-      <c r="J54" s="77"/>
+      <c r="B54" s="87"/>
+      <c r="C54" s="87"/>
+      <c r="D54" s="87"/>
+      <c r="E54" s="87"/>
+      <c r="F54" s="87"/>
+      <c r="G54" s="87"/>
+      <c r="H54" s="87"/>
+      <c r="I54" s="87"/>
+      <c r="J54" s="88"/>
     </row>
     <row r="55" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A55" s="49"/>
-      <c r="B55" s="76"/>
-      <c r="C55" s="76"/>
-      <c r="D55" s="76"/>
-      <c r="E55" s="76"/>
-      <c r="F55" s="76"/>
-      <c r="G55" s="76"/>
-      <c r="H55" s="76"/>
-      <c r="I55" s="76"/>
-      <c r="J55" s="77"/>
+      <c r="B55" s="87"/>
+      <c r="C55" s="87"/>
+      <c r="D55" s="87"/>
+      <c r="E55" s="87"/>
+      <c r="F55" s="87"/>
+      <c r="G55" s="87"/>
+      <c r="H55" s="87"/>
+      <c r="I55" s="87"/>
+      <c r="J55" s="88"/>
     </row>
     <row r="56" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A56" s="49"/>
-      <c r="B56" s="76"/>
-      <c r="C56" s="76"/>
-      <c r="D56" s="76"/>
-      <c r="E56" s="76"/>
-      <c r="F56" s="76"/>
-      <c r="G56" s="76"/>
-      <c r="H56" s="76"/>
-      <c r="I56" s="76"/>
-      <c r="J56" s="77"/>
+      <c r="B56" s="87"/>
+      <c r="C56" s="87"/>
+      <c r="D56" s="87"/>
+      <c r="E56" s="87"/>
+      <c r="F56" s="87"/>
+      <c r="G56" s="87"/>
+      <c r="H56" s="87"/>
+      <c r="I56" s="87"/>
+      <c r="J56" s="88"/>
     </row>
     <row r="57" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A57" s="49"/>
-      <c r="B57" s="76"/>
-      <c r="C57" s="76"/>
-      <c r="D57" s="76"/>
-      <c r="E57" s="76"/>
-      <c r="F57" s="76"/>
-      <c r="G57" s="76"/>
-      <c r="H57" s="76"/>
-      <c r="I57" s="76"/>
-      <c r="J57" s="77"/>
+      <c r="B57" s="87"/>
+      <c r="C57" s="87"/>
+      <c r="D57" s="87"/>
+      <c r="E57" s="87"/>
+      <c r="F57" s="87"/>
+      <c r="G57" s="87"/>
+      <c r="H57" s="87"/>
+      <c r="I57" s="87"/>
+      <c r="J57" s="88"/>
     </row>
     <row r="58" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A58" s="49"/>
-      <c r="B58" s="76"/>
-      <c r="C58" s="76"/>
-      <c r="D58" s="76"/>
-      <c r="E58" s="76"/>
-      <c r="F58" s="76"/>
-      <c r="G58" s="76"/>
-      <c r="H58" s="76"/>
-      <c r="I58" s="76"/>
-      <c r="J58" s="77"/>
+      <c r="B58" s="87"/>
+      <c r="C58" s="87"/>
+      <c r="D58" s="87"/>
+      <c r="E58" s="87"/>
+      <c r="F58" s="87"/>
+      <c r="G58" s="87"/>
+      <c r="H58" s="87"/>
+      <c r="I58" s="87"/>
+      <c r="J58" s="88"/>
     </row>
     <row r="59" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A59" s="49"/>
-      <c r="B59" s="76"/>
-      <c r="C59" s="76"/>
-      <c r="D59" s="76"/>
-      <c r="E59" s="76"/>
-      <c r="F59" s="76"/>
-      <c r="G59" s="76"/>
-      <c r="H59" s="76"/>
-      <c r="I59" s="76"/>
-      <c r="J59" s="77"/>
+      <c r="B59" s="87"/>
+      <c r="C59" s="87"/>
+      <c r="D59" s="87"/>
+      <c r="E59" s="87"/>
+      <c r="F59" s="87"/>
+      <c r="G59" s="87"/>
+      <c r="H59" s="87"/>
+      <c r="I59" s="87"/>
+      <c r="J59" s="88"/>
     </row>
     <row r="60" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A60" s="49"/>
-      <c r="B60" s="76"/>
-      <c r="C60" s="76"/>
-      <c r="D60" s="76"/>
-      <c r="E60" s="76"/>
-      <c r="F60" s="76"/>
-      <c r="G60" s="76"/>
-      <c r="H60" s="76"/>
-      <c r="I60" s="76"/>
-      <c r="J60" s="77"/>
+      <c r="B60" s="87"/>
+      <c r="C60" s="87"/>
+      <c r="D60" s="87"/>
+      <c r="E60" s="87"/>
+      <c r="F60" s="87"/>
+      <c r="G60" s="87"/>
+      <c r="H60" s="87"/>
+      <c r="I60" s="87"/>
+      <c r="J60" s="88"/>
     </row>
     <row r="61" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A61" s="49"/>
-      <c r="B61" s="76"/>
-      <c r="C61" s="76"/>
-      <c r="D61" s="76"/>
-      <c r="E61" s="76"/>
-      <c r="F61" s="76"/>
-      <c r="G61" s="76"/>
-      <c r="H61" s="76"/>
-      <c r="I61" s="76"/>
-      <c r="J61" s="77"/>
+      <c r="B61" s="87"/>
+      <c r="C61" s="87"/>
+      <c r="D61" s="87"/>
+      <c r="E61" s="87"/>
+      <c r="F61" s="87"/>
+      <c r="G61" s="87"/>
+      <c r="H61" s="87"/>
+      <c r="I61" s="87"/>
+      <c r="J61" s="88"/>
     </row>
     <row r="62" spans="1:10" ht="13.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A62" s="50"/>
-      <c r="B62" s="78"/>
-      <c r="C62" s="78"/>
-      <c r="D62" s="78"/>
-      <c r="E62" s="78"/>
-      <c r="F62" s="78"/>
-      <c r="G62" s="78"/>
-      <c r="H62" s="78"/>
-      <c r="I62" s="78"/>
-      <c r="J62" s="79"/>
+      <c r="B62" s="89"/>
+      <c r="C62" s="89"/>
+      <c r="D62" s="89"/>
+      <c r="E62" s="89"/>
+      <c r="F62" s="89"/>
+      <c r="G62" s="89"/>
+      <c r="H62" s="89"/>
+      <c r="I62" s="89"/>
+      <c r="J62" s="90"/>
     </row>
     <row r="63" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A63" s="48">
+      <c r="A63" s="47">
         <v>4</v>
       </c>
-      <c r="B63" s="55" t="s">
+      <c r="B63" s="51" t="s">
         <v>6</v>
       </c>
-      <c r="C63" s="55"/>
-      <c r="D63" s="55"/>
-      <c r="E63" s="55"/>
-      <c r="F63" s="55"/>
-      <c r="G63" s="55"/>
-      <c r="H63" s="55"/>
-      <c r="I63" s="55"/>
-      <c r="J63" s="87"/>
+      <c r="C63" s="51"/>
+      <c r="D63" s="51"/>
+      <c r="E63" s="51"/>
+      <c r="F63" s="51"/>
+      <c r="G63" s="51"/>
+      <c r="H63" s="51"/>
+      <c r="I63" s="51"/>
+      <c r="J63" s="52"/>
     </row>
     <row r="64" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A64" s="49"/>
-      <c r="B64" s="51" t="s">
+      <c r="B64" s="91" t="s">
         <v>7</v>
       </c>
-      <c r="C64" s="51"/>
-      <c r="D64" s="44" t="s">
+      <c r="C64" s="91"/>
+      <c r="D64" s="53" t="s">
         <v>74</v>
       </c>
-      <c r="E64" s="44"/>
-      <c r="F64" s="44"/>
-      <c r="G64" s="44"/>
-      <c r="H64" s="44"/>
-      <c r="I64" s="44"/>
-      <c r="J64" s="65"/>
+      <c r="E64" s="53"/>
+      <c r="F64" s="53"/>
+      <c r="G64" s="53"/>
+      <c r="H64" s="53"/>
+      <c r="I64" s="53"/>
+      <c r="J64" s="54"/>
     </row>
     <row r="65" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A65" s="49"/>
-      <c r="B65" s="51" t="s">
+      <c r="B65" s="91" t="s">
         <v>8</v>
       </c>
-      <c r="C65" s="51"/>
-      <c r="D65" s="44" t="s">
+      <c r="C65" s="91"/>
+      <c r="D65" s="53" t="s">
         <v>72</v>
       </c>
-      <c r="E65" s="44"/>
-      <c r="F65" s="44"/>
-      <c r="G65" s="44"/>
-      <c r="H65" s="44"/>
-      <c r="I65" s="44"/>
-      <c r="J65" s="65"/>
+      <c r="E65" s="53"/>
+      <c r="F65" s="53"/>
+      <c r="G65" s="53"/>
+      <c r="H65" s="53"/>
+      <c r="I65" s="53"/>
+      <c r="J65" s="54"/>
     </row>
     <row r="66" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A66" s="49"/>
-      <c r="B66" s="51" t="s">
+      <c r="B66" s="91" t="s">
         <v>9</v>
       </c>
-      <c r="C66" s="51"/>
-      <c r="D66" s="44" t="s">
+      <c r="C66" s="91"/>
+      <c r="D66" s="53" t="s">
         <v>71</v>
       </c>
-      <c r="E66" s="44"/>
-      <c r="F66" s="44"/>
-      <c r="G66" s="44"/>
-      <c r="H66" s="44"/>
-      <c r="I66" s="44"/>
-      <c r="J66" s="65"/>
+      <c r="E66" s="53"/>
+      <c r="F66" s="53"/>
+      <c r="G66" s="53"/>
+      <c r="H66" s="53"/>
+      <c r="I66" s="53"/>
+      <c r="J66" s="54"/>
     </row>
     <row r="67" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A67" s="49"/>
-      <c r="B67" s="51" t="s">
+      <c r="B67" s="91" t="s">
         <v>68</v>
       </c>
-      <c r="C67" s="51"/>
-      <c r="D67" s="44" t="s">
+      <c r="C67" s="91"/>
+      <c r="D67" s="53" t="s">
         <v>73</v>
       </c>
-      <c r="E67" s="44"/>
-      <c r="F67" s="44"/>
-      <c r="G67" s="44"/>
-      <c r="H67" s="44"/>
-      <c r="I67" s="44"/>
-      <c r="J67" s="65"/>
+      <c r="E67" s="53"/>
+      <c r="F67" s="53"/>
+      <c r="G67" s="53"/>
+      <c r="H67" s="53"/>
+      <c r="I67" s="53"/>
+      <c r="J67" s="54"/>
     </row>
     <row r="68" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A68" s="49"/>
-      <c r="B68" s="51" t="s">
+      <c r="B68" s="91" t="s">
         <v>10</v>
       </c>
-      <c r="C68" s="51"/>
-      <c r="D68" s="51"/>
-      <c r="E68" s="51"/>
-      <c r="F68" s="51"/>
-      <c r="G68" s="51"/>
-      <c r="H68" s="51"/>
-      <c r="I68" s="51"/>
-      <c r="J68" s="80"/>
+      <c r="C68" s="91"/>
+      <c r="D68" s="91"/>
+      <c r="E68" s="91"/>
+      <c r="F68" s="91"/>
+      <c r="G68" s="91"/>
+      <c r="H68" s="91"/>
+      <c r="I68" s="91"/>
+      <c r="J68" s="92"/>
     </row>
     <row r="69" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A69" s="49"/>
-      <c r="B69" s="61"/>
-      <c r="C69" s="61"/>
-      <c r="D69" s="61"/>
-      <c r="E69" s="61"/>
-      <c r="F69" s="61"/>
-      <c r="G69" s="61"/>
-      <c r="H69" s="61"/>
-      <c r="I69" s="61"/>
-      <c r="J69" s="62"/>
+      <c r="B69" s="78"/>
+      <c r="C69" s="78"/>
+      <c r="D69" s="78"/>
+      <c r="E69" s="78"/>
+      <c r="F69" s="78"/>
+      <c r="G69" s="78"/>
+      <c r="H69" s="78"/>
+      <c r="I69" s="78"/>
+      <c r="J69" s="79"/>
     </row>
     <row r="70" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A70" s="49"/>
-      <c r="B70" s="61"/>
-      <c r="C70" s="61"/>
-      <c r="D70" s="61"/>
-      <c r="E70" s="61"/>
-      <c r="F70" s="61"/>
-      <c r="G70" s="61"/>
-      <c r="H70" s="61"/>
-      <c r="I70" s="61"/>
-      <c r="J70" s="62"/>
+      <c r="B70" s="78"/>
+      <c r="C70" s="78"/>
+      <c r="D70" s="78"/>
+      <c r="E70" s="78"/>
+      <c r="F70" s="78"/>
+      <c r="G70" s="78"/>
+      <c r="H70" s="78"/>
+      <c r="I70" s="78"/>
+      <c r="J70" s="79"/>
     </row>
     <row r="71" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A71" s="49"/>
-      <c r="B71" s="61"/>
-      <c r="C71" s="61"/>
-      <c r="D71" s="61"/>
-      <c r="E71" s="61"/>
-      <c r="F71" s="61"/>
-      <c r="G71" s="61"/>
-      <c r="H71" s="61"/>
-      <c r="I71" s="61"/>
-      <c r="J71" s="62"/>
+      <c r="B71" s="78"/>
+      <c r="C71" s="78"/>
+      <c r="D71" s="78"/>
+      <c r="E71" s="78"/>
+      <c r="F71" s="78"/>
+      <c r="G71" s="78"/>
+      <c r="H71" s="78"/>
+      <c r="I71" s="78"/>
+      <c r="J71" s="79"/>
     </row>
     <row r="72" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A72" s="49"/>
-      <c r="B72" s="61"/>
-      <c r="C72" s="61"/>
-      <c r="D72" s="61"/>
-      <c r="E72" s="61"/>
-      <c r="F72" s="61"/>
-      <c r="G72" s="61"/>
-      <c r="H72" s="61"/>
-      <c r="I72" s="61"/>
-      <c r="J72" s="62"/>
+      <c r="B72" s="78"/>
+      <c r="C72" s="78"/>
+      <c r="D72" s="78"/>
+      <c r="E72" s="78"/>
+      <c r="F72" s="78"/>
+      <c r="G72" s="78"/>
+      <c r="H72" s="78"/>
+      <c r="I72" s="78"/>
+      <c r="J72" s="79"/>
     </row>
     <row r="73" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A73" s="49"/>
-      <c r="B73" s="61"/>
-      <c r="C73" s="61"/>
-      <c r="D73" s="61"/>
-      <c r="E73" s="61"/>
-      <c r="F73" s="61"/>
-      <c r="G73" s="61"/>
-      <c r="H73" s="61"/>
-      <c r="I73" s="61"/>
-      <c r="J73" s="62"/>
+      <c r="B73" s="78"/>
+      <c r="C73" s="78"/>
+      <c r="D73" s="78"/>
+      <c r="E73" s="78"/>
+      <c r="F73" s="78"/>
+      <c r="G73" s="78"/>
+      <c r="H73" s="78"/>
+      <c r="I73" s="78"/>
+      <c r="J73" s="79"/>
     </row>
     <row r="74" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A74" s="49"/>
-      <c r="B74" s="61"/>
-      <c r="C74" s="61"/>
-      <c r="D74" s="61"/>
-      <c r="E74" s="61"/>
-      <c r="F74" s="61"/>
-      <c r="G74" s="61"/>
-      <c r="H74" s="61"/>
-      <c r="I74" s="61"/>
-      <c r="J74" s="62"/>
+      <c r="B74" s="78"/>
+      <c r="C74" s="78"/>
+      <c r="D74" s="78"/>
+      <c r="E74" s="78"/>
+      <c r="F74" s="78"/>
+      <c r="G74" s="78"/>
+      <c r="H74" s="78"/>
+      <c r="I74" s="78"/>
+      <c r="J74" s="79"/>
     </row>
     <row r="75" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A75" s="49"/>
-      <c r="B75" s="61"/>
-      <c r="C75" s="61"/>
-      <c r="D75" s="61"/>
-      <c r="E75" s="61"/>
-      <c r="F75" s="61"/>
-      <c r="G75" s="61"/>
-      <c r="H75" s="61"/>
-      <c r="I75" s="61"/>
-      <c r="J75" s="62"/>
+      <c r="B75" s="78"/>
+      <c r="C75" s="78"/>
+      <c r="D75" s="78"/>
+      <c r="E75" s="78"/>
+      <c r="F75" s="78"/>
+      <c r="G75" s="78"/>
+      <c r="H75" s="78"/>
+      <c r="I75" s="78"/>
+      <c r="J75" s="79"/>
     </row>
     <row r="76" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A76" s="49"/>
-      <c r="B76" s="61"/>
-      <c r="C76" s="61"/>
-      <c r="D76" s="61"/>
-      <c r="E76" s="61"/>
-      <c r="F76" s="61"/>
-      <c r="G76" s="61"/>
-      <c r="H76" s="61"/>
-      <c r="I76" s="61"/>
-      <c r="J76" s="62"/>
+      <c r="B76" s="78"/>
+      <c r="C76" s="78"/>
+      <c r="D76" s="78"/>
+      <c r="E76" s="78"/>
+      <c r="F76" s="78"/>
+      <c r="G76" s="78"/>
+      <c r="H76" s="78"/>
+      <c r="I76" s="78"/>
+      <c r="J76" s="79"/>
     </row>
     <row r="77" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A77" s="49"/>
-      <c r="B77" s="61"/>
-      <c r="C77" s="61"/>
-      <c r="D77" s="61"/>
-      <c r="E77" s="61"/>
-      <c r="F77" s="61"/>
-      <c r="G77" s="61"/>
-      <c r="H77" s="61"/>
-      <c r="I77" s="61"/>
-      <c r="J77" s="62"/>
+      <c r="B77" s="78"/>
+      <c r="C77" s="78"/>
+      <c r="D77" s="78"/>
+      <c r="E77" s="78"/>
+      <c r="F77" s="78"/>
+      <c r="G77" s="78"/>
+      <c r="H77" s="78"/>
+      <c r="I77" s="78"/>
+      <c r="J77" s="79"/>
     </row>
     <row r="78" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A78" s="49"/>
-      <c r="B78" s="61"/>
-      <c r="C78" s="61"/>
-      <c r="D78" s="61"/>
-      <c r="E78" s="61"/>
-      <c r="F78" s="61"/>
-      <c r="G78" s="61"/>
-      <c r="H78" s="61"/>
-      <c r="I78" s="61"/>
-      <c r="J78" s="62"/>
+      <c r="B78" s="78"/>
+      <c r="C78" s="78"/>
+      <c r="D78" s="78"/>
+      <c r="E78" s="78"/>
+      <c r="F78" s="78"/>
+      <c r="G78" s="78"/>
+      <c r="H78" s="78"/>
+      <c r="I78" s="78"/>
+      <c r="J78" s="79"/>
     </row>
     <row r="79" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A79" s="49"/>
-      <c r="B79" s="61"/>
-      <c r="C79" s="61"/>
-      <c r="D79" s="61"/>
-      <c r="E79" s="61"/>
-      <c r="F79" s="61"/>
-      <c r="G79" s="61"/>
-      <c r="H79" s="61"/>
-      <c r="I79" s="61"/>
-      <c r="J79" s="62"/>
+      <c r="B79" s="78"/>
+      <c r="C79" s="78"/>
+      <c r="D79" s="78"/>
+      <c r="E79" s="78"/>
+      <c r="F79" s="78"/>
+      <c r="G79" s="78"/>
+      <c r="H79" s="78"/>
+      <c r="I79" s="78"/>
+      <c r="J79" s="79"/>
     </row>
     <row r="80" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A80" s="49"/>
-      <c r="B80" s="61"/>
-      <c r="C80" s="61"/>
-      <c r="D80" s="61"/>
-      <c r="E80" s="61"/>
-      <c r="F80" s="61"/>
-      <c r="G80" s="61"/>
-      <c r="H80" s="61"/>
-      <c r="I80" s="61"/>
-      <c r="J80" s="62"/>
+      <c r="B80" s="78"/>
+      <c r="C80" s="78"/>
+      <c r="D80" s="78"/>
+      <c r="E80" s="78"/>
+      <c r="F80" s="78"/>
+      <c r="G80" s="78"/>
+      <c r="H80" s="78"/>
+      <c r="I80" s="78"/>
+      <c r="J80" s="79"/>
     </row>
     <row r="81" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A81" s="49"/>
-      <c r="B81" s="61"/>
-      <c r="C81" s="61"/>
-      <c r="D81" s="61"/>
-      <c r="E81" s="61"/>
-      <c r="F81" s="61"/>
-      <c r="G81" s="61"/>
-      <c r="H81" s="61"/>
-      <c r="I81" s="61"/>
-      <c r="J81" s="62"/>
+      <c r="B81" s="78"/>
+      <c r="C81" s="78"/>
+      <c r="D81" s="78"/>
+      <c r="E81" s="78"/>
+      <c r="F81" s="78"/>
+      <c r="G81" s="78"/>
+      <c r="H81" s="78"/>
+      <c r="I81" s="78"/>
+      <c r="J81" s="79"/>
     </row>
     <row r="82" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A82" s="49"/>
-      <c r="B82" s="61"/>
-      <c r="C82" s="61"/>
-      <c r="D82" s="61"/>
-      <c r="E82" s="61"/>
-      <c r="F82" s="61"/>
-      <c r="G82" s="61"/>
-      <c r="H82" s="61"/>
-      <c r="I82" s="61"/>
-      <c r="J82" s="62"/>
+      <c r="B82" s="78"/>
+      <c r="C82" s="78"/>
+      <c r="D82" s="78"/>
+      <c r="E82" s="78"/>
+      <c r="F82" s="78"/>
+      <c r="G82" s="78"/>
+      <c r="H82" s="78"/>
+      <c r="I82" s="78"/>
+      <c r="J82" s="79"/>
     </row>
     <row r="83" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A83" s="49"/>
-      <c r="B83" s="61"/>
-      <c r="C83" s="61"/>
-      <c r="D83" s="61"/>
-      <c r="E83" s="61"/>
-      <c r="F83" s="61"/>
-      <c r="G83" s="61"/>
-      <c r="H83" s="61"/>
-      <c r="I83" s="61"/>
-      <c r="J83" s="62"/>
+      <c r="B83" s="78"/>
+      <c r="C83" s="78"/>
+      <c r="D83" s="78"/>
+      <c r="E83" s="78"/>
+      <c r="F83" s="78"/>
+      <c r="G83" s="78"/>
+      <c r="H83" s="78"/>
+      <c r="I83" s="78"/>
+      <c r="J83" s="79"/>
     </row>
     <row r="84" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A84" s="49"/>
-      <c r="B84" s="61"/>
-      <c r="C84" s="61"/>
-      <c r="D84" s="61"/>
-      <c r="E84" s="61"/>
-      <c r="F84" s="61"/>
-      <c r="G84" s="61"/>
-      <c r="H84" s="61"/>
-      <c r="I84" s="61"/>
-      <c r="J84" s="62"/>
+      <c r="B84" s="78"/>
+      <c r="C84" s="78"/>
+      <c r="D84" s="78"/>
+      <c r="E84" s="78"/>
+      <c r="F84" s="78"/>
+      <c r="G84" s="78"/>
+      <c r="H84" s="78"/>
+      <c r="I84" s="78"/>
+      <c r="J84" s="79"/>
     </row>
     <row r="85" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A85" s="49"/>
-      <c r="B85" s="61"/>
-      <c r="C85" s="61"/>
-      <c r="D85" s="61"/>
-      <c r="E85" s="61"/>
-      <c r="F85" s="61"/>
-      <c r="G85" s="61"/>
-      <c r="H85" s="61"/>
-      <c r="I85" s="61"/>
-      <c r="J85" s="62"/>
+      <c r="B85" s="78"/>
+      <c r="C85" s="78"/>
+      <c r="D85" s="78"/>
+      <c r="E85" s="78"/>
+      <c r="F85" s="78"/>
+      <c r="G85" s="78"/>
+      <c r="H85" s="78"/>
+      <c r="I85" s="78"/>
+      <c r="J85" s="79"/>
     </row>
     <row r="86" spans="1:10" ht="13.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A86" s="52"/>
-      <c r="B86" s="63"/>
-      <c r="C86" s="63"/>
-      <c r="D86" s="63"/>
-      <c r="E86" s="63"/>
-      <c r="F86" s="63"/>
-      <c r="G86" s="63"/>
-      <c r="H86" s="63"/>
-      <c r="I86" s="63"/>
-      <c r="J86" s="64"/>
+      <c r="A86" s="48"/>
+      <c r="B86" s="29"/>
+      <c r="C86" s="29"/>
+      <c r="D86" s="29"/>
+      <c r="E86" s="29"/>
+      <c r="F86" s="29"/>
+      <c r="G86" s="29"/>
+      <c r="H86" s="29"/>
+      <c r="I86" s="29"/>
+      <c r="J86" s="80"/>
     </row>
     <row r="87" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A87" s="48">
+      <c r="A87" s="47">
         <v>5</v>
       </c>
-      <c r="B87" s="55" t="s">
+      <c r="B87" s="51" t="s">
         <v>11</v>
       </c>
-      <c r="C87" s="55"/>
-      <c r="D87" s="55"/>
-      <c r="E87" s="55"/>
-      <c r="F87" s="55"/>
-      <c r="G87" s="55"/>
-      <c r="H87" s="55"/>
-      <c r="I87" s="55"/>
-      <c r="J87" s="87"/>
+      <c r="C87" s="51"/>
+      <c r="D87" s="51"/>
+      <c r="E87" s="51"/>
+      <c r="F87" s="51"/>
+      <c r="G87" s="51"/>
+      <c r="H87" s="51"/>
+      <c r="I87" s="51"/>
+      <c r="J87" s="52"/>
     </row>
     <row r="88" spans="1:10" ht="13.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A88" s="49"/>
-      <c r="B88" s="33" t="s">
+      <c r="B88" s="37" t="s">
         <v>12</v>
       </c>
-      <c r="C88" s="33"/>
-      <c r="D88" s="33"/>
-      <c r="E88" s="33"/>
-      <c r="F88" s="33"/>
-      <c r="G88" s="33"/>
-      <c r="H88" s="33"/>
-      <c r="I88" s="33"/>
-      <c r="J88" s="96"/>
+      <c r="C88" s="37"/>
+      <c r="D88" s="37"/>
+      <c r="E88" s="37"/>
+      <c r="F88" s="37"/>
+      <c r="G88" s="37"/>
+      <c r="H88" s="37"/>
+      <c r="I88" s="37"/>
+      <c r="J88" s="68"/>
     </row>
     <row r="89" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A89" s="48">
+      <c r="A89" s="47">
         <v>6</v>
       </c>
-      <c r="B89" s="53" t="s">
+      <c r="B89" s="61" t="s">
         <v>13</v>
       </c>
-      <c r="C89" s="53"/>
-      <c r="D89" s="53"/>
-      <c r="E89" s="53"/>
-      <c r="F89" s="53"/>
-      <c r="G89" s="53"/>
-      <c r="H89" s="53"/>
-      <c r="I89" s="53"/>
-      <c r="J89" s="54"/>
+      <c r="C89" s="61"/>
+      <c r="D89" s="61"/>
+      <c r="E89" s="61"/>
+      <c r="F89" s="61"/>
+      <c r="G89" s="61"/>
+      <c r="H89" s="61"/>
+      <c r="I89" s="61"/>
+      <c r="J89" s="62"/>
     </row>
     <row r="90" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A90" s="95"/>
-      <c r="B90" s="66" t="s">
+      <c r="A90" s="63"/>
+      <c r="B90" s="64" t="s">
         <v>14</v>
       </c>
-      <c r="C90" s="66"/>
-      <c r="D90" s="66"/>
-      <c r="E90" s="66"/>
-      <c r="F90" s="66"/>
-      <c r="G90" s="66"/>
-      <c r="H90" s="66"/>
-      <c r="I90" s="66"/>
-      <c r="J90" s="67"/>
+      <c r="C90" s="64"/>
+      <c r="D90" s="64"/>
+      <c r="E90" s="64"/>
+      <c r="F90" s="64"/>
+      <c r="G90" s="64"/>
+      <c r="H90" s="64"/>
+      <c r="I90" s="64"/>
+      <c r="J90" s="65"/>
     </row>
     <row r="91" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A91" s="95"/>
-      <c r="B91" s="66"/>
-      <c r="C91" s="66"/>
-      <c r="D91" s="66"/>
-      <c r="E91" s="66"/>
-      <c r="F91" s="66"/>
-      <c r="G91" s="66"/>
-      <c r="H91" s="66"/>
-      <c r="I91" s="66"/>
-      <c r="J91" s="67"/>
+      <c r="A91" s="63"/>
+      <c r="B91" s="64"/>
+      <c r="C91" s="64"/>
+      <c r="D91" s="64"/>
+      <c r="E91" s="64"/>
+      <c r="F91" s="64"/>
+      <c r="G91" s="64"/>
+      <c r="H91" s="64"/>
+      <c r="I91" s="64"/>
+      <c r="J91" s="65"/>
     </row>
     <row r="92" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A92" s="95"/>
-      <c r="B92" s="68"/>
-      <c r="C92" s="68"/>
-      <c r="D92" s="68"/>
-      <c r="E92" s="68"/>
-      <c r="F92" s="68"/>
-      <c r="G92" s="68"/>
-      <c r="H92" s="68"/>
-      <c r="I92" s="68"/>
-      <c r="J92" s="69"/>
+      <c r="A92" s="63"/>
+      <c r="B92" s="66"/>
+      <c r="C92" s="66"/>
+      <c r="D92" s="66"/>
+      <c r="E92" s="66"/>
+      <c r="F92" s="66"/>
+      <c r="G92" s="66"/>
+      <c r="H92" s="66"/>
+      <c r="I92" s="66"/>
+      <c r="J92" s="67"/>
     </row>
     <row r="93" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A93" s="49"/>
-      <c r="B93" s="97"/>
-      <c r="C93" s="82"/>
-      <c r="D93" s="82"/>
-      <c r="E93" s="82"/>
-      <c r="F93" s="82"/>
-      <c r="G93" s="82"/>
-      <c r="H93" s="82"/>
-      <c r="I93" s="82"/>
-      <c r="J93" s="83"/>
+      <c r="B93" s="69"/>
+      <c r="C93" s="70"/>
+      <c r="D93" s="70"/>
+      <c r="E93" s="70"/>
+      <c r="F93" s="70"/>
+      <c r="G93" s="70"/>
+      <c r="H93" s="70"/>
+      <c r="I93" s="70"/>
+      <c r="J93" s="71"/>
     </row>
     <row r="94" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A94" s="49"/>
-      <c r="B94" s="84"/>
-      <c r="C94" s="85"/>
-      <c r="D94" s="85"/>
-      <c r="E94" s="85"/>
-      <c r="F94" s="85"/>
-      <c r="G94" s="85"/>
-      <c r="H94" s="85"/>
-      <c r="I94" s="85"/>
-      <c r="J94" s="86"/>
+      <c r="B94" s="72"/>
+      <c r="C94" s="73"/>
+      <c r="D94" s="73"/>
+      <c r="E94" s="73"/>
+      <c r="F94" s="73"/>
+      <c r="G94" s="73"/>
+      <c r="H94" s="73"/>
+      <c r="I94" s="73"/>
+      <c r="J94" s="74"/>
     </row>
     <row r="95" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A95" s="49"/>
-      <c r="B95" s="84"/>
-      <c r="C95" s="85"/>
-      <c r="D95" s="85"/>
-      <c r="E95" s="85"/>
-      <c r="F95" s="85"/>
-      <c r="G95" s="85"/>
-      <c r="H95" s="85"/>
-      <c r="I95" s="85"/>
-      <c r="J95" s="86"/>
+      <c r="B95" s="72"/>
+      <c r="C95" s="73"/>
+      <c r="D95" s="73"/>
+      <c r="E95" s="73"/>
+      <c r="F95" s="73"/>
+      <c r="G95" s="73"/>
+      <c r="H95" s="73"/>
+      <c r="I95" s="73"/>
+      <c r="J95" s="74"/>
     </row>
     <row r="96" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A96" s="49"/>
-      <c r="B96" s="84"/>
-      <c r="C96" s="85"/>
-      <c r="D96" s="85"/>
-      <c r="E96" s="85"/>
-      <c r="F96" s="85"/>
-      <c r="G96" s="85"/>
-      <c r="H96" s="85"/>
-      <c r="I96" s="85"/>
-      <c r="J96" s="86"/>
+      <c r="B96" s="72"/>
+      <c r="C96" s="73"/>
+      <c r="D96" s="73"/>
+      <c r="E96" s="73"/>
+      <c r="F96" s="73"/>
+      <c r="G96" s="73"/>
+      <c r="H96" s="73"/>
+      <c r="I96" s="73"/>
+      <c r="J96" s="74"/>
     </row>
     <row r="97" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A97" s="49"/>
-      <c r="B97" s="84"/>
-      <c r="C97" s="85"/>
-      <c r="D97" s="85"/>
-      <c r="E97" s="85"/>
-      <c r="F97" s="85"/>
-      <c r="G97" s="85"/>
-      <c r="H97" s="85"/>
-      <c r="I97" s="85"/>
-      <c r="J97" s="86"/>
+      <c r="B97" s="72"/>
+      <c r="C97" s="73"/>
+      <c r="D97" s="73"/>
+      <c r="E97" s="73"/>
+      <c r="F97" s="73"/>
+      <c r="G97" s="73"/>
+      <c r="H97" s="73"/>
+      <c r="I97" s="73"/>
+      <c r="J97" s="74"/>
     </row>
     <row r="98" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A98" s="49"/>
-      <c r="B98" s="84"/>
-      <c r="C98" s="85"/>
-      <c r="D98" s="85"/>
-      <c r="E98" s="85"/>
-      <c r="F98" s="85"/>
-      <c r="G98" s="85"/>
-      <c r="H98" s="85"/>
-      <c r="I98" s="85"/>
-      <c r="J98" s="86"/>
+      <c r="B98" s="72"/>
+      <c r="C98" s="73"/>
+      <c r="D98" s="73"/>
+      <c r="E98" s="73"/>
+      <c r="F98" s="73"/>
+      <c r="G98" s="73"/>
+      <c r="H98" s="73"/>
+      <c r="I98" s="73"/>
+      <c r="J98" s="74"/>
     </row>
     <row r="99" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A99" s="49"/>
-      <c r="B99" s="84"/>
-      <c r="C99" s="85"/>
-      <c r="D99" s="85"/>
-      <c r="E99" s="85"/>
-      <c r="F99" s="85"/>
-      <c r="G99" s="85"/>
-      <c r="H99" s="85"/>
-      <c r="I99" s="85"/>
-      <c r="J99" s="86"/>
+      <c r="B99" s="72"/>
+      <c r="C99" s="73"/>
+      <c r="D99" s="73"/>
+      <c r="E99" s="73"/>
+      <c r="F99" s="73"/>
+      <c r="G99" s="73"/>
+      <c r="H99" s="73"/>
+      <c r="I99" s="73"/>
+      <c r="J99" s="74"/>
     </row>
     <row r="100" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A100" s="49"/>
-      <c r="B100" s="84"/>
-      <c r="C100" s="85"/>
-      <c r="D100" s="85"/>
-      <c r="E100" s="85"/>
-      <c r="F100" s="85"/>
-      <c r="G100" s="85"/>
-      <c r="H100" s="85"/>
-      <c r="I100" s="85"/>
-      <c r="J100" s="86"/>
+      <c r="B100" s="72"/>
+      <c r="C100" s="73"/>
+      <c r="D100" s="73"/>
+      <c r="E100" s="73"/>
+      <c r="F100" s="73"/>
+      <c r="G100" s="73"/>
+      <c r="H100" s="73"/>
+      <c r="I100" s="73"/>
+      <c r="J100" s="74"/>
     </row>
     <row r="101" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A101" s="49"/>
-      <c r="B101" s="84"/>
-      <c r="C101" s="85"/>
-      <c r="D101" s="85"/>
-      <c r="E101" s="85"/>
-      <c r="F101" s="85"/>
-      <c r="G101" s="85"/>
-      <c r="H101" s="85"/>
-      <c r="I101" s="85"/>
-      <c r="J101" s="86"/>
+      <c r="B101" s="72"/>
+      <c r="C101" s="73"/>
+      <c r="D101" s="73"/>
+      <c r="E101" s="73"/>
+      <c r="F101" s="73"/>
+      <c r="G101" s="73"/>
+      <c r="H101" s="73"/>
+      <c r="I101" s="73"/>
+      <c r="J101" s="74"/>
     </row>
     <row r="102" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A102" s="49"/>
-      <c r="B102" s="84"/>
-      <c r="C102" s="85"/>
-      <c r="D102" s="85"/>
-      <c r="E102" s="85"/>
-      <c r="F102" s="85"/>
-      <c r="G102" s="85"/>
-      <c r="H102" s="85"/>
-      <c r="I102" s="85"/>
-      <c r="J102" s="86"/>
+      <c r="B102" s="72"/>
+      <c r="C102" s="73"/>
+      <c r="D102" s="73"/>
+      <c r="E102" s="73"/>
+      <c r="F102" s="73"/>
+      <c r="G102" s="73"/>
+      <c r="H102" s="73"/>
+      <c r="I102" s="73"/>
+      <c r="J102" s="74"/>
     </row>
     <row r="103" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A103" s="49"/>
-      <c r="B103" s="84"/>
-      <c r="C103" s="85"/>
-      <c r="D103" s="85"/>
-      <c r="E103" s="85"/>
-      <c r="F103" s="85"/>
-      <c r="G103" s="85"/>
-      <c r="H103" s="85"/>
-      <c r="I103" s="85"/>
-      <c r="J103" s="86"/>
+      <c r="B103" s="72"/>
+      <c r="C103" s="73"/>
+      <c r="D103" s="73"/>
+      <c r="E103" s="73"/>
+      <c r="F103" s="73"/>
+      <c r="G103" s="73"/>
+      <c r="H103" s="73"/>
+      <c r="I103" s="73"/>
+      <c r="J103" s="74"/>
     </row>
     <row r="104" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A104" s="49"/>
-      <c r="B104" s="84"/>
-      <c r="C104" s="85"/>
-      <c r="D104" s="85"/>
-      <c r="E104" s="85"/>
-      <c r="F104" s="85"/>
-      <c r="G104" s="85"/>
-      <c r="H104" s="85"/>
-      <c r="I104" s="85"/>
-      <c r="J104" s="86"/>
+      <c r="B104" s="72"/>
+      <c r="C104" s="73"/>
+      <c r="D104" s="73"/>
+      <c r="E104" s="73"/>
+      <c r="F104" s="73"/>
+      <c r="G104" s="73"/>
+      <c r="H104" s="73"/>
+      <c r="I104" s="73"/>
+      <c r="J104" s="74"/>
     </row>
     <row r="105" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A105" s="49"/>
-      <c r="B105" s="84"/>
-      <c r="C105" s="85"/>
-      <c r="D105" s="85"/>
-      <c r="E105" s="85"/>
-      <c r="F105" s="85"/>
-      <c r="G105" s="85"/>
-      <c r="H105" s="85"/>
-      <c r="I105" s="85"/>
-      <c r="J105" s="86"/>
+      <c r="B105" s="72"/>
+      <c r="C105" s="73"/>
+      <c r="D105" s="73"/>
+      <c r="E105" s="73"/>
+      <c r="F105" s="73"/>
+      <c r="G105" s="73"/>
+      <c r="H105" s="73"/>
+      <c r="I105" s="73"/>
+      <c r="J105" s="74"/>
     </row>
     <row r="106" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A106" s="49"/>
-      <c r="B106" s="84"/>
-      <c r="C106" s="85"/>
-      <c r="D106" s="85"/>
-      <c r="E106" s="85"/>
-      <c r="F106" s="85"/>
-      <c r="G106" s="85"/>
-      <c r="H106" s="85"/>
-      <c r="I106" s="85"/>
-      <c r="J106" s="86"/>
+      <c r="B106" s="72"/>
+      <c r="C106" s="73"/>
+      <c r="D106" s="73"/>
+      <c r="E106" s="73"/>
+      <c r="F106" s="73"/>
+      <c r="G106" s="73"/>
+      <c r="H106" s="73"/>
+      <c r="I106" s="73"/>
+      <c r="J106" s="74"/>
     </row>
     <row r="107" spans="1:10" ht="13.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A107" s="50"/>
-      <c r="B107" s="98"/>
-      <c r="C107" s="99"/>
-      <c r="D107" s="99"/>
-      <c r="E107" s="99"/>
-      <c r="F107" s="99"/>
-      <c r="G107" s="99"/>
-      <c r="H107" s="99"/>
-      <c r="I107" s="99"/>
-      <c r="J107" s="100"/>
+      <c r="B107" s="75"/>
+      <c r="C107" s="76"/>
+      <c r="D107" s="76"/>
+      <c r="E107" s="76"/>
+      <c r="F107" s="76"/>
+      <c r="G107" s="76"/>
+      <c r="H107" s="76"/>
+      <c r="I107" s="76"/>
+      <c r="J107" s="77"/>
     </row>
     <row r="108" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A108" s="48">
+      <c r="A108" s="47">
         <v>7</v>
       </c>
-      <c r="B108" s="55" t="s">
+      <c r="B108" s="51" t="s">
         <v>15</v>
       </c>
-      <c r="C108" s="55"/>
-      <c r="D108" s="55"/>
-      <c r="E108" s="55"/>
-      <c r="F108" s="55"/>
-      <c r="G108" s="55"/>
-      <c r="H108" s="55"/>
-      <c r="I108" s="55"/>
-      <c r="J108" s="87"/>
+      <c r="C108" s="51"/>
+      <c r="D108" s="51"/>
+      <c r="E108" s="51"/>
+      <c r="F108" s="51"/>
+      <c r="G108" s="51"/>
+      <c r="H108" s="51"/>
+      <c r="I108" s="51"/>
+      <c r="J108" s="52"/>
     </row>
     <row r="109" spans="1:10" ht="13.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A109" s="52"/>
-      <c r="B109" s="93" t="s">
+      <c r="A109" s="48"/>
+      <c r="B109" s="59" t="s">
         <v>16</v>
       </c>
-      <c r="C109" s="93"/>
-      <c r="D109" s="93"/>
-      <c r="E109" s="93"/>
-      <c r="F109" s="93"/>
-      <c r="G109" s="93"/>
-      <c r="H109" s="93"/>
-      <c r="I109" s="93"/>
-      <c r="J109" s="94"/>
+      <c r="C109" s="59"/>
+      <c r="D109" s="59"/>
+      <c r="E109" s="59"/>
+      <c r="F109" s="59"/>
+      <c r="G109" s="59"/>
+      <c r="H109" s="59"/>
+      <c r="I109" s="59"/>
+      <c r="J109" s="60"/>
     </row>
     <row r="110" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A110" s="48">
+      <c r="A110" s="47">
         <v>8</v>
       </c>
-      <c r="B110" s="55" t="s">
+      <c r="B110" s="51" t="s">
         <v>17</v>
       </c>
-      <c r="C110" s="55"/>
-      <c r="D110" s="55"/>
-      <c r="E110" s="55"/>
-      <c r="F110" s="55"/>
-      <c r="G110" s="55"/>
-      <c r="H110" s="55"/>
-      <c r="I110" s="55"/>
-      <c r="J110" s="87"/>
+      <c r="C110" s="51"/>
+      <c r="D110" s="51"/>
+      <c r="E110" s="51"/>
+      <c r="F110" s="51"/>
+      <c r="G110" s="51"/>
+      <c r="H110" s="51"/>
+      <c r="I110" s="51"/>
+      <c r="J110" s="52"/>
     </row>
     <row r="111" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A111" s="49"/>
-      <c r="B111" s="44"/>
-      <c r="C111" s="44"/>
-      <c r="D111" s="44"/>
-      <c r="E111" s="44"/>
-      <c r="F111" s="44"/>
-      <c r="G111" s="44"/>
-      <c r="H111" s="44"/>
-      <c r="I111" s="44"/>
-      <c r="J111" s="65"/>
+      <c r="B111" s="53"/>
+      <c r="C111" s="53"/>
+      <c r="D111" s="53"/>
+      <c r="E111" s="53"/>
+      <c r="F111" s="53"/>
+      <c r="G111" s="53"/>
+      <c r="H111" s="53"/>
+      <c r="I111" s="53"/>
+      <c r="J111" s="54"/>
     </row>
     <row r="112" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A112" s="49"/>
-      <c r="B112" s="44"/>
-      <c r="C112" s="44"/>
-      <c r="D112" s="44"/>
-      <c r="E112" s="44"/>
-      <c r="F112" s="44"/>
-      <c r="G112" s="44"/>
-      <c r="H112" s="44"/>
-      <c r="I112" s="44"/>
-      <c r="J112" s="65"/>
+      <c r="B112" s="53"/>
+      <c r="C112" s="53"/>
+      <c r="D112" s="53"/>
+      <c r="E112" s="53"/>
+      <c r="F112" s="53"/>
+      <c r="G112" s="53"/>
+      <c r="H112" s="53"/>
+      <c r="I112" s="53"/>
+      <c r="J112" s="54"/>
     </row>
     <row r="113" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A113" s="49"/>
-      <c r="B113" s="44"/>
-      <c r="C113" s="44"/>
-      <c r="D113" s="44"/>
-      <c r="E113" s="44"/>
-      <c r="F113" s="44"/>
-      <c r="G113" s="44"/>
-      <c r="H113" s="44"/>
-      <c r="I113" s="44"/>
-      <c r="J113" s="65"/>
+      <c r="B113" s="53"/>
+      <c r="C113" s="53"/>
+      <c r="D113" s="53"/>
+      <c r="E113" s="53"/>
+      <c r="F113" s="53"/>
+      <c r="G113" s="53"/>
+      <c r="H113" s="53"/>
+      <c r="I113" s="53"/>
+      <c r="J113" s="54"/>
     </row>
     <row r="114" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A114" s="49"/>
-      <c r="B114" s="44"/>
-      <c r="C114" s="44"/>
-      <c r="D114" s="44"/>
-      <c r="E114" s="44"/>
-      <c r="F114" s="44"/>
-      <c r="G114" s="44"/>
-      <c r="H114" s="44"/>
-      <c r="I114" s="44"/>
-      <c r="J114" s="65"/>
+      <c r="B114" s="53"/>
+      <c r="C114" s="53"/>
+      <c r="D114" s="53"/>
+      <c r="E114" s="53"/>
+      <c r="F114" s="53"/>
+      <c r="G114" s="53"/>
+      <c r="H114" s="53"/>
+      <c r="I114" s="53"/>
+      <c r="J114" s="54"/>
     </row>
     <row r="115" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A115" s="49"/>
-      <c r="B115" s="44"/>
-      <c r="C115" s="44"/>
-      <c r="D115" s="44"/>
-      <c r="E115" s="44"/>
-      <c r="F115" s="44"/>
-      <c r="G115" s="44"/>
-      <c r="H115" s="44"/>
-      <c r="I115" s="44"/>
-      <c r="J115" s="65"/>
+      <c r="B115" s="53"/>
+      <c r="C115" s="53"/>
+      <c r="D115" s="53"/>
+      <c r="E115" s="53"/>
+      <c r="F115" s="53"/>
+      <c r="G115" s="53"/>
+      <c r="H115" s="53"/>
+      <c r="I115" s="53"/>
+      <c r="J115" s="54"/>
     </row>
     <row r="116" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A116" s="49"/>
-      <c r="B116" s="44"/>
-      <c r="C116" s="44"/>
-      <c r="D116" s="44"/>
-      <c r="E116" s="44"/>
-      <c r="F116" s="44"/>
-      <c r="G116" s="44"/>
-      <c r="H116" s="44"/>
-      <c r="I116" s="44"/>
-      <c r="J116" s="65"/>
+      <c r="B116" s="53"/>
+      <c r="C116" s="53"/>
+      <c r="D116" s="53"/>
+      <c r="E116" s="53"/>
+      <c r="F116" s="53"/>
+      <c r="G116" s="53"/>
+      <c r="H116" s="53"/>
+      <c r="I116" s="53"/>
+      <c r="J116" s="54"/>
     </row>
     <row r="117" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A117" s="49"/>
-      <c r="B117" s="89" t="s">
+      <c r="B117" s="55" t="s">
         <v>18</v>
       </c>
-      <c r="C117" s="89"/>
-      <c r="D117" s="89"/>
-      <c r="E117" s="89"/>
-      <c r="F117" s="89"/>
-      <c r="G117" s="89"/>
-      <c r="H117" s="89"/>
-      <c r="I117" s="89"/>
-      <c r="J117" s="90"/>
+      <c r="C117" s="55"/>
+      <c r="D117" s="55"/>
+      <c r="E117" s="55"/>
+      <c r="F117" s="55"/>
+      <c r="G117" s="55"/>
+      <c r="H117" s="55"/>
+      <c r="I117" s="55"/>
+      <c r="J117" s="56"/>
     </row>
     <row r="118" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A118" s="49"/>
-      <c r="B118" s="44"/>
-      <c r="C118" s="44"/>
-      <c r="D118" s="44"/>
-      <c r="E118" s="44"/>
-      <c r="F118" s="44"/>
-      <c r="G118" s="44"/>
-      <c r="H118" s="44"/>
-      <c r="I118" s="44"/>
-      <c r="J118" s="65"/>
+      <c r="B118" s="53"/>
+      <c r="C118" s="53"/>
+      <c r="D118" s="53"/>
+      <c r="E118" s="53"/>
+      <c r="F118" s="53"/>
+      <c r="G118" s="53"/>
+      <c r="H118" s="53"/>
+      <c r="I118" s="53"/>
+      <c r="J118" s="54"/>
     </row>
     <row r="119" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A119" s="49"/>
-      <c r="B119" s="44"/>
-      <c r="C119" s="44"/>
-      <c r="D119" s="44"/>
-      <c r="E119" s="44"/>
-      <c r="F119" s="44"/>
-      <c r="G119" s="44"/>
-      <c r="H119" s="44"/>
-      <c r="I119" s="44"/>
-      <c r="J119" s="65"/>
+      <c r="B119" s="53"/>
+      <c r="C119" s="53"/>
+      <c r="D119" s="53"/>
+      <c r="E119" s="53"/>
+      <c r="F119" s="53"/>
+      <c r="G119" s="53"/>
+      <c r="H119" s="53"/>
+      <c r="I119" s="53"/>
+      <c r="J119" s="54"/>
     </row>
     <row r="120" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A120" s="49"/>
-      <c r="B120" s="44"/>
-      <c r="C120" s="44"/>
-      <c r="D120" s="44"/>
-      <c r="E120" s="44"/>
-      <c r="F120" s="44"/>
-      <c r="G120" s="44"/>
-      <c r="H120" s="44"/>
-      <c r="I120" s="44"/>
-      <c r="J120" s="65"/>
+      <c r="B120" s="53"/>
+      <c r="C120" s="53"/>
+      <c r="D120" s="53"/>
+      <c r="E120" s="53"/>
+      <c r="F120" s="53"/>
+      <c r="G120" s="53"/>
+      <c r="H120" s="53"/>
+      <c r="I120" s="53"/>
+      <c r="J120" s="54"/>
     </row>
     <row r="121" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A121" s="49"/>
-      <c r="B121" s="44"/>
-      <c r="C121" s="44"/>
-      <c r="D121" s="44"/>
-      <c r="E121" s="44"/>
-      <c r="F121" s="44"/>
-      <c r="G121" s="44"/>
-      <c r="H121" s="44"/>
-      <c r="I121" s="44"/>
-      <c r="J121" s="65"/>
+      <c r="B121" s="53"/>
+      <c r="C121" s="53"/>
+      <c r="D121" s="53"/>
+      <c r="E121" s="53"/>
+      <c r="F121" s="53"/>
+      <c r="G121" s="53"/>
+      <c r="H121" s="53"/>
+      <c r="I121" s="53"/>
+      <c r="J121" s="54"/>
     </row>
     <row r="122" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A122" s="49"/>
-      <c r="B122" s="44"/>
-      <c r="C122" s="44"/>
-      <c r="D122" s="44"/>
-      <c r="E122" s="44"/>
-      <c r="F122" s="44"/>
-      <c r="G122" s="44"/>
-      <c r="H122" s="44"/>
-      <c r="I122" s="44"/>
-      <c r="J122" s="65"/>
+      <c r="B122" s="53"/>
+      <c r="C122" s="53"/>
+      <c r="D122" s="53"/>
+      <c r="E122" s="53"/>
+      <c r="F122" s="53"/>
+      <c r="G122" s="53"/>
+      <c r="H122" s="53"/>
+      <c r="I122" s="53"/>
+      <c r="J122" s="54"/>
     </row>
     <row r="123" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A123" s="49"/>
-      <c r="B123" s="44"/>
-      <c r="C123" s="44"/>
-      <c r="D123" s="44"/>
-      <c r="E123" s="44"/>
-      <c r="F123" s="44"/>
-      <c r="G123" s="44"/>
-      <c r="H123" s="44"/>
-      <c r="I123" s="44"/>
-      <c r="J123" s="65"/>
+      <c r="B123" s="53"/>
+      <c r="C123" s="53"/>
+      <c r="D123" s="53"/>
+      <c r="E123" s="53"/>
+      <c r="F123" s="53"/>
+      <c r="G123" s="53"/>
+      <c r="H123" s="53"/>
+      <c r="I123" s="53"/>
+      <c r="J123" s="54"/>
     </row>
     <row r="124" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A124" s="49"/>
-      <c r="B124" s="44"/>
-      <c r="C124" s="44"/>
-      <c r="D124" s="44"/>
-      <c r="E124" s="44"/>
-      <c r="F124" s="44"/>
-      <c r="G124" s="44"/>
-      <c r="H124" s="44"/>
-      <c r="I124" s="44"/>
-      <c r="J124" s="65"/>
+      <c r="B124" s="53"/>
+      <c r="C124" s="53"/>
+      <c r="D124" s="53"/>
+      <c r="E124" s="53"/>
+      <c r="F124" s="53"/>
+      <c r="G124" s="53"/>
+      <c r="H124" s="53"/>
+      <c r="I124" s="53"/>
+      <c r="J124" s="54"/>
     </row>
     <row r="125" spans="1:10" ht="13.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A125" s="50"/>
-      <c r="B125" s="91"/>
-      <c r="C125" s="91"/>
-      <c r="D125" s="91"/>
-      <c r="E125" s="91"/>
-      <c r="F125" s="91"/>
-      <c r="G125" s="91"/>
-      <c r="H125" s="91"/>
-      <c r="I125" s="91"/>
-      <c r="J125" s="92"/>
+      <c r="B125" s="57"/>
+      <c r="C125" s="57"/>
+      <c r="D125" s="57"/>
+      <c r="E125" s="57"/>
+      <c r="F125" s="57"/>
+      <c r="G125" s="57"/>
+      <c r="H125" s="57"/>
+      <c r="I125" s="57"/>
+      <c r="J125" s="58"/>
     </row>
   </sheetData>
   <mergeCells count="39">
+    <mergeCell ref="A21:A62"/>
+    <mergeCell ref="B64:C64"/>
+    <mergeCell ref="A2:A3"/>
+    <mergeCell ref="A4:A20"/>
+    <mergeCell ref="B4:J4"/>
+    <mergeCell ref="B2:D3"/>
+    <mergeCell ref="E2:J3"/>
+    <mergeCell ref="B69:J86"/>
+    <mergeCell ref="A63:A86"/>
+    <mergeCell ref="D64:J64"/>
+    <mergeCell ref="B5:J7"/>
+    <mergeCell ref="B22:J25"/>
+    <mergeCell ref="B26:J62"/>
+    <mergeCell ref="B21:J21"/>
+    <mergeCell ref="B68:J68"/>
+    <mergeCell ref="B8:J20"/>
+    <mergeCell ref="B63:J63"/>
+    <mergeCell ref="D67:J67"/>
+    <mergeCell ref="B67:C67"/>
+    <mergeCell ref="D66:J66"/>
+    <mergeCell ref="B66:C66"/>
+    <mergeCell ref="D65:J65"/>
+    <mergeCell ref="B65:C65"/>
     <mergeCell ref="A1:J1"/>
     <mergeCell ref="A108:A109"/>
     <mergeCell ref="A110:A125"/>
@@ -5590,29 +5613,6 @@
     <mergeCell ref="B87:J87"/>
     <mergeCell ref="B88:J88"/>
     <mergeCell ref="B93:J107"/>
-    <mergeCell ref="B69:J86"/>
-    <mergeCell ref="A63:A86"/>
-    <mergeCell ref="D64:J64"/>
-    <mergeCell ref="B5:J7"/>
-    <mergeCell ref="B22:J25"/>
-    <mergeCell ref="B26:J62"/>
-    <mergeCell ref="B21:J21"/>
-    <mergeCell ref="B68:J68"/>
-    <mergeCell ref="B8:J20"/>
-    <mergeCell ref="B63:J63"/>
-    <mergeCell ref="D67:J67"/>
-    <mergeCell ref="B67:C67"/>
-    <mergeCell ref="D66:J66"/>
-    <mergeCell ref="B66:C66"/>
-    <mergeCell ref="D65:J65"/>
-    <mergeCell ref="B65:C65"/>
-    <mergeCell ref="A21:A62"/>
-    <mergeCell ref="B64:C64"/>
-    <mergeCell ref="A2:A3"/>
-    <mergeCell ref="A4:A20"/>
-    <mergeCell ref="B4:J4"/>
-    <mergeCell ref="B2:D3"/>
-    <mergeCell ref="E2:J3"/>
   </mergeCells>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.75" right="0.75" top="0.6" bottom="0.61" header="0.4" footer="0.39"/>
@@ -5641,71 +5641,71 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="56" t="s">
+      <c r="A1" s="36" t="s">
         <v>19</v>
       </c>
-      <c r="B1" s="56"/>
-      <c r="C1" s="56"/>
+      <c r="B1" s="36"/>
+      <c r="C1" s="36"/>
     </row>
     <row r="2" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="32" t="s">
+      <c r="A2" s="39" t="s">
         <v>20</v>
       </c>
-      <c r="B2" s="32"/>
-      <c r="C2" s="32"/>
-      <c r="D2" s="32"/>
-      <c r="E2" s="32"/>
-      <c r="F2" s="32"/>
-      <c r="G2" s="32"/>
-      <c r="H2" s="32"/>
+      <c r="B2" s="39"/>
+      <c r="C2" s="39"/>
+      <c r="D2" s="39"/>
+      <c r="E2" s="39"/>
+      <c r="F2" s="39"/>
+      <c r="G2" s="39"/>
+      <c r="H2" s="39"/>
     </row>
     <row r="3" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="32"/>
-      <c r="B3" s="32"/>
-      <c r="C3" s="32"/>
-      <c r="D3" s="32"/>
-      <c r="E3" s="32"/>
-      <c r="F3" s="32"/>
-      <c r="G3" s="32"/>
-      <c r="H3" s="32"/>
+      <c r="A3" s="39"/>
+      <c r="B3" s="39"/>
+      <c r="C3" s="39"/>
+      <c r="D3" s="39"/>
+      <c r="E3" s="39"/>
+      <c r="F3" s="39"/>
+      <c r="G3" s="39"/>
+      <c r="H3" s="39"/>
     </row>
     <row r="4" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="32"/>
-      <c r="B4" s="32"/>
-      <c r="C4" s="32"/>
-      <c r="D4" s="32"/>
-      <c r="E4" s="32"/>
-      <c r="F4" s="32"/>
-      <c r="G4" s="32"/>
-      <c r="H4" s="32"/>
+      <c r="A4" s="39"/>
+      <c r="B4" s="39"/>
+      <c r="C4" s="39"/>
+      <c r="D4" s="39"/>
+      <c r="E4" s="39"/>
+      <c r="F4" s="39"/>
+      <c r="G4" s="39"/>
+      <c r="H4" s="39"/>
     </row>
     <row r="5" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="33"/>
-      <c r="B5" s="33"/>
-      <c r="C5" s="33"/>
+      <c r="A5" s="37"/>
+      <c r="B5" s="37"/>
+      <c r="C5" s="37"/>
     </row>
     <row r="6" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="34" t="s">
+      <c r="A6" s="38" t="s">
         <v>21</v>
       </c>
-      <c r="B6" s="34" t="s">
+      <c r="B6" s="38" t="s">
         <v>22</v>
       </c>
-      <c r="C6" s="34"/>
-      <c r="D6" s="34"/>
-      <c r="E6" s="34" t="s">
+      <c r="C6" s="38"/>
+      <c r="D6" s="38"/>
+      <c r="E6" s="38" t="s">
         <v>23</v>
       </c>
-      <c r="F6" s="37" t="s">
+      <c r="F6" s="40" t="s">
         <v>24</v>
       </c>
-      <c r="G6" s="38"/>
-      <c r="H6" s="35" t="s">
+      <c r="G6" s="41"/>
+      <c r="H6" s="44" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="7" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="34"/>
+      <c r="A7" s="38"/>
       <c r="B7" s="23" t="s">
         <v>26</v>
       </c>
@@ -5715,19 +5715,19 @@
       <c r="D7" s="23" t="s">
         <v>28</v>
       </c>
-      <c r="E7" s="34"/>
-      <c r="F7" s="39"/>
-      <c r="G7" s="40"/>
-      <c r="H7" s="36"/>
+      <c r="E7" s="38"/>
+      <c r="F7" s="42"/>
+      <c r="G7" s="43"/>
+      <c r="H7" s="45"/>
     </row>
     <row r="8" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="4">
         <v>1</v>
       </c>
-      <c r="B8" s="63" t="s">
+      <c r="B8" s="29" t="s">
         <v>75</v>
       </c>
-      <c r="C8" s="63" t="s">
+      <c r="C8" s="29" t="s">
         <v>76</v>
       </c>
       <c r="D8" s="27" t="s">
@@ -5736,54 +5736,54 @@
       <c r="E8" s="27" t="s">
         <v>102</v>
       </c>
-      <c r="F8" s="101" t="s">
+      <c r="F8" s="34" t="s">
         <v>106</v>
       </c>
-      <c r="G8" s="102"/>
+      <c r="G8" s="35"/>
       <c r="H8" s="27"/>
     </row>
     <row r="9" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="4">
         <v>2</v>
       </c>
-      <c r="B9" s="104"/>
-      <c r="C9" s="104"/>
+      <c r="B9" s="31"/>
+      <c r="C9" s="31"/>
       <c r="D9" s="27" t="s">
         <v>78</v>
       </c>
       <c r="E9" s="27" t="s">
         <v>102</v>
       </c>
-      <c r="F9" s="101" t="s">
+      <c r="F9" s="34" t="s">
         <v>107</v>
       </c>
-      <c r="G9" s="102"/>
+      <c r="G9" s="35"/>
       <c r="H9" s="27"/>
     </row>
     <row r="10" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="4">
         <v>3</v>
       </c>
-      <c r="B10" s="104"/>
-      <c r="C10" s="105"/>
+      <c r="B10" s="31"/>
+      <c r="C10" s="32"/>
       <c r="D10" s="27" t="s">
         <v>79</v>
       </c>
       <c r="E10" s="27" t="s">
         <v>102</v>
       </c>
-      <c r="F10" s="101" t="s">
+      <c r="F10" s="34" t="s">
         <v>108</v>
       </c>
-      <c r="G10" s="102"/>
+      <c r="G10" s="35"/>
       <c r="H10" s="27"/>
     </row>
     <row r="11" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="4">
         <v>4</v>
       </c>
-      <c r="B11" s="104"/>
-      <c r="C11" s="63" t="s">
+      <c r="B11" s="31"/>
+      <c r="C11" s="29" t="s">
         <v>80</v>
       </c>
       <c r="D11" s="27" t="s">
@@ -5792,35 +5792,35 @@
       <c r="E11" s="27" t="s">
         <v>102</v>
       </c>
-      <c r="F11" s="101" t="s">
+      <c r="F11" s="34" t="s">
         <v>109</v>
       </c>
-      <c r="G11" s="102"/>
+      <c r="G11" s="35"/>
       <c r="H11" s="27"/>
     </row>
     <row r="12" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="4">
         <v>5</v>
       </c>
-      <c r="B12" s="105"/>
-      <c r="C12" s="105"/>
+      <c r="B12" s="32"/>
+      <c r="C12" s="32"/>
       <c r="D12" s="27" t="s">
         <v>82</v>
       </c>
       <c r="E12" s="27" t="s">
         <v>102</v>
       </c>
-      <c r="F12" s="101" t="s">
+      <c r="F12" s="34" t="s">
         <v>110</v>
       </c>
-      <c r="G12" s="102"/>
+      <c r="G12" s="35"/>
       <c r="H12" s="27"/>
     </row>
     <row r="13" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="4">
         <v>6</v>
       </c>
-      <c r="B13" s="63" t="s">
+      <c r="B13" s="29" t="s">
         <v>83</v>
       </c>
       <c r="C13" s="27" t="s">
@@ -5832,17 +5832,17 @@
       <c r="E13" s="27" t="s">
         <v>103</v>
       </c>
-      <c r="F13" s="101" t="s">
+      <c r="F13" s="34" t="s">
         <v>114</v>
       </c>
-      <c r="G13" s="102"/>
+      <c r="G13" s="35"/>
       <c r="H13" s="27"/>
     </row>
     <row r="14" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="4">
         <v>7</v>
       </c>
-      <c r="B14" s="106"/>
+      <c r="B14" s="33"/>
       <c r="C14" s="27" t="s">
         <v>86</v>
       </c>
@@ -5852,18 +5852,18 @@
       <c r="E14" s="27" t="s">
         <v>104</v>
       </c>
-      <c r="F14" s="101" t="s">
+      <c r="F14" s="34" t="s">
         <v>111</v>
       </c>
-      <c r="G14" s="102"/>
+      <c r="G14" s="35"/>
       <c r="H14" s="27"/>
     </row>
     <row r="15" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="4">
         <v>8</v>
       </c>
-      <c r="B15" s="106"/>
-      <c r="C15" s="63" t="s">
+      <c r="B15" s="33"/>
+      <c r="C15" s="29" t="s">
         <v>88</v>
       </c>
       <c r="D15" s="27" t="s">
@@ -5872,35 +5872,35 @@
       <c r="E15" s="27" t="s">
         <v>104</v>
       </c>
-      <c r="F15" s="101" t="s">
+      <c r="F15" s="34" t="s">
         <v>112</v>
       </c>
-      <c r="G15" s="102"/>
+      <c r="G15" s="35"/>
       <c r="H15" s="27"/>
     </row>
     <row r="16" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="4">
         <v>9</v>
       </c>
-      <c r="B16" s="103"/>
-      <c r="C16" s="103"/>
+      <c r="B16" s="30"/>
+      <c r="C16" s="30"/>
       <c r="D16" s="27" t="s">
         <v>90</v>
       </c>
       <c r="E16" s="27" t="s">
         <v>104</v>
       </c>
-      <c r="F16" s="101" t="s">
+      <c r="F16" s="34" t="s">
         <v>113</v>
       </c>
-      <c r="G16" s="102"/>
+      <c r="G16" s="35"/>
       <c r="H16" s="27"/>
     </row>
     <row r="17" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="4">
         <v>10</v>
       </c>
-      <c r="B17" s="63" t="s">
+      <c r="B17" s="29" t="s">
         <v>91</v>
       </c>
       <c r="C17" s="27" t="s">
@@ -5912,17 +5912,17 @@
       <c r="E17" s="27" t="s">
         <v>104</v>
       </c>
-      <c r="F17" s="101" t="s">
+      <c r="F17" s="34" t="s">
         <v>115</v>
       </c>
-      <c r="G17" s="102"/>
+      <c r="G17" s="35"/>
       <c r="H17" s="27"/>
     </row>
     <row r="18" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="4">
         <v>11</v>
       </c>
-      <c r="B18" s="106"/>
+      <c r="B18" s="33"/>
       <c r="C18" s="27" t="s">
         <v>94</v>
       </c>
@@ -5932,17 +5932,17 @@
       <c r="E18" s="27" t="s">
         <v>104</v>
       </c>
-      <c r="F18" s="101" t="s">
+      <c r="F18" s="34" t="s">
         <v>119</v>
       </c>
-      <c r="G18" s="102"/>
+      <c r="G18" s="35"/>
       <c r="H18" s="27"/>
     </row>
     <row r="19" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="4">
         <v>12</v>
       </c>
-      <c r="B19" s="103"/>
+      <c r="B19" s="30"/>
       <c r="C19" s="27" t="s">
         <v>96</v>
       </c>
@@ -5952,20 +5952,20 @@
       <c r="E19" s="27" t="s">
         <v>104</v>
       </c>
-      <c r="F19" s="101" t="s">
+      <c r="F19" s="34" t="s">
         <v>116</v>
       </c>
-      <c r="G19" s="102"/>
+      <c r="G19" s="35"/>
       <c r="H19" s="27"/>
     </row>
     <row r="20" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="4">
         <v>13</v>
       </c>
-      <c r="B20" s="63" t="s">
+      <c r="B20" s="29" t="s">
         <v>98</v>
       </c>
-      <c r="C20" s="63" t="s">
+      <c r="C20" s="29" t="s">
         <v>99</v>
       </c>
       <c r="D20" s="27" t="s">
@@ -5974,28 +5974,28 @@
       <c r="E20" s="27" t="s">
         <v>105</v>
       </c>
-      <c r="F20" s="101" t="s">
+      <c r="F20" s="34" t="s">
         <v>118</v>
       </c>
-      <c r="G20" s="102"/>
+      <c r="G20" s="35"/>
       <c r="H20" s="27"/>
     </row>
     <row r="21" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="4">
         <v>14</v>
       </c>
-      <c r="B21" s="103"/>
-      <c r="C21" s="103"/>
+      <c r="B21" s="30"/>
+      <c r="C21" s="30"/>
       <c r="D21" s="27" t="s">
         <v>101</v>
       </c>
       <c r="E21" s="27" t="s">
         <v>105</v>
       </c>
-      <c r="F21" s="101" t="s">
+      <c r="F21" s="34" t="s">
         <v>117</v>
       </c>
-      <c r="G21" s="102"/>
+      <c r="G21" s="35"/>
       <c r="H21" s="27"/>
     </row>
     <row r="22" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -6006,8 +6006,8 @@
       <c r="C22" s="27"/>
       <c r="D22" s="27"/>
       <c r="E22" s="27"/>
-      <c r="F22" s="101"/>
-      <c r="G22" s="102"/>
+      <c r="F22" s="34"/>
+      <c r="G22" s="35"/>
       <c r="H22" s="27"/>
     </row>
     <row r="23" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -6018,8 +6018,8 @@
       <c r="C23" s="27"/>
       <c r="D23" s="27"/>
       <c r="E23" s="27"/>
-      <c r="F23" s="101"/>
-      <c r="G23" s="102"/>
+      <c r="F23" s="34"/>
+      <c r="G23" s="35"/>
       <c r="H23" s="27"/>
     </row>
     <row r="24" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -6030,8 +6030,8 @@
       <c r="C24" s="27"/>
       <c r="D24" s="27"/>
       <c r="E24" s="27"/>
-      <c r="F24" s="101"/>
-      <c r="G24" s="102"/>
+      <c r="F24" s="34"/>
+      <c r="G24" s="35"/>
       <c r="H24" s="27"/>
     </row>
     <row r="25" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -6042,8 +6042,8 @@
       <c r="C25" s="27"/>
       <c r="D25" s="27"/>
       <c r="E25" s="27"/>
-      <c r="F25" s="101"/>
-      <c r="G25" s="102"/>
+      <c r="F25" s="34"/>
+      <c r="G25" s="35"/>
       <c r="H25" s="27"/>
     </row>
     <row r="26" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -6054,8 +6054,8 @@
       <c r="C26" s="27"/>
       <c r="D26" s="27"/>
       <c r="E26" s="27"/>
-      <c r="F26" s="101"/>
-      <c r="G26" s="102"/>
+      <c r="F26" s="34"/>
+      <c r="G26" s="35"/>
       <c r="H26" s="27"/>
     </row>
     <row r="27" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -6066,8 +6066,8 @@
       <c r="C27" s="27"/>
       <c r="D27" s="27"/>
       <c r="E27" s="27"/>
-      <c r="F27" s="101"/>
-      <c r="G27" s="102"/>
+      <c r="F27" s="34"/>
+      <c r="G27" s="35"/>
       <c r="H27" s="27"/>
     </row>
     <row r="28" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -6078,8 +6078,8 @@
       <c r="C28" s="27"/>
       <c r="D28" s="27"/>
       <c r="E28" s="27"/>
-      <c r="F28" s="101"/>
-      <c r="G28" s="102"/>
+      <c r="F28" s="34"/>
+      <c r="G28" s="35"/>
       <c r="H28" s="27"/>
     </row>
     <row r="29" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -6090,8 +6090,8 @@
       <c r="C29" s="27"/>
       <c r="D29" s="27"/>
       <c r="E29" s="27"/>
-      <c r="F29" s="101"/>
-      <c r="G29" s="102"/>
+      <c r="F29" s="34"/>
+      <c r="G29" s="35"/>
       <c r="H29" s="27"/>
     </row>
     <row r="30" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -6102,8 +6102,8 @@
       <c r="C30" s="27"/>
       <c r="D30" s="27"/>
       <c r="E30" s="27"/>
-      <c r="F30" s="101"/>
-      <c r="G30" s="102"/>
+      <c r="F30" s="34"/>
+      <c r="G30" s="35"/>
       <c r="H30" s="27"/>
     </row>
     <row r="31" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -6114,8 +6114,8 @@
       <c r="C31" s="27"/>
       <c r="D31" s="27"/>
       <c r="E31" s="27"/>
-      <c r="F31" s="101"/>
-      <c r="G31" s="102"/>
+      <c r="F31" s="34"/>
+      <c r="G31" s="35"/>
       <c r="H31" s="27"/>
     </row>
     <row r="32" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -6126,8 +6126,8 @@
       <c r="C32" s="27"/>
       <c r="D32" s="27"/>
       <c r="E32" s="27"/>
-      <c r="F32" s="101"/>
-      <c r="G32" s="102"/>
+      <c r="F32" s="34"/>
+      <c r="G32" s="35"/>
       <c r="H32" s="27"/>
     </row>
     <row r="33" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -6138,8 +6138,8 @@
       <c r="C33" s="27"/>
       <c r="D33" s="27"/>
       <c r="E33" s="27"/>
-      <c r="F33" s="101"/>
-      <c r="G33" s="102"/>
+      <c r="F33" s="34"/>
+      <c r="G33" s="35"/>
       <c r="H33" s="27"/>
     </row>
     <row r="34" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -6150,8 +6150,8 @@
       <c r="C34" s="27"/>
       <c r="D34" s="27"/>
       <c r="E34" s="27"/>
-      <c r="F34" s="101"/>
-      <c r="G34" s="102"/>
+      <c r="F34" s="34"/>
+      <c r="G34" s="35"/>
       <c r="H34" s="27"/>
     </row>
     <row r="35" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -6162,8 +6162,8 @@
       <c r="C35" s="27"/>
       <c r="D35" s="27"/>
       <c r="E35" s="27"/>
-      <c r="F35" s="101"/>
-      <c r="G35" s="102"/>
+      <c r="F35" s="34"/>
+      <c r="G35" s="35"/>
       <c r="H35" s="27"/>
     </row>
     <row r="36" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -6174,8 +6174,8 @@
       <c r="C36" s="27"/>
       <c r="D36" s="27"/>
       <c r="E36" s="27"/>
-      <c r="F36" s="101"/>
-      <c r="G36" s="102"/>
+      <c r="F36" s="34"/>
+      <c r="G36" s="35"/>
       <c r="H36" s="27"/>
     </row>
     <row r="37" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -6186,12 +6186,50 @@
       <c r="C37" s="27"/>
       <c r="D37" s="27"/>
       <c r="E37" s="27"/>
-      <c r="F37" s="101"/>
-      <c r="G37" s="102"/>
+      <c r="F37" s="34"/>
+      <c r="G37" s="35"/>
       <c r="H37" s="27"/>
     </row>
   </sheetData>
   <mergeCells count="46">
+    <mergeCell ref="A1:C1"/>
+    <mergeCell ref="A5:C5"/>
+    <mergeCell ref="A6:A7"/>
+    <mergeCell ref="B6:D6"/>
+    <mergeCell ref="E6:E7"/>
+    <mergeCell ref="A2:H4"/>
+    <mergeCell ref="F6:G7"/>
+    <mergeCell ref="H6:H7"/>
+    <mergeCell ref="F8:G8"/>
+    <mergeCell ref="F9:G9"/>
+    <mergeCell ref="F10:G10"/>
+    <mergeCell ref="F11:G11"/>
+    <mergeCell ref="F12:G12"/>
+    <mergeCell ref="F13:G13"/>
+    <mergeCell ref="F14:G14"/>
+    <mergeCell ref="F15:G15"/>
+    <mergeCell ref="F16:G16"/>
+    <mergeCell ref="F17:G17"/>
+    <mergeCell ref="F18:G18"/>
+    <mergeCell ref="F19:G19"/>
+    <mergeCell ref="F20:G20"/>
+    <mergeCell ref="F21:G21"/>
+    <mergeCell ref="F22:G22"/>
+    <mergeCell ref="F23:G23"/>
+    <mergeCell ref="F24:G24"/>
+    <mergeCell ref="F25:G25"/>
+    <mergeCell ref="F26:G26"/>
+    <mergeCell ref="F27:G27"/>
+    <mergeCell ref="F28:G28"/>
+    <mergeCell ref="F29:G29"/>
+    <mergeCell ref="F30:G30"/>
+    <mergeCell ref="F31:G31"/>
+    <mergeCell ref="F32:G32"/>
+    <mergeCell ref="F33:G33"/>
+    <mergeCell ref="F34:G34"/>
+    <mergeCell ref="F35:G35"/>
+    <mergeCell ref="F36:G36"/>
+    <mergeCell ref="F37:G37"/>
     <mergeCell ref="B20:B21"/>
     <mergeCell ref="C20:C21"/>
     <mergeCell ref="B8:B12"/>
@@ -6200,44 +6238,6 @@
     <mergeCell ref="B13:B16"/>
     <mergeCell ref="B17:B19"/>
     <mergeCell ref="C15:C16"/>
-    <mergeCell ref="F33:G33"/>
-    <mergeCell ref="F34:G34"/>
-    <mergeCell ref="F35:G35"/>
-    <mergeCell ref="F36:G36"/>
-    <mergeCell ref="F37:G37"/>
-    <mergeCell ref="F28:G28"/>
-    <mergeCell ref="F29:G29"/>
-    <mergeCell ref="F30:G30"/>
-    <mergeCell ref="F31:G31"/>
-    <mergeCell ref="F32:G32"/>
-    <mergeCell ref="F23:G23"/>
-    <mergeCell ref="F24:G24"/>
-    <mergeCell ref="F25:G25"/>
-    <mergeCell ref="F26:G26"/>
-    <mergeCell ref="F27:G27"/>
-    <mergeCell ref="F18:G18"/>
-    <mergeCell ref="F19:G19"/>
-    <mergeCell ref="F20:G20"/>
-    <mergeCell ref="F21:G21"/>
-    <mergeCell ref="F22:G22"/>
-    <mergeCell ref="F13:G13"/>
-    <mergeCell ref="F14:G14"/>
-    <mergeCell ref="F15:G15"/>
-    <mergeCell ref="F16:G16"/>
-    <mergeCell ref="F17:G17"/>
-    <mergeCell ref="F8:G8"/>
-    <mergeCell ref="F9:G9"/>
-    <mergeCell ref="F10:G10"/>
-    <mergeCell ref="F11:G11"/>
-    <mergeCell ref="F12:G12"/>
-    <mergeCell ref="A1:C1"/>
-    <mergeCell ref="A5:C5"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="B6:D6"/>
-    <mergeCell ref="E6:E7"/>
-    <mergeCell ref="A2:H4"/>
-    <mergeCell ref="F6:G7"/>
-    <mergeCell ref="H6:H7"/>
   </mergeCells>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.75" right="0.75" top="0.6" bottom="0.61" header="0.4" footer="0.39"/>
@@ -6264,458 +6264,458 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="41" t="s">
+      <c r="A1" s="103" t="s">
         <v>29</v>
       </c>
-      <c r="B1" s="42"/>
-      <c r="C1" s="43"/>
+      <c r="B1" s="104"/>
+      <c r="C1" s="105"/>
       <c r="D1" s="19"/>
     </row>
     <row r="2" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="32" t="s">
+      <c r="A2" s="39" t="s">
         <v>30</v>
       </c>
-      <c r="B2" s="32"/>
-      <c r="C2" s="32"/>
-      <c r="D2" s="32"/>
-      <c r="E2" s="32"/>
-      <c r="F2" s="32"/>
-      <c r="G2" s="32"/>
-      <c r="H2" s="32"/>
-      <c r="I2" s="32"/>
+      <c r="B2" s="39"/>
+      <c r="C2" s="39"/>
+      <c r="D2" s="39"/>
+      <c r="E2" s="39"/>
+      <c r="F2" s="39"/>
+      <c r="G2" s="39"/>
+      <c r="H2" s="39"/>
+      <c r="I2" s="39"/>
     </row>
     <row r="3" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="32"/>
-      <c r="B3" s="32"/>
-      <c r="C3" s="32"/>
-      <c r="D3" s="32"/>
-      <c r="E3" s="32"/>
-      <c r="F3" s="32"/>
-      <c r="G3" s="32"/>
-      <c r="H3" s="32"/>
-      <c r="I3" s="32"/>
+      <c r="A3" s="39"/>
+      <c r="B3" s="39"/>
+      <c r="C3" s="39"/>
+      <c r="D3" s="39"/>
+      <c r="E3" s="39"/>
+      <c r="F3" s="39"/>
+      <c r="G3" s="39"/>
+      <c r="H3" s="39"/>
+      <c r="I3" s="39"/>
     </row>
     <row r="4" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="33"/>
-      <c r="B4" s="33"/>
+      <c r="A4" s="37"/>
+      <c r="B4" s="37"/>
     </row>
     <row r="5" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="34" t="s">
+      <c r="A5" s="38" t="s">
         <v>21</v>
       </c>
-      <c r="B5" s="35" t="s">
+      <c r="B5" s="44" t="s">
         <v>31</v>
       </c>
-      <c r="C5" s="35" t="s">
+      <c r="C5" s="44" t="s">
         <v>32</v>
       </c>
-      <c r="D5" s="37" t="s">
+      <c r="D5" s="40" t="s">
         <v>24</v>
       </c>
-      <c r="E5" s="38"/>
-      <c r="F5" s="38"/>
-      <c r="G5" s="38"/>
-      <c r="H5" s="38"/>
-      <c r="I5" s="34" t="s">
+      <c r="E5" s="41"/>
+      <c r="F5" s="41"/>
+      <c r="G5" s="41"/>
+      <c r="H5" s="41"/>
+      <c r="I5" s="38" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="6" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="34"/>
-      <c r="B6" s="36"/>
-      <c r="C6" s="36"/>
-      <c r="D6" s="39"/>
-      <c r="E6" s="40"/>
-      <c r="F6" s="40"/>
-      <c r="G6" s="40"/>
-      <c r="H6" s="40"/>
-      <c r="I6" s="34"/>
+      <c r="A6" s="38"/>
+      <c r="B6" s="45"/>
+      <c r="C6" s="45"/>
+      <c r="D6" s="42"/>
+      <c r="E6" s="43"/>
+      <c r="F6" s="43"/>
+      <c r="G6" s="43"/>
+      <c r="H6" s="43"/>
+      <c r="I6" s="38"/>
     </row>
     <row r="7" spans="1:9" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A7" s="4">
         <v>1</v>
       </c>
-      <c r="B7" s="28" t="s">
+      <c r="B7" s="101" t="s">
         <v>33</v>
       </c>
       <c r="C7" s="22" t="s">
         <v>120</v>
       </c>
-      <c r="D7" s="44" t="s">
+      <c r="D7" s="53" t="s">
         <v>121</v>
       </c>
-      <c r="E7" s="44"/>
-      <c r="F7" s="44"/>
-      <c r="G7" s="44"/>
-      <c r="H7" s="44"/>
+      <c r="E7" s="53"/>
+      <c r="F7" s="53"/>
+      <c r="G7" s="53"/>
+      <c r="H7" s="53"/>
       <c r="I7" s="22"/>
     </row>
     <row r="8" spans="1:9" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A8" s="4">
         <v>2</v>
       </c>
-      <c r="B8" s="29"/>
+      <c r="B8" s="107"/>
       <c r="C8" s="22"/>
-      <c r="D8" s="44"/>
-      <c r="E8" s="44"/>
-      <c r="F8" s="44"/>
-      <c r="G8" s="44"/>
-      <c r="H8" s="44"/>
+      <c r="D8" s="53"/>
+      <c r="E8" s="53"/>
+      <c r="F8" s="53"/>
+      <c r="G8" s="53"/>
+      <c r="H8" s="53"/>
       <c r="I8" s="22"/>
     </row>
     <row r="9" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="4">
         <v>3</v>
       </c>
-      <c r="B9" s="29"/>
+      <c r="B9" s="107"/>
       <c r="C9" s="22"/>
-      <c r="D9" s="44"/>
-      <c r="E9" s="44"/>
-      <c r="F9" s="44"/>
-      <c r="G9" s="44"/>
-      <c r="H9" s="44"/>
+      <c r="D9" s="53"/>
+      <c r="E9" s="53"/>
+      <c r="F9" s="53"/>
+      <c r="G9" s="53"/>
+      <c r="H9" s="53"/>
       <c r="I9" s="22"/>
     </row>
     <row r="10" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="4">
         <v>4</v>
       </c>
-      <c r="B10" s="30"/>
+      <c r="B10" s="102"/>
       <c r="C10" s="22"/>
-      <c r="D10" s="44"/>
-      <c r="E10" s="44"/>
-      <c r="F10" s="44"/>
-      <c r="G10" s="44"/>
-      <c r="H10" s="44"/>
+      <c r="D10" s="53"/>
+      <c r="E10" s="53"/>
+      <c r="F10" s="53"/>
+      <c r="G10" s="53"/>
+      <c r="H10" s="53"/>
       <c r="I10" s="22"/>
     </row>
     <row r="11" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="4">
         <v>5</v>
       </c>
-      <c r="B11" s="31" t="s">
+      <c r="B11" s="106" t="s">
         <v>34</v>
       </c>
-      <c r="C11" s="28" t="s">
+      <c r="C11" s="101" t="s">
         <v>122</v>
       </c>
-      <c r="D11" s="44" t="s">
+      <c r="D11" s="53" t="s">
         <v>123</v>
       </c>
-      <c r="E11" s="44"/>
-      <c r="F11" s="44"/>
-      <c r="G11" s="44"/>
-      <c r="H11" s="44"/>
+      <c r="E11" s="53"/>
+      <c r="F11" s="53"/>
+      <c r="G11" s="53"/>
+      <c r="H11" s="53"/>
       <c r="I11" s="22"/>
     </row>
     <row r="12" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="4">
         <v>6</v>
       </c>
-      <c r="B12" s="29"/>
-      <c r="C12" s="30"/>
-      <c r="D12" s="44" t="s">
+      <c r="B12" s="107"/>
+      <c r="C12" s="102"/>
+      <c r="D12" s="53" t="s">
         <v>124</v>
       </c>
-      <c r="E12" s="44"/>
-      <c r="F12" s="44"/>
-      <c r="G12" s="44"/>
-      <c r="H12" s="44"/>
+      <c r="E12" s="53"/>
+      <c r="F12" s="53"/>
+      <c r="G12" s="53"/>
+      <c r="H12" s="53"/>
       <c r="I12" s="22"/>
     </row>
     <row r="13" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="4">
         <v>7</v>
       </c>
-      <c r="B13" s="29"/>
+      <c r="B13" s="107"/>
       <c r="C13" s="22" t="s">
         <v>125</v>
       </c>
-      <c r="D13" s="199" t="s">
+      <c r="D13" s="108" t="s">
         <v>126</v>
       </c>
-      <c r="E13" s="199"/>
-      <c r="F13" s="199"/>
-      <c r="G13" s="199"/>
-      <c r="H13" s="199"/>
+      <c r="E13" s="108"/>
+      <c r="F13" s="108"/>
+      <c r="G13" s="108"/>
+      <c r="H13" s="108"/>
       <c r="I13" s="22"/>
     </row>
     <row r="14" spans="1:9" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A14" s="4">
         <v>8</v>
       </c>
-      <c r="B14" s="30"/>
+      <c r="B14" s="102"/>
       <c r="C14" s="22"/>
-      <c r="D14" s="44"/>
-      <c r="E14" s="44"/>
-      <c r="F14" s="44"/>
-      <c r="G14" s="44"/>
-      <c r="H14" s="44"/>
+      <c r="D14" s="53"/>
+      <c r="E14" s="53"/>
+      <c r="F14" s="53"/>
+      <c r="G14" s="53"/>
+      <c r="H14" s="53"/>
       <c r="I14" s="22"/>
     </row>
     <row r="15" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="4">
         <v>9</v>
       </c>
-      <c r="B15" s="31" t="s">
+      <c r="B15" s="106" t="s">
         <v>35</v>
       </c>
       <c r="C15" s="22" t="s">
         <v>127</v>
       </c>
-      <c r="D15" s="44" t="s">
+      <c r="D15" s="53" t="s">
         <v>128</v>
       </c>
-      <c r="E15" s="44"/>
-      <c r="F15" s="44"/>
-      <c r="G15" s="44"/>
-      <c r="H15" s="44"/>
+      <c r="E15" s="53"/>
+      <c r="F15" s="53"/>
+      <c r="G15" s="53"/>
+      <c r="H15" s="53"/>
       <c r="I15" s="22"/>
     </row>
     <row r="16" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="4">
         <v>10</v>
       </c>
-      <c r="B16" s="29"/>
+      <c r="B16" s="107"/>
       <c r="C16" s="22"/>
-      <c r="D16" s="44"/>
-      <c r="E16" s="44"/>
-      <c r="F16" s="44"/>
-      <c r="G16" s="44"/>
-      <c r="H16" s="44"/>
+      <c r="D16" s="53"/>
+      <c r="E16" s="53"/>
+      <c r="F16" s="53"/>
+      <c r="G16" s="53"/>
+      <c r="H16" s="53"/>
       <c r="I16" s="22"/>
     </row>
     <row r="17" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="4">
         <v>11</v>
       </c>
-      <c r="B17" s="29"/>
+      <c r="B17" s="107"/>
       <c r="C17" s="22"/>
-      <c r="D17" s="44"/>
-      <c r="E17" s="44"/>
-      <c r="F17" s="44"/>
-      <c r="G17" s="44"/>
-      <c r="H17" s="44"/>
+      <c r="D17" s="53"/>
+      <c r="E17" s="53"/>
+      <c r="F17" s="53"/>
+      <c r="G17" s="53"/>
+      <c r="H17" s="53"/>
       <c r="I17" s="22"/>
     </row>
     <row r="18" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="4">
         <v>12</v>
       </c>
-      <c r="B18" s="30"/>
+      <c r="B18" s="102"/>
       <c r="C18" s="22"/>
-      <c r="D18" s="44"/>
-      <c r="E18" s="44"/>
-      <c r="F18" s="44"/>
-      <c r="G18" s="44"/>
-      <c r="H18" s="44"/>
+      <c r="D18" s="53"/>
+      <c r="E18" s="53"/>
+      <c r="F18" s="53"/>
+      <c r="G18" s="53"/>
+      <c r="H18" s="53"/>
       <c r="I18" s="22"/>
     </row>
     <row r="19" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="4">
         <v>13</v>
       </c>
-      <c r="B19" s="31" t="s">
+      <c r="B19" s="106" t="s">
         <v>36</v>
       </c>
       <c r="C19" s="22" t="s">
         <v>129</v>
       </c>
-      <c r="D19" s="44" t="s">
+      <c r="D19" s="53" t="s">
         <v>130</v>
       </c>
-      <c r="E19" s="44"/>
-      <c r="F19" s="44"/>
-      <c r="G19" s="44"/>
-      <c r="H19" s="44"/>
+      <c r="E19" s="53"/>
+      <c r="F19" s="53"/>
+      <c r="G19" s="53"/>
+      <c r="H19" s="53"/>
       <c r="I19" s="22"/>
     </row>
     <row r="20" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="4">
         <v>14</v>
       </c>
-      <c r="B20" s="29"/>
+      <c r="B20" s="107"/>
       <c r="C20" s="22"/>
-      <c r="D20" s="44"/>
-      <c r="E20" s="44"/>
-      <c r="F20" s="44"/>
-      <c r="G20" s="44"/>
-      <c r="H20" s="44"/>
+      <c r="D20" s="53"/>
+      <c r="E20" s="53"/>
+      <c r="F20" s="53"/>
+      <c r="G20" s="53"/>
+      <c r="H20" s="53"/>
       <c r="I20" s="22"/>
     </row>
     <row r="21" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="4">
         <v>15</v>
       </c>
-      <c r="B21" s="29"/>
+      <c r="B21" s="107"/>
       <c r="C21" s="22"/>
-      <c r="D21" s="44"/>
-      <c r="E21" s="44"/>
-      <c r="F21" s="44"/>
-      <c r="G21" s="44"/>
-      <c r="H21" s="44"/>
+      <c r="D21" s="53"/>
+      <c r="E21" s="53"/>
+      <c r="F21" s="53"/>
+      <c r="G21" s="53"/>
+      <c r="H21" s="53"/>
       <c r="I21" s="22"/>
     </row>
     <row r="22" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="4">
         <v>16</v>
       </c>
-      <c r="B22" s="30"/>
+      <c r="B22" s="102"/>
       <c r="C22" s="22"/>
-      <c r="D22" s="44"/>
-      <c r="E22" s="44"/>
-      <c r="F22" s="44"/>
-      <c r="G22" s="44"/>
-      <c r="H22" s="44"/>
+      <c r="D22" s="53"/>
+      <c r="E22" s="53"/>
+      <c r="F22" s="53"/>
+      <c r="G22" s="53"/>
+      <c r="H22" s="53"/>
       <c r="I22" s="22"/>
     </row>
     <row r="23" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="4">
         <v>17</v>
       </c>
-      <c r="B23" s="31" t="s">
+      <c r="B23" s="106" t="s">
         <v>37</v>
       </c>
       <c r="C23" s="22" t="s">
         <v>131</v>
       </c>
-      <c r="D23" s="44" t="s">
+      <c r="D23" s="53" t="s">
         <v>132</v>
       </c>
-      <c r="E23" s="44"/>
-      <c r="F23" s="44"/>
-      <c r="G23" s="44"/>
-      <c r="H23" s="44"/>
+      <c r="E23" s="53"/>
+      <c r="F23" s="53"/>
+      <c r="G23" s="53"/>
+      <c r="H23" s="53"/>
       <c r="I23" s="22"/>
     </row>
     <row r="24" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" s="4">
         <v>18</v>
       </c>
-      <c r="B24" s="201"/>
-      <c r="C24" s="200" t="s">
+      <c r="B24" s="109"/>
+      <c r="C24" s="28" t="s">
         <v>133</v>
       </c>
-      <c r="D24" s="44" t="s">
+      <c r="D24" s="53" t="s">
         <v>134</v>
       </c>
-      <c r="E24" s="44"/>
-      <c r="F24" s="44"/>
-      <c r="G24" s="44"/>
-      <c r="H24" s="44"/>
+      <c r="E24" s="53"/>
+      <c r="F24" s="53"/>
+      <c r="G24" s="53"/>
+      <c r="H24" s="53"/>
       <c r="I24" s="22"/>
     </row>
     <row r="25" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A25" s="4">
         <v>19</v>
       </c>
-      <c r="B25" s="201"/>
+      <c r="B25" s="109"/>
       <c r="C25" s="22" t="s">
         <v>135</v>
       </c>
-      <c r="D25" s="44" t="s">
+      <c r="D25" s="53" t="s">
         <v>136</v>
       </c>
-      <c r="E25" s="44"/>
-      <c r="F25" s="44"/>
-      <c r="G25" s="44"/>
-      <c r="H25" s="44"/>
+      <c r="E25" s="53"/>
+      <c r="F25" s="53"/>
+      <c r="G25" s="53"/>
+      <c r="H25" s="53"/>
       <c r="I25" s="22"/>
     </row>
     <row r="26" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26" s="4">
         <v>20</v>
       </c>
-      <c r="B26" s="201"/>
+      <c r="B26" s="109"/>
       <c r="C26" s="22" t="s">
         <v>137</v>
       </c>
-      <c r="D26" s="199" t="s">
+      <c r="D26" s="108" t="s">
         <v>138</v>
       </c>
-      <c r="E26" s="199"/>
-      <c r="F26" s="199"/>
-      <c r="G26" s="199"/>
-      <c r="H26" s="199"/>
+      <c r="E26" s="108"/>
+      <c r="F26" s="108"/>
+      <c r="G26" s="108"/>
+      <c r="H26" s="108"/>
       <c r="I26" s="22"/>
     </row>
     <row r="27" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A27" s="4">
         <v>21</v>
       </c>
-      <c r="B27" s="202"/>
+      <c r="B27" s="110"/>
       <c r="C27" s="22" t="s">
         <v>139</v>
       </c>
-      <c r="D27" s="45" t="s">
+      <c r="D27" s="98" t="s">
         <v>141</v>
       </c>
-      <c r="E27" s="46"/>
-      <c r="F27" s="46"/>
-      <c r="G27" s="46"/>
-      <c r="H27" s="47"/>
+      <c r="E27" s="99"/>
+      <c r="F27" s="99"/>
+      <c r="G27" s="99"/>
+      <c r="H27" s="100"/>
       <c r="I27" s="22"/>
     </row>
     <row r="28" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A28" s="4">
         <v>22</v>
       </c>
-      <c r="B28" s="31" t="s">
+      <c r="B28" s="106" t="s">
         <v>38</v>
       </c>
       <c r="C28" s="22" t="s">
         <v>140</v>
       </c>
-      <c r="D28" s="44" t="s">
-        <v>142</v>
-      </c>
-      <c r="E28" s="44"/>
-      <c r="F28" s="44"/>
-      <c r="G28" s="44"/>
-      <c r="H28" s="44"/>
+      <c r="D28" s="53" t="s">
+        <v>144</v>
+      </c>
+      <c r="E28" s="53"/>
+      <c r="F28" s="53"/>
+      <c r="G28" s="53"/>
+      <c r="H28" s="53"/>
       <c r="I28" s="22"/>
     </row>
     <row r="29" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A29" s="4">
         <v>23</v>
       </c>
-      <c r="B29" s="29"/>
+      <c r="B29" s="107"/>
       <c r="C29" s="22" t="s">
+        <v>142</v>
+      </c>
+      <c r="D29" s="53" t="s">
         <v>143</v>
       </c>
-      <c r="D29" s="44" t="s">
-        <v>144</v>
-      </c>
-      <c r="E29" s="44"/>
-      <c r="F29" s="44"/>
-      <c r="G29" s="44"/>
-      <c r="H29" s="44"/>
+      <c r="E29" s="53"/>
+      <c r="F29" s="53"/>
+      <c r="G29" s="53"/>
+      <c r="H29" s="53"/>
       <c r="I29" s="22"/>
     </row>
     <row r="30" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A30" s="4">
         <v>24</v>
       </c>
-      <c r="B30" s="29"/>
+      <c r="B30" s="107"/>
       <c r="C30" s="22"/>
-      <c r="D30" s="44"/>
-      <c r="E30" s="44"/>
-      <c r="F30" s="44"/>
-      <c r="G30" s="44"/>
-      <c r="H30" s="44"/>
+      <c r="D30" s="53"/>
+      <c r="E30" s="53"/>
+      <c r="F30" s="53"/>
+      <c r="G30" s="53"/>
+      <c r="H30" s="53"/>
       <c r="I30" s="22"/>
     </row>
     <row r="31" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A31" s="4">
         <v>25</v>
       </c>
-      <c r="B31" s="30"/>
+      <c r="B31" s="102"/>
       <c r="C31" s="22"/>
-      <c r="D31" s="44"/>
-      <c r="E31" s="44"/>
-      <c r="F31" s="44"/>
-      <c r="G31" s="44"/>
-      <c r="H31" s="44"/>
+      <c r="D31" s="53"/>
+      <c r="E31" s="53"/>
+      <c r="F31" s="53"/>
+      <c r="G31" s="53"/>
+      <c r="H31" s="53"/>
       <c r="I31" s="22"/>
     </row>
     <row r="32" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -6724,11 +6724,11 @@
       </c>
       <c r="B32" s="4"/>
       <c r="C32" s="22"/>
-      <c r="D32" s="44"/>
-      <c r="E32" s="44"/>
-      <c r="F32" s="44"/>
-      <c r="G32" s="44"/>
-      <c r="H32" s="44"/>
+      <c r="D32" s="53"/>
+      <c r="E32" s="53"/>
+      <c r="F32" s="53"/>
+      <c r="G32" s="53"/>
+      <c r="H32" s="53"/>
       <c r="I32" s="22"/>
     </row>
     <row r="33" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -6737,11 +6737,11 @@
       </c>
       <c r="B33" s="4"/>
       <c r="C33" s="22"/>
-      <c r="D33" s="44"/>
-      <c r="E33" s="44"/>
-      <c r="F33" s="44"/>
-      <c r="G33" s="44"/>
-      <c r="H33" s="44"/>
+      <c r="D33" s="53"/>
+      <c r="E33" s="53"/>
+      <c r="F33" s="53"/>
+      <c r="G33" s="53"/>
+      <c r="H33" s="53"/>
       <c r="I33" s="22"/>
     </row>
     <row r="34" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -6750,11 +6750,11 @@
       </c>
       <c r="B34" s="4"/>
       <c r="C34" s="22"/>
-      <c r="D34" s="44"/>
-      <c r="E34" s="44"/>
-      <c r="F34" s="44"/>
-      <c r="G34" s="44"/>
-      <c r="H34" s="44"/>
+      <c r="D34" s="53"/>
+      <c r="E34" s="53"/>
+      <c r="F34" s="53"/>
+      <c r="G34" s="53"/>
+      <c r="H34" s="53"/>
       <c r="I34" s="22"/>
     </row>
     <row r="35" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -6763,11 +6763,11 @@
       </c>
       <c r="B35" s="4"/>
       <c r="C35" s="22"/>
-      <c r="D35" s="44"/>
-      <c r="E35" s="44"/>
-      <c r="F35" s="44"/>
-      <c r="G35" s="44"/>
-      <c r="H35" s="44"/>
+      <c r="D35" s="53"/>
+      <c r="E35" s="53"/>
+      <c r="F35" s="53"/>
+      <c r="G35" s="53"/>
+      <c r="H35" s="53"/>
       <c r="I35" s="22"/>
     </row>
     <row r="36" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -6776,11 +6776,11 @@
       </c>
       <c r="B36" s="4"/>
       <c r="C36" s="22"/>
-      <c r="D36" s="44"/>
-      <c r="E36" s="44"/>
-      <c r="F36" s="44"/>
-      <c r="G36" s="44"/>
-      <c r="H36" s="44"/>
+      <c r="D36" s="53"/>
+      <c r="E36" s="53"/>
+      <c r="F36" s="53"/>
+      <c r="G36" s="53"/>
+      <c r="H36" s="53"/>
       <c r="I36" s="22"/>
     </row>
     <row r="37" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -6789,20 +6789,29 @@
       </c>
       <c r="B37" s="4"/>
       <c r="C37" s="22"/>
-      <c r="D37" s="44"/>
-      <c r="E37" s="44"/>
-      <c r="F37" s="44"/>
-      <c r="G37" s="44"/>
-      <c r="H37" s="44"/>
+      <c r="D37" s="53"/>
+      <c r="E37" s="53"/>
+      <c r="F37" s="53"/>
+      <c r="G37" s="53"/>
+      <c r="H37" s="53"/>
       <c r="I37" s="22"/>
     </row>
   </sheetData>
   <mergeCells count="46">
-    <mergeCell ref="D27:H27"/>
-    <mergeCell ref="C11:C12"/>
-    <mergeCell ref="A1:C1"/>
-    <mergeCell ref="D33:H33"/>
-    <mergeCell ref="D34:H34"/>
+    <mergeCell ref="B19:B22"/>
+    <mergeCell ref="B28:B31"/>
+    <mergeCell ref="B23:B27"/>
+    <mergeCell ref="B5:B6"/>
+    <mergeCell ref="D5:H6"/>
+    <mergeCell ref="I5:I6"/>
+    <mergeCell ref="B7:B10"/>
+    <mergeCell ref="B15:B18"/>
+    <mergeCell ref="D37:H37"/>
+    <mergeCell ref="D28:H28"/>
+    <mergeCell ref="D29:H29"/>
+    <mergeCell ref="D30:H30"/>
+    <mergeCell ref="D31:H31"/>
+    <mergeCell ref="D32:H32"/>
     <mergeCell ref="D35:H35"/>
     <mergeCell ref="D36:H36"/>
     <mergeCell ref="B11:B14"/>
@@ -6816,15 +6825,14 @@
     <mergeCell ref="D12:H12"/>
     <mergeCell ref="D13:H13"/>
     <mergeCell ref="D14:H14"/>
-    <mergeCell ref="D37:H37"/>
-    <mergeCell ref="D28:H28"/>
-    <mergeCell ref="D29:H29"/>
-    <mergeCell ref="D30:H30"/>
-    <mergeCell ref="D31:H31"/>
-    <mergeCell ref="D32:H32"/>
     <mergeCell ref="D15:H15"/>
     <mergeCell ref="D16:H16"/>
     <mergeCell ref="D17:H17"/>
+    <mergeCell ref="D27:H27"/>
+    <mergeCell ref="C11:C12"/>
+    <mergeCell ref="A1:C1"/>
+    <mergeCell ref="D33:H33"/>
+    <mergeCell ref="D34:H34"/>
     <mergeCell ref="D25:H25"/>
     <mergeCell ref="D26:H26"/>
     <mergeCell ref="D20:H20"/>
@@ -6836,14 +6844,6 @@
     <mergeCell ref="A4:B4"/>
     <mergeCell ref="A5:A6"/>
     <mergeCell ref="C5:C6"/>
-    <mergeCell ref="B5:B6"/>
-    <mergeCell ref="D5:H6"/>
-    <mergeCell ref="I5:I6"/>
-    <mergeCell ref="B7:B10"/>
-    <mergeCell ref="B15:B18"/>
-    <mergeCell ref="B19:B22"/>
-    <mergeCell ref="B28:B31"/>
-    <mergeCell ref="B23:B27"/>
   </mergeCells>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.75" right="0.75" top="0.6" bottom="0.61" header="0.4" footer="0.39"/>
@@ -6867,23 +6867,23 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:52" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B1" s="194" t="s">
+      <c r="B1" s="111" t="s">
         <v>39</v>
       </c>
-      <c r="C1" s="195"/>
-      <c r="D1" s="195"/>
-      <c r="E1" s="195"/>
-      <c r="F1" s="195"/>
-      <c r="G1" s="195"/>
-      <c r="H1" s="195"/>
-      <c r="I1" s="195"/>
-      <c r="J1" s="195"/>
-      <c r="K1" s="195"/>
-      <c r="L1" s="195"/>
-      <c r="M1" s="195"/>
-      <c r="N1" s="195"/>
-      <c r="O1" s="195"/>
-      <c r="P1" s="195"/>
+      <c r="C1" s="112"/>
+      <c r="D1" s="112"/>
+      <c r="E1" s="112"/>
+      <c r="F1" s="112"/>
+      <c r="G1" s="112"/>
+      <c r="H1" s="112"/>
+      <c r="I1" s="112"/>
+      <c r="J1" s="112"/>
+      <c r="K1" s="112"/>
+      <c r="L1" s="112"/>
+      <c r="M1" s="112"/>
+      <c r="N1" s="112"/>
+      <c r="O1" s="112"/>
+      <c r="P1" s="112"/>
       <c r="Q1" s="21"/>
       <c r="R1" s="20"/>
       <c r="S1" s="20"/>
@@ -6900,139 +6900,139 @@
       <c r="AD1" s="20"/>
     </row>
     <row r="2" spans="2:52" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B2" s="143" t="s">
+      <c r="B2" s="191" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="143"/>
-      <c r="D2" s="143"/>
-      <c r="E2" s="143"/>
-      <c r="F2" s="143"/>
-      <c r="G2" s="143"/>
-      <c r="H2" s="143"/>
-      <c r="I2" s="143"/>
-      <c r="J2" s="147"/>
-      <c r="K2" s="147"/>
-      <c r="L2" s="147"/>
-      <c r="M2" s="147"/>
-      <c r="N2" s="147"/>
-      <c r="O2" s="147"/>
-      <c r="P2" s="147"/>
-      <c r="Q2" s="147"/>
-      <c r="R2" s="147"/>
-      <c r="S2" s="147"/>
-      <c r="T2" s="147"/>
-      <c r="U2" s="147"/>
-      <c r="V2" s="147"/>
-      <c r="W2" s="147"/>
-      <c r="X2" s="147"/>
-      <c r="Y2" s="147"/>
-      <c r="Z2" s="147"/>
-      <c r="AA2" s="147"/>
-      <c r="AB2" s="147"/>
-      <c r="AC2" s="147"/>
-      <c r="AD2" s="147"/>
+      <c r="C2" s="191"/>
+      <c r="D2" s="191"/>
+      <c r="E2" s="191"/>
+      <c r="F2" s="191"/>
+      <c r="G2" s="191"/>
+      <c r="H2" s="191"/>
+      <c r="I2" s="191"/>
+      <c r="J2" s="120"/>
+      <c r="K2" s="120"/>
+      <c r="L2" s="120"/>
+      <c r="M2" s="120"/>
+      <c r="N2" s="120"/>
+      <c r="O2" s="120"/>
+      <c r="P2" s="120"/>
+      <c r="Q2" s="120"/>
+      <c r="R2" s="120"/>
+      <c r="S2" s="120"/>
+      <c r="T2" s="120"/>
+      <c r="U2" s="120"/>
+      <c r="V2" s="120"/>
+      <c r="W2" s="120"/>
+      <c r="X2" s="120"/>
+      <c r="Y2" s="120"/>
+      <c r="Z2" s="120"/>
+      <c r="AA2" s="120"/>
+      <c r="AB2" s="120"/>
+      <c r="AC2" s="120"/>
+      <c r="AD2" s="120"/>
     </row>
     <row r="3" spans="2:52" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="4" spans="2:52" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B4" s="154" t="s">
+      <c r="B4" s="199" t="s">
         <v>40</v>
       </c>
-      <c r="C4" s="141"/>
-      <c r="D4" s="141"/>
-      <c r="E4" s="141"/>
-      <c r="F4" s="141"/>
-      <c r="G4" s="141"/>
-      <c r="H4" s="141"/>
-      <c r="I4" s="141"/>
-      <c r="J4" s="141" t="s">
+      <c r="C4" s="189"/>
+      <c r="D4" s="189"/>
+      <c r="E4" s="189"/>
+      <c r="F4" s="189"/>
+      <c r="G4" s="189"/>
+      <c r="H4" s="189"/>
+      <c r="I4" s="189"/>
+      <c r="J4" s="189" t="s">
         <v>41</v>
       </c>
-      <c r="K4" s="141"/>
-      <c r="L4" s="141"/>
-      <c r="M4" s="141"/>
-      <c r="N4" s="141"/>
-      <c r="O4" s="141"/>
-      <c r="P4" s="141"/>
-      <c r="Q4" s="148" t="s">
+      <c r="K4" s="189"/>
+      <c r="L4" s="189"/>
+      <c r="M4" s="189"/>
+      <c r="N4" s="189"/>
+      <c r="O4" s="189"/>
+      <c r="P4" s="189"/>
+      <c r="Q4" s="193" t="s">
         <v>42</v>
       </c>
-      <c r="R4" s="152"/>
-      <c r="S4" s="149"/>
-      <c r="T4" s="148" t="s">
+      <c r="R4" s="197"/>
+      <c r="S4" s="194"/>
+      <c r="T4" s="193" t="s">
         <v>43</v>
       </c>
-      <c r="U4" s="152"/>
-      <c r="V4" s="152"/>
-      <c r="W4" s="149"/>
-      <c r="X4" s="148" t="s">
+      <c r="U4" s="197"/>
+      <c r="V4" s="197"/>
+      <c r="W4" s="194"/>
+      <c r="X4" s="193" t="s">
         <v>44</v>
       </c>
-      <c r="Y4" s="149"/>
-      <c r="Z4" s="141" t="s">
+      <c r="Y4" s="194"/>
+      <c r="Z4" s="189" t="s">
         <v>45</v>
       </c>
-      <c r="AA4" s="141"/>
-      <c r="AB4" s="141"/>
-      <c r="AC4" s="141" t="s">
+      <c r="AA4" s="189"/>
+      <c r="AB4" s="189"/>
+      <c r="AC4" s="189" t="s">
         <v>45</v>
       </c>
-      <c r="AD4" s="141"/>
-      <c r="AE4" s="141"/>
-      <c r="AF4" s="141" t="s">
+      <c r="AD4" s="189"/>
+      <c r="AE4" s="189"/>
+      <c r="AF4" s="189" t="s">
         <v>45</v>
       </c>
-      <c r="AG4" s="141"/>
-      <c r="AH4" s="141"/>
-      <c r="AI4" s="141" t="s">
+      <c r="AG4" s="189"/>
+      <c r="AH4" s="189"/>
+      <c r="AI4" s="189" t="s">
         <v>45</v>
       </c>
-      <c r="AJ4" s="141"/>
-      <c r="AK4" s="141"/>
-      <c r="AL4" s="141" t="s">
+      <c r="AJ4" s="189"/>
+      <c r="AK4" s="189"/>
+      <c r="AL4" s="189" t="s">
         <v>45</v>
       </c>
-      <c r="AM4" s="141"/>
-      <c r="AN4" s="141"/>
-      <c r="AO4" s="141" t="s">
+      <c r="AM4" s="189"/>
+      <c r="AN4" s="189"/>
+      <c r="AO4" s="189" t="s">
         <v>46</v>
       </c>
-      <c r="AP4" s="141"/>
-      <c r="AQ4" s="141"/>
-      <c r="AR4" s="141"/>
-      <c r="AS4" s="141"/>
-      <c r="AT4" s="141"/>
-      <c r="AU4" s="141"/>
-      <c r="AV4" s="141"/>
-      <c r="AW4" s="141"/>
-      <c r="AX4" s="141"/>
-      <c r="AY4" s="141"/>
-      <c r="AZ4" s="142"/>
+      <c r="AP4" s="189"/>
+      <c r="AQ4" s="189"/>
+      <c r="AR4" s="189"/>
+      <c r="AS4" s="189"/>
+      <c r="AT4" s="189"/>
+      <c r="AU4" s="189"/>
+      <c r="AV4" s="189"/>
+      <c r="AW4" s="189"/>
+      <c r="AX4" s="189"/>
+      <c r="AY4" s="189"/>
+      <c r="AZ4" s="190"/>
     </row>
     <row r="5" spans="2:52" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B5" s="155"/>
-      <c r="C5" s="143"/>
-      <c r="D5" s="143"/>
-      <c r="E5" s="143"/>
-      <c r="F5" s="143"/>
-      <c r="G5" s="143"/>
-      <c r="H5" s="143"/>
-      <c r="I5" s="143"/>
-      <c r="J5" s="143"/>
-      <c r="K5" s="143"/>
-      <c r="L5" s="143"/>
-      <c r="M5" s="143"/>
-      <c r="N5" s="143"/>
-      <c r="O5" s="143"/>
-      <c r="P5" s="143"/>
-      <c r="Q5" s="150"/>
-      <c r="R5" s="153"/>
-      <c r="S5" s="151"/>
-      <c r="T5" s="150"/>
-      <c r="U5" s="153"/>
-      <c r="V5" s="153"/>
-      <c r="W5" s="151"/>
-      <c r="X5" s="150"/>
-      <c r="Y5" s="151"/>
+      <c r="B5" s="200"/>
+      <c r="C5" s="191"/>
+      <c r="D5" s="191"/>
+      <c r="E5" s="191"/>
+      <c r="F5" s="191"/>
+      <c r="G5" s="191"/>
+      <c r="H5" s="191"/>
+      <c r="I5" s="191"/>
+      <c r="J5" s="191"/>
+      <c r="K5" s="191"/>
+      <c r="L5" s="191"/>
+      <c r="M5" s="191"/>
+      <c r="N5" s="191"/>
+      <c r="O5" s="191"/>
+      <c r="P5" s="191"/>
+      <c r="Q5" s="195"/>
+      <c r="R5" s="198"/>
+      <c r="S5" s="196"/>
+      <c r="T5" s="195"/>
+      <c r="U5" s="198"/>
+      <c r="V5" s="198"/>
+      <c r="W5" s="196"/>
+      <c r="X5" s="195"/>
+      <c r="Y5" s="196"/>
       <c r="Z5" s="6" t="s">
         <v>47</v>
       </c>
@@ -7078,54 +7078,54 @@
       <c r="AN5" s="8" t="s">
         <v>49</v>
       </c>
-      <c r="AO5" s="143"/>
-      <c r="AP5" s="143"/>
-      <c r="AQ5" s="143"/>
-      <c r="AR5" s="143"/>
-      <c r="AS5" s="143"/>
-      <c r="AT5" s="143"/>
-      <c r="AU5" s="143"/>
-      <c r="AV5" s="143"/>
-      <c r="AW5" s="143"/>
-      <c r="AX5" s="143"/>
-      <c r="AY5" s="143"/>
-      <c r="AZ5" s="144"/>
+      <c r="AO5" s="191"/>
+      <c r="AP5" s="191"/>
+      <c r="AQ5" s="191"/>
+      <c r="AR5" s="191"/>
+      <c r="AS5" s="191"/>
+      <c r="AT5" s="191"/>
+      <c r="AU5" s="191"/>
+      <c r="AV5" s="191"/>
+      <c r="AW5" s="191"/>
+      <c r="AX5" s="191"/>
+      <c r="AY5" s="191"/>
+      <c r="AZ5" s="192"/>
     </row>
     <row r="6" spans="2:52" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B6" s="170">
+      <c r="B6" s="117">
         <v>1</v>
       </c>
-      <c r="C6" s="156" t="s">
+      <c r="C6" s="113" t="s">
         <v>50</v>
       </c>
-      <c r="D6" s="156"/>
-      <c r="E6" s="156"/>
-      <c r="F6" s="156"/>
-      <c r="G6" s="156"/>
-      <c r="H6" s="156"/>
-      <c r="I6" s="156"/>
-      <c r="J6" s="156"/>
-      <c r="K6" s="156"/>
-      <c r="L6" s="156"/>
-      <c r="M6" s="156"/>
-      <c r="N6" s="156"/>
-      <c r="O6" s="156"/>
-      <c r="P6" s="156"/>
-      <c r="Q6" s="147"/>
-      <c r="R6" s="147"/>
-      <c r="S6" s="147"/>
-      <c r="T6" s="161" t="s">
+      <c r="D6" s="113"/>
+      <c r="E6" s="113"/>
+      <c r="F6" s="113"/>
+      <c r="G6" s="113"/>
+      <c r="H6" s="113"/>
+      <c r="I6" s="113"/>
+      <c r="J6" s="113"/>
+      <c r="K6" s="113"/>
+      <c r="L6" s="113"/>
+      <c r="M6" s="113"/>
+      <c r="N6" s="113"/>
+      <c r="O6" s="113"/>
+      <c r="P6" s="113"/>
+      <c r="Q6" s="120"/>
+      <c r="R6" s="120"/>
+      <c r="S6" s="120"/>
+      <c r="T6" s="118" t="s">
         <v>51</v>
       </c>
-      <c r="U6" s="161"/>
-      <c r="V6" s="159">
+      <c r="U6" s="118"/>
+      <c r="V6" s="115">
         <v>0</v>
       </c>
-      <c r="W6" s="159"/>
-      <c r="X6" s="145">
+      <c r="W6" s="115"/>
+      <c r="X6" s="136">
         <v>0</v>
       </c>
-      <c r="Y6" s="145"/>
+      <c r="Y6" s="136"/>
       <c r="Z6" s="9"/>
       <c r="AA6" s="10"/>
       <c r="AB6" s="11"/>
@@ -7141,50 +7141,50 @@
       <c r="AL6" s="9"/>
       <c r="AM6" s="10"/>
       <c r="AN6" s="11"/>
-      <c r="AO6" s="156"/>
-      <c r="AP6" s="156"/>
-      <c r="AQ6" s="156"/>
-      <c r="AR6" s="156"/>
-      <c r="AS6" s="156"/>
-      <c r="AT6" s="156"/>
-      <c r="AU6" s="156"/>
-      <c r="AV6" s="156"/>
-      <c r="AW6" s="156"/>
-      <c r="AX6" s="156"/>
-      <c r="AY6" s="156"/>
-      <c r="AZ6" s="157"/>
+      <c r="AO6" s="113"/>
+      <c r="AP6" s="113"/>
+      <c r="AQ6" s="113"/>
+      <c r="AR6" s="113"/>
+      <c r="AS6" s="113"/>
+      <c r="AT6" s="113"/>
+      <c r="AU6" s="113"/>
+      <c r="AV6" s="113"/>
+      <c r="AW6" s="113"/>
+      <c r="AX6" s="113"/>
+      <c r="AY6" s="113"/>
+      <c r="AZ6" s="135"/>
     </row>
     <row r="7" spans="2:52" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B7" s="170"/>
-      <c r="C7" s="156"/>
-      <c r="D7" s="156"/>
-      <c r="E7" s="156"/>
-      <c r="F7" s="156"/>
-      <c r="G7" s="156"/>
-      <c r="H7" s="156"/>
-      <c r="I7" s="156"/>
-      <c r="J7" s="156"/>
-      <c r="K7" s="156"/>
-      <c r="L7" s="156"/>
-      <c r="M7" s="156"/>
-      <c r="N7" s="156"/>
-      <c r="O7" s="156"/>
-      <c r="P7" s="156"/>
-      <c r="Q7" s="147"/>
-      <c r="R7" s="147"/>
-      <c r="S7" s="147"/>
-      <c r="T7" s="158" t="s">
+      <c r="B7" s="117"/>
+      <c r="C7" s="113"/>
+      <c r="D7" s="113"/>
+      <c r="E7" s="113"/>
+      <c r="F7" s="113"/>
+      <c r="G7" s="113"/>
+      <c r="H7" s="113"/>
+      <c r="I7" s="113"/>
+      <c r="J7" s="113"/>
+      <c r="K7" s="113"/>
+      <c r="L7" s="113"/>
+      <c r="M7" s="113"/>
+      <c r="N7" s="113"/>
+      <c r="O7" s="113"/>
+      <c r="P7" s="113"/>
+      <c r="Q7" s="120"/>
+      <c r="R7" s="120"/>
+      <c r="S7" s="120"/>
+      <c r="T7" s="119" t="s">
         <v>25</v>
       </c>
-      <c r="U7" s="158"/>
-      <c r="V7" s="160">
+      <c r="U7" s="119"/>
+      <c r="V7" s="116">
         <v>0</v>
       </c>
-      <c r="W7" s="160"/>
-      <c r="X7" s="146">
+      <c r="W7" s="116"/>
+      <c r="X7" s="137">
         <v>0</v>
       </c>
-      <c r="Y7" s="146"/>
+      <c r="Y7" s="137"/>
       <c r="Z7" s="12"/>
       <c r="AA7" s="13"/>
       <c r="AB7" s="14"/>
@@ -7200,54 +7200,54 @@
       <c r="AL7" s="12"/>
       <c r="AM7" s="13"/>
       <c r="AN7" s="14"/>
-      <c r="AO7" s="156"/>
-      <c r="AP7" s="156"/>
-      <c r="AQ7" s="156"/>
-      <c r="AR7" s="156"/>
-      <c r="AS7" s="156"/>
-      <c r="AT7" s="156"/>
-      <c r="AU7" s="156"/>
-      <c r="AV7" s="156"/>
-      <c r="AW7" s="156"/>
-      <c r="AX7" s="156"/>
-      <c r="AY7" s="156"/>
-      <c r="AZ7" s="157"/>
+      <c r="AO7" s="113"/>
+      <c r="AP7" s="113"/>
+      <c r="AQ7" s="113"/>
+      <c r="AR7" s="113"/>
+      <c r="AS7" s="113"/>
+      <c r="AT7" s="113"/>
+      <c r="AU7" s="113"/>
+      <c r="AV7" s="113"/>
+      <c r="AW7" s="113"/>
+      <c r="AX7" s="113"/>
+      <c r="AY7" s="113"/>
+      <c r="AZ7" s="135"/>
     </row>
     <row r="8" spans="2:52" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B8" s="170">
+      <c r="B8" s="117">
         <v>2</v>
       </c>
-      <c r="C8" s="156" t="s">
+      <c r="C8" s="113" t="s">
         <v>52</v>
       </c>
-      <c r="D8" s="156"/>
-      <c r="E8" s="156"/>
-      <c r="F8" s="156"/>
-      <c r="G8" s="156"/>
-      <c r="H8" s="156"/>
-      <c r="I8" s="156"/>
-      <c r="J8" s="115"/>
-      <c r="K8" s="116"/>
-      <c r="L8" s="116"/>
-      <c r="M8" s="116"/>
-      <c r="N8" s="116"/>
-      <c r="O8" s="116"/>
-      <c r="P8" s="117"/>
-      <c r="Q8" s="147"/>
-      <c r="R8" s="147"/>
-      <c r="S8" s="147"/>
-      <c r="T8" s="161" t="s">
+      <c r="D8" s="113"/>
+      <c r="E8" s="113"/>
+      <c r="F8" s="113"/>
+      <c r="G8" s="113"/>
+      <c r="H8" s="113"/>
+      <c r="I8" s="113"/>
+      <c r="J8" s="121"/>
+      <c r="K8" s="122"/>
+      <c r="L8" s="122"/>
+      <c r="M8" s="122"/>
+      <c r="N8" s="122"/>
+      <c r="O8" s="122"/>
+      <c r="P8" s="123"/>
+      <c r="Q8" s="120"/>
+      <c r="R8" s="120"/>
+      <c r="S8" s="120"/>
+      <c r="T8" s="118" t="s">
         <v>51</v>
       </c>
-      <c r="U8" s="161"/>
-      <c r="V8" s="159">
+      <c r="U8" s="118"/>
+      <c r="V8" s="115">
         <v>0</v>
       </c>
-      <c r="W8" s="159"/>
-      <c r="X8" s="145">
+      <c r="W8" s="115"/>
+      <c r="X8" s="136">
         <v>0</v>
       </c>
-      <c r="Y8" s="145"/>
+      <c r="Y8" s="136"/>
       <c r="Z8" s="9"/>
       <c r="AA8" s="10"/>
       <c r="AB8" s="11"/>
@@ -7263,50 +7263,50 @@
       <c r="AL8" s="9"/>
       <c r="AM8" s="10"/>
       <c r="AN8" s="11"/>
-      <c r="AO8" s="156"/>
-      <c r="AP8" s="156"/>
-      <c r="AQ8" s="156"/>
-      <c r="AR8" s="156"/>
-      <c r="AS8" s="156"/>
-      <c r="AT8" s="156"/>
-      <c r="AU8" s="156"/>
-      <c r="AV8" s="156"/>
-      <c r="AW8" s="156"/>
-      <c r="AX8" s="156"/>
-      <c r="AY8" s="156"/>
-      <c r="AZ8" s="157"/>
+      <c r="AO8" s="113"/>
+      <c r="AP8" s="113"/>
+      <c r="AQ8" s="113"/>
+      <c r="AR8" s="113"/>
+      <c r="AS8" s="113"/>
+      <c r="AT8" s="113"/>
+      <c r="AU8" s="113"/>
+      <c r="AV8" s="113"/>
+      <c r="AW8" s="113"/>
+      <c r="AX8" s="113"/>
+      <c r="AY8" s="113"/>
+      <c r="AZ8" s="135"/>
     </row>
     <row r="9" spans="2:52" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B9" s="170"/>
-      <c r="C9" s="156"/>
-      <c r="D9" s="156"/>
-      <c r="E9" s="156"/>
-      <c r="F9" s="156"/>
-      <c r="G9" s="156"/>
-      <c r="H9" s="156"/>
-      <c r="I9" s="156"/>
-      <c r="J9" s="118"/>
-      <c r="K9" s="119"/>
-      <c r="L9" s="119"/>
-      <c r="M9" s="119"/>
-      <c r="N9" s="119"/>
-      <c r="O9" s="119"/>
-      <c r="P9" s="120"/>
-      <c r="Q9" s="147"/>
-      <c r="R9" s="147"/>
-      <c r="S9" s="147"/>
-      <c r="T9" s="158" t="s">
+      <c r="B9" s="117"/>
+      <c r="C9" s="113"/>
+      <c r="D9" s="113"/>
+      <c r="E9" s="113"/>
+      <c r="F9" s="113"/>
+      <c r="G9" s="113"/>
+      <c r="H9" s="113"/>
+      <c r="I9" s="113"/>
+      <c r="J9" s="124"/>
+      <c r="K9" s="125"/>
+      <c r="L9" s="125"/>
+      <c r="M9" s="125"/>
+      <c r="N9" s="125"/>
+      <c r="O9" s="125"/>
+      <c r="P9" s="126"/>
+      <c r="Q9" s="120"/>
+      <c r="R9" s="120"/>
+      <c r="S9" s="120"/>
+      <c r="T9" s="119" t="s">
         <v>25</v>
       </c>
-      <c r="U9" s="158"/>
-      <c r="V9" s="160">
+      <c r="U9" s="119"/>
+      <c r="V9" s="116">
         <v>0</v>
       </c>
-      <c r="W9" s="160"/>
-      <c r="X9" s="146">
+      <c r="W9" s="116"/>
+      <c r="X9" s="137">
         <v>0</v>
       </c>
-      <c r="Y9" s="146"/>
+      <c r="Y9" s="137"/>
       <c r="Z9" s="12"/>
       <c r="AA9" s="13"/>
       <c r="AB9" s="14"/>
@@ -7322,54 +7322,54 @@
       <c r="AL9" s="12"/>
       <c r="AM9" s="13"/>
       <c r="AN9" s="14"/>
-      <c r="AO9" s="156"/>
-      <c r="AP9" s="156"/>
-      <c r="AQ9" s="156"/>
-      <c r="AR9" s="156"/>
-      <c r="AS9" s="156"/>
-      <c r="AT9" s="156"/>
-      <c r="AU9" s="156"/>
-      <c r="AV9" s="156"/>
-      <c r="AW9" s="156"/>
-      <c r="AX9" s="156"/>
-      <c r="AY9" s="156"/>
-      <c r="AZ9" s="157"/>
+      <c r="AO9" s="113"/>
+      <c r="AP9" s="113"/>
+      <c r="AQ9" s="113"/>
+      <c r="AR9" s="113"/>
+      <c r="AS9" s="113"/>
+      <c r="AT9" s="113"/>
+      <c r="AU9" s="113"/>
+      <c r="AV9" s="113"/>
+      <c r="AW9" s="113"/>
+      <c r="AX9" s="113"/>
+      <c r="AY9" s="113"/>
+      <c r="AZ9" s="135"/>
     </row>
     <row r="10" spans="2:52" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B10" s="170">
+      <c r="B10" s="117">
         <v>3</v>
       </c>
-      <c r="C10" s="156" t="s">
+      <c r="C10" s="113" t="s">
         <v>53</v>
       </c>
-      <c r="D10" s="156"/>
-      <c r="E10" s="156"/>
-      <c r="F10" s="156"/>
-      <c r="G10" s="156"/>
-      <c r="H10" s="156"/>
-      <c r="I10" s="156"/>
-      <c r="J10" s="156"/>
-      <c r="K10" s="156"/>
-      <c r="L10" s="156"/>
-      <c r="M10" s="156"/>
-      <c r="N10" s="156"/>
-      <c r="O10" s="156"/>
-      <c r="P10" s="156"/>
-      <c r="Q10" s="147"/>
-      <c r="R10" s="147"/>
-      <c r="S10" s="147"/>
-      <c r="T10" s="161" t="s">
+      <c r="D10" s="113"/>
+      <c r="E10" s="113"/>
+      <c r="F10" s="113"/>
+      <c r="G10" s="113"/>
+      <c r="H10" s="113"/>
+      <c r="I10" s="113"/>
+      <c r="J10" s="113"/>
+      <c r="K10" s="113"/>
+      <c r="L10" s="113"/>
+      <c r="M10" s="113"/>
+      <c r="N10" s="113"/>
+      <c r="O10" s="113"/>
+      <c r="P10" s="113"/>
+      <c r="Q10" s="120"/>
+      <c r="R10" s="120"/>
+      <c r="S10" s="120"/>
+      <c r="T10" s="118" t="s">
         <v>51</v>
       </c>
-      <c r="U10" s="161"/>
-      <c r="V10" s="159">
+      <c r="U10" s="118"/>
+      <c r="V10" s="115">
         <v>0</v>
       </c>
-      <c r="W10" s="159"/>
-      <c r="X10" s="145">
+      <c r="W10" s="115"/>
+      <c r="X10" s="136">
         <v>0</v>
       </c>
-      <c r="Y10" s="145"/>
+      <c r="Y10" s="136"/>
       <c r="Z10" s="9"/>
       <c r="AA10" s="10"/>
       <c r="AB10" s="11"/>
@@ -7385,50 +7385,50 @@
       <c r="AL10" s="9"/>
       <c r="AM10" s="10"/>
       <c r="AN10" s="11"/>
-      <c r="AO10" s="156"/>
-      <c r="AP10" s="156"/>
-      <c r="AQ10" s="156"/>
-      <c r="AR10" s="156"/>
-      <c r="AS10" s="156"/>
-      <c r="AT10" s="156"/>
-      <c r="AU10" s="156"/>
-      <c r="AV10" s="156"/>
-      <c r="AW10" s="156"/>
-      <c r="AX10" s="156"/>
-      <c r="AY10" s="156"/>
-      <c r="AZ10" s="157"/>
+      <c r="AO10" s="113"/>
+      <c r="AP10" s="113"/>
+      <c r="AQ10" s="113"/>
+      <c r="AR10" s="113"/>
+      <c r="AS10" s="113"/>
+      <c r="AT10" s="113"/>
+      <c r="AU10" s="113"/>
+      <c r="AV10" s="113"/>
+      <c r="AW10" s="113"/>
+      <c r="AX10" s="113"/>
+      <c r="AY10" s="113"/>
+      <c r="AZ10" s="135"/>
     </row>
     <row r="11" spans="2:52" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B11" s="170"/>
-      <c r="C11" s="156"/>
-      <c r="D11" s="156"/>
-      <c r="E11" s="156"/>
-      <c r="F11" s="156"/>
-      <c r="G11" s="156"/>
-      <c r="H11" s="156"/>
-      <c r="I11" s="156"/>
-      <c r="J11" s="156"/>
-      <c r="K11" s="156"/>
-      <c r="L11" s="156"/>
-      <c r="M11" s="156"/>
-      <c r="N11" s="156"/>
-      <c r="O11" s="156"/>
-      <c r="P11" s="156"/>
-      <c r="Q11" s="147"/>
-      <c r="R11" s="147"/>
-      <c r="S11" s="147"/>
-      <c r="T11" s="158" t="s">
+      <c r="B11" s="117"/>
+      <c r="C11" s="113"/>
+      <c r="D11" s="113"/>
+      <c r="E11" s="113"/>
+      <c r="F11" s="113"/>
+      <c r="G11" s="113"/>
+      <c r="H11" s="113"/>
+      <c r="I11" s="113"/>
+      <c r="J11" s="113"/>
+      <c r="K11" s="113"/>
+      <c r="L11" s="113"/>
+      <c r="M11" s="113"/>
+      <c r="N11" s="113"/>
+      <c r="O11" s="113"/>
+      <c r="P11" s="113"/>
+      <c r="Q11" s="120"/>
+      <c r="R11" s="120"/>
+      <c r="S11" s="120"/>
+      <c r="T11" s="119" t="s">
         <v>25</v>
       </c>
-      <c r="U11" s="158"/>
-      <c r="V11" s="160">
+      <c r="U11" s="119"/>
+      <c r="V11" s="116">
         <v>0</v>
       </c>
-      <c r="W11" s="160"/>
-      <c r="X11" s="146">
+      <c r="W11" s="116"/>
+      <c r="X11" s="137">
         <v>0</v>
       </c>
-      <c r="Y11" s="146"/>
+      <c r="Y11" s="137"/>
       <c r="Z11" s="12"/>
       <c r="AA11" s="13"/>
       <c r="AB11" s="14"/>
@@ -7444,54 +7444,54 @@
       <c r="AL11" s="12"/>
       <c r="AM11" s="13"/>
       <c r="AN11" s="14"/>
-      <c r="AO11" s="156"/>
-      <c r="AP11" s="156"/>
-      <c r="AQ11" s="156"/>
-      <c r="AR11" s="156"/>
-      <c r="AS11" s="156"/>
-      <c r="AT11" s="156"/>
-      <c r="AU11" s="156"/>
-      <c r="AV11" s="156"/>
-      <c r="AW11" s="156"/>
-      <c r="AX11" s="156"/>
-      <c r="AY11" s="156"/>
-      <c r="AZ11" s="157"/>
+      <c r="AO11" s="113"/>
+      <c r="AP11" s="113"/>
+      <c r="AQ11" s="113"/>
+      <c r="AR11" s="113"/>
+      <c r="AS11" s="113"/>
+      <c r="AT11" s="113"/>
+      <c r="AU11" s="113"/>
+      <c r="AV11" s="113"/>
+      <c r="AW11" s="113"/>
+      <c r="AX11" s="113"/>
+      <c r="AY11" s="113"/>
+      <c r="AZ11" s="135"/>
     </row>
     <row r="12" spans="2:52" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B12" s="170">
+      <c r="B12" s="117">
         <v>4</v>
       </c>
-      <c r="C12" s="156" t="s">
+      <c r="C12" s="113" t="s">
         <v>54</v>
       </c>
-      <c r="D12" s="156"/>
-      <c r="E12" s="156"/>
-      <c r="F12" s="156"/>
-      <c r="G12" s="156"/>
-      <c r="H12" s="156"/>
-      <c r="I12" s="156"/>
-      <c r="J12" s="156"/>
-      <c r="K12" s="156"/>
-      <c r="L12" s="156"/>
-      <c r="M12" s="156"/>
-      <c r="N12" s="156"/>
-      <c r="O12" s="156"/>
-      <c r="P12" s="156"/>
-      <c r="Q12" s="121"/>
-      <c r="R12" s="122"/>
-      <c r="S12" s="123"/>
-      <c r="T12" s="161" t="s">
+      <c r="D12" s="113"/>
+      <c r="E12" s="113"/>
+      <c r="F12" s="113"/>
+      <c r="G12" s="113"/>
+      <c r="H12" s="113"/>
+      <c r="I12" s="113"/>
+      <c r="J12" s="113"/>
+      <c r="K12" s="113"/>
+      <c r="L12" s="113"/>
+      <c r="M12" s="113"/>
+      <c r="N12" s="113"/>
+      <c r="O12" s="113"/>
+      <c r="P12" s="113"/>
+      <c r="Q12" s="179"/>
+      <c r="R12" s="180"/>
+      <c r="S12" s="181"/>
+      <c r="T12" s="118" t="s">
         <v>51</v>
       </c>
-      <c r="U12" s="161"/>
-      <c r="V12" s="159">
+      <c r="U12" s="118"/>
+      <c r="V12" s="115">
         <v>0</v>
       </c>
-      <c r="W12" s="159"/>
-      <c r="X12" s="145">
+      <c r="W12" s="115"/>
+      <c r="X12" s="136">
         <v>0</v>
       </c>
-      <c r="Y12" s="145"/>
+      <c r="Y12" s="136"/>
       <c r="Z12" s="9"/>
       <c r="AA12" s="10"/>
       <c r="AB12" s="11"/>
@@ -7507,50 +7507,50 @@
       <c r="AL12" s="9"/>
       <c r="AM12" s="10"/>
       <c r="AN12" s="11"/>
-      <c r="AO12" s="156"/>
-      <c r="AP12" s="156"/>
-      <c r="AQ12" s="156"/>
-      <c r="AR12" s="156"/>
-      <c r="AS12" s="156"/>
-      <c r="AT12" s="156"/>
-      <c r="AU12" s="156"/>
-      <c r="AV12" s="156"/>
-      <c r="AW12" s="156"/>
-      <c r="AX12" s="156"/>
-      <c r="AY12" s="156"/>
-      <c r="AZ12" s="157"/>
+      <c r="AO12" s="113"/>
+      <c r="AP12" s="113"/>
+      <c r="AQ12" s="113"/>
+      <c r="AR12" s="113"/>
+      <c r="AS12" s="113"/>
+      <c r="AT12" s="113"/>
+      <c r="AU12" s="113"/>
+      <c r="AV12" s="113"/>
+      <c r="AW12" s="113"/>
+      <c r="AX12" s="113"/>
+      <c r="AY12" s="113"/>
+      <c r="AZ12" s="135"/>
     </row>
     <row r="13" spans="2:52" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B13" s="170"/>
-      <c r="C13" s="156"/>
-      <c r="D13" s="156"/>
-      <c r="E13" s="156"/>
-      <c r="F13" s="156"/>
-      <c r="G13" s="156"/>
-      <c r="H13" s="156"/>
-      <c r="I13" s="156"/>
-      <c r="J13" s="156"/>
-      <c r="K13" s="156"/>
-      <c r="L13" s="156"/>
-      <c r="M13" s="156"/>
-      <c r="N13" s="156"/>
-      <c r="O13" s="156"/>
-      <c r="P13" s="156"/>
-      <c r="Q13" s="124"/>
-      <c r="R13" s="125"/>
-      <c r="S13" s="126"/>
-      <c r="T13" s="158" t="s">
+      <c r="B13" s="117"/>
+      <c r="C13" s="113"/>
+      <c r="D13" s="113"/>
+      <c r="E13" s="113"/>
+      <c r="F13" s="113"/>
+      <c r="G13" s="113"/>
+      <c r="H13" s="113"/>
+      <c r="I13" s="113"/>
+      <c r="J13" s="113"/>
+      <c r="K13" s="113"/>
+      <c r="L13" s="113"/>
+      <c r="M13" s="113"/>
+      <c r="N13" s="113"/>
+      <c r="O13" s="113"/>
+      <c r="P13" s="113"/>
+      <c r="Q13" s="182"/>
+      <c r="R13" s="183"/>
+      <c r="S13" s="184"/>
+      <c r="T13" s="119" t="s">
         <v>25</v>
       </c>
-      <c r="U13" s="158"/>
-      <c r="V13" s="160">
+      <c r="U13" s="119"/>
+      <c r="V13" s="116">
         <v>0</v>
       </c>
-      <c r="W13" s="160"/>
-      <c r="X13" s="146">
+      <c r="W13" s="116"/>
+      <c r="X13" s="137">
         <v>0</v>
       </c>
-      <c r="Y13" s="146"/>
+      <c r="Y13" s="137"/>
       <c r="Z13" s="12"/>
       <c r="AA13" s="13"/>
       <c r="AB13" s="14"/>
@@ -7566,54 +7566,54 @@
       <c r="AL13" s="12"/>
       <c r="AM13" s="13"/>
       <c r="AN13" s="14"/>
-      <c r="AO13" s="156"/>
-      <c r="AP13" s="156"/>
-      <c r="AQ13" s="156"/>
-      <c r="AR13" s="156"/>
-      <c r="AS13" s="156"/>
-      <c r="AT13" s="156"/>
-      <c r="AU13" s="156"/>
-      <c r="AV13" s="156"/>
-      <c r="AW13" s="156"/>
-      <c r="AX13" s="156"/>
-      <c r="AY13" s="156"/>
-      <c r="AZ13" s="157"/>
+      <c r="AO13" s="113"/>
+      <c r="AP13" s="113"/>
+      <c r="AQ13" s="113"/>
+      <c r="AR13" s="113"/>
+      <c r="AS13" s="113"/>
+      <c r="AT13" s="113"/>
+      <c r="AU13" s="113"/>
+      <c r="AV13" s="113"/>
+      <c r="AW13" s="113"/>
+      <c r="AX13" s="113"/>
+      <c r="AY13" s="113"/>
+      <c r="AZ13" s="135"/>
     </row>
     <row r="14" spans="2:52" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B14" s="170">
+      <c r="B14" s="117">
         <v>5</v>
       </c>
-      <c r="C14" s="115" t="s">
+      <c r="C14" s="121" t="s">
         <v>55</v>
       </c>
-      <c r="D14" s="116"/>
-      <c r="E14" s="116"/>
-      <c r="F14" s="116"/>
-      <c r="G14" s="116"/>
-      <c r="H14" s="116"/>
-      <c r="I14" s="117"/>
-      <c r="J14" s="196"/>
-      <c r="K14" s="156"/>
-      <c r="L14" s="156"/>
-      <c r="M14" s="156"/>
-      <c r="N14" s="156"/>
-      <c r="O14" s="156"/>
-      <c r="P14" s="156"/>
-      <c r="Q14" s="121"/>
-      <c r="R14" s="122"/>
-      <c r="S14" s="123"/>
-      <c r="T14" s="161" t="s">
+      <c r="D14" s="122"/>
+      <c r="E14" s="122"/>
+      <c r="F14" s="122"/>
+      <c r="G14" s="122"/>
+      <c r="H14" s="122"/>
+      <c r="I14" s="123"/>
+      <c r="J14" s="114"/>
+      <c r="K14" s="113"/>
+      <c r="L14" s="113"/>
+      <c r="M14" s="113"/>
+      <c r="N14" s="113"/>
+      <c r="O14" s="113"/>
+      <c r="P14" s="113"/>
+      <c r="Q14" s="179"/>
+      <c r="R14" s="180"/>
+      <c r="S14" s="181"/>
+      <c r="T14" s="118" t="s">
         <v>51</v>
       </c>
-      <c r="U14" s="161"/>
-      <c r="V14" s="159">
+      <c r="U14" s="118"/>
+      <c r="V14" s="115">
         <v>0</v>
       </c>
-      <c r="W14" s="159"/>
-      <c r="X14" s="145">
+      <c r="W14" s="115"/>
+      <c r="X14" s="136">
         <v>0</v>
       </c>
-      <c r="Y14" s="145"/>
+      <c r="Y14" s="136"/>
       <c r="Z14" s="9"/>
       <c r="AA14" s="10"/>
       <c r="AB14" s="11"/>
@@ -7629,50 +7629,50 @@
       <c r="AL14" s="9"/>
       <c r="AM14" s="10"/>
       <c r="AN14" s="11"/>
-      <c r="AO14" s="156"/>
-      <c r="AP14" s="156"/>
-      <c r="AQ14" s="156"/>
-      <c r="AR14" s="156"/>
-      <c r="AS14" s="156"/>
-      <c r="AT14" s="156"/>
-      <c r="AU14" s="156"/>
-      <c r="AV14" s="156"/>
-      <c r="AW14" s="156"/>
-      <c r="AX14" s="156"/>
-      <c r="AY14" s="156"/>
-      <c r="AZ14" s="157"/>
+      <c r="AO14" s="113"/>
+      <c r="AP14" s="113"/>
+      <c r="AQ14" s="113"/>
+      <c r="AR14" s="113"/>
+      <c r="AS14" s="113"/>
+      <c r="AT14" s="113"/>
+      <c r="AU14" s="113"/>
+      <c r="AV14" s="113"/>
+      <c r="AW14" s="113"/>
+      <c r="AX14" s="113"/>
+      <c r="AY14" s="113"/>
+      <c r="AZ14" s="135"/>
     </row>
     <row r="15" spans="2:52" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B15" s="170"/>
-      <c r="C15" s="118"/>
-      <c r="D15" s="119"/>
-      <c r="E15" s="119"/>
-      <c r="F15" s="119"/>
-      <c r="G15" s="119"/>
-      <c r="H15" s="119"/>
-      <c r="I15" s="120"/>
-      <c r="J15" s="156"/>
-      <c r="K15" s="156"/>
-      <c r="L15" s="156"/>
-      <c r="M15" s="156"/>
-      <c r="N15" s="156"/>
-      <c r="O15" s="156"/>
-      <c r="P15" s="156"/>
-      <c r="Q15" s="124"/>
-      <c r="R15" s="125"/>
-      <c r="S15" s="126"/>
-      <c r="T15" s="158" t="s">
+      <c r="B15" s="117"/>
+      <c r="C15" s="124"/>
+      <c r="D15" s="125"/>
+      <c r="E15" s="125"/>
+      <c r="F15" s="125"/>
+      <c r="G15" s="125"/>
+      <c r="H15" s="125"/>
+      <c r="I15" s="126"/>
+      <c r="J15" s="113"/>
+      <c r="K15" s="113"/>
+      <c r="L15" s="113"/>
+      <c r="M15" s="113"/>
+      <c r="N15" s="113"/>
+      <c r="O15" s="113"/>
+      <c r="P15" s="113"/>
+      <c r="Q15" s="182"/>
+      <c r="R15" s="183"/>
+      <c r="S15" s="184"/>
+      <c r="T15" s="119" t="s">
         <v>25</v>
       </c>
-      <c r="U15" s="158"/>
-      <c r="V15" s="160">
+      <c r="U15" s="119"/>
+      <c r="V15" s="116">
         <v>0</v>
       </c>
-      <c r="W15" s="160"/>
-      <c r="X15" s="146">
+      <c r="W15" s="116"/>
+      <c r="X15" s="137">
         <v>0</v>
       </c>
-      <c r="Y15" s="146"/>
+      <c r="Y15" s="137"/>
       <c r="Z15" s="12"/>
       <c r="AA15" s="13"/>
       <c r="AB15" s="14"/>
@@ -7688,54 +7688,54 @@
       <c r="AL15" s="12"/>
       <c r="AM15" s="13"/>
       <c r="AN15" s="14"/>
-      <c r="AO15" s="156"/>
-      <c r="AP15" s="156"/>
-      <c r="AQ15" s="156"/>
-      <c r="AR15" s="156"/>
-      <c r="AS15" s="156"/>
-      <c r="AT15" s="156"/>
-      <c r="AU15" s="156"/>
-      <c r="AV15" s="156"/>
-      <c r="AW15" s="156"/>
-      <c r="AX15" s="156"/>
-      <c r="AY15" s="156"/>
-      <c r="AZ15" s="157"/>
+      <c r="AO15" s="113"/>
+      <c r="AP15" s="113"/>
+      <c r="AQ15" s="113"/>
+      <c r="AR15" s="113"/>
+      <c r="AS15" s="113"/>
+      <c r="AT15" s="113"/>
+      <c r="AU15" s="113"/>
+      <c r="AV15" s="113"/>
+      <c r="AW15" s="113"/>
+      <c r="AX15" s="113"/>
+      <c r="AY15" s="113"/>
+      <c r="AZ15" s="135"/>
     </row>
     <row r="16" spans="2:52" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B16" s="170">
+      <c r="B16" s="117">
         <v>6</v>
       </c>
-      <c r="C16" s="115" t="s">
+      <c r="C16" s="121" t="s">
         <v>56</v>
       </c>
-      <c r="D16" s="116"/>
-      <c r="E16" s="116"/>
-      <c r="F16" s="116"/>
-      <c r="G16" s="116"/>
-      <c r="H16" s="116"/>
-      <c r="I16" s="117"/>
-      <c r="J16" s="196"/>
-      <c r="K16" s="156"/>
-      <c r="L16" s="156"/>
-      <c r="M16" s="156"/>
-      <c r="N16" s="156"/>
-      <c r="O16" s="156"/>
-      <c r="P16" s="156"/>
-      <c r="Q16" s="147"/>
-      <c r="R16" s="147"/>
-      <c r="S16" s="147"/>
-      <c r="T16" s="161" t="s">
+      <c r="D16" s="122"/>
+      <c r="E16" s="122"/>
+      <c r="F16" s="122"/>
+      <c r="G16" s="122"/>
+      <c r="H16" s="122"/>
+      <c r="I16" s="123"/>
+      <c r="J16" s="114"/>
+      <c r="K16" s="113"/>
+      <c r="L16" s="113"/>
+      <c r="M16" s="113"/>
+      <c r="N16" s="113"/>
+      <c r="O16" s="113"/>
+      <c r="P16" s="113"/>
+      <c r="Q16" s="120"/>
+      <c r="R16" s="120"/>
+      <c r="S16" s="120"/>
+      <c r="T16" s="118" t="s">
         <v>51</v>
       </c>
-      <c r="U16" s="161"/>
-      <c r="V16" s="159">
+      <c r="U16" s="118"/>
+      <c r="V16" s="115">
         <v>0</v>
       </c>
-      <c r="W16" s="159"/>
-      <c r="X16" s="145">
+      <c r="W16" s="115"/>
+      <c r="X16" s="136">
         <v>0</v>
       </c>
-      <c r="Y16" s="145"/>
+      <c r="Y16" s="136"/>
       <c r="Z16" s="9"/>
       <c r="AA16" s="10"/>
       <c r="AB16" s="11"/>
@@ -7751,50 +7751,50 @@
       <c r="AL16" s="9"/>
       <c r="AM16" s="10"/>
       <c r="AN16" s="11"/>
-      <c r="AO16" s="156"/>
-      <c r="AP16" s="156"/>
-      <c r="AQ16" s="156"/>
-      <c r="AR16" s="156"/>
-      <c r="AS16" s="156"/>
-      <c r="AT16" s="156"/>
-      <c r="AU16" s="156"/>
-      <c r="AV16" s="156"/>
-      <c r="AW16" s="156"/>
-      <c r="AX16" s="156"/>
-      <c r="AY16" s="156"/>
-      <c r="AZ16" s="157"/>
+      <c r="AO16" s="113"/>
+      <c r="AP16" s="113"/>
+      <c r="AQ16" s="113"/>
+      <c r="AR16" s="113"/>
+      <c r="AS16" s="113"/>
+      <c r="AT16" s="113"/>
+      <c r="AU16" s="113"/>
+      <c r="AV16" s="113"/>
+      <c r="AW16" s="113"/>
+      <c r="AX16" s="113"/>
+      <c r="AY16" s="113"/>
+      <c r="AZ16" s="135"/>
     </row>
     <row r="17" spans="2:52" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B17" s="170"/>
-      <c r="C17" s="118"/>
-      <c r="D17" s="119"/>
-      <c r="E17" s="119"/>
-      <c r="F17" s="119"/>
-      <c r="G17" s="119"/>
-      <c r="H17" s="119"/>
-      <c r="I17" s="120"/>
-      <c r="J17" s="156"/>
-      <c r="K17" s="156"/>
-      <c r="L17" s="156"/>
-      <c r="M17" s="156"/>
-      <c r="N17" s="156"/>
-      <c r="O17" s="156"/>
-      <c r="P17" s="156"/>
-      <c r="Q17" s="147"/>
-      <c r="R17" s="147"/>
-      <c r="S17" s="147"/>
-      <c r="T17" s="158" t="s">
+      <c r="B17" s="117"/>
+      <c r="C17" s="124"/>
+      <c r="D17" s="125"/>
+      <c r="E17" s="125"/>
+      <c r="F17" s="125"/>
+      <c r="G17" s="125"/>
+      <c r="H17" s="125"/>
+      <c r="I17" s="126"/>
+      <c r="J17" s="113"/>
+      <c r="K17" s="113"/>
+      <c r="L17" s="113"/>
+      <c r="M17" s="113"/>
+      <c r="N17" s="113"/>
+      <c r="O17" s="113"/>
+      <c r="P17" s="113"/>
+      <c r="Q17" s="120"/>
+      <c r="R17" s="120"/>
+      <c r="S17" s="120"/>
+      <c r="T17" s="119" t="s">
         <v>25</v>
       </c>
-      <c r="U17" s="158"/>
-      <c r="V17" s="160">
+      <c r="U17" s="119"/>
+      <c r="V17" s="116">
         <v>0</v>
       </c>
-      <c r="W17" s="160"/>
-      <c r="X17" s="146">
+      <c r="W17" s="116"/>
+      <c r="X17" s="137">
         <v>0</v>
       </c>
-      <c r="Y17" s="146"/>
+      <c r="Y17" s="137"/>
       <c r="Z17" s="12"/>
       <c r="AA17" s="13"/>
       <c r="AB17" s="14"/>
@@ -7810,54 +7810,54 @@
       <c r="AL17" s="12"/>
       <c r="AM17" s="13"/>
       <c r="AN17" s="14"/>
-      <c r="AO17" s="156"/>
-      <c r="AP17" s="156"/>
-      <c r="AQ17" s="156"/>
-      <c r="AR17" s="156"/>
-      <c r="AS17" s="156"/>
-      <c r="AT17" s="156"/>
-      <c r="AU17" s="156"/>
-      <c r="AV17" s="156"/>
-      <c r="AW17" s="156"/>
-      <c r="AX17" s="156"/>
-      <c r="AY17" s="156"/>
-      <c r="AZ17" s="157"/>
+      <c r="AO17" s="113"/>
+      <c r="AP17" s="113"/>
+      <c r="AQ17" s="113"/>
+      <c r="AR17" s="113"/>
+      <c r="AS17" s="113"/>
+      <c r="AT17" s="113"/>
+      <c r="AU17" s="113"/>
+      <c r="AV17" s="113"/>
+      <c r="AW17" s="113"/>
+      <c r="AX17" s="113"/>
+      <c r="AY17" s="113"/>
+      <c r="AZ17" s="135"/>
     </row>
     <row r="18" spans="2:52" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B18" s="107">
+      <c r="B18" s="133">
         <v>7</v>
       </c>
-      <c r="C18" s="109" t="s">
+      <c r="C18" s="166" t="s">
         <v>57</v>
       </c>
-      <c r="D18" s="110"/>
-      <c r="E18" s="110"/>
-      <c r="F18" s="110"/>
-      <c r="G18" s="110"/>
-      <c r="H18" s="110"/>
-      <c r="I18" s="111"/>
-      <c r="J18" s="115"/>
-      <c r="K18" s="116"/>
-      <c r="L18" s="116"/>
-      <c r="M18" s="116"/>
-      <c r="N18" s="116"/>
-      <c r="O18" s="116"/>
-      <c r="P18" s="117"/>
-      <c r="Q18" s="121"/>
-      <c r="R18" s="122"/>
-      <c r="S18" s="123"/>
-      <c r="T18" s="127" t="s">
+      <c r="D18" s="167"/>
+      <c r="E18" s="167"/>
+      <c r="F18" s="167"/>
+      <c r="G18" s="167"/>
+      <c r="H18" s="167"/>
+      <c r="I18" s="168"/>
+      <c r="J18" s="121"/>
+      <c r="K18" s="122"/>
+      <c r="L18" s="122"/>
+      <c r="M18" s="122"/>
+      <c r="N18" s="122"/>
+      <c r="O18" s="122"/>
+      <c r="P18" s="123"/>
+      <c r="Q18" s="179"/>
+      <c r="R18" s="180"/>
+      <c r="S18" s="181"/>
+      <c r="T18" s="169" t="s">
         <v>51</v>
       </c>
-      <c r="U18" s="128"/>
+      <c r="U18" s="170"/>
       <c r="V18" s="129">
         <v>0</v>
       </c>
       <c r="W18" s="130"/>
-      <c r="X18" s="131">
+      <c r="X18" s="175">
         <v>0</v>
       </c>
-      <c r="Y18" s="132"/>
+      <c r="Y18" s="176"/>
       <c r="Z18" s="9"/>
       <c r="AA18" s="10"/>
       <c r="AB18" s="11"/>
@@ -7873,50 +7873,50 @@
       <c r="AL18" s="9"/>
       <c r="AM18" s="10"/>
       <c r="AN18" s="11"/>
-      <c r="AO18" s="115"/>
-      <c r="AP18" s="116"/>
-      <c r="AQ18" s="116"/>
-      <c r="AR18" s="116"/>
-      <c r="AS18" s="116"/>
-      <c r="AT18" s="116"/>
-      <c r="AU18" s="116"/>
-      <c r="AV18" s="116"/>
-      <c r="AW18" s="116"/>
-      <c r="AX18" s="116"/>
-      <c r="AY18" s="116"/>
-      <c r="AZ18" s="133"/>
+      <c r="AO18" s="121"/>
+      <c r="AP18" s="122"/>
+      <c r="AQ18" s="122"/>
+      <c r="AR18" s="122"/>
+      <c r="AS18" s="122"/>
+      <c r="AT18" s="122"/>
+      <c r="AU18" s="122"/>
+      <c r="AV18" s="122"/>
+      <c r="AW18" s="122"/>
+      <c r="AX18" s="122"/>
+      <c r="AY18" s="122"/>
+      <c r="AZ18" s="171"/>
     </row>
     <row r="19" spans="2:52" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B19" s="108"/>
-      <c r="C19" s="112"/>
-      <c r="D19" s="113"/>
-      <c r="E19" s="113"/>
-      <c r="F19" s="113"/>
-      <c r="G19" s="113"/>
-      <c r="H19" s="113"/>
-      <c r="I19" s="114"/>
-      <c r="J19" s="118"/>
-      <c r="K19" s="119"/>
-      <c r="L19" s="119"/>
-      <c r="M19" s="119"/>
-      <c r="N19" s="119"/>
-      <c r="O19" s="119"/>
-      <c r="P19" s="120"/>
-      <c r="Q19" s="124"/>
-      <c r="R19" s="125"/>
-      <c r="S19" s="126"/>
-      <c r="T19" s="135" t="s">
+      <c r="B19" s="134"/>
+      <c r="C19" s="151"/>
+      <c r="D19" s="152"/>
+      <c r="E19" s="152"/>
+      <c r="F19" s="152"/>
+      <c r="G19" s="152"/>
+      <c r="H19" s="152"/>
+      <c r="I19" s="153"/>
+      <c r="J19" s="124"/>
+      <c r="K19" s="125"/>
+      <c r="L19" s="125"/>
+      <c r="M19" s="125"/>
+      <c r="N19" s="125"/>
+      <c r="O19" s="125"/>
+      <c r="P19" s="126"/>
+      <c r="Q19" s="182"/>
+      <c r="R19" s="183"/>
+      <c r="S19" s="184"/>
+      <c r="T19" s="173" t="s">
         <v>25</v>
       </c>
-      <c r="U19" s="136"/>
-      <c r="V19" s="137">
+      <c r="U19" s="174"/>
+      <c r="V19" s="131">
         <v>0</v>
       </c>
-      <c r="W19" s="138"/>
-      <c r="X19" s="139">
+      <c r="W19" s="132"/>
+      <c r="X19" s="177">
         <v>0</v>
       </c>
-      <c r="Y19" s="140"/>
+      <c r="Y19" s="178"/>
       <c r="Z19" s="12"/>
       <c r="AA19" s="13"/>
       <c r="AB19" s="14"/>
@@ -7932,54 +7932,54 @@
       <c r="AL19" s="12"/>
       <c r="AM19" s="13"/>
       <c r="AN19" s="14"/>
-      <c r="AO19" s="118"/>
-      <c r="AP19" s="119"/>
-      <c r="AQ19" s="119"/>
-      <c r="AR19" s="119"/>
-      <c r="AS19" s="119"/>
-      <c r="AT19" s="119"/>
-      <c r="AU19" s="119"/>
-      <c r="AV19" s="119"/>
-      <c r="AW19" s="119"/>
-      <c r="AX19" s="119"/>
-      <c r="AY19" s="119"/>
-      <c r="AZ19" s="134"/>
+      <c r="AO19" s="124"/>
+      <c r="AP19" s="125"/>
+      <c r="AQ19" s="125"/>
+      <c r="AR19" s="125"/>
+      <c r="AS19" s="125"/>
+      <c r="AT19" s="125"/>
+      <c r="AU19" s="125"/>
+      <c r="AV19" s="125"/>
+      <c r="AW19" s="125"/>
+      <c r="AX19" s="125"/>
+      <c r="AY19" s="125"/>
+      <c r="AZ19" s="172"/>
     </row>
     <row r="20" spans="2:52" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B20" s="107">
+      <c r="B20" s="133">
         <v>8</v>
       </c>
-      <c r="C20" s="109" t="s">
+      <c r="C20" s="166" t="s">
         <v>58</v>
       </c>
-      <c r="D20" s="110"/>
-      <c r="E20" s="110"/>
-      <c r="F20" s="110"/>
-      <c r="G20" s="110"/>
-      <c r="H20" s="110"/>
-      <c r="I20" s="111"/>
-      <c r="J20" s="115"/>
-      <c r="K20" s="116"/>
-      <c r="L20" s="116"/>
-      <c r="M20" s="116"/>
-      <c r="N20" s="116"/>
-      <c r="O20" s="116"/>
-      <c r="P20" s="117"/>
-      <c r="Q20" s="121"/>
-      <c r="R20" s="122"/>
-      <c r="S20" s="123"/>
-      <c r="T20" s="127" t="s">
+      <c r="D20" s="167"/>
+      <c r="E20" s="167"/>
+      <c r="F20" s="167"/>
+      <c r="G20" s="167"/>
+      <c r="H20" s="167"/>
+      <c r="I20" s="168"/>
+      <c r="J20" s="121"/>
+      <c r="K20" s="122"/>
+      <c r="L20" s="122"/>
+      <c r="M20" s="122"/>
+      <c r="N20" s="122"/>
+      <c r="O20" s="122"/>
+      <c r="P20" s="123"/>
+      <c r="Q20" s="179"/>
+      <c r="R20" s="180"/>
+      <c r="S20" s="181"/>
+      <c r="T20" s="169" t="s">
         <v>51</v>
       </c>
-      <c r="U20" s="128"/>
+      <c r="U20" s="170"/>
       <c r="V20" s="129">
         <v>0</v>
       </c>
       <c r="W20" s="130"/>
-      <c r="X20" s="131">
+      <c r="X20" s="175">
         <v>0</v>
       </c>
-      <c r="Y20" s="132"/>
+      <c r="Y20" s="176"/>
       <c r="Z20" s="9"/>
       <c r="AA20" s="10"/>
       <c r="AB20" s="11"/>
@@ -7995,50 +7995,50 @@
       <c r="AL20" s="9"/>
       <c r="AM20" s="10"/>
       <c r="AN20" s="11"/>
-      <c r="AO20" s="115"/>
-      <c r="AP20" s="116"/>
-      <c r="AQ20" s="116"/>
-      <c r="AR20" s="116"/>
-      <c r="AS20" s="116"/>
-      <c r="AT20" s="116"/>
-      <c r="AU20" s="116"/>
-      <c r="AV20" s="116"/>
-      <c r="AW20" s="116"/>
-      <c r="AX20" s="116"/>
-      <c r="AY20" s="116"/>
-      <c r="AZ20" s="133"/>
+      <c r="AO20" s="121"/>
+      <c r="AP20" s="122"/>
+      <c r="AQ20" s="122"/>
+      <c r="AR20" s="122"/>
+      <c r="AS20" s="122"/>
+      <c r="AT20" s="122"/>
+      <c r="AU20" s="122"/>
+      <c r="AV20" s="122"/>
+      <c r="AW20" s="122"/>
+      <c r="AX20" s="122"/>
+      <c r="AY20" s="122"/>
+      <c r="AZ20" s="171"/>
     </row>
     <row r="21" spans="2:52" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B21" s="108"/>
-      <c r="C21" s="112"/>
-      <c r="D21" s="113"/>
-      <c r="E21" s="113"/>
-      <c r="F21" s="113"/>
-      <c r="G21" s="113"/>
-      <c r="H21" s="113"/>
-      <c r="I21" s="114"/>
-      <c r="J21" s="118"/>
-      <c r="K21" s="119"/>
-      <c r="L21" s="119"/>
-      <c r="M21" s="119"/>
-      <c r="N21" s="119"/>
-      <c r="O21" s="119"/>
-      <c r="P21" s="120"/>
-      <c r="Q21" s="124"/>
-      <c r="R21" s="125"/>
-      <c r="S21" s="126"/>
-      <c r="T21" s="135" t="s">
+      <c r="B21" s="134"/>
+      <c r="C21" s="151"/>
+      <c r="D21" s="152"/>
+      <c r="E21" s="152"/>
+      <c r="F21" s="152"/>
+      <c r="G21" s="152"/>
+      <c r="H21" s="152"/>
+      <c r="I21" s="153"/>
+      <c r="J21" s="124"/>
+      <c r="K21" s="125"/>
+      <c r="L21" s="125"/>
+      <c r="M21" s="125"/>
+      <c r="N21" s="125"/>
+      <c r="O21" s="125"/>
+      <c r="P21" s="126"/>
+      <c r="Q21" s="182"/>
+      <c r="R21" s="183"/>
+      <c r="S21" s="184"/>
+      <c r="T21" s="173" t="s">
         <v>25</v>
       </c>
-      <c r="U21" s="136"/>
-      <c r="V21" s="137">
+      <c r="U21" s="174"/>
+      <c r="V21" s="131">
         <v>0</v>
       </c>
-      <c r="W21" s="138"/>
-      <c r="X21" s="139">
+      <c r="W21" s="132"/>
+      <c r="X21" s="177">
         <v>0</v>
       </c>
-      <c r="Y21" s="140"/>
+      <c r="Y21" s="178"/>
       <c r="Z21" s="12"/>
       <c r="AA21" s="13"/>
       <c r="AB21" s="14"/>
@@ -8054,54 +8054,54 @@
       <c r="AL21" s="12"/>
       <c r="AM21" s="13"/>
       <c r="AN21" s="14"/>
-      <c r="AO21" s="118"/>
-      <c r="AP21" s="119"/>
-      <c r="AQ21" s="119"/>
-      <c r="AR21" s="119"/>
-      <c r="AS21" s="119"/>
-      <c r="AT21" s="119"/>
-      <c r="AU21" s="119"/>
-      <c r="AV21" s="119"/>
-      <c r="AW21" s="119"/>
-      <c r="AX21" s="119"/>
-      <c r="AY21" s="119"/>
-      <c r="AZ21" s="134"/>
+      <c r="AO21" s="124"/>
+      <c r="AP21" s="125"/>
+      <c r="AQ21" s="125"/>
+      <c r="AR21" s="125"/>
+      <c r="AS21" s="125"/>
+      <c r="AT21" s="125"/>
+      <c r="AU21" s="125"/>
+      <c r="AV21" s="125"/>
+      <c r="AW21" s="125"/>
+      <c r="AX21" s="125"/>
+      <c r="AY21" s="125"/>
+      <c r="AZ21" s="172"/>
     </row>
     <row r="22" spans="2:52" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B22" s="177">
+      <c r="B22" s="146">
         <v>9</v>
       </c>
-      <c r="C22" s="179" t="s">
+      <c r="C22" s="148" t="s">
         <v>59</v>
       </c>
-      <c r="D22" s="180"/>
-      <c r="E22" s="180"/>
-      <c r="F22" s="180"/>
-      <c r="G22" s="180"/>
-      <c r="H22" s="180"/>
-      <c r="I22" s="181"/>
-      <c r="J22" s="164"/>
-      <c r="K22" s="165"/>
-      <c r="L22" s="165"/>
-      <c r="M22" s="165"/>
-      <c r="N22" s="165"/>
-      <c r="O22" s="165"/>
-      <c r="P22" s="166"/>
-      <c r="Q22" s="186"/>
-      <c r="R22" s="187"/>
-      <c r="S22" s="188"/>
-      <c r="T22" s="182" t="s">
+      <c r="D22" s="149"/>
+      <c r="E22" s="149"/>
+      <c r="F22" s="149"/>
+      <c r="G22" s="149"/>
+      <c r="H22" s="149"/>
+      <c r="I22" s="150"/>
+      <c r="J22" s="138"/>
+      <c r="K22" s="139"/>
+      <c r="L22" s="139"/>
+      <c r="M22" s="139"/>
+      <c r="N22" s="139"/>
+      <c r="O22" s="139"/>
+      <c r="P22" s="187"/>
+      <c r="Q22" s="158"/>
+      <c r="R22" s="159"/>
+      <c r="S22" s="160"/>
+      <c r="T22" s="154" t="s">
         <v>51</v>
       </c>
-      <c r="U22" s="183"/>
-      <c r="V22" s="162">
+      <c r="U22" s="155"/>
+      <c r="V22" s="185">
         <v>0</v>
       </c>
-      <c r="W22" s="163"/>
-      <c r="X22" s="175">
+      <c r="W22" s="186"/>
+      <c r="X22" s="144">
         <v>0</v>
       </c>
-      <c r="Y22" s="176"/>
+      <c r="Y22" s="145"/>
       <c r="Z22" s="24"/>
       <c r="AA22" s="25"/>
       <c r="AB22" s="26"/>
@@ -8117,50 +8117,50 @@
       <c r="AL22" s="24"/>
       <c r="AM22" s="25"/>
       <c r="AN22" s="26"/>
-      <c r="AO22" s="164"/>
-      <c r="AP22" s="165"/>
-      <c r="AQ22" s="165"/>
-      <c r="AR22" s="165"/>
-      <c r="AS22" s="165"/>
-      <c r="AT22" s="165"/>
-      <c r="AU22" s="165"/>
-      <c r="AV22" s="165"/>
-      <c r="AW22" s="165"/>
-      <c r="AX22" s="165"/>
-      <c r="AY22" s="165"/>
-      <c r="AZ22" s="173"/>
+      <c r="AO22" s="138"/>
+      <c r="AP22" s="139"/>
+      <c r="AQ22" s="139"/>
+      <c r="AR22" s="139"/>
+      <c r="AS22" s="139"/>
+      <c r="AT22" s="139"/>
+      <c r="AU22" s="139"/>
+      <c r="AV22" s="139"/>
+      <c r="AW22" s="139"/>
+      <c r="AX22" s="139"/>
+      <c r="AY22" s="139"/>
+      <c r="AZ22" s="140"/>
     </row>
     <row r="23" spans="2:52" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B23" s="178"/>
-      <c r="C23" s="112"/>
-      <c r="D23" s="113"/>
-      <c r="E23" s="113"/>
-      <c r="F23" s="113"/>
-      <c r="G23" s="113"/>
-      <c r="H23" s="113"/>
-      <c r="I23" s="114"/>
-      <c r="J23" s="167"/>
-      <c r="K23" s="168"/>
-      <c r="L23" s="168"/>
-      <c r="M23" s="168"/>
-      <c r="N23" s="168"/>
-      <c r="O23" s="168"/>
-      <c r="P23" s="169"/>
-      <c r="Q23" s="189"/>
-      <c r="R23" s="190"/>
-      <c r="S23" s="191"/>
-      <c r="T23" s="184" t="s">
+      <c r="B23" s="147"/>
+      <c r="C23" s="151"/>
+      <c r="D23" s="152"/>
+      <c r="E23" s="152"/>
+      <c r="F23" s="152"/>
+      <c r="G23" s="152"/>
+      <c r="H23" s="152"/>
+      <c r="I23" s="153"/>
+      <c r="J23" s="141"/>
+      <c r="K23" s="142"/>
+      <c r="L23" s="142"/>
+      <c r="M23" s="142"/>
+      <c r="N23" s="142"/>
+      <c r="O23" s="142"/>
+      <c r="P23" s="188"/>
+      <c r="Q23" s="161"/>
+      <c r="R23" s="162"/>
+      <c r="S23" s="163"/>
+      <c r="T23" s="156" t="s">
         <v>25</v>
       </c>
-      <c r="U23" s="185"/>
-      <c r="V23" s="171">
+      <c r="U23" s="157"/>
+      <c r="V23" s="127">
         <v>0</v>
       </c>
-      <c r="W23" s="172"/>
-      <c r="X23" s="192">
+      <c r="W23" s="128"/>
+      <c r="X23" s="164">
         <v>0</v>
       </c>
-      <c r="Y23" s="193"/>
+      <c r="Y23" s="165"/>
       <c r="Z23" s="15"/>
       <c r="AA23" s="16"/>
       <c r="AB23" s="17"/>
@@ -8176,18 +8176,18 @@
       <c r="AL23" s="15"/>
       <c r="AM23" s="16"/>
       <c r="AN23" s="17"/>
-      <c r="AO23" s="167"/>
-      <c r="AP23" s="168"/>
-      <c r="AQ23" s="168"/>
-      <c r="AR23" s="168"/>
-      <c r="AS23" s="168"/>
-      <c r="AT23" s="168"/>
-      <c r="AU23" s="168"/>
-      <c r="AV23" s="168"/>
-      <c r="AW23" s="168"/>
-      <c r="AX23" s="168"/>
-      <c r="AY23" s="168"/>
-      <c r="AZ23" s="174"/>
+      <c r="AO23" s="141"/>
+      <c r="AP23" s="142"/>
+      <c r="AQ23" s="142"/>
+      <c r="AR23" s="142"/>
+      <c r="AS23" s="142"/>
+      <c r="AT23" s="142"/>
+      <c r="AU23" s="142"/>
+      <c r="AV23" s="142"/>
+      <c r="AW23" s="142"/>
+      <c r="AX23" s="142"/>
+      <c r="AY23" s="142"/>
+      <c r="AZ23" s="143"/>
     </row>
     <row r="24" spans="2:52" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D24" s="18"/>
@@ -8246,27 +8246,74 @@
     <row r="50" ht="18" customHeight="1" x14ac:dyDescent="0.2"/>
   </sheetData>
   <mergeCells count="113">
-    <mergeCell ref="B1:P1"/>
-    <mergeCell ref="J10:P11"/>
-    <mergeCell ref="J12:P13"/>
-    <mergeCell ref="J14:P15"/>
-    <mergeCell ref="J16:P17"/>
-    <mergeCell ref="V10:W10"/>
-    <mergeCell ref="V11:W11"/>
-    <mergeCell ref="V13:W13"/>
-    <mergeCell ref="V14:W14"/>
-    <mergeCell ref="V15:W15"/>
-    <mergeCell ref="V17:W17"/>
-    <mergeCell ref="B6:B7"/>
-    <mergeCell ref="T6:U6"/>
-    <mergeCell ref="T7:U7"/>
-    <mergeCell ref="B10:B11"/>
-    <mergeCell ref="C10:I11"/>
-    <mergeCell ref="Q8:S9"/>
-    <mergeCell ref="Q10:S11"/>
-    <mergeCell ref="B8:B9"/>
-    <mergeCell ref="C8:I9"/>
-    <mergeCell ref="J8:P9"/>
+    <mergeCell ref="B20:B21"/>
+    <mergeCell ref="C20:I21"/>
+    <mergeCell ref="J20:P21"/>
+    <mergeCell ref="Q20:S21"/>
+    <mergeCell ref="T20:U20"/>
+    <mergeCell ref="V20:W20"/>
+    <mergeCell ref="X20:Y20"/>
+    <mergeCell ref="AO20:AZ21"/>
+    <mergeCell ref="T21:U21"/>
+    <mergeCell ref="V21:W21"/>
+    <mergeCell ref="X21:Y21"/>
+    <mergeCell ref="AO4:AZ5"/>
+    <mergeCell ref="AI4:AK4"/>
+    <mergeCell ref="AL4:AN4"/>
+    <mergeCell ref="AF4:AH4"/>
+    <mergeCell ref="X6:Y6"/>
+    <mergeCell ref="X7:Y7"/>
+    <mergeCell ref="X8:Y8"/>
+    <mergeCell ref="B2:I2"/>
+    <mergeCell ref="J2:AD2"/>
+    <mergeCell ref="X4:Y5"/>
+    <mergeCell ref="T4:W5"/>
+    <mergeCell ref="Z4:AB4"/>
+    <mergeCell ref="AC4:AE4"/>
+    <mergeCell ref="B4:I5"/>
+    <mergeCell ref="J4:P5"/>
+    <mergeCell ref="Q4:S5"/>
+    <mergeCell ref="AO6:AZ7"/>
+    <mergeCell ref="C6:I7"/>
+    <mergeCell ref="Q6:S7"/>
+    <mergeCell ref="J6:P7"/>
+    <mergeCell ref="AO10:AZ11"/>
+    <mergeCell ref="T11:U11"/>
+    <mergeCell ref="X9:Y9"/>
+    <mergeCell ref="X10:Y10"/>
+    <mergeCell ref="X11:Y11"/>
+    <mergeCell ref="V8:W8"/>
+    <mergeCell ref="V9:W9"/>
+    <mergeCell ref="AO8:AZ9"/>
+    <mergeCell ref="V6:W6"/>
+    <mergeCell ref="V7:W7"/>
+    <mergeCell ref="T9:U9"/>
+    <mergeCell ref="T10:U10"/>
+    <mergeCell ref="T8:U8"/>
+    <mergeCell ref="AO18:AZ19"/>
+    <mergeCell ref="T19:U19"/>
+    <mergeCell ref="X18:Y18"/>
+    <mergeCell ref="X19:Y19"/>
+    <mergeCell ref="Q18:S19"/>
+    <mergeCell ref="V22:W22"/>
+    <mergeCell ref="J22:P23"/>
+    <mergeCell ref="B12:B13"/>
+    <mergeCell ref="C12:I13"/>
+    <mergeCell ref="T12:U12"/>
+    <mergeCell ref="AO12:AZ13"/>
+    <mergeCell ref="T13:U13"/>
+    <mergeCell ref="X12:Y12"/>
+    <mergeCell ref="X13:Y13"/>
+    <mergeCell ref="V12:W12"/>
+    <mergeCell ref="B14:B15"/>
+    <mergeCell ref="C14:I15"/>
+    <mergeCell ref="T14:U14"/>
+    <mergeCell ref="AO14:AZ15"/>
+    <mergeCell ref="T15:U15"/>
+    <mergeCell ref="X14:Y14"/>
+    <mergeCell ref="X15:Y15"/>
+    <mergeCell ref="Q12:S13"/>
+    <mergeCell ref="Q14:S15"/>
     <mergeCell ref="V23:W23"/>
     <mergeCell ref="V18:W18"/>
     <mergeCell ref="V19:W19"/>
@@ -8291,74 +8338,27 @@
     <mergeCell ref="X23:Y23"/>
     <mergeCell ref="C18:I19"/>
     <mergeCell ref="T18:U18"/>
-    <mergeCell ref="AO18:AZ19"/>
-    <mergeCell ref="T19:U19"/>
-    <mergeCell ref="X18:Y18"/>
-    <mergeCell ref="X19:Y19"/>
-    <mergeCell ref="Q18:S19"/>
-    <mergeCell ref="V22:W22"/>
-    <mergeCell ref="J22:P23"/>
-    <mergeCell ref="B12:B13"/>
-    <mergeCell ref="C12:I13"/>
-    <mergeCell ref="T12:U12"/>
-    <mergeCell ref="AO12:AZ13"/>
-    <mergeCell ref="T13:U13"/>
-    <mergeCell ref="X12:Y12"/>
-    <mergeCell ref="X13:Y13"/>
-    <mergeCell ref="V12:W12"/>
-    <mergeCell ref="B14:B15"/>
-    <mergeCell ref="C14:I15"/>
-    <mergeCell ref="T14:U14"/>
-    <mergeCell ref="AO14:AZ15"/>
-    <mergeCell ref="T15:U15"/>
-    <mergeCell ref="X14:Y14"/>
-    <mergeCell ref="X15:Y15"/>
-    <mergeCell ref="Q12:S13"/>
-    <mergeCell ref="Q14:S15"/>
-    <mergeCell ref="AO10:AZ11"/>
-    <mergeCell ref="T11:U11"/>
-    <mergeCell ref="X9:Y9"/>
-    <mergeCell ref="X10:Y10"/>
-    <mergeCell ref="X11:Y11"/>
-    <mergeCell ref="V8:W8"/>
-    <mergeCell ref="V9:W9"/>
-    <mergeCell ref="AO8:AZ9"/>
-    <mergeCell ref="V6:W6"/>
-    <mergeCell ref="V7:W7"/>
-    <mergeCell ref="T9:U9"/>
-    <mergeCell ref="T10:U10"/>
-    <mergeCell ref="T8:U8"/>
-    <mergeCell ref="AO4:AZ5"/>
-    <mergeCell ref="AI4:AK4"/>
-    <mergeCell ref="AL4:AN4"/>
-    <mergeCell ref="AF4:AH4"/>
-    <mergeCell ref="X6:Y6"/>
-    <mergeCell ref="X7:Y7"/>
-    <mergeCell ref="X8:Y8"/>
-    <mergeCell ref="B2:I2"/>
-    <mergeCell ref="J2:AD2"/>
-    <mergeCell ref="X4:Y5"/>
-    <mergeCell ref="T4:W5"/>
-    <mergeCell ref="Z4:AB4"/>
-    <mergeCell ref="AC4:AE4"/>
-    <mergeCell ref="B4:I5"/>
-    <mergeCell ref="J4:P5"/>
-    <mergeCell ref="Q4:S5"/>
-    <mergeCell ref="AO6:AZ7"/>
-    <mergeCell ref="C6:I7"/>
-    <mergeCell ref="Q6:S7"/>
-    <mergeCell ref="J6:P7"/>
-    <mergeCell ref="B20:B21"/>
-    <mergeCell ref="C20:I21"/>
-    <mergeCell ref="J20:P21"/>
-    <mergeCell ref="Q20:S21"/>
-    <mergeCell ref="T20:U20"/>
-    <mergeCell ref="V20:W20"/>
-    <mergeCell ref="X20:Y20"/>
-    <mergeCell ref="AO20:AZ21"/>
-    <mergeCell ref="T21:U21"/>
-    <mergeCell ref="V21:W21"/>
-    <mergeCell ref="X21:Y21"/>
+    <mergeCell ref="B1:P1"/>
+    <mergeCell ref="J10:P11"/>
+    <mergeCell ref="J12:P13"/>
+    <mergeCell ref="J14:P15"/>
+    <mergeCell ref="J16:P17"/>
+    <mergeCell ref="V10:W10"/>
+    <mergeCell ref="V11:W11"/>
+    <mergeCell ref="V13:W13"/>
+    <mergeCell ref="V14:W14"/>
+    <mergeCell ref="V15:W15"/>
+    <mergeCell ref="V17:W17"/>
+    <mergeCell ref="B6:B7"/>
+    <mergeCell ref="T6:U6"/>
+    <mergeCell ref="T7:U7"/>
+    <mergeCell ref="B10:B11"/>
+    <mergeCell ref="C10:I11"/>
+    <mergeCell ref="Q8:S9"/>
+    <mergeCell ref="Q10:S11"/>
+    <mergeCell ref="B8:B9"/>
+    <mergeCell ref="C8:I9"/>
+    <mergeCell ref="J8:P9"/>
   </mergeCells>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.51200000000000001" footer="0.51200000000000001"/>
@@ -8382,610 +8382,609 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="48">
+      <c r="A1" s="47">
         <v>1</v>
       </c>
-      <c r="B1" s="55" t="s">
+      <c r="B1" s="51" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="55"/>
-      <c r="D1" s="55"/>
-      <c r="E1" s="57"/>
-      <c r="F1" s="57"/>
-      <c r="G1" s="57"/>
-      <c r="H1" s="57"/>
-      <c r="I1" s="57"/>
-      <c r="J1" s="58"/>
+      <c r="C1" s="51"/>
+      <c r="D1" s="51"/>
+      <c r="E1" s="94"/>
+      <c r="F1" s="94"/>
+      <c r="G1" s="94"/>
+      <c r="H1" s="94"/>
+      <c r="I1" s="94"/>
+      <c r="J1" s="95"/>
     </row>
     <row r="2" spans="1:10" ht="13.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="52"/>
-      <c r="B2" s="56"/>
-      <c r="C2" s="56"/>
-      <c r="D2" s="56"/>
-      <c r="E2" s="59"/>
-      <c r="F2" s="59"/>
-      <c r="G2" s="59"/>
-      <c r="H2" s="59"/>
-      <c r="I2" s="59"/>
-      <c r="J2" s="60"/>
+      <c r="A2" s="48"/>
+      <c r="B2" s="36"/>
+      <c r="C2" s="36"/>
+      <c r="D2" s="36"/>
+      <c r="E2" s="96"/>
+      <c r="F2" s="96"/>
+      <c r="G2" s="96"/>
+      <c r="H2" s="96"/>
+      <c r="I2" s="96"/>
+      <c r="J2" s="97"/>
     </row>
     <row r="3" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="48">
+      <c r="A3" s="47">
         <v>2</v>
       </c>
-      <c r="B3" s="55" t="s">
+      <c r="B3" s="51" t="s">
         <v>60</v>
       </c>
-      <c r="C3" s="55"/>
-      <c r="D3" s="55"/>
-      <c r="E3" s="55"/>
-      <c r="F3" s="55"/>
-      <c r="G3" s="55"/>
-      <c r="H3" s="55"/>
-      <c r="I3" s="55"/>
-      <c r="J3" s="87"/>
+      <c r="C3" s="51"/>
+      <c r="D3" s="51"/>
+      <c r="E3" s="51"/>
+      <c r="F3" s="51"/>
+      <c r="G3" s="51"/>
+      <c r="H3" s="51"/>
+      <c r="I3" s="51"/>
+      <c r="J3" s="52"/>
     </row>
     <row r="4" spans="1:10" ht="13.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A4" s="49"/>
-      <c r="B4" s="197" t="s">
+      <c r="B4" s="201" t="s">
         <v>61</v>
       </c>
-      <c r="C4" s="197"/>
-      <c r="D4" s="197"/>
-      <c r="E4" s="197"/>
-      <c r="F4" s="197"/>
-      <c r="G4" s="197"/>
-      <c r="H4" s="197"/>
-      <c r="I4" s="197"/>
-      <c r="J4" s="198"/>
+      <c r="C4" s="201"/>
+      <c r="D4" s="201"/>
+      <c r="E4" s="201"/>
+      <c r="F4" s="201"/>
+      <c r="G4" s="201"/>
+      <c r="H4" s="201"/>
+      <c r="I4" s="201"/>
+      <c r="J4" s="202"/>
     </row>
     <row r="5" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="48">
+      <c r="A5" s="47">
         <v>3</v>
       </c>
-      <c r="B5" s="55" t="s">
+      <c r="B5" s="51" t="s">
         <v>62</v>
       </c>
-      <c r="C5" s="55"/>
-      <c r="D5" s="55"/>
-      <c r="E5" s="55"/>
-      <c r="F5" s="55"/>
-      <c r="G5" s="55"/>
-      <c r="H5" s="55"/>
-      <c r="I5" s="55"/>
-      <c r="J5" s="87"/>
+      <c r="C5" s="51"/>
+      <c r="D5" s="51"/>
+      <c r="E5" s="51"/>
+      <c r="F5" s="51"/>
+      <c r="G5" s="51"/>
+      <c r="H5" s="51"/>
+      <c r="I5" s="51"/>
+      <c r="J5" s="52"/>
     </row>
     <row r="6" spans="1:10" ht="13.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="52"/>
-      <c r="B6" s="93" t="s">
+      <c r="A6" s="48"/>
+      <c r="B6" s="59" t="s">
         <v>16</v>
       </c>
-      <c r="C6" s="93"/>
-      <c r="D6" s="93"/>
-      <c r="E6" s="93"/>
-      <c r="F6" s="93"/>
-      <c r="G6" s="93"/>
-      <c r="H6" s="93"/>
-      <c r="I6" s="93"/>
-      <c r="J6" s="94"/>
+      <c r="C6" s="59"/>
+      <c r="D6" s="59"/>
+      <c r="E6" s="59"/>
+      <c r="F6" s="59"/>
+      <c r="G6" s="59"/>
+      <c r="H6" s="59"/>
+      <c r="I6" s="59"/>
+      <c r="J6" s="60"/>
     </row>
     <row r="7" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="48">
+      <c r="A7" s="47">
         <v>4</v>
       </c>
-      <c r="B7" s="55" t="s">
+      <c r="B7" s="51" t="s">
         <v>63</v>
       </c>
-      <c r="C7" s="55"/>
-      <c r="D7" s="55"/>
-      <c r="E7" s="55"/>
-      <c r="F7" s="55"/>
-      <c r="G7" s="55"/>
-      <c r="H7" s="55"/>
-      <c r="I7" s="55"/>
-      <c r="J7" s="87"/>
+      <c r="C7" s="51"/>
+      <c r="D7" s="51"/>
+      <c r="E7" s="51"/>
+      <c r="F7" s="51"/>
+      <c r="G7" s="51"/>
+      <c r="H7" s="51"/>
+      <c r="I7" s="51"/>
+      <c r="J7" s="52"/>
     </row>
     <row r="8" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="49"/>
-      <c r="B8" s="89" t="s">
+      <c r="B8" s="55" t="s">
         <v>64</v>
       </c>
-      <c r="C8" s="89"/>
-      <c r="D8" s="89"/>
-      <c r="E8" s="89"/>
-      <c r="F8" s="89"/>
-      <c r="G8" s="89"/>
-      <c r="H8" s="89"/>
-      <c r="I8" s="89"/>
-      <c r="J8" s="90"/>
+      <c r="C8" s="55"/>
+      <c r="D8" s="55"/>
+      <c r="E8" s="55"/>
+      <c r="F8" s="55"/>
+      <c r="G8" s="55"/>
+      <c r="H8" s="55"/>
+      <c r="I8" s="55"/>
+      <c r="J8" s="56"/>
     </row>
     <row r="9" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="49"/>
-      <c r="B9" s="44"/>
-      <c r="C9" s="44"/>
-      <c r="D9" s="44"/>
-      <c r="E9" s="44"/>
-      <c r="F9" s="44"/>
-      <c r="G9" s="44"/>
-      <c r="H9" s="44"/>
-      <c r="I9" s="44"/>
-      <c r="J9" s="65"/>
+      <c r="B9" s="53"/>
+      <c r="C9" s="53"/>
+      <c r="D9" s="53"/>
+      <c r="E9" s="53"/>
+      <c r="F9" s="53"/>
+      <c r="G9" s="53"/>
+      <c r="H9" s="53"/>
+      <c r="I9" s="53"/>
+      <c r="J9" s="54"/>
     </row>
     <row r="10" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="49"/>
-      <c r="B10" s="44"/>
-      <c r="C10" s="44"/>
-      <c r="D10" s="44"/>
-      <c r="E10" s="44"/>
-      <c r="F10" s="44"/>
-      <c r="G10" s="44"/>
-      <c r="H10" s="44"/>
-      <c r="I10" s="44"/>
-      <c r="J10" s="65"/>
+      <c r="B10" s="53"/>
+      <c r="C10" s="53"/>
+      <c r="D10" s="53"/>
+      <c r="E10" s="53"/>
+      <c r="F10" s="53"/>
+      <c r="G10" s="53"/>
+      <c r="H10" s="53"/>
+      <c r="I10" s="53"/>
+      <c r="J10" s="54"/>
     </row>
     <row r="11" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="49"/>
-      <c r="B11" s="44"/>
-      <c r="C11" s="44"/>
-      <c r="D11" s="44"/>
-      <c r="E11" s="44"/>
-      <c r="F11" s="44"/>
-      <c r="G11" s="44"/>
-      <c r="H11" s="44"/>
-      <c r="I11" s="44"/>
-      <c r="J11" s="65"/>
+      <c r="B11" s="53"/>
+      <c r="C11" s="53"/>
+      <c r="D11" s="53"/>
+      <c r="E11" s="53"/>
+      <c r="F11" s="53"/>
+      <c r="G11" s="53"/>
+      <c r="H11" s="53"/>
+      <c r="I11" s="53"/>
+      <c r="J11" s="54"/>
     </row>
     <row r="12" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="49"/>
-      <c r="B12" s="44"/>
-      <c r="C12" s="44"/>
-      <c r="D12" s="44"/>
-      <c r="E12" s="44"/>
-      <c r="F12" s="44"/>
-      <c r="G12" s="44"/>
-      <c r="H12" s="44"/>
-      <c r="I12" s="44"/>
-      <c r="J12" s="65"/>
+      <c r="B12" s="53"/>
+      <c r="C12" s="53"/>
+      <c r="D12" s="53"/>
+      <c r="E12" s="53"/>
+      <c r="F12" s="53"/>
+      <c r="G12" s="53"/>
+      <c r="H12" s="53"/>
+      <c r="I12" s="53"/>
+      <c r="J12" s="54"/>
     </row>
     <row r="13" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="49"/>
-      <c r="B13" s="44"/>
-      <c r="C13" s="44"/>
-      <c r="D13" s="44"/>
-      <c r="E13" s="44"/>
-      <c r="F13" s="44"/>
-      <c r="G13" s="44"/>
-      <c r="H13" s="44"/>
-      <c r="I13" s="44"/>
-      <c r="J13" s="65"/>
+      <c r="B13" s="53"/>
+      <c r="C13" s="53"/>
+      <c r="D13" s="53"/>
+      <c r="E13" s="53"/>
+      <c r="F13" s="53"/>
+      <c r="G13" s="53"/>
+      <c r="H13" s="53"/>
+      <c r="I13" s="53"/>
+      <c r="J13" s="54"/>
     </row>
     <row r="14" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="49"/>
-      <c r="B14" s="44"/>
-      <c r="C14" s="44"/>
-      <c r="D14" s="44"/>
-      <c r="E14" s="44"/>
-      <c r="F14" s="44"/>
-      <c r="G14" s="44"/>
-      <c r="H14" s="44"/>
-      <c r="I14" s="44"/>
-      <c r="J14" s="65"/>
+      <c r="B14" s="53"/>
+      <c r="C14" s="53"/>
+      <c r="D14" s="53"/>
+      <c r="E14" s="53"/>
+      <c r="F14" s="53"/>
+      <c r="G14" s="53"/>
+      <c r="H14" s="53"/>
+      <c r="I14" s="53"/>
+      <c r="J14" s="54"/>
     </row>
     <row r="15" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="49"/>
-      <c r="B15" s="89" t="s">
+      <c r="B15" s="55" t="s">
         <v>65</v>
       </c>
-      <c r="C15" s="89"/>
-      <c r="D15" s="89"/>
-      <c r="E15" s="89"/>
-      <c r="F15" s="89"/>
-      <c r="G15" s="89"/>
-      <c r="H15" s="89"/>
-      <c r="I15" s="89"/>
-      <c r="J15" s="90"/>
+      <c r="C15" s="55"/>
+      <c r="D15" s="55"/>
+      <c r="E15" s="55"/>
+      <c r="F15" s="55"/>
+      <c r="G15" s="55"/>
+      <c r="H15" s="55"/>
+      <c r="I15" s="55"/>
+      <c r="J15" s="56"/>
     </row>
     <row r="16" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="49"/>
-      <c r="B16" s="44"/>
-      <c r="C16" s="44"/>
-      <c r="D16" s="44"/>
-      <c r="E16" s="44"/>
-      <c r="F16" s="44"/>
-      <c r="G16" s="44"/>
-      <c r="H16" s="44"/>
-      <c r="I16" s="44"/>
-      <c r="J16" s="65"/>
+      <c r="B16" s="53"/>
+      <c r="C16" s="53"/>
+      <c r="D16" s="53"/>
+      <c r="E16" s="53"/>
+      <c r="F16" s="53"/>
+      <c r="G16" s="53"/>
+      <c r="H16" s="53"/>
+      <c r="I16" s="53"/>
+      <c r="J16" s="54"/>
     </row>
     <row r="17" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="49"/>
-      <c r="B17" s="44"/>
-      <c r="C17" s="44"/>
-      <c r="D17" s="44"/>
-      <c r="E17" s="44"/>
-      <c r="F17" s="44"/>
-      <c r="G17" s="44"/>
-      <c r="H17" s="44"/>
-      <c r="I17" s="44"/>
-      <c r="J17" s="65"/>
+      <c r="B17" s="53"/>
+      <c r="C17" s="53"/>
+      <c r="D17" s="53"/>
+      <c r="E17" s="53"/>
+      <c r="F17" s="53"/>
+      <c r="G17" s="53"/>
+      <c r="H17" s="53"/>
+      <c r="I17" s="53"/>
+      <c r="J17" s="54"/>
     </row>
     <row r="18" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="49"/>
-      <c r="B18" s="44"/>
-      <c r="C18" s="44"/>
-      <c r="D18" s="44"/>
-      <c r="E18" s="44"/>
-      <c r="F18" s="44"/>
-      <c r="G18" s="44"/>
-      <c r="H18" s="44"/>
-      <c r="I18" s="44"/>
-      <c r="J18" s="65"/>
+      <c r="B18" s="53"/>
+      <c r="C18" s="53"/>
+      <c r="D18" s="53"/>
+      <c r="E18" s="53"/>
+      <c r="F18" s="53"/>
+      <c r="G18" s="53"/>
+      <c r="H18" s="53"/>
+      <c r="I18" s="53"/>
+      <c r="J18" s="54"/>
     </row>
     <row r="19" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="49"/>
-      <c r="B19" s="44"/>
-      <c r="C19" s="44"/>
-      <c r="D19" s="44"/>
-      <c r="E19" s="44"/>
-      <c r="F19" s="44"/>
-      <c r="G19" s="44"/>
-      <c r="H19" s="44"/>
-      <c r="I19" s="44"/>
-      <c r="J19" s="65"/>
+      <c r="B19" s="53"/>
+      <c r="C19" s="53"/>
+      <c r="D19" s="53"/>
+      <c r="E19" s="53"/>
+      <c r="F19" s="53"/>
+      <c r="G19" s="53"/>
+      <c r="H19" s="53"/>
+      <c r="I19" s="53"/>
+      <c r="J19" s="54"/>
     </row>
     <row r="20" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="49"/>
-      <c r="B20" s="44"/>
-      <c r="C20" s="44"/>
-      <c r="D20" s="44"/>
-      <c r="E20" s="44"/>
-      <c r="F20" s="44"/>
-      <c r="G20" s="44"/>
-      <c r="H20" s="44"/>
-      <c r="I20" s="44"/>
-      <c r="J20" s="65"/>
+      <c r="B20" s="53"/>
+      <c r="C20" s="53"/>
+      <c r="D20" s="53"/>
+      <c r="E20" s="53"/>
+      <c r="F20" s="53"/>
+      <c r="G20" s="53"/>
+      <c r="H20" s="53"/>
+      <c r="I20" s="53"/>
+      <c r="J20" s="54"/>
     </row>
     <row r="21" spans="1:10" ht="13.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="52"/>
-      <c r="B21" s="59"/>
-      <c r="C21" s="59"/>
-      <c r="D21" s="59"/>
-      <c r="E21" s="59"/>
-      <c r="F21" s="59"/>
-      <c r="G21" s="59"/>
-      <c r="H21" s="59"/>
-      <c r="I21" s="59"/>
-      <c r="J21" s="60"/>
+      <c r="A21" s="48"/>
+      <c r="B21" s="96"/>
+      <c r="C21" s="96"/>
+      <c r="D21" s="96"/>
+      <c r="E21" s="96"/>
+      <c r="F21" s="96"/>
+      <c r="G21" s="96"/>
+      <c r="H21" s="96"/>
+      <c r="I21" s="96"/>
+      <c r="J21" s="97"/>
     </row>
     <row r="22" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A22" s="48">
+      <c r="A22" s="47">
         <v>5</v>
       </c>
-      <c r="B22" s="55" t="s">
+      <c r="B22" s="51" t="s">
         <v>66</v>
       </c>
-      <c r="C22" s="55"/>
-      <c r="D22" s="55"/>
-      <c r="E22" s="55"/>
-      <c r="F22" s="55"/>
-      <c r="G22" s="55"/>
-      <c r="H22" s="55"/>
-      <c r="I22" s="55"/>
-      <c r="J22" s="87"/>
+      <c r="C22" s="51"/>
+      <c r="D22" s="51"/>
+      <c r="E22" s="51"/>
+      <c r="F22" s="51"/>
+      <c r="G22" s="51"/>
+      <c r="H22" s="51"/>
+      <c r="I22" s="51"/>
+      <c r="J22" s="52"/>
     </row>
     <row r="23" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="49"/>
-      <c r="B23" s="44"/>
-      <c r="C23" s="44"/>
-      <c r="D23" s="44"/>
-      <c r="E23" s="44"/>
-      <c r="F23" s="44"/>
-      <c r="G23" s="44"/>
-      <c r="H23" s="44"/>
-      <c r="I23" s="44"/>
-      <c r="J23" s="65"/>
+      <c r="B23" s="53"/>
+      <c r="C23" s="53"/>
+      <c r="D23" s="53"/>
+      <c r="E23" s="53"/>
+      <c r="F23" s="53"/>
+      <c r="G23" s="53"/>
+      <c r="H23" s="53"/>
+      <c r="I23" s="53"/>
+      <c r="J23" s="54"/>
     </row>
     <row r="24" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" s="49"/>
-      <c r="B24" s="44"/>
-      <c r="C24" s="44"/>
-      <c r="D24" s="44"/>
-      <c r="E24" s="44"/>
-      <c r="F24" s="44"/>
-      <c r="G24" s="44"/>
-      <c r="H24" s="44"/>
-      <c r="I24" s="44"/>
-      <c r="J24" s="65"/>
+      <c r="B24" s="53"/>
+      <c r="C24" s="53"/>
+      <c r="D24" s="53"/>
+      <c r="E24" s="53"/>
+      <c r="F24" s="53"/>
+      <c r="G24" s="53"/>
+      <c r="H24" s="53"/>
+      <c r="I24" s="53"/>
+      <c r="J24" s="54"/>
     </row>
     <row r="25" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A25" s="49"/>
-      <c r="B25" s="44"/>
-      <c r="C25" s="44"/>
-      <c r="D25" s="44"/>
-      <c r="E25" s="44"/>
-      <c r="F25" s="44"/>
-      <c r="G25" s="44"/>
-      <c r="H25" s="44"/>
-      <c r="I25" s="44"/>
-      <c r="J25" s="65"/>
+      <c r="B25" s="53"/>
+      <c r="C25" s="53"/>
+      <c r="D25" s="53"/>
+      <c r="E25" s="53"/>
+      <c r="F25" s="53"/>
+      <c r="G25" s="53"/>
+      <c r="H25" s="53"/>
+      <c r="I25" s="53"/>
+      <c r="J25" s="54"/>
     </row>
     <row r="26" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26" s="49"/>
-      <c r="B26" s="44"/>
-      <c r="C26" s="44"/>
-      <c r="D26" s="44"/>
-      <c r="E26" s="44"/>
-      <c r="F26" s="44"/>
-      <c r="G26" s="44"/>
-      <c r="H26" s="44"/>
-      <c r="I26" s="44"/>
-      <c r="J26" s="65"/>
+      <c r="B26" s="53"/>
+      <c r="C26" s="53"/>
+      <c r="D26" s="53"/>
+      <c r="E26" s="53"/>
+      <c r="F26" s="53"/>
+      <c r="G26" s="53"/>
+      <c r="H26" s="53"/>
+      <c r="I26" s="53"/>
+      <c r="J26" s="54"/>
     </row>
     <row r="27" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A27" s="49"/>
-      <c r="B27" s="44"/>
-      <c r="C27" s="44"/>
-      <c r="D27" s="44"/>
-      <c r="E27" s="44"/>
-      <c r="F27" s="44"/>
-      <c r="G27" s="44"/>
-      <c r="H27" s="44"/>
-      <c r="I27" s="44"/>
-      <c r="J27" s="65"/>
+      <c r="B27" s="53"/>
+      <c r="C27" s="53"/>
+      <c r="D27" s="53"/>
+      <c r="E27" s="53"/>
+      <c r="F27" s="53"/>
+      <c r="G27" s="53"/>
+      <c r="H27" s="53"/>
+      <c r="I27" s="53"/>
+      <c r="J27" s="54"/>
     </row>
     <row r="28" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A28" s="49"/>
-      <c r="B28" s="44"/>
-      <c r="C28" s="44"/>
-      <c r="D28" s="44"/>
-      <c r="E28" s="44"/>
-      <c r="F28" s="44"/>
-      <c r="G28" s="44"/>
-      <c r="H28" s="44"/>
-      <c r="I28" s="44"/>
-      <c r="J28" s="65"/>
+      <c r="B28" s="53"/>
+      <c r="C28" s="53"/>
+      <c r="D28" s="53"/>
+      <c r="E28" s="53"/>
+      <c r="F28" s="53"/>
+      <c r="G28" s="53"/>
+      <c r="H28" s="53"/>
+      <c r="I28" s="53"/>
+      <c r="J28" s="54"/>
     </row>
     <row r="29" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A29" s="49"/>
-      <c r="B29" s="44"/>
-      <c r="C29" s="44"/>
-      <c r="D29" s="44"/>
-      <c r="E29" s="44"/>
-      <c r="F29" s="44"/>
-      <c r="G29" s="44"/>
-      <c r="H29" s="44"/>
-      <c r="I29" s="44"/>
-      <c r="J29" s="65"/>
+      <c r="B29" s="53"/>
+      <c r="C29" s="53"/>
+      <c r="D29" s="53"/>
+      <c r="E29" s="53"/>
+      <c r="F29" s="53"/>
+      <c r="G29" s="53"/>
+      <c r="H29" s="53"/>
+      <c r="I29" s="53"/>
+      <c r="J29" s="54"/>
     </row>
     <row r="30" spans="1:10" ht="13.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="52"/>
-      <c r="B30" s="59"/>
-      <c r="C30" s="59"/>
-      <c r="D30" s="59"/>
-      <c r="E30" s="59"/>
-      <c r="F30" s="59"/>
-      <c r="G30" s="59"/>
-      <c r="H30" s="59"/>
-      <c r="I30" s="59"/>
-      <c r="J30" s="60"/>
+      <c r="A30" s="48"/>
+      <c r="B30" s="96"/>
+      <c r="C30" s="96"/>
+      <c r="D30" s="96"/>
+      <c r="E30" s="96"/>
+      <c r="F30" s="96"/>
+      <c r="G30" s="96"/>
+      <c r="H30" s="96"/>
+      <c r="I30" s="96"/>
+      <c r="J30" s="97"/>
     </row>
     <row r="31" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A31" s="48">
+      <c r="A31" s="47">
         <v>6</v>
       </c>
-      <c r="B31" s="55" t="s">
+      <c r="B31" s="51" t="s">
         <v>67</v>
       </c>
-      <c r="C31" s="55"/>
-      <c r="D31" s="55"/>
-      <c r="E31" s="55"/>
-      <c r="F31" s="55"/>
-      <c r="G31" s="55"/>
-      <c r="H31" s="55"/>
-      <c r="I31" s="55"/>
-      <c r="J31" s="87"/>
+      <c r="C31" s="51"/>
+      <c r="D31" s="51"/>
+      <c r="E31" s="51"/>
+      <c r="F31" s="51"/>
+      <c r="G31" s="51"/>
+      <c r="H31" s="51"/>
+      <c r="I31" s="51"/>
+      <c r="J31" s="52"/>
     </row>
     <row r="32" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A32" s="49"/>
-      <c r="B32" s="44"/>
-      <c r="C32" s="44"/>
-      <c r="D32" s="44"/>
-      <c r="E32" s="44"/>
-      <c r="F32" s="44"/>
-      <c r="G32" s="44"/>
-      <c r="H32" s="44"/>
-      <c r="I32" s="44"/>
-      <c r="J32" s="65"/>
+      <c r="B32" s="53"/>
+      <c r="C32" s="53"/>
+      <c r="D32" s="53"/>
+      <c r="E32" s="53"/>
+      <c r="F32" s="53"/>
+      <c r="G32" s="53"/>
+      <c r="H32" s="53"/>
+      <c r="I32" s="53"/>
+      <c r="J32" s="54"/>
     </row>
     <row r="33" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A33" s="49"/>
-      <c r="B33" s="44"/>
-      <c r="C33" s="44"/>
-      <c r="D33" s="44"/>
-      <c r="E33" s="44"/>
-      <c r="F33" s="44"/>
-      <c r="G33" s="44"/>
-      <c r="H33" s="44"/>
-      <c r="I33" s="44"/>
-      <c r="J33" s="65"/>
+      <c r="B33" s="53"/>
+      <c r="C33" s="53"/>
+      <c r="D33" s="53"/>
+      <c r="E33" s="53"/>
+      <c r="F33" s="53"/>
+      <c r="G33" s="53"/>
+      <c r="H33" s="53"/>
+      <c r="I33" s="53"/>
+      <c r="J33" s="54"/>
     </row>
     <row r="34" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A34" s="49"/>
-      <c r="B34" s="44"/>
-      <c r="C34" s="44"/>
-      <c r="D34" s="44"/>
-      <c r="E34" s="44"/>
-      <c r="F34" s="44"/>
-      <c r="G34" s="44"/>
-      <c r="H34" s="44"/>
-      <c r="I34" s="44"/>
-      <c r="J34" s="65"/>
+      <c r="B34" s="53"/>
+      <c r="C34" s="53"/>
+      <c r="D34" s="53"/>
+      <c r="E34" s="53"/>
+      <c r="F34" s="53"/>
+      <c r="G34" s="53"/>
+      <c r="H34" s="53"/>
+      <c r="I34" s="53"/>
+      <c r="J34" s="54"/>
     </row>
     <row r="35" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A35" s="49"/>
-      <c r="B35" s="44"/>
-      <c r="C35" s="44"/>
-      <c r="D35" s="44"/>
-      <c r="E35" s="44"/>
-      <c r="F35" s="44"/>
-      <c r="G35" s="44"/>
-      <c r="H35" s="44"/>
-      <c r="I35" s="44"/>
-      <c r="J35" s="65"/>
+      <c r="B35" s="53"/>
+      <c r="C35" s="53"/>
+      <c r="D35" s="53"/>
+      <c r="E35" s="53"/>
+      <c r="F35" s="53"/>
+      <c r="G35" s="53"/>
+      <c r="H35" s="53"/>
+      <c r="I35" s="53"/>
+      <c r="J35" s="54"/>
     </row>
     <row r="36" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A36" s="49"/>
-      <c r="B36" s="44"/>
-      <c r="C36" s="44"/>
-      <c r="D36" s="44"/>
-      <c r="E36" s="44"/>
-      <c r="F36" s="44"/>
-      <c r="G36" s="44"/>
-      <c r="H36" s="44"/>
-      <c r="I36" s="44"/>
-      <c r="J36" s="65"/>
+      <c r="B36" s="53"/>
+      <c r="C36" s="53"/>
+      <c r="D36" s="53"/>
+      <c r="E36" s="53"/>
+      <c r="F36" s="53"/>
+      <c r="G36" s="53"/>
+      <c r="H36" s="53"/>
+      <c r="I36" s="53"/>
+      <c r="J36" s="54"/>
     </row>
     <row r="37" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A37" s="49"/>
-      <c r="B37" s="44"/>
-      <c r="C37" s="44"/>
-      <c r="D37" s="44"/>
-      <c r="E37" s="44"/>
-      <c r="F37" s="44"/>
-      <c r="G37" s="44"/>
-      <c r="H37" s="44"/>
-      <c r="I37" s="44"/>
-      <c r="J37" s="65"/>
+      <c r="B37" s="53"/>
+      <c r="C37" s="53"/>
+      <c r="D37" s="53"/>
+      <c r="E37" s="53"/>
+      <c r="F37" s="53"/>
+      <c r="G37" s="53"/>
+      <c r="H37" s="53"/>
+      <c r="I37" s="53"/>
+      <c r="J37" s="54"/>
     </row>
     <row r="38" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A38" s="49"/>
-      <c r="B38" s="44"/>
-      <c r="C38" s="44"/>
-      <c r="D38" s="44"/>
-      <c r="E38" s="44"/>
-      <c r="F38" s="44"/>
-      <c r="G38" s="44"/>
-      <c r="H38" s="44"/>
-      <c r="I38" s="44"/>
-      <c r="J38" s="65"/>
+      <c r="B38" s="53"/>
+      <c r="C38" s="53"/>
+      <c r="D38" s="53"/>
+      <c r="E38" s="53"/>
+      <c r="F38" s="53"/>
+      <c r="G38" s="53"/>
+      <c r="H38" s="53"/>
+      <c r="I38" s="53"/>
+      <c r="J38" s="54"/>
     </row>
     <row r="39" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A39" s="49"/>
-      <c r="B39" s="44"/>
-      <c r="C39" s="44"/>
-      <c r="D39" s="44"/>
-      <c r="E39" s="44"/>
-      <c r="F39" s="44"/>
-      <c r="G39" s="44"/>
-      <c r="H39" s="44"/>
-      <c r="I39" s="44"/>
-      <c r="J39" s="65"/>
+      <c r="B39" s="53"/>
+      <c r="C39" s="53"/>
+      <c r="D39" s="53"/>
+      <c r="E39" s="53"/>
+      <c r="F39" s="53"/>
+      <c r="G39" s="53"/>
+      <c r="H39" s="53"/>
+      <c r="I39" s="53"/>
+      <c r="J39" s="54"/>
     </row>
     <row r="40" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A40" s="49"/>
-      <c r="B40" s="44"/>
-      <c r="C40" s="44"/>
-      <c r="D40" s="44"/>
-      <c r="E40" s="44"/>
-      <c r="F40" s="44"/>
-      <c r="G40" s="44"/>
-      <c r="H40" s="44"/>
-      <c r="I40" s="44"/>
-      <c r="J40" s="65"/>
+      <c r="B40" s="53"/>
+      <c r="C40" s="53"/>
+      <c r="D40" s="53"/>
+      <c r="E40" s="53"/>
+      <c r="F40" s="53"/>
+      <c r="G40" s="53"/>
+      <c r="H40" s="53"/>
+      <c r="I40" s="53"/>
+      <c r="J40" s="54"/>
     </row>
     <row r="41" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A41" s="49"/>
-      <c r="B41" s="44"/>
-      <c r="C41" s="44"/>
-      <c r="D41" s="44"/>
-      <c r="E41" s="44"/>
-      <c r="F41" s="44"/>
-      <c r="G41" s="44"/>
-      <c r="H41" s="44"/>
-      <c r="I41" s="44"/>
-      <c r="J41" s="65"/>
+      <c r="B41" s="53"/>
+      <c r="C41" s="53"/>
+      <c r="D41" s="53"/>
+      <c r="E41" s="53"/>
+      <c r="F41" s="53"/>
+      <c r="G41" s="53"/>
+      <c r="H41" s="53"/>
+      <c r="I41" s="53"/>
+      <c r="J41" s="54"/>
     </row>
     <row r="42" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A42" s="49"/>
-      <c r="B42" s="44"/>
-      <c r="C42" s="44"/>
-      <c r="D42" s="44"/>
-      <c r="E42" s="44"/>
-      <c r="F42" s="44"/>
-      <c r="G42" s="44"/>
-      <c r="H42" s="44"/>
-      <c r="I42" s="44"/>
-      <c r="J42" s="65"/>
+      <c r="B42" s="53"/>
+      <c r="C42" s="53"/>
+      <c r="D42" s="53"/>
+      <c r="E42" s="53"/>
+      <c r="F42" s="53"/>
+      <c r="G42" s="53"/>
+      <c r="H42" s="53"/>
+      <c r="I42" s="53"/>
+      <c r="J42" s="54"/>
     </row>
     <row r="43" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A43" s="49"/>
-      <c r="B43" s="44"/>
-      <c r="C43" s="44"/>
-      <c r="D43" s="44"/>
-      <c r="E43" s="44"/>
-      <c r="F43" s="44"/>
-      <c r="G43" s="44"/>
-      <c r="H43" s="44"/>
-      <c r="I43" s="44"/>
-      <c r="J43" s="65"/>
+      <c r="B43" s="53"/>
+      <c r="C43" s="53"/>
+      <c r="D43" s="53"/>
+      <c r="E43" s="53"/>
+      <c r="F43" s="53"/>
+      <c r="G43" s="53"/>
+      <c r="H43" s="53"/>
+      <c r="I43" s="53"/>
+      <c r="J43" s="54"/>
     </row>
     <row r="44" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A44" s="49"/>
-      <c r="B44" s="44"/>
-      <c r="C44" s="44"/>
-      <c r="D44" s="44"/>
-      <c r="E44" s="44"/>
-      <c r="F44" s="44"/>
-      <c r="G44" s="44"/>
-      <c r="H44" s="44"/>
-      <c r="I44" s="44"/>
-      <c r="J44" s="65"/>
+      <c r="B44" s="53"/>
+      <c r="C44" s="53"/>
+      <c r="D44" s="53"/>
+      <c r="E44" s="53"/>
+      <c r="F44" s="53"/>
+      <c r="G44" s="53"/>
+      <c r="H44" s="53"/>
+      <c r="I44" s="53"/>
+      <c r="J44" s="54"/>
     </row>
     <row r="45" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A45" s="49"/>
-      <c r="B45" s="44"/>
-      <c r="C45" s="44"/>
-      <c r="D45" s="44"/>
-      <c r="E45" s="44"/>
-      <c r="F45" s="44"/>
-      <c r="G45" s="44"/>
-      <c r="H45" s="44"/>
-      <c r="I45" s="44"/>
-      <c r="J45" s="65"/>
+      <c r="B45" s="53"/>
+      <c r="C45" s="53"/>
+      <c r="D45" s="53"/>
+      <c r="E45" s="53"/>
+      <c r="F45" s="53"/>
+      <c r="G45" s="53"/>
+      <c r="H45" s="53"/>
+      <c r="I45" s="53"/>
+      <c r="J45" s="54"/>
     </row>
     <row r="46" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A46" s="49"/>
-      <c r="B46" s="44"/>
-      <c r="C46" s="44"/>
-      <c r="D46" s="44"/>
-      <c r="E46" s="44"/>
-      <c r="F46" s="44"/>
-      <c r="G46" s="44"/>
-      <c r="H46" s="44"/>
-      <c r="I46" s="44"/>
-      <c r="J46" s="65"/>
+      <c r="B46" s="53"/>
+      <c r="C46" s="53"/>
+      <c r="D46" s="53"/>
+      <c r="E46" s="53"/>
+      <c r="F46" s="53"/>
+      <c r="G46" s="53"/>
+      <c r="H46" s="53"/>
+      <c r="I46" s="53"/>
+      <c r="J46" s="54"/>
     </row>
     <row r="47" spans="1:10" ht="13.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A47" s="50"/>
-      <c r="B47" s="91"/>
-      <c r="C47" s="91"/>
-      <c r="D47" s="91"/>
-      <c r="E47" s="91"/>
-      <c r="F47" s="91"/>
-      <c r="G47" s="91"/>
-      <c r="H47" s="91"/>
-      <c r="I47" s="91"/>
-      <c r="J47" s="92"/>
+      <c r="B47" s="57"/>
+      <c r="C47" s="57"/>
+      <c r="D47" s="57"/>
+      <c r="E47" s="57"/>
+      <c r="F47" s="57"/>
+      <c r="G47" s="57"/>
+      <c r="H47" s="57"/>
+      <c r="I47" s="57"/>
+      <c r="J47" s="58"/>
     </row>
   </sheetData>
   <mergeCells count="21">
-    <mergeCell ref="B32:J47"/>
-    <mergeCell ref="A31:A47"/>
-    <mergeCell ref="B16:J21"/>
-    <mergeCell ref="A22:A30"/>
-    <mergeCell ref="B23:J30"/>
-    <mergeCell ref="B22:J22"/>
-    <mergeCell ref="B31:J31"/>
+    <mergeCell ref="B3:J3"/>
+    <mergeCell ref="B4:J4"/>
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="B1:D2"/>
+    <mergeCell ref="E1:J2"/>
+    <mergeCell ref="A3:A4"/>
     <mergeCell ref="B15:J15"/>
     <mergeCell ref="B8:J8"/>
     <mergeCell ref="A5:A6"/>
@@ -8994,12 +8993,13 @@
     <mergeCell ref="B7:J7"/>
     <mergeCell ref="B9:J14"/>
     <mergeCell ref="A7:A21"/>
-    <mergeCell ref="B3:J3"/>
-    <mergeCell ref="B4:J4"/>
-    <mergeCell ref="A1:A2"/>
-    <mergeCell ref="B1:D2"/>
-    <mergeCell ref="E1:J2"/>
-    <mergeCell ref="A3:A4"/>
+    <mergeCell ref="B32:J47"/>
+    <mergeCell ref="A31:A47"/>
+    <mergeCell ref="B16:J21"/>
+    <mergeCell ref="A22:A30"/>
+    <mergeCell ref="B23:J30"/>
+    <mergeCell ref="B22:J22"/>
+    <mergeCell ref="B31:J31"/>
   </mergeCells>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.51200000000000001" footer="0.51200000000000001"/>
@@ -9021,6 +9021,17 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="88cc3c26-756f-41ab-80ed-43e7289fee5b">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="55239288-d498-4dd6-9609-491b39ec8fae" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="ドキュメント" ma:contentTypeID="0x01010058BEBA3CD4E69545839402B5D4E5400B" ma:contentTypeVersion="13" ma:contentTypeDescription="新しいドキュメントを作成します。" ma:contentTypeScope="" ma:versionID="85fadafb228503a8e253560e9cdffc69">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="88cc3c26-756f-41ab-80ed-43e7289fee5b" xmlns:ns3="55239288-d498-4dd6-9609-491b39ec8fae" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="9785dde68d2e35ac7b66dd15e8e44124" ns2:_="" ns3:_="">
     <xsd:import namespace="88cc3c26-756f-41ab-80ed-43e7289fee5b"/>
@@ -9227,17 +9238,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="88cc3c26-756f-41ab-80ed-43e7289fee5b">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="55239288-d498-4dd6-9609-491b39ec8fae" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0843C284-C2B9-4564-B59A-F2FA129FE5C7}">
   <ds:schemaRefs>
@@ -9247,6 +9247,25 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{82E555AC-3D9C-4ECE-9578-D2E452F320B7}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="4707ffff-3746-4042-a13f-bfbbbbe730e0"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="96e9746f-acab-410f-8363-815e1ac6f97e"/>
+    <ds:schemaRef ds:uri="88cc3c26-756f-41ab-80ed-43e7289fee5b"/>
+    <ds:schemaRef ds:uri="55239288-d498-4dd6-9609-491b39ec8fae"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{18D765C5-969E-4095-9A45-9E80C6C2EDED}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -9263,23 +9282,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{82E555AC-3D9C-4ECE-9578-D2E452F320B7}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="4707ffff-3746-4042-a13f-bfbbbbe730e0"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="96e9746f-acab-410f-8363-815e1ac6f97e"/>
-    <ds:schemaRef ds:uri="88cc3c26-756f-41ab-80ed-43e7289fee5b"/>
-    <ds:schemaRef ds:uri="55239288-d498-4dd6-9609-491b39ec8fae"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>